--- a/data/prod_parameters/FeedMgmt.xlsx
+++ b/data/prod_parameters/FeedMgmt.xlsx
@@ -145,7 +145,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -173,6 +173,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -216,7 +223,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -227,6 +234,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -681,13 +689,14 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="I9" t="s">
+      <c r="I9" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="10">
         <v>0</v>
       </c>
-      <c r="L9" t="s">
+      <c r="K9" s="10"/>
+      <c r="L9" s="10" t="s">
         <v>39</v>
       </c>
     </row>
@@ -765,13 +774,14 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="I15" s="3" t="s">
+      <c r="I15" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="J15" s="3">
+      <c r="J15" s="10">
         <v>0</v>
       </c>
-      <c r="L15" s="3" t="s">
+      <c r="K15" s="10"/>
+      <c r="L15" s="10" t="s">
         <v>39</v>
       </c>
     </row>
@@ -821,13 +831,14 @@
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="I19" s="3" t="s">
+      <c r="I19" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="J19" s="3">
+      <c r="J19" s="10">
         <v>0</v>
       </c>
-      <c r="L19" s="3" t="s">
+      <c r="K19" s="10"/>
+      <c r="L19" s="10" t="s">
         <v>39</v>
       </c>
     </row>

--- a/data/prod_parameters/FeedMgmt.xlsx
+++ b/data/prod_parameters/FeedMgmt.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="460">
   <si>
     <t>f_feed</t>
   </si>
@@ -1402,9 +1402,6 @@
   </si>
   <si>
     <t>include as crop??</t>
-  </si>
-  <si>
-    <t>until incl. as crop</t>
   </si>
 </sst>
 </file>
@@ -1863,7 +1860,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N106"/>
+  <dimension ref="A1:N99"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="20.28515625" customWidth="1"/>
@@ -2510,128 +2507,176 @@
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="G42" t="s">
-        <v>43</v>
-      </c>
-      <c r="I42" t="s">
-        <v>35</v>
-      </c>
-      <c r="J42" s="3">
-        <v>100</v>
-      </c>
-      <c r="K42" t="s">
-        <v>32</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>460</v>
-      </c>
+      <c r="J42" s="3"/>
+      <c r="L42" s="3"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="G43" t="s">
-        <v>45</v>
-      </c>
-      <c r="I43" t="s">
-        <v>35</v>
-      </c>
-      <c r="J43" s="3">
-        <v>100</v>
-      </c>
-      <c r="K43" t="s">
-        <v>32</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>460</v>
-      </c>
+      <c r="A43" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="M43" s="2"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="G44" t="s">
-        <v>46</v>
-      </c>
-      <c r="I44" t="s">
-        <v>35</v>
-      </c>
-      <c r="J44" s="3">
-        <v>100</v>
-      </c>
-      <c r="K44" t="s">
-        <v>32</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>460</v>
-      </c>
+      <c r="A44" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B44" s="7"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="6"/>
+      <c r="K44" s="6"/>
+      <c r="L44" s="6"/>
+      <c r="M44" s="6"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="G45" t="s">
-        <v>39</v>
+      <c r="A45" t="s">
+        <v>28</v>
+      </c>
+      <c r="F45" t="s">
+        <v>19</v>
       </c>
       <c r="I45" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="J45" s="3">
-        <v>100</v>
+        <v>12.4</v>
       </c>
       <c r="K45" t="s">
-        <v>32</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>460</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="J46" s="3"/>
-      <c r="L46" s="3"/>
+      <c r="A46" t="s">
+        <v>28</v>
+      </c>
+      <c r="B46" t="s">
+        <v>22</v>
+      </c>
+      <c r="E46" t="s">
+        <v>23</v>
+      </c>
+      <c r="F46" t="s">
+        <v>2</v>
+      </c>
+      <c r="I46" t="s">
+        <v>20</v>
+      </c>
+      <c r="J46" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="K46" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="J47" s="3"/>
-      <c r="L47" s="3"/>
+      <c r="A47" t="s">
+        <v>28</v>
+      </c>
+      <c r="F47" t="s">
+        <v>2</v>
+      </c>
+      <c r="I47" t="s">
+        <v>20</v>
+      </c>
+      <c r="J47" s="3">
+        <v>11</v>
+      </c>
+      <c r="K47" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="J48" s="3"/>
-      <c r="L48" s="3"/>
+      <c r="A48" t="s">
+        <v>28</v>
+      </c>
+      <c r="F48" t="s">
+        <v>13</v>
+      </c>
+      <c r="I48" t="s">
+        <v>20</v>
+      </c>
+      <c r="J48" s="3">
+        <v>13</v>
+      </c>
+      <c r="K48" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="J49" s="3"/>
-      <c r="L49" s="3"/>
+      <c r="A49" t="s">
+        <v>28</v>
+      </c>
+      <c r="F49" t="s">
+        <v>37</v>
+      </c>
+      <c r="I49" t="s">
+        <v>20</v>
+      </c>
+      <c r="J49" s="3">
+        <v>10</v>
+      </c>
+      <c r="K49" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
-      <c r="K50" s="2"/>
-      <c r="L50" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="M50" s="2"/>
+      <c r="A50" t="s">
+        <v>28</v>
+      </c>
+      <c r="F50" t="s">
+        <v>15</v>
+      </c>
+      <c r="I50" t="s">
+        <v>20</v>
+      </c>
+      <c r="J50" s="3">
+        <v>15</v>
+      </c>
+      <c r="K50" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A51" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B51" s="7"/>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="6"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="6"/>
-      <c r="J51" s="6"/>
-      <c r="K51" s="6"/>
-      <c r="L51" s="6"/>
-      <c r="M51" s="6"/>
+      <c r="A51" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B51" s="8"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="9"/>
+      <c r="F51" s="9"/>
+      <c r="G51" s="9"/>
+      <c r="H51" s="9"/>
+      <c r="I51" s="9"/>
+      <c r="J51" s="9"/>
+      <c r="K51" s="9"/>
+      <c r="L51" s="9"/>
+      <c r="M51" s="9"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="E52" t="s">
+        <v>454</v>
       </c>
       <c r="F52" t="s">
         <v>19</v>
@@ -2639,120 +2684,139 @@
       <c r="I52" t="s">
         <v>20</v>
       </c>
-      <c r="J52" s="3">
-        <v>12.4</v>
+      <c r="J52" s="23">
+        <f>'feed pars'!F6</f>
+        <v>12.3</v>
       </c>
       <c r="K52" t="s">
-        <v>21</v>
+        <v>455</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>28</v>
-      </c>
-      <c r="B53" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E53" t="s">
-        <v>23</v>
+        <v>454</v>
       </c>
       <c r="F53" t="s">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="I53" t="s">
         <v>20</v>
       </c>
-      <c r="J53" s="3">
-        <v>12.5</v>
+      <c r="J53" s="23">
+        <f>'feed pars'!F7</f>
+        <v>11.2</v>
       </c>
       <c r="K53" t="s">
-        <v>21</v>
+        <v>455</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="E54" t="s">
+        <v>454</v>
       </c>
       <c r="F54" t="s">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="I54" t="s">
         <v>20</v>
       </c>
-      <c r="J54" s="3">
-        <v>11</v>
+      <c r="J54" s="23">
+        <f>'feed pars'!F8</f>
+        <v>9.4</v>
       </c>
       <c r="K54" t="s">
-        <v>21</v>
+        <v>455</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="E55" t="s">
+        <v>454</v>
       </c>
       <c r="F55" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="I55" t="s">
         <v>20</v>
       </c>
-      <c r="J55" s="3">
-        <v>13</v>
+      <c r="J55" s="23">
+        <f>'feed pars'!F9</f>
+        <v>12</v>
       </c>
       <c r="K55" t="s">
-        <v>21</v>
+        <v>455</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="E56" t="s">
+        <v>454</v>
       </c>
       <c r="F56" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I56" t="s">
         <v>20</v>
       </c>
-      <c r="J56" s="3">
-        <v>10</v>
+      <c r="J56" s="23">
+        <f>'feed pars'!F10</f>
+        <v>13.2</v>
       </c>
       <c r="K56" t="s">
-        <v>21</v>
+        <v>455</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="E57" t="s">
+        <v>454</v>
       </c>
       <c r="F57" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="I57" t="s">
         <v>20</v>
       </c>
-      <c r="J57" s="3">
-        <v>15</v>
+      <c r="J57" s="23">
+        <f>'feed pars'!F11</f>
+        <v>11.5</v>
       </c>
       <c r="K57" t="s">
-        <v>21</v>
+        <v>455</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A58" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B58" s="8"/>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="9"/>
-      <c r="H58" s="9"/>
-      <c r="I58" s="9"/>
-      <c r="J58" s="9"/>
-      <c r="K58" s="9"/>
-      <c r="L58" s="9"/>
-      <c r="M58" s="9"/>
+      <c r="A58" t="s">
+        <v>29</v>
+      </c>
+      <c r="E58" t="s">
+        <v>454</v>
+      </c>
+      <c r="F58" t="s">
+        <v>46</v>
+      </c>
+      <c r="I58" t="s">
+        <v>20</v>
+      </c>
+      <c r="J58" s="23">
+        <f>'feed pars'!F12</f>
+        <v>10.9</v>
+      </c>
+      <c r="K58" t="s">
+        <v>455</v>
+      </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
@@ -2762,14 +2826,14 @@
         <v>454</v>
       </c>
       <c r="F59" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="I59" t="s">
         <v>20</v>
       </c>
       <c r="J59" s="23">
-        <f>'feed pars'!F6</f>
-        <v>12.3</v>
+        <f>'feed pars'!F13</f>
+        <v>18.5</v>
       </c>
       <c r="K59" t="s">
         <v>455</v>
@@ -2783,14 +2847,14 @@
         <v>454</v>
       </c>
       <c r="F60" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I60" t="s">
         <v>20</v>
       </c>
       <c r="J60" s="23">
-        <f>'feed pars'!F7</f>
-        <v>11.2</v>
+        <f>'feed pars'!F14</f>
+        <v>17.5</v>
       </c>
       <c r="K60" t="s">
         <v>455</v>
@@ -2804,14 +2868,14 @@
         <v>454</v>
       </c>
       <c r="F61" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I61" t="s">
         <v>20</v>
       </c>
       <c r="J61" s="23">
-        <f>'feed pars'!F8</f>
-        <v>9.4</v>
+        <f>'feed pars'!F15</f>
+        <v>9.9</v>
       </c>
       <c r="K61" t="s">
         <v>455</v>
@@ -2825,14 +2889,14 @@
         <v>454</v>
       </c>
       <c r="F62" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I62" t="s">
         <v>20</v>
       </c>
       <c r="J62" s="23">
-        <f>'feed pars'!F9</f>
-        <v>12</v>
+        <f>'feed pars'!F16</f>
+        <v>10.3</v>
       </c>
       <c r="K62" t="s">
         <v>455</v>
@@ -2846,14 +2910,14 @@
         <v>454</v>
       </c>
       <c r="F63" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I63" t="s">
         <v>20</v>
       </c>
       <c r="J63" s="23">
-        <f>'feed pars'!F10</f>
-        <v>13.2</v>
+        <f>'feed pars'!F17</f>
+        <v>7.7</v>
       </c>
       <c r="K63" t="s">
         <v>455</v>
@@ -2867,14 +2931,14 @@
         <v>454</v>
       </c>
       <c r="F64" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="I64" t="s">
         <v>20</v>
       </c>
       <c r="J64" s="23">
-        <f>'feed pars'!F11</f>
-        <v>11.5</v>
+        <f>'feed pars'!F18</f>
+        <v>6.5</v>
       </c>
       <c r="K64" t="s">
         <v>455</v>
@@ -2888,14 +2952,14 @@
         <v>454</v>
       </c>
       <c r="F65" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="I65" t="s">
         <v>20</v>
       </c>
       <c r="J65" s="23">
-        <f>'feed pars'!F12</f>
-        <v>10.9</v>
+        <f>'feed pars'!F19</f>
+        <v>6.2</v>
       </c>
       <c r="K65" t="s">
         <v>455</v>
@@ -2909,14 +2973,14 @@
         <v>454</v>
       </c>
       <c r="F66" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="I66" t="s">
         <v>20</v>
       </c>
       <c r="J66" s="23">
-        <f>'feed pars'!F13</f>
-        <v>18.5</v>
+        <f>'feed pars'!F20</f>
+        <v>7.8</v>
       </c>
       <c r="K66" t="s">
         <v>455</v>
@@ -2930,14 +2994,14 @@
         <v>454</v>
       </c>
       <c r="F67" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="I67" t="s">
         <v>20</v>
       </c>
       <c r="J67" s="23">
-        <f>'feed pars'!F14</f>
-        <v>17.5</v>
+        <f>'feed pars'!F21</f>
+        <v>9.1999999999999993</v>
       </c>
       <c r="K67" t="s">
         <v>455</v>
@@ -2951,14 +3015,14 @@
         <v>454</v>
       </c>
       <c r="F68" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I68" t="s">
         <v>20</v>
       </c>
       <c r="J68" s="23">
-        <f>'feed pars'!F15</f>
-        <v>9.9</v>
+        <f>'feed pars'!F22</f>
+        <v>8.6999999999999993</v>
       </c>
       <c r="K68" t="s">
         <v>455</v>
@@ -2972,14 +3036,14 @@
         <v>454</v>
       </c>
       <c r="F69" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="I69" t="s">
         <v>20</v>
       </c>
       <c r="J69" s="23">
-        <f>'feed pars'!F16</f>
-        <v>10.3</v>
+        <f>'feed pars'!F23</f>
+        <v>8.9</v>
       </c>
       <c r="K69" t="s">
         <v>455</v>
@@ -2993,14 +3057,14 @@
         <v>454</v>
       </c>
       <c r="F70" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I70" t="s">
         <v>20</v>
       </c>
       <c r="J70" s="23">
-        <f>'feed pars'!F17</f>
-        <v>7.7</v>
+        <f>'feed pars'!F24</f>
+        <v>9</v>
       </c>
       <c r="K70" t="s">
         <v>455</v>
@@ -3014,14 +3078,14 @@
         <v>454</v>
       </c>
       <c r="F71" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="I71" t="s">
         <v>20</v>
       </c>
       <c r="J71" s="23">
-        <f>'feed pars'!F18</f>
-        <v>6.5</v>
+        <f>'feed pars'!F25</f>
+        <v>8</v>
       </c>
       <c r="K71" t="s">
         <v>455</v>
@@ -3035,14 +3099,14 @@
         <v>454</v>
       </c>
       <c r="F72" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="I72" t="s">
         <v>20</v>
       </c>
       <c r="J72" s="23">
-        <f>'feed pars'!F19</f>
-        <v>6.2</v>
+        <f>'feed pars'!F26</f>
+        <v>12.2</v>
       </c>
       <c r="K72" t="s">
         <v>455</v>
@@ -3056,14 +3120,14 @@
         <v>454</v>
       </c>
       <c r="F73" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="I73" t="s">
         <v>20</v>
       </c>
       <c r="J73" s="23">
-        <f>'feed pars'!F20</f>
-        <v>7.8</v>
+        <f>'feed pars'!F27</f>
+        <v>12.2</v>
       </c>
       <c r="K73" t="s">
         <v>455</v>
@@ -3077,14 +3141,14 @@
         <v>454</v>
       </c>
       <c r="F74" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I74" t="s">
         <v>20</v>
       </c>
       <c r="J74" s="23">
-        <f>'feed pars'!F21</f>
-        <v>9.1999999999999993</v>
+        <f>'feed pars'!F28</f>
+        <v>11.3</v>
       </c>
       <c r="K74" t="s">
         <v>455</v>
@@ -3098,14 +3162,14 @@
         <v>454</v>
       </c>
       <c r="F75" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="I75" t="s">
         <v>20</v>
       </c>
       <c r="J75" s="23">
-        <f>'feed pars'!F22</f>
-        <v>8.6999999999999993</v>
+        <f>'feed pars'!F29</f>
+        <v>10.8</v>
       </c>
       <c r="K75" t="s">
         <v>455</v>
@@ -3115,147 +3179,126 @@
       <c r="A76" t="s">
         <v>29</v>
       </c>
-      <c r="E76" t="s">
-        <v>454</v>
-      </c>
       <c r="F76" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="I76" t="s">
         <v>20</v>
       </c>
-      <c r="J76" s="23">
-        <f>'feed pars'!F23</f>
-        <v>8.9</v>
+      <c r="J76">
+        <f>'feed pars'!E6</f>
+        <v>12.1</v>
       </c>
       <c r="K76" t="s">
-        <v>455</v>
+        <v>26</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>29</v>
       </c>
-      <c r="E77" t="s">
-        <v>454</v>
-      </c>
       <c r="F77" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="I77" t="s">
         <v>20</v>
       </c>
-      <c r="J77" s="23">
-        <f>'feed pars'!F24</f>
-        <v>9</v>
+      <c r="J77">
+        <f>'feed pars'!E7</f>
+        <v>11</v>
       </c>
       <c r="K77" t="s">
-        <v>455</v>
+        <v>26</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>29</v>
       </c>
-      <c r="E78" t="s">
-        <v>454</v>
-      </c>
       <c r="F78" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="I78" t="s">
         <v>20</v>
       </c>
-      <c r="J78" s="23">
-        <f>'feed pars'!F25</f>
-        <v>8</v>
+      <c r="J78">
+        <f>'feed pars'!E8</f>
+        <v>9</v>
       </c>
       <c r="K78" t="s">
-        <v>455</v>
+        <v>26</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>29</v>
       </c>
-      <c r="E79" t="s">
-        <v>454</v>
-      </c>
       <c r="F79" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="I79" t="s">
         <v>20</v>
       </c>
-      <c r="J79" s="23">
-        <f>'feed pars'!F26</f>
-        <v>12.2</v>
+      <c r="J79">
+        <f>'feed pars'!E9</f>
+        <v>11.9</v>
       </c>
       <c r="K79" t="s">
-        <v>455</v>
+        <v>26</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>29</v>
       </c>
-      <c r="E80" t="s">
-        <v>454</v>
-      </c>
       <c r="F80" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="I80" t="s">
         <v>20</v>
       </c>
-      <c r="J80" s="23">
-        <f>'feed pars'!F27</f>
-        <v>12.2</v>
+      <c r="J80">
+        <f>'feed pars'!E10</f>
+        <v>12.8</v>
       </c>
       <c r="K80" t="s">
-        <v>455</v>
+        <v>26</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>29</v>
       </c>
-      <c r="E81" t="s">
-        <v>454</v>
-      </c>
       <c r="F81" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I81" t="s">
         <v>20</v>
       </c>
-      <c r="J81" s="23">
-        <f>'feed pars'!F28</f>
-        <v>11.3</v>
+      <c r="J81">
+        <f>'feed pars'!E11</f>
+        <v>11.2</v>
       </c>
       <c r="K81" t="s">
-        <v>455</v>
+        <v>26</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>29</v>
       </c>
-      <c r="E82" t="s">
-        <v>454</v>
-      </c>
       <c r="F82" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="I82" t="s">
         <v>20</v>
       </c>
-      <c r="J82" s="23">
-        <f>'feed pars'!F29</f>
-        <v>10.8</v>
+      <c r="J82">
+        <f>'feed pars'!E12</f>
+        <v>10.7</v>
       </c>
       <c r="K82" t="s">
-        <v>455</v>
+        <v>26</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -3263,14 +3306,14 @@
         <v>29</v>
       </c>
       <c r="F83" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="I83" t="s">
         <v>20</v>
       </c>
       <c r="J83">
-        <f>'feed pars'!E6</f>
-        <v>12.1</v>
+        <f>'feed pars'!E13</f>
+        <v>18</v>
       </c>
       <c r="K83" t="s">
         <v>26</v>
@@ -3281,14 +3324,14 @@
         <v>29</v>
       </c>
       <c r="F84" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I84" t="s">
         <v>20</v>
       </c>
       <c r="J84">
-        <f>'feed pars'!E7</f>
-        <v>11</v>
+        <f>'feed pars'!E14</f>
+        <v>17.3</v>
       </c>
       <c r="K84" t="s">
         <v>26</v>
@@ -3299,14 +3342,14 @@
         <v>29</v>
       </c>
       <c r="F85" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I85" t="s">
         <v>20</v>
       </c>
       <c r="J85">
-        <f>'feed pars'!E8</f>
-        <v>9</v>
+        <f>'feed pars'!E15</f>
+        <v>9.3000000000000007</v>
       </c>
       <c r="K85" t="s">
         <v>26</v>
@@ -3317,14 +3360,14 @@
         <v>29</v>
       </c>
       <c r="F86" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I86" t="s">
         <v>20</v>
       </c>
       <c r="J86">
-        <f>'feed pars'!E9</f>
-        <v>11.9</v>
+        <f>'feed pars'!E16</f>
+        <v>9.6999999999999993</v>
       </c>
       <c r="K86" t="s">
         <v>26</v>
@@ -3335,14 +3378,14 @@
         <v>29</v>
       </c>
       <c r="F87" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I87" t="s">
         <v>20</v>
       </c>
       <c r="J87">
-        <f>'feed pars'!E10</f>
-        <v>12.8</v>
+        <f>'feed pars'!E17</f>
+        <v>7.1</v>
       </c>
       <c r="K87" t="s">
         <v>26</v>
@@ -3353,14 +3396,14 @@
         <v>29</v>
       </c>
       <c r="F88" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="I88" t="s">
         <v>20</v>
       </c>
       <c r="J88">
-        <f>'feed pars'!E11</f>
-        <v>11.2</v>
+        <f>'feed pars'!E18</f>
+        <v>5.9</v>
       </c>
       <c r="K88" t="s">
         <v>26</v>
@@ -3371,14 +3414,14 @@
         <v>29</v>
       </c>
       <c r="F89" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="I89" t="s">
         <v>20</v>
       </c>
       <c r="J89">
-        <f>'feed pars'!E12</f>
-        <v>10.7</v>
+        <f>'feed pars'!E19</f>
+        <v>5.4</v>
       </c>
       <c r="K89" t="s">
         <v>26</v>
@@ -3389,14 +3432,14 @@
         <v>29</v>
       </c>
       <c r="F90" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="I90" t="s">
         <v>20</v>
       </c>
       <c r="J90">
-        <f>'feed pars'!E13</f>
-        <v>18</v>
+        <f>'feed pars'!E20</f>
+        <v>7.2</v>
       </c>
       <c r="K90" t="s">
         <v>26</v>
@@ -3407,14 +3450,14 @@
         <v>29</v>
       </c>
       <c r="F91" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="I91" t="s">
         <v>20</v>
       </c>
       <c r="J91">
-        <f>'feed pars'!E14</f>
-        <v>17.3</v>
+        <f>'feed pars'!E21</f>
+        <v>8.6999999999999993</v>
       </c>
       <c r="K91" t="s">
         <v>26</v>
@@ -3425,14 +3468,14 @@
         <v>29</v>
       </c>
       <c r="F92" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I92" t="s">
         <v>20</v>
       </c>
       <c r="J92">
-        <f>'feed pars'!E15</f>
-        <v>9.3000000000000007</v>
+        <f>'feed pars'!E22</f>
+        <v>8.1</v>
       </c>
       <c r="K92" t="s">
         <v>26</v>
@@ -3443,14 +3486,14 @@
         <v>29</v>
       </c>
       <c r="F93" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="I93" t="s">
         <v>20</v>
       </c>
       <c r="J93">
-        <f>'feed pars'!E16</f>
-        <v>9.6999999999999993</v>
+        <f>'feed pars'!E23</f>
+        <v>8.1999999999999993</v>
       </c>
       <c r="K93" t="s">
         <v>26</v>
@@ -3461,14 +3504,14 @@
         <v>29</v>
       </c>
       <c r="F94" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I94" t="s">
         <v>20</v>
       </c>
       <c r="J94">
-        <f>'feed pars'!E17</f>
-        <v>7.1</v>
+        <f>'feed pars'!E24</f>
+        <v>8.6999999999999993</v>
       </c>
       <c r="K94" t="s">
         <v>26</v>
@@ -3479,14 +3522,14 @@
         <v>29</v>
       </c>
       <c r="F95" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="I95" t="s">
         <v>20</v>
       </c>
       <c r="J95">
-        <f>'feed pars'!E18</f>
-        <v>5.9</v>
+        <f>'feed pars'!E25</f>
+        <v>6.9</v>
       </c>
       <c r="K95" t="s">
         <v>26</v>
@@ -3497,14 +3540,14 @@
         <v>29</v>
       </c>
       <c r="F96" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="I96" t="s">
         <v>20</v>
       </c>
       <c r="J96">
-        <f>'feed pars'!E19</f>
-        <v>5.4</v>
+        <f>'feed pars'!E26</f>
+        <v>12.4</v>
       </c>
       <c r="K96" t="s">
         <v>26</v>
@@ -3515,14 +3558,14 @@
         <v>29</v>
       </c>
       <c r="F97" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="I97" t="s">
         <v>20</v>
       </c>
       <c r="J97">
-        <f>'feed pars'!E20</f>
-        <v>7.2</v>
+        <f>'feed pars'!E27</f>
+        <v>12.4</v>
       </c>
       <c r="K97" t="s">
         <v>26</v>
@@ -3533,14 +3576,14 @@
         <v>29</v>
       </c>
       <c r="F98" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I98" t="s">
         <v>20</v>
       </c>
       <c r="J98">
-        <f>'feed pars'!E21</f>
-        <v>8.6999999999999993</v>
+        <f>'feed pars'!E28</f>
+        <v>11.1</v>
       </c>
       <c r="K98" t="s">
         <v>26</v>
@@ -3551,142 +3594,16 @@
         <v>29</v>
       </c>
       <c r="F99" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="I99" t="s">
         <v>20</v>
       </c>
       <c r="J99">
-        <f>'feed pars'!E22</f>
-        <v>8.1</v>
-      </c>
-      <c r="K99" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>29</v>
-      </c>
-      <c r="F100" t="s">
-        <v>55</v>
-      </c>
-      <c r="I100" t="s">
-        <v>20</v>
-      </c>
-      <c r="J100">
-        <f>'feed pars'!E23</f>
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="K100" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>29</v>
-      </c>
-      <c r="F101" t="s">
-        <v>56</v>
-      </c>
-      <c r="I101" t="s">
-        <v>20</v>
-      </c>
-      <c r="J101">
-        <f>'feed pars'!E24</f>
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="K101" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>29</v>
-      </c>
-      <c r="F102" t="s">
-        <v>57</v>
-      </c>
-      <c r="I102" t="s">
-        <v>20</v>
-      </c>
-      <c r="J102">
-        <f>'feed pars'!E25</f>
-        <v>6.9</v>
-      </c>
-      <c r="K102" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>29</v>
-      </c>
-      <c r="F103" t="s">
-        <v>58</v>
-      </c>
-      <c r="I103" t="s">
-        <v>20</v>
-      </c>
-      <c r="J103">
-        <f>'feed pars'!E26</f>
-        <v>12.4</v>
-      </c>
-      <c r="K103" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>29</v>
-      </c>
-      <c r="F104" t="s">
-        <v>59</v>
-      </c>
-      <c r="I104" t="s">
-        <v>20</v>
-      </c>
-      <c r="J104">
-        <f>'feed pars'!E27</f>
-        <v>12.4</v>
-      </c>
-      <c r="K104" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>29</v>
-      </c>
-      <c r="F105" t="s">
-        <v>60</v>
-      </c>
-      <c r="I105" t="s">
-        <v>20</v>
-      </c>
-      <c r="J105">
-        <f>'feed pars'!E28</f>
-        <v>11.1</v>
-      </c>
-      <c r="K105" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>29</v>
-      </c>
-      <c r="F106" t="s">
-        <v>61</v>
-      </c>
-      <c r="I106" t="s">
-        <v>20</v>
-      </c>
-      <c r="J106">
         <f>'feed pars'!E29</f>
         <v>10.8</v>
       </c>
-      <c r="K106" t="s">
+      <c r="K99" t="s">
         <v>26</v>
       </c>
     </row>

--- a/data/prod_parameters/FeedMgmt.xlsx
+++ b/data/prod_parameters/FeedMgmt.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="325">
   <si>
     <t>f_feed</t>
   </si>
@@ -30,9 +30,6 @@
     <t>f_crop_prod</t>
   </si>
   <si>
-    <t>silage</t>
-  </si>
-  <si>
     <t>hay</t>
   </si>
   <si>
@@ -87,12 +84,6 @@
     <t>MJ ME/kg DM</t>
   </si>
   <si>
-    <t>dairy</t>
-  </si>
-  <si>
-    <t>cows</t>
-  </si>
-  <si>
     <t>Cattle</t>
   </si>
   <si>
@@ -963,16 +954,49 @@
     <t>need to align with DM in products and by-products</t>
   </si>
   <si>
-    <t xml:space="preserve">   1st cut</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   regrowth</t>
-  </si>
-  <si>
-    <t>80% 1st cut</t>
-  </si>
-  <si>
-    <t>50% 1st cut</t>
+    <t>ley silage, 1st cut</t>
+  </si>
+  <si>
+    <t>ley silage, regrowth</t>
+  </si>
+  <si>
+    <t>other silage</t>
+  </si>
+  <si>
+    <t>barley brewers grain</t>
+  </si>
+  <si>
+    <t>vegetable oils</t>
+  </si>
+  <si>
+    <t>feed_to_by_prod</t>
+  </si>
+  <si>
+    <t>https://www.feedipedia.org/node/74</t>
+  </si>
+  <si>
+    <t>rye</t>
+  </si>
+  <si>
+    <t>soybeans</t>
+  </si>
+  <si>
+    <t>luzern meal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.feedipedia.org/node/11744 </t>
+  </si>
+  <si>
+    <t>add by-prod generation calculation method!</t>
+  </si>
+  <si>
+    <t>https://www.feedipedia.org/node/12799</t>
+  </si>
+  <si>
+    <t>https://www.feedtables.com/content/rapeseed-oil</t>
+  </si>
+  <si>
+    <t>minerals</t>
   </si>
 </sst>
 </file>
@@ -982,7 +1006,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1044,14 +1068,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1120,7 +1136,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1160,12 +1176,13 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1447,7 +1464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N120"/>
+  <dimension ref="A1:N141"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="20.28515625" customWidth="1"/>
@@ -1461,19 +1478,19 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>17</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>0</v>
@@ -1482,27 +1499,27 @@
         <v>1</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>7</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1514,1942 +1531,2293 @@
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="L2" s="25" t="s">
-        <v>312</v>
+        <v>302</v>
+      </c>
+      <c r="L2" s="24" t="s">
+        <v>309</v>
       </c>
       <c r="M2" s="2"/>
       <c r="N2" s="5"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="I3" s="10" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J3" s="21">
         <v>0</v>
       </c>
       <c r="K3" s="10"/>
       <c r="L3" s="10" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F4" t="s">
-        <v>2</v>
+        <v>310</v>
       </c>
       <c r="G4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J4" s="22">
+        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F4,'feed pars'!B$6:B$42,0))</f>
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F5" t="s">
-        <v>3</v>
+        <v>311</v>
       </c>
       <c r="G5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J5" s="22">
+        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F5,'feed pars'!B$6:B$42,0))</f>
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F6" t="s">
-        <v>13</v>
+        <v>312</v>
       </c>
       <c r="G6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J6" s="22">
+        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F6,'feed pars'!B$6:B$42,0))</f>
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F7" t="s">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="I7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J7" s="22">
+        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F7,'feed pars'!B$6:B$42,0))</f>
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F8" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I8" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J8" s="22">
-        <f>'feed pars'!C13/100</f>
-        <v>0.87</v>
+        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F8,'feed pars'!B$6:B$42,0))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F9" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G9" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="I9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J9" s="22">
-        <f>'feed pars'!C14/100</f>
-        <v>0.87</v>
+        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F9,'feed pars'!B$6:B$42,0))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F10" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="I10" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J10" s="22">
-        <f>'feed pars'!C15/100</f>
-        <v>0.86</v>
+        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F10,'feed pars'!B$6:B$42,0))</f>
+        <v>1.1494252873563218</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F11" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G11" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="I11" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J11" s="22">
-        <f>'feed pars'!C16/100</f>
-        <v>0.87</v>
+        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F11,'feed pars'!B$6:B$42,0))</f>
+        <v>1.1494252873563218</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F12" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G12" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I12" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J12" s="22">
-        <f>'feed pars'!C17/100</f>
-        <v>0.67500000000000004</v>
+        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F12,'feed pars'!B$6:B$42,0))</f>
+        <v>1.1627906976744187</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F13" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="I13" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J13" s="22">
-        <f>'feed pars'!C18/100</f>
-        <v>0.87</v>
+        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F13,'feed pars'!B$6:B$42,0))</f>
+        <v>1.1494252873563218</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F14" t="s">
-        <v>45</v>
+        <v>317</v>
       </c>
       <c r="G14" t="s">
-        <v>45</v>
+        <v>317</v>
       </c>
       <c r="I14" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J14" s="22">
-        <f>'feed pars'!C19/100</f>
-        <v>0.87</v>
+        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F14,'feed pars'!B$6:B$42,0))</f>
+        <v>1.1494252873563218</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I15" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J15" s="22">
-        <f>'feed pars'!C20/100</f>
-        <v>0.92500000000000004</v>
+        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F15,'feed pars'!B$6:B$42,0))</f>
+        <v>1.4814814814814814</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F16" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16" t="s">
+        <v>41</v>
+      </c>
+      <c r="I16" t="s">
+        <v>32</v>
+      </c>
+      <c r="J16" s="22">
+        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F16,'feed pars'!B$6:B$42,0))</f>
+        <v>1.1494252873563218</v>
+      </c>
+    </row>
+    <row r="17" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" t="s">
+        <v>42</v>
+      </c>
+      <c r="I17" t="s">
+        <v>32</v>
+      </c>
+      <c r="J17" s="22">
+        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F17,'feed pars'!B$6:B$42,0))</f>
+        <v>1.1520737327188941</v>
+      </c>
+    </row>
+    <row r="18" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F18" t="s">
+        <v>35</v>
+      </c>
+      <c r="G18" t="s">
+        <v>35</v>
+      </c>
+      <c r="I18" t="s">
+        <v>32</v>
+      </c>
+      <c r="J18" s="22">
+        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F18,'feed pars'!B$6:B$42,0))</f>
+        <v>1.0810810810810809</v>
+      </c>
+    </row>
+    <row r="19" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F19" t="s">
+        <v>43</v>
+      </c>
+      <c r="G19" t="s">
+        <v>43</v>
+      </c>
+      <c r="I19" t="s">
+        <v>32</v>
+      </c>
+      <c r="J19" s="22">
+        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F19,'feed pars'!B$6:B$42,0))</f>
+        <v>1.0869565217391304</v>
+      </c>
+    </row>
+    <row r="20" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F20" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J20" s="20">
+        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F20,'feed pars'!B$6:B$42,0))*1/0.38</f>
+        <v>2.6315789473684212</v>
+      </c>
+    </row>
+    <row r="21" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F21" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J21" s="22"/>
+      <c r="L21" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="22" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F22" t="s">
+        <v>305</v>
+      </c>
+      <c r="H22" t="s">
+        <v>305</v>
+      </c>
+      <c r="I22" t="s">
+        <v>32</v>
+      </c>
+      <c r="J22" s="22">
+        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F22,'feed pars'!B$6:B$42,0))</f>
+        <v>1.1764705882352942</v>
+      </c>
+    </row>
+    <row r="23" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F23" t="s">
+        <v>318</v>
+      </c>
+      <c r="H23" t="s">
+        <v>318</v>
+      </c>
+      <c r="I23" t="s">
+        <v>32</v>
+      </c>
+      <c r="J23" s="22">
+        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F23,'feed pars'!B$6:B$42,0))</f>
+        <v>1.1494252873563218</v>
+      </c>
+    </row>
+    <row r="24" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F24" t="s">
+        <v>44</v>
+      </c>
+      <c r="H24" t="s">
+        <v>44</v>
+      </c>
+      <c r="I24" t="s">
+        <v>32</v>
+      </c>
+      <c r="J24" s="22">
+        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F24,'feed pars'!B$6:B$42,0))</f>
+        <v>1.1428571428571428</v>
+      </c>
+    </row>
+    <row r="25" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F25" t="s">
+        <v>45</v>
+      </c>
+      <c r="H25" t="s">
+        <v>45</v>
+      </c>
+      <c r="I25" t="s">
+        <v>32</v>
+      </c>
+      <c r="J25" s="22">
+        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F25,'feed pars'!B$6:B$42,0))</f>
+        <v>1.1494252873563218</v>
+      </c>
+    </row>
+    <row r="26" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F26" t="s">
+        <v>36</v>
+      </c>
+      <c r="H26" t="s">
+        <v>36</v>
+      </c>
+      <c r="I26" t="s">
+        <v>32</v>
+      </c>
+      <c r="J26" s="22">
+        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F26,'feed pars'!B$6:B$42,0))</f>
+        <v>1.1173184357541899</v>
+      </c>
+    </row>
+    <row r="27" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F27" t="s">
         <v>46</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H27" t="s">
         <v>46</v>
       </c>
-      <c r="I16" t="s">
+      <c r="I27" t="s">
+        <v>32</v>
+      </c>
+      <c r="J27" s="22">
+        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F27,'feed pars'!B$6:B$42,0))</f>
+        <v>1.0989010989010988</v>
+      </c>
+    </row>
+    <row r="28" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F28" t="s">
+        <v>47</v>
+      </c>
+      <c r="H28" t="s">
+        <v>47</v>
+      </c>
+      <c r="I28" t="s">
+        <v>32</v>
+      </c>
+      <c r="J28" s="22">
+        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F28,'feed pars'!B$6:B$42,0))</f>
+        <v>1.0989010989010988</v>
+      </c>
+    </row>
+    <row r="29" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F29" t="s">
+        <v>319</v>
+      </c>
+      <c r="H29" t="s">
+        <v>319</v>
+      </c>
+      <c r="I29" t="s">
+        <v>32</v>
+      </c>
+      <c r="J29" s="22">
+        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F29,'feed pars'!B$6:B$42,0))</f>
+        <v>1.1111111111111112</v>
+      </c>
+    </row>
+    <row r="30" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F30" t="s">
+        <v>48</v>
+      </c>
+      <c r="H30" t="s">
+        <v>48</v>
+      </c>
+      <c r="I30" t="s">
+        <v>32</v>
+      </c>
+      <c r="J30" s="22">
+        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F30,'feed pars'!B$6:B$42,0))</f>
+        <v>1.1494252873563218</v>
+      </c>
+    </row>
+    <row r="31" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F31" t="s">
+        <v>49</v>
+      </c>
+      <c r="H31" t="s">
+        <v>48</v>
+      </c>
+      <c r="I31" t="s">
+        <v>32</v>
+      </c>
+      <c r="J31" s="22">
+        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F31,'feed pars'!B$6:B$42,0))</f>
+        <v>1.1363636363636365</v>
+      </c>
+    </row>
+    <row r="32" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F32" t="s">
+        <v>50</v>
+      </c>
+      <c r="H32" t="s">
+        <v>301</v>
+      </c>
+      <c r="I32" t="s">
+        <v>32</v>
+      </c>
+      <c r="J32" s="20">
+        <f>J33</f>
+        <v>9.0909090909090917</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="F33" t="s">
+        <v>51</v>
+      </c>
+      <c r="H33" t="s">
+        <v>301</v>
+      </c>
+      <c r="I33" t="s">
+        <v>32</v>
+      </c>
+      <c r="J33" s="22">
+        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F33,'feed pars'!B$6:B$42,0))</f>
+        <v>9.0909090909090917</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="F34" t="s">
+        <v>313</v>
+      </c>
+      <c r="H34" t="s">
+        <v>313</v>
+      </c>
+      <c r="I34" t="s">
+        <v>32</v>
+      </c>
+      <c r="J34" s="20">
+        <f>1/0.25</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="F35" t="s">
+        <v>52</v>
+      </c>
+      <c r="H35" t="s">
+        <v>52</v>
+      </c>
+      <c r="I35" t="s">
+        <v>32</v>
+      </c>
+      <c r="J35" s="22">
+        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F35,'feed pars'!B$6:B$42,0))</f>
+        <v>1.3245033112582782</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="F36" t="s">
+        <v>53</v>
+      </c>
+      <c r="H36" t="s">
+        <v>53</v>
+      </c>
+      <c r="I36" t="s">
+        <v>32</v>
+      </c>
+      <c r="J36" s="22">
+        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F36,'feed pars'!B$6:B$42,0))</f>
+        <v>1.1173184357541899</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="F37" t="s">
+        <v>54</v>
+      </c>
+      <c r="H37" t="s">
+        <v>54</v>
+      </c>
+      <c r="I37" t="s">
+        <v>32</v>
+      </c>
+      <c r="J37" s="22">
+        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F37,'feed pars'!B$6:B$42,0))</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="F38" t="s">
+        <v>55</v>
+      </c>
+      <c r="H38" t="s">
+        <v>54</v>
+      </c>
+      <c r="I38" t="s">
+        <v>32</v>
+      </c>
+      <c r="J38" s="20">
+        <f>J37</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="F39" t="s">
+        <v>56</v>
+      </c>
+      <c r="H39" t="s">
+        <v>56</v>
+      </c>
+      <c r="I39" t="s">
+        <v>32</v>
+      </c>
+      <c r="J39" s="22">
+        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F39,'feed pars'!B$6:B$42,0))</f>
+        <v>1.0989010989010988</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="F40" t="s">
+        <v>57</v>
+      </c>
+      <c r="H40" t="s">
+        <v>57</v>
+      </c>
+      <c r="I40" t="s">
+        <v>32</v>
+      </c>
+      <c r="J40" s="22">
+        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F40,'feed pars'!B$6:B$42,0))</f>
+        <v>1.0869565217391304</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I42" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J42" s="10">
+        <v>0</v>
+      </c>
+      <c r="K42" s="10"/>
+      <c r="L42" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G43" t="s">
+        <v>10</v>
+      </c>
+      <c r="I43" t="s">
+        <v>27</v>
+      </c>
+      <c r="J43" s="3">
+        <v>95</v>
+      </c>
+      <c r="K43" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G44" t="s">
+        <v>11</v>
+      </c>
+      <c r="I44" t="s">
+        <v>27</v>
+      </c>
+      <c r="J44" s="3">
+        <v>95</v>
+      </c>
+      <c r="K44" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G45" t="s">
+        <v>33</v>
+      </c>
+      <c r="I45" t="s">
+        <v>27</v>
+      </c>
+      <c r="J45" s="3">
+        <v>95</v>
+      </c>
+      <c r="K45" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
+      <c r="L46" s="2"/>
+      <c r="M46" s="2"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I47" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="J47" s="10">
+        <v>0</v>
+      </c>
+      <c r="K47" s="10"/>
+      <c r="L47" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H48" t="s">
+        <v>318</v>
+      </c>
+      <c r="I48" t="s">
+        <v>31</v>
+      </c>
+      <c r="J48" s="29">
+        <v>100</v>
+      </c>
+      <c r="K48" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="L48" s="10"/>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H49" t="s">
+        <v>44</v>
+      </c>
+      <c r="I49" t="s">
+        <v>31</v>
+      </c>
+      <c r="J49" s="29">
+        <v>100</v>
+      </c>
+      <c r="K49" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="L49" s="10"/>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H50" t="s">
+        <v>36</v>
+      </c>
+      <c r="I50" t="s">
+        <v>31</v>
+      </c>
+      <c r="J50" s="29">
+        <v>61</v>
+      </c>
+      <c r="K50" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G51" t="s">
+        <v>43</v>
+      </c>
+      <c r="I51" t="s">
+        <v>31</v>
+      </c>
+      <c r="J51" s="3">
+        <v>100</v>
+      </c>
+      <c r="K51" t="s">
+        <v>28</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J52" s="3"/>
+      <c r="L52" s="3"/>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2"/>
+      <c r="L53" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="M53" s="2"/>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B54" s="7"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="6"/>
+      <c r="K54" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L54" s="6"/>
+      <c r="M54" s="6"/>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>24</v>
+      </c>
+      <c r="F55" t="s">
+        <v>310</v>
+      </c>
+      <c r="I55" t="s">
+        <v>18</v>
+      </c>
+      <c r="J55" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F55,'feed pars'!B$6:B$42,0))</f>
+        <v>11.5</v>
+      </c>
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>24</v>
+      </c>
+      <c r="F56" t="s">
+        <v>311</v>
+      </c>
+      <c r="I56" t="s">
+        <v>18</v>
+      </c>
+      <c r="J56" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F56,'feed pars'!B$6:B$42,0))</f>
+        <v>10.4</v>
+      </c>
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>24</v>
+      </c>
+      <c r="F57" t="s">
+        <v>312</v>
+      </c>
+      <c r="I57" t="s">
+        <v>18</v>
+      </c>
+      <c r="J57" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F57,'feed pars'!B$6:B$42,0))</f>
+        <v>10</v>
+      </c>
+      <c r="L57" s="3"/>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>24</v>
+      </c>
+      <c r="F58" t="s">
+        <v>12</v>
+      </c>
+      <c r="I58" t="s">
+        <v>18</v>
+      </c>
+      <c r="J58" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F58,'feed pars'!B$6:B$42,0))</f>
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>24</v>
+      </c>
+      <c r="F59" t="s">
+        <v>33</v>
+      </c>
+      <c r="I59" t="s">
+        <v>18</v>
+      </c>
+      <c r="J59" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F59,'feed pars'!B$6:B$42,0))</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J60" s="3"/>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>24</v>
+      </c>
+      <c r="F61" t="s">
+        <v>17</v>
+      </c>
+      <c r="I61" t="s">
+        <v>18</v>
+      </c>
+      <c r="J61" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F61,'feed pars'!B$6:B$42,0))</f>
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>24</v>
+      </c>
+      <c r="F62" t="s">
+        <v>37</v>
+      </c>
+      <c r="I62" t="s">
+        <v>18</v>
+      </c>
+      <c r="J62" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F62,'feed pars'!B$6:B$42,0))</f>
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>24</v>
+      </c>
+      <c r="F63" t="s">
+        <v>38</v>
+      </c>
+      <c r="I63" t="s">
+        <v>18</v>
+      </c>
+      <c r="J63" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F63,'feed pars'!B$6:B$42,0))</f>
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>24</v>
+      </c>
+      <c r="F64" t="s">
+        <v>39</v>
+      </c>
+      <c r="I64" t="s">
+        <v>18</v>
+      </c>
+      <c r="J64" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F64,'feed pars'!B$6:B$42,0))</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>24</v>
+      </c>
+      <c r="F65" t="s">
+        <v>317</v>
+      </c>
+      <c r="I65" t="s">
+        <v>18</v>
+      </c>
+      <c r="J65" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F65,'feed pars'!B$6:B$42,0))</f>
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>24</v>
+      </c>
+      <c r="F66" t="s">
+        <v>40</v>
+      </c>
+      <c r="I66" t="s">
+        <v>18</v>
+      </c>
+      <c r="J66" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F66,'feed pars'!B$6:B$42,0))</f>
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>24</v>
+      </c>
+      <c r="F67" t="s">
+        <v>41</v>
+      </c>
+      <c r="I67" t="s">
+        <v>18</v>
+      </c>
+      <c r="J67" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F67,'feed pars'!B$6:B$42,0))</f>
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>24</v>
+      </c>
+      <c r="F68" t="s">
+        <v>42</v>
+      </c>
+      <c r="I68" t="s">
+        <v>18</v>
+      </c>
+      <c r="J68" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F68,'feed pars'!B$6:B$42,0))</f>
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>24</v>
+      </c>
+      <c r="F69" t="s">
         <v>35</v>
       </c>
-      <c r="J16" s="22">
-        <f>'feed pars'!C21/100</f>
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="17" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F17" t="s">
-        <v>308</v>
-      </c>
-      <c r="H17" t="s">
-        <v>308</v>
-      </c>
-      <c r="I17" t="s">
+      <c r="I69" t="s">
+        <v>18</v>
+      </c>
+      <c r="J69" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F69,'feed pars'!B$6:B$42,0))</f>
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>24</v>
+      </c>
+      <c r="F70" t="s">
+        <v>43</v>
+      </c>
+      <c r="I70" t="s">
+        <v>18</v>
+      </c>
+      <c r="J70" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F70,'feed pars'!B$6:B$42,0))</f>
+        <v>20.100000000000001</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>24</v>
+      </c>
+      <c r="F71" t="s">
+        <v>305</v>
+      </c>
+      <c r="I71" t="s">
+        <v>18</v>
+      </c>
+      <c r="J71" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F71,'feed pars'!B$6:B$42,0))</f>
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>24</v>
+      </c>
+      <c r="F72" t="s">
+        <v>314</v>
+      </c>
+      <c r="I72" t="s">
+        <v>18</v>
+      </c>
+      <c r="J72" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F72,'feed pars'!B$6:B$42,0))</f>
+        <v>36.6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>24</v>
+      </c>
+      <c r="F73" t="s">
+        <v>318</v>
+      </c>
+      <c r="I73" t="s">
+        <v>18</v>
+      </c>
+      <c r="J73" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F73,'feed pars'!B$6:B$42,0))</f>
+        <v>16.399999999999999</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>24</v>
+      </c>
+      <c r="F74" t="s">
+        <v>44</v>
+      </c>
+      <c r="I74" t="s">
+        <v>18</v>
+      </c>
+      <c r="J74" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F74,'feed pars'!B$6:B$42,0))</f>
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>24</v>
+      </c>
+      <c r="F75" t="s">
+        <v>36</v>
+      </c>
+      <c r="I75" t="s">
+        <v>18</v>
+      </c>
+      <c r="J75" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F75,'feed pars'!B$6:B$42,0))</f>
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>24</v>
+      </c>
+      <c r="F76" t="s">
+        <v>46</v>
+      </c>
+      <c r="I76" t="s">
+        <v>18</v>
+      </c>
+      <c r="J76" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F76,'feed pars'!B$6:B$42,0))</f>
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>24</v>
+      </c>
+      <c r="F77" t="s">
+        <v>47</v>
+      </c>
+      <c r="I77" t="s">
+        <v>18</v>
+      </c>
+      <c r="J77" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F77,'feed pars'!B$6:B$42,0))</f>
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>24</v>
+      </c>
+      <c r="F78" t="s">
+        <v>319</v>
+      </c>
+      <c r="I78" t="s">
+        <v>18</v>
+      </c>
+      <c r="J78" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F78,'feed pars'!B$6:B$42,0))</f>
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>24</v>
+      </c>
+      <c r="F79" t="s">
+        <v>48</v>
+      </c>
+      <c r="I79" t="s">
+        <v>18</v>
+      </c>
+      <c r="J79" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F79,'feed pars'!B$6:B$42,0))</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>24</v>
+      </c>
+      <c r="F80" t="s">
+        <v>50</v>
+      </c>
+      <c r="I80" t="s">
+        <v>18</v>
+      </c>
+      <c r="J80" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F80,'feed pars'!B$6:B$42,0))</f>
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>24</v>
+      </c>
+      <c r="F81" t="s">
+        <v>313</v>
+      </c>
+      <c r="I81" t="s">
+        <v>18</v>
+      </c>
+      <c r="J81" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F81,'feed pars'!B$6:B$42,0))</f>
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>24</v>
+      </c>
+      <c r="F82" t="s">
+        <v>52</v>
+      </c>
+      <c r="I82" t="s">
+        <v>18</v>
+      </c>
+      <c r="J82" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F82,'feed pars'!B$6:B$42,0))</f>
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>24</v>
+      </c>
+      <c r="F83" t="s">
+        <v>53</v>
+      </c>
+      <c r="I83" t="s">
+        <v>18</v>
+      </c>
+      <c r="J83" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F83,'feed pars'!B$6:B$42,0))</f>
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>24</v>
+      </c>
+      <c r="F84" t="s">
+        <v>54</v>
+      </c>
+      <c r="I84" t="s">
+        <v>18</v>
+      </c>
+      <c r="J84" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F84,'feed pars'!B$6:B$42,0))</f>
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>24</v>
+      </c>
+      <c r="F85" t="s">
+        <v>56</v>
+      </c>
+      <c r="I85" t="s">
+        <v>18</v>
+      </c>
+      <c r="J85" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F85,'feed pars'!B$6:B$42,0))</f>
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>24</v>
+      </c>
+      <c r="F86" t="s">
+        <v>324</v>
+      </c>
+      <c r="I86" t="s">
+        <v>18</v>
+      </c>
+      <c r="J86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J87" s="3"/>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A88" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B88" s="8"/>
+      <c r="C88" s="9"/>
+      <c r="D88" s="9"/>
+      <c r="E88" s="9"/>
+      <c r="F88" s="9"/>
+      <c r="G88" s="9"/>
+      <c r="H88" s="9"/>
+      <c r="I88" s="9"/>
+      <c r="J88" s="9"/>
+      <c r="K88" s="9"/>
+      <c r="L88" s="9"/>
+      <c r="M88" s="9"/>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>25</v>
+      </c>
+      <c r="E89" t="s">
+        <v>299</v>
+      </c>
+      <c r="F89" t="s">
+        <v>17</v>
+      </c>
+      <c r="I89" t="s">
+        <v>18</v>
+      </c>
+      <c r="J89" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F89,'feed pars'!B$6:B$42,0))</f>
+        <v>12.3</v>
+      </c>
+      <c r="K89" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>25</v>
+      </c>
+      <c r="E90" t="s">
+        <v>299</v>
+      </c>
+      <c r="F90" t="s">
+        <v>37</v>
+      </c>
+      <c r="I90" t="s">
+        <v>18</v>
+      </c>
+      <c r="J90" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F90,'feed pars'!B$6:B$42,0))</f>
+        <v>11.2</v>
+      </c>
+      <c r="K90" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>25</v>
+      </c>
+      <c r="E91" t="s">
+        <v>299</v>
+      </c>
+      <c r="F91" t="s">
+        <v>38</v>
+      </c>
+      <c r="I91" t="s">
+        <v>18</v>
+      </c>
+      <c r="J91" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F91,'feed pars'!B$6:B$42,0))</f>
+        <v>9.4</v>
+      </c>
+      <c r="K91" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>25</v>
+      </c>
+      <c r="E92" t="s">
+        <v>299</v>
+      </c>
+      <c r="F92" t="s">
+        <v>39</v>
+      </c>
+      <c r="I92" t="s">
+        <v>18</v>
+      </c>
+      <c r="J92" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F92,'feed pars'!B$6:B$42,0))</f>
+        <v>12</v>
+      </c>
+      <c r="K92" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>25</v>
+      </c>
+      <c r="E93" t="s">
+        <v>299</v>
+      </c>
+      <c r="F93" t="s">
+        <v>40</v>
+      </c>
+      <c r="I93" t="s">
+        <v>18</v>
+      </c>
+      <c r="J93" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F93,'feed pars'!B$6:B$42,0))</f>
+        <v>13.2</v>
+      </c>
+      <c r="K93" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>25</v>
+      </c>
+      <c r="E94" t="s">
+        <v>299</v>
+      </c>
+      <c r="F94" t="s">
+        <v>41</v>
+      </c>
+      <c r="I94" t="s">
+        <v>18</v>
+      </c>
+      <c r="J94" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F94,'feed pars'!B$6:B$42,0))</f>
+        <v>11.5</v>
+      </c>
+      <c r="K94" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>25</v>
+      </c>
+      <c r="E95" t="s">
+        <v>299</v>
+      </c>
+      <c r="F95" t="s">
+        <v>42</v>
+      </c>
+      <c r="I95" t="s">
+        <v>18</v>
+      </c>
+      <c r="J95" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F95,'feed pars'!B$6:B$42,0))</f>
+        <v>10.9</v>
+      </c>
+      <c r="K95" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>25</v>
+      </c>
+      <c r="E96" t="s">
+        <v>299</v>
+      </c>
+      <c r="F96" t="s">
         <v>35</v>
       </c>
-      <c r="J17" s="22">
-        <f>'feed pars'!C22/100</f>
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="18" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F18" t="s">
-        <v>47</v>
-      </c>
-      <c r="H18" t="s">
-        <v>47</v>
-      </c>
-      <c r="I18" t="s">
-        <v>35</v>
-      </c>
-      <c r="J18" s="22">
-        <f>'feed pars'!C23/100</f>
-        <v>0.875</v>
-      </c>
-    </row>
-    <row r="19" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F19" t="s">
-        <v>48</v>
-      </c>
-      <c r="H19" t="s">
-        <v>48</v>
-      </c>
-      <c r="I19" t="s">
-        <v>35</v>
-      </c>
-      <c r="J19" s="22">
-        <f>'feed pars'!C24/100</f>
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="20" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F20" t="s">
-        <v>39</v>
-      </c>
-      <c r="H20" t="s">
-        <v>39</v>
-      </c>
-      <c r="I20" t="s">
-        <v>35</v>
-      </c>
-      <c r="J20" s="22">
-        <f>'feed pars'!C25/100</f>
-        <v>0.89500000000000002</v>
-      </c>
-    </row>
-    <row r="21" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F21" t="s">
-        <v>49</v>
-      </c>
-      <c r="H21" t="s">
-        <v>49</v>
-      </c>
-      <c r="I21" t="s">
-        <v>35</v>
-      </c>
-      <c r="J21" s="22">
-        <f>'feed pars'!C26/100</f>
-        <v>0.91</v>
-      </c>
-    </row>
-    <row r="22" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F22" t="s">
-        <v>50</v>
-      </c>
-      <c r="H22" t="s">
-        <v>50</v>
-      </c>
-      <c r="I22" t="s">
-        <v>35</v>
-      </c>
-      <c r="J22" s="22">
-        <f>'feed pars'!C27/100</f>
-        <v>0.91</v>
-      </c>
-    </row>
-    <row r="23" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F23" t="s">
-        <v>51</v>
-      </c>
-      <c r="H23" t="s">
-        <v>51</v>
-      </c>
-      <c r="I23" t="s">
-        <v>35</v>
-      </c>
-      <c r="J23" s="22">
-        <f>'feed pars'!C28/100</f>
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="24" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F24" t="s">
-        <v>52</v>
-      </c>
-      <c r="H24" t="s">
-        <v>51</v>
-      </c>
-      <c r="I24" t="s">
-        <v>35</v>
-      </c>
-      <c r="J24" s="22">
-        <f>'feed pars'!C29/100</f>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="25" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F25" t="s">
-        <v>53</v>
-      </c>
-      <c r="H25" t="s">
-        <v>304</v>
-      </c>
-      <c r="I25" t="s">
-        <v>35</v>
-      </c>
-      <c r="J25" s="20">
-        <f>J26</f>
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="26" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F26" t="s">
-        <v>54</v>
-      </c>
-      <c r="H26" t="s">
-        <v>304</v>
-      </c>
-      <c r="I26" t="s">
-        <v>35</v>
-      </c>
-      <c r="J26" s="22">
-        <f>'feed pars'!C31/100</f>
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="27" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F27" t="s">
-        <v>55</v>
-      </c>
-      <c r="H27" t="s">
-        <v>55</v>
-      </c>
-      <c r="I27" t="s">
-        <v>35</v>
-      </c>
-      <c r="J27" s="22">
-        <f>'feed pars'!C32/100</f>
-        <v>0.755</v>
-      </c>
-    </row>
-    <row r="28" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F28" t="s">
-        <v>56</v>
-      </c>
-      <c r="H28" t="s">
-        <v>56</v>
-      </c>
-      <c r="I28" t="s">
-        <v>35</v>
-      </c>
-      <c r="J28" s="22">
-        <f>'feed pars'!C33/100</f>
-        <v>0.89500000000000002</v>
-      </c>
-    </row>
-    <row r="29" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F29" t="s">
-        <v>57</v>
-      </c>
-      <c r="H29" t="s">
-        <v>57</v>
-      </c>
-      <c r="I29" t="s">
-        <v>35</v>
-      </c>
-      <c r="J29" s="22">
-        <f>'feed pars'!C34/100</f>
-        <v>6.25E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F30" t="s">
-        <v>58</v>
-      </c>
-      <c r="H30" t="s">
-        <v>57</v>
-      </c>
-      <c r="I30" t="s">
-        <v>35</v>
-      </c>
-      <c r="J30" s="20">
-        <f>J29</f>
-        <v>6.25E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F31" t="s">
-        <v>59</v>
-      </c>
-      <c r="H31" t="s">
-        <v>59</v>
-      </c>
-      <c r="I31" t="s">
-        <v>35</v>
-      </c>
-      <c r="J31" s="22">
-        <f>'feed pars'!C36/100</f>
-        <v>0.91</v>
-      </c>
-    </row>
-    <row r="32" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F32" t="s">
-        <v>60</v>
-      </c>
-      <c r="H32" t="s">
-        <v>60</v>
-      </c>
-      <c r="I32" t="s">
-        <v>35</v>
-      </c>
-      <c r="J32" s="22">
-        <f>'feed pars'!C37/100</f>
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
-      <c r="M33" s="2"/>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="I34" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="J34" s="10">
-        <v>0</v>
-      </c>
-      <c r="K34" s="10"/>
-      <c r="L34" s="10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="G35" t="s">
-        <v>11</v>
-      </c>
-      <c r="I35" t="s">
-        <v>30</v>
-      </c>
-      <c r="J35" s="3">
-        <v>95</v>
-      </c>
-      <c r="K35" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="G36" t="s">
-        <v>12</v>
-      </c>
-      <c r="I36" t="s">
-        <v>30</v>
-      </c>
-      <c r="J36" s="3">
-        <v>95</v>
-      </c>
-      <c r="K36" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="G37" t="s">
-        <v>36</v>
-      </c>
-      <c r="I37" t="s">
-        <v>30</v>
-      </c>
-      <c r="J37" s="3">
-        <v>95</v>
-      </c>
-      <c r="K37" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
-      <c r="L38" s="2"/>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="I39" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="J39" s="10">
-        <v>0</v>
-      </c>
-      <c r="K39" s="10"/>
-      <c r="L39" s="10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="H40" t="s">
-        <v>39</v>
-      </c>
-      <c r="I40" t="s">
-        <v>34</v>
-      </c>
-      <c r="J40" s="3">
-        <v>20</v>
-      </c>
-      <c r="K40" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="G41" t="s">
-        <v>43</v>
-      </c>
-      <c r="I41" t="s">
-        <v>34</v>
-      </c>
-      <c r="J41" s="3">
-        <v>100</v>
-      </c>
-      <c r="K41" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="G42" t="s">
-        <v>46</v>
-      </c>
-      <c r="I42" t="s">
-        <v>34</v>
-      </c>
-      <c r="J42" s="3">
-        <v>100</v>
-      </c>
-      <c r="K42" t="s">
-        <v>31</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="J43" s="3"/>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="2"/>
-      <c r="K44" s="2"/>
-      <c r="L44" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="M44" s="2"/>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A45" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B45" s="7"/>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="6"/>
-      <c r="J45" s="6"/>
-      <c r="K45" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="L45" s="6"/>
-      <c r="M45" s="6"/>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>27</v>
-      </c>
-      <c r="B46" t="s">
-        <v>21</v>
-      </c>
-      <c r="E46" t="s">
-        <v>22</v>
-      </c>
-      <c r="F46" t="s">
-        <v>2</v>
-      </c>
-      <c r="I46" t="s">
-        <v>19</v>
-      </c>
-      <c r="J46" s="27">
-        <f>'feed pars'!K7*0.8+'feed pars'!K8*0.2</f>
-        <v>11.280000000000001</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>27</v>
-      </c>
-      <c r="F47" t="s">
-        <v>2</v>
-      </c>
-      <c r="I47" t="s">
-        <v>19</v>
-      </c>
-      <c r="J47" s="27">
-        <f>'feed pars'!K7*0.5+'feed pars'!K8*0.5</f>
-        <v>10.95</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>27</v>
-      </c>
-      <c r="F48" t="s">
-        <v>13</v>
-      </c>
-      <c r="I48" t="s">
-        <v>19</v>
-      </c>
-      <c r="J48" s="3">
-        <f>'feed pars'!K10</f>
-        <v>11.3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>27</v>
-      </c>
-      <c r="F49" t="s">
-        <v>36</v>
-      </c>
-      <c r="I49" t="s">
-        <v>19</v>
-      </c>
-      <c r="J49" s="27">
-        <f>'feed pars'!K11</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="J50" s="3"/>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>27</v>
-      </c>
-      <c r="F51" t="s">
+      <c r="I96" t="s">
         <v>18</v>
       </c>
-      <c r="I51" t="s">
-        <v>19</v>
-      </c>
-      <c r="J51">
-        <v>14.1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>27</v>
-      </c>
-      <c r="F52" t="s">
-        <v>40</v>
-      </c>
-      <c r="I52" t="s">
-        <v>19</v>
-      </c>
-      <c r="J52">
-        <v>13.2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>27</v>
-      </c>
-      <c r="F53" t="s">
-        <v>41</v>
-      </c>
-      <c r="I53" t="s">
-        <v>19</v>
-      </c>
-      <c r="J53">
-        <v>11.7</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>27</v>
-      </c>
-      <c r="F54" t="s">
-        <v>42</v>
-      </c>
-      <c r="I54" t="s">
-        <v>19</v>
-      </c>
-      <c r="J54" s="28">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>27</v>
-      </c>
-      <c r="F55" t="s">
-        <v>43</v>
-      </c>
-      <c r="I55" t="s">
-        <v>19</v>
-      </c>
-      <c r="J55">
-        <v>12.8</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>27</v>
-      </c>
-      <c r="F56" t="s">
-        <v>44</v>
-      </c>
-      <c r="I56" t="s">
-        <v>19</v>
-      </c>
-      <c r="J56">
-        <v>13.8</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>27</v>
-      </c>
-      <c r="F57" t="s">
-        <v>38</v>
-      </c>
-      <c r="I57" t="s">
-        <v>19</v>
-      </c>
-      <c r="J57">
-        <v>22.1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>27</v>
-      </c>
-      <c r="F58" t="s">
-        <v>46</v>
-      </c>
-      <c r="I58" t="s">
-        <v>19</v>
-      </c>
-      <c r="J58">
-        <v>20.100000000000001</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>27</v>
-      </c>
-      <c r="F59" t="s">
-        <v>308</v>
-      </c>
-      <c r="I59" t="s">
-        <v>19</v>
-      </c>
-      <c r="J59">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>27</v>
-      </c>
-      <c r="F60" t="s">
-        <v>47</v>
-      </c>
-      <c r="I60" t="s">
-        <v>19</v>
-      </c>
-      <c r="J60">
-        <v>14.6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>27</v>
-      </c>
-      <c r="F61" t="s">
-        <v>39</v>
-      </c>
-      <c r="I61" t="s">
-        <v>19</v>
-      </c>
-      <c r="J61">
-        <v>12.2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>27</v>
-      </c>
-      <c r="F62" t="s">
-        <v>49</v>
-      </c>
-      <c r="I62" t="s">
-        <v>19</v>
-      </c>
-      <c r="J62">
-        <v>11.4</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>27</v>
-      </c>
-      <c r="F63" t="s">
-        <v>50</v>
-      </c>
-      <c r="I63" t="s">
-        <v>19</v>
-      </c>
-      <c r="J63">
-        <v>13.4</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>27</v>
-      </c>
-      <c r="F64" t="s">
-        <v>51</v>
-      </c>
-      <c r="I64" t="s">
-        <v>19</v>
-      </c>
-      <c r="J64" s="28">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>27</v>
-      </c>
-      <c r="F65" t="s">
-        <v>53</v>
-      </c>
-      <c r="I65" t="s">
-        <v>19</v>
-      </c>
-      <c r="J65">
-        <v>13.3</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>27</v>
-      </c>
-      <c r="F66" t="s">
-        <v>55</v>
-      </c>
-      <c r="I66" t="s">
-        <v>19</v>
-      </c>
-      <c r="J66">
-        <v>12.4</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>27</v>
-      </c>
-      <c r="F67" t="s">
-        <v>56</v>
-      </c>
-      <c r="I67" t="s">
-        <v>19</v>
-      </c>
-      <c r="J67">
-        <v>12.3</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>27</v>
-      </c>
-      <c r="F68" t="s">
-        <v>57</v>
-      </c>
-      <c r="I68" t="s">
-        <v>19</v>
-      </c>
-      <c r="J68">
-        <v>13.6</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>27</v>
-      </c>
-      <c r="F69" t="s">
-        <v>59</v>
-      </c>
-      <c r="I69" t="s">
-        <v>19</v>
-      </c>
-      <c r="J69">
-        <v>15.5</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="J70" s="3"/>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="J71" s="3"/>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A72" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B72" s="8"/>
-      <c r="C72" s="9"/>
-      <c r="D72" s="9"/>
-      <c r="E72" s="9"/>
-      <c r="F72" s="9"/>
-      <c r="G72" s="9"/>
-      <c r="H72" s="9"/>
-      <c r="I72" s="9"/>
-      <c r="J72" s="9"/>
-      <c r="K72" s="9"/>
-      <c r="L72" s="9"/>
-      <c r="M72" s="9"/>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>28</v>
-      </c>
-      <c r="E73" t="s">
-        <v>302</v>
-      </c>
-      <c r="F73" t="s">
-        <v>18</v>
-      </c>
-      <c r="I73" t="s">
-        <v>19</v>
-      </c>
-      <c r="J73" s="23">
-        <f>'feed pars'!H13</f>
-        <v>12.3</v>
-      </c>
-      <c r="K73" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>28</v>
-      </c>
-      <c r="E74" t="s">
-        <v>302</v>
-      </c>
-      <c r="F74" t="s">
-        <v>40</v>
-      </c>
-      <c r="I74" t="s">
-        <v>19</v>
-      </c>
-      <c r="J74" s="23">
-        <f>'feed pars'!H14</f>
-        <v>11.2</v>
-      </c>
-      <c r="K74" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>28</v>
-      </c>
-      <c r="E75" t="s">
-        <v>302</v>
-      </c>
-      <c r="F75" t="s">
-        <v>41</v>
-      </c>
-      <c r="I75" t="s">
-        <v>19</v>
-      </c>
-      <c r="J75" s="23">
-        <f>'feed pars'!H15</f>
-        <v>9.4</v>
-      </c>
-      <c r="K75" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>28</v>
-      </c>
-      <c r="E76" t="s">
-        <v>302</v>
-      </c>
-      <c r="F76" t="s">
-        <v>42</v>
-      </c>
-      <c r="I76" t="s">
-        <v>19</v>
-      </c>
-      <c r="J76" s="23">
-        <f>'feed pars'!H16</f>
-        <v>12</v>
-      </c>
-      <c r="K76" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>28</v>
-      </c>
-      <c r="E77" t="s">
-        <v>302</v>
-      </c>
-      <c r="F77" t="s">
-        <v>43</v>
-      </c>
-      <c r="I77" t="s">
-        <v>19</v>
-      </c>
-      <c r="J77" s="23">
-        <f>'feed pars'!H17</f>
-        <v>13.2</v>
-      </c>
-      <c r="K77" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>28</v>
-      </c>
-      <c r="E78" t="s">
-        <v>302</v>
-      </c>
-      <c r="F78" t="s">
-        <v>44</v>
-      </c>
-      <c r="I78" t="s">
-        <v>19</v>
-      </c>
-      <c r="J78" s="23">
-        <f>'feed pars'!H18</f>
-        <v>11.5</v>
-      </c>
-      <c r="K78" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>28</v>
-      </c>
-      <c r="E79" t="s">
-        <v>302</v>
-      </c>
-      <c r="F79" t="s">
-        <v>45</v>
-      </c>
-      <c r="I79" t="s">
-        <v>19</v>
-      </c>
-      <c r="J79" s="23">
-        <f>'feed pars'!H19</f>
-        <v>10.9</v>
-      </c>
-      <c r="K79" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>28</v>
-      </c>
-      <c r="E80" t="s">
-        <v>302</v>
-      </c>
-      <c r="F80" t="s">
-        <v>38</v>
-      </c>
-      <c r="I80" t="s">
-        <v>19</v>
-      </c>
-      <c r="J80" s="23">
-        <f>'feed pars'!H20</f>
+      <c r="J96" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F96,'feed pars'!B$6:B$42,0))</f>
         <v>18.5</v>
       </c>
-      <c r="K80" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>28</v>
-      </c>
-      <c r="E81" t="s">
-        <v>302</v>
-      </c>
-      <c r="F81" t="s">
-        <v>46</v>
-      </c>
-      <c r="I81" t="s">
-        <v>19</v>
-      </c>
-      <c r="J81" s="23">
-        <f>'feed pars'!H21</f>
-        <v>17.5</v>
-      </c>
-      <c r="K81" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>28</v>
-      </c>
-      <c r="E82" t="s">
-        <v>302</v>
-      </c>
-      <c r="F82" t="s">
-        <v>47</v>
-      </c>
-      <c r="I82" t="s">
-        <v>19</v>
-      </c>
-      <c r="J82" s="23">
-        <f>'feed pars'!H23</f>
-        <v>9.9</v>
-      </c>
-      <c r="K82" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>28</v>
-      </c>
-      <c r="E83" t="s">
-        <v>302</v>
-      </c>
-      <c r="F83" t="s">
-        <v>48</v>
-      </c>
-      <c r="I83" t="s">
-        <v>19</v>
-      </c>
-      <c r="J83" s="23">
-        <f>'feed pars'!H24</f>
-        <v>10.3</v>
-      </c>
-      <c r="K83" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>28</v>
-      </c>
-      <c r="E84" t="s">
-        <v>302</v>
-      </c>
-      <c r="F84" t="s">
-        <v>39</v>
-      </c>
-      <c r="I84" t="s">
-        <v>19</v>
-      </c>
-      <c r="J84" s="23">
-        <f>'feed pars'!H25</f>
-        <v>7.7</v>
-      </c>
-      <c r="K84" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>28</v>
-      </c>
-      <c r="E85" t="s">
-        <v>302</v>
-      </c>
-      <c r="F85" t="s">
-        <v>49</v>
-      </c>
-      <c r="I85" t="s">
-        <v>19</v>
-      </c>
-      <c r="J85" s="23">
-        <f>'feed pars'!H26</f>
-        <v>6.5</v>
-      </c>
-      <c r="K85" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>28</v>
-      </c>
-      <c r="E86" t="s">
-        <v>302</v>
-      </c>
-      <c r="F86" t="s">
-        <v>50</v>
-      </c>
-      <c r="I86" t="s">
-        <v>19</v>
-      </c>
-      <c r="J86" s="23">
-        <f>'feed pars'!H27</f>
-        <v>6.2</v>
-      </c>
-      <c r="K86" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>28</v>
-      </c>
-      <c r="E87" t="s">
-        <v>302</v>
-      </c>
-      <c r="F87" t="s">
-        <v>51</v>
-      </c>
-      <c r="I87" t="s">
-        <v>19</v>
-      </c>
-      <c r="J87" s="23">
-        <f>'feed pars'!H28</f>
-        <v>7.8</v>
-      </c>
-      <c r="K87" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>28</v>
-      </c>
-      <c r="E88" t="s">
-        <v>302</v>
-      </c>
-      <c r="F88" t="s">
-        <v>52</v>
-      </c>
-      <c r="I88" t="s">
-        <v>19</v>
-      </c>
-      <c r="J88" s="23">
-        <f>'feed pars'!H29</f>
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="K88" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>28</v>
-      </c>
-      <c r="E89" t="s">
-        <v>302</v>
-      </c>
-      <c r="F89" t="s">
-        <v>53</v>
-      </c>
-      <c r="I89" t="s">
-        <v>19</v>
-      </c>
-      <c r="J89" s="23">
-        <f>'feed pars'!H30</f>
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="K89" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>28</v>
-      </c>
-      <c r="E90" t="s">
-        <v>302</v>
-      </c>
-      <c r="F90" t="s">
-        <v>54</v>
-      </c>
-      <c r="I90" t="s">
-        <v>19</v>
-      </c>
-      <c r="J90" s="23">
-        <f>'feed pars'!H31</f>
-        <v>8.9</v>
-      </c>
-      <c r="K90" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>28</v>
-      </c>
-      <c r="E91" t="s">
-        <v>302</v>
-      </c>
-      <c r="F91" t="s">
-        <v>55</v>
-      </c>
-      <c r="I91" t="s">
-        <v>19</v>
-      </c>
-      <c r="J91" s="23">
-        <f>'feed pars'!H32</f>
-        <v>9</v>
-      </c>
-      <c r="K91" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>28</v>
-      </c>
-      <c r="E92" t="s">
-        <v>302</v>
-      </c>
-      <c r="F92" t="s">
-        <v>56</v>
-      </c>
-      <c r="I92" t="s">
-        <v>19</v>
-      </c>
-      <c r="J92" s="23">
-        <f>'feed pars'!H33</f>
-        <v>8</v>
-      </c>
-      <c r="K92" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>28</v>
-      </c>
-      <c r="E93" t="s">
-        <v>302</v>
-      </c>
-      <c r="F93" t="s">
-        <v>57</v>
-      </c>
-      <c r="I93" t="s">
-        <v>19</v>
-      </c>
-      <c r="J93" s="23">
-        <f>'feed pars'!H34</f>
-        <v>12.2</v>
-      </c>
-      <c r="K93" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>28</v>
-      </c>
-      <c r="E94" t="s">
-        <v>302</v>
-      </c>
-      <c r="F94" t="s">
-        <v>58</v>
-      </c>
-      <c r="I94" t="s">
-        <v>19</v>
-      </c>
-      <c r="J94" s="23">
-        <f>'feed pars'!H35</f>
-        <v>12.2</v>
-      </c>
-      <c r="K94" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>28</v>
-      </c>
-      <c r="E95" t="s">
-        <v>302</v>
-      </c>
-      <c r="F95" t="s">
-        <v>59</v>
-      </c>
-      <c r="I95" t="s">
-        <v>19</v>
-      </c>
-      <c r="J95" s="23">
-        <f>'feed pars'!H36</f>
-        <v>11.3</v>
-      </c>
-      <c r="K95" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>28</v>
-      </c>
-      <c r="E96" t="s">
-        <v>302</v>
-      </c>
-      <c r="F96" t="s">
-        <v>60</v>
-      </c>
-      <c r="I96" t="s">
-        <v>19</v>
-      </c>
-      <c r="J96" s="23">
-        <f>'feed pars'!H37</f>
-        <v>10.8</v>
-      </c>
       <c r="K96" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="E97" t="s">
+        <v>299</v>
       </c>
       <c r="F97" t="s">
+        <v>43</v>
+      </c>
+      <c r="I97" t="s">
         <v>18</v>
       </c>
-      <c r="I97" t="s">
-        <v>19</v>
-      </c>
-      <c r="J97">
-        <f>'feed pars'!G13</f>
-        <v>12.1</v>
+      <c r="J97" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F97,'feed pars'!B$6:B$42,0))</f>
+        <v>17.5</v>
       </c>
       <c r="K97" t="s">
-        <v>25</v>
+        <v>300</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="E98" t="s">
+        <v>299</v>
       </c>
       <c r="F98" t="s">
-        <v>40</v>
+        <v>314</v>
       </c>
       <c r="I98" t="s">
-        <v>19</v>
-      </c>
-      <c r="J98">
-        <f>'feed pars'!G14</f>
-        <v>11</v>
+        <v>18</v>
+      </c>
+      <c r="J98" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F98,'feed pars'!B$6:B$42,0))</f>
+        <v>29.8</v>
       </c>
       <c r="K98" t="s">
-        <v>25</v>
+        <v>300</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="E99" t="s">
+        <v>299</v>
       </c>
       <c r="F99" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I99" t="s">
-        <v>19</v>
-      </c>
-      <c r="J99">
-        <f>'feed pars'!G15</f>
-        <v>9</v>
+        <v>18</v>
+      </c>
+      <c r="J99" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F99,'feed pars'!B$6:B$42,0))</f>
+        <v>9.9</v>
       </c>
       <c r="K99" t="s">
-        <v>25</v>
+        <v>300</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="E100" t="s">
+        <v>299</v>
       </c>
       <c r="F100" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I100" t="s">
-        <v>19</v>
-      </c>
-      <c r="J100">
-        <f>'feed pars'!G16</f>
-        <v>11.9</v>
+        <v>18</v>
+      </c>
+      <c r="J100" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F100,'feed pars'!B$6:B$42,0))</f>
+        <v>10.3</v>
       </c>
       <c r="K100" t="s">
-        <v>25</v>
+        <v>300</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="E101" t="s">
+        <v>299</v>
       </c>
       <c r="F101" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I101" t="s">
-        <v>19</v>
-      </c>
-      <c r="J101">
-        <f>'feed pars'!G17</f>
-        <v>12.8</v>
+        <v>18</v>
+      </c>
+      <c r="J101" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F101,'feed pars'!B$6:B$42,0))</f>
+        <v>7.7</v>
       </c>
       <c r="K101" t="s">
-        <v>25</v>
+        <v>300</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="E102" t="s">
+        <v>299</v>
       </c>
       <c r="F102" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I102" t="s">
-        <v>19</v>
-      </c>
-      <c r="J102">
-        <f>'feed pars'!G18</f>
-        <v>11.2</v>
+        <v>18</v>
+      </c>
+      <c r="J102" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F102,'feed pars'!B$6:B$42,0))</f>
+        <v>6.5</v>
       </c>
       <c r="K102" t="s">
-        <v>25</v>
+        <v>300</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="E103" t="s">
+        <v>299</v>
       </c>
       <c r="F103" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I103" t="s">
-        <v>19</v>
-      </c>
-      <c r="J103">
-        <f>'feed pars'!G19</f>
-        <v>10.7</v>
+        <v>18</v>
+      </c>
+      <c r="J103" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F103,'feed pars'!B$6:B$42,0))</f>
+        <v>6.2</v>
       </c>
       <c r="K103" t="s">
-        <v>25</v>
+        <v>300</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="E104" t="s">
+        <v>299</v>
       </c>
       <c r="F104" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="I104" t="s">
-        <v>19</v>
-      </c>
-      <c r="J104">
-        <f>'feed pars'!G20</f>
         <v>18</v>
       </c>
+      <c r="J104" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F104,'feed pars'!B$6:B$42,0))</f>
+        <v>7.8</v>
+      </c>
       <c r="K104" t="s">
-        <v>25</v>
+        <v>300</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="E105" t="s">
+        <v>299</v>
       </c>
       <c r="F105" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I105" t="s">
-        <v>19</v>
-      </c>
-      <c r="J105">
-        <f>'feed pars'!G21</f>
-        <v>17.3</v>
+        <v>18</v>
+      </c>
+      <c r="J105" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F105,'feed pars'!B$6:B$42,0))</f>
+        <v>9.1999999999999993</v>
       </c>
       <c r="K105" t="s">
-        <v>25</v>
+        <v>300</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="E106" t="s">
+        <v>299</v>
       </c>
       <c r="F106" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I106" t="s">
-        <v>19</v>
-      </c>
-      <c r="J106">
-        <f>'feed pars'!G23</f>
-        <v>9.3000000000000007</v>
+        <v>18</v>
+      </c>
+      <c r="J106" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F106,'feed pars'!B$6:B$42,0))</f>
+        <v>8.6999999999999993</v>
       </c>
       <c r="K106" t="s">
-        <v>25</v>
+        <v>300</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="E107" t="s">
+        <v>299</v>
       </c>
       <c r="F107" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I107" t="s">
-        <v>19</v>
-      </c>
-      <c r="J107">
-        <f>'feed pars'!G24</f>
-        <v>9.6999999999999993</v>
+        <v>18</v>
+      </c>
+      <c r="J107" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F107,'feed pars'!B$6:B$42,0))</f>
+        <v>8.9</v>
       </c>
       <c r="K107" t="s">
-        <v>25</v>
+        <v>300</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="E108" t="s">
+        <v>299</v>
       </c>
       <c r="F108" t="s">
-        <v>39</v>
+        <v>313</v>
       </c>
       <c r="I108" t="s">
-        <v>19</v>
-      </c>
-      <c r="J108">
-        <f>'feed pars'!G25</f>
-        <v>7.1</v>
+        <v>18</v>
+      </c>
+      <c r="J108" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F108,'feed pars'!B$6:B$42,0))</f>
+        <v>7.0888888888888877</v>
       </c>
       <c r="K108" t="s">
-        <v>25</v>
+        <v>300</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="E109" t="s">
+        <v>299</v>
       </c>
       <c r="F109" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="I109" t="s">
-        <v>19</v>
-      </c>
-      <c r="J109">
-        <f>'feed pars'!G26</f>
-        <v>5.9</v>
+        <v>18</v>
+      </c>
+      <c r="J109" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F109,'feed pars'!B$6:B$42,0))</f>
+        <v>9</v>
       </c>
       <c r="K109" t="s">
-        <v>25</v>
+        <v>300</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="E110" t="s">
+        <v>299</v>
       </c>
       <c r="F110" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I110" t="s">
-        <v>19</v>
-      </c>
-      <c r="J110">
-        <f>'feed pars'!G27</f>
-        <v>5.4</v>
+        <v>18</v>
+      </c>
+      <c r="J110" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F110,'feed pars'!B$6:B$42,0))</f>
+        <v>8</v>
       </c>
       <c r="K110" t="s">
-        <v>25</v>
+        <v>300</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="E111" t="s">
+        <v>299</v>
       </c>
       <c r="F111" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I111" t="s">
-        <v>19</v>
-      </c>
-      <c r="J111">
-        <f>'feed pars'!G28</f>
-        <v>7.2</v>
+        <v>18</v>
+      </c>
+      <c r="J111" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F111,'feed pars'!B$6:B$42,0))</f>
+        <v>12.2</v>
       </c>
       <c r="K111" t="s">
-        <v>25</v>
+        <v>300</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="E112" t="s">
+        <v>299</v>
       </c>
       <c r="F112" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I112" t="s">
-        <v>19</v>
-      </c>
-      <c r="J112">
-        <f>'feed pars'!G29</f>
-        <v>8.6999999999999993</v>
+        <v>18</v>
+      </c>
+      <c r="J112" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F112,'feed pars'!B$6:B$42,0))</f>
+        <v>12.2</v>
       </c>
       <c r="K112" t="s">
-        <v>25</v>
+        <v>300</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="E113" t="s">
+        <v>299</v>
       </c>
       <c r="F113" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I113" t="s">
-        <v>19</v>
-      </c>
-      <c r="J113">
-        <f>'feed pars'!G30</f>
-        <v>8.1</v>
+        <v>18</v>
+      </c>
+      <c r="J113" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F113,'feed pars'!B$6:B$42,0))</f>
+        <v>11.3</v>
       </c>
       <c r="K113" t="s">
-        <v>25</v>
+        <v>300</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="E114" t="s">
+        <v>299</v>
       </c>
       <c r="F114" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I114" t="s">
-        <v>19</v>
-      </c>
-      <c r="J114">
-        <f>'feed pars'!G31</f>
-        <v>8.1999999999999993</v>
+        <v>18</v>
+      </c>
+      <c r="J114" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F114,'feed pars'!B$6:B$42,0))</f>
+        <v>10.8</v>
       </c>
       <c r="K114" t="s">
-        <v>25</v>
+        <v>300</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>28</v>
-      </c>
-      <c r="F115" t="s">
-        <v>55</v>
-      </c>
-      <c r="I115" t="s">
-        <v>19</v>
-      </c>
-      <c r="J115">
-        <f>'feed pars'!G32</f>
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="K115" t="s">
-        <v>25</v>
-      </c>
+      <c r="J115" s="26"/>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F116" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="I116" t="s">
-        <v>19</v>
-      </c>
-      <c r="J116">
-        <f>'feed pars'!G33</f>
-        <v>6.9</v>
+        <v>18</v>
+      </c>
+      <c r="J116" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F116,'feed pars'!B$6:B$42,0))</f>
+        <v>12.1</v>
       </c>
       <c r="K116" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F117" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="I117" t="s">
-        <v>19</v>
-      </c>
-      <c r="J117">
-        <f>'feed pars'!G34</f>
-        <v>12.4</v>
+        <v>18</v>
+      </c>
+      <c r="J117" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F117,'feed pars'!B$6:B$42,0))</f>
+        <v>11</v>
       </c>
       <c r="K117" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F118" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="I118" t="s">
-        <v>19</v>
-      </c>
-      <c r="J118">
-        <f>'feed pars'!G35</f>
-        <v>12.4</v>
+        <v>18</v>
+      </c>
+      <c r="J118" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F118,'feed pars'!B$6:B$42,0))</f>
+        <v>9</v>
       </c>
       <c r="K118" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F119" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="I119" t="s">
-        <v>19</v>
-      </c>
-      <c r="J119">
-        <f>'feed pars'!G36</f>
-        <v>11.1</v>
+        <v>18</v>
+      </c>
+      <c r="J119" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F119,'feed pars'!B$6:B$42,0))</f>
+        <v>11.9</v>
       </c>
       <c r="K119" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F120" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I120" t="s">
-        <v>19</v>
-      </c>
-      <c r="J120">
-        <f>'feed pars'!G37</f>
+        <v>18</v>
+      </c>
+      <c r="J120" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F120,'feed pars'!B$6:B$42,0))</f>
+        <v>12.8</v>
+      </c>
+      <c r="K120" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>25</v>
+      </c>
+      <c r="F121" t="s">
+        <v>41</v>
+      </c>
+      <c r="I121" t="s">
+        <v>18</v>
+      </c>
+      <c r="J121" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F121,'feed pars'!B$6:B$42,0))</f>
+        <v>11.2</v>
+      </c>
+      <c r="K121" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>25</v>
+      </c>
+      <c r="F122" t="s">
+        <v>42</v>
+      </c>
+      <c r="I122" t="s">
+        <v>18</v>
+      </c>
+      <c r="J122" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F122,'feed pars'!B$6:B$42,0))</f>
+        <v>10.7</v>
+      </c>
+      <c r="K122" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>25</v>
+      </c>
+      <c r="F123" t="s">
+        <v>35</v>
+      </c>
+      <c r="I123" t="s">
+        <v>18</v>
+      </c>
+      <c r="J123" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F123,'feed pars'!B$6:B$42,0))</f>
+        <v>18</v>
+      </c>
+      <c r="K123" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>25</v>
+      </c>
+      <c r="F124" t="s">
+        <v>43</v>
+      </c>
+      <c r="I124" t="s">
+        <v>18</v>
+      </c>
+      <c r="J124" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F124,'feed pars'!B$6:B$42,0))</f>
+        <v>17.3</v>
+      </c>
+      <c r="K124" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>25</v>
+      </c>
+      <c r="F125" t="s">
+        <v>314</v>
+      </c>
+      <c r="I125" t="s">
+        <v>18</v>
+      </c>
+      <c r="J125" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F125,'feed pars'!B$6:B$42,0))</f>
+        <v>29.8</v>
+      </c>
+      <c r="K125" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>25</v>
+      </c>
+      <c r="F126" t="s">
+        <v>44</v>
+      </c>
+      <c r="I126" t="s">
+        <v>18</v>
+      </c>
+      <c r="J126" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F126,'feed pars'!B$6:B$42,0))</f>
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="K126" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>25</v>
+      </c>
+      <c r="F127" t="s">
+        <v>45</v>
+      </c>
+      <c r="I127" t="s">
+        <v>18</v>
+      </c>
+      <c r="J127" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F127,'feed pars'!B$6:B$42,0))</f>
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="K127" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>25</v>
+      </c>
+      <c r="F128" t="s">
+        <v>36</v>
+      </c>
+      <c r="I128" t="s">
+        <v>18</v>
+      </c>
+      <c r="J128" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F128,'feed pars'!B$6:B$42,0))</f>
+        <v>7.1</v>
+      </c>
+      <c r="K128" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>25</v>
+      </c>
+      <c r="F129" t="s">
+        <v>46</v>
+      </c>
+      <c r="I129" t="s">
+        <v>18</v>
+      </c>
+      <c r="J129" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F129,'feed pars'!B$6:B$42,0))</f>
+        <v>5.9</v>
+      </c>
+      <c r="K129" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>25</v>
+      </c>
+      <c r="F130" t="s">
+        <v>47</v>
+      </c>
+      <c r="I130" t="s">
+        <v>18</v>
+      </c>
+      <c r="J130" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F130,'feed pars'!B$6:B$42,0))</f>
+        <v>5.4</v>
+      </c>
+      <c r="K130" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>25</v>
+      </c>
+      <c r="F131" t="s">
+        <v>48</v>
+      </c>
+      <c r="I131" t="s">
+        <v>18</v>
+      </c>
+      <c r="J131" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F131,'feed pars'!B$6:B$42,0))</f>
+        <v>7.2</v>
+      </c>
+      <c r="K131" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>25</v>
+      </c>
+      <c r="F132" t="s">
+        <v>49</v>
+      </c>
+      <c r="I132" t="s">
+        <v>18</v>
+      </c>
+      <c r="J132" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F132,'feed pars'!B$6:B$42,0))</f>
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="K132" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>25</v>
+      </c>
+      <c r="F133" t="s">
+        <v>50</v>
+      </c>
+      <c r="I133" t="s">
+        <v>18</v>
+      </c>
+      <c r="J133" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F133,'feed pars'!B$6:B$42,0))</f>
+        <v>8.1</v>
+      </c>
+      <c r="K133" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>25</v>
+      </c>
+      <c r="F134" t="s">
+        <v>51</v>
+      </c>
+      <c r="I134" t="s">
+        <v>18</v>
+      </c>
+      <c r="J134" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F134,'feed pars'!B$6:B$42,0))</f>
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="K134" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>25</v>
+      </c>
+      <c r="F135" t="s">
+        <v>313</v>
+      </c>
+      <c r="I135" t="s">
+        <v>18</v>
+      </c>
+      <c r="J135" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F135,'feed pars'!B$6:B$42,0))</f>
+        <v>6.6</v>
+      </c>
+      <c r="K135" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>25</v>
+      </c>
+      <c r="F136" t="s">
+        <v>52</v>
+      </c>
+      <c r="I136" t="s">
+        <v>18</v>
+      </c>
+      <c r="J136" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F136,'feed pars'!B$6:B$42,0))</f>
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="K136" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>25</v>
+      </c>
+      <c r="F137" t="s">
+        <v>53</v>
+      </c>
+      <c r="I137" t="s">
+        <v>18</v>
+      </c>
+      <c r="J137" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F137,'feed pars'!B$6:B$42,0))</f>
+        <v>6.9</v>
+      </c>
+      <c r="K137" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>25</v>
+      </c>
+      <c r="F138" t="s">
+        <v>54</v>
+      </c>
+      <c r="I138" t="s">
+        <v>18</v>
+      </c>
+      <c r="J138" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F138,'feed pars'!B$6:B$42,0))</f>
+        <v>12.4</v>
+      </c>
+      <c r="K138" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>25</v>
+      </c>
+      <c r="F139" t="s">
+        <v>55</v>
+      </c>
+      <c r="I139" t="s">
+        <v>18</v>
+      </c>
+      <c r="J139" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F139,'feed pars'!B$6:B$42,0))</f>
+        <v>12.4</v>
+      </c>
+      <c r="K139" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>25</v>
+      </c>
+      <c r="F140" t="s">
+        <v>56</v>
+      </c>
+      <c r="I140" t="s">
+        <v>18</v>
+      </c>
+      <c r="J140" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F140,'feed pars'!B$6:B$42,0))</f>
+        <v>11.1</v>
+      </c>
+      <c r="K140" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>25</v>
+      </c>
+      <c r="F141" t="s">
+        <v>57</v>
+      </c>
+      <c r="I141" t="s">
+        <v>18</v>
+      </c>
+      <c r="J141" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F141,'feed pars'!B$6:B$42,0))</f>
         <v>10.8</v>
       </c>
-      <c r="K120" t="s">
-        <v>25</v>
+      <c r="K141" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -3460,38 +3828,38 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:L37"/>
+  <dimension ref="B1:N42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="7.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D1" s="11"/>
       <c r="E1" s="11"/>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C3" s="4" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C4" s="4"/>
       <c r="E4" s="4" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F4" s="4">
         <v>1</v>
@@ -3502,111 +3870,118 @@
       <c r="H4" s="4">
         <v>3</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="J4" s="4">
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="L4" s="4">
         <v>1</v>
       </c>
-      <c r="K4" s="4">
+      <c r="M4" s="4">
         <v>2</v>
       </c>
-      <c r="L4" s="4"/>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="N4" s="4"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>62</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
       <c r="K5" s="4" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>2</v>
+        <v>310</v>
       </c>
       <c r="C6">
         <v>100</v>
       </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B7" s="26" t="s">
-        <v>313</v>
+      <c r="M6" s="27">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>311</v>
       </c>
       <c r="C7">
         <v>100</v>
       </c>
-      <c r="K7">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B8" s="26" t="s">
-        <v>314</v>
+      <c r="M7" s="27">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>312</v>
       </c>
       <c r="C8">
         <v>100</v>
       </c>
-      <c r="K8">
-        <v>10.4</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M8" s="25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9">
         <v>100</v>
       </c>
-      <c r="K9">
+      <c r="M9" s="27">
         <v>9.1</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10">
         <v>100</v>
       </c>
-      <c r="I10" s="4"/>
-      <c r="K10">
+      <c r="K10" s="4"/>
+      <c r="M10" s="27">
         <v>11.3</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C11">
         <v>100</v>
       </c>
-      <c r="K11">
+      <c r="M11" s="27">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="E12" s="4"/>
@@ -3616,13 +3991,15 @@
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="L12" s="4"/>
+      <c r="M12" s="28"/>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="24">
-        <f>AVERAGE(F13,J13)</f>
+        <v>17</v>
+      </c>
+      <c r="C13" s="23">
+        <f>AVERAGE(F13,L13)</f>
         <v>87</v>
       </c>
       <c r="D13" s="4"/>
@@ -3642,25 +4019,25 @@
         <f>INDEX(pigs!$D$3:$AO$60,$E13,H$4)</f>
         <v>12.3</v>
       </c>
-      <c r="I13" s="4">
+      <c r="K13" s="4">
         <f>MATCH($B13,cattle!$A$3:$A$120,0)</f>
         <v>112</v>
       </c>
-      <c r="J13">
-        <f>INDEX(cattle!$D$3:$AH$120,$I13,J$4)</f>
+      <c r="L13">
+        <f>INDEX(cattle!$D$3:$AH$120,$K13,L$4)</f>
         <v>87</v>
       </c>
-      <c r="K13">
-        <f>INDEX(cattle!$D$3:$AH$120,$I13,K$4)</f>
+      <c r="M13" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$K13,M$4)</f>
         <v>14.1</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="24">
-        <f t="shared" ref="C14:C37" si="0">AVERAGE(F14,J14)</f>
+        <v>37</v>
+      </c>
+      <c r="C14" s="23">
+        <f t="shared" ref="C14:C42" si="0">AVERAGE(F14,L14)</f>
         <v>87</v>
       </c>
       <c r="D14" s="4"/>
@@ -3680,24 +4057,24 @@
         <f>INDEX(pigs!$D$3:$AO$60,$E14,H$4)</f>
         <v>11.2</v>
       </c>
-      <c r="I14" s="4">
+      <c r="K14" s="4">
         <f>MATCH($B14,cattle!$A$3:$A$120,0)</f>
         <v>42</v>
       </c>
-      <c r="J14">
-        <f>INDEX(cattle!$D$3:$AH$120,$I14,J$4)</f>
+      <c r="L14">
+        <f>INDEX(cattle!$D$3:$AH$120,$K14,L$4)</f>
         <v>87</v>
       </c>
-      <c r="K14">
-        <f>INDEX(cattle!$D$3:$AH$120,$I14,K$4)</f>
+      <c r="M14" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$K14,M$4)</f>
         <v>13.2</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="24">
+        <v>38</v>
+      </c>
+      <c r="C15" s="23">
         <f t="shared" si="0"/>
         <v>86</v>
       </c>
@@ -3718,24 +4095,24 @@
         <f>INDEX(pigs!$D$3:$AO$60,$E15,H$4)</f>
         <v>9.4</v>
       </c>
-      <c r="I15" s="4">
+      <c r="K15" s="4">
         <f>MATCH($B15,cattle!$A$3:$A$120,0)</f>
         <v>28</v>
       </c>
-      <c r="J15">
-        <f>INDEX(cattle!$D$3:$AH$120,$I15,J$4)</f>
+      <c r="L15">
+        <f>INDEX(cattle!$D$3:$AH$120,$K15,L$4)</f>
         <v>85</v>
       </c>
-      <c r="K15">
-        <f>INDEX(cattle!$D$3:$AH$120,$I15,K$4)</f>
+      <c r="M15" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$K15,M$4)</f>
         <v>11.7</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="24">
+        <v>39</v>
+      </c>
+      <c r="C16" s="23">
         <f t="shared" si="0"/>
         <v>87</v>
       </c>
@@ -3756,69 +4133,57 @@
         <f>INDEX(pigs!$D$3:$AO$60,$E16,H$4)</f>
         <v>12</v>
       </c>
-      <c r="I16" s="4">
+      <c r="K16" s="4">
         <f>MATCH($B16,cattle!$A$3:$A$120,0)</f>
         <v>78</v>
       </c>
-      <c r="J16">
-        <f>INDEX(cattle!$D$3:$AH$120,$I16,J$4)</f>
+      <c r="L16">
+        <f>INDEX(cattle!$D$3:$AH$120,$K16,L$4)</f>
         <v>87</v>
       </c>
-      <c r="K16">
-        <f>INDEX(cattle!$D$3:$AH$120,$I16,K$4)</f>
+      <c r="M16" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$K16,M$4)</f>
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" s="24">
+        <v>317</v>
+      </c>
+      <c r="C17" s="23">
         <f t="shared" si="0"/>
-        <v>67.5</v>
+        <v>87</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4">
         <f>MATCH($B17,pigs!$A$3:$A$60,0)</f>
-        <v>19</v>
-      </c>
-      <c r="F17">
-        <f>INDEX(pigs!$D$3:$AO$60,$E17,F$4)</f>
+        <v>38</v>
+      </c>
+      <c r="K17" s="4">
+        <f>MATCH($B17,cattle!$A$3:$A$120,0)</f>
+        <v>77</v>
+      </c>
+      <c r="L17">
+        <f>INDEX(cattle!$D$3:$AH$120,$K17,L$4)</f>
         <v>87</v>
       </c>
-      <c r="G17">
-        <f>INDEX(pigs!$D$3:$AO$60,$E17,G$4)</f>
-        <v>12.8</v>
-      </c>
-      <c r="H17">
-        <f>INDEX(pigs!$D$3:$AO$60,$E17,H$4)</f>
-        <v>13.2</v>
-      </c>
-      <c r="I17" s="4">
-        <f>MATCH($B17,cattle!$A$3:$A$120,0)</f>
-        <v>53</v>
-      </c>
-      <c r="J17">
-        <f>INDEX(cattle!$D$3:$AH$120,$I17,J$4)</f>
-        <v>48</v>
-      </c>
-      <c r="K17">
-        <f>INDEX(cattle!$D$3:$AH$120,$I17,K$4)</f>
-        <v>12.8</v>
-      </c>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="M17" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$K17,M$4)</f>
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="24">
+        <v>40</v>
+      </c>
+      <c r="C18" s="23">
         <f t="shared" si="0"/>
-        <v>87</v>
+        <v>67.5</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4">
         <f>MATCH($B18,pigs!$A$3:$A$60,0)</f>
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="F18">
         <f>INDEX(pigs!$D$3:$AO$60,$E18,F$4)</f>
@@ -3826,37 +4191,37 @@
       </c>
       <c r="G18">
         <f>INDEX(pigs!$D$3:$AO$60,$E18,G$4)</f>
-        <v>11.2</v>
+        <v>12.8</v>
       </c>
       <c r="H18">
         <f>INDEX(pigs!$D$3:$AO$60,$E18,H$4)</f>
-        <v>11.5</v>
-      </c>
-      <c r="I18" s="4">
+        <v>13.2</v>
+      </c>
+      <c r="K18" s="4">
         <f>MATCH($B18,cattle!$A$3:$A$120,0)</f>
-        <v>115</v>
-      </c>
-      <c r="J18">
-        <f>INDEX(cattle!$D$3:$AH$120,$I18,J$4)</f>
-        <v>87</v>
-      </c>
-      <c r="K18">
-        <f>INDEX(cattle!$D$3:$AH$120,$I18,K$4)</f>
-        <v>13.8</v>
-      </c>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="L18">
+        <f>INDEX(cattle!$D$3:$AH$120,$K18,L$4)</f>
+        <v>48</v>
+      </c>
+      <c r="M18" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$K18,M$4)</f>
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>45</v>
-      </c>
-      <c r="C19" s="24">
+        <v>41</v>
+      </c>
+      <c r="C19" s="23">
         <f t="shared" si="0"/>
         <v>87</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4">
         <f>MATCH($B19,pigs!$A$3:$A$60,0)</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F19">
         <f>INDEX(pigs!$D$3:$AO$60,$E19,F$4)</f>
@@ -3864,637 +4229,803 @@
       </c>
       <c r="G19">
         <f>INDEX(pigs!$D$3:$AO$60,$E19,G$4)</f>
-        <v>10.7</v>
+        <v>11.2</v>
       </c>
       <c r="H19">
         <f>INDEX(pigs!$D$3:$AO$60,$E19,H$4)</f>
-        <v>10.9</v>
-      </c>
-      <c r="I19" s="4"/>
-    </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+        <v>11.5</v>
+      </c>
+      <c r="K19" s="4">
+        <f>MATCH($B19,cattle!$A$3:$A$120,0)</f>
+        <v>115</v>
+      </c>
+      <c r="L19">
+        <f>INDEX(cattle!$D$3:$AH$120,$K19,L$4)</f>
+        <v>87</v>
+      </c>
+      <c r="M19" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$K19,M$4)</f>
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="24">
+        <v>42</v>
+      </c>
+      <c r="C20" s="23">
         <f t="shared" si="0"/>
-        <v>92.5</v>
+        <v>86.8</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4">
         <f>MATCH($B20,pigs!$A$3:$A$60,0)</f>
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="F20">
         <f>INDEX(pigs!$D$3:$AO$60,$E20,F$4)</f>
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="G20">
         <f>INDEX(pigs!$D$3:$AO$60,$E20,G$4)</f>
-        <v>18</v>
+        <v>10.7</v>
       </c>
       <c r="H20">
         <f>INDEX(pigs!$D$3:$AO$60,$E20,H$4)</f>
-        <v>18.5</v>
-      </c>
-      <c r="I20" s="4">
-        <f>MATCH($B20,cattle!$A$3:$A$120,0)</f>
-        <v>71</v>
-      </c>
-      <c r="J20">
-        <f>INDEX(cattle!$D$3:$AH$120,$I20,J$4)</f>
-        <v>93</v>
-      </c>
-      <c r="K20">
-        <f>INDEX(cattle!$D$3:$AH$120,$I20,K$4)</f>
-        <v>22.1</v>
-      </c>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+        <v>10.9</v>
+      </c>
+      <c r="K20" s="4"/>
+      <c r="L20">
+        <v>86.6</v>
+      </c>
+      <c r="M20" s="27">
+        <v>13.3</v>
+      </c>
+      <c r="N20" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>46</v>
-      </c>
-      <c r="C21" s="24">
+        <v>35</v>
+      </c>
+      <c r="C21" s="23">
         <f t="shared" si="0"/>
-        <v>92</v>
+        <v>92.5</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4">
         <f>MATCH($B21,pigs!$A$3:$A$60,0)</f>
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F21">
         <f>INDEX(pigs!$D$3:$AO$60,$E21,F$4)</f>
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G21">
         <f>INDEX(pigs!$D$3:$AO$60,$E21,G$4)</f>
-        <v>17.3</v>
+        <v>18</v>
       </c>
       <c r="H21">
         <f>INDEX(pigs!$D$3:$AO$60,$E21,H$4)</f>
+        <v>18.5</v>
+      </c>
+      <c r="K21" s="4">
+        <f>MATCH($B21,cattle!$A$3:$A$120,0)</f>
+        <v>71</v>
+      </c>
+      <c r="L21">
+        <f>INDEX(cattle!$D$3:$AH$120,$K21,L$4)</f>
+        <v>93</v>
+      </c>
+      <c r="M21" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$K21,M$4)</f>
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="23">
+        <f t="shared" si="0"/>
+        <v>92</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4">
+        <f>MATCH($B22,pigs!$A$3:$A$60,0)</f>
+        <v>14</v>
+      </c>
+      <c r="F22">
+        <f>INDEX(pigs!$D$3:$AO$60,$E22,F$4)</f>
+        <v>91</v>
+      </c>
+      <c r="G22">
+        <f>INDEX(pigs!$D$3:$AO$60,$E22,G$4)</f>
+        <v>17.3</v>
+      </c>
+      <c r="H22">
+        <f>INDEX(pigs!$D$3:$AO$60,$E22,H$4)</f>
         <v>17.5</v>
       </c>
-      <c r="I21" s="4">
-        <f>MATCH($B21,cattle!$A$3:$A$120,0)</f>
+      <c r="K22" s="4">
+        <f>MATCH($B22,cattle!$A$3:$A$120,0)</f>
         <v>45</v>
       </c>
-      <c r="J21">
-        <f>INDEX(cattle!$D$3:$AH$120,$I21,J$4)</f>
+      <c r="L22">
+        <f>INDEX(cattle!$D$3:$AH$120,$K22,L$4)</f>
         <v>93</v>
       </c>
-      <c r="K21">
-        <f>INDEX(cattle!$D$3:$AH$120,$I21,K$4)</f>
+      <c r="M22" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$K22,M$4)</f>
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>308</v>
-      </c>
-      <c r="C22" s="24">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>314</v>
+      </c>
+      <c r="C23" s="23">
         <f t="shared" si="0"/>
-        <v>85</v>
-      </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22">
-        <v>85</v>
-      </c>
-      <c r="I22" s="4">
-        <f>MATCH($B22,cattle!$A$3:$A$120,0)</f>
-        <v>22</v>
-      </c>
-      <c r="J22">
-        <f>INDEX(cattle!$D$3:$AH$120,$I22,J$4)</f>
-        <v>85</v>
-      </c>
-      <c r="K22">
-        <f>INDEX(cattle!$D$3:$AH$120,$I22,K$4)</f>
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
-        <v>47</v>
-      </c>
-      <c r="C23" s="24">
-        <f t="shared" si="0"/>
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4">
         <f>MATCH($B23,pigs!$A$3:$A$60,0)</f>
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="F23">
         <f>INDEX(pigs!$D$3:$AO$60,$E23,F$4)</f>
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="G23">
         <f>INDEX(pigs!$D$3:$AO$60,$E23,G$4)</f>
-        <v>9.3000000000000007</v>
+        <v>29.8</v>
       </c>
       <c r="H23">
         <f>INDEX(pigs!$D$3:$AO$60,$E23,H$4)</f>
-        <v>9.9</v>
-      </c>
-      <c r="I23" s="4">
-        <f>MATCH($B23,cattle!$A$3:$A$120,0)</f>
-        <v>93</v>
-      </c>
-      <c r="J23">
-        <f>INDEX(cattle!$D$3:$AH$120,$I23,J$4)</f>
-        <v>87</v>
-      </c>
-      <c r="K23">
-        <f>INDEX(cattle!$D$3:$AH$120,$I23,K$4)</f>
-        <v>14.6</v>
-      </c>
-    </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
+        <v>29.8</v>
+      </c>
+      <c r="K23" s="4"/>
+      <c r="L23">
+        <v>100</v>
+      </c>
+      <c r="M23" s="27">
+        <v>36.6</v>
+      </c>
+      <c r="N23" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" s="24">
+        <v>305</v>
+      </c>
+      <c r="C24" s="23">
+        <f t="shared" si="0"/>
+        <v>85</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="K24" s="4">
+        <f>MATCH($B24,cattle!$A$3:$A$120,0)</f>
+        <v>22</v>
+      </c>
+      <c r="L24">
+        <f>INDEX(cattle!$D$3:$AH$120,$K24,L$4)</f>
+        <v>85</v>
+      </c>
+      <c r="M24" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$K24,M$4)</f>
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>318</v>
+      </c>
+      <c r="C25" s="23">
         <f t="shared" si="0"/>
         <v>87</v>
       </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4">
-        <f>MATCH($B24,pigs!$A$3:$A$60,0)</f>
-        <v>45</v>
-      </c>
-      <c r="F24">
-        <f>INDEX(pigs!$D$3:$AO$60,$E24,F$4)</f>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="K25" s="4">
+        <f>MATCH($B25,cattle!$A$3:$A$120,0)</f>
+        <v>92</v>
+      </c>
+      <c r="L25">
+        <f>INDEX(cattle!$D$3:$AH$120,$K25,L$4)</f>
         <v>87</v>
       </c>
-      <c r="G24">
-        <f>INDEX(pigs!$D$3:$AO$60,$E24,G$4)</f>
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="H24">
-        <f>INDEX(pigs!$D$3:$AO$60,$E24,H$4)</f>
-        <v>10.3</v>
-      </c>
-      <c r="I24" s="4"/>
-    </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B25" t="s">
-        <v>39</v>
-      </c>
-      <c r="C25" s="24">
+      <c r="M25" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$K25,M$4)</f>
+        <v>16.399999999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="23">
         <f t="shared" si="0"/>
-        <v>89.5</v>
-      </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4">
-        <f>MATCH($B25,pigs!$A$3:$A$60,0)</f>
-        <v>36</v>
-      </c>
-      <c r="F25">
-        <f>INDEX(pigs!$D$3:$AO$60,$E25,F$4)</f>
-        <v>89</v>
-      </c>
-      <c r="G25">
-        <f>INDEX(pigs!$D$3:$AO$60,$E25,G$4)</f>
-        <v>7.1</v>
-      </c>
-      <c r="H25">
-        <f>INDEX(pigs!$D$3:$AO$60,$E25,H$4)</f>
-        <v>7.7</v>
-      </c>
-      <c r="I25" s="4">
-        <f>MATCH($B25,cattle!$A$3:$A$120,0)</f>
-        <v>70</v>
-      </c>
-      <c r="J25">
-        <f>INDEX(cattle!$D$3:$AH$120,$I25,J$4)</f>
-        <v>90</v>
-      </c>
-      <c r="K25">
-        <f>INDEX(cattle!$D$3:$AH$120,$I25,K$4)</f>
-        <v>12.2</v>
-      </c>
-    </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C26" s="24">
-        <f t="shared" si="0"/>
-        <v>91</v>
+        <v>87.5</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4">
         <f>MATCH($B26,pigs!$A$3:$A$60,0)</f>
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F26">
         <f>INDEX(pigs!$D$3:$AO$60,$E26,F$4)</f>
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G26">
         <f>INDEX(pigs!$D$3:$AO$60,$E26,G$4)</f>
-        <v>5.9</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="H26">
         <f>INDEX(pigs!$D$3:$AO$60,$E26,H$4)</f>
-        <v>6.5</v>
-      </c>
-      <c r="I26" s="4">
+        <v>9.9</v>
+      </c>
+      <c r="K26" s="4">
         <f>MATCH($B26,cattle!$A$3:$A$120,0)</f>
-        <v>99</v>
-      </c>
-      <c r="J26">
-        <f>INDEX(cattle!$D$3:$AH$120,$I26,J$4)</f>
-        <v>92</v>
-      </c>
-      <c r="K26">
-        <f>INDEX(cattle!$D$3:$AH$120,$I26,K$4)</f>
-        <v>11.4</v>
-      </c>
-    </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+      <c r="L26">
+        <f>INDEX(cattle!$D$3:$AH$120,$K26,L$4)</f>
+        <v>87</v>
+      </c>
+      <c r="M26" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$K26,M$4)</f>
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>50</v>
-      </c>
-      <c r="C27" s="24">
+        <v>45</v>
+      </c>
+      <c r="C27" s="23">
         <f t="shared" si="0"/>
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4">
         <f>MATCH($B27,pigs!$A$3:$A$60,0)</f>
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F27">
         <f>INDEX(pigs!$D$3:$AO$60,$E27,F$4)</f>
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G27">
         <f>INDEX(pigs!$D$3:$AO$60,$E27,G$4)</f>
-        <v>5.4</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="H27">
         <f>INDEX(pigs!$D$3:$AO$60,$E27,H$4)</f>
-        <v>6.2</v>
-      </c>
-      <c r="I27" s="4">
-        <f>MATCH($B27,cattle!$A$3:$A$120,0)</f>
-        <v>60</v>
-      </c>
-      <c r="J27">
-        <f>INDEX(cattle!$D$3:$AH$120,$I27,J$4)</f>
-        <v>91</v>
-      </c>
-      <c r="K27">
-        <f>INDEX(cattle!$D$3:$AH$120,$I27,K$4)</f>
-        <v>13.4</v>
-      </c>
-    </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
+        <v>10.3</v>
+      </c>
+      <c r="K27" s="4"/>
+      <c r="M27" s="27"/>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>51</v>
-      </c>
-      <c r="C28" s="24">
+        <v>36</v>
+      </c>
+      <c r="C28" s="23">
         <f t="shared" si="0"/>
-        <v>87</v>
+        <v>89.5</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4">
         <f>MATCH($B28,pigs!$A$3:$A$60,0)</f>
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="F28">
         <f>INDEX(pigs!$D$3:$AO$60,$E28,F$4)</f>
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G28">
         <f>INDEX(pigs!$D$3:$AO$60,$E28,G$4)</f>
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="H28">
         <f>INDEX(pigs!$D$3:$AO$60,$E28,H$4)</f>
-        <v>7.8</v>
-      </c>
-      <c r="I28" s="4">
+        <v>7.7</v>
+      </c>
+      <c r="K28" s="4">
         <f>MATCH($B28,cattle!$A$3:$A$120,0)</f>
-        <v>111</v>
-      </c>
-      <c r="J28">
-        <f>INDEX(cattle!$D$3:$AH$120,$I28,J$4)</f>
-        <v>87</v>
-      </c>
-      <c r="K28">
-        <f>INDEX(cattle!$D$3:$AH$120,$I28,K$4)</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="L28">
+        <f>INDEX(cattle!$D$3:$AH$120,$K28,L$4)</f>
+        <v>90</v>
+      </c>
+      <c r="M28" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$K28,M$4)</f>
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>52</v>
-      </c>
-      <c r="C29" s="24">
+        <v>46</v>
+      </c>
+      <c r="C29" s="23">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4">
         <f>MATCH($B29,pigs!$A$3:$A$60,0)</f>
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="F29">
         <f>INDEX(pigs!$D$3:$AO$60,$E29,F$4)</f>
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G29">
         <f>INDEX(pigs!$D$3:$AO$60,$E29,G$4)</f>
-        <v>8.6999999999999993</v>
+        <v>5.9</v>
       </c>
       <c r="H29">
         <f>INDEX(pigs!$D$3:$AO$60,$E29,H$4)</f>
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="I29" s="4"/>
-    </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
+        <v>6.5</v>
+      </c>
+      <c r="K29" s="4">
+        <f>MATCH($B29,cattle!$A$3:$A$120,0)</f>
+        <v>99</v>
+      </c>
+      <c r="L29">
+        <f>INDEX(cattle!$D$3:$AH$120,$K29,L$4)</f>
+        <v>92</v>
+      </c>
+      <c r="M29" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$K29,M$4)</f>
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>53</v>
-      </c>
-      <c r="C30" s="24">
+        <v>47</v>
+      </c>
+      <c r="C30" s="23">
         <f t="shared" si="0"/>
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4">
         <f>MATCH($B30,pigs!$A$3:$A$60,0)</f>
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="F30">
         <f>INDEX(pigs!$D$3:$AO$60,$E30,F$4)</f>
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G30">
         <f>INDEX(pigs!$D$3:$AO$60,$E30,G$4)</f>
-        <v>8.1</v>
+        <v>5.4</v>
       </c>
       <c r="H30">
         <f>INDEX(pigs!$D$3:$AO$60,$E30,H$4)</f>
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="I30" s="4">
+        <v>6.2</v>
+      </c>
+      <c r="K30" s="4">
         <f>MATCH($B30,cattle!$A$3:$A$120,0)</f>
-        <v>109</v>
-      </c>
-      <c r="J30">
-        <f>INDEX(cattle!$D$3:$AH$120,$I30,J$4)</f>
+        <v>60</v>
+      </c>
+      <c r="L30">
+        <f>INDEX(cattle!$D$3:$AH$120,$K30,L$4)</f>
+        <v>91</v>
+      </c>
+      <c r="M30" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$K30,M$4)</f>
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>319</v>
+      </c>
+      <c r="C31" s="23">
+        <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="K30">
-        <f>INDEX(cattle!$D$3:$AH$120,$I30,K$4)</f>
-        <v>13.3</v>
-      </c>
-    </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B31" t="s">
-        <v>54</v>
-      </c>
-      <c r="C31" s="24">
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="K31" s="4"/>
+      <c r="L31">
+        <v>90</v>
+      </c>
+      <c r="M31" s="27">
+        <v>8.5</v>
+      </c>
+      <c r="N31" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32" s="23">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4">
-        <f>MATCH($B31,pigs!$A$3:$A$60,0)</f>
-        <v>1</v>
-      </c>
-      <c r="F31">
-        <f>INDEX(pigs!$D$3:$AO$60,$E31,F$4)</f>
-        <v>11</v>
-      </c>
-      <c r="G31">
-        <f>INDEX(pigs!$D$3:$AO$60,$E31,G$4)</f>
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="H31">
-        <f>INDEX(pigs!$D$3:$AO$60,$E31,H$4)</f>
-        <v>8.9</v>
-      </c>
-      <c r="I31" s="4"/>
-    </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
-        <v>55</v>
-      </c>
-      <c r="C32" s="24">
-        <f t="shared" si="0"/>
-        <v>75.5</v>
+        <v>87</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4">
         <f>MATCH($B32,pigs!$A$3:$A$60,0)</f>
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="F32">
         <f>INDEX(pigs!$D$3:$AO$60,$E32,F$4)</f>
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G32">
         <f>INDEX(pigs!$D$3:$AO$60,$E32,G$4)</f>
-        <v>8.6999999999999993</v>
+        <v>7.2</v>
       </c>
       <c r="H32">
         <f>INDEX(pigs!$D$3:$AO$60,$E32,H$4)</f>
-        <v>9</v>
-      </c>
-      <c r="I32" s="4">
+        <v>7.8</v>
+      </c>
+      <c r="K32" s="4">
         <f>MATCH($B32,cattle!$A$3:$A$120,0)</f>
+        <v>111</v>
+      </c>
+      <c r="L32">
+        <f>INDEX(cattle!$D$3:$AH$120,$K32,L$4)</f>
+        <v>87</v>
+      </c>
+      <c r="M32" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$K32,M$4)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>49</v>
+      </c>
+      <c r="C33" s="23">
+        <f t="shared" si="0"/>
         <v>88</v>
-      </c>
-      <c r="J32">
-        <f>INDEX(cattle!$D$3:$AH$120,$I32,J$4)</f>
-        <v>75</v>
-      </c>
-      <c r="K32">
-        <f>INDEX(cattle!$D$3:$AH$120,$I32,K$4)</f>
-        <v>12.4</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B33" t="s">
-        <v>56</v>
-      </c>
-      <c r="C33" s="24">
-        <f t="shared" si="0"/>
-        <v>89.5</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4">
         <f>MATCH($B33,pigs!$A$3:$A$60,0)</f>
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="F33">
         <f>INDEX(pigs!$D$3:$AO$60,$E33,F$4)</f>
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G33">
         <f>INDEX(pigs!$D$3:$AO$60,$E33,G$4)</f>
-        <v>6.9</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="H33">
         <f>INDEX(pigs!$D$3:$AO$60,$E33,H$4)</f>
-        <v>8</v>
-      </c>
-      <c r="I33" s="4">
-        <f>MATCH($B33,cattle!$A$3:$A$120,0)</f>
-        <v>91</v>
-      </c>
-      <c r="J33">
-        <f>INDEX(cattle!$D$3:$AH$120,$I33,J$4)</f>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="K33" s="4"/>
+      <c r="M33" s="27"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>50</v>
+      </c>
+      <c r="C34" s="23">
+        <f t="shared" si="0"/>
         <v>90</v>
-      </c>
-      <c r="K33">
-        <f>INDEX(cattle!$D$3:$AH$120,$I33,K$4)</f>
-        <v>12.3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B34" t="s">
-        <v>57</v>
-      </c>
-      <c r="C34" s="24">
-        <f t="shared" si="0"/>
-        <v>6.25</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4">
         <f>MATCH($B34,pigs!$A$3:$A$60,0)</f>
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="F34">
         <f>INDEX(pigs!$D$3:$AO$60,$E34,F$4)</f>
-        <v>5.5</v>
+        <v>90</v>
       </c>
       <c r="G34">
         <f>INDEX(pigs!$D$3:$AO$60,$E34,G$4)</f>
-        <v>12.4</v>
+        <v>8.1</v>
       </c>
       <c r="H34">
         <f>INDEX(pigs!$D$3:$AO$60,$E34,H$4)</f>
-        <v>12.2</v>
-      </c>
-      <c r="I34" s="4">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="K34" s="4">
         <f>MATCH($B34,cattle!$A$3:$A$120,0)</f>
-        <v>57</v>
-      </c>
-      <c r="J34">
-        <f>INDEX(cattle!$D$3:$AH$120,$I34,J$4)</f>
-        <v>7</v>
-      </c>
-      <c r="K34">
-        <f>INDEX(cattle!$D$3:$AH$120,$I34,K$4)</f>
-        <v>13.6</v>
-      </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="L34">
+        <f>INDEX(cattle!$D$3:$AH$120,$K34,L$4)</f>
+        <v>90</v>
+      </c>
+      <c r="M34" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$K34,M$4)</f>
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>58</v>
-      </c>
-      <c r="C35" s="24">
+        <v>51</v>
+      </c>
+      <c r="C35" s="23">
         <f t="shared" si="0"/>
-        <v>97</v>
+        <v>11</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4">
         <f>MATCH($B35,pigs!$A$3:$A$60,0)</f>
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="F35">
         <f>INDEX(pigs!$D$3:$AO$60,$E35,F$4)</f>
-        <v>97</v>
+        <v>11</v>
       </c>
       <c r="G35">
         <f>INDEX(pigs!$D$3:$AO$60,$E35,G$4)</f>
-        <v>12.4</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="H35">
         <f>INDEX(pigs!$D$3:$AO$60,$E35,H$4)</f>
-        <v>12.2</v>
-      </c>
-      <c r="I35" s="4"/>
-    </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
+        <v>8.9</v>
+      </c>
+      <c r="K35" s="4"/>
+      <c r="M35" s="27"/>
+    </row>
+    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>59</v>
-      </c>
-      <c r="C36" s="24">
+        <v>313</v>
+      </c>
+      <c r="C36" s="23">
         <f t="shared" si="0"/>
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D36" s="4"/>
-      <c r="E36" s="4">
-        <f>MATCH($B36,pigs!$A$3:$A$60,0)</f>
-        <v>31</v>
-      </c>
+      <c r="E36" s="4"/>
       <c r="F36">
-        <f>INDEX(pigs!$D$3:$AO$60,$E36,F$4)</f>
-        <v>92</v>
-      </c>
-      <c r="G36">
-        <f>INDEX(pigs!$D$3:$AO$60,$E36,G$4)</f>
-        <v>11.1</v>
-      </c>
-      <c r="H36">
-        <f>INDEX(pigs!$D$3:$AO$60,$E36,H$4)</f>
-        <v>11.3</v>
-      </c>
-      <c r="I36" s="4">
+        <v>90</v>
+      </c>
+      <c r="G36" s="3">
+        <v>6.6</v>
+      </c>
+      <c r="H36" s="25">
+        <f>H34/G34*G36</f>
+        <v>7.0888888888888877</v>
+      </c>
+      <c r="I36" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="K36" s="4">
         <f>MATCH($B36,cattle!$A$3:$A$120,0)</f>
-        <v>65</v>
-      </c>
-      <c r="J36">
-        <f>INDEX(cattle!$D$3:$AH$120,$I36,J$4)</f>
+        <v>38</v>
+      </c>
+      <c r="L36">
+        <f>INDEX(cattle!$D$3:$AH$120,$K36,L$4)</f>
         <v>90</v>
       </c>
-      <c r="K36">
-        <f>INDEX(cattle!$D$3:$AH$120,$I36,K$4)</f>
-        <v>15.5</v>
-      </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="M36" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$K36,M$4)</f>
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>60</v>
-      </c>
-      <c r="C37" s="24">
+        <v>52</v>
+      </c>
+      <c r="C37" s="23">
         <f t="shared" si="0"/>
-        <v>92</v>
+        <v>75.5</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="4">
         <f>MATCH($B37,pigs!$A$3:$A$60,0)</f>
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="F37">
         <f>INDEX(pigs!$D$3:$AO$60,$E37,F$4)</f>
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="G37">
         <f>INDEX(pigs!$D$3:$AO$60,$E37,G$4)</f>
-        <v>10.8</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="H37">
         <f>INDEX(pigs!$D$3:$AO$60,$E37,H$4)</f>
+        <v>9</v>
+      </c>
+      <c r="K37" s="4">
+        <f>MATCH($B37,cattle!$A$3:$A$120,0)</f>
+        <v>88</v>
+      </c>
+      <c r="L37">
+        <f>INDEX(cattle!$D$3:$AH$120,$K37,L$4)</f>
+        <v>75</v>
+      </c>
+      <c r="M37" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$K37,M$4)</f>
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="38" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>53</v>
+      </c>
+      <c r="C38" s="23">
+        <f t="shared" si="0"/>
+        <v>89.5</v>
+      </c>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4">
+        <f>MATCH($B38,pigs!$A$3:$A$60,0)</f>
+        <v>4</v>
+      </c>
+      <c r="F38">
+        <f>INDEX(pigs!$D$3:$AO$60,$E38,F$4)</f>
+        <v>89</v>
+      </c>
+      <c r="G38">
+        <f>INDEX(pigs!$D$3:$AO$60,$E38,G$4)</f>
+        <v>6.9</v>
+      </c>
+      <c r="H38">
+        <f>INDEX(pigs!$D$3:$AO$60,$E38,H$4)</f>
+        <v>8</v>
+      </c>
+      <c r="K38" s="4">
+        <f>MATCH($B38,cattle!$A$3:$A$120,0)</f>
+        <v>91</v>
+      </c>
+      <c r="L38">
+        <f>INDEX(cattle!$D$3:$AH$120,$K38,L$4)</f>
+        <v>90</v>
+      </c>
+      <c r="M38" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$K38,M$4)</f>
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" s="23">
+        <f t="shared" si="0"/>
+        <v>6.25</v>
+      </c>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4">
+        <f>MATCH($B39,pigs!$A$3:$A$60,0)</f>
+        <v>50</v>
+      </c>
+      <c r="F39">
+        <f>INDEX(pigs!$D$3:$AO$60,$E39,F$4)</f>
+        <v>5.5</v>
+      </c>
+      <c r="G39">
+        <f>INDEX(pigs!$D$3:$AO$60,$E39,G$4)</f>
+        <v>12.4</v>
+      </c>
+      <c r="H39">
+        <f>INDEX(pigs!$D$3:$AO$60,$E39,H$4)</f>
+        <v>12.2</v>
+      </c>
+      <c r="K39" s="4">
+        <f>MATCH($B39,cattle!$A$3:$A$120,0)</f>
+        <v>57</v>
+      </c>
+      <c r="L39">
+        <f>INDEX(cattle!$D$3:$AH$120,$K39,L$4)</f>
+        <v>7</v>
+      </c>
+      <c r="M39" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$K39,M$4)</f>
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>55</v>
+      </c>
+      <c r="C40" s="23">
+        <f t="shared" si="0"/>
+        <v>97</v>
+      </c>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4">
+        <f>MATCH($B40,pigs!$A$3:$A$60,0)</f>
+        <v>52</v>
+      </c>
+      <c r="F40">
+        <f>INDEX(pigs!$D$3:$AO$60,$E40,F$4)</f>
+        <v>97</v>
+      </c>
+      <c r="G40">
+        <f>INDEX(pigs!$D$3:$AO$60,$E40,G$4)</f>
+        <v>12.4</v>
+      </c>
+      <c r="H40">
+        <f>INDEX(pigs!$D$3:$AO$60,$E40,H$4)</f>
+        <v>12.2</v>
+      </c>
+      <c r="K40" s="4"/>
+      <c r="M40" s="27"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>56</v>
+      </c>
+      <c r="C41" s="23">
+        <f t="shared" si="0"/>
+        <v>91</v>
+      </c>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4">
+        <f>MATCH($B41,pigs!$A$3:$A$60,0)</f>
+        <v>31</v>
+      </c>
+      <c r="F41">
+        <f>INDEX(pigs!$D$3:$AO$60,$E41,F$4)</f>
+        <v>92</v>
+      </c>
+      <c r="G41">
+        <f>INDEX(pigs!$D$3:$AO$60,$E41,G$4)</f>
+        <v>11.1</v>
+      </c>
+      <c r="H41">
+        <f>INDEX(pigs!$D$3:$AO$60,$E41,H$4)</f>
+        <v>11.3</v>
+      </c>
+      <c r="K41" s="4">
+        <f>MATCH($B41,cattle!$A$3:$A$120,0)</f>
+        <v>65</v>
+      </c>
+      <c r="L41">
+        <f>INDEX(cattle!$D$3:$AH$120,$K41,L$4)</f>
+        <v>90</v>
+      </c>
+      <c r="M41" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$K41,M$4)</f>
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>57</v>
+      </c>
+      <c r="C42" s="23">
+        <f t="shared" si="0"/>
+        <v>92</v>
+      </c>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4">
+        <f>MATCH($B42,pigs!$A$3:$A$60,0)</f>
+        <v>7</v>
+      </c>
+      <c r="F42">
+        <f>INDEX(pigs!$D$3:$AO$60,$E42,F$4)</f>
+        <v>92</v>
+      </c>
+      <c r="G42">
+        <f>INDEX(pigs!$D$3:$AO$60,$E42,G$4)</f>
         <v>10.8</v>
       </c>
-      <c r="I37" s="4"/>
+      <c r="H42">
+        <f>INDEX(pigs!$D$3:$AO$60,$E42,H$4)</f>
+        <v>10.8</v>
+      </c>
+      <c r="K42" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C1" r:id="rId1"/>
+    <hyperlink ref="I36" r:id="rId2"/>
+    <hyperlink ref="N31" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
 
@@ -4625,138 +5156,138 @@
     </row>
     <row r="2" spans="1:41" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B2" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="D2" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="I2" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="J2" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="K2" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="L2" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="F2" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="G2" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="H2" s="19" t="s">
+      <c r="M2" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="N2" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="J2" s="19" t="s">
+      <c r="O2" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="K2" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="L2" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="M2" s="19" t="s">
+      <c r="P2" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="N2" s="19" t="s">
+      <c r="Q2" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="O2" s="19" t="s">
+      <c r="R2" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="P2" s="19" t="s">
+      <c r="S2" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="Q2" s="19" t="s">
+      <c r="T2" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="R2" s="19" t="s">
+      <c r="U2" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="S2" s="19" t="s">
+      <c r="V2" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="T2" s="19" t="s">
+      <c r="W2" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="U2" s="19" t="s">
+      <c r="X2" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="V2" s="19" t="s">
+      <c r="Y2" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="W2" s="19" t="s">
+      <c r="Z2" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="X2" s="19" t="s">
+      <c r="AA2" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="Y2" s="19" t="s">
+      <c r="AB2" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="Z2" s="19" t="s">
+      <c r="AC2" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="AA2" s="19" t="s">
+      <c r="AD2" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="AB2" s="19" t="s">
+      <c r="AE2" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="AC2" s="19" t="s">
+      <c r="AF2" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="AD2" s="19" t="s">
+      <c r="AG2" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="AE2" s="19" t="s">
+      <c r="AH2" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="AF2" s="19" t="s">
+      <c r="AI2" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="AG2" s="19" t="s">
+      <c r="AJ2" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="AH2" s="19" t="s">
+      <c r="AK2" s="19" t="s">
         <v>157</v>
       </c>
-      <c r="AI2" s="19" t="s">
+      <c r="AL2" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="AJ2" s="19" t="s">
+      <c r="AM2" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="AK2" s="19" t="s">
+      <c r="AN2" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="AL2" s="19" t="s">
+      <c r="AO2" s="19" t="s">
         <v>161</v>
-      </c>
-      <c r="AM2" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="AN2" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="AO2" s="19" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B3" s="12">
         <v>1</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D3" s="14">
         <v>11</v>
@@ -4858,7 +5389,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D4" s="17">
         <v>28</v>
@@ -4961,13 +5492,13 @@
     </row>
     <row r="5" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B5" s="12">
         <v>3</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D5" s="14">
         <v>90</v>
@@ -5072,13 +5603,13 @@
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B6" s="15">
         <v>4</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D6" s="17">
         <v>89</v>
@@ -5200,7 +5731,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D7" s="14">
         <v>8.1</v>
@@ -5310,7 +5841,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D8" s="17">
         <v>100</v>
@@ -5429,13 +5960,13 @@
     </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B9" s="12">
         <v>7</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D9" s="14">
         <v>92</v>
@@ -5557,7 +6088,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D10" s="17">
         <v>100</v>
@@ -5679,7 +6210,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D11" s="14">
         <v>90</v>
@@ -5801,7 +6332,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D12" s="17">
         <v>91</v>
@@ -5916,13 +6447,13 @@
     </row>
     <row r="13" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B13" s="12">
         <v>11</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D13" s="14">
         <v>87</v>
@@ -6044,7 +6575,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D14" s="17">
         <v>87</v>
@@ -6147,13 +6678,13 @@
     </row>
     <row r="15" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B15" s="12">
         <v>13</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D15" s="14">
         <v>87</v>
@@ -6272,13 +6803,13 @@
     </row>
     <row r="16" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B16" s="15">
         <v>14</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D16" s="17">
         <v>91</v>
@@ -6400,7 +6931,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D17" s="14">
         <v>90</v>
@@ -6522,7 +7053,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D18" s="17">
         <v>89</v>
@@ -6644,7 +7175,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D19" s="14">
         <v>91</v>
@@ -6766,7 +7297,7 @@
         <v>18</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D20" s="17">
         <v>99.5</v>
@@ -6885,13 +7416,13 @@
     </row>
     <row r="21" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B21" s="12">
         <v>19</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D21" s="14">
         <v>87</v>
@@ -7013,7 +7544,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D22" s="17">
         <v>88</v>
@@ -7135,7 +7666,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D23" s="14">
         <v>88</v>
@@ -7257,7 +7788,7 @@
         <v>22</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D24" s="17">
         <v>90</v>
@@ -7376,13 +7907,13 @@
     </row>
     <row r="25" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B25" s="12">
         <v>23</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D25" s="14">
         <v>76</v>
@@ -7504,7 +8035,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D26" s="17">
         <v>74</v>
@@ -7626,7 +8157,7 @@
         <v>25</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D27" s="14">
         <v>99.5</v>
@@ -7748,7 +8279,7 @@
         <v>26</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D28" s="17">
         <v>88</v>
@@ -7870,7 +8401,7 @@
         <v>27</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D29" s="14">
         <v>100</v>
@@ -7988,11 +8519,14 @@
       </c>
     </row>
     <row r="30" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>314</v>
+      </c>
       <c r="B30" s="15">
         <v>28</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D30" s="17">
         <v>100</v>
@@ -8111,13 +8645,13 @@
     </row>
     <row r="31" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B31" s="12">
         <v>29</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D31" s="14">
         <v>91</v>
@@ -8235,7 +8769,7 @@
         <v>30</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D32" s="17">
         <v>16.5</v>
@@ -8346,13 +8880,13 @@
     </row>
     <row r="33" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B33" s="12">
         <v>31</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D33" s="14">
         <v>92</v>
@@ -8472,7 +9006,7 @@
         <v>32</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D34" s="17">
         <v>18</v>
@@ -8577,13 +9111,13 @@
     </row>
     <row r="35" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B35" s="12">
         <v>33</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D35" s="14">
         <v>92</v>
@@ -8703,7 +9237,7 @@
         <v>34</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D36" s="17">
         <v>89</v>
@@ -8823,7 +9357,7 @@
         <v>35</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D37" s="14">
         <v>89</v>
@@ -8942,13 +9476,13 @@
     </row>
     <row r="38" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B38" s="15">
         <v>36</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D38" s="17">
         <v>89</v>
@@ -9070,7 +9604,7 @@
         <v>37</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D39" s="14">
         <v>87</v>
@@ -9188,11 +9722,14 @@
       </c>
     </row>
     <row r="40" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>317</v>
+      </c>
       <c r="B40" s="15">
         <v>38</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D40" s="17">
         <v>87</v>
@@ -9311,13 +9848,13 @@
     </row>
     <row r="41" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B41" s="12">
         <v>39</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D41" s="14">
         <v>87</v>
@@ -9437,7 +9974,7 @@
         <v>40</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D42" s="17">
         <v>100</v>
@@ -9559,7 +10096,7 @@
         <v>41</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D43" s="14">
         <v>95</v>
@@ -9681,7 +10218,7 @@
         <v>42</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D44" s="17">
         <v>88</v>
@@ -9794,13 +10331,13 @@
     </row>
     <row r="45" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B45" s="12">
         <v>43</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D45" s="14">
         <v>88</v>
@@ -9922,7 +10459,7 @@
         <v>44</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D46" s="17">
         <v>88</v>
@@ -10041,13 +10578,13 @@
     </row>
     <row r="47" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B47" s="12">
         <v>45</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D47" s="14">
         <v>87</v>
@@ -10164,13 +10701,13 @@
     </row>
     <row r="48" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B48" s="15">
         <v>46</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D48" s="17">
         <v>90</v>
@@ -10292,7 +10829,7 @@
         <v>47</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D49" s="14">
         <v>87</v>
@@ -10414,7 +10951,7 @@
         <v>48</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D50" s="17">
         <v>99</v>
@@ -10536,7 +11073,7 @@
         <v>49</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D51" s="14">
         <v>99</v>
@@ -10653,13 +11190,13 @@
     </row>
     <row r="52" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B52" s="15">
         <v>50</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D52" s="17">
         <v>5.5</v>
@@ -10781,7 +11318,7 @@
         <v>51</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D53" s="14">
         <v>98</v>
@@ -10900,13 +11437,13 @@
     </row>
     <row r="54" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B54" s="15">
         <v>52</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D54" s="17">
         <v>97</v>
@@ -11025,13 +11562,13 @@
     </row>
     <row r="55" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B55" s="12">
         <v>53</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D55" s="14">
         <v>87</v>
@@ -11150,13 +11687,13 @@
     </row>
     <row r="56" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B56" s="15">
         <v>54</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D56" s="17">
         <v>88</v>
@@ -11275,13 +11812,13 @@
     </row>
     <row r="57" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B57" s="12">
         <v>55</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D57" s="14">
         <v>87</v>
@@ -11400,13 +11937,13 @@
     </row>
     <row r="58" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B58" s="15">
         <v>56</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D58" s="17">
         <v>87</v>
@@ -11523,13 +12060,13 @@
     </row>
     <row r="59" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B59" s="12">
         <v>57</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D59" s="14">
         <v>87</v>
@@ -11651,7 +12188,7 @@
         <v>58</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D60" s="17">
         <v>12</v>
@@ -11929,106 +12466,106 @@
     </row>
     <row r="2" spans="1:34" ht="57.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B2" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="D2" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K2" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="L2" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="E2" s="19" t="s">
-        <v>282</v>
-      </c>
-      <c r="F2" s="19" t="s">
-        <v>283</v>
-      </c>
-      <c r="G2" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="H2" s="19" t="s">
+      <c r="M2" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="N2" s="19" t="s">
         <v>285</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="O2" s="19" t="s">
         <v>286</v>
       </c>
-      <c r="J2" s="19" t="s">
+      <c r="P2" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="Q2" s="19" t="s">
+        <v>288</v>
+      </c>
+      <c r="R2" s="19" t="s">
+        <v>289</v>
+      </c>
+      <c r="S2" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="T2" s="19" t="s">
+        <v>291</v>
+      </c>
+      <c r="U2" s="19" t="s">
+        <v>292</v>
+      </c>
+      <c r="V2" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="W2" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="L2" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="M2" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="N2" s="19" t="s">
-        <v>288</v>
-      </c>
-      <c r="O2" s="19" t="s">
-        <v>289</v>
-      </c>
-      <c r="P2" s="19" t="s">
-        <v>290</v>
-      </c>
-      <c r="Q2" s="19" t="s">
-        <v>291</v>
-      </c>
-      <c r="R2" s="19" t="s">
-        <v>292</v>
-      </c>
-      <c r="S2" s="19" t="s">
-        <v>293</v>
-      </c>
-      <c r="T2" s="19" t="s">
+      <c r="X2" s="19" t="s">
         <v>294</v>
       </c>
-      <c r="U2" s="19" t="s">
+      <c r="Y2" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="Z2" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="AA2" s="19" t="s">
         <v>295</v>
       </c>
-      <c r="V2" s="19" t="s">
+      <c r="AB2" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="AC2" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="AD2" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE2" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="AF2" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="AG2" s="19" t="s">
         <v>296</v>
       </c>
-      <c r="W2" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="X2" s="19" t="s">
-        <v>297</v>
-      </c>
-      <c r="Y2" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Z2" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="AA2" s="19" t="s">
-        <v>298</v>
-      </c>
-      <c r="AB2" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="AC2" s="19" t="s">
+      <c r="AH2" s="19" t="s">
         <v>155</v>
-      </c>
-      <c r="AD2" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="AE2" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="AF2" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="AG2" s="19" t="s">
-        <v>299</v>
-      </c>
-      <c r="AH2" s="19" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.25">
@@ -12036,7 +12573,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D3" s="14">
         <v>50</v>
@@ -12107,7 +12644,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D4" s="17">
         <v>85</v>
@@ -12178,7 +12715,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D5" s="14">
         <v>90</v>
@@ -12257,7 +12794,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D6" s="17">
         <v>90</v>
@@ -12328,7 +12865,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D7" s="14">
         <v>84</v>
@@ -12423,7 +12960,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D8" s="17">
         <v>14</v>
@@ -12512,7 +13049,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D9" s="14">
         <v>85</v>
@@ -12583,7 +13120,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D10" s="17">
         <v>92</v>
@@ -12670,7 +13207,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D11" s="14">
         <v>92</v>
@@ -12769,7 +13306,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D12" s="17">
         <v>92</v>
@@ -12852,7 +13389,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D13" s="14">
         <v>92</v>
@@ -12935,7 +13472,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D14" s="17">
         <v>90</v>
@@ -13030,7 +13567,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D15" s="14">
         <v>90</v>
@@ -13121,7 +13658,7 @@
         <v>14</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D16" s="17">
         <v>99</v>
@@ -13200,7 +13737,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D17" s="14">
         <v>12</v>
@@ -13293,7 +13830,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D18" s="17">
         <v>90</v>
@@ -13368,7 +13905,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D19" s="14">
         <v>15</v>
@@ -13457,7 +13994,7 @@
         <v>18</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D20" s="17">
         <v>16</v>
@@ -13548,7 +14085,7 @@
         <v>19</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D21" s="14">
         <v>90</v>
@@ -13639,7 +14176,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D22" s="17">
         <v>89</v>
@@ -13730,7 +14267,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D23" s="14">
         <v>80</v>
@@ -13818,13 +14355,13 @@
     </row>
     <row r="24" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B24" s="15">
         <v>22</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D24" s="17">
         <v>85</v>
@@ -13923,7 +14460,7 @@
         <v>23</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D25" s="14">
         <v>59</v>
@@ -14016,7 +14553,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D26" s="17">
         <v>74</v>
@@ -14099,7 +14636,7 @@
         <v>25</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D27" s="14">
         <v>93</v>
@@ -14170,7 +14707,7 @@
         <v>26</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D28" s="17">
         <v>37</v>
@@ -14259,7 +14796,7 @@
         <v>27</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D29" s="14">
         <v>87</v>
@@ -14335,13 +14872,13 @@
     </row>
     <row r="30" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B30" s="15">
         <v>28</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D30" s="17">
         <v>85</v>
@@ -14442,7 +14979,7 @@
         <v>29</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D31" s="14">
         <v>87</v>
@@ -14529,7 +15066,7 @@
         <v>30</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D32" s="17">
         <v>87</v>
@@ -14620,7 +15157,7 @@
         <v>31</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D33" s="14">
         <v>50</v>
@@ -14691,7 +15228,7 @@
         <v>32</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D34" s="17">
         <v>82</v>
@@ -14778,7 +15315,7 @@
         <v>33</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D35" s="14">
         <v>90</v>
@@ -14865,7 +15402,7 @@
         <v>34</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D36" s="17">
         <v>88</v>
@@ -14956,7 +15493,7 @@
         <v>35</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D37" s="14">
         <v>94</v>
@@ -15053,7 +15590,7 @@
         <v>36</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D38" s="17">
         <v>92</v>
@@ -15146,7 +15683,7 @@
         <v>37</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D39" s="14">
         <v>7</v>
@@ -15229,11 +15766,14 @@
       </c>
     </row>
     <row r="40" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>313</v>
+      </c>
       <c r="B40" s="15">
         <v>38</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D40" s="17">
         <v>90</v>
@@ -15330,7 +15870,7 @@
         <v>39</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D41" s="14">
         <v>90</v>
@@ -15421,7 +15961,7 @@
         <v>40</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D42" s="17">
         <v>37</v>
@@ -15518,7 +16058,7 @@
         <v>41</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D43" s="14">
         <v>87</v>
@@ -15594,13 +16134,13 @@
     </row>
     <row r="44" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B44" s="15">
         <v>42</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D44" s="17">
         <v>87</v>
@@ -15701,7 +16241,7 @@
         <v>43</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D45" s="14">
         <v>86</v>
@@ -15798,7 +16338,7 @@
         <v>44</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D46" s="17">
         <v>12</v>
@@ -15890,13 +16430,13 @@
     </row>
     <row r="47" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B47" s="12">
         <v>45</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D47" s="14">
         <v>93</v>
@@ -15989,7 +16529,7 @@
         <v>46</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D48" s="17">
         <v>90</v>
@@ -16084,7 +16624,7 @@
         <v>47</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D49" s="14">
         <v>90</v>
@@ -16177,7 +16717,7 @@
         <v>48</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D50" s="17">
         <v>87</v>
@@ -16270,7 +16810,7 @@
         <v>49</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D51" s="14">
         <v>13</v>
@@ -16359,7 +16899,7 @@
         <v>50</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D52" s="17">
         <v>92</v>
@@ -16455,13 +16995,13 @@
     </row>
     <row r="53" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B53" s="12">
         <v>51</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D53" s="14">
         <v>22</v>
@@ -16552,7 +17092,7 @@
         <v>52</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D54" s="17">
         <v>32</v>
@@ -16646,13 +17186,13 @@
     </row>
     <row r="55" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B55" s="12">
         <v>53</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D55" s="14">
         <v>48</v>
@@ -16743,7 +17283,7 @@
         <v>54</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D56" s="17">
         <v>87</v>
@@ -16840,7 +17380,7 @@
         <v>55</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D57" s="14">
         <v>13</v>
@@ -16937,7 +17477,7 @@
         <v>56</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D58" s="17">
         <v>8</v>
@@ -17025,13 +17565,13 @@
     </row>
     <row r="59" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B59" s="12">
         <v>57</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D59" s="14">
         <v>7</v>
@@ -17126,7 +17666,7 @@
         <v>58</v>
       </c>
       <c r="C60" s="17" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D60" s="17">
         <v>6</v>
@@ -17221,7 +17761,7 @@
         <v>59</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D61" s="14">
         <v>12</v>
@@ -17313,13 +17853,13 @@
     </row>
     <row r="62" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B62" s="15">
         <v>60</v>
       </c>
       <c r="C62" s="17" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D62" s="17">
         <v>91</v>
@@ -17414,7 +17954,7 @@
         <v>61</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D63" s="14">
         <v>91</v>
@@ -17507,7 +18047,7 @@
         <v>62</v>
       </c>
       <c r="C64" s="17" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D64" s="17">
         <v>6</v>
@@ -17594,7 +18134,7 @@
         <v>63</v>
       </c>
       <c r="C65" s="14" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D65" s="14">
         <v>23</v>
@@ -17693,7 +18233,7 @@
         <v>64</v>
       </c>
       <c r="C66" s="17" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D66" s="17">
         <v>14</v>
@@ -17779,13 +18319,13 @@
     </row>
     <row r="67" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B67" s="12">
         <v>65</v>
       </c>
       <c r="C67" s="14" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D67" s="14">
         <v>90</v>
@@ -17871,13 +18411,13 @@
     </row>
     <row r="68" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B68" s="15">
         <v>66</v>
       </c>
       <c r="C68" s="17" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D68" s="17">
         <v>94</v>
@@ -17974,7 +18514,7 @@
         <v>67</v>
       </c>
       <c r="C69" s="14" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D69" s="14">
         <v>94</v>
@@ -18073,7 +18613,7 @@
         <v>68</v>
       </c>
       <c r="C70" s="17" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D70" s="17">
         <v>21</v>
@@ -18150,7 +18690,7 @@
         <v>69</v>
       </c>
       <c r="C71" s="14" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D71" s="14">
         <v>90</v>
@@ -18246,13 +18786,13 @@
     </row>
     <row r="72" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B72" s="15">
         <v>70</v>
       </c>
       <c r="C72" s="17" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D72" s="17">
         <v>90</v>
@@ -18348,13 +18888,13 @@
     </row>
     <row r="73" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B73" s="12">
         <v>71</v>
       </c>
       <c r="C73" s="14" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D73" s="14">
         <v>93</v>
@@ -18453,7 +18993,7 @@
         <v>72</v>
       </c>
       <c r="C74" s="17" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D74" s="17">
         <v>35</v>
@@ -18534,7 +19074,7 @@
         <v>73</v>
       </c>
       <c r="C75" s="14" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D75" s="14">
         <v>89</v>
@@ -18627,7 +19167,7 @@
         <v>74</v>
       </c>
       <c r="C76" s="17" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D76" s="17">
         <v>87</v>
@@ -18722,7 +19262,7 @@
         <v>75</v>
       </c>
       <c r="C77" s="14" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D77" s="14">
         <v>9</v>
@@ -18813,7 +19353,7 @@
         <v>76</v>
       </c>
       <c r="C78" s="17" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D78" s="17">
         <v>87</v>
@@ -18900,11 +19440,14 @@
       </c>
     </row>
     <row r="79" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>317</v>
+      </c>
       <c r="B79" s="12">
         <v>77</v>
       </c>
       <c r="C79" s="14" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D79" s="14">
         <v>87</v>
@@ -18996,13 +19539,13 @@
     </row>
     <row r="80" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B80" s="15">
         <v>78</v>
       </c>
       <c r="C80" s="17" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D80" s="17">
         <v>87</v>
@@ -19099,7 +19642,7 @@
         <v>79</v>
       </c>
       <c r="C81" s="14" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D81" s="14">
         <v>78</v>
@@ -19186,7 +19729,7 @@
         <v>80</v>
       </c>
       <c r="C82" s="17" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D82" s="17">
         <v>93</v>
@@ -19257,7 +19800,7 @@
         <v>81</v>
       </c>
       <c r="C83" s="14" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D83" s="14">
         <v>90</v>
@@ -19344,7 +19887,7 @@
         <v>82</v>
       </c>
       <c r="C84" s="17" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D84" s="17">
         <v>94</v>
@@ -19415,7 +19958,7 @@
         <v>83</v>
       </c>
       <c r="C85" s="14" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D85" s="14">
         <v>90</v>
@@ -19502,7 +20045,7 @@
         <v>84</v>
       </c>
       <c r="C86" s="17" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D86" s="17">
         <v>90</v>
@@ -19585,7 +20128,7 @@
         <v>85</v>
       </c>
       <c r="C87" s="14" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D87" s="14">
         <v>24</v>
@@ -19674,7 +20217,7 @@
         <v>86</v>
       </c>
       <c r="C88" s="17" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D88" s="17">
         <v>14</v>
@@ -19759,7 +20302,7 @@
         <v>87</v>
       </c>
       <c r="C89" s="14" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D89" s="14">
         <v>27</v>
@@ -19849,13 +20392,13 @@
     </row>
     <row r="90" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B90" s="15">
         <v>88</v>
       </c>
       <c r="C90" s="17" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D90" s="17">
         <v>75</v>
@@ -19940,7 +20483,7 @@
         <v>89</v>
       </c>
       <c r="C91" s="14" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D91" s="14">
         <v>19</v>
@@ -20025,7 +20568,7 @@
         <v>90</v>
       </c>
       <c r="C92" s="17" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D92" s="17">
         <v>91</v>
@@ -20119,13 +20662,13 @@
     </row>
     <row r="93" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B93" s="12">
         <v>91</v>
       </c>
       <c r="C93" s="14" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D93" s="14">
         <v>90</v>
@@ -20214,11 +20757,14 @@
       </c>
     </row>
     <row r="94" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>318</v>
+      </c>
       <c r="B94" s="15">
         <v>92</v>
       </c>
       <c r="C94" s="17" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D94" s="17">
         <v>87</v>
@@ -20308,13 +20854,13 @@
     </row>
     <row r="95" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B95" s="12">
         <v>93</v>
       </c>
       <c r="C95" s="14" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D95" s="14">
         <v>87</v>
@@ -20411,7 +20957,7 @@
         <v>94</v>
       </c>
       <c r="C96" s="17" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D96" s="17">
         <v>87</v>
@@ -20498,7 +21044,7 @@
         <v>95</v>
       </c>
       <c r="C97" s="14" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D97" s="14">
         <v>92</v>
@@ -20591,7 +21137,7 @@
         <v>96</v>
       </c>
       <c r="C98" s="17" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D98" s="17">
         <v>92</v>
@@ -20686,7 +21232,7 @@
         <v>97</v>
       </c>
       <c r="C99" s="14" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D99" s="14">
         <v>93</v>
@@ -20777,7 +21323,7 @@
         <v>98</v>
       </c>
       <c r="C100" s="17" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D100" s="17">
         <v>92</v>
@@ -20867,13 +21413,13 @@
     </row>
     <row r="101" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B101" s="12">
         <v>99</v>
       </c>
       <c r="C101" s="14" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D101" s="14">
         <v>92</v>
@@ -20968,7 +21514,7 @@
         <v>100</v>
       </c>
       <c r="C102" s="17" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D102" s="17">
         <v>87</v>
@@ -21059,7 +21605,7 @@
         <v>101</v>
       </c>
       <c r="C103" s="14" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D103" s="14">
         <v>50</v>
@@ -21138,7 +21684,7 @@
         <v>102</v>
       </c>
       <c r="C104" s="17" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D104" s="17">
         <v>88</v>
@@ -21231,7 +21777,7 @@
         <v>103</v>
       </c>
       <c r="C105" s="14" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="D105" s="14">
         <v>50</v>
@@ -21316,7 +21862,7 @@
         <v>104</v>
       </c>
       <c r="C106" s="17" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D106" s="17">
         <v>89</v>
@@ -21387,7 +21933,7 @@
         <v>105</v>
       </c>
       <c r="C107" s="14" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D107" s="14">
         <v>98</v>
@@ -21468,7 +22014,7 @@
         <v>106</v>
       </c>
       <c r="C108" s="17" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="D108" s="17">
         <v>93</v>
@@ -21535,7 +22081,7 @@
         <v>107</v>
       </c>
       <c r="C109" s="14" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D109" s="14">
         <v>90</v>
@@ -21606,7 +22152,7 @@
         <v>108</v>
       </c>
       <c r="C110" s="17" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D110" s="17">
         <v>85</v>
@@ -21674,13 +22220,13 @@
     </row>
     <row r="111" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B111" s="12">
         <v>109</v>
       </c>
       <c r="C111" s="14" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D111" s="14">
         <v>90</v>
@@ -21773,7 +22319,7 @@
         <v>110</v>
       </c>
       <c r="C112" s="17" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D112" s="17">
         <v>87</v>
@@ -21857,13 +22403,13 @@
     </row>
     <row r="113" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B113" s="12">
         <v>111</v>
       </c>
       <c r="C113" s="14" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D113" s="14">
         <v>87</v>
@@ -21957,13 +22503,13 @@
     </row>
     <row r="114" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B114" s="15">
         <v>112</v>
       </c>
       <c r="C114" s="17" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D114" s="17">
         <v>87</v>
@@ -22062,7 +22608,7 @@
         <v>113</v>
       </c>
       <c r="C115" s="14" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D115" s="14">
         <v>87</v>
@@ -22141,7 +22687,7 @@
         <v>114</v>
       </c>
       <c r="C116" s="17" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D116" s="17">
         <v>19</v>
@@ -22233,13 +22779,13 @@
     </row>
     <row r="117" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B117" s="12">
         <v>115</v>
       </c>
       <c r="C117" s="14" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D117" s="14">
         <v>87</v>
@@ -22338,7 +22884,7 @@
         <v>116</v>
       </c>
       <c r="C118" s="17" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D118" s="17">
         <v>31</v>
@@ -22421,7 +22967,7 @@
         <v>117</v>
       </c>
       <c r="C119" s="14" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D119" s="14">
         <v>31</v>
@@ -22504,7 +23050,7 @@
         <v>118</v>
       </c>
       <c r="C120" s="17" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D120" s="17">
         <v>18</v>

--- a/data/prod_parameters/FeedMgmt.xlsx
+++ b/data/prod_parameters/FeedMgmt.xlsx
@@ -12,7 +12,7 @@
     <sheet name="pigs" sheetId="3" r:id="rId3"/>
     <sheet name="cattle" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913" iterate="1"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="337">
   <si>
     <t>f_feed</t>
   </si>
@@ -997,6 +997,54 @@
   </si>
   <si>
     <t>minerals</t>
+  </si>
+  <si>
+    <t>f_crop</t>
+  </si>
+  <si>
+    <t>dairy</t>
+  </si>
+  <si>
+    <t>cows</t>
+  </si>
+  <si>
+    <t>calves</t>
+  </si>
+  <si>
+    <t>bulls</t>
+  </si>
+  <si>
+    <t>heifers</t>
+  </si>
+  <si>
+    <t>steers</t>
+  </si>
+  <si>
+    <t>breeding bulls</t>
+  </si>
+  <si>
+    <t>beef</t>
+  </si>
+  <si>
+    <t>Semi-natural pastures</t>
+  </si>
+  <si>
+    <t>max_crop_in_crop_prod</t>
+  </si>
+  <si>
+    <r>
+      <t>Maximum contribution of crop to crop product demand for feed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Primarily used to limit semi-natural pastures in grazing)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1464,19 +1512,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N141"/>
+  <dimension ref="A1:O156"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="20.28515625" customWidth="1"/>
-    <col min="7" max="7" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.140625" customWidth="1"/>
-    <col min="9" max="9" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="38.140625" customWidth="1"/>
-    <col min="13" max="13" width="58" customWidth="1"/>
+    <col min="6" max="7" width="20.28515625" customWidth="1"/>
+    <col min="8" max="8" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" customWidth="1"/>
+    <col min="10" max="10" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="38.140625" customWidth="1"/>
+    <col min="14" max="14" width="58" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>23</v>
       </c>
@@ -1496,28 +1544,31 @@
         <v>0</v>
       </c>
       <c r="G1" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -1528,589 +1579,592 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-      <c r="I2" s="2"/>
+      <c r="I2" s="1"/>
       <c r="J2" s="2"/>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="2"/>
+      <c r="L2" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="L2" s="24" t="s">
+      <c r="M2" s="24" t="s">
         <v>309</v>
       </c>
-      <c r="M2" s="2"/>
-      <c r="N2" s="5"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="I3" s="10" t="s">
+      <c r="N2" s="2"/>
+      <c r="O2" s="5"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J3" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="J3" s="21">
-        <v>0</v>
-      </c>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10" t="s">
+      <c r="K3" s="21">
+        <v>0</v>
+      </c>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F4" t="s">
         <v>310</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>10</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="22">
+      <c r="K4" s="22">
         <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F4,'feed pars'!B$6:B$42,0))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F5" t="s">
         <v>311</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>10</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="22">
+      <c r="K5" s="22">
         <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F5,'feed pars'!B$6:B$42,0))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F6" t="s">
         <v>312</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>10</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>32</v>
       </c>
-      <c r="J6" s="22">
+      <c r="K6" s="22">
         <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F6,'feed pars'!B$6:B$42,0))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F7" t="s">
         <v>2</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>10</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>32</v>
       </c>
-      <c r="J7" s="22">
+      <c r="K7" s="22">
         <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F7,'feed pars'!B$6:B$42,0))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F8" t="s">
         <v>12</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>11</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>32</v>
       </c>
-      <c r="J8" s="22">
+      <c r="K8" s="22">
         <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F8,'feed pars'!B$6:B$42,0))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F9" t="s">
         <v>33</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>33</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>32</v>
       </c>
-      <c r="J9" s="22">
+      <c r="K9" s="22">
         <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F9,'feed pars'!B$6:B$42,0))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F10" t="s">
         <v>17</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>17</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>32</v>
       </c>
-      <c r="J10" s="22">
+      <c r="K10" s="22">
         <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F10,'feed pars'!B$6:B$42,0))</f>
         <v>1.1494252873563218</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F11" t="s">
         <v>37</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>37</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>32</v>
       </c>
-      <c r="J11" s="22">
+      <c r="K11" s="22">
         <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F11,'feed pars'!B$6:B$42,0))</f>
         <v>1.1494252873563218</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F12" t="s">
         <v>38</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>38</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>32</v>
       </c>
-      <c r="J12" s="22">
+      <c r="K12" s="22">
         <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F12,'feed pars'!B$6:B$42,0))</f>
         <v>1.1627906976744187</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F13" t="s">
         <v>39</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>39</v>
       </c>
-      <c r="I13" t="s">
+      <c r="J13" t="s">
         <v>32</v>
       </c>
-      <c r="J13" s="22">
+      <c r="K13" s="22">
         <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F13,'feed pars'!B$6:B$42,0))</f>
         <v>1.1494252873563218</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F14" t="s">
         <v>317</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>317</v>
       </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
         <v>32</v>
       </c>
-      <c r="J14" s="22">
+      <c r="K14" s="22">
         <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F14,'feed pars'!B$6:B$42,0))</f>
         <v>1.1494252873563218</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F15" t="s">
         <v>40</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>40</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
         <v>32</v>
       </c>
-      <c r="J15" s="22">
+      <c r="K15" s="22">
         <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F15,'feed pars'!B$6:B$42,0))</f>
         <v>1.4814814814814814</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F16" t="s">
         <v>41</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>41</v>
       </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
         <v>32</v>
       </c>
-      <c r="J16" s="22">
+      <c r="K16" s="22">
         <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F16,'feed pars'!B$6:B$42,0))</f>
         <v>1.1494252873563218</v>
       </c>
     </row>
-    <row r="17" spans="6:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F17" t="s">
         <v>42</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>42</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>32</v>
       </c>
-      <c r="J17" s="22">
+      <c r="K17" s="22">
         <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F17,'feed pars'!B$6:B$42,0))</f>
         <v>1.1520737327188941</v>
       </c>
     </row>
-    <row r="18" spans="6:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F18" t="s">
         <v>35</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>35</v>
       </c>
-      <c r="I18" t="s">
+      <c r="J18" t="s">
         <v>32</v>
       </c>
-      <c r="J18" s="22">
+      <c r="K18" s="22">
         <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F18,'feed pars'!B$6:B$42,0))</f>
         <v>1.0810810810810809</v>
       </c>
     </row>
-    <row r="19" spans="6:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F19" t="s">
         <v>43</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>43</v>
       </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
         <v>32</v>
       </c>
-      <c r="J19" s="22">
+      <c r="K19" s="22">
         <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F19,'feed pars'!B$6:B$42,0))</f>
         <v>1.0869565217391304</v>
       </c>
     </row>
-    <row r="20" spans="6:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F20" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="G20" s="3"/>
+      <c r="H20" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3" t="s">
+      <c r="I20" s="3"/>
+      <c r="J20" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J20" s="20">
+      <c r="K20" s="20">
         <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F20,'feed pars'!B$6:B$42,0))*1/0.38</f>
         <v>2.6315789473684212</v>
       </c>
     </row>
-    <row r="21" spans="6:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F21" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G21" s="3"/>
+      <c r="H21" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H21" s="3" t="s">
+      <c r="I21" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="J21" s="22"/>
-      <c r="L21" s="3" t="s">
+      <c r="K21" s="22"/>
+      <c r="M21" s="3" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="22" spans="6:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F22" t="s">
         <v>305</v>
       </c>
-      <c r="H22" t="s">
+      <c r="I22" t="s">
         <v>305</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>32</v>
       </c>
-      <c r="J22" s="22">
+      <c r="K22" s="22">
         <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F22,'feed pars'!B$6:B$42,0))</f>
         <v>1.1764705882352942</v>
       </c>
     </row>
-    <row r="23" spans="6:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F23" t="s">
         <v>318</v>
       </c>
-      <c r="H23" t="s">
+      <c r="I23" t="s">
         <v>318</v>
       </c>
-      <c r="I23" t="s">
+      <c r="J23" t="s">
         <v>32</v>
       </c>
-      <c r="J23" s="22">
+      <c r="K23" s="22">
         <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F23,'feed pars'!B$6:B$42,0))</f>
         <v>1.1494252873563218</v>
       </c>
     </row>
-    <row r="24" spans="6:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F24" t="s">
         <v>44</v>
       </c>
-      <c r="H24" t="s">
+      <c r="I24" t="s">
         <v>44</v>
       </c>
-      <c r="I24" t="s">
+      <c r="J24" t="s">
         <v>32</v>
       </c>
-      <c r="J24" s="22">
+      <c r="K24" s="22">
         <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F24,'feed pars'!B$6:B$42,0))</f>
         <v>1.1428571428571428</v>
       </c>
     </row>
-    <row r="25" spans="6:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F25" t="s">
         <v>45</v>
       </c>
-      <c r="H25" t="s">
+      <c r="I25" t="s">
         <v>45</v>
       </c>
-      <c r="I25" t="s">
+      <c r="J25" t="s">
         <v>32</v>
       </c>
-      <c r="J25" s="22">
+      <c r="K25" s="22">
         <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F25,'feed pars'!B$6:B$42,0))</f>
         <v>1.1494252873563218</v>
       </c>
     </row>
-    <row r="26" spans="6:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F26" t="s">
         <v>36</v>
       </c>
-      <c r="H26" t="s">
+      <c r="I26" t="s">
         <v>36</v>
       </c>
-      <c r="I26" t="s">
+      <c r="J26" t="s">
         <v>32</v>
       </c>
-      <c r="J26" s="22">
+      <c r="K26" s="22">
         <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F26,'feed pars'!B$6:B$42,0))</f>
         <v>1.1173184357541899</v>
       </c>
     </row>
-    <row r="27" spans="6:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F27" t="s">
         <v>46</v>
       </c>
-      <c r="H27" t="s">
+      <c r="I27" t="s">
         <v>46</v>
       </c>
-      <c r="I27" t="s">
+      <c r="J27" t="s">
         <v>32</v>
       </c>
-      <c r="J27" s="22">
+      <c r="K27" s="22">
         <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F27,'feed pars'!B$6:B$42,0))</f>
         <v>1.0989010989010988</v>
       </c>
     </row>
-    <row r="28" spans="6:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F28" t="s">
         <v>47</v>
       </c>
-      <c r="H28" t="s">
+      <c r="I28" t="s">
         <v>47</v>
       </c>
-      <c r="I28" t="s">
+      <c r="J28" t="s">
         <v>32</v>
       </c>
-      <c r="J28" s="22">
+      <c r="K28" s="22">
         <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F28,'feed pars'!B$6:B$42,0))</f>
         <v>1.0989010989010988</v>
       </c>
     </row>
-    <row r="29" spans="6:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F29" t="s">
         <v>319</v>
       </c>
-      <c r="H29" t="s">
+      <c r="I29" t="s">
         <v>319</v>
       </c>
-      <c r="I29" t="s">
+      <c r="J29" t="s">
         <v>32</v>
       </c>
-      <c r="J29" s="22">
+      <c r="K29" s="22">
         <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F29,'feed pars'!B$6:B$42,0))</f>
         <v>1.1111111111111112</v>
       </c>
     </row>
-    <row r="30" spans="6:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F30" t="s">
         <v>48</v>
       </c>
-      <c r="H30" t="s">
+      <c r="I30" t="s">
         <v>48</v>
       </c>
-      <c r="I30" t="s">
+      <c r="J30" t="s">
         <v>32</v>
       </c>
-      <c r="J30" s="22">
+      <c r="K30" s="22">
         <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F30,'feed pars'!B$6:B$42,0))</f>
         <v>1.1494252873563218</v>
       </c>
     </row>
-    <row r="31" spans="6:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F31" t="s">
         <v>49</v>
       </c>
-      <c r="H31" t="s">
+      <c r="I31" t="s">
         <v>48</v>
       </c>
-      <c r="I31" t="s">
+      <c r="J31" t="s">
         <v>32</v>
       </c>
-      <c r="J31" s="22">
+      <c r="K31" s="22">
         <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F31,'feed pars'!B$6:B$42,0))</f>
         <v>1.1363636363636365</v>
       </c>
     </row>
-    <row r="32" spans="6:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F32" t="s">
         <v>50</v>
       </c>
-      <c r="H32" t="s">
+      <c r="I32" t="s">
         <v>301</v>
       </c>
-      <c r="I32" t="s">
+      <c r="J32" t="s">
         <v>32</v>
       </c>
-      <c r="J32" s="20">
-        <f>J33</f>
+      <c r="K32" s="20">
+        <f>K33</f>
         <v>9.0909090909090917</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F33" t="s">
         <v>51</v>
       </c>
-      <c r="H33" t="s">
+      <c r="I33" t="s">
         <v>301</v>
       </c>
-      <c r="I33" t="s">
+      <c r="J33" t="s">
         <v>32</v>
       </c>
-      <c r="J33" s="22">
+      <c r="K33" s="22">
         <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F33,'feed pars'!B$6:B$42,0))</f>
         <v>9.0909090909090917</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F34" t="s">
         <v>313</v>
       </c>
-      <c r="H34" t="s">
+      <c r="I34" t="s">
         <v>313</v>
       </c>
-      <c r="I34" t="s">
+      <c r="J34" t="s">
         <v>32</v>
       </c>
-      <c r="J34" s="20">
+      <c r="K34" s="20">
         <f>1/0.25</f>
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F35" t="s">
         <v>52</v>
       </c>
-      <c r="H35" t="s">
+      <c r="I35" t="s">
         <v>52</v>
       </c>
-      <c r="I35" t="s">
+      <c r="J35" t="s">
         <v>32</v>
       </c>
-      <c r="J35" s="22">
+      <c r="K35" s="22">
         <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F35,'feed pars'!B$6:B$42,0))</f>
         <v>1.3245033112582782</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F36" t="s">
         <v>53</v>
       </c>
-      <c r="H36" t="s">
+      <c r="I36" t="s">
         <v>53</v>
       </c>
-      <c r="I36" t="s">
+      <c r="J36" t="s">
         <v>32</v>
       </c>
-      <c r="J36" s="22">
+      <c r="K36" s="22">
         <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F36,'feed pars'!B$6:B$42,0))</f>
         <v>1.1173184357541899</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F37" t="s">
         <v>54</v>
       </c>
-      <c r="H37" t="s">
+      <c r="I37" t="s">
         <v>54</v>
       </c>
-      <c r="I37" t="s">
+      <c r="J37" t="s">
         <v>32</v>
       </c>
-      <c r="J37" s="22">
+      <c r="K37" s="22">
         <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F37,'feed pars'!B$6:B$42,0))</f>
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F38" t="s">
         <v>55</v>
       </c>
-      <c r="H38" t="s">
+      <c r="I38" t="s">
         <v>54</v>
       </c>
-      <c r="I38" t="s">
+      <c r="J38" t="s">
         <v>32</v>
       </c>
-      <c r="J38" s="20">
-        <f>J37</f>
+      <c r="K38" s="20">
+        <f>K37</f>
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F39" t="s">
         <v>56</v>
       </c>
-      <c r="H39" t="s">
+      <c r="I39" t="s">
         <v>56</v>
       </c>
-      <c r="I39" t="s">
+      <c r="J39" t="s">
         <v>32</v>
       </c>
-      <c r="J39" s="22">
+      <c r="K39" s="22">
         <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F39,'feed pars'!B$6:B$42,0))</f>
         <v>1.0989010989010988</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F40" t="s">
         <v>57</v>
       </c>
-      <c r="H40" t="s">
+      <c r="I40" t="s">
         <v>57</v>
       </c>
-      <c r="I40" t="s">
+      <c r="J40" t="s">
         <v>32</v>
       </c>
-      <c r="J40" s="22">
+      <c r="K40" s="22">
         <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F40,'feed pars'!B$6:B$42,0))</f>
         <v>1.0869565217391304</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>29</v>
       </c>
@@ -2126,62 +2180,63 @@
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="I42" s="10" t="s">
+      <c r="N41" s="2"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J42" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="J42" s="10">
-        <v>0</v>
-      </c>
-      <c r="K42" s="10"/>
-      <c r="L42" s="10" t="s">
+      <c r="K42" s="10">
+        <v>0</v>
+      </c>
+      <c r="L42" s="10"/>
+      <c r="M42" s="10" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="G43" t="s">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="H43" t="s">
         <v>10</v>
       </c>
-      <c r="I43" t="s">
+      <c r="J43" t="s">
         <v>27</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>95</v>
       </c>
-      <c r="K43" t="s">
+      <c r="L43" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="G44" t="s">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="H44" t="s">
         <v>11</v>
       </c>
-      <c r="I44" t="s">
+      <c r="J44" t="s">
         <v>27</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>95</v>
       </c>
-      <c r="K44" t="s">
+      <c r="L44" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="G45" t="s">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="H45" t="s">
         <v>33</v>
       </c>
-      <c r="I45" t="s">
+      <c r="J45" t="s">
         <v>27</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>95</v>
       </c>
-      <c r="K45" t="s">
+      <c r="L45" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>30</v>
       </c>
@@ -2197,928 +2252,967 @@
       <c r="K46" s="2"/>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="I47" s="10" t="s">
+      <c r="N46" s="2"/>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J47" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="J47" s="10">
-        <v>0</v>
-      </c>
-      <c r="K47" s="10"/>
-      <c r="L47" s="10" t="s">
+      <c r="K47" s="10">
+        <v>0</v>
+      </c>
+      <c r="L47" s="10"/>
+      <c r="M47" s="10" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="H48" t="s">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I48" t="s">
         <v>318</v>
       </c>
-      <c r="I48" t="s">
+      <c r="J48" t="s">
         <v>31</v>
       </c>
-      <c r="J48" s="29">
+      <c r="K48" s="29">
         <v>100</v>
       </c>
-      <c r="K48" s="29" t="s">
+      <c r="L48" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="L48" s="10"/>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="H49" t="s">
+      <c r="M48" s="10"/>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I49" t="s">
         <v>44</v>
       </c>
-      <c r="I49" t="s">
+      <c r="J49" t="s">
         <v>31</v>
       </c>
-      <c r="J49" s="29">
+      <c r="K49" s="29">
         <v>100</v>
       </c>
-      <c r="K49" s="29" t="s">
+      <c r="L49" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="L49" s="10"/>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="H50" t="s">
+      <c r="M49" s="10"/>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I50" t="s">
         <v>36</v>
       </c>
-      <c r="I50" t="s">
+      <c r="J50" t="s">
         <v>31</v>
       </c>
-      <c r="J50" s="29">
+      <c r="K50" s="29">
         <v>61</v>
       </c>
-      <c r="K50" t="s">
+      <c r="L50" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="G51" t="s">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="H51" t="s">
         <v>43</v>
       </c>
-      <c r="I51" t="s">
+      <c r="J51" t="s">
         <v>31</v>
       </c>
-      <c r="J51" s="3">
+      <c r="K51" s="3">
         <v>100</v>
       </c>
-      <c r="K51" t="s">
+      <c r="L51" t="s">
         <v>28</v>
       </c>
-      <c r="L51" s="3" t="s">
+      <c r="M51" s="3" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="J52" s="3"/>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
-      <c r="D53" s="1"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
-      <c r="J53" s="2"/>
-      <c r="K53" s="2"/>
-      <c r="L53" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="M53" s="2"/>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A54" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B54" s="7"/>
-      <c r="C54" s="6"/>
-      <c r="D54" s="6"/>
-      <c r="E54" s="6"/>
-      <c r="F54" s="6"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6"/>
-      <c r="J54" s="6"/>
-      <c r="K54" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L54" s="6"/>
-      <c r="M54" s="6"/>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2"/>
+      <c r="L52" s="2"/>
+      <c r="M52" s="2"/>
+      <c r="N52" s="2"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>24</v>
+      </c>
+      <c r="B53" t="s">
+        <v>326</v>
+      </c>
+      <c r="E53" t="s">
+        <v>327</v>
+      </c>
+      <c r="G53" t="s">
+        <v>334</v>
+      </c>
+      <c r="H53" t="s">
+        <v>33</v>
+      </c>
+      <c r="J53" t="s">
+        <v>335</v>
+      </c>
+      <c r="K53" s="3">
+        <v>5</v>
+      </c>
+      <c r="L53" t="s">
+        <v>28</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>24</v>
+      </c>
+      <c r="B54" t="s">
+        <v>326</v>
+      </c>
+      <c r="E54" t="s">
+        <v>328</v>
+      </c>
+      <c r="G54" t="s">
+        <v>334</v>
+      </c>
+      <c r="H54" t="s">
+        <v>33</v>
+      </c>
+      <c r="J54" t="s">
+        <v>335</v>
+      </c>
+      <c r="K54" s="3">
+        <v>5</v>
+      </c>
+      <c r="L54" t="s">
+        <v>28</v>
+      </c>
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>24</v>
       </c>
-      <c r="F55" t="s">
-        <v>310</v>
-      </c>
-      <c r="I55" t="s">
-        <v>18</v>
-      </c>
-      <c r="J55" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F55,'feed pars'!B$6:B$42,0))</f>
-        <v>11.5</v>
-      </c>
-      <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
+        <v>326</v>
+      </c>
+      <c r="E55" t="s">
+        <v>329</v>
+      </c>
+      <c r="G55" t="s">
+        <v>334</v>
+      </c>
+      <c r="H55" t="s">
+        <v>33</v>
+      </c>
+      <c r="J55" t="s">
+        <v>335</v>
+      </c>
+      <c r="K55" s="3">
+        <v>0</v>
+      </c>
+      <c r="L55" t="s">
+        <v>28</v>
+      </c>
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>24</v>
       </c>
-      <c r="F56" t="s">
-        <v>311</v>
-      </c>
-      <c r="I56" t="s">
-        <v>18</v>
-      </c>
-      <c r="J56" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F56,'feed pars'!B$6:B$42,0))</f>
-        <v>10.4</v>
-      </c>
-      <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
+        <v>326</v>
+      </c>
+      <c r="E56" t="s">
+        <v>330</v>
+      </c>
+      <c r="G56" t="s">
+        <v>334</v>
+      </c>
+      <c r="H56" t="s">
+        <v>33</v>
+      </c>
+      <c r="J56" t="s">
+        <v>335</v>
+      </c>
+      <c r="K56" s="3">
+        <v>90</v>
+      </c>
+      <c r="L56" t="s">
+        <v>28</v>
+      </c>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>24</v>
       </c>
-      <c r="F57" t="s">
-        <v>312</v>
-      </c>
-      <c r="I57" t="s">
-        <v>18</v>
-      </c>
-      <c r="J57" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F57,'feed pars'!B$6:B$42,0))</f>
-        <v>10</v>
-      </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
+        <v>326</v>
+      </c>
+      <c r="E57" t="s">
+        <v>331</v>
+      </c>
+      <c r="G57" t="s">
+        <v>334</v>
+      </c>
+      <c r="H57" t="s">
+        <v>33</v>
+      </c>
+      <c r="J57" t="s">
+        <v>335</v>
+      </c>
+      <c r="K57" s="3">
+        <v>90</v>
+      </c>
+      <c r="L57" t="s">
+        <v>28</v>
+      </c>
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>24</v>
       </c>
-      <c r="F58" t="s">
-        <v>12</v>
-      </c>
-      <c r="I58" t="s">
-        <v>18</v>
-      </c>
-      <c r="J58" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F58,'feed pars'!B$6:B$42,0))</f>
-        <v>11.3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
+        <v>326</v>
+      </c>
+      <c r="E58" t="s">
+        <v>332</v>
+      </c>
+      <c r="G58" t="s">
+        <v>334</v>
+      </c>
+      <c r="H58" t="s">
+        <v>33</v>
+      </c>
+      <c r="J58" t="s">
+        <v>335</v>
+      </c>
+      <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" t="s">
+        <v>28</v>
+      </c>
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>24</v>
       </c>
-      <c r="F59" t="s">
+      <c r="B59" t="s">
+        <v>333</v>
+      </c>
+      <c r="E59" t="s">
+        <v>327</v>
+      </c>
+      <c r="G59" t="s">
+        <v>334</v>
+      </c>
+      <c r="H59" t="s">
         <v>33</v>
       </c>
-      <c r="I59" t="s">
-        <v>18</v>
-      </c>
-      <c r="J59" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F59,'feed pars'!B$6:B$42,0))</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="J60" s="3"/>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J59" t="s">
+        <v>335</v>
+      </c>
+      <c r="K59" s="3">
+        <v>90</v>
+      </c>
+      <c r="L59" t="s">
+        <v>28</v>
+      </c>
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>24</v>
+      </c>
+      <c r="B60" t="s">
+        <v>333</v>
+      </c>
+      <c r="E60" t="s">
+        <v>328</v>
+      </c>
+      <c r="G60" t="s">
+        <v>334</v>
+      </c>
+      <c r="H60" t="s">
+        <v>33</v>
+      </c>
+      <c r="J60" t="s">
+        <v>335</v>
+      </c>
+      <c r="K60" s="3">
+        <v>90</v>
+      </c>
+      <c r="L60" t="s">
+        <v>28</v>
+      </c>
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>24</v>
       </c>
-      <c r="F61" t="s">
-        <v>17</v>
-      </c>
-      <c r="I61" t="s">
-        <v>18</v>
-      </c>
-      <c r="J61" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F61,'feed pars'!B$6:B$42,0))</f>
-        <v>14.1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B61" t="s">
+        <v>333</v>
+      </c>
+      <c r="E61" t="s">
+        <v>329</v>
+      </c>
+      <c r="G61" t="s">
+        <v>334</v>
+      </c>
+      <c r="H61" t="s">
+        <v>33</v>
+      </c>
+      <c r="J61" t="s">
+        <v>335</v>
+      </c>
+      <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" t="s">
+        <v>28</v>
+      </c>
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>24</v>
       </c>
-      <c r="F62" t="s">
-        <v>37</v>
-      </c>
-      <c r="I62" t="s">
-        <v>18</v>
-      </c>
-      <c r="J62" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F62,'feed pars'!B$6:B$42,0))</f>
-        <v>13.2</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B62" t="s">
+        <v>333</v>
+      </c>
+      <c r="E62" t="s">
+        <v>330</v>
+      </c>
+      <c r="G62" t="s">
+        <v>334</v>
+      </c>
+      <c r="H62" t="s">
+        <v>33</v>
+      </c>
+      <c r="J62" t="s">
+        <v>335</v>
+      </c>
+      <c r="K62" s="3">
+        <v>90</v>
+      </c>
+      <c r="L62" t="s">
+        <v>28</v>
+      </c>
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>24</v>
       </c>
-      <c r="F63" t="s">
-        <v>38</v>
-      </c>
-      <c r="I63" t="s">
-        <v>18</v>
-      </c>
-      <c r="J63" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F63,'feed pars'!B$6:B$42,0))</f>
-        <v>11.7</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B63" t="s">
+        <v>333</v>
+      </c>
+      <c r="E63" t="s">
+        <v>331</v>
+      </c>
+      <c r="G63" t="s">
+        <v>334</v>
+      </c>
+      <c r="H63" t="s">
+        <v>33</v>
+      </c>
+      <c r="J63" t="s">
+        <v>335</v>
+      </c>
+      <c r="K63" s="3">
+        <v>90</v>
+      </c>
+      <c r="L63" t="s">
+        <v>28</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>24</v>
       </c>
-      <c r="F64" t="s">
-        <v>39</v>
-      </c>
-      <c r="I64" t="s">
-        <v>18</v>
-      </c>
-      <c r="J64" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F64,'feed pars'!B$6:B$42,0))</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>24</v>
-      </c>
-      <c r="F65" t="s">
-        <v>317</v>
-      </c>
-      <c r="I65" t="s">
-        <v>18</v>
-      </c>
-      <c r="J65" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F65,'feed pars'!B$6:B$42,0))</f>
-        <v>13.9</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>24</v>
-      </c>
-      <c r="F66" t="s">
-        <v>40</v>
-      </c>
-      <c r="I66" t="s">
-        <v>18</v>
-      </c>
-      <c r="J66" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F66,'feed pars'!B$6:B$42,0))</f>
-        <v>12.8</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>24</v>
-      </c>
-      <c r="F67" t="s">
-        <v>41</v>
-      </c>
-      <c r="I67" t="s">
-        <v>18</v>
-      </c>
-      <c r="J67" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F67,'feed pars'!B$6:B$42,0))</f>
-        <v>13.8</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>24</v>
-      </c>
-      <c r="F68" t="s">
-        <v>42</v>
-      </c>
-      <c r="I68" t="s">
-        <v>18</v>
-      </c>
-      <c r="J68" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F68,'feed pars'!B$6:B$42,0))</f>
-        <v>13.3</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>24</v>
-      </c>
-      <c r="F69" t="s">
-        <v>35</v>
-      </c>
-      <c r="I69" t="s">
-        <v>18</v>
-      </c>
-      <c r="J69" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F69,'feed pars'!B$6:B$42,0))</f>
-        <v>22.1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
+        <v>333</v>
+      </c>
+      <c r="E64" t="s">
+        <v>332</v>
+      </c>
+      <c r="G64" t="s">
+        <v>334</v>
+      </c>
+      <c r="H64" t="s">
+        <v>33</v>
+      </c>
+      <c r="J64" t="s">
+        <v>335</v>
+      </c>
+      <c r="K64" s="3">
+        <v>90</v>
+      </c>
+      <c r="L64" t="s">
+        <v>28</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K65" s="3"/>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K66" s="3"/>
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K67" s="3"/>
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2"/>
+      <c r="L68" s="2"/>
+      <c r="M68" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="N68" s="2"/>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A69" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B69" s="7"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="6"/>
+      <c r="I69" s="6"/>
+      <c r="J69" s="6"/>
+      <c r="K69" s="6"/>
+      <c r="L69" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M69" s="6"/>
+      <c r="N69" s="6"/>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>24</v>
       </c>
       <c r="F70" t="s">
-        <v>43</v>
-      </c>
-      <c r="I70" t="s">
+        <v>310</v>
+      </c>
+      <c r="J70" t="s">
         <v>18</v>
       </c>
-      <c r="J70" s="26">
+      <c r="K70" s="26">
         <f>INDEX('feed pars'!M$6:M$42,MATCH(F70,'feed pars'!B$6:B$42,0))</f>
-        <v>20.100000000000001</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+        <v>11.5</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>24</v>
       </c>
       <c r="F71" t="s">
-        <v>305</v>
-      </c>
-      <c r="I71" t="s">
+        <v>311</v>
+      </c>
+      <c r="J71" t="s">
         <v>18</v>
       </c>
-      <c r="J71" s="26">
+      <c r="K71" s="26">
         <f>INDEX('feed pars'!M$6:M$42,MATCH(F71,'feed pars'!B$6:B$42,0))</f>
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+        <v>10.4</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>24</v>
       </c>
       <c r="F72" t="s">
-        <v>314</v>
-      </c>
-      <c r="I72" t="s">
+        <v>312</v>
+      </c>
+      <c r="J72" t="s">
         <v>18</v>
       </c>
-      <c r="J72" s="26">
+      <c r="K72" s="26">
         <f>INDEX('feed pars'!M$6:M$42,MATCH(F72,'feed pars'!B$6:B$42,0))</f>
-        <v>36.6</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>24</v>
       </c>
       <c r="F73" t="s">
-        <v>318</v>
-      </c>
-      <c r="I73" t="s">
+        <v>12</v>
+      </c>
+      <c r="J73" t="s">
         <v>18</v>
       </c>
-      <c r="J73" s="26">
+      <c r="K73" s="26">
         <f>INDEX('feed pars'!M$6:M$42,MATCH(F73,'feed pars'!B$6:B$42,0))</f>
-        <v>16.399999999999999</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>24</v>
       </c>
       <c r="F74" t="s">
-        <v>44</v>
-      </c>
-      <c r="I74" t="s">
+        <v>33</v>
+      </c>
+      <c r="J74" t="s">
         <v>18</v>
       </c>
-      <c r="J74" s="26">
+      <c r="K74" s="26">
         <f>INDEX('feed pars'!M$6:M$42,MATCH(F74,'feed pars'!B$6:B$42,0))</f>
-        <v>14.6</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>24</v>
-      </c>
-      <c r="F75" t="s">
-        <v>36</v>
-      </c>
-      <c r="I75" t="s">
-        <v>18</v>
-      </c>
-      <c r="J75" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F75,'feed pars'!B$6:B$42,0))</f>
-        <v>12.2</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K75" s="3"/>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>24</v>
       </c>
       <c r="F76" t="s">
-        <v>46</v>
-      </c>
-      <c r="I76" t="s">
+        <v>17</v>
+      </c>
+      <c r="J76" t="s">
         <v>18</v>
       </c>
-      <c r="J76" s="26">
+      <c r="K76" s="26">
         <f>INDEX('feed pars'!M$6:M$42,MATCH(F76,'feed pars'!B$6:B$42,0))</f>
-        <v>11.4</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>24</v>
       </c>
       <c r="F77" t="s">
-        <v>47</v>
-      </c>
-      <c r="I77" t="s">
+        <v>37</v>
+      </c>
+      <c r="J77" t="s">
         <v>18</v>
       </c>
-      <c r="J77" s="26">
+      <c r="K77" s="26">
         <f>INDEX('feed pars'!M$6:M$42,MATCH(F77,'feed pars'!B$6:B$42,0))</f>
-        <v>13.4</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>24</v>
       </c>
       <c r="F78" t="s">
-        <v>319</v>
-      </c>
-      <c r="I78" t="s">
+        <v>38</v>
+      </c>
+      <c r="J78" t="s">
         <v>18</v>
       </c>
-      <c r="J78" s="26">
+      <c r="K78" s="26">
         <f>INDEX('feed pars'!M$6:M$42,MATCH(F78,'feed pars'!B$6:B$42,0))</f>
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>24</v>
       </c>
       <c r="F79" t="s">
-        <v>48</v>
-      </c>
-      <c r="I79" t="s">
+        <v>39</v>
+      </c>
+      <c r="J79" t="s">
         <v>18</v>
       </c>
-      <c r="J79" s="26">
+      <c r="K79" s="26">
         <f>INDEX('feed pars'!M$6:M$42,MATCH(F79,'feed pars'!B$6:B$42,0))</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>24</v>
       </c>
       <c r="F80" t="s">
-        <v>50</v>
-      </c>
-      <c r="I80" t="s">
+        <v>317</v>
+      </c>
+      <c r="J80" t="s">
         <v>18</v>
       </c>
-      <c r="J80" s="26">
+      <c r="K80" s="26">
         <f>INDEX('feed pars'!M$6:M$42,MATCH(F80,'feed pars'!B$6:B$42,0))</f>
-        <v>13.3</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>24</v>
       </c>
       <c r="F81" t="s">
-        <v>313</v>
-      </c>
-      <c r="I81" t="s">
+        <v>40</v>
+      </c>
+      <c r="J81" t="s">
         <v>18</v>
       </c>
-      <c r="J81" s="26">
+      <c r="K81" s="26">
         <f>INDEX('feed pars'!M$6:M$42,MATCH(F81,'feed pars'!B$6:B$42,0))</f>
-        <v>11.6</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>24</v>
       </c>
       <c r="F82" t="s">
-        <v>52</v>
-      </c>
-      <c r="I82" t="s">
+        <v>41</v>
+      </c>
+      <c r="J82" t="s">
         <v>18</v>
       </c>
-      <c r="J82" s="26">
+      <c r="K82" s="26">
         <f>INDEX('feed pars'!M$6:M$42,MATCH(F82,'feed pars'!B$6:B$42,0))</f>
-        <v>12.4</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>24</v>
       </c>
       <c r="F83" t="s">
-        <v>53</v>
-      </c>
-      <c r="I83" t="s">
+        <v>42</v>
+      </c>
+      <c r="J83" t="s">
         <v>18</v>
       </c>
-      <c r="J83" s="26">
+      <c r="K83" s="26">
         <f>INDEX('feed pars'!M$6:M$42,MATCH(F83,'feed pars'!B$6:B$42,0))</f>
-        <v>12.3</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>24</v>
       </c>
       <c r="F84" t="s">
-        <v>54</v>
-      </c>
-      <c r="I84" t="s">
+        <v>35</v>
+      </c>
+      <c r="J84" t="s">
         <v>18</v>
       </c>
-      <c r="J84" s="26">
+      <c r="K84" s="26">
         <f>INDEX('feed pars'!M$6:M$42,MATCH(F84,'feed pars'!B$6:B$42,0))</f>
-        <v>13.6</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>24</v>
       </c>
       <c r="F85" t="s">
-        <v>56</v>
-      </c>
-      <c r="I85" t="s">
+        <v>43</v>
+      </c>
+      <c r="J85" t="s">
         <v>18</v>
       </c>
-      <c r="J85" s="26">
+      <c r="K85" s="26">
         <f>INDEX('feed pars'!M$6:M$42,MATCH(F85,'feed pars'!B$6:B$42,0))</f>
-        <v>15.5</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+        <v>20.100000000000001</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>24</v>
       </c>
       <c r="F86" t="s">
+        <v>305</v>
+      </c>
+      <c r="J86" t="s">
+        <v>18</v>
+      </c>
+      <c r="K86" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F86,'feed pars'!B$6:B$42,0))</f>
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>24</v>
+      </c>
+      <c r="F87" t="s">
+        <v>314</v>
+      </c>
+      <c r="J87" t="s">
+        <v>18</v>
+      </c>
+      <c r="K87" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F87,'feed pars'!B$6:B$42,0))</f>
+        <v>36.6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>24</v>
+      </c>
+      <c r="F88" t="s">
+        <v>318</v>
+      </c>
+      <c r="J88" t="s">
+        <v>18</v>
+      </c>
+      <c r="K88" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F88,'feed pars'!B$6:B$42,0))</f>
+        <v>16.399999999999999</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>24</v>
+      </c>
+      <c r="F89" t="s">
+        <v>44</v>
+      </c>
+      <c r="J89" t="s">
+        <v>18</v>
+      </c>
+      <c r="K89" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F89,'feed pars'!B$6:B$42,0))</f>
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>24</v>
+      </c>
+      <c r="F90" t="s">
+        <v>36</v>
+      </c>
+      <c r="J90" t="s">
+        <v>18</v>
+      </c>
+      <c r="K90" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F90,'feed pars'!B$6:B$42,0))</f>
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>24</v>
+      </c>
+      <c r="F91" t="s">
+        <v>46</v>
+      </c>
+      <c r="J91" t="s">
+        <v>18</v>
+      </c>
+      <c r="K91" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F91,'feed pars'!B$6:B$42,0))</f>
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>24</v>
+      </c>
+      <c r="F92" t="s">
+        <v>47</v>
+      </c>
+      <c r="J92" t="s">
+        <v>18</v>
+      </c>
+      <c r="K92" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F92,'feed pars'!B$6:B$42,0))</f>
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>24</v>
+      </c>
+      <c r="F93" t="s">
+        <v>319</v>
+      </c>
+      <c r="J93" t="s">
+        <v>18</v>
+      </c>
+      <c r="K93" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F93,'feed pars'!B$6:B$42,0))</f>
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>24</v>
+      </c>
+      <c r="F94" t="s">
+        <v>48</v>
+      </c>
+      <c r="J94" t="s">
+        <v>18</v>
+      </c>
+      <c r="K94" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F94,'feed pars'!B$6:B$42,0))</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>24</v>
+      </c>
+      <c r="F95" t="s">
+        <v>50</v>
+      </c>
+      <c r="J95" t="s">
+        <v>18</v>
+      </c>
+      <c r="K95" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F95,'feed pars'!B$6:B$42,0))</f>
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>24</v>
+      </c>
+      <c r="F96" t="s">
+        <v>313</v>
+      </c>
+      <c r="J96" t="s">
+        <v>18</v>
+      </c>
+      <c r="K96" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F96,'feed pars'!B$6:B$42,0))</f>
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>24</v>
+      </c>
+      <c r="F97" t="s">
+        <v>52</v>
+      </c>
+      <c r="J97" t="s">
+        <v>18</v>
+      </c>
+      <c r="K97" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F97,'feed pars'!B$6:B$42,0))</f>
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>24</v>
+      </c>
+      <c r="F98" t="s">
+        <v>53</v>
+      </c>
+      <c r="J98" t="s">
+        <v>18</v>
+      </c>
+      <c r="K98" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F98,'feed pars'!B$6:B$42,0))</f>
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>24</v>
+      </c>
+      <c r="F99" t="s">
+        <v>54</v>
+      </c>
+      <c r="J99" t="s">
+        <v>18</v>
+      </c>
+      <c r="K99" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F99,'feed pars'!B$6:B$42,0))</f>
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>24</v>
+      </c>
+      <c r="F100" t="s">
+        <v>56</v>
+      </c>
+      <c r="J100" t="s">
+        <v>18</v>
+      </c>
+      <c r="K100" s="26">
+        <f>INDEX('feed pars'!M$6:M$42,MATCH(F100,'feed pars'!B$6:B$42,0))</f>
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>24</v>
+      </c>
+      <c r="F101" t="s">
         <v>324</v>
       </c>
-      <c r="I86" t="s">
+      <c r="J101" t="s">
         <v>18</v>
       </c>
-      <c r="J86" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="J87" s="3"/>
-    </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A88" s="8" t="s">
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K102" s="3"/>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A103" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B88" s="8"/>
-      <c r="C88" s="9"/>
-      <c r="D88" s="9"/>
-      <c r="E88" s="9"/>
-      <c r="F88" s="9"/>
-      <c r="G88" s="9"/>
-      <c r="H88" s="9"/>
-      <c r="I88" s="9"/>
-      <c r="J88" s="9"/>
-      <c r="K88" s="9"/>
-      <c r="L88" s="9"/>
-      <c r="M88" s="9"/>
-    </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>25</v>
-      </c>
-      <c r="E89" t="s">
-        <v>299</v>
-      </c>
-      <c r="F89" t="s">
-        <v>17</v>
-      </c>
-      <c r="I89" t="s">
-        <v>18</v>
-      </c>
-      <c r="J89" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F89,'feed pars'!B$6:B$42,0))</f>
-        <v>12.3</v>
-      </c>
-      <c r="K89" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>25</v>
-      </c>
-      <c r="E90" t="s">
-        <v>299</v>
-      </c>
-      <c r="F90" t="s">
-        <v>37</v>
-      </c>
-      <c r="I90" t="s">
-        <v>18</v>
-      </c>
-      <c r="J90" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F90,'feed pars'!B$6:B$42,0))</f>
-        <v>11.2</v>
-      </c>
-      <c r="K90" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>25</v>
-      </c>
-      <c r="E91" t="s">
-        <v>299</v>
-      </c>
-      <c r="F91" t="s">
-        <v>38</v>
-      </c>
-      <c r="I91" t="s">
-        <v>18</v>
-      </c>
-      <c r="J91" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F91,'feed pars'!B$6:B$42,0))</f>
-        <v>9.4</v>
-      </c>
-      <c r="K91" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>25</v>
-      </c>
-      <c r="E92" t="s">
-        <v>299</v>
-      </c>
-      <c r="F92" t="s">
-        <v>39</v>
-      </c>
-      <c r="I92" t="s">
-        <v>18</v>
-      </c>
-      <c r="J92" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F92,'feed pars'!B$6:B$42,0))</f>
-        <v>12</v>
-      </c>
-      <c r="K92" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>25</v>
-      </c>
-      <c r="E93" t="s">
-        <v>299</v>
-      </c>
-      <c r="F93" t="s">
-        <v>40</v>
-      </c>
-      <c r="I93" t="s">
-        <v>18</v>
-      </c>
-      <c r="J93" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F93,'feed pars'!B$6:B$42,0))</f>
-        <v>13.2</v>
-      </c>
-      <c r="K93" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>25</v>
-      </c>
-      <c r="E94" t="s">
-        <v>299</v>
-      </c>
-      <c r="F94" t="s">
-        <v>41</v>
-      </c>
-      <c r="I94" t="s">
-        <v>18</v>
-      </c>
-      <c r="J94" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F94,'feed pars'!B$6:B$42,0))</f>
-        <v>11.5</v>
-      </c>
-      <c r="K94" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>25</v>
-      </c>
-      <c r="E95" t="s">
-        <v>299</v>
-      </c>
-      <c r="F95" t="s">
-        <v>42</v>
-      </c>
-      <c r="I95" t="s">
-        <v>18</v>
-      </c>
-      <c r="J95" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F95,'feed pars'!B$6:B$42,0))</f>
-        <v>10.9</v>
-      </c>
-      <c r="K95" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>25</v>
-      </c>
-      <c r="E96" t="s">
-        <v>299</v>
-      </c>
-      <c r="F96" t="s">
-        <v>35</v>
-      </c>
-      <c r="I96" t="s">
-        <v>18</v>
-      </c>
-      <c r="J96" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F96,'feed pars'!B$6:B$42,0))</f>
-        <v>18.5</v>
-      </c>
-      <c r="K96" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>25</v>
-      </c>
-      <c r="E97" t="s">
-        <v>299</v>
-      </c>
-      <c r="F97" t="s">
-        <v>43</v>
-      </c>
-      <c r="I97" t="s">
-        <v>18</v>
-      </c>
-      <c r="J97" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F97,'feed pars'!B$6:B$42,0))</f>
-        <v>17.5</v>
-      </c>
-      <c r="K97" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>25</v>
-      </c>
-      <c r="E98" t="s">
-        <v>299</v>
-      </c>
-      <c r="F98" t="s">
-        <v>314</v>
-      </c>
-      <c r="I98" t="s">
-        <v>18</v>
-      </c>
-      <c r="J98" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F98,'feed pars'!B$6:B$42,0))</f>
-        <v>29.8</v>
-      </c>
-      <c r="K98" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>25</v>
-      </c>
-      <c r="E99" t="s">
-        <v>299</v>
-      </c>
-      <c r="F99" t="s">
-        <v>44</v>
-      </c>
-      <c r="I99" t="s">
-        <v>18</v>
-      </c>
-      <c r="J99" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F99,'feed pars'!B$6:B$42,0))</f>
-        <v>9.9</v>
-      </c>
-      <c r="K99" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>25</v>
-      </c>
-      <c r="E100" t="s">
-        <v>299</v>
-      </c>
-      <c r="F100" t="s">
-        <v>45</v>
-      </c>
-      <c r="I100" t="s">
-        <v>18</v>
-      </c>
-      <c r="J100" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F100,'feed pars'!B$6:B$42,0))</f>
-        <v>10.3</v>
-      </c>
-      <c r="K100" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>25</v>
-      </c>
-      <c r="E101" t="s">
-        <v>299</v>
-      </c>
-      <c r="F101" t="s">
-        <v>36</v>
-      </c>
-      <c r="I101" t="s">
-        <v>18</v>
-      </c>
-      <c r="J101" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F101,'feed pars'!B$6:B$42,0))</f>
-        <v>7.7</v>
-      </c>
-      <c r="K101" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>25</v>
-      </c>
-      <c r="E102" t="s">
-        <v>299</v>
-      </c>
-      <c r="F102" t="s">
-        <v>46</v>
-      </c>
-      <c r="I102" t="s">
-        <v>18</v>
-      </c>
-      <c r="J102" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F102,'feed pars'!B$6:B$42,0))</f>
-        <v>6.5</v>
-      </c>
-      <c r="K102" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>25</v>
-      </c>
-      <c r="E103" t="s">
-        <v>299</v>
-      </c>
-      <c r="F103" t="s">
-        <v>47</v>
-      </c>
-      <c r="I103" t="s">
-        <v>18</v>
-      </c>
-      <c r="J103" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F103,'feed pars'!B$6:B$42,0))</f>
-        <v>6.2</v>
-      </c>
-      <c r="K103" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B103" s="8"/>
+      <c r="C103" s="9"/>
+      <c r="D103" s="9"/>
+      <c r="E103" s="9"/>
+      <c r="F103" s="9"/>
+      <c r="G103" s="9"/>
+      <c r="H103" s="9"/>
+      <c r="I103" s="9"/>
+      <c r="J103" s="9"/>
+      <c r="K103" s="9"/>
+      <c r="L103" s="9"/>
+      <c r="M103" s="9"/>
+      <c r="N103" s="9"/>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>25</v>
       </c>
@@ -3126,20 +3220,20 @@
         <v>299</v>
       </c>
       <c r="F104" t="s">
-        <v>48</v>
-      </c>
-      <c r="I104" t="s">
+        <v>17</v>
+      </c>
+      <c r="J104" t="s">
         <v>18</v>
       </c>
-      <c r="J104" s="26">
+      <c r="K104" s="26">
         <f>INDEX('feed pars'!H$6:H$42,MATCH(F104,'feed pars'!B$6:B$42,0))</f>
-        <v>7.8</v>
-      </c>
-      <c r="K104" t="s">
+        <v>12.3</v>
+      </c>
+      <c r="L104" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>25</v>
       </c>
@@ -3147,20 +3241,20 @@
         <v>299</v>
       </c>
       <c r="F105" t="s">
-        <v>49</v>
-      </c>
-      <c r="I105" t="s">
+        <v>37</v>
+      </c>
+      <c r="J105" t="s">
         <v>18</v>
       </c>
-      <c r="J105" s="26">
+      <c r="K105" s="26">
         <f>INDEX('feed pars'!H$6:H$42,MATCH(F105,'feed pars'!B$6:B$42,0))</f>
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="K105" t="s">
+        <v>11.2</v>
+      </c>
+      <c r="L105" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>25</v>
       </c>
@@ -3168,20 +3262,20 @@
         <v>299</v>
       </c>
       <c r="F106" t="s">
-        <v>50</v>
-      </c>
-      <c r="I106" t="s">
+        <v>38</v>
+      </c>
+      <c r="J106" t="s">
         <v>18</v>
       </c>
-      <c r="J106" s="26">
+      <c r="K106" s="26">
         <f>INDEX('feed pars'!H$6:H$42,MATCH(F106,'feed pars'!B$6:B$42,0))</f>
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="K106" t="s">
+        <v>9.4</v>
+      </c>
+      <c r="L106" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>25</v>
       </c>
@@ -3189,20 +3283,20 @@
         <v>299</v>
       </c>
       <c r="F107" t="s">
-        <v>51</v>
-      </c>
-      <c r="I107" t="s">
+        <v>39</v>
+      </c>
+      <c r="J107" t="s">
         <v>18</v>
       </c>
-      <c r="J107" s="26">
+      <c r="K107" s="26">
         <f>INDEX('feed pars'!H$6:H$42,MATCH(F107,'feed pars'!B$6:B$42,0))</f>
-        <v>8.9</v>
-      </c>
-      <c r="K107" t="s">
+        <v>12</v>
+      </c>
+      <c r="L107" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>25</v>
       </c>
@@ -3210,20 +3304,20 @@
         <v>299</v>
       </c>
       <c r="F108" t="s">
-        <v>313</v>
-      </c>
-      <c r="I108" t="s">
+        <v>40</v>
+      </c>
+      <c r="J108" t="s">
         <v>18</v>
       </c>
-      <c r="J108" s="26">
+      <c r="K108" s="26">
         <f>INDEX('feed pars'!H$6:H$42,MATCH(F108,'feed pars'!B$6:B$42,0))</f>
-        <v>7.0888888888888877</v>
-      </c>
-      <c r="K108" t="s">
+        <v>13.2</v>
+      </c>
+      <c r="L108" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>25</v>
       </c>
@@ -3231,20 +3325,20 @@
         <v>299</v>
       </c>
       <c r="F109" t="s">
-        <v>52</v>
-      </c>
-      <c r="I109" t="s">
+        <v>41</v>
+      </c>
+      <c r="J109" t="s">
         <v>18</v>
       </c>
-      <c r="J109" s="26">
+      <c r="K109" s="26">
         <f>INDEX('feed pars'!H$6:H$42,MATCH(F109,'feed pars'!B$6:B$42,0))</f>
-        <v>9</v>
-      </c>
-      <c r="K109" t="s">
+        <v>11.5</v>
+      </c>
+      <c r="L109" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>25</v>
       </c>
@@ -3252,20 +3346,20 @@
         <v>299</v>
       </c>
       <c r="F110" t="s">
-        <v>53</v>
-      </c>
-      <c r="I110" t="s">
+        <v>42</v>
+      </c>
+      <c r="J110" t="s">
         <v>18</v>
       </c>
-      <c r="J110" s="26">
+      <c r="K110" s="26">
         <f>INDEX('feed pars'!H$6:H$42,MATCH(F110,'feed pars'!B$6:B$42,0))</f>
-        <v>8</v>
-      </c>
-      <c r="K110" t="s">
+        <v>10.9</v>
+      </c>
+      <c r="L110" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>25</v>
       </c>
@@ -3273,20 +3367,20 @@
         <v>299</v>
       </c>
       <c r="F111" t="s">
-        <v>54</v>
-      </c>
-      <c r="I111" t="s">
+        <v>35</v>
+      </c>
+      <c r="J111" t="s">
         <v>18</v>
       </c>
-      <c r="J111" s="26">
+      <c r="K111" s="26">
         <f>INDEX('feed pars'!H$6:H$42,MATCH(F111,'feed pars'!B$6:B$42,0))</f>
-        <v>12.2</v>
-      </c>
-      <c r="K111" t="s">
+        <v>18.5</v>
+      </c>
+      <c r="L111" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>25</v>
       </c>
@@ -3294,20 +3388,20 @@
         <v>299</v>
       </c>
       <c r="F112" t="s">
-        <v>55</v>
-      </c>
-      <c r="I112" t="s">
+        <v>43</v>
+      </c>
+      <c r="J112" t="s">
         <v>18</v>
       </c>
-      <c r="J112" s="26">
+      <c r="K112" s="26">
         <f>INDEX('feed pars'!H$6:H$42,MATCH(F112,'feed pars'!B$6:B$42,0))</f>
-        <v>12.2</v>
-      </c>
-      <c r="K112" t="s">
+        <v>17.5</v>
+      </c>
+      <c r="L112" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>25</v>
       </c>
@@ -3315,20 +3409,20 @@
         <v>299</v>
       </c>
       <c r="F113" t="s">
-        <v>56</v>
-      </c>
-      <c r="I113" t="s">
+        <v>314</v>
+      </c>
+      <c r="J113" t="s">
         <v>18</v>
       </c>
-      <c r="J113" s="26">
+      <c r="K113" s="26">
         <f>INDEX('feed pars'!H$6:H$42,MATCH(F113,'feed pars'!B$6:B$42,0))</f>
-        <v>11.3</v>
-      </c>
-      <c r="K113" t="s">
+        <v>29.8</v>
+      </c>
+      <c r="L113" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>25</v>
       </c>
@@ -3336,487 +3430,802 @@
         <v>299</v>
       </c>
       <c r="F114" t="s">
-        <v>57</v>
-      </c>
-      <c r="I114" t="s">
+        <v>44</v>
+      </c>
+      <c r="J114" t="s">
         <v>18</v>
       </c>
-      <c r="J114" s="26">
+      <c r="K114" s="26">
         <f>INDEX('feed pars'!H$6:H$42,MATCH(F114,'feed pars'!B$6:B$42,0))</f>
-        <v>10.8</v>
-      </c>
-      <c r="K114" t="s">
+        <v>9.9</v>
+      </c>
+      <c r="L114" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="J115" s="26"/>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>25</v>
+      </c>
+      <c r="E115" t="s">
+        <v>299</v>
+      </c>
+      <c r="F115" t="s">
+        <v>45</v>
+      </c>
+      <c r="J115" t="s">
+        <v>18</v>
+      </c>
+      <c r="K115" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F115,'feed pars'!B$6:B$42,0))</f>
+        <v>10.3</v>
+      </c>
+      <c r="L115" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>25</v>
       </c>
+      <c r="E116" t="s">
+        <v>299</v>
+      </c>
       <c r="F116" t="s">
-        <v>17</v>
-      </c>
-      <c r="I116" t="s">
+        <v>36</v>
+      </c>
+      <c r="J116" t="s">
         <v>18</v>
       </c>
-      <c r="J116" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F116,'feed pars'!B$6:B$42,0))</f>
-        <v>12.1</v>
-      </c>
-      <c r="K116" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K116" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F116,'feed pars'!B$6:B$42,0))</f>
+        <v>7.7</v>
+      </c>
+      <c r="L116" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>25</v>
       </c>
+      <c r="E117" t="s">
+        <v>299</v>
+      </c>
       <c r="F117" t="s">
-        <v>37</v>
-      </c>
-      <c r="I117" t="s">
+        <v>46</v>
+      </c>
+      <c r="J117" t="s">
         <v>18</v>
       </c>
-      <c r="J117" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F117,'feed pars'!B$6:B$42,0))</f>
-        <v>11</v>
-      </c>
-      <c r="K117" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K117" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F117,'feed pars'!B$6:B$42,0))</f>
+        <v>6.5</v>
+      </c>
+      <c r="L117" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>25</v>
       </c>
+      <c r="E118" t="s">
+        <v>299</v>
+      </c>
       <c r="F118" t="s">
-        <v>38</v>
-      </c>
-      <c r="I118" t="s">
+        <v>47</v>
+      </c>
+      <c r="J118" t="s">
         <v>18</v>
       </c>
-      <c r="J118" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F118,'feed pars'!B$6:B$42,0))</f>
-        <v>9</v>
-      </c>
-      <c r="K118" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K118" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F118,'feed pars'!B$6:B$42,0))</f>
+        <v>6.2</v>
+      </c>
+      <c r="L118" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>25</v>
       </c>
+      <c r="E119" t="s">
+        <v>299</v>
+      </c>
       <c r="F119" t="s">
-        <v>39</v>
-      </c>
-      <c r="I119" t="s">
+        <v>48</v>
+      </c>
+      <c r="J119" t="s">
         <v>18</v>
       </c>
-      <c r="J119" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F119,'feed pars'!B$6:B$42,0))</f>
-        <v>11.9</v>
-      </c>
-      <c r="K119" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K119" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F119,'feed pars'!B$6:B$42,0))</f>
+        <v>7.8</v>
+      </c>
+      <c r="L119" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>25</v>
       </c>
+      <c r="E120" t="s">
+        <v>299</v>
+      </c>
       <c r="F120" t="s">
-        <v>40</v>
-      </c>
-      <c r="I120" t="s">
+        <v>49</v>
+      </c>
+      <c r="J120" t="s">
         <v>18</v>
       </c>
-      <c r="J120" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F120,'feed pars'!B$6:B$42,0))</f>
-        <v>12.8</v>
-      </c>
-      <c r="K120" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K120" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F120,'feed pars'!B$6:B$42,0))</f>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="L120" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>25</v>
       </c>
+      <c r="E121" t="s">
+        <v>299</v>
+      </c>
       <c r="F121" t="s">
-        <v>41</v>
-      </c>
-      <c r="I121" t="s">
+        <v>50</v>
+      </c>
+      <c r="J121" t="s">
         <v>18</v>
       </c>
-      <c r="J121" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F121,'feed pars'!B$6:B$42,0))</f>
-        <v>11.2</v>
-      </c>
-      <c r="K121" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K121" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F121,'feed pars'!B$6:B$42,0))</f>
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="L121" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>25</v>
       </c>
+      <c r="E122" t="s">
+        <v>299</v>
+      </c>
       <c r="F122" t="s">
-        <v>42</v>
-      </c>
-      <c r="I122" t="s">
+        <v>51</v>
+      </c>
+      <c r="J122" t="s">
         <v>18</v>
       </c>
-      <c r="J122" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F122,'feed pars'!B$6:B$42,0))</f>
-        <v>10.7</v>
-      </c>
-      <c r="K122" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K122" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F122,'feed pars'!B$6:B$42,0))</f>
+        <v>8.9</v>
+      </c>
+      <c r="L122" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>25</v>
       </c>
+      <c r="E123" t="s">
+        <v>299</v>
+      </c>
       <c r="F123" t="s">
-        <v>35</v>
-      </c>
-      <c r="I123" t="s">
+        <v>313</v>
+      </c>
+      <c r="J123" t="s">
         <v>18</v>
       </c>
-      <c r="J123" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F123,'feed pars'!B$6:B$42,0))</f>
-        <v>18</v>
-      </c>
-      <c r="K123" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K123" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F123,'feed pars'!B$6:B$42,0))</f>
+        <v>7.0888888888888877</v>
+      </c>
+      <c r="L123" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>25</v>
       </c>
+      <c r="E124" t="s">
+        <v>299</v>
+      </c>
       <c r="F124" t="s">
-        <v>43</v>
-      </c>
-      <c r="I124" t="s">
+        <v>52</v>
+      </c>
+      <c r="J124" t="s">
         <v>18</v>
       </c>
-      <c r="J124" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F124,'feed pars'!B$6:B$42,0))</f>
-        <v>17.3</v>
-      </c>
-      <c r="K124" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K124" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F124,'feed pars'!B$6:B$42,0))</f>
+        <v>9</v>
+      </c>
+      <c r="L124" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>25</v>
       </c>
+      <c r="E125" t="s">
+        <v>299</v>
+      </c>
       <c r="F125" t="s">
-        <v>314</v>
-      </c>
-      <c r="I125" t="s">
+        <v>53</v>
+      </c>
+      <c r="J125" t="s">
         <v>18</v>
       </c>
-      <c r="J125" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F125,'feed pars'!B$6:B$42,0))</f>
-        <v>29.8</v>
-      </c>
-      <c r="K125" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K125" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F125,'feed pars'!B$6:B$42,0))</f>
+        <v>8</v>
+      </c>
+      <c r="L125" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>25</v>
       </c>
+      <c r="E126" t="s">
+        <v>299</v>
+      </c>
       <c r="F126" t="s">
-        <v>44</v>
-      </c>
-      <c r="I126" t="s">
+        <v>54</v>
+      </c>
+      <c r="J126" t="s">
         <v>18</v>
       </c>
-      <c r="J126" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F126,'feed pars'!B$6:B$42,0))</f>
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="K126" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K126" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F126,'feed pars'!B$6:B$42,0))</f>
+        <v>12.2</v>
+      </c>
+      <c r="L126" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>25</v>
       </c>
+      <c r="E127" t="s">
+        <v>299</v>
+      </c>
       <c r="F127" t="s">
-        <v>45</v>
-      </c>
-      <c r="I127" t="s">
+        <v>55</v>
+      </c>
+      <c r="J127" t="s">
         <v>18</v>
       </c>
-      <c r="J127" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F127,'feed pars'!B$6:B$42,0))</f>
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="K127" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K127" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F127,'feed pars'!B$6:B$42,0))</f>
+        <v>12.2</v>
+      </c>
+      <c r="L127" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>25</v>
       </c>
+      <c r="E128" t="s">
+        <v>299</v>
+      </c>
       <c r="F128" t="s">
-        <v>36</v>
-      </c>
-      <c r="I128" t="s">
+        <v>56</v>
+      </c>
+      <c r="J128" t="s">
         <v>18</v>
       </c>
-      <c r="J128" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F128,'feed pars'!B$6:B$42,0))</f>
-        <v>7.1</v>
-      </c>
-      <c r="K128" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K128" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F128,'feed pars'!B$6:B$42,0))</f>
+        <v>11.3</v>
+      </c>
+      <c r="L128" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>25</v>
       </c>
+      <c r="E129" t="s">
+        <v>299</v>
+      </c>
       <c r="F129" t="s">
-        <v>46</v>
-      </c>
-      <c r="I129" t="s">
+        <v>57</v>
+      </c>
+      <c r="J129" t="s">
         <v>18</v>
       </c>
-      <c r="J129" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F129,'feed pars'!B$6:B$42,0))</f>
-        <v>5.9</v>
-      </c>
-      <c r="K129" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>25</v>
-      </c>
-      <c r="F130" t="s">
-        <v>47</v>
-      </c>
-      <c r="I130" t="s">
-        <v>18</v>
-      </c>
-      <c r="J130" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F130,'feed pars'!B$6:B$42,0))</f>
-        <v>5.4</v>
-      </c>
-      <c r="K130" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K129" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F129,'feed pars'!B$6:B$42,0))</f>
+        <v>10.8</v>
+      </c>
+      <c r="L129" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K130" s="26"/>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>25</v>
       </c>
       <c r="F131" t="s">
-        <v>48</v>
-      </c>
-      <c r="I131" t="s">
+        <v>17</v>
+      </c>
+      <c r="J131" t="s">
         <v>18</v>
       </c>
-      <c r="J131" s="26">
+      <c r="K131" s="26">
         <f>INDEX('feed pars'!G$6:G$42,MATCH(F131,'feed pars'!B$6:B$42,0))</f>
-        <v>7.2</v>
-      </c>
-      <c r="K131" t="s">
+        <v>12.1</v>
+      </c>
+      <c r="L131" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>25</v>
       </c>
       <c r="F132" t="s">
-        <v>49</v>
-      </c>
-      <c r="I132" t="s">
+        <v>37</v>
+      </c>
+      <c r="J132" t="s">
         <v>18</v>
       </c>
-      <c r="J132" s="26">
+      <c r="K132" s="26">
         <f>INDEX('feed pars'!G$6:G$42,MATCH(F132,'feed pars'!B$6:B$42,0))</f>
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="K132" t="s">
+        <v>11</v>
+      </c>
+      <c r="L132" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>25</v>
       </c>
       <c r="F133" t="s">
-        <v>50</v>
-      </c>
-      <c r="I133" t="s">
+        <v>38</v>
+      </c>
+      <c r="J133" t="s">
         <v>18</v>
       </c>
-      <c r="J133" s="26">
+      <c r="K133" s="26">
         <f>INDEX('feed pars'!G$6:G$42,MATCH(F133,'feed pars'!B$6:B$42,0))</f>
-        <v>8.1</v>
-      </c>
-      <c r="K133" t="s">
+        <v>9</v>
+      </c>
+      <c r="L133" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>25</v>
       </c>
       <c r="F134" t="s">
-        <v>51</v>
-      </c>
-      <c r="I134" t="s">
+        <v>39</v>
+      </c>
+      <c r="J134" t="s">
         <v>18</v>
       </c>
-      <c r="J134" s="26">
+      <c r="K134" s="26">
         <f>INDEX('feed pars'!G$6:G$42,MATCH(F134,'feed pars'!B$6:B$42,0))</f>
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="K134" t="s">
+        <v>11.9</v>
+      </c>
+      <c r="L134" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>25</v>
       </c>
       <c r="F135" t="s">
-        <v>313</v>
-      </c>
-      <c r="I135" t="s">
+        <v>40</v>
+      </c>
+      <c r="J135" t="s">
         <v>18</v>
       </c>
-      <c r="J135" s="26">
+      <c r="K135" s="26">
         <f>INDEX('feed pars'!G$6:G$42,MATCH(F135,'feed pars'!B$6:B$42,0))</f>
-        <v>6.6</v>
-      </c>
-      <c r="K135" t="s">
+        <v>12.8</v>
+      </c>
+      <c r="L135" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>25</v>
       </c>
       <c r="F136" t="s">
-        <v>52</v>
-      </c>
-      <c r="I136" t="s">
+        <v>41</v>
+      </c>
+      <c r="J136" t="s">
         <v>18</v>
       </c>
-      <c r="J136" s="26">
+      <c r="K136" s="26">
         <f>INDEX('feed pars'!G$6:G$42,MATCH(F136,'feed pars'!B$6:B$42,0))</f>
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="K136" t="s">
+        <v>11.2</v>
+      </c>
+      <c r="L136" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>25</v>
       </c>
       <c r="F137" t="s">
-        <v>53</v>
-      </c>
-      <c r="I137" t="s">
+        <v>42</v>
+      </c>
+      <c r="J137" t="s">
         <v>18</v>
       </c>
-      <c r="J137" s="26">
+      <c r="K137" s="26">
         <f>INDEX('feed pars'!G$6:G$42,MATCH(F137,'feed pars'!B$6:B$42,0))</f>
-        <v>6.9</v>
-      </c>
-      <c r="K137" t="s">
+        <v>10.7</v>
+      </c>
+      <c r="L137" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>25</v>
       </c>
       <c r="F138" t="s">
-        <v>54</v>
-      </c>
-      <c r="I138" t="s">
+        <v>35</v>
+      </c>
+      <c r="J138" t="s">
         <v>18</v>
       </c>
-      <c r="J138" s="26">
+      <c r="K138" s="26">
         <f>INDEX('feed pars'!G$6:G$42,MATCH(F138,'feed pars'!B$6:B$42,0))</f>
-        <v>12.4</v>
-      </c>
-      <c r="K138" t="s">
+        <v>18</v>
+      </c>
+      <c r="L138" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>25</v>
       </c>
       <c r="F139" t="s">
-        <v>55</v>
-      </c>
-      <c r="I139" t="s">
+        <v>43</v>
+      </c>
+      <c r="J139" t="s">
         <v>18</v>
       </c>
-      <c r="J139" s="26">
+      <c r="K139" s="26">
         <f>INDEX('feed pars'!G$6:G$42,MATCH(F139,'feed pars'!B$6:B$42,0))</f>
-        <v>12.4</v>
-      </c>
-      <c r="K139" t="s">
+        <v>17.3</v>
+      </c>
+      <c r="L139" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>25</v>
       </c>
       <c r="F140" t="s">
-        <v>56</v>
-      </c>
-      <c r="I140" t="s">
+        <v>314</v>
+      </c>
+      <c r="J140" t="s">
         <v>18</v>
       </c>
-      <c r="J140" s="26">
+      <c r="K140" s="26">
         <f>INDEX('feed pars'!G$6:G$42,MATCH(F140,'feed pars'!B$6:B$42,0))</f>
-        <v>11.1</v>
-      </c>
-      <c r="K140" t="s">
+        <v>29.8</v>
+      </c>
+      <c r="L140" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>25</v>
       </c>
       <c r="F141" t="s">
+        <v>44</v>
+      </c>
+      <c r="J141" t="s">
+        <v>18</v>
+      </c>
+      <c r="K141" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F141,'feed pars'!B$6:B$42,0))</f>
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="L141" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>25</v>
+      </c>
+      <c r="F142" t="s">
+        <v>45</v>
+      </c>
+      <c r="J142" t="s">
+        <v>18</v>
+      </c>
+      <c r="K142" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F142,'feed pars'!B$6:B$42,0))</f>
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="L142" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>25</v>
+      </c>
+      <c r="F143" t="s">
+        <v>36</v>
+      </c>
+      <c r="J143" t="s">
+        <v>18</v>
+      </c>
+      <c r="K143" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F143,'feed pars'!B$6:B$42,0))</f>
+        <v>7.1</v>
+      </c>
+      <c r="L143" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>25</v>
+      </c>
+      <c r="F144" t="s">
+        <v>46</v>
+      </c>
+      <c r="J144" t="s">
+        <v>18</v>
+      </c>
+      <c r="K144" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F144,'feed pars'!B$6:B$42,0))</f>
+        <v>5.9</v>
+      </c>
+      <c r="L144" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>25</v>
+      </c>
+      <c r="F145" t="s">
+        <v>47</v>
+      </c>
+      <c r="J145" t="s">
+        <v>18</v>
+      </c>
+      <c r="K145" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F145,'feed pars'!B$6:B$42,0))</f>
+        <v>5.4</v>
+      </c>
+      <c r="L145" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>25</v>
+      </c>
+      <c r="F146" t="s">
+        <v>48</v>
+      </c>
+      <c r="J146" t="s">
+        <v>18</v>
+      </c>
+      <c r="K146" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F146,'feed pars'!B$6:B$42,0))</f>
+        <v>7.2</v>
+      </c>
+      <c r="L146" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>25</v>
+      </c>
+      <c r="F147" t="s">
+        <v>49</v>
+      </c>
+      <c r="J147" t="s">
+        <v>18</v>
+      </c>
+      <c r="K147" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F147,'feed pars'!B$6:B$42,0))</f>
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="L147" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>25</v>
+      </c>
+      <c r="F148" t="s">
+        <v>50</v>
+      </c>
+      <c r="J148" t="s">
+        <v>18</v>
+      </c>
+      <c r="K148" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F148,'feed pars'!B$6:B$42,0))</f>
+        <v>8.1</v>
+      </c>
+      <c r="L148" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>25</v>
+      </c>
+      <c r="F149" t="s">
+        <v>51</v>
+      </c>
+      <c r="J149" t="s">
+        <v>18</v>
+      </c>
+      <c r="K149" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F149,'feed pars'!B$6:B$42,0))</f>
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="L149" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>25</v>
+      </c>
+      <c r="F150" t="s">
+        <v>313</v>
+      </c>
+      <c r="J150" t="s">
+        <v>18</v>
+      </c>
+      <c r="K150" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F150,'feed pars'!B$6:B$42,0))</f>
+        <v>6.6</v>
+      </c>
+      <c r="L150" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>25</v>
+      </c>
+      <c r="F151" t="s">
+        <v>52</v>
+      </c>
+      <c r="J151" t="s">
+        <v>18</v>
+      </c>
+      <c r="K151" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F151,'feed pars'!B$6:B$42,0))</f>
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="L151" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>25</v>
+      </c>
+      <c r="F152" t="s">
+        <v>53</v>
+      </c>
+      <c r="J152" t="s">
+        <v>18</v>
+      </c>
+      <c r="K152" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F152,'feed pars'!B$6:B$42,0))</f>
+        <v>6.9</v>
+      </c>
+      <c r="L152" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>25</v>
+      </c>
+      <c r="F153" t="s">
+        <v>54</v>
+      </c>
+      <c r="J153" t="s">
+        <v>18</v>
+      </c>
+      <c r="K153" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F153,'feed pars'!B$6:B$42,0))</f>
+        <v>12.4</v>
+      </c>
+      <c r="L153" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>25</v>
+      </c>
+      <c r="F154" t="s">
+        <v>55</v>
+      </c>
+      <c r="J154" t="s">
+        <v>18</v>
+      </c>
+      <c r="K154" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F154,'feed pars'!B$6:B$42,0))</f>
+        <v>12.4</v>
+      </c>
+      <c r="L154" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>25</v>
+      </c>
+      <c r="F155" t="s">
+        <v>56</v>
+      </c>
+      <c r="J155" t="s">
+        <v>18</v>
+      </c>
+      <c r="K155" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F155,'feed pars'!B$6:B$42,0))</f>
+        <v>11.1</v>
+      </c>
+      <c r="L155" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>25</v>
+      </c>
+      <c r="F156" t="s">
         <v>57</v>
       </c>
-      <c r="I141" t="s">
+      <c r="J156" t="s">
         <v>18</v>
       </c>
-      <c r="J141" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F141,'feed pars'!B$6:B$42,0))</f>
+      <c r="K156" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F156,'feed pars'!B$6:B$42,0))</f>
         <v>10.8</v>
       </c>
-      <c r="K141" t="s">
+      <c r="L156" t="s">
         <v>22</v>
       </c>
     </row>

--- a/data/prod_parameters/FeedMgmt.xlsx
+++ b/data/prod_parameters/FeedMgmt.xlsx
@@ -11,6 +11,7 @@
     <sheet name="feed pars" sheetId="2" r:id="rId2"/>
     <sheet name="pigs" sheetId="3" r:id="rId3"/>
     <sheet name="cattle" sheetId="4" r:id="rId4"/>
+    <sheet name="poultry" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="394">
   <si>
     <t>f_feed</t>
   </si>
@@ -1045,6 +1046,177 @@
       </rPr>
       <t xml:space="preserve"> (Primarily used to limit semi-natural pastures in grazing)</t>
     </r>
+  </si>
+  <si>
+    <t>%TS</t>
+  </si>
+  <si>
+    <t>MJ</t>
+  </si>
+  <si>
+    <t>PR, g</t>
+  </si>
+  <si>
+    <t>LYS, g</t>
+  </si>
+  <si>
+    <t>MET, g</t>
+  </si>
+  <si>
+    <t>MET+CYS, g</t>
+  </si>
+  <si>
+    <t>Fett, g</t>
+  </si>
+  <si>
+    <t>Linolsyra, g</t>
+  </si>
+  <si>
+    <t>P tot., g</t>
+  </si>
+  <si>
+    <t>P tillg., g</t>
+  </si>
+  <si>
+    <t>Cl, g</t>
+  </si>
+  <si>
+    <t>Xantofyll, mg</t>
+  </si>
+  <si>
+    <t>AKOFEED Standard</t>
+  </si>
+  <si>
+    <t>AKOFEEDF30</t>
+  </si>
+  <si>
+    <t>DIKALCIUMFOSFAT</t>
+  </si>
+  <si>
+    <t>DINATRIUMFOSFAT</t>
+  </si>
+  <si>
+    <t>DL-METIONIN</t>
+  </si>
+  <si>
+    <t>FISKMJÖL, 2-8% fett</t>
+  </si>
+  <si>
+    <t>FISKMJÖL, under 2% FETT</t>
+  </si>
+  <si>
+    <t>FISKMJÖL, över 8% fett</t>
+  </si>
+  <si>
+    <t>FODERKALK</t>
+  </si>
+  <si>
+    <t>HAVRE 490-580 g/l</t>
+  </si>
+  <si>
+    <t>HAVRE SKALAD</t>
+  </si>
+  <si>
+    <t>HAVRE under 490 g/l</t>
+  </si>
+  <si>
+    <t>HAVRE över 580 g/l</t>
+  </si>
+  <si>
+    <t>HAVRESKAL</t>
+  </si>
+  <si>
+    <t>KOKSALT</t>
+  </si>
+  <si>
+    <t>KORN 600-700 g/l</t>
+  </si>
+  <si>
+    <t>KORN under 600 g/l</t>
+  </si>
+  <si>
+    <t>KORN över 700 g/l</t>
+  </si>
+  <si>
+    <t>KÖTTFODERMJÖL, 51-56% rp</t>
+  </si>
+  <si>
+    <t>KÖTTFODERMJÖL, 56-63% rp</t>
+  </si>
+  <si>
+    <t>KÖTTFODERMJÖL, över 63% rp</t>
+  </si>
+  <si>
+    <t>LUCERNMJÖL</t>
+  </si>
+  <si>
+    <t>LYSIN_HCL</t>
+  </si>
+  <si>
+    <t>MAJS</t>
+  </si>
+  <si>
+    <t>MAJSGLUTENMJÖL</t>
+  </si>
+  <si>
+    <t>MONOKALCIUMFOSFAT</t>
+  </si>
+  <si>
+    <t>NABIKARBONAT</t>
+  </si>
+  <si>
+    <t>P0TATISPROTEIN</t>
+  </si>
+  <si>
+    <t>RAPSMJöL</t>
+  </si>
+  <si>
+    <t>RÅG</t>
+  </si>
+  <si>
+    <t>RÅGVETE</t>
+  </si>
+  <si>
+    <t>SLAKTERIFETT</t>
+  </si>
+  <si>
+    <t>SOJAMJöL</t>
+  </si>
+  <si>
+    <t>SOJAOLJA</t>
+  </si>
+  <si>
+    <t>VETE</t>
+  </si>
+  <si>
+    <t>VETEFODERMJÖL under 5% vt</t>
+  </si>
+  <si>
+    <t>VETEFODERMJÖL över 5% vt</t>
+  </si>
+  <si>
+    <t>VETEKLI</t>
+  </si>
+  <si>
+    <t>ÄRTOR</t>
+  </si>
+  <si>
+    <t>maize gluten meal</t>
+  </si>
+  <si>
+    <t>poultry</t>
+  </si>
+  <si>
+    <t>feed_par_DM</t>
+  </si>
+  <si>
+    <t>Sows</t>
+  </si>
+  <si>
+    <t>Other pigs</t>
+  </si>
+  <si>
+    <t>Percent dry matter in feed as fed</t>
   </si>
 </sst>
 </file>
@@ -1121,7 +1293,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1170,6 +1342,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1184,7 +1362,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1231,6 +1409,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1512,7 +1693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O156"/>
+  <dimension ref="A1:O193"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="7" width="20.28515625" customWidth="1"/>
@@ -2702,1531 +2883,1990 @@
       <c r="N68" s="2"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A69" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B69" s="7"/>
-      <c r="C69" s="6"/>
-      <c r="D69" s="6"/>
-      <c r="E69" s="6"/>
-      <c r="F69" s="6"/>
-      <c r="G69" s="6"/>
-      <c r="H69" s="6"/>
-      <c r="I69" s="6"/>
-      <c r="J69" s="6"/>
-      <c r="K69" s="6"/>
-      <c r="L69" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M69" s="6"/>
-      <c r="N69" s="6"/>
+      <c r="F69" t="s">
+        <v>310</v>
+      </c>
+      <c r="J69" t="s">
+        <v>390</v>
+      </c>
+      <c r="K69" s="26">
+        <f>INDEX('feed pars'!C$6:C$42,MATCH(F69,'feed pars'!B$6:B$42,0))</f>
+        <v>100</v>
+      </c>
+      <c r="L69" t="s">
+        <v>28</v>
+      </c>
+      <c r="M69" s="29" t="s">
+        <v>393</v>
+      </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>24</v>
-      </c>
       <c r="F70" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J70" t="s">
-        <v>18</v>
+        <v>390</v>
       </c>
       <c r="K70" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F70,'feed pars'!B$6:B$42,0))</f>
-        <v>11.5</v>
+        <f>INDEX('feed pars'!C$6:C$42,MATCH(F70,'feed pars'!B$6:B$42,0))</f>
+        <v>100</v>
+      </c>
+      <c r="L70" t="s">
+        <v>28</v>
       </c>
       <c r="M70" s="3"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>24</v>
-      </c>
       <c r="F71" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J71" t="s">
-        <v>18</v>
+        <v>390</v>
       </c>
       <c r="K71" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F71,'feed pars'!B$6:B$42,0))</f>
-        <v>10.4</v>
+        <f>INDEX('feed pars'!C$6:C$42,MATCH(F71,'feed pars'!B$6:B$42,0))</f>
+        <v>100</v>
+      </c>
+      <c r="L71" t="s">
+        <v>28</v>
       </c>
       <c r="M71" s="3"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>24</v>
-      </c>
       <c r="F72" t="s">
-        <v>312</v>
+        <v>2</v>
       </c>
       <c r="J72" t="s">
-        <v>18</v>
+        <v>390</v>
       </c>
       <c r="K72" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F72,'feed pars'!B$6:B$42,0))</f>
-        <v>10</v>
+        <f>INDEX('feed pars'!C$6:C$42,MATCH(F72,'feed pars'!B$6:B$42,0))</f>
+        <v>100</v>
+      </c>
+      <c r="L72" t="s">
+        <v>28</v>
       </c>
       <c r="M72" s="3"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>24</v>
-      </c>
       <c r="F73" t="s">
         <v>12</v>
       </c>
       <c r="J73" t="s">
-        <v>18</v>
+        <v>390</v>
       </c>
       <c r="K73" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F73,'feed pars'!B$6:B$42,0))</f>
-        <v>11.3</v>
-      </c>
+        <f>INDEX('feed pars'!C$6:C$42,MATCH(F73,'feed pars'!B$6:B$42,0))</f>
+        <v>100</v>
+      </c>
+      <c r="L73" t="s">
+        <v>28</v>
+      </c>
+      <c r="M73" s="3"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>24</v>
-      </c>
       <c r="F74" t="s">
         <v>33</v>
       </c>
       <c r="J74" t="s">
-        <v>18</v>
+        <v>390</v>
       </c>
       <c r="K74" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F74,'feed pars'!B$6:B$42,0))</f>
-        <v>10</v>
-      </c>
+        <f>INDEX('feed pars'!C$6:C$42,MATCH(F74,'feed pars'!B$6:B$42,0))</f>
+        <v>100</v>
+      </c>
+      <c r="L74" t="s">
+        <v>28</v>
+      </c>
+      <c r="M74" s="3"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K75" s="3"/>
+      <c r="F75" t="s">
+        <v>17</v>
+      </c>
+      <c r="J75" t="s">
+        <v>390</v>
+      </c>
+      <c r="K75" s="26">
+        <f>INDEX('feed pars'!C$6:C$42,MATCH(F75,'feed pars'!B$6:B$42,0))</f>
+        <v>87</v>
+      </c>
+      <c r="L75" t="s">
+        <v>28</v>
+      </c>
+      <c r="M75" s="3"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>24</v>
-      </c>
       <c r="F76" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="J76" t="s">
-        <v>18</v>
+        <v>390</v>
       </c>
       <c r="K76" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F76,'feed pars'!B$6:B$42,0))</f>
-        <v>14.1</v>
-      </c>
+        <f>INDEX('feed pars'!C$6:C$42,MATCH(F76,'feed pars'!B$6:B$42,0))</f>
+        <v>87</v>
+      </c>
+      <c r="L76" t="s">
+        <v>28</v>
+      </c>
+      <c r="M76" s="3"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>24</v>
-      </c>
       <c r="F77" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J77" t="s">
-        <v>18</v>
+        <v>390</v>
       </c>
       <c r="K77" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F77,'feed pars'!B$6:B$42,0))</f>
-        <v>13.2</v>
-      </c>
+        <f>INDEX('feed pars'!C$6:C$42,MATCH(F77,'feed pars'!B$6:B$42,0))</f>
+        <v>86</v>
+      </c>
+      <c r="L77" t="s">
+        <v>28</v>
+      </c>
+      <c r="M77" s="3"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>24</v>
-      </c>
       <c r="F78" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J78" t="s">
-        <v>18</v>
+        <v>390</v>
       </c>
       <c r="K78" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F78,'feed pars'!B$6:B$42,0))</f>
-        <v>11.7</v>
-      </c>
+        <f>INDEX('feed pars'!C$6:C$42,MATCH(F78,'feed pars'!B$6:B$42,0))</f>
+        <v>87</v>
+      </c>
+      <c r="L78" t="s">
+        <v>28</v>
+      </c>
+      <c r="M78" s="3"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>24</v>
-      </c>
       <c r="F79" t="s">
-        <v>39</v>
+        <v>317</v>
       </c>
       <c r="J79" t="s">
-        <v>18</v>
+        <v>390</v>
       </c>
       <c r="K79" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F79,'feed pars'!B$6:B$42,0))</f>
-        <v>14</v>
-      </c>
+        <f>INDEX('feed pars'!C$6:C$42,MATCH(F79,'feed pars'!B$6:B$42,0))</f>
+        <v>87</v>
+      </c>
+      <c r="L79" t="s">
+        <v>28</v>
+      </c>
+      <c r="M79" s="3"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>24</v>
-      </c>
       <c r="F80" t="s">
-        <v>317</v>
+        <v>40</v>
       </c>
       <c r="J80" t="s">
-        <v>18</v>
+        <v>390</v>
       </c>
       <c r="K80" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F80,'feed pars'!B$6:B$42,0))</f>
-        <v>13.9</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>24</v>
-      </c>
+        <f>INDEX('feed pars'!C$6:C$42,MATCH(F80,'feed pars'!B$6:B$42,0))</f>
+        <v>67.5</v>
+      </c>
+      <c r="L80" t="s">
+        <v>28</v>
+      </c>
+      <c r="M80" s="3"/>
+    </row>
+    <row r="81" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F81" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J81" t="s">
-        <v>18</v>
+        <v>390</v>
       </c>
       <c r="K81" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F81,'feed pars'!B$6:B$42,0))</f>
-        <v>12.8</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>24</v>
-      </c>
+        <f>INDEX('feed pars'!C$6:C$42,MATCH(F81,'feed pars'!B$6:B$42,0))</f>
+        <v>87</v>
+      </c>
+      <c r="L81" t="s">
+        <v>28</v>
+      </c>
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F82" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J82" t="s">
-        <v>18</v>
+        <v>390</v>
       </c>
       <c r="K82" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F82,'feed pars'!B$6:B$42,0))</f>
-        <v>13.8</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>24</v>
-      </c>
+        <f>INDEX('feed pars'!C$6:C$42,MATCH(F82,'feed pars'!B$6:B$42,0))</f>
+        <v>86.8</v>
+      </c>
+      <c r="L82" t="s">
+        <v>28</v>
+      </c>
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F83" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J83" t="s">
-        <v>18</v>
+        <v>390</v>
       </c>
       <c r="K83" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F83,'feed pars'!B$6:B$42,0))</f>
-        <v>13.3</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>24</v>
-      </c>
+        <f>INDEX('feed pars'!C$6:C$42,MATCH(F83,'feed pars'!B$6:B$42,0))</f>
+        <v>92.5</v>
+      </c>
+      <c r="L83" t="s">
+        <v>28</v>
+      </c>
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F84" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="J84" t="s">
-        <v>18</v>
+        <v>390</v>
       </c>
       <c r="K84" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F84,'feed pars'!B$6:B$42,0))</f>
-        <v>22.1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>24</v>
-      </c>
+        <f>INDEX('feed pars'!C$6:C$42,MATCH(F84,'feed pars'!B$6:B$42,0))</f>
+        <v>92</v>
+      </c>
+      <c r="L84" t="s">
+        <v>28</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F85" t="s">
-        <v>43</v>
+        <v>314</v>
       </c>
       <c r="J85" t="s">
-        <v>18</v>
+        <v>390</v>
       </c>
       <c r="K85" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F85,'feed pars'!B$6:B$42,0))</f>
-        <v>20.100000000000001</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>24</v>
-      </c>
+        <f>INDEX('feed pars'!C$6:C$42,MATCH(F85,'feed pars'!B$6:B$42,0))</f>
+        <v>100</v>
+      </c>
+      <c r="L85" t="s">
+        <v>28</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F86" t="s">
         <v>305</v>
       </c>
       <c r="J86" t="s">
-        <v>18</v>
+        <v>390</v>
       </c>
       <c r="K86" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F86,'feed pars'!B$6:B$42,0))</f>
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>24</v>
-      </c>
+        <f>INDEX('feed pars'!C$6:C$42,MATCH(F86,'feed pars'!B$6:B$42,0))</f>
+        <v>85</v>
+      </c>
+      <c r="L86" t="s">
+        <v>28</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F87" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="J87" t="s">
-        <v>18</v>
+        <v>390</v>
       </c>
       <c r="K87" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F87,'feed pars'!B$6:B$42,0))</f>
-        <v>36.6</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>24</v>
-      </c>
+        <f>INDEX('feed pars'!C$6:C$42,MATCH(F87,'feed pars'!B$6:B$42,0))</f>
+        <v>87</v>
+      </c>
+      <c r="L87" t="s">
+        <v>28</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F88" t="s">
-        <v>318</v>
+        <v>44</v>
       </c>
       <c r="J88" t="s">
-        <v>18</v>
+        <v>390</v>
       </c>
       <c r="K88" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F88,'feed pars'!B$6:B$42,0))</f>
-        <v>16.399999999999999</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>24</v>
-      </c>
+        <f>INDEX('feed pars'!C$6:C$42,MATCH(F88,'feed pars'!B$6:B$42,0))</f>
+        <v>87.5</v>
+      </c>
+      <c r="L88" t="s">
+        <v>28</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F89" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J89" t="s">
-        <v>18</v>
+        <v>390</v>
       </c>
       <c r="K89" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F89,'feed pars'!B$6:B$42,0))</f>
-        <v>14.6</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>24</v>
-      </c>
+        <f>INDEX('feed pars'!C$6:C$42,MATCH(F89,'feed pars'!B$6:B$42,0))</f>
+        <v>87</v>
+      </c>
+      <c r="L89" t="s">
+        <v>28</v>
+      </c>
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F90" t="s">
         <v>36</v>
       </c>
       <c r="J90" t="s">
-        <v>18</v>
+        <v>390</v>
       </c>
       <c r="K90" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F90,'feed pars'!B$6:B$42,0))</f>
-        <v>12.2</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>24</v>
-      </c>
+        <f>INDEX('feed pars'!C$6:C$42,MATCH(F90,'feed pars'!B$6:B$42,0))</f>
+        <v>89.5</v>
+      </c>
+      <c r="L90" t="s">
+        <v>28</v>
+      </c>
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F91" t="s">
         <v>46</v>
       </c>
       <c r="J91" t="s">
-        <v>18</v>
+        <v>390</v>
       </c>
       <c r="K91" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F91,'feed pars'!B$6:B$42,0))</f>
-        <v>11.4</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>24</v>
-      </c>
+        <f>INDEX('feed pars'!C$6:C$42,MATCH(F91,'feed pars'!B$6:B$42,0))</f>
+        <v>91</v>
+      </c>
+      <c r="L91" t="s">
+        <v>28</v>
+      </c>
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F92" t="s">
         <v>47</v>
       </c>
       <c r="J92" t="s">
-        <v>18</v>
+        <v>390</v>
       </c>
       <c r="K92" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F92,'feed pars'!B$6:B$42,0))</f>
-        <v>13.4</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>24</v>
-      </c>
+        <f>INDEX('feed pars'!C$6:C$42,MATCH(F92,'feed pars'!B$6:B$42,0))</f>
+        <v>91</v>
+      </c>
+      <c r="L92" t="s">
+        <v>28</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F93" t="s">
         <v>319</v>
       </c>
       <c r="J93" t="s">
-        <v>18</v>
+        <v>390</v>
       </c>
       <c r="K93" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F93,'feed pars'!B$6:B$42,0))</f>
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>24</v>
-      </c>
+        <f>INDEX('feed pars'!C$6:C$42,MATCH(F93,'feed pars'!B$6:B$42,0))</f>
+        <v>90</v>
+      </c>
+      <c r="L93" t="s">
+        <v>28</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F94" t="s">
         <v>48</v>
       </c>
       <c r="J94" t="s">
-        <v>18</v>
+        <v>390</v>
       </c>
       <c r="K94" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F94,'feed pars'!B$6:B$42,0))</f>
+        <f>INDEX('feed pars'!C$6:C$42,MATCH(F94,'feed pars'!B$6:B$42,0))</f>
+        <v>87</v>
+      </c>
+      <c r="L94" t="s">
+        <v>28</v>
+      </c>
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="6:13" x14ac:dyDescent="0.25">
+      <c r="F95" t="s">
+        <v>49</v>
+      </c>
+      <c r="J95" t="s">
+        <v>390</v>
+      </c>
+      <c r="K95" s="26">
+        <f>INDEX('feed pars'!C$6:C$42,MATCH(F95,'feed pars'!B$6:B$42,0))</f>
+        <v>88</v>
+      </c>
+      <c r="L95" t="s">
+        <v>28</v>
+      </c>
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="6:13" x14ac:dyDescent="0.25">
+      <c r="F96" t="s">
+        <v>50</v>
+      </c>
+      <c r="J96" t="s">
+        <v>390</v>
+      </c>
+      <c r="K96" s="26">
+        <f>INDEX('feed pars'!C$6:C$42,MATCH(F96,'feed pars'!B$6:B$42,0))</f>
+        <v>90</v>
+      </c>
+      <c r="L96" t="s">
+        <v>28</v>
+      </c>
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F97" t="s">
+        <v>51</v>
+      </c>
+      <c r="J97" t="s">
+        <v>390</v>
+      </c>
+      <c r="K97" s="26">
+        <f>INDEX('feed pars'!C$6:C$42,MATCH(F97,'feed pars'!B$6:B$42,0))</f>
         <v>11</v>
       </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>24</v>
-      </c>
-      <c r="F95" t="s">
-        <v>50</v>
-      </c>
-      <c r="J95" t="s">
-        <v>18</v>
-      </c>
-      <c r="K95" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F95,'feed pars'!B$6:B$42,0))</f>
-        <v>13.3</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>24</v>
-      </c>
-      <c r="F96" t="s">
+      <c r="L97" t="s">
+        <v>28</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F98" t="s">
         <v>313</v>
       </c>
-      <c r="J96" t="s">
-        <v>18</v>
-      </c>
-      <c r="K96" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F96,'feed pars'!B$6:B$42,0))</f>
-        <v>11.6</v>
-      </c>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>24</v>
-      </c>
-      <c r="F97" t="s">
+      <c r="J98" t="s">
+        <v>390</v>
+      </c>
+      <c r="K98" s="26">
+        <f>INDEX('feed pars'!C$6:C$42,MATCH(F98,'feed pars'!B$6:B$42,0))</f>
+        <v>90</v>
+      </c>
+      <c r="L98" t="s">
+        <v>28</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F99" t="s">
         <v>52</v>
       </c>
-      <c r="J97" t="s">
-        <v>18</v>
-      </c>
-      <c r="K97" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F97,'feed pars'!B$6:B$42,0))</f>
-        <v>12.4</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>24</v>
-      </c>
-      <c r="F98" t="s">
+      <c r="J99" t="s">
+        <v>390</v>
+      </c>
+      <c r="K99" s="26">
+        <f>INDEX('feed pars'!C$6:C$42,MATCH(F99,'feed pars'!B$6:B$42,0))</f>
+        <v>75.5</v>
+      </c>
+      <c r="L99" t="s">
+        <v>28</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F100" t="s">
         <v>53</v>
       </c>
-      <c r="J98" t="s">
-        <v>18</v>
-      </c>
-      <c r="K98" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F98,'feed pars'!B$6:B$42,0))</f>
-        <v>12.3</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>24</v>
-      </c>
-      <c r="F99" t="s">
+      <c r="J100" t="s">
+        <v>390</v>
+      </c>
+      <c r="K100" s="26">
+        <f>INDEX('feed pars'!C$6:C$42,MATCH(F100,'feed pars'!B$6:B$42,0))</f>
+        <v>89.5</v>
+      </c>
+      <c r="L100" t="s">
+        <v>28</v>
+      </c>
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F101" t="s">
         <v>54</v>
       </c>
-      <c r="J99" t="s">
-        <v>18</v>
-      </c>
-      <c r="K99" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F99,'feed pars'!B$6:B$42,0))</f>
-        <v>13.6</v>
-      </c>
-    </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>24</v>
-      </c>
-      <c r="F100" t="s">
+      <c r="J101" t="s">
+        <v>390</v>
+      </c>
+      <c r="K101" s="26">
+        <f>INDEX('feed pars'!C$6:C$42,MATCH(F101,'feed pars'!B$6:B$42,0))</f>
+        <v>6.25</v>
+      </c>
+      <c r="L101" t="s">
+        <v>28</v>
+      </c>
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F102" t="s">
+        <v>55</v>
+      </c>
+      <c r="J102" t="s">
+        <v>390</v>
+      </c>
+      <c r="K102" s="26">
+        <f>INDEX('feed pars'!C$6:C$42,MATCH(F102,'feed pars'!B$6:B$42,0))</f>
+        <v>97</v>
+      </c>
+      <c r="L102" t="s">
+        <v>28</v>
+      </c>
+      <c r="M102" s="3"/>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F103" t="s">
         <v>56</v>
       </c>
-      <c r="J100" t="s">
-        <v>18</v>
-      </c>
-      <c r="K100" s="26">
-        <f>INDEX('feed pars'!M$6:M$42,MATCH(F100,'feed pars'!B$6:B$42,0))</f>
-        <v>15.5</v>
-      </c>
-    </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>24</v>
-      </c>
-      <c r="F101" t="s">
-        <v>324</v>
-      </c>
-      <c r="J101" t="s">
-        <v>18</v>
-      </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K102" s="3"/>
-    </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A103" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B103" s="8"/>
-      <c r="C103" s="9"/>
-      <c r="D103" s="9"/>
-      <c r="E103" s="9"/>
-      <c r="F103" s="9"/>
-      <c r="G103" s="9"/>
-      <c r="H103" s="9"/>
-      <c r="I103" s="9"/>
-      <c r="J103" s="9"/>
-      <c r="K103" s="9"/>
-      <c r="L103" s="9"/>
-      <c r="M103" s="9"/>
-      <c r="N103" s="9"/>
+      <c r="J103" t="s">
+        <v>390</v>
+      </c>
+      <c r="K103" s="26">
+        <f>INDEX('feed pars'!C$6:C$42,MATCH(F103,'feed pars'!B$6:B$42,0))</f>
+        <v>91</v>
+      </c>
+      <c r="L103" t="s">
+        <v>28</v>
+      </c>
+      <c r="M103" s="3"/>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>25</v>
-      </c>
-      <c r="E104" t="s">
-        <v>299</v>
-      </c>
       <c r="F104" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="J104" t="s">
-        <v>18</v>
+        <v>390</v>
       </c>
       <c r="K104" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F104,'feed pars'!B$6:B$42,0))</f>
-        <v>12.3</v>
+        <f>INDEX('feed pars'!C$6:C$42,MATCH(F104,'feed pars'!B$6:B$42,0))</f>
+        <v>92</v>
       </c>
       <c r="L104" t="s">
-        <v>300</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="M104" s="3"/>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>25</v>
-      </c>
-      <c r="E105" t="s">
-        <v>299</v>
-      </c>
-      <c r="F105" t="s">
-        <v>37</v>
-      </c>
-      <c r="J105" t="s">
-        <v>18</v>
-      </c>
-      <c r="K105" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F105,'feed pars'!B$6:B$42,0))</f>
-        <v>11.2</v>
-      </c>
-      <c r="L105" t="s">
-        <v>300</v>
-      </c>
+      <c r="A105" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B105" s="7"/>
+      <c r="C105" s="6"/>
+      <c r="D105" s="6"/>
+      <c r="E105" s="6"/>
+      <c r="F105" s="6"/>
+      <c r="G105" s="6"/>
+      <c r="H105" s="6"/>
+      <c r="I105" s="6"/>
+      <c r="J105" s="6"/>
+      <c r="K105" s="6"/>
+      <c r="L105" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M105" s="6"/>
+      <c r="N105" s="6"/>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>25</v>
-      </c>
-      <c r="E106" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F106" t="s">
-        <v>38</v>
+        <v>310</v>
       </c>
       <c r="J106" t="s">
         <v>18</v>
       </c>
       <c r="K106" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F106,'feed pars'!B$6:B$42,0))</f>
-        <v>9.4</v>
-      </c>
-      <c r="L106" t="s">
-        <v>300</v>
-      </c>
+        <f>INDEX('feed pars'!L$6:L$42,MATCH(F106,'feed pars'!B$6:B$42,0))</f>
+        <v>11.5</v>
+      </c>
+      <c r="M106" s="3"/>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>25</v>
-      </c>
-      <c r="E107" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F107" t="s">
-        <v>39</v>
+        <v>311</v>
       </c>
       <c r="J107" t="s">
         <v>18</v>
       </c>
       <c r="K107" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F107,'feed pars'!B$6:B$42,0))</f>
-        <v>12</v>
-      </c>
-      <c r="L107" t="s">
-        <v>300</v>
-      </c>
+        <f>INDEX('feed pars'!L$6:L$42,MATCH(F107,'feed pars'!B$6:B$42,0))</f>
+        <v>10.4</v>
+      </c>
+      <c r="M107" s="3"/>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>25</v>
-      </c>
-      <c r="E108" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F108" t="s">
-        <v>40</v>
+        <v>312</v>
       </c>
       <c r="J108" t="s">
         <v>18</v>
       </c>
       <c r="K108" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F108,'feed pars'!B$6:B$42,0))</f>
-        <v>13.2</v>
-      </c>
-      <c r="L108" t="s">
-        <v>300</v>
-      </c>
+        <f>INDEX('feed pars'!L$6:L$42,MATCH(F108,'feed pars'!B$6:B$42,0))</f>
+        <v>10</v>
+      </c>
+      <c r="M108" s="3"/>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>25</v>
-      </c>
-      <c r="E109" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F109" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="J109" t="s">
         <v>18</v>
       </c>
       <c r="K109" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F109,'feed pars'!B$6:B$42,0))</f>
-        <v>11.5</v>
-      </c>
-      <c r="L109" t="s">
-        <v>300</v>
+        <f>INDEX('feed pars'!L$6:L$42,MATCH(F109,'feed pars'!B$6:B$42,0))</f>
+        <v>11.3</v>
       </c>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>25</v>
-      </c>
-      <c r="E110" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F110" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="J110" t="s">
         <v>18</v>
       </c>
       <c r="K110" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F110,'feed pars'!B$6:B$42,0))</f>
-        <v>10.9</v>
-      </c>
-      <c r="L110" t="s">
-        <v>300</v>
+        <f>INDEX('feed pars'!L$6:L$42,MATCH(F110,'feed pars'!B$6:B$42,0))</f>
+        <v>10</v>
       </c>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>25</v>
-      </c>
-      <c r="E111" t="s">
-        <v>299</v>
-      </c>
-      <c r="F111" t="s">
-        <v>35</v>
-      </c>
-      <c r="J111" t="s">
-        <v>18</v>
-      </c>
-      <c r="K111" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F111,'feed pars'!B$6:B$42,0))</f>
-        <v>18.5</v>
-      </c>
-      <c r="L111" t="s">
-        <v>300</v>
-      </c>
+      <c r="K111" s="3"/>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>25</v>
-      </c>
-      <c r="E112" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F112" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="J112" t="s">
         <v>18</v>
       </c>
       <c r="K112" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F112,'feed pars'!B$6:B$42,0))</f>
-        <v>17.5</v>
-      </c>
-      <c r="L112" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$42,MATCH(F112,'feed pars'!B$6:B$42,0))</f>
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>25</v>
-      </c>
-      <c r="E113" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F113" t="s">
-        <v>314</v>
+        <v>37</v>
       </c>
       <c r="J113" t="s">
         <v>18</v>
       </c>
       <c r="K113" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F113,'feed pars'!B$6:B$42,0))</f>
-        <v>29.8</v>
-      </c>
-      <c r="L113" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$42,MATCH(F113,'feed pars'!B$6:B$42,0))</f>
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>25</v>
-      </c>
-      <c r="E114" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F114" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="J114" t="s">
         <v>18</v>
       </c>
       <c r="K114" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F114,'feed pars'!B$6:B$42,0))</f>
-        <v>9.9</v>
-      </c>
-      <c r="L114" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$42,MATCH(F114,'feed pars'!B$6:B$42,0))</f>
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>25</v>
-      </c>
-      <c r="E115" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F115" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="J115" t="s">
         <v>18</v>
       </c>
       <c r="K115" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F115,'feed pars'!B$6:B$42,0))</f>
-        <v>10.3</v>
-      </c>
-      <c r="L115" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$42,MATCH(F115,'feed pars'!B$6:B$42,0))</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>25</v>
-      </c>
-      <c r="E116" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F116" t="s">
-        <v>36</v>
+        <v>317</v>
       </c>
       <c r="J116" t="s">
         <v>18</v>
       </c>
       <c r="K116" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F116,'feed pars'!B$6:B$42,0))</f>
-        <v>7.7</v>
-      </c>
-      <c r="L116" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$42,MATCH(F116,'feed pars'!B$6:B$42,0))</f>
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>25</v>
-      </c>
-      <c r="E117" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F117" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="J117" t="s">
         <v>18</v>
       </c>
       <c r="K117" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F117,'feed pars'!B$6:B$42,0))</f>
-        <v>6.5</v>
-      </c>
-      <c r="L117" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$42,MATCH(F117,'feed pars'!B$6:B$42,0))</f>
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>25</v>
-      </c>
-      <c r="E118" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F118" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J118" t="s">
         <v>18</v>
       </c>
       <c r="K118" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F118,'feed pars'!B$6:B$42,0))</f>
-        <v>6.2</v>
-      </c>
-      <c r="L118" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$42,MATCH(F118,'feed pars'!B$6:B$42,0))</f>
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>25</v>
-      </c>
-      <c r="E119" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F119" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="J119" t="s">
         <v>18</v>
       </c>
       <c r="K119" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F119,'feed pars'!B$6:B$42,0))</f>
-        <v>7.8</v>
-      </c>
-      <c r="L119" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$42,MATCH(F119,'feed pars'!B$6:B$42,0))</f>
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>25</v>
-      </c>
-      <c r="E120" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F120" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="J120" t="s">
         <v>18</v>
       </c>
       <c r="K120" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F120,'feed pars'!B$6:B$42,0))</f>
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="L120" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$42,MATCH(F120,'feed pars'!B$6:B$42,0))</f>
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>25</v>
-      </c>
-      <c r="E121" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F121" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="J121" t="s">
         <v>18</v>
       </c>
       <c r="K121" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F121,'feed pars'!B$6:B$42,0))</f>
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="L121" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$42,MATCH(F121,'feed pars'!B$6:B$42,0))</f>
+        <v>20.100000000000001</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>25</v>
-      </c>
-      <c r="E122" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F122" t="s">
-        <v>51</v>
+        <v>305</v>
       </c>
       <c r="J122" t="s">
         <v>18</v>
       </c>
       <c r="K122" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F122,'feed pars'!B$6:B$42,0))</f>
-        <v>8.9</v>
-      </c>
-      <c r="L122" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$42,MATCH(F122,'feed pars'!B$6:B$42,0))</f>
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>25</v>
-      </c>
-      <c r="E123" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F123" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J123" t="s">
         <v>18</v>
       </c>
       <c r="K123" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F123,'feed pars'!B$6:B$42,0))</f>
-        <v>7.0888888888888877</v>
-      </c>
-      <c r="L123" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$42,MATCH(F123,'feed pars'!B$6:B$42,0))</f>
+        <v>36.6</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>25</v>
-      </c>
-      <c r="E124" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F124" t="s">
-        <v>52</v>
+        <v>318</v>
       </c>
       <c r="J124" t="s">
         <v>18</v>
       </c>
       <c r="K124" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F124,'feed pars'!B$6:B$42,0))</f>
-        <v>9</v>
-      </c>
-      <c r="L124" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$42,MATCH(F124,'feed pars'!B$6:B$42,0))</f>
+        <v>16.399999999999999</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>25</v>
-      </c>
-      <c r="E125" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F125" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="J125" t="s">
         <v>18</v>
       </c>
       <c r="K125" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F125,'feed pars'!B$6:B$42,0))</f>
-        <v>8</v>
-      </c>
-      <c r="L125" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$42,MATCH(F125,'feed pars'!B$6:B$42,0))</f>
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>25</v>
-      </c>
-      <c r="E126" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F126" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="J126" t="s">
         <v>18</v>
       </c>
       <c r="K126" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F126,'feed pars'!B$6:B$42,0))</f>
+        <f>INDEX('feed pars'!L$6:L$42,MATCH(F126,'feed pars'!B$6:B$42,0))</f>
         <v>12.2</v>
       </c>
-      <c r="L126" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>25</v>
-      </c>
-      <c r="E127" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F127" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="J127" t="s">
         <v>18</v>
       </c>
       <c r="K127" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F127,'feed pars'!B$6:B$42,0))</f>
-        <v>12.2</v>
-      </c>
-      <c r="L127" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$42,MATCH(F127,'feed pars'!B$6:B$42,0))</f>
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>25</v>
-      </c>
-      <c r="E128" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F128" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="J128" t="s">
         <v>18</v>
       </c>
       <c r="K128" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F128,'feed pars'!B$6:B$42,0))</f>
-        <v>11.3</v>
-      </c>
-      <c r="L128" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$42,MATCH(F128,'feed pars'!B$6:B$42,0))</f>
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>25</v>
-      </c>
-      <c r="E129" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F129" t="s">
-        <v>57</v>
+        <v>319</v>
       </c>
       <c r="J129" t="s">
         <v>18</v>
       </c>
       <c r="K129" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F129,'feed pars'!B$6:B$42,0))</f>
-        <v>10.8</v>
-      </c>
-      <c r="L129" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="K130" s="26"/>
-    </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$42,MATCH(F129,'feed pars'!B$6:B$42,0))</f>
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>24</v>
+      </c>
+      <c r="F130" t="s">
+        <v>48</v>
+      </c>
+      <c r="J130" t="s">
+        <v>18</v>
+      </c>
+      <c r="K130" s="26">
+        <f>INDEX('feed pars'!L$6:L$42,MATCH(F130,'feed pars'!B$6:B$42,0))</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F131" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="J131" t="s">
         <v>18</v>
       </c>
       <c r="K131" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F131,'feed pars'!B$6:B$42,0))</f>
-        <v>12.1</v>
-      </c>
-      <c r="L131" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$42,MATCH(F131,'feed pars'!B$6:B$42,0))</f>
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F132" t="s">
-        <v>37</v>
+        <v>313</v>
       </c>
       <c r="J132" t="s">
         <v>18</v>
       </c>
       <c r="K132" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F132,'feed pars'!B$6:B$42,0))</f>
-        <v>11</v>
-      </c>
-      <c r="L132" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$42,MATCH(F132,'feed pars'!B$6:B$42,0))</f>
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F133" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="J133" t="s">
         <v>18</v>
       </c>
       <c r="K133" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F133,'feed pars'!B$6:B$42,0))</f>
-        <v>9</v>
-      </c>
-      <c r="L133" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$42,MATCH(F133,'feed pars'!B$6:B$42,0))</f>
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F134" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="J134" t="s">
         <v>18</v>
       </c>
       <c r="K134" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F134,'feed pars'!B$6:B$42,0))</f>
-        <v>11.9</v>
-      </c>
-      <c r="L134" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$42,MATCH(F134,'feed pars'!B$6:B$42,0))</f>
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F135" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="J135" t="s">
         <v>18</v>
       </c>
       <c r="K135" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F135,'feed pars'!B$6:B$42,0))</f>
-        <v>12.8</v>
-      </c>
-      <c r="L135" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$42,MATCH(F135,'feed pars'!B$6:B$42,0))</f>
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F136" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="J136" t="s">
         <v>18</v>
       </c>
       <c r="K136" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F136,'feed pars'!B$6:B$42,0))</f>
-        <v>11.2</v>
-      </c>
-      <c r="L136" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$42,MATCH(F136,'feed pars'!B$6:B$42,0))</f>
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F137" t="s">
-        <v>42</v>
+        <v>324</v>
       </c>
       <c r="J137" t="s">
         <v>18</v>
       </c>
-      <c r="K137" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F137,'feed pars'!B$6:B$42,0))</f>
-        <v>10.7</v>
-      </c>
-      <c r="L137" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>25</v>
-      </c>
-      <c r="F138" t="s">
-        <v>35</v>
-      </c>
-      <c r="J138" t="s">
-        <v>18</v>
-      </c>
-      <c r="K138" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F138,'feed pars'!B$6:B$42,0))</f>
-        <v>18</v>
-      </c>
-      <c r="L138" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>25</v>
-      </c>
-      <c r="F139" t="s">
-        <v>43</v>
-      </c>
-      <c r="J139" t="s">
-        <v>18</v>
-      </c>
-      <c r="K139" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F139,'feed pars'!B$6:B$42,0))</f>
-        <v>17.3</v>
-      </c>
-      <c r="L139" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>25</v>
-      </c>
-      <c r="F140" t="s">
-        <v>314</v>
-      </c>
-      <c r="J140" t="s">
-        <v>18</v>
-      </c>
-      <c r="K140" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F140,'feed pars'!B$6:B$42,0))</f>
-        <v>29.8</v>
-      </c>
-      <c r="L140" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K137" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K138" s="3"/>
+    </row>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A139" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B139" s="8"/>
+      <c r="C139" s="9"/>
+      <c r="D139" s="9"/>
+      <c r="E139" s="9"/>
+      <c r="F139" s="9"/>
+      <c r="G139" s="9"/>
+      <c r="H139" s="9"/>
+      <c r="I139" s="9"/>
+      <c r="J139" s="9"/>
+      <c r="K139" s="9"/>
+      <c r="L139" s="9"/>
+      <c r="M139" s="9"/>
+      <c r="N139" s="9"/>
+    </row>
+    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A140" s="30" t="s">
+        <v>391</v>
+      </c>
+      <c r="B140" s="31"/>
+      <c r="C140" s="32"/>
+      <c r="D140" s="32"/>
+      <c r="E140" s="32"/>
+      <c r="F140" s="32"/>
+      <c r="G140" s="32"/>
+      <c r="H140" s="32"/>
+      <c r="I140" s="32"/>
+      <c r="J140" s="32"/>
+      <c r="K140" s="32"/>
+      <c r="L140" s="32" t="s">
+        <v>300</v>
+      </c>
+      <c r="M140" s="32"/>
+      <c r="N140" s="32"/>
+    </row>
+    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>25</v>
       </c>
+      <c r="E141" t="s">
+        <v>299</v>
+      </c>
       <c r="F141" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="J141" t="s">
         <v>18</v>
       </c>
       <c r="K141" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F141,'feed pars'!B$6:B$42,0))</f>
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="L141" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F141,'feed pars'!B$6:B$42,0))</f>
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>25</v>
       </c>
+      <c r="E142" t="s">
+        <v>299</v>
+      </c>
       <c r="F142" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="J142" t="s">
         <v>18</v>
       </c>
       <c r="K142" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F142,'feed pars'!B$6:B$42,0))</f>
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="L142" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F142,'feed pars'!B$6:B$42,0))</f>
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>25</v>
       </c>
+      <c r="E143" t="s">
+        <v>299</v>
+      </c>
       <c r="F143" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J143" t="s">
         <v>18</v>
       </c>
       <c r="K143" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F143,'feed pars'!B$6:B$42,0))</f>
-        <v>7.1</v>
-      </c>
-      <c r="L143" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F143,'feed pars'!B$6:B$42,0))</f>
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>25</v>
       </c>
+      <c r="E144" t="s">
+        <v>299</v>
+      </c>
       <c r="F144" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="J144" t="s">
         <v>18</v>
       </c>
       <c r="K144" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F144,'feed pars'!B$6:B$42,0))</f>
-        <v>5.9</v>
-      </c>
-      <c r="L144" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F144,'feed pars'!B$6:B$42,0))</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>25</v>
       </c>
+      <c r="E145" t="s">
+        <v>299</v>
+      </c>
       <c r="F145" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="J145" t="s">
         <v>18</v>
       </c>
       <c r="K145" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F145,'feed pars'!B$6:B$42,0))</f>
-        <v>5.4</v>
-      </c>
-      <c r="L145" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F145,'feed pars'!B$6:B$42,0))</f>
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>25</v>
       </c>
+      <c r="E146" t="s">
+        <v>299</v>
+      </c>
       <c r="F146" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J146" t="s">
         <v>18</v>
       </c>
       <c r="K146" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F146,'feed pars'!B$6:B$42,0))</f>
-        <v>7.2</v>
-      </c>
-      <c r="L146" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F146,'feed pars'!B$6:B$42,0))</f>
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>25</v>
       </c>
+      <c r="E147" t="s">
+        <v>299</v>
+      </c>
       <c r="F147" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J147" t="s">
         <v>18</v>
       </c>
       <c r="K147" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F147,'feed pars'!B$6:B$42,0))</f>
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="L147" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F147,'feed pars'!B$6:B$42,0))</f>
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>25</v>
       </c>
+      <c r="E148" t="s">
+        <v>299</v>
+      </c>
       <c r="F148" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="J148" t="s">
         <v>18</v>
       </c>
       <c r="K148" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F148,'feed pars'!B$6:B$42,0))</f>
-        <v>8.1</v>
-      </c>
-      <c r="L148" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F148,'feed pars'!B$6:B$42,0))</f>
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>25</v>
       </c>
+      <c r="E149" t="s">
+        <v>299</v>
+      </c>
       <c r="F149" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="J149" t="s">
         <v>18</v>
       </c>
       <c r="K149" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F149,'feed pars'!B$6:B$42,0))</f>
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="L149" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F149,'feed pars'!B$6:B$42,0))</f>
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>25</v>
       </c>
+      <c r="E150" t="s">
+        <v>299</v>
+      </c>
       <c r="F150" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J150" t="s">
         <v>18</v>
       </c>
       <c r="K150" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F150,'feed pars'!B$6:B$42,0))</f>
-        <v>6.6</v>
-      </c>
-      <c r="L150" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F150,'feed pars'!B$6:B$42,0))</f>
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>25</v>
       </c>
+      <c r="E151" t="s">
+        <v>299</v>
+      </c>
       <c r="F151" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="J151" t="s">
         <v>18</v>
       </c>
       <c r="K151" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F151,'feed pars'!B$6:B$42,0))</f>
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="L151" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F151,'feed pars'!B$6:B$42,0))</f>
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>25</v>
       </c>
+      <c r="E152" t="s">
+        <v>299</v>
+      </c>
       <c r="F152" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="J152" t="s">
         <v>18</v>
       </c>
       <c r="K152" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F152,'feed pars'!B$6:B$42,0))</f>
-        <v>6.9</v>
-      </c>
-      <c r="L152" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F152,'feed pars'!B$6:B$42,0))</f>
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>25</v>
       </c>
+      <c r="E153" t="s">
+        <v>299</v>
+      </c>
       <c r="F153" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="J153" t="s">
         <v>18</v>
       </c>
       <c r="K153" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F153,'feed pars'!B$6:B$42,0))</f>
-        <v>12.4</v>
-      </c>
-      <c r="L153" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F153,'feed pars'!B$6:B$42,0))</f>
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>25</v>
       </c>
+      <c r="E154" t="s">
+        <v>299</v>
+      </c>
       <c r="F154" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="J154" t="s">
         <v>18</v>
       </c>
       <c r="K154" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F154,'feed pars'!B$6:B$42,0))</f>
-        <v>12.4</v>
-      </c>
-      <c r="L154" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F154,'feed pars'!B$6:B$42,0))</f>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>25</v>
       </c>
+      <c r="E155" t="s">
+        <v>299</v>
+      </c>
       <c r="F155" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="J155" t="s">
         <v>18</v>
       </c>
       <c r="K155" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F155,'feed pars'!B$6:B$42,0))</f>
-        <v>11.1</v>
-      </c>
-      <c r="L155" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F155,'feed pars'!B$6:B$42,0))</f>
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>25</v>
       </c>
+      <c r="E156" t="s">
+        <v>299</v>
+      </c>
       <c r="F156" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="J156" t="s">
         <v>18</v>
       </c>
       <c r="K156" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F156,'feed pars'!B$6:B$42,0))</f>
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F156,'feed pars'!B$6:B$42,0))</f>
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>25</v>
+      </c>
+      <c r="E157" t="s">
+        <v>299</v>
+      </c>
+      <c r="F157" t="s">
+        <v>49</v>
+      </c>
+      <c r="J157" t="s">
+        <v>18</v>
+      </c>
+      <c r="K157" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F157,'feed pars'!B$6:B$42,0))</f>
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>25</v>
+      </c>
+      <c r="E158" t="s">
+        <v>299</v>
+      </c>
+      <c r="F158" t="s">
+        <v>50</v>
+      </c>
+      <c r="J158" t="s">
+        <v>18</v>
+      </c>
+      <c r="K158" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F158,'feed pars'!B$6:B$42,0))</f>
+        <v>8.6999999999999993</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>25</v>
+      </c>
+      <c r="E159" t="s">
+        <v>299</v>
+      </c>
+      <c r="F159" t="s">
+        <v>51</v>
+      </c>
+      <c r="J159" t="s">
+        <v>18</v>
+      </c>
+      <c r="K159" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F159,'feed pars'!B$6:B$42,0))</f>
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>25</v>
+      </c>
+      <c r="E160" t="s">
+        <v>299</v>
+      </c>
+      <c r="F160" t="s">
+        <v>313</v>
+      </c>
+      <c r="J160" t="s">
+        <v>18</v>
+      </c>
+      <c r="K160" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F160,'feed pars'!B$6:B$42,0))</f>
+        <v>7.0888888888888877</v>
+      </c>
+    </row>
+    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>25</v>
+      </c>
+      <c r="E161" t="s">
+        <v>299</v>
+      </c>
+      <c r="F161" t="s">
+        <v>52</v>
+      </c>
+      <c r="J161" t="s">
+        <v>18</v>
+      </c>
+      <c r="K161" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F161,'feed pars'!B$6:B$42,0))</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>25</v>
+      </c>
+      <c r="E162" t="s">
+        <v>299</v>
+      </c>
+      <c r="F162" t="s">
+        <v>53</v>
+      </c>
+      <c r="J162" t="s">
+        <v>18</v>
+      </c>
+      <c r="K162" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F162,'feed pars'!B$6:B$42,0))</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>25</v>
+      </c>
+      <c r="E163" t="s">
+        <v>299</v>
+      </c>
+      <c r="F163" t="s">
+        <v>54</v>
+      </c>
+      <c r="J163" t="s">
+        <v>18</v>
+      </c>
+      <c r="K163" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F163,'feed pars'!B$6:B$42,0))</f>
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>25</v>
+      </c>
+      <c r="E164" t="s">
+        <v>299</v>
+      </c>
+      <c r="F164" t="s">
+        <v>55</v>
+      </c>
+      <c r="J164" t="s">
+        <v>18</v>
+      </c>
+      <c r="K164" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F164,'feed pars'!B$6:B$42,0))</f>
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>25</v>
+      </c>
+      <c r="E165" t="s">
+        <v>299</v>
+      </c>
+      <c r="F165" t="s">
+        <v>56</v>
+      </c>
+      <c r="J165" t="s">
+        <v>18</v>
+      </c>
+      <c r="K165" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F165,'feed pars'!B$6:B$42,0))</f>
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>25</v>
+      </c>
+      <c r="E166" t="s">
+        <v>299</v>
+      </c>
+      <c r="F166" t="s">
+        <v>57</v>
+      </c>
+      <c r="J166" t="s">
+        <v>18</v>
+      </c>
+      <c r="K166" s="26">
+        <f>INDEX('feed pars'!H$6:H$42,MATCH(F166,'feed pars'!B$6:B$42,0))</f>
         <v>10.8</v>
       </c>
-      <c r="L156" t="s">
+    </row>
+    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A167" s="30" t="s">
+        <v>392</v>
+      </c>
+      <c r="B167" s="31"/>
+      <c r="C167" s="32"/>
+      <c r="D167" s="32"/>
+      <c r="E167" s="32"/>
+      <c r="F167" s="32"/>
+      <c r="G167" s="32"/>
+      <c r="H167" s="32"/>
+      <c r="I167" s="32"/>
+      <c r="J167" s="32"/>
+      <c r="K167" s="32"/>
+      <c r="L167" s="32" t="s">
         <v>22</v>
+      </c>
+      <c r="M167" s="32"/>
+      <c r="N167" s="32"/>
+    </row>
+    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>25</v>
+      </c>
+      <c r="F168" t="s">
+        <v>17</v>
+      </c>
+      <c r="J168" t="s">
+        <v>18</v>
+      </c>
+      <c r="K168" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F168,'feed pars'!B$6:B$42,0))</f>
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>25</v>
+      </c>
+      <c r="F169" t="s">
+        <v>37</v>
+      </c>
+      <c r="J169" t="s">
+        <v>18</v>
+      </c>
+      <c r="K169" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F169,'feed pars'!B$6:B$42,0))</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="170" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>25</v>
+      </c>
+      <c r="F170" t="s">
+        <v>38</v>
+      </c>
+      <c r="J170" t="s">
+        <v>18</v>
+      </c>
+      <c r="K170" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F170,'feed pars'!B$6:B$42,0))</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>25</v>
+      </c>
+      <c r="F171" t="s">
+        <v>39</v>
+      </c>
+      <c r="J171" t="s">
+        <v>18</v>
+      </c>
+      <c r="K171" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F171,'feed pars'!B$6:B$42,0))</f>
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>25</v>
+      </c>
+      <c r="F172" t="s">
+        <v>40</v>
+      </c>
+      <c r="J172" t="s">
+        <v>18</v>
+      </c>
+      <c r="K172" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F172,'feed pars'!B$6:B$42,0))</f>
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>25</v>
+      </c>
+      <c r="F173" t="s">
+        <v>41</v>
+      </c>
+      <c r="J173" t="s">
+        <v>18</v>
+      </c>
+      <c r="K173" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F173,'feed pars'!B$6:B$42,0))</f>
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>25</v>
+      </c>
+      <c r="F174" t="s">
+        <v>42</v>
+      </c>
+      <c r="J174" t="s">
+        <v>18</v>
+      </c>
+      <c r="K174" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F174,'feed pars'!B$6:B$42,0))</f>
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>25</v>
+      </c>
+      <c r="F175" t="s">
+        <v>35</v>
+      </c>
+      <c r="J175" t="s">
+        <v>18</v>
+      </c>
+      <c r="K175" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F175,'feed pars'!B$6:B$42,0))</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>25</v>
+      </c>
+      <c r="F176" t="s">
+        <v>43</v>
+      </c>
+      <c r="J176" t="s">
+        <v>18</v>
+      </c>
+      <c r="K176" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F176,'feed pars'!B$6:B$42,0))</f>
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>25</v>
+      </c>
+      <c r="F177" t="s">
+        <v>314</v>
+      </c>
+      <c r="J177" t="s">
+        <v>18</v>
+      </c>
+      <c r="K177" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F177,'feed pars'!B$6:B$42,0))</f>
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>25</v>
+      </c>
+      <c r="F178" t="s">
+        <v>44</v>
+      </c>
+      <c r="J178" t="s">
+        <v>18</v>
+      </c>
+      <c r="K178" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F178,'feed pars'!B$6:B$42,0))</f>
+        <v>9.3000000000000007</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>25</v>
+      </c>
+      <c r="F179" t="s">
+        <v>45</v>
+      </c>
+      <c r="J179" t="s">
+        <v>18</v>
+      </c>
+      <c r="K179" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F179,'feed pars'!B$6:B$42,0))</f>
+        <v>9.6999999999999993</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>25</v>
+      </c>
+      <c r="F180" t="s">
+        <v>36</v>
+      </c>
+      <c r="J180" t="s">
+        <v>18</v>
+      </c>
+      <c r="K180" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F180,'feed pars'!B$6:B$42,0))</f>
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>25</v>
+      </c>
+      <c r="F181" t="s">
+        <v>46</v>
+      </c>
+      <c r="J181" t="s">
+        <v>18</v>
+      </c>
+      <c r="K181" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F181,'feed pars'!B$6:B$42,0))</f>
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>25</v>
+      </c>
+      <c r="F182" t="s">
+        <v>47</v>
+      </c>
+      <c r="J182" t="s">
+        <v>18</v>
+      </c>
+      <c r="K182" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F182,'feed pars'!B$6:B$42,0))</f>
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>25</v>
+      </c>
+      <c r="F183" t="s">
+        <v>48</v>
+      </c>
+      <c r="J183" t="s">
+        <v>18</v>
+      </c>
+      <c r="K183" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F183,'feed pars'!B$6:B$42,0))</f>
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>25</v>
+      </c>
+      <c r="F184" t="s">
+        <v>49</v>
+      </c>
+      <c r="J184" t="s">
+        <v>18</v>
+      </c>
+      <c r="K184" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F184,'feed pars'!B$6:B$42,0))</f>
+        <v>8.6999999999999993</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>25</v>
+      </c>
+      <c r="F185" t="s">
+        <v>50</v>
+      </c>
+      <c r="J185" t="s">
+        <v>18</v>
+      </c>
+      <c r="K185" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F185,'feed pars'!B$6:B$42,0))</f>
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>25</v>
+      </c>
+      <c r="F186" t="s">
+        <v>51</v>
+      </c>
+      <c r="J186" t="s">
+        <v>18</v>
+      </c>
+      <c r="K186" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F186,'feed pars'!B$6:B$42,0))</f>
+        <v>8.1999999999999993</v>
+      </c>
+    </row>
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>25</v>
+      </c>
+      <c r="F187" t="s">
+        <v>313</v>
+      </c>
+      <c r="J187" t="s">
+        <v>18</v>
+      </c>
+      <c r="K187" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F187,'feed pars'!B$6:B$42,0))</f>
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>25</v>
+      </c>
+      <c r="F188" t="s">
+        <v>52</v>
+      </c>
+      <c r="J188" t="s">
+        <v>18</v>
+      </c>
+      <c r="K188" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F188,'feed pars'!B$6:B$42,0))</f>
+        <v>8.6999999999999993</v>
+      </c>
+    </row>
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>25</v>
+      </c>
+      <c r="F189" t="s">
+        <v>53</v>
+      </c>
+      <c r="J189" t="s">
+        <v>18</v>
+      </c>
+      <c r="K189" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F189,'feed pars'!B$6:B$42,0))</f>
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>25</v>
+      </c>
+      <c r="F190" t="s">
+        <v>54</v>
+      </c>
+      <c r="J190" t="s">
+        <v>18</v>
+      </c>
+      <c r="K190" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F190,'feed pars'!B$6:B$42,0))</f>
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>25</v>
+      </c>
+      <c r="F191" t="s">
+        <v>55</v>
+      </c>
+      <c r="J191" t="s">
+        <v>18</v>
+      </c>
+      <c r="K191" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F191,'feed pars'!B$6:B$42,0))</f>
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>25</v>
+      </c>
+      <c r="F192" t="s">
+        <v>56</v>
+      </c>
+      <c r="J192" t="s">
+        <v>18</v>
+      </c>
+      <c r="K192" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F192,'feed pars'!B$6:B$42,0))</f>
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>25</v>
+      </c>
+      <c r="F193" t="s">
+        <v>57</v>
+      </c>
+      <c r="J193" t="s">
+        <v>18</v>
+      </c>
+      <c r="K193" s="26">
+        <f>INDEX('feed pars'!G$6:G$42,MATCH(F193,'feed pars'!B$6:B$42,0))</f>
+        <v>10.8</v>
       </c>
     </row>
   </sheetData>
@@ -4237,14 +4877,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:N42"/>
+  <dimension ref="B1:O42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="7.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>119</v>
       </c>
@@ -4254,18 +4894,21 @@
       <c r="D1" s="11"/>
       <c r="E1" s="11"/>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C3" s="4" t="s">
         <v>307</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N3" s="4" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C4" s="4"/>
       <c r="E4" s="4" t="s">
         <v>297</v>
@@ -4280,19 +4923,24 @@
         <v>3</v>
       </c>
       <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>297</v>
       </c>
+      <c r="K4" s="4">
+        <v>1</v>
+      </c>
       <c r="L4" s="4">
+        <v>2</v>
+      </c>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="O4" s="4">
         <v>1</v>
       </c>
-      <c r="M4" s="4">
-        <v>2</v>
-      </c>
-      <c r="N4" s="4"/>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>58</v>
       </c>
@@ -4312,85 +4960,90 @@
         <v>121</v>
       </c>
       <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
+      <c r="J5" s="4" t="s">
+        <v>298</v>
+      </c>
       <c r="K5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="N5" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="O5" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="M5" s="4" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>310</v>
       </c>
       <c r="C6">
         <v>100</v>
       </c>
-      <c r="M6" s="27">
+      <c r="L6" s="27">
         <v>11.5</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>311</v>
       </c>
       <c r="C7">
         <v>100</v>
       </c>
-      <c r="M7" s="27">
+      <c r="L7" s="27">
         <v>10.4</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>312</v>
       </c>
       <c r="C8">
         <v>100</v>
       </c>
-      <c r="M8" s="25">
+      <c r="L8" s="25">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>2</v>
       </c>
       <c r="C9">
         <v>100</v>
       </c>
-      <c r="M9" s="27">
+      <c r="L9" s="27">
         <v>9.1</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>12</v>
       </c>
       <c r="C10">
         <v>100</v>
       </c>
-      <c r="K10" s="4"/>
-      <c r="M10" s="27">
+      <c r="J10" s="4"/>
+      <c r="L10" s="27">
         <v>11.3</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>33</v>
       </c>
       <c r="C11">
         <v>100</v>
       </c>
-      <c r="M11" s="27">
+      <c r="L11" s="27">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="E12" s="4"/>
@@ -4400,15 +5053,14 @@
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="28"/>
-    </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="L12" s="28"/>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>17</v>
       </c>
       <c r="C13" s="23">
-        <f>AVERAGE(F13,L13)</f>
+        <f>AVERAGE(F13,K13)</f>
         <v>87</v>
       </c>
       <c r="D13" s="4"/>
@@ -4428,25 +5080,33 @@
         <f>INDEX(pigs!$D$3:$AO$60,$E13,H$4)</f>
         <v>12.3</v>
       </c>
-      <c r="K13" s="4">
+      <c r="J13" s="4">
         <f>MATCH($B13,cattle!$A$3:$A$120,0)</f>
         <v>112</v>
       </c>
-      <c r="L13">
-        <f>INDEX(cattle!$D$3:$AH$120,$K13,L$4)</f>
+      <c r="K13">
+        <f>INDEX(cattle!$D$3:$AH$120,$J13,K$4)</f>
         <v>87</v>
       </c>
-      <c r="M13" s="27">
-        <f>INDEX(cattle!$D$3:$AH$120,$K13,M$4)</f>
+      <c r="L13" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$J13,L$4)</f>
         <v>14.1</v>
       </c>
-    </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N13" s="4">
+        <f>MATCH($B13,poultry!$A$3:$A$41,0)</f>
+        <v>35</v>
+      </c>
+      <c r="O13">
+        <f>INDEX(poultry!$D$3:$U$41,$N13,O$4)</f>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>37</v>
       </c>
       <c r="C14" s="23">
-        <f t="shared" ref="C14:C42" si="0">AVERAGE(F14,L14)</f>
+        <f>AVERAGE(F14,K14)</f>
         <v>87</v>
       </c>
       <c r="D14" s="4"/>
@@ -4466,25 +5126,33 @@
         <f>INDEX(pigs!$D$3:$AO$60,$E14,H$4)</f>
         <v>11.2</v>
       </c>
-      <c r="K14" s="4">
+      <c r="J14" s="4">
         <f>MATCH($B14,cattle!$A$3:$A$120,0)</f>
         <v>42</v>
       </c>
-      <c r="L14">
-        <f>INDEX(cattle!$D$3:$AH$120,$K14,L$4)</f>
+      <c r="K14">
+        <f>INDEX(cattle!$D$3:$AH$120,$J14,K$4)</f>
         <v>87</v>
       </c>
-      <c r="M14" s="27">
-        <f>INDEX(cattle!$D$3:$AH$120,$K14,M$4)</f>
+      <c r="L14" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$J14,L$4)</f>
         <v>13.2</v>
       </c>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N14" s="4">
+        <f>MATCH($B14,poultry!$A$3:$A$41,0)</f>
+        <v>16</v>
+      </c>
+      <c r="O14">
+        <f>INDEX(poultry!$D$3:$U$41,$N14,O$4)</f>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>38</v>
       </c>
       <c r="C15" s="23">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(F15,K15)</f>
         <v>86</v>
       </c>
       <c r="D15" s="4"/>
@@ -4504,25 +5172,33 @@
         <f>INDEX(pigs!$D$3:$AO$60,$E15,H$4)</f>
         <v>9.4</v>
       </c>
-      <c r="K15" s="4">
+      <c r="J15" s="4">
         <f>MATCH($B15,cattle!$A$3:$A$120,0)</f>
         <v>28</v>
       </c>
-      <c r="L15">
-        <f>INDEX(cattle!$D$3:$AH$120,$K15,L$4)</f>
+      <c r="K15">
+        <f>INDEX(cattle!$D$3:$AH$120,$J15,K$4)</f>
         <v>85</v>
       </c>
-      <c r="M15" s="27">
-        <f>INDEX(cattle!$D$3:$AH$120,$K15,M$4)</f>
+      <c r="L15" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$J15,L$4)</f>
         <v>11.7</v>
       </c>
-    </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N15" s="4">
+        <f>MATCH($B15,poultry!$A$3:$A$41,0)</f>
+        <v>10</v>
+      </c>
+      <c r="O15">
+        <f>INDEX(poultry!$D$3:$U$41,$N15,O$4)</f>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>39</v>
       </c>
       <c r="C16" s="23">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(F16,K16)</f>
         <v>87</v>
       </c>
       <c r="D16" s="4"/>
@@ -4542,25 +5218,33 @@
         <f>INDEX(pigs!$D$3:$AO$60,$E16,H$4)</f>
         <v>12</v>
       </c>
-      <c r="K16" s="4">
+      <c r="J16" s="4">
         <f>MATCH($B16,cattle!$A$3:$A$120,0)</f>
         <v>78</v>
       </c>
-      <c r="L16">
-        <f>INDEX(cattle!$D$3:$AH$120,$K16,L$4)</f>
+      <c r="K16">
+        <f>INDEX(cattle!$D$3:$AH$120,$J16,K$4)</f>
         <v>87</v>
       </c>
-      <c r="M16" s="27">
-        <f>INDEX(cattle!$D$3:$AH$120,$K16,M$4)</f>
+      <c r="L16" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$J16,L$4)</f>
         <v>14</v>
       </c>
-    </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N16" s="4">
+        <f>MATCH($B16,poultry!$A$3:$A$41,0)</f>
+        <v>31</v>
+      </c>
+      <c r="O16">
+        <f>INDEX(poultry!$D$3:$U$41,$N16,O$4)</f>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>317</v>
       </c>
       <c r="C17" s="23">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(F17,K17)</f>
         <v>87</v>
       </c>
       <c r="D17" s="4"/>
@@ -4568,25 +5252,33 @@
         <f>MATCH($B17,pigs!$A$3:$A$60,0)</f>
         <v>38</v>
       </c>
-      <c r="K17" s="4">
+      <c r="J17" s="4">
         <f>MATCH($B17,cattle!$A$3:$A$120,0)</f>
         <v>77</v>
       </c>
-      <c r="L17">
-        <f>INDEX(cattle!$D$3:$AH$120,$K17,L$4)</f>
+      <c r="K17">
+        <f>INDEX(cattle!$D$3:$AH$120,$J17,K$4)</f>
         <v>87</v>
       </c>
-      <c r="M17" s="27">
-        <f>INDEX(cattle!$D$3:$AH$120,$K17,M$4)</f>
+      <c r="L17" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$J17,L$4)</f>
         <v>13.9</v>
       </c>
-    </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N17" s="4">
+        <f>MATCH($B17,poultry!$A$3:$A$41,0)</f>
+        <v>30</v>
+      </c>
+      <c r="O17">
+        <f>INDEX(poultry!$D$3:$U$41,$N17,O$4)</f>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>40</v>
       </c>
       <c r="C18" s="23">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(F18,K18)</f>
         <v>67.5</v>
       </c>
       <c r="D18" s="4"/>
@@ -4606,25 +5298,33 @@
         <f>INDEX(pigs!$D$3:$AO$60,$E18,H$4)</f>
         <v>13.2</v>
       </c>
-      <c r="K18" s="4">
+      <c r="J18" s="4">
         <f>MATCH($B18,cattle!$A$3:$A$120,0)</f>
         <v>53</v>
       </c>
-      <c r="L18">
-        <f>INDEX(cattle!$D$3:$AH$120,$K18,L$4)</f>
+      <c r="K18">
+        <f>INDEX(cattle!$D$3:$AH$120,$J18,K$4)</f>
         <v>48</v>
       </c>
-      <c r="M18" s="27">
-        <f>INDEX(cattle!$D$3:$AH$120,$K18,M$4)</f>
+      <c r="L18" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$J18,L$4)</f>
         <v>12.8</v>
       </c>
-    </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N18" s="4">
+        <f>MATCH($B18,poultry!$A$3:$A$41,0)</f>
+        <v>24</v>
+      </c>
+      <c r="O18">
+        <f>INDEX(poultry!$D$3:$U$41,$N18,O$4)</f>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>41</v>
       </c>
       <c r="C19" s="23">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(F19,K19)</f>
         <v>87</v>
       </c>
       <c r="D19" s="4"/>
@@ -4644,25 +5344,33 @@
         <f>INDEX(pigs!$D$3:$AO$60,$E19,H$4)</f>
         <v>11.5</v>
       </c>
-      <c r="K19" s="4">
+      <c r="J19" s="4">
         <f>MATCH($B19,cattle!$A$3:$A$120,0)</f>
         <v>115</v>
       </c>
-      <c r="L19">
-        <f>INDEX(cattle!$D$3:$AH$120,$K19,L$4)</f>
+      <c r="K19">
+        <f>INDEX(cattle!$D$3:$AH$120,$J19,K$4)</f>
         <v>87</v>
       </c>
-      <c r="M19" s="27">
-        <f>INDEX(cattle!$D$3:$AH$120,$K19,M$4)</f>
+      <c r="L19" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$J19,L$4)</f>
         <v>13.8</v>
       </c>
-    </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N19" s="4">
+        <f>MATCH($B19,poultry!$A$3:$A$41,0)</f>
+        <v>39</v>
+      </c>
+      <c r="O19">
+        <f>INDEX(poultry!$D$3:$U$41,$N19,O$4)</f>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>42</v>
       </c>
       <c r="C20" s="23">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(F20,K20)</f>
         <v>86.8</v>
       </c>
       <c r="D20" s="4"/>
@@ -4682,23 +5390,24 @@
         <f>INDEX(pigs!$D$3:$AO$60,$E20,H$4)</f>
         <v>10.9</v>
       </c>
-      <c r="K20" s="4"/>
-      <c r="L20">
+      <c r="J20" s="4"/>
+      <c r="K20">
         <v>86.6</v>
       </c>
-      <c r="M20" s="27">
+      <c r="L20" s="27">
         <v>13.3</v>
       </c>
-      <c r="N20" t="s">
+      <c r="M20" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N20" s="4"/>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>35</v>
       </c>
       <c r="C21" s="23">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(F21,K21)</f>
         <v>92.5</v>
       </c>
       <c r="D21" s="4"/>
@@ -4718,25 +5427,26 @@
         <f>INDEX(pigs!$D$3:$AO$60,$E21,H$4)</f>
         <v>18.5</v>
       </c>
-      <c r="K21" s="4">
+      <c r="J21" s="4">
         <f>MATCH($B21,cattle!$A$3:$A$120,0)</f>
         <v>71</v>
       </c>
-      <c r="L21">
-        <f>INDEX(cattle!$D$3:$AH$120,$K21,L$4)</f>
+      <c r="K21">
+        <f>INDEX(cattle!$D$3:$AH$120,$J21,K$4)</f>
         <v>93</v>
       </c>
-      <c r="M21" s="27">
-        <f>INDEX(cattle!$D$3:$AH$120,$K21,M$4)</f>
+      <c r="L21" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$J21,L$4)</f>
         <v>22.1</v>
       </c>
-    </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N21" s="4"/>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>43</v>
       </c>
       <c r="C22" s="23">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(F22,K22)</f>
         <v>92</v>
       </c>
       <c r="D22" s="4"/>
@@ -4756,25 +5466,26 @@
         <f>INDEX(pigs!$D$3:$AO$60,$E22,H$4)</f>
         <v>17.5</v>
       </c>
-      <c r="K22" s="4">
+      <c r="J22" s="4">
         <f>MATCH($B22,cattle!$A$3:$A$120,0)</f>
         <v>45</v>
       </c>
-      <c r="L22">
-        <f>INDEX(cattle!$D$3:$AH$120,$K22,L$4)</f>
+      <c r="K22">
+        <f>INDEX(cattle!$D$3:$AH$120,$J22,K$4)</f>
         <v>93</v>
       </c>
-      <c r="M22" s="27">
-        <f>INDEX(cattle!$D$3:$AH$120,$K22,M$4)</f>
+      <c r="L22" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$J22,L$4)</f>
         <v>20.100000000000001</v>
       </c>
-    </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N22" s="4"/>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>314</v>
       </c>
       <c r="C23" s="23">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(F23,K23)</f>
         <v>100</v>
       </c>
       <c r="D23" s="4"/>
@@ -4794,69 +5505,79 @@
         <f>INDEX(pigs!$D$3:$AO$60,$E23,H$4)</f>
         <v>29.8</v>
       </c>
-      <c r="K23" s="4"/>
-      <c r="L23">
+      <c r="J23" s="4"/>
+      <c r="K23">
         <v>100</v>
       </c>
-      <c r="M23" s="27">
+      <c r="L23" s="27">
         <v>36.6</v>
       </c>
-      <c r="N23" t="s">
+      <c r="M23" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N23" s="4">
+        <f>MATCH($B23,poultry!$A$3:$A$41,0)</f>
+        <v>1</v>
+      </c>
+      <c r="O23">
+        <f>INDEX(poultry!$D$3:$U$41,$N23,O$4)</f>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>305</v>
       </c>
       <c r="C24" s="23">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(F24,K24)</f>
         <v>85</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
-      <c r="K24" s="4">
+      <c r="J24" s="4">
         <f>MATCH($B24,cattle!$A$3:$A$120,0)</f>
         <v>22</v>
       </c>
-      <c r="L24">
-        <f>INDEX(cattle!$D$3:$AH$120,$K24,L$4)</f>
+      <c r="K24">
+        <f>INDEX(cattle!$D$3:$AH$120,$J24,K$4)</f>
         <v>85</v>
       </c>
-      <c r="M24" s="27">
-        <f>INDEX(cattle!$D$3:$AH$120,$K24,M$4)</f>
+      <c r="L24" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$J24,L$4)</f>
         <v>6.6</v>
       </c>
-    </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N24" s="4"/>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>318</v>
       </c>
       <c r="C25" s="23">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(F25,K25)</f>
         <v>87</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
-      <c r="K25" s="4">
+      <c r="J25" s="4">
         <f>MATCH($B25,cattle!$A$3:$A$120,0)</f>
         <v>92</v>
       </c>
-      <c r="L25">
-        <f>INDEX(cattle!$D$3:$AH$120,$K25,L$4)</f>
+      <c r="K25">
+        <f>INDEX(cattle!$D$3:$AH$120,$J25,K$4)</f>
         <v>87</v>
       </c>
-      <c r="M25" s="27">
-        <f>INDEX(cattle!$D$3:$AH$120,$K25,M$4)</f>
+      <c r="L25" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$J25,L$4)</f>
         <v>16.399999999999999</v>
       </c>
-    </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N25" s="4"/>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>44</v>
       </c>
       <c r="C26" s="23">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(F26,K26)</f>
         <v>87.5</v>
       </c>
       <c r="D26" s="4"/>
@@ -4876,25 +5597,33 @@
         <f>INDEX(pigs!$D$3:$AO$60,$E26,H$4)</f>
         <v>9.9</v>
       </c>
-      <c r="K26" s="4">
+      <c r="J26" s="4">
         <f>MATCH($B26,cattle!$A$3:$A$120,0)</f>
         <v>93</v>
       </c>
-      <c r="L26">
-        <f>INDEX(cattle!$D$3:$AH$120,$K26,L$4)</f>
+      <c r="K26">
+        <f>INDEX(cattle!$D$3:$AH$120,$J26,K$4)</f>
         <v>87</v>
       </c>
-      <c r="M26" s="27">
-        <f>INDEX(cattle!$D$3:$AH$120,$K26,M$4)</f>
+      <c r="L26" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$J26,L$4)</f>
         <v>14.6</v>
       </c>
-    </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N26" s="4">
+        <f>MATCH($B26,poultry!$A$3:$A$41,0)</f>
+        <v>33</v>
+      </c>
+      <c r="O26">
+        <f>INDEX(poultry!$D$3:$U$41,$N26,O$4)</f>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>45</v>
       </c>
       <c r="C27" s="23">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(F27,K27)</f>
         <v>87</v>
       </c>
       <c r="D27" s="4"/>
@@ -4914,15 +5643,16 @@
         <f>INDEX(pigs!$D$3:$AO$60,$E27,H$4)</f>
         <v>10.3</v>
       </c>
-      <c r="K27" s="4"/>
-      <c r="M27" s="27"/>
-    </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="J27" s="4"/>
+      <c r="L27" s="27"/>
+      <c r="N27" s="4"/>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>36</v>
       </c>
       <c r="C28" s="23">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(F28,K28)</f>
         <v>89.5</v>
       </c>
       <c r="D28" s="4"/>
@@ -4942,25 +5672,33 @@
         <f>INDEX(pigs!$D$3:$AO$60,$E28,H$4)</f>
         <v>7.7</v>
       </c>
-      <c r="K28" s="4">
+      <c r="J28" s="4">
         <f>MATCH($B28,cattle!$A$3:$A$120,0)</f>
         <v>70</v>
       </c>
-      <c r="L28">
-        <f>INDEX(cattle!$D$3:$AH$120,$K28,L$4)</f>
+      <c r="K28">
+        <f>INDEX(cattle!$D$3:$AH$120,$J28,K$4)</f>
         <v>90</v>
       </c>
-      <c r="M28" s="27">
-        <f>INDEX(cattle!$D$3:$AH$120,$K28,M$4)</f>
+      <c r="L28" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$J28,L$4)</f>
         <v>12.2</v>
       </c>
-    </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N28" s="4">
+        <f>MATCH($B28,poultry!$A$3:$A$41,0)</f>
+        <v>29</v>
+      </c>
+      <c r="O28">
+        <f>INDEX(poultry!$D$3:$U$41,$N28,O$4)</f>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>46</v>
       </c>
       <c r="C29" s="23">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(F29,K29)</f>
         <v>91</v>
       </c>
       <c r="D29" s="4"/>
@@ -4980,25 +5718,26 @@
         <f>INDEX(pigs!$D$3:$AO$60,$E29,H$4)</f>
         <v>6.5</v>
       </c>
-      <c r="K29" s="4">
+      <c r="J29" s="4">
         <f>MATCH($B29,cattle!$A$3:$A$120,0)</f>
         <v>99</v>
       </c>
-      <c r="L29">
-        <f>INDEX(cattle!$D$3:$AH$120,$K29,L$4)</f>
+      <c r="K29">
+        <f>INDEX(cattle!$D$3:$AH$120,$J29,K$4)</f>
         <v>92</v>
       </c>
-      <c r="M29" s="27">
-        <f>INDEX(cattle!$D$3:$AH$120,$K29,M$4)</f>
+      <c r="L29" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$J29,L$4)</f>
         <v>11.4</v>
       </c>
-    </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N29" s="4"/>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>47</v>
       </c>
       <c r="C30" s="23">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(F30,K30)</f>
         <v>91</v>
       </c>
       <c r="D30" s="4"/>
@@ -5018,46 +5757,48 @@
         <f>INDEX(pigs!$D$3:$AO$60,$E30,H$4)</f>
         <v>6.2</v>
       </c>
-      <c r="K30" s="4">
+      <c r="J30" s="4">
         <f>MATCH($B30,cattle!$A$3:$A$120,0)</f>
         <v>60</v>
       </c>
-      <c r="L30">
-        <f>INDEX(cattle!$D$3:$AH$120,$K30,L$4)</f>
+      <c r="K30">
+        <f>INDEX(cattle!$D$3:$AH$120,$J30,K$4)</f>
         <v>91</v>
       </c>
-      <c r="M30" s="27">
-        <f>INDEX(cattle!$D$3:$AH$120,$K30,M$4)</f>
+      <c r="L30" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$J30,L$4)</f>
         <v>13.4</v>
       </c>
-    </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N30" s="4"/>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>319</v>
       </c>
       <c r="C31" s="23">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(F31,K31)</f>
         <v>90</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
-      <c r="K31" s="4"/>
-      <c r="L31">
+      <c r="J31" s="4"/>
+      <c r="K31">
         <v>90</v>
       </c>
-      <c r="M31" s="27">
+      <c r="L31" s="27">
         <v>8.5</v>
       </c>
-      <c r="N31" s="11" t="s">
+      <c r="M31" s="11" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N31" s="4"/>
+    </row>
+    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>48</v>
       </c>
       <c r="C32" s="23">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(F32,K32)</f>
         <v>87</v>
       </c>
       <c r="D32" s="4"/>
@@ -5077,25 +5818,33 @@
         <f>INDEX(pigs!$D$3:$AO$60,$E32,H$4)</f>
         <v>7.8</v>
       </c>
-      <c r="K32" s="4">
+      <c r="J32" s="4">
         <f>MATCH($B32,cattle!$A$3:$A$120,0)</f>
         <v>111</v>
       </c>
-      <c r="L32">
-        <f>INDEX(cattle!$D$3:$AH$120,$K32,L$4)</f>
+      <c r="K32">
+        <f>INDEX(cattle!$D$3:$AH$120,$J32,K$4)</f>
         <v>87</v>
       </c>
-      <c r="M32" s="27">
-        <f>INDEX(cattle!$D$3:$AH$120,$K32,M$4)</f>
+      <c r="L32" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$J32,L$4)</f>
         <v>11</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N32" s="4">
+        <f>MATCH($B32,poultry!$A$3:$A$41,0)</f>
+        <v>38</v>
+      </c>
+      <c r="O32">
+        <f>INDEX(poultry!$D$3:$U$41,$N32,O$4)</f>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>49</v>
       </c>
       <c r="C33" s="23">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(F33,K33)</f>
         <v>88</v>
       </c>
       <c r="D33" s="4"/>
@@ -5115,15 +5864,23 @@
         <f>INDEX(pigs!$D$3:$AO$60,$E33,H$4)</f>
         <v>9.1999999999999993</v>
       </c>
-      <c r="K33" s="4"/>
-      <c r="M33" s="27"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="J33" s="4"/>
+      <c r="L33" s="27"/>
+      <c r="N33" s="4">
+        <f>MATCH($B33,poultry!$A$3:$A$41,0)</f>
+        <v>36</v>
+      </c>
+      <c r="O33">
+        <f>INDEX(poultry!$D$3:$U$41,$N33,O$4)</f>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>50</v>
       </c>
       <c r="C34" s="23">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(F34,K34)</f>
         <v>90</v>
       </c>
       <c r="D34" s="4"/>
@@ -5143,25 +5900,26 @@
         <f>INDEX(pigs!$D$3:$AO$60,$E34,H$4)</f>
         <v>8.6999999999999993</v>
       </c>
-      <c r="K34" s="4">
+      <c r="J34" s="4">
         <f>MATCH($B34,cattle!$A$3:$A$120,0)</f>
         <v>109</v>
       </c>
-      <c r="L34">
-        <f>INDEX(cattle!$D$3:$AH$120,$K34,L$4)</f>
+      <c r="K34">
+        <f>INDEX(cattle!$D$3:$AH$120,$J34,K$4)</f>
         <v>90</v>
       </c>
-      <c r="M34" s="27">
-        <f>INDEX(cattle!$D$3:$AH$120,$K34,M$4)</f>
+      <c r="L34" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$J34,L$4)</f>
         <v>13.3</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N34" s="4"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>51</v>
       </c>
       <c r="C35" s="23">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(F35,K35)</f>
         <v>11</v>
       </c>
       <c r="D35" s="4"/>
@@ -5181,15 +5939,16 @@
         <f>INDEX(pigs!$D$3:$AO$60,$E35,H$4)</f>
         <v>8.9</v>
       </c>
-      <c r="K35" s="4"/>
-      <c r="M35" s="27"/>
-    </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="J35" s="4"/>
+      <c r="L35" s="27"/>
+      <c r="N35" s="4"/>
+    </row>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>313</v>
       </c>
       <c r="C36" s="23">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(F36,K36)</f>
         <v>90</v>
       </c>
       <c r="D36" s="4"/>
@@ -5207,25 +5966,26 @@
       <c r="I36" s="11" t="s">
         <v>316</v>
       </c>
-      <c r="K36" s="4">
+      <c r="J36" s="4">
         <f>MATCH($B36,cattle!$A$3:$A$120,0)</f>
         <v>38</v>
       </c>
-      <c r="L36">
-        <f>INDEX(cattle!$D$3:$AH$120,$K36,L$4)</f>
+      <c r="K36">
+        <f>INDEX(cattle!$D$3:$AH$120,$J36,K$4)</f>
         <v>90</v>
       </c>
-      <c r="M36" s="27">
-        <f>INDEX(cattle!$D$3:$AH$120,$K36,M$4)</f>
+      <c r="L36" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$J36,L$4)</f>
         <v>11.6</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N36" s="4"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>52</v>
       </c>
       <c r="C37" s="23">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(F37,K37)</f>
         <v>75.5</v>
       </c>
       <c r="D37" s="4"/>
@@ -5245,25 +6005,26 @@
         <f>INDEX(pigs!$D$3:$AO$60,$E37,H$4)</f>
         <v>9</v>
       </c>
-      <c r="K37" s="4">
+      <c r="J37" s="4">
         <f>MATCH($B37,cattle!$A$3:$A$120,0)</f>
         <v>88</v>
       </c>
-      <c r="L37">
-        <f>INDEX(cattle!$D$3:$AH$120,$K37,L$4)</f>
+      <c r="K37">
+        <f>INDEX(cattle!$D$3:$AH$120,$J37,K$4)</f>
         <v>75</v>
       </c>
-      <c r="M37" s="27">
-        <f>INDEX(cattle!$D$3:$AH$120,$K37,M$4)</f>
+      <c r="L37" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$J37,L$4)</f>
         <v>12.4</v>
       </c>
-    </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N37" s="4"/>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>53</v>
       </c>
       <c r="C38" s="23">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(F38,K38)</f>
         <v>89.5</v>
       </c>
       <c r="D38" s="4"/>
@@ -5283,25 +6044,26 @@
         <f>INDEX(pigs!$D$3:$AO$60,$E38,H$4)</f>
         <v>8</v>
       </c>
-      <c r="K38" s="4">
+      <c r="J38" s="4">
         <f>MATCH($B38,cattle!$A$3:$A$120,0)</f>
         <v>91</v>
       </c>
-      <c r="L38">
-        <f>INDEX(cattle!$D$3:$AH$120,$K38,L$4)</f>
+      <c r="K38">
+        <f>INDEX(cattle!$D$3:$AH$120,$J38,K$4)</f>
         <v>90</v>
       </c>
-      <c r="M38" s="27">
-        <f>INDEX(cattle!$D$3:$AH$120,$K38,M$4)</f>
+      <c r="L38" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$J38,L$4)</f>
         <v>12.3</v>
       </c>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N38" s="4"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>54</v>
       </c>
       <c r="C39" s="23">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(F39,K39)</f>
         <v>6.25</v>
       </c>
       <c r="D39" s="4"/>
@@ -5321,25 +6083,26 @@
         <f>INDEX(pigs!$D$3:$AO$60,$E39,H$4)</f>
         <v>12.2</v>
       </c>
-      <c r="K39" s="4">
+      <c r="J39" s="4">
         <f>MATCH($B39,cattle!$A$3:$A$120,0)</f>
         <v>57</v>
       </c>
-      <c r="L39">
-        <f>INDEX(cattle!$D$3:$AH$120,$K39,L$4)</f>
+      <c r="K39">
+        <f>INDEX(cattle!$D$3:$AH$120,$J39,K$4)</f>
         <v>7</v>
       </c>
-      <c r="M39" s="27">
-        <f>INDEX(cattle!$D$3:$AH$120,$K39,M$4)</f>
+      <c r="L39" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$J39,L$4)</f>
         <v>13.6</v>
       </c>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N39" s="4"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>55</v>
       </c>
       <c r="C40" s="23">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(F40,K40)</f>
         <v>97</v>
       </c>
       <c r="D40" s="4"/>
@@ -5359,15 +6122,16 @@
         <f>INDEX(pigs!$D$3:$AO$60,$E40,H$4)</f>
         <v>12.2</v>
       </c>
-      <c r="K40" s="4"/>
-      <c r="M40" s="27"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="J40" s="4"/>
+      <c r="L40" s="27"/>
+      <c r="N40" s="4"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>56</v>
       </c>
       <c r="C41" s="23">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(F41,K41)</f>
         <v>91</v>
       </c>
       <c r="D41" s="4"/>
@@ -5387,25 +6151,33 @@
         <f>INDEX(pigs!$D$3:$AO$60,$E41,H$4)</f>
         <v>11.3</v>
       </c>
-      <c r="K41" s="4">
+      <c r="J41" s="4">
         <f>MATCH($B41,cattle!$A$3:$A$120,0)</f>
         <v>65</v>
       </c>
-      <c r="L41">
-        <f>INDEX(cattle!$D$3:$AH$120,$K41,L$4)</f>
+      <c r="K41">
+        <f>INDEX(cattle!$D$3:$AH$120,$J41,K$4)</f>
         <v>90</v>
       </c>
-      <c r="M41" s="27">
-        <f>INDEX(cattle!$D$3:$AH$120,$K41,M$4)</f>
+      <c r="L41" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$J41,L$4)</f>
         <v>15.5</v>
       </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N41" s="4">
+        <f>MATCH($B41,poultry!$A$3:$A$41,0)</f>
+        <v>28</v>
+      </c>
+      <c r="O41">
+        <f>INDEX(poultry!$D$3:$U$41,$N41,O$4)</f>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>57</v>
       </c>
       <c r="C42" s="23">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(F42,K42)</f>
         <v>92</v>
       </c>
       <c r="D42" s="4"/>
@@ -5425,13 +6197,21 @@
         <f>INDEX(pigs!$D$3:$AO$60,$E42,H$4)</f>
         <v>10.8</v>
       </c>
-      <c r="K42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="N42" s="4">
+        <f>MATCH($B42,poultry!$A$3:$A$41,0)</f>
+        <v>6</v>
+      </c>
+      <c r="O42">
+        <f>INDEX(poultry!$D$3:$U$41,$N42,O$4)</f>
+        <v>92</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C1" r:id="rId1"/>
     <hyperlink ref="I36" r:id="rId2"/>
-    <hyperlink ref="N31" r:id="rId3"/>
+    <hyperlink ref="M31" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
@@ -23542,4 +24322,2602 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:U41"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="33" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="D1">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>2</v>
+      </c>
+      <c r="F1">
+        <v>3</v>
+      </c>
+      <c r="G1">
+        <v>4</v>
+      </c>
+      <c r="H1">
+        <v>5</v>
+      </c>
+      <c r="I1">
+        <v>6</v>
+      </c>
+      <c r="J1">
+        <v>7</v>
+      </c>
+      <c r="K1">
+        <v>8</v>
+      </c>
+      <c r="L1">
+        <v>9</v>
+      </c>
+      <c r="M1">
+        <v>10</v>
+      </c>
+      <c r="N1">
+        <v>11</v>
+      </c>
+      <c r="O1">
+        <v>12</v>
+      </c>
+      <c r="P1">
+        <v>13</v>
+      </c>
+      <c r="Q1">
+        <v>14</v>
+      </c>
+      <c r="R1">
+        <v>15</v>
+      </c>
+      <c r="S1">
+        <v>16</v>
+      </c>
+      <c r="T1">
+        <v>17</v>
+      </c>
+      <c r="U1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="29.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>337</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>338</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>339</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>340</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>341</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>342</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>343</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>344</v>
+      </c>
+      <c r="L2" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="M2" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="O2" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="P2" s="19" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q2" s="19" t="s">
+        <v>346</v>
+      </c>
+      <c r="R2" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="S2" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="T2" s="19" t="s">
+        <v>347</v>
+      </c>
+      <c r="U2" s="19" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B3" s="12">
+        <v>1</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>349</v>
+      </c>
+      <c r="D3" s="14">
+        <v>99</v>
+      </c>
+      <c r="E3" s="14">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="F3" s="14">
+        <v>0</v>
+      </c>
+      <c r="G3" s="14">
+        <v>0</v>
+      </c>
+      <c r="H3" s="14">
+        <v>0</v>
+      </c>
+      <c r="I3" s="14">
+        <v>0</v>
+      </c>
+      <c r="J3" s="14">
+        <v>965</v>
+      </c>
+      <c r="K3" s="14">
+        <v>170</v>
+      </c>
+      <c r="L3" s="14">
+        <v>0</v>
+      </c>
+      <c r="M3" s="14">
+        <v>0</v>
+      </c>
+      <c r="N3" s="14">
+        <v>0</v>
+      </c>
+      <c r="O3" s="14">
+        <v>0</v>
+      </c>
+      <c r="P3" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="14">
+        <v>0</v>
+      </c>
+      <c r="R3" s="14">
+        <v>0</v>
+      </c>
+      <c r="S3" s="14">
+        <v>0</v>
+      </c>
+      <c r="T3" s="14">
+        <v>0</v>
+      </c>
+      <c r="U3" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B4" s="15">
+        <v>2</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>350</v>
+      </c>
+      <c r="D4" s="17">
+        <v>99</v>
+      </c>
+      <c r="E4" s="17">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="F4" s="17">
+        <v>0</v>
+      </c>
+      <c r="G4" s="17">
+        <v>0</v>
+      </c>
+      <c r="H4" s="17">
+        <v>0</v>
+      </c>
+      <c r="I4" s="17">
+        <v>0</v>
+      </c>
+      <c r="J4" s="17">
+        <v>975</v>
+      </c>
+      <c r="K4" s="17">
+        <v>300</v>
+      </c>
+      <c r="L4" s="17">
+        <v>0</v>
+      </c>
+      <c r="M4" s="17">
+        <v>0</v>
+      </c>
+      <c r="N4" s="17">
+        <v>0</v>
+      </c>
+      <c r="O4" s="17">
+        <v>0</v>
+      </c>
+      <c r="P4" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="17">
+        <v>0</v>
+      </c>
+      <c r="R4" s="17">
+        <v>0</v>
+      </c>
+      <c r="S4" s="17">
+        <v>0</v>
+      </c>
+      <c r="T4" s="17">
+        <v>0</v>
+      </c>
+      <c r="U4" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B5" s="12">
+        <v>3</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>351</v>
+      </c>
+      <c r="D5" s="14">
+        <v>100</v>
+      </c>
+      <c r="E5" s="14">
+        <v>0</v>
+      </c>
+      <c r="F5" s="14">
+        <v>0</v>
+      </c>
+      <c r="G5" s="14">
+        <v>0</v>
+      </c>
+      <c r="H5" s="14">
+        <v>0</v>
+      </c>
+      <c r="I5" s="14">
+        <v>0</v>
+      </c>
+      <c r="J5" s="14">
+        <v>0</v>
+      </c>
+      <c r="K5" s="14">
+        <v>0</v>
+      </c>
+      <c r="L5" s="14">
+        <v>0</v>
+      </c>
+      <c r="M5" s="14">
+        <v>0</v>
+      </c>
+      <c r="N5" s="14">
+        <v>0</v>
+      </c>
+      <c r="O5" s="14">
+        <v>213</v>
+      </c>
+      <c r="P5" s="14">
+        <v>187</v>
+      </c>
+      <c r="Q5" s="14">
+        <v>165</v>
+      </c>
+      <c r="R5" s="14">
+        <v>1</v>
+      </c>
+      <c r="S5" s="14">
+        <v>0.6</v>
+      </c>
+      <c r="T5" s="14">
+        <v>0.13</v>
+      </c>
+      <c r="U5" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B6" s="15">
+        <v>4</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>352</v>
+      </c>
+      <c r="D6" s="17">
+        <v>100</v>
+      </c>
+      <c r="E6" s="17">
+        <v>0</v>
+      </c>
+      <c r="F6" s="17">
+        <v>0</v>
+      </c>
+      <c r="G6" s="17">
+        <v>0</v>
+      </c>
+      <c r="H6" s="17">
+        <v>0</v>
+      </c>
+      <c r="I6" s="17">
+        <v>0</v>
+      </c>
+      <c r="J6" s="17">
+        <v>0</v>
+      </c>
+      <c r="K6" s="17">
+        <v>0</v>
+      </c>
+      <c r="L6" s="17">
+        <v>0</v>
+      </c>
+      <c r="M6" s="17">
+        <v>0</v>
+      </c>
+      <c r="N6" s="17">
+        <v>0</v>
+      </c>
+      <c r="O6" s="17">
+        <v>0</v>
+      </c>
+      <c r="P6" s="17">
+        <v>208</v>
+      </c>
+      <c r="Q6" s="17">
+        <v>208</v>
+      </c>
+      <c r="R6" s="17">
+        <v>0</v>
+      </c>
+      <c r="S6" s="17">
+        <v>310</v>
+      </c>
+      <c r="T6" s="17">
+        <v>0</v>
+      </c>
+      <c r="U6" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B7" s="12">
+        <v>5</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="D7" s="14">
+        <v>100</v>
+      </c>
+      <c r="E7" s="14">
+        <v>15.4</v>
+      </c>
+      <c r="F7" s="14">
+        <v>587</v>
+      </c>
+      <c r="G7" s="14">
+        <v>0</v>
+      </c>
+      <c r="H7" s="14">
+        <v>980</v>
+      </c>
+      <c r="I7" s="14">
+        <v>980</v>
+      </c>
+      <c r="J7" s="14">
+        <v>0</v>
+      </c>
+      <c r="K7" s="14">
+        <v>0</v>
+      </c>
+      <c r="L7" s="14">
+        <v>0</v>
+      </c>
+      <c r="M7" s="14">
+        <v>0</v>
+      </c>
+      <c r="N7" s="14">
+        <v>0</v>
+      </c>
+      <c r="O7" s="14">
+        <v>0</v>
+      </c>
+      <c r="P7" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="14">
+        <v>0</v>
+      </c>
+      <c r="R7" s="14">
+        <v>0</v>
+      </c>
+      <c r="S7" s="14">
+        <v>0</v>
+      </c>
+      <c r="T7" s="14">
+        <v>0</v>
+      </c>
+      <c r="U7" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="15">
+        <v>6</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>354</v>
+      </c>
+      <c r="D8" s="17">
+        <v>92</v>
+      </c>
+      <c r="E8" s="17">
+        <v>12.6</v>
+      </c>
+      <c r="F8" s="17">
+        <v>621</v>
+      </c>
+      <c r="G8" s="17">
+        <v>48.1</v>
+      </c>
+      <c r="H8" s="17">
+        <v>17.7</v>
+      </c>
+      <c r="I8" s="17">
+        <v>23.4</v>
+      </c>
+      <c r="J8" s="17">
+        <v>50</v>
+      </c>
+      <c r="K8" s="17">
+        <v>0.8</v>
+      </c>
+      <c r="L8" s="17">
+        <v>0</v>
+      </c>
+      <c r="M8" s="17">
+        <v>0</v>
+      </c>
+      <c r="N8" s="17">
+        <v>0</v>
+      </c>
+      <c r="O8" s="17">
+        <v>41</v>
+      </c>
+      <c r="P8" s="17">
+        <v>26</v>
+      </c>
+      <c r="Q8" s="17">
+        <v>21</v>
+      </c>
+      <c r="R8" s="17">
+        <v>9</v>
+      </c>
+      <c r="S8" s="17">
+        <v>6</v>
+      </c>
+      <c r="T8" s="17">
+        <v>9</v>
+      </c>
+      <c r="U8" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B9" s="12">
+        <v>7</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="D9" s="14">
+        <v>92</v>
+      </c>
+      <c r="E9" s="14">
+        <v>10.8</v>
+      </c>
+      <c r="F9" s="14">
+        <v>653</v>
+      </c>
+      <c r="G9" s="14">
+        <v>50.1</v>
+      </c>
+      <c r="H9" s="14">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="I9" s="14">
+        <v>24.2</v>
+      </c>
+      <c r="J9" s="14">
+        <v>18</v>
+      </c>
+      <c r="K9" s="14">
+        <v>0.3</v>
+      </c>
+      <c r="L9" s="14">
+        <v>0</v>
+      </c>
+      <c r="M9" s="14">
+        <v>0</v>
+      </c>
+      <c r="N9" s="14">
+        <v>0</v>
+      </c>
+      <c r="O9" s="14">
+        <v>41</v>
+      </c>
+      <c r="P9" s="14">
+        <v>26</v>
+      </c>
+      <c r="Q9" s="14">
+        <v>21</v>
+      </c>
+      <c r="R9" s="14">
+        <v>9</v>
+      </c>
+      <c r="S9" s="14">
+        <v>6</v>
+      </c>
+      <c r="T9" s="14">
+        <v>9</v>
+      </c>
+      <c r="U9" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B10" s="15">
+        <v>8</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>356</v>
+      </c>
+      <c r="D10" s="17">
+        <v>92</v>
+      </c>
+      <c r="E10" s="17">
+        <v>13.6</v>
+      </c>
+      <c r="F10" s="17">
+        <v>661</v>
+      </c>
+      <c r="G10" s="17">
+        <v>51.5</v>
+      </c>
+      <c r="H10" s="17">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="I10" s="17">
+        <v>24.9</v>
+      </c>
+      <c r="J10" s="17">
+        <v>100</v>
+      </c>
+      <c r="K10" s="17">
+        <v>1.2</v>
+      </c>
+      <c r="L10" s="17">
+        <v>0</v>
+      </c>
+      <c r="M10" s="17">
+        <v>0</v>
+      </c>
+      <c r="N10" s="17">
+        <v>0</v>
+      </c>
+      <c r="O10" s="17">
+        <v>41</v>
+      </c>
+      <c r="P10" s="17">
+        <v>26</v>
+      </c>
+      <c r="Q10" s="17">
+        <v>21</v>
+      </c>
+      <c r="R10" s="17">
+        <v>9</v>
+      </c>
+      <c r="S10" s="17">
+        <v>6</v>
+      </c>
+      <c r="T10" s="17">
+        <v>9</v>
+      </c>
+      <c r="U10" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B11" s="12">
+        <v>9</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>357</v>
+      </c>
+      <c r="D11" s="14">
+        <v>100</v>
+      </c>
+      <c r="E11" s="14">
+        <v>0</v>
+      </c>
+      <c r="F11" s="14">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14">
+        <v>0</v>
+      </c>
+      <c r="I11" s="14">
+        <v>0</v>
+      </c>
+      <c r="J11" s="14">
+        <v>0</v>
+      </c>
+      <c r="K11" s="14">
+        <v>0</v>
+      </c>
+      <c r="L11" s="14">
+        <v>0</v>
+      </c>
+      <c r="M11" s="14">
+        <v>0</v>
+      </c>
+      <c r="N11" s="14">
+        <v>0</v>
+      </c>
+      <c r="O11" s="14">
+        <v>375</v>
+      </c>
+      <c r="P11" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="14">
+        <v>0</v>
+      </c>
+      <c r="R11" s="14">
+        <v>0.6</v>
+      </c>
+      <c r="S11" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="T11" s="14">
+        <v>0</v>
+      </c>
+      <c r="U11" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="15">
+        <v>10</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="D12" s="17">
+        <v>87</v>
+      </c>
+      <c r="E12" s="17">
+        <v>10.7</v>
+      </c>
+      <c r="F12" s="17">
+        <v>104</v>
+      </c>
+      <c r="G12" s="17">
+        <v>4.5</v>
+      </c>
+      <c r="H12" s="17">
+        <v>1.8</v>
+      </c>
+      <c r="I12" s="17">
+        <v>4.8</v>
+      </c>
+      <c r="J12" s="17">
+        <v>52</v>
+      </c>
+      <c r="K12" s="17">
+        <v>21</v>
+      </c>
+      <c r="L12" s="17">
+        <v>400</v>
+      </c>
+      <c r="M12" s="17">
+        <v>10</v>
+      </c>
+      <c r="N12" s="17">
+        <v>87</v>
+      </c>
+      <c r="O12" s="17">
+        <v>0.8</v>
+      </c>
+      <c r="P12" s="17">
+        <v>3.4</v>
+      </c>
+      <c r="Q12" s="17">
+        <v>0.8</v>
+      </c>
+      <c r="R12" s="17">
+        <v>4.5</v>
+      </c>
+      <c r="S12" s="17">
+        <v>0.8</v>
+      </c>
+      <c r="T12" s="17">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U12" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B13" s="12">
+        <v>11</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>359</v>
+      </c>
+      <c r="D13" s="14">
+        <v>87</v>
+      </c>
+      <c r="E13" s="14">
+        <v>13.8</v>
+      </c>
+      <c r="F13" s="14">
+        <v>132</v>
+      </c>
+      <c r="G13" s="14">
+        <v>5.5</v>
+      </c>
+      <c r="H13" s="14">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I13" s="14">
+        <v>6</v>
+      </c>
+      <c r="J13" s="14">
+        <v>65</v>
+      </c>
+      <c r="K13" s="14">
+        <v>25</v>
+      </c>
+      <c r="L13" s="14">
+        <v>400</v>
+      </c>
+      <c r="M13" s="14">
+        <v>10</v>
+      </c>
+      <c r="N13" s="14">
+        <v>25</v>
+      </c>
+      <c r="O13" s="14">
+        <v>0.7</v>
+      </c>
+      <c r="P13" s="14">
+        <v>3.6</v>
+      </c>
+      <c r="Q13" s="14">
+        <v>0.9</v>
+      </c>
+      <c r="R13" s="14">
+        <v>4.5</v>
+      </c>
+      <c r="S13" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="T13" s="14">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U13" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B14" s="15">
+        <v>12</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>360</v>
+      </c>
+      <c r="D14" s="17">
+        <v>87</v>
+      </c>
+      <c r="E14" s="17">
+        <v>10</v>
+      </c>
+      <c r="F14" s="17">
+        <v>100</v>
+      </c>
+      <c r="G14" s="17">
+        <v>3.7</v>
+      </c>
+      <c r="H14" s="17">
+        <v>1.8</v>
+      </c>
+      <c r="I14" s="17">
+        <v>4.3</v>
+      </c>
+      <c r="J14" s="17">
+        <v>52</v>
+      </c>
+      <c r="K14" s="17">
+        <v>21</v>
+      </c>
+      <c r="L14" s="17">
+        <v>380</v>
+      </c>
+      <c r="M14" s="17">
+        <v>8</v>
+      </c>
+      <c r="N14" s="17">
+        <v>104</v>
+      </c>
+      <c r="O14" s="17">
+        <v>0.8</v>
+      </c>
+      <c r="P14" s="17">
+        <v>3.4</v>
+      </c>
+      <c r="Q14" s="17">
+        <v>0.8</v>
+      </c>
+      <c r="R14" s="17">
+        <v>4.5</v>
+      </c>
+      <c r="S14" s="17">
+        <v>0.8</v>
+      </c>
+      <c r="T14" s="17">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U14" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B15" s="12">
+        <v>13</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>361</v>
+      </c>
+      <c r="D15" s="14">
+        <v>87</v>
+      </c>
+      <c r="E15" s="14">
+        <v>11.1</v>
+      </c>
+      <c r="F15" s="14">
+        <v>109</v>
+      </c>
+      <c r="G15" s="14">
+        <v>4.7</v>
+      </c>
+      <c r="H15" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="I15" s="14">
+        <v>5</v>
+      </c>
+      <c r="J15" s="14">
+        <v>52</v>
+      </c>
+      <c r="K15" s="14">
+        <v>21</v>
+      </c>
+      <c r="L15" s="14">
+        <v>420</v>
+      </c>
+      <c r="M15" s="14">
+        <v>12</v>
+      </c>
+      <c r="N15" s="14">
+        <v>78</v>
+      </c>
+      <c r="O15" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="P15" s="14">
+        <v>3.4</v>
+      </c>
+      <c r="Q15" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="R15" s="14">
+        <v>4.5</v>
+      </c>
+      <c r="S15" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="T15" s="14">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U15" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B16" s="15">
+        <v>14</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>362</v>
+      </c>
+      <c r="D16" s="17">
+        <v>87</v>
+      </c>
+      <c r="E16" s="17">
+        <v>1.7</v>
+      </c>
+      <c r="F16" s="17">
+        <v>46</v>
+      </c>
+      <c r="G16" s="17">
+        <v>1.4</v>
+      </c>
+      <c r="H16" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="I16" s="17">
+        <v>1.3</v>
+      </c>
+      <c r="J16" s="17">
+        <v>14</v>
+      </c>
+      <c r="K16" s="17">
+        <v>0</v>
+      </c>
+      <c r="L16" s="17">
+        <v>0</v>
+      </c>
+      <c r="M16" s="17">
+        <v>0</v>
+      </c>
+      <c r="N16" s="17">
+        <v>287</v>
+      </c>
+      <c r="O16" s="17">
+        <v>1.3</v>
+      </c>
+      <c r="P16" s="17">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="17">
+        <v>0</v>
+      </c>
+      <c r="R16" s="17">
+        <v>5.3</v>
+      </c>
+      <c r="S16" s="17">
+        <v>0.4</v>
+      </c>
+      <c r="T16" s="17">
+        <v>1</v>
+      </c>
+      <c r="U16" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B17" s="12">
+        <v>15</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="D17" s="14">
+        <v>100</v>
+      </c>
+      <c r="E17" s="14">
+        <v>0</v>
+      </c>
+      <c r="F17" s="14">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14">
+        <v>0</v>
+      </c>
+      <c r="I17" s="14">
+        <v>0</v>
+      </c>
+      <c r="J17" s="14">
+        <v>0</v>
+      </c>
+      <c r="K17" s="14">
+        <v>0</v>
+      </c>
+      <c r="L17" s="14">
+        <v>0</v>
+      </c>
+      <c r="M17" s="14">
+        <v>0</v>
+      </c>
+      <c r="N17" s="14">
+        <v>0</v>
+      </c>
+      <c r="O17" s="14">
+        <v>3</v>
+      </c>
+      <c r="P17" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="14">
+        <v>0</v>
+      </c>
+      <c r="R17" s="14">
+        <v>0</v>
+      </c>
+      <c r="S17" s="14">
+        <v>390</v>
+      </c>
+      <c r="T17" s="14">
+        <v>600</v>
+      </c>
+      <c r="U17" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="15">
+        <v>16</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>364</v>
+      </c>
+      <c r="D18" s="17">
+        <v>87</v>
+      </c>
+      <c r="E18" s="17">
+        <v>11.8</v>
+      </c>
+      <c r="F18" s="17">
+        <v>104</v>
+      </c>
+      <c r="G18" s="17">
+        <v>3.8</v>
+      </c>
+      <c r="H18" s="17">
+        <v>1.8</v>
+      </c>
+      <c r="I18" s="17">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="J18" s="17">
+        <v>25</v>
+      </c>
+      <c r="K18" s="17">
+        <v>10</v>
+      </c>
+      <c r="L18" s="17">
+        <v>490</v>
+      </c>
+      <c r="M18" s="17">
+        <v>26</v>
+      </c>
+      <c r="N18" s="17">
+        <v>41</v>
+      </c>
+      <c r="O18" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="P18" s="17">
+        <v>3.5</v>
+      </c>
+      <c r="Q18" s="17">
+        <v>1.7</v>
+      </c>
+      <c r="R18" s="17">
+        <v>4.8</v>
+      </c>
+      <c r="S18" s="17">
+        <v>0.4</v>
+      </c>
+      <c r="T18" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="U18" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B19" s="12">
+        <v>17</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>365</v>
+      </c>
+      <c r="D19" s="14">
+        <v>87</v>
+      </c>
+      <c r="E19" s="14">
+        <v>11.1</v>
+      </c>
+      <c r="F19" s="14">
+        <v>100</v>
+      </c>
+      <c r="G19" s="14">
+        <v>3.7</v>
+      </c>
+      <c r="H19" s="14">
+        <v>1.7</v>
+      </c>
+      <c r="I19" s="14">
+        <v>4</v>
+      </c>
+      <c r="J19" s="14">
+        <v>25</v>
+      </c>
+      <c r="K19" s="14">
+        <v>10</v>
+      </c>
+      <c r="L19" s="14">
+        <v>450</v>
+      </c>
+      <c r="M19" s="14">
+        <v>22</v>
+      </c>
+      <c r="N19" s="14">
+        <v>71</v>
+      </c>
+      <c r="O19" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="P19" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="Q19" s="14">
+        <v>1.7</v>
+      </c>
+      <c r="R19" s="14">
+        <v>4.8</v>
+      </c>
+      <c r="S19" s="14">
+        <v>0.4</v>
+      </c>
+      <c r="T19" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="U19" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B20" s="15">
+        <v>18</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>366</v>
+      </c>
+      <c r="D20" s="17">
+        <v>87</v>
+      </c>
+      <c r="E20" s="17">
+        <v>12.2</v>
+      </c>
+      <c r="F20" s="17">
+        <v>117</v>
+      </c>
+      <c r="G20" s="17">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H20" s="17">
+        <v>2</v>
+      </c>
+      <c r="I20" s="17">
+        <v>4.5</v>
+      </c>
+      <c r="J20" s="17">
+        <v>25</v>
+      </c>
+      <c r="K20" s="17">
+        <v>10</v>
+      </c>
+      <c r="L20" s="17">
+        <v>517</v>
+      </c>
+      <c r="M20" s="17">
+        <v>28</v>
+      </c>
+      <c r="N20" s="17">
+        <v>37</v>
+      </c>
+      <c r="O20" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="P20" s="17">
+        <v>3.5</v>
+      </c>
+      <c r="Q20" s="17">
+        <v>1.7</v>
+      </c>
+      <c r="R20" s="17">
+        <v>4.8</v>
+      </c>
+      <c r="S20" s="17">
+        <v>0.4</v>
+      </c>
+      <c r="T20" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="U20" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B21" s="12">
+        <v>19</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>367</v>
+      </c>
+      <c r="D21" s="14">
+        <v>95</v>
+      </c>
+      <c r="E21" s="14">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="F21" s="14">
+        <v>530</v>
+      </c>
+      <c r="G21" s="14">
+        <v>29</v>
+      </c>
+      <c r="H21" s="14">
+        <v>8.1</v>
+      </c>
+      <c r="I21" s="14">
+        <v>13.9</v>
+      </c>
+      <c r="J21" s="14">
+        <v>104</v>
+      </c>
+      <c r="K21" s="14">
+        <v>15</v>
+      </c>
+      <c r="L21" s="14">
+        <v>0</v>
+      </c>
+      <c r="M21" s="14">
+        <v>0</v>
+      </c>
+      <c r="N21" s="14">
+        <v>0</v>
+      </c>
+      <c r="O21" s="14">
+        <v>100</v>
+      </c>
+      <c r="P21" s="14">
+        <v>45</v>
+      </c>
+      <c r="Q21" s="14">
+        <v>36</v>
+      </c>
+      <c r="R21" s="14">
+        <v>6</v>
+      </c>
+      <c r="S21" s="14">
+        <v>7</v>
+      </c>
+      <c r="T21" s="14">
+        <v>7.5</v>
+      </c>
+      <c r="U21" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B22" s="15">
+        <v>20</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>368</v>
+      </c>
+      <c r="D22" s="17">
+        <v>93</v>
+      </c>
+      <c r="E22" s="17">
+        <v>11</v>
+      </c>
+      <c r="F22" s="17">
+        <v>590</v>
+      </c>
+      <c r="G22" s="17">
+        <v>30</v>
+      </c>
+      <c r="H22" s="17">
+        <v>8.4</v>
+      </c>
+      <c r="I22" s="17">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="J22" s="17">
+        <v>79</v>
+      </c>
+      <c r="K22" s="17">
+        <v>12</v>
+      </c>
+      <c r="L22" s="17">
+        <v>0</v>
+      </c>
+      <c r="M22" s="17">
+        <v>0</v>
+      </c>
+      <c r="N22" s="17">
+        <v>0</v>
+      </c>
+      <c r="O22" s="17">
+        <v>80</v>
+      </c>
+      <c r="P22" s="17">
+        <v>37</v>
+      </c>
+      <c r="Q22" s="17">
+        <v>30</v>
+      </c>
+      <c r="R22" s="17">
+        <v>5</v>
+      </c>
+      <c r="S22" s="17">
+        <v>6</v>
+      </c>
+      <c r="T22" s="17">
+        <v>7</v>
+      </c>
+      <c r="U22" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B23" s="12">
+        <v>21</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>369</v>
+      </c>
+      <c r="D23" s="14">
+        <v>93</v>
+      </c>
+      <c r="E23" s="14">
+        <v>11.4</v>
+      </c>
+      <c r="F23" s="14">
+        <v>648</v>
+      </c>
+      <c r="G23" s="14">
+        <v>37</v>
+      </c>
+      <c r="H23" s="14">
+        <v>10.4</v>
+      </c>
+      <c r="I23" s="14">
+        <v>17.8</v>
+      </c>
+      <c r="J23" s="14">
+        <v>100</v>
+      </c>
+      <c r="K23" s="14">
+        <v>15</v>
+      </c>
+      <c r="L23" s="14">
+        <v>0</v>
+      </c>
+      <c r="M23" s="14">
+        <v>0</v>
+      </c>
+      <c r="N23" s="14">
+        <v>0</v>
+      </c>
+      <c r="O23" s="14">
+        <v>76</v>
+      </c>
+      <c r="P23" s="14">
+        <v>40</v>
+      </c>
+      <c r="Q23" s="14">
+        <v>30</v>
+      </c>
+      <c r="R23" s="14">
+        <v>10</v>
+      </c>
+      <c r="S23" s="14">
+        <v>7.2</v>
+      </c>
+      <c r="T23" s="14">
+        <v>7.4</v>
+      </c>
+      <c r="U23" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B24" s="15">
+        <v>22</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>370</v>
+      </c>
+      <c r="D24" s="17">
+        <v>90</v>
+      </c>
+      <c r="E24" s="17">
+        <v>6.67</v>
+      </c>
+      <c r="F24" s="17">
+        <v>193</v>
+      </c>
+      <c r="G24" s="17">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="H24" s="17">
+        <v>2.9</v>
+      </c>
+      <c r="I24" s="17">
+        <v>5.4</v>
+      </c>
+      <c r="J24" s="17">
+        <v>36</v>
+      </c>
+      <c r="K24" s="17">
+        <v>5</v>
+      </c>
+      <c r="L24" s="17">
+        <v>45</v>
+      </c>
+      <c r="M24" s="17">
+        <v>51</v>
+      </c>
+      <c r="N24" s="17">
+        <v>193</v>
+      </c>
+      <c r="O24" s="17">
+        <v>14</v>
+      </c>
+      <c r="P24" s="17">
+        <v>2.5</v>
+      </c>
+      <c r="Q24" s="17">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="R24" s="17">
+        <v>22</v>
+      </c>
+      <c r="S24" s="17">
+        <v>1.3</v>
+      </c>
+      <c r="T24" s="17">
+        <v>4.7</v>
+      </c>
+      <c r="U24" s="17">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B25" s="12">
+        <v>23</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>371</v>
+      </c>
+      <c r="D25" s="14">
+        <v>100</v>
+      </c>
+      <c r="E25" s="14">
+        <v>16.7</v>
+      </c>
+      <c r="F25" s="14">
+        <v>934</v>
+      </c>
+      <c r="G25" s="14">
+        <v>780</v>
+      </c>
+      <c r="H25" s="14">
+        <v>0</v>
+      </c>
+      <c r="I25" s="14">
+        <v>0</v>
+      </c>
+      <c r="J25" s="14">
+        <v>0</v>
+      </c>
+      <c r="K25" s="14">
+        <v>0</v>
+      </c>
+      <c r="L25" s="14">
+        <v>0</v>
+      </c>
+      <c r="M25" s="14">
+        <v>0</v>
+      </c>
+      <c r="N25" s="14">
+        <v>0</v>
+      </c>
+      <c r="O25" s="14">
+        <v>0</v>
+      </c>
+      <c r="P25" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="14">
+        <v>0</v>
+      </c>
+      <c r="R25" s="14">
+        <v>0</v>
+      </c>
+      <c r="S25" s="14">
+        <v>0</v>
+      </c>
+      <c r="T25" s="14">
+        <v>0</v>
+      </c>
+      <c r="U25" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="15">
+        <v>24</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>372</v>
+      </c>
+      <c r="D26" s="17">
+        <v>87</v>
+      </c>
+      <c r="E26" s="17">
+        <v>13.8</v>
+      </c>
+      <c r="F26" s="17">
+        <v>87</v>
+      </c>
+      <c r="G26" s="17">
+        <v>2.4</v>
+      </c>
+      <c r="H26" s="17">
+        <v>1.8</v>
+      </c>
+      <c r="I26" s="17">
+        <v>3.8</v>
+      </c>
+      <c r="J26" s="17">
+        <v>40</v>
+      </c>
+      <c r="K26" s="17">
+        <v>32</v>
+      </c>
+      <c r="L26" s="17">
+        <v>650</v>
+      </c>
+      <c r="M26" s="17">
+        <v>16.3</v>
+      </c>
+      <c r="N26" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="O26" s="17">
+        <v>2.5</v>
+      </c>
+      <c r="P26" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="Q26" s="17">
+        <v>3.3</v>
+      </c>
+      <c r="R26" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="S26" s="17">
+        <v>0.4</v>
+      </c>
+      <c r="T26" s="17">
+        <v>50</v>
+      </c>
+      <c r="U26" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>388</v>
+      </c>
+      <c r="B27" s="12">
+        <v>25</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>373</v>
+      </c>
+      <c r="D27" s="14">
+        <v>87</v>
+      </c>
+      <c r="E27" s="14">
+        <v>14.2</v>
+      </c>
+      <c r="F27" s="14">
+        <v>644</v>
+      </c>
+      <c r="G27" s="14">
+        <v>10.8</v>
+      </c>
+      <c r="H27" s="14">
+        <v>15.2</v>
+      </c>
+      <c r="I27" s="14">
+        <v>26.8</v>
+      </c>
+      <c r="J27" s="14">
+        <v>39</v>
+      </c>
+      <c r="K27" s="14">
+        <v>20</v>
+      </c>
+      <c r="L27" s="14">
+        <v>123</v>
+      </c>
+      <c r="M27" s="14">
+        <v>6</v>
+      </c>
+      <c r="N27" s="14">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="O27" s="14">
+        <v>1.6</v>
+      </c>
+      <c r="P27" s="14">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="14">
+        <v>1.9</v>
+      </c>
+      <c r="R27" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="S27" s="14">
+        <v>2</v>
+      </c>
+      <c r="T27" s="14">
+        <v>5</v>
+      </c>
+      <c r="U27" s="14">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B28" s="15">
+        <v>26</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>374</v>
+      </c>
+      <c r="D28" s="17">
+        <v>100</v>
+      </c>
+      <c r="E28" s="17">
+        <v>0</v>
+      </c>
+      <c r="F28" s="17">
+        <v>0</v>
+      </c>
+      <c r="G28" s="17">
+        <v>0</v>
+      </c>
+      <c r="H28" s="17">
+        <v>0</v>
+      </c>
+      <c r="I28" s="17">
+        <v>0</v>
+      </c>
+      <c r="J28" s="17">
+        <v>0</v>
+      </c>
+      <c r="K28" s="17">
+        <v>0</v>
+      </c>
+      <c r="L28" s="17">
+        <v>0</v>
+      </c>
+      <c r="M28" s="17">
+        <v>0</v>
+      </c>
+      <c r="N28" s="17">
+        <v>0</v>
+      </c>
+      <c r="O28" s="17">
+        <v>160</v>
+      </c>
+      <c r="P28" s="17">
+        <v>210</v>
+      </c>
+      <c r="Q28" s="17">
+        <v>190</v>
+      </c>
+      <c r="R28" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="S28" s="17">
+        <v>0.6</v>
+      </c>
+      <c r="T28" s="17">
+        <v>0</v>
+      </c>
+      <c r="U28" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B29" s="12">
+        <v>27</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>375</v>
+      </c>
+      <c r="D29" s="14">
+        <v>100</v>
+      </c>
+      <c r="E29" s="14">
+        <v>0</v>
+      </c>
+      <c r="F29" s="14">
+        <v>0</v>
+      </c>
+      <c r="G29" s="14">
+        <v>0</v>
+      </c>
+      <c r="H29" s="14">
+        <v>0</v>
+      </c>
+      <c r="I29" s="14">
+        <v>0</v>
+      </c>
+      <c r="J29" s="14">
+        <v>0</v>
+      </c>
+      <c r="K29" s="14">
+        <v>0</v>
+      </c>
+      <c r="L29" s="14">
+        <v>0</v>
+      </c>
+      <c r="M29" s="14">
+        <v>0</v>
+      </c>
+      <c r="N29" s="14">
+        <v>0</v>
+      </c>
+      <c r="O29" s="14">
+        <v>0</v>
+      </c>
+      <c r="P29" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="14">
+        <v>0</v>
+      </c>
+      <c r="R29" s="14">
+        <v>0</v>
+      </c>
+      <c r="S29" s="14">
+        <v>270</v>
+      </c>
+      <c r="T29" s="14">
+        <v>0</v>
+      </c>
+      <c r="U29" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" s="15">
+        <v>28</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>376</v>
+      </c>
+      <c r="D30" s="17">
+        <v>90</v>
+      </c>
+      <c r="E30" s="17">
+        <v>14.4</v>
+      </c>
+      <c r="F30" s="17">
+        <v>790</v>
+      </c>
+      <c r="G30" s="17">
+        <v>64</v>
+      </c>
+      <c r="H30" s="17">
+        <v>18</v>
+      </c>
+      <c r="I30" s="17">
+        <v>31</v>
+      </c>
+      <c r="J30" s="17">
+        <v>40</v>
+      </c>
+      <c r="K30" s="17">
+        <v>0.4</v>
+      </c>
+      <c r="L30" s="17">
+        <v>0</v>
+      </c>
+      <c r="M30" s="17">
+        <v>0</v>
+      </c>
+      <c r="N30" s="17">
+        <v>0</v>
+      </c>
+      <c r="O30" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="P30" s="17">
+        <v>4</v>
+      </c>
+      <c r="Q30" s="17">
+        <v>2</v>
+      </c>
+      <c r="R30" s="17">
+        <v>1</v>
+      </c>
+      <c r="S30" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="T30" s="17">
+        <v>2.1</v>
+      </c>
+      <c r="U30" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31" s="12">
+        <v>29</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>377</v>
+      </c>
+      <c r="D31" s="14">
+        <v>90</v>
+      </c>
+      <c r="E31" s="14">
+        <v>7.6</v>
+      </c>
+      <c r="F31" s="14">
+        <v>348</v>
+      </c>
+      <c r="G31" s="14">
+        <v>19.5</v>
+      </c>
+      <c r="H31" s="14">
+        <v>7.1</v>
+      </c>
+      <c r="I31" s="14">
+        <v>15.9</v>
+      </c>
+      <c r="J31" s="14">
+        <v>23</v>
+      </c>
+      <c r="K31" s="14">
+        <v>7</v>
+      </c>
+      <c r="L31" s="14">
+        <v>40</v>
+      </c>
+      <c r="M31" s="14">
+        <v>78</v>
+      </c>
+      <c r="N31" s="14">
+        <v>120</v>
+      </c>
+      <c r="O31" s="14">
+        <v>5</v>
+      </c>
+      <c r="P31" s="14">
+        <v>10</v>
+      </c>
+      <c r="Q31" s="14">
+        <v>2.8</v>
+      </c>
+      <c r="R31" s="14">
+        <v>14</v>
+      </c>
+      <c r="S31" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="T31" s="14">
+        <v>0.13</v>
+      </c>
+      <c r="U31" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>317</v>
+      </c>
+      <c r="B32" s="15">
+        <v>30</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>378</v>
+      </c>
+      <c r="D32" s="17">
+        <v>87</v>
+      </c>
+      <c r="E32" s="17">
+        <v>11.2</v>
+      </c>
+      <c r="F32" s="17">
+        <v>96</v>
+      </c>
+      <c r="G32" s="17">
+        <v>3.9</v>
+      </c>
+      <c r="H32" s="17">
+        <v>1.7</v>
+      </c>
+      <c r="I32" s="17">
+        <v>4.2</v>
+      </c>
+      <c r="J32" s="17">
+        <v>16</v>
+      </c>
+      <c r="K32" s="17">
+        <v>7</v>
+      </c>
+      <c r="L32" s="17">
+        <v>568</v>
+      </c>
+      <c r="M32" s="17">
+        <v>55</v>
+      </c>
+      <c r="N32" s="17">
+        <v>26</v>
+      </c>
+      <c r="O32" s="17">
+        <v>0.6</v>
+      </c>
+      <c r="P32" s="17">
+        <v>3.3</v>
+      </c>
+      <c r="Q32" s="17">
+        <v>1.7</v>
+      </c>
+      <c r="R32" s="17">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="S32" s="17">
+        <v>0.2</v>
+      </c>
+      <c r="T32" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="U32" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="12">
+        <v>31</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>379</v>
+      </c>
+      <c r="D33" s="14">
+        <v>89</v>
+      </c>
+      <c r="E33" s="14">
+        <v>13</v>
+      </c>
+      <c r="F33" s="14">
+        <v>115</v>
+      </c>
+      <c r="G33" s="14">
+        <v>4.2</v>
+      </c>
+      <c r="H33" s="14">
+        <v>2.8</v>
+      </c>
+      <c r="I33" s="14">
+        <v>2.1</v>
+      </c>
+      <c r="J33" s="14">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="K33" s="14">
+        <v>8</v>
+      </c>
+      <c r="L33" s="14">
+        <v>550</v>
+      </c>
+      <c r="M33" s="14">
+        <v>60</v>
+      </c>
+      <c r="N33" s="14">
+        <v>21</v>
+      </c>
+      <c r="O33" s="14">
+        <v>0.6</v>
+      </c>
+      <c r="P33" s="14">
+        <v>3.3</v>
+      </c>
+      <c r="Q33" s="14">
+        <v>0</v>
+      </c>
+      <c r="R33" s="14">
+        <v>1.7</v>
+      </c>
+      <c r="S33" s="14">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="T33" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="U33" s="14">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B34" s="15">
+        <v>32</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>380</v>
+      </c>
+      <c r="D34" s="17">
+        <v>99</v>
+      </c>
+      <c r="E34" s="17">
+        <v>34</v>
+      </c>
+      <c r="F34" s="17">
+        <v>0</v>
+      </c>
+      <c r="G34" s="17">
+        <v>0</v>
+      </c>
+      <c r="H34" s="17">
+        <v>0</v>
+      </c>
+      <c r="I34" s="17">
+        <v>0</v>
+      </c>
+      <c r="J34" s="17">
+        <v>990</v>
+      </c>
+      <c r="K34" s="17">
+        <v>40</v>
+      </c>
+      <c r="L34" s="17">
+        <v>0</v>
+      </c>
+      <c r="M34" s="17">
+        <v>0</v>
+      </c>
+      <c r="N34" s="17">
+        <v>0</v>
+      </c>
+      <c r="O34" s="17">
+        <v>0</v>
+      </c>
+      <c r="P34" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="17">
+        <v>0</v>
+      </c>
+      <c r="R34" s="17">
+        <v>0</v>
+      </c>
+      <c r="S34" s="17">
+        <v>0</v>
+      </c>
+      <c r="T34" s="17">
+        <v>0</v>
+      </c>
+      <c r="U34" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" s="12">
+        <v>33</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>381</v>
+      </c>
+      <c r="D35" s="14">
+        <v>87</v>
+      </c>
+      <c r="E35" s="14">
+        <v>9.1</v>
+      </c>
+      <c r="F35" s="14">
+        <v>440</v>
+      </c>
+      <c r="G35" s="14">
+        <v>27.5</v>
+      </c>
+      <c r="H35" s="14">
+        <v>6.4</v>
+      </c>
+      <c r="I35" s="14">
+        <v>13.1</v>
+      </c>
+      <c r="J35" s="14">
+        <v>13</v>
+      </c>
+      <c r="K35" s="14">
+        <v>6</v>
+      </c>
+      <c r="L35" s="14">
+        <v>64</v>
+      </c>
+      <c r="M35" s="14">
+        <v>93</v>
+      </c>
+      <c r="N35" s="14">
+        <v>60</v>
+      </c>
+      <c r="O35" s="14">
+        <v>2</v>
+      </c>
+      <c r="P35" s="14">
+        <v>6</v>
+      </c>
+      <c r="Q35" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="R35" s="14">
+        <v>20</v>
+      </c>
+      <c r="S35" s="14">
+        <v>0.02</v>
+      </c>
+      <c r="T35" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="U35" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B36" s="15">
+        <v>34</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>382</v>
+      </c>
+      <c r="D36" s="17">
+        <v>99</v>
+      </c>
+      <c r="E36" s="17">
+        <v>36</v>
+      </c>
+      <c r="F36" s="17">
+        <v>0</v>
+      </c>
+      <c r="G36" s="17">
+        <v>0</v>
+      </c>
+      <c r="H36" s="17">
+        <v>0</v>
+      </c>
+      <c r="I36" s="17">
+        <v>0</v>
+      </c>
+      <c r="J36" s="17">
+        <v>990</v>
+      </c>
+      <c r="K36" s="17">
+        <v>524</v>
+      </c>
+      <c r="L36" s="17">
+        <v>0</v>
+      </c>
+      <c r="M36" s="17">
+        <v>0</v>
+      </c>
+      <c r="N36" s="17">
+        <v>0</v>
+      </c>
+      <c r="O36" s="17">
+        <v>0</v>
+      </c>
+      <c r="P36" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="17">
+        <v>0</v>
+      </c>
+      <c r="R36" s="17">
+        <v>0</v>
+      </c>
+      <c r="S36" s="17">
+        <v>0</v>
+      </c>
+      <c r="T36" s="17">
+        <v>0</v>
+      </c>
+      <c r="U36" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>17</v>
+      </c>
+      <c r="B37" s="12">
+        <v>35</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="D37" s="14">
+        <v>87</v>
+      </c>
+      <c r="E37" s="14">
+        <v>12.8</v>
+      </c>
+      <c r="F37" s="14">
+        <v>113</v>
+      </c>
+      <c r="G37" s="14">
+        <v>3.1</v>
+      </c>
+      <c r="H37" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="I37" s="14">
+        <v>4.2</v>
+      </c>
+      <c r="J37" s="14">
+        <v>19</v>
+      </c>
+      <c r="K37" s="14">
+        <v>8</v>
+      </c>
+      <c r="L37" s="14">
+        <v>580</v>
+      </c>
+      <c r="M37" s="14">
+        <v>78</v>
+      </c>
+      <c r="N37" s="14">
+        <v>21</v>
+      </c>
+      <c r="O37" s="14">
+        <v>0.6</v>
+      </c>
+      <c r="P37" s="14">
+        <v>3.3</v>
+      </c>
+      <c r="Q37" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="R37" s="14">
+        <v>4</v>
+      </c>
+      <c r="S37" s="14">
+        <v>0.4</v>
+      </c>
+      <c r="T37" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="U37" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>49</v>
+      </c>
+      <c r="B38" s="15">
+        <v>36</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>384</v>
+      </c>
+      <c r="D38" s="17">
+        <v>87</v>
+      </c>
+      <c r="E38" s="17">
+        <v>12.2</v>
+      </c>
+      <c r="F38" s="17">
+        <v>169</v>
+      </c>
+      <c r="G38" s="17">
+        <v>5.9</v>
+      </c>
+      <c r="H38" s="17">
+        <v>2.8</v>
+      </c>
+      <c r="I38" s="17">
+        <v>6.3</v>
+      </c>
+      <c r="J38" s="17">
+        <v>44</v>
+      </c>
+      <c r="K38" s="17">
+        <v>15</v>
+      </c>
+      <c r="L38" s="17">
+        <v>419</v>
+      </c>
+      <c r="M38" s="17">
+        <v>60</v>
+      </c>
+      <c r="N38" s="17">
+        <v>26</v>
+      </c>
+      <c r="O38" s="17">
+        <v>0.8</v>
+      </c>
+      <c r="P38" s="17">
+        <v>4</v>
+      </c>
+      <c r="Q38" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="R38" s="17">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="S38" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="T38" s="17">
+        <v>1.4</v>
+      </c>
+      <c r="U38" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B39" s="12">
+        <v>37</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>385</v>
+      </c>
+      <c r="D39" s="14">
+        <v>87</v>
+      </c>
+      <c r="E39" s="14">
+        <v>9.4</v>
+      </c>
+      <c r="F39" s="14">
+        <v>157</v>
+      </c>
+      <c r="G39" s="14">
+        <v>5.7</v>
+      </c>
+      <c r="H39" s="14">
+        <v>2.6</v>
+      </c>
+      <c r="I39" s="14">
+        <v>5.8</v>
+      </c>
+      <c r="J39" s="14">
+        <v>39</v>
+      </c>
+      <c r="K39" s="14">
+        <v>12</v>
+      </c>
+      <c r="L39" s="14">
+        <v>270</v>
+      </c>
+      <c r="M39" s="14">
+        <v>66</v>
+      </c>
+      <c r="N39" s="14">
+        <v>65</v>
+      </c>
+      <c r="O39" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="P39" s="14">
+        <v>4</v>
+      </c>
+      <c r="Q39" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="R39" s="14">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="S39" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="T39" s="14">
+        <v>1.4</v>
+      </c>
+      <c r="U39" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40" s="15">
+        <v>38</v>
+      </c>
+      <c r="C40" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="D40" s="17">
+        <v>87</v>
+      </c>
+      <c r="E40" s="17">
+        <v>6.8</v>
+      </c>
+      <c r="F40" s="17">
+        <v>157</v>
+      </c>
+      <c r="G40" s="17">
+        <v>6.4</v>
+      </c>
+      <c r="H40" s="17">
+        <v>2.5</v>
+      </c>
+      <c r="I40" s="17">
+        <v>5.8</v>
+      </c>
+      <c r="J40" s="17">
+        <v>45</v>
+      </c>
+      <c r="K40" s="17">
+        <v>12</v>
+      </c>
+      <c r="L40" s="17">
+        <v>135</v>
+      </c>
+      <c r="M40" s="17">
+        <v>55</v>
+      </c>
+      <c r="N40" s="17">
+        <v>100</v>
+      </c>
+      <c r="O40" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="P40" s="17">
+        <v>11.5</v>
+      </c>
+      <c r="Q40" s="17">
+        <v>6</v>
+      </c>
+      <c r="R40" s="17">
+        <v>9.9</v>
+      </c>
+      <c r="S40" s="17">
+        <v>0.8</v>
+      </c>
+      <c r="T40" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="U40" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="12">
+        <v>39</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>387</v>
+      </c>
+      <c r="D41" s="14">
+        <v>87</v>
+      </c>
+      <c r="E41" s="14">
+        <v>11</v>
+      </c>
+      <c r="F41" s="14">
+        <v>226</v>
+      </c>
+      <c r="G41" s="14">
+        <v>15.8</v>
+      </c>
+      <c r="H41" s="14">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I41" s="14">
+        <v>5.6</v>
+      </c>
+      <c r="J41" s="14">
+        <v>13</v>
+      </c>
+      <c r="K41" s="14">
+        <v>2.7</v>
+      </c>
+      <c r="L41" s="14">
+        <v>416</v>
+      </c>
+      <c r="M41" s="14">
+        <v>56</v>
+      </c>
+      <c r="N41" s="14">
+        <v>61</v>
+      </c>
+      <c r="O41" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="P41" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="Q41" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="R41" s="14">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="S41" s="14">
+        <v>0.4</v>
+      </c>
+      <c r="T41" s="14">
+        <v>0.6</v>
+      </c>
+      <c r="U41" s="14">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/prod_parameters/FeedMgmt.xlsx
+++ b/data/prod_parameters/FeedMgmt.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="395">
   <si>
     <t>f_feed</t>
   </si>
@@ -1217,6 +1217,9 @@
   </si>
   <si>
     <t>Percent dry matter in feed as fed</t>
+  </si>
+  <si>
+    <t>Borde denna vara 100%? Vad är den tröskade majsarealen?</t>
   </si>
 </sst>
 </file>
@@ -1693,7 +1696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O193"/>
+  <dimension ref="A1:O195"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="7" width="20.28515625" customWidth="1"/>
@@ -1795,7 +1798,7 @@
         <v>32</v>
       </c>
       <c r="K4" s="22">
-        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F4,'feed pars'!B$6:B$42,0))</f>
+        <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F4,'feed pars'!B$6:B$43,0))</f>
         <v>1</v>
       </c>
     </row>
@@ -1810,7 +1813,7 @@
         <v>32</v>
       </c>
       <c r="K5" s="22">
-        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F5,'feed pars'!B$6:B$42,0))</f>
+        <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F5,'feed pars'!B$6:B$43,0))</f>
         <v>1</v>
       </c>
     </row>
@@ -1825,7 +1828,7 @@
         <v>32</v>
       </c>
       <c r="K6" s="22">
-        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F6,'feed pars'!B$6:B$42,0))</f>
+        <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F6,'feed pars'!B$6:B$43,0))</f>
         <v>1</v>
       </c>
     </row>
@@ -1840,7 +1843,7 @@
         <v>32</v>
       </c>
       <c r="K7" s="22">
-        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F7,'feed pars'!B$6:B$42,0))</f>
+        <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F7,'feed pars'!B$6:B$43,0))</f>
         <v>1</v>
       </c>
     </row>
@@ -1855,7 +1858,7 @@
         <v>32</v>
       </c>
       <c r="K8" s="22">
-        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F8,'feed pars'!B$6:B$42,0))</f>
+        <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F8,'feed pars'!B$6:B$43,0))</f>
         <v>1</v>
       </c>
     </row>
@@ -1870,7 +1873,7 @@
         <v>32</v>
       </c>
       <c r="K9" s="22">
-        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F9,'feed pars'!B$6:B$42,0))</f>
+        <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F9,'feed pars'!B$6:B$43,0))</f>
         <v>1</v>
       </c>
     </row>
@@ -1885,7 +1888,7 @@
         <v>32</v>
       </c>
       <c r="K10" s="22">
-        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F10,'feed pars'!B$6:B$42,0))</f>
+        <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F10,'feed pars'!B$6:B$43,0))</f>
         <v>1.1494252873563218</v>
       </c>
     </row>
@@ -1900,7 +1903,7 @@
         <v>32</v>
       </c>
       <c r="K11" s="22">
-        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F11,'feed pars'!B$6:B$42,0))</f>
+        <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F11,'feed pars'!B$6:B$43,0))</f>
         <v>1.1494252873563218</v>
       </c>
     </row>
@@ -1915,7 +1918,7 @@
         <v>32</v>
       </c>
       <c r="K12" s="22">
-        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F12,'feed pars'!B$6:B$42,0))</f>
+        <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F12,'feed pars'!B$6:B$43,0))</f>
         <v>1.1627906976744187</v>
       </c>
     </row>
@@ -1930,7 +1933,7 @@
         <v>32</v>
       </c>
       <c r="K13" s="22">
-        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F13,'feed pars'!B$6:B$42,0))</f>
+        <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F13,'feed pars'!B$6:B$43,0))</f>
         <v>1.1494252873563218</v>
       </c>
     </row>
@@ -1945,7 +1948,7 @@
         <v>32</v>
       </c>
       <c r="K14" s="22">
-        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F14,'feed pars'!B$6:B$42,0))</f>
+        <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F14,'feed pars'!B$6:B$43,0))</f>
         <v>1.1494252873563218</v>
       </c>
     </row>
@@ -1960,7 +1963,7 @@
         <v>32</v>
       </c>
       <c r="K15" s="22">
-        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F15,'feed pars'!B$6:B$42,0))</f>
+        <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F15,'feed pars'!B$6:B$43,0))</f>
         <v>1.4814814814814814</v>
       </c>
     </row>
@@ -1975,7 +1978,7 @@
         <v>32</v>
       </c>
       <c r="K16" s="22">
-        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F16,'feed pars'!B$6:B$42,0))</f>
+        <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F16,'feed pars'!B$6:B$43,0))</f>
         <v>1.1494252873563218</v>
       </c>
     </row>
@@ -1990,7 +1993,7 @@
         <v>32</v>
       </c>
       <c r="K17" s="22">
-        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F17,'feed pars'!B$6:B$42,0))</f>
+        <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F17,'feed pars'!B$6:B$43,0))</f>
         <v>1.1520737327188941</v>
       </c>
     </row>
@@ -2005,7 +2008,7 @@
         <v>32</v>
       </c>
       <c r="K18" s="22">
-        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F18,'feed pars'!B$6:B$42,0))</f>
+        <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F18,'feed pars'!B$6:B$43,0))</f>
         <v>1.0810810810810809</v>
       </c>
     </row>
@@ -2020,7 +2023,7 @@
         <v>32</v>
       </c>
       <c r="K19" s="22">
-        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F19,'feed pars'!B$6:B$42,0))</f>
+        <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F19,'feed pars'!B$6:B$43,0))</f>
         <v>1.0869565217391304</v>
       </c>
     </row>
@@ -2037,7 +2040,7 @@
         <v>32</v>
       </c>
       <c r="K20" s="20">
-        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F20,'feed pars'!B$6:B$42,0))*1/0.38</f>
+        <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F20,'feed pars'!B$6:B$43,0))*1/0.38</f>
         <v>2.6315789473684212</v>
       </c>
     </row>
@@ -2071,7 +2074,7 @@
         <v>32</v>
       </c>
       <c r="K22" s="22">
-        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F22,'feed pars'!B$6:B$42,0))</f>
+        <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F22,'feed pars'!B$6:B$43,0))</f>
         <v>1.1764705882352942</v>
       </c>
     </row>
@@ -2086,7 +2089,7 @@
         <v>32</v>
       </c>
       <c r="K23" s="22">
-        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F23,'feed pars'!B$6:B$42,0))</f>
+        <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F23,'feed pars'!B$6:B$43,0))</f>
         <v>1.1494252873563218</v>
       </c>
     </row>
@@ -2101,7 +2104,7 @@
         <v>32</v>
       </c>
       <c r="K24" s="22">
-        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F24,'feed pars'!B$6:B$42,0))</f>
+        <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F24,'feed pars'!B$6:B$43,0))</f>
         <v>1.1428571428571428</v>
       </c>
     </row>
@@ -2116,7 +2119,7 @@
         <v>32</v>
       </c>
       <c r="K25" s="22">
-        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F25,'feed pars'!B$6:B$42,0))</f>
+        <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F25,'feed pars'!B$6:B$43,0))</f>
         <v>1.1494252873563218</v>
       </c>
     </row>
@@ -2131,7 +2134,7 @@
         <v>32</v>
       </c>
       <c r="K26" s="22">
-        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F26,'feed pars'!B$6:B$42,0))</f>
+        <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F26,'feed pars'!B$6:B$43,0))</f>
         <v>1.1173184357541899</v>
       </c>
     </row>
@@ -2146,7 +2149,7 @@
         <v>32</v>
       </c>
       <c r="K27" s="22">
-        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F27,'feed pars'!B$6:B$42,0))</f>
+        <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F27,'feed pars'!B$6:B$43,0))</f>
         <v>1.0989010989010988</v>
       </c>
     </row>
@@ -2161,7 +2164,7 @@
         <v>32</v>
       </c>
       <c r="K28" s="22">
-        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F28,'feed pars'!B$6:B$42,0))</f>
+        <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F28,'feed pars'!B$6:B$43,0))</f>
         <v>1.0989010989010988</v>
       </c>
     </row>
@@ -2176,7 +2179,7 @@
         <v>32</v>
       </c>
       <c r="K29" s="22">
-        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F29,'feed pars'!B$6:B$42,0))</f>
+        <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F29,'feed pars'!B$6:B$43,0))</f>
         <v>1.1111111111111112</v>
       </c>
     </row>
@@ -2191,7 +2194,7 @@
         <v>32</v>
       </c>
       <c r="K30" s="22">
-        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F30,'feed pars'!B$6:B$42,0))</f>
+        <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F30,'feed pars'!B$6:B$43,0))</f>
         <v>1.1494252873563218</v>
       </c>
     </row>
@@ -2206,7 +2209,7 @@
         <v>32</v>
       </c>
       <c r="K31" s="22">
-        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F31,'feed pars'!B$6:B$42,0))</f>
+        <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F31,'feed pars'!B$6:B$43,0))</f>
         <v>1.1363636363636365</v>
       </c>
     </row>
@@ -2236,7 +2239,7 @@
         <v>32</v>
       </c>
       <c r="K33" s="22">
-        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F33,'feed pars'!B$6:B$42,0))</f>
+        <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F33,'feed pars'!B$6:B$43,0))</f>
         <v>9.0909090909090917</v>
       </c>
     </row>
@@ -2266,7 +2269,7 @@
         <v>32</v>
       </c>
       <c r="K35" s="22">
-        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F35,'feed pars'!B$6:B$42,0))</f>
+        <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F35,'feed pars'!B$6:B$43,0))</f>
         <v>1.3245033112582782</v>
       </c>
     </row>
@@ -2281,7 +2284,7 @@
         <v>32</v>
       </c>
       <c r="K36" s="22">
-        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F36,'feed pars'!B$6:B$42,0))</f>
+        <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F36,'feed pars'!B$6:B$43,0))</f>
         <v>1.1173184357541899</v>
       </c>
     </row>
@@ -2296,7 +2299,7 @@
         <v>32</v>
       </c>
       <c r="K37" s="22">
-        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F37,'feed pars'!B$6:B$42,0))</f>
+        <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F37,'feed pars'!B$6:B$43,0))</f>
         <v>16</v>
       </c>
     </row>
@@ -2326,7 +2329,7 @@
         <v>32</v>
       </c>
       <c r="K39" s="22">
-        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F39,'feed pars'!B$6:B$42,0))</f>
+        <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F39,'feed pars'!B$6:B$43,0))</f>
         <v>1.0989010989010988</v>
       </c>
     </row>
@@ -2341,7 +2344,7 @@
         <v>32</v>
       </c>
       <c r="K40" s="22">
-        <f>1/INDEX('feed pars'!C$6:C$42/100,MATCH(F40,'feed pars'!B$6:B$42,0))</f>
+        <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F40,'feed pars'!B$6:B$43,0))</f>
         <v>1.0869565217391304</v>
       </c>
     </row>
@@ -2509,49 +2512,39 @@
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
+      <c r="H52" t="s">
+        <v>40</v>
+      </c>
+      <c r="J52" t="s">
+        <v>31</v>
+      </c>
+      <c r="K52" s="3">
+        <v>50</v>
+      </c>
+      <c r="L52" t="s">
+        <v>28</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
-      <c r="K52" s="2"/>
-      <c r="L52" s="2"/>
-      <c r="M52" s="2"/>
-      <c r="N52" s="2"/>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>24</v>
-      </c>
-      <c r="B53" t="s">
-        <v>326</v>
-      </c>
-      <c r="E53" t="s">
-        <v>327</v>
-      </c>
-      <c r="G53" t="s">
-        <v>334</v>
-      </c>
-      <c r="H53" t="s">
-        <v>33</v>
-      </c>
-      <c r="J53" t="s">
-        <v>335</v>
-      </c>
-      <c r="K53" s="3">
-        <v>5</v>
-      </c>
-      <c r="L53" t="s">
-        <v>28</v>
-      </c>
-      <c r="M53" s="3"/>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2"/>
+      <c r="L53" s="2"/>
+      <c r="M53" s="2"/>
+      <c r="N53" s="2"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
@@ -2561,7 +2554,7 @@
         <v>326</v>
       </c>
       <c r="E54" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G54" t="s">
         <v>334</v>
@@ -2588,7 +2581,7 @@
         <v>326</v>
       </c>
       <c r="E55" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G55" t="s">
         <v>334</v>
@@ -2600,7 +2593,7 @@
         <v>335</v>
       </c>
       <c r="K55" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L55" t="s">
         <v>28</v>
@@ -2615,7 +2608,7 @@
         <v>326</v>
       </c>
       <c r="E56" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G56" t="s">
         <v>334</v>
@@ -2627,7 +2620,7 @@
         <v>335</v>
       </c>
       <c r="K56" s="3">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L56" t="s">
         <v>28</v>
@@ -2642,7 +2635,7 @@
         <v>326</v>
       </c>
       <c r="E57" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G57" t="s">
         <v>334</v>
@@ -2669,7 +2662,7 @@
         <v>326</v>
       </c>
       <c r="E58" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G58" t="s">
         <v>334</v>
@@ -2681,7 +2674,7 @@
         <v>335</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L58" t="s">
         <v>28</v>
@@ -2693,10 +2686,10 @@
         <v>24</v>
       </c>
       <c r="B59" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="E59" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="G59" t="s">
         <v>334</v>
@@ -2708,7 +2701,7 @@
         <v>335</v>
       </c>
       <c r="K59" s="3">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L59" t="s">
         <v>28</v>
@@ -2723,7 +2716,7 @@
         <v>333</v>
       </c>
       <c r="E60" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G60" t="s">
         <v>334</v>
@@ -2750,7 +2743,7 @@
         <v>333</v>
       </c>
       <c r="E61" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G61" t="s">
         <v>334</v>
@@ -2762,7 +2755,7 @@
         <v>335</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L61" t="s">
         <v>28</v>
@@ -2777,7 +2770,7 @@
         <v>333</v>
       </c>
       <c r="E62" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G62" t="s">
         <v>334</v>
@@ -2789,7 +2782,7 @@
         <v>335</v>
       </c>
       <c r="K62" s="3">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L62" t="s">
         <v>28</v>
@@ -2804,7 +2797,7 @@
         <v>333</v>
       </c>
       <c r="E63" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G63" t="s">
         <v>334</v>
@@ -2831,7 +2824,7 @@
         <v>333</v>
       </c>
       <c r="E64" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G64" t="s">
         <v>334</v>
@@ -2851,7 +2844,30 @@
       <c r="M64" s="3"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K65" s="3"/>
+      <c r="A65" t="s">
+        <v>24</v>
+      </c>
+      <c r="B65" t="s">
+        <v>333</v>
+      </c>
+      <c r="E65" t="s">
+        <v>332</v>
+      </c>
+      <c r="G65" t="s">
+        <v>334</v>
+      </c>
+      <c r="H65" t="s">
+        <v>33</v>
+      </c>
+      <c r="J65" t="s">
+        <v>335</v>
+      </c>
+      <c r="K65" s="3">
+        <v>90</v>
+      </c>
+      <c r="L65" t="s">
+        <v>28</v>
+      </c>
       <c r="M65" s="3"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
@@ -2863,68 +2879,56 @@
       <c r="M67" s="3"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
+      <c r="K68" s="3"/>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B68" s="1"/>
-      <c r="C68" s="1"/>
-      <c r="D68" s="1"/>
-      <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="2"/>
-      <c r="I68" s="2"/>
-      <c r="J68" s="2"/>
-      <c r="K68" s="2"/>
-      <c r="L68" s="2"/>
-      <c r="M68" s="2" t="s">
+      <c r="B69" s="1"/>
+      <c r="C69" s="1"/>
+      <c r="D69" s="1"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
+      <c r="I69" s="2"/>
+      <c r="J69" s="2"/>
+      <c r="K69" s="2"/>
+      <c r="L69" s="2"/>
+      <c r="M69" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="N68" s="2"/>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F69" t="s">
-        <v>310</v>
-      </c>
-      <c r="J69" t="s">
-        <v>390</v>
-      </c>
-      <c r="K69" s="26">
-        <f>INDEX('feed pars'!C$6:C$42,MATCH(F69,'feed pars'!B$6:B$42,0))</f>
-        <v>100</v>
-      </c>
-      <c r="L69" t="s">
-        <v>28</v>
-      </c>
-      <c r="M69" s="29" t="s">
-        <v>393</v>
-      </c>
+      <c r="N69" s="2"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F70" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="J70" t="s">
         <v>390</v>
       </c>
       <c r="K70" s="26">
-        <f>INDEX('feed pars'!C$6:C$42,MATCH(F70,'feed pars'!B$6:B$42,0))</f>
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F70,'feed pars'!B$6:B$43,0))</f>
         <v>100</v>
       </c>
       <c r="L70" t="s">
         <v>28</v>
       </c>
-      <c r="M70" s="3"/>
+      <c r="M70" s="29" t="s">
+        <v>393</v>
+      </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F71" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J71" t="s">
         <v>390</v>
       </c>
       <c r="K71" s="26">
-        <f>INDEX('feed pars'!C$6:C$42,MATCH(F71,'feed pars'!B$6:B$42,0))</f>
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F71,'feed pars'!B$6:B$43,0))</f>
         <v>100</v>
       </c>
       <c r="L71" t="s">
@@ -2934,13 +2938,13 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F72" t="s">
-        <v>2</v>
+        <v>312</v>
       </c>
       <c r="J72" t="s">
         <v>390</v>
       </c>
       <c r="K72" s="26">
-        <f>INDEX('feed pars'!C$6:C$42,MATCH(F72,'feed pars'!B$6:B$42,0))</f>
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F72,'feed pars'!B$6:B$43,0))</f>
         <v>100</v>
       </c>
       <c r="L72" t="s">
@@ -2950,13 +2954,13 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F73" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J73" t="s">
         <v>390</v>
       </c>
       <c r="K73" s="26">
-        <f>INDEX('feed pars'!C$6:C$42,MATCH(F73,'feed pars'!B$6:B$42,0))</f>
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F73,'feed pars'!B$6:B$43,0))</f>
         <v>100</v>
       </c>
       <c r="L73" t="s">
@@ -2966,13 +2970,13 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F74" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="J74" t="s">
         <v>390</v>
       </c>
       <c r="K74" s="26">
-        <f>INDEX('feed pars'!C$6:C$42,MATCH(F74,'feed pars'!B$6:B$42,0))</f>
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F74,'feed pars'!B$6:B$43,0))</f>
         <v>100</v>
       </c>
       <c r="L74" t="s">
@@ -2982,14 +2986,14 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F75" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="J75" t="s">
         <v>390</v>
       </c>
       <c r="K75" s="26">
-        <f>INDEX('feed pars'!C$6:C$42,MATCH(F75,'feed pars'!B$6:B$42,0))</f>
-        <v>87</v>
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F75,'feed pars'!B$6:B$43,0))</f>
+        <v>100</v>
       </c>
       <c r="L75" t="s">
         <v>28</v>
@@ -2998,13 +3002,13 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F76" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="J76" t="s">
         <v>390</v>
       </c>
       <c r="K76" s="26">
-        <f>INDEX('feed pars'!C$6:C$42,MATCH(F76,'feed pars'!B$6:B$42,0))</f>
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F76,'feed pars'!B$6:B$43,0))</f>
         <v>87</v>
       </c>
       <c r="L76" t="s">
@@ -3014,14 +3018,14 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F77" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J77" t="s">
         <v>390</v>
       </c>
       <c r="K77" s="26">
-        <f>INDEX('feed pars'!C$6:C$42,MATCH(F77,'feed pars'!B$6:B$42,0))</f>
-        <v>86</v>
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F77,'feed pars'!B$6:B$43,0))</f>
+        <v>87</v>
       </c>
       <c r="L77" t="s">
         <v>28</v>
@@ -3030,14 +3034,14 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F78" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J78" t="s">
         <v>390</v>
       </c>
       <c r="K78" s="26">
-        <f>INDEX('feed pars'!C$6:C$42,MATCH(F78,'feed pars'!B$6:B$42,0))</f>
-        <v>87</v>
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F78,'feed pars'!B$6:B$43,0))</f>
+        <v>86</v>
       </c>
       <c r="L78" t="s">
         <v>28</v>
@@ -3046,13 +3050,13 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F79" t="s">
-        <v>317</v>
+        <v>39</v>
       </c>
       <c r="J79" t="s">
         <v>390</v>
       </c>
       <c r="K79" s="26">
-        <f>INDEX('feed pars'!C$6:C$42,MATCH(F79,'feed pars'!B$6:B$42,0))</f>
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F79,'feed pars'!B$6:B$43,0))</f>
         <v>87</v>
       </c>
       <c r="L79" t="s">
@@ -3062,14 +3066,14 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F80" t="s">
-        <v>40</v>
+        <v>317</v>
       </c>
       <c r="J80" t="s">
         <v>390</v>
       </c>
       <c r="K80" s="26">
-        <f>INDEX('feed pars'!C$6:C$42,MATCH(F80,'feed pars'!B$6:B$42,0))</f>
-        <v>67.5</v>
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F80,'feed pars'!B$6:B$43,0))</f>
+        <v>87</v>
       </c>
       <c r="L80" t="s">
         <v>28</v>
@@ -3078,14 +3082,14 @@
     </row>
     <row r="81" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F81" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J81" t="s">
         <v>390</v>
       </c>
       <c r="K81" s="26">
-        <f>INDEX('feed pars'!C$6:C$42,MATCH(F81,'feed pars'!B$6:B$42,0))</f>
-        <v>87</v>
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F81,'feed pars'!B$6:B$43,0))</f>
+        <v>67.5</v>
       </c>
       <c r="L81" t="s">
         <v>28</v>
@@ -3094,14 +3098,14 @@
     </row>
     <row r="82" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F82" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J82" t="s">
         <v>390</v>
       </c>
       <c r="K82" s="26">
-        <f>INDEX('feed pars'!C$6:C$42,MATCH(F82,'feed pars'!B$6:B$42,0))</f>
-        <v>86.8</v>
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F82,'feed pars'!B$6:B$43,0))</f>
+        <v>87</v>
       </c>
       <c r="L82" t="s">
         <v>28</v>
@@ -3110,14 +3114,14 @@
     </row>
     <row r="83" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F83" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="J83" t="s">
         <v>390</v>
       </c>
       <c r="K83" s="26">
-        <f>INDEX('feed pars'!C$6:C$42,MATCH(F83,'feed pars'!B$6:B$42,0))</f>
-        <v>92.5</v>
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F83,'feed pars'!B$6:B$43,0))</f>
+        <v>86.8</v>
       </c>
       <c r="L83" t="s">
         <v>28</v>
@@ -3126,14 +3130,14 @@
     </row>
     <row r="84" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F84" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="J84" t="s">
         <v>390</v>
       </c>
       <c r="K84" s="26">
-        <f>INDEX('feed pars'!C$6:C$42,MATCH(F84,'feed pars'!B$6:B$42,0))</f>
-        <v>92</v>
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F84,'feed pars'!B$6:B$43,0))</f>
+        <v>92.5</v>
       </c>
       <c r="L84" t="s">
         <v>28</v>
@@ -3142,14 +3146,14 @@
     </row>
     <row r="85" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F85" t="s">
-        <v>314</v>
+        <v>43</v>
       </c>
       <c r="J85" t="s">
         <v>390</v>
       </c>
       <c r="K85" s="26">
-        <f>INDEX('feed pars'!C$6:C$42,MATCH(F85,'feed pars'!B$6:B$42,0))</f>
-        <v>100</v>
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F85,'feed pars'!B$6:B$43,0))</f>
+        <v>92</v>
       </c>
       <c r="L85" t="s">
         <v>28</v>
@@ -3158,14 +3162,14 @@
     </row>
     <row r="86" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F86" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="J86" t="s">
         <v>390</v>
       </c>
       <c r="K86" s="26">
-        <f>INDEX('feed pars'!C$6:C$42,MATCH(F86,'feed pars'!B$6:B$42,0))</f>
-        <v>85</v>
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F86,'feed pars'!B$6:B$43,0))</f>
+        <v>100</v>
       </c>
       <c r="L86" t="s">
         <v>28</v>
@@ -3174,14 +3178,14 @@
     </row>
     <row r="87" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F87" t="s">
-        <v>318</v>
+        <v>305</v>
       </c>
       <c r="J87" t="s">
         <v>390</v>
       </c>
       <c r="K87" s="26">
-        <f>INDEX('feed pars'!C$6:C$42,MATCH(F87,'feed pars'!B$6:B$42,0))</f>
-        <v>87</v>
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F87,'feed pars'!B$6:B$43,0))</f>
+        <v>85</v>
       </c>
       <c r="L87" t="s">
         <v>28</v>
@@ -3190,14 +3194,14 @@
     </row>
     <row r="88" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F88" t="s">
-        <v>44</v>
+        <v>318</v>
       </c>
       <c r="J88" t="s">
         <v>390</v>
       </c>
       <c r="K88" s="26">
-        <f>INDEX('feed pars'!C$6:C$42,MATCH(F88,'feed pars'!B$6:B$42,0))</f>
-        <v>87.5</v>
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F88,'feed pars'!B$6:B$43,0))</f>
+        <v>87</v>
       </c>
       <c r="L88" t="s">
         <v>28</v>
@@ -3206,14 +3210,14 @@
     </row>
     <row r="89" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F89" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J89" t="s">
         <v>390</v>
       </c>
       <c r="K89" s="26">
-        <f>INDEX('feed pars'!C$6:C$42,MATCH(F89,'feed pars'!B$6:B$42,0))</f>
-        <v>87</v>
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F89,'feed pars'!B$6:B$43,0))</f>
+        <v>87.5</v>
       </c>
       <c r="L89" t="s">
         <v>28</v>
@@ -3222,14 +3226,14 @@
     </row>
     <row r="90" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F90" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="J90" t="s">
         <v>390</v>
       </c>
       <c r="K90" s="26">
-        <f>INDEX('feed pars'!C$6:C$42,MATCH(F90,'feed pars'!B$6:B$42,0))</f>
-        <v>89.5</v>
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F90,'feed pars'!B$6:B$43,0))</f>
+        <v>87</v>
       </c>
       <c r="L90" t="s">
         <v>28</v>
@@ -3238,14 +3242,14 @@
     </row>
     <row r="91" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F91" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="J91" t="s">
         <v>390</v>
       </c>
       <c r="K91" s="26">
-        <f>INDEX('feed pars'!C$6:C$42,MATCH(F91,'feed pars'!B$6:B$42,0))</f>
-        <v>91</v>
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F91,'feed pars'!B$6:B$43,0))</f>
+        <v>89.5</v>
       </c>
       <c r="L91" t="s">
         <v>28</v>
@@ -3254,13 +3258,13 @@
     </row>
     <row r="92" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F92" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J92" t="s">
         <v>390</v>
       </c>
       <c r="K92" s="26">
-        <f>INDEX('feed pars'!C$6:C$42,MATCH(F92,'feed pars'!B$6:B$42,0))</f>
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F92,'feed pars'!B$6:B$43,0))</f>
         <v>91</v>
       </c>
       <c r="L92" t="s">
@@ -3270,14 +3274,14 @@
     </row>
     <row r="93" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F93" t="s">
-        <v>319</v>
+        <v>47</v>
       </c>
       <c r="J93" t="s">
         <v>390</v>
       </c>
       <c r="K93" s="26">
-        <f>INDEX('feed pars'!C$6:C$42,MATCH(F93,'feed pars'!B$6:B$42,0))</f>
-        <v>90</v>
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F93,'feed pars'!B$6:B$43,0))</f>
+        <v>91</v>
       </c>
       <c r="L93" t="s">
         <v>28</v>
@@ -3286,14 +3290,14 @@
     </row>
     <row r="94" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F94" t="s">
-        <v>48</v>
+        <v>319</v>
       </c>
       <c r="J94" t="s">
         <v>390</v>
       </c>
       <c r="K94" s="26">
-        <f>INDEX('feed pars'!C$6:C$42,MATCH(F94,'feed pars'!B$6:B$42,0))</f>
-        <v>87</v>
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F94,'feed pars'!B$6:B$43,0))</f>
+        <v>90</v>
       </c>
       <c r="L94" t="s">
         <v>28</v>
@@ -3302,14 +3306,14 @@
     </row>
     <row r="95" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F95" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J95" t="s">
         <v>390</v>
       </c>
       <c r="K95" s="26">
-        <f>INDEX('feed pars'!C$6:C$42,MATCH(F95,'feed pars'!B$6:B$42,0))</f>
-        <v>88</v>
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F95,'feed pars'!B$6:B$43,0))</f>
+        <v>87</v>
       </c>
       <c r="L95" t="s">
         <v>28</v>
@@ -3318,14 +3322,14 @@
     </row>
     <row r="96" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F96" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J96" t="s">
         <v>390</v>
       </c>
       <c r="K96" s="26">
-        <f>INDEX('feed pars'!C$6:C$42,MATCH(F96,'feed pars'!B$6:B$42,0))</f>
-        <v>90</v>
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F96,'feed pars'!B$6:B$43,0))</f>
+        <v>88</v>
       </c>
       <c r="L96" t="s">
         <v>28</v>
@@ -3334,14 +3338,14 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F97" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J97" t="s">
         <v>390</v>
       </c>
       <c r="K97" s="26">
-        <f>INDEX('feed pars'!C$6:C$42,MATCH(F97,'feed pars'!B$6:B$42,0))</f>
-        <v>11</v>
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F97,'feed pars'!B$6:B$43,0))</f>
+        <v>90</v>
       </c>
       <c r="L97" t="s">
         <v>28</v>
@@ -3350,14 +3354,14 @@
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F98" t="s">
-        <v>313</v>
+        <v>51</v>
       </c>
       <c r="J98" t="s">
         <v>390</v>
       </c>
       <c r="K98" s="26">
-        <f>INDEX('feed pars'!C$6:C$42,MATCH(F98,'feed pars'!B$6:B$42,0))</f>
-        <v>90</v>
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F98,'feed pars'!B$6:B$43,0))</f>
+        <v>11</v>
       </c>
       <c r="L98" t="s">
         <v>28</v>
@@ -3366,14 +3370,14 @@
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F99" t="s">
-        <v>52</v>
+        <v>313</v>
       </c>
       <c r="J99" t="s">
         <v>390</v>
       </c>
       <c r="K99" s="26">
-        <f>INDEX('feed pars'!C$6:C$42,MATCH(F99,'feed pars'!B$6:B$42,0))</f>
-        <v>75.5</v>
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F99,'feed pars'!B$6:B$43,0))</f>
+        <v>90</v>
       </c>
       <c r="L99" t="s">
         <v>28</v>
@@ -3382,14 +3386,14 @@
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F100" t="s">
-        <v>53</v>
+        <v>388</v>
       </c>
       <c r="J100" t="s">
         <v>390</v>
       </c>
       <c r="K100" s="26">
-        <f>INDEX('feed pars'!C$6:C$42,MATCH(F100,'feed pars'!B$6:B$42,0))</f>
-        <v>89.5</v>
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F100,'feed pars'!B$6:B$43,0))</f>
+        <v>87</v>
       </c>
       <c r="L100" t="s">
         <v>28</v>
@@ -3398,14 +3402,14 @@
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F101" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J101" t="s">
         <v>390</v>
       </c>
       <c r="K101" s="26">
-        <f>INDEX('feed pars'!C$6:C$42,MATCH(F101,'feed pars'!B$6:B$42,0))</f>
-        <v>6.25</v>
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F101,'feed pars'!B$6:B$43,0))</f>
+        <v>75.5</v>
       </c>
       <c r="L101" t="s">
         <v>28</v>
@@ -3414,14 +3418,14 @@
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F102" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J102" t="s">
         <v>390</v>
       </c>
       <c r="K102" s="26">
-        <f>INDEX('feed pars'!C$6:C$42,MATCH(F102,'feed pars'!B$6:B$42,0))</f>
-        <v>97</v>
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F102,'feed pars'!B$6:B$43,0))</f>
+        <v>89.5</v>
       </c>
       <c r="L102" t="s">
         <v>28</v>
@@ -3430,14 +3434,14 @@
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F103" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J103" t="s">
         <v>390</v>
       </c>
       <c r="K103" s="26">
-        <f>INDEX('feed pars'!C$6:C$42,MATCH(F103,'feed pars'!B$6:B$42,0))</f>
-        <v>91</v>
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F103,'feed pars'!B$6:B$43,0))</f>
+        <v>6.25</v>
       </c>
       <c r="L103" t="s">
         <v>28</v>
@@ -3446,14 +3450,14 @@
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F104" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J104" t="s">
         <v>390</v>
       </c>
       <c r="K104" s="26">
-        <f>INDEX('feed pars'!C$6:C$42,MATCH(F104,'feed pars'!B$6:B$42,0))</f>
-        <v>92</v>
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F104,'feed pars'!B$6:B$43,0))</f>
+        <v>97</v>
       </c>
       <c r="L104" t="s">
         <v>28</v>
@@ -3461,70 +3465,70 @@
       <c r="M104" s="3"/>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A105" s="7" t="s">
+      <c r="F105" t="s">
+        <v>56</v>
+      </c>
+      <c r="J105" t="s">
+        <v>390</v>
+      </c>
+      <c r="K105" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F105,'feed pars'!B$6:B$43,0))</f>
+        <v>91</v>
+      </c>
+      <c r="L105" t="s">
+        <v>28</v>
+      </c>
+      <c r="M105" s="3"/>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F106" t="s">
+        <v>57</v>
+      </c>
+      <c r="J106" t="s">
+        <v>390</v>
+      </c>
+      <c r="K106" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F106,'feed pars'!B$6:B$43,0))</f>
+        <v>92</v>
+      </c>
+      <c r="L106" t="s">
+        <v>28</v>
+      </c>
+      <c r="M106" s="3"/>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A107" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B105" s="7"/>
-      <c r="C105" s="6"/>
-      <c r="D105" s="6"/>
-      <c r="E105" s="6"/>
-      <c r="F105" s="6"/>
-      <c r="G105" s="6"/>
-      <c r="H105" s="6"/>
-      <c r="I105" s="6"/>
-      <c r="J105" s="6"/>
-      <c r="K105" s="6"/>
-      <c r="L105" s="6" t="s">
+      <c r="B107" s="7"/>
+      <c r="C107" s="6"/>
+      <c r="D107" s="6"/>
+      <c r="E107" s="6"/>
+      <c r="F107" s="6"/>
+      <c r="G107" s="6"/>
+      <c r="H107" s="6"/>
+      <c r="I107" s="6"/>
+      <c r="J107" s="6"/>
+      <c r="K107" s="6"/>
+      <c r="L107" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="M105" s="6"/>
-      <c r="N105" s="6"/>
-    </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>24</v>
-      </c>
-      <c r="F106" t="s">
-        <v>310</v>
-      </c>
-      <c r="J106" t="s">
-        <v>18</v>
-      </c>
-      <c r="K106" s="26">
-        <f>INDEX('feed pars'!L$6:L$42,MATCH(F106,'feed pars'!B$6:B$42,0))</f>
-        <v>11.5</v>
-      </c>
-      <c r="M106" s="3"/>
-    </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>24</v>
-      </c>
-      <c r="F107" t="s">
-        <v>311</v>
-      </c>
-      <c r="J107" t="s">
-        <v>18</v>
-      </c>
-      <c r="K107" s="26">
-        <f>INDEX('feed pars'!L$6:L$42,MATCH(F107,'feed pars'!B$6:B$42,0))</f>
-        <v>10.4</v>
-      </c>
-      <c r="M107" s="3"/>
+      <c r="M107" s="6"/>
+      <c r="N107" s="6"/>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>24</v>
       </c>
       <c r="F108" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="J108" t="s">
         <v>18</v>
       </c>
       <c r="K108" s="26">
-        <f>INDEX('feed pars'!L$6:L$42,MATCH(F108,'feed pars'!B$6:B$42,0))</f>
-        <v>10</v>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F108,'feed pars'!B$6:B$43,0))</f>
+        <v>11.5</v>
       </c>
       <c r="M108" s="3"/>
     </row>
@@ -3533,77 +3537,79 @@
         <v>24</v>
       </c>
       <c r="F109" t="s">
-        <v>12</v>
+        <v>311</v>
       </c>
       <c r="J109" t="s">
         <v>18</v>
       </c>
       <c r="K109" s="26">
-        <f>INDEX('feed pars'!L$6:L$42,MATCH(F109,'feed pars'!B$6:B$42,0))</f>
-        <v>11.3</v>
-      </c>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F109,'feed pars'!B$6:B$43,0))</f>
+        <v>10.4</v>
+      </c>
+      <c r="M109" s="3"/>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>24</v>
       </c>
       <c r="F110" t="s">
-        <v>33</v>
+        <v>312</v>
       </c>
       <c r="J110" t="s">
         <v>18</v>
       </c>
       <c r="K110" s="26">
-        <f>INDEX('feed pars'!L$6:L$42,MATCH(F110,'feed pars'!B$6:B$42,0))</f>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F110,'feed pars'!B$6:B$43,0))</f>
         <v>10</v>
       </c>
+      <c r="M110" s="3"/>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K111" s="3"/>
+      <c r="A111" t="s">
+        <v>24</v>
+      </c>
+      <c r="F111" t="s">
+        <v>12</v>
+      </c>
+      <c r="J111" t="s">
+        <v>18</v>
+      </c>
+      <c r="K111" s="26">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F111,'feed pars'!B$6:B$43,0))</f>
+        <v>11.3</v>
+      </c>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>24</v>
       </c>
       <c r="F112" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="J112" t="s">
         <v>18</v>
       </c>
       <c r="K112" s="26">
-        <f>INDEX('feed pars'!L$6:L$42,MATCH(F112,'feed pars'!B$6:B$42,0))</f>
-        <v>14.1</v>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F112,'feed pars'!B$6:B$43,0))</f>
+        <v>10</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>24</v>
-      </c>
-      <c r="F113" t="s">
-        <v>37</v>
-      </c>
-      <c r="J113" t="s">
-        <v>18</v>
-      </c>
-      <c r="K113" s="26">
-        <f>INDEX('feed pars'!L$6:L$42,MATCH(F113,'feed pars'!B$6:B$42,0))</f>
-        <v>13.2</v>
-      </c>
+      <c r="K113" s="3"/>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>24</v>
       </c>
       <c r="F114" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="J114" t="s">
         <v>18</v>
       </c>
       <c r="K114" s="26">
-        <f>INDEX('feed pars'!L$6:L$42,MATCH(F114,'feed pars'!B$6:B$42,0))</f>
-        <v>11.7</v>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F114,'feed pars'!B$6:B$43,0))</f>
+        <v>14.1</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
@@ -3611,14 +3617,14 @@
         <v>24</v>
       </c>
       <c r="F115" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="J115" t="s">
         <v>18</v>
       </c>
       <c r="K115" s="26">
-        <f>INDEX('feed pars'!L$6:L$42,MATCH(F115,'feed pars'!B$6:B$42,0))</f>
-        <v>14</v>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F115,'feed pars'!B$6:B$43,0))</f>
+        <v>13.2</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
@@ -3626,14 +3632,14 @@
         <v>24</v>
       </c>
       <c r="F116" t="s">
-        <v>317</v>
+        <v>38</v>
       </c>
       <c r="J116" t="s">
         <v>18</v>
       </c>
       <c r="K116" s="26">
-        <f>INDEX('feed pars'!L$6:L$42,MATCH(F116,'feed pars'!B$6:B$42,0))</f>
-        <v>13.9</v>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F116,'feed pars'!B$6:B$43,0))</f>
+        <v>11.7</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
@@ -3641,14 +3647,14 @@
         <v>24</v>
       </c>
       <c r="F117" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J117" t="s">
         <v>18</v>
       </c>
       <c r="K117" s="26">
-        <f>INDEX('feed pars'!L$6:L$42,MATCH(F117,'feed pars'!B$6:B$42,0))</f>
-        <v>12.8</v>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F117,'feed pars'!B$6:B$43,0))</f>
+        <v>14</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
@@ -3656,14 +3662,14 @@
         <v>24</v>
       </c>
       <c r="F118" t="s">
-        <v>41</v>
+        <v>317</v>
       </c>
       <c r="J118" t="s">
         <v>18</v>
       </c>
       <c r="K118" s="26">
-        <f>INDEX('feed pars'!L$6:L$42,MATCH(F118,'feed pars'!B$6:B$42,0))</f>
-        <v>13.8</v>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F118,'feed pars'!B$6:B$43,0))</f>
+        <v>13.9</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
@@ -3671,14 +3677,14 @@
         <v>24</v>
       </c>
       <c r="F119" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J119" t="s">
         <v>18</v>
       </c>
       <c r="K119" s="26">
-        <f>INDEX('feed pars'!L$6:L$42,MATCH(F119,'feed pars'!B$6:B$42,0))</f>
-        <v>13.3</v>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F119,'feed pars'!B$6:B$43,0))</f>
+        <v>12.8</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
@@ -3686,14 +3692,14 @@
         <v>24</v>
       </c>
       <c r="F120" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J120" t="s">
         <v>18</v>
       </c>
       <c r="K120" s="26">
-        <f>INDEX('feed pars'!L$6:L$42,MATCH(F120,'feed pars'!B$6:B$42,0))</f>
-        <v>22.1</v>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F120,'feed pars'!B$6:B$43,0))</f>
+        <v>13.8</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
@@ -3701,14 +3707,14 @@
         <v>24</v>
       </c>
       <c r="F121" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J121" t="s">
         <v>18</v>
       </c>
       <c r="K121" s="26">
-        <f>INDEX('feed pars'!L$6:L$42,MATCH(F121,'feed pars'!B$6:B$42,0))</f>
-        <v>20.100000000000001</v>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F121,'feed pars'!B$6:B$43,0))</f>
+        <v>13.3</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
@@ -3716,14 +3722,14 @@
         <v>24</v>
       </c>
       <c r="F122" t="s">
-        <v>305</v>
+        <v>35</v>
       </c>
       <c r="J122" t="s">
         <v>18</v>
       </c>
       <c r="K122" s="26">
-        <f>INDEX('feed pars'!L$6:L$42,MATCH(F122,'feed pars'!B$6:B$42,0))</f>
-        <v>6.6</v>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F122,'feed pars'!B$6:B$43,0))</f>
+        <v>22.1</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
@@ -3731,14 +3737,14 @@
         <v>24</v>
       </c>
       <c r="F123" t="s">
-        <v>314</v>
+        <v>43</v>
       </c>
       <c r="J123" t="s">
         <v>18</v>
       </c>
       <c r="K123" s="26">
-        <f>INDEX('feed pars'!L$6:L$42,MATCH(F123,'feed pars'!B$6:B$42,0))</f>
-        <v>36.6</v>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F123,'feed pars'!B$6:B$43,0))</f>
+        <v>20.100000000000001</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
@@ -3746,14 +3752,14 @@
         <v>24</v>
       </c>
       <c r="F124" t="s">
-        <v>318</v>
+        <v>305</v>
       </c>
       <c r="J124" t="s">
         <v>18</v>
       </c>
       <c r="K124" s="26">
-        <f>INDEX('feed pars'!L$6:L$42,MATCH(F124,'feed pars'!B$6:B$42,0))</f>
-        <v>16.399999999999999</v>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F124,'feed pars'!B$6:B$43,0))</f>
+        <v>6.6</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
@@ -3761,14 +3767,14 @@
         <v>24</v>
       </c>
       <c r="F125" t="s">
-        <v>44</v>
+        <v>314</v>
       </c>
       <c r="J125" t="s">
         <v>18</v>
       </c>
       <c r="K125" s="26">
-        <f>INDEX('feed pars'!L$6:L$42,MATCH(F125,'feed pars'!B$6:B$42,0))</f>
-        <v>14.6</v>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F125,'feed pars'!B$6:B$43,0))</f>
+        <v>36.6</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
@@ -3776,14 +3782,14 @@
         <v>24</v>
       </c>
       <c r="F126" t="s">
-        <v>36</v>
+        <v>318</v>
       </c>
       <c r="J126" t="s">
         <v>18</v>
       </c>
       <c r="K126" s="26">
-        <f>INDEX('feed pars'!L$6:L$42,MATCH(F126,'feed pars'!B$6:B$42,0))</f>
-        <v>12.2</v>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F126,'feed pars'!B$6:B$43,0))</f>
+        <v>16.399999999999999</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
@@ -3791,14 +3797,14 @@
         <v>24</v>
       </c>
       <c r="F127" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J127" t="s">
         <v>18</v>
       </c>
       <c r="K127" s="26">
-        <f>INDEX('feed pars'!L$6:L$42,MATCH(F127,'feed pars'!B$6:B$42,0))</f>
-        <v>11.4</v>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F127,'feed pars'!B$6:B$43,0))</f>
+        <v>14.6</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
@@ -3806,14 +3812,14 @@
         <v>24</v>
       </c>
       <c r="F128" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="J128" t="s">
         <v>18</v>
       </c>
       <c r="K128" s="26">
-        <f>INDEX('feed pars'!L$6:L$42,MATCH(F128,'feed pars'!B$6:B$42,0))</f>
-        <v>13.4</v>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F128,'feed pars'!B$6:B$43,0))</f>
+        <v>12.2</v>
       </c>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.25">
@@ -3821,14 +3827,14 @@
         <v>24</v>
       </c>
       <c r="F129" t="s">
-        <v>319</v>
+        <v>46</v>
       </c>
       <c r="J129" t="s">
         <v>18</v>
       </c>
       <c r="K129" s="26">
-        <f>INDEX('feed pars'!L$6:L$42,MATCH(F129,'feed pars'!B$6:B$42,0))</f>
-        <v>8.5</v>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F129,'feed pars'!B$6:B$43,0))</f>
+        <v>11.4</v>
       </c>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.25">
@@ -3836,14 +3842,14 @@
         <v>24</v>
       </c>
       <c r="F130" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J130" t="s">
         <v>18</v>
       </c>
       <c r="K130" s="26">
-        <f>INDEX('feed pars'!L$6:L$42,MATCH(F130,'feed pars'!B$6:B$42,0))</f>
-        <v>11</v>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F130,'feed pars'!B$6:B$43,0))</f>
+        <v>13.4</v>
       </c>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.25">
@@ -3851,14 +3857,14 @@
         <v>24</v>
       </c>
       <c r="F131" t="s">
-        <v>50</v>
+        <v>319</v>
       </c>
       <c r="J131" t="s">
         <v>18</v>
       </c>
       <c r="K131" s="26">
-        <f>INDEX('feed pars'!L$6:L$42,MATCH(F131,'feed pars'!B$6:B$42,0))</f>
-        <v>13.3</v>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F131,'feed pars'!B$6:B$43,0))</f>
+        <v>8.5</v>
       </c>
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.25">
@@ -3866,14 +3872,14 @@
         <v>24</v>
       </c>
       <c r="F132" t="s">
-        <v>313</v>
+        <v>48</v>
       </c>
       <c r="J132" t="s">
         <v>18</v>
       </c>
       <c r="K132" s="26">
-        <f>INDEX('feed pars'!L$6:L$42,MATCH(F132,'feed pars'!B$6:B$42,0))</f>
-        <v>11.6</v>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F132,'feed pars'!B$6:B$43,0))</f>
+        <v>11</v>
       </c>
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.25">
@@ -3881,14 +3887,14 @@
         <v>24</v>
       </c>
       <c r="F133" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="J133" t="s">
         <v>18</v>
       </c>
       <c r="K133" s="26">
-        <f>INDEX('feed pars'!L$6:L$42,MATCH(F133,'feed pars'!B$6:B$42,0))</f>
-        <v>12.4</v>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F133,'feed pars'!B$6:B$43,0))</f>
+        <v>13.3</v>
       </c>
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.25">
@@ -3896,14 +3902,14 @@
         <v>24</v>
       </c>
       <c r="F134" t="s">
-        <v>53</v>
+        <v>313</v>
       </c>
       <c r="J134" t="s">
         <v>18</v>
       </c>
       <c r="K134" s="26">
-        <f>INDEX('feed pars'!L$6:L$42,MATCH(F134,'feed pars'!B$6:B$42,0))</f>
-        <v>12.3</v>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F134,'feed pars'!B$6:B$43,0))</f>
+        <v>11.6</v>
       </c>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.25">
@@ -3911,14 +3917,14 @@
         <v>24</v>
       </c>
       <c r="F135" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J135" t="s">
         <v>18</v>
       </c>
       <c r="K135" s="26">
-        <f>INDEX('feed pars'!L$6:L$42,MATCH(F135,'feed pars'!B$6:B$42,0))</f>
-        <v>13.6</v>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F135,'feed pars'!B$6:B$43,0))</f>
+        <v>12.4</v>
       </c>
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.25">
@@ -3926,14 +3932,14 @@
         <v>24</v>
       </c>
       <c r="F136" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="J136" t="s">
         <v>18</v>
       </c>
       <c r="K136" s="26">
-        <f>INDEX('feed pars'!L$6:L$42,MATCH(F136,'feed pars'!B$6:B$42,0))</f>
-        <v>15.5</v>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F136,'feed pars'!B$6:B$43,0))</f>
+        <v>12.3</v>
       </c>
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.25">
@@ -3941,91 +3947,85 @@
         <v>24</v>
       </c>
       <c r="F137" t="s">
-        <v>324</v>
+        <v>54</v>
       </c>
       <c r="J137" t="s">
         <v>18</v>
       </c>
-      <c r="K137" s="3">
-        <v>0</v>
+      <c r="K137" s="26">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F137,'feed pars'!B$6:B$43,0))</f>
+        <v>13.6</v>
       </c>
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K138" s="3"/>
+      <c r="A138" t="s">
+        <v>24</v>
+      </c>
+      <c r="F138" t="s">
+        <v>56</v>
+      </c>
+      <c r="J138" t="s">
+        <v>18</v>
+      </c>
+      <c r="K138" s="26">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F138,'feed pars'!B$6:B$43,0))</f>
+        <v>15.5</v>
+      </c>
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A139" s="8" t="s">
+      <c r="A139" t="s">
+        <v>24</v>
+      </c>
+      <c r="F139" t="s">
+        <v>324</v>
+      </c>
+      <c r="J139" t="s">
+        <v>18</v>
+      </c>
+      <c r="K139" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K140" s="3"/>
+    </row>
+    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A141" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B139" s="8"/>
-      <c r="C139" s="9"/>
-      <c r="D139" s="9"/>
-      <c r="E139" s="9"/>
-      <c r="F139" s="9"/>
-      <c r="G139" s="9"/>
-      <c r="H139" s="9"/>
-      <c r="I139" s="9"/>
-      <c r="J139" s="9"/>
-      <c r="K139" s="9"/>
-      <c r="L139" s="9"/>
-      <c r="M139" s="9"/>
-      <c r="N139" s="9"/>
-    </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A140" s="30" t="s">
+      <c r="B141" s="8"/>
+      <c r="C141" s="9"/>
+      <c r="D141" s="9"/>
+      <c r="E141" s="9"/>
+      <c r="F141" s="9"/>
+      <c r="G141" s="9"/>
+      <c r="H141" s="9"/>
+      <c r="I141" s="9"/>
+      <c r="J141" s="9"/>
+      <c r="K141" s="9"/>
+      <c r="L141" s="9"/>
+      <c r="M141" s="9"/>
+      <c r="N141" s="9"/>
+    </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A142" s="30" t="s">
         <v>391</v>
       </c>
-      <c r="B140" s="31"/>
-      <c r="C140" s="32"/>
-      <c r="D140" s="32"/>
-      <c r="E140" s="32"/>
-      <c r="F140" s="32"/>
-      <c r="G140" s="32"/>
-      <c r="H140" s="32"/>
-      <c r="I140" s="32"/>
-      <c r="J140" s="32"/>
-      <c r="K140" s="32"/>
-      <c r="L140" s="32" t="s">
+      <c r="B142" s="31"/>
+      <c r="C142" s="32"/>
+      <c r="D142" s="32"/>
+      <c r="E142" s="32"/>
+      <c r="F142" s="32"/>
+      <c r="G142" s="32"/>
+      <c r="H142" s="32"/>
+      <c r="I142" s="32"/>
+      <c r="J142" s="32"/>
+      <c r="K142" s="32"/>
+      <c r="L142" s="32" t="s">
         <v>300</v>
       </c>
-      <c r="M140" s="32"/>
-      <c r="N140" s="32"/>
-    </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>25</v>
-      </c>
-      <c r="E141" t="s">
-        <v>299</v>
-      </c>
-      <c r="F141" t="s">
-        <v>17</v>
-      </c>
-      <c r="J141" t="s">
-        <v>18</v>
-      </c>
-      <c r="K141" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F141,'feed pars'!B$6:B$42,0))</f>
-        <v>12.3</v>
-      </c>
-    </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>25</v>
-      </c>
-      <c r="E142" t="s">
-        <v>299</v>
-      </c>
-      <c r="F142" t="s">
-        <v>37</v>
-      </c>
-      <c r="J142" t="s">
-        <v>18</v>
-      </c>
-      <c r="K142" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F142,'feed pars'!B$6:B$42,0))</f>
-        <v>11.2</v>
-      </c>
+      <c r="M142" s="32"/>
+      <c r="N142" s="32"/>
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
@@ -4035,14 +4035,14 @@
         <v>299</v>
       </c>
       <c r="F143" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="J143" t="s">
         <v>18</v>
       </c>
       <c r="K143" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F143,'feed pars'!B$6:B$42,0))</f>
-        <v>9.4</v>
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F143,'feed pars'!B$6:B$43,0))</f>
+        <v>12.3</v>
       </c>
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.25">
@@ -4053,14 +4053,14 @@
         <v>299</v>
       </c>
       <c r="F144" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="J144" t="s">
         <v>18</v>
       </c>
       <c r="K144" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F144,'feed pars'!B$6:B$42,0))</f>
-        <v>12</v>
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F144,'feed pars'!B$6:B$43,0))</f>
+        <v>11.2</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
@@ -4071,14 +4071,14 @@
         <v>299</v>
       </c>
       <c r="F145" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J145" t="s">
         <v>18</v>
       </c>
       <c r="K145" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F145,'feed pars'!B$6:B$42,0))</f>
-        <v>13.2</v>
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F145,'feed pars'!B$6:B$43,0))</f>
+        <v>9.4</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
@@ -4089,14 +4089,14 @@
         <v>299</v>
       </c>
       <c r="F146" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J146" t="s">
         <v>18</v>
       </c>
       <c r="K146" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F146,'feed pars'!B$6:B$42,0))</f>
-        <v>11.5</v>
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F146,'feed pars'!B$6:B$43,0))</f>
+        <v>12</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
@@ -4107,14 +4107,14 @@
         <v>299</v>
       </c>
       <c r="F147" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J147" t="s">
         <v>18</v>
       </c>
       <c r="K147" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F147,'feed pars'!B$6:B$42,0))</f>
-        <v>10.9</v>
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F147,'feed pars'!B$6:B$43,0))</f>
+        <v>13.2</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
@@ -4125,14 +4125,14 @@
         <v>299</v>
       </c>
       <c r="F148" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J148" t="s">
         <v>18</v>
       </c>
       <c r="K148" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F148,'feed pars'!B$6:B$42,0))</f>
-        <v>18.5</v>
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F148,'feed pars'!B$6:B$43,0))</f>
+        <v>11.5</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
@@ -4143,14 +4143,14 @@
         <v>299</v>
       </c>
       <c r="F149" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J149" t="s">
         <v>18</v>
       </c>
       <c r="K149" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F149,'feed pars'!B$6:B$42,0))</f>
-        <v>17.5</v>
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F149,'feed pars'!B$6:B$43,0))</f>
+        <v>10.9</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
@@ -4161,14 +4161,14 @@
         <v>299</v>
       </c>
       <c r="F150" t="s">
-        <v>314</v>
+        <v>35</v>
       </c>
       <c r="J150" t="s">
         <v>18</v>
       </c>
       <c r="K150" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F150,'feed pars'!B$6:B$42,0))</f>
-        <v>29.8</v>
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F150,'feed pars'!B$6:B$43,0))</f>
+        <v>18.5</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
@@ -4179,14 +4179,14 @@
         <v>299</v>
       </c>
       <c r="F151" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J151" t="s">
         <v>18</v>
       </c>
       <c r="K151" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F151,'feed pars'!B$6:B$42,0))</f>
-        <v>9.9</v>
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F151,'feed pars'!B$6:B$43,0))</f>
+        <v>17.5</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
@@ -4197,14 +4197,14 @@
         <v>299</v>
       </c>
       <c r="F152" t="s">
-        <v>45</v>
+        <v>314</v>
       </c>
       <c r="J152" t="s">
         <v>18</v>
       </c>
       <c r="K152" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F152,'feed pars'!B$6:B$42,0))</f>
-        <v>10.3</v>
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F152,'feed pars'!B$6:B$43,0))</f>
+        <v>29.8</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
@@ -4215,14 +4215,14 @@
         <v>299</v>
       </c>
       <c r="F153" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J153" t="s">
         <v>18</v>
       </c>
       <c r="K153" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F153,'feed pars'!B$6:B$42,0))</f>
-        <v>7.7</v>
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F153,'feed pars'!B$6:B$43,0))</f>
+        <v>9.9</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
@@ -4233,14 +4233,14 @@
         <v>299</v>
       </c>
       <c r="F154" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J154" t="s">
         <v>18</v>
       </c>
       <c r="K154" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F154,'feed pars'!B$6:B$42,0))</f>
-        <v>6.5</v>
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F154,'feed pars'!B$6:B$43,0))</f>
+        <v>10.3</v>
       </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
@@ -4251,14 +4251,14 @@
         <v>299</v>
       </c>
       <c r="F155" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="J155" t="s">
         <v>18</v>
       </c>
       <c r="K155" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F155,'feed pars'!B$6:B$42,0))</f>
-        <v>6.2</v>
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F155,'feed pars'!B$6:B$43,0))</f>
+        <v>7.7</v>
       </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.25">
@@ -4269,14 +4269,14 @@
         <v>299</v>
       </c>
       <c r="F156" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J156" t="s">
         <v>18</v>
       </c>
       <c r="K156" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F156,'feed pars'!B$6:B$42,0))</f>
-        <v>7.8</v>
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F156,'feed pars'!B$6:B$43,0))</f>
+        <v>6.5</v>
       </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
@@ -4287,14 +4287,14 @@
         <v>299</v>
       </c>
       <c r="F157" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J157" t="s">
         <v>18</v>
       </c>
       <c r="K157" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F157,'feed pars'!B$6:B$42,0))</f>
-        <v>9.1999999999999993</v>
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F157,'feed pars'!B$6:B$43,0))</f>
+        <v>6.2</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
@@ -4305,14 +4305,14 @@
         <v>299</v>
       </c>
       <c r="F158" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J158" t="s">
         <v>18</v>
       </c>
       <c r="K158" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F158,'feed pars'!B$6:B$42,0))</f>
-        <v>8.6999999999999993</v>
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F158,'feed pars'!B$6:B$43,0))</f>
+        <v>7.8</v>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
@@ -4323,14 +4323,14 @@
         <v>299</v>
       </c>
       <c r="F159" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J159" t="s">
         <v>18</v>
       </c>
       <c r="K159" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F159,'feed pars'!B$6:B$42,0))</f>
-        <v>8.9</v>
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F159,'feed pars'!B$6:B$43,0))</f>
+        <v>9.1999999999999993</v>
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
@@ -4341,14 +4341,14 @@
         <v>299</v>
       </c>
       <c r="F160" t="s">
-        <v>313</v>
+        <v>50</v>
       </c>
       <c r="J160" t="s">
         <v>18</v>
       </c>
       <c r="K160" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F160,'feed pars'!B$6:B$42,0))</f>
-        <v>7.0888888888888877</v>
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F160,'feed pars'!B$6:B$43,0))</f>
+        <v>8.6999999999999993</v>
       </c>
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.25">
@@ -4359,14 +4359,14 @@
         <v>299</v>
       </c>
       <c r="F161" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J161" t="s">
         <v>18</v>
       </c>
       <c r="K161" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F161,'feed pars'!B$6:B$42,0))</f>
-        <v>9</v>
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F161,'feed pars'!B$6:B$43,0))</f>
+        <v>8.9</v>
       </c>
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.25">
@@ -4377,14 +4377,14 @@
         <v>299</v>
       </c>
       <c r="F162" t="s">
-        <v>53</v>
+        <v>313</v>
       </c>
       <c r="J162" t="s">
         <v>18</v>
       </c>
       <c r="K162" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F162,'feed pars'!B$6:B$42,0))</f>
-        <v>8</v>
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F162,'feed pars'!B$6:B$43,0))</f>
+        <v>7.0888888888888877</v>
       </c>
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.25">
@@ -4395,14 +4395,14 @@
         <v>299</v>
       </c>
       <c r="F163" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J163" t="s">
         <v>18</v>
       </c>
       <c r="K163" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F163,'feed pars'!B$6:B$42,0))</f>
-        <v>12.2</v>
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F163,'feed pars'!B$6:B$43,0))</f>
+        <v>9</v>
       </c>
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.25">
@@ -4413,14 +4413,14 @@
         <v>299</v>
       </c>
       <c r="F164" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J164" t="s">
         <v>18</v>
       </c>
       <c r="K164" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F164,'feed pars'!B$6:B$42,0))</f>
-        <v>12.2</v>
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F164,'feed pars'!B$6:B$43,0))</f>
+        <v>8</v>
       </c>
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.25">
@@ -4431,14 +4431,14 @@
         <v>299</v>
       </c>
       <c r="F165" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J165" t="s">
         <v>18</v>
       </c>
       <c r="K165" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F165,'feed pars'!B$6:B$42,0))</f>
-        <v>11.3</v>
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F165,'feed pars'!B$6:B$43,0))</f>
+        <v>12.2</v>
       </c>
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.25">
@@ -4449,79 +4449,85 @@
         <v>299</v>
       </c>
       <c r="F166" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J166" t="s">
         <v>18</v>
       </c>
       <c r="K166" s="26">
-        <f>INDEX('feed pars'!H$6:H$42,MATCH(F166,'feed pars'!B$6:B$42,0))</f>
-        <v>10.8</v>
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F166,'feed pars'!B$6:B$43,0))</f>
+        <v>12.2</v>
       </c>
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A167" s="30" t="s">
-        <v>392</v>
-      </c>
-      <c r="B167" s="31"/>
-      <c r="C167" s="32"/>
-      <c r="D167" s="32"/>
-      <c r="E167" s="32"/>
-      <c r="F167" s="32"/>
-      <c r="G167" s="32"/>
-      <c r="H167" s="32"/>
-      <c r="I167" s="32"/>
-      <c r="J167" s="32"/>
-      <c r="K167" s="32"/>
-      <c r="L167" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="M167" s="32"/>
-      <c r="N167" s="32"/>
+      <c r="A167" t="s">
+        <v>25</v>
+      </c>
+      <c r="E167" t="s">
+        <v>299</v>
+      </c>
+      <c r="F167" t="s">
+        <v>56</v>
+      </c>
+      <c r="J167" t="s">
+        <v>18</v>
+      </c>
+      <c r="K167" s="26">
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F167,'feed pars'!B$6:B$43,0))</f>
+        <v>11.3</v>
+      </c>
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>25</v>
       </c>
+      <c r="E168" t="s">
+        <v>299</v>
+      </c>
       <c r="F168" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="J168" t="s">
         <v>18</v>
       </c>
       <c r="K168" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F168,'feed pars'!B$6:B$42,0))</f>
-        <v>12.1</v>
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F168,'feed pars'!B$6:B$43,0))</f>
+        <v>10.8</v>
       </c>
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
-        <v>25</v>
-      </c>
-      <c r="F169" t="s">
-        <v>37</v>
-      </c>
-      <c r="J169" t="s">
-        <v>18</v>
-      </c>
-      <c r="K169" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F169,'feed pars'!B$6:B$42,0))</f>
-        <v>11</v>
-      </c>
+      <c r="A169" s="30" t="s">
+        <v>392</v>
+      </c>
+      <c r="B169" s="31"/>
+      <c r="C169" s="32"/>
+      <c r="D169" s="32"/>
+      <c r="E169" s="32"/>
+      <c r="F169" s="32"/>
+      <c r="G169" s="32"/>
+      <c r="H169" s="32"/>
+      <c r="I169" s="32"/>
+      <c r="J169" s="32"/>
+      <c r="K169" s="32"/>
+      <c r="L169" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="M169" s="32"/>
+      <c r="N169" s="32"/>
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>25</v>
       </c>
       <c r="F170" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="J170" t="s">
         <v>18</v>
       </c>
       <c r="K170" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F170,'feed pars'!B$6:B$42,0))</f>
-        <v>9</v>
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F170,'feed pars'!B$6:B$43,0))</f>
+        <v>12.1</v>
       </c>
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.25">
@@ -4529,14 +4535,14 @@
         <v>25</v>
       </c>
       <c r="F171" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="J171" t="s">
         <v>18</v>
       </c>
       <c r="K171" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F171,'feed pars'!B$6:B$42,0))</f>
-        <v>11.9</v>
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F171,'feed pars'!B$6:B$43,0))</f>
+        <v>11</v>
       </c>
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.25">
@@ -4544,14 +4550,14 @@
         <v>25</v>
       </c>
       <c r="F172" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J172" t="s">
         <v>18</v>
       </c>
       <c r="K172" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F172,'feed pars'!B$6:B$42,0))</f>
-        <v>12.8</v>
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F172,'feed pars'!B$6:B$43,0))</f>
+        <v>9</v>
       </c>
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.25">
@@ -4559,14 +4565,14 @@
         <v>25</v>
       </c>
       <c r="F173" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J173" t="s">
         <v>18</v>
       </c>
       <c r="K173" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F173,'feed pars'!B$6:B$42,0))</f>
-        <v>11.2</v>
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F173,'feed pars'!B$6:B$43,0))</f>
+        <v>11.9</v>
       </c>
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.25">
@@ -4574,14 +4580,14 @@
         <v>25</v>
       </c>
       <c r="F174" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J174" t="s">
         <v>18</v>
       </c>
       <c r="K174" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F174,'feed pars'!B$6:B$42,0))</f>
-        <v>10.7</v>
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F174,'feed pars'!B$6:B$43,0))</f>
+        <v>12.8</v>
       </c>
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.25">
@@ -4589,14 +4595,14 @@
         <v>25</v>
       </c>
       <c r="F175" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J175" t="s">
         <v>18</v>
       </c>
       <c r="K175" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F175,'feed pars'!B$6:B$42,0))</f>
-        <v>18</v>
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F175,'feed pars'!B$6:B$43,0))</f>
+        <v>11.2</v>
       </c>
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.25">
@@ -4604,14 +4610,14 @@
         <v>25</v>
       </c>
       <c r="F176" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J176" t="s">
         <v>18</v>
       </c>
       <c r="K176" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F176,'feed pars'!B$6:B$42,0))</f>
-        <v>17.3</v>
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F176,'feed pars'!B$6:B$43,0))</f>
+        <v>10.7</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
@@ -4619,14 +4625,14 @@
         <v>25</v>
       </c>
       <c r="F177" t="s">
-        <v>314</v>
+        <v>35</v>
       </c>
       <c r="J177" t="s">
         <v>18</v>
       </c>
       <c r="K177" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F177,'feed pars'!B$6:B$42,0))</f>
-        <v>29.8</v>
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F177,'feed pars'!B$6:B$43,0))</f>
+        <v>18</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
@@ -4634,14 +4640,14 @@
         <v>25</v>
       </c>
       <c r="F178" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J178" t="s">
         <v>18</v>
       </c>
       <c r="K178" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F178,'feed pars'!B$6:B$42,0))</f>
-        <v>9.3000000000000007</v>
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F178,'feed pars'!B$6:B$43,0))</f>
+        <v>17.3</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
@@ -4649,14 +4655,14 @@
         <v>25</v>
       </c>
       <c r="F179" t="s">
-        <v>45</v>
+        <v>314</v>
       </c>
       <c r="J179" t="s">
         <v>18</v>
       </c>
       <c r="K179" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F179,'feed pars'!B$6:B$42,0))</f>
-        <v>9.6999999999999993</v>
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F179,'feed pars'!B$6:B$43,0))</f>
+        <v>29.8</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
@@ -4664,14 +4670,14 @@
         <v>25</v>
       </c>
       <c r="F180" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J180" t="s">
         <v>18</v>
       </c>
       <c r="K180" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F180,'feed pars'!B$6:B$42,0))</f>
-        <v>7.1</v>
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F180,'feed pars'!B$6:B$43,0))</f>
+        <v>9.3000000000000007</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
@@ -4679,14 +4685,14 @@
         <v>25</v>
       </c>
       <c r="F181" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J181" t="s">
         <v>18</v>
       </c>
       <c r="K181" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F181,'feed pars'!B$6:B$42,0))</f>
-        <v>5.9</v>
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F181,'feed pars'!B$6:B$43,0))</f>
+        <v>9.6999999999999993</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
@@ -4694,14 +4700,14 @@
         <v>25</v>
       </c>
       <c r="F182" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="J182" t="s">
         <v>18</v>
       </c>
       <c r="K182" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F182,'feed pars'!B$6:B$42,0))</f>
-        <v>5.4</v>
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F182,'feed pars'!B$6:B$43,0))</f>
+        <v>7.1</v>
       </c>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.25">
@@ -4709,14 +4715,14 @@
         <v>25</v>
       </c>
       <c r="F183" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J183" t="s">
         <v>18</v>
       </c>
       <c r="K183" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F183,'feed pars'!B$6:B$42,0))</f>
-        <v>7.2</v>
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F183,'feed pars'!B$6:B$43,0))</f>
+        <v>5.9</v>
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.25">
@@ -4724,14 +4730,14 @@
         <v>25</v>
       </c>
       <c r="F184" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J184" t="s">
         <v>18</v>
       </c>
       <c r="K184" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F184,'feed pars'!B$6:B$42,0))</f>
-        <v>8.6999999999999993</v>
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F184,'feed pars'!B$6:B$43,0))</f>
+        <v>5.4</v>
       </c>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.25">
@@ -4739,14 +4745,14 @@
         <v>25</v>
       </c>
       <c r="F185" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J185" t="s">
         <v>18</v>
       </c>
       <c r="K185" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F185,'feed pars'!B$6:B$42,0))</f>
-        <v>8.1</v>
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F185,'feed pars'!B$6:B$43,0))</f>
+        <v>7.2</v>
       </c>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.25">
@@ -4754,14 +4760,14 @@
         <v>25</v>
       </c>
       <c r="F186" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J186" t="s">
         <v>18</v>
       </c>
       <c r="K186" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F186,'feed pars'!B$6:B$42,0))</f>
-        <v>8.1999999999999993</v>
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F186,'feed pars'!B$6:B$43,0))</f>
+        <v>8.6999999999999993</v>
       </c>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.25">
@@ -4769,14 +4775,14 @@
         <v>25</v>
       </c>
       <c r="F187" t="s">
-        <v>313</v>
+        <v>50</v>
       </c>
       <c r="J187" t="s">
         <v>18</v>
       </c>
       <c r="K187" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F187,'feed pars'!B$6:B$42,0))</f>
-        <v>6.6</v>
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F187,'feed pars'!B$6:B$43,0))</f>
+        <v>8.1</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
@@ -4784,14 +4790,14 @@
         <v>25</v>
       </c>
       <c r="F188" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J188" t="s">
         <v>18</v>
       </c>
       <c r="K188" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F188,'feed pars'!B$6:B$42,0))</f>
-        <v>8.6999999999999993</v>
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F188,'feed pars'!B$6:B$43,0))</f>
+        <v>8.1999999999999993</v>
       </c>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.25">
@@ -4799,14 +4805,14 @@
         <v>25</v>
       </c>
       <c r="F189" t="s">
-        <v>53</v>
+        <v>313</v>
       </c>
       <c r="J189" t="s">
         <v>18</v>
       </c>
       <c r="K189" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F189,'feed pars'!B$6:B$42,0))</f>
-        <v>6.9</v>
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F189,'feed pars'!B$6:B$43,0))</f>
+        <v>6.6</v>
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.25">
@@ -4814,14 +4820,14 @@
         <v>25</v>
       </c>
       <c r="F190" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J190" t="s">
         <v>18</v>
       </c>
       <c r="K190" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F190,'feed pars'!B$6:B$42,0))</f>
-        <v>12.4</v>
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F190,'feed pars'!B$6:B$43,0))</f>
+        <v>8.6999999999999993</v>
       </c>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.25">
@@ -4829,14 +4835,14 @@
         <v>25</v>
       </c>
       <c r="F191" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J191" t="s">
         <v>18</v>
       </c>
       <c r="K191" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F191,'feed pars'!B$6:B$42,0))</f>
-        <v>12.4</v>
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F191,'feed pars'!B$6:B$43,0))</f>
+        <v>6.9</v>
       </c>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.25">
@@ -4844,14 +4850,14 @@
         <v>25</v>
       </c>
       <c r="F192" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J192" t="s">
         <v>18</v>
       </c>
       <c r="K192" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F192,'feed pars'!B$6:B$42,0))</f>
-        <v>11.1</v>
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F192,'feed pars'!B$6:B$43,0))</f>
+        <v>12.4</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.25">
@@ -4859,13 +4865,43 @@
         <v>25</v>
       </c>
       <c r="F193" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J193" t="s">
         <v>18</v>
       </c>
       <c r="K193" s="26">
-        <f>INDEX('feed pars'!G$6:G$42,MATCH(F193,'feed pars'!B$6:B$42,0))</f>
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F193,'feed pars'!B$6:B$43,0))</f>
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>25</v>
+      </c>
+      <c r="F194" t="s">
+        <v>56</v>
+      </c>
+      <c r="J194" t="s">
+        <v>18</v>
+      </c>
+      <c r="K194" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F194,'feed pars'!B$6:B$43,0))</f>
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>25</v>
+      </c>
+      <c r="F195" t="s">
+        <v>57</v>
+      </c>
+      <c r="J195" t="s">
+        <v>18</v>
+      </c>
+      <c r="K195" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F195,'feed pars'!B$6:B$43,0))</f>
         <v>10.8</v>
       </c>
     </row>
@@ -4877,7 +4913,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:O42"/>
+  <dimension ref="B1:O43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
@@ -5060,7 +5096,7 @@
         <v>17</v>
       </c>
       <c r="C13" s="23">
-        <f>AVERAGE(F13,K13)</f>
+        <f t="shared" ref="C13:C43" si="0">AVERAGE(F13,K13)</f>
         <v>87</v>
       </c>
       <c r="D13" s="4"/>
@@ -5106,7 +5142,7 @@
         <v>37</v>
       </c>
       <c r="C14" s="23">
-        <f>AVERAGE(F14,K14)</f>
+        <f t="shared" si="0"/>
         <v>87</v>
       </c>
       <c r="D14" s="4"/>
@@ -5152,7 +5188,7 @@
         <v>38</v>
       </c>
       <c r="C15" s="23">
-        <f>AVERAGE(F15,K15)</f>
+        <f t="shared" si="0"/>
         <v>86</v>
       </c>
       <c r="D15" s="4"/>
@@ -5198,7 +5234,7 @@
         <v>39</v>
       </c>
       <c r="C16" s="23">
-        <f>AVERAGE(F16,K16)</f>
+        <f t="shared" si="0"/>
         <v>87</v>
       </c>
       <c r="D16" s="4"/>
@@ -5244,7 +5280,7 @@
         <v>317</v>
       </c>
       <c r="C17" s="23">
-        <f>AVERAGE(F17,K17)</f>
+        <f t="shared" si="0"/>
         <v>87</v>
       </c>
       <c r="D17" s="4"/>
@@ -5278,7 +5314,7 @@
         <v>40</v>
       </c>
       <c r="C18" s="23">
-        <f>AVERAGE(F18,K18)</f>
+        <f t="shared" si="0"/>
         <v>67.5</v>
       </c>
       <c r="D18" s="4"/>
@@ -5324,7 +5360,7 @@
         <v>41</v>
       </c>
       <c r="C19" s="23">
-        <f>AVERAGE(F19,K19)</f>
+        <f t="shared" si="0"/>
         <v>87</v>
       </c>
       <c r="D19" s="4"/>
@@ -5370,7 +5406,7 @@
         <v>42</v>
       </c>
       <c r="C20" s="23">
-        <f>AVERAGE(F20,K20)</f>
+        <f t="shared" si="0"/>
         <v>86.8</v>
       </c>
       <c r="D20" s="4"/>
@@ -5407,7 +5443,7 @@
         <v>35</v>
       </c>
       <c r="C21" s="23">
-        <f>AVERAGE(F21,K21)</f>
+        <f t="shared" si="0"/>
         <v>92.5</v>
       </c>
       <c r="D21" s="4"/>
@@ -5446,7 +5482,7 @@
         <v>43</v>
       </c>
       <c r="C22" s="23">
-        <f>AVERAGE(F22,K22)</f>
+        <f t="shared" si="0"/>
         <v>92</v>
       </c>
       <c r="D22" s="4"/>
@@ -5485,7 +5521,7 @@
         <v>314</v>
       </c>
       <c r="C23" s="23">
-        <f>AVERAGE(F23,K23)</f>
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="D23" s="4"/>
@@ -5529,7 +5565,7 @@
         <v>305</v>
       </c>
       <c r="C24" s="23">
-        <f>AVERAGE(F24,K24)</f>
+        <f t="shared" si="0"/>
         <v>85</v>
       </c>
       <c r="D24" s="4"/>
@@ -5553,7 +5589,7 @@
         <v>318</v>
       </c>
       <c r="C25" s="23">
-        <f>AVERAGE(F25,K25)</f>
+        <f t="shared" si="0"/>
         <v>87</v>
       </c>
       <c r="D25" s="4"/>
@@ -5577,7 +5613,7 @@
         <v>44</v>
       </c>
       <c r="C26" s="23">
-        <f>AVERAGE(F26,K26)</f>
+        <f t="shared" si="0"/>
         <v>87.5</v>
       </c>
       <c r="D26" s="4"/>
@@ -5623,7 +5659,7 @@
         <v>45</v>
       </c>
       <c r="C27" s="23">
-        <f>AVERAGE(F27,K27)</f>
+        <f t="shared" si="0"/>
         <v>87</v>
       </c>
       <c r="D27" s="4"/>
@@ -5652,7 +5688,7 @@
         <v>36</v>
       </c>
       <c r="C28" s="23">
-        <f>AVERAGE(F28,K28)</f>
+        <f t="shared" si="0"/>
         <v>89.5</v>
       </c>
       <c r="D28" s="4"/>
@@ -5698,7 +5734,7 @@
         <v>46</v>
       </c>
       <c r="C29" s="23">
-        <f>AVERAGE(F29,K29)</f>
+        <f t="shared" si="0"/>
         <v>91</v>
       </c>
       <c r="D29" s="4"/>
@@ -5737,7 +5773,7 @@
         <v>47</v>
       </c>
       <c r="C30" s="23">
-        <f>AVERAGE(F30,K30)</f>
+        <f t="shared" si="0"/>
         <v>91</v>
       </c>
       <c r="D30" s="4"/>
@@ -5776,7 +5812,7 @@
         <v>319</v>
       </c>
       <c r="C31" s="23">
-        <f>AVERAGE(F31,K31)</f>
+        <f t="shared" si="0"/>
         <v>90</v>
       </c>
       <c r="D31" s="4"/>
@@ -5798,7 +5834,7 @@
         <v>48</v>
       </c>
       <c r="C32" s="23">
-        <f>AVERAGE(F32,K32)</f>
+        <f t="shared" si="0"/>
         <v>87</v>
       </c>
       <c r="D32" s="4"/>
@@ -5844,7 +5880,7 @@
         <v>49</v>
       </c>
       <c r="C33" s="23">
-        <f>AVERAGE(F33,K33)</f>
+        <f t="shared" si="0"/>
         <v>88</v>
       </c>
       <c r="D33" s="4"/>
@@ -5880,7 +5916,7 @@
         <v>50</v>
       </c>
       <c r="C34" s="23">
-        <f>AVERAGE(F34,K34)</f>
+        <f t="shared" si="0"/>
         <v>90</v>
       </c>
       <c r="D34" s="4"/>
@@ -5919,7 +5955,7 @@
         <v>51</v>
       </c>
       <c r="C35" s="23">
-        <f>AVERAGE(F35,K35)</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="D35" s="4"/>
@@ -5948,7 +5984,7 @@
         <v>313</v>
       </c>
       <c r="C36" s="23">
-        <f>AVERAGE(F36,K36)</f>
+        <f t="shared" si="0"/>
         <v>90</v>
       </c>
       <c r="D36" s="4"/>
@@ -5982,137 +6018,122 @@
     </row>
     <row r="37" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>52</v>
+        <v>388</v>
       </c>
       <c r="C37" s="23">
-        <f>AVERAGE(F37,K37)</f>
-        <v>75.5</v>
+        <f>AVERAGE(F37,K37,O37)</f>
+        <v>87</v>
       </c>
       <c r="D37" s="4"/>
-      <c r="E37" s="4">
-        <f>MATCH($B37,pigs!$A$3:$A$60,0)</f>
-        <v>23</v>
-      </c>
-      <c r="F37">
-        <f>INDEX(pigs!$D$3:$AO$60,$E37,F$4)</f>
-        <v>76</v>
-      </c>
-      <c r="G37">
-        <f>INDEX(pigs!$D$3:$AO$60,$E37,G$4)</f>
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="H37">
-        <f>INDEX(pigs!$D$3:$AO$60,$E37,H$4)</f>
-        <v>9</v>
-      </c>
-      <c r="J37" s="4">
-        <f>MATCH($B37,cattle!$A$3:$A$120,0)</f>
-        <v>88</v>
-      </c>
-      <c r="K37">
-        <f>INDEX(cattle!$D$3:$AH$120,$J37,K$4)</f>
-        <v>75</v>
-      </c>
-      <c r="L37" s="27">
-        <f>INDEX(cattle!$D$3:$AH$120,$J37,L$4)</f>
-        <v>12.4</v>
-      </c>
-      <c r="N37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="4"/>
+      <c r="L37" s="27"/>
+      <c r="N37" s="4">
+        <f>MATCH($B37,poultry!$A$3:$A$41,0)</f>
+        <v>25</v>
+      </c>
+      <c r="O37">
+        <f>INDEX(poultry!$D$3:$U$41,$N37,O$4)</f>
+        <v>87</v>
+      </c>
     </row>
     <row r="38" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C38" s="23">
-        <f>AVERAGE(F38,K38)</f>
-        <v>89.5</v>
+        <f t="shared" si="0"/>
+        <v>75.5</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="4">
         <f>MATCH($B38,pigs!$A$3:$A$60,0)</f>
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F38">
         <f>INDEX(pigs!$D$3:$AO$60,$E38,F$4)</f>
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="G38">
         <f>INDEX(pigs!$D$3:$AO$60,$E38,G$4)</f>
-        <v>6.9</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="H38">
         <f>INDEX(pigs!$D$3:$AO$60,$E38,H$4)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J38" s="4">
         <f>MATCH($B38,cattle!$A$3:$A$120,0)</f>
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="K38">
         <f>INDEX(cattle!$D$3:$AH$120,$J38,K$4)</f>
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="L38" s="27">
         <f>INDEX(cattle!$D$3:$AH$120,$J38,L$4)</f>
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="N38" s="4"/>
     </row>
     <row r="39" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C39" s="23">
-        <f>AVERAGE(F39,K39)</f>
-        <v>6.25</v>
+        <f t="shared" si="0"/>
+        <v>89.5</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="4">
         <f>MATCH($B39,pigs!$A$3:$A$60,0)</f>
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="F39">
         <f>INDEX(pigs!$D$3:$AO$60,$E39,F$4)</f>
-        <v>5.5</v>
+        <v>89</v>
       </c>
       <c r="G39">
         <f>INDEX(pigs!$D$3:$AO$60,$E39,G$4)</f>
-        <v>12.4</v>
+        <v>6.9</v>
       </c>
       <c r="H39">
         <f>INDEX(pigs!$D$3:$AO$60,$E39,H$4)</f>
-        <v>12.2</v>
+        <v>8</v>
       </c>
       <c r="J39" s="4">
         <f>MATCH($B39,cattle!$A$3:$A$120,0)</f>
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="K39">
         <f>INDEX(cattle!$D$3:$AH$120,$J39,K$4)</f>
-        <v>7</v>
+        <v>90</v>
       </c>
       <c r="L39" s="27">
         <f>INDEX(cattle!$D$3:$AH$120,$J39,L$4)</f>
-        <v>13.6</v>
+        <v>12.3</v>
       </c>
       <c r="N39" s="4"/>
     </row>
     <row r="40" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C40" s="23">
-        <f>AVERAGE(F40,K40)</f>
-        <v>97</v>
+        <f t="shared" si="0"/>
+        <v>6.25</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="4">
         <f>MATCH($B40,pigs!$A$3:$A$60,0)</f>
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F40">
         <f>INDEX(pigs!$D$3:$AO$60,$E40,F$4)</f>
-        <v>97</v>
+        <v>5.5</v>
       </c>
       <c r="G40">
         <f>INDEX(pigs!$D$3:$AO$60,$E40,G$4)</f>
@@ -6122,68 +6143,61 @@
         <f>INDEX(pigs!$D$3:$AO$60,$E40,H$4)</f>
         <v>12.2</v>
       </c>
-      <c r="J40" s="4"/>
-      <c r="L40" s="27"/>
+      <c r="J40" s="4">
+        <f>MATCH($B40,cattle!$A$3:$A$120,0)</f>
+        <v>57</v>
+      </c>
+      <c r="K40">
+        <f>INDEX(cattle!$D$3:$AH$120,$J40,K$4)</f>
+        <v>7</v>
+      </c>
+      <c r="L40" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$J40,L$4)</f>
+        <v>13.6</v>
+      </c>
       <c r="N40" s="4"/>
     </row>
     <row r="41" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C41" s="23">
-        <f>AVERAGE(F41,K41)</f>
-        <v>91</v>
+        <f t="shared" si="0"/>
+        <v>97</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="4">
         <f>MATCH($B41,pigs!$A$3:$A$60,0)</f>
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="F41">
         <f>INDEX(pigs!$D$3:$AO$60,$E41,F$4)</f>
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G41">
         <f>INDEX(pigs!$D$3:$AO$60,$E41,G$4)</f>
-        <v>11.1</v>
+        <v>12.4</v>
       </c>
       <c r="H41">
         <f>INDEX(pigs!$D$3:$AO$60,$E41,H$4)</f>
-        <v>11.3</v>
-      </c>
-      <c r="J41" s="4">
-        <f>MATCH($B41,cattle!$A$3:$A$120,0)</f>
-        <v>65</v>
-      </c>
-      <c r="K41">
-        <f>INDEX(cattle!$D$3:$AH$120,$J41,K$4)</f>
-        <v>90</v>
-      </c>
-      <c r="L41" s="27">
-        <f>INDEX(cattle!$D$3:$AH$120,$J41,L$4)</f>
-        <v>15.5</v>
-      </c>
-      <c r="N41" s="4">
-        <f>MATCH($B41,poultry!$A$3:$A$41,0)</f>
-        <v>28</v>
-      </c>
-      <c r="O41">
-        <f>INDEX(poultry!$D$3:$U$41,$N41,O$4)</f>
-        <v>90</v>
-      </c>
+        <v>12.2</v>
+      </c>
+      <c r="J41" s="4"/>
+      <c r="L41" s="27"/>
+      <c r="N41" s="4"/>
     </row>
     <row r="42" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C42" s="23">
-        <f>AVERAGE(F42,K42)</f>
-        <v>92</v>
+        <f t="shared" si="0"/>
+        <v>91</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="4">
         <f>MATCH($B42,pigs!$A$3:$A$60,0)</f>
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="F42">
         <f>INDEX(pigs!$D$3:$AO$60,$E42,F$4)</f>
@@ -6191,19 +6205,65 @@
       </c>
       <c r="G42">
         <f>INDEX(pigs!$D$3:$AO$60,$E42,G$4)</f>
-        <v>10.8</v>
+        <v>11.1</v>
       </c>
       <c r="H42">
         <f>INDEX(pigs!$D$3:$AO$60,$E42,H$4)</f>
-        <v>10.8</v>
-      </c>
-      <c r="J42" s="4"/>
+        <v>11.3</v>
+      </c>
+      <c r="J42" s="4">
+        <f>MATCH($B42,cattle!$A$3:$A$120,0)</f>
+        <v>65</v>
+      </c>
+      <c r="K42">
+        <f>INDEX(cattle!$D$3:$AH$120,$J42,K$4)</f>
+        <v>90</v>
+      </c>
+      <c r="L42" s="27">
+        <f>INDEX(cattle!$D$3:$AH$120,$J42,L$4)</f>
+        <v>15.5</v>
+      </c>
       <c r="N42" s="4">
         <f>MATCH($B42,poultry!$A$3:$A$41,0)</f>
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="O42">
         <f>INDEX(poultry!$D$3:$U$41,$N42,O$4)</f>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>57</v>
+      </c>
+      <c r="C43" s="23">
+        <f t="shared" si="0"/>
+        <v>92</v>
+      </c>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4">
+        <f>MATCH($B43,pigs!$A$3:$A$60,0)</f>
+        <v>7</v>
+      </c>
+      <c r="F43">
+        <f>INDEX(pigs!$D$3:$AO$60,$E43,F$4)</f>
+        <v>92</v>
+      </c>
+      <c r="G43">
+        <f>INDEX(pigs!$D$3:$AO$60,$E43,G$4)</f>
+        <v>10.8</v>
+      </c>
+      <c r="H43">
+        <f>INDEX(pigs!$D$3:$AO$60,$E43,H$4)</f>
+        <v>10.8</v>
+      </c>
+      <c r="J43" s="4"/>
+      <c r="N43" s="4">
+        <f>MATCH($B43,poultry!$A$3:$A$41,0)</f>
+        <v>6</v>
+      </c>
+      <c r="O43">
+        <f>INDEX(poultry!$D$3:$U$41,$N43,O$4)</f>
         <v>92</v>
       </c>
     </row>

--- a/data/prod_parameters/FeedMgmt.xlsx
+++ b/data/prod_parameters/FeedMgmt.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="397">
   <si>
     <t>f_feed</t>
   </si>
@@ -1220,6 +1220,12 @@
   </si>
   <si>
     <t>Borde denna vara 100%? Vad är den tröskade majsarealen?</t>
+  </si>
+  <si>
+    <t>horses</t>
+  </si>
+  <si>
+    <t>Horses</t>
   </si>
 </sst>
 </file>
@@ -1696,7 +1702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O195"/>
+  <dimension ref="A1:O197"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="7" width="20.28515625" customWidth="1"/>
@@ -2871,7 +2877,24 @@
       <c r="M65" s="3"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K66" s="3"/>
+      <c r="A66" t="s">
+        <v>395</v>
+      </c>
+      <c r="G66" t="s">
+        <v>334</v>
+      </c>
+      <c r="H66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J66" t="s">
+        <v>335</v>
+      </c>
+      <c r="K66" s="3">
+        <v>10</v>
+      </c>
+      <c r="L66" t="s">
+        <v>28</v>
+      </c>
       <c r="M66" s="3"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
@@ -3987,81 +4010,90 @@
       </c>
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K140" s="3"/>
+      <c r="A140" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="B140" s="7"/>
+      <c r="C140" s="6"/>
+      <c r="D140" s="6"/>
+      <c r="E140" s="6"/>
+      <c r="F140" s="6"/>
+      <c r="G140" s="6"/>
+      <c r="H140" s="6"/>
+      <c r="I140" s="6"/>
+      <c r="J140" s="6"/>
+      <c r="K140" s="6"/>
+      <c r="L140" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M140" s="6"/>
+      <c r="N140" s="6"/>
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A141" s="8" t="s">
+      <c r="A141" t="s">
+        <v>395</v>
+      </c>
+      <c r="F141" t="s">
+        <v>2</v>
+      </c>
+      <c r="J141" t="s">
+        <v>18</v>
+      </c>
+      <c r="K141" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>395</v>
+      </c>
+      <c r="F142" t="s">
+        <v>33</v>
+      </c>
+      <c r="J142" t="s">
+        <v>18</v>
+      </c>
+      <c r="K142" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A143" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B141" s="8"/>
-      <c r="C141" s="9"/>
-      <c r="D141" s="9"/>
-      <c r="E141" s="9"/>
-      <c r="F141" s="9"/>
-      <c r="G141" s="9"/>
-      <c r="H141" s="9"/>
-      <c r="I141" s="9"/>
-      <c r="J141" s="9"/>
-      <c r="K141" s="9"/>
-      <c r="L141" s="9"/>
-      <c r="M141" s="9"/>
-      <c r="N141" s="9"/>
-    </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A142" s="30" t="s">
+      <c r="B143" s="8"/>
+      <c r="C143" s="9"/>
+      <c r="D143" s="9"/>
+      <c r="E143" s="9"/>
+      <c r="F143" s="9"/>
+      <c r="G143" s="9"/>
+      <c r="H143" s="9"/>
+      <c r="I143" s="9"/>
+      <c r="J143" s="9"/>
+      <c r="K143" s="9"/>
+      <c r="L143" s="9"/>
+      <c r="M143" s="9"/>
+      <c r="N143" s="9"/>
+    </row>
+    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A144" s="30" t="s">
         <v>391</v>
       </c>
-      <c r="B142" s="31"/>
-      <c r="C142" s="32"/>
-      <c r="D142" s="32"/>
-      <c r="E142" s="32"/>
-      <c r="F142" s="32"/>
-      <c r="G142" s="32"/>
-      <c r="H142" s="32"/>
-      <c r="I142" s="32"/>
-      <c r="J142" s="32"/>
-      <c r="K142" s="32"/>
-      <c r="L142" s="32" t="s">
+      <c r="B144" s="31"/>
+      <c r="C144" s="32"/>
+      <c r="D144" s="32"/>
+      <c r="E144" s="32"/>
+      <c r="F144" s="32"/>
+      <c r="G144" s="32"/>
+      <c r="H144" s="32"/>
+      <c r="I144" s="32"/>
+      <c r="J144" s="32"/>
+      <c r="K144" s="32"/>
+      <c r="L144" s="32" t="s">
         <v>300</v>
       </c>
-      <c r="M142" s="32"/>
-      <c r="N142" s="32"/>
-    </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>25</v>
-      </c>
-      <c r="E143" t="s">
-        <v>299</v>
-      </c>
-      <c r="F143" t="s">
-        <v>17</v>
-      </c>
-      <c r="J143" t="s">
-        <v>18</v>
-      </c>
-      <c r="K143" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F143,'feed pars'!B$6:B$43,0))</f>
-        <v>12.3</v>
-      </c>
-    </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>25</v>
-      </c>
-      <c r="E144" t="s">
-        <v>299</v>
-      </c>
-      <c r="F144" t="s">
-        <v>37</v>
-      </c>
-      <c r="J144" t="s">
-        <v>18</v>
-      </c>
-      <c r="K144" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F144,'feed pars'!B$6:B$43,0))</f>
-        <v>11.2</v>
-      </c>
+      <c r="M144" s="32"/>
+      <c r="N144" s="32"/>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
@@ -4071,14 +4103,14 @@
         <v>299</v>
       </c>
       <c r="F145" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="J145" t="s">
         <v>18</v>
       </c>
       <c r="K145" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F145,'feed pars'!B$6:B$43,0))</f>
-        <v>9.4</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
@@ -4089,14 +4121,14 @@
         <v>299</v>
       </c>
       <c r="F146" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="J146" t="s">
         <v>18</v>
       </c>
       <c r="K146" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F146,'feed pars'!B$6:B$43,0))</f>
-        <v>12</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
@@ -4107,14 +4139,14 @@
         <v>299</v>
       </c>
       <c r="F147" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J147" t="s">
         <v>18</v>
       </c>
       <c r="K147" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F147,'feed pars'!B$6:B$43,0))</f>
-        <v>13.2</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
@@ -4125,14 +4157,14 @@
         <v>299</v>
       </c>
       <c r="F148" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J148" t="s">
         <v>18</v>
       </c>
       <c r="K148" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F148,'feed pars'!B$6:B$43,0))</f>
-        <v>11.5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
@@ -4143,14 +4175,14 @@
         <v>299</v>
       </c>
       <c r="F149" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J149" t="s">
         <v>18</v>
       </c>
       <c r="K149" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F149,'feed pars'!B$6:B$43,0))</f>
-        <v>10.9</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
@@ -4161,14 +4193,14 @@
         <v>299</v>
       </c>
       <c r="F150" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J150" t="s">
         <v>18</v>
       </c>
       <c r="K150" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F150,'feed pars'!B$6:B$43,0))</f>
-        <v>18.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
@@ -4179,14 +4211,14 @@
         <v>299</v>
       </c>
       <c r="F151" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J151" t="s">
         <v>18</v>
       </c>
       <c r="K151" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F151,'feed pars'!B$6:B$43,0))</f>
-        <v>17.5</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
@@ -4197,14 +4229,14 @@
         <v>299</v>
       </c>
       <c r="F152" t="s">
-        <v>314</v>
+        <v>35</v>
       </c>
       <c r="J152" t="s">
         <v>18</v>
       </c>
       <c r="K152" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F152,'feed pars'!B$6:B$43,0))</f>
-        <v>29.8</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
@@ -4215,14 +4247,14 @@
         <v>299</v>
       </c>
       <c r="F153" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J153" t="s">
         <v>18</v>
       </c>
       <c r="K153" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F153,'feed pars'!B$6:B$43,0))</f>
-        <v>9.9</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
@@ -4233,14 +4265,14 @@
         <v>299</v>
       </c>
       <c r="F154" t="s">
-        <v>45</v>
+        <v>314</v>
       </c>
       <c r="J154" t="s">
         <v>18</v>
       </c>
       <c r="K154" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F154,'feed pars'!B$6:B$43,0))</f>
-        <v>10.3</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
@@ -4251,14 +4283,14 @@
         <v>299</v>
       </c>
       <c r="F155" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J155" t="s">
         <v>18</v>
       </c>
       <c r="K155" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F155,'feed pars'!B$6:B$43,0))</f>
-        <v>7.7</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.25">
@@ -4269,14 +4301,14 @@
         <v>299</v>
       </c>
       <c r="F156" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J156" t="s">
         <v>18</v>
       </c>
       <c r="K156" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F156,'feed pars'!B$6:B$43,0))</f>
-        <v>6.5</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
@@ -4287,14 +4319,14 @@
         <v>299</v>
       </c>
       <c r="F157" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="J157" t="s">
         <v>18</v>
       </c>
       <c r="K157" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F157,'feed pars'!B$6:B$43,0))</f>
-        <v>6.2</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
@@ -4305,14 +4337,14 @@
         <v>299</v>
       </c>
       <c r="F158" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J158" t="s">
         <v>18</v>
       </c>
       <c r="K158" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F158,'feed pars'!B$6:B$43,0))</f>
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
@@ -4323,14 +4355,14 @@
         <v>299</v>
       </c>
       <c r="F159" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J159" t="s">
         <v>18</v>
       </c>
       <c r="K159" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F159,'feed pars'!B$6:B$43,0))</f>
-        <v>9.1999999999999993</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
@@ -4341,14 +4373,14 @@
         <v>299</v>
       </c>
       <c r="F160" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J160" t="s">
         <v>18</v>
       </c>
       <c r="K160" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F160,'feed pars'!B$6:B$43,0))</f>
-        <v>8.6999999999999993</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.25">
@@ -4359,14 +4391,14 @@
         <v>299</v>
       </c>
       <c r="F161" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J161" t="s">
         <v>18</v>
       </c>
       <c r="K161" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F161,'feed pars'!B$6:B$43,0))</f>
-        <v>8.9</v>
+        <v>9.1999999999999993</v>
       </c>
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.25">
@@ -4377,14 +4409,14 @@
         <v>299</v>
       </c>
       <c r="F162" t="s">
-        <v>313</v>
+        <v>50</v>
       </c>
       <c r="J162" t="s">
         <v>18</v>
       </c>
       <c r="K162" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F162,'feed pars'!B$6:B$43,0))</f>
-        <v>7.0888888888888877</v>
+        <v>8.6999999999999993</v>
       </c>
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.25">
@@ -4395,14 +4427,14 @@
         <v>299</v>
       </c>
       <c r="F163" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J163" t="s">
         <v>18</v>
       </c>
       <c r="K163" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F163,'feed pars'!B$6:B$43,0))</f>
-        <v>9</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.25">
@@ -4413,14 +4445,14 @@
         <v>299</v>
       </c>
       <c r="F164" t="s">
-        <v>53</v>
+        <v>313</v>
       </c>
       <c r="J164" t="s">
         <v>18</v>
       </c>
       <c r="K164" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F164,'feed pars'!B$6:B$43,0))</f>
-        <v>8</v>
+        <v>7.0888888888888877</v>
       </c>
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.25">
@@ -4431,14 +4463,14 @@
         <v>299</v>
       </c>
       <c r="F165" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J165" t="s">
         <v>18</v>
       </c>
       <c r="K165" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F165,'feed pars'!B$6:B$43,0))</f>
-        <v>12.2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.25">
@@ -4449,14 +4481,14 @@
         <v>299</v>
       </c>
       <c r="F166" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J166" t="s">
         <v>18</v>
       </c>
       <c r="K166" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F166,'feed pars'!B$6:B$43,0))</f>
-        <v>12.2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.25">
@@ -4467,14 +4499,14 @@
         <v>299</v>
       </c>
       <c r="F167" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J167" t="s">
         <v>18</v>
       </c>
       <c r="K167" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F167,'feed pars'!B$6:B$43,0))</f>
-        <v>11.3</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.25">
@@ -4485,79 +4517,85 @@
         <v>299</v>
       </c>
       <c r="F168" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J168" t="s">
         <v>18</v>
       </c>
       <c r="K168" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F168,'feed pars'!B$6:B$43,0))</f>
-        <v>10.8</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A169" s="30" t="s">
-        <v>392</v>
-      </c>
-      <c r="B169" s="31"/>
-      <c r="C169" s="32"/>
-      <c r="D169" s="32"/>
-      <c r="E169" s="32"/>
-      <c r="F169" s="32"/>
-      <c r="G169" s="32"/>
-      <c r="H169" s="32"/>
-      <c r="I169" s="32"/>
-      <c r="J169" s="32"/>
-      <c r="K169" s="32"/>
-      <c r="L169" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="M169" s="32"/>
-      <c r="N169" s="32"/>
+      <c r="A169" t="s">
+        <v>25</v>
+      </c>
+      <c r="E169" t="s">
+        <v>299</v>
+      </c>
+      <c r="F169" t="s">
+        <v>56</v>
+      </c>
+      <c r="J169" t="s">
+        <v>18</v>
+      </c>
+      <c r="K169" s="26">
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F169,'feed pars'!B$6:B$43,0))</f>
+        <v>11.3</v>
+      </c>
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>25</v>
       </c>
+      <c r="E170" t="s">
+        <v>299</v>
+      </c>
       <c r="F170" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="J170" t="s">
         <v>18</v>
       </c>
       <c r="K170" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F170,'feed pars'!B$6:B$43,0))</f>
-        <v>12.1</v>
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F170,'feed pars'!B$6:B$43,0))</f>
+        <v>10.8</v>
       </c>
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
-        <v>25</v>
-      </c>
-      <c r="F171" t="s">
-        <v>37</v>
-      </c>
-      <c r="J171" t="s">
-        <v>18</v>
-      </c>
-      <c r="K171" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F171,'feed pars'!B$6:B$43,0))</f>
-        <v>11</v>
-      </c>
+      <c r="A171" s="30" t="s">
+        <v>392</v>
+      </c>
+      <c r="B171" s="31"/>
+      <c r="C171" s="32"/>
+      <c r="D171" s="32"/>
+      <c r="E171" s="32"/>
+      <c r="F171" s="32"/>
+      <c r="G171" s="32"/>
+      <c r="H171" s="32"/>
+      <c r="I171" s="32"/>
+      <c r="J171" s="32"/>
+      <c r="K171" s="32"/>
+      <c r="L171" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="M171" s="32"/>
+      <c r="N171" s="32"/>
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>25</v>
       </c>
       <c r="F172" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="J172" t="s">
         <v>18</v>
       </c>
       <c r="K172" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F172,'feed pars'!B$6:B$43,0))</f>
-        <v>9</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.25">
@@ -4565,14 +4603,14 @@
         <v>25</v>
       </c>
       <c r="F173" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="J173" t="s">
         <v>18</v>
       </c>
       <c r="K173" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F173,'feed pars'!B$6:B$43,0))</f>
-        <v>11.9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.25">
@@ -4580,14 +4618,14 @@
         <v>25</v>
       </c>
       <c r="F174" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J174" t="s">
         <v>18</v>
       </c>
       <c r="K174" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F174,'feed pars'!B$6:B$43,0))</f>
-        <v>12.8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.25">
@@ -4595,14 +4633,14 @@
         <v>25</v>
       </c>
       <c r="F175" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J175" t="s">
         <v>18</v>
       </c>
       <c r="K175" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F175,'feed pars'!B$6:B$43,0))</f>
-        <v>11.2</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.25">
@@ -4610,14 +4648,14 @@
         <v>25</v>
       </c>
       <c r="F176" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J176" t="s">
         <v>18</v>
       </c>
       <c r="K176" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F176,'feed pars'!B$6:B$43,0))</f>
-        <v>10.7</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
@@ -4625,14 +4663,14 @@
         <v>25</v>
       </c>
       <c r="F177" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J177" t="s">
         <v>18</v>
       </c>
       <c r="K177" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F177,'feed pars'!B$6:B$43,0))</f>
-        <v>18</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
@@ -4640,14 +4678,14 @@
         <v>25</v>
       </c>
       <c r="F178" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J178" t="s">
         <v>18</v>
       </c>
       <c r="K178" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F178,'feed pars'!B$6:B$43,0))</f>
-        <v>17.3</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
@@ -4655,14 +4693,14 @@
         <v>25</v>
       </c>
       <c r="F179" t="s">
-        <v>314</v>
+        <v>35</v>
       </c>
       <c r="J179" t="s">
         <v>18</v>
       </c>
       <c r="K179" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F179,'feed pars'!B$6:B$43,0))</f>
-        <v>29.8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
@@ -4670,14 +4708,14 @@
         <v>25</v>
       </c>
       <c r="F180" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J180" t="s">
         <v>18</v>
       </c>
       <c r="K180" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F180,'feed pars'!B$6:B$43,0))</f>
-        <v>9.3000000000000007</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
@@ -4685,14 +4723,14 @@
         <v>25</v>
       </c>
       <c r="F181" t="s">
-        <v>45</v>
+        <v>314</v>
       </c>
       <c r="J181" t="s">
         <v>18</v>
       </c>
       <c r="K181" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F181,'feed pars'!B$6:B$43,0))</f>
-        <v>9.6999999999999993</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
@@ -4700,14 +4738,14 @@
         <v>25</v>
       </c>
       <c r="F182" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J182" t="s">
         <v>18</v>
       </c>
       <c r="K182" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F182,'feed pars'!B$6:B$43,0))</f>
-        <v>7.1</v>
+        <v>9.3000000000000007</v>
       </c>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.25">
@@ -4715,14 +4753,14 @@
         <v>25</v>
       </c>
       <c r="F183" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J183" t="s">
         <v>18</v>
       </c>
       <c r="K183" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F183,'feed pars'!B$6:B$43,0))</f>
-        <v>5.9</v>
+        <v>9.6999999999999993</v>
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.25">
@@ -4730,14 +4768,14 @@
         <v>25</v>
       </c>
       <c r="F184" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="J184" t="s">
         <v>18</v>
       </c>
       <c r="K184" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F184,'feed pars'!B$6:B$43,0))</f>
-        <v>5.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.25">
@@ -4745,14 +4783,14 @@
         <v>25</v>
       </c>
       <c r="F185" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J185" t="s">
         <v>18</v>
       </c>
       <c r="K185" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F185,'feed pars'!B$6:B$43,0))</f>
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.25">
@@ -4760,14 +4798,14 @@
         <v>25</v>
       </c>
       <c r="F186" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J186" t="s">
         <v>18</v>
       </c>
       <c r="K186" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F186,'feed pars'!B$6:B$43,0))</f>
-        <v>8.6999999999999993</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.25">
@@ -4775,14 +4813,14 @@
         <v>25</v>
       </c>
       <c r="F187" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J187" t="s">
         <v>18</v>
       </c>
       <c r="K187" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F187,'feed pars'!B$6:B$43,0))</f>
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
@@ -4790,14 +4828,14 @@
         <v>25</v>
       </c>
       <c r="F188" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J188" t="s">
         <v>18</v>
       </c>
       <c r="K188" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F188,'feed pars'!B$6:B$43,0))</f>
-        <v>8.1999999999999993</v>
+        <v>8.6999999999999993</v>
       </c>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.25">
@@ -4805,14 +4843,14 @@
         <v>25</v>
       </c>
       <c r="F189" t="s">
-        <v>313</v>
+        <v>50</v>
       </c>
       <c r="J189" t="s">
         <v>18</v>
       </c>
       <c r="K189" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F189,'feed pars'!B$6:B$43,0))</f>
-        <v>6.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.25">
@@ -4820,14 +4858,14 @@
         <v>25</v>
       </c>
       <c r="F190" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J190" t="s">
         <v>18</v>
       </c>
       <c r="K190" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F190,'feed pars'!B$6:B$43,0))</f>
-        <v>8.6999999999999993</v>
+        <v>8.1999999999999993</v>
       </c>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.25">
@@ -4835,14 +4873,14 @@
         <v>25</v>
       </c>
       <c r="F191" t="s">
-        <v>53</v>
+        <v>313</v>
       </c>
       <c r="J191" t="s">
         <v>18</v>
       </c>
       <c r="K191" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F191,'feed pars'!B$6:B$43,0))</f>
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.25">
@@ -4850,14 +4888,14 @@
         <v>25</v>
       </c>
       <c r="F192" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J192" t="s">
         <v>18</v>
       </c>
       <c r="K192" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F192,'feed pars'!B$6:B$43,0))</f>
-        <v>12.4</v>
+        <v>8.6999999999999993</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.25">
@@ -4865,14 +4903,14 @@
         <v>25</v>
       </c>
       <c r="F193" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J193" t="s">
         <v>18</v>
       </c>
       <c r="K193" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F193,'feed pars'!B$6:B$43,0))</f>
-        <v>12.4</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.25">
@@ -4880,14 +4918,14 @@
         <v>25</v>
       </c>
       <c r="F194" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J194" t="s">
         <v>18</v>
       </c>
       <c r="K194" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F194,'feed pars'!B$6:B$43,0))</f>
-        <v>11.1</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.25">
@@ -4895,13 +4933,43 @@
         <v>25</v>
       </c>
       <c r="F195" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J195" t="s">
         <v>18</v>
       </c>
       <c r="K195" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F195,'feed pars'!B$6:B$43,0))</f>
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>25</v>
+      </c>
+      <c r="F196" t="s">
+        <v>56</v>
+      </c>
+      <c r="J196" t="s">
+        <v>18</v>
+      </c>
+      <c r="K196" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F196,'feed pars'!B$6:B$43,0))</f>
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>25</v>
+      </c>
+      <c r="F197" t="s">
+        <v>57</v>
+      </c>
+      <c r="J197" t="s">
+        <v>18</v>
+      </c>
+      <c r="K197" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F197,'feed pars'!B$6:B$43,0))</f>
         <v>10.8</v>
       </c>
     </row>

--- a/data/prod_parameters/FeedMgmt.xlsx
+++ b/data/prod_parameters/FeedMgmt.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="410">
   <si>
     <t>f_feed</t>
   </si>
@@ -1227,6 +1227,45 @@
   <si>
     <t>Horses</t>
   </si>
+  <si>
+    <t>storage_losses</t>
+  </si>
+  <si>
+    <t>feeding_losses</t>
+  </si>
+  <si>
+    <t>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</t>
+  </si>
+  <si>
+    <t>Storage and feeding losses</t>
+  </si>
+  <si>
+    <t>100% - pasture utilisation</t>
+  </si>
+  <si>
+    <t>sheep</t>
+  </si>
+  <si>
+    <t>80% in silo</t>
+  </si>
+  <si>
+    <t>60% in silo</t>
+  </si>
+  <si>
+    <t>0% in silo</t>
+  </si>
+  <si>
+    <t>No feeding on pasture</t>
+  </si>
+  <si>
+    <t>10% feeding on pasture</t>
+  </si>
+  <si>
+    <t>Need to add losses for grains and concentrates</t>
+  </si>
+  <si>
+    <t>No storage</t>
+  </si>
 </sst>
 </file>
 
@@ -1235,7 +1274,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1297,6 +1336,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="2" tint="-0.499984740745262"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1371,7 +1417,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1421,6 +1467,7 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1702,7 +1749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O197"/>
+  <dimension ref="A1:O242"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="7" width="20.28515625" customWidth="1"/>
@@ -2902,2074 +2949,3208 @@
       <c r="M67" s="3"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K68" s="3"/>
-      <c r="M68" s="3"/>
+      <c r="A68" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2"/>
+      <c r="L68" s="2"/>
+      <c r="M68" s="2"/>
+      <c r="N68" s="2"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B69" s="1"/>
-      <c r="C69" s="1"/>
-      <c r="D69" s="1"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
-      <c r="H69" s="2"/>
-      <c r="I69" s="2"/>
-      <c r="J69" s="2"/>
-      <c r="K69" s="2"/>
-      <c r="L69" s="2"/>
-      <c r="M69" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="N69" s="2"/>
+      <c r="J69" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="K69" s="10">
+        <v>0</v>
+      </c>
+      <c r="L69" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="M69" s="10" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F70" t="s">
+      <c r="J70" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="K70" s="10">
+        <v>0</v>
+      </c>
+      <c r="L70" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="M70" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>24</v>
+      </c>
+      <c r="B71" t="s">
+        <v>326</v>
+      </c>
+      <c r="E71" t="s">
+        <v>327</v>
+      </c>
+      <c r="F71" t="s">
         <v>310</v>
       </c>
-      <c r="J70" t="s">
-        <v>390</v>
-      </c>
-      <c r="K70" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F70,'feed pars'!B$6:B$43,0))</f>
-        <v>100</v>
-      </c>
-      <c r="L70" t="s">
+      <c r="J71" s="29" t="s">
+        <v>397</v>
+      </c>
+      <c r="K71" s="29">
+        <f>(0.8*20+0.2*2)</f>
+        <v>16.399999999999999</v>
+      </c>
+      <c r="L71" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="M70" s="29" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F71" t="s">
+      <c r="M71" s="29" t="s">
+        <v>403</v>
+      </c>
+      <c r="N71" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>24</v>
+      </c>
+      <c r="F72" t="s">
+        <v>310</v>
+      </c>
+      <c r="J72" s="29" t="s">
+        <v>397</v>
+      </c>
+      <c r="K72" s="29">
+        <f>(0.6*20+0.4*2)</f>
+        <v>12.8</v>
+      </c>
+      <c r="L72" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="M72" s="29" t="s">
+        <v>404</v>
+      </c>
+      <c r="N72" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>402</v>
+      </c>
+      <c r="F73" t="s">
+        <v>310</v>
+      </c>
+      <c r="J73" s="29" t="s">
+        <v>397</v>
+      </c>
+      <c r="K73" s="29">
+        <v>2</v>
+      </c>
+      <c r="L73" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="M73" s="29" t="s">
+        <v>405</v>
+      </c>
+      <c r="N73" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>395</v>
+      </c>
+      <c r="F74" t="s">
+        <v>310</v>
+      </c>
+      <c r="J74" s="29" t="s">
+        <v>397</v>
+      </c>
+      <c r="K74" s="29">
+        <v>2</v>
+      </c>
+      <c r="L74" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="M74" s="29" t="s">
+        <v>405</v>
+      </c>
+      <c r="N74" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>24</v>
+      </c>
+      <c r="B75" t="s">
+        <v>326</v>
+      </c>
+      <c r="E75" t="s">
+        <v>327</v>
+      </c>
+      <c r="F75" t="s">
+        <v>310</v>
+      </c>
+      <c r="J75" s="29" t="s">
+        <v>398</v>
+      </c>
+      <c r="K75" s="29">
+        <v>5</v>
+      </c>
+      <c r="L75" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="M75" s="29" t="s">
+        <v>406</v>
+      </c>
+      <c r="N75" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>24</v>
+      </c>
+      <c r="E76" t="s">
+        <v>329</v>
+      </c>
+      <c r="F76" t="s">
+        <v>310</v>
+      </c>
+      <c r="J76" s="29" t="s">
+        <v>398</v>
+      </c>
+      <c r="K76" s="29">
+        <v>5</v>
+      </c>
+      <c r="L76" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="M76" s="29" t="s">
+        <v>406</v>
+      </c>
+      <c r="N76" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>24</v>
+      </c>
+      <c r="F77" t="s">
+        <v>310</v>
+      </c>
+      <c r="J77" s="29" t="s">
+        <v>398</v>
+      </c>
+      <c r="K77" s="29">
+        <f>0.9*5+0.1*15</f>
+        <v>6</v>
+      </c>
+      <c r="L77" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="M77" s="29" t="s">
+        <v>407</v>
+      </c>
+      <c r="N77" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>402</v>
+      </c>
+      <c r="F78" t="s">
+        <v>310</v>
+      </c>
+      <c r="J78" s="29" t="s">
+        <v>398</v>
+      </c>
+      <c r="K78" s="29">
+        <v>15</v>
+      </c>
+      <c r="L78" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="M78" s="29"/>
+      <c r="N78" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>395</v>
+      </c>
+      <c r="F79" t="s">
+        <v>310</v>
+      </c>
+      <c r="J79" s="29" t="s">
+        <v>398</v>
+      </c>
+      <c r="K79" s="29">
+        <v>15</v>
+      </c>
+      <c r="L79" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="M79" s="29"/>
+      <c r="N79" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A80" s="33" t="str">
+        <f>A71</f>
+        <v>cattle</v>
+      </c>
+      <c r="B80" s="33" t="str">
+        <f>B71</f>
+        <v>dairy</v>
+      </c>
+      <c r="E80" s="33" t="str">
+        <f>E71</f>
+        <v>cows</v>
+      </c>
+      <c r="F80" t="s">
         <v>311</v>
       </c>
-      <c r="J71" t="s">
-        <v>390</v>
-      </c>
-      <c r="K71" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F71,'feed pars'!B$6:B$43,0))</f>
-        <v>100</v>
-      </c>
-      <c r="L71" t="s">
+      <c r="J80" s="33" t="str">
+        <f>J71</f>
+        <v>storage_losses</v>
+      </c>
+      <c r="K80" s="33">
+        <f>K71</f>
+        <v>16.399999999999999</v>
+      </c>
+      <c r="L80" s="33" t="str">
+        <f>L71</f>
+        <v>%</v>
+      </c>
+      <c r="M80" s="33" t="str">
+        <f>M71</f>
+        <v>80% in silo</v>
+      </c>
+      <c r="N80" s="33" t="str">
+        <f>N71</f>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A81" s="33" t="str">
+        <f t="shared" ref="A81:A88" si="0">A72</f>
+        <v>cattle</v>
+      </c>
+      <c r="F81" t="s">
+        <v>311</v>
+      </c>
+      <c r="J81" s="33" t="str">
+        <f t="shared" ref="J81:N88" si="1">J72</f>
+        <v>storage_losses</v>
+      </c>
+      <c r="K81" s="33">
+        <f t="shared" si="1"/>
+        <v>12.8</v>
+      </c>
+      <c r="L81" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>%</v>
+      </c>
+      <c r="M81" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>60% in silo</v>
+      </c>
+      <c r="N81" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A82" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>sheep</v>
+      </c>
+      <c r="F82" t="s">
+        <v>311</v>
+      </c>
+      <c r="J82" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>storage_losses</v>
+      </c>
+      <c r="K82" s="33">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L82" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>%</v>
+      </c>
+      <c r="M82" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>0% in silo</v>
+      </c>
+      <c r="N82" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A83" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>horses</v>
+      </c>
+      <c r="F83" t="s">
+        <v>311</v>
+      </c>
+      <c r="J83" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>storage_losses</v>
+      </c>
+      <c r="K83" s="33">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L83" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>%</v>
+      </c>
+      <c r="M83" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>0% in silo</v>
+      </c>
+      <c r="N83" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A84" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>cattle</v>
+      </c>
+      <c r="B84" s="33" t="str">
+        <f>B75</f>
+        <v>dairy</v>
+      </c>
+      <c r="E84" s="33" t="str">
+        <f>E75</f>
+        <v>cows</v>
+      </c>
+      <c r="F84" t="s">
+        <v>311</v>
+      </c>
+      <c r="J84" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K84" s="33">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="L84" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>%</v>
+      </c>
+      <c r="M84" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>No feeding on pasture</v>
+      </c>
+      <c r="N84" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A85" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>cattle</v>
+      </c>
+      <c r="E85" s="33" t="str">
+        <f>E76</f>
+        <v>bulls</v>
+      </c>
+      <c r="F85" t="s">
+        <v>311</v>
+      </c>
+      <c r="J85" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K85" s="33">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="L85" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>%</v>
+      </c>
+      <c r="M85" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>No feeding on pasture</v>
+      </c>
+      <c r="N85" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A86" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>cattle</v>
+      </c>
+      <c r="F86" t="s">
+        <v>311</v>
+      </c>
+      <c r="J86" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K86" s="33">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="L86" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>%</v>
+      </c>
+      <c r="M86" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>10% feeding on pasture</v>
+      </c>
+      <c r="N86" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A87" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>sheep</v>
+      </c>
+      <c r="F87" t="s">
+        <v>311</v>
+      </c>
+      <c r="J87" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K87" s="33">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="L87" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>%</v>
+      </c>
+      <c r="M87" s="33"/>
+      <c r="N87" s="33" t="str">
+        <f t="shared" ref="N87:N88" si="2">N78</f>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A88" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>horses</v>
+      </c>
+      <c r="F88" t="s">
+        <v>311</v>
+      </c>
+      <c r="J88" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K88" s="33">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="L88" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>%</v>
+      </c>
+      <c r="M88" s="33"/>
+      <c r="N88" s="33" t="str">
+        <f t="shared" si="2"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A89" s="33"/>
+      <c r="B89" s="33"/>
+      <c r="E89" s="33"/>
+      <c r="F89" t="s">
+        <v>312</v>
+      </c>
+      <c r="J89" s="29" t="s">
+        <v>397</v>
+      </c>
+      <c r="K89" s="29">
+        <v>5</v>
+      </c>
+      <c r="L89" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F72" t="s">
+      <c r="M89" s="29"/>
+      <c r="N89" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A90" s="33" t="str">
+        <f>A75</f>
+        <v>cattle</v>
+      </c>
+      <c r="B90" s="33" t="str">
+        <f>B75</f>
+        <v>dairy</v>
+      </c>
+      <c r="E90" s="33" t="str">
+        <f t="shared" ref="E90:E91" si="3">E75</f>
+        <v>cows</v>
+      </c>
+      <c r="F90" t="s">
         <v>312</v>
       </c>
-      <c r="J72" t="s">
-        <v>390</v>
-      </c>
-      <c r="K72" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F72,'feed pars'!B$6:B$43,0))</f>
-        <v>100</v>
-      </c>
-      <c r="L72" t="s">
+      <c r="J90" s="33" t="str">
+        <f t="shared" ref="J90:N94" si="4">J75</f>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K90" s="33">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="L90" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>%</v>
+      </c>
+      <c r="M90" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>No feeding on pasture</v>
+      </c>
+      <c r="N90" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A91" s="33" t="str">
+        <f t="shared" ref="A91:A94" si="5">A76</f>
+        <v>cattle</v>
+      </c>
+      <c r="E91" s="33" t="str">
+        <f t="shared" si="3"/>
+        <v>bulls</v>
+      </c>
+      <c r="F91" t="s">
+        <v>312</v>
+      </c>
+      <c r="J91" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K91" s="33">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="L91" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>%</v>
+      </c>
+      <c r="M91" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>No feeding on pasture</v>
+      </c>
+      <c r="N91" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A92" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>cattle</v>
+      </c>
+      <c r="F92" t="s">
+        <v>312</v>
+      </c>
+      <c r="J92" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K92" s="33">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="L92" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>%</v>
+      </c>
+      <c r="M92" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>10% feeding on pasture</v>
+      </c>
+      <c r="N92" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A93" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>sheep</v>
+      </c>
+      <c r="F93" t="s">
+        <v>312</v>
+      </c>
+      <c r="J93" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K93" s="33">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="L93" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>%</v>
+      </c>
+      <c r="M93" s="33"/>
+      <c r="N93" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A94" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>horses</v>
+      </c>
+      <c r="F94" t="s">
+        <v>312</v>
+      </c>
+      <c r="J94" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K94" s="33">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="L94" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>%</v>
+      </c>
+      <c r="M94" s="33"/>
+      <c r="N94" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F95" t="s">
+        <v>2</v>
+      </c>
+      <c r="J95" s="29" t="s">
+        <v>397</v>
+      </c>
+      <c r="K95" s="29">
+        <v>5</v>
+      </c>
+      <c r="L95" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F73" t="s">
+      <c r="M95" s="29"/>
+      <c r="N95" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A96" s="33" t="str">
+        <f>A75</f>
+        <v>cattle</v>
+      </c>
+      <c r="B96" s="33" t="str">
+        <f>B75</f>
+        <v>dairy</v>
+      </c>
+      <c r="E96" s="33" t="str">
+        <f t="shared" ref="E96:E97" si="6">E75</f>
+        <v>cows</v>
+      </c>
+      <c r="F96" t="s">
         <v>2</v>
       </c>
-      <c r="J73" t="s">
-        <v>390</v>
-      </c>
-      <c r="K73" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F73,'feed pars'!B$6:B$43,0))</f>
-        <v>100</v>
-      </c>
-      <c r="L73" t="s">
-        <v>28</v>
-      </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F74" t="s">
-        <v>12</v>
-      </c>
-      <c r="J74" t="s">
-        <v>390</v>
-      </c>
-      <c r="K74" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F74,'feed pars'!B$6:B$43,0))</f>
-        <v>100</v>
-      </c>
-      <c r="L74" t="s">
-        <v>28</v>
-      </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F75" t="s">
-        <v>33</v>
-      </c>
-      <c r="J75" t="s">
-        <v>390</v>
-      </c>
-      <c r="K75" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F75,'feed pars'!B$6:B$43,0))</f>
-        <v>100</v>
-      </c>
-      <c r="L75" t="s">
-        <v>28</v>
-      </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F76" t="s">
-        <v>17</v>
-      </c>
-      <c r="J76" t="s">
-        <v>390</v>
-      </c>
-      <c r="K76" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F76,'feed pars'!B$6:B$43,0))</f>
-        <v>87</v>
-      </c>
-      <c r="L76" t="s">
-        <v>28</v>
-      </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F77" t="s">
-        <v>37</v>
-      </c>
-      <c r="J77" t="s">
-        <v>390</v>
-      </c>
-      <c r="K77" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F77,'feed pars'!B$6:B$43,0))</f>
-        <v>87</v>
-      </c>
-      <c r="L77" t="s">
-        <v>28</v>
-      </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F78" t="s">
-        <v>38</v>
-      </c>
-      <c r="J78" t="s">
-        <v>390</v>
-      </c>
-      <c r="K78" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F78,'feed pars'!B$6:B$43,0))</f>
-        <v>86</v>
-      </c>
-      <c r="L78" t="s">
-        <v>28</v>
-      </c>
-      <c r="M78" s="3"/>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F79" t="s">
-        <v>39</v>
-      </c>
-      <c r="J79" t="s">
-        <v>390</v>
-      </c>
-      <c r="K79" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F79,'feed pars'!B$6:B$43,0))</f>
-        <v>87</v>
-      </c>
-      <c r="L79" t="s">
-        <v>28</v>
-      </c>
-      <c r="M79" s="3"/>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F80" t="s">
-        <v>317</v>
-      </c>
-      <c r="J80" t="s">
-        <v>390</v>
-      </c>
-      <c r="K80" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F80,'feed pars'!B$6:B$43,0))</f>
-        <v>87</v>
-      </c>
-      <c r="L80" t="s">
-        <v>28</v>
-      </c>
-      <c r="M80" s="3"/>
-    </row>
-    <row r="81" spans="6:13" x14ac:dyDescent="0.25">
-      <c r="F81" t="s">
-        <v>40</v>
-      </c>
-      <c r="J81" t="s">
-        <v>390</v>
-      </c>
-      <c r="K81" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F81,'feed pars'!B$6:B$43,0))</f>
-        <v>67.5</v>
-      </c>
-      <c r="L81" t="s">
-        <v>28</v>
-      </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="6:13" x14ac:dyDescent="0.25">
-      <c r="F82" t="s">
-        <v>41</v>
-      </c>
-      <c r="J82" t="s">
-        <v>390</v>
-      </c>
-      <c r="K82" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F82,'feed pars'!B$6:B$43,0))</f>
-        <v>87</v>
-      </c>
-      <c r="L82" t="s">
-        <v>28</v>
-      </c>
-      <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="6:13" x14ac:dyDescent="0.25">
-      <c r="F83" t="s">
-        <v>42</v>
-      </c>
-      <c r="J83" t="s">
-        <v>390</v>
-      </c>
-      <c r="K83" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F83,'feed pars'!B$6:B$43,0))</f>
-        <v>86.8</v>
-      </c>
-      <c r="L83" t="s">
-        <v>28</v>
-      </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="6:13" x14ac:dyDescent="0.25">
-      <c r="F84" t="s">
-        <v>35</v>
-      </c>
-      <c r="J84" t="s">
-        <v>390</v>
-      </c>
-      <c r="K84" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F84,'feed pars'!B$6:B$43,0))</f>
-        <v>92.5</v>
-      </c>
-      <c r="L84" t="s">
-        <v>28</v>
-      </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="6:13" x14ac:dyDescent="0.25">
-      <c r="F85" t="s">
-        <v>43</v>
-      </c>
-      <c r="J85" t="s">
-        <v>390</v>
-      </c>
-      <c r="K85" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F85,'feed pars'!B$6:B$43,0))</f>
-        <v>92</v>
-      </c>
-      <c r="L85" t="s">
-        <v>28</v>
-      </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="6:13" x14ac:dyDescent="0.25">
-      <c r="F86" t="s">
-        <v>314</v>
-      </c>
-      <c r="J86" t="s">
-        <v>390</v>
-      </c>
-      <c r="K86" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F86,'feed pars'!B$6:B$43,0))</f>
-        <v>100</v>
-      </c>
-      <c r="L86" t="s">
-        <v>28</v>
-      </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="6:13" x14ac:dyDescent="0.25">
-      <c r="F87" t="s">
-        <v>305</v>
-      </c>
-      <c r="J87" t="s">
-        <v>390</v>
-      </c>
-      <c r="K87" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F87,'feed pars'!B$6:B$43,0))</f>
-        <v>85</v>
-      </c>
-      <c r="L87" t="s">
-        <v>28</v>
-      </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="6:13" x14ac:dyDescent="0.25">
-      <c r="F88" t="s">
-        <v>318</v>
-      </c>
-      <c r="J88" t="s">
-        <v>390</v>
-      </c>
-      <c r="K88" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F88,'feed pars'!B$6:B$43,0))</f>
-        <v>87</v>
-      </c>
-      <c r="L88" t="s">
-        <v>28</v>
-      </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="6:13" x14ac:dyDescent="0.25">
-      <c r="F89" t="s">
-        <v>44</v>
-      </c>
-      <c r="J89" t="s">
-        <v>390</v>
-      </c>
-      <c r="K89" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F89,'feed pars'!B$6:B$43,0))</f>
-        <v>87.5</v>
-      </c>
-      <c r="L89" t="s">
-        <v>28</v>
-      </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="6:13" x14ac:dyDescent="0.25">
-      <c r="F90" t="s">
-        <v>45</v>
-      </c>
-      <c r="J90" t="s">
-        <v>390</v>
-      </c>
-      <c r="K90" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F90,'feed pars'!B$6:B$43,0))</f>
-        <v>87</v>
-      </c>
-      <c r="L90" t="s">
-        <v>28</v>
-      </c>
-      <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="6:13" x14ac:dyDescent="0.25">
-      <c r="F91" t="s">
-        <v>36</v>
-      </c>
-      <c r="J91" t="s">
-        <v>390</v>
-      </c>
-      <c r="K91" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F91,'feed pars'!B$6:B$43,0))</f>
-        <v>89.5</v>
-      </c>
-      <c r="L91" t="s">
-        <v>28</v>
-      </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="6:13" x14ac:dyDescent="0.25">
-      <c r="F92" t="s">
-        <v>46</v>
-      </c>
-      <c r="J92" t="s">
-        <v>390</v>
-      </c>
-      <c r="K92" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F92,'feed pars'!B$6:B$43,0))</f>
-        <v>91</v>
-      </c>
-      <c r="L92" t="s">
-        <v>28</v>
-      </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="6:13" x14ac:dyDescent="0.25">
-      <c r="F93" t="s">
-        <v>47</v>
-      </c>
-      <c r="J93" t="s">
-        <v>390</v>
-      </c>
-      <c r="K93" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F93,'feed pars'!B$6:B$43,0))</f>
-        <v>91</v>
-      </c>
-      <c r="L93" t="s">
-        <v>28</v>
-      </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="6:13" x14ac:dyDescent="0.25">
-      <c r="F94" t="s">
-        <v>319</v>
-      </c>
-      <c r="J94" t="s">
-        <v>390</v>
-      </c>
-      <c r="K94" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F94,'feed pars'!B$6:B$43,0))</f>
-        <v>90</v>
-      </c>
-      <c r="L94" t="s">
-        <v>28</v>
-      </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="6:13" x14ac:dyDescent="0.25">
-      <c r="F95" t="s">
-        <v>48</v>
-      </c>
-      <c r="J95" t="s">
-        <v>390</v>
-      </c>
-      <c r="K95" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F95,'feed pars'!B$6:B$43,0))</f>
-        <v>87</v>
-      </c>
-      <c r="L95" t="s">
-        <v>28</v>
-      </c>
-      <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="6:13" x14ac:dyDescent="0.25">
-      <c r="F96" t="s">
-        <v>49</v>
-      </c>
-      <c r="J96" t="s">
-        <v>390</v>
-      </c>
-      <c r="K96" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F96,'feed pars'!B$6:B$43,0))</f>
-        <v>88</v>
-      </c>
-      <c r="L96" t="s">
-        <v>28</v>
-      </c>
-      <c r="M96" s="3"/>
+      <c r="J96" s="33" t="str">
+        <f t="shared" ref="J96:N100" si="7">J75</f>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K96" s="33">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="L96" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>%</v>
+      </c>
+      <c r="M96" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>No feeding on pasture</v>
+      </c>
+      <c r="N96" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A97" s="33" t="str">
+        <f t="shared" ref="A97:A100" si="8">A76</f>
+        <v>cattle</v>
+      </c>
+      <c r="E97" s="33" t="str">
+        <f t="shared" si="6"/>
+        <v>bulls</v>
+      </c>
       <c r="F97" t="s">
-        <v>50</v>
-      </c>
-      <c r="J97" t="s">
-        <v>390</v>
-      </c>
-      <c r="K97" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F97,'feed pars'!B$6:B$43,0))</f>
-        <v>90</v>
-      </c>
-      <c r="L97" t="s">
-        <v>28</v>
-      </c>
-      <c r="M97" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="J97" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K97" s="33">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="L97" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>%</v>
+      </c>
+      <c r="M97" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>No feeding on pasture</v>
+      </c>
+      <c r="N97" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A98" s="33" t="str">
+        <f t="shared" si="8"/>
+        <v>cattle</v>
+      </c>
       <c r="F98" t="s">
-        <v>51</v>
-      </c>
-      <c r="J98" t="s">
-        <v>390</v>
-      </c>
-      <c r="K98" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F98,'feed pars'!B$6:B$43,0))</f>
-        <v>11</v>
-      </c>
-      <c r="L98" t="s">
-        <v>28</v>
-      </c>
-      <c r="M98" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="J98" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K98" s="33">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="L98" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>%</v>
+      </c>
+      <c r="M98" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>10% feeding on pasture</v>
+      </c>
+      <c r="N98" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A99" s="33" t="str">
+        <f t="shared" si="8"/>
+        <v>sheep</v>
+      </c>
       <c r="F99" t="s">
-        <v>313</v>
-      </c>
-      <c r="J99" t="s">
-        <v>390</v>
-      </c>
-      <c r="K99" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F99,'feed pars'!B$6:B$43,0))</f>
-        <v>90</v>
-      </c>
-      <c r="L99" t="s">
-        <v>28</v>
-      </c>
-      <c r="M99" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="J99" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K99" s="33">
+        <f t="shared" si="7"/>
+        <v>15</v>
+      </c>
+      <c r="L99" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>%</v>
+      </c>
+      <c r="M99" s="29"/>
+      <c r="N99" s="33" t="str">
+        <f t="shared" ref="N99:N100" si="9">N78</f>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A100" s="33" t="str">
+        <f t="shared" si="8"/>
+        <v>horses</v>
+      </c>
       <c r="F100" t="s">
-        <v>388</v>
-      </c>
-      <c r="J100" t="s">
-        <v>390</v>
-      </c>
-      <c r="K100" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F100,'feed pars'!B$6:B$43,0))</f>
-        <v>87</v>
-      </c>
-      <c r="L100" t="s">
-        <v>28</v>
-      </c>
-      <c r="M100" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="J100" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K100" s="33">
+        <f t="shared" si="7"/>
+        <v>15</v>
+      </c>
+      <c r="L100" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>%</v>
+      </c>
+      <c r="M100" s="29"/>
+      <c r="N100" s="33" t="str">
+        <f t="shared" si="9"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F101" t="s">
-        <v>52</v>
-      </c>
-      <c r="J101" t="s">
-        <v>390</v>
-      </c>
-      <c r="K101" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F101,'feed pars'!B$6:B$43,0))</f>
-        <v>75.5</v>
-      </c>
-      <c r="L101" t="s">
+        <v>12</v>
+      </c>
+      <c r="J101" s="29" t="s">
+        <v>397</v>
+      </c>
+      <c r="K101" s="29">
+        <v>5</v>
+      </c>
+      <c r="L101" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="M101" s="3"/>
+      <c r="M101" s="29"/>
+      <c r="N101" t="s">
+        <v>399</v>
+      </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A102" s="33" t="str">
+        <f>A75</f>
+        <v>cattle</v>
+      </c>
+      <c r="B102" s="33" t="str">
+        <f>B75</f>
+        <v>dairy</v>
+      </c>
+      <c r="E102" s="33" t="str">
+        <f t="shared" ref="E102:E103" si="10">E75</f>
+        <v>cows</v>
+      </c>
       <c r="F102" t="s">
-        <v>53</v>
-      </c>
-      <c r="J102" t="s">
-        <v>390</v>
-      </c>
-      <c r="K102" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F102,'feed pars'!B$6:B$43,0))</f>
-        <v>89.5</v>
-      </c>
-      <c r="L102" t="s">
+        <v>12</v>
+      </c>
+      <c r="J102" s="33" t="str">
+        <f t="shared" ref="J102:N106" si="11">J75</f>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K102" s="33">
+        <f t="shared" si="11"/>
+        <v>5</v>
+      </c>
+      <c r="L102" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>%</v>
+      </c>
+      <c r="M102" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>No feeding on pasture</v>
+      </c>
+      <c r="N102" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A103" s="33" t="str">
+        <f t="shared" ref="A103:A106" si="12">A76</f>
+        <v>cattle</v>
+      </c>
+      <c r="E103" s="33" t="str">
+        <f t="shared" si="10"/>
+        <v>bulls</v>
+      </c>
+      <c r="F103" t="s">
+        <v>12</v>
+      </c>
+      <c r="J103" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K103" s="33">
+        <f t="shared" si="11"/>
+        <v>5</v>
+      </c>
+      <c r="L103" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>%</v>
+      </c>
+      <c r="M103" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>No feeding on pasture</v>
+      </c>
+      <c r="N103" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A104" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v>cattle</v>
+      </c>
+      <c r="F104" t="s">
+        <v>12</v>
+      </c>
+      <c r="J104" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K104" s="33">
+        <f t="shared" si="11"/>
+        <v>6</v>
+      </c>
+      <c r="L104" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>%</v>
+      </c>
+      <c r="M104" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>10% feeding on pasture</v>
+      </c>
+      <c r="N104" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A105" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v>sheep</v>
+      </c>
+      <c r="F105" t="s">
+        <v>12</v>
+      </c>
+      <c r="J105" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K105" s="33">
+        <f t="shared" si="11"/>
+        <v>15</v>
+      </c>
+      <c r="L105" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>%</v>
+      </c>
+      <c r="M105" s="29"/>
+      <c r="N105" s="33" t="str">
+        <f t="shared" ref="N105:N106" si="13">N78</f>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A106" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v>horses</v>
+      </c>
+      <c r="F106" t="s">
+        <v>12</v>
+      </c>
+      <c r="J106" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K106" s="33">
+        <f t="shared" si="11"/>
+        <v>15</v>
+      </c>
+      <c r="L106" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>%</v>
+      </c>
+      <c r="M106" s="29"/>
+      <c r="N106" s="33" t="str">
+        <f t="shared" si="13"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A107" s="33"/>
+      <c r="F107" t="s">
+        <v>33</v>
+      </c>
+      <c r="J107" s="29" t="s">
+        <v>397</v>
+      </c>
+      <c r="K107" s="29">
+        <v>0</v>
+      </c>
+      <c r="L107" t="s">
         <v>28</v>
       </c>
-      <c r="M102" s="3"/>
-    </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F103" t="s">
-        <v>54</v>
-      </c>
-      <c r="J103" t="s">
-        <v>390</v>
-      </c>
-      <c r="K103" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F103,'feed pars'!B$6:B$43,0))</f>
-        <v>6.25</v>
-      </c>
-      <c r="L103" t="s">
-        <v>28</v>
-      </c>
-      <c r="M103" s="3"/>
-    </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F104" t="s">
-        <v>55</v>
-      </c>
-      <c r="J104" t="s">
-        <v>390</v>
-      </c>
-      <c r="K104" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F104,'feed pars'!B$6:B$43,0))</f>
-        <v>97</v>
-      </c>
-      <c r="L104" t="s">
-        <v>28</v>
-      </c>
-      <c r="M104" s="3"/>
-    </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F105" t="s">
-        <v>56</v>
-      </c>
-      <c r="J105" t="s">
-        <v>390</v>
-      </c>
-      <c r="K105" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F105,'feed pars'!B$6:B$43,0))</f>
-        <v>91</v>
-      </c>
-      <c r="L105" t="s">
-        <v>28</v>
-      </c>
-      <c r="M105" s="3"/>
-    </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F106" t="s">
-        <v>57</v>
-      </c>
-      <c r="J106" t="s">
-        <v>390</v>
-      </c>
-      <c r="K106" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F106,'feed pars'!B$6:B$43,0))</f>
-        <v>92</v>
-      </c>
-      <c r="L106" t="s">
-        <v>28</v>
-      </c>
-      <c r="M106" s="3"/>
-    </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A107" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B107" s="7"/>
-      <c r="C107" s="6"/>
-      <c r="D107" s="6"/>
-      <c r="E107" s="6"/>
-      <c r="F107" s="6"/>
-      <c r="G107" s="6"/>
-      <c r="H107" s="6"/>
-      <c r="I107" s="6"/>
-      <c r="J107" s="6"/>
-      <c r="K107" s="6"/>
-      <c r="L107" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M107" s="6"/>
-      <c r="N107" s="6"/>
+      <c r="M107" s="29" t="s">
+        <v>409</v>
+      </c>
+      <c r="N107" s="33"/>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>24</v>
       </c>
       <c r="F108" t="s">
-        <v>310</v>
+        <v>33</v>
       </c>
       <c r="J108" t="s">
-        <v>18</v>
-      </c>
-      <c r="K108" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F108,'feed pars'!B$6:B$43,0))</f>
-        <v>11.5</v>
-      </c>
-      <c r="M108" s="3"/>
+        <v>398</v>
+      </c>
+      <c r="K108" s="29">
+        <f>100-55</f>
+        <v>45</v>
+      </c>
+      <c r="L108" t="s">
+        <v>28</v>
+      </c>
+      <c r="M108" s="29" t="s">
+        <v>401</v>
+      </c>
+      <c r="N108" t="s">
+        <v>399</v>
+      </c>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>395</v>
+      </c>
+      <c r="F109" t="s">
+        <v>33</v>
+      </c>
+      <c r="J109" t="s">
+        <v>398</v>
+      </c>
+      <c r="K109" s="29">
+        <f>100-50</f>
+        <v>50</v>
+      </c>
+      <c r="L109" t="s">
+        <v>28</v>
+      </c>
+      <c r="M109" s="29" t="s">
+        <v>401</v>
+      </c>
+      <c r="N109" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K110" s="3"/>
+      <c r="M110" s="29"/>
+    </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="K111" s="3"/>
+      <c r="M111" s="29"/>
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K112" s="3"/>
+      <c r="M112" s="29"/>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K113" s="3"/>
+      <c r="M113" s="3"/>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B114" s="1"/>
+      <c r="C114" s="1"/>
+      <c r="D114" s="1"/>
+      <c r="E114" s="2"/>
+      <c r="F114" s="2"/>
+      <c r="G114" s="2"/>
+      <c r="H114" s="2"/>
+      <c r="I114" s="2"/>
+      <c r="J114" s="2"/>
+      <c r="K114" s="2"/>
+      <c r="L114" s="2"/>
+      <c r="M114" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="N114" s="2"/>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F115" t="s">
+        <v>310</v>
+      </c>
+      <c r="J115" t="s">
+        <v>390</v>
+      </c>
+      <c r="K115" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F115,'feed pars'!B$6:B$43,0))</f>
+        <v>100</v>
+      </c>
+      <c r="L115" t="s">
+        <v>28</v>
+      </c>
+      <c r="M115" s="29" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F116" t="s">
+        <v>311</v>
+      </c>
+      <c r="J116" t="s">
+        <v>390</v>
+      </c>
+      <c r="K116" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F116,'feed pars'!B$6:B$43,0))</f>
+        <v>100</v>
+      </c>
+      <c r="L116" t="s">
+        <v>28</v>
+      </c>
+      <c r="M116" s="3"/>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F117" t="s">
+        <v>312</v>
+      </c>
+      <c r="J117" t="s">
+        <v>390</v>
+      </c>
+      <c r="K117" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F117,'feed pars'!B$6:B$43,0))</f>
+        <v>100</v>
+      </c>
+      <c r="L117" t="s">
+        <v>28</v>
+      </c>
+      <c r="M117" s="3"/>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F118" t="s">
+        <v>2</v>
+      </c>
+      <c r="J118" t="s">
+        <v>390</v>
+      </c>
+      <c r="K118" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F118,'feed pars'!B$6:B$43,0))</f>
+        <v>100</v>
+      </c>
+      <c r="L118" t="s">
+        <v>28</v>
+      </c>
+      <c r="M118" s="3"/>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F119" t="s">
+        <v>12</v>
+      </c>
+      <c r="J119" t="s">
+        <v>390</v>
+      </c>
+      <c r="K119" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F119,'feed pars'!B$6:B$43,0))</f>
+        <v>100</v>
+      </c>
+      <c r="L119" t="s">
+        <v>28</v>
+      </c>
+      <c r="M119" s="3"/>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F120" t="s">
+        <v>33</v>
+      </c>
+      <c r="J120" t="s">
+        <v>390</v>
+      </c>
+      <c r="K120" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F120,'feed pars'!B$6:B$43,0))</f>
+        <v>100</v>
+      </c>
+      <c r="L120" t="s">
+        <v>28</v>
+      </c>
+      <c r="M120" s="3"/>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F121" t="s">
+        <v>17</v>
+      </c>
+      <c r="J121" t="s">
+        <v>390</v>
+      </c>
+      <c r="K121" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F121,'feed pars'!B$6:B$43,0))</f>
+        <v>87</v>
+      </c>
+      <c r="L121" t="s">
+        <v>28</v>
+      </c>
+      <c r="M121" s="3"/>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F122" t="s">
+        <v>37</v>
+      </c>
+      <c r="J122" t="s">
+        <v>390</v>
+      </c>
+      <c r="K122" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F122,'feed pars'!B$6:B$43,0))</f>
+        <v>87</v>
+      </c>
+      <c r="L122" t="s">
+        <v>28</v>
+      </c>
+      <c r="M122" s="3"/>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F123" t="s">
+        <v>38</v>
+      </c>
+      <c r="J123" t="s">
+        <v>390</v>
+      </c>
+      <c r="K123" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F123,'feed pars'!B$6:B$43,0))</f>
+        <v>86</v>
+      </c>
+      <c r="L123" t="s">
+        <v>28</v>
+      </c>
+      <c r="M123" s="3"/>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F124" t="s">
+        <v>39</v>
+      </c>
+      <c r="J124" t="s">
+        <v>390</v>
+      </c>
+      <c r="K124" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F124,'feed pars'!B$6:B$43,0))</f>
+        <v>87</v>
+      </c>
+      <c r="L124" t="s">
+        <v>28</v>
+      </c>
+      <c r="M124" s="3"/>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F125" t="s">
+        <v>317</v>
+      </c>
+      <c r="J125" t="s">
+        <v>390</v>
+      </c>
+      <c r="K125" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F125,'feed pars'!B$6:B$43,0))</f>
+        <v>87</v>
+      </c>
+      <c r="L125" t="s">
+        <v>28</v>
+      </c>
+      <c r="M125" s="3"/>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F126" t="s">
+        <v>40</v>
+      </c>
+      <c r="J126" t="s">
+        <v>390</v>
+      </c>
+      <c r="K126" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F126,'feed pars'!B$6:B$43,0))</f>
+        <v>67.5</v>
+      </c>
+      <c r="L126" t="s">
+        <v>28</v>
+      </c>
+      <c r="M126" s="3"/>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F127" t="s">
+        <v>41</v>
+      </c>
+      <c r="J127" t="s">
+        <v>390</v>
+      </c>
+      <c r="K127" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F127,'feed pars'!B$6:B$43,0))</f>
+        <v>87</v>
+      </c>
+      <c r="L127" t="s">
+        <v>28</v>
+      </c>
+      <c r="M127" s="3"/>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F128" t="s">
+        <v>42</v>
+      </c>
+      <c r="J128" t="s">
+        <v>390</v>
+      </c>
+      <c r="K128" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F128,'feed pars'!B$6:B$43,0))</f>
+        <v>86.8</v>
+      </c>
+      <c r="L128" t="s">
+        <v>28</v>
+      </c>
+      <c r="M128" s="3"/>
+    </row>
+    <row r="129" spans="6:13" x14ac:dyDescent="0.25">
+      <c r="F129" t="s">
+        <v>35</v>
+      </c>
+      <c r="J129" t="s">
+        <v>390</v>
+      </c>
+      <c r="K129" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F129,'feed pars'!B$6:B$43,0))</f>
+        <v>92.5</v>
+      </c>
+      <c r="L129" t="s">
+        <v>28</v>
+      </c>
+      <c r="M129" s="3"/>
+    </row>
+    <row r="130" spans="6:13" x14ac:dyDescent="0.25">
+      <c r="F130" t="s">
+        <v>43</v>
+      </c>
+      <c r="J130" t="s">
+        <v>390</v>
+      </c>
+      <c r="K130" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F130,'feed pars'!B$6:B$43,0))</f>
+        <v>92</v>
+      </c>
+      <c r="L130" t="s">
+        <v>28</v>
+      </c>
+      <c r="M130" s="3"/>
+    </row>
+    <row r="131" spans="6:13" x14ac:dyDescent="0.25">
+      <c r="F131" t="s">
+        <v>314</v>
+      </c>
+      <c r="J131" t="s">
+        <v>390</v>
+      </c>
+      <c r="K131" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F131,'feed pars'!B$6:B$43,0))</f>
+        <v>100</v>
+      </c>
+      <c r="L131" t="s">
+        <v>28</v>
+      </c>
+      <c r="M131" s="3"/>
+    </row>
+    <row r="132" spans="6:13" x14ac:dyDescent="0.25">
+      <c r="F132" t="s">
+        <v>305</v>
+      </c>
+      <c r="J132" t="s">
+        <v>390</v>
+      </c>
+      <c r="K132" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F132,'feed pars'!B$6:B$43,0))</f>
+        <v>85</v>
+      </c>
+      <c r="L132" t="s">
+        <v>28</v>
+      </c>
+      <c r="M132" s="3"/>
+    </row>
+    <row r="133" spans="6:13" x14ac:dyDescent="0.25">
+      <c r="F133" t="s">
+        <v>318</v>
+      </c>
+      <c r="J133" t="s">
+        <v>390</v>
+      </c>
+      <c r="K133" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F133,'feed pars'!B$6:B$43,0))</f>
+        <v>87</v>
+      </c>
+      <c r="L133" t="s">
+        <v>28</v>
+      </c>
+      <c r="M133" s="3"/>
+    </row>
+    <row r="134" spans="6:13" x14ac:dyDescent="0.25">
+      <c r="F134" t="s">
+        <v>44</v>
+      </c>
+      <c r="J134" t="s">
+        <v>390</v>
+      </c>
+      <c r="K134" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F134,'feed pars'!B$6:B$43,0))</f>
+        <v>87.5</v>
+      </c>
+      <c r="L134" t="s">
+        <v>28</v>
+      </c>
+      <c r="M134" s="3"/>
+    </row>
+    <row r="135" spans="6:13" x14ac:dyDescent="0.25">
+      <c r="F135" t="s">
+        <v>45</v>
+      </c>
+      <c r="J135" t="s">
+        <v>390</v>
+      </c>
+      <c r="K135" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F135,'feed pars'!B$6:B$43,0))</f>
+        <v>87</v>
+      </c>
+      <c r="L135" t="s">
+        <v>28</v>
+      </c>
+      <c r="M135" s="3"/>
+    </row>
+    <row r="136" spans="6:13" x14ac:dyDescent="0.25">
+      <c r="F136" t="s">
+        <v>36</v>
+      </c>
+      <c r="J136" t="s">
+        <v>390</v>
+      </c>
+      <c r="K136" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F136,'feed pars'!B$6:B$43,0))</f>
+        <v>89.5</v>
+      </c>
+      <c r="L136" t="s">
+        <v>28</v>
+      </c>
+      <c r="M136" s="3"/>
+    </row>
+    <row r="137" spans="6:13" x14ac:dyDescent="0.25">
+      <c r="F137" t="s">
+        <v>46</v>
+      </c>
+      <c r="J137" t="s">
+        <v>390</v>
+      </c>
+      <c r="K137" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F137,'feed pars'!B$6:B$43,0))</f>
+        <v>91</v>
+      </c>
+      <c r="L137" t="s">
+        <v>28</v>
+      </c>
+      <c r="M137" s="3"/>
+    </row>
+    <row r="138" spans="6:13" x14ac:dyDescent="0.25">
+      <c r="F138" t="s">
+        <v>47</v>
+      </c>
+      <c r="J138" t="s">
+        <v>390</v>
+      </c>
+      <c r="K138" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F138,'feed pars'!B$6:B$43,0))</f>
+        <v>91</v>
+      </c>
+      <c r="L138" t="s">
+        <v>28</v>
+      </c>
+      <c r="M138" s="3"/>
+    </row>
+    <row r="139" spans="6:13" x14ac:dyDescent="0.25">
+      <c r="F139" t="s">
+        <v>319</v>
+      </c>
+      <c r="J139" t="s">
+        <v>390</v>
+      </c>
+      <c r="K139" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F139,'feed pars'!B$6:B$43,0))</f>
+        <v>90</v>
+      </c>
+      <c r="L139" t="s">
+        <v>28</v>
+      </c>
+      <c r="M139" s="3"/>
+    </row>
+    <row r="140" spans="6:13" x14ac:dyDescent="0.25">
+      <c r="F140" t="s">
+        <v>48</v>
+      </c>
+      <c r="J140" t="s">
+        <v>390</v>
+      </c>
+      <c r="K140" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F140,'feed pars'!B$6:B$43,0))</f>
+        <v>87</v>
+      </c>
+      <c r="L140" t="s">
+        <v>28</v>
+      </c>
+      <c r="M140" s="3"/>
+    </row>
+    <row r="141" spans="6:13" x14ac:dyDescent="0.25">
+      <c r="F141" t="s">
+        <v>49</v>
+      </c>
+      <c r="J141" t="s">
+        <v>390</v>
+      </c>
+      <c r="K141" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F141,'feed pars'!B$6:B$43,0))</f>
+        <v>88</v>
+      </c>
+      <c r="L141" t="s">
+        <v>28</v>
+      </c>
+      <c r="M141" s="3"/>
+    </row>
+    <row r="142" spans="6:13" x14ac:dyDescent="0.25">
+      <c r="F142" t="s">
+        <v>50</v>
+      </c>
+      <c r="J142" t="s">
+        <v>390</v>
+      </c>
+      <c r="K142" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F142,'feed pars'!B$6:B$43,0))</f>
+        <v>90</v>
+      </c>
+      <c r="L142" t="s">
+        <v>28</v>
+      </c>
+      <c r="M142" s="3"/>
+    </row>
+    <row r="143" spans="6:13" x14ac:dyDescent="0.25">
+      <c r="F143" t="s">
+        <v>51</v>
+      </c>
+      <c r="J143" t="s">
+        <v>390</v>
+      </c>
+      <c r="K143" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F143,'feed pars'!B$6:B$43,0))</f>
+        <v>11</v>
+      </c>
+      <c r="L143" t="s">
+        <v>28</v>
+      </c>
+      <c r="M143" s="3"/>
+    </row>
+    <row r="144" spans="6:13" x14ac:dyDescent="0.25">
+      <c r="F144" t="s">
+        <v>313</v>
+      </c>
+      <c r="J144" t="s">
+        <v>390</v>
+      </c>
+      <c r="K144" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F144,'feed pars'!B$6:B$43,0))</f>
+        <v>90</v>
+      </c>
+      <c r="L144" t="s">
+        <v>28</v>
+      </c>
+      <c r="M144" s="3"/>
+    </row>
+    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F145" t="s">
+        <v>388</v>
+      </c>
+      <c r="J145" t="s">
+        <v>390</v>
+      </c>
+      <c r="K145" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F145,'feed pars'!B$6:B$43,0))</f>
+        <v>87</v>
+      </c>
+      <c r="L145" t="s">
+        <v>28</v>
+      </c>
+      <c r="M145" s="3"/>
+    </row>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F146" t="s">
+        <v>52</v>
+      </c>
+      <c r="J146" t="s">
+        <v>390</v>
+      </c>
+      <c r="K146" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F146,'feed pars'!B$6:B$43,0))</f>
+        <v>75.5</v>
+      </c>
+      <c r="L146" t="s">
+        <v>28</v>
+      </c>
+      <c r="M146" s="3"/>
+    </row>
+    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F147" t="s">
+        <v>53</v>
+      </c>
+      <c r="J147" t="s">
+        <v>390</v>
+      </c>
+      <c r="K147" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F147,'feed pars'!B$6:B$43,0))</f>
+        <v>89.5</v>
+      </c>
+      <c r="L147" t="s">
+        <v>28</v>
+      </c>
+      <c r="M147" s="3"/>
+    </row>
+    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F148" t="s">
+        <v>54</v>
+      </c>
+      <c r="J148" t="s">
+        <v>390</v>
+      </c>
+      <c r="K148" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F148,'feed pars'!B$6:B$43,0))</f>
+        <v>6.25</v>
+      </c>
+      <c r="L148" t="s">
+        <v>28</v>
+      </c>
+      <c r="M148" s="3"/>
+    </row>
+    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F149" t="s">
+        <v>55</v>
+      </c>
+      <c r="J149" t="s">
+        <v>390</v>
+      </c>
+      <c r="K149" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F149,'feed pars'!B$6:B$43,0))</f>
+        <v>97</v>
+      </c>
+      <c r="L149" t="s">
+        <v>28</v>
+      </c>
+      <c r="M149" s="3"/>
+    </row>
+    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F150" t="s">
+        <v>56</v>
+      </c>
+      <c r="J150" t="s">
+        <v>390</v>
+      </c>
+      <c r="K150" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F150,'feed pars'!B$6:B$43,0))</f>
+        <v>91</v>
+      </c>
+      <c r="L150" t="s">
+        <v>28</v>
+      </c>
+      <c r="M150" s="3"/>
+    </row>
+    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F151" t="s">
+        <v>57</v>
+      </c>
+      <c r="J151" t="s">
+        <v>390</v>
+      </c>
+      <c r="K151" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F151,'feed pars'!B$6:B$43,0))</f>
+        <v>92</v>
+      </c>
+      <c r="L151" t="s">
+        <v>28</v>
+      </c>
+      <c r="M151" s="3"/>
+    </row>
+    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A152" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B152" s="7"/>
+      <c r="C152" s="6"/>
+      <c r="D152" s="6"/>
+      <c r="E152" s="6"/>
+      <c r="F152" s="6"/>
+      <c r="G152" s="6"/>
+      <c r="H152" s="6"/>
+      <c r="I152" s="6"/>
+      <c r="J152" s="6"/>
+      <c r="K152" s="6"/>
+      <c r="L152" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M152" s="6"/>
+      <c r="N152" s="6"/>
+    </row>
+    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
         <v>24</v>
       </c>
-      <c r="F109" t="s">
-        <v>311</v>
-      </c>
-      <c r="J109" t="s">
-        <v>18</v>
-      </c>
-      <c r="K109" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F109,'feed pars'!B$6:B$43,0))</f>
-        <v>10.4</v>
-      </c>
-      <c r="M109" s="3"/>
-    </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>24</v>
-      </c>
-      <c r="F110" t="s">
-        <v>312</v>
-      </c>
-      <c r="J110" t="s">
-        <v>18</v>
-      </c>
-      <c r="K110" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F110,'feed pars'!B$6:B$43,0))</f>
-        <v>10</v>
-      </c>
-      <c r="M110" s="3"/>
-    </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>24</v>
-      </c>
-      <c r="F111" t="s">
-        <v>12</v>
-      </c>
-      <c r="J111" t="s">
-        <v>18</v>
-      </c>
-      <c r="K111" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F111,'feed pars'!B$6:B$43,0))</f>
-        <v>11.3</v>
-      </c>
-    </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>24</v>
-      </c>
-      <c r="F112" t="s">
-        <v>33</v>
-      </c>
-      <c r="J112" t="s">
-        <v>18</v>
-      </c>
-      <c r="K112" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F112,'feed pars'!B$6:B$43,0))</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K113" s="3"/>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>24</v>
-      </c>
-      <c r="F114" t="s">
-        <v>17</v>
-      </c>
-      <c r="J114" t="s">
-        <v>18</v>
-      </c>
-      <c r="K114" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F114,'feed pars'!B$6:B$43,0))</f>
-        <v>14.1</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>24</v>
-      </c>
-      <c r="F115" t="s">
-        <v>37</v>
-      </c>
-      <c r="J115" t="s">
-        <v>18</v>
-      </c>
-      <c r="K115" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F115,'feed pars'!B$6:B$43,0))</f>
-        <v>13.2</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>24</v>
-      </c>
-      <c r="F116" t="s">
-        <v>38</v>
-      </c>
-      <c r="J116" t="s">
-        <v>18</v>
-      </c>
-      <c r="K116" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F116,'feed pars'!B$6:B$43,0))</f>
-        <v>11.7</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>24</v>
-      </c>
-      <c r="F117" t="s">
-        <v>39</v>
-      </c>
-      <c r="J117" t="s">
-        <v>18</v>
-      </c>
-      <c r="K117" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F117,'feed pars'!B$6:B$43,0))</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>24</v>
-      </c>
-      <c r="F118" t="s">
-        <v>317</v>
-      </c>
-      <c r="J118" t="s">
-        <v>18</v>
-      </c>
-      <c r="K118" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F118,'feed pars'!B$6:B$43,0))</f>
-        <v>13.9</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>24</v>
-      </c>
-      <c r="F119" t="s">
-        <v>40</v>
-      </c>
-      <c r="J119" t="s">
-        <v>18</v>
-      </c>
-      <c r="K119" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F119,'feed pars'!B$6:B$43,0))</f>
-        <v>12.8</v>
-      </c>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
-        <v>24</v>
-      </c>
-      <c r="F120" t="s">
-        <v>41</v>
-      </c>
-      <c r="J120" t="s">
-        <v>18</v>
-      </c>
-      <c r="K120" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F120,'feed pars'!B$6:B$43,0))</f>
-        <v>13.8</v>
-      </c>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>24</v>
-      </c>
-      <c r="F121" t="s">
-        <v>42</v>
-      </c>
-      <c r="J121" t="s">
-        <v>18</v>
-      </c>
-      <c r="K121" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F121,'feed pars'!B$6:B$43,0))</f>
-        <v>13.3</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>24</v>
-      </c>
-      <c r="F122" t="s">
-        <v>35</v>
-      </c>
-      <c r="J122" t="s">
-        <v>18</v>
-      </c>
-      <c r="K122" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F122,'feed pars'!B$6:B$43,0))</f>
-        <v>22.1</v>
-      </c>
-    </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>24</v>
-      </c>
-      <c r="F123" t="s">
-        <v>43</v>
-      </c>
-      <c r="J123" t="s">
-        <v>18</v>
-      </c>
-      <c r="K123" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F123,'feed pars'!B$6:B$43,0))</f>
-        <v>20.100000000000001</v>
-      </c>
-    </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>24</v>
-      </c>
-      <c r="F124" t="s">
-        <v>305</v>
-      </c>
-      <c r="J124" t="s">
-        <v>18</v>
-      </c>
-      <c r="K124" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F124,'feed pars'!B$6:B$43,0))</f>
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
-        <v>24</v>
-      </c>
-      <c r="F125" t="s">
-        <v>314</v>
-      </c>
-      <c r="J125" t="s">
-        <v>18</v>
-      </c>
-      <c r="K125" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F125,'feed pars'!B$6:B$43,0))</f>
-        <v>36.6</v>
-      </c>
-    </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>24</v>
-      </c>
-      <c r="F126" t="s">
-        <v>318</v>
-      </c>
-      <c r="J126" t="s">
-        <v>18</v>
-      </c>
-      <c r="K126" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F126,'feed pars'!B$6:B$43,0))</f>
-        <v>16.399999999999999</v>
-      </c>
-    </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>24</v>
-      </c>
-      <c r="F127" t="s">
-        <v>44</v>
-      </c>
-      <c r="J127" t="s">
-        <v>18</v>
-      </c>
-      <c r="K127" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F127,'feed pars'!B$6:B$43,0))</f>
-        <v>14.6</v>
-      </c>
-    </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>24</v>
-      </c>
-      <c r="F128" t="s">
-        <v>36</v>
-      </c>
-      <c r="J128" t="s">
-        <v>18</v>
-      </c>
-      <c r="K128" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F128,'feed pars'!B$6:B$43,0))</f>
-        <v>12.2</v>
-      </c>
-    </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>24</v>
-      </c>
-      <c r="F129" t="s">
-        <v>46</v>
-      </c>
-      <c r="J129" t="s">
-        <v>18</v>
-      </c>
-      <c r="K129" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F129,'feed pars'!B$6:B$43,0))</f>
-        <v>11.4</v>
-      </c>
-    </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>24</v>
-      </c>
-      <c r="F130" t="s">
-        <v>47</v>
-      </c>
-      <c r="J130" t="s">
-        <v>18</v>
-      </c>
-      <c r="K130" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F130,'feed pars'!B$6:B$43,0))</f>
-        <v>13.4</v>
-      </c>
-    </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>24</v>
-      </c>
-      <c r="F131" t="s">
-        <v>319</v>
-      </c>
-      <c r="J131" t="s">
-        <v>18</v>
-      </c>
-      <c r="K131" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F131,'feed pars'!B$6:B$43,0))</f>
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>24</v>
-      </c>
-      <c r="F132" t="s">
-        <v>48</v>
-      </c>
-      <c r="J132" t="s">
-        <v>18</v>
-      </c>
-      <c r="K132" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F132,'feed pars'!B$6:B$43,0))</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>24</v>
-      </c>
-      <c r="F133" t="s">
-        <v>50</v>
-      </c>
-      <c r="J133" t="s">
-        <v>18</v>
-      </c>
-      <c r="K133" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F133,'feed pars'!B$6:B$43,0))</f>
-        <v>13.3</v>
-      </c>
-    </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>24</v>
-      </c>
-      <c r="F134" t="s">
-        <v>313</v>
-      </c>
-      <c r="J134" t="s">
-        <v>18</v>
-      </c>
-      <c r="K134" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F134,'feed pars'!B$6:B$43,0))</f>
-        <v>11.6</v>
-      </c>
-    </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>24</v>
-      </c>
-      <c r="F135" t="s">
-        <v>52</v>
-      </c>
-      <c r="J135" t="s">
-        <v>18</v>
-      </c>
-      <c r="K135" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F135,'feed pars'!B$6:B$43,0))</f>
-        <v>12.4</v>
-      </c>
-    </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>24</v>
-      </c>
-      <c r="F136" t="s">
-        <v>53</v>
-      </c>
-      <c r="J136" t="s">
-        <v>18</v>
-      </c>
-      <c r="K136" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F136,'feed pars'!B$6:B$43,0))</f>
-        <v>12.3</v>
-      </c>
-    </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>24</v>
-      </c>
-      <c r="F137" t="s">
-        <v>54</v>
-      </c>
-      <c r="J137" t="s">
-        <v>18</v>
-      </c>
-      <c r="K137" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F137,'feed pars'!B$6:B$43,0))</f>
-        <v>13.6</v>
-      </c>
-    </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>24</v>
-      </c>
-      <c r="F138" t="s">
-        <v>56</v>
-      </c>
-      <c r="J138" t="s">
-        <v>18</v>
-      </c>
-      <c r="K138" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F138,'feed pars'!B$6:B$43,0))</f>
-        <v>15.5</v>
-      </c>
-    </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>24</v>
-      </c>
-      <c r="F139" t="s">
-        <v>324</v>
-      </c>
-      <c r="J139" t="s">
-        <v>18</v>
-      </c>
-      <c r="K139" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A140" s="7" t="s">
-        <v>396</v>
-      </c>
-      <c r="B140" s="7"/>
-      <c r="C140" s="6"/>
-      <c r="D140" s="6"/>
-      <c r="E140" s="6"/>
-      <c r="F140" s="6"/>
-      <c r="G140" s="6"/>
-      <c r="H140" s="6"/>
-      <c r="I140" s="6"/>
-      <c r="J140" s="6"/>
-      <c r="K140" s="6"/>
-      <c r="L140" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M140" s="6"/>
-      <c r="N140" s="6"/>
-    </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>395</v>
-      </c>
-      <c r="F141" t="s">
-        <v>2</v>
-      </c>
-      <c r="J141" t="s">
-        <v>18</v>
-      </c>
-      <c r="K141" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>395</v>
-      </c>
-      <c r="F142" t="s">
-        <v>33</v>
-      </c>
-      <c r="J142" t="s">
-        <v>18</v>
-      </c>
-      <c r="K142" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A143" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B143" s="8"/>
-      <c r="C143" s="9"/>
-      <c r="D143" s="9"/>
-      <c r="E143" s="9"/>
-      <c r="F143" s="9"/>
-      <c r="G143" s="9"/>
-      <c r="H143" s="9"/>
-      <c r="I143" s="9"/>
-      <c r="J143" s="9"/>
-      <c r="K143" s="9"/>
-      <c r="L143" s="9"/>
-      <c r="M143" s="9"/>
-      <c r="N143" s="9"/>
-    </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A144" s="30" t="s">
-        <v>391</v>
-      </c>
-      <c r="B144" s="31"/>
-      <c r="C144" s="32"/>
-      <c r="D144" s="32"/>
-      <c r="E144" s="32"/>
-      <c r="F144" s="32"/>
-      <c r="G144" s="32"/>
-      <c r="H144" s="32"/>
-      <c r="I144" s="32"/>
-      <c r="J144" s="32"/>
-      <c r="K144" s="32"/>
-      <c r="L144" s="32" t="s">
-        <v>300</v>
-      </c>
-      <c r="M144" s="32"/>
-      <c r="N144" s="32"/>
-    </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>25</v>
-      </c>
-      <c r="E145" t="s">
-        <v>299</v>
-      </c>
-      <c r="F145" t="s">
-        <v>17</v>
-      </c>
-      <c r="J145" t="s">
-        <v>18</v>
-      </c>
-      <c r="K145" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F145,'feed pars'!B$6:B$43,0))</f>
-        <v>12.3</v>
-      </c>
-    </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>25</v>
-      </c>
-      <c r="E146" t="s">
-        <v>299</v>
-      </c>
-      <c r="F146" t="s">
-        <v>37</v>
-      </c>
-      <c r="J146" t="s">
-        <v>18</v>
-      </c>
-      <c r="K146" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F146,'feed pars'!B$6:B$43,0))</f>
-        <v>11.2</v>
-      </c>
-    </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>25</v>
-      </c>
-      <c r="E147" t="s">
-        <v>299</v>
-      </c>
-      <c r="F147" t="s">
-        <v>38</v>
-      </c>
-      <c r="J147" t="s">
-        <v>18</v>
-      </c>
-      <c r="K147" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F147,'feed pars'!B$6:B$43,0))</f>
-        <v>9.4</v>
-      </c>
-    </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>25</v>
-      </c>
-      <c r="E148" t="s">
-        <v>299</v>
-      </c>
-      <c r="F148" t="s">
-        <v>39</v>
-      </c>
-      <c r="J148" t="s">
-        <v>18</v>
-      </c>
-      <c r="K148" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F148,'feed pars'!B$6:B$43,0))</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
-        <v>25</v>
-      </c>
-      <c r="E149" t="s">
-        <v>299</v>
-      </c>
-      <c r="F149" t="s">
-        <v>40</v>
-      </c>
-      <c r="J149" t="s">
-        <v>18</v>
-      </c>
-      <c r="K149" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F149,'feed pars'!B$6:B$43,0))</f>
-        <v>13.2</v>
-      </c>
-    </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
-        <v>25</v>
-      </c>
-      <c r="E150" t="s">
-        <v>299</v>
-      </c>
-      <c r="F150" t="s">
-        <v>41</v>
-      </c>
-      <c r="J150" t="s">
-        <v>18</v>
-      </c>
-      <c r="K150" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F150,'feed pars'!B$6:B$43,0))</f>
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
-        <v>25</v>
-      </c>
-      <c r="E151" t="s">
-        <v>299</v>
-      </c>
-      <c r="F151" t="s">
-        <v>42</v>
-      </c>
-      <c r="J151" t="s">
-        <v>18</v>
-      </c>
-      <c r="K151" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F151,'feed pars'!B$6:B$43,0))</f>
-        <v>10.9</v>
-      </c>
-    </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
-        <v>25</v>
-      </c>
-      <c r="E152" t="s">
-        <v>299</v>
-      </c>
-      <c r="F152" t="s">
-        <v>35</v>
-      </c>
-      <c r="J152" t="s">
-        <v>18</v>
-      </c>
-      <c r="K152" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F152,'feed pars'!B$6:B$43,0))</f>
-        <v>18.5</v>
-      </c>
-    </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
-        <v>25</v>
-      </c>
-      <c r="E153" t="s">
-        <v>299</v>
-      </c>
       <c r="F153" t="s">
-        <v>43</v>
+        <v>310</v>
       </c>
       <c r="J153" t="s">
         <v>18</v>
       </c>
       <c r="K153" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F153,'feed pars'!B$6:B$43,0))</f>
-        <v>17.5</v>
-      </c>
-    </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F153,'feed pars'!B$6:B$43,0))</f>
+        <v>11.5</v>
+      </c>
+      <c r="M153" s="3"/>
+    </row>
+    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>25</v>
-      </c>
-      <c r="E154" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F154" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="J154" t="s">
         <v>18</v>
       </c>
       <c r="K154" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F154,'feed pars'!B$6:B$43,0))</f>
-        <v>29.8</v>
-      </c>
-    </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F154,'feed pars'!B$6:B$43,0))</f>
+        <v>10.4</v>
+      </c>
+      <c r="M154" s="3"/>
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>25</v>
-      </c>
-      <c r="E155" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F155" t="s">
-        <v>44</v>
+        <v>312</v>
       </c>
       <c r="J155" t="s">
         <v>18</v>
       </c>
       <c r="K155" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F155,'feed pars'!B$6:B$43,0))</f>
-        <v>9.9</v>
-      </c>
-    </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F155,'feed pars'!B$6:B$43,0))</f>
+        <v>10</v>
+      </c>
+      <c r="M155" s="3"/>
+    </row>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>25</v>
-      </c>
-      <c r="E156" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F156" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="J156" t="s">
         <v>18</v>
       </c>
       <c r="K156" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F156,'feed pars'!B$6:B$43,0))</f>
-        <v>10.3</v>
-      </c>
-    </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F156,'feed pars'!B$6:B$43,0))</f>
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>25</v>
-      </c>
-      <c r="E157" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F157" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J157" t="s">
         <v>18</v>
       </c>
       <c r="K157" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F157,'feed pars'!B$6:B$43,0))</f>
-        <v>7.7</v>
-      </c>
-    </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
-        <v>25</v>
-      </c>
-      <c r="E158" t="s">
-        <v>299</v>
-      </c>
-      <c r="F158" t="s">
-        <v>46</v>
-      </c>
-      <c r="J158" t="s">
-        <v>18</v>
-      </c>
-      <c r="K158" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F158,'feed pars'!B$6:B$43,0))</f>
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F157,'feed pars'!B$6:B$43,0))</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K158" s="3"/>
+    </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>25</v>
-      </c>
-      <c r="E159" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F159" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="J159" t="s">
         <v>18</v>
       </c>
       <c r="K159" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F159,'feed pars'!B$6:B$43,0))</f>
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F159,'feed pars'!B$6:B$43,0))</f>
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>25</v>
-      </c>
-      <c r="E160" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F160" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="J160" t="s">
         <v>18</v>
       </c>
       <c r="K160" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F160,'feed pars'!B$6:B$43,0))</f>
-        <v>7.8</v>
-      </c>
-    </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F160,'feed pars'!B$6:B$43,0))</f>
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>25</v>
-      </c>
-      <c r="E161" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F161" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="J161" t="s">
         <v>18</v>
       </c>
       <c r="K161" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F161,'feed pars'!B$6:B$43,0))</f>
-        <v>9.1999999999999993</v>
-      </c>
-    </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F161,'feed pars'!B$6:B$43,0))</f>
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>25</v>
-      </c>
-      <c r="E162" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F162" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="J162" t="s">
         <v>18</v>
       </c>
       <c r="K162" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F162,'feed pars'!B$6:B$43,0))</f>
-        <v>8.6999999999999993</v>
-      </c>
-    </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F162,'feed pars'!B$6:B$43,0))</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>25</v>
-      </c>
-      <c r="E163" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F163" t="s">
-        <v>51</v>
+        <v>317</v>
       </c>
       <c r="J163" t="s">
         <v>18</v>
       </c>
       <c r="K163" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F163,'feed pars'!B$6:B$43,0))</f>
-        <v>8.9</v>
-      </c>
-    </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F163,'feed pars'!B$6:B$43,0))</f>
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>25</v>
-      </c>
-      <c r="E164" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F164" t="s">
-        <v>313</v>
+        <v>40</v>
       </c>
       <c r="J164" t="s">
         <v>18</v>
       </c>
       <c r="K164" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F164,'feed pars'!B$6:B$43,0))</f>
-        <v>7.0888888888888877</v>
-      </c>
-    </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F164,'feed pars'!B$6:B$43,0))</f>
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>25</v>
-      </c>
-      <c r="E165" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F165" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="J165" t="s">
         <v>18</v>
       </c>
       <c r="K165" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F165,'feed pars'!B$6:B$43,0))</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F165,'feed pars'!B$6:B$43,0))</f>
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>25</v>
-      </c>
-      <c r="E166" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F166" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="J166" t="s">
         <v>18</v>
       </c>
       <c r="K166" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F166,'feed pars'!B$6:B$43,0))</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F166,'feed pars'!B$6:B$43,0))</f>
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>25</v>
-      </c>
-      <c r="E167" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F167" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="J167" t="s">
         <v>18</v>
       </c>
       <c r="K167" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F167,'feed pars'!B$6:B$43,0))</f>
-        <v>12.2</v>
-      </c>
-    </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F167,'feed pars'!B$6:B$43,0))</f>
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>25</v>
-      </c>
-      <c r="E168" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F168" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="J168" t="s">
         <v>18</v>
       </c>
       <c r="K168" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F168,'feed pars'!B$6:B$43,0))</f>
-        <v>12.2</v>
-      </c>
-    </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F168,'feed pars'!B$6:B$43,0))</f>
+        <v>20.100000000000001</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>25</v>
-      </c>
-      <c r="E169" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F169" t="s">
-        <v>56</v>
+        <v>305</v>
       </c>
       <c r="J169" t="s">
         <v>18</v>
       </c>
       <c r="K169" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F169,'feed pars'!B$6:B$43,0))</f>
-        <v>11.3</v>
-      </c>
-    </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F169,'feed pars'!B$6:B$43,0))</f>
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>25</v>
-      </c>
-      <c r="E170" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="F170" t="s">
-        <v>57</v>
+        <v>314</v>
       </c>
       <c r="J170" t="s">
         <v>18</v>
       </c>
       <c r="K170" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F170,'feed pars'!B$6:B$43,0))</f>
-        <v>10.8</v>
-      </c>
-    </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A171" s="30" t="s">
-        <v>392</v>
-      </c>
-      <c r="B171" s="31"/>
-      <c r="C171" s="32"/>
-      <c r="D171" s="32"/>
-      <c r="E171" s="32"/>
-      <c r="F171" s="32"/>
-      <c r="G171" s="32"/>
-      <c r="H171" s="32"/>
-      <c r="I171" s="32"/>
-      <c r="J171" s="32"/>
-      <c r="K171" s="32"/>
-      <c r="L171" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="M171" s="32"/>
-      <c r="N171" s="32"/>
-    </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F170,'feed pars'!B$6:B$43,0))</f>
+        <v>36.6</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>24</v>
+      </c>
+      <c r="F171" t="s">
+        <v>318</v>
+      </c>
+      <c r="J171" t="s">
+        <v>18</v>
+      </c>
+      <c r="K171" s="26">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F171,'feed pars'!B$6:B$43,0))</f>
+        <v>16.399999999999999</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F172" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="J172" t="s">
         <v>18</v>
       </c>
       <c r="K172" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F172,'feed pars'!B$6:B$43,0))</f>
-        <v>12.1</v>
-      </c>
-    </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F172,'feed pars'!B$6:B$43,0))</f>
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F173" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J173" t="s">
         <v>18</v>
       </c>
       <c r="K173" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F173,'feed pars'!B$6:B$43,0))</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F173,'feed pars'!B$6:B$43,0))</f>
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F174" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="J174" t="s">
         <v>18</v>
       </c>
       <c r="K174" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F174,'feed pars'!B$6:B$43,0))</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F174,'feed pars'!B$6:B$43,0))</f>
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F175" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="J175" t="s">
         <v>18</v>
       </c>
       <c r="K175" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F175,'feed pars'!B$6:B$43,0))</f>
-        <v>11.9</v>
-      </c>
-    </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F175,'feed pars'!B$6:B$43,0))</f>
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F176" t="s">
-        <v>40</v>
+        <v>319</v>
       </c>
       <c r="J176" t="s">
         <v>18</v>
       </c>
       <c r="K176" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F176,'feed pars'!B$6:B$43,0))</f>
-        <v>12.8</v>
-      </c>
-    </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F176,'feed pars'!B$6:B$43,0))</f>
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F177" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="J177" t="s">
         <v>18</v>
       </c>
       <c r="K177" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F177,'feed pars'!B$6:B$43,0))</f>
-        <v>11.2</v>
-      </c>
-    </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F177,'feed pars'!B$6:B$43,0))</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F178" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="J178" t="s">
         <v>18</v>
       </c>
       <c r="K178" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F178,'feed pars'!B$6:B$43,0))</f>
-        <v>10.7</v>
-      </c>
-    </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F178,'feed pars'!B$6:B$43,0))</f>
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F179" t="s">
-        <v>35</v>
+        <v>313</v>
       </c>
       <c r="J179" t="s">
         <v>18</v>
       </c>
       <c r="K179" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F179,'feed pars'!B$6:B$43,0))</f>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F179,'feed pars'!B$6:B$43,0))</f>
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F180" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="J180" t="s">
         <v>18</v>
       </c>
       <c r="K180" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F180,'feed pars'!B$6:B$43,0))</f>
-        <v>17.3</v>
-      </c>
-    </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F180,'feed pars'!B$6:B$43,0))</f>
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F181" t="s">
-        <v>314</v>
+        <v>53</v>
       </c>
       <c r="J181" t="s">
         <v>18</v>
       </c>
       <c r="K181" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F181,'feed pars'!B$6:B$43,0))</f>
-        <v>29.8</v>
-      </c>
-    </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F181,'feed pars'!B$6:B$43,0))</f>
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F182" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="J182" t="s">
         <v>18</v>
       </c>
       <c r="K182" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F182,'feed pars'!B$6:B$43,0))</f>
-        <v>9.3000000000000007</v>
-      </c>
-    </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F182,'feed pars'!B$6:B$43,0))</f>
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F183" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="J183" t="s">
         <v>18</v>
       </c>
       <c r="K183" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F183,'feed pars'!B$6:B$43,0))</f>
-        <v>9.6999999999999993</v>
-      </c>
-    </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F183,'feed pars'!B$6:B$43,0))</f>
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F184" t="s">
-        <v>36</v>
+        <v>324</v>
       </c>
       <c r="J184" t="s">
         <v>18</v>
       </c>
-      <c r="K184" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F184,'feed pars'!B$6:B$43,0))</f>
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
-        <v>25</v>
-      </c>
-      <c r="F185" t="s">
-        <v>46</v>
-      </c>
-      <c r="J185" t="s">
-        <v>18</v>
-      </c>
-      <c r="K185" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F185,'feed pars'!B$6:B$43,0))</f>
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K184" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A185" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="B185" s="7"/>
+      <c r="C185" s="6"/>
+      <c r="D185" s="6"/>
+      <c r="E185" s="6"/>
+      <c r="F185" s="6"/>
+      <c r="G185" s="6"/>
+      <c r="H185" s="6"/>
+      <c r="I185" s="6"/>
+      <c r="J185" s="6"/>
+      <c r="K185" s="6"/>
+      <c r="L185" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M185" s="6"/>
+      <c r="N185" s="6"/>
+    </row>
+    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>25</v>
+        <v>395</v>
       </c>
       <c r="F186" t="s">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="J186" t="s">
         <v>18</v>
       </c>
-      <c r="K186" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F186,'feed pars'!B$6:B$43,0))</f>
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K186" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>25</v>
+        <v>395</v>
       </c>
       <c r="F187" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="J187" t="s">
         <v>18</v>
       </c>
-      <c r="K187" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F187,'feed pars'!B$6:B$43,0))</f>
-        <v>7.2</v>
-      </c>
-    </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A188" t="s">
-        <v>25</v>
-      </c>
-      <c r="F188" t="s">
-        <v>49</v>
-      </c>
-      <c r="J188" t="s">
-        <v>18</v>
-      </c>
-      <c r="K188" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F188,'feed pars'!B$6:B$43,0))</f>
-        <v>8.6999999999999993</v>
-      </c>
-    </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
-        <v>25</v>
-      </c>
-      <c r="F189" t="s">
-        <v>50</v>
-      </c>
-      <c r="J189" t="s">
-        <v>18</v>
-      </c>
-      <c r="K189" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F189,'feed pars'!B$6:B$43,0))</f>
-        <v>8.1</v>
-      </c>
-    </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K187" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A188" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B188" s="8"/>
+      <c r="C188" s="9"/>
+      <c r="D188" s="9"/>
+      <c r="E188" s="9"/>
+      <c r="F188" s="9"/>
+      <c r="G188" s="9"/>
+      <c r="H188" s="9"/>
+      <c r="I188" s="9"/>
+      <c r="J188" s="9"/>
+      <c r="K188" s="9"/>
+      <c r="L188" s="9"/>
+      <c r="M188" s="9"/>
+      <c r="N188" s="9"/>
+    </row>
+    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A189" s="30" t="s">
+        <v>391</v>
+      </c>
+      <c r="B189" s="31"/>
+      <c r="C189" s="32"/>
+      <c r="D189" s="32"/>
+      <c r="E189" s="32"/>
+      <c r="F189" s="32"/>
+      <c r="G189" s="32"/>
+      <c r="H189" s="32"/>
+      <c r="I189" s="32"/>
+      <c r="J189" s="32"/>
+      <c r="K189" s="32"/>
+      <c r="L189" s="32" t="s">
+        <v>300</v>
+      </c>
+      <c r="M189" s="32"/>
+      <c r="N189" s="32"/>
+    </row>
+    <row r="190" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>25</v>
       </c>
+      <c r="E190" t="s">
+        <v>299</v>
+      </c>
       <c r="F190" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="J190" t="s">
         <v>18</v>
       </c>
       <c r="K190" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F190,'feed pars'!B$6:B$43,0))</f>
-        <v>8.1999999999999993</v>
-      </c>
-    </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F190,'feed pars'!B$6:B$43,0))</f>
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>25</v>
       </c>
+      <c r="E191" t="s">
+        <v>299</v>
+      </c>
       <c r="F191" t="s">
-        <v>313</v>
+        <v>37</v>
       </c>
       <c r="J191" t="s">
         <v>18</v>
       </c>
       <c r="K191" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F191,'feed pars'!B$6:B$43,0))</f>
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F191,'feed pars'!B$6:B$43,0))</f>
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>25</v>
       </c>
+      <c r="E192" t="s">
+        <v>299</v>
+      </c>
       <c r="F192" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="J192" t="s">
         <v>18</v>
       </c>
       <c r="K192" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F192,'feed pars'!B$6:B$43,0))</f>
-        <v>8.6999999999999993</v>
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F192,'feed pars'!B$6:B$43,0))</f>
+        <v>9.4</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>25</v>
       </c>
+      <c r="E193" t="s">
+        <v>299</v>
+      </c>
       <c r="F193" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="J193" t="s">
         <v>18</v>
       </c>
       <c r="K193" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F193,'feed pars'!B$6:B$43,0))</f>
-        <v>6.9</v>
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F193,'feed pars'!B$6:B$43,0))</f>
+        <v>12</v>
       </c>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>25</v>
       </c>
+      <c r="E194" t="s">
+        <v>299</v>
+      </c>
       <c r="F194" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="J194" t="s">
         <v>18</v>
       </c>
       <c r="K194" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F194,'feed pars'!B$6:B$43,0))</f>
-        <v>12.4</v>
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F194,'feed pars'!B$6:B$43,0))</f>
+        <v>13.2</v>
       </c>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>25</v>
       </c>
+      <c r="E195" t="s">
+        <v>299</v>
+      </c>
       <c r="F195" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="J195" t="s">
         <v>18</v>
       </c>
       <c r="K195" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F195,'feed pars'!B$6:B$43,0))</f>
-        <v>12.4</v>
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F195,'feed pars'!B$6:B$43,0))</f>
+        <v>11.5</v>
       </c>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>25</v>
       </c>
+      <c r="E196" t="s">
+        <v>299</v>
+      </c>
       <c r="F196" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="J196" t="s">
         <v>18</v>
       </c>
       <c r="K196" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F196,'feed pars'!B$6:B$43,0))</f>
-        <v>11.1</v>
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F196,'feed pars'!B$6:B$43,0))</f>
+        <v>10.9</v>
       </c>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>25</v>
       </c>
+      <c r="E197" t="s">
+        <v>299</v>
+      </c>
       <c r="F197" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="J197" t="s">
         <v>18</v>
       </c>
       <c r="K197" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F197,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F197,'feed pars'!B$6:B$43,0))</f>
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>25</v>
+      </c>
+      <c r="E198" t="s">
+        <v>299</v>
+      </c>
+      <c r="F198" t="s">
+        <v>43</v>
+      </c>
+      <c r="J198" t="s">
+        <v>18</v>
+      </c>
+      <c r="K198" s="26">
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F198,'feed pars'!B$6:B$43,0))</f>
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>25</v>
+      </c>
+      <c r="E199" t="s">
+        <v>299</v>
+      </c>
+      <c r="F199" t="s">
+        <v>314</v>
+      </c>
+      <c r="J199" t="s">
+        <v>18</v>
+      </c>
+      <c r="K199" s="26">
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F199,'feed pars'!B$6:B$43,0))</f>
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>25</v>
+      </c>
+      <c r="E200" t="s">
+        <v>299</v>
+      </c>
+      <c r="F200" t="s">
+        <v>44</v>
+      </c>
+      <c r="J200" t="s">
+        <v>18</v>
+      </c>
+      <c r="K200" s="26">
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F200,'feed pars'!B$6:B$43,0))</f>
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>25</v>
+      </c>
+      <c r="E201" t="s">
+        <v>299</v>
+      </c>
+      <c r="F201" t="s">
+        <v>45</v>
+      </c>
+      <c r="J201" t="s">
+        <v>18</v>
+      </c>
+      <c r="K201" s="26">
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F201,'feed pars'!B$6:B$43,0))</f>
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>25</v>
+      </c>
+      <c r="E202" t="s">
+        <v>299</v>
+      </c>
+      <c r="F202" t="s">
+        <v>36</v>
+      </c>
+      <c r="J202" t="s">
+        <v>18</v>
+      </c>
+      <c r="K202" s="26">
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F202,'feed pars'!B$6:B$43,0))</f>
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>25</v>
+      </c>
+      <c r="E203" t="s">
+        <v>299</v>
+      </c>
+      <c r="F203" t="s">
+        <v>46</v>
+      </c>
+      <c r="J203" t="s">
+        <v>18</v>
+      </c>
+      <c r="K203" s="26">
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F203,'feed pars'!B$6:B$43,0))</f>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>25</v>
+      </c>
+      <c r="E204" t="s">
+        <v>299</v>
+      </c>
+      <c r="F204" t="s">
+        <v>47</v>
+      </c>
+      <c r="J204" t="s">
+        <v>18</v>
+      </c>
+      <c r="K204" s="26">
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F204,'feed pars'!B$6:B$43,0))</f>
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>25</v>
+      </c>
+      <c r="E205" t="s">
+        <v>299</v>
+      </c>
+      <c r="F205" t="s">
+        <v>48</v>
+      </c>
+      <c r="J205" t="s">
+        <v>18</v>
+      </c>
+      <c r="K205" s="26">
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F205,'feed pars'!B$6:B$43,0))</f>
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>25</v>
+      </c>
+      <c r="E206" t="s">
+        <v>299</v>
+      </c>
+      <c r="F206" t="s">
+        <v>49</v>
+      </c>
+      <c r="J206" t="s">
+        <v>18</v>
+      </c>
+      <c r="K206" s="26">
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F206,'feed pars'!B$6:B$43,0))</f>
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>25</v>
+      </c>
+      <c r="E207" t="s">
+        <v>299</v>
+      </c>
+      <c r="F207" t="s">
+        <v>50</v>
+      </c>
+      <c r="J207" t="s">
+        <v>18</v>
+      </c>
+      <c r="K207" s="26">
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F207,'feed pars'!B$6:B$43,0))</f>
+        <v>8.6999999999999993</v>
+      </c>
+    </row>
+    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>25</v>
+      </c>
+      <c r="E208" t="s">
+        <v>299</v>
+      </c>
+      <c r="F208" t="s">
+        <v>51</v>
+      </c>
+      <c r="J208" t="s">
+        <v>18</v>
+      </c>
+      <c r="K208" s="26">
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F208,'feed pars'!B$6:B$43,0))</f>
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="209" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>25</v>
+      </c>
+      <c r="E209" t="s">
+        <v>299</v>
+      </c>
+      <c r="F209" t="s">
+        <v>313</v>
+      </c>
+      <c r="J209" t="s">
+        <v>18</v>
+      </c>
+      <c r="K209" s="26">
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F209,'feed pars'!B$6:B$43,0))</f>
+        <v>7.0888888888888877</v>
+      </c>
+    </row>
+    <row r="210" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>25</v>
+      </c>
+      <c r="E210" t="s">
+        <v>299</v>
+      </c>
+      <c r="F210" t="s">
+        <v>52</v>
+      </c>
+      <c r="J210" t="s">
+        <v>18</v>
+      </c>
+      <c r="K210" s="26">
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F210,'feed pars'!B$6:B$43,0))</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="211" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>25</v>
+      </c>
+      <c r="E211" t="s">
+        <v>299</v>
+      </c>
+      <c r="F211" t="s">
+        <v>53</v>
+      </c>
+      <c r="J211" t="s">
+        <v>18</v>
+      </c>
+      <c r="K211" s="26">
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F211,'feed pars'!B$6:B$43,0))</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="212" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>25</v>
+      </c>
+      <c r="E212" t="s">
+        <v>299</v>
+      </c>
+      <c r="F212" t="s">
+        <v>54</v>
+      </c>
+      <c r="J212" t="s">
+        <v>18</v>
+      </c>
+      <c r="K212" s="26">
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F212,'feed pars'!B$6:B$43,0))</f>
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="213" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>25</v>
+      </c>
+      <c r="E213" t="s">
+        <v>299</v>
+      </c>
+      <c r="F213" t="s">
+        <v>55</v>
+      </c>
+      <c r="J213" t="s">
+        <v>18</v>
+      </c>
+      <c r="K213" s="26">
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F213,'feed pars'!B$6:B$43,0))</f>
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="214" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>25</v>
+      </c>
+      <c r="E214" t="s">
+        <v>299</v>
+      </c>
+      <c r="F214" t="s">
+        <v>56</v>
+      </c>
+      <c r="J214" t="s">
+        <v>18</v>
+      </c>
+      <c r="K214" s="26">
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F214,'feed pars'!B$6:B$43,0))</f>
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="215" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>25</v>
+      </c>
+      <c r="E215" t="s">
+        <v>299</v>
+      </c>
+      <c r="F215" t="s">
+        <v>57</v>
+      </c>
+      <c r="J215" t="s">
+        <v>18</v>
+      </c>
+      <c r="K215" s="26">
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F215,'feed pars'!B$6:B$43,0))</f>
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="216" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A216" s="30" t="s">
+        <v>392</v>
+      </c>
+      <c r="B216" s="31"/>
+      <c r="C216" s="32"/>
+      <c r="D216" s="32"/>
+      <c r="E216" s="32"/>
+      <c r="F216" s="32"/>
+      <c r="G216" s="32"/>
+      <c r="H216" s="32"/>
+      <c r="I216" s="32"/>
+      <c r="J216" s="32"/>
+      <c r="K216" s="32"/>
+      <c r="L216" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="M216" s="32"/>
+      <c r="N216" s="32"/>
+    </row>
+    <row r="217" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>25</v>
+      </c>
+      <c r="F217" t="s">
+        <v>17</v>
+      </c>
+      <c r="J217" t="s">
+        <v>18</v>
+      </c>
+      <c r="K217" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F217,'feed pars'!B$6:B$43,0))</f>
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>25</v>
+      </c>
+      <c r="F218" t="s">
+        <v>37</v>
+      </c>
+      <c r="J218" t="s">
+        <v>18</v>
+      </c>
+      <c r="K218" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F218,'feed pars'!B$6:B$43,0))</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="219" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>25</v>
+      </c>
+      <c r="F219" t="s">
+        <v>38</v>
+      </c>
+      <c r="J219" t="s">
+        <v>18</v>
+      </c>
+      <c r="K219" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F219,'feed pars'!B$6:B$43,0))</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="220" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>25</v>
+      </c>
+      <c r="F220" t="s">
+        <v>39</v>
+      </c>
+      <c r="J220" t="s">
+        <v>18</v>
+      </c>
+      <c r="K220" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F220,'feed pars'!B$6:B$43,0))</f>
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="221" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>25</v>
+      </c>
+      <c r="F221" t="s">
+        <v>40</v>
+      </c>
+      <c r="J221" t="s">
+        <v>18</v>
+      </c>
+      <c r="K221" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F221,'feed pars'!B$6:B$43,0))</f>
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="222" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>25</v>
+      </c>
+      <c r="F222" t="s">
+        <v>41</v>
+      </c>
+      <c r="J222" t="s">
+        <v>18</v>
+      </c>
+      <c r="K222" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F222,'feed pars'!B$6:B$43,0))</f>
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="223" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>25</v>
+      </c>
+      <c r="F223" t="s">
+        <v>42</v>
+      </c>
+      <c r="J223" t="s">
+        <v>18</v>
+      </c>
+      <c r="K223" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F223,'feed pars'!B$6:B$43,0))</f>
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="224" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>25</v>
+      </c>
+      <c r="F224" t="s">
+        <v>35</v>
+      </c>
+      <c r="J224" t="s">
+        <v>18</v>
+      </c>
+      <c r="K224" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F224,'feed pars'!B$6:B$43,0))</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>25</v>
+      </c>
+      <c r="F225" t="s">
+        <v>43</v>
+      </c>
+      <c r="J225" t="s">
+        <v>18</v>
+      </c>
+      <c r="K225" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F225,'feed pars'!B$6:B$43,0))</f>
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>25</v>
+      </c>
+      <c r="F226" t="s">
+        <v>314</v>
+      </c>
+      <c r="J226" t="s">
+        <v>18</v>
+      </c>
+      <c r="K226" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F226,'feed pars'!B$6:B$43,0))</f>
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>25</v>
+      </c>
+      <c r="F227" t="s">
+        <v>44</v>
+      </c>
+      <c r="J227" t="s">
+        <v>18</v>
+      </c>
+      <c r="K227" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F227,'feed pars'!B$6:B$43,0))</f>
+        <v>9.3000000000000007</v>
+      </c>
+    </row>
+    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>25</v>
+      </c>
+      <c r="F228" t="s">
+        <v>45</v>
+      </c>
+      <c r="J228" t="s">
+        <v>18</v>
+      </c>
+      <c r="K228" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F228,'feed pars'!B$6:B$43,0))</f>
+        <v>9.6999999999999993</v>
+      </c>
+    </row>
+    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>25</v>
+      </c>
+      <c r="F229" t="s">
+        <v>36</v>
+      </c>
+      <c r="J229" t="s">
+        <v>18</v>
+      </c>
+      <c r="K229" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F229,'feed pars'!B$6:B$43,0))</f>
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>25</v>
+      </c>
+      <c r="F230" t="s">
+        <v>46</v>
+      </c>
+      <c r="J230" t="s">
+        <v>18</v>
+      </c>
+      <c r="K230" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F230,'feed pars'!B$6:B$43,0))</f>
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>25</v>
+      </c>
+      <c r="F231" t="s">
+        <v>47</v>
+      </c>
+      <c r="J231" t="s">
+        <v>18</v>
+      </c>
+      <c r="K231" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F231,'feed pars'!B$6:B$43,0))</f>
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>25</v>
+      </c>
+      <c r="F232" t="s">
+        <v>48</v>
+      </c>
+      <c r="J232" t="s">
+        <v>18</v>
+      </c>
+      <c r="K232" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F232,'feed pars'!B$6:B$43,0))</f>
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="233" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>25</v>
+      </c>
+      <c r="F233" t="s">
+        <v>49</v>
+      </c>
+      <c r="J233" t="s">
+        <v>18</v>
+      </c>
+      <c r="K233" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F233,'feed pars'!B$6:B$43,0))</f>
+        <v>8.6999999999999993</v>
+      </c>
+    </row>
+    <row r="234" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>25</v>
+      </c>
+      <c r="F234" t="s">
+        <v>50</v>
+      </c>
+      <c r="J234" t="s">
+        <v>18</v>
+      </c>
+      <c r="K234" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F234,'feed pars'!B$6:B$43,0))</f>
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>25</v>
+      </c>
+      <c r="F235" t="s">
+        <v>51</v>
+      </c>
+      <c r="J235" t="s">
+        <v>18</v>
+      </c>
+      <c r="K235" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F235,'feed pars'!B$6:B$43,0))</f>
+        <v>8.1999999999999993</v>
+      </c>
+    </row>
+    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>25</v>
+      </c>
+      <c r="F236" t="s">
+        <v>313</v>
+      </c>
+      <c r="J236" t="s">
+        <v>18</v>
+      </c>
+      <c r="K236" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F236,'feed pars'!B$6:B$43,0))</f>
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>25</v>
+      </c>
+      <c r="F237" t="s">
+        <v>52</v>
+      </c>
+      <c r="J237" t="s">
+        <v>18</v>
+      </c>
+      <c r="K237" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F237,'feed pars'!B$6:B$43,0))</f>
+        <v>8.6999999999999993</v>
+      </c>
+    </row>
+    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>25</v>
+      </c>
+      <c r="F238" t="s">
+        <v>53</v>
+      </c>
+      <c r="J238" t="s">
+        <v>18</v>
+      </c>
+      <c r="K238" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F238,'feed pars'!B$6:B$43,0))</f>
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>25</v>
+      </c>
+      <c r="F239" t="s">
+        <v>54</v>
+      </c>
+      <c r="J239" t="s">
+        <v>18</v>
+      </c>
+      <c r="K239" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F239,'feed pars'!B$6:B$43,0))</f>
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>25</v>
+      </c>
+      <c r="F240" t="s">
+        <v>55</v>
+      </c>
+      <c r="J240" t="s">
+        <v>18</v>
+      </c>
+      <c r="K240" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F240,'feed pars'!B$6:B$43,0))</f>
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>25</v>
+      </c>
+      <c r="F241" t="s">
+        <v>56</v>
+      </c>
+      <c r="J241" t="s">
+        <v>18</v>
+      </c>
+      <c r="K241" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F241,'feed pars'!B$6:B$43,0))</f>
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>25</v>
+      </c>
+      <c r="F242" t="s">
+        <v>57</v>
+      </c>
+      <c r="J242" t="s">
+        <v>18</v>
+      </c>
+      <c r="K242" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F242,'feed pars'!B$6:B$43,0))</f>
         <v>10.8</v>
       </c>
     </row>

--- a/data/prod_parameters/FeedMgmt.xlsx
+++ b/data/prod_parameters/FeedMgmt.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1243" uniqueCount="411">
   <si>
     <t>f_feed</t>
   </si>
@@ -1225,9 +1225,6 @@
     <t>horses</t>
   </si>
   <si>
-    <t>Horses</t>
-  </si>
-  <si>
     <t>storage_losses</t>
   </si>
   <si>
@@ -1265,6 +1262,25 @@
   </si>
   <si>
     <t>No storage</t>
+  </si>
+  <si>
+    <r>
+      <t>Horses</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Assume same as cattle for now)</t>
+    </r>
+  </si>
+  <si>
+    <t>https://glw-feeds.co.uk/index.php/wheat-feed-2/</t>
   </si>
 </sst>
 </file>
@@ -1274,7 +1290,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1343,6 +1359,14 @@
     <font>
       <sz val="11"/>
       <color theme="2" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1417,7 +1441,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1468,6 +1492,7 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1749,7 +1774,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O242"/>
+  <dimension ref="A1:O254"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="7" width="20.28515625" customWidth="1"/>
@@ -2263,7 +2288,7 @@
       </c>
       <c r="K31" s="22">
         <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F31,'feed pars'!B$6:B$43,0))</f>
-        <v>1.1363636363636365</v>
+        <v>1.1299435028248588</v>
       </c>
     </row>
     <row r="32" spans="6:13" x14ac:dyDescent="0.25">
@@ -2950,7 +2975,7 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -2968,7 +2993,7 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="J69" s="10" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K69" s="10">
         <v>0</v>
@@ -2982,7 +3007,7 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="J70" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="K70" s="10">
         <v>0</v>
@@ -3008,7 +3033,7 @@
         <v>310</v>
       </c>
       <c r="J71" s="29" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K71" s="29">
         <f>(0.8*20+0.2*2)</f>
@@ -3018,10 +3043,10 @@
         <v>28</v>
       </c>
       <c r="M71" s="29" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="N71" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
@@ -3032,7 +3057,7 @@
         <v>310</v>
       </c>
       <c r="J72" s="29" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K72" s="29">
         <f>(0.6*20+0.4*2)</f>
@@ -3042,21 +3067,21 @@
         <v>28</v>
       </c>
       <c r="M72" s="29" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="N72" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F73" t="s">
         <v>310</v>
       </c>
       <c r="J73" s="29" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K73" s="29">
         <v>2</v>
@@ -3065,10 +3090,10 @@
         <v>28</v>
       </c>
       <c r="M73" s="29" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="N73" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
@@ -3079,7 +3104,7 @@
         <v>310</v>
       </c>
       <c r="J74" s="29" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K74" s="29">
         <v>2</v>
@@ -3088,10 +3113,10 @@
         <v>28</v>
       </c>
       <c r="M74" s="29" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="N74" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
@@ -3108,7 +3133,7 @@
         <v>310</v>
       </c>
       <c r="J75" s="29" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="K75" s="29">
         <v>5</v>
@@ -3117,10 +3142,10 @@
         <v>28</v>
       </c>
       <c r="M75" s="29" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="N75" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
@@ -3134,7 +3159,7 @@
         <v>310</v>
       </c>
       <c r="J76" s="29" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="K76" s="29">
         <v>5</v>
@@ -3143,10 +3168,10 @@
         <v>28</v>
       </c>
       <c r="M76" s="29" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="N76" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
@@ -3157,7 +3182,7 @@
         <v>310</v>
       </c>
       <c r="J77" s="29" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="K77" s="29">
         <f>0.9*5+0.1*15</f>
@@ -3167,21 +3192,21 @@
         <v>28</v>
       </c>
       <c r="M77" s="29" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="N77" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F78" t="s">
         <v>310</v>
       </c>
       <c r="J78" s="29" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="K78" s="29">
         <v>15</v>
@@ -3191,7 +3216,7 @@
       </c>
       <c r="M78" s="29"/>
       <c r="N78" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
@@ -3202,7 +3227,7 @@
         <v>310</v>
       </c>
       <c r="J79" s="29" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="K79" s="29">
         <v>15</v>
@@ -3212,7 +3237,7 @@
       </c>
       <c r="M79" s="29"/>
       <c r="N79" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
@@ -3498,7 +3523,7 @@
         <v>312</v>
       </c>
       <c r="J89" s="29" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K89" s="29">
         <v>5</v>
@@ -3508,7 +3533,7 @@
       </c>
       <c r="M89" s="29"/>
       <c r="N89" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
@@ -3667,7 +3692,7 @@
         <v>2</v>
       </c>
       <c r="J95" s="29" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K95" s="29">
         <v>5</v>
@@ -3677,7 +3702,7 @@
       </c>
       <c r="M95" s="29"/>
       <c r="N95" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
@@ -3836,7 +3861,7 @@
         <v>12</v>
       </c>
       <c r="J101" s="29" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K101" s="29">
         <v>5</v>
@@ -3846,7 +3871,7 @@
       </c>
       <c r="M101" s="29"/>
       <c r="N101" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
@@ -4006,7 +4031,7 @@
         <v>33</v>
       </c>
       <c r="J107" s="29" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K107" s="29">
         <v>0</v>
@@ -4015,7 +4040,7 @@
         <v>28</v>
       </c>
       <c r="M107" s="29" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="N107" s="33"/>
     </row>
@@ -4027,7 +4052,7 @@
         <v>33</v>
       </c>
       <c r="J108" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="K108" s="29">
         <f>100-55</f>
@@ -4037,10 +4062,10 @@
         <v>28</v>
       </c>
       <c r="M108" s="29" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="N108" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.25">
@@ -4051,7 +4076,7 @@
         <v>33</v>
       </c>
       <c r="J109" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="K109" s="29">
         <f>100-50</f>
@@ -4061,10 +4086,10 @@
         <v>28</v>
       </c>
       <c r="M109" s="29" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="N109" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.25">
@@ -4073,7 +4098,7 @@
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K111" s="3"/>
       <c r="M111" s="29"/>
@@ -4533,7 +4558,7 @@
       </c>
       <c r="K141" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F141,'feed pars'!B$6:B$43,0))</f>
-        <v>88</v>
+        <v>88.5</v>
       </c>
       <c r="L141" t="s">
         <v>28</v>
@@ -5192,7 +5217,7 @@
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A185" s="7" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="B185" s="7"/>
       <c r="C185" s="6"/>
@@ -5220,8 +5245,9 @@
       <c r="J186" t="s">
         <v>18</v>
       </c>
-      <c r="K186" s="3">
-        <v>10</v>
+      <c r="K186" s="26">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F186,'feed pars'!B$6:B$43,0))</f>
+        <v>9.1</v>
       </c>
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.25">
@@ -5234,265 +5260,206 @@
       <c r="J187" t="s">
         <v>18</v>
       </c>
-      <c r="K187" s="3">
+      <c r="K187" s="34">
+        <f>K157</f>
         <v>10</v>
       </c>
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A188" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B188" s="8"/>
-      <c r="C188" s="9"/>
-      <c r="D188" s="9"/>
-      <c r="E188" s="9"/>
-      <c r="F188" s="9"/>
-      <c r="G188" s="9"/>
-      <c r="H188" s="9"/>
-      <c r="I188" s="9"/>
-      <c r="J188" s="9"/>
-      <c r="K188" s="9"/>
-      <c r="L188" s="9"/>
-      <c r="M188" s="9"/>
-      <c r="N188" s="9"/>
+      <c r="K188" s="34"/>
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A189" s="30" t="s">
-        <v>391</v>
-      </c>
-      <c r="B189" s="31"/>
-      <c r="C189" s="32"/>
-      <c r="D189" s="32"/>
-      <c r="E189" s="32"/>
-      <c r="F189" s="32"/>
-      <c r="G189" s="32"/>
-      <c r="H189" s="32"/>
-      <c r="I189" s="32"/>
-      <c r="J189" s="32"/>
-      <c r="K189" s="32"/>
-      <c r="L189" s="32" t="s">
-        <v>300</v>
-      </c>
-      <c r="M189" s="32"/>
-      <c r="N189" s="32"/>
+      <c r="A189" t="s">
+        <v>395</v>
+      </c>
+      <c r="F189" t="s">
+        <v>38</v>
+      </c>
+      <c r="J189" t="s">
+        <v>18</v>
+      </c>
+      <c r="K189" s="34">
+        <f>K161</f>
+        <v>11.7</v>
+      </c>
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>25</v>
-      </c>
-      <c r="E190" t="s">
-        <v>299</v>
+        <v>395</v>
       </c>
       <c r="F190" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="J190" t="s">
         <v>18</v>
       </c>
-      <c r="K190" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F190,'feed pars'!B$6:B$43,0))</f>
-        <v>12.3</v>
+      <c r="K190" s="34">
+        <f>K160</f>
+        <v>13.2</v>
       </c>
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>25</v>
-      </c>
-      <c r="E191" t="s">
-        <v>299</v>
+        <v>395</v>
       </c>
       <c r="F191" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="J191" t="s">
         <v>18</v>
       </c>
-      <c r="K191" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F191,'feed pars'!B$6:B$43,0))</f>
-        <v>11.2</v>
+      <c r="K191" s="34">
+        <f>K159</f>
+        <v>14.1</v>
       </c>
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>25</v>
-      </c>
-      <c r="E192" t="s">
-        <v>299</v>
+        <v>395</v>
       </c>
       <c r="F192" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="J192" t="s">
         <v>18</v>
       </c>
-      <c r="K192" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F192,'feed pars'!B$6:B$43,0))</f>
-        <v>9.4</v>
-      </c>
-    </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K192" s="34">
+        <f t="shared" ref="K192:K198" si="14">K160</f>
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="193" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>25</v>
-      </c>
-      <c r="E193" t="s">
-        <v>299</v>
+        <v>395</v>
       </c>
       <c r="F193" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="J193" t="s">
         <v>18</v>
       </c>
-      <c r="K193" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F193,'feed pars'!B$6:B$43,0))</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K193" s="34">
+        <f t="shared" si="14"/>
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="194" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>25</v>
-      </c>
-      <c r="E194" t="s">
-        <v>299</v>
+        <v>395</v>
       </c>
       <c r="F194" t="s">
-        <v>40</v>
+        <v>314</v>
       </c>
       <c r="J194" t="s">
         <v>18</v>
       </c>
-      <c r="K194" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F194,'feed pars'!B$6:B$43,0))</f>
-        <v>13.2</v>
-      </c>
-    </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K194" s="34">
+        <f t="shared" si="14"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="195" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>25</v>
-      </c>
-      <c r="E195" t="s">
-        <v>299</v>
+        <v>395</v>
       </c>
       <c r="F195" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="J195" t="s">
         <v>18</v>
       </c>
-      <c r="K195" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F195,'feed pars'!B$6:B$43,0))</f>
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K195" s="34">
+        <f t="shared" si="14"/>
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="196" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>25</v>
-      </c>
-      <c r="E196" t="s">
-        <v>299</v>
+        <v>395</v>
       </c>
       <c r="F196" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="J196" t="s">
         <v>18</v>
       </c>
-      <c r="K196" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F196,'feed pars'!B$6:B$43,0))</f>
-        <v>10.9</v>
-      </c>
-    </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K196" s="34">
+        <f t="shared" si="14"/>
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="197" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>25</v>
-      </c>
-      <c r="E197" t="s">
-        <v>299</v>
+        <v>395</v>
       </c>
       <c r="F197" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="J197" t="s">
         <v>18</v>
       </c>
-      <c r="K197" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F197,'feed pars'!B$6:B$43,0))</f>
-        <v>18.5</v>
-      </c>
-    </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K197" s="34">
+        <f t="shared" si="14"/>
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="198" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>25</v>
-      </c>
-      <c r="E198" t="s">
-        <v>299</v>
+        <v>395</v>
       </c>
       <c r="F198" t="s">
-        <v>43</v>
+        <v>319</v>
       </c>
       <c r="J198" t="s">
         <v>18</v>
       </c>
-      <c r="K198" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F198,'feed pars'!B$6:B$43,0))</f>
-        <v>17.5</v>
-      </c>
-    </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A199" t="s">
-        <v>25</v>
-      </c>
-      <c r="E199" t="s">
-        <v>299</v>
-      </c>
-      <c r="F199" t="s">
-        <v>314</v>
-      </c>
-      <c r="J199" t="s">
-        <v>18</v>
-      </c>
-      <c r="K199" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F199,'feed pars'!B$6:B$43,0))</f>
-        <v>29.8</v>
-      </c>
-    </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A200" t="s">
-        <v>25</v>
-      </c>
-      <c r="E200" t="s">
-        <v>299</v>
-      </c>
-      <c r="F200" t="s">
-        <v>44</v>
-      </c>
-      <c r="J200" t="s">
-        <v>18</v>
-      </c>
-      <c r="K200" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F200,'feed pars'!B$6:B$43,0))</f>
-        <v>9.9</v>
-      </c>
-    </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
-        <v>25</v>
-      </c>
-      <c r="E201" t="s">
-        <v>299</v>
-      </c>
-      <c r="F201" t="s">
-        <v>45</v>
-      </c>
-      <c r="J201" t="s">
-        <v>18</v>
-      </c>
-      <c r="K201" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F201,'feed pars'!B$6:B$43,0))</f>
-        <v>10.3</v>
-      </c>
-    </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K198" s="34">
+        <f t="shared" si="14"/>
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="199" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K199" s="3"/>
+    </row>
+    <row r="200" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A200" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B200" s="8"/>
+      <c r="C200" s="9"/>
+      <c r="D200" s="9"/>
+      <c r="E200" s="9"/>
+      <c r="F200" s="9"/>
+      <c r="G200" s="9"/>
+      <c r="H200" s="9"/>
+      <c r="I200" s="9"/>
+      <c r="J200" s="9"/>
+      <c r="K200" s="9"/>
+      <c r="L200" s="9"/>
+      <c r="M200" s="9"/>
+      <c r="N200" s="9"/>
+    </row>
+    <row r="201" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A201" s="30" t="s">
+        <v>391</v>
+      </c>
+      <c r="B201" s="31"/>
+      <c r="C201" s="32"/>
+      <c r="D201" s="32"/>
+      <c r="E201" s="32"/>
+      <c r="F201" s="32"/>
+      <c r="G201" s="32"/>
+      <c r="H201" s="32"/>
+      <c r="I201" s="32"/>
+      <c r="J201" s="32"/>
+      <c r="K201" s="32"/>
+      <c r="L201" s="32" t="s">
+        <v>300</v>
+      </c>
+      <c r="M201" s="32"/>
+      <c r="N201" s="32"/>
+    </row>
+    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>25</v>
       </c>
@@ -5500,17 +5467,17 @@
         <v>299</v>
       </c>
       <c r="F202" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="J202" t="s">
         <v>18</v>
       </c>
       <c r="K202" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F202,'feed pars'!B$6:B$43,0))</f>
-        <v>7.7</v>
-      </c>
-    </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>25</v>
       </c>
@@ -5518,17 +5485,17 @@
         <v>299</v>
       </c>
       <c r="F203" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J203" t="s">
         <v>18</v>
       </c>
       <c r="K203" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F203,'feed pars'!B$6:B$43,0))</f>
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>25</v>
       </c>
@@ -5536,17 +5503,17 @@
         <v>299</v>
       </c>
       <c r="F204" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="J204" t="s">
         <v>18</v>
       </c>
       <c r="K204" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F204,'feed pars'!B$6:B$43,0))</f>
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>25</v>
       </c>
@@ -5554,17 +5521,17 @@
         <v>299</v>
       </c>
       <c r="F205" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="J205" t="s">
         <v>18</v>
       </c>
       <c r="K205" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F205,'feed pars'!B$6:B$43,0))</f>
-        <v>7.8</v>
-      </c>
-    </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>25</v>
       </c>
@@ -5572,17 +5539,17 @@
         <v>299</v>
       </c>
       <c r="F206" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="J206" t="s">
         <v>18</v>
       </c>
       <c r="K206" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F206,'feed pars'!B$6:B$43,0))</f>
-        <v>9.1999999999999993</v>
-      </c>
-    </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>25</v>
       </c>
@@ -5590,17 +5557,17 @@
         <v>299</v>
       </c>
       <c r="F207" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="J207" t="s">
         <v>18</v>
       </c>
       <c r="K207" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F207,'feed pars'!B$6:B$43,0))</f>
-        <v>8.6999999999999993</v>
-      </c>
-    </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>25</v>
       </c>
@@ -5608,17 +5575,17 @@
         <v>299</v>
       </c>
       <c r="F208" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="J208" t="s">
         <v>18</v>
       </c>
       <c r="K208" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F208,'feed pars'!B$6:B$43,0))</f>
-        <v>8.9</v>
-      </c>
-    </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.25">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>25</v>
       </c>
@@ -5626,17 +5593,17 @@
         <v>299</v>
       </c>
       <c r="F209" t="s">
-        <v>313</v>
+        <v>35</v>
       </c>
       <c r="J209" t="s">
         <v>18</v>
       </c>
       <c r="K209" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F209,'feed pars'!B$6:B$43,0))</f>
-        <v>7.0888888888888877</v>
-      </c>
-    </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.25">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>25</v>
       </c>
@@ -5644,17 +5611,17 @@
         <v>299</v>
       </c>
       <c r="F210" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="J210" t="s">
         <v>18</v>
       </c>
       <c r="K210" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F210,'feed pars'!B$6:B$43,0))</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.25">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>25</v>
       </c>
@@ -5662,17 +5629,17 @@
         <v>299</v>
       </c>
       <c r="F211" t="s">
-        <v>53</v>
+        <v>314</v>
       </c>
       <c r="J211" t="s">
         <v>18</v>
       </c>
       <c r="K211" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F211,'feed pars'!B$6:B$43,0))</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.25">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>25</v>
       </c>
@@ -5680,17 +5647,17 @@
         <v>299</v>
       </c>
       <c r="F212" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="J212" t="s">
         <v>18</v>
       </c>
       <c r="K212" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F212,'feed pars'!B$6:B$43,0))</f>
-        <v>12.2</v>
-      </c>
-    </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.25">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>25</v>
       </c>
@@ -5698,17 +5665,17 @@
         <v>299</v>
       </c>
       <c r="F213" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="J213" t="s">
         <v>18</v>
       </c>
       <c r="K213" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F213,'feed pars'!B$6:B$43,0))</f>
-        <v>12.2</v>
-      </c>
-    </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.25">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>25</v>
       </c>
@@ -5716,17 +5683,17 @@
         <v>299</v>
       </c>
       <c r="F214" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="J214" t="s">
         <v>18</v>
       </c>
       <c r="K214" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F214,'feed pars'!B$6:B$43,0))</f>
-        <v>11.3</v>
-      </c>
-    </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.25">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>25</v>
       </c>
@@ -5734,394 +5701,430 @@
         <v>299</v>
       </c>
       <c r="F215" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="J215" t="s">
         <v>18</v>
       </c>
       <c r="K215" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F215,'feed pars'!B$6:B$43,0))</f>
-        <v>10.8</v>
-      </c>
-    </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A216" s="30" t="s">
-        <v>392</v>
-      </c>
-      <c r="B216" s="31"/>
-      <c r="C216" s="32"/>
-      <c r="D216" s="32"/>
-      <c r="E216" s="32"/>
-      <c r="F216" s="32"/>
-      <c r="G216" s="32"/>
-      <c r="H216" s="32"/>
-      <c r="I216" s="32"/>
-      <c r="J216" s="32"/>
-      <c r="K216" s="32"/>
-      <c r="L216" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="M216" s="32"/>
-      <c r="N216" s="32"/>
-    </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.25">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>25</v>
+      </c>
+      <c r="E216" t="s">
+        <v>299</v>
+      </c>
+      <c r="F216" t="s">
+        <v>47</v>
+      </c>
+      <c r="J216" t="s">
+        <v>18</v>
+      </c>
+      <c r="K216" s="26">
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F216,'feed pars'!B$6:B$43,0))</f>
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>25</v>
       </c>
+      <c r="E217" t="s">
+        <v>299</v>
+      </c>
       <c r="F217" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="J217" t="s">
         <v>18</v>
       </c>
       <c r="K217" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F217,'feed pars'!B$6:B$43,0))</f>
-        <v>12.1</v>
-      </c>
-    </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F217,'feed pars'!B$6:B$43,0))</f>
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="218" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>25</v>
       </c>
+      <c r="E218" t="s">
+        <v>299</v>
+      </c>
       <c r="F218" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="J218" t="s">
         <v>18</v>
       </c>
       <c r="K218" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F218,'feed pars'!B$6:B$43,0))</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F218,'feed pars'!B$6:B$43,0))</f>
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>25</v>
       </c>
+      <c r="E219" t="s">
+        <v>299</v>
+      </c>
       <c r="F219" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="J219" t="s">
         <v>18</v>
       </c>
       <c r="K219" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F219,'feed pars'!B$6:B$43,0))</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F219,'feed pars'!B$6:B$43,0))</f>
+        <v>8.6999999999999993</v>
+      </c>
+    </row>
+    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>25</v>
       </c>
+      <c r="E220" t="s">
+        <v>299</v>
+      </c>
       <c r="F220" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="J220" t="s">
         <v>18</v>
       </c>
       <c r="K220" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F220,'feed pars'!B$6:B$43,0))</f>
-        <v>11.9</v>
-      </c>
-    </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F220,'feed pars'!B$6:B$43,0))</f>
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>25</v>
       </c>
+      <c r="E221" t="s">
+        <v>299</v>
+      </c>
       <c r="F221" t="s">
-        <v>40</v>
+        <v>313</v>
       </c>
       <c r="J221" t="s">
         <v>18</v>
       </c>
       <c r="K221" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F221,'feed pars'!B$6:B$43,0))</f>
-        <v>12.8</v>
-      </c>
-    </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F221,'feed pars'!B$6:B$43,0))</f>
+        <v>7.0888888888888877</v>
+      </c>
+    </row>
+    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>25</v>
       </c>
+      <c r="E222" t="s">
+        <v>299</v>
+      </c>
       <c r="F222" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="J222" t="s">
         <v>18</v>
       </c>
       <c r="K222" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F222,'feed pars'!B$6:B$43,0))</f>
-        <v>11.2</v>
-      </c>
-    </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F222,'feed pars'!B$6:B$43,0))</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>25</v>
       </c>
+      <c r="E223" t="s">
+        <v>299</v>
+      </c>
       <c r="F223" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="J223" t="s">
         <v>18</v>
       </c>
       <c r="K223" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F223,'feed pars'!B$6:B$43,0))</f>
-        <v>10.7</v>
-      </c>
-    </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F223,'feed pars'!B$6:B$43,0))</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>25</v>
       </c>
+      <c r="E224" t="s">
+        <v>299</v>
+      </c>
       <c r="F224" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="J224" t="s">
         <v>18</v>
       </c>
       <c r="K224" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F224,'feed pars'!B$6:B$43,0))</f>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F224,'feed pars'!B$6:B$43,0))</f>
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="225" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>25</v>
       </c>
+      <c r="E225" t="s">
+        <v>299</v>
+      </c>
       <c r="F225" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="J225" t="s">
         <v>18</v>
       </c>
       <c r="K225" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F225,'feed pars'!B$6:B$43,0))</f>
-        <v>17.3</v>
-      </c>
-    </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F225,'feed pars'!B$6:B$43,0))</f>
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="226" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>25</v>
       </c>
+      <c r="E226" t="s">
+        <v>299</v>
+      </c>
       <c r="F226" t="s">
-        <v>314</v>
+        <v>56</v>
       </c>
       <c r="J226" t="s">
         <v>18</v>
       </c>
       <c r="K226" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F226,'feed pars'!B$6:B$43,0))</f>
-        <v>29.8</v>
-      </c>
-    </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F226,'feed pars'!B$6:B$43,0))</f>
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="227" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>25</v>
       </c>
+      <c r="E227" t="s">
+        <v>299</v>
+      </c>
       <c r="F227" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="J227" t="s">
         <v>18</v>
       </c>
       <c r="K227" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F227,'feed pars'!B$6:B$43,0))</f>
-        <v>9.3000000000000007</v>
-      </c>
-    </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A228" t="s">
-        <v>25</v>
-      </c>
-      <c r="F228" t="s">
-        <v>45</v>
-      </c>
-      <c r="J228" t="s">
-        <v>18</v>
-      </c>
-      <c r="K228" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F228,'feed pars'!B$6:B$43,0))</f>
-        <v>9.6999999999999993</v>
-      </c>
-    </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F227,'feed pars'!B$6:B$43,0))</f>
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="228" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A228" s="30" t="s">
+        <v>392</v>
+      </c>
+      <c r="B228" s="31"/>
+      <c r="C228" s="32"/>
+      <c r="D228" s="32"/>
+      <c r="E228" s="32"/>
+      <c r="F228" s="32"/>
+      <c r="G228" s="32"/>
+      <c r="H228" s="32"/>
+      <c r="I228" s="32"/>
+      <c r="J228" s="32"/>
+      <c r="K228" s="32"/>
+      <c r="L228" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="M228" s="32"/>
+      <c r="N228" s="32"/>
+    </row>
+    <row r="229" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>25</v>
       </c>
       <c r="F229" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="J229" t="s">
         <v>18</v>
       </c>
       <c r="K229" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F229,'feed pars'!B$6:B$43,0))</f>
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>25</v>
       </c>
       <c r="F230" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J230" t="s">
         <v>18</v>
       </c>
       <c r="K230" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F230,'feed pars'!B$6:B$43,0))</f>
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="231" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>25</v>
       </c>
       <c r="F231" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="J231" t="s">
         <v>18</v>
       </c>
       <c r="K231" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F231,'feed pars'!B$6:B$43,0))</f>
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="232" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>25</v>
       </c>
       <c r="F232" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="J232" t="s">
         <v>18</v>
       </c>
       <c r="K232" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F232,'feed pars'!B$6:B$43,0))</f>
-        <v>7.2</v>
-      </c>
-    </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.25">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="233" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>25</v>
       </c>
       <c r="F233" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="J233" t="s">
         <v>18</v>
       </c>
       <c r="K233" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F233,'feed pars'!B$6:B$43,0))</f>
-        <v>8.6999999999999993</v>
-      </c>
-    </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.25">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="234" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>25</v>
       </c>
       <c r="F234" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="J234" t="s">
         <v>18</v>
       </c>
       <c r="K234" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F234,'feed pars'!B$6:B$43,0))</f>
-        <v>8.1</v>
-      </c>
-    </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="235" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>25</v>
       </c>
       <c r="F235" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="J235" t="s">
         <v>18</v>
       </c>
       <c r="K235" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F235,'feed pars'!B$6:B$43,0))</f>
-        <v>8.1999999999999993</v>
-      </c>
-    </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="236" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>25</v>
       </c>
       <c r="F236" t="s">
-        <v>313</v>
+        <v>35</v>
       </c>
       <c r="J236" t="s">
         <v>18</v>
       </c>
       <c r="K236" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F236,'feed pars'!B$6:B$43,0))</f>
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="237" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>25</v>
       </c>
       <c r="F237" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="J237" t="s">
         <v>18</v>
       </c>
       <c r="K237" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F237,'feed pars'!B$6:B$43,0))</f>
-        <v>8.6999999999999993</v>
-      </c>
-    </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="238" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>25</v>
       </c>
       <c r="F238" t="s">
-        <v>53</v>
+        <v>314</v>
       </c>
       <c r="J238" t="s">
         <v>18</v>
       </c>
       <c r="K238" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F238,'feed pars'!B$6:B$43,0))</f>
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="239" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>25</v>
       </c>
       <c r="F239" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="J239" t="s">
         <v>18</v>
       </c>
       <c r="K239" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F239,'feed pars'!B$6:B$43,0))</f>
-        <v>12.4</v>
-      </c>
-    </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
+        <v>9.3000000000000007</v>
+      </c>
+    </row>
+    <row r="240" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>25</v>
       </c>
       <c r="F240" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="J240" t="s">
         <v>18</v>
       </c>
       <c r="K240" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F240,'feed pars'!B$6:B$43,0))</f>
-        <v>12.4</v>
+        <v>9.6999999999999993</v>
       </c>
     </row>
     <row r="241" spans="1:11" x14ac:dyDescent="0.25">
@@ -6129,14 +6132,14 @@
         <v>25</v>
       </c>
       <c r="F241" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="J241" t="s">
         <v>18</v>
       </c>
       <c r="K241" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F241,'feed pars'!B$6:B$43,0))</f>
-        <v>11.1</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.25">
@@ -6144,13 +6147,193 @@
         <v>25</v>
       </c>
       <c r="F242" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="J242" t="s">
         <v>18</v>
       </c>
       <c r="K242" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F242,'feed pars'!B$6:B$43,0))</f>
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>25</v>
+      </c>
+      <c r="F243" t="s">
+        <v>47</v>
+      </c>
+      <c r="J243" t="s">
+        <v>18</v>
+      </c>
+      <c r="K243" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F243,'feed pars'!B$6:B$43,0))</f>
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>25</v>
+      </c>
+      <c r="F244" t="s">
+        <v>48</v>
+      </c>
+      <c r="J244" t="s">
+        <v>18</v>
+      </c>
+      <c r="K244" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F244,'feed pars'!B$6:B$43,0))</f>
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>25</v>
+      </c>
+      <c r="F245" t="s">
+        <v>49</v>
+      </c>
+      <c r="J245" t="s">
+        <v>18</v>
+      </c>
+      <c r="K245" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F245,'feed pars'!B$6:B$43,0))</f>
+        <v>8.6999999999999993</v>
+      </c>
+    </row>
+    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>25</v>
+      </c>
+      <c r="F246" t="s">
+        <v>50</v>
+      </c>
+      <c r="J246" t="s">
+        <v>18</v>
+      </c>
+      <c r="K246" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F246,'feed pars'!B$6:B$43,0))</f>
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>25</v>
+      </c>
+      <c r="F247" t="s">
+        <v>51</v>
+      </c>
+      <c r="J247" t="s">
+        <v>18</v>
+      </c>
+      <c r="K247" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F247,'feed pars'!B$6:B$43,0))</f>
+        <v>8.1999999999999993</v>
+      </c>
+    </row>
+    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>25</v>
+      </c>
+      <c r="F248" t="s">
+        <v>313</v>
+      </c>
+      <c r="J248" t="s">
+        <v>18</v>
+      </c>
+      <c r="K248" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F248,'feed pars'!B$6:B$43,0))</f>
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>25</v>
+      </c>
+      <c r="F249" t="s">
+        <v>52</v>
+      </c>
+      <c r="J249" t="s">
+        <v>18</v>
+      </c>
+      <c r="K249" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F249,'feed pars'!B$6:B$43,0))</f>
+        <v>8.6999999999999993</v>
+      </c>
+    </row>
+    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>25</v>
+      </c>
+      <c r="F250" t="s">
+        <v>53</v>
+      </c>
+      <c r="J250" t="s">
+        <v>18</v>
+      </c>
+      <c r="K250" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F250,'feed pars'!B$6:B$43,0))</f>
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>25</v>
+      </c>
+      <c r="F251" t="s">
+        <v>54</v>
+      </c>
+      <c r="J251" t="s">
+        <v>18</v>
+      </c>
+      <c r="K251" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F251,'feed pars'!B$6:B$43,0))</f>
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="252" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>25</v>
+      </c>
+      <c r="F252" t="s">
+        <v>55</v>
+      </c>
+      <c r="J252" t="s">
+        <v>18</v>
+      </c>
+      <c r="K252" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F252,'feed pars'!B$6:B$43,0))</f>
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="253" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>25</v>
+      </c>
+      <c r="F253" t="s">
+        <v>56</v>
+      </c>
+      <c r="J253" t="s">
+        <v>18</v>
+      </c>
+      <c r="K253" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F253,'feed pars'!B$6:B$43,0))</f>
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>25</v>
+      </c>
+      <c r="F254" t="s">
+        <v>57</v>
+      </c>
+      <c r="J254" t="s">
+        <v>18</v>
+      </c>
+      <c r="K254" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F254,'feed pars'!B$6:B$43,0))</f>
         <v>10.8</v>
       </c>
     </row>
@@ -7130,7 +7313,7 @@
       </c>
       <c r="C33" s="23">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>88.5</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4">
@@ -7150,7 +7333,15 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="J33" s="4"/>
-      <c r="L33" s="27"/>
+      <c r="K33">
+        <v>89</v>
+      </c>
+      <c r="L33" s="27">
+        <v>11.5</v>
+      </c>
+      <c r="M33" s="11" t="s">
+        <v>410</v>
+      </c>
       <c r="N33" s="4">
         <f>MATCH($B33,poultry!$A$3:$A$41,0)</f>
         <v>36</v>
@@ -7521,9 +7712,10 @@
     <hyperlink ref="C1" r:id="rId1"/>
     <hyperlink ref="I36" r:id="rId2"/>
     <hyperlink ref="M31" r:id="rId3"/>
+    <hyperlink ref="M33" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>
 

--- a/data/prod_parameters/FeedMgmt.xlsx
+++ b/data/prod_parameters/FeedMgmt.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1243" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1258" uniqueCount="414">
   <si>
     <t>f_feed</t>
   </si>
@@ -1281,6 +1281,15 @@
   </si>
   <si>
     <t>https://glw-feeds.co.uk/index.php/wheat-feed-2/</t>
+  </si>
+  <si>
+    <t>no solution if these are used…</t>
+  </si>
+  <si>
+    <t>probably some problem with animals</t>
+  </si>
+  <si>
+    <t>needing to be exactly 0 in some regions</t>
   </si>
 </sst>
 </file>
@@ -1774,7 +1783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O254"/>
+  <dimension ref="A1:O258"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="7" width="20.28515625" customWidth="1"/>
@@ -2499,238 +2508,195 @@
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
+        <v>25</v>
+      </c>
+      <c r="H46" t="s">
+        <v>37</v>
+      </c>
+      <c r="K46" s="3">
+        <v>10</v>
+      </c>
+      <c r="L46" t="s">
+        <v>28</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>389</v>
+      </c>
+      <c r="H47" t="s">
+        <v>37</v>
+      </c>
+      <c r="K47" s="3">
+        <v>10</v>
+      </c>
+      <c r="L47" t="s">
+        <v>28</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>25</v>
+      </c>
+      <c r="H48" t="s">
+        <v>17</v>
+      </c>
+      <c r="K48" s="3">
+        <v>10</v>
+      </c>
+      <c r="L48" t="s">
+        <v>28</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>389</v>
+      </c>
+      <c r="H49" t="s">
+        <v>17</v>
+      </c>
+      <c r="K49" s="3">
+        <v>10</v>
+      </c>
+      <c r="L49" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
-      <c r="L46" s="2"/>
-      <c r="M46" s="2"/>
-      <c r="N46" s="2"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J47" s="10" t="s">
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="2"/>
+      <c r="K50" s="2"/>
+      <c r="L50" s="2"/>
+      <c r="M50" s="2"/>
+      <c r="N50" s="2"/>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J51" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="K47" s="10">
-        <v>0</v>
-      </c>
-      <c r="L47" s="10"/>
-      <c r="M47" s="10" t="s">
+      <c r="K51" s="10">
+        <v>0</v>
+      </c>
+      <c r="L51" s="10"/>
+      <c r="M51" s="10" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="I48" t="s">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I52" t="s">
         <v>318</v>
-      </c>
-      <c r="J48" t="s">
-        <v>31</v>
-      </c>
-      <c r="K48" s="29">
-        <v>100</v>
-      </c>
-      <c r="L48" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="M48" s="10"/>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="I49" t="s">
-        <v>44</v>
-      </c>
-      <c r="J49" t="s">
-        <v>31</v>
-      </c>
-      <c r="K49" s="29">
-        <v>100</v>
-      </c>
-      <c r="L49" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="M49" s="10"/>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="I50" t="s">
-        <v>36</v>
-      </c>
-      <c r="J50" t="s">
-        <v>31</v>
-      </c>
-      <c r="K50" s="29">
-        <v>61</v>
-      </c>
-      <c r="L50" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="H51" t="s">
-        <v>43</v>
-      </c>
-      <c r="J51" t="s">
-        <v>31</v>
-      </c>
-      <c r="K51" s="3">
-        <v>100</v>
-      </c>
-      <c r="L51" t="s">
-        <v>28</v>
-      </c>
-      <c r="M51" s="3" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="H52" t="s">
-        <v>40</v>
       </c>
       <c r="J52" t="s">
         <v>31</v>
       </c>
-      <c r="K52" s="3">
-        <v>50</v>
-      </c>
-      <c r="L52" t="s">
+      <c r="K52" s="29">
+        <v>100</v>
+      </c>
+      <c r="L52" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>394</v>
-      </c>
+      <c r="M52" s="10"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
-      <c r="D53" s="1"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
-      <c r="J53" s="2"/>
-      <c r="K53" s="2"/>
-      <c r="L53" s="2"/>
-      <c r="M53" s="2"/>
-      <c r="N53" s="2"/>
+      <c r="I53" t="s">
+        <v>44</v>
+      </c>
+      <c r="J53" t="s">
+        <v>31</v>
+      </c>
+      <c r="K53" s="29">
+        <v>100</v>
+      </c>
+      <c r="L53" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="M53" s="10"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>24</v>
-      </c>
-      <c r="B54" t="s">
-        <v>326</v>
-      </c>
-      <c r="E54" t="s">
-        <v>327</v>
-      </c>
-      <c r="G54" t="s">
-        <v>334</v>
-      </c>
-      <c r="H54" t="s">
-        <v>33</v>
+      <c r="I54" t="s">
+        <v>36</v>
       </c>
       <c r="J54" t="s">
-        <v>335</v>
-      </c>
-      <c r="K54" s="3">
-        <v>5</v>
+        <v>31</v>
+      </c>
+      <c r="K54" s="29">
+        <v>61</v>
       </c>
       <c r="L54" t="s">
         <v>28</v>
       </c>
-      <c r="M54" s="3"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>24</v>
-      </c>
-      <c r="B55" t="s">
-        <v>326</v>
-      </c>
-      <c r="E55" t="s">
-        <v>328</v>
-      </c>
-      <c r="G55" t="s">
-        <v>334</v>
-      </c>
       <c r="H55" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="J55" t="s">
-        <v>335</v>
+        <v>31</v>
       </c>
       <c r="K55" s="3">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="L55" t="s">
         <v>28</v>
       </c>
-      <c r="M55" s="3"/>
+      <c r="M55" s="3" t="s">
+        <v>304</v>
+      </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>24</v>
-      </c>
-      <c r="B56" t="s">
-        <v>326</v>
-      </c>
-      <c r="E56" t="s">
-        <v>329</v>
-      </c>
-      <c r="G56" t="s">
-        <v>334</v>
-      </c>
       <c r="H56" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="J56" t="s">
-        <v>335</v>
+        <v>31</v>
       </c>
       <c r="K56" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L56" t="s">
         <v>28</v>
       </c>
-      <c r="M56" s="3"/>
+      <c r="M56" s="3" t="s">
+        <v>394</v>
+      </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>24</v>
-      </c>
-      <c r="B57" t="s">
-        <v>326</v>
-      </c>
-      <c r="E57" t="s">
-        <v>330</v>
-      </c>
-      <c r="G57" t="s">
-        <v>334</v>
-      </c>
-      <c r="H57" t="s">
-        <v>33</v>
-      </c>
-      <c r="J57" t="s">
-        <v>335</v>
-      </c>
-      <c r="K57" s="3">
-        <v>90</v>
-      </c>
-      <c r="L57" t="s">
-        <v>28</v>
-      </c>
-      <c r="M57" s="3"/>
+      <c r="A57" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
+      <c r="K57" s="2"/>
+      <c r="L57" s="2"/>
+      <c r="M57" s="2"/>
+      <c r="N57" s="2"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
@@ -2740,7 +2706,7 @@
         <v>326</v>
       </c>
       <c r="E58" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G58" t="s">
         <v>334</v>
@@ -2752,7 +2718,7 @@
         <v>335</v>
       </c>
       <c r="K58" s="3">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="L58" t="s">
         <v>28</v>
@@ -2767,7 +2733,7 @@
         <v>326</v>
       </c>
       <c r="E59" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="G59" t="s">
         <v>334</v>
@@ -2779,7 +2745,7 @@
         <v>335</v>
       </c>
       <c r="K59" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L59" t="s">
         <v>28</v>
@@ -2791,10 +2757,10 @@
         <v>24</v>
       </c>
       <c r="B60" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="E60" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G60" t="s">
         <v>334</v>
@@ -2806,7 +2772,7 @@
         <v>335</v>
       </c>
       <c r="K60" s="3">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L60" t="s">
         <v>28</v>
@@ -2818,10 +2784,10 @@
         <v>24</v>
       </c>
       <c r="B61" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="E61" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="G61" t="s">
         <v>334</v>
@@ -2845,10 +2811,10 @@
         <v>24</v>
       </c>
       <c r="B62" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="E62" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="G62" t="s">
         <v>334</v>
@@ -2860,7 +2826,7 @@
         <v>335</v>
       </c>
       <c r="K62" s="3">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L62" t="s">
         <v>28</v>
@@ -2872,10 +2838,10 @@
         <v>24</v>
       </c>
       <c r="B63" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="E63" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G63" t="s">
         <v>334</v>
@@ -2887,7 +2853,7 @@
         <v>335</v>
       </c>
       <c r="K63" s="3">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L63" t="s">
         <v>28</v>
@@ -2902,7 +2868,7 @@
         <v>333</v>
       </c>
       <c r="E64" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G64" t="s">
         <v>334</v>
@@ -2929,7 +2895,7 @@
         <v>333</v>
       </c>
       <c r="E65" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="G65" t="s">
         <v>334</v>
@@ -2950,7 +2916,13 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>395</v>
+        <v>24</v>
+      </c>
+      <c r="B66" t="s">
+        <v>333</v>
+      </c>
+      <c r="E66" t="s">
+        <v>329</v>
       </c>
       <c r="G66" t="s">
         <v>334</v>
@@ -2962,7 +2934,7 @@
         <v>335</v>
       </c>
       <c r="K66" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L66" t="s">
         <v>28</v>
@@ -2970,153 +2942,155 @@
       <c r="M66" s="3"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K67" s="3"/>
+      <c r="A67" t="s">
+        <v>24</v>
+      </c>
+      <c r="B67" t="s">
+        <v>333</v>
+      </c>
+      <c r="E67" t="s">
+        <v>330</v>
+      </c>
+      <c r="G67" t="s">
+        <v>334</v>
+      </c>
+      <c r="H67" t="s">
+        <v>33</v>
+      </c>
+      <c r="J67" t="s">
+        <v>335</v>
+      </c>
+      <c r="K67" s="3">
+        <v>90</v>
+      </c>
+      <c r="L67" t="s">
+        <v>28</v>
+      </c>
       <c r="M67" s="3"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
+      <c r="A68" t="s">
+        <v>24</v>
+      </c>
+      <c r="B68" t="s">
+        <v>333</v>
+      </c>
+      <c r="E68" t="s">
+        <v>331</v>
+      </c>
+      <c r="G68" t="s">
+        <v>334</v>
+      </c>
+      <c r="H68" t="s">
+        <v>33</v>
+      </c>
+      <c r="J68" t="s">
+        <v>335</v>
+      </c>
+      <c r="K68" s="3">
+        <v>90</v>
+      </c>
+      <c r="L68" t="s">
+        <v>28</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>24</v>
+      </c>
+      <c r="B69" t="s">
+        <v>333</v>
+      </c>
+      <c r="E69" t="s">
+        <v>332</v>
+      </c>
+      <c r="G69" t="s">
+        <v>334</v>
+      </c>
+      <c r="H69" t="s">
+        <v>33</v>
+      </c>
+      <c r="J69" t="s">
+        <v>335</v>
+      </c>
+      <c r="K69" s="3">
+        <v>90</v>
+      </c>
+      <c r="L69" t="s">
+        <v>28</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>395</v>
+      </c>
+      <c r="G70" t="s">
+        <v>334</v>
+      </c>
+      <c r="H70" t="s">
+        <v>33</v>
+      </c>
+      <c r="J70" t="s">
+        <v>335</v>
+      </c>
+      <c r="K70" s="3">
+        <v>10</v>
+      </c>
+      <c r="L70" t="s">
+        <v>28</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K71" s="3"/>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B68" s="1"/>
-      <c r="C68" s="1"/>
-      <c r="D68" s="1"/>
-      <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="2"/>
-      <c r="I68" s="2"/>
-      <c r="J68" s="2"/>
-      <c r="K68" s="2"/>
-      <c r="L68" s="2"/>
-      <c r="M68" s="2"/>
-      <c r="N68" s="2"/>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J69" s="10" t="s">
+      <c r="B72" s="1"/>
+      <c r="C72" s="1"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+      <c r="I72" s="2"/>
+      <c r="J72" s="2"/>
+      <c r="K72" s="2"/>
+      <c r="L72" s="2"/>
+      <c r="M72" s="2"/>
+      <c r="N72" s="2"/>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J73" s="10" t="s">
         <v>396</v>
       </c>
-      <c r="K69" s="10">
-        <v>0</v>
-      </c>
-      <c r="L69" s="10" t="s">
+      <c r="K73" s="10">
+        <v>0</v>
+      </c>
+      <c r="L73" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="M69" s="10" t="s">
+      <c r="M73" s="10" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J70" s="10" t="s">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J74" s="10" t="s">
         <v>397</v>
       </c>
-      <c r="K70" s="10">
-        <v>0</v>
-      </c>
-      <c r="L70" s="10" t="s">
+      <c r="K74" s="10">
+        <v>0</v>
+      </c>
+      <c r="L74" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="M70" s="10" t="s">
+      <c r="M74" s="10" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>24</v>
-      </c>
-      <c r="B71" t="s">
-        <v>326</v>
-      </c>
-      <c r="E71" t="s">
-        <v>327</v>
-      </c>
-      <c r="F71" t="s">
-        <v>310</v>
-      </c>
-      <c r="J71" s="29" t="s">
-        <v>396</v>
-      </c>
-      <c r="K71" s="29">
-        <f>(0.8*20+0.2*2)</f>
-        <v>16.399999999999999</v>
-      </c>
-      <c r="L71" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="M71" s="29" t="s">
-        <v>402</v>
-      </c>
-      <c r="N71" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>24</v>
-      </c>
-      <c r="F72" t="s">
-        <v>310</v>
-      </c>
-      <c r="J72" s="29" t="s">
-        <v>396</v>
-      </c>
-      <c r="K72" s="29">
-        <f>(0.6*20+0.4*2)</f>
-        <v>12.8</v>
-      </c>
-      <c r="L72" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="M72" s="29" t="s">
-        <v>403</v>
-      </c>
-      <c r="N72" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>401</v>
-      </c>
-      <c r="F73" t="s">
-        <v>310</v>
-      </c>
-      <c r="J73" s="29" t="s">
-        <v>396</v>
-      </c>
-      <c r="K73" s="29">
-        <v>2</v>
-      </c>
-      <c r="L73" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="M73" s="29" t="s">
-        <v>404</v>
-      </c>
-      <c r="N73" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>395</v>
-      </c>
-      <c r="F74" t="s">
-        <v>310</v>
-      </c>
-      <c r="J74" s="29" t="s">
-        <v>396</v>
-      </c>
-      <c r="K74" s="29">
-        <v>2</v>
-      </c>
-      <c r="L74" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="M74" s="29" t="s">
-        <v>404</v>
-      </c>
-      <c r="N74" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
@@ -3133,16 +3107,17 @@
         <v>310</v>
       </c>
       <c r="J75" s="29" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K75" s="29">
-        <v>5</v>
+        <f>(0.8*20+0.2*2)</f>
+        <v>16.399999999999999</v>
       </c>
       <c r="L75" s="29" t="s">
         <v>28</v>
       </c>
       <c r="M75" s="29" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="N75" t="s">
         <v>398</v>
@@ -3152,23 +3127,21 @@
       <c r="A76" t="s">
         <v>24</v>
       </c>
-      <c r="E76" t="s">
-        <v>329</v>
-      </c>
       <c r="F76" t="s">
         <v>310</v>
       </c>
       <c r="J76" s="29" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K76" s="29">
-        <v>5</v>
+        <f>(0.6*20+0.4*2)</f>
+        <v>12.8</v>
       </c>
       <c r="L76" s="29" t="s">
         <v>28</v>
       </c>
       <c r="M76" s="29" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="N76" t="s">
         <v>398</v>
@@ -3176,197 +3149,174 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>24</v>
+        <v>401</v>
       </c>
       <c r="F77" t="s">
         <v>310</v>
       </c>
       <c r="J77" s="29" t="s">
+        <v>396</v>
+      </c>
+      <c r="K77" s="29">
+        <v>2</v>
+      </c>
+      <c r="L77" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="M77" s="29" t="s">
+        <v>404</v>
+      </c>
+      <c r="N77" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>395</v>
+      </c>
+      <c r="F78" t="s">
+        <v>310</v>
+      </c>
+      <c r="J78" s="29" t="s">
+        <v>396</v>
+      </c>
+      <c r="K78" s="29">
+        <v>2</v>
+      </c>
+      <c r="L78" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="M78" s="29" t="s">
+        <v>404</v>
+      </c>
+      <c r="N78" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>24</v>
+      </c>
+      <c r="B79" t="s">
+        <v>326</v>
+      </c>
+      <c r="E79" t="s">
+        <v>327</v>
+      </c>
+      <c r="F79" t="s">
+        <v>310</v>
+      </c>
+      <c r="J79" s="29" t="s">
         <v>397</v>
       </c>
-      <c r="K77" s="29">
+      <c r="K79" s="29">
+        <v>5</v>
+      </c>
+      <c r="L79" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="M79" s="29" t="s">
+        <v>405</v>
+      </c>
+      <c r="N79" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>24</v>
+      </c>
+      <c r="E80" t="s">
+        <v>329</v>
+      </c>
+      <c r="F80" t="s">
+        <v>310</v>
+      </c>
+      <c r="J80" s="29" t="s">
+        <v>397</v>
+      </c>
+      <c r="K80" s="29">
+        <v>5</v>
+      </c>
+      <c r="L80" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="M80" s="29" t="s">
+        <v>405</v>
+      </c>
+      <c r="N80" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>24</v>
+      </c>
+      <c r="F81" t="s">
+        <v>310</v>
+      </c>
+      <c r="J81" s="29" t="s">
+        <v>397</v>
+      </c>
+      <c r="K81" s="29">
         <f>0.9*5+0.1*15</f>
         <v>6</v>
       </c>
-      <c r="L77" s="29" t="s">
+      <c r="L81" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="M77" s="29" t="s">
+      <c r="M81" s="29" t="s">
         <v>406</v>
       </c>
-      <c r="N77" t="s">
+      <c r="N81" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
         <v>401</v>
       </c>
-      <c r="F78" t="s">
+      <c r="F82" t="s">
         <v>310</v>
       </c>
-      <c r="J78" s="29" t="s">
+      <c r="J82" s="29" t="s">
         <v>397</v>
       </c>
-      <c r="K78" s="29">
+      <c r="K82" s="29">
         <v>15</v>
       </c>
-      <c r="L78" s="29" t="s">
+      <c r="L82" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="M78" s="29"/>
-      <c r="N78" t="s">
+      <c r="M82" s="29"/>
+      <c r="N82" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
         <v>395</v>
       </c>
-      <c r="F79" t="s">
+      <c r="F83" t="s">
         <v>310</v>
       </c>
-      <c r="J79" s="29" t="s">
+      <c r="J83" s="29" t="s">
         <v>397</v>
       </c>
-      <c r="K79" s="29">
+      <c r="K83" s="29">
         <v>15</v>
       </c>
-      <c r="L79" s="29" t="s">
+      <c r="L83" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="M79" s="29"/>
-      <c r="N79" t="s">
+      <c r="M83" s="29"/>
+      <c r="N83" t="s">
         <v>398</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A80" s="33" t="str">
-        <f>A71</f>
-        <v>cattle</v>
-      </c>
-      <c r="B80" s="33" t="str">
-        <f>B71</f>
-        <v>dairy</v>
-      </c>
-      <c r="E80" s="33" t="str">
-        <f>E71</f>
-        <v>cows</v>
-      </c>
-      <c r="F80" t="s">
-        <v>311</v>
-      </c>
-      <c r="J80" s="33" t="str">
-        <f>J71</f>
-        <v>storage_losses</v>
-      </c>
-      <c r="K80" s="33">
-        <f>K71</f>
-        <v>16.399999999999999</v>
-      </c>
-      <c r="L80" s="33" t="str">
-        <f>L71</f>
-        <v>%</v>
-      </c>
-      <c r="M80" s="33" t="str">
-        <f>M71</f>
-        <v>80% in silo</v>
-      </c>
-      <c r="N80" s="33" t="str">
-        <f>N71</f>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A81" s="33" t="str">
-        <f t="shared" ref="A81:A88" si="0">A72</f>
-        <v>cattle</v>
-      </c>
-      <c r="F81" t="s">
-        <v>311</v>
-      </c>
-      <c r="J81" s="33" t="str">
-        <f t="shared" ref="J81:N88" si="1">J72</f>
-        <v>storage_losses</v>
-      </c>
-      <c r="K81" s="33">
-        <f t="shared" si="1"/>
-        <v>12.8</v>
-      </c>
-      <c r="L81" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>%</v>
-      </c>
-      <c r="M81" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>60% in silo</v>
-      </c>
-      <c r="N81" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A82" s="33" t="str">
-        <f t="shared" si="0"/>
-        <v>sheep</v>
-      </c>
-      <c r="F82" t="s">
-        <v>311</v>
-      </c>
-      <c r="J82" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>storage_losses</v>
-      </c>
-      <c r="K82" s="33">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="L82" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>%</v>
-      </c>
-      <c r="M82" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>0% in silo</v>
-      </c>
-      <c r="N82" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A83" s="33" t="str">
-        <f t="shared" si="0"/>
-        <v>horses</v>
-      </c>
-      <c r="F83" t="s">
-        <v>311</v>
-      </c>
-      <c r="J83" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>storage_losses</v>
-      </c>
-      <c r="K83" s="33">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="L83" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>%</v>
-      </c>
-      <c r="M83" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>0% in silo</v>
-      </c>
-      <c r="N83" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="33" t="str">
-        <f t="shared" si="0"/>
+        <f>A75</f>
         <v>cattle</v>
       </c>
       <c r="B84" s="33" t="str">
@@ -3381,45 +3331,41 @@
         <v>311</v>
       </c>
       <c r="J84" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>feeding_losses</v>
+        <f>J75</f>
+        <v>storage_losses</v>
       </c>
       <c r="K84" s="33">
-        <f t="shared" si="1"/>
-        <v>5</v>
+        <f>K75</f>
+        <v>16.399999999999999</v>
       </c>
       <c r="L84" s="33" t="str">
-        <f t="shared" si="1"/>
+        <f>L75</f>
         <v>%</v>
       </c>
       <c r="M84" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>No feeding on pasture</v>
+        <f>M75</f>
+        <v>80% in silo</v>
       </c>
       <c r="N84" s="33" t="str">
-        <f t="shared" si="1"/>
+        <f>N75</f>
         <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="33" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A85:A92" si="0">A76</f>
         <v>cattle</v>
-      </c>
-      <c r="E85" s="33" t="str">
-        <f>E76</f>
-        <v>bulls</v>
       </c>
       <c r="F85" t="s">
         <v>311</v>
       </c>
       <c r="J85" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>feeding_losses</v>
+        <f t="shared" ref="J85:N92" si="1">J76</f>
+        <v>storage_losses</v>
       </c>
       <c r="K85" s="33">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>12.8</v>
       </c>
       <c r="L85" s="33" t="str">
         <f t="shared" si="1"/>
@@ -3427,7 +3373,7 @@
       </c>
       <c r="M85" s="33" t="str">
         <f t="shared" si="1"/>
-        <v>No feeding on pasture</v>
+        <v>60% in silo</v>
       </c>
       <c r="N85" s="33" t="str">
         <f t="shared" si="1"/>
@@ -3437,18 +3383,18 @@
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="33" t="str">
         <f t="shared" si="0"/>
-        <v>cattle</v>
+        <v>sheep</v>
       </c>
       <c r="F86" t="s">
         <v>311</v>
       </c>
       <c r="J86" s="33" t="str">
         <f t="shared" si="1"/>
-        <v>feeding_losses</v>
+        <v>storage_losses</v>
       </c>
       <c r="K86" s="33">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L86" s="33" t="str">
         <f t="shared" si="1"/>
@@ -3456,7 +3402,7 @@
       </c>
       <c r="M86" s="33" t="str">
         <f t="shared" si="1"/>
-        <v>10% feeding on pasture</v>
+        <v>0% in silo</v>
       </c>
       <c r="N86" s="33" t="str">
         <f t="shared" si="1"/>
@@ -3466,33 +3412,44 @@
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="33" t="str">
         <f t="shared" si="0"/>
-        <v>sheep</v>
+        <v>horses</v>
       </c>
       <c r="F87" t="s">
         <v>311</v>
       </c>
       <c r="J87" s="33" t="str">
         <f t="shared" si="1"/>
-        <v>feeding_losses</v>
+        <v>storage_losses</v>
       </c>
       <c r="K87" s="33">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="L87" s="33" t="str">
         <f t="shared" si="1"/>
         <v>%</v>
       </c>
-      <c r="M87" s="33"/>
+      <c r="M87" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>0% in silo</v>
+      </c>
       <c r="N87" s="33" t="str">
-        <f t="shared" ref="N87:N88" si="2">N78</f>
+        <f t="shared" si="1"/>
         <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="33" t="str">
         <f t="shared" si="0"/>
-        <v>horses</v>
+        <v>cattle</v>
+      </c>
+      <c r="B88" s="33" t="str">
+        <f>B79</f>
+        <v>dairy</v>
+      </c>
+      <c r="E88" s="33" t="str">
+        <f>E79</f>
+        <v>cows</v>
       </c>
       <c r="F88" t="s">
         <v>311</v>
@@ -3503,703 +3460,754 @@
       </c>
       <c r="K88" s="33">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="L88" s="33" t="str">
         <f t="shared" si="1"/>
         <v>%</v>
       </c>
-      <c r="M88" s="33"/>
+      <c r="M88" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>No feeding on pasture</v>
+      </c>
       <c r="N88" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A89" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>cattle</v>
+      </c>
+      <c r="E89" s="33" t="str">
+        <f>E80</f>
+        <v>bulls</v>
+      </c>
+      <c r="F89" t="s">
+        <v>311</v>
+      </c>
+      <c r="J89" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K89" s="33">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="L89" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>%</v>
+      </c>
+      <c r="M89" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>No feeding on pasture</v>
+      </c>
+      <c r="N89" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A90" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>cattle</v>
+      </c>
+      <c r="F90" t="s">
+        <v>311</v>
+      </c>
+      <c r="J90" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K90" s="33">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="L90" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>%</v>
+      </c>
+      <c r="M90" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>10% feeding on pasture</v>
+      </c>
+      <c r="N90" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A91" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>sheep</v>
+      </c>
+      <c r="F91" t="s">
+        <v>311</v>
+      </c>
+      <c r="J91" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K91" s="33">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="L91" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>%</v>
+      </c>
+      <c r="M91" s="33"/>
+      <c r="N91" s="33" t="str">
+        <f t="shared" ref="N91:N92" si="2">N82</f>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A92" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>horses</v>
+      </c>
+      <c r="F92" t="s">
+        <v>311</v>
+      </c>
+      <c r="J92" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K92" s="33">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="L92" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>%</v>
+      </c>
+      <c r="M92" s="33"/>
+      <c r="N92" s="33" t="str">
         <f t="shared" si="2"/>
         <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A89" s="33"/>
-      <c r="B89" s="33"/>
-      <c r="E89" s="33"/>
-      <c r="F89" t="s">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A93" s="33"/>
+      <c r="B93" s="33"/>
+      <c r="E93" s="33"/>
+      <c r="F93" t="s">
         <v>312</v>
       </c>
-      <c r="J89" s="29" t="s">
+      <c r="J93" s="29" t="s">
         <v>396</v>
       </c>
-      <c r="K89" s="29">
+      <c r="K93" s="29">
         <v>5</v>
       </c>
-      <c r="L89" s="29" t="s">
+      <c r="L93" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="M89" s="29"/>
-      <c r="N89" t="s">
+      <c r="M93" s="29"/>
+      <c r="N93" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A90" s="33" t="str">
-        <f>A75</f>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A94" s="33" t="str">
+        <f>A79</f>
         <v>cattle</v>
       </c>
-      <c r="B90" s="33" t="str">
-        <f>B75</f>
+      <c r="B94" s="33" t="str">
+        <f>B79</f>
         <v>dairy</v>
       </c>
-      <c r="E90" s="33" t="str">
-        <f t="shared" ref="E90:E91" si="3">E75</f>
+      <c r="E94" s="33" t="str">
+        <f t="shared" ref="E94:E95" si="3">E79</f>
         <v>cows</v>
       </c>
-      <c r="F90" t="s">
+      <c r="F94" t="s">
         <v>312</v>
       </c>
-      <c r="J90" s="33" t="str">
-        <f t="shared" ref="J90:N94" si="4">J75</f>
+      <c r="J94" s="33" t="str">
+        <f t="shared" ref="J94:N98" si="4">J79</f>
         <v>feeding_losses</v>
       </c>
-      <c r="K90" s="33">
+      <c r="K94" s="33">
         <f t="shared" si="4"/>
         <v>5</v>
-      </c>
-      <c r="L90" s="33" t="str">
-        <f t="shared" si="4"/>
-        <v>%</v>
-      </c>
-      <c r="M90" s="33" t="str">
-        <f t="shared" si="4"/>
-        <v>No feeding on pasture</v>
-      </c>
-      <c r="N90" s="33" t="str">
-        <f t="shared" si="4"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A91" s="33" t="str">
-        <f t="shared" ref="A91:A94" si="5">A76</f>
-        <v>cattle</v>
-      </c>
-      <c r="E91" s="33" t="str">
-        <f t="shared" si="3"/>
-        <v>bulls</v>
-      </c>
-      <c r="F91" t="s">
-        <v>312</v>
-      </c>
-      <c r="J91" s="33" t="str">
-        <f t="shared" si="4"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="K91" s="33">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="L91" s="33" t="str">
-        <f t="shared" si="4"/>
-        <v>%</v>
-      </c>
-      <c r="M91" s="33" t="str">
-        <f t="shared" si="4"/>
-        <v>No feeding on pasture</v>
-      </c>
-      <c r="N91" s="33" t="str">
-        <f t="shared" si="4"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A92" s="33" t="str">
-        <f t="shared" si="5"/>
-        <v>cattle</v>
-      </c>
-      <c r="F92" t="s">
-        <v>312</v>
-      </c>
-      <c r="J92" s="33" t="str">
-        <f t="shared" si="4"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="K92" s="33">
-        <f t="shared" si="4"/>
-        <v>6</v>
-      </c>
-      <c r="L92" s="33" t="str">
-        <f t="shared" si="4"/>
-        <v>%</v>
-      </c>
-      <c r="M92" s="33" t="str">
-        <f t="shared" si="4"/>
-        <v>10% feeding on pasture</v>
-      </c>
-      <c r="N92" s="33" t="str">
-        <f t="shared" si="4"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A93" s="33" t="str">
-        <f t="shared" si="5"/>
-        <v>sheep</v>
-      </c>
-      <c r="F93" t="s">
-        <v>312</v>
-      </c>
-      <c r="J93" s="33" t="str">
-        <f t="shared" si="4"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="K93" s="33">
-        <f t="shared" si="4"/>
-        <v>15</v>
-      </c>
-      <c r="L93" s="33" t="str">
-        <f t="shared" si="4"/>
-        <v>%</v>
-      </c>
-      <c r="M93" s="33"/>
-      <c r="N93" s="33" t="str">
-        <f t="shared" si="4"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A94" s="33" t="str">
-        <f t="shared" si="5"/>
-        <v>horses</v>
-      </c>
-      <c r="F94" t="s">
-        <v>312</v>
-      </c>
-      <c r="J94" s="33" t="str">
-        <f t="shared" si="4"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="K94" s="33">
-        <f t="shared" si="4"/>
-        <v>15</v>
       </c>
       <c r="L94" s="33" t="str">
         <f t="shared" si="4"/>
         <v>%</v>
       </c>
-      <c r="M94" s="33"/>
+      <c r="M94" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>No feeding on pasture</v>
+      </c>
       <c r="N94" s="33" t="str">
         <f t="shared" si="4"/>
         <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A95" s="33" t="str">
+        <f t="shared" ref="A95:A98" si="5">A80</f>
+        <v>cattle</v>
+      </c>
+      <c r="E95" s="33" t="str">
+        <f t="shared" si="3"/>
+        <v>bulls</v>
+      </c>
       <c r="F95" t="s">
-        <v>2</v>
-      </c>
-      <c r="J95" s="29" t="s">
-        <v>396</v>
-      </c>
-      <c r="K95" s="29">
+        <v>312</v>
+      </c>
+      <c r="J95" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K95" s="33">
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="L95" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="M95" s="29"/>
-      <c r="N95" t="s">
-        <v>398</v>
+      <c r="L95" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>%</v>
+      </c>
+      <c r="M95" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>No feeding on pasture</v>
+      </c>
+      <c r="N95" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="33" t="str">
-        <f>A75</f>
+        <f t="shared" si="5"/>
         <v>cattle</v>
       </c>
-      <c r="B96" s="33" t="str">
-        <f>B75</f>
+      <c r="F96" t="s">
+        <v>312</v>
+      </c>
+      <c r="J96" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K96" s="33">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="L96" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>%</v>
+      </c>
+      <c r="M96" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>10% feeding on pasture</v>
+      </c>
+      <c r="N96" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A97" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>sheep</v>
+      </c>
+      <c r="F97" t="s">
+        <v>312</v>
+      </c>
+      <c r="J97" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K97" s="33">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="L97" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>%</v>
+      </c>
+      <c r="M97" s="33"/>
+      <c r="N97" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A98" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>horses</v>
+      </c>
+      <c r="F98" t="s">
+        <v>312</v>
+      </c>
+      <c r="J98" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K98" s="33">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="L98" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>%</v>
+      </c>
+      <c r="M98" s="33"/>
+      <c r="N98" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F99" t="s">
+        <v>2</v>
+      </c>
+      <c r="J99" s="29" t="s">
+        <v>396</v>
+      </c>
+      <c r="K99" s="29">
+        <v>5</v>
+      </c>
+      <c r="L99" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="M99" s="29"/>
+      <c r="N99" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A100" s="33" t="str">
+        <f>A79</f>
+        <v>cattle</v>
+      </c>
+      <c r="B100" s="33" t="str">
+        <f>B79</f>
         <v>dairy</v>
       </c>
-      <c r="E96" s="33" t="str">
-        <f t="shared" ref="E96:E97" si="6">E75</f>
+      <c r="E100" s="33" t="str">
+        <f t="shared" ref="E100:E101" si="6">E79</f>
         <v>cows</v>
       </c>
-      <c r="F96" t="s">
+      <c r="F100" t="s">
         <v>2</v>
       </c>
-      <c r="J96" s="33" t="str">
-        <f t="shared" ref="J96:N100" si="7">J75</f>
+      <c r="J100" s="33" t="str">
+        <f t="shared" ref="J100:N104" si="7">J79</f>
         <v>feeding_losses</v>
       </c>
-      <c r="K96" s="33">
+      <c r="K100" s="33">
         <f t="shared" si="7"/>
         <v>5</v>
-      </c>
-      <c r="L96" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>%</v>
-      </c>
-      <c r="M96" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>No feeding on pasture</v>
-      </c>
-      <c r="N96" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A97" s="33" t="str">
-        <f t="shared" ref="A97:A100" si="8">A76</f>
-        <v>cattle</v>
-      </c>
-      <c r="E97" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>bulls</v>
-      </c>
-      <c r="F97" t="s">
-        <v>2</v>
-      </c>
-      <c r="J97" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="K97" s="33">
-        <f t="shared" si="7"/>
-        <v>5</v>
-      </c>
-      <c r="L97" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>%</v>
-      </c>
-      <c r="M97" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>No feeding on pasture</v>
-      </c>
-      <c r="N97" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A98" s="33" t="str">
-        <f t="shared" si="8"/>
-        <v>cattle</v>
-      </c>
-      <c r="F98" t="s">
-        <v>2</v>
-      </c>
-      <c r="J98" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="K98" s="33">
-        <f t="shared" si="7"/>
-        <v>6</v>
-      </c>
-      <c r="L98" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>%</v>
-      </c>
-      <c r="M98" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>10% feeding on pasture</v>
-      </c>
-      <c r="N98" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A99" s="33" t="str">
-        <f t="shared" si="8"/>
-        <v>sheep</v>
-      </c>
-      <c r="F99" t="s">
-        <v>2</v>
-      </c>
-      <c r="J99" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="K99" s="33">
-        <f t="shared" si="7"/>
-        <v>15</v>
-      </c>
-      <c r="L99" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>%</v>
-      </c>
-      <c r="M99" s="29"/>
-      <c r="N99" s="33" t="str">
-        <f t="shared" ref="N99:N100" si="9">N78</f>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A100" s="33" t="str">
-        <f t="shared" si="8"/>
-        <v>horses</v>
-      </c>
-      <c r="F100" t="s">
-        <v>2</v>
-      </c>
-      <c r="J100" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="K100" s="33">
-        <f t="shared" si="7"/>
-        <v>15</v>
       </c>
       <c r="L100" s="33" t="str">
         <f t="shared" si="7"/>
         <v>%</v>
       </c>
-      <c r="M100" s="29"/>
+      <c r="M100" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>No feeding on pasture</v>
+      </c>
       <c r="N100" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A101" s="33" t="str">
+        <f t="shared" ref="A101:A104" si="8">A80</f>
+        <v>cattle</v>
+      </c>
+      <c r="E101" s="33" t="str">
+        <f t="shared" si="6"/>
+        <v>bulls</v>
+      </c>
+      <c r="F101" t="s">
+        <v>2</v>
+      </c>
+      <c r="J101" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K101" s="33">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="L101" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>%</v>
+      </c>
+      <c r="M101" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>No feeding on pasture</v>
+      </c>
+      <c r="N101" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A102" s="33" t="str">
+        <f t="shared" si="8"/>
+        <v>cattle</v>
+      </c>
+      <c r="F102" t="s">
+        <v>2</v>
+      </c>
+      <c r="J102" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K102" s="33">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="L102" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>%</v>
+      </c>
+      <c r="M102" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>10% feeding on pasture</v>
+      </c>
+      <c r="N102" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A103" s="33" t="str">
+        <f t="shared" si="8"/>
+        <v>sheep</v>
+      </c>
+      <c r="F103" t="s">
+        <v>2</v>
+      </c>
+      <c r="J103" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K103" s="33">
+        <f t="shared" si="7"/>
+        <v>15</v>
+      </c>
+      <c r="L103" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>%</v>
+      </c>
+      <c r="M103" s="29"/>
+      <c r="N103" s="33" t="str">
+        <f t="shared" ref="N103:N104" si="9">N82</f>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A104" s="33" t="str">
+        <f t="shared" si="8"/>
+        <v>horses</v>
+      </c>
+      <c r="F104" t="s">
+        <v>2</v>
+      </c>
+      <c r="J104" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K104" s="33">
+        <f t="shared" si="7"/>
+        <v>15</v>
+      </c>
+      <c r="L104" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>%</v>
+      </c>
+      <c r="M104" s="29"/>
+      <c r="N104" s="33" t="str">
         <f t="shared" si="9"/>
         <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F101" t="s">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F105" t="s">
         <v>12</v>
       </c>
-      <c r="J101" s="29" t="s">
+      <c r="J105" s="29" t="s">
         <v>396</v>
       </c>
-      <c r="K101" s="29">
+      <c r="K105" s="29">
         <v>5</v>
       </c>
-      <c r="L101" s="29" t="s">
+      <c r="L105" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="M101" s="29"/>
-      <c r="N101" t="s">
+      <c r="M105" s="29"/>
+      <c r="N105" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A102" s="33" t="str">
-        <f>A75</f>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A106" s="33" t="str">
+        <f>A79</f>
         <v>cattle</v>
       </c>
-      <c r="B102" s="33" t="str">
-        <f>B75</f>
+      <c r="B106" s="33" t="str">
+        <f>B79</f>
         <v>dairy</v>
       </c>
-      <c r="E102" s="33" t="str">
-        <f t="shared" ref="E102:E103" si="10">E75</f>
+      <c r="E106" s="33" t="str">
+        <f t="shared" ref="E106:E107" si="10">E79</f>
         <v>cows</v>
       </c>
-      <c r="F102" t="s">
+      <c r="F106" t="s">
         <v>12</v>
       </c>
-      <c r="J102" s="33" t="str">
-        <f t="shared" ref="J102:N106" si="11">J75</f>
+      <c r="J106" s="33" t="str">
+        <f t="shared" ref="J106:N110" si="11">J79</f>
         <v>feeding_losses</v>
       </c>
-      <c r="K102" s="33">
+      <c r="K106" s="33">
         <f t="shared" si="11"/>
         <v>5</v>
-      </c>
-      <c r="L102" s="33" t="str">
-        <f t="shared" si="11"/>
-        <v>%</v>
-      </c>
-      <c r="M102" s="33" t="str">
-        <f t="shared" si="11"/>
-        <v>No feeding on pasture</v>
-      </c>
-      <c r="N102" s="33" t="str">
-        <f t="shared" si="11"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A103" s="33" t="str">
-        <f t="shared" ref="A103:A106" si="12">A76</f>
-        <v>cattle</v>
-      </c>
-      <c r="E103" s="33" t="str">
-        <f t="shared" si="10"/>
-        <v>bulls</v>
-      </c>
-      <c r="F103" t="s">
-        <v>12</v>
-      </c>
-      <c r="J103" s="33" t="str">
-        <f t="shared" si="11"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="K103" s="33">
-        <f t="shared" si="11"/>
-        <v>5</v>
-      </c>
-      <c r="L103" s="33" t="str">
-        <f t="shared" si="11"/>
-        <v>%</v>
-      </c>
-      <c r="M103" s="33" t="str">
-        <f t="shared" si="11"/>
-        <v>No feeding on pasture</v>
-      </c>
-      <c r="N103" s="33" t="str">
-        <f t="shared" si="11"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A104" s="33" t="str">
-        <f t="shared" si="12"/>
-        <v>cattle</v>
-      </c>
-      <c r="F104" t="s">
-        <v>12</v>
-      </c>
-      <c r="J104" s="33" t="str">
-        <f t="shared" si="11"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="K104" s="33">
-        <f t="shared" si="11"/>
-        <v>6</v>
-      </c>
-      <c r="L104" s="33" t="str">
-        <f t="shared" si="11"/>
-        <v>%</v>
-      </c>
-      <c r="M104" s="33" t="str">
-        <f t="shared" si="11"/>
-        <v>10% feeding on pasture</v>
-      </c>
-      <c r="N104" s="33" t="str">
-        <f t="shared" si="11"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A105" s="33" t="str">
-        <f t="shared" si="12"/>
-        <v>sheep</v>
-      </c>
-      <c r="F105" t="s">
-        <v>12</v>
-      </c>
-      <c r="J105" s="33" t="str">
-        <f t="shared" si="11"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="K105" s="33">
-        <f t="shared" si="11"/>
-        <v>15</v>
-      </c>
-      <c r="L105" s="33" t="str">
-        <f t="shared" si="11"/>
-        <v>%</v>
-      </c>
-      <c r="M105" s="29"/>
-      <c r="N105" s="33" t="str">
-        <f t="shared" ref="N105:N106" si="13">N78</f>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A106" s="33" t="str">
-        <f t="shared" si="12"/>
-        <v>horses</v>
-      </c>
-      <c r="F106" t="s">
-        <v>12</v>
-      </c>
-      <c r="J106" s="33" t="str">
-        <f t="shared" si="11"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="K106" s="33">
-        <f t="shared" si="11"/>
-        <v>15</v>
       </c>
       <c r="L106" s="33" t="str">
         <f t="shared" si="11"/>
         <v>%</v>
       </c>
-      <c r="M106" s="29"/>
+      <c r="M106" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>No feeding on pasture</v>
+      </c>
       <c r="N106" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A107" s="33" t="str">
+        <f t="shared" ref="A107:A110" si="12">A80</f>
+        <v>cattle</v>
+      </c>
+      <c r="E107" s="33" t="str">
+        <f t="shared" si="10"/>
+        <v>bulls</v>
+      </c>
+      <c r="F107" t="s">
+        <v>12</v>
+      </c>
+      <c r="J107" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K107" s="33">
+        <f t="shared" si="11"/>
+        <v>5</v>
+      </c>
+      <c r="L107" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>%</v>
+      </c>
+      <c r="M107" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>No feeding on pasture</v>
+      </c>
+      <c r="N107" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A108" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v>cattle</v>
+      </c>
+      <c r="F108" t="s">
+        <v>12</v>
+      </c>
+      <c r="J108" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K108" s="33">
+        <f t="shared" si="11"/>
+        <v>6</v>
+      </c>
+      <c r="L108" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>%</v>
+      </c>
+      <c r="M108" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>10% feeding on pasture</v>
+      </c>
+      <c r="N108" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A109" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v>sheep</v>
+      </c>
+      <c r="F109" t="s">
+        <v>12</v>
+      </c>
+      <c r="J109" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K109" s="33">
+        <f t="shared" si="11"/>
+        <v>15</v>
+      </c>
+      <c r="L109" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>%</v>
+      </c>
+      <c r="M109" s="29"/>
+      <c r="N109" s="33" t="str">
+        <f t="shared" ref="N109:N110" si="13">N82</f>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A110" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v>horses</v>
+      </c>
+      <c r="F110" t="s">
+        <v>12</v>
+      </c>
+      <c r="J110" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K110" s="33">
+        <f t="shared" si="11"/>
+        <v>15</v>
+      </c>
+      <c r="L110" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>%</v>
+      </c>
+      <c r="M110" s="29"/>
+      <c r="N110" s="33" t="str">
         <f t="shared" si="13"/>
         <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A107" s="33"/>
-      <c r="F107" t="s">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A111" s="33"/>
+      <c r="F111" t="s">
         <v>33</v>
       </c>
-      <c r="J107" s="29" t="s">
+      <c r="J111" s="29" t="s">
         <v>396</v>
       </c>
-      <c r="K107" s="29">
-        <v>0</v>
-      </c>
-      <c r="L107" t="s">
+      <c r="K111" s="29">
+        <v>0</v>
+      </c>
+      <c r="L111" t="s">
         <v>28</v>
       </c>
-      <c r="M107" s="29" t="s">
+      <c r="M111" s="29" t="s">
         <v>408</v>
       </c>
-      <c r="N107" s="33"/>
-    </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
+      <c r="N111" s="33"/>
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
         <v>24</v>
       </c>
-      <c r="F108" t="s">
+      <c r="F112" t="s">
         <v>33</v>
       </c>
-      <c r="J108" t="s">
+      <c r="J112" t="s">
         <v>397</v>
       </c>
-      <c r="K108" s="29">
+      <c r="K112" s="29">
         <f>100-55</f>
         <v>45</v>
       </c>
-      <c r="L108" t="s">
+      <c r="L112" t="s">
         <v>28</v>
       </c>
-      <c r="M108" s="29" t="s">
+      <c r="M112" s="29" t="s">
         <v>400</v>
       </c>
-      <c r="N108" t="s">
+      <c r="N112" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
         <v>395</v>
       </c>
-      <c r="F109" t="s">
+      <c r="F113" t="s">
         <v>33</v>
       </c>
-      <c r="J109" t="s">
+      <c r="J113" t="s">
         <v>397</v>
       </c>
-      <c r="K109" s="29">
+      <c r="K113" s="29">
         <f>100-50</f>
         <v>50</v>
       </c>
-      <c r="L109" t="s">
+      <c r="L113" t="s">
         <v>28</v>
       </c>
-      <c r="M109" s="29" t="s">
+      <c r="M113" s="29" t="s">
         <v>400</v>
       </c>
-      <c r="N109" t="s">
+      <c r="N113" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K110" s="3"/>
-      <c r="M110" s="29"/>
-    </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A111" s="3" t="s">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K114" s="3"/>
+      <c r="M114" s="29"/>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A115" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="K111" s="3"/>
-      <c r="M111" s="29"/>
-    </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K112" s="3"/>
-      <c r="M112" s="29"/>
-    </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K113" s="3"/>
-      <c r="M113" s="3"/>
-    </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A114" s="1" t="s">
+      <c r="K115" s="3"/>
+      <c r="M115" s="29"/>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K116" s="3"/>
+      <c r="M116" s="29"/>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K117" s="3"/>
+      <c r="M117" s="3"/>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B114" s="1"/>
-      <c r="C114" s="1"/>
-      <c r="D114" s="1"/>
-      <c r="E114" s="2"/>
-      <c r="F114" s="2"/>
-      <c r="G114" s="2"/>
-      <c r="H114" s="2"/>
-      <c r="I114" s="2"/>
-      <c r="J114" s="2"/>
-      <c r="K114" s="2"/>
-      <c r="L114" s="2"/>
-      <c r="M114" s="2" t="s">
+      <c r="B118" s="1"/>
+      <c r="C118" s="1"/>
+      <c r="D118" s="1"/>
+      <c r="E118" s="2"/>
+      <c r="F118" s="2"/>
+      <c r="G118" s="2"/>
+      <c r="H118" s="2"/>
+      <c r="I118" s="2"/>
+      <c r="J118" s="2"/>
+      <c r="K118" s="2"/>
+      <c r="L118" s="2"/>
+      <c r="M118" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="N114" s="2"/>
-    </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F115" t="s">
-        <v>310</v>
-      </c>
-      <c r="J115" t="s">
-        <v>390</v>
-      </c>
-      <c r="K115" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F115,'feed pars'!B$6:B$43,0))</f>
-        <v>100</v>
-      </c>
-      <c r="L115" t="s">
-        <v>28</v>
-      </c>
-      <c r="M115" s="29" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F116" t="s">
-        <v>311</v>
-      </c>
-      <c r="J116" t="s">
-        <v>390</v>
-      </c>
-      <c r="K116" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F116,'feed pars'!B$6:B$43,0))</f>
-        <v>100</v>
-      </c>
-      <c r="L116" t="s">
-        <v>28</v>
-      </c>
-      <c r="M116" s="3"/>
-    </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F117" t="s">
-        <v>312</v>
-      </c>
-      <c r="J117" t="s">
-        <v>390</v>
-      </c>
-      <c r="K117" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F117,'feed pars'!B$6:B$43,0))</f>
-        <v>100</v>
-      </c>
-      <c r="L117" t="s">
-        <v>28</v>
-      </c>
-      <c r="M117" s="3"/>
-    </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F118" t="s">
-        <v>2</v>
-      </c>
-      <c r="J118" t="s">
-        <v>390</v>
-      </c>
-      <c r="K118" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F118,'feed pars'!B$6:B$43,0))</f>
-        <v>100</v>
-      </c>
-      <c r="L118" t="s">
-        <v>28</v>
-      </c>
-      <c r="M118" s="3"/>
+      <c r="N118" s="2"/>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F119" t="s">
-        <v>12</v>
+        <v>310</v>
       </c>
       <c r="J119" t="s">
         <v>390</v>
@@ -4211,11 +4219,13 @@
       <c r="L119" t="s">
         <v>28</v>
       </c>
-      <c r="M119" s="3"/>
+      <c r="M119" s="29" t="s">
+        <v>393</v>
+      </c>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F120" t="s">
-        <v>33</v>
+        <v>311</v>
       </c>
       <c r="J120" t="s">
         <v>390</v>
@@ -4231,14 +4241,14 @@
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F121" t="s">
-        <v>17</v>
+        <v>312</v>
       </c>
       <c r="J121" t="s">
         <v>390</v>
       </c>
       <c r="K121" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F121,'feed pars'!B$6:B$43,0))</f>
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="L121" t="s">
         <v>28</v>
@@ -4247,14 +4257,14 @@
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F122" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="J122" t="s">
         <v>390</v>
       </c>
       <c r="K122" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F122,'feed pars'!B$6:B$43,0))</f>
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="L122" t="s">
         <v>28</v>
@@ -4263,14 +4273,14 @@
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F123" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="J123" t="s">
         <v>390</v>
       </c>
       <c r="K123" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F123,'feed pars'!B$6:B$43,0))</f>
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="L123" t="s">
         <v>28</v>
@@ -4279,14 +4289,14 @@
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F124" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="J124" t="s">
         <v>390</v>
       </c>
       <c r="K124" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F124,'feed pars'!B$6:B$43,0))</f>
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="L124" t="s">
         <v>28</v>
@@ -4295,7 +4305,7 @@
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F125" t="s">
-        <v>317</v>
+        <v>17</v>
       </c>
       <c r="J125" t="s">
         <v>390</v>
@@ -4311,14 +4321,14 @@
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F126" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J126" t="s">
         <v>390</v>
       </c>
       <c r="K126" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F126,'feed pars'!B$6:B$43,0))</f>
-        <v>67.5</v>
+        <v>87</v>
       </c>
       <c r="L126" t="s">
         <v>28</v>
@@ -4327,14 +4337,14 @@
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F127" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="J127" t="s">
         <v>390</v>
       </c>
       <c r="K127" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F127,'feed pars'!B$6:B$43,0))</f>
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L127" t="s">
         <v>28</v>
@@ -4343,14 +4353,14 @@
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F128" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="J128" t="s">
         <v>390</v>
       </c>
       <c r="K128" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F128,'feed pars'!B$6:B$43,0))</f>
-        <v>86.8</v>
+        <v>87</v>
       </c>
       <c r="L128" t="s">
         <v>28</v>
@@ -4359,14 +4369,14 @@
     </row>
     <row r="129" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F129" t="s">
-        <v>35</v>
+        <v>317</v>
       </c>
       <c r="J129" t="s">
         <v>390</v>
       </c>
       <c r="K129" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F129,'feed pars'!B$6:B$43,0))</f>
-        <v>92.5</v>
+        <v>87</v>
       </c>
       <c r="L129" t="s">
         <v>28</v>
@@ -4375,14 +4385,14 @@
     </row>
     <row r="130" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F130" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J130" t="s">
         <v>390</v>
       </c>
       <c r="K130" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F130,'feed pars'!B$6:B$43,0))</f>
-        <v>92</v>
+        <v>67.5</v>
       </c>
       <c r="L130" t="s">
         <v>28</v>
@@ -4391,14 +4401,14 @@
     </row>
     <row r="131" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F131" t="s">
-        <v>314</v>
+        <v>41</v>
       </c>
       <c r="J131" t="s">
         <v>390</v>
       </c>
       <c r="K131" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F131,'feed pars'!B$6:B$43,0))</f>
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L131" t="s">
         <v>28</v>
@@ -4407,14 +4417,14 @@
     </row>
     <row r="132" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F132" t="s">
-        <v>305</v>
+        <v>42</v>
       </c>
       <c r="J132" t="s">
         <v>390</v>
       </c>
       <c r="K132" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F132,'feed pars'!B$6:B$43,0))</f>
-        <v>85</v>
+        <v>86.8</v>
       </c>
       <c r="L132" t="s">
         <v>28</v>
@@ -4423,14 +4433,14 @@
     </row>
     <row r="133" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F133" t="s">
-        <v>318</v>
+        <v>35</v>
       </c>
       <c r="J133" t="s">
         <v>390</v>
       </c>
       <c r="K133" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F133,'feed pars'!B$6:B$43,0))</f>
-        <v>87</v>
+        <v>92.5</v>
       </c>
       <c r="L133" t="s">
         <v>28</v>
@@ -4439,14 +4449,14 @@
     </row>
     <row r="134" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F134" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J134" t="s">
         <v>390</v>
       </c>
       <c r="K134" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F134,'feed pars'!B$6:B$43,0))</f>
-        <v>87.5</v>
+        <v>92</v>
       </c>
       <c r="L134" t="s">
         <v>28</v>
@@ -4455,14 +4465,14 @@
     </row>
     <row r="135" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F135" t="s">
-        <v>45</v>
+        <v>314</v>
       </c>
       <c r="J135" t="s">
         <v>390</v>
       </c>
       <c r="K135" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F135,'feed pars'!B$6:B$43,0))</f>
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="L135" t="s">
         <v>28</v>
@@ -4471,14 +4481,14 @@
     </row>
     <row r="136" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F136" t="s">
-        <v>36</v>
+        <v>305</v>
       </c>
       <c r="J136" t="s">
         <v>390</v>
       </c>
       <c r="K136" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F136,'feed pars'!B$6:B$43,0))</f>
-        <v>89.5</v>
+        <v>85</v>
       </c>
       <c r="L136" t="s">
         <v>28</v>
@@ -4487,14 +4497,14 @@
     </row>
     <row r="137" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F137" t="s">
-        <v>46</v>
+        <v>318</v>
       </c>
       <c r="J137" t="s">
         <v>390</v>
       </c>
       <c r="K137" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F137,'feed pars'!B$6:B$43,0))</f>
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="L137" t="s">
         <v>28</v>
@@ -4503,14 +4513,14 @@
     </row>
     <row r="138" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F138" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="J138" t="s">
         <v>390</v>
       </c>
       <c r="K138" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F138,'feed pars'!B$6:B$43,0))</f>
-        <v>91</v>
+        <v>87.5</v>
       </c>
       <c r="L138" t="s">
         <v>28</v>
@@ -4519,14 +4529,14 @@
     </row>
     <row r="139" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F139" t="s">
-        <v>319</v>
+        <v>45</v>
       </c>
       <c r="J139" t="s">
         <v>390</v>
       </c>
       <c r="K139" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F139,'feed pars'!B$6:B$43,0))</f>
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L139" t="s">
         <v>28</v>
@@ -4535,14 +4545,14 @@
     </row>
     <row r="140" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F140" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="J140" t="s">
         <v>390</v>
       </c>
       <c r="K140" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F140,'feed pars'!B$6:B$43,0))</f>
-        <v>87</v>
+        <v>89.5</v>
       </c>
       <c r="L140" t="s">
         <v>28</v>
@@ -4551,14 +4561,14 @@
     </row>
     <row r="141" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F141" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="J141" t="s">
         <v>390</v>
       </c>
       <c r="K141" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F141,'feed pars'!B$6:B$43,0))</f>
-        <v>88.5</v>
+        <v>91</v>
       </c>
       <c r="L141" t="s">
         <v>28</v>
@@ -4567,14 +4577,14 @@
     </row>
     <row r="142" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F142" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="J142" t="s">
         <v>390</v>
       </c>
       <c r="K142" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F142,'feed pars'!B$6:B$43,0))</f>
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L142" t="s">
         <v>28</v>
@@ -4583,14 +4593,14 @@
     </row>
     <row r="143" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F143" t="s">
-        <v>51</v>
+        <v>319</v>
       </c>
       <c r="J143" t="s">
         <v>390</v>
       </c>
       <c r="K143" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F143,'feed pars'!B$6:B$43,0))</f>
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="L143" t="s">
         <v>28</v>
@@ -4599,14 +4609,14 @@
     </row>
     <row r="144" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F144" t="s">
-        <v>313</v>
+        <v>48</v>
       </c>
       <c r="J144" t="s">
         <v>390</v>
       </c>
       <c r="K144" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F144,'feed pars'!B$6:B$43,0))</f>
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L144" t="s">
         <v>28</v>
@@ -4615,14 +4625,14 @@
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F145" t="s">
-        <v>388</v>
+        <v>49</v>
       </c>
       <c r="J145" t="s">
         <v>390</v>
       </c>
       <c r="K145" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F145,'feed pars'!B$6:B$43,0))</f>
-        <v>87</v>
+        <v>88.5</v>
       </c>
       <c r="L145" t="s">
         <v>28</v>
@@ -4631,14 +4641,14 @@
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F146" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="J146" t="s">
         <v>390</v>
       </c>
       <c r="K146" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F146,'feed pars'!B$6:B$43,0))</f>
-        <v>75.5</v>
+        <v>90</v>
       </c>
       <c r="L146" t="s">
         <v>28</v>
@@ -4647,14 +4657,14 @@
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F147" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J147" t="s">
         <v>390</v>
       </c>
       <c r="K147" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F147,'feed pars'!B$6:B$43,0))</f>
-        <v>89.5</v>
+        <v>11</v>
       </c>
       <c r="L147" t="s">
         <v>28</v>
@@ -4663,14 +4673,14 @@
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F148" t="s">
-        <v>54</v>
+        <v>313</v>
       </c>
       <c r="J148" t="s">
         <v>390</v>
       </c>
       <c r="K148" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F148,'feed pars'!B$6:B$43,0))</f>
-        <v>6.25</v>
+        <v>90</v>
       </c>
       <c r="L148" t="s">
         <v>28</v>
@@ -4679,14 +4689,14 @@
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F149" t="s">
-        <v>55</v>
+        <v>388</v>
       </c>
       <c r="J149" t="s">
         <v>390</v>
       </c>
       <c r="K149" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F149,'feed pars'!B$6:B$43,0))</f>
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="L149" t="s">
         <v>28</v>
@@ -4695,14 +4705,14 @@
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F150" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="J150" t="s">
         <v>390</v>
       </c>
       <c r="K150" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F150,'feed pars'!B$6:B$43,0))</f>
-        <v>91</v>
+        <v>75.5</v>
       </c>
       <c r="L150" t="s">
         <v>28</v>
@@ -4711,14 +4721,14 @@
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F151" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="J151" t="s">
         <v>390</v>
       </c>
       <c r="K151" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F151,'feed pars'!B$6:B$43,0))</f>
-        <v>92</v>
+        <v>89.5</v>
       </c>
       <c r="L151" t="s">
         <v>28</v>
@@ -4726,134 +4736,150 @@
       <c r="M151" s="3"/>
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A152" s="7" t="s">
+      <c r="F152" t="s">
+        <v>54</v>
+      </c>
+      <c r="J152" t="s">
+        <v>390</v>
+      </c>
+      <c r="K152" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F152,'feed pars'!B$6:B$43,0))</f>
+        <v>6.25</v>
+      </c>
+      <c r="L152" t="s">
+        <v>28</v>
+      </c>
+      <c r="M152" s="3"/>
+    </row>
+    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F153" t="s">
+        <v>55</v>
+      </c>
+      <c r="J153" t="s">
+        <v>390</v>
+      </c>
+      <c r="K153" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F153,'feed pars'!B$6:B$43,0))</f>
+        <v>97</v>
+      </c>
+      <c r="L153" t="s">
+        <v>28</v>
+      </c>
+      <c r="M153" s="3"/>
+    </row>
+    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F154" t="s">
+        <v>56</v>
+      </c>
+      <c r="J154" t="s">
+        <v>390</v>
+      </c>
+      <c r="K154" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F154,'feed pars'!B$6:B$43,0))</f>
+        <v>91</v>
+      </c>
+      <c r="L154" t="s">
+        <v>28</v>
+      </c>
+      <c r="M154" s="3"/>
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F155" t="s">
+        <v>57</v>
+      </c>
+      <c r="J155" t="s">
+        <v>390</v>
+      </c>
+      <c r="K155" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F155,'feed pars'!B$6:B$43,0))</f>
+        <v>92</v>
+      </c>
+      <c r="L155" t="s">
+        <v>28</v>
+      </c>
+      <c r="M155" s="3"/>
+    </row>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A156" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B152" s="7"/>
-      <c r="C152" s="6"/>
-      <c r="D152" s="6"/>
-      <c r="E152" s="6"/>
-      <c r="F152" s="6"/>
-      <c r="G152" s="6"/>
-      <c r="H152" s="6"/>
-      <c r="I152" s="6"/>
-      <c r="J152" s="6"/>
-      <c r="K152" s="6"/>
-      <c r="L152" s="6" t="s">
+      <c r="B156" s="7"/>
+      <c r="C156" s="6"/>
+      <c r="D156" s="6"/>
+      <c r="E156" s="6"/>
+      <c r="F156" s="6"/>
+      <c r="G156" s="6"/>
+      <c r="H156" s="6"/>
+      <c r="I156" s="6"/>
+      <c r="J156" s="6"/>
+      <c r="K156" s="6"/>
+      <c r="L156" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="M152" s="6"/>
-      <c r="N152" s="6"/>
-    </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
-        <v>24</v>
-      </c>
-      <c r="F153" t="s">
-        <v>310</v>
-      </c>
-      <c r="J153" t="s">
-        <v>18</v>
-      </c>
-      <c r="K153" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F153,'feed pars'!B$6:B$43,0))</f>
-        <v>11.5</v>
-      </c>
-      <c r="M153" s="3"/>
-    </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
-        <v>24</v>
-      </c>
-      <c r="F154" t="s">
-        <v>311</v>
-      </c>
-      <c r="J154" t="s">
-        <v>18</v>
-      </c>
-      <c r="K154" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F154,'feed pars'!B$6:B$43,0))</f>
-        <v>10.4</v>
-      </c>
-      <c r="M154" s="3"/>
-    </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
-        <v>24</v>
-      </c>
-      <c r="F155" t="s">
-        <v>312</v>
-      </c>
-      <c r="J155" t="s">
-        <v>18</v>
-      </c>
-      <c r="K155" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F155,'feed pars'!B$6:B$43,0))</f>
-        <v>10</v>
-      </c>
-      <c r="M155" s="3"/>
-    </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
-        <v>24</v>
-      </c>
-      <c r="F156" t="s">
-        <v>12</v>
-      </c>
-      <c r="J156" t="s">
-        <v>18</v>
-      </c>
-      <c r="K156" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F156,'feed pars'!B$6:B$43,0))</f>
-        <v>11.3</v>
-      </c>
+      <c r="M156" s="6"/>
+      <c r="N156" s="6"/>
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>24</v>
       </c>
       <c r="F157" t="s">
-        <v>33</v>
+        <v>310</v>
       </c>
       <c r="J157" t="s">
         <v>18</v>
       </c>
       <c r="K157" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F157,'feed pars'!B$6:B$43,0))</f>
-        <v>10</v>
-      </c>
+        <v>11.5</v>
+      </c>
+      <c r="M157" s="3"/>
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K158" s="3"/>
+      <c r="A158" t="s">
+        <v>24</v>
+      </c>
+      <c r="F158" t="s">
+        <v>311</v>
+      </c>
+      <c r="J158" t="s">
+        <v>18</v>
+      </c>
+      <c r="K158" s="26">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F158,'feed pars'!B$6:B$43,0))</f>
+        <v>10.4</v>
+      </c>
+      <c r="M158" s="3"/>
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>24</v>
       </c>
       <c r="F159" t="s">
-        <v>17</v>
+        <v>312</v>
       </c>
       <c r="J159" t="s">
         <v>18</v>
       </c>
       <c r="K159" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F159,'feed pars'!B$6:B$43,0))</f>
-        <v>14.1</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="M159" s="3"/>
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>24</v>
       </c>
       <c r="F160" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="J160" t="s">
         <v>18</v>
       </c>
       <c r="K160" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F160,'feed pars'!B$6:B$43,0))</f>
-        <v>13.2</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
@@ -4861,44 +4887,32 @@
         <v>24</v>
       </c>
       <c r="F161" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="J161" t="s">
         <v>18</v>
       </c>
       <c r="K161" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F161,'feed pars'!B$6:B$43,0))</f>
-        <v>11.7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
-        <v>24</v>
-      </c>
-      <c r="F162" t="s">
-        <v>39</v>
-      </c>
-      <c r="J162" t="s">
-        <v>18</v>
-      </c>
-      <c r="K162" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F162,'feed pars'!B$6:B$43,0))</f>
-        <v>14</v>
-      </c>
+      <c r="K162" s="3"/>
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>24</v>
       </c>
       <c r="F163" t="s">
-        <v>317</v>
+        <v>17</v>
       </c>
       <c r="J163" t="s">
         <v>18</v>
       </c>
       <c r="K163" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F163,'feed pars'!B$6:B$43,0))</f>
-        <v>13.9</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
@@ -4906,14 +4920,14 @@
         <v>24</v>
       </c>
       <c r="F164" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J164" t="s">
         <v>18</v>
       </c>
       <c r="K164" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F164,'feed pars'!B$6:B$43,0))</f>
-        <v>12.8</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.25">
@@ -4921,14 +4935,14 @@
         <v>24</v>
       </c>
       <c r="F165" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="J165" t="s">
         <v>18</v>
       </c>
       <c r="K165" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F165,'feed pars'!B$6:B$43,0))</f>
-        <v>13.8</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.25">
@@ -4936,14 +4950,14 @@
         <v>24</v>
       </c>
       <c r="F166" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="J166" t="s">
         <v>18</v>
       </c>
       <c r="K166" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F166,'feed pars'!B$6:B$43,0))</f>
-        <v>13.3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
@@ -4951,14 +4965,14 @@
         <v>24</v>
       </c>
       <c r="F167" t="s">
-        <v>35</v>
+        <v>317</v>
       </c>
       <c r="J167" t="s">
         <v>18</v>
       </c>
       <c r="K167" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F167,'feed pars'!B$6:B$43,0))</f>
-        <v>22.1</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
@@ -4966,14 +4980,14 @@
         <v>24</v>
       </c>
       <c r="F168" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J168" t="s">
         <v>18</v>
       </c>
       <c r="K168" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F168,'feed pars'!B$6:B$43,0))</f>
-        <v>20.100000000000001</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
@@ -4981,14 +4995,14 @@
         <v>24</v>
       </c>
       <c r="F169" t="s">
-        <v>305</v>
+        <v>41</v>
       </c>
       <c r="J169" t="s">
         <v>18</v>
       </c>
       <c r="K169" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F169,'feed pars'!B$6:B$43,0))</f>
-        <v>6.6</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.25">
@@ -4996,14 +5010,14 @@
         <v>24</v>
       </c>
       <c r="F170" t="s">
-        <v>314</v>
+        <v>42</v>
       </c>
       <c r="J170" t="s">
         <v>18</v>
       </c>
       <c r="K170" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F170,'feed pars'!B$6:B$43,0))</f>
-        <v>36.6</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.25">
@@ -5011,14 +5025,14 @@
         <v>24</v>
       </c>
       <c r="F171" t="s">
-        <v>318</v>
+        <v>35</v>
       </c>
       <c r="J171" t="s">
         <v>18</v>
       </c>
       <c r="K171" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F171,'feed pars'!B$6:B$43,0))</f>
-        <v>16.399999999999999</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.25">
@@ -5026,14 +5040,14 @@
         <v>24</v>
       </c>
       <c r="F172" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J172" t="s">
         <v>18</v>
       </c>
       <c r="K172" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F172,'feed pars'!B$6:B$43,0))</f>
-        <v>14.6</v>
+        <v>20.100000000000001</v>
       </c>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
@@ -5041,14 +5055,14 @@
         <v>24</v>
       </c>
       <c r="F173" t="s">
-        <v>36</v>
+        <v>305</v>
       </c>
       <c r="J173" t="s">
         <v>18</v>
       </c>
       <c r="K173" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F173,'feed pars'!B$6:B$43,0))</f>
-        <v>12.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
@@ -5056,14 +5070,14 @@
         <v>24</v>
       </c>
       <c r="F174" t="s">
-        <v>46</v>
+        <v>314</v>
       </c>
       <c r="J174" t="s">
         <v>18</v>
       </c>
       <c r="K174" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F174,'feed pars'!B$6:B$43,0))</f>
-        <v>11.4</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
@@ -5071,14 +5085,14 @@
         <v>24</v>
       </c>
       <c r="F175" t="s">
-        <v>47</v>
+        <v>318</v>
       </c>
       <c r="J175" t="s">
         <v>18</v>
       </c>
       <c r="K175" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F175,'feed pars'!B$6:B$43,0))</f>
-        <v>13.4</v>
+        <v>16.399999999999999</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
@@ -5086,14 +5100,14 @@
         <v>24</v>
       </c>
       <c r="F176" t="s">
-        <v>319</v>
+        <v>44</v>
       </c>
       <c r="J176" t="s">
         <v>18</v>
       </c>
       <c r="K176" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F176,'feed pars'!B$6:B$43,0))</f>
-        <v>8.5</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.25">
@@ -5101,14 +5115,14 @@
         <v>24</v>
       </c>
       <c r="F177" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="J177" t="s">
         <v>18</v>
       </c>
       <c r="K177" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F177,'feed pars'!B$6:B$43,0))</f>
-        <v>11</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.25">
@@ -5116,14 +5130,14 @@
         <v>24</v>
       </c>
       <c r="F178" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="J178" t="s">
         <v>18</v>
       </c>
       <c r="K178" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F178,'feed pars'!B$6:B$43,0))</f>
-        <v>13.3</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.25">
@@ -5131,14 +5145,14 @@
         <v>24</v>
       </c>
       <c r="F179" t="s">
-        <v>313</v>
+        <v>47</v>
       </c>
       <c r="J179" t="s">
         <v>18</v>
       </c>
       <c r="K179" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F179,'feed pars'!B$6:B$43,0))</f>
-        <v>11.6</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.25">
@@ -5146,14 +5160,14 @@
         <v>24</v>
       </c>
       <c r="F180" t="s">
-        <v>52</v>
+        <v>319</v>
       </c>
       <c r="J180" t="s">
         <v>18</v>
       </c>
       <c r="K180" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F180,'feed pars'!B$6:B$43,0))</f>
-        <v>12.4</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.25">
@@ -5161,14 +5175,14 @@
         <v>24</v>
       </c>
       <c r="F181" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="J181" t="s">
         <v>18</v>
       </c>
       <c r="K181" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F181,'feed pars'!B$6:B$43,0))</f>
-        <v>12.3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.25">
@@ -5176,14 +5190,14 @@
         <v>24</v>
       </c>
       <c r="F182" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="J182" t="s">
         <v>18</v>
       </c>
       <c r="K182" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F182,'feed pars'!B$6:B$43,0))</f>
-        <v>13.6</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.25">
@@ -5191,14 +5205,14 @@
         <v>24</v>
       </c>
       <c r="F183" t="s">
-        <v>56</v>
+        <v>313</v>
       </c>
       <c r="J183" t="s">
         <v>18</v>
       </c>
       <c r="K183" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F183,'feed pars'!B$6:B$43,0))</f>
-        <v>15.5</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.25">
@@ -5206,96 +5220,108 @@
         <v>24</v>
       </c>
       <c r="F184" t="s">
-        <v>324</v>
+        <v>52</v>
       </c>
       <c r="J184" t="s">
         <v>18</v>
       </c>
-      <c r="K184" s="3">
-        <v>0</v>
+      <c r="K184" s="26">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F184,'feed pars'!B$6:B$43,0))</f>
+        <v>12.4</v>
       </c>
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A185" s="7" t="s">
-        <v>409</v>
-      </c>
-      <c r="B185" s="7"/>
-      <c r="C185" s="6"/>
-      <c r="D185" s="6"/>
-      <c r="E185" s="6"/>
-      <c r="F185" s="6"/>
-      <c r="G185" s="6"/>
-      <c r="H185" s="6"/>
-      <c r="I185" s="6"/>
-      <c r="J185" s="6"/>
-      <c r="K185" s="6"/>
-      <c r="L185" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M185" s="6"/>
-      <c r="N185" s="6"/>
+      <c r="A185" t="s">
+        <v>24</v>
+      </c>
+      <c r="F185" t="s">
+        <v>53</v>
+      </c>
+      <c r="J185" t="s">
+        <v>18</v>
+      </c>
+      <c r="K185" s="26">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F185,'feed pars'!B$6:B$43,0))</f>
+        <v>12.3</v>
+      </c>
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>395</v>
+        <v>24</v>
       </c>
       <c r="F186" t="s">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="J186" t="s">
         <v>18</v>
       </c>
       <c r="K186" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F186,'feed pars'!B$6:B$43,0))</f>
-        <v>9.1</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>395</v>
+        <v>24</v>
       </c>
       <c r="F187" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="J187" t="s">
         <v>18</v>
       </c>
-      <c r="K187" s="34">
-        <f>K157</f>
-        <v>10</v>
+      <c r="K187" s="26">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F187,'feed pars'!B$6:B$43,0))</f>
+        <v>15.5</v>
       </c>
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K188" s="34"/>
+      <c r="A188" t="s">
+        <v>24</v>
+      </c>
+      <c r="F188" t="s">
+        <v>324</v>
+      </c>
+      <c r="J188" t="s">
+        <v>18</v>
+      </c>
+      <c r="K188" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
-        <v>395</v>
-      </c>
-      <c r="F189" t="s">
-        <v>38</v>
-      </c>
-      <c r="J189" t="s">
-        <v>18</v>
-      </c>
-      <c r="K189" s="34">
-        <f>K161</f>
-        <v>11.7</v>
-      </c>
+      <c r="A189" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="B189" s="7"/>
+      <c r="C189" s="6"/>
+      <c r="D189" s="6"/>
+      <c r="E189" s="6"/>
+      <c r="F189" s="6"/>
+      <c r="G189" s="6"/>
+      <c r="H189" s="6"/>
+      <c r="I189" s="6"/>
+      <c r="J189" s="6"/>
+      <c r="K189" s="6"/>
+      <c r="L189" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M189" s="6"/>
+      <c r="N189" s="6"/>
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>395</v>
       </c>
       <c r="F190" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="J190" t="s">
         <v>18</v>
       </c>
-      <c r="K190" s="34">
-        <f>K160</f>
-        <v>13.2</v>
+      <c r="K190" s="26">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F190,'feed pars'!B$6:B$43,0))</f>
+        <v>9.1</v>
       </c>
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.25">
@@ -5303,43 +5329,31 @@
         <v>395</v>
       </c>
       <c r="F191" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="J191" t="s">
         <v>18</v>
       </c>
       <c r="K191" s="34">
-        <f>K159</f>
-        <v>14.1</v>
+        <f>K161</f>
+        <v>10</v>
       </c>
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A192" t="s">
-        <v>395</v>
-      </c>
-      <c r="F192" t="s">
-        <v>49</v>
-      </c>
-      <c r="J192" t="s">
-        <v>18</v>
-      </c>
-      <c r="K192" s="34">
-        <f t="shared" ref="K192:K198" si="14">K160</f>
-        <v>13.2</v>
-      </c>
+      <c r="K192" s="34"/>
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>395</v>
       </c>
       <c r="F193" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="J193" t="s">
         <v>18</v>
       </c>
       <c r="K193" s="34">
-        <f t="shared" si="14"/>
+        <f>K165</f>
         <v>11.7</v>
       </c>
     </row>
@@ -5348,14 +5362,14 @@
         <v>395</v>
       </c>
       <c r="F194" t="s">
-        <v>314</v>
+        <v>37</v>
       </c>
       <c r="J194" t="s">
         <v>18</v>
       </c>
       <c r="K194" s="34">
-        <f t="shared" si="14"/>
-        <v>14</v>
+        <f>K164</f>
+        <v>13.2</v>
       </c>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.25">
@@ -5363,14 +5377,14 @@
         <v>395</v>
       </c>
       <c r="F195" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="J195" t="s">
         <v>18</v>
       </c>
       <c r="K195" s="34">
-        <f t="shared" si="14"/>
-        <v>13.9</v>
+        <f>K163</f>
+        <v>14.1</v>
       </c>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.25">
@@ -5378,14 +5392,14 @@
         <v>395</v>
       </c>
       <c r="F196" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J196" t="s">
         <v>18</v>
       </c>
       <c r="K196" s="34">
-        <f t="shared" si="14"/>
-        <v>12.8</v>
+        <f t="shared" ref="K196:K202" si="14">K164</f>
+        <v>13.2</v>
       </c>
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.25">
@@ -5393,14 +5407,14 @@
         <v>395</v>
       </c>
       <c r="F197" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="J197" t="s">
         <v>18</v>
       </c>
       <c r="K197" s="34">
         <f t="shared" si="14"/>
-        <v>13.8</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.25">
@@ -5408,128 +5422,116 @@
         <v>395</v>
       </c>
       <c r="F198" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="J198" t="s">
         <v>18</v>
       </c>
       <c r="K198" s="34">
         <f t="shared" si="14"/>
-        <v>13.3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K199" s="3"/>
+      <c r="A199" t="s">
+        <v>395</v>
+      </c>
+      <c r="F199" t="s">
+        <v>53</v>
+      </c>
+      <c r="J199" t="s">
+        <v>18</v>
+      </c>
+      <c r="K199" s="34">
+        <f t="shared" si="14"/>
+        <v>13.9</v>
+      </c>
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A200" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B200" s="8"/>
-      <c r="C200" s="9"/>
-      <c r="D200" s="9"/>
-      <c r="E200" s="9"/>
-      <c r="F200" s="9"/>
-      <c r="G200" s="9"/>
-      <c r="H200" s="9"/>
-      <c r="I200" s="9"/>
-      <c r="J200" s="9"/>
-      <c r="K200" s="9"/>
-      <c r="L200" s="9"/>
-      <c r="M200" s="9"/>
-      <c r="N200" s="9"/>
+      <c r="A200" t="s">
+        <v>395</v>
+      </c>
+      <c r="F200" t="s">
+        <v>52</v>
+      </c>
+      <c r="J200" t="s">
+        <v>18</v>
+      </c>
+      <c r="K200" s="34">
+        <f t="shared" si="14"/>
+        <v>12.8</v>
+      </c>
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A201" s="30" t="s">
-        <v>391</v>
-      </c>
-      <c r="B201" s="31"/>
-      <c r="C201" s="32"/>
-      <c r="D201" s="32"/>
-      <c r="E201" s="32"/>
-      <c r="F201" s="32"/>
-      <c r="G201" s="32"/>
-      <c r="H201" s="32"/>
-      <c r="I201" s="32"/>
-      <c r="J201" s="32"/>
-      <c r="K201" s="32"/>
-      <c r="L201" s="32" t="s">
-        <v>300</v>
-      </c>
-      <c r="M201" s="32"/>
-      <c r="N201" s="32"/>
+      <c r="A201" t="s">
+        <v>395</v>
+      </c>
+      <c r="F201" t="s">
+        <v>56</v>
+      </c>
+      <c r="J201" t="s">
+        <v>18</v>
+      </c>
+      <c r="K201" s="34">
+        <f t="shared" si="14"/>
+        <v>13.8</v>
+      </c>
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>25</v>
-      </c>
-      <c r="E202" t="s">
-        <v>299</v>
+        <v>395</v>
       </c>
       <c r="F202" t="s">
-        <v>17</v>
+        <v>319</v>
       </c>
       <c r="J202" t="s">
         <v>18</v>
       </c>
-      <c r="K202" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F202,'feed pars'!B$6:B$43,0))</f>
-        <v>12.3</v>
+      <c r="K202" s="34">
+        <f t="shared" si="14"/>
+        <v>13.3</v>
       </c>
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A203" t="s">
-        <v>25</v>
-      </c>
-      <c r="E203" t="s">
-        <v>299</v>
-      </c>
-      <c r="F203" t="s">
-        <v>37</v>
-      </c>
-      <c r="J203" t="s">
-        <v>18</v>
-      </c>
-      <c r="K203" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F203,'feed pars'!B$6:B$43,0))</f>
-        <v>11.2</v>
-      </c>
+      <c r="K203" s="3"/>
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A204" t="s">
-        <v>25</v>
-      </c>
-      <c r="E204" t="s">
-        <v>299</v>
-      </c>
-      <c r="F204" t="s">
-        <v>38</v>
-      </c>
-      <c r="J204" t="s">
-        <v>18</v>
-      </c>
-      <c r="K204" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F204,'feed pars'!B$6:B$43,0))</f>
-        <v>9.4</v>
-      </c>
+      <c r="A204" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B204" s="8"/>
+      <c r="C204" s="9"/>
+      <c r="D204" s="9"/>
+      <c r="E204" s="9"/>
+      <c r="F204" s="9"/>
+      <c r="G204" s="9"/>
+      <c r="H204" s="9"/>
+      <c r="I204" s="9"/>
+      <c r="J204" s="9"/>
+      <c r="K204" s="9"/>
+      <c r="L204" s="9"/>
+      <c r="M204" s="9"/>
+      <c r="N204" s="9"/>
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A205" t="s">
-        <v>25</v>
-      </c>
-      <c r="E205" t="s">
-        <v>299</v>
-      </c>
-      <c r="F205" t="s">
-        <v>39</v>
-      </c>
-      <c r="J205" t="s">
-        <v>18</v>
-      </c>
-      <c r="K205" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F205,'feed pars'!B$6:B$43,0))</f>
-        <v>12</v>
-      </c>
+      <c r="A205" s="30" t="s">
+        <v>391</v>
+      </c>
+      <c r="B205" s="31"/>
+      <c r="C205" s="32"/>
+      <c r="D205" s="32"/>
+      <c r="E205" s="32"/>
+      <c r="F205" s="32"/>
+      <c r="G205" s="32"/>
+      <c r="H205" s="32"/>
+      <c r="I205" s="32"/>
+      <c r="J205" s="32"/>
+      <c r="K205" s="32"/>
+      <c r="L205" s="32" t="s">
+        <v>300</v>
+      </c>
+      <c r="M205" s="32"/>
+      <c r="N205" s="32"/>
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
@@ -5539,14 +5541,14 @@
         <v>299</v>
       </c>
       <c r="F206" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="J206" t="s">
         <v>18</v>
       </c>
       <c r="K206" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F206,'feed pars'!B$6:B$43,0))</f>
-        <v>13.2</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.25">
@@ -5557,14 +5559,14 @@
         <v>299</v>
       </c>
       <c r="F207" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J207" t="s">
         <v>18</v>
       </c>
       <c r="K207" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F207,'feed pars'!B$6:B$43,0))</f>
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.25">
@@ -5575,14 +5577,14 @@
         <v>299</v>
       </c>
       <c r="F208" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J208" t="s">
         <v>18</v>
       </c>
       <c r="K208" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F208,'feed pars'!B$6:B$43,0))</f>
-        <v>10.9</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.25">
@@ -5593,14 +5595,14 @@
         <v>299</v>
       </c>
       <c r="F209" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J209" t="s">
         <v>18</v>
       </c>
       <c r="K209" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F209,'feed pars'!B$6:B$43,0))</f>
-        <v>18.5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
@@ -5611,14 +5613,14 @@
         <v>299</v>
       </c>
       <c r="F210" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J210" t="s">
         <v>18</v>
       </c>
       <c r="K210" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F210,'feed pars'!B$6:B$43,0))</f>
-        <v>17.5</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.25">
@@ -5629,14 +5631,14 @@
         <v>299</v>
       </c>
       <c r="F211" t="s">
-        <v>314</v>
+        <v>41</v>
       </c>
       <c r="J211" t="s">
         <v>18</v>
       </c>
       <c r="K211" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F211,'feed pars'!B$6:B$43,0))</f>
-        <v>29.8</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.25">
@@ -5647,14 +5649,14 @@
         <v>299</v>
       </c>
       <c r="F212" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J212" t="s">
         <v>18</v>
       </c>
       <c r="K212" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F212,'feed pars'!B$6:B$43,0))</f>
-        <v>9.9</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.25">
@@ -5665,14 +5667,14 @@
         <v>299</v>
       </c>
       <c r="F213" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="J213" t="s">
         <v>18</v>
       </c>
       <c r="K213" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F213,'feed pars'!B$6:B$43,0))</f>
-        <v>10.3</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.25">
@@ -5683,14 +5685,14 @@
         <v>299</v>
       </c>
       <c r="F214" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="J214" t="s">
         <v>18</v>
       </c>
       <c r="K214" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F214,'feed pars'!B$6:B$43,0))</f>
-        <v>7.7</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.25">
@@ -5701,14 +5703,14 @@
         <v>299</v>
       </c>
       <c r="F215" t="s">
-        <v>46</v>
+        <v>314</v>
       </c>
       <c r="J215" t="s">
         <v>18</v>
       </c>
       <c r="K215" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F215,'feed pars'!B$6:B$43,0))</f>
-        <v>6.5</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.25">
@@ -5719,14 +5721,14 @@
         <v>299</v>
       </c>
       <c r="F216" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="J216" t="s">
         <v>18</v>
       </c>
       <c r="K216" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F216,'feed pars'!B$6:B$43,0))</f>
-        <v>6.2</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.25">
@@ -5737,14 +5739,14 @@
         <v>299</v>
       </c>
       <c r="F217" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J217" t="s">
         <v>18</v>
       </c>
       <c r="K217" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F217,'feed pars'!B$6:B$43,0))</f>
-        <v>7.8</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.25">
@@ -5755,14 +5757,14 @@
         <v>299</v>
       </c>
       <c r="F218" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="J218" t="s">
         <v>18</v>
       </c>
       <c r="K218" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F218,'feed pars'!B$6:B$43,0))</f>
-        <v>9.1999999999999993</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.25">
@@ -5773,14 +5775,14 @@
         <v>299</v>
       </c>
       <c r="F219" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="J219" t="s">
         <v>18</v>
       </c>
       <c r="K219" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F219,'feed pars'!B$6:B$43,0))</f>
-        <v>8.6999999999999993</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.25">
@@ -5791,14 +5793,14 @@
         <v>299</v>
       </c>
       <c r="F220" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="J220" t="s">
         <v>18</v>
       </c>
       <c r="K220" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F220,'feed pars'!B$6:B$43,0))</f>
-        <v>8.9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.25">
@@ -5809,14 +5811,14 @@
         <v>299</v>
       </c>
       <c r="F221" t="s">
-        <v>313</v>
+        <v>48</v>
       </c>
       <c r="J221" t="s">
         <v>18</v>
       </c>
       <c r="K221" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F221,'feed pars'!B$6:B$43,0))</f>
-        <v>7.0888888888888877</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.25">
@@ -5827,14 +5829,14 @@
         <v>299</v>
       </c>
       <c r="F222" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J222" t="s">
         <v>18</v>
       </c>
       <c r="K222" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F222,'feed pars'!B$6:B$43,0))</f>
-        <v>9</v>
+        <v>9.1999999999999993</v>
       </c>
     </row>
     <row r="223" spans="1:11" x14ac:dyDescent="0.25">
@@ -5845,14 +5847,14 @@
         <v>299</v>
       </c>
       <c r="F223" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J223" t="s">
         <v>18</v>
       </c>
       <c r="K223" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F223,'feed pars'!B$6:B$43,0))</f>
-        <v>8</v>
+        <v>8.6999999999999993</v>
       </c>
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.25">
@@ -5863,14 +5865,14 @@
         <v>299</v>
       </c>
       <c r="F224" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="J224" t="s">
         <v>18</v>
       </c>
       <c r="K224" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F224,'feed pars'!B$6:B$43,0))</f>
-        <v>12.2</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="225" spans="1:14" x14ac:dyDescent="0.25">
@@ -5881,14 +5883,14 @@
         <v>299</v>
       </c>
       <c r="F225" t="s">
-        <v>55</v>
+        <v>313</v>
       </c>
       <c r="J225" t="s">
         <v>18</v>
       </c>
       <c r="K225" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F225,'feed pars'!B$6:B$43,0))</f>
-        <v>12.2</v>
+        <v>7.0888888888888877</v>
       </c>
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.25">
@@ -5899,14 +5901,14 @@
         <v>299</v>
       </c>
       <c r="F226" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="J226" t="s">
         <v>18</v>
       </c>
       <c r="K226" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F226,'feed pars'!B$6:B$43,0))</f>
-        <v>11.3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.25">
@@ -5917,109 +5919,121 @@
         <v>299</v>
       </c>
       <c r="F227" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="J227" t="s">
         <v>18</v>
       </c>
       <c r="K227" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F227,'feed pars'!B$6:B$43,0))</f>
-        <v>10.8</v>
+        <v>8</v>
       </c>
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A228" s="30" t="s">
-        <v>392</v>
-      </c>
-      <c r="B228" s="31"/>
-      <c r="C228" s="32"/>
-      <c r="D228" s="32"/>
-      <c r="E228" s="32"/>
-      <c r="F228" s="32"/>
-      <c r="G228" s="32"/>
-      <c r="H228" s="32"/>
-      <c r="I228" s="32"/>
-      <c r="J228" s="32"/>
-      <c r="K228" s="32"/>
-      <c r="L228" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="M228" s="32"/>
-      <c r="N228" s="32"/>
+      <c r="A228" t="s">
+        <v>25</v>
+      </c>
+      <c r="E228" t="s">
+        <v>299</v>
+      </c>
+      <c r="F228" t="s">
+        <v>54</v>
+      </c>
+      <c r="J228" t="s">
+        <v>18</v>
+      </c>
+      <c r="K228" s="26">
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F228,'feed pars'!B$6:B$43,0))</f>
+        <v>12.2</v>
+      </c>
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>25</v>
       </c>
+      <c r="E229" t="s">
+        <v>299</v>
+      </c>
       <c r="F229" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="J229" t="s">
         <v>18</v>
       </c>
       <c r="K229" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F229,'feed pars'!B$6:B$43,0))</f>
-        <v>12.1</v>
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F229,'feed pars'!B$6:B$43,0))</f>
+        <v>12.2</v>
       </c>
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>25</v>
       </c>
+      <c r="E230" t="s">
+        <v>299</v>
+      </c>
       <c r="F230" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="J230" t="s">
         <v>18</v>
       </c>
       <c r="K230" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F230,'feed pars'!B$6:B$43,0))</f>
-        <v>11</v>
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F230,'feed pars'!B$6:B$43,0))</f>
+        <v>11.3</v>
       </c>
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>25</v>
       </c>
+      <c r="E231" t="s">
+        <v>299</v>
+      </c>
       <c r="F231" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="J231" t="s">
         <v>18</v>
       </c>
       <c r="K231" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F231,'feed pars'!B$6:B$43,0))</f>
-        <v>9</v>
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F231,'feed pars'!B$6:B$43,0))</f>
+        <v>10.8</v>
       </c>
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A232" t="s">
-        <v>25</v>
-      </c>
-      <c r="F232" t="s">
-        <v>39</v>
-      </c>
-      <c r="J232" t="s">
-        <v>18</v>
-      </c>
-      <c r="K232" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F232,'feed pars'!B$6:B$43,0))</f>
-        <v>11.9</v>
-      </c>
+      <c r="A232" s="30" t="s">
+        <v>392</v>
+      </c>
+      <c r="B232" s="31"/>
+      <c r="C232" s="32"/>
+      <c r="D232" s="32"/>
+      <c r="E232" s="32"/>
+      <c r="F232" s="32"/>
+      <c r="G232" s="32"/>
+      <c r="H232" s="32"/>
+      <c r="I232" s="32"/>
+      <c r="J232" s="32"/>
+      <c r="K232" s="32"/>
+      <c r="L232" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="M232" s="32"/>
+      <c r="N232" s="32"/>
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>25</v>
       </c>
       <c r="F233" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="J233" t="s">
         <v>18</v>
       </c>
       <c r="K233" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F233,'feed pars'!B$6:B$43,0))</f>
-        <v>12.8</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.25">
@@ -6027,14 +6041,14 @@
         <v>25</v>
       </c>
       <c r="F234" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J234" t="s">
         <v>18</v>
       </c>
       <c r="K234" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F234,'feed pars'!B$6:B$43,0))</f>
-        <v>11.2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.25">
@@ -6042,14 +6056,14 @@
         <v>25</v>
       </c>
       <c r="F235" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J235" t="s">
         <v>18</v>
       </c>
       <c r="K235" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F235,'feed pars'!B$6:B$43,0))</f>
-        <v>10.7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.25">
@@ -6057,14 +6071,14 @@
         <v>25</v>
       </c>
       <c r="F236" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J236" t="s">
         <v>18</v>
       </c>
       <c r="K236" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F236,'feed pars'!B$6:B$43,0))</f>
-        <v>18</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.25">
@@ -6072,14 +6086,14 @@
         <v>25</v>
       </c>
       <c r="F237" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J237" t="s">
         <v>18</v>
       </c>
       <c r="K237" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F237,'feed pars'!B$6:B$43,0))</f>
-        <v>17.3</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="238" spans="1:14" x14ac:dyDescent="0.25">
@@ -6087,14 +6101,14 @@
         <v>25</v>
       </c>
       <c r="F238" t="s">
-        <v>314</v>
+        <v>41</v>
       </c>
       <c r="J238" t="s">
         <v>18</v>
       </c>
       <c r="K238" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F238,'feed pars'!B$6:B$43,0))</f>
-        <v>29.8</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="239" spans="1:14" x14ac:dyDescent="0.25">
@@ -6102,14 +6116,14 @@
         <v>25</v>
       </c>
       <c r="F239" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J239" t="s">
         <v>18</v>
       </c>
       <c r="K239" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F239,'feed pars'!B$6:B$43,0))</f>
-        <v>9.3000000000000007</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="240" spans="1:14" x14ac:dyDescent="0.25">
@@ -6117,14 +6131,14 @@
         <v>25</v>
       </c>
       <c r="F240" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="J240" t="s">
         <v>18</v>
       </c>
       <c r="K240" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F240,'feed pars'!B$6:B$43,0))</f>
-        <v>9.6999999999999993</v>
+        <v>18</v>
       </c>
     </row>
     <row r="241" spans="1:11" x14ac:dyDescent="0.25">
@@ -6132,14 +6146,14 @@
         <v>25</v>
       </c>
       <c r="F241" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="J241" t="s">
         <v>18</v>
       </c>
       <c r="K241" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F241,'feed pars'!B$6:B$43,0))</f>
-        <v>7.1</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.25">
@@ -6147,14 +6161,14 @@
         <v>25</v>
       </c>
       <c r="F242" t="s">
-        <v>46</v>
+        <v>314</v>
       </c>
       <c r="J242" t="s">
         <v>18</v>
       </c>
       <c r="K242" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F242,'feed pars'!B$6:B$43,0))</f>
-        <v>5.9</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.25">
@@ -6162,14 +6176,14 @@
         <v>25</v>
       </c>
       <c r="F243" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="J243" t="s">
         <v>18</v>
       </c>
       <c r="K243" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F243,'feed pars'!B$6:B$43,0))</f>
-        <v>5.4</v>
+        <v>9.3000000000000007</v>
       </c>
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.25">
@@ -6177,14 +6191,14 @@
         <v>25</v>
       </c>
       <c r="F244" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J244" t="s">
         <v>18</v>
       </c>
       <c r="K244" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F244,'feed pars'!B$6:B$43,0))</f>
-        <v>7.2</v>
+        <v>9.6999999999999993</v>
       </c>
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.25">
@@ -6192,14 +6206,14 @@
         <v>25</v>
       </c>
       <c r="F245" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="J245" t="s">
         <v>18</v>
       </c>
       <c r="K245" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F245,'feed pars'!B$6:B$43,0))</f>
-        <v>8.6999999999999993</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.25">
@@ -6207,14 +6221,14 @@
         <v>25</v>
       </c>
       <c r="F246" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="J246" t="s">
         <v>18</v>
       </c>
       <c r="K246" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F246,'feed pars'!B$6:B$43,0))</f>
-        <v>8.1</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.25">
@@ -6222,14 +6236,14 @@
         <v>25</v>
       </c>
       <c r="F247" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="J247" t="s">
         <v>18</v>
       </c>
       <c r="K247" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F247,'feed pars'!B$6:B$43,0))</f>
-        <v>8.1999999999999993</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.25">
@@ -6237,14 +6251,14 @@
         <v>25</v>
       </c>
       <c r="F248" t="s">
-        <v>313</v>
+        <v>48</v>
       </c>
       <c r="J248" t="s">
         <v>18</v>
       </c>
       <c r="K248" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F248,'feed pars'!B$6:B$43,0))</f>
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.25">
@@ -6252,7 +6266,7 @@
         <v>25</v>
       </c>
       <c r="F249" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J249" t="s">
         <v>18</v>
@@ -6267,14 +6281,14 @@
         <v>25</v>
       </c>
       <c r="F250" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J250" t="s">
         <v>18</v>
       </c>
       <c r="K250" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F250,'feed pars'!B$6:B$43,0))</f>
-        <v>6.9</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.25">
@@ -6282,14 +6296,14 @@
         <v>25</v>
       </c>
       <c r="F251" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="J251" t="s">
         <v>18</v>
       </c>
       <c r="K251" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F251,'feed pars'!B$6:B$43,0))</f>
-        <v>12.4</v>
+        <v>8.1999999999999993</v>
       </c>
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.25">
@@ -6297,14 +6311,14 @@
         <v>25</v>
       </c>
       <c r="F252" t="s">
-        <v>55</v>
+        <v>313</v>
       </c>
       <c r="J252" t="s">
         <v>18</v>
       </c>
       <c r="K252" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F252,'feed pars'!B$6:B$43,0))</f>
-        <v>12.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.25">
@@ -6312,14 +6326,14 @@
         <v>25</v>
       </c>
       <c r="F253" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="J253" t="s">
         <v>18</v>
       </c>
       <c r="K253" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F253,'feed pars'!B$6:B$43,0))</f>
-        <v>11.1</v>
+        <v>8.6999999999999993</v>
       </c>
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.25">
@@ -6327,13 +6341,73 @@
         <v>25</v>
       </c>
       <c r="F254" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="J254" t="s">
         <v>18</v>
       </c>
       <c r="K254" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F254,'feed pars'!B$6:B$43,0))</f>
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="255" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>25</v>
+      </c>
+      <c r="F255" t="s">
+        <v>54</v>
+      </c>
+      <c r="J255" t="s">
+        <v>18</v>
+      </c>
+      <c r="K255" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F255,'feed pars'!B$6:B$43,0))</f>
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="256" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>25</v>
+      </c>
+      <c r="F256" t="s">
+        <v>55</v>
+      </c>
+      <c r="J256" t="s">
+        <v>18</v>
+      </c>
+      <c r="K256" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F256,'feed pars'!B$6:B$43,0))</f>
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="257" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>25</v>
+      </c>
+      <c r="F257" t="s">
+        <v>56</v>
+      </c>
+      <c r="J257" t="s">
+        <v>18</v>
+      </c>
+      <c r="K257" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F257,'feed pars'!B$6:B$43,0))</f>
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>25</v>
+      </c>
+      <c r="F258" t="s">
+        <v>57</v>
+      </c>
+      <c r="J258" t="s">
+        <v>18</v>
+      </c>
+      <c r="K258" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F258,'feed pars'!B$6:B$43,0))</f>
         <v>10.8</v>
       </c>
     </row>

--- a/data/prod_parameters/FeedMgmt.xlsx
+++ b/data/prod_parameters/FeedMgmt.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1258" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1271" uniqueCount="415">
   <si>
     <t>f_feed</t>
   </si>
@@ -1283,13 +1283,16 @@
     <t>https://glw-feeds.co.uk/index.php/wheat-feed-2/</t>
   </si>
   <si>
-    <t>no solution if these are used…</t>
-  </si>
-  <si>
-    <t>probably some problem with animals</t>
-  </si>
-  <si>
-    <t>needing to be exactly 0 in some regions</t>
+    <t>Slow solving and inaccurate solution warning</t>
+  </si>
+  <si>
+    <t>if these are used. Potential solution: remove</t>
+  </si>
+  <si>
+    <t>crops and animals that cant be pressent in</t>
+  </si>
+  <si>
+    <t>a region from variables instead of using constraints.</t>
   </si>
 </sst>
 </file>
@@ -1783,7 +1786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O258"/>
+  <dimension ref="A1:O260"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="7" width="20.28515625" customWidth="1"/>
@@ -2514,8 +2517,11 @@
       <c r="H46" t="s">
         <v>37</v>
       </c>
+      <c r="J46" t="s">
+        <v>27</v>
+      </c>
       <c r="K46" s="3">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="L46" t="s">
         <v>28</v>
@@ -2531,8 +2537,11 @@
       <c r="H47" t="s">
         <v>37</v>
       </c>
+      <c r="J47" t="s">
+        <v>27</v>
+      </c>
       <c r="K47" s="3">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="L47" t="s">
         <v>28</v>
@@ -2548,8 +2557,11 @@
       <c r="H48" t="s">
         <v>17</v>
       </c>
+      <c r="J48" t="s">
+        <v>27</v>
+      </c>
       <c r="K48" s="3">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="L48" t="s">
         <v>28</v>
@@ -2565,192 +2577,180 @@
       <c r="H49" t="s">
         <v>17</v>
       </c>
+      <c r="J49" t="s">
+        <v>27</v>
+      </c>
       <c r="K49" s="3">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="L49" t="s">
         <v>28</v>
       </c>
+      <c r="M49" s="3" t="s">
+        <v>414</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
+        <v>25</v>
+      </c>
+      <c r="H50" t="s">
+        <v>38</v>
+      </c>
+      <c r="J50" t="s">
+        <v>27</v>
+      </c>
+      <c r="K50" s="3">
+        <v>40</v>
+      </c>
+      <c r="L50" t="s">
+        <v>28</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>389</v>
+      </c>
+      <c r="H51" t="s">
+        <v>38</v>
+      </c>
+      <c r="J51" t="s">
+        <v>27</v>
+      </c>
+      <c r="K51" s="3">
+        <v>40</v>
+      </c>
+      <c r="L51" t="s">
+        <v>28</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
-      <c r="K50" s="2"/>
-      <c r="L50" s="2"/>
-      <c r="M50" s="2"/>
-      <c r="N50" s="2"/>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J51" s="10" t="s">
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2"/>
+      <c r="L52" s="2"/>
+      <c r="M52" s="2"/>
+      <c r="N52" s="2"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J53" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="K51" s="10">
-        <v>0</v>
-      </c>
-      <c r="L51" s="10"/>
-      <c r="M51" s="10" t="s">
+      <c r="K53" s="10">
+        <v>0</v>
+      </c>
+      <c r="L53" s="10"/>
+      <c r="M53" s="10" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="I52" t="s">
-        <v>318</v>
-      </c>
-      <c r="J52" t="s">
-        <v>31</v>
-      </c>
-      <c r="K52" s="29">
-        <v>100</v>
-      </c>
-      <c r="L52" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="M52" s="10"/>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="I53" t="s">
-        <v>44</v>
-      </c>
-      <c r="J53" t="s">
-        <v>31</v>
-      </c>
-      <c r="K53" s="29">
-        <v>100</v>
-      </c>
-      <c r="L53" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="M53" s="10"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="I54" t="s">
-        <v>36</v>
+        <v>318</v>
       </c>
       <c r="J54" t="s">
         <v>31</v>
       </c>
       <c r="K54" s="29">
-        <v>61</v>
-      </c>
-      <c r="L54" t="s">
+        <v>100</v>
+      </c>
+      <c r="L54" s="29" t="s">
         <v>28</v>
       </c>
+      <c r="M54" s="10"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="H55" t="s">
-        <v>43</v>
+      <c r="I55" t="s">
+        <v>44</v>
       </c>
       <c r="J55" t="s">
         <v>31</v>
       </c>
-      <c r="K55" s="3">
+      <c r="K55" s="29">
         <v>100</v>
       </c>
-      <c r="L55" t="s">
+      <c r="L55" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="M55" s="3" t="s">
-        <v>304</v>
-      </c>
+      <c r="M55" s="10"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="H56" t="s">
-        <v>40</v>
+      <c r="I56" t="s">
+        <v>36</v>
       </c>
       <c r="J56" t="s">
         <v>31</v>
       </c>
-      <c r="K56" s="3">
-        <v>50</v>
+      <c r="K56" s="29">
+        <v>61</v>
       </c>
       <c r="L56" t="s">
         <v>28</v>
       </c>
-      <c r="M56" s="3" t="s">
-        <v>394</v>
-      </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="B57" s="1"/>
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="2"/>
-      <c r="I57" s="2"/>
-      <c r="J57" s="2"/>
-      <c r="K57" s="2"/>
-      <c r="L57" s="2"/>
-      <c r="M57" s="2"/>
-      <c r="N57" s="2"/>
+      <c r="H57" t="s">
+        <v>43</v>
+      </c>
+      <c r="J57" t="s">
+        <v>31</v>
+      </c>
+      <c r="K57" s="3">
+        <v>100</v>
+      </c>
+      <c r="L57" t="s">
+        <v>28</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>304</v>
+      </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>24</v>
-      </c>
-      <c r="B58" t="s">
-        <v>326</v>
-      </c>
-      <c r="E58" t="s">
-        <v>327</v>
-      </c>
-      <c r="G58" t="s">
-        <v>334</v>
-      </c>
       <c r="H58" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="J58" t="s">
-        <v>335</v>
+        <v>31</v>
       </c>
       <c r="K58" s="3">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="L58" t="s">
         <v>28</v>
       </c>
-      <c r="M58" s="3"/>
+      <c r="M58" s="3" t="s">
+        <v>394</v>
+      </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>24</v>
-      </c>
-      <c r="B59" t="s">
-        <v>326</v>
-      </c>
-      <c r="E59" t="s">
-        <v>328</v>
-      </c>
-      <c r="G59" t="s">
-        <v>334</v>
-      </c>
-      <c r="H59" t="s">
-        <v>33</v>
-      </c>
-      <c r="J59" t="s">
-        <v>335</v>
-      </c>
-      <c r="K59" s="3">
-        <v>5</v>
-      </c>
-      <c r="L59" t="s">
-        <v>28</v>
-      </c>
-      <c r="M59" s="3"/>
+      <c r="A59" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="2"/>
+      <c r="L59" s="2"/>
+      <c r="M59" s="2"/>
+      <c r="N59" s="2"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
@@ -2760,7 +2760,7 @@
         <v>326</v>
       </c>
       <c r="E60" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G60" t="s">
         <v>334</v>
@@ -2772,7 +2772,7 @@
         <v>335</v>
       </c>
       <c r="K60" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L60" t="s">
         <v>28</v>
@@ -2787,7 +2787,7 @@
         <v>326</v>
       </c>
       <c r="E61" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="G61" t="s">
         <v>334</v>
@@ -2799,7 +2799,7 @@
         <v>335</v>
       </c>
       <c r="K61" s="3">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="L61" t="s">
         <v>28</v>
@@ -2814,7 +2814,7 @@
         <v>326</v>
       </c>
       <c r="E62" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="G62" t="s">
         <v>334</v>
@@ -2826,7 +2826,7 @@
         <v>335</v>
       </c>
       <c r="K62" s="3">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L62" t="s">
         <v>28</v>
@@ -2841,7 +2841,7 @@
         <v>326</v>
       </c>
       <c r="E63" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G63" t="s">
         <v>334</v>
@@ -2853,7 +2853,7 @@
         <v>335</v>
       </c>
       <c r="K63" s="3">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L63" t="s">
         <v>28</v>
@@ -2865,10 +2865,10 @@
         <v>24</v>
       </c>
       <c r="B64" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="E64" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G64" t="s">
         <v>334</v>
@@ -2892,10 +2892,10 @@
         <v>24</v>
       </c>
       <c r="B65" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="E65" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G65" t="s">
         <v>334</v>
@@ -2907,7 +2907,7 @@
         <v>335</v>
       </c>
       <c r="K65" s="3">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L65" t="s">
         <v>28</v>
@@ -2922,7 +2922,7 @@
         <v>333</v>
       </c>
       <c r="E66" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G66" t="s">
         <v>334</v>
@@ -2934,7 +2934,7 @@
         <v>335</v>
       </c>
       <c r="K66" s="3">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L66" t="s">
         <v>28</v>
@@ -2949,7 +2949,7 @@
         <v>333</v>
       </c>
       <c r="E67" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="G67" t="s">
         <v>334</v>
@@ -2976,7 +2976,7 @@
         <v>333</v>
       </c>
       <c r="E68" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="G68" t="s">
         <v>334</v>
@@ -2988,7 +2988,7 @@
         <v>335</v>
       </c>
       <c r="K68" s="3">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L68" t="s">
         <v>28</v>
@@ -3003,7 +3003,7 @@
         <v>333</v>
       </c>
       <c r="E69" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G69" t="s">
         <v>334</v>
@@ -3024,7 +3024,13 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>395</v>
+        <v>24</v>
+      </c>
+      <c r="B70" t="s">
+        <v>333</v>
+      </c>
+      <c r="E70" t="s">
+        <v>331</v>
       </c>
       <c r="G70" t="s">
         <v>334</v>
@@ -3036,7 +3042,7 @@
         <v>335</v>
       </c>
       <c r="K70" s="3">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="L70" t="s">
         <v>28</v>
@@ -3044,150 +3050,152 @@
       <c r="M70" s="3"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K71" s="3"/>
+      <c r="A71" t="s">
+        <v>24</v>
+      </c>
+      <c r="B71" t="s">
+        <v>333</v>
+      </c>
+      <c r="E71" t="s">
+        <v>332</v>
+      </c>
+      <c r="G71" t="s">
+        <v>334</v>
+      </c>
+      <c r="H71" t="s">
+        <v>33</v>
+      </c>
+      <c r="J71" t="s">
+        <v>335</v>
+      </c>
+      <c r="K71" s="3">
+        <v>90</v>
+      </c>
+      <c r="L71" t="s">
+        <v>28</v>
+      </c>
       <c r="M71" s="3"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
+      <c r="A72" t="s">
+        <v>395</v>
+      </c>
+      <c r="G72" t="s">
+        <v>334</v>
+      </c>
+      <c r="H72" t="s">
+        <v>33</v>
+      </c>
+      <c r="J72" t="s">
+        <v>335</v>
+      </c>
+      <c r="K72" s="3">
+        <v>10</v>
+      </c>
+      <c r="L72" t="s">
+        <v>28</v>
+      </c>
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K73" s="3"/>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B72" s="1"/>
-      <c r="C72" s="1"/>
-      <c r="D72" s="1"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="2"/>
-      <c r="I72" s="2"/>
-      <c r="J72" s="2"/>
-      <c r="K72" s="2"/>
-      <c r="L72" s="2"/>
-      <c r="M72" s="2"/>
-      <c r="N72" s="2"/>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J73" s="10" t="s">
+      <c r="B74" s="1"/>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
+      <c r="I74" s="2"/>
+      <c r="J74" s="2"/>
+      <c r="K74" s="2"/>
+      <c r="L74" s="2"/>
+      <c r="M74" s="2"/>
+      <c r="N74" s="2"/>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J75" s="10" t="s">
         <v>396</v>
       </c>
-      <c r="K73" s="10">
-        <v>0</v>
-      </c>
-      <c r="L73" s="10" t="s">
+      <c r="K75" s="10">
+        <v>0</v>
+      </c>
+      <c r="L75" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="M73" s="10" t="s">
+      <c r="M75" s="10" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J74" s="10" t="s">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J76" s="10" t="s">
         <v>397</v>
       </c>
-      <c r="K74" s="10">
-        <v>0</v>
-      </c>
-      <c r="L74" s="10" t="s">
+      <c r="K76" s="10">
+        <v>0</v>
+      </c>
+      <c r="L76" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="M74" s="10" t="s">
+      <c r="M76" s="10" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
         <v>24</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B77" t="s">
         <v>326</v>
       </c>
-      <c r="E75" t="s">
+      <c r="E77" t="s">
         <v>327</v>
       </c>
-      <c r="F75" t="s">
+      <c r="F77" t="s">
         <v>310</v>
       </c>
-      <c r="J75" s="29" t="s">
+      <c r="J77" s="29" t="s">
         <v>396</v>
       </c>
-      <c r="K75" s="29">
+      <c r="K77" s="29">
         <f>(0.8*20+0.2*2)</f>
         <v>16.399999999999999</v>
       </c>
-      <c r="L75" s="29" t="s">
+      <c r="L77" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="M75" s="29" t="s">
+      <c r="M77" s="29" t="s">
         <v>402</v>
       </c>
-      <c r="N75" t="s">
+      <c r="N77" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
         <v>24</v>
       </c>
-      <c r="F76" t="s">
+      <c r="F78" t="s">
         <v>310</v>
       </c>
-      <c r="J76" s="29" t="s">
+      <c r="J78" s="29" t="s">
         <v>396</v>
       </c>
-      <c r="K76" s="29">
+      <c r="K78" s="29">
         <f>(0.6*20+0.4*2)</f>
         <v>12.8</v>
       </c>
-      <c r="L76" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="M76" s="29" t="s">
-        <v>403</v>
-      </c>
-      <c r="N76" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>401</v>
-      </c>
-      <c r="F77" t="s">
-        <v>310</v>
-      </c>
-      <c r="J77" s="29" t="s">
-        <v>396</v>
-      </c>
-      <c r="K77" s="29">
-        <v>2</v>
-      </c>
-      <c r="L77" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="M77" s="29" t="s">
-        <v>404</v>
-      </c>
-      <c r="N77" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>395</v>
-      </c>
-      <c r="F78" t="s">
-        <v>310</v>
-      </c>
-      <c r="J78" s="29" t="s">
-        <v>396</v>
-      </c>
-      <c r="K78" s="29">
-        <v>2</v>
-      </c>
       <c r="L78" s="29" t="s">
         <v>28</v>
       </c>
       <c r="M78" s="29" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="N78" t="s">
         <v>398</v>
@@ -3195,28 +3203,22 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>24</v>
-      </c>
-      <c r="B79" t="s">
-        <v>326</v>
-      </c>
-      <c r="E79" t="s">
-        <v>327</v>
+        <v>401</v>
       </c>
       <c r="F79" t="s">
         <v>310</v>
       </c>
       <c r="J79" s="29" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K79" s="29">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L79" s="29" t="s">
         <v>28</v>
       </c>
       <c r="M79" s="29" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="N79" t="s">
         <v>398</v>
@@ -3224,25 +3226,22 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>24</v>
-      </c>
-      <c r="E80" t="s">
-        <v>329</v>
+        <v>395</v>
       </c>
       <c r="F80" t="s">
         <v>310</v>
       </c>
       <c r="J80" s="29" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K80" s="29">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L80" s="29" t="s">
         <v>28</v>
       </c>
       <c r="M80" s="29" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="N80" t="s">
         <v>398</v>
@@ -3252,6 +3251,12 @@
       <c r="A81" t="s">
         <v>24</v>
       </c>
+      <c r="B81" t="s">
+        <v>326</v>
+      </c>
+      <c r="E81" t="s">
+        <v>327</v>
+      </c>
       <c r="F81" t="s">
         <v>310</v>
       </c>
@@ -3259,171 +3264,162 @@
         <v>397</v>
       </c>
       <c r="K81" s="29">
+        <v>5</v>
+      </c>
+      <c r="L81" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="M81" s="29" t="s">
+        <v>405</v>
+      </c>
+      <c r="N81" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>24</v>
+      </c>
+      <c r="E82" t="s">
+        <v>329</v>
+      </c>
+      <c r="F82" t="s">
+        <v>310</v>
+      </c>
+      <c r="J82" s="29" t="s">
+        <v>397</v>
+      </c>
+      <c r="K82" s="29">
+        <v>5</v>
+      </c>
+      <c r="L82" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="M82" s="29" t="s">
+        <v>405</v>
+      </c>
+      <c r="N82" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>24</v>
+      </c>
+      <c r="F83" t="s">
+        <v>310</v>
+      </c>
+      <c r="J83" s="29" t="s">
+        <v>397</v>
+      </c>
+      <c r="K83" s="29">
         <f>0.9*5+0.1*15</f>
         <v>6</v>
       </c>
-      <c r="L81" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="M81" s="29" t="s">
-        <v>406</v>
-      </c>
-      <c r="N81" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>401</v>
-      </c>
-      <c r="F82" t="s">
-        <v>310</v>
-      </c>
-      <c r="J82" s="29" t="s">
-        <v>397</v>
-      </c>
-      <c r="K82" s="29">
-        <v>15</v>
-      </c>
-      <c r="L82" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="M82" s="29"/>
-      <c r="N82" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>395</v>
-      </c>
-      <c r="F83" t="s">
-        <v>310</v>
-      </c>
-      <c r="J83" s="29" t="s">
-        <v>397</v>
-      </c>
-      <c r="K83" s="29">
-        <v>15</v>
-      </c>
       <c r="L83" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="M83" s="29"/>
+      <c r="M83" s="29" t="s">
+        <v>406</v>
+      </c>
       <c r="N83" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A84" s="33" t="str">
-        <f>A75</f>
+      <c r="A84" t="s">
+        <v>401</v>
+      </c>
+      <c r="F84" t="s">
+        <v>310</v>
+      </c>
+      <c r="J84" s="29" t="s">
+        <v>397</v>
+      </c>
+      <c r="K84" s="29">
+        <v>15</v>
+      </c>
+      <c r="L84" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="M84" s="29"/>
+      <c r="N84" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>395</v>
+      </c>
+      <c r="F85" t="s">
+        <v>310</v>
+      </c>
+      <c r="J85" s="29" t="s">
+        <v>397</v>
+      </c>
+      <c r="K85" s="29">
+        <v>15</v>
+      </c>
+      <c r="L85" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="M85" s="29"/>
+      <c r="N85" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A86" s="33" t="str">
+        <f>A77</f>
         <v>cattle</v>
       </c>
-      <c r="B84" s="33" t="str">
-        <f>B75</f>
+      <c r="B86" s="33" t="str">
+        <f>B77</f>
         <v>dairy</v>
       </c>
-      <c r="E84" s="33" t="str">
-        <f>E75</f>
+      <c r="E86" s="33" t="str">
+        <f>E77</f>
         <v>cows</v>
       </c>
-      <c r="F84" t="s">
+      <c r="F86" t="s">
         <v>311</v>
       </c>
-      <c r="J84" s="33" t="str">
-        <f>J75</f>
+      <c r="J86" s="33" t="str">
+        <f>J77</f>
         <v>storage_losses</v>
       </c>
-      <c r="K84" s="33">
-        <f>K75</f>
+      <c r="K86" s="33">
+        <f>K77</f>
         <v>16.399999999999999</v>
       </c>
-      <c r="L84" s="33" t="str">
-        <f>L75</f>
+      <c r="L86" s="33" t="str">
+        <f>L77</f>
         <v>%</v>
       </c>
-      <c r="M84" s="33" t="str">
-        <f>M75</f>
+      <c r="M86" s="33" t="str">
+        <f>M77</f>
         <v>80% in silo</v>
       </c>
-      <c r="N84" s="33" t="str">
-        <f>N75</f>
+      <c r="N86" s="33" t="str">
+        <f>N77</f>
         <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A85" s="33" t="str">
-        <f t="shared" ref="A85:A92" si="0">A76</f>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A87" s="33" t="str">
+        <f t="shared" ref="A87:A94" si="0">A78</f>
         <v>cattle</v>
       </c>
-      <c r="F85" t="s">
+      <c r="F87" t="s">
         <v>311</v>
       </c>
-      <c r="J85" s="33" t="str">
-        <f t="shared" ref="J85:N92" si="1">J76</f>
+      <c r="J87" s="33" t="str">
+        <f t="shared" ref="J87:N94" si="1">J78</f>
         <v>storage_losses</v>
       </c>
-      <c r="K85" s="33">
+      <c r="K87" s="33">
         <f t="shared" si="1"/>
         <v>12.8</v>
-      </c>
-      <c r="L85" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>%</v>
-      </c>
-      <c r="M85" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>60% in silo</v>
-      </c>
-      <c r="N85" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A86" s="33" t="str">
-        <f t="shared" si="0"/>
-        <v>sheep</v>
-      </c>
-      <c r="F86" t="s">
-        <v>311</v>
-      </c>
-      <c r="J86" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>storage_losses</v>
-      </c>
-      <c r="K86" s="33">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="L86" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>%</v>
-      </c>
-      <c r="M86" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>0% in silo</v>
-      </c>
-      <c r="N86" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A87" s="33" t="str">
-        <f t="shared" si="0"/>
-        <v>horses</v>
-      </c>
-      <c r="F87" t="s">
-        <v>311</v>
-      </c>
-      <c r="J87" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>storage_losses</v>
-      </c>
-      <c r="K87" s="33">
-        <f t="shared" si="1"/>
-        <v>2</v>
       </c>
       <c r="L87" s="33" t="str">
         <f t="shared" si="1"/>
@@ -3431,7 +3427,7 @@
       </c>
       <c r="M87" s="33" t="str">
         <f t="shared" si="1"/>
-        <v>0% in silo</v>
+        <v>60% in silo</v>
       </c>
       <c r="N87" s="33" t="str">
         <f t="shared" si="1"/>
@@ -3441,26 +3437,18 @@
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="33" t="str">
         <f t="shared" si="0"/>
-        <v>cattle</v>
-      </c>
-      <c r="B88" s="33" t="str">
-        <f>B79</f>
-        <v>dairy</v>
-      </c>
-      <c r="E88" s="33" t="str">
-        <f>E79</f>
-        <v>cows</v>
+        <v>sheep</v>
       </c>
       <c r="F88" t="s">
         <v>311</v>
       </c>
       <c r="J88" s="33" t="str">
         <f t="shared" si="1"/>
-        <v>feeding_losses</v>
+        <v>storage_losses</v>
       </c>
       <c r="K88" s="33">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L88" s="33" t="str">
         <f t="shared" si="1"/>
@@ -3468,7 +3456,7 @@
       </c>
       <c r="M88" s="33" t="str">
         <f t="shared" si="1"/>
-        <v>No feeding on pasture</v>
+        <v>0% in silo</v>
       </c>
       <c r="N88" s="33" t="str">
         <f t="shared" si="1"/>
@@ -3478,22 +3466,18 @@
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="33" t="str">
         <f t="shared" si="0"/>
-        <v>cattle</v>
-      </c>
-      <c r="E89" s="33" t="str">
-        <f>E80</f>
-        <v>bulls</v>
+        <v>horses</v>
       </c>
       <c r="F89" t="s">
         <v>311</v>
       </c>
       <c r="J89" s="33" t="str">
         <f t="shared" si="1"/>
-        <v>feeding_losses</v>
+        <v>storage_losses</v>
       </c>
       <c r="K89" s="33">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L89" s="33" t="str">
         <f t="shared" si="1"/>
@@ -3501,7 +3485,7 @@
       </c>
       <c r="M89" s="33" t="str">
         <f t="shared" si="1"/>
-        <v>No feeding on pasture</v>
+        <v>0% in silo</v>
       </c>
       <c r="N89" s="33" t="str">
         <f t="shared" si="1"/>
@@ -3513,6 +3497,14 @@
         <f t="shared" si="0"/>
         <v>cattle</v>
       </c>
+      <c r="B90" s="33" t="str">
+        <f>B81</f>
+        <v>dairy</v>
+      </c>
+      <c r="E90" s="33" t="str">
+        <f>E81</f>
+        <v>cows</v>
+      </c>
       <c r="F90" t="s">
         <v>311</v>
       </c>
@@ -3522,7 +3514,7 @@
       </c>
       <c r="K90" s="33">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L90" s="33" t="str">
         <f t="shared" si="1"/>
@@ -3530,7 +3522,7 @@
       </c>
       <c r="M90" s="33" t="str">
         <f t="shared" si="1"/>
-        <v>10% feeding on pasture</v>
+        <v>No feeding on pasture</v>
       </c>
       <c r="N90" s="33" t="str">
         <f t="shared" si="1"/>
@@ -3540,7 +3532,11 @@
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="33" t="str">
         <f t="shared" si="0"/>
-        <v>sheep</v>
+        <v>cattle</v>
+      </c>
+      <c r="E91" s="33" t="str">
+        <f>E82</f>
+        <v>bulls</v>
       </c>
       <c r="F91" t="s">
         <v>311</v>
@@ -3551,22 +3547,25 @@
       </c>
       <c r="K91" s="33">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="L91" s="33" t="str">
         <f t="shared" si="1"/>
         <v>%</v>
       </c>
-      <c r="M91" s="33"/>
+      <c r="M91" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>No feeding on pasture</v>
+      </c>
       <c r="N91" s="33" t="str">
-        <f t="shared" ref="N91:N92" si="2">N82</f>
+        <f t="shared" si="1"/>
         <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="33" t="str">
         <f t="shared" si="0"/>
-        <v>horses</v>
+        <v>cattle</v>
       </c>
       <c r="F92" t="s">
         <v>311</v>
@@ -3577,124 +3576,117 @@
       </c>
       <c r="K92" s="33">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="L92" s="33" t="str">
         <f t="shared" si="1"/>
         <v>%</v>
       </c>
-      <c r="M92" s="33"/>
+      <c r="M92" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>10% feeding on pasture</v>
+      </c>
       <c r="N92" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A93" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>sheep</v>
+      </c>
+      <c r="F93" t="s">
+        <v>311</v>
+      </c>
+      <c r="J93" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K93" s="33">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="L93" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>%</v>
+      </c>
+      <c r="M93" s="33"/>
+      <c r="N93" s="33" t="str">
+        <f t="shared" ref="N93:N94" si="2">N84</f>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A94" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>horses</v>
+      </c>
+      <c r="F94" t="s">
+        <v>311</v>
+      </c>
+      <c r="J94" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K94" s="33">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="L94" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>%</v>
+      </c>
+      <c r="M94" s="33"/>
+      <c r="N94" s="33" t="str">
         <f t="shared" si="2"/>
         <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A93" s="33"/>
-      <c r="B93" s="33"/>
-      <c r="E93" s="33"/>
-      <c r="F93" t="s">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A95" s="33"/>
+      <c r="B95" s="33"/>
+      <c r="E95" s="33"/>
+      <c r="F95" t="s">
         <v>312</v>
       </c>
-      <c r="J93" s="29" t="s">
+      <c r="J95" s="29" t="s">
         <v>396</v>
       </c>
-      <c r="K93" s="29">
+      <c r="K95" s="29">
         <v>5</v>
       </c>
-      <c r="L93" s="29" t="s">
+      <c r="L95" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="M93" s="29"/>
-      <c r="N93" t="s">
+      <c r="M95" s="29"/>
+      <c r="N95" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A94" s="33" t="str">
-        <f>A79</f>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A96" s="33" t="str">
+        <f>A81</f>
         <v>cattle</v>
       </c>
-      <c r="B94" s="33" t="str">
-        <f>B79</f>
+      <c r="B96" s="33" t="str">
+        <f>B81</f>
         <v>dairy</v>
       </c>
-      <c r="E94" s="33" t="str">
-        <f t="shared" ref="E94:E95" si="3">E79</f>
+      <c r="E96" s="33" t="str">
+        <f t="shared" ref="E96:E97" si="3">E81</f>
         <v>cows</v>
       </c>
-      <c r="F94" t="s">
+      <c r="F96" t="s">
         <v>312</v>
       </c>
-      <c r="J94" s="33" t="str">
-        <f t="shared" ref="J94:N98" si="4">J79</f>
+      <c r="J96" s="33" t="str">
+        <f t="shared" ref="J96:N100" si="4">J81</f>
         <v>feeding_losses</v>
       </c>
-      <c r="K94" s="33">
+      <c r="K96" s="33">
         <f t="shared" si="4"/>
         <v>5</v>
-      </c>
-      <c r="L94" s="33" t="str">
-        <f t="shared" si="4"/>
-        <v>%</v>
-      </c>
-      <c r="M94" s="33" t="str">
-        <f t="shared" si="4"/>
-        <v>No feeding on pasture</v>
-      </c>
-      <c r="N94" s="33" t="str">
-        <f t="shared" si="4"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A95" s="33" t="str">
-        <f t="shared" ref="A95:A98" si="5">A80</f>
-        <v>cattle</v>
-      </c>
-      <c r="E95" s="33" t="str">
-        <f t="shared" si="3"/>
-        <v>bulls</v>
-      </c>
-      <c r="F95" t="s">
-        <v>312</v>
-      </c>
-      <c r="J95" s="33" t="str">
-        <f t="shared" si="4"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="K95" s="33">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="L95" s="33" t="str">
-        <f t="shared" si="4"/>
-        <v>%</v>
-      </c>
-      <c r="M95" s="33" t="str">
-        <f t="shared" si="4"/>
-        <v>No feeding on pasture</v>
-      </c>
-      <c r="N95" s="33" t="str">
-        <f t="shared" si="4"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A96" s="33" t="str">
-        <f t="shared" si="5"/>
-        <v>cattle</v>
-      </c>
-      <c r="F96" t="s">
-        <v>312</v>
-      </c>
-      <c r="J96" s="33" t="str">
-        <f t="shared" si="4"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="K96" s="33">
-        <f t="shared" si="4"/>
-        <v>6</v>
       </c>
       <c r="L96" s="33" t="str">
         <f t="shared" si="4"/>
@@ -3702,7 +3694,7 @@
       </c>
       <c r="M96" s="33" t="str">
         <f t="shared" si="4"/>
-        <v>10% feeding on pasture</v>
+        <v>No feeding on pasture</v>
       </c>
       <c r="N96" s="33" t="str">
         <f t="shared" si="4"/>
@@ -3711,8 +3703,12 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="33" t="str">
-        <f t="shared" si="5"/>
-        <v>sheep</v>
+        <f t="shared" ref="A97:A100" si="5">A82</f>
+        <v>cattle</v>
+      </c>
+      <c r="E97" s="33" t="str">
+        <f t="shared" si="3"/>
+        <v>bulls</v>
       </c>
       <c r="F97" t="s">
         <v>312</v>
@@ -3723,13 +3719,16 @@
       </c>
       <c r="K97" s="33">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="L97" s="33" t="str">
         <f t="shared" si="4"/>
         <v>%</v>
       </c>
-      <c r="M97" s="33"/>
+      <c r="M97" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>No feeding on pasture</v>
+      </c>
       <c r="N97" s="33" t="str">
         <f t="shared" si="4"/>
         <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
@@ -3738,7 +3737,7 @@
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="33" t="str">
         <f t="shared" si="5"/>
-        <v>horses</v>
+        <v>cattle</v>
       </c>
       <c r="F98" t="s">
         <v>312</v>
@@ -3749,121 +3748,114 @@
       </c>
       <c r="K98" s="33">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="L98" s="33" t="str">
         <f t="shared" si="4"/>
         <v>%</v>
       </c>
-      <c r="M98" s="33"/>
+      <c r="M98" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>10% feeding on pasture</v>
+      </c>
       <c r="N98" s="33" t="str">
         <f t="shared" si="4"/>
         <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
       </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A99" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>sheep</v>
+      </c>
       <c r="F99" t="s">
-        <v>2</v>
-      </c>
-      <c r="J99" s="29" t="s">
-        <v>396</v>
-      </c>
-      <c r="K99" s="29">
-        <v>5</v>
-      </c>
-      <c r="L99" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="M99" s="29"/>
-      <c r="N99" t="s">
-        <v>398</v>
+        <v>312</v>
+      </c>
+      <c r="J99" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K99" s="33">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="L99" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>%</v>
+      </c>
+      <c r="M99" s="33"/>
+      <c r="N99" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
       </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" s="33" t="str">
-        <f>A79</f>
+        <f t="shared" si="5"/>
+        <v>horses</v>
+      </c>
+      <c r="F100" t="s">
+        <v>312</v>
+      </c>
+      <c r="J100" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K100" s="33">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="L100" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>%</v>
+      </c>
+      <c r="M100" s="33"/>
+      <c r="N100" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F101" t="s">
+        <v>2</v>
+      </c>
+      <c r="J101" s="29" t="s">
+        <v>396</v>
+      </c>
+      <c r="K101" s="29">
+        <v>5</v>
+      </c>
+      <c r="L101" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="M101" s="29"/>
+      <c r="N101" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A102" s="33" t="str">
+        <f>A81</f>
         <v>cattle</v>
       </c>
-      <c r="B100" s="33" t="str">
-        <f>B79</f>
+      <c r="B102" s="33" t="str">
+        <f>B81</f>
         <v>dairy</v>
       </c>
-      <c r="E100" s="33" t="str">
-        <f t="shared" ref="E100:E101" si="6">E79</f>
+      <c r="E102" s="33" t="str">
+        <f t="shared" ref="E102:E103" si="6">E81</f>
         <v>cows</v>
       </c>
-      <c r="F100" t="s">
+      <c r="F102" t="s">
         <v>2</v>
       </c>
-      <c r="J100" s="33" t="str">
-        <f t="shared" ref="J100:N104" si="7">J79</f>
+      <c r="J102" s="33" t="str">
+        <f t="shared" ref="J102:N106" si="7">J81</f>
         <v>feeding_losses</v>
       </c>
-      <c r="K100" s="33">
+      <c r="K102" s="33">
         <f t="shared" si="7"/>
         <v>5</v>
-      </c>
-      <c r="L100" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>%</v>
-      </c>
-      <c r="M100" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>No feeding on pasture</v>
-      </c>
-      <c r="N100" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A101" s="33" t="str">
-        <f t="shared" ref="A101:A104" si="8">A80</f>
-        <v>cattle</v>
-      </c>
-      <c r="E101" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>bulls</v>
-      </c>
-      <c r="F101" t="s">
-        <v>2</v>
-      </c>
-      <c r="J101" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="K101" s="33">
-        <f t="shared" si="7"/>
-        <v>5</v>
-      </c>
-      <c r="L101" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>%</v>
-      </c>
-      <c r="M101" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>No feeding on pasture</v>
-      </c>
-      <c r="N101" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A102" s="33" t="str">
-        <f t="shared" si="8"/>
-        <v>cattle</v>
-      </c>
-      <c r="F102" t="s">
-        <v>2</v>
-      </c>
-      <c r="J102" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="K102" s="33">
-        <f t="shared" si="7"/>
-        <v>6</v>
       </c>
       <c r="L102" s="33" t="str">
         <f t="shared" si="7"/>
@@ -3871,7 +3863,7 @@
       </c>
       <c r="M102" s="33" t="str">
         <f t="shared" si="7"/>
-        <v>10% feeding on pasture</v>
+        <v>No feeding on pasture</v>
       </c>
       <c r="N102" s="33" t="str">
         <f t="shared" si="7"/>
@@ -3880,8 +3872,12 @@
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" s="33" t="str">
-        <f t="shared" si="8"/>
-        <v>sheep</v>
+        <f t="shared" ref="A103:A106" si="8">A82</f>
+        <v>cattle</v>
+      </c>
+      <c r="E103" s="33" t="str">
+        <f t="shared" si="6"/>
+        <v>bulls</v>
       </c>
       <c r="F103" t="s">
         <v>2</v>
@@ -3892,22 +3888,25 @@
       </c>
       <c r="K103" s="33">
         <f t="shared" si="7"/>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="L103" s="33" t="str">
         <f t="shared" si="7"/>
         <v>%</v>
       </c>
-      <c r="M103" s="29"/>
+      <c r="M103" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>No feeding on pasture</v>
+      </c>
       <c r="N103" s="33" t="str">
-        <f t="shared" ref="N103:N104" si="9">N82</f>
+        <f t="shared" si="7"/>
         <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
       </c>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" s="33" t="str">
         <f t="shared" si="8"/>
-        <v>horses</v>
+        <v>cattle</v>
       </c>
       <c r="F104" t="s">
         <v>2</v>
@@ -3918,121 +3917,114 @@
       </c>
       <c r="K104" s="33">
         <f t="shared" si="7"/>
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="L104" s="33" t="str">
         <f t="shared" si="7"/>
         <v>%</v>
       </c>
-      <c r="M104" s="29"/>
+      <c r="M104" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>10% feeding on pasture</v>
+      </c>
       <c r="N104" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A105" s="33" t="str">
+        <f t="shared" si="8"/>
+        <v>sheep</v>
+      </c>
+      <c r="F105" t="s">
+        <v>2</v>
+      </c>
+      <c r="J105" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K105" s="33">
+        <f t="shared" si="7"/>
+        <v>15</v>
+      </c>
+      <c r="L105" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>%</v>
+      </c>
+      <c r="M105" s="29"/>
+      <c r="N105" s="33" t="str">
+        <f t="shared" ref="N105:N106" si="9">N84</f>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A106" s="33" t="str">
+        <f t="shared" si="8"/>
+        <v>horses</v>
+      </c>
+      <c r="F106" t="s">
+        <v>2</v>
+      </c>
+      <c r="J106" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K106" s="33">
+        <f t="shared" si="7"/>
+        <v>15</v>
+      </c>
+      <c r="L106" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>%</v>
+      </c>
+      <c r="M106" s="29"/>
+      <c r="N106" s="33" t="str">
         <f t="shared" si="9"/>
         <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F105" t="s">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F107" t="s">
         <v>12</v>
       </c>
-      <c r="J105" s="29" t="s">
+      <c r="J107" s="29" t="s">
         <v>396</v>
       </c>
-      <c r="K105" s="29">
+      <c r="K107" s="29">
         <v>5</v>
       </c>
-      <c r="L105" s="29" t="s">
+      <c r="L107" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="M105" s="29"/>
-      <c r="N105" t="s">
+      <c r="M107" s="29"/>
+      <c r="N107" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A106" s="33" t="str">
-        <f>A79</f>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A108" s="33" t="str">
+        <f>A81</f>
         <v>cattle</v>
       </c>
-      <c r="B106" s="33" t="str">
-        <f>B79</f>
+      <c r="B108" s="33" t="str">
+        <f>B81</f>
         <v>dairy</v>
       </c>
-      <c r="E106" s="33" t="str">
-        <f t="shared" ref="E106:E107" si="10">E79</f>
+      <c r="E108" s="33" t="str">
+        <f t="shared" ref="E108:E109" si="10">E81</f>
         <v>cows</v>
       </c>
-      <c r="F106" t="s">
+      <c r="F108" t="s">
         <v>12</v>
       </c>
-      <c r="J106" s="33" t="str">
-        <f t="shared" ref="J106:N110" si="11">J79</f>
+      <c r="J108" s="33" t="str">
+        <f t="shared" ref="J108:N112" si="11">J81</f>
         <v>feeding_losses</v>
       </c>
-      <c r="K106" s="33">
+      <c r="K108" s="33">
         <f t="shared" si="11"/>
         <v>5</v>
-      </c>
-      <c r="L106" s="33" t="str">
-        <f t="shared" si="11"/>
-        <v>%</v>
-      </c>
-      <c r="M106" s="33" t="str">
-        <f t="shared" si="11"/>
-        <v>No feeding on pasture</v>
-      </c>
-      <c r="N106" s="33" t="str">
-        <f t="shared" si="11"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A107" s="33" t="str">
-        <f t="shared" ref="A107:A110" si="12">A80</f>
-        <v>cattle</v>
-      </c>
-      <c r="E107" s="33" t="str">
-        <f t="shared" si="10"/>
-        <v>bulls</v>
-      </c>
-      <c r="F107" t="s">
-        <v>12</v>
-      </c>
-      <c r="J107" s="33" t="str">
-        <f t="shared" si="11"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="K107" s="33">
-        <f t="shared" si="11"/>
-        <v>5</v>
-      </c>
-      <c r="L107" s="33" t="str">
-        <f t="shared" si="11"/>
-        <v>%</v>
-      </c>
-      <c r="M107" s="33" t="str">
-        <f t="shared" si="11"/>
-        <v>No feeding on pasture</v>
-      </c>
-      <c r="N107" s="33" t="str">
-        <f t="shared" si="11"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A108" s="33" t="str">
-        <f t="shared" si="12"/>
-        <v>cattle</v>
-      </c>
-      <c r="F108" t="s">
-        <v>12</v>
-      </c>
-      <c r="J108" s="33" t="str">
-        <f t="shared" si="11"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="K108" s="33">
-        <f t="shared" si="11"/>
-        <v>6</v>
       </c>
       <c r="L108" s="33" t="str">
         <f t="shared" si="11"/>
@@ -4040,7 +4032,7 @@
       </c>
       <c r="M108" s="33" t="str">
         <f t="shared" si="11"/>
-        <v>10% feeding on pasture</v>
+        <v>No feeding on pasture</v>
       </c>
       <c r="N108" s="33" t="str">
         <f t="shared" si="11"/>
@@ -4049,8 +4041,12 @@
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109" s="33" t="str">
-        <f t="shared" si="12"/>
-        <v>sheep</v>
+        <f t="shared" ref="A109:A112" si="12">A82</f>
+        <v>cattle</v>
+      </c>
+      <c r="E109" s="33" t="str">
+        <f t="shared" si="10"/>
+        <v>bulls</v>
       </c>
       <c r="F109" t="s">
         <v>12</v>
@@ -4061,22 +4057,25 @@
       </c>
       <c r="K109" s="33">
         <f t="shared" si="11"/>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="L109" s="33" t="str">
         <f t="shared" si="11"/>
         <v>%</v>
       </c>
-      <c r="M109" s="29"/>
+      <c r="M109" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>No feeding on pasture</v>
+      </c>
       <c r="N109" s="33" t="str">
-        <f t="shared" ref="N109:N110" si="13">N82</f>
+        <f t="shared" si="11"/>
         <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
       </c>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110" s="33" t="str">
         <f t="shared" si="12"/>
-        <v>horses</v>
+        <v>cattle</v>
       </c>
       <c r="F110" t="s">
         <v>12</v>
@@ -4087,161 +4086,182 @@
       </c>
       <c r="K110" s="33">
         <f t="shared" si="11"/>
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="L110" s="33" t="str">
         <f t="shared" si="11"/>
         <v>%</v>
       </c>
-      <c r="M110" s="29"/>
+      <c r="M110" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>10% feeding on pasture</v>
+      </c>
       <c r="N110" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A111" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v>sheep</v>
+      </c>
+      <c r="F111" t="s">
+        <v>12</v>
+      </c>
+      <c r="J111" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K111" s="33">
+        <f t="shared" si="11"/>
+        <v>15</v>
+      </c>
+      <c r="L111" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>%</v>
+      </c>
+      <c r="M111" s="29"/>
+      <c r="N111" s="33" t="str">
+        <f t="shared" ref="N111:N112" si="13">N84</f>
+        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A112" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v>horses</v>
+      </c>
+      <c r="F112" t="s">
+        <v>12</v>
+      </c>
+      <c r="J112" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="K112" s="33">
+        <f t="shared" si="11"/>
+        <v>15</v>
+      </c>
+      <c r="L112" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>%</v>
+      </c>
+      <c r="M112" s="29"/>
+      <c r="N112" s="33" t="str">
         <f t="shared" si="13"/>
         <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A111" s="33"/>
-      <c r="F111" t="s">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A113" s="33"/>
+      <c r="F113" t="s">
         <v>33</v>
       </c>
-      <c r="J111" s="29" t="s">
+      <c r="J113" s="29" t="s">
         <v>396</v>
       </c>
-      <c r="K111" s="29">
-        <v>0</v>
-      </c>
-      <c r="L111" t="s">
+      <c r="K113" s="29">
+        <v>0</v>
+      </c>
+      <c r="L113" t="s">
         <v>28</v>
       </c>
-      <c r="M111" s="29" t="s">
+      <c r="M113" s="29" t="s">
         <v>408</v>
       </c>
-      <c r="N111" s="33"/>
-    </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
+      <c r="N113" s="33"/>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
         <v>24</v>
       </c>
-      <c r="F112" t="s">
+      <c r="F114" t="s">
         <v>33</v>
       </c>
-      <c r="J112" t="s">
+      <c r="J114" t="s">
         <v>397</v>
       </c>
-      <c r="K112" s="29">
+      <c r="K114" s="29">
         <f>100-55</f>
         <v>45</v>
       </c>
-      <c r="L112" t="s">
+      <c r="L114" t="s">
         <v>28</v>
       </c>
-      <c r="M112" s="29" t="s">
+      <c r="M114" s="29" t="s">
         <v>400</v>
       </c>
-      <c r="N112" t="s">
+      <c r="N114" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
         <v>395</v>
       </c>
-      <c r="F113" t="s">
+      <c r="F115" t="s">
         <v>33</v>
       </c>
-      <c r="J113" t="s">
+      <c r="J115" t="s">
         <v>397</v>
       </c>
-      <c r="K113" s="29">
+      <c r="K115" s="29">
         <f>100-50</f>
         <v>50</v>
       </c>
-      <c r="L113" t="s">
+      <c r="L115" t="s">
         <v>28</v>
       </c>
-      <c r="M113" s="29" t="s">
+      <c r="M115" s="29" t="s">
         <v>400</v>
       </c>
-      <c r="N113" t="s">
+      <c r="N115" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K114" s="3"/>
-      <c r="M114" s="29"/>
-    </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A115" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="K115" s="3"/>
-      <c r="M115" s="29"/>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.25">
       <c r="K116" s="3"/>
       <c r="M116" s="29"/>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A117" s="3" t="s">
+        <v>407</v>
+      </c>
       <c r="K117" s="3"/>
-      <c r="M117" s="3"/>
+      <c r="M117" s="29"/>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A118" s="1" t="s">
+      <c r="K118" s="3"/>
+      <c r="M118" s="29"/>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K119" s="3"/>
+      <c r="M119" s="3"/>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B118" s="1"/>
-      <c r="C118" s="1"/>
-      <c r="D118" s="1"/>
-      <c r="E118" s="2"/>
-      <c r="F118" s="2"/>
-      <c r="G118" s="2"/>
-      <c r="H118" s="2"/>
-      <c r="I118" s="2"/>
-      <c r="J118" s="2"/>
-      <c r="K118" s="2"/>
-      <c r="L118" s="2"/>
-      <c r="M118" s="2" t="s">
+      <c r="B120" s="1"/>
+      <c r="C120" s="1"/>
+      <c r="D120" s="1"/>
+      <c r="E120" s="2"/>
+      <c r="F120" s="2"/>
+      <c r="G120" s="2"/>
+      <c r="H120" s="2"/>
+      <c r="I120" s="2"/>
+      <c r="J120" s="2"/>
+      <c r="K120" s="2"/>
+      <c r="L120" s="2"/>
+      <c r="M120" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="N118" s="2"/>
-    </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F119" t="s">
-        <v>310</v>
-      </c>
-      <c r="J119" t="s">
-        <v>390</v>
-      </c>
-      <c r="K119" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F119,'feed pars'!B$6:B$43,0))</f>
-        <v>100</v>
-      </c>
-      <c r="L119" t="s">
-        <v>28</v>
-      </c>
-      <c r="M119" s="29" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F120" t="s">
-        <v>311</v>
-      </c>
-      <c r="J120" t="s">
-        <v>390</v>
-      </c>
-      <c r="K120" s="26">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F120,'feed pars'!B$6:B$43,0))</f>
-        <v>100</v>
-      </c>
-      <c r="L120" t="s">
-        <v>28</v>
-      </c>
-      <c r="M120" s="3"/>
+      <c r="N120" s="2"/>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F121" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="J121" t="s">
         <v>390</v>
@@ -4253,11 +4273,13 @@
       <c r="L121" t="s">
         <v>28</v>
       </c>
-      <c r="M121" s="3"/>
+      <c r="M121" s="29" t="s">
+        <v>393</v>
+      </c>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F122" t="s">
-        <v>2</v>
+        <v>311</v>
       </c>
       <c r="J122" t="s">
         <v>390</v>
@@ -4273,7 +4295,7 @@
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F123" t="s">
-        <v>12</v>
+        <v>312</v>
       </c>
       <c r="J123" t="s">
         <v>390</v>
@@ -4289,7 +4311,7 @@
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F124" t="s">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="J124" t="s">
         <v>390</v>
@@ -4305,14 +4327,14 @@
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F125" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J125" t="s">
         <v>390</v>
       </c>
       <c r="K125" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F125,'feed pars'!B$6:B$43,0))</f>
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="L125" t="s">
         <v>28</v>
@@ -4321,14 +4343,14 @@
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F126" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="J126" t="s">
         <v>390</v>
       </c>
       <c r="K126" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F126,'feed pars'!B$6:B$43,0))</f>
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="L126" t="s">
         <v>28</v>
@@ -4337,14 +4359,14 @@
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F127" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="J127" t="s">
         <v>390</v>
       </c>
       <c r="K127" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F127,'feed pars'!B$6:B$43,0))</f>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L127" t="s">
         <v>28</v>
@@ -4353,7 +4375,7 @@
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F128" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="J128" t="s">
         <v>390</v>
@@ -4369,14 +4391,14 @@
     </row>
     <row r="129" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F129" t="s">
-        <v>317</v>
+        <v>38</v>
       </c>
       <c r="J129" t="s">
         <v>390</v>
       </c>
       <c r="K129" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F129,'feed pars'!B$6:B$43,0))</f>
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L129" t="s">
         <v>28</v>
@@ -4385,14 +4407,14 @@
     </row>
     <row r="130" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F130" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J130" t="s">
         <v>390</v>
       </c>
       <c r="K130" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F130,'feed pars'!B$6:B$43,0))</f>
-        <v>67.5</v>
+        <v>87</v>
       </c>
       <c r="L130" t="s">
         <v>28</v>
@@ -4401,7 +4423,7 @@
     </row>
     <row r="131" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F131" t="s">
-        <v>41</v>
+        <v>317</v>
       </c>
       <c r="J131" t="s">
         <v>390</v>
@@ -4417,14 +4439,14 @@
     </row>
     <row r="132" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F132" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J132" t="s">
         <v>390</v>
       </c>
       <c r="K132" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F132,'feed pars'!B$6:B$43,0))</f>
-        <v>86.8</v>
+        <v>67.5</v>
       </c>
       <c r="L132" t="s">
         <v>28</v>
@@ -4433,14 +4455,14 @@
     </row>
     <row r="133" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F133" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J133" t="s">
         <v>390</v>
       </c>
       <c r="K133" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F133,'feed pars'!B$6:B$43,0))</f>
-        <v>92.5</v>
+        <v>87</v>
       </c>
       <c r="L133" t="s">
         <v>28</v>
@@ -4449,14 +4471,14 @@
     </row>
     <row r="134" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F134" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J134" t="s">
         <v>390</v>
       </c>
       <c r="K134" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F134,'feed pars'!B$6:B$43,0))</f>
-        <v>92</v>
+        <v>86.8</v>
       </c>
       <c r="L134" t="s">
         <v>28</v>
@@ -4465,14 +4487,14 @@
     </row>
     <row r="135" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F135" t="s">
-        <v>314</v>
+        <v>35</v>
       </c>
       <c r="J135" t="s">
         <v>390</v>
       </c>
       <c r="K135" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F135,'feed pars'!B$6:B$43,0))</f>
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="L135" t="s">
         <v>28</v>
@@ -4481,14 +4503,14 @@
     </row>
     <row r="136" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F136" t="s">
-        <v>305</v>
+        <v>43</v>
       </c>
       <c r="J136" t="s">
         <v>390</v>
       </c>
       <c r="K136" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F136,'feed pars'!B$6:B$43,0))</f>
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="L136" t="s">
         <v>28</v>
@@ -4497,14 +4519,14 @@
     </row>
     <row r="137" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F137" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="J137" t="s">
         <v>390</v>
       </c>
       <c r="K137" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F137,'feed pars'!B$6:B$43,0))</f>
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="L137" t="s">
         <v>28</v>
@@ -4513,14 +4535,14 @@
     </row>
     <row r="138" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F138" t="s">
-        <v>44</v>
+        <v>305</v>
       </c>
       <c r="J138" t="s">
         <v>390</v>
       </c>
       <c r="K138" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F138,'feed pars'!B$6:B$43,0))</f>
-        <v>87.5</v>
+        <v>85</v>
       </c>
       <c r="L138" t="s">
         <v>28</v>
@@ -4529,7 +4551,7 @@
     </row>
     <row r="139" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F139" t="s">
-        <v>45</v>
+        <v>318</v>
       </c>
       <c r="J139" t="s">
         <v>390</v>
@@ -4545,14 +4567,14 @@
     </row>
     <row r="140" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F140" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J140" t="s">
         <v>390</v>
       </c>
       <c r="K140" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F140,'feed pars'!B$6:B$43,0))</f>
-        <v>89.5</v>
+        <v>87.5</v>
       </c>
       <c r="L140" t="s">
         <v>28</v>
@@ -4561,14 +4583,14 @@
     </row>
     <row r="141" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F141" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J141" t="s">
         <v>390</v>
       </c>
       <c r="K141" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F141,'feed pars'!B$6:B$43,0))</f>
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="L141" t="s">
         <v>28</v>
@@ -4577,14 +4599,14 @@
     </row>
     <row r="142" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F142" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="J142" t="s">
         <v>390</v>
       </c>
       <c r="K142" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F142,'feed pars'!B$6:B$43,0))</f>
-        <v>91</v>
+        <v>89.5</v>
       </c>
       <c r="L142" t="s">
         <v>28</v>
@@ -4593,14 +4615,14 @@
     </row>
     <row r="143" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F143" t="s">
-        <v>319</v>
+        <v>46</v>
       </c>
       <c r="J143" t="s">
         <v>390</v>
       </c>
       <c r="K143" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F143,'feed pars'!B$6:B$43,0))</f>
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L143" t="s">
         <v>28</v>
@@ -4609,14 +4631,14 @@
     </row>
     <row r="144" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F144" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J144" t="s">
         <v>390</v>
       </c>
       <c r="K144" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F144,'feed pars'!B$6:B$43,0))</f>
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="L144" t="s">
         <v>28</v>
@@ -4625,14 +4647,14 @@
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F145" t="s">
-        <v>49</v>
+        <v>319</v>
       </c>
       <c r="J145" t="s">
         <v>390</v>
       </c>
       <c r="K145" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F145,'feed pars'!B$6:B$43,0))</f>
-        <v>88.5</v>
+        <v>90</v>
       </c>
       <c r="L145" t="s">
         <v>28</v>
@@ -4641,14 +4663,14 @@
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F146" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J146" t="s">
         <v>390</v>
       </c>
       <c r="K146" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F146,'feed pars'!B$6:B$43,0))</f>
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L146" t="s">
         <v>28</v>
@@ -4657,14 +4679,14 @@
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F147" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J147" t="s">
         <v>390</v>
       </c>
       <c r="K147" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F147,'feed pars'!B$6:B$43,0))</f>
-        <v>11</v>
+        <v>88.5</v>
       </c>
       <c r="L147" t="s">
         <v>28</v>
@@ -4673,7 +4695,7 @@
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F148" t="s">
-        <v>313</v>
+        <v>50</v>
       </c>
       <c r="J148" t="s">
         <v>390</v>
@@ -4689,14 +4711,14 @@
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F149" t="s">
-        <v>388</v>
+        <v>51</v>
       </c>
       <c r="J149" t="s">
         <v>390</v>
       </c>
       <c r="K149" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F149,'feed pars'!B$6:B$43,0))</f>
-        <v>87</v>
+        <v>11</v>
       </c>
       <c r="L149" t="s">
         <v>28</v>
@@ -4705,14 +4727,14 @@
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F150" t="s">
-        <v>52</v>
+        <v>313</v>
       </c>
       <c r="J150" t="s">
         <v>390</v>
       </c>
       <c r="K150" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F150,'feed pars'!B$6:B$43,0))</f>
-        <v>75.5</v>
+        <v>90</v>
       </c>
       <c r="L150" t="s">
         <v>28</v>
@@ -4721,14 +4743,14 @@
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F151" t="s">
-        <v>53</v>
+        <v>388</v>
       </c>
       <c r="J151" t="s">
         <v>390</v>
       </c>
       <c r="K151" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F151,'feed pars'!B$6:B$43,0))</f>
-        <v>89.5</v>
+        <v>87</v>
       </c>
       <c r="L151" t="s">
         <v>28</v>
@@ -4737,14 +4759,14 @@
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F152" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J152" t="s">
         <v>390</v>
       </c>
       <c r="K152" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F152,'feed pars'!B$6:B$43,0))</f>
-        <v>6.25</v>
+        <v>75.5</v>
       </c>
       <c r="L152" t="s">
         <v>28</v>
@@ -4753,14 +4775,14 @@
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F153" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J153" t="s">
         <v>390</v>
       </c>
       <c r="K153" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F153,'feed pars'!B$6:B$43,0))</f>
-        <v>97</v>
+        <v>89.5</v>
       </c>
       <c r="L153" t="s">
         <v>28</v>
@@ -4769,14 +4791,14 @@
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F154" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J154" t="s">
         <v>390</v>
       </c>
       <c r="K154" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F154,'feed pars'!B$6:B$43,0))</f>
-        <v>91</v>
+        <v>6.25</v>
       </c>
       <c r="L154" t="s">
         <v>28</v>
@@ -4785,14 +4807,14 @@
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F155" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J155" t="s">
         <v>390</v>
       </c>
       <c r="K155" s="26">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F155,'feed pars'!B$6:B$43,0))</f>
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="L155" t="s">
         <v>28</v>
@@ -4800,70 +4822,70 @@
       <c r="M155" s="3"/>
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A156" s="7" t="s">
+      <c r="F156" t="s">
+        <v>56</v>
+      </c>
+      <c r="J156" t="s">
+        <v>390</v>
+      </c>
+      <c r="K156" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F156,'feed pars'!B$6:B$43,0))</f>
+        <v>91</v>
+      </c>
+      <c r="L156" t="s">
+        <v>28</v>
+      </c>
+      <c r="M156" s="3"/>
+    </row>
+    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F157" t="s">
+        <v>57</v>
+      </c>
+      <c r="J157" t="s">
+        <v>390</v>
+      </c>
+      <c r="K157" s="26">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F157,'feed pars'!B$6:B$43,0))</f>
+        <v>92</v>
+      </c>
+      <c r="L157" t="s">
+        <v>28</v>
+      </c>
+      <c r="M157" s="3"/>
+    </row>
+    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A158" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B156" s="7"/>
-      <c r="C156" s="6"/>
-      <c r="D156" s="6"/>
-      <c r="E156" s="6"/>
-      <c r="F156" s="6"/>
-      <c r="G156" s="6"/>
-      <c r="H156" s="6"/>
-      <c r="I156" s="6"/>
-      <c r="J156" s="6"/>
-      <c r="K156" s="6"/>
-      <c r="L156" s="6" t="s">
+      <c r="B158" s="7"/>
+      <c r="C158" s="6"/>
+      <c r="D158" s="6"/>
+      <c r="E158" s="6"/>
+      <c r="F158" s="6"/>
+      <c r="G158" s="6"/>
+      <c r="H158" s="6"/>
+      <c r="I158" s="6"/>
+      <c r="J158" s="6"/>
+      <c r="K158" s="6"/>
+      <c r="L158" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="M156" s="6"/>
-      <c r="N156" s="6"/>
-    </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
-        <v>24</v>
-      </c>
-      <c r="F157" t="s">
-        <v>310</v>
-      </c>
-      <c r="J157" t="s">
-        <v>18</v>
-      </c>
-      <c r="K157" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F157,'feed pars'!B$6:B$43,0))</f>
-        <v>11.5</v>
-      </c>
-      <c r="M157" s="3"/>
-    </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
-        <v>24</v>
-      </c>
-      <c r="F158" t="s">
-        <v>311</v>
-      </c>
-      <c r="J158" t="s">
-        <v>18</v>
-      </c>
-      <c r="K158" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F158,'feed pars'!B$6:B$43,0))</f>
-        <v>10.4</v>
-      </c>
-      <c r="M158" s="3"/>
+      <c r="M158" s="6"/>
+      <c r="N158" s="6"/>
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>24</v>
       </c>
       <c r="F159" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="J159" t="s">
         <v>18</v>
       </c>
       <c r="K159" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F159,'feed pars'!B$6:B$43,0))</f>
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="M159" s="3"/>
     </row>
@@ -4872,22 +4894,23 @@
         <v>24</v>
       </c>
       <c r="F160" t="s">
-        <v>12</v>
+        <v>311</v>
       </c>
       <c r="J160" t="s">
         <v>18</v>
       </c>
       <c r="K160" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F160,'feed pars'!B$6:B$43,0))</f>
-        <v>11.3</v>
-      </c>
-    </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
+        <v>10.4</v>
+      </c>
+      <c r="M160" s="3"/>
+    </row>
+    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>24</v>
       </c>
       <c r="F161" t="s">
-        <v>33</v>
+        <v>312</v>
       </c>
       <c r="J161" t="s">
         <v>18</v>
@@ -4896,218 +4919,219 @@
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F161,'feed pars'!B$6:B$43,0))</f>
         <v>10</v>
       </c>
-    </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K162" s="3"/>
-    </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M161" s="3"/>
+    </row>
+    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>24</v>
+      </c>
+      <c r="F162" t="s">
+        <v>12</v>
+      </c>
+      <c r="J162" t="s">
+        <v>18</v>
+      </c>
+      <c r="K162" s="26">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F162,'feed pars'!B$6:B$43,0))</f>
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>24</v>
       </c>
       <c r="F163" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="J163" t="s">
         <v>18</v>
       </c>
       <c r="K163" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F163,'feed pars'!B$6:B$43,0))</f>
-        <v>14.1</v>
-      </c>
-    </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
-        <v>24</v>
-      </c>
-      <c r="F164" t="s">
-        <v>37</v>
-      </c>
-      <c r="J164" t="s">
-        <v>18</v>
-      </c>
-      <c r="K164" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F164,'feed pars'!B$6:B$43,0))</f>
-        <v>13.2</v>
-      </c>
-    </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K164" s="3"/>
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>24</v>
       </c>
       <c r="F165" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="J165" t="s">
         <v>18</v>
       </c>
       <c r="K165" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F165,'feed pars'!B$6:B$43,0))</f>
-        <v>11.7</v>
-      </c>
-    </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>24</v>
       </c>
       <c r="F166" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="J166" t="s">
         <v>18</v>
       </c>
       <c r="K166" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F166,'feed pars'!B$6:B$43,0))</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>24</v>
       </c>
       <c r="F167" t="s">
-        <v>317</v>
+        <v>38</v>
       </c>
       <c r="J167" t="s">
         <v>18</v>
       </c>
       <c r="K167" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F167,'feed pars'!B$6:B$43,0))</f>
-        <v>13.9</v>
-      </c>
-    </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>24</v>
       </c>
       <c r="F168" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J168" t="s">
         <v>18</v>
       </c>
       <c r="K168" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F168,'feed pars'!B$6:B$43,0))</f>
-        <v>12.8</v>
-      </c>
-    </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>24</v>
       </c>
       <c r="F169" t="s">
-        <v>41</v>
+        <v>317</v>
       </c>
       <c r="J169" t="s">
         <v>18</v>
       </c>
       <c r="K169" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F169,'feed pars'!B$6:B$43,0))</f>
-        <v>13.8</v>
-      </c>
-    </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>24</v>
       </c>
       <c r="F170" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J170" t="s">
         <v>18</v>
       </c>
       <c r="K170" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F170,'feed pars'!B$6:B$43,0))</f>
-        <v>13.3</v>
-      </c>
-    </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>24</v>
       </c>
       <c r="F171" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J171" t="s">
         <v>18</v>
       </c>
       <c r="K171" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F171,'feed pars'!B$6:B$43,0))</f>
-        <v>22.1</v>
-      </c>
-    </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>24</v>
       </c>
       <c r="F172" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J172" t="s">
         <v>18</v>
       </c>
       <c r="K172" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F172,'feed pars'!B$6:B$43,0))</f>
-        <v>20.100000000000001</v>
-      </c>
-    </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>24</v>
       </c>
       <c r="F173" t="s">
-        <v>305</v>
+        <v>35</v>
       </c>
       <c r="J173" t="s">
         <v>18</v>
       </c>
       <c r="K173" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F173,'feed pars'!B$6:B$43,0))</f>
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>24</v>
       </c>
       <c r="F174" t="s">
-        <v>314</v>
+        <v>43</v>
       </c>
       <c r="J174" t="s">
         <v>18</v>
       </c>
       <c r="K174" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F174,'feed pars'!B$6:B$43,0))</f>
-        <v>36.6</v>
-      </c>
-    </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
+        <v>20.100000000000001</v>
+      </c>
+    </row>
+    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>24</v>
       </c>
       <c r="F175" t="s">
-        <v>318</v>
+        <v>305</v>
       </c>
       <c r="J175" t="s">
         <v>18</v>
       </c>
       <c r="K175" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F175,'feed pars'!B$6:B$43,0))</f>
-        <v>16.399999999999999</v>
-      </c>
-    </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>24</v>
       </c>
       <c r="F176" t="s">
-        <v>44</v>
+        <v>314</v>
       </c>
       <c r="J176" t="s">
         <v>18</v>
       </c>
       <c r="K176" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F176,'feed pars'!B$6:B$43,0))</f>
-        <v>14.6</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.25">
@@ -5115,14 +5139,14 @@
         <v>24</v>
       </c>
       <c r="F177" t="s">
-        <v>36</v>
+        <v>318</v>
       </c>
       <c r="J177" t="s">
         <v>18</v>
       </c>
       <c r="K177" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F177,'feed pars'!B$6:B$43,0))</f>
-        <v>12.2</v>
+        <v>16.399999999999999</v>
       </c>
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.25">
@@ -5130,14 +5154,14 @@
         <v>24</v>
       </c>
       <c r="F178" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J178" t="s">
         <v>18</v>
       </c>
       <c r="K178" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F178,'feed pars'!B$6:B$43,0))</f>
-        <v>11.4</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.25">
@@ -5145,14 +5169,14 @@
         <v>24</v>
       </c>
       <c r="F179" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="J179" t="s">
         <v>18</v>
       </c>
       <c r="K179" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F179,'feed pars'!B$6:B$43,0))</f>
-        <v>13.4</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.25">
@@ -5160,14 +5184,14 @@
         <v>24</v>
       </c>
       <c r="F180" t="s">
-        <v>319</v>
+        <v>46</v>
       </c>
       <c r="J180" t="s">
         <v>18</v>
       </c>
       <c r="K180" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F180,'feed pars'!B$6:B$43,0))</f>
-        <v>8.5</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.25">
@@ -5175,14 +5199,14 @@
         <v>24</v>
       </c>
       <c r="F181" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J181" t="s">
         <v>18</v>
       </c>
       <c r="K181" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F181,'feed pars'!B$6:B$43,0))</f>
-        <v>11</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.25">
@@ -5190,14 +5214,14 @@
         <v>24</v>
       </c>
       <c r="F182" t="s">
-        <v>50</v>
+        <v>319</v>
       </c>
       <c r="J182" t="s">
         <v>18</v>
       </c>
       <c r="K182" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F182,'feed pars'!B$6:B$43,0))</f>
-        <v>13.3</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.25">
@@ -5205,14 +5229,14 @@
         <v>24</v>
       </c>
       <c r="F183" t="s">
-        <v>313</v>
+        <v>48</v>
       </c>
       <c r="J183" t="s">
         <v>18</v>
       </c>
       <c r="K183" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F183,'feed pars'!B$6:B$43,0))</f>
-        <v>11.6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.25">
@@ -5220,14 +5244,14 @@
         <v>24</v>
       </c>
       <c r="F184" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="J184" t="s">
         <v>18</v>
       </c>
       <c r="K184" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F184,'feed pars'!B$6:B$43,0))</f>
-        <v>12.4</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.25">
@@ -5235,14 +5259,14 @@
         <v>24</v>
       </c>
       <c r="F185" t="s">
-        <v>53</v>
+        <v>313</v>
       </c>
       <c r="J185" t="s">
         <v>18</v>
       </c>
       <c r="K185" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F185,'feed pars'!B$6:B$43,0))</f>
-        <v>12.3</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.25">
@@ -5250,14 +5274,14 @@
         <v>24</v>
       </c>
       <c r="F186" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J186" t="s">
         <v>18</v>
       </c>
       <c r="K186" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F186,'feed pars'!B$6:B$43,0))</f>
-        <v>13.6</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.25">
@@ -5265,14 +5289,14 @@
         <v>24</v>
       </c>
       <c r="F187" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="J187" t="s">
         <v>18</v>
       </c>
       <c r="K187" s="26">
         <f>INDEX('feed pars'!L$6:L$43,MATCH(F187,'feed pars'!B$6:B$43,0))</f>
-        <v>15.5</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.25">
@@ -5280,111 +5304,111 @@
         <v>24</v>
       </c>
       <c r="F188" t="s">
-        <v>324</v>
+        <v>54</v>
       </c>
       <c r="J188" t="s">
         <v>18</v>
       </c>
-      <c r="K188" s="3">
-        <v>0</v>
+      <c r="K188" s="26">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F188,'feed pars'!B$6:B$43,0))</f>
+        <v>13.6</v>
       </c>
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A189" s="7" t="s">
-        <v>409</v>
-      </c>
-      <c r="B189" s="7"/>
-      <c r="C189" s="6"/>
-      <c r="D189" s="6"/>
-      <c r="E189" s="6"/>
-      <c r="F189" s="6"/>
-      <c r="G189" s="6"/>
-      <c r="H189" s="6"/>
-      <c r="I189" s="6"/>
-      <c r="J189" s="6"/>
-      <c r="K189" s="6"/>
-      <c r="L189" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M189" s="6"/>
-      <c r="N189" s="6"/>
+      <c r="A189" t="s">
+        <v>24</v>
+      </c>
+      <c r="F189" t="s">
+        <v>56</v>
+      </c>
+      <c r="J189" t="s">
+        <v>18</v>
+      </c>
+      <c r="K189" s="26">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F189,'feed pars'!B$6:B$43,0))</f>
+        <v>15.5</v>
+      </c>
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>395</v>
+        <v>24</v>
       </c>
       <c r="F190" t="s">
-        <v>2</v>
+        <v>324</v>
       </c>
       <c r="J190" t="s">
         <v>18</v>
       </c>
-      <c r="K190" s="26">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F190,'feed pars'!B$6:B$43,0))</f>
+      <c r="K190" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A191" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="B191" s="7"/>
+      <c r="C191" s="6"/>
+      <c r="D191" s="6"/>
+      <c r="E191" s="6"/>
+      <c r="F191" s="6"/>
+      <c r="G191" s="6"/>
+      <c r="H191" s="6"/>
+      <c r="I191" s="6"/>
+      <c r="J191" s="6"/>
+      <c r="K191" s="6"/>
+      <c r="L191" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M191" s="6"/>
+      <c r="N191" s="6"/>
+    </row>
+    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>395</v>
+      </c>
+      <c r="F192" t="s">
+        <v>2</v>
+      </c>
+      <c r="J192" t="s">
+        <v>18</v>
+      </c>
+      <c r="K192" s="26">
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F192,'feed pars'!B$6:B$43,0))</f>
         <v>9.1</v>
       </c>
-    </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A191" t="s">
-        <v>395</v>
-      </c>
-      <c r="F191" t="s">
-        <v>33</v>
-      </c>
-      <c r="J191" t="s">
-        <v>18</v>
-      </c>
-      <c r="K191" s="34">
-        <f>K161</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K192" s="34"/>
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>395</v>
       </c>
       <c r="F193" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="J193" t="s">
         <v>18</v>
       </c>
       <c r="K193" s="34">
-        <f>K165</f>
-        <v>11.7</v>
+        <f>K163</f>
+        <v>10</v>
       </c>
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A194" t="s">
-        <v>395</v>
-      </c>
-      <c r="F194" t="s">
-        <v>37</v>
-      </c>
-      <c r="J194" t="s">
-        <v>18</v>
-      </c>
-      <c r="K194" s="34">
-        <f>K164</f>
-        <v>13.2</v>
-      </c>
+      <c r="K194" s="34"/>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>395</v>
       </c>
       <c r="F195" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="J195" t="s">
         <v>18</v>
       </c>
       <c r="K195" s="34">
-        <f>K163</f>
-        <v>14.1</v>
+        <f>K167</f>
+        <v>11.7</v>
       </c>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.25">
@@ -5392,13 +5416,13 @@
         <v>395</v>
       </c>
       <c r="F196" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="J196" t="s">
         <v>18</v>
       </c>
       <c r="K196" s="34">
-        <f t="shared" ref="K196:K202" si="14">K164</f>
+        <f>K166</f>
         <v>13.2</v>
       </c>
     </row>
@@ -5407,14 +5431,14 @@
         <v>395</v>
       </c>
       <c r="F197" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="J197" t="s">
         <v>18</v>
       </c>
       <c r="K197" s="34">
-        <f t="shared" si="14"/>
-        <v>11.7</v>
+        <f>K165</f>
+        <v>14.1</v>
       </c>
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.25">
@@ -5422,14 +5446,14 @@
         <v>395</v>
       </c>
       <c r="F198" t="s">
-        <v>314</v>
+        <v>49</v>
       </c>
       <c r="J198" t="s">
         <v>18</v>
       </c>
       <c r="K198" s="34">
-        <f t="shared" si="14"/>
-        <v>14</v>
+        <f t="shared" ref="K198:K204" si="14">K166</f>
+        <v>13.2</v>
       </c>
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.25">
@@ -5437,14 +5461,14 @@
         <v>395</v>
       </c>
       <c r="F199" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="J199" t="s">
         <v>18</v>
       </c>
       <c r="K199" s="34">
         <f t="shared" si="14"/>
-        <v>13.9</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.25">
@@ -5452,14 +5476,14 @@
         <v>395</v>
       </c>
       <c r="F200" t="s">
-        <v>52</v>
+        <v>314</v>
       </c>
       <c r="J200" t="s">
         <v>18</v>
       </c>
       <c r="K200" s="34">
         <f t="shared" si="14"/>
-        <v>12.8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.25">
@@ -5467,14 +5491,14 @@
         <v>395</v>
       </c>
       <c r="F201" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="J201" t="s">
         <v>18</v>
       </c>
       <c r="K201" s="34">
         <f t="shared" si="14"/>
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.25">
@@ -5482,92 +5506,86 @@
         <v>395</v>
       </c>
       <c r="F202" t="s">
-        <v>319</v>
+        <v>52</v>
       </c>
       <c r="J202" t="s">
         <v>18</v>
       </c>
       <c r="K202" s="34">
         <f t="shared" si="14"/>
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>395</v>
+      </c>
+      <c r="F203" t="s">
+        <v>56</v>
+      </c>
+      <c r="J203" t="s">
+        <v>18</v>
+      </c>
+      <c r="K203" s="34">
+        <f t="shared" si="14"/>
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>395</v>
+      </c>
+      <c r="F204" t="s">
+        <v>319</v>
+      </c>
+      <c r="J204" t="s">
+        <v>18</v>
+      </c>
+      <c r="K204" s="34">
+        <f t="shared" si="14"/>
         <v>13.3</v>
       </c>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K203" s="3"/>
-    </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A204" s="8" t="s">
+    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K205" s="3"/>
+    </row>
+    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A206" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B204" s="8"/>
-      <c r="C204" s="9"/>
-      <c r="D204" s="9"/>
-      <c r="E204" s="9"/>
-      <c r="F204" s="9"/>
-      <c r="G204" s="9"/>
-      <c r="H204" s="9"/>
-      <c r="I204" s="9"/>
-      <c r="J204" s="9"/>
-      <c r="K204" s="9"/>
-      <c r="L204" s="9"/>
-      <c r="M204" s="9"/>
-      <c r="N204" s="9"/>
-    </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A205" s="30" t="s">
+      <c r="B206" s="8"/>
+      <c r="C206" s="9"/>
+      <c r="D206" s="9"/>
+      <c r="E206" s="9"/>
+      <c r="F206" s="9"/>
+      <c r="G206" s="9"/>
+      <c r="H206" s="9"/>
+      <c r="I206" s="9"/>
+      <c r="J206" s="9"/>
+      <c r="K206" s="9"/>
+      <c r="L206" s="9"/>
+      <c r="M206" s="9"/>
+      <c r="N206" s="9"/>
+    </row>
+    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A207" s="30" t="s">
         <v>391</v>
       </c>
-      <c r="B205" s="31"/>
-      <c r="C205" s="32"/>
-      <c r="D205" s="32"/>
-      <c r="E205" s="32"/>
-      <c r="F205" s="32"/>
-      <c r="G205" s="32"/>
-      <c r="H205" s="32"/>
-      <c r="I205" s="32"/>
-      <c r="J205" s="32"/>
-      <c r="K205" s="32"/>
-      <c r="L205" s="32" t="s">
+      <c r="B207" s="31"/>
+      <c r="C207" s="32"/>
+      <c r="D207" s="32"/>
+      <c r="E207" s="32"/>
+      <c r="F207" s="32"/>
+      <c r="G207" s="32"/>
+      <c r="H207" s="32"/>
+      <c r="I207" s="32"/>
+      <c r="J207" s="32"/>
+      <c r="K207" s="32"/>
+      <c r="L207" s="32" t="s">
         <v>300</v>
       </c>
-      <c r="M205" s="32"/>
-      <c r="N205" s="32"/>
-    </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A206" t="s">
-        <v>25</v>
-      </c>
-      <c r="E206" t="s">
-        <v>299</v>
-      </c>
-      <c r="F206" t="s">
-        <v>17</v>
-      </c>
-      <c r="J206" t="s">
-        <v>18</v>
-      </c>
-      <c r="K206" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F206,'feed pars'!B$6:B$43,0))</f>
-        <v>12.3</v>
-      </c>
-    </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A207" t="s">
-        <v>25</v>
-      </c>
-      <c r="E207" t="s">
-        <v>299</v>
-      </c>
-      <c r="F207" t="s">
-        <v>37</v>
-      </c>
-      <c r="J207" t="s">
-        <v>18</v>
-      </c>
-      <c r="K207" s="26">
-        <f>INDEX('feed pars'!H$6:H$43,MATCH(F207,'feed pars'!B$6:B$43,0))</f>
-        <v>11.2</v>
-      </c>
+      <c r="M207" s="32"/>
+      <c r="N207" s="32"/>
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
@@ -5577,14 +5595,14 @@
         <v>299</v>
       </c>
       <c r="F208" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="J208" t="s">
         <v>18</v>
       </c>
       <c r="K208" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F208,'feed pars'!B$6:B$43,0))</f>
-        <v>9.4</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.25">
@@ -5595,14 +5613,14 @@
         <v>299</v>
       </c>
       <c r="F209" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="J209" t="s">
         <v>18</v>
       </c>
       <c r="K209" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F209,'feed pars'!B$6:B$43,0))</f>
-        <v>12</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
@@ -5613,14 +5631,14 @@
         <v>299</v>
       </c>
       <c r="F210" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J210" t="s">
         <v>18</v>
       </c>
       <c r="K210" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F210,'feed pars'!B$6:B$43,0))</f>
-        <v>13.2</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.25">
@@ -5631,14 +5649,14 @@
         <v>299</v>
       </c>
       <c r="F211" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J211" t="s">
         <v>18</v>
       </c>
       <c r="K211" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F211,'feed pars'!B$6:B$43,0))</f>
-        <v>11.5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.25">
@@ -5649,14 +5667,14 @@
         <v>299</v>
       </c>
       <c r="F212" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J212" t="s">
         <v>18</v>
       </c>
       <c r="K212" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F212,'feed pars'!B$6:B$43,0))</f>
-        <v>10.9</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.25">
@@ -5667,14 +5685,14 @@
         <v>299</v>
       </c>
       <c r="F213" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J213" t="s">
         <v>18</v>
       </c>
       <c r="K213" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F213,'feed pars'!B$6:B$43,0))</f>
-        <v>18.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.25">
@@ -5685,14 +5703,14 @@
         <v>299</v>
       </c>
       <c r="F214" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J214" t="s">
         <v>18</v>
       </c>
       <c r="K214" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F214,'feed pars'!B$6:B$43,0))</f>
-        <v>17.5</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.25">
@@ -5703,14 +5721,14 @@
         <v>299</v>
       </c>
       <c r="F215" t="s">
-        <v>314</v>
+        <v>35</v>
       </c>
       <c r="J215" t="s">
         <v>18</v>
       </c>
       <c r="K215" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F215,'feed pars'!B$6:B$43,0))</f>
-        <v>29.8</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.25">
@@ -5721,14 +5739,14 @@
         <v>299</v>
       </c>
       <c r="F216" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J216" t="s">
         <v>18</v>
       </c>
       <c r="K216" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F216,'feed pars'!B$6:B$43,0))</f>
-        <v>9.9</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.25">
@@ -5739,14 +5757,14 @@
         <v>299</v>
       </c>
       <c r="F217" t="s">
-        <v>45</v>
+        <v>314</v>
       </c>
       <c r="J217" t="s">
         <v>18</v>
       </c>
       <c r="K217" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F217,'feed pars'!B$6:B$43,0))</f>
-        <v>10.3</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.25">
@@ -5757,14 +5775,14 @@
         <v>299</v>
       </c>
       <c r="F218" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J218" t="s">
         <v>18</v>
       </c>
       <c r="K218" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F218,'feed pars'!B$6:B$43,0))</f>
-        <v>7.7</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.25">
@@ -5775,14 +5793,14 @@
         <v>299</v>
       </c>
       <c r="F219" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J219" t="s">
         <v>18</v>
       </c>
       <c r="K219" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F219,'feed pars'!B$6:B$43,0))</f>
-        <v>6.5</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.25">
@@ -5793,14 +5811,14 @@
         <v>299</v>
       </c>
       <c r="F220" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="J220" t="s">
         <v>18</v>
       </c>
       <c r="K220" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F220,'feed pars'!B$6:B$43,0))</f>
-        <v>6.2</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.25">
@@ -5811,14 +5829,14 @@
         <v>299</v>
       </c>
       <c r="F221" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J221" t="s">
         <v>18</v>
       </c>
       <c r="K221" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F221,'feed pars'!B$6:B$43,0))</f>
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.25">
@@ -5829,14 +5847,14 @@
         <v>299</v>
       </c>
       <c r="F222" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J222" t="s">
         <v>18</v>
       </c>
       <c r="K222" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F222,'feed pars'!B$6:B$43,0))</f>
-        <v>9.1999999999999993</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="223" spans="1:11" x14ac:dyDescent="0.25">
@@ -5847,14 +5865,14 @@
         <v>299</v>
       </c>
       <c r="F223" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J223" t="s">
         <v>18</v>
       </c>
       <c r="K223" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F223,'feed pars'!B$6:B$43,0))</f>
-        <v>8.6999999999999993</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.25">
@@ -5865,14 +5883,14 @@
         <v>299</v>
       </c>
       <c r="F224" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J224" t="s">
         <v>18</v>
       </c>
       <c r="K224" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F224,'feed pars'!B$6:B$43,0))</f>
-        <v>8.9</v>
+        <v>9.1999999999999993</v>
       </c>
     </row>
     <row r="225" spans="1:14" x14ac:dyDescent="0.25">
@@ -5883,14 +5901,14 @@
         <v>299</v>
       </c>
       <c r="F225" t="s">
-        <v>313</v>
+        <v>50</v>
       </c>
       <c r="J225" t="s">
         <v>18</v>
       </c>
       <c r="K225" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F225,'feed pars'!B$6:B$43,0))</f>
-        <v>7.0888888888888877</v>
+        <v>8.6999999999999993</v>
       </c>
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.25">
@@ -5901,14 +5919,14 @@
         <v>299</v>
       </c>
       <c r="F226" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J226" t="s">
         <v>18</v>
       </c>
       <c r="K226" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F226,'feed pars'!B$6:B$43,0))</f>
-        <v>9</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.25">
@@ -5919,14 +5937,14 @@
         <v>299</v>
       </c>
       <c r="F227" t="s">
-        <v>53</v>
+        <v>313</v>
       </c>
       <c r="J227" t="s">
         <v>18</v>
       </c>
       <c r="K227" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F227,'feed pars'!B$6:B$43,0))</f>
-        <v>8</v>
+        <v>7.0888888888888877</v>
       </c>
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.25">
@@ -5937,14 +5955,14 @@
         <v>299</v>
       </c>
       <c r="F228" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J228" t="s">
         <v>18</v>
       </c>
       <c r="K228" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F228,'feed pars'!B$6:B$43,0))</f>
-        <v>12.2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.25">
@@ -5955,14 +5973,14 @@
         <v>299</v>
       </c>
       <c r="F229" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J229" t="s">
         <v>18</v>
       </c>
       <c r="K229" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F229,'feed pars'!B$6:B$43,0))</f>
-        <v>12.2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.25">
@@ -5973,14 +5991,14 @@
         <v>299</v>
       </c>
       <c r="F230" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J230" t="s">
         <v>18</v>
       </c>
       <c r="K230" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F230,'feed pars'!B$6:B$43,0))</f>
-        <v>11.3</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.25">
@@ -5991,79 +6009,85 @@
         <v>299</v>
       </c>
       <c r="F231" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J231" t="s">
         <v>18</v>
       </c>
       <c r="K231" s="26">
         <f>INDEX('feed pars'!H$6:H$43,MATCH(F231,'feed pars'!B$6:B$43,0))</f>
-        <v>10.8</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A232" s="30" t="s">
-        <v>392</v>
-      </c>
-      <c r="B232" s="31"/>
-      <c r="C232" s="32"/>
-      <c r="D232" s="32"/>
-      <c r="E232" s="32"/>
-      <c r="F232" s="32"/>
-      <c r="G232" s="32"/>
-      <c r="H232" s="32"/>
-      <c r="I232" s="32"/>
-      <c r="J232" s="32"/>
-      <c r="K232" s="32"/>
-      <c r="L232" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="M232" s="32"/>
-      <c r="N232" s="32"/>
+      <c r="A232" t="s">
+        <v>25</v>
+      </c>
+      <c r="E232" t="s">
+        <v>299</v>
+      </c>
+      <c r="F232" t="s">
+        <v>56</v>
+      </c>
+      <c r="J232" t="s">
+        <v>18</v>
+      </c>
+      <c r="K232" s="26">
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F232,'feed pars'!B$6:B$43,0))</f>
+        <v>11.3</v>
+      </c>
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>25</v>
       </c>
+      <c r="E233" t="s">
+        <v>299</v>
+      </c>
       <c r="F233" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="J233" t="s">
         <v>18</v>
       </c>
       <c r="K233" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F233,'feed pars'!B$6:B$43,0))</f>
-        <v>12.1</v>
+        <f>INDEX('feed pars'!H$6:H$43,MATCH(F233,'feed pars'!B$6:B$43,0))</f>
+        <v>10.8</v>
       </c>
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A234" t="s">
-        <v>25</v>
-      </c>
-      <c r="F234" t="s">
-        <v>37</v>
-      </c>
-      <c r="J234" t="s">
-        <v>18</v>
-      </c>
-      <c r="K234" s="26">
-        <f>INDEX('feed pars'!G$6:G$43,MATCH(F234,'feed pars'!B$6:B$43,0))</f>
-        <v>11</v>
-      </c>
+      <c r="A234" s="30" t="s">
+        <v>392</v>
+      </c>
+      <c r="B234" s="31"/>
+      <c r="C234" s="32"/>
+      <c r="D234" s="32"/>
+      <c r="E234" s="32"/>
+      <c r="F234" s="32"/>
+      <c r="G234" s="32"/>
+      <c r="H234" s="32"/>
+      <c r="I234" s="32"/>
+      <c r="J234" s="32"/>
+      <c r="K234" s="32"/>
+      <c r="L234" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="M234" s="32"/>
+      <c r="N234" s="32"/>
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>25</v>
       </c>
       <c r="F235" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="J235" t="s">
         <v>18</v>
       </c>
       <c r="K235" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F235,'feed pars'!B$6:B$43,0))</f>
-        <v>9</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.25">
@@ -6071,14 +6095,14 @@
         <v>25</v>
       </c>
       <c r="F236" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="J236" t="s">
         <v>18</v>
       </c>
       <c r="K236" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F236,'feed pars'!B$6:B$43,0))</f>
-        <v>11.9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.25">
@@ -6086,14 +6110,14 @@
         <v>25</v>
       </c>
       <c r="F237" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J237" t="s">
         <v>18</v>
       </c>
       <c r="K237" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F237,'feed pars'!B$6:B$43,0))</f>
-        <v>12.8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="238" spans="1:14" x14ac:dyDescent="0.25">
@@ -6101,14 +6125,14 @@
         <v>25</v>
       </c>
       <c r="F238" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J238" t="s">
         <v>18</v>
       </c>
       <c r="K238" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F238,'feed pars'!B$6:B$43,0))</f>
-        <v>11.2</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="239" spans="1:14" x14ac:dyDescent="0.25">
@@ -6116,14 +6140,14 @@
         <v>25</v>
       </c>
       <c r="F239" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J239" t="s">
         <v>18</v>
       </c>
       <c r="K239" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F239,'feed pars'!B$6:B$43,0))</f>
-        <v>10.7</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="240" spans="1:14" x14ac:dyDescent="0.25">
@@ -6131,14 +6155,14 @@
         <v>25</v>
       </c>
       <c r="F240" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J240" t="s">
         <v>18</v>
       </c>
       <c r="K240" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F240,'feed pars'!B$6:B$43,0))</f>
-        <v>18</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="241" spans="1:11" x14ac:dyDescent="0.25">
@@ -6146,14 +6170,14 @@
         <v>25</v>
       </c>
       <c r="F241" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J241" t="s">
         <v>18</v>
       </c>
       <c r="K241" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F241,'feed pars'!B$6:B$43,0))</f>
-        <v>17.3</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.25">
@@ -6161,14 +6185,14 @@
         <v>25</v>
       </c>
       <c r="F242" t="s">
-        <v>314</v>
+        <v>35</v>
       </c>
       <c r="J242" t="s">
         <v>18</v>
       </c>
       <c r="K242" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F242,'feed pars'!B$6:B$43,0))</f>
-        <v>29.8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.25">
@@ -6176,14 +6200,14 @@
         <v>25</v>
       </c>
       <c r="F243" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J243" t="s">
         <v>18</v>
       </c>
       <c r="K243" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F243,'feed pars'!B$6:B$43,0))</f>
-        <v>9.3000000000000007</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.25">
@@ -6191,14 +6215,14 @@
         <v>25</v>
       </c>
       <c r="F244" t="s">
-        <v>45</v>
+        <v>314</v>
       </c>
       <c r="J244" t="s">
         <v>18</v>
       </c>
       <c r="K244" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F244,'feed pars'!B$6:B$43,0))</f>
-        <v>9.6999999999999993</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.25">
@@ -6206,14 +6230,14 @@
         <v>25</v>
       </c>
       <c r="F245" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J245" t="s">
         <v>18</v>
       </c>
       <c r="K245" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F245,'feed pars'!B$6:B$43,0))</f>
-        <v>7.1</v>
+        <v>9.3000000000000007</v>
       </c>
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.25">
@@ -6221,14 +6245,14 @@
         <v>25</v>
       </c>
       <c r="F246" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J246" t="s">
         <v>18</v>
       </c>
       <c r="K246" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F246,'feed pars'!B$6:B$43,0))</f>
-        <v>5.9</v>
+        <v>9.6999999999999993</v>
       </c>
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.25">
@@ -6236,14 +6260,14 @@
         <v>25</v>
       </c>
       <c r="F247" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="J247" t="s">
         <v>18</v>
       </c>
       <c r="K247" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F247,'feed pars'!B$6:B$43,0))</f>
-        <v>5.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.25">
@@ -6251,14 +6275,14 @@
         <v>25</v>
       </c>
       <c r="F248" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J248" t="s">
         <v>18</v>
       </c>
       <c r="K248" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F248,'feed pars'!B$6:B$43,0))</f>
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.25">
@@ -6266,14 +6290,14 @@
         <v>25</v>
       </c>
       <c r="F249" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J249" t="s">
         <v>18</v>
       </c>
       <c r="K249" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F249,'feed pars'!B$6:B$43,0))</f>
-        <v>8.6999999999999993</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.25">
@@ -6281,14 +6305,14 @@
         <v>25</v>
       </c>
       <c r="F250" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J250" t="s">
         <v>18</v>
       </c>
       <c r="K250" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F250,'feed pars'!B$6:B$43,0))</f>
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.25">
@@ -6296,14 +6320,14 @@
         <v>25</v>
       </c>
       <c r="F251" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J251" t="s">
         <v>18</v>
       </c>
       <c r="K251" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F251,'feed pars'!B$6:B$43,0))</f>
-        <v>8.1999999999999993</v>
+        <v>8.6999999999999993</v>
       </c>
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.25">
@@ -6311,14 +6335,14 @@
         <v>25</v>
       </c>
       <c r="F252" t="s">
-        <v>313</v>
+        <v>50</v>
       </c>
       <c r="J252" t="s">
         <v>18</v>
       </c>
       <c r="K252" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F252,'feed pars'!B$6:B$43,0))</f>
-        <v>6.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.25">
@@ -6326,14 +6350,14 @@
         <v>25</v>
       </c>
       <c r="F253" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J253" t="s">
         <v>18</v>
       </c>
       <c r="K253" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F253,'feed pars'!B$6:B$43,0))</f>
-        <v>8.6999999999999993</v>
+        <v>8.1999999999999993</v>
       </c>
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.25">
@@ -6341,14 +6365,14 @@
         <v>25</v>
       </c>
       <c r="F254" t="s">
-        <v>53</v>
+        <v>313</v>
       </c>
       <c r="J254" t="s">
         <v>18</v>
       </c>
       <c r="K254" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F254,'feed pars'!B$6:B$43,0))</f>
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.25">
@@ -6356,14 +6380,14 @@
         <v>25</v>
       </c>
       <c r="F255" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J255" t="s">
         <v>18</v>
       </c>
       <c r="K255" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F255,'feed pars'!B$6:B$43,0))</f>
-        <v>12.4</v>
+        <v>8.6999999999999993</v>
       </c>
     </row>
     <row r="256" spans="1:11" x14ac:dyDescent="0.25">
@@ -6371,14 +6395,14 @@
         <v>25</v>
       </c>
       <c r="F256" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J256" t="s">
         <v>18</v>
       </c>
       <c r="K256" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F256,'feed pars'!B$6:B$43,0))</f>
-        <v>12.4</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.25">
@@ -6386,14 +6410,14 @@
         <v>25</v>
       </c>
       <c r="F257" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J257" t="s">
         <v>18</v>
       </c>
       <c r="K257" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F257,'feed pars'!B$6:B$43,0))</f>
-        <v>11.1</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.25">
@@ -6401,13 +6425,43 @@
         <v>25</v>
       </c>
       <c r="F258" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J258" t="s">
         <v>18</v>
       </c>
       <c r="K258" s="26">
         <f>INDEX('feed pars'!G$6:G$43,MATCH(F258,'feed pars'!B$6:B$43,0))</f>
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="259" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>25</v>
+      </c>
+      <c r="F259" t="s">
+        <v>56</v>
+      </c>
+      <c r="J259" t="s">
+        <v>18</v>
+      </c>
+      <c r="K259" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F259,'feed pars'!B$6:B$43,0))</f>
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>25</v>
+      </c>
+      <c r="F260" t="s">
+        <v>57</v>
+      </c>
+      <c r="J260" t="s">
+        <v>18</v>
+      </c>
+      <c r="K260" s="26">
+        <f>INDEX('feed pars'!G$6:G$43,MATCH(F260,'feed pars'!B$6:B$43,0))</f>
         <v>10.8</v>
       </c>
     </row>

--- a/data/prod_parameters/FeedMgmt.xlsx
+++ b/data/prod_parameters/FeedMgmt.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1420" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1523" uniqueCount="506">
   <si>
     <t>f_feed</t>
   </si>
@@ -1550,6 +1550,24 @@
   <si>
     <t>Gross energy</t>
   </si>
+  <si>
+    <t>feed_par_fat</t>
+  </si>
+  <si>
+    <t>g/kg DM</t>
+  </si>
+  <si>
+    <t>Metabolizable energy</t>
+  </si>
+  <si>
+    <t>Net energy for sows</t>
+  </si>
+  <si>
+    <t>Net energy for growing pigs</t>
+  </si>
+  <si>
+    <t>Total fat</t>
+  </si>
 </sst>
 </file>
 
@@ -1558,7 +1576,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1669,6 +1687,13 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1880,7 +1905,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1955,7 +1980,6 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1990,6 +2014,11 @@
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2271,7 +2300,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O298"/>
+  <dimension ref="A1:O330"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="7" width="20.28515625" customWidth="1"/>
@@ -4737,22 +4766,22 @@
       <c r="N120" s="2"/>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A121" s="80" t="s">
+      <c r="A121" s="79" t="s">
         <v>496</v>
       </c>
-      <c r="B121" s="81"/>
-      <c r="C121" s="81"/>
-      <c r="D121" s="81"/>
-      <c r="E121" s="82"/>
-      <c r="F121" s="82"/>
-      <c r="G121" s="82"/>
-      <c r="H121" s="82"/>
-      <c r="I121" s="82"/>
-      <c r="J121" s="82"/>
-      <c r="K121" s="82"/>
-      <c r="L121" s="82"/>
-      <c r="M121" s="82"/>
-      <c r="N121" s="82"/>
+      <c r="B121" s="80"/>
+      <c r="C121" s="80"/>
+      <c r="D121" s="80"/>
+      <c r="E121" s="81"/>
+      <c r="F121" s="81"/>
+      <c r="G121" s="81"/>
+      <c r="H121" s="81"/>
+      <c r="I121" s="81"/>
+      <c r="J121" s="81"/>
+      <c r="K121" s="81"/>
+      <c r="L121" s="81"/>
+      <c r="M121" s="81"/>
+      <c r="N121" s="81"/>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F122" t="s">
@@ -4761,7 +4790,7 @@
       <c r="J122" t="s">
         <v>386</v>
       </c>
-      <c r="K122" s="25">
+      <c r="K122" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F122,'feed pars'!B$6:B$43,0))</f>
         <v>100</v>
       </c>
@@ -4779,7 +4808,7 @@
       <c r="J123" t="s">
         <v>386</v>
       </c>
-      <c r="K123" s="25">
+      <c r="K123" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F123,'feed pars'!B$6:B$43,0))</f>
         <v>100</v>
       </c>
@@ -4792,7 +4821,7 @@
       <c r="J124" t="s">
         <v>386</v>
       </c>
-      <c r="K124" s="25">
+      <c r="K124" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F124,'feed pars'!B$6:B$43,0))</f>
         <v>100</v>
       </c>
@@ -4805,7 +4834,7 @@
       <c r="J125" t="s">
         <v>386</v>
       </c>
-      <c r="K125" s="25">
+      <c r="K125" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F125,'feed pars'!B$6:B$43,0))</f>
         <v>100</v>
       </c>
@@ -4818,7 +4847,7 @@
       <c r="J126" t="s">
         <v>386</v>
       </c>
-      <c r="K126" s="25">
+      <c r="K126" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F126,'feed pars'!B$6:B$43,0))</f>
         <v>100</v>
       </c>
@@ -4831,7 +4860,7 @@
       <c r="J127" t="s">
         <v>386</v>
       </c>
-      <c r="K127" s="25">
+      <c r="K127" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F127,'feed pars'!B$6:B$43,0))</f>
         <v>100</v>
       </c>
@@ -4844,7 +4873,7 @@
       <c r="J128" t="s">
         <v>386</v>
       </c>
-      <c r="K128" s="25">
+      <c r="K128" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F128,'feed pars'!B$6:B$43,0))</f>
         <v>87</v>
       </c>
@@ -4857,7 +4886,7 @@
       <c r="J129" t="s">
         <v>386</v>
       </c>
-      <c r="K129" s="25">
+      <c r="K129" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F129,'feed pars'!B$6:B$43,0))</f>
         <v>87</v>
       </c>
@@ -4870,7 +4899,7 @@
       <c r="J130" t="s">
         <v>386</v>
       </c>
-      <c r="K130" s="25">
+      <c r="K130" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F130,'feed pars'!B$6:B$43,0))</f>
         <v>86</v>
       </c>
@@ -4883,7 +4912,7 @@
       <c r="J131" t="s">
         <v>386</v>
       </c>
-      <c r="K131" s="25">
+      <c r="K131" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F131,'feed pars'!B$6:B$43,0))</f>
         <v>87</v>
       </c>
@@ -4896,7 +4925,7 @@
       <c r="J132" t="s">
         <v>386</v>
       </c>
-      <c r="K132" s="25">
+      <c r="K132" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F132,'feed pars'!B$6:B$43,0))</f>
         <v>87</v>
       </c>
@@ -4909,7 +4938,7 @@
       <c r="J133" t="s">
         <v>386</v>
       </c>
-      <c r="K133" s="25">
+      <c r="K133" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F133,'feed pars'!B$6:B$43,0))</f>
         <v>67.5</v>
       </c>
@@ -4922,7 +4951,7 @@
       <c r="J134" t="s">
         <v>386</v>
       </c>
-      <c r="K134" s="25">
+      <c r="K134" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F134,'feed pars'!B$6:B$43,0))</f>
         <v>87</v>
       </c>
@@ -4935,7 +4964,7 @@
       <c r="J135" t="s">
         <v>386</v>
       </c>
-      <c r="K135" s="25">
+      <c r="K135" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F135,'feed pars'!B$6:B$43,0))</f>
         <v>86.8</v>
       </c>
@@ -4948,7 +4977,7 @@
       <c r="J136" t="s">
         <v>386</v>
       </c>
-      <c r="K136" s="25">
+      <c r="K136" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F136,'feed pars'!B$6:B$43,0))</f>
         <v>92.5</v>
       </c>
@@ -4961,7 +4990,7 @@
       <c r="J137" t="s">
         <v>386</v>
       </c>
-      <c r="K137" s="25">
+      <c r="K137" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F137,'feed pars'!B$6:B$43,0))</f>
         <v>92</v>
       </c>
@@ -4974,7 +5003,7 @@
       <c r="J138" t="s">
         <v>386</v>
       </c>
-      <c r="K138" s="25">
+      <c r="K138" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F138,'feed pars'!B$6:B$43,0))</f>
         <v>100</v>
       </c>
@@ -4987,7 +5016,7 @@
       <c r="J139" t="s">
         <v>386</v>
       </c>
-      <c r="K139" s="25">
+      <c r="K139" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F139,'feed pars'!B$6:B$43,0))</f>
         <v>85</v>
       </c>
@@ -5000,7 +5029,7 @@
       <c r="J140" t="s">
         <v>386</v>
       </c>
-      <c r="K140" s="25">
+      <c r="K140" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F140,'feed pars'!B$6:B$43,0))</f>
         <v>87</v>
       </c>
@@ -5013,7 +5042,7 @@
       <c r="J141" t="s">
         <v>386</v>
       </c>
-      <c r="K141" s="25">
+      <c r="K141" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F141,'feed pars'!B$6:B$43,0))</f>
         <v>87.5</v>
       </c>
@@ -5026,7 +5055,7 @@
       <c r="J142" t="s">
         <v>386</v>
       </c>
-      <c r="K142" s="25">
+      <c r="K142" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F142,'feed pars'!B$6:B$43,0))</f>
         <v>87</v>
       </c>
@@ -5039,7 +5068,7 @@
       <c r="J143" t="s">
         <v>386</v>
       </c>
-      <c r="K143" s="25">
+      <c r="K143" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F143,'feed pars'!B$6:B$43,0))</f>
         <v>89.5</v>
       </c>
@@ -5052,7 +5081,7 @@
       <c r="J144" t="s">
         <v>386</v>
       </c>
-      <c r="K144" s="25">
+      <c r="K144" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F144,'feed pars'!B$6:B$43,0))</f>
         <v>91</v>
       </c>
@@ -5065,7 +5094,7 @@
       <c r="J145" t="s">
         <v>386</v>
       </c>
-      <c r="K145" s="25">
+      <c r="K145" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F145,'feed pars'!B$6:B$43,0))</f>
         <v>91</v>
       </c>
@@ -5078,7 +5107,7 @@
       <c r="J146" t="s">
         <v>386</v>
       </c>
-      <c r="K146" s="25">
+      <c r="K146" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F146,'feed pars'!B$6:B$43,0))</f>
         <v>90</v>
       </c>
@@ -5091,7 +5120,7 @@
       <c r="J147" t="s">
         <v>386</v>
       </c>
-      <c r="K147" s="25">
+      <c r="K147" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F147,'feed pars'!B$6:B$43,0))</f>
         <v>87</v>
       </c>
@@ -5104,7 +5133,7 @@
       <c r="J148" t="s">
         <v>386</v>
       </c>
-      <c r="K148" s="25">
+      <c r="K148" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F148,'feed pars'!B$6:B$43,0))</f>
         <v>88.5</v>
       </c>
@@ -5117,7 +5146,7 @@
       <c r="J149" t="s">
         <v>386</v>
       </c>
-      <c r="K149" s="25">
+      <c r="K149" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F149,'feed pars'!B$6:B$43,0))</f>
         <v>90</v>
       </c>
@@ -5130,7 +5159,7 @@
       <c r="J150" t="s">
         <v>386</v>
       </c>
-      <c r="K150" s="25">
+      <c r="K150" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F150,'feed pars'!B$6:B$43,0))</f>
         <v>11</v>
       </c>
@@ -5143,7 +5172,7 @@
       <c r="J151" t="s">
         <v>386</v>
       </c>
-      <c r="K151" s="25">
+      <c r="K151" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F151,'feed pars'!B$6:B$43,0))</f>
         <v>90</v>
       </c>
@@ -5156,7 +5185,7 @@
       <c r="J152" t="s">
         <v>386</v>
       </c>
-      <c r="K152" s="25">
+      <c r="K152" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F152,'feed pars'!B$6:B$43,0))</f>
         <v>88.5</v>
       </c>
@@ -5169,7 +5198,7 @@
       <c r="J153" t="s">
         <v>386</v>
       </c>
-      <c r="K153" s="25">
+      <c r="K153" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F153,'feed pars'!B$6:B$43,0))</f>
         <v>75.5</v>
       </c>
@@ -5182,7 +5211,7 @@
       <c r="J154" t="s">
         <v>386</v>
       </c>
-      <c r="K154" s="25">
+      <c r="K154" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F154,'feed pars'!B$6:B$43,0))</f>
         <v>89.5</v>
       </c>
@@ -5195,7 +5224,7 @@
       <c r="J155" t="s">
         <v>386</v>
       </c>
-      <c r="K155" s="25">
+      <c r="K155" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F155,'feed pars'!B$6:B$43,0))</f>
         <v>6.25</v>
       </c>
@@ -5208,7 +5237,7 @@
       <c r="J156" t="s">
         <v>386</v>
       </c>
-      <c r="K156" s="25">
+      <c r="K156" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F156,'feed pars'!B$6:B$43,0))</f>
         <v>97</v>
       </c>
@@ -5221,7 +5250,7 @@
       <c r="J157" t="s">
         <v>386</v>
       </c>
-      <c r="K157" s="25">
+      <c r="K157" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F157,'feed pars'!B$6:B$43,0))</f>
         <v>91</v>
       </c>
@@ -5234,7 +5263,7 @@
       <c r="J158" t="s">
         <v>386</v>
       </c>
-      <c r="K158" s="25">
+      <c r="K158" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F158,'feed pars'!B$6:B$43,0))</f>
         <v>92</v>
       </c>
@@ -5242,605 +5271,613 @@
     </row>
     <row r="159" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F159" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="J159" t="s">
-        <v>498</v>
-      </c>
-      <c r="K159" s="25">
-        <f>INDEX('feed pars'!D$6:D$43,MATCH(F159,'feed pars'!B$6:B$43,0))</f>
-        <v>17.538700400000003</v>
-      </c>
-      <c r="L159" t="s">
-        <v>497</v>
-      </c>
-      <c r="M159" s="26" t="s">
-        <v>499</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="K159" s="86">
+        <v>100</v>
+      </c>
+      <c r="M159" s="3"/>
     </row>
     <row r="160" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F160" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J160" t="s">
         <v>498</v>
       </c>
       <c r="K160" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F160,'feed pars'!B$6:B$43,0))</f>
-        <v>17.371968000000003</v>
-      </c>
-      <c r="M160" s="3"/>
+        <v>17.316948400000001</v>
+      </c>
+      <c r="L160" t="s">
+        <v>497</v>
+      </c>
+      <c r="M160" s="26" t="s">
+        <v>499</v>
+      </c>
     </row>
     <row r="161" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F161" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J161" t="s">
         <v>498</v>
       </c>
       <c r="K161" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F161,'feed pars'!B$6:B$43,0))</f>
-        <v>16.819680000000002</v>
+        <v>17.150216</v>
       </c>
       <c r="M161" s="3"/>
     </row>
     <row r="162" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F162" t="s">
-        <v>2</v>
+        <v>308</v>
       </c>
       <c r="J162" t="s">
         <v>498</v>
       </c>
       <c r="K162" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F162,'feed pars'!B$6:B$43,0))</f>
-        <v>17.3820096</v>
+        <v>16.819680000000002</v>
       </c>
       <c r="M162" s="3"/>
     </row>
     <row r="163" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F163" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J163" t="s">
         <v>498</v>
       </c>
       <c r="K163" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F163,'feed pars'!B$6:B$43,0))</f>
-        <v>17.6573168</v>
+        <v>17.160257599999998</v>
       </c>
       <c r="M163" s="3"/>
     </row>
     <row r="164" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F164" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="J164" t="s">
         <v>498</v>
       </c>
       <c r="K164" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F164,'feed pars'!B$6:B$43,0))</f>
-        <v>17.633189066666667</v>
+        <v>17.6573168</v>
       </c>
       <c r="M164" s="3"/>
     </row>
     <row r="165" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F165" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="J165" t="s">
         <v>498</v>
       </c>
       <c r="K165" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F165,'feed pars'!B$6:B$43,0))</f>
-        <v>18.210023200000002</v>
+        <v>17.411437066666668</v>
       </c>
       <c r="M165" s="3"/>
     </row>
     <row r="166" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F166" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="J166" t="s">
         <v>498</v>
       </c>
       <c r="K166" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F166,'feed pars'!B$6:B$43,0))</f>
-        <v>18.089524000000001</v>
+        <v>18.210023200000002</v>
       </c>
       <c r="M166" s="3"/>
     </row>
     <row r="167" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F167" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J167" t="s">
         <v>498</v>
       </c>
       <c r="K167" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F167,'feed pars'!B$6:B$43,0))</f>
-        <v>18.6602216</v>
+        <v>18.089524000000001</v>
       </c>
       <c r="M167" s="3"/>
     </row>
     <row r="168" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F168" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J168" t="s">
         <v>498</v>
       </c>
       <c r="K168" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F168,'feed pars'!B$6:B$43,0))</f>
-        <v>18.2284328</v>
+        <v>18.6602216</v>
       </c>
       <c r="M168" s="3"/>
     </row>
     <row r="169" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F169" t="s">
-        <v>313</v>
+        <v>39</v>
       </c>
       <c r="J169" t="s">
         <v>498</v>
       </c>
       <c r="K169" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F169,'feed pars'!B$6:B$43,0))</f>
-        <v>17.924256</v>
+        <v>18.2284328</v>
       </c>
       <c r="M169" s="3"/>
     </row>
     <row r="170" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F170" t="s">
-        <v>40</v>
+        <v>313</v>
       </c>
       <c r="J170" t="s">
         <v>498</v>
       </c>
       <c r="K170" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F170,'feed pars'!B$6:B$43,0))</f>
-        <v>18.3899352</v>
+        <v>17.924256</v>
       </c>
       <c r="M170" s="3"/>
     </row>
     <row r="171" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F171" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J171" t="s">
         <v>498</v>
       </c>
       <c r="K171" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F171,'feed pars'!B$6:B$43,0))</f>
-        <v>18.478217600000001</v>
+        <v>18.3899352</v>
       </c>
       <c r="M171" s="3"/>
     </row>
     <row r="172" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F172" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J172" t="s">
         <v>498</v>
       </c>
       <c r="K172" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F172,'feed pars'!B$6:B$43,0))</f>
-        <v>18.737207199999997</v>
+        <v>18.478217600000001</v>
       </c>
       <c r="M172" s="3"/>
     </row>
     <row r="173" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F173" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="J173" t="s">
         <v>498</v>
       </c>
       <c r="K173" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F173,'feed pars'!B$6:B$43,0))</f>
-        <v>27.903096000000001</v>
+        <v>18.737207199999997</v>
       </c>
       <c r="M173" s="3"/>
     </row>
     <row r="174" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F174" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="J174" t="s">
         <v>498</v>
       </c>
       <c r="K174" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F174,'feed pars'!B$6:B$43,0))</f>
-        <v>26.501456000000001</v>
+        <v>27.903096000000001</v>
       </c>
       <c r="M174" s="3"/>
     </row>
     <row r="175" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F175" t="s">
-        <v>310</v>
+        <v>43</v>
       </c>
       <c r="J175" t="s">
         <v>498</v>
       </c>
       <c r="K175" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F175,'feed pars'!B$6:B$43,0))</f>
-        <v>39.329599999999999</v>
+        <v>26.501456000000001</v>
       </c>
       <c r="M175" s="3"/>
     </row>
     <row r="176" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F176" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="J176" t="s">
         <v>498</v>
       </c>
       <c r="K176" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F176,'feed pars'!B$6:B$43,0))</f>
-        <v>16.927627199999996</v>
+        <v>39.329599999999999</v>
       </c>
       <c r="M176" s="3"/>
     </row>
     <row r="177" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F177" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="J177" t="s">
         <v>498</v>
       </c>
       <c r="K177" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F177,'feed pars'!B$6:B$43,0))</f>
-        <v>22.965976000000001</v>
+        <v>16.927627199999996</v>
       </c>
       <c r="M177" s="3"/>
     </row>
     <row r="178" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F178" t="s">
-        <v>44</v>
+        <v>314</v>
       </c>
       <c r="J178" t="s">
         <v>498</v>
       </c>
       <c r="K178" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F178,'feed pars'!B$6:B$43,0))</f>
-        <v>19.589487999999999</v>
+        <v>22.965976000000001</v>
       </c>
       <c r="M178" s="3"/>
     </row>
     <row r="179" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F179" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J179" t="s">
         <v>498</v>
       </c>
       <c r="K179" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F179,'feed pars'!B$6:B$43,0))</f>
-        <v>20.560594400000003</v>
+        <v>19.589487999999999</v>
       </c>
       <c r="M179" s="3"/>
     </row>
     <row r="180" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F180" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="J180" t="s">
         <v>498</v>
       </c>
       <c r="K180" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F180,'feed pars'!B$6:B$43,0))</f>
-        <v>19.4920008</v>
+        <v>20.560594400000003</v>
       </c>
       <c r="M180" s="3"/>
     </row>
     <row r="181" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F181" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="J181" t="s">
         <v>498</v>
       </c>
       <c r="K181" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F181,'feed pars'!B$6:B$43,0))</f>
-        <v>19.083224000000001</v>
+        <v>19.4920008</v>
       </c>
       <c r="M181" s="3"/>
     </row>
     <row r="182" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F182" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J182" t="s">
         <v>498</v>
       </c>
       <c r="K182" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F182,'feed pars'!B$6:B$43,0))</f>
-        <v>19.581538399999999</v>
+        <v>19.083224000000001</v>
       </c>
       <c r="M182" s="3"/>
     </row>
     <row r="183" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F183" t="s">
-        <v>315</v>
+        <v>47</v>
       </c>
       <c r="J183" t="s">
         <v>498</v>
       </c>
       <c r="K183" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F183,'feed pars'!B$6:B$43,0))</f>
-        <v>16.971140800000001</v>
+        <v>19.581538399999999</v>
       </c>
       <c r="M183" s="3"/>
     </row>
     <row r="184" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F184" t="s">
-        <v>48</v>
+        <v>315</v>
       </c>
       <c r="J184" t="s">
         <v>498</v>
       </c>
       <c r="K184" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F184,'feed pars'!B$6:B$43,0))</f>
-        <v>18.194124000000002</v>
+        <v>16.971140800000001</v>
       </c>
       <c r="M184" s="3"/>
     </row>
     <row r="185" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F185" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J185" t="s">
         <v>498</v>
       </c>
       <c r="K185" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F185,'feed pars'!B$6:B$43,0))</f>
-        <v>17.8828344</v>
+        <v>18.194124000000002</v>
       </c>
       <c r="M185" s="3"/>
     </row>
     <row r="186" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F186" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J186" t="s">
         <v>498</v>
       </c>
       <c r="K186" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F186,'feed pars'!B$6:B$43,0))</f>
-        <v>19.659779199999999</v>
+        <v>17.8828344</v>
       </c>
       <c r="M186" s="3"/>
     </row>
     <row r="187" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F187" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J187" t="s">
         <v>498</v>
       </c>
       <c r="K187" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F187,'feed pars'!B$6:B$43,0))</f>
-        <v>18.8602168</v>
+        <v>19.659779199999999</v>
       </c>
       <c r="M187" s="3"/>
     </row>
     <row r="188" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F188" t="s">
-        <v>309</v>
+        <v>51</v>
       </c>
       <c r="J188" t="s">
         <v>498</v>
       </c>
       <c r="K188" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F188,'feed pars'!B$6:B$43,0))</f>
-        <v>19.848896</v>
+        <v>18.8602168</v>
       </c>
       <c r="M188" s="3"/>
     </row>
     <row r="189" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F189" t="s">
-        <v>384</v>
+        <v>309</v>
       </c>
       <c r="J189" t="s">
         <v>498</v>
       </c>
       <c r="K189" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F189,'feed pars'!B$6:B$43,0))</f>
-        <v>22.900705599999998</v>
+        <v>19.848896</v>
       </c>
       <c r="M189" s="3"/>
     </row>
     <row r="190" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F190" t="s">
-        <v>52</v>
+        <v>384</v>
       </c>
       <c r="J190" t="s">
         <v>498</v>
       </c>
       <c r="K190" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F190,'feed pars'!B$6:B$43,0))</f>
-        <v>16.1615368</v>
+        <v>22.900705599999998</v>
       </c>
       <c r="M190" s="3"/>
     </row>
     <row r="191" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F191" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J191" t="s">
         <v>498</v>
       </c>
       <c r="K191" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F191,'feed pars'!B$6:B$43,0))</f>
-        <v>17.334312000000001</v>
+        <v>16.1615368</v>
       </c>
       <c r="M191" s="3"/>
     </row>
     <row r="192" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F192" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J192" t="s">
         <v>498</v>
       </c>
       <c r="K192" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F192,'feed pars'!B$6:B$43,0))</f>
-        <v>16.464040000000001</v>
+        <v>17.334312000000001</v>
       </c>
       <c r="M192" s="3"/>
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F193" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J193" t="s">
         <v>498</v>
       </c>
       <c r="K193" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F193,'feed pars'!B$6:B$43,0))</f>
-        <v>16.975324799999999</v>
+        <v>16.464040000000001</v>
       </c>
       <c r="M193" s="3"/>
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F194" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J194" t="s">
         <v>498</v>
       </c>
       <c r="K194" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F194,'feed pars'!B$6:B$43,0))</f>
-        <v>23.055932000000002</v>
+        <v>16.975324799999999</v>
       </c>
       <c r="M194" s="3"/>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F195" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J195" t="s">
         <v>498</v>
       </c>
       <c r="K195" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F195,'feed pars'!B$6:B$43,0))</f>
+        <v>23.055932000000002</v>
+      </c>
+      <c r="M195" s="3"/>
+    </row>
+    <row r="196" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F196" t="s">
+        <v>57</v>
+      </c>
+      <c r="J196" t="s">
+        <v>498</v>
+      </c>
+      <c r="K196" s="25">
+        <f>INDEX('feed pars'!D$6:D$43,MATCH(F196,'feed pars'!B$6:B$43,0))</f>
         <v>22.254696000000003</v>
       </c>
-      <c r="M195" s="3"/>
-    </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A196" s="7" t="s">
+      <c r="M196" s="3"/>
+    </row>
+    <row r="197" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F197" t="s">
+        <v>320</v>
+      </c>
+      <c r="J197" t="s">
+        <v>498</v>
+      </c>
+      <c r="K197" s="85">
+        <v>0</v>
+      </c>
+      <c r="M197" s="3"/>
+    </row>
+    <row r="198" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A198" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B196" s="7"/>
-      <c r="C196" s="6"/>
-      <c r="D196" s="6"/>
-      <c r="E196" s="6"/>
-      <c r="F196" s="6"/>
-      <c r="G196" s="6"/>
-      <c r="H196" s="6"/>
-      <c r="I196" s="6"/>
-      <c r="J196" s="6"/>
-      <c r="K196" s="6"/>
-      <c r="L196" s="6"/>
-      <c r="M196" s="6"/>
-      <c r="N196" s="6"/>
-    </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A197" t="s">
-        <v>24</v>
-      </c>
-      <c r="F197" t="s">
-        <v>306</v>
-      </c>
-      <c r="J197" t="s">
-        <v>18</v>
-      </c>
-      <c r="K197" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F197,'feed pars'!B$6:B$43,0))</f>
-        <v>11.3</v>
-      </c>
-      <c r="L197" t="s">
-        <v>19</v>
-      </c>
-      <c r="M197" s="3"/>
-    </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A198" t="s">
-        <v>24</v>
-      </c>
-      <c r="F198" t="s">
-        <v>307</v>
-      </c>
-      <c r="J198" t="s">
-        <v>18</v>
-      </c>
-      <c r="K198" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F198,'feed pars'!B$6:B$43,0))</f>
-        <v>10.1</v>
-      </c>
-      <c r="M198" s="3"/>
+      <c r="B198" s="7"/>
+      <c r="C198" s="6"/>
+      <c r="D198" s="6"/>
+      <c r="E198" s="6"/>
+      <c r="F198" s="6"/>
+      <c r="G198" s="6"/>
+      <c r="H198" s="6"/>
+      <c r="I198" s="6"/>
+      <c r="J198" s="6"/>
+      <c r="K198" s="6"/>
+      <c r="L198" s="6"/>
+      <c r="M198" s="6"/>
+      <c r="N198" s="6"/>
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>24</v>
       </c>
       <c r="F199" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="J199" t="s">
         <v>18</v>
       </c>
       <c r="K199" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F199,'feed pars'!B$6:B$43,0))</f>
-        <v>9.25</v>
-      </c>
-      <c r="M199" s="3"/>
+        <v>11.3</v>
+      </c>
+      <c r="L199" t="s">
+        <v>19</v>
+      </c>
+      <c r="M199" s="26" t="s">
+        <v>502</v>
+      </c>
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>24</v>
       </c>
       <c r="F200" t="s">
-        <v>12</v>
+        <v>307</v>
       </c>
       <c r="J200" t="s">
         <v>18</v>
       </c>
       <c r="K200" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F200,'feed pars'!B$6:B$43,0))</f>
-        <v>11</v>
-      </c>
+        <v>10.1</v>
+      </c>
+      <c r="M200" s="3"/>
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>24</v>
       </c>
       <c r="F201" t="s">
-        <v>33</v>
+        <v>308</v>
       </c>
       <c r="J201" t="s">
         <v>18</v>
       </c>
       <c r="K201" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F201,'feed pars'!B$6:B$43,0))</f>
-        <v>9.9416666666666664</v>
-      </c>
+        <v>9.25</v>
+      </c>
+      <c r="M201" s="3"/>
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K202" s="3"/>
+      <c r="A202" t="s">
+        <v>24</v>
+      </c>
+      <c r="F202" t="s">
+        <v>12</v>
+      </c>
+      <c r="J202" t="s">
+        <v>18</v>
+      </c>
+      <c r="K202" s="25">
+        <f>INDEX('feed pars'!I$6:I$43,MATCH(F202,'feed pars'!B$6:B$43,0))</f>
+        <v>11</v>
+      </c>
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>24</v>
       </c>
       <c r="F203" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="J203" t="s">
         <v>18</v>
       </c>
       <c r="K203" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F203,'feed pars'!B$6:B$43,0))</f>
-        <v>14.1</v>
+        <v>9.9416666666666664</v>
       </c>
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.25">
@@ -5848,14 +5885,14 @@
         <v>24</v>
       </c>
       <c r="F204" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="J204" t="s">
         <v>18</v>
       </c>
       <c r="K204" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F204,'feed pars'!B$6:B$43,0))</f>
-        <v>13.2</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.25">
@@ -5863,14 +5900,14 @@
         <v>24</v>
       </c>
       <c r="F205" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J205" t="s">
         <v>18</v>
       </c>
       <c r="K205" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F205,'feed pars'!B$6:B$43,0))</f>
-        <v>11.7</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.25">
@@ -5878,14 +5915,14 @@
         <v>24</v>
       </c>
       <c r="F206" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J206" t="s">
         <v>18</v>
       </c>
       <c r="K206" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F206,'feed pars'!B$6:B$43,0))</f>
-        <v>14</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.25">
@@ -5893,14 +5930,14 @@
         <v>24</v>
       </c>
       <c r="F207" t="s">
-        <v>313</v>
+        <v>39</v>
       </c>
       <c r="J207" t="s">
         <v>18</v>
       </c>
       <c r="K207" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F207,'feed pars'!B$6:B$43,0))</f>
-        <v>13.9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.25">
@@ -5908,14 +5945,14 @@
         <v>24</v>
       </c>
       <c r="F208" t="s">
-        <v>40</v>
+        <v>313</v>
       </c>
       <c r="J208" t="s">
         <v>18</v>
       </c>
       <c r="K208" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F208,'feed pars'!B$6:B$43,0))</f>
-        <v>12.8</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.25">
@@ -5923,14 +5960,14 @@
         <v>24</v>
       </c>
       <c r="F209" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J209" t="s">
         <v>18</v>
       </c>
       <c r="K209" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F209,'feed pars'!B$6:B$43,0))</f>
-        <v>13.8</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
@@ -5938,14 +5975,14 @@
         <v>24</v>
       </c>
       <c r="F210" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J210" t="s">
         <v>18</v>
       </c>
       <c r="K210" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F210,'feed pars'!B$6:B$43,0))</f>
-        <v>13.3</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.25">
@@ -5953,14 +5990,14 @@
         <v>24</v>
       </c>
       <c r="F211" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="J211" t="s">
         <v>18</v>
       </c>
       <c r="K211" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F211,'feed pars'!B$6:B$43,0))</f>
-        <v>22.1</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.25">
@@ -5968,14 +6005,14 @@
         <v>24</v>
       </c>
       <c r="F212" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="J212" t="s">
         <v>18</v>
       </c>
       <c r="K212" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F212,'feed pars'!B$6:B$43,0))</f>
-        <v>20.100000000000001</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.25">
@@ -5983,14 +6020,14 @@
         <v>24</v>
       </c>
       <c r="F213" t="s">
-        <v>302</v>
+        <v>43</v>
       </c>
       <c r="J213" t="s">
         <v>18</v>
       </c>
       <c r="K213" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F213,'feed pars'!B$6:B$43,0))</f>
-        <v>6.6</v>
+        <v>20.100000000000001</v>
       </c>
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.25">
@@ -5998,14 +6035,14 @@
         <v>24</v>
       </c>
       <c r="F214" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="J214" t="s">
         <v>18</v>
       </c>
       <c r="K214" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F214,'feed pars'!B$6:B$43,0))</f>
-        <v>36.6</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.25">
@@ -6013,14 +6050,14 @@
         <v>24</v>
       </c>
       <c r="F215" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J215" t="s">
         <v>18</v>
       </c>
       <c r="K215" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F215,'feed pars'!B$6:B$43,0))</f>
-        <v>16.399999999999999</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.25">
@@ -6028,14 +6065,14 @@
         <v>24</v>
       </c>
       <c r="F216" t="s">
-        <v>44</v>
+        <v>314</v>
       </c>
       <c r="J216" t="s">
         <v>18</v>
       </c>
       <c r="K216" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F216,'feed pars'!B$6:B$43,0))</f>
-        <v>14.6</v>
+        <v>16.399999999999999</v>
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.25">
@@ -6043,14 +6080,14 @@
         <v>24</v>
       </c>
       <c r="F217" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J217" t="s">
         <v>18</v>
       </c>
       <c r="K217" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F217,'feed pars'!B$6:B$43,0))</f>
-        <v>12.2</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.25">
@@ -6058,14 +6095,14 @@
         <v>24</v>
       </c>
       <c r="F218" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="J218" t="s">
         <v>18</v>
       </c>
       <c r="K218" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F218,'feed pars'!B$6:B$43,0))</f>
-        <v>11.4</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.25">
@@ -6073,14 +6110,14 @@
         <v>24</v>
       </c>
       <c r="F219" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J219" t="s">
         <v>18</v>
       </c>
       <c r="K219" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F219,'feed pars'!B$6:B$43,0))</f>
-        <v>13.4</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.25">
@@ -6088,14 +6125,14 @@
         <v>24</v>
       </c>
       <c r="F220" t="s">
-        <v>315</v>
+        <v>47</v>
       </c>
       <c r="J220" t="s">
         <v>18</v>
       </c>
       <c r="K220" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F220,'feed pars'!B$6:B$43,0))</f>
-        <v>8.5</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.25">
@@ -6103,14 +6140,14 @@
         <v>24</v>
       </c>
       <c r="F221" t="s">
-        <v>48</v>
+        <v>315</v>
       </c>
       <c r="J221" t="s">
         <v>18</v>
       </c>
       <c r="K221" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F221,'feed pars'!B$6:B$43,0))</f>
-        <v>11</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.25">
@@ -6118,14 +6155,14 @@
         <v>24</v>
       </c>
       <c r="F222" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J222" t="s">
         <v>18</v>
       </c>
       <c r="K222" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F222,'feed pars'!B$6:B$43,0))</f>
-        <v>13.3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="223" spans="1:11" x14ac:dyDescent="0.25">
@@ -6133,14 +6170,14 @@
         <v>24</v>
       </c>
       <c r="F223" t="s">
-        <v>309</v>
+        <v>50</v>
       </c>
       <c r="J223" t="s">
         <v>18</v>
       </c>
       <c r="K223" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F223,'feed pars'!B$6:B$43,0))</f>
-        <v>11.6</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.25">
@@ -6148,1195 +6185,1693 @@
         <v>24</v>
       </c>
       <c r="F224" t="s">
-        <v>52</v>
+        <v>309</v>
       </c>
       <c r="J224" t="s">
         <v>18</v>
       </c>
       <c r="K224" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F224,'feed pars'!B$6:B$43,0))</f>
-        <v>12.4</v>
-      </c>
-    </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.25">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>24</v>
       </c>
       <c r="F225" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J225" t="s">
         <v>18</v>
       </c>
       <c r="K225" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F225,'feed pars'!B$6:B$43,0))</f>
-        <v>12.3</v>
-      </c>
-    </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.25">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>24</v>
       </c>
       <c r="F226" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J226" t="s">
         <v>18</v>
       </c>
       <c r="K226" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F226,'feed pars'!B$6:B$43,0))</f>
-        <v>13.6</v>
-      </c>
-    </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.25">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>24</v>
       </c>
       <c r="F227" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J227" t="s">
         <v>18</v>
       </c>
       <c r="K227" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F227,'feed pars'!B$6:B$43,0))</f>
-        <v>15.5</v>
-      </c>
-    </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.25">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>24</v>
       </c>
       <c r="F228" t="s">
-        <v>320</v>
+        <v>56</v>
       </c>
       <c r="J228" t="s">
         <v>18</v>
       </c>
-      <c r="K228" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A229" s="7" t="s">
-        <v>405</v>
-      </c>
-      <c r="B229" s="7"/>
-      <c r="C229" s="6"/>
-      <c r="D229" s="6"/>
-      <c r="E229" s="6"/>
-      <c r="F229" s="6"/>
-      <c r="G229" s="6"/>
-      <c r="H229" s="6"/>
-      <c r="I229" s="6"/>
-      <c r="J229" s="6"/>
-      <c r="K229" s="6"/>
-      <c r="L229" s="6"/>
-      <c r="M229" s="6"/>
-      <c r="N229" s="6"/>
-    </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K228" s="25">
+        <f>INDEX('feed pars'!I$6:I$43,MATCH(F228,'feed pars'!B$6:B$43,0))</f>
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>24</v>
+      </c>
+      <c r="F229" t="s">
+        <v>320</v>
+      </c>
+      <c r="J229" t="s">
+        <v>18</v>
+      </c>
+      <c r="K229" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>391</v>
+        <v>24</v>
       </c>
       <c r="F230" t="s">
-        <v>2</v>
+        <v>306</v>
       </c>
       <c r="J230" t="s">
-        <v>18</v>
-      </c>
-      <c r="K230" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F230,'feed pars'!B$6:B$43,0))</f>
-        <v>9.1</v>
+        <v>500</v>
+      </c>
+      <c r="K230" s="82">
+        <f>INDEX('feed pars'!K$6:K$43,MATCH(F230,'feed pars'!B$6:B$43,0))</f>
+        <v>20</v>
       </c>
       <c r="L230" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.25">
+        <v>501</v>
+      </c>
+      <c r="M230" s="26" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>391</v>
+        <v>24</v>
       </c>
       <c r="F231" t="s">
+        <v>307</v>
+      </c>
+      <c r="J231" t="s">
+        <v>500</v>
+      </c>
+      <c r="K231" s="82">
+        <f>INDEX('feed pars'!K$6:K$43,MATCH(F231,'feed pars'!B$6:B$43,0))</f>
+        <v>20</v>
+      </c>
+      <c r="M231" s="3"/>
+    </row>
+    <row r="232" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>24</v>
+      </c>
+      <c r="F232" t="s">
+        <v>308</v>
+      </c>
+      <c r="J232" t="s">
+        <v>500</v>
+      </c>
+      <c r="K232" s="82">
+        <f>INDEX('feed pars'!K$6:K$43,MATCH(F232,'feed pars'!B$6:B$43,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M232" s="3"/>
+    </row>
+    <row r="233" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>24</v>
+      </c>
+      <c r="F233" t="s">
+        <v>12</v>
+      </c>
+      <c r="J233" t="s">
+        <v>500</v>
+      </c>
+      <c r="K233" s="82">
+        <f>INDEX('feed pars'!K$6:K$43,MATCH(F233,'feed pars'!B$6:B$43,0))</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="234" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>24</v>
+      </c>
+      <c r="F234" t="s">
         <v>33</v>
       </c>
-      <c r="J231" t="s">
-        <v>18</v>
-      </c>
-      <c r="K231" s="31">
-        <f>K201</f>
-        <v>9.9416666666666664</v>
-      </c>
-    </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K232" s="31"/>
-    </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A233" t="s">
-        <v>391</v>
-      </c>
-      <c r="F233" t="s">
-        <v>38</v>
-      </c>
-      <c r="J233" t="s">
-        <v>18</v>
-      </c>
-      <c r="K233" s="31">
-        <f>K205</f>
-        <v>11.7</v>
-      </c>
-    </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A234" t="s">
-        <v>391</v>
-      </c>
-      <c r="F234" t="s">
-        <v>37</v>
-      </c>
       <c r="J234" t="s">
-        <v>18</v>
-      </c>
-      <c r="K234" s="31">
-        <f>K204</f>
-        <v>13.2</v>
-      </c>
-    </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.25">
+        <v>500</v>
+      </c>
+      <c r="K234" s="82">
+        <f>INDEX('feed pars'!K$6:K$43,MATCH(F234,'feed pars'!B$6:B$43,0))</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="235" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>391</v>
+        <v>24</v>
       </c>
       <c r="F235" t="s">
         <v>17</v>
       </c>
       <c r="J235" t="s">
+        <v>500</v>
+      </c>
+      <c r="K235" s="82">
+        <f>INDEX('feed pars'!K$6:K$43,MATCH(F235,'feed pars'!B$6:B$43,0))</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="236" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>24</v>
+      </c>
+      <c r="F236" t="s">
+        <v>37</v>
+      </c>
+      <c r="J236" t="s">
+        <v>500</v>
+      </c>
+      <c r="K236" s="82">
+        <f>INDEX('feed pars'!K$6:K$43,MATCH(F236,'feed pars'!B$6:B$43,0))</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="237" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>24</v>
+      </c>
+      <c r="F237" t="s">
+        <v>38</v>
+      </c>
+      <c r="J237" t="s">
+        <v>500</v>
+      </c>
+      <c r="K237" s="82">
+        <f>INDEX('feed pars'!K$6:K$43,MATCH(F237,'feed pars'!B$6:B$43,0))</f>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="238" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>24</v>
+      </c>
+      <c r="F238" t="s">
+        <v>39</v>
+      </c>
+      <c r="J238" t="s">
+        <v>500</v>
+      </c>
+      <c r="K238" s="82">
+        <f>INDEX('feed pars'!K$6:K$43,MATCH(F238,'feed pars'!B$6:B$43,0))</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="239" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>24</v>
+      </c>
+      <c r="F239" t="s">
+        <v>313</v>
+      </c>
+      <c r="J239" t="s">
+        <v>500</v>
+      </c>
+      <c r="K239" s="82">
+        <f>INDEX('feed pars'!K$6:K$43,MATCH(F239,'feed pars'!B$6:B$43,0))</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="240" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>24</v>
+      </c>
+      <c r="F240" t="s">
+        <v>40</v>
+      </c>
+      <c r="J240" t="s">
+        <v>500</v>
+      </c>
+      <c r="K240" s="82">
+        <f>INDEX('feed pars'!K$6:K$43,MATCH(F240,'feed pars'!B$6:B$43,0))</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>24</v>
+      </c>
+      <c r="F241" t="s">
+        <v>41</v>
+      </c>
+      <c r="J241" t="s">
+        <v>500</v>
+      </c>
+      <c r="K241" s="82">
+        <f>INDEX('feed pars'!K$6:K$43,MATCH(F241,'feed pars'!B$6:B$43,0))</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>24</v>
+      </c>
+      <c r="F242" t="s">
+        <v>42</v>
+      </c>
+      <c r="J242" t="s">
+        <v>500</v>
+      </c>
+      <c r="K242" s="82">
+        <f>INDEX('feed pars'!K$6:K$43,MATCH(F242,'feed pars'!B$6:B$43,0))</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>24</v>
+      </c>
+      <c r="F243" t="s">
+        <v>35</v>
+      </c>
+      <c r="J243" t="s">
+        <v>500</v>
+      </c>
+      <c r="K243" s="82">
+        <f>INDEX('feed pars'!K$6:K$43,MATCH(F243,'feed pars'!B$6:B$43,0))</f>
+        <v>460</v>
+      </c>
+    </row>
+    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>24</v>
+      </c>
+      <c r="F244" t="s">
+        <v>43</v>
+      </c>
+      <c r="J244" t="s">
+        <v>500</v>
+      </c>
+      <c r="K244" s="82">
+        <f>INDEX('feed pars'!K$6:K$43,MATCH(F244,'feed pars'!B$6:B$43,0))</f>
+        <v>380</v>
+      </c>
+    </row>
+    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>24</v>
+      </c>
+      <c r="F245" t="s">
+        <v>302</v>
+      </c>
+      <c r="J245" t="s">
+        <v>500</v>
+      </c>
+      <c r="K245" s="82">
+        <f>INDEX('feed pars'!K$6:K$43,MATCH(F245,'feed pars'!B$6:B$43,0))</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>24</v>
+      </c>
+      <c r="F246" t="s">
+        <v>310</v>
+      </c>
+      <c r="J246" t="s">
+        <v>500</v>
+      </c>
+      <c r="K246" s="82">
+        <f>INDEX('feed pars'!K$6:K$43,MATCH(F246,'feed pars'!B$6:B$43,0))</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>24</v>
+      </c>
+      <c r="F247" t="s">
+        <v>314</v>
+      </c>
+      <c r="J247" t="s">
+        <v>500</v>
+      </c>
+      <c r="K247" s="82">
+        <f>INDEX('feed pars'!K$6:K$43,MATCH(F247,'feed pars'!B$6:B$43,0))</f>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>24</v>
+      </c>
+      <c r="F248" t="s">
+        <v>44</v>
+      </c>
+      <c r="J248" t="s">
+        <v>500</v>
+      </c>
+      <c r="K248" s="82">
+        <f>INDEX('feed pars'!K$6:K$43,MATCH(F248,'feed pars'!B$6:B$43,0))</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>24</v>
+      </c>
+      <c r="F249" t="s">
+        <v>36</v>
+      </c>
+      <c r="J249" t="s">
+        <v>500</v>
+      </c>
+      <c r="K249" s="82">
+        <f>INDEX('feed pars'!K$6:K$43,MATCH(F249,'feed pars'!B$6:B$43,0))</f>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>24</v>
+      </c>
+      <c r="F250" t="s">
+        <v>46</v>
+      </c>
+      <c r="J250" t="s">
+        <v>500</v>
+      </c>
+      <c r="K250" s="82">
+        <f>INDEX('feed pars'!K$6:K$43,MATCH(F250,'feed pars'!B$6:B$43,0))</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>24</v>
+      </c>
+      <c r="F251" t="s">
+        <v>47</v>
+      </c>
+      <c r="J251" t="s">
+        <v>500</v>
+      </c>
+      <c r="K251" s="82">
+        <f>INDEX('feed pars'!K$6:K$43,MATCH(F251,'feed pars'!B$6:B$43,0))</f>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="252" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>24</v>
+      </c>
+      <c r="F252" t="s">
+        <v>315</v>
+      </c>
+      <c r="J252" t="s">
+        <v>500</v>
+      </c>
+      <c r="K252" s="82">
+        <f>INDEX('feed pars'!K$6:K$43,MATCH(F252,'feed pars'!B$6:B$43,0))</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="253" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>24</v>
+      </c>
+      <c r="F253" t="s">
+        <v>48</v>
+      </c>
+      <c r="J253" t="s">
+        <v>500</v>
+      </c>
+      <c r="K253" s="82">
+        <f>INDEX('feed pars'!K$6:K$43,MATCH(F253,'feed pars'!B$6:B$43,0))</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="254" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>24</v>
+      </c>
+      <c r="F254" t="s">
+        <v>50</v>
+      </c>
+      <c r="J254" t="s">
+        <v>500</v>
+      </c>
+      <c r="K254" s="82">
+        <f>INDEX('feed pars'!K$6:K$43,MATCH(F254,'feed pars'!B$6:B$43,0))</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="255" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>24</v>
+      </c>
+      <c r="F255" t="s">
+        <v>309</v>
+      </c>
+      <c r="J255" t="s">
+        <v>500</v>
+      </c>
+      <c r="K255" s="82">
+        <f>INDEX('feed pars'!K$6:K$43,MATCH(F255,'feed pars'!B$6:B$43,0))</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="256" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>24</v>
+      </c>
+      <c r="F256" t="s">
+        <v>52</v>
+      </c>
+      <c r="J256" t="s">
+        <v>500</v>
+      </c>
+      <c r="K256" s="82">
+        <f>INDEX('feed pars'!K$6:K$43,MATCH(F256,'feed pars'!B$6:B$43,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>24</v>
+      </c>
+      <c r="F257" t="s">
+        <v>53</v>
+      </c>
+      <c r="J257" t="s">
+        <v>500</v>
+      </c>
+      <c r="K257" s="82">
+        <f>INDEX('feed pars'!K$6:K$43,MATCH(F257,'feed pars'!B$6:B$43,0))</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="258" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>24</v>
+      </c>
+      <c r="F258" t="s">
+        <v>54</v>
+      </c>
+      <c r="J258" t="s">
+        <v>500</v>
+      </c>
+      <c r="K258" s="82">
+        <f>INDEX('feed pars'!K$6:K$43,MATCH(F258,'feed pars'!B$6:B$43,0))</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="259" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>24</v>
+      </c>
+      <c r="F259" t="s">
+        <v>56</v>
+      </c>
+      <c r="J259" t="s">
+        <v>500</v>
+      </c>
+      <c r="K259" s="82">
+        <f>INDEX('feed pars'!K$6:K$43,MATCH(F259,'feed pars'!B$6:B$43,0))</f>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="260" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>24</v>
+      </c>
+      <c r="F260" t="s">
+        <v>320</v>
+      </c>
+      <c r="J260" t="s">
+        <v>500</v>
+      </c>
+      <c r="K260" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A261" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="B261" s="7"/>
+      <c r="C261" s="6"/>
+      <c r="D261" s="6"/>
+      <c r="E261" s="6"/>
+      <c r="F261" s="6"/>
+      <c r="G261" s="6"/>
+      <c r="H261" s="6"/>
+      <c r="I261" s="6"/>
+      <c r="J261" s="6"/>
+      <c r="K261" s="6"/>
+      <c r="L261" s="6"/>
+      <c r="M261" s="6"/>
+      <c r="N261" s="6"/>
+    </row>
+    <row r="262" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>391</v>
+      </c>
+      <c r="F262" t="s">
+        <v>2</v>
+      </c>
+      <c r="J262" t="s">
         <v>18</v>
       </c>
-      <c r="K235" s="31">
+      <c r="K262" s="25">
+        <f>INDEX('feed pars'!I$6:I$43,MATCH(F262,'feed pars'!B$6:B$43,0))</f>
+        <v>9.1</v>
+      </c>
+      <c r="L262" t="s">
+        <v>19</v>
+      </c>
+      <c r="M262" s="26" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="263" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>391</v>
+      </c>
+      <c r="F263" t="s">
+        <v>33</v>
+      </c>
+      <c r="J263" t="s">
+        <v>18</v>
+      </c>
+      <c r="K263" s="31">
         <f>K203</f>
+        <v>9.9416666666666664</v>
+      </c>
+    </row>
+    <row r="264" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K264" s="31"/>
+    </row>
+    <row r="265" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>391</v>
+      </c>
+      <c r="F265" t="s">
+        <v>38</v>
+      </c>
+      <c r="J265" t="s">
+        <v>18</v>
+      </c>
+      <c r="K265" s="31">
+        <f>K206</f>
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="266" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>391</v>
+      </c>
+      <c r="F266" t="s">
+        <v>37</v>
+      </c>
+      <c r="J266" t="s">
+        <v>18</v>
+      </c>
+      <c r="K266" s="31">
+        <f>K205</f>
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="267" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>391</v>
+      </c>
+      <c r="F267" t="s">
+        <v>17</v>
+      </c>
+      <c r="J267" t="s">
+        <v>18</v>
+      </c>
+      <c r="K267" s="31">
+        <f>K204</f>
         <v>14.1</v>
       </c>
     </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A236" t="s">
+    <row r="268" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
         <v>391</v>
       </c>
-      <c r="F236" t="s">
+      <c r="F268" t="s">
         <v>49</v>
       </c>
-      <c r="J236" t="s">
+      <c r="J268" t="s">
         <v>18</v>
       </c>
-      <c r="K236" s="31">
-        <f t="shared" ref="K236:K242" si="14">K204</f>
+      <c r="K268" s="31">
+        <f t="shared" ref="K268:K274" si="14">K205</f>
         <v>13.2</v>
       </c>
     </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A237" t="s">
+    <row r="269" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
         <v>391</v>
       </c>
-      <c r="F237" t="s">
+      <c r="F269" t="s">
         <v>48</v>
       </c>
-      <c r="J237" t="s">
+      <c r="J269" t="s">
         <v>18</v>
       </c>
-      <c r="K237" s="31">
+      <c r="K269" s="31">
         <f t="shared" si="14"/>
         <v>11.7</v>
       </c>
     </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A238" t="s">
+    <row r="270" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
         <v>391</v>
       </c>
-      <c r="F238" t="s">
+      <c r="F270" t="s">
         <v>310</v>
       </c>
-      <c r="J238" t="s">
+      <c r="J270" t="s">
         <v>18</v>
       </c>
-      <c r="K238" s="31">
+      <c r="K270" s="31">
         <f t="shared" si="14"/>
         <v>14</v>
       </c>
     </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A239" t="s">
+    <row r="271" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
         <v>391</v>
       </c>
-      <c r="F239" t="s">
+      <c r="F271" t="s">
         <v>53</v>
       </c>
-      <c r="J239" t="s">
+      <c r="J271" t="s">
         <v>18</v>
       </c>
-      <c r="K239" s="31">
+      <c r="K271" s="31">
         <f t="shared" si="14"/>
         <v>13.9</v>
       </c>
     </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A240" t="s">
+    <row r="272" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
         <v>391</v>
       </c>
-      <c r="F240" t="s">
+      <c r="F272" t="s">
         <v>52</v>
       </c>
-      <c r="J240" t="s">
+      <c r="J272" t="s">
         <v>18</v>
       </c>
-      <c r="K240" s="31">
+      <c r="K272" s="31">
         <f t="shared" si="14"/>
         <v>12.8</v>
       </c>
     </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A241" t="s">
+    <row r="273" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
         <v>391</v>
       </c>
-      <c r="F241" t="s">
+      <c r="F273" t="s">
         <v>56</v>
       </c>
-      <c r="J241" t="s">
+      <c r="J273" t="s">
         <v>18</v>
       </c>
-      <c r="K241" s="31">
+      <c r="K273" s="31">
         <f t="shared" si="14"/>
         <v>13.8</v>
       </c>
     </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A242" t="s">
+    <row r="274" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
         <v>391</v>
       </c>
-      <c r="F242" t="s">
+      <c r="F274" t="s">
         <v>315</v>
       </c>
-      <c r="J242" t="s">
+      <c r="J274" t="s">
         <v>18</v>
       </c>
-      <c r="K242" s="31">
+      <c r="K274" s="31">
         <f t="shared" si="14"/>
         <v>13.3</v>
       </c>
     </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K243" s="3"/>
-    </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A244" s="8" t="s">
+    <row r="275" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K275" s="3"/>
+    </row>
+    <row r="276" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A276" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B244" s="8"/>
-      <c r="C244" s="9"/>
-      <c r="D244" s="9"/>
-      <c r="E244" s="9"/>
-      <c r="F244" s="9"/>
-      <c r="G244" s="9"/>
-      <c r="H244" s="9"/>
-      <c r="I244" s="9"/>
-      <c r="J244" s="9"/>
-      <c r="K244" s="9"/>
-      <c r="L244" s="9"/>
-      <c r="M244" s="9"/>
-      <c r="N244" s="9"/>
-    </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A245" s="27" t="s">
+      <c r="B276" s="8"/>
+      <c r="C276" s="9"/>
+      <c r="D276" s="9"/>
+      <c r="E276" s="9"/>
+      <c r="F276" s="9"/>
+      <c r="G276" s="9"/>
+      <c r="H276" s="9"/>
+      <c r="I276" s="9"/>
+      <c r="J276" s="9"/>
+      <c r="K276" s="9"/>
+      <c r="L276" s="9"/>
+      <c r="M276" s="9"/>
+      <c r="N276" s="9"/>
+    </row>
+    <row r="277" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A277" s="27" t="s">
         <v>387</v>
       </c>
-      <c r="B245" s="28"/>
-      <c r="C245" s="29"/>
-      <c r="D245" s="29"/>
-      <c r="E245" s="29"/>
-      <c r="F245" s="29"/>
-      <c r="G245" s="29"/>
-      <c r="H245" s="29"/>
-      <c r="I245" s="29"/>
-      <c r="J245" s="29"/>
-      <c r="K245" s="29"/>
-      <c r="L245" s="29" t="s">
-        <v>297</v>
-      </c>
-      <c r="M245" s="29"/>
-      <c r="N245" s="29"/>
-    </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A246" t="s">
-        <v>25</v>
-      </c>
-      <c r="E246" t="s">
-        <v>296</v>
-      </c>
-      <c r="F246" t="s">
-        <v>17</v>
-      </c>
-      <c r="J246" t="s">
-        <v>18</v>
-      </c>
-      <c r="K246" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F246,'feed pars'!B$6:B$43,0))</f>
-        <v>12.3</v>
-      </c>
-    </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A247" t="s">
-        <v>25</v>
-      </c>
-      <c r="E247" t="s">
-        <v>296</v>
-      </c>
-      <c r="F247" t="s">
-        <v>37</v>
-      </c>
-      <c r="J247" t="s">
-        <v>18</v>
-      </c>
-      <c r="K247" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F247,'feed pars'!B$6:B$43,0))</f>
-        <v>11.2</v>
-      </c>
-    </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A248" t="s">
-        <v>25</v>
-      </c>
-      <c r="E248" t="s">
-        <v>296</v>
-      </c>
-      <c r="F248" t="s">
-        <v>38</v>
-      </c>
-      <c r="J248" t="s">
-        <v>18</v>
-      </c>
-      <c r="K248" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F248,'feed pars'!B$6:B$43,0))</f>
-        <v>9.4</v>
-      </c>
-    </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A249" t="s">
-        <v>25</v>
-      </c>
-      <c r="E249" t="s">
-        <v>296</v>
-      </c>
-      <c r="F249" t="s">
-        <v>39</v>
-      </c>
-      <c r="J249" t="s">
-        <v>18</v>
-      </c>
-      <c r="K249" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F249,'feed pars'!B$6:B$43,0))</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A250" t="s">
-        <v>25</v>
-      </c>
-      <c r="E250" t="s">
-        <v>296</v>
-      </c>
-      <c r="F250" t="s">
-        <v>40</v>
-      </c>
-      <c r="J250" t="s">
-        <v>18</v>
-      </c>
-      <c r="K250" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F250,'feed pars'!B$6:B$43,0))</f>
-        <v>13.2</v>
-      </c>
-    </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A251" t="s">
-        <v>25</v>
-      </c>
-      <c r="E251" t="s">
-        <v>296</v>
-      </c>
-      <c r="F251" t="s">
-        <v>41</v>
-      </c>
-      <c r="J251" t="s">
-        <v>18</v>
-      </c>
-      <c r="K251" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F251,'feed pars'!B$6:B$43,0))</f>
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A252" t="s">
-        <v>25</v>
-      </c>
-      <c r="E252" t="s">
-        <v>296</v>
-      </c>
-      <c r="F252" t="s">
-        <v>42</v>
-      </c>
-      <c r="J252" t="s">
-        <v>18</v>
-      </c>
-      <c r="K252" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F252,'feed pars'!B$6:B$43,0))</f>
-        <v>10.9</v>
-      </c>
-    </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A253" t="s">
-        <v>25</v>
-      </c>
-      <c r="E253" t="s">
-        <v>296</v>
-      </c>
-      <c r="F253" t="s">
-        <v>35</v>
-      </c>
-      <c r="J253" t="s">
-        <v>18</v>
-      </c>
-      <c r="K253" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F253,'feed pars'!B$6:B$43,0))</f>
-        <v>18.5</v>
-      </c>
-    </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A254" t="s">
-        <v>25</v>
-      </c>
-      <c r="E254" t="s">
-        <v>296</v>
-      </c>
-      <c r="F254" t="s">
-        <v>43</v>
-      </c>
-      <c r="J254" t="s">
-        <v>18</v>
-      </c>
-      <c r="K254" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F254,'feed pars'!B$6:B$43,0))</f>
-        <v>17.5</v>
-      </c>
-    </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A255" t="s">
-        <v>25</v>
-      </c>
-      <c r="E255" t="s">
-        <v>296</v>
-      </c>
-      <c r="F255" t="s">
-        <v>310</v>
-      </c>
-      <c r="J255" t="s">
-        <v>18</v>
-      </c>
-      <c r="K255" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F255,'feed pars'!B$6:B$43,0))</f>
-        <v>29.8</v>
-      </c>
-    </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A256" t="s">
-        <v>25</v>
-      </c>
-      <c r="E256" t="s">
-        <v>296</v>
-      </c>
-      <c r="F256" t="s">
-        <v>44</v>
-      </c>
-      <c r="J256" t="s">
-        <v>18</v>
-      </c>
-      <c r="K256" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F256,'feed pars'!B$6:B$43,0))</f>
-        <v>9.9</v>
-      </c>
-    </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A257" t="s">
-        <v>25</v>
-      </c>
-      <c r="E257" t="s">
-        <v>296</v>
-      </c>
-      <c r="F257" t="s">
-        <v>45</v>
-      </c>
-      <c r="J257" t="s">
-        <v>18</v>
-      </c>
-      <c r="K257" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F257,'feed pars'!B$6:B$43,0))</f>
-        <v>10.3</v>
-      </c>
-    </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A258" t="s">
-        <v>25</v>
-      </c>
-      <c r="E258" t="s">
-        <v>296</v>
-      </c>
-      <c r="F258" t="s">
-        <v>36</v>
-      </c>
-      <c r="J258" t="s">
-        <v>18</v>
-      </c>
-      <c r="K258" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F258,'feed pars'!B$6:B$43,0))</f>
-        <v>7.7</v>
-      </c>
-    </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A259" t="s">
-        <v>25</v>
-      </c>
-      <c r="E259" t="s">
-        <v>296</v>
-      </c>
-      <c r="F259" t="s">
-        <v>46</v>
-      </c>
-      <c r="J259" t="s">
-        <v>18</v>
-      </c>
-      <c r="K259" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F259,'feed pars'!B$6:B$43,0))</f>
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A260" t="s">
-        <v>25</v>
-      </c>
-      <c r="E260" t="s">
-        <v>296</v>
-      </c>
-      <c r="F260" t="s">
-        <v>47</v>
-      </c>
-      <c r="J260" t="s">
-        <v>18</v>
-      </c>
-      <c r="K260" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F260,'feed pars'!B$6:B$43,0))</f>
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A261" t="s">
-        <v>25</v>
-      </c>
-      <c r="E261" t="s">
-        <v>296</v>
-      </c>
-      <c r="F261" t="s">
-        <v>48</v>
-      </c>
-      <c r="J261" t="s">
-        <v>18</v>
-      </c>
-      <c r="K261" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F261,'feed pars'!B$6:B$43,0))</f>
-        <v>7.8</v>
-      </c>
-    </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A262" t="s">
-        <v>25</v>
-      </c>
-      <c r="E262" t="s">
-        <v>296</v>
-      </c>
-      <c r="F262" t="s">
-        <v>49</v>
-      </c>
-      <c r="J262" t="s">
-        <v>18</v>
-      </c>
-      <c r="K262" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F262,'feed pars'!B$6:B$43,0))</f>
-        <v>9.1999999999999993</v>
-      </c>
-    </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A263" t="s">
-        <v>25</v>
-      </c>
-      <c r="E263" t="s">
-        <v>296</v>
-      </c>
-      <c r="F263" t="s">
-        <v>50</v>
-      </c>
-      <c r="J263" t="s">
-        <v>18</v>
-      </c>
-      <c r="K263" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F263,'feed pars'!B$6:B$43,0))</f>
-        <v>8.6999999999999993</v>
-      </c>
-    </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A264" t="s">
-        <v>25</v>
-      </c>
-      <c r="E264" t="s">
-        <v>296</v>
-      </c>
-      <c r="F264" t="s">
-        <v>51</v>
-      </c>
-      <c r="J264" t="s">
-        <v>18</v>
-      </c>
-      <c r="K264" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F264,'feed pars'!B$6:B$43,0))</f>
-        <v>8.9</v>
-      </c>
-    </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A265" t="s">
-        <v>25</v>
-      </c>
-      <c r="E265" t="s">
-        <v>296</v>
-      </c>
-      <c r="F265" t="s">
-        <v>309</v>
-      </c>
-      <c r="J265" t="s">
-        <v>18</v>
-      </c>
-      <c r="K265" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F265,'feed pars'!B$6:B$43,0))</f>
-        <v>7.0888888888888877</v>
-      </c>
-    </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A266" t="s">
-        <v>25</v>
-      </c>
-      <c r="E266" t="s">
-        <v>296</v>
-      </c>
-      <c r="F266" t="s">
-        <v>52</v>
-      </c>
-      <c r="J266" t="s">
-        <v>18</v>
-      </c>
-      <c r="K266" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F266,'feed pars'!B$6:B$43,0))</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A267" t="s">
-        <v>25</v>
-      </c>
-      <c r="E267" t="s">
-        <v>296</v>
-      </c>
-      <c r="F267" t="s">
-        <v>53</v>
-      </c>
-      <c r="J267" t="s">
-        <v>18</v>
-      </c>
-      <c r="K267" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F267,'feed pars'!B$6:B$43,0))</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A268" t="s">
-        <v>25</v>
-      </c>
-      <c r="E268" t="s">
-        <v>296</v>
-      </c>
-      <c r="F268" t="s">
-        <v>54</v>
-      </c>
-      <c r="J268" t="s">
-        <v>18</v>
-      </c>
-      <c r="K268" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F268,'feed pars'!B$6:B$43,0))</f>
-        <v>12.2</v>
-      </c>
-    </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A269" t="s">
-        <v>25</v>
-      </c>
-      <c r="E269" t="s">
-        <v>296</v>
-      </c>
-      <c r="F269" t="s">
-        <v>55</v>
-      </c>
-      <c r="J269" t="s">
-        <v>18</v>
-      </c>
-      <c r="K269" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F269,'feed pars'!B$6:B$43,0))</f>
-        <v>12.2</v>
-      </c>
-    </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A270" t="s">
-        <v>25</v>
-      </c>
-      <c r="E270" t="s">
-        <v>296</v>
-      </c>
-      <c r="F270" t="s">
-        <v>56</v>
-      </c>
-      <c r="J270" t="s">
-        <v>18</v>
-      </c>
-      <c r="K270" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F270,'feed pars'!B$6:B$43,0))</f>
-        <v>11.3</v>
-      </c>
-    </row>
-    <row r="271" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A271" t="s">
-        <v>25</v>
-      </c>
-      <c r="E271" t="s">
-        <v>296</v>
-      </c>
-      <c r="F271" t="s">
-        <v>57</v>
-      </c>
-      <c r="J271" t="s">
-        <v>18</v>
-      </c>
-      <c r="K271" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F271,'feed pars'!B$6:B$43,0))</f>
-        <v>10.8</v>
-      </c>
-    </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A272" s="27" t="s">
-        <v>388</v>
-      </c>
-      <c r="B272" s="28"/>
-      <c r="C272" s="29"/>
-      <c r="D272" s="29"/>
-      <c r="E272" s="29"/>
-      <c r="F272" s="29"/>
-      <c r="G272" s="29"/>
-      <c r="H272" s="29"/>
-      <c r="I272" s="29"/>
-      <c r="J272" s="29"/>
-      <c r="K272" s="29"/>
-      <c r="L272" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="M272" s="29"/>
-      <c r="N272" s="29"/>
-    </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A273" t="s">
-        <v>25</v>
-      </c>
-      <c r="F273" t="s">
-        <v>17</v>
-      </c>
-      <c r="J273" t="s">
-        <v>18</v>
-      </c>
-      <c r="K273" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F273,'feed pars'!B$6:B$43,0))</f>
-        <v>12.1</v>
-      </c>
-    </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A274" t="s">
-        <v>25</v>
-      </c>
-      <c r="F274" t="s">
-        <v>37</v>
-      </c>
-      <c r="J274" t="s">
-        <v>18</v>
-      </c>
-      <c r="K274" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F274,'feed pars'!B$6:B$43,0))</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A275" t="s">
-        <v>25</v>
-      </c>
-      <c r="F275" t="s">
-        <v>38</v>
-      </c>
-      <c r="J275" t="s">
-        <v>18</v>
-      </c>
-      <c r="K275" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F275,'feed pars'!B$6:B$43,0))</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A276" t="s">
-        <v>25</v>
-      </c>
-      <c r="F276" t="s">
-        <v>39</v>
-      </c>
-      <c r="J276" t="s">
-        <v>18</v>
-      </c>
-      <c r="K276" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F276,'feed pars'!B$6:B$43,0))</f>
-        <v>11.9</v>
-      </c>
-    </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A277" t="s">
-        <v>25</v>
-      </c>
-      <c r="F277" t="s">
-        <v>40</v>
-      </c>
-      <c r="J277" t="s">
-        <v>18</v>
-      </c>
-      <c r="K277" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F277,'feed pars'!B$6:B$43,0))</f>
-        <v>12.8</v>
-      </c>
-    </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B277" s="28"/>
+      <c r="C277" s="29"/>
+      <c r="D277" s="29"/>
+      <c r="E277" s="29"/>
+      <c r="F277" s="29"/>
+      <c r="G277" s="29"/>
+      <c r="H277" s="29"/>
+      <c r="I277" s="29"/>
+      <c r="J277" s="29"/>
+      <c r="K277" s="29"/>
+      <c r="L277" s="29"/>
+      <c r="M277" s="29"/>
+      <c r="N277" s="29"/>
+    </row>
+    <row r="278" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>25</v>
       </c>
+      <c r="E278" t="s">
+        <v>296</v>
+      </c>
       <c r="F278" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="J278" t="s">
         <v>18</v>
       </c>
       <c r="K278" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F278,'feed pars'!B$6:B$43,0))</f>
-        <v>11.2</v>
-      </c>
-    </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!U$6:U$43,MATCH(F278,'feed pars'!B$6:B$43,0))</f>
+        <v>12.3</v>
+      </c>
+      <c r="L278" t="s">
+        <v>297</v>
+      </c>
+      <c r="M278" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="279" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>25</v>
       </c>
+      <c r="E279" t="s">
+        <v>296</v>
+      </c>
       <c r="F279" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="J279" t="s">
         <v>18</v>
       </c>
       <c r="K279" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F279,'feed pars'!B$6:B$43,0))</f>
-        <v>10.7</v>
-      </c>
-    </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!U$6:U$43,MATCH(F279,'feed pars'!B$6:B$43,0))</f>
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="280" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>25</v>
       </c>
+      <c r="E280" t="s">
+        <v>296</v>
+      </c>
       <c r="F280" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J280" t="s">
         <v>18</v>
       </c>
       <c r="K280" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F280,'feed pars'!B$6:B$43,0))</f>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!U$6:U$43,MATCH(F280,'feed pars'!B$6:B$43,0))</f>
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="281" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>25</v>
       </c>
+      <c r="E281" t="s">
+        <v>296</v>
+      </c>
       <c r="F281" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J281" t="s">
         <v>18</v>
       </c>
       <c r="K281" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F281,'feed pars'!B$6:B$43,0))</f>
-        <v>17.3</v>
-      </c>
-    </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!U$6:U$43,MATCH(F281,'feed pars'!B$6:B$43,0))</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="282" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>25</v>
       </c>
+      <c r="E282" t="s">
+        <v>296</v>
+      </c>
       <c r="F282" t="s">
-        <v>310</v>
+        <v>40</v>
       </c>
       <c r="J282" t="s">
         <v>18</v>
       </c>
       <c r="K282" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F282,'feed pars'!B$6:B$43,0))</f>
-        <v>29.8</v>
-      </c>
-    </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!U$6:U$43,MATCH(F282,'feed pars'!B$6:B$43,0))</f>
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="283" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>25</v>
       </c>
+      <c r="E283" t="s">
+        <v>296</v>
+      </c>
       <c r="F283" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J283" t="s">
         <v>18</v>
       </c>
       <c r="K283" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F283,'feed pars'!B$6:B$43,0))</f>
-        <v>9.3000000000000007</v>
-      </c>
-    </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!U$6:U$43,MATCH(F283,'feed pars'!B$6:B$43,0))</f>
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="284" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>25</v>
       </c>
+      <c r="E284" t="s">
+        <v>296</v>
+      </c>
       <c r="F284" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J284" t="s">
         <v>18</v>
       </c>
       <c r="K284" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F284,'feed pars'!B$6:B$43,0))</f>
-        <v>9.6999999999999993</v>
-      </c>
-    </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!U$6:U$43,MATCH(F284,'feed pars'!B$6:B$43,0))</f>
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="285" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>25</v>
       </c>
+      <c r="E285" t="s">
+        <v>296</v>
+      </c>
       <c r="F285" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J285" t="s">
         <v>18</v>
       </c>
       <c r="K285" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F285,'feed pars'!B$6:B$43,0))</f>
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!U$6:U$43,MATCH(F285,'feed pars'!B$6:B$43,0))</f>
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="286" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>25</v>
       </c>
+      <c r="E286" t="s">
+        <v>296</v>
+      </c>
       <c r="F286" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="J286" t="s">
         <v>18</v>
       </c>
       <c r="K286" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F286,'feed pars'!B$6:B$43,0))</f>
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!U$6:U$43,MATCH(F286,'feed pars'!B$6:B$43,0))</f>
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="287" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>25</v>
       </c>
+      <c r="E287" t="s">
+        <v>296</v>
+      </c>
       <c r="F287" t="s">
-        <v>47</v>
+        <v>310</v>
       </c>
       <c r="J287" t="s">
         <v>18</v>
       </c>
       <c r="K287" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F287,'feed pars'!B$6:B$43,0))</f>
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!U$6:U$43,MATCH(F287,'feed pars'!B$6:B$43,0))</f>
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="288" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>25</v>
       </c>
+      <c r="E288" t="s">
+        <v>296</v>
+      </c>
       <c r="F288" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="J288" t="s">
         <v>18</v>
       </c>
       <c r="K288" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F288,'feed pars'!B$6:B$43,0))</f>
-        <v>7.2</v>
-      </c>
-    </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!U$6:U$43,MATCH(F288,'feed pars'!B$6:B$43,0))</f>
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="289" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>25</v>
       </c>
+      <c r="E289" t="s">
+        <v>296</v>
+      </c>
       <c r="F289" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="J289" t="s">
         <v>18</v>
       </c>
       <c r="K289" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F289,'feed pars'!B$6:B$43,0))</f>
-        <v>8.6999999999999993</v>
-      </c>
-    </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!U$6:U$43,MATCH(F289,'feed pars'!B$6:B$43,0))</f>
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="290" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>25</v>
       </c>
+      <c r="E290" t="s">
+        <v>296</v>
+      </c>
       <c r="F290" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="J290" t="s">
         <v>18</v>
       </c>
       <c r="K290" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F290,'feed pars'!B$6:B$43,0))</f>
-        <v>8.1</v>
-      </c>
-    </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!U$6:U$43,MATCH(F290,'feed pars'!B$6:B$43,0))</f>
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="291" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>25</v>
       </c>
+      <c r="E291" t="s">
+        <v>296</v>
+      </c>
       <c r="F291" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="J291" t="s">
         <v>18</v>
       </c>
       <c r="K291" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F291,'feed pars'!B$6:B$43,0))</f>
-        <v>8.1999999999999993</v>
-      </c>
-    </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!U$6:U$43,MATCH(F291,'feed pars'!B$6:B$43,0))</f>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="292" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>25</v>
       </c>
+      <c r="E292" t="s">
+        <v>296</v>
+      </c>
       <c r="F292" t="s">
-        <v>309</v>
+        <v>47</v>
       </c>
       <c r="J292" t="s">
         <v>18</v>
       </c>
       <c r="K292" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F292,'feed pars'!B$6:B$43,0))</f>
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!U$6:U$43,MATCH(F292,'feed pars'!B$6:B$43,0))</f>
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="293" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>25</v>
       </c>
+      <c r="E293" t="s">
+        <v>296</v>
+      </c>
       <c r="F293" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="J293" t="s">
         <v>18</v>
       </c>
       <c r="K293" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F293,'feed pars'!B$6:B$43,0))</f>
-        <v>8.6999999999999993</v>
-      </c>
-    </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!U$6:U$43,MATCH(F293,'feed pars'!B$6:B$43,0))</f>
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="294" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>25</v>
       </c>
+      <c r="E294" t="s">
+        <v>296</v>
+      </c>
       <c r="F294" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="J294" t="s">
         <v>18</v>
       </c>
       <c r="K294" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F294,'feed pars'!B$6:B$43,0))</f>
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!U$6:U$43,MATCH(F294,'feed pars'!B$6:B$43,0))</f>
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="295" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>25</v>
       </c>
+      <c r="E295" t="s">
+        <v>296</v>
+      </c>
       <c r="F295" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="J295" t="s">
         <v>18</v>
       </c>
       <c r="K295" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F295,'feed pars'!B$6:B$43,0))</f>
-        <v>12.4</v>
-      </c>
-    </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!U$6:U$43,MATCH(F295,'feed pars'!B$6:B$43,0))</f>
+        <v>8.6999999999999993</v>
+      </c>
+    </row>
+    <row r="296" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>25</v>
       </c>
+      <c r="E296" t="s">
+        <v>296</v>
+      </c>
       <c r="F296" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="J296" t="s">
         <v>18</v>
       </c>
       <c r="K296" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F296,'feed pars'!B$6:B$43,0))</f>
-        <v>12.4</v>
-      </c>
-    </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!U$6:U$43,MATCH(F296,'feed pars'!B$6:B$43,0))</f>
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="297" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>25</v>
       </c>
+      <c r="E297" t="s">
+        <v>296</v>
+      </c>
       <c r="F297" t="s">
-        <v>56</v>
+        <v>309</v>
       </c>
       <c r="J297" t="s">
         <v>18</v>
       </c>
       <c r="K297" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F297,'feed pars'!B$6:B$43,0))</f>
-        <v>11.1</v>
-      </c>
-    </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!U$6:U$43,MATCH(F297,'feed pars'!B$6:B$43,0))</f>
+        <v>7.0888888888888877</v>
+      </c>
+    </row>
+    <row r="298" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>25</v>
       </c>
+      <c r="E298" t="s">
+        <v>296</v>
+      </c>
       <c r="F298" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="J298" t="s">
         <v>18</v>
       </c>
       <c r="K298" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F298,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!U$6:U$43,MATCH(F298,'feed pars'!B$6:B$43,0))</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="299" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>25</v>
+      </c>
+      <c r="E299" t="s">
+        <v>296</v>
+      </c>
+      <c r="F299" t="s">
+        <v>53</v>
+      </c>
+      <c r="J299" t="s">
+        <v>18</v>
+      </c>
+      <c r="K299" s="25">
+        <f>INDEX('feed pars'!U$6:U$43,MATCH(F299,'feed pars'!B$6:B$43,0))</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="300" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>25</v>
+      </c>
+      <c r="E300" t="s">
+        <v>296</v>
+      </c>
+      <c r="F300" t="s">
+        <v>54</v>
+      </c>
+      <c r="J300" t="s">
+        <v>18</v>
+      </c>
+      <c r="K300" s="25">
+        <f>INDEX('feed pars'!U$6:U$43,MATCH(F300,'feed pars'!B$6:B$43,0))</f>
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="301" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>25</v>
+      </c>
+      <c r="E301" t="s">
+        <v>296</v>
+      </c>
+      <c r="F301" t="s">
+        <v>55</v>
+      </c>
+      <c r="J301" t="s">
+        <v>18</v>
+      </c>
+      <c r="K301" s="25">
+        <f>INDEX('feed pars'!U$6:U$43,MATCH(F301,'feed pars'!B$6:B$43,0))</f>
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="302" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>25</v>
+      </c>
+      <c r="E302" t="s">
+        <v>296</v>
+      </c>
+      <c r="F302" t="s">
+        <v>56</v>
+      </c>
+      <c r="J302" t="s">
+        <v>18</v>
+      </c>
+      <c r="K302" s="25">
+        <f>INDEX('feed pars'!U$6:U$43,MATCH(F302,'feed pars'!B$6:B$43,0))</f>
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="303" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>25</v>
+      </c>
+      <c r="E303" t="s">
+        <v>296</v>
+      </c>
+      <c r="F303" t="s">
+        <v>57</v>
+      </c>
+      <c r="J303" t="s">
+        <v>18</v>
+      </c>
+      <c r="K303" s="25">
+        <f>INDEX('feed pars'!U$6:U$43,MATCH(F303,'feed pars'!B$6:B$43,0))</f>
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="304" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A304" s="27" t="s">
+        <v>388</v>
+      </c>
+      <c r="B304" s="28"/>
+      <c r="C304" s="29"/>
+      <c r="D304" s="29"/>
+      <c r="E304" s="29"/>
+      <c r="F304" s="29"/>
+      <c r="G304" s="29"/>
+      <c r="H304" s="29"/>
+      <c r="I304" s="29"/>
+      <c r="J304" s="29"/>
+      <c r="K304" s="29"/>
+      <c r="L304" s="29"/>
+      <c r="M304" s="29"/>
+      <c r="N304" s="29"/>
+    </row>
+    <row r="305" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>25</v>
+      </c>
+      <c r="F305" t="s">
+        <v>17</v>
+      </c>
+      <c r="J305" t="s">
+        <v>18</v>
+      </c>
+      <c r="K305" s="25">
+        <f>INDEX('feed pars'!T$6:T$43,MATCH(F305,'feed pars'!B$6:B$43,0))</f>
+        <v>12.1</v>
+      </c>
+      <c r="L305" t="s">
+        <v>22</v>
+      </c>
+      <c r="M305" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="306" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>25</v>
+      </c>
+      <c r="F306" t="s">
+        <v>37</v>
+      </c>
+      <c r="J306" t="s">
+        <v>18</v>
+      </c>
+      <c r="K306" s="25">
+        <f>INDEX('feed pars'!T$6:T$43,MATCH(F306,'feed pars'!B$6:B$43,0))</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="307" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>25</v>
+      </c>
+      <c r="F307" t="s">
+        <v>38</v>
+      </c>
+      <c r="J307" t="s">
+        <v>18</v>
+      </c>
+      <c r="K307" s="25">
+        <f>INDEX('feed pars'!T$6:T$43,MATCH(F307,'feed pars'!B$6:B$43,0))</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="308" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>25</v>
+      </c>
+      <c r="F308" t="s">
+        <v>39</v>
+      </c>
+      <c r="J308" t="s">
+        <v>18</v>
+      </c>
+      <c r="K308" s="25">
+        <f>INDEX('feed pars'!T$6:T$43,MATCH(F308,'feed pars'!B$6:B$43,0))</f>
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="309" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>25</v>
+      </c>
+      <c r="F309" t="s">
+        <v>40</v>
+      </c>
+      <c r="J309" t="s">
+        <v>18</v>
+      </c>
+      <c r="K309" s="25">
+        <f>INDEX('feed pars'!T$6:T$43,MATCH(F309,'feed pars'!B$6:B$43,0))</f>
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="310" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>25</v>
+      </c>
+      <c r="F310" t="s">
+        <v>41</v>
+      </c>
+      <c r="J310" t="s">
+        <v>18</v>
+      </c>
+      <c r="K310" s="25">
+        <f>INDEX('feed pars'!T$6:T$43,MATCH(F310,'feed pars'!B$6:B$43,0))</f>
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="311" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>25</v>
+      </c>
+      <c r="F311" t="s">
+        <v>42</v>
+      </c>
+      <c r="J311" t="s">
+        <v>18</v>
+      </c>
+      <c r="K311" s="25">
+        <f>INDEX('feed pars'!T$6:T$43,MATCH(F311,'feed pars'!B$6:B$43,0))</f>
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="312" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>25</v>
+      </c>
+      <c r="F312" t="s">
+        <v>35</v>
+      </c>
+      <c r="J312" t="s">
+        <v>18</v>
+      </c>
+      <c r="K312" s="25">
+        <f>INDEX('feed pars'!T$6:T$43,MATCH(F312,'feed pars'!B$6:B$43,0))</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="313" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>25</v>
+      </c>
+      <c r="F313" t="s">
+        <v>43</v>
+      </c>
+      <c r="J313" t="s">
+        <v>18</v>
+      </c>
+      <c r="K313" s="25">
+        <f>INDEX('feed pars'!T$6:T$43,MATCH(F313,'feed pars'!B$6:B$43,0))</f>
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="314" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>25</v>
+      </c>
+      <c r="F314" t="s">
+        <v>310</v>
+      </c>
+      <c r="J314" t="s">
+        <v>18</v>
+      </c>
+      <c r="K314" s="25">
+        <f>INDEX('feed pars'!T$6:T$43,MATCH(F314,'feed pars'!B$6:B$43,0))</f>
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="315" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>25</v>
+      </c>
+      <c r="F315" t="s">
+        <v>44</v>
+      </c>
+      <c r="J315" t="s">
+        <v>18</v>
+      </c>
+      <c r="K315" s="25">
+        <f>INDEX('feed pars'!T$6:T$43,MATCH(F315,'feed pars'!B$6:B$43,0))</f>
+        <v>9.3000000000000007</v>
+      </c>
+    </row>
+    <row r="316" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>25</v>
+      </c>
+      <c r="F316" t="s">
+        <v>45</v>
+      </c>
+      <c r="J316" t="s">
+        <v>18</v>
+      </c>
+      <c r="K316" s="25">
+        <f>INDEX('feed pars'!T$6:T$43,MATCH(F316,'feed pars'!B$6:B$43,0))</f>
+        <v>9.6999999999999993</v>
+      </c>
+    </row>
+    <row r="317" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>25</v>
+      </c>
+      <c r="F317" t="s">
+        <v>36</v>
+      </c>
+      <c r="J317" t="s">
+        <v>18</v>
+      </c>
+      <c r="K317" s="25">
+        <f>INDEX('feed pars'!T$6:T$43,MATCH(F317,'feed pars'!B$6:B$43,0))</f>
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="318" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>25</v>
+      </c>
+      <c r="F318" t="s">
+        <v>46</v>
+      </c>
+      <c r="J318" t="s">
+        <v>18</v>
+      </c>
+      <c r="K318" s="25">
+        <f>INDEX('feed pars'!T$6:T$43,MATCH(F318,'feed pars'!B$6:B$43,0))</f>
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="319" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>25</v>
+      </c>
+      <c r="F319" t="s">
+        <v>47</v>
+      </c>
+      <c r="J319" t="s">
+        <v>18</v>
+      </c>
+      <c r="K319" s="25">
+        <f>INDEX('feed pars'!T$6:T$43,MATCH(F319,'feed pars'!B$6:B$43,0))</f>
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="320" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>25</v>
+      </c>
+      <c r="F320" t="s">
+        <v>48</v>
+      </c>
+      <c r="J320" t="s">
+        <v>18</v>
+      </c>
+      <c r="K320" s="25">
+        <f>INDEX('feed pars'!T$6:T$43,MATCH(F320,'feed pars'!B$6:B$43,0))</f>
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="321" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>25</v>
+      </c>
+      <c r="F321" t="s">
+        <v>49</v>
+      </c>
+      <c r="J321" t="s">
+        <v>18</v>
+      </c>
+      <c r="K321" s="25">
+        <f>INDEX('feed pars'!T$6:T$43,MATCH(F321,'feed pars'!B$6:B$43,0))</f>
+        <v>8.6999999999999993</v>
+      </c>
+    </row>
+    <row r="322" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>25</v>
+      </c>
+      <c r="F322" t="s">
+        <v>50</v>
+      </c>
+      <c r="J322" t="s">
+        <v>18</v>
+      </c>
+      <c r="K322" s="25">
+        <f>INDEX('feed pars'!T$6:T$43,MATCH(F322,'feed pars'!B$6:B$43,0))</f>
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="323" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>25</v>
+      </c>
+      <c r="F323" t="s">
+        <v>51</v>
+      </c>
+      <c r="J323" t="s">
+        <v>18</v>
+      </c>
+      <c r="K323" s="25">
+        <f>INDEX('feed pars'!T$6:T$43,MATCH(F323,'feed pars'!B$6:B$43,0))</f>
+        <v>8.1999999999999993</v>
+      </c>
+    </row>
+    <row r="324" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>25</v>
+      </c>
+      <c r="F324" t="s">
+        <v>309</v>
+      </c>
+      <c r="J324" t="s">
+        <v>18</v>
+      </c>
+      <c r="K324" s="25">
+        <f>INDEX('feed pars'!T$6:T$43,MATCH(F324,'feed pars'!B$6:B$43,0))</f>
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="325" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>25</v>
+      </c>
+      <c r="F325" t="s">
+        <v>52</v>
+      </c>
+      <c r="J325" t="s">
+        <v>18</v>
+      </c>
+      <c r="K325" s="25">
+        <f>INDEX('feed pars'!T$6:T$43,MATCH(F325,'feed pars'!B$6:B$43,0))</f>
+        <v>8.6999999999999993</v>
+      </c>
+    </row>
+    <row r="326" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>25</v>
+      </c>
+      <c r="F326" t="s">
+        <v>53</v>
+      </c>
+      <c r="J326" t="s">
+        <v>18</v>
+      </c>
+      <c r="K326" s="25">
+        <f>INDEX('feed pars'!T$6:T$43,MATCH(F326,'feed pars'!B$6:B$43,0))</f>
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="327" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>25</v>
+      </c>
+      <c r="F327" t="s">
+        <v>54</v>
+      </c>
+      <c r="J327" t="s">
+        <v>18</v>
+      </c>
+      <c r="K327" s="25">
+        <f>INDEX('feed pars'!T$6:T$43,MATCH(F327,'feed pars'!B$6:B$43,0))</f>
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="328" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>25</v>
+      </c>
+      <c r="F328" t="s">
+        <v>55</v>
+      </c>
+      <c r="J328" t="s">
+        <v>18</v>
+      </c>
+      <c r="K328" s="25">
+        <f>INDEX('feed pars'!T$6:T$43,MATCH(F328,'feed pars'!B$6:B$43,0))</f>
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="329" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>25</v>
+      </c>
+      <c r="F329" t="s">
+        <v>56</v>
+      </c>
+      <c r="J329" t="s">
+        <v>18</v>
+      </c>
+      <c r="K329" s="25">
+        <f>INDEX('feed pars'!T$6:T$43,MATCH(F329,'feed pars'!B$6:B$43,0))</f>
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="330" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>25</v>
+      </c>
+      <c r="F330" t="s">
+        <v>57</v>
+      </c>
+      <c r="J330" t="s">
+        <v>18</v>
+      </c>
+      <c r="K330" s="25">
+        <f>INDEX('feed pars'!T$6:T$43,MATCH(F330,'feed pars'!B$6:B$43,0))</f>
         <v>10.8</v>
       </c>
     </row>
@@ -7368,96 +7903,96 @@
       <c r="Q1" s="11"/>
     </row>
     <row r="3" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="C3" s="63" t="s">
+      <c r="C3" s="62" t="s">
         <v>303</v>
       </c>
-      <c r="D3" s="64"/>
-      <c r="F3" s="63" t="s">
+      <c r="D3" s="63"/>
+      <c r="F3" s="62" t="s">
         <v>489</v>
       </c>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="64"/>
-      <c r="L3" s="64"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="64"/>
-      <c r="Q3" s="63" t="s">
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="63"/>
+      <c r="L3" s="63"/>
+      <c r="M3" s="63"/>
+      <c r="N3" s="63"/>
+      <c r="Q3" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="64"/>
-      <c r="W3" s="64"/>
-      <c r="X3" s="64"/>
-      <c r="Y3" s="64"/>
-      <c r="AB3" s="63" t="s">
+      <c r="R3" s="63"/>
+      <c r="S3" s="63"/>
+      <c r="T3" s="63"/>
+      <c r="U3" s="63"/>
+      <c r="V3" s="63"/>
+      <c r="W3" s="63"/>
+      <c r="X3" s="63"/>
+      <c r="Y3" s="63"/>
+      <c r="AB3" s="62" t="s">
         <v>385</v>
       </c>
-      <c r="AC3" s="64"/>
+      <c r="AC3" s="63"/>
     </row>
     <row r="4" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="C4" s="62"/>
+      <c r="C4" s="61"/>
       <c r="D4" s="2"/>
-      <c r="F4" s="69" t="s">
+      <c r="F4" s="68" t="s">
         <v>294</v>
       </c>
-      <c r="G4" s="70">
+      <c r="G4" s="69">
         <v>1</v>
       </c>
-      <c r="H4" s="70"/>
-      <c r="I4" s="70">
+      <c r="H4" s="69"/>
+      <c r="I4" s="69">
         <v>2</v>
       </c>
-      <c r="J4" s="70">
+      <c r="J4" s="69">
         <v>7</v>
       </c>
-      <c r="K4" s="70">
+      <c r="K4" s="69">
         <v>8</v>
       </c>
-      <c r="L4" s="70">
+      <c r="L4" s="69">
         <v>9</v>
       </c>
-      <c r="M4" s="70">
+      <c r="M4" s="69">
         <v>11</v>
       </c>
-      <c r="N4" s="70">
+      <c r="N4" s="69">
         <v>10</v>
       </c>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
-      <c r="Q4" s="69" t="s">
+      <c r="Q4" s="68" t="s">
         <v>294</v>
       </c>
-      <c r="R4" s="70">
+      <c r="R4" s="69">
         <v>1</v>
       </c>
-      <c r="S4" s="70"/>
-      <c r="T4" s="70">
+      <c r="S4" s="69"/>
+      <c r="T4" s="69">
         <v>2</v>
       </c>
-      <c r="U4" s="70">
+      <c r="U4" s="69">
         <v>3</v>
       </c>
-      <c r="V4" s="70">
+      <c r="V4" s="69">
         <v>5</v>
       </c>
-      <c r="W4" s="70">
+      <c r="W4" s="69">
         <v>6</v>
       </c>
-      <c r="X4" s="70"/>
-      <c r="Y4" s="70">
+      <c r="X4" s="69"/>
+      <c r="Y4" s="69">
         <v>12</v>
       </c>
       <c r="Z4" s="4"/>
       <c r="AA4" s="4"/>
-      <c r="AB4" s="69" t="s">
+      <c r="AB4" s="68" t="s">
         <v>294</v>
       </c>
-      <c r="AC4" s="70">
+      <c r="AC4" s="69">
         <v>1</v>
       </c>
     </row>
@@ -7465,80 +8000,80 @@
       <c r="B5" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="72" t="s">
+      <c r="C5" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="D5" s="74" t="s">
+      <c r="D5" s="73" t="s">
         <v>407</v>
       </c>
-      <c r="F5" s="69" t="s">
+      <c r="F5" s="68" t="s">
         <v>295</v>
       </c>
-      <c r="G5" s="72" t="s">
+      <c r="G5" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="H5" s="73" t="s">
+      <c r="H5" s="72" t="s">
         <v>495</v>
       </c>
-      <c r="I5" s="73" t="s">
+      <c r="I5" s="72" t="s">
         <v>494</v>
       </c>
-      <c r="J5" s="73" t="s">
+      <c r="J5" s="72" t="s">
         <v>410</v>
       </c>
-      <c r="K5" s="73" t="s">
+      <c r="K5" s="72" t="s">
         <v>411</v>
       </c>
-      <c r="L5" s="73" t="s">
+      <c r="L5" s="72" t="s">
         <v>412</v>
       </c>
-      <c r="M5" s="73" t="s">
+      <c r="M5" s="72" t="s">
         <v>282</v>
       </c>
-      <c r="N5" s="74" t="s">
+      <c r="N5" s="73" t="s">
         <v>487</v>
       </c>
-      <c r="O5" s="76" t="s">
+      <c r="O5" s="75" t="s">
         <v>492</v>
       </c>
-      <c r="Q5" s="69" t="s">
+      <c r="Q5" s="68" t="s">
         <v>295</v>
       </c>
-      <c r="R5" s="72" t="s">
+      <c r="R5" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="S5" s="73" t="s">
+      <c r="S5" s="72" t="s">
         <v>495</v>
       </c>
-      <c r="T5" s="73" t="s">
+      <c r="T5" s="72" t="s">
         <v>121</v>
       </c>
-      <c r="U5" s="73" t="s">
+      <c r="U5" s="72" t="s">
         <v>120</v>
       </c>
-      <c r="V5" s="73" t="s">
+      <c r="V5" s="72" t="s">
         <v>410</v>
       </c>
-      <c r="W5" s="73" t="s">
+      <c r="W5" s="72" t="s">
         <v>411</v>
       </c>
-      <c r="X5" s="73" t="s">
+      <c r="X5" s="72" t="s">
         <v>493</v>
       </c>
-      <c r="Y5" s="74" t="s">
+      <c r="Y5" s="73" t="s">
         <v>487</v>
       </c>
-      <c r="Z5" s="76" t="s">
+      <c r="Z5" s="75" t="s">
         <v>492</v>
       </c>
       <c r="AA5" s="4"/>
-      <c r="AB5" s="69" t="s">
+      <c r="AB5" s="68" t="s">
         <v>295</v>
       </c>
-      <c r="AC5" s="71" t="s">
+      <c r="AC5" s="70" t="s">
         <v>59</v>
       </c>
-      <c r="AD5" s="76" t="s">
+      <c r="AD5" s="75" t="s">
         <v>492</v>
       </c>
     </row>
@@ -7547,20 +8082,20 @@
         <v>306</v>
       </c>
       <c r="C6" s="37">
-        <f>AVERAGE(R6,G6)</f>
+        <f t="shared" ref="C6:C11" si="0">AVERAGE(R6,G6)</f>
         <v>100</v>
       </c>
-      <c r="D6" s="65">
-        <f>H6</f>
-        <v>17.538700400000003</v>
-      </c>
-      <c r="F6" s="69"/>
+      <c r="D6" s="64">
+        <f t="shared" ref="D6:D11" si="1">H6</f>
+        <v>17.316948400000001</v>
+      </c>
+      <c r="F6" s="68"/>
       <c r="G6" s="37">
         <v>100</v>
       </c>
-      <c r="H6" s="78">
-        <f t="shared" ref="H6:H11" si="0">( 5.7*J6+9.4*K6+4.1*(L6+M6) ) * 0.004184</f>
-        <v>17.538700400000003</v>
+      <c r="H6" s="77">
+        <f t="shared" ref="H6:H11" si="2">( 5.7*J6+9.4*K6+4.1*(L6+M6) ) * 0.004184</f>
+        <v>17.316948400000001</v>
       </c>
       <c r="I6" s="38">
         <f>AVERAGE('ruminants, roughage'!D21:D22)</f>
@@ -7570,49 +8105,49 @@
         <f>AVERAGE('ruminants, roughage'!I21:I22)</f>
         <v>151.5</v>
       </c>
-      <c r="K6" s="40">
-        <v>30</v>
+      <c r="K6" s="44">
+        <v>20</v>
       </c>
       <c r="L6" s="39"/>
       <c r="M6" s="41">
-        <f>1000-SUM(J6:L6,N6)</f>
-        <v>743</v>
+        <f t="shared" ref="M6:M11" si="3">1000-SUM(J6:L6,N6)</f>
+        <v>753</v>
       </c>
       <c r="N6" s="42">
         <f>AVERAGE('ruminants, roughage'!K21:K22)</f>
         <v>75.5</v>
       </c>
-      <c r="Q6" s="69"/>
+      <c r="Q6" s="68"/>
       <c r="R6" s="37"/>
-      <c r="S6" s="55"/>
-      <c r="T6" s="55"/>
-      <c r="U6" s="55"/>
-      <c r="V6" s="55"/>
-      <c r="W6" s="55"/>
-      <c r="X6" s="55"/>
-      <c r="Y6" s="56"/>
-      <c r="AB6" s="69"/>
-      <c r="AC6" s="60"/>
+      <c r="S6" s="54"/>
+      <c r="T6" s="54"/>
+      <c r="U6" s="54"/>
+      <c r="V6" s="54"/>
+      <c r="W6" s="54"/>
+      <c r="X6" s="54"/>
+      <c r="Y6" s="55"/>
+      <c r="AB6" s="68"/>
+      <c r="AC6" s="59"/>
     </row>
     <row r="7" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>307</v>
       </c>
       <c r="C7" s="37">
-        <f>AVERAGE(R7,G7)</f>
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="D7" s="65">
-        <f>H7</f>
-        <v>17.371968000000003</v>
-      </c>
-      <c r="F7" s="69"/>
+      <c r="D7" s="64">
+        <f t="shared" si="1"/>
+        <v>17.150216</v>
+      </c>
+      <c r="F7" s="68"/>
       <c r="G7" s="37">
         <v>100</v>
       </c>
-      <c r="H7" s="78">
-        <f t="shared" si="0"/>
-        <v>17.371968000000003</v>
+      <c r="H7" s="77">
+        <f t="shared" si="2"/>
+        <v>17.150216</v>
       </c>
       <c r="I7" s="38">
         <f>AVERAGE('ruminants, roughage'!D25:D25)</f>
@@ -7622,48 +8157,48 @@
         <f>AVERAGE('ruminants, roughage'!I25:I25)</f>
         <v>133</v>
       </c>
-      <c r="K7" s="40">
-        <v>30</v>
+      <c r="K7" s="44">
+        <v>20</v>
       </c>
       <c r="L7" s="39"/>
       <c r="M7" s="41">
-        <f>1000-SUM(J7:L7,N7)</f>
-        <v>759</v>
+        <f t="shared" si="3"/>
+        <v>769</v>
       </c>
       <c r="N7" s="42">
         <f>AVERAGE('ruminants, roughage'!K25:K25)</f>
         <v>78</v>
       </c>
-      <c r="Q7" s="69"/>
+      <c r="Q7" s="68"/>
       <c r="R7" s="37"/>
-      <c r="S7" s="55"/>
-      <c r="T7" s="55"/>
-      <c r="U7" s="55"/>
-      <c r="V7" s="55"/>
-      <c r="W7" s="55"/>
-      <c r="X7" s="55"/>
-      <c r="Y7" s="56"/>
-      <c r="AB7" s="69"/>
-      <c r="AC7" s="60"/>
+      <c r="S7" s="54"/>
+      <c r="T7" s="54"/>
+      <c r="U7" s="54"/>
+      <c r="V7" s="54"/>
+      <c r="W7" s="54"/>
+      <c r="X7" s="54"/>
+      <c r="Y7" s="55"/>
+      <c r="AB7" s="68"/>
+      <c r="AC7" s="59"/>
     </row>
     <row r="8" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>308</v>
       </c>
       <c r="C8" s="37">
-        <f>AVERAGE(R8,G8)</f>
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="D8" s="65">
-        <f>H8</f>
+      <c r="D8" s="64">
+        <f t="shared" si="1"/>
         <v>16.819680000000002</v>
       </c>
-      <c r="F8" s="69"/>
+      <c r="F8" s="68"/>
       <c r="G8" s="37">
         <v>100</v>
       </c>
-      <c r="H8" s="78">
-        <f t="shared" si="0"/>
+      <c r="H8" s="77">
+        <f t="shared" si="2"/>
         <v>16.819680000000002</v>
       </c>
       <c r="I8" s="43">
@@ -7680,7 +8215,7 @@
       </c>
       <c r="L8" s="40"/>
       <c r="M8" s="41">
-        <f>1000-SUM(J8:L8,N8)</f>
+        <f t="shared" si="3"/>
         <v>748.5</v>
       </c>
       <c r="N8" s="45">
@@ -7693,37 +8228,37 @@
       <c r="P8" t="s">
         <v>490</v>
       </c>
-      <c r="Q8" s="69"/>
+      <c r="Q8" s="68"/>
       <c r="R8" s="37"/>
-      <c r="S8" s="55"/>
-      <c r="T8" s="55"/>
-      <c r="U8" s="55"/>
-      <c r="V8" s="55"/>
-      <c r="W8" s="55"/>
-      <c r="X8" s="55"/>
-      <c r="Y8" s="56"/>
-      <c r="AB8" s="69"/>
-      <c r="AC8" s="60"/>
+      <c r="S8" s="54"/>
+      <c r="T8" s="54"/>
+      <c r="U8" s="54"/>
+      <c r="V8" s="54"/>
+      <c r="W8" s="54"/>
+      <c r="X8" s="54"/>
+      <c r="Y8" s="55"/>
+      <c r="AB8" s="68"/>
+      <c r="AC8" s="59"/>
     </row>
     <row r="9" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>2</v>
       </c>
       <c r="C9" s="37">
-        <f>AVERAGE(R9,G9)</f>
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="D9" s="65">
-        <f>H9</f>
-        <v>17.3820096</v>
-      </c>
-      <c r="F9" s="69"/>
+      <c r="D9" s="64">
+        <f t="shared" si="1"/>
+        <v>17.160257599999998</v>
+      </c>
+      <c r="F9" s="68"/>
       <c r="G9" s="37">
         <v>100</v>
       </c>
-      <c r="H9" s="78">
-        <f t="shared" si="0"/>
-        <v>17.3820096</v>
+      <c r="H9" s="77">
+        <f t="shared" si="2"/>
+        <v>17.160257599999998</v>
       </c>
       <c r="I9" s="38">
         <f>AVERAGE('ruminants, roughage'!D33:D33)</f>
@@ -7733,48 +8268,48 @@
         <f>AVERAGE('ruminants, roughage'!I33:I33)</f>
         <v>93.5</v>
       </c>
-      <c r="K9" s="40">
-        <v>30</v>
+      <c r="K9" s="44">
+        <v>20</v>
       </c>
       <c r="L9" s="39"/>
       <c r="M9" s="41">
-        <f>1000-SUM(J9:L9,N9)</f>
-        <v>814.5</v>
+        <f t="shared" si="3"/>
+        <v>824.5</v>
       </c>
       <c r="N9" s="42">
         <f>AVERAGE('ruminants, roughage'!K33:K33)</f>
         <v>62</v>
       </c>
-      <c r="Q9" s="69"/>
+      <c r="Q9" s="68"/>
       <c r="R9" s="37"/>
-      <c r="S9" s="55"/>
-      <c r="T9" s="55"/>
-      <c r="U9" s="55"/>
-      <c r="V9" s="55"/>
-      <c r="W9" s="55"/>
-      <c r="X9" s="55"/>
-      <c r="Y9" s="56"/>
-      <c r="AB9" s="69"/>
-      <c r="AC9" s="60"/>
+      <c r="S9" s="54"/>
+      <c r="T9" s="54"/>
+      <c r="U9" s="54"/>
+      <c r="V9" s="54"/>
+      <c r="W9" s="54"/>
+      <c r="X9" s="54"/>
+      <c r="Y9" s="55"/>
+      <c r="AB9" s="68"/>
+      <c r="AC9" s="59"/>
     </row>
     <row r="10" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="37">
-        <f>AVERAGE(R10,G10)</f>
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="D10" s="65">
-        <f>H10</f>
+      <c r="D10" s="64">
+        <f t="shared" si="1"/>
         <v>17.6573168</v>
       </c>
-      <c r="F10" s="69"/>
+      <c r="F10" s="68"/>
       <c r="G10" s="37">
         <v>100</v>
       </c>
-      <c r="H10" s="78">
-        <f t="shared" si="0"/>
+      <c r="H10" s="77">
+        <f t="shared" si="2"/>
         <v>17.6573168</v>
       </c>
       <c r="I10" s="38">
@@ -7790,7 +8325,7 @@
         <v>198</v>
       </c>
       <c r="M10" s="41">
-        <f>1000-SUM(J10:L10,N10)</f>
+        <f t="shared" si="3"/>
         <v>668</v>
       </c>
       <c r="N10" s="42">
@@ -7802,37 +8337,37 @@
       <c r="P10" s="11" t="s">
         <v>490</v>
       </c>
-      <c r="Q10" s="69"/>
+      <c r="Q10" s="68"/>
       <c r="R10" s="37"/>
-      <c r="S10" s="55"/>
-      <c r="T10" s="55"/>
-      <c r="U10" s="55"/>
-      <c r="V10" s="55"/>
-      <c r="W10" s="55"/>
-      <c r="X10" s="55"/>
-      <c r="Y10" s="56"/>
-      <c r="AB10" s="69"/>
-      <c r="AC10" s="60"/>
+      <c r="S10" s="54"/>
+      <c r="T10" s="54"/>
+      <c r="U10" s="54"/>
+      <c r="V10" s="54"/>
+      <c r="W10" s="54"/>
+      <c r="X10" s="54"/>
+      <c r="Y10" s="55"/>
+      <c r="AB10" s="68"/>
+      <c r="AC10" s="59"/>
     </row>
     <row r="11" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>33</v>
       </c>
       <c r="C11" s="37">
-        <f>AVERAGE(R11,G11)</f>
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="D11" s="65">
-        <f>H11</f>
-        <v>17.633189066666667</v>
-      </c>
-      <c r="F11" s="69"/>
+      <c r="D11" s="64">
+        <f t="shared" si="1"/>
+        <v>17.411437066666668</v>
+      </c>
+      <c r="F11" s="68"/>
       <c r="G11" s="37">
         <v>100</v>
       </c>
-      <c r="H11" s="78">
-        <f t="shared" si="0"/>
-        <v>17.633189066666667</v>
+      <c r="H11" s="77">
+        <f t="shared" si="2"/>
+        <v>17.411437066666668</v>
       </c>
       <c r="I11" s="38">
         <f>AVERAGE('ruminants, roughage'!D3:D14)</f>
@@ -7842,71 +8377,71 @@
         <f>AVERAGE('ruminants, roughage'!I3:I14)</f>
         <v>140.41666666666666</v>
       </c>
-      <c r="K11" s="40">
-        <v>30</v>
+      <c r="K11" s="44">
+        <v>20</v>
       </c>
       <c r="L11" s="39"/>
       <c r="M11" s="41">
-        <f>1000-SUM(J11:L11,N11)</f>
-        <v>763.91666666666674</v>
+        <f t="shared" si="3"/>
+        <v>773.91666666666674</v>
       </c>
       <c r="N11" s="42">
         <f>AVERAGE('ruminants, roughage'!K3:K14)</f>
         <v>65.666666666666657</v>
       </c>
-      <c r="Q11" s="69"/>
+      <c r="Q11" s="68"/>
       <c r="R11" s="37"/>
-      <c r="S11" s="55"/>
-      <c r="T11" s="55"/>
-      <c r="U11" s="55"/>
-      <c r="V11" s="55"/>
-      <c r="W11" s="55"/>
-      <c r="X11" s="55"/>
-      <c r="Y11" s="56"/>
-      <c r="AB11" s="69"/>
-      <c r="AC11" s="60"/>
+      <c r="S11" s="54"/>
+      <c r="T11" s="54"/>
+      <c r="U11" s="54"/>
+      <c r="V11" s="54"/>
+      <c r="W11" s="54"/>
+      <c r="X11" s="54"/>
+      <c r="Y11" s="55"/>
+      <c r="AB11" s="68"/>
+      <c r="AC11" s="59"/>
     </row>
     <row r="12" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B12" s="4"/>
       <c r="C12" s="46"/>
-      <c r="D12" s="56"/>
-      <c r="F12" s="69"/>
+      <c r="D12" s="55"/>
+      <c r="F12" s="68"/>
       <c r="G12" s="46"/>
-      <c r="H12" s="57"/>
+      <c r="H12" s="56"/>
       <c r="I12" s="47"/>
       <c r="J12" s="48"/>
       <c r="K12" s="48"/>
       <c r="L12" s="48"/>
       <c r="M12" s="48"/>
       <c r="N12" s="49"/>
-      <c r="Q12" s="69"/>
+      <c r="Q12" s="68"/>
       <c r="R12" s="46"/>
-      <c r="S12" s="57"/>
-      <c r="T12" s="57"/>
-      <c r="U12" s="57"/>
-      <c r="V12" s="57"/>
-      <c r="W12" s="57"/>
-      <c r="X12" s="57"/>
-      <c r="Y12" s="58"/>
+      <c r="S12" s="56"/>
+      <c r="T12" s="56"/>
+      <c r="U12" s="56"/>
+      <c r="V12" s="56"/>
+      <c r="W12" s="56"/>
+      <c r="X12" s="56"/>
+      <c r="Y12" s="57"/>
       <c r="Z12" s="4"/>
       <c r="AA12" s="4"/>
-      <c r="AB12" s="69"/>
-      <c r="AC12" s="60"/>
+      <c r="AB12" s="68"/>
+      <c r="AC12" s="59"/>
     </row>
     <row r="13" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="66">
-        <f>AVERAGE(R13,G13)</f>
+      <c r="C13" s="65">
+        <f t="shared" ref="C13:C36" si="4">AVERAGE(R13,G13)</f>
         <v>87</v>
       </c>
-      <c r="D13" s="65">
-        <f>H13</f>
+      <c r="D13" s="64">
+        <f t="shared" ref="D13:D26" si="5">H13</f>
         <v>18.210023200000002</v>
       </c>
       <c r="E13" s="4"/>
-      <c r="F13" s="69">
+      <c r="F13" s="68">
         <f>MATCH($B13,ruminants!$A$3:$A$120,0)</f>
         <v>112</v>
       </c>
@@ -7914,7 +8449,7 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F13,G$4)</f>
         <v>87</v>
       </c>
-      <c r="H13" s="78">
+      <c r="H13" s="77">
         <f>( 5.7*J13+9.4*K13+4.1*(L13+M13) ) * 0.004184</f>
         <v>18.210023200000002</v>
       </c>
@@ -7942,7 +8477,7 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F13,N$4)</f>
         <v>18</v>
       </c>
-      <c r="Q13" s="69">
+      <c r="Q13" s="68">
         <f>MATCH($B13,pigs!$A$3:$A$60,0)</f>
         <v>53</v>
       </c>
@@ -7950,23 +8485,23 @@
         <f>INDEX(pigs!$D$3:$AO$60,$Q13,R$4)</f>
         <v>87</v>
       </c>
-      <c r="S13" s="78">
+      <c r="S13" s="77">
         <f>( 5.7*V13+9.4*W13+4.1*(X13) ) * 0.004184</f>
         <v>18.032621599999999</v>
       </c>
-      <c r="T13" s="55">
+      <c r="T13" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q13,T$4)</f>
         <v>12.1</v>
       </c>
-      <c r="U13" s="55">
+      <c r="U13" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q13,U$4)</f>
         <v>12.3</v>
       </c>
-      <c r="V13" s="55">
+      <c r="V13" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q13,V$4)</f>
         <v>121</v>
       </c>
-      <c r="W13" s="55">
+      <c r="W13" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q13,W$4)</f>
         <v>17</v>
       </c>
@@ -7974,15 +8509,15 @@
         <f>1000-SUM(V13:W13,Y13)</f>
         <v>844</v>
       </c>
-      <c r="Y13" s="56">
+      <c r="Y13" s="55">
         <f>INDEX(pigs!$D$3:$AO$60,$Q13,Y$4)</f>
         <v>18</v>
       </c>
-      <c r="AB13" s="69">
+      <c r="AB13" s="68">
         <f>MATCH($B13,poultry!$A$3:$A$41,0)</f>
         <v>35</v>
       </c>
-      <c r="AC13" s="60">
+      <c r="AC13" s="59">
         <f>INDEX(poultry!$D$3:$U$41,$AB13,AC$4)</f>
         <v>87</v>
       </c>
@@ -7991,16 +8526,16 @@
       <c r="B14" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="66">
-        <f>AVERAGE(R14,G14)</f>
+      <c r="C14" s="65">
+        <f t="shared" si="4"/>
         <v>87</v>
       </c>
-      <c r="D14" s="65">
-        <f>H14</f>
+      <c r="D14" s="64">
+        <f t="shared" si="5"/>
         <v>18.089524000000001</v>
       </c>
       <c r="E14" s="4"/>
-      <c r="F14" s="69">
+      <c r="F14" s="68">
         <f>MATCH($B14,ruminants!$A$3:$A$120,0)</f>
         <v>42</v>
       </c>
@@ -8008,8 +8543,8 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F14,G$4)</f>
         <v>87</v>
       </c>
-      <c r="H14" s="78">
-        <f t="shared" ref="H14:H42" si="1">( 5.7*J14+9.4*K14+4.1*(L14+M14) ) * 0.004184</f>
+      <c r="H14" s="77">
+        <f t="shared" ref="H14:H42" si="6">( 5.7*J14+9.4*K14+4.1*(L14+M14) ) * 0.004184</f>
         <v>18.089524000000001</v>
       </c>
       <c r="I14" s="38">
@@ -8036,7 +8571,7 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F14,N$4)</f>
         <v>28</v>
       </c>
-      <c r="Q14" s="69">
+      <c r="Q14" s="68">
         <f>MATCH($B14,pigs!$A$3:$A$60,0)</f>
         <v>13</v>
       </c>
@@ -8044,39 +8579,39 @@
         <f>INDEX(pigs!$D$3:$AO$60,$Q14,R$4)</f>
         <v>87</v>
       </c>
-      <c r="S14" s="78">
-        <f t="shared" ref="S14:S16" si="2">( 5.7*V14+9.4*W14+4.1*(X14) ) * 0.004184</f>
+      <c r="S14" s="77">
+        <f t="shared" ref="S14:S16" si="7">( 5.7*V14+9.4*W14+4.1*(X14) ) * 0.004184</f>
         <v>17.950615200000001</v>
       </c>
-      <c r="T14" s="55">
+      <c r="T14" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q14,T$4)</f>
         <v>11</v>
       </c>
-      <c r="U14" s="55">
+      <c r="U14" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q14,U$4)</f>
         <v>11.2</v>
       </c>
-      <c r="V14" s="55">
+      <c r="V14" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q14,V$4)</f>
         <v>116</v>
       </c>
-      <c r="W14" s="55">
+      <c r="W14" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q14,W$4)</f>
         <v>21</v>
       </c>
       <c r="X14" s="41">
-        <f t="shared" ref="X14:X16" si="3">1000-SUM(V14:W14,Y14)</f>
+        <f t="shared" ref="X14:X16" si="8">1000-SUM(V14:W14,Y14)</f>
         <v>837</v>
       </c>
-      <c r="Y14" s="56">
+      <c r="Y14" s="55">
         <f>INDEX(pigs!$D$3:$AO$60,$Q14,Y$4)</f>
         <v>26</v>
       </c>
-      <c r="AB14" s="69">
+      <c r="AB14" s="68">
         <f>MATCH($B14,poultry!$A$3:$A$41,0)</f>
         <v>16</v>
       </c>
-      <c r="AC14" s="60">
+      <c r="AC14" s="59">
         <f>INDEX(poultry!$D$3:$U$41,$AB14,AC$4)</f>
         <v>87</v>
       </c>
@@ -8085,16 +8620,16 @@
       <c r="B15" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="66">
-        <f>AVERAGE(R15,G15)</f>
+      <c r="C15" s="65">
+        <f t="shared" si="4"/>
         <v>86</v>
       </c>
-      <c r="D15" s="65">
-        <f>H15</f>
+      <c r="D15" s="64">
+        <f t="shared" si="5"/>
         <v>18.6602216</v>
       </c>
       <c r="E15" s="4"/>
-      <c r="F15" s="69">
+      <c r="F15" s="68">
         <f>MATCH($B15,ruminants!$A$3:$A$120,0)</f>
         <v>28</v>
       </c>
@@ -8102,8 +8637,8 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F15,G$4)</f>
         <v>85</v>
       </c>
-      <c r="H15" s="78">
-        <f t="shared" si="1"/>
+      <c r="H15" s="77">
+        <f t="shared" si="6"/>
         <v>18.6602216</v>
       </c>
       <c r="I15" s="38">
@@ -8130,7 +8665,7 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F15,N$4)</f>
         <v>34</v>
       </c>
-      <c r="Q15" s="69">
+      <c r="Q15" s="68">
         <f>MATCH($B15,pigs!$A$3:$A$60,0)</f>
         <v>11</v>
       </c>
@@ -8138,39 +8673,39 @@
         <f>INDEX(pigs!$D$3:$AO$60,$Q15,R$4)</f>
         <v>87</v>
       </c>
-      <c r="S15" s="78">
-        <f t="shared" si="2"/>
+      <c r="S15" s="77">
+        <f t="shared" si="7"/>
         <v>18.580307199999996</v>
       </c>
-      <c r="T15" s="55">
+      <c r="T15" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q15,T$4)</f>
         <v>9</v>
       </c>
-      <c r="U15" s="55">
+      <c r="U15" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q15,U$4)</f>
         <v>9.4</v>
       </c>
-      <c r="V15" s="55">
+      <c r="V15" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q15,V$4)</f>
         <v>111</v>
       </c>
-      <c r="W15" s="55">
+      <c r="W15" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q15,W$4)</f>
         <v>54</v>
       </c>
       <c r="X15" s="41">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>805</v>
       </c>
-      <c r="Y15" s="56">
+      <c r="Y15" s="55">
         <f>INDEX(pigs!$D$3:$AO$60,$Q15,Y$4)</f>
         <v>30</v>
       </c>
-      <c r="AB15" s="69">
+      <c r="AB15" s="68">
         <f>MATCH($B15,poultry!$A$3:$A$41,0)</f>
         <v>10</v>
       </c>
-      <c r="AC15" s="60">
+      <c r="AC15" s="59">
         <f>INDEX(poultry!$D$3:$U$41,$AB15,AC$4)</f>
         <v>87</v>
       </c>
@@ -8179,16 +8714,16 @@
       <c r="B16" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="66">
-        <f>AVERAGE(R16,G16)</f>
+      <c r="C16" s="65">
+        <f t="shared" si="4"/>
         <v>87</v>
       </c>
-      <c r="D16" s="65">
-        <f>H16</f>
+      <c r="D16" s="64">
+        <f t="shared" si="5"/>
         <v>18.2284328</v>
       </c>
       <c r="E16" s="4"/>
-      <c r="F16" s="69">
+      <c r="F16" s="68">
         <f>MATCH($B16,ruminants!$A$3:$A$120,0)</f>
         <v>78</v>
       </c>
@@ -8196,8 +8731,8 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F16,G$4)</f>
         <v>87</v>
       </c>
-      <c r="H16" s="78">
-        <f t="shared" si="1"/>
+      <c r="H16" s="77">
+        <f t="shared" si="6"/>
         <v>18.2284328</v>
       </c>
       <c r="I16" s="38">
@@ -8224,7 +8759,7 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F16,N$4)</f>
         <v>19</v>
       </c>
-      <c r="Q16" s="69">
+      <c r="Q16" s="68">
         <f>MATCH($B16,pigs!$A$3:$A$60,0)</f>
         <v>39</v>
       </c>
@@ -8232,39 +8767,39 @@
         <f>INDEX(pigs!$D$3:$AO$60,$Q16,R$4)</f>
         <v>87</v>
       </c>
-      <c r="S16" s="78">
-        <f t="shared" si="2"/>
+      <c r="S16" s="77">
+        <f t="shared" si="7"/>
         <v>17.846015199999997</v>
       </c>
-      <c r="T16" s="55">
+      <c r="T16" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q16,T$4)</f>
         <v>11.9</v>
       </c>
-      <c r="U16" s="55">
+      <c r="U16" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q16,U$4)</f>
         <v>12</v>
       </c>
-      <c r="V16" s="55">
+      <c r="V16" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q16,V$4)</f>
         <v>110</v>
       </c>
-      <c r="W16" s="55">
+      <c r="W16" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q16,W$4)</f>
         <v>15</v>
       </c>
       <c r="X16" s="41">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>853</v>
       </c>
-      <c r="Y16" s="56">
+      <c r="Y16" s="55">
         <f>INDEX(pigs!$D$3:$AO$60,$Q16,Y$4)</f>
         <v>22</v>
       </c>
-      <c r="AB16" s="69">
+      <c r="AB16" s="68">
         <f>MATCH($B16,poultry!$A$3:$A$41,0)</f>
         <v>31</v>
       </c>
-      <c r="AC16" s="60">
+      <c r="AC16" s="59">
         <f>INDEX(poultry!$D$3:$U$41,$AB16,AC$4)</f>
         <v>89</v>
       </c>
@@ -8273,16 +8808,16 @@
       <c r="B17" t="s">
         <v>313</v>
       </c>
-      <c r="C17" s="66">
-        <f>AVERAGE(R17,G17)</f>
+      <c r="C17" s="65">
+        <f t="shared" si="4"/>
         <v>87</v>
       </c>
-      <c r="D17" s="65">
-        <f>H17</f>
+      <c r="D17" s="64">
+        <f t="shared" si="5"/>
         <v>17.924256</v>
       </c>
       <c r="E17" s="4"/>
-      <c r="F17" s="69">
+      <c r="F17" s="68">
         <f>MATCH($B17,ruminants!$A$3:$A$120,0)</f>
         <v>77</v>
       </c>
@@ -8290,8 +8825,8 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F17,G$4)</f>
         <v>87</v>
       </c>
-      <c r="H17" s="78">
-        <f t="shared" si="1"/>
+      <c r="H17" s="77">
+        <f t="shared" si="6"/>
         <v>17.924256</v>
       </c>
       <c r="I17" s="38">
@@ -8318,23 +8853,23 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F17,N$4)</f>
         <v>20</v>
       </c>
-      <c r="Q17" s="69">
+      <c r="Q17" s="68">
         <f>MATCH($B17,pigs!$A$3:$A$60,0)</f>
         <v>38</v>
       </c>
       <c r="R17" s="37"/>
-      <c r="S17" s="55"/>
-      <c r="T17" s="55"/>
-      <c r="U17" s="55"/>
-      <c r="V17" s="55"/>
-      <c r="W17" s="55"/>
-      <c r="X17" s="55"/>
-      <c r="Y17" s="56"/>
-      <c r="AB17" s="69">
+      <c r="S17" s="54"/>
+      <c r="T17" s="54"/>
+      <c r="U17" s="54"/>
+      <c r="V17" s="54"/>
+      <c r="W17" s="54"/>
+      <c r="X17" s="54"/>
+      <c r="Y17" s="55"/>
+      <c r="AB17" s="68">
         <f>MATCH($B17,poultry!$A$3:$A$41,0)</f>
         <v>30</v>
       </c>
-      <c r="AC17" s="60">
+      <c r="AC17" s="59">
         <f>INDEX(poultry!$D$3:$U$41,$AB17,AC$4)</f>
         <v>87</v>
       </c>
@@ -8343,16 +8878,16 @@
       <c r="B18" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="66">
-        <f>AVERAGE(R18,G18)</f>
+      <c r="C18" s="65">
+        <f t="shared" si="4"/>
         <v>67.5</v>
       </c>
-      <c r="D18" s="65">
-        <f>H18</f>
+      <c r="D18" s="64">
+        <f t="shared" si="5"/>
         <v>18.3899352</v>
       </c>
       <c r="E18" s="4"/>
-      <c r="F18" s="69">
+      <c r="F18" s="68">
         <f>MATCH($B18,ruminants!$A$3:$A$120,0)</f>
         <v>53</v>
       </c>
@@ -8360,8 +8895,8 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F18,G$4)</f>
         <v>48</v>
       </c>
-      <c r="H18" s="78">
-        <f t="shared" si="1"/>
+      <c r="H18" s="77">
+        <f t="shared" si="6"/>
         <v>18.3899352</v>
       </c>
       <c r="I18" s="38">
@@ -8388,7 +8923,7 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F18,N$4)</f>
         <v>23</v>
       </c>
-      <c r="Q18" s="69">
+      <c r="Q18" s="68">
         <f>MATCH($B18,pigs!$A$3:$A$60,0)</f>
         <v>19</v>
       </c>
@@ -8396,39 +8931,39 @@
         <f>INDEX(pigs!$D$3:$AO$60,$Q18,R$4)</f>
         <v>87</v>
       </c>
-      <c r="S18" s="78">
-        <f t="shared" ref="S18:S23" si="4">( 5.7*V18+9.4*W18+4.1*(X18) ) * 0.004184</f>
+      <c r="S18" s="77">
+        <f t="shared" ref="S18:S23" si="9">( 5.7*V18+9.4*W18+4.1*(X18) ) * 0.004184</f>
         <v>18.4970456</v>
       </c>
-      <c r="T18" s="55">
+      <c r="T18" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q18,T$4)</f>
         <v>12.8</v>
       </c>
-      <c r="U18" s="55">
+      <c r="U18" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q18,U$4)</f>
         <v>13.2</v>
       </c>
-      <c r="V18" s="55">
+      <c r="V18" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q18,V$4)</f>
         <v>94</v>
       </c>
-      <c r="W18" s="55">
+      <c r="W18" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q18,W$4)</f>
         <v>43</v>
       </c>
       <c r="X18" s="41">
-        <f t="shared" ref="X18:X23" si="5">1000-SUM(V18:W18,Y18)</f>
+        <f t="shared" ref="X18:X23" si="10">1000-SUM(V18:W18,Y18)</f>
         <v>849</v>
       </c>
-      <c r="Y18" s="56">
+      <c r="Y18" s="55">
         <f>INDEX(pigs!$D$3:$AO$60,$Q18,Y$4)</f>
         <v>14</v>
       </c>
-      <c r="AB18" s="69">
+      <c r="AB18" s="68">
         <f>MATCH($B18,poultry!$A$3:$A$41,0)</f>
         <v>24</v>
       </c>
-      <c r="AC18" s="60">
+      <c r="AC18" s="59">
         <f>INDEX(poultry!$D$3:$U$41,$AB18,AC$4)</f>
         <v>87</v>
       </c>
@@ -8437,16 +8972,16 @@
       <c r="B19" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="66">
-        <f>AVERAGE(R19,G19)</f>
+      <c r="C19" s="65">
+        <f t="shared" si="4"/>
         <v>87</v>
       </c>
-      <c r="D19" s="65">
-        <f>H19</f>
+      <c r="D19" s="64">
+        <f t="shared" si="5"/>
         <v>18.478217600000001</v>
       </c>
       <c r="E19" s="4"/>
-      <c r="F19" s="69">
+      <c r="F19" s="68">
         <f>MATCH($B19,ruminants!$A$3:$A$120,0)</f>
         <v>115</v>
       </c>
@@ -8454,8 +8989,8 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F19,G$4)</f>
         <v>87</v>
       </c>
-      <c r="H19" s="78">
-        <f t="shared" si="1"/>
+      <c r="H19" s="77">
+        <f t="shared" si="6"/>
         <v>18.478217600000001</v>
       </c>
       <c r="I19" s="38">
@@ -8482,7 +9017,7 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F19,N$4)</f>
         <v>33</v>
       </c>
-      <c r="Q19" s="69">
+      <c r="Q19" s="68">
         <f>MATCH($B19,pigs!$A$3:$A$60,0)</f>
         <v>56</v>
       </c>
@@ -8490,39 +9025,39 @@
         <f>INDEX(pigs!$D$3:$AO$60,$Q19,R$4)</f>
         <v>87</v>
       </c>
-      <c r="S19" s="78">
-        <f t="shared" si="4"/>
+      <c r="S19" s="77">
+        <f t="shared" si="9"/>
         <v>18.420059999999999</v>
       </c>
-      <c r="T19" s="55">
+      <c r="T19" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q19,T$4)</f>
         <v>11.2</v>
       </c>
-      <c r="U19" s="55">
+      <c r="U19" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q19,U$4)</f>
         <v>11.5</v>
       </c>
-      <c r="V19" s="55">
+      <c r="V19" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q19,V$4)</f>
         <v>239</v>
       </c>
-      <c r="W19" s="55">
+      <c r="W19" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q19,W$4)</f>
         <v>12</v>
       </c>
       <c r="X19" s="41">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>714</v>
       </c>
-      <c r="Y19" s="56">
+      <c r="Y19" s="55">
         <f>INDEX(pigs!$D$3:$AO$60,$Q19,Y$4)</f>
         <v>35</v>
       </c>
-      <c r="AB19" s="69">
+      <c r="AB19" s="68">
         <f>MATCH($B19,poultry!$A$3:$A$41,0)</f>
         <v>39</v>
       </c>
-      <c r="AC19" s="60">
+      <c r="AC19" s="59">
         <f>INDEX(poultry!$D$3:$U$41,$AB19,AC$4)</f>
         <v>87</v>
       </c>
@@ -8531,21 +9066,21 @@
       <c r="B20" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="66">
-        <f>AVERAGE(R20,G20)</f>
+      <c r="C20" s="65">
+        <f t="shared" si="4"/>
         <v>86.8</v>
       </c>
-      <c r="D20" s="65">
-        <f>H20</f>
+      <c r="D20" s="64">
+        <f t="shared" si="5"/>
         <v>18.737207199999997</v>
       </c>
       <c r="E20" s="4"/>
-      <c r="F20" s="69"/>
-      <c r="G20" s="66">
+      <c r="F20" s="68"/>
+      <c r="G20" s="65">
         <v>86.6</v>
       </c>
-      <c r="H20" s="78">
-        <f t="shared" si="1"/>
+      <c r="H20" s="77">
+        <f t="shared" si="6"/>
         <v>18.737207199999997</v>
       </c>
       <c r="I20" s="38">
@@ -8573,7 +9108,7 @@
       <c r="P20" s="11" t="s">
         <v>490</v>
       </c>
-      <c r="Q20" s="69">
+      <c r="Q20" s="68">
         <f>MATCH($B20,pigs!$A$3:$A$60,0)</f>
         <v>57</v>
       </c>
@@ -8581,51 +9116,51 @@
         <f>INDEX(pigs!$D$3:$AO$60,$Q20,R$4)</f>
         <v>87</v>
       </c>
-      <c r="S20" s="78">
-        <f t="shared" si="4"/>
+      <c r="S20" s="77">
+        <f t="shared" si="9"/>
         <v>18.821305599999999</v>
       </c>
-      <c r="T20" s="55">
+      <c r="T20" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q20,T$4)</f>
         <v>10.7</v>
       </c>
-      <c r="U20" s="55">
+      <c r="U20" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q20,U$4)</f>
         <v>10.9</v>
       </c>
-      <c r="V20" s="55">
+      <c r="V20" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q20,V$4)</f>
         <v>311</v>
       </c>
-      <c r="W20" s="55">
+      <c r="W20" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q20,W$4)</f>
         <v>13</v>
       </c>
       <c r="X20" s="41">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>635</v>
       </c>
-      <c r="Y20" s="56">
+      <c r="Y20" s="55">
         <f>INDEX(pigs!$D$3:$AO$60,$Q20,Y$4)</f>
         <v>41</v>
       </c>
-      <c r="AB20" s="69"/>
-      <c r="AC20" s="60"/>
+      <c r="AB20" s="68"/>
+      <c r="AC20" s="59"/>
     </row>
     <row r="21" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="66">
-        <f>AVERAGE(R21,G21)</f>
+      <c r="C21" s="65">
+        <f t="shared" si="4"/>
         <v>92.5</v>
       </c>
-      <c r="D21" s="65">
-        <f>H21</f>
+      <c r="D21" s="64">
+        <f t="shared" si="5"/>
         <v>27.903096000000001</v>
       </c>
       <c r="E21" s="4"/>
-      <c r="F21" s="69">
+      <c r="F21" s="68">
         <f>MATCH($B21,ruminants!$A$3:$A$120,0)</f>
         <v>71</v>
       </c>
@@ -8633,8 +9168,8 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F21,G$4)</f>
         <v>93</v>
       </c>
-      <c r="H21" s="78">
-        <f t="shared" si="1"/>
+      <c r="H21" s="77">
+        <f t="shared" si="6"/>
         <v>27.903096000000001</v>
       </c>
       <c r="I21" s="38">
@@ -8661,7 +9196,7 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F21,N$4)</f>
         <v>50</v>
       </c>
-      <c r="Q21" s="69">
+      <c r="Q21" s="68">
         <f>MATCH($B21,pigs!$A$3:$A$60,0)</f>
         <v>33</v>
       </c>
@@ -8669,51 +9204,51 @@
         <f>INDEX(pigs!$D$3:$AO$60,$Q21,R$4)</f>
         <v>92</v>
       </c>
-      <c r="S21" s="78">
-        <f t="shared" si="4"/>
+      <c r="S21" s="77">
+        <f t="shared" si="9"/>
         <v>27.892217599999999</v>
       </c>
-      <c r="T21" s="55">
+      <c r="T21" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q21,T$4)</f>
         <v>18</v>
       </c>
-      <c r="U21" s="55">
+      <c r="U21" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q21,U$4)</f>
         <v>18.5</v>
       </c>
-      <c r="V21" s="55">
+      <c r="V21" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q21,V$4)</f>
         <v>207</v>
       </c>
-      <c r="W21" s="55">
+      <c r="W21" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q21,W$4)</f>
         <v>455</v>
       </c>
       <c r="X21" s="41">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>295</v>
       </c>
-      <c r="Y21" s="56">
+      <c r="Y21" s="55">
         <f>INDEX(pigs!$D$3:$AO$60,$Q21,Y$4)</f>
         <v>43</v>
       </c>
-      <c r="AB21" s="69"/>
-      <c r="AC21" s="60"/>
+      <c r="AB21" s="68"/>
+      <c r="AC21" s="59"/>
     </row>
     <row r="22" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="66">
-        <f>AVERAGE(R22,G22)</f>
+      <c r="C22" s="65">
+        <f t="shared" si="4"/>
         <v>92</v>
       </c>
-      <c r="D22" s="65">
-        <f>H22</f>
+      <c r="D22" s="64">
+        <f t="shared" si="5"/>
         <v>26.501456000000001</v>
       </c>
       <c r="E22" s="4"/>
-      <c r="F22" s="69">
+      <c r="F22" s="68">
         <f>MATCH($B22,ruminants!$A$3:$A$120,0)</f>
         <v>45</v>
       </c>
@@ -8721,8 +9256,8 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F22,G$4)</f>
         <v>93</v>
       </c>
-      <c r="H22" s="78">
-        <f t="shared" si="1"/>
+      <c r="H22" s="77">
+        <f t="shared" si="6"/>
         <v>26.501456000000001</v>
       </c>
       <c r="I22" s="38">
@@ -8749,7 +9284,7 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F22,N$4)</f>
         <v>40</v>
       </c>
-      <c r="Q22" s="69">
+      <c r="Q22" s="68">
         <f>MATCH($B22,pigs!$A$3:$A$60,0)</f>
         <v>14</v>
       </c>
@@ -8757,56 +9292,56 @@
         <f>INDEX(pigs!$D$3:$AO$60,$Q22,R$4)</f>
         <v>91</v>
       </c>
-      <c r="S22" s="78">
-        <f t="shared" si="4"/>
+      <c r="S22" s="77">
+        <f t="shared" si="9"/>
         <v>27.712724000000005</v>
       </c>
-      <c r="T22" s="55">
+      <c r="T22" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q22,T$4)</f>
         <v>17.3</v>
       </c>
-      <c r="U22" s="55">
+      <c r="U22" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q22,U$4)</f>
         <v>17.5</v>
       </c>
-      <c r="V22" s="55">
+      <c r="V22" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q22,V$4)</f>
         <v>227</v>
       </c>
-      <c r="W22" s="55">
+      <c r="W22" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q22,W$4)</f>
         <v>437</v>
       </c>
       <c r="X22" s="41">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>298</v>
       </c>
-      <c r="Y22" s="56">
+      <c r="Y22" s="55">
         <f>INDEX(pigs!$D$3:$AO$60,$Q22,Y$4)</f>
         <v>38</v>
       </c>
-      <c r="AB22" s="69"/>
-      <c r="AC22" s="60"/>
+      <c r="AB22" s="68"/>
+      <c r="AC22" s="59"/>
     </row>
     <row r="23" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>310</v>
       </c>
-      <c r="C23" s="66">
-        <f>AVERAGE(R23,G23)</f>
+      <c r="C23" s="65">
+        <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="D23" s="65">
-        <f>H23</f>
+      <c r="D23" s="64">
+        <f t="shared" si="5"/>
         <v>39.329599999999999</v>
       </c>
       <c r="E23" s="4"/>
-      <c r="F23" s="69"/>
+      <c r="F23" s="68"/>
       <c r="G23" s="37">
         <v>100</v>
       </c>
-      <c r="H23" s="78">
-        <f t="shared" si="1"/>
+      <c r="H23" s="77">
+        <f t="shared" si="6"/>
         <v>39.329599999999999</v>
       </c>
       <c r="I23" s="38">
@@ -8825,7 +9360,7 @@
       <c r="P23" t="s">
         <v>490</v>
       </c>
-      <c r="Q23" s="69">
+      <c r="Q23" s="68">
         <f>MATCH($B23,pigs!$A$3:$A$60,0)</f>
         <v>28</v>
       </c>
@@ -8833,39 +9368,39 @@
         <f>INDEX(pigs!$D$3:$AO$60,$Q23,R$4)</f>
         <v>100</v>
       </c>
-      <c r="S23" s="78">
-        <f t="shared" si="4"/>
+      <c r="S23" s="77">
+        <f t="shared" si="9"/>
         <v>39.329599999999999</v>
       </c>
-      <c r="T23" s="55">
+      <c r="T23" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q23,T$4)</f>
         <v>29.8</v>
       </c>
-      <c r="U23" s="55">
+      <c r="U23" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q23,U$4)</f>
         <v>29.8</v>
       </c>
-      <c r="V23" s="55">
+      <c r="V23" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q23,V$4)</f>
         <v>0</v>
       </c>
-      <c r="W23" s="55">
+      <c r="W23" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q23,W$4)</f>
         <v>1000</v>
       </c>
       <c r="X23" s="41">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Y23" s="56">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="55">
         <f>INDEX(pigs!$D$3:$AO$60,$Q23,Y$4)</f>
         <v>0</v>
       </c>
-      <c r="AB23" s="69">
+      <c r="AB23" s="68">
         <f>MATCH($B23,poultry!$A$3:$A$41,0)</f>
         <v>1</v>
       </c>
-      <c r="AC23" s="60">
+      <c r="AC23" s="59">
         <f>INDEX(poultry!$D$3:$U$41,$AB23,AC$4)</f>
         <v>99</v>
       </c>
@@ -8874,16 +9409,16 @@
       <c r="B24" t="s">
         <v>302</v>
       </c>
-      <c r="C24" s="66">
-        <f>AVERAGE(R24,G24)</f>
+      <c r="C24" s="65">
+        <f t="shared" si="4"/>
         <v>85</v>
       </c>
-      <c r="D24" s="65">
-        <f>H24</f>
+      <c r="D24" s="64">
+        <f t="shared" si="5"/>
         <v>16.927627199999996</v>
       </c>
       <c r="E24" s="4"/>
-      <c r="F24" s="69">
+      <c r="F24" s="68">
         <f>MATCH($B24,ruminants!$A$3:$A$120,0)</f>
         <v>22</v>
       </c>
@@ -8891,8 +9426,8 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F24,G$4)</f>
         <v>85</v>
       </c>
-      <c r="H24" s="78">
-        <f t="shared" si="1"/>
+      <c r="H24" s="77">
+        <f t="shared" si="6"/>
         <v>16.927627199999996</v>
       </c>
       <c r="I24" s="38">
@@ -8919,32 +9454,32 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F24,N$4)</f>
         <v>66</v>
       </c>
-      <c r="Q24" s="69"/>
+      <c r="Q24" s="68"/>
       <c r="R24" s="37"/>
-      <c r="S24" s="55"/>
-      <c r="T24" s="55"/>
-      <c r="U24" s="55"/>
-      <c r="V24" s="55"/>
-      <c r="W24" s="55"/>
-      <c r="X24" s="55"/>
-      <c r="Y24" s="56"/>
-      <c r="AB24" s="69"/>
-      <c r="AC24" s="60"/>
+      <c r="S24" s="54"/>
+      <c r="T24" s="54"/>
+      <c r="U24" s="54"/>
+      <c r="V24" s="54"/>
+      <c r="W24" s="54"/>
+      <c r="X24" s="54"/>
+      <c r="Y24" s="55"/>
+      <c r="AB24" s="68"/>
+      <c r="AC24" s="59"/>
     </row>
     <row r="25" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>314</v>
       </c>
-      <c r="C25" s="66">
-        <f>AVERAGE(R25,G25)</f>
+      <c r="C25" s="65">
+        <f t="shared" si="4"/>
         <v>87</v>
       </c>
-      <c r="D25" s="65">
-        <f>H25</f>
+      <c r="D25" s="64">
+        <f t="shared" si="5"/>
         <v>22.965976000000001</v>
       </c>
       <c r="E25" s="4"/>
-      <c r="F25" s="69">
+      <c r="F25" s="68">
         <f>MATCH($B25,ruminants!$A$3:$A$120,0)</f>
         <v>92</v>
       </c>
@@ -8952,8 +9487,8 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F25,G$4)</f>
         <v>87</v>
       </c>
-      <c r="H25" s="78">
-        <f t="shared" si="1"/>
+      <c r="H25" s="77">
+        <f t="shared" si="6"/>
         <v>22.965976000000001</v>
       </c>
       <c r="I25" s="38">
@@ -8980,32 +9515,32 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F25,N$4)</f>
         <v>50</v>
       </c>
-      <c r="Q25" s="69"/>
+      <c r="Q25" s="68"/>
       <c r="R25" s="37"/>
-      <c r="S25" s="55"/>
-      <c r="T25" s="55"/>
-      <c r="U25" s="55"/>
-      <c r="V25" s="55"/>
-      <c r="W25" s="55"/>
-      <c r="X25" s="55"/>
-      <c r="Y25" s="56"/>
-      <c r="AB25" s="69"/>
-      <c r="AC25" s="60"/>
+      <c r="S25" s="54"/>
+      <c r="T25" s="54"/>
+      <c r="U25" s="54"/>
+      <c r="V25" s="54"/>
+      <c r="W25" s="54"/>
+      <c r="X25" s="54"/>
+      <c r="Y25" s="55"/>
+      <c r="AB25" s="68"/>
+      <c r="AC25" s="59"/>
     </row>
     <row r="26" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>44</v>
       </c>
-      <c r="C26" s="66">
-        <f>AVERAGE(R26,G26)</f>
+      <c r="C26" s="65">
+        <f t="shared" si="4"/>
         <v>87.5</v>
       </c>
-      <c r="D26" s="65">
-        <f>H26</f>
+      <c r="D26" s="64">
+        <f t="shared" si="5"/>
         <v>19.589487999999999</v>
       </c>
       <c r="E26" s="4"/>
-      <c r="F26" s="69">
+      <c r="F26" s="68">
         <f>MATCH($B26,ruminants!$A$3:$A$120,0)</f>
         <v>93</v>
       </c>
@@ -9013,8 +9548,8 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F26,G$4)</f>
         <v>87</v>
       </c>
-      <c r="H26" s="78">
-        <f t="shared" si="1"/>
+      <c r="H26" s="77">
+        <f t="shared" si="6"/>
         <v>19.589487999999999</v>
       </c>
       <c r="I26" s="38">
@@ -9041,7 +9576,7 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F26,N$4)</f>
         <v>70</v>
       </c>
-      <c r="Q26" s="69">
+      <c r="Q26" s="68">
         <f>MATCH($B26,pigs!$A$3:$A$60,0)</f>
         <v>43</v>
       </c>
@@ -9049,39 +9584,39 @@
         <f>INDEX(pigs!$D$3:$AO$60,$Q26,R$4)</f>
         <v>88</v>
       </c>
-      <c r="S26" s="78">
-        <f t="shared" ref="S26:S30" si="6">( 5.7*V26+9.4*W26+4.1*(X26) ) * 0.004184</f>
+      <c r="S26" s="77">
+        <f t="shared" ref="S26:S30" si="11">( 5.7*V26+9.4*W26+4.1*(X26) ) * 0.004184</f>
         <v>19.822118400000001</v>
       </c>
-      <c r="T26" s="55">
+      <c r="T26" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q26,T$4)</f>
         <v>9.3000000000000007</v>
       </c>
-      <c r="U26" s="55">
+      <c r="U26" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q26,U$4)</f>
         <v>9.9</v>
       </c>
-      <c r="V26" s="55">
+      <c r="V26" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q26,V$4)</f>
         <v>516</v>
       </c>
-      <c r="W26" s="55">
+      <c r="W26" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q26,W$4)</f>
         <v>21</v>
       </c>
       <c r="X26" s="41">
-        <f t="shared" ref="X26:X30" si="7">1000-SUM(V26:W26,Y26)</f>
+        <f t="shared" ref="X26:X30" si="12">1000-SUM(V26:W26,Y26)</f>
         <v>390</v>
       </c>
-      <c r="Y26" s="56">
+      <c r="Y26" s="55">
         <f>INDEX(pigs!$D$3:$AO$60,$Q26,Y$4)</f>
         <v>73</v>
       </c>
-      <c r="AB26" s="69">
+      <c r="AB26" s="68">
         <f>MATCH($B26,poultry!$A$3:$A$41,0)</f>
         <v>33</v>
       </c>
-      <c r="AC26" s="60">
+      <c r="AC26" s="59">
         <f>INDEX(poultry!$D$3:$U$41,$AB26,AC$4)</f>
         <v>87</v>
       </c>
@@ -9090,25 +9625,25 @@
       <c r="B27" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="66">
-        <f>AVERAGE(R27,G27)</f>
+      <c r="C27" s="65">
+        <f t="shared" si="4"/>
         <v>87</v>
       </c>
-      <c r="D27" s="65">
+      <c r="D27" s="64">
         <f>S27</f>
         <v>20.560594400000003</v>
       </c>
       <c r="E27" s="4"/>
-      <c r="F27" s="69"/>
+      <c r="F27" s="68"/>
       <c r="G27" s="37"/>
-      <c r="H27" s="55"/>
+      <c r="H27" s="54"/>
       <c r="I27" s="38"/>
       <c r="J27" s="39"/>
       <c r="K27" s="39"/>
       <c r="L27" s="39"/>
       <c r="M27" s="39"/>
       <c r="N27" s="42"/>
-      <c r="Q27" s="69">
+      <c r="Q27" s="68">
         <f>MATCH($B27,pigs!$A$3:$A$60,0)</f>
         <v>45</v>
       </c>
@@ -9116,51 +9651,51 @@
         <f>INDEX(pigs!$D$3:$AO$60,$Q27,R$4)</f>
         <v>87</v>
       </c>
-      <c r="S27" s="78">
-        <f t="shared" si="6"/>
+      <c r="S27" s="77">
+        <f t="shared" si="11"/>
         <v>20.560594400000003</v>
       </c>
-      <c r="T27" s="55">
+      <c r="T27" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q27,T$4)</f>
         <v>9.6999999999999993</v>
       </c>
-      <c r="U27" s="55">
+      <c r="U27" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q27,U$4)</f>
         <v>10.3</v>
       </c>
-      <c r="V27" s="55">
+      <c r="V27" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q27,V$4)</f>
         <v>609</v>
       </c>
-      <c r="W27" s="55">
+      <c r="W27" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q27,W$4)</f>
         <v>27</v>
       </c>
       <c r="X27" s="41">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>290</v>
       </c>
-      <c r="Y27" s="56">
+      <c r="Y27" s="55">
         <f>INDEX(pigs!$D$3:$AO$60,$Q27,Y$4)</f>
         <v>74</v>
       </c>
-      <c r="AB27" s="69"/>
-      <c r="AC27" s="60"/>
+      <c r="AB27" s="68"/>
+      <c r="AC27" s="59"/>
     </row>
     <row r="28" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>36</v>
       </c>
-      <c r="C28" s="66">
-        <f>AVERAGE(R28,G28)</f>
+      <c r="C28" s="65">
+        <f t="shared" si="4"/>
         <v>89.5</v>
       </c>
-      <c r="D28" s="65">
-        <f>H28</f>
+      <c r="D28" s="64">
+        <f t="shared" ref="D28:D34" si="13">H28</f>
         <v>19.4920008</v>
       </c>
       <c r="E28" s="4"/>
-      <c r="F28" s="69">
+      <c r="F28" s="68">
         <f>MATCH($B28,ruminants!$A$3:$A$120,0)</f>
         <v>70</v>
       </c>
@@ -9168,8 +9703,8 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F28,G$4)</f>
         <v>90</v>
       </c>
-      <c r="H28" s="78">
-        <f t="shared" si="1"/>
+      <c r="H28" s="77">
+        <f t="shared" si="6"/>
         <v>19.4920008</v>
       </c>
       <c r="I28" s="38">
@@ -9196,7 +9731,7 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F28,N$4)</f>
         <v>75</v>
       </c>
-      <c r="Q28" s="69">
+      <c r="Q28" s="68">
         <f>MATCH($B28,pigs!$A$3:$A$60,0)</f>
         <v>36</v>
       </c>
@@ -9204,39 +9739,39 @@
         <f>INDEX(pigs!$D$3:$AO$60,$Q28,R$4)</f>
         <v>89</v>
       </c>
-      <c r="S28" s="78">
-        <f t="shared" si="6"/>
+      <c r="S28" s="77">
+        <f t="shared" si="11"/>
         <v>18.9196296</v>
       </c>
-      <c r="T28" s="55">
+      <c r="T28" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q28,T$4)</f>
         <v>7.1</v>
       </c>
-      <c r="U28" s="55">
+      <c r="U28" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q28,U$4)</f>
         <v>7.7</v>
       </c>
-      <c r="V28" s="55">
+      <c r="V28" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q28,V$4)</f>
         <v>380</v>
       </c>
-      <c r="W28" s="55">
+      <c r="W28" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q28,W$4)</f>
         <v>26</v>
       </c>
       <c r="X28" s="41">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>515</v>
       </c>
-      <c r="Y28" s="56">
+      <c r="Y28" s="55">
         <f>INDEX(pigs!$D$3:$AO$60,$Q28,Y$4)</f>
         <v>79</v>
       </c>
-      <c r="AB28" s="69">
+      <c r="AB28" s="68">
         <f>MATCH($B28,poultry!$A$3:$A$41,0)</f>
         <v>29</v>
       </c>
-      <c r="AC28" s="60">
+      <c r="AC28" s="59">
         <f>INDEX(poultry!$D$3:$U$41,$AB28,AC$4)</f>
         <v>90</v>
       </c>
@@ -9245,16 +9780,16 @@
       <c r="B29" t="s">
         <v>46</v>
       </c>
-      <c r="C29" s="66">
-        <f>AVERAGE(R29,G29)</f>
+      <c r="C29" s="65">
+        <f t="shared" si="4"/>
         <v>91</v>
       </c>
-      <c r="D29" s="65">
-        <f>H29</f>
+      <c r="D29" s="64">
+        <f t="shared" si="13"/>
         <v>19.083224000000001</v>
       </c>
       <c r="E29" s="4"/>
-      <c r="F29" s="69">
+      <c r="F29" s="68">
         <f>MATCH($B29,ruminants!$A$3:$A$120,0)</f>
         <v>99</v>
       </c>
@@ -9262,8 +9797,8 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F29,G$4)</f>
         <v>92</v>
       </c>
-      <c r="H29" s="78">
-        <f t="shared" si="1"/>
+      <c r="H29" s="77">
+        <f t="shared" si="6"/>
         <v>19.083224000000001</v>
       </c>
       <c r="I29" s="38">
@@ -9290,7 +9825,7 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F29,N$4)</f>
         <v>80</v>
       </c>
-      <c r="Q29" s="69">
+      <c r="Q29" s="68">
         <f>MATCH($B29,pigs!$A$3:$A$60,0)</f>
         <v>46</v>
       </c>
@@ -9298,51 +9833,51 @@
         <f>INDEX(pigs!$D$3:$AO$60,$Q29,R$4)</f>
         <v>90</v>
       </c>
-      <c r="S29" s="78">
-        <f t="shared" si="6"/>
+      <c r="S29" s="77">
+        <f t="shared" si="11"/>
         <v>18.786160000000002</v>
       </c>
-      <c r="T29" s="55">
+      <c r="T29" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q29,T$4)</f>
         <v>5.9</v>
       </c>
-      <c r="U29" s="55">
+      <c r="U29" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q29,U$4)</f>
         <v>6.5</v>
       </c>
-      <c r="V29" s="55">
+      <c r="V29" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q29,V$4)</f>
         <v>373</v>
       </c>
-      <c r="W29" s="55">
+      <c r="W29" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q29,W$4)</f>
         <v>19</v>
       </c>
       <c r="X29" s="41">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>533</v>
       </c>
-      <c r="Y29" s="56">
+      <c r="Y29" s="55">
         <f>INDEX(pigs!$D$3:$AO$60,$Q29,Y$4)</f>
         <v>75</v>
       </c>
-      <c r="AB29" s="69"/>
-      <c r="AC29" s="60"/>
+      <c r="AB29" s="68"/>
+      <c r="AC29" s="59"/>
     </row>
     <row r="30" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>47</v>
       </c>
-      <c r="C30" s="66">
-        <f>AVERAGE(R30,G30)</f>
+      <c r="C30" s="65">
+        <f t="shared" si="4"/>
         <v>91</v>
       </c>
-      <c r="D30" s="65">
-        <f>H30</f>
+      <c r="D30" s="64">
+        <f t="shared" si="13"/>
         <v>19.581538399999999</v>
       </c>
       <c r="E30" s="4"/>
-      <c r="F30" s="69">
+      <c r="F30" s="68">
         <f>MATCH($B30,ruminants!$A$3:$A$120,0)</f>
         <v>60</v>
       </c>
@@ -9350,8 +9885,8 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F30,G$4)</f>
         <v>91</v>
       </c>
-      <c r="H30" s="78">
-        <f t="shared" si="1"/>
+      <c r="H30" s="77">
+        <f t="shared" si="6"/>
         <v>19.581538399999999</v>
       </c>
       <c r="I30" s="38">
@@ -9378,7 +9913,7 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F30,N$4)</f>
         <v>44</v>
       </c>
-      <c r="Q30" s="69">
+      <c r="Q30" s="68">
         <f>MATCH($B30,pigs!$A$3:$A$60,0)</f>
         <v>29</v>
       </c>
@@ -9386,56 +9921,56 @@
         <f>INDEX(pigs!$D$3:$AO$60,$Q30,R$4)</f>
         <v>91</v>
       </c>
-      <c r="S30" s="78">
-        <f t="shared" si="6"/>
+      <c r="S30" s="77">
+        <f t="shared" si="11"/>
         <v>19.540953599999998</v>
       </c>
-      <c r="T30" s="55">
+      <c r="T30" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q30,T$4)</f>
         <v>5.4</v>
       </c>
-      <c r="U30" s="55">
+      <c r="U30" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q30,U$4)</f>
         <v>6.2</v>
       </c>
-      <c r="V30" s="55">
+      <c r="V30" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q30,V$4)</f>
         <v>163</v>
       </c>
-      <c r="W30" s="55">
+      <c r="W30" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q30,W$4)</f>
         <v>94</v>
       </c>
       <c r="X30" s="41">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>697</v>
       </c>
-      <c r="Y30" s="56">
+      <c r="Y30" s="55">
         <f>INDEX(pigs!$D$3:$AO$60,$Q30,Y$4)</f>
         <v>46</v>
       </c>
-      <c r="AB30" s="69"/>
-      <c r="AC30" s="60"/>
+      <c r="AB30" s="68"/>
+      <c r="AC30" s="59"/>
     </row>
     <row r="31" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>315</v>
       </c>
-      <c r="C31" s="66">
-        <f>AVERAGE(R31,G31)</f>
+      <c r="C31" s="65">
+        <f t="shared" si="4"/>
         <v>90</v>
       </c>
-      <c r="D31" s="65">
-        <f>H31</f>
+      <c r="D31" s="64">
+        <f t="shared" si="13"/>
         <v>16.971140800000001</v>
       </c>
       <c r="E31" s="4"/>
-      <c r="F31" s="69"/>
+      <c r="F31" s="68"/>
       <c r="G31" s="37">
         <v>90</v>
       </c>
-      <c r="H31" s="78">
-        <f t="shared" si="1"/>
+      <c r="H31" s="77">
+        <f t="shared" si="6"/>
         <v>16.971140800000001</v>
       </c>
       <c r="I31" s="38">
@@ -9463,32 +9998,32 @@
       <c r="P31" s="11" t="s">
         <v>490</v>
       </c>
-      <c r="Q31" s="69"/>
+      <c r="Q31" s="68"/>
       <c r="R31" s="37"/>
-      <c r="S31" s="55"/>
-      <c r="T31" s="55"/>
-      <c r="U31" s="55"/>
-      <c r="V31" s="55"/>
-      <c r="W31" s="55"/>
-      <c r="X31" s="55"/>
-      <c r="Y31" s="56"/>
-      <c r="AB31" s="69"/>
-      <c r="AC31" s="60"/>
+      <c r="S31" s="54"/>
+      <c r="T31" s="54"/>
+      <c r="U31" s="54"/>
+      <c r="V31" s="54"/>
+      <c r="W31" s="54"/>
+      <c r="X31" s="54"/>
+      <c r="Y31" s="55"/>
+      <c r="AB31" s="68"/>
+      <c r="AC31" s="59"/>
     </row>
     <row r="32" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="66">
-        <f>AVERAGE(R32,G32)</f>
+      <c r="C32" s="65">
+        <f t="shared" si="4"/>
         <v>87</v>
       </c>
-      <c r="D32" s="65">
-        <f>H32</f>
+      <c r="D32" s="64">
+        <f t="shared" si="13"/>
         <v>18.194124000000002</v>
       </c>
       <c r="E32" s="4"/>
-      <c r="F32" s="69">
+      <c r="F32" s="68">
         <f>MATCH($B32,ruminants!$A$3:$A$120,0)</f>
         <v>111</v>
       </c>
@@ -9496,8 +10031,8 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F32,G$4)</f>
         <v>87</v>
       </c>
-      <c r="H32" s="78">
-        <f t="shared" si="1"/>
+      <c r="H32" s="77">
+        <f t="shared" si="6"/>
         <v>18.194124000000002</v>
       </c>
       <c r="I32" s="38">
@@ -9524,7 +10059,7 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F32,N$4)</f>
         <v>60</v>
       </c>
-      <c r="Q32" s="69">
+      <c r="Q32" s="68">
         <f>MATCH($B32,pigs!$A$3:$A$60,0)</f>
         <v>55</v>
       </c>
@@ -9532,39 +10067,39 @@
         <f>INDEX(pigs!$D$3:$AO$60,$Q32,R$4)</f>
         <v>87</v>
       </c>
-      <c r="S32" s="78">
-        <f t="shared" ref="S32:S37" si="8">( 5.7*V32+9.4*W32+4.1*(X32) ) * 0.004184</f>
+      <c r="S32" s="77">
+        <f t="shared" ref="S32:S37" si="14">( 5.7*V32+9.4*W32+4.1*(X32) ) * 0.004184</f>
         <v>18.184500799999999</v>
       </c>
-      <c r="T32" s="55">
+      <c r="T32" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q32,T$4)</f>
         <v>7.2</v>
       </c>
-      <c r="U32" s="55">
+      <c r="U32" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q32,U$4)</f>
         <v>7.8</v>
       </c>
-      <c r="V32" s="55">
+      <c r="V32" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q32,V$4)</f>
         <v>170</v>
       </c>
-      <c r="W32" s="55">
+      <c r="W32" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q32,W$4)</f>
         <v>40</v>
       </c>
       <c r="X32" s="41">
-        <f t="shared" ref="X32:X36" si="9">1000-SUM(V32:W32,Y32)</f>
+        <f t="shared" ref="X32:X36" si="15">1000-SUM(V32:W32,Y32)</f>
         <v>732</v>
       </c>
-      <c r="Y32" s="56">
+      <c r="Y32" s="55">
         <f>INDEX(pigs!$D$3:$AO$60,$Q32,Y$4)</f>
         <v>58</v>
       </c>
-      <c r="AB32" s="69">
+      <c r="AB32" s="68">
         <f>MATCH($B32,poultry!$A$3:$A$41,0)</f>
         <v>38</v>
       </c>
-      <c r="AC32" s="60">
+      <c r="AC32" s="59">
         <f>INDEX(poultry!$D$3:$U$41,$AB32,AC$4)</f>
         <v>87</v>
       </c>
@@ -9573,21 +10108,21 @@
       <c r="B33" t="s">
         <v>49</v>
       </c>
-      <c r="C33" s="66">
-        <f>AVERAGE(R33,G33)</f>
+      <c r="C33" s="65">
+        <f t="shared" si="4"/>
         <v>88.5</v>
       </c>
-      <c r="D33" s="65">
-        <f>H33</f>
+      <c r="D33" s="64">
+        <f t="shared" si="13"/>
         <v>17.8828344</v>
       </c>
       <c r="E33" s="4"/>
-      <c r="F33" s="69"/>
+      <c r="F33" s="68"/>
       <c r="G33" s="37">
         <v>89</v>
       </c>
-      <c r="H33" s="78">
-        <f t="shared" si="1"/>
+      <c r="H33" s="77">
+        <f t="shared" si="6"/>
         <v>17.8828344</v>
       </c>
       <c r="I33" s="38">
@@ -9606,7 +10141,7 @@
         <f>1000-SUM(J33:L33,N33)</f>
         <v>678</v>
       </c>
-      <c r="N33" s="50">
+      <c r="N33" s="83">
         <f>N32</f>
         <v>60</v>
       </c>
@@ -9616,7 +10151,7 @@
       <c r="P33" s="11" t="s">
         <v>490</v>
       </c>
-      <c r="Q33" s="69">
+      <c r="Q33" s="68">
         <f>MATCH($B33,pigs!$A$3:$A$60,0)</f>
         <v>54</v>
       </c>
@@ -9624,39 +10159,39 @@
         <f>INDEX(pigs!$D$3:$AO$60,$Q33,R$4)</f>
         <v>88</v>
       </c>
-      <c r="S33" s="78">
-        <f t="shared" si="8"/>
+      <c r="S33" s="77">
+        <f t="shared" si="14"/>
         <v>18.379056800000001</v>
       </c>
-      <c r="T33" s="55">
+      <c r="T33" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q33,T$4)</f>
         <v>8.6999999999999993</v>
       </c>
-      <c r="U33" s="55">
+      <c r="U33" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q33,U$4)</f>
         <v>9.1999999999999993</v>
       </c>
-      <c r="V33" s="55">
+      <c r="V33" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q33,V$4)</f>
         <v>176</v>
       </c>
-      <c r="W33" s="55">
+      <c r="W33" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q33,W$4)</f>
         <v>40</v>
       </c>
       <c r="X33" s="41">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>735</v>
       </c>
-      <c r="Y33" s="56">
+      <c r="Y33" s="55">
         <f>INDEX(pigs!$D$3:$AO$60,$Q33,Y$4)</f>
         <v>49</v>
       </c>
-      <c r="AB33" s="69">
+      <c r="AB33" s="68">
         <f>MATCH($B33,poultry!$A$3:$A$41,0)</f>
         <v>36</v>
       </c>
-      <c r="AC33" s="60">
+      <c r="AC33" s="59">
         <f>INDEX(poultry!$D$3:$U$41,$AB33,AC$4)</f>
         <v>87</v>
       </c>
@@ -9665,16 +10200,16 @@
       <c r="B34" t="s">
         <v>50</v>
       </c>
-      <c r="C34" s="66">
-        <f>AVERAGE(R34,G34)</f>
+      <c r="C34" s="65">
+        <f t="shared" si="4"/>
         <v>90</v>
       </c>
-      <c r="D34" s="65">
-        <f>H34</f>
+      <c r="D34" s="64">
+        <f t="shared" si="13"/>
         <v>19.659779199999999</v>
       </c>
       <c r="E34" s="4"/>
-      <c r="F34" s="69">
+      <c r="F34" s="68">
         <f>MATCH($B34,ruminants!$A$3:$A$120,0)</f>
         <v>109</v>
       </c>
@@ -9682,8 +10217,8 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F34,G$4)</f>
         <v>90</v>
       </c>
-      <c r="H34" s="78">
-        <f t="shared" si="1"/>
+      <c r="H34" s="77">
+        <f t="shared" si="6"/>
         <v>19.659779199999999</v>
       </c>
       <c r="I34" s="38">
@@ -9710,7 +10245,7 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F34,N$4)</f>
         <v>37</v>
       </c>
-      <c r="Q34" s="69">
+      <c r="Q34" s="68">
         <f>MATCH($B34,pigs!$A$3:$A$60,0)</f>
         <v>3</v>
       </c>
@@ -9718,60 +10253,60 @@
         <f>INDEX(pigs!$D$3:$AO$60,$Q34,R$4)</f>
         <v>90</v>
       </c>
-      <c r="S34" s="78">
-        <f t="shared" si="8"/>
+      <c r="S34" s="77">
+        <f t="shared" si="14"/>
         <v>20.139265599999998</v>
       </c>
-      <c r="T34" s="55">
+      <c r="T34" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q34,T$4)</f>
         <v>8.1</v>
       </c>
-      <c r="U34" s="55">
+      <c r="U34" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q34,U$4)</f>
         <v>8.6999999999999993</v>
       </c>
-      <c r="V34" s="55">
+      <c r="V34" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q34,V$4)</f>
         <v>340</v>
       </c>
-      <c r="W34" s="55">
+      <c r="W34" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q34,W$4)</f>
         <v>66</v>
       </c>
       <c r="X34" s="41">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>550</v>
       </c>
-      <c r="Y34" s="56">
+      <c r="Y34" s="55">
         <f>INDEX(pigs!$D$3:$AO$60,$Q34,Y$4)</f>
         <v>44</v>
       </c>
-      <c r="AB34" s="69"/>
-      <c r="AC34" s="60"/>
+      <c r="AB34" s="68"/>
+      <c r="AC34" s="59"/>
     </row>
     <row r="35" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>51</v>
       </c>
-      <c r="C35" s="66">
-        <f>AVERAGE(R35,G35)</f>
+      <c r="C35" s="65">
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="D35" s="65">
+      <c r="D35" s="64">
         <f>S35</f>
         <v>18.8602168</v>
       </c>
       <c r="E35" s="4"/>
-      <c r="F35" s="69"/>
+      <c r="F35" s="68"/>
       <c r="G35" s="37"/>
-      <c r="H35" s="55"/>
+      <c r="H35" s="54"/>
       <c r="I35" s="38"/>
       <c r="J35" s="39"/>
       <c r="K35" s="39"/>
       <c r="L35" s="39"/>
       <c r="M35" s="39"/>
       <c r="N35" s="42"/>
-      <c r="Q35" s="69">
+      <c r="Q35" s="68">
         <f>MATCH($B35,pigs!$A$3:$A$60,0)</f>
         <v>1</v>
       </c>
@@ -9779,51 +10314,51 @@
         <f>INDEX(pigs!$D$3:$AO$60,$Q35,R$4)</f>
         <v>11</v>
       </c>
-      <c r="S35" s="78">
-        <f t="shared" si="8"/>
+      <c r="S35" s="77">
+        <f t="shared" si="14"/>
         <v>18.8602168</v>
       </c>
-      <c r="T35" s="55">
+      <c r="T35" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q35,T$4)</f>
         <v>8.1999999999999993</v>
       </c>
-      <c r="U35" s="55">
+      <c r="U35" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q35,U$4)</f>
         <v>8.9</v>
       </c>
-      <c r="V35" s="55">
+      <c r="V35" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q35,V$4)</f>
         <v>280</v>
       </c>
-      <c r="W35" s="55">
+      <c r="W35" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q35,W$4)</f>
         <v>45</v>
       </c>
       <c r="X35" s="41">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>607</v>
       </c>
-      <c r="Y35" s="56">
+      <c r="Y35" s="55">
         <f>INDEX(pigs!$D$3:$AO$60,$Q35,Y$4)</f>
         <v>68</v>
       </c>
-      <c r="AB35" s="69"/>
-      <c r="AC35" s="60"/>
+      <c r="AB35" s="68"/>
+      <c r="AC35" s="59"/>
     </row>
     <row r="36" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>309</v>
       </c>
-      <c r="C36" s="66">
-        <f>AVERAGE(R36,G36)</f>
+      <c r="C36" s="65">
+        <f t="shared" si="4"/>
         <v>90</v>
       </c>
-      <c r="D36" s="65">
+      <c r="D36" s="64">
         <f>H36</f>
         <v>19.848896</v>
       </c>
       <c r="E36" s="4"/>
-      <c r="F36" s="69">
+      <c r="F36" s="68">
         <f>MATCH($B36,ruminants!$A$3:$A$120,0)</f>
         <v>38</v>
       </c>
@@ -9831,8 +10366,8 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F36,G$4)</f>
         <v>90</v>
       </c>
-      <c r="H36" s="78">
-        <f t="shared" si="1"/>
+      <c r="H36" s="77">
+        <f t="shared" si="6"/>
         <v>19.848896</v>
       </c>
       <c r="I36" s="38">
@@ -9859,29 +10394,29 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F36,N$4)</f>
         <v>40</v>
       </c>
-      <c r="Q36" s="69"/>
+      <c r="Q36" s="68"/>
       <c r="R36" s="37">
         <v>90</v>
       </c>
-      <c r="S36" s="78">
-        <f t="shared" si="8"/>
+      <c r="S36" s="77">
+        <f t="shared" si="14"/>
         <v>19.578191199999999</v>
       </c>
-      <c r="T36" s="75">
+      <c r="T36" s="74">
         <v>6.6</v>
       </c>
-      <c r="U36" s="43">
+      <c r="U36" s="84">
         <f>U34/T34*T36</f>
         <v>7.0888888888888877</v>
       </c>
-      <c r="V36" s="75">
+      <c r="V36" s="74">
         <v>258</v>
       </c>
-      <c r="W36" s="75">
+      <c r="W36" s="74">
         <v>67</v>
       </c>
       <c r="X36" s="41">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>629</v>
       </c>
       <c r="Y36" s="45">
@@ -9893,32 +10428,32 @@
       <c r="AA36" s="11" t="s">
         <v>490</v>
       </c>
-      <c r="AB36" s="69"/>
-      <c r="AC36" s="60"/>
+      <c r="AB36" s="68"/>
+      <c r="AC36" s="59"/>
     </row>
     <row r="37" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>384</v>
       </c>
-      <c r="C37" s="66">
+      <c r="C37" s="65">
         <f>AVERAGE(R37,G37,AC37)</f>
         <v>88.5</v>
       </c>
-      <c r="D37" s="65">
+      <c r="D37" s="64">
         <f>S37</f>
         <v>22.900705599999998</v>
       </c>
       <c r="E37" s="4"/>
-      <c r="F37" s="69"/>
+      <c r="F37" s="68"/>
       <c r="G37" s="37"/>
-      <c r="H37" s="55"/>
+      <c r="H37" s="54"/>
       <c r="I37" s="38"/>
       <c r="J37" s="39"/>
       <c r="K37" s="39"/>
       <c r="L37" s="39"/>
       <c r="M37" s="39"/>
       <c r="N37" s="42"/>
-      <c r="Q37" s="69">
+      <c r="Q37" s="68">
         <f>MATCH($B37,pigs!$A$3:$A$60,0)</f>
         <v>22</v>
       </c>
@@ -9926,41 +10461,41 @@
         <f>INDEX(pigs!$D$3:$AO$60,$Q37,R$4)</f>
         <v>90</v>
       </c>
-      <c r="S37" s="78">
-        <f t="shared" si="8"/>
+      <c r="S37" s="77">
+        <f t="shared" si="14"/>
         <v>22.900705599999998</v>
       </c>
-      <c r="T37" s="55">
+      <c r="T37" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q37,T$4)</f>
         <v>12.9</v>
       </c>
-      <c r="U37" s="55">
+      <c r="U37" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q37,U$4)</f>
         <v>13.3</v>
       </c>
-      <c r="V37" s="55">
+      <c r="V37" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q37,V$4)</f>
         <v>677</v>
       </c>
-      <c r="W37" s="55">
+      <c r="W37" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q37,W$4)</f>
         <v>71</v>
       </c>
       <c r="X37" s="41">
-        <f t="shared" ref="X37" si="10">1000-SUM(V37:W37,Y37)</f>
+        <f t="shared" ref="X37" si="16">1000-SUM(V37:W37,Y37)</f>
         <v>231</v>
       </c>
-      <c r="Y37" s="56">
+      <c r="Y37" s="55">
         <f>INDEX(pigs!$D$3:$AO$60,$Q37,Y$4)</f>
         <v>21</v>
       </c>
       <c r="Z37" s="11"/>
       <c r="AA37" s="11"/>
-      <c r="AB37" s="69">
+      <c r="AB37" s="68">
         <f>MATCH($B37,poultry!$A$3:$A$41,0)</f>
         <v>25</v>
       </c>
-      <c r="AC37" s="60">
+      <c r="AC37" s="59">
         <f>INDEX(poultry!$D$3:$U$41,$AB37,AC$4)</f>
         <v>87</v>
       </c>
@@ -9969,16 +10504,16 @@
       <c r="B38" t="s">
         <v>52</v>
       </c>
-      <c r="C38" s="66">
-        <f>AVERAGE(R38,G38)</f>
+      <c r="C38" s="65">
+        <f t="shared" ref="C38:C43" si="17">AVERAGE(R38,G38)</f>
         <v>75.5</v>
       </c>
-      <c r="D38" s="65">
+      <c r="D38" s="64">
         <f>H38</f>
         <v>16.1615368</v>
       </c>
       <c r="E38" s="4"/>
-      <c r="F38" s="69">
+      <c r="F38" s="68">
         <f>MATCH($B38,ruminants!$A$3:$A$120,0)</f>
         <v>88</v>
       </c>
@@ -9986,8 +10521,8 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F38,G$4)</f>
         <v>75</v>
       </c>
-      <c r="H38" s="78">
-        <f t="shared" si="1"/>
+      <c r="H38" s="77">
+        <f t="shared" si="6"/>
         <v>16.1615368</v>
       </c>
       <c r="I38" s="38">
@@ -10014,7 +10549,7 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F38,N$4)</f>
         <v>109</v>
       </c>
-      <c r="Q38" s="69">
+      <c r="Q38" s="68">
         <f>MATCH($B38,pigs!$A$3:$A$60,0)</f>
         <v>23</v>
       </c>
@@ -10022,51 +10557,51 @@
         <f>INDEX(pigs!$D$3:$AO$60,$Q38,R$4)</f>
         <v>76</v>
       </c>
-      <c r="S38" s="78">
-        <f t="shared" ref="S38:S43" si="11">( 5.7*V38+9.4*W38+4.1*(X38) ) * 0.004184</f>
+      <c r="S38" s="77">
+        <f t="shared" ref="S38:S43" si="18">( 5.7*V38+9.4*W38+4.1*(X38) ) * 0.004184</f>
         <v>15.9565208</v>
       </c>
-      <c r="T38" s="55">
+      <c r="T38" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q38,T$4)</f>
         <v>8.6999999999999993</v>
       </c>
-      <c r="U38" s="55">
+      <c r="U38" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q38,U$4)</f>
         <v>9</v>
       </c>
-      <c r="V38" s="55">
+      <c r="V38" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q38,V$4)</f>
         <v>145</v>
       </c>
-      <c r="W38" s="55">
+      <c r="W38" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q38,W$4)</f>
         <v>2</v>
       </c>
       <c r="X38" s="41">
-        <f t="shared" ref="X38:X43" si="12">1000-SUM(V38:W38,Y38)</f>
+        <f t="shared" ref="X38:X43" si="19">1000-SUM(V38:W38,Y38)</f>
         <v>724</v>
       </c>
-      <c r="Y38" s="56">
+      <c r="Y38" s="55">
         <f>INDEX(pigs!$D$3:$AO$60,$Q38,Y$4)</f>
         <v>129</v>
       </c>
-      <c r="AB38" s="69"/>
-      <c r="AC38" s="60"/>
+      <c r="AB38" s="68"/>
+      <c r="AC38" s="59"/>
     </row>
     <row r="39" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>53</v>
       </c>
-      <c r="C39" s="66">
-        <f>AVERAGE(R39,G39)</f>
+      <c r="C39" s="65">
+        <f t="shared" si="17"/>
         <v>89.5</v>
       </c>
-      <c r="D39" s="65">
+      <c r="D39" s="64">
         <f>H39</f>
         <v>17.334312000000001</v>
       </c>
       <c r="E39" s="4"/>
-      <c r="F39" s="69">
+      <c r="F39" s="68">
         <f>MATCH($B39,ruminants!$A$3:$A$120,0)</f>
         <v>91</v>
       </c>
@@ -10074,8 +10609,8 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F39,G$4)</f>
         <v>90</v>
       </c>
-      <c r="H39" s="78">
-        <f t="shared" si="1"/>
+      <c r="H39" s="77">
+        <f t="shared" si="6"/>
         <v>17.334312000000001</v>
       </c>
       <c r="I39" s="38">
@@ -10102,7 +10637,7 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F39,N$4)</f>
         <v>66</v>
       </c>
-      <c r="Q39" s="69">
+      <c r="Q39" s="68">
         <f>MATCH($B39,pigs!$A$3:$A$60,0)</f>
         <v>4</v>
       </c>
@@ -10110,51 +10645,51 @@
         <f>INDEX(pigs!$D$3:$AO$60,$Q39,R$4)</f>
         <v>89</v>
       </c>
-      <c r="S39" s="78">
-        <f t="shared" si="11"/>
+      <c r="S39" s="77">
+        <f t="shared" si="18"/>
         <v>16.664453599999998</v>
       </c>
-      <c r="T39" s="55">
+      <c r="T39" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q39,T$4)</f>
         <v>6.9</v>
       </c>
-      <c r="U39" s="55">
+      <c r="U39" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q39,U$4)</f>
         <v>8</v>
       </c>
-      <c r="V39" s="55">
+      <c r="V39" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q39,V$4)</f>
         <v>91</v>
       </c>
-      <c r="W39" s="55">
+      <c r="W39" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q39,W$4)</f>
         <v>10</v>
       </c>
       <c r="X39" s="41">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>822</v>
       </c>
-      <c r="Y39" s="56">
+      <c r="Y39" s="55">
         <f>INDEX(pigs!$D$3:$AO$60,$Q39,Y$4)</f>
         <v>77</v>
       </c>
-      <c r="AB39" s="69"/>
-      <c r="AC39" s="60"/>
+      <c r="AB39" s="68"/>
+      <c r="AC39" s="59"/>
     </row>
     <row r="40" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>54</v>
       </c>
-      <c r="C40" s="66">
-        <f>AVERAGE(R40,G40)</f>
+      <c r="C40" s="65">
+        <f t="shared" si="17"/>
         <v>6.25</v>
       </c>
-      <c r="D40" s="65">
+      <c r="D40" s="64">
         <f>H40</f>
         <v>16.464040000000001</v>
       </c>
       <c r="E40" s="4"/>
-      <c r="F40" s="69">
+      <c r="F40" s="68">
         <f>MATCH($B40,ruminants!$A$3:$A$120,0)</f>
         <v>57</v>
       </c>
@@ -10162,8 +10697,8 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F40,G$4)</f>
         <v>7</v>
       </c>
-      <c r="H40" s="78">
-        <f t="shared" si="1"/>
+      <c r="H40" s="77">
+        <f t="shared" si="6"/>
         <v>16.464040000000001</v>
       </c>
       <c r="I40" s="38">
@@ -10190,7 +10725,7 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F40,N$4)</f>
         <v>100</v>
       </c>
-      <c r="Q40" s="69">
+      <c r="Q40" s="68">
         <f>MATCH($B40,pigs!$A$3:$A$60,0)</f>
         <v>50</v>
       </c>
@@ -10198,60 +10733,60 @@
         <f>INDEX(pigs!$D$3:$AO$60,$Q40,R$4)</f>
         <v>5.5</v>
       </c>
-      <c r="S40" s="78">
-        <f t="shared" si="11"/>
+      <c r="S40" s="77">
+        <f t="shared" si="18"/>
         <v>16.870306399999997</v>
       </c>
-      <c r="T40" s="55">
+      <c r="T40" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q40,T$4)</f>
         <v>12.4</v>
       </c>
-      <c r="U40" s="55">
+      <c r="U40" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q40,U$4)</f>
         <v>12.2</v>
       </c>
-      <c r="V40" s="55">
+      <c r="V40" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q40,V$4)</f>
         <v>115</v>
       </c>
-      <c r="W40" s="55">
+      <c r="W40" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q40,W$4)</f>
         <v>19</v>
       </c>
       <c r="X40" s="41">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>780</v>
       </c>
-      <c r="Y40" s="56">
+      <c r="Y40" s="55">
         <f>INDEX(pigs!$D$3:$AO$60,$Q40,Y$4)</f>
         <v>86</v>
       </c>
-      <c r="AB40" s="69"/>
-      <c r="AC40" s="60"/>
+      <c r="AB40" s="68"/>
+      <c r="AC40" s="59"/>
     </row>
     <row r="41" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>55</v>
       </c>
-      <c r="C41" s="66">
-        <f>AVERAGE(R41,G41)</f>
+      <c r="C41" s="65">
+        <f t="shared" si="17"/>
         <v>97</v>
       </c>
-      <c r="D41" s="65">
+      <c r="D41" s="64">
         <f>S41</f>
         <v>16.975324799999999</v>
       </c>
       <c r="E41" s="4"/>
-      <c r="F41" s="69"/>
+      <c r="F41" s="68"/>
       <c r="G41" s="37"/>
-      <c r="H41" s="55"/>
+      <c r="H41" s="54"/>
       <c r="I41" s="38"/>
       <c r="J41" s="39"/>
       <c r="K41" s="39"/>
       <c r="L41" s="39"/>
       <c r="M41" s="39"/>
       <c r="N41" s="42"/>
-      <c r="Q41" s="69">
+      <c r="Q41" s="68">
         <f>MATCH($B41,pigs!$A$3:$A$60,0)</f>
         <v>52</v>
       </c>
@@ -10259,51 +10794,51 @@
         <f>INDEX(pigs!$D$3:$AO$60,$Q41,R$4)</f>
         <v>97</v>
       </c>
-      <c r="S41" s="78">
-        <f t="shared" si="11"/>
+      <c r="S41" s="77">
+        <f t="shared" si="18"/>
         <v>16.975324799999999</v>
       </c>
-      <c r="T41" s="55">
+      <c r="T41" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q41,T$4)</f>
         <v>12.4</v>
       </c>
-      <c r="U41" s="55">
+      <c r="U41" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q41,U$4)</f>
         <v>12.2</v>
       </c>
-      <c r="V41" s="55">
+      <c r="V41" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q41,V$4)</f>
         <v>131</v>
       </c>
-      <c r="W41" s="55">
+      <c r="W41" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q41,W$4)</f>
         <v>22</v>
       </c>
       <c r="X41" s="41">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>757</v>
       </c>
-      <c r="Y41" s="56">
+      <c r="Y41" s="55">
         <f>INDEX(pigs!$D$3:$AO$60,$Q41,Y$4)</f>
         <v>90</v>
       </c>
-      <c r="AB41" s="69"/>
-      <c r="AC41" s="60"/>
+      <c r="AB41" s="68"/>
+      <c r="AC41" s="59"/>
     </row>
     <row r="42" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>56</v>
       </c>
-      <c r="C42" s="66">
-        <f>AVERAGE(R42,G42)</f>
+      <c r="C42" s="65">
+        <f t="shared" si="17"/>
         <v>91</v>
       </c>
-      <c r="D42" s="65">
+      <c r="D42" s="64">
         <f>H42</f>
         <v>23.055932000000002</v>
       </c>
       <c r="E42" s="4"/>
-      <c r="F42" s="69">
+      <c r="F42" s="68">
         <f>MATCH($B42,ruminants!$A$3:$A$120,0)</f>
         <v>65</v>
       </c>
@@ -10311,8 +10846,8 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F42,G$4)</f>
         <v>90</v>
       </c>
-      <c r="H42" s="78">
-        <f t="shared" si="1"/>
+      <c r="H42" s="77">
+        <f t="shared" si="6"/>
         <v>23.055932000000002</v>
       </c>
       <c r="I42" s="38">
@@ -10339,7 +10874,7 @@
         <f>INDEX(ruminants!$D$3:$AH$120,$F42,N$4)</f>
         <v>28</v>
       </c>
-      <c r="Q42" s="69">
+      <c r="Q42" s="68">
         <f>MATCH($B42,pigs!$A$3:$A$60,0)</f>
         <v>31</v>
       </c>
@@ -10347,39 +10882,39 @@
         <f>INDEX(pigs!$D$3:$AO$60,$Q42,R$4)</f>
         <v>92</v>
       </c>
-      <c r="S42" s="78">
-        <f t="shared" si="11"/>
+      <c r="S42" s="77">
+        <f t="shared" si="18"/>
         <v>22.525819200000001</v>
       </c>
-      <c r="T42" s="55">
+      <c r="T42" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q42,T$4)</f>
         <v>11.1</v>
       </c>
-      <c r="U42" s="55">
+      <c r="U42" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q42,U$4)</f>
         <v>11.3</v>
       </c>
-      <c r="V42" s="55">
+      <c r="V42" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q42,V$4)</f>
         <v>841</v>
       </c>
-      <c r="W42" s="55">
+      <c r="W42" s="54">
         <f>INDEX(pigs!$D$3:$AO$60,$Q42,W$4)</f>
         <v>10</v>
       </c>
       <c r="X42" s="41">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>121</v>
       </c>
-      <c r="Y42" s="56">
+      <c r="Y42" s="55">
         <f>INDEX(pigs!$D$3:$AO$60,$Q42,Y$4)</f>
         <v>28</v>
       </c>
-      <c r="AB42" s="69">
+      <c r="AB42" s="68">
         <f>MATCH($B42,poultry!$A$3:$A$41,0)</f>
         <v>28</v>
       </c>
-      <c r="AC42" s="60">
+      <c r="AC42" s="59">
         <f>INDEX(poultry!$D$3:$U$41,$AB42,AC$4)</f>
         <v>90</v>
       </c>
@@ -10388,65 +10923,65 @@
       <c r="B43" t="s">
         <v>57</v>
       </c>
-      <c r="C43" s="67">
-        <f>AVERAGE(R43,G43)</f>
+      <c r="C43" s="66">
+        <f t="shared" si="17"/>
         <v>92</v>
       </c>
-      <c r="D43" s="68">
+      <c r="D43" s="67">
         <f>S43</f>
         <v>22.254696000000003</v>
       </c>
       <c r="E43" s="4"/>
-      <c r="F43" s="69"/>
-      <c r="G43" s="51"/>
-      <c r="H43" s="52"/>
-      <c r="I43" s="52"/>
-      <c r="J43" s="53"/>
-      <c r="K43" s="53"/>
-      <c r="L43" s="53"/>
-      <c r="M43" s="53"/>
-      <c r="N43" s="54"/>
-      <c r="Q43" s="69">
+      <c r="F43" s="68"/>
+      <c r="G43" s="50"/>
+      <c r="H43" s="51"/>
+      <c r="I43" s="51"/>
+      <c r="J43" s="52"/>
+      <c r="K43" s="52"/>
+      <c r="L43" s="52"/>
+      <c r="M43" s="52"/>
+      <c r="N43" s="53"/>
+      <c r="Q43" s="68">
         <f>MATCH($B43,pigs!$A$3:$A$60,0)</f>
         <v>7</v>
       </c>
-      <c r="R43" s="51">
+      <c r="R43" s="50">
         <f>INDEX(pigs!$D$3:$AO$60,$Q43,R$4)</f>
         <v>92</v>
       </c>
-      <c r="S43" s="79">
-        <f t="shared" si="11"/>
+      <c r="S43" s="78">
+        <f t="shared" si="18"/>
         <v>22.254696000000003</v>
       </c>
-      <c r="T43" s="52">
+      <c r="T43" s="51">
         <f>INDEX(pigs!$D$3:$AO$60,$Q43,T$4)</f>
         <v>10.8</v>
       </c>
-      <c r="U43" s="52">
+      <c r="U43" s="51">
         <f>INDEX(pigs!$D$3:$AO$60,$Q43,U$4)</f>
         <v>10.8</v>
       </c>
-      <c r="V43" s="52">
+      <c r="V43" s="51">
         <f>INDEX(pigs!$D$3:$AO$60,$Q43,V$4)</f>
         <v>760</v>
       </c>
-      <c r="W43" s="52">
+      <c r="W43" s="51">
         <f>INDEX(pigs!$D$3:$AO$60,$Q43,W$4)</f>
         <v>105</v>
       </c>
-      <c r="X43" s="77">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="Y43" s="59">
+      <c r="X43" s="76">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="Y43" s="58">
         <f>INDEX(pigs!$D$3:$AO$60,$Q43,Y$4)</f>
         <v>135</v>
       </c>
-      <c r="AB43" s="69">
+      <c r="AB43" s="68">
         <f>MATCH($B43,poultry!$A$3:$A$41,0)</f>
         <v>6</v>
       </c>
-      <c r="AC43" s="61">
+      <c r="AC43" s="60">
         <f>INDEX(poultry!$D$3:$U$41,$AB43,AC$4)</f>
         <v>92</v>
       </c>

--- a/data/prod_parameters/FeedMgmt.xlsx
+++ b/data/prod_parameters/FeedMgmt.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1523" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1544" uniqueCount="513">
   <si>
     <t>f_feed</t>
   </si>
@@ -1567,6 +1567,39 @@
   </si>
   <si>
     <t>Total fat</t>
+  </si>
+  <si>
+    <r>
+      <t>Enteric fermentation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (for cattle Ym is calculated from feed ration)</t>
+    </r>
+  </si>
+  <si>
+    <t>EF_enteric</t>
+  </si>
+  <si>
+    <t>Ym_enteric</t>
+  </si>
+  <si>
+    <t>NIR 2021</t>
+  </si>
+  <si>
+    <t>lambs</t>
+  </si>
+  <si>
+    <t>% of GE</t>
+  </si>
+  <si>
+    <t>kg CH4/head/year</t>
   </si>
 </sst>
 </file>
@@ -2300,7 +2333,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O330"/>
+  <dimension ref="A1:O336"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="7" width="20.28515625" customWidth="1"/>
@@ -4742,211 +4775,255 @@
       <c r="M118" s="26"/>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K119" s="3"/>
-      <c r="M119" s="3"/>
+      <c r="A119" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="B119" s="1"/>
+      <c r="C119" s="1"/>
+      <c r="D119" s="1"/>
+      <c r="E119" s="2"/>
+      <c r="F119" s="2"/>
+      <c r="G119" s="2"/>
+      <c r="H119" s="2"/>
+      <c r="I119" s="2"/>
+      <c r="J119" s="2"/>
+      <c r="K119" s="2"/>
+      <c r="L119" s="2"/>
+      <c r="M119" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="N119" s="2"/>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A120" s="1" t="s">
+      <c r="A120" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="B120" s="3"/>
+      <c r="C120" s="3"/>
+      <c r="D120" s="3"/>
+      <c r="E120" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="F120" s="3"/>
+      <c r="G120" s="3"/>
+      <c r="H120" s="3"/>
+      <c r="I120" s="3"/>
+      <c r="J120" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="K120" s="3">
+        <v>4.5</v>
+      </c>
+      <c r="L120" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="M120" s="3"/>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="B121" s="3"/>
+      <c r="C121" s="3"/>
+      <c r="D121" s="3"/>
+      <c r="E121" s="3"/>
+      <c r="F121" s="3"/>
+      <c r="G121" s="3"/>
+      <c r="H121" s="3"/>
+      <c r="I121" s="3"/>
+      <c r="J121" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="K121" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="L121" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="M121" s="3"/>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>391</v>
+      </c>
+      <c r="J122" t="s">
+        <v>507</v>
+      </c>
+      <c r="K122" s="26">
+        <v>18</v>
+      </c>
+      <c r="L122" t="s">
+        <v>512</v>
+      </c>
+      <c r="M122" s="3"/>
+      <c r="N122" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>25</v>
+      </c>
+      <c r="J123" t="s">
+        <v>507</v>
+      </c>
+      <c r="K123" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="L123" t="s">
+        <v>512</v>
+      </c>
+      <c r="M123" s="3"/>
+      <c r="N123" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>385</v>
+      </c>
+      <c r="J124" t="s">
+        <v>507</v>
+      </c>
+      <c r="K124" s="26">
+        <v>0</v>
+      </c>
+      <c r="L124" t="s">
+        <v>512</v>
+      </c>
+      <c r="M124" s="3"/>
+      <c r="N124" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K125" s="3"/>
+      <c r="M125" s="3"/>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B120" s="1"/>
-      <c r="C120" s="1"/>
-      <c r="D120" s="1"/>
-      <c r="E120" s="2"/>
-      <c r="F120" s="2"/>
-      <c r="G120" s="2"/>
-      <c r="H120" s="2"/>
-      <c r="I120" s="2"/>
-      <c r="J120" s="2"/>
-      <c r="K120" s="2"/>
-      <c r="L120" s="2"/>
-      <c r="M120" s="2" t="s">
+      <c r="B126" s="1"/>
+      <c r="C126" s="1"/>
+      <c r="D126" s="1"/>
+      <c r="E126" s="2"/>
+      <c r="F126" s="2"/>
+      <c r="G126" s="2"/>
+      <c r="H126" s="2"/>
+      <c r="I126" s="2"/>
+      <c r="J126" s="2"/>
+      <c r="K126" s="2"/>
+      <c r="L126" s="2"/>
+      <c r="M126" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="N120" s="2"/>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A121" s="79" t="s">
+      <c r="N126" s="2"/>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A127" s="79" t="s">
         <v>496</v>
       </c>
-      <c r="B121" s="80"/>
-      <c r="C121" s="80"/>
-      <c r="D121" s="80"/>
-      <c r="E121" s="81"/>
-      <c r="F121" s="81"/>
-      <c r="G121" s="81"/>
-      <c r="H121" s="81"/>
-      <c r="I121" s="81"/>
-      <c r="J121" s="81"/>
-      <c r="K121" s="81"/>
-      <c r="L121" s="81"/>
-      <c r="M121" s="81"/>
-      <c r="N121" s="81"/>
-    </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F122" t="s">
-        <v>306</v>
-      </c>
-      <c r="J122" t="s">
-        <v>386</v>
-      </c>
-      <c r="K122" s="82">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F122,'feed pars'!B$6:B$43,0))</f>
-        <v>100</v>
-      </c>
-      <c r="L122" t="s">
-        <v>28</v>
-      </c>
-      <c r="M122" s="26" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F123" t="s">
-        <v>307</v>
-      </c>
-      <c r="J123" t="s">
-        <v>386</v>
-      </c>
-      <c r="K123" s="82">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F123,'feed pars'!B$6:B$43,0))</f>
-        <v>100</v>
-      </c>
-      <c r="M123" s="3"/>
-    </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F124" t="s">
-        <v>308</v>
-      </c>
-      <c r="J124" t="s">
-        <v>386</v>
-      </c>
-      <c r="K124" s="82">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F124,'feed pars'!B$6:B$43,0))</f>
-        <v>100</v>
-      </c>
-      <c r="M124" s="3"/>
-    </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F125" t="s">
-        <v>2</v>
-      </c>
-      <c r="J125" t="s">
-        <v>386</v>
-      </c>
-      <c r="K125" s="82">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F125,'feed pars'!B$6:B$43,0))</f>
-        <v>100</v>
-      </c>
-      <c r="M125" s="3"/>
-    </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F126" t="s">
-        <v>12</v>
-      </c>
-      <c r="J126" t="s">
-        <v>386</v>
-      </c>
-      <c r="K126" s="82">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F126,'feed pars'!B$6:B$43,0))</f>
-        <v>100</v>
-      </c>
-      <c r="M126" s="3"/>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F127" t="s">
-        <v>33</v>
-      </c>
-      <c r="J127" t="s">
-        <v>386</v>
-      </c>
-      <c r="K127" s="82">
-        <f>INDEX('feed pars'!C$6:C$43,MATCH(F127,'feed pars'!B$6:B$43,0))</f>
-        <v>100</v>
-      </c>
-      <c r="M127" s="3"/>
+      <c r="B127" s="80"/>
+      <c r="C127" s="80"/>
+      <c r="D127" s="80"/>
+      <c r="E127" s="81"/>
+      <c r="F127" s="81"/>
+      <c r="G127" s="81"/>
+      <c r="H127" s="81"/>
+      <c r="I127" s="81"/>
+      <c r="J127" s="81"/>
+      <c r="K127" s="81"/>
+      <c r="L127" s="81"/>
+      <c r="M127" s="81"/>
+      <c r="N127" s="81"/>
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F128" t="s">
-        <v>17</v>
+        <v>306</v>
       </c>
       <c r="J128" t="s">
         <v>386</v>
       </c>
       <c r="K128" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F128,'feed pars'!B$6:B$43,0))</f>
-        <v>87</v>
-      </c>
-      <c r="M128" s="3"/>
+        <v>100</v>
+      </c>
+      <c r="L128" t="s">
+        <v>28</v>
+      </c>
+      <c r="M128" s="26" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="129" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F129" t="s">
-        <v>37</v>
+        <v>307</v>
       </c>
       <c r="J129" t="s">
         <v>386</v>
       </c>
       <c r="K129" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F129,'feed pars'!B$6:B$43,0))</f>
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="M129" s="3"/>
     </row>
     <row r="130" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F130" t="s">
-        <v>38</v>
+        <v>308</v>
       </c>
       <c r="J130" t="s">
         <v>386</v>
       </c>
       <c r="K130" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F130,'feed pars'!B$6:B$43,0))</f>
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="M130" s="3"/>
     </row>
     <row r="131" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F131" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="J131" t="s">
         <v>386</v>
       </c>
       <c r="K131" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F131,'feed pars'!B$6:B$43,0))</f>
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="M131" s="3"/>
     </row>
     <row r="132" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F132" t="s">
-        <v>313</v>
+        <v>12</v>
       </c>
       <c r="J132" t="s">
         <v>386</v>
       </c>
       <c r="K132" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F132,'feed pars'!B$6:B$43,0))</f>
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="M132" s="3"/>
     </row>
     <row r="133" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F133" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="J133" t="s">
         <v>386</v>
       </c>
       <c r="K133" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F133,'feed pars'!B$6:B$43,0))</f>
-        <v>67.5</v>
+        <v>100</v>
       </c>
       <c r="M133" s="3"/>
     </row>
     <row r="134" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F134" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="J134" t="s">
         <v>386</v>
@@ -4959,72 +5036,72 @@
     </row>
     <row r="135" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F135" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="J135" t="s">
         <v>386</v>
       </c>
       <c r="K135" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F135,'feed pars'!B$6:B$43,0))</f>
-        <v>86.8</v>
+        <v>87</v>
       </c>
       <c r="M135" s="3"/>
     </row>
     <row r="136" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F136" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J136" t="s">
         <v>386</v>
       </c>
       <c r="K136" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F136,'feed pars'!B$6:B$43,0))</f>
-        <v>92.5</v>
+        <v>86</v>
       </c>
       <c r="M136" s="3"/>
     </row>
     <row r="137" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F137" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J137" t="s">
         <v>386</v>
       </c>
       <c r="K137" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F137,'feed pars'!B$6:B$43,0))</f>
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="M137" s="3"/>
     </row>
     <row r="138" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F138" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="J138" t="s">
         <v>386</v>
       </c>
       <c r="K138" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F138,'feed pars'!B$6:B$43,0))</f>
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="M138" s="3"/>
     </row>
     <row r="139" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F139" t="s">
-        <v>302</v>
+        <v>40</v>
       </c>
       <c r="J139" t="s">
         <v>386</v>
       </c>
       <c r="K139" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F139,'feed pars'!B$6:B$43,0))</f>
-        <v>85</v>
+        <v>67.5</v>
       </c>
       <c r="M139" s="3"/>
     </row>
     <row r="140" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F140" t="s">
-        <v>314</v>
+        <v>41</v>
       </c>
       <c r="J140" t="s">
         <v>386</v>
@@ -5037,877 +5114,863 @@
     </row>
     <row r="141" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F141" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J141" t="s">
         <v>386</v>
       </c>
       <c r="K141" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F141,'feed pars'!B$6:B$43,0))</f>
-        <v>87.5</v>
+        <v>86.8</v>
       </c>
       <c r="M141" s="3"/>
     </row>
     <row r="142" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F142" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="J142" t="s">
         <v>386</v>
       </c>
       <c r="K142" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F142,'feed pars'!B$6:B$43,0))</f>
-        <v>87</v>
+        <v>92.5</v>
       </c>
       <c r="M142" s="3"/>
     </row>
     <row r="143" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F143" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="J143" t="s">
         <v>386</v>
       </c>
       <c r="K143" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F143,'feed pars'!B$6:B$43,0))</f>
-        <v>89.5</v>
+        <v>92</v>
       </c>
       <c r="M143" s="3"/>
     </row>
     <row r="144" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F144" t="s">
-        <v>46</v>
+        <v>310</v>
       </c>
       <c r="J144" t="s">
         <v>386</v>
       </c>
       <c r="K144" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F144,'feed pars'!B$6:B$43,0))</f>
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="M144" s="3"/>
     </row>
     <row r="145" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F145" t="s">
-        <v>47</v>
+        <v>302</v>
       </c>
       <c r="J145" t="s">
         <v>386</v>
       </c>
       <c r="K145" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F145,'feed pars'!B$6:B$43,0))</f>
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="M145" s="3"/>
     </row>
     <row r="146" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F146" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J146" t="s">
         <v>386</v>
       </c>
       <c r="K146" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F146,'feed pars'!B$6:B$43,0))</f>
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="M146" s="3"/>
     </row>
     <row r="147" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F147" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="J147" t="s">
         <v>386</v>
       </c>
       <c r="K147" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F147,'feed pars'!B$6:B$43,0))</f>
-        <v>87</v>
+        <v>87.5</v>
       </c>
       <c r="M147" s="3"/>
     </row>
     <row r="148" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F148" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="J148" t="s">
         <v>386</v>
       </c>
       <c r="K148" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F148,'feed pars'!B$6:B$43,0))</f>
-        <v>88.5</v>
+        <v>87</v>
       </c>
       <c r="M148" s="3"/>
     </row>
     <row r="149" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F149" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="J149" t="s">
         <v>386</v>
       </c>
       <c r="K149" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F149,'feed pars'!B$6:B$43,0))</f>
-        <v>90</v>
+        <v>89.5</v>
       </c>
       <c r="M149" s="3"/>
     </row>
     <row r="150" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F150" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="J150" t="s">
         <v>386</v>
       </c>
       <c r="K150" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F150,'feed pars'!B$6:B$43,0))</f>
-        <v>11</v>
+        <v>91</v>
       </c>
       <c r="M150" s="3"/>
     </row>
     <row r="151" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F151" t="s">
-        <v>309</v>
+        <v>47</v>
       </c>
       <c r="J151" t="s">
         <v>386</v>
       </c>
       <c r="K151" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F151,'feed pars'!B$6:B$43,0))</f>
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M151" s="3"/>
     </row>
     <row r="152" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F152" t="s">
-        <v>384</v>
+        <v>315</v>
       </c>
       <c r="J152" t="s">
         <v>386</v>
       </c>
       <c r="K152" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F152,'feed pars'!B$6:B$43,0))</f>
-        <v>88.5</v>
+        <v>90</v>
       </c>
       <c r="M152" s="3"/>
     </row>
     <row r="153" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F153" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="J153" t="s">
         <v>386</v>
       </c>
       <c r="K153" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F153,'feed pars'!B$6:B$43,0))</f>
-        <v>75.5</v>
+        <v>87</v>
       </c>
       <c r="M153" s="3"/>
     </row>
     <row r="154" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F154" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="J154" t="s">
         <v>386</v>
       </c>
       <c r="K154" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F154,'feed pars'!B$6:B$43,0))</f>
-        <v>89.5</v>
+        <v>88.5</v>
       </c>
       <c r="M154" s="3"/>
     </row>
     <row r="155" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F155" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="J155" t="s">
         <v>386</v>
       </c>
       <c r="K155" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F155,'feed pars'!B$6:B$43,0))</f>
-        <v>6.25</v>
+        <v>90</v>
       </c>
       <c r="M155" s="3"/>
     </row>
     <row r="156" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F156" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="J156" t="s">
         <v>386</v>
       </c>
       <c r="K156" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F156,'feed pars'!B$6:B$43,0))</f>
-        <v>97</v>
+        <v>11</v>
       </c>
       <c r="M156" s="3"/>
     </row>
     <row r="157" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F157" t="s">
-        <v>56</v>
+        <v>309</v>
       </c>
       <c r="J157" t="s">
         <v>386</v>
       </c>
       <c r="K157" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F157,'feed pars'!B$6:B$43,0))</f>
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M157" s="3"/>
     </row>
     <row r="158" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F158" t="s">
-        <v>57</v>
+        <v>384</v>
       </c>
       <c r="J158" t="s">
         <v>386</v>
       </c>
       <c r="K158" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F158,'feed pars'!B$6:B$43,0))</f>
-        <v>92</v>
+        <v>88.5</v>
       </c>
       <c r="M158" s="3"/>
     </row>
     <row r="159" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F159" t="s">
-        <v>320</v>
+        <v>52</v>
       </c>
       <c r="J159" t="s">
         <v>386</v>
       </c>
-      <c r="K159" s="86">
-        <v>100</v>
+      <c r="K159" s="82">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F159,'feed pars'!B$6:B$43,0))</f>
+        <v>75.5</v>
       </c>
       <c r="M159" s="3"/>
     </row>
     <row r="160" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F160" t="s">
-        <v>306</v>
+        <v>53</v>
       </c>
       <c r="J160" t="s">
-        <v>498</v>
-      </c>
-      <c r="K160" s="25">
-        <f>INDEX('feed pars'!D$6:D$43,MATCH(F160,'feed pars'!B$6:B$43,0))</f>
-        <v>17.316948400000001</v>
-      </c>
-      <c r="L160" t="s">
-        <v>497</v>
-      </c>
-      <c r="M160" s="26" t="s">
-        <v>499</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="K160" s="82">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F160,'feed pars'!B$6:B$43,0))</f>
+        <v>89.5</v>
+      </c>
+      <c r="M160" s="3"/>
     </row>
     <row r="161" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F161" t="s">
-        <v>307</v>
+        <v>54</v>
       </c>
       <c r="J161" t="s">
-        <v>498</v>
-      </c>
-      <c r="K161" s="25">
-        <f>INDEX('feed pars'!D$6:D$43,MATCH(F161,'feed pars'!B$6:B$43,0))</f>
-        <v>17.150216</v>
+        <v>386</v>
+      </c>
+      <c r="K161" s="82">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F161,'feed pars'!B$6:B$43,0))</f>
+        <v>6.25</v>
       </c>
       <c r="M161" s="3"/>
     </row>
     <row r="162" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F162" t="s">
-        <v>308</v>
+        <v>55</v>
       </c>
       <c r="J162" t="s">
-        <v>498</v>
-      </c>
-      <c r="K162" s="25">
-        <f>INDEX('feed pars'!D$6:D$43,MATCH(F162,'feed pars'!B$6:B$43,0))</f>
-        <v>16.819680000000002</v>
+        <v>386</v>
+      </c>
+      <c r="K162" s="82">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F162,'feed pars'!B$6:B$43,0))</f>
+        <v>97</v>
       </c>
       <c r="M162" s="3"/>
     </row>
     <row r="163" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F163" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="J163" t="s">
-        <v>498</v>
-      </c>
-      <c r="K163" s="25">
-        <f>INDEX('feed pars'!D$6:D$43,MATCH(F163,'feed pars'!B$6:B$43,0))</f>
-        <v>17.160257599999998</v>
+        <v>386</v>
+      </c>
+      <c r="K163" s="82">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F163,'feed pars'!B$6:B$43,0))</f>
+        <v>91</v>
       </c>
       <c r="M163" s="3"/>
     </row>
     <row r="164" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F164" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="J164" t="s">
-        <v>498</v>
-      </c>
-      <c r="K164" s="25">
-        <f>INDEX('feed pars'!D$6:D$43,MATCH(F164,'feed pars'!B$6:B$43,0))</f>
-        <v>17.6573168</v>
+        <v>386</v>
+      </c>
+      <c r="K164" s="82">
+        <f>INDEX('feed pars'!C$6:C$43,MATCH(F164,'feed pars'!B$6:B$43,0))</f>
+        <v>92</v>
       </c>
       <c r="M164" s="3"/>
     </row>
     <row r="165" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F165" t="s">
-        <v>33</v>
+        <v>320</v>
       </c>
       <c r="J165" t="s">
-        <v>498</v>
-      </c>
-      <c r="K165" s="25">
-        <f>INDEX('feed pars'!D$6:D$43,MATCH(F165,'feed pars'!B$6:B$43,0))</f>
-        <v>17.411437066666668</v>
+        <v>386</v>
+      </c>
+      <c r="K165" s="86">
+        <v>100</v>
       </c>
       <c r="M165" s="3"/>
     </row>
     <row r="166" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F166" t="s">
-        <v>17</v>
+        <v>306</v>
       </c>
       <c r="J166" t="s">
         <v>498</v>
       </c>
       <c r="K166" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F166,'feed pars'!B$6:B$43,0))</f>
-        <v>18.210023200000002</v>
-      </c>
-      <c r="M166" s="3"/>
+        <v>17.316948400000001</v>
+      </c>
+      <c r="L166" t="s">
+        <v>497</v>
+      </c>
+      <c r="M166" s="26" t="s">
+        <v>499</v>
+      </c>
     </row>
     <row r="167" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F167" t="s">
-        <v>37</v>
+        <v>307</v>
       </c>
       <c r="J167" t="s">
         <v>498</v>
       </c>
       <c r="K167" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F167,'feed pars'!B$6:B$43,0))</f>
-        <v>18.089524000000001</v>
+        <v>17.150216</v>
       </c>
       <c r="M167" s="3"/>
     </row>
     <row r="168" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F168" t="s">
-        <v>38</v>
+        <v>308</v>
       </c>
       <c r="J168" t="s">
         <v>498</v>
       </c>
       <c r="K168" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F168,'feed pars'!B$6:B$43,0))</f>
-        <v>18.6602216</v>
+        <v>16.819680000000002</v>
       </c>
       <c r="M168" s="3"/>
     </row>
     <row r="169" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F169" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="J169" t="s">
         <v>498</v>
       </c>
       <c r="K169" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F169,'feed pars'!B$6:B$43,0))</f>
-        <v>18.2284328</v>
+        <v>17.160257599999998</v>
       </c>
       <c r="M169" s="3"/>
     </row>
     <row r="170" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F170" t="s">
-        <v>313</v>
+        <v>12</v>
       </c>
       <c r="J170" t="s">
         <v>498</v>
       </c>
       <c r="K170" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F170,'feed pars'!B$6:B$43,0))</f>
-        <v>17.924256</v>
+        <v>17.6573168</v>
       </c>
       <c r="M170" s="3"/>
     </row>
     <row r="171" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F171" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="J171" t="s">
         <v>498</v>
       </c>
       <c r="K171" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F171,'feed pars'!B$6:B$43,0))</f>
-        <v>18.3899352</v>
+        <v>17.411437066666668</v>
       </c>
       <c r="M171" s="3"/>
     </row>
     <row r="172" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F172" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="J172" t="s">
         <v>498</v>
       </c>
       <c r="K172" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F172,'feed pars'!B$6:B$43,0))</f>
-        <v>18.478217600000001</v>
+        <v>18.210023200000002</v>
       </c>
       <c r="M172" s="3"/>
     </row>
     <row r="173" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F173" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="J173" t="s">
         <v>498</v>
       </c>
       <c r="K173" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F173,'feed pars'!B$6:B$43,0))</f>
-        <v>18.737207199999997</v>
+        <v>18.089524000000001</v>
       </c>
       <c r="M173" s="3"/>
     </row>
     <row r="174" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F174" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J174" t="s">
         <v>498</v>
       </c>
       <c r="K174" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F174,'feed pars'!B$6:B$43,0))</f>
-        <v>27.903096000000001</v>
+        <v>18.6602216</v>
       </c>
       <c r="M174" s="3"/>
     </row>
     <row r="175" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F175" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J175" t="s">
         <v>498</v>
       </c>
       <c r="K175" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F175,'feed pars'!B$6:B$43,0))</f>
-        <v>26.501456000000001</v>
+        <v>18.2284328</v>
       </c>
       <c r="M175" s="3"/>
     </row>
     <row r="176" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F176" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="J176" t="s">
         <v>498</v>
       </c>
       <c r="K176" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F176,'feed pars'!B$6:B$43,0))</f>
-        <v>39.329599999999999</v>
+        <v>17.924256</v>
       </c>
       <c r="M176" s="3"/>
     </row>
     <row r="177" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F177" t="s">
-        <v>302</v>
+        <v>40</v>
       </c>
       <c r="J177" t="s">
         <v>498</v>
       </c>
       <c r="K177" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F177,'feed pars'!B$6:B$43,0))</f>
-        <v>16.927627199999996</v>
+        <v>18.3899352</v>
       </c>
       <c r="M177" s="3"/>
     </row>
     <row r="178" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F178" t="s">
-        <v>314</v>
+        <v>41</v>
       </c>
       <c r="J178" t="s">
         <v>498</v>
       </c>
       <c r="K178" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F178,'feed pars'!B$6:B$43,0))</f>
-        <v>22.965976000000001</v>
+        <v>18.478217600000001</v>
       </c>
       <c r="M178" s="3"/>
     </row>
     <row r="179" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F179" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J179" t="s">
         <v>498</v>
       </c>
       <c r="K179" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F179,'feed pars'!B$6:B$43,0))</f>
-        <v>19.589487999999999</v>
+        <v>18.737207199999997</v>
       </c>
       <c r="M179" s="3"/>
     </row>
     <row r="180" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F180" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="J180" t="s">
         <v>498</v>
       </c>
       <c r="K180" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F180,'feed pars'!B$6:B$43,0))</f>
-        <v>20.560594400000003</v>
+        <v>27.903096000000001</v>
       </c>
       <c r="M180" s="3"/>
     </row>
     <row r="181" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F181" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="J181" t="s">
         <v>498</v>
       </c>
       <c r="K181" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F181,'feed pars'!B$6:B$43,0))</f>
-        <v>19.4920008</v>
+        <v>26.501456000000001</v>
       </c>
       <c r="M181" s="3"/>
     </row>
     <row r="182" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F182" t="s">
-        <v>46</v>
+        <v>310</v>
       </c>
       <c r="J182" t="s">
         <v>498</v>
       </c>
       <c r="K182" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F182,'feed pars'!B$6:B$43,0))</f>
-        <v>19.083224000000001</v>
+        <v>39.329599999999999</v>
       </c>
       <c r="M182" s="3"/>
     </row>
     <row r="183" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F183" t="s">
-        <v>47</v>
+        <v>302</v>
       </c>
       <c r="J183" t="s">
         <v>498</v>
       </c>
       <c r="K183" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F183,'feed pars'!B$6:B$43,0))</f>
-        <v>19.581538399999999</v>
+        <v>16.927627199999996</v>
       </c>
       <c r="M183" s="3"/>
     </row>
     <row r="184" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F184" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J184" t="s">
         <v>498</v>
       </c>
       <c r="K184" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F184,'feed pars'!B$6:B$43,0))</f>
-        <v>16.971140800000001</v>
+        <v>22.965976000000001</v>
       </c>
       <c r="M184" s="3"/>
     </row>
     <row r="185" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F185" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="J185" t="s">
         <v>498</v>
       </c>
       <c r="K185" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F185,'feed pars'!B$6:B$43,0))</f>
-        <v>18.194124000000002</v>
+        <v>19.589487999999999</v>
       </c>
       <c r="M185" s="3"/>
     </row>
     <row r="186" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F186" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="J186" t="s">
         <v>498</v>
       </c>
       <c r="K186" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F186,'feed pars'!B$6:B$43,0))</f>
-        <v>17.8828344</v>
+        <v>20.560594400000003</v>
       </c>
       <c r="M186" s="3"/>
     </row>
     <row r="187" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F187" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="J187" t="s">
         <v>498</v>
       </c>
       <c r="K187" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F187,'feed pars'!B$6:B$43,0))</f>
-        <v>19.659779199999999</v>
+        <v>19.4920008</v>
       </c>
       <c r="M187" s="3"/>
     </row>
     <row r="188" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F188" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="J188" t="s">
         <v>498</v>
       </c>
       <c r="K188" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F188,'feed pars'!B$6:B$43,0))</f>
-        <v>18.8602168</v>
+        <v>19.083224000000001</v>
       </c>
       <c r="M188" s="3"/>
     </row>
     <row r="189" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F189" t="s">
-        <v>309</v>
+        <v>47</v>
       </c>
       <c r="J189" t="s">
         <v>498</v>
       </c>
       <c r="K189" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F189,'feed pars'!B$6:B$43,0))</f>
-        <v>19.848896</v>
+        <v>19.581538399999999</v>
       </c>
       <c r="M189" s="3"/>
     </row>
     <row r="190" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F190" t="s">
-        <v>384</v>
+        <v>315</v>
       </c>
       <c r="J190" t="s">
         <v>498</v>
       </c>
       <c r="K190" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F190,'feed pars'!B$6:B$43,0))</f>
-        <v>22.900705599999998</v>
+        <v>16.971140800000001</v>
       </c>
       <c r="M190" s="3"/>
     </row>
     <row r="191" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F191" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="J191" t="s">
         <v>498</v>
       </c>
       <c r="K191" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F191,'feed pars'!B$6:B$43,0))</f>
-        <v>16.1615368</v>
+        <v>18.194124000000002</v>
       </c>
       <c r="M191" s="3"/>
     </row>
     <row r="192" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F192" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="J192" t="s">
         <v>498</v>
       </c>
       <c r="K192" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F192,'feed pars'!B$6:B$43,0))</f>
-        <v>17.334312000000001</v>
+        <v>17.8828344</v>
       </c>
       <c r="M192" s="3"/>
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F193" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="J193" t="s">
         <v>498</v>
       </c>
       <c r="K193" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F193,'feed pars'!B$6:B$43,0))</f>
-        <v>16.464040000000001</v>
+        <v>19.659779199999999</v>
       </c>
       <c r="M193" s="3"/>
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F194" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="J194" t="s">
         <v>498</v>
       </c>
       <c r="K194" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F194,'feed pars'!B$6:B$43,0))</f>
-        <v>16.975324799999999</v>
+        <v>18.8602168</v>
       </c>
       <c r="M194" s="3"/>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F195" t="s">
-        <v>56</v>
+        <v>309</v>
       </c>
       <c r="J195" t="s">
         <v>498</v>
       </c>
       <c r="K195" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F195,'feed pars'!B$6:B$43,0))</f>
-        <v>23.055932000000002</v>
+        <v>19.848896</v>
       </c>
       <c r="M195" s="3"/>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F196" t="s">
-        <v>57</v>
+        <v>384</v>
       </c>
       <c r="J196" t="s">
         <v>498</v>
       </c>
       <c r="K196" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F196,'feed pars'!B$6:B$43,0))</f>
-        <v>22.254696000000003</v>
+        <v>22.900705599999998</v>
       </c>
       <c r="M196" s="3"/>
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F197" t="s">
-        <v>320</v>
+        <v>52</v>
       </c>
       <c r="J197" t="s">
         <v>498</v>
       </c>
-      <c r="K197" s="85">
-        <v>0</v>
+      <c r="K197" s="25">
+        <f>INDEX('feed pars'!D$6:D$43,MATCH(F197,'feed pars'!B$6:B$43,0))</f>
+        <v>16.1615368</v>
       </c>
       <c r="M197" s="3"/>
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A198" s="7" t="s">
+      <c r="F198" t="s">
+        <v>53</v>
+      </c>
+      <c r="J198" t="s">
+        <v>498</v>
+      </c>
+      <c r="K198" s="25">
+        <f>INDEX('feed pars'!D$6:D$43,MATCH(F198,'feed pars'!B$6:B$43,0))</f>
+        <v>17.334312000000001</v>
+      </c>
+      <c r="M198" s="3"/>
+    </row>
+    <row r="199" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F199" t="s">
+        <v>54</v>
+      </c>
+      <c r="J199" t="s">
+        <v>498</v>
+      </c>
+      <c r="K199" s="25">
+        <f>INDEX('feed pars'!D$6:D$43,MATCH(F199,'feed pars'!B$6:B$43,0))</f>
+        <v>16.464040000000001</v>
+      </c>
+      <c r="M199" s="3"/>
+    </row>
+    <row r="200" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F200" t="s">
+        <v>55</v>
+      </c>
+      <c r="J200" t="s">
+        <v>498</v>
+      </c>
+      <c r="K200" s="25">
+        <f>INDEX('feed pars'!D$6:D$43,MATCH(F200,'feed pars'!B$6:B$43,0))</f>
+        <v>16.975324799999999</v>
+      </c>
+      <c r="M200" s="3"/>
+    </row>
+    <row r="201" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F201" t="s">
+        <v>56</v>
+      </c>
+      <c r="J201" t="s">
+        <v>498</v>
+      </c>
+      <c r="K201" s="25">
+        <f>INDEX('feed pars'!D$6:D$43,MATCH(F201,'feed pars'!B$6:B$43,0))</f>
+        <v>23.055932000000002</v>
+      </c>
+      <c r="M201" s="3"/>
+    </row>
+    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F202" t="s">
+        <v>57</v>
+      </c>
+      <c r="J202" t="s">
+        <v>498</v>
+      </c>
+      <c r="K202" s="25">
+        <f>INDEX('feed pars'!D$6:D$43,MATCH(F202,'feed pars'!B$6:B$43,0))</f>
+        <v>22.254696000000003</v>
+      </c>
+      <c r="M202" s="3"/>
+    </row>
+    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F203" t="s">
+        <v>320</v>
+      </c>
+      <c r="J203" t="s">
+        <v>498</v>
+      </c>
+      <c r="K203" s="85">
+        <v>0</v>
+      </c>
+      <c r="M203" s="3"/>
+    </row>
+    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A204" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B198" s="7"/>
-      <c r="C198" s="6"/>
-      <c r="D198" s="6"/>
-      <c r="E198" s="6"/>
-      <c r="F198" s="6"/>
-      <c r="G198" s="6"/>
-      <c r="H198" s="6"/>
-      <c r="I198" s="6"/>
-      <c r="J198" s="6"/>
-      <c r="K198" s="6"/>
-      <c r="L198" s="6"/>
-      <c r="M198" s="6"/>
-      <c r="N198" s="6"/>
-    </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A199" t="s">
-        <v>24</v>
-      </c>
-      <c r="F199" t="s">
-        <v>306</v>
-      </c>
-      <c r="J199" t="s">
-        <v>18</v>
-      </c>
-      <c r="K199" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F199,'feed pars'!B$6:B$43,0))</f>
-        <v>11.3</v>
-      </c>
-      <c r="L199" t="s">
-        <v>19</v>
-      </c>
-      <c r="M199" s="26" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A200" t="s">
-        <v>24</v>
-      </c>
-      <c r="F200" t="s">
-        <v>307</v>
-      </c>
-      <c r="J200" t="s">
-        <v>18</v>
-      </c>
-      <c r="K200" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F200,'feed pars'!B$6:B$43,0))</f>
-        <v>10.1</v>
-      </c>
-      <c r="M200" s="3"/>
-    </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
-        <v>24</v>
-      </c>
-      <c r="F201" t="s">
-        <v>308</v>
-      </c>
-      <c r="J201" t="s">
-        <v>18</v>
-      </c>
-      <c r="K201" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F201,'feed pars'!B$6:B$43,0))</f>
-        <v>9.25</v>
-      </c>
-      <c r="M201" s="3"/>
-    </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A202" t="s">
-        <v>24</v>
-      </c>
-      <c r="F202" t="s">
-        <v>12</v>
-      </c>
-      <c r="J202" t="s">
-        <v>18</v>
-      </c>
-      <c r="K202" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F202,'feed pars'!B$6:B$43,0))</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A203" t="s">
-        <v>24</v>
-      </c>
-      <c r="F203" t="s">
-        <v>33</v>
-      </c>
-      <c r="J203" t="s">
-        <v>18</v>
-      </c>
-      <c r="K203" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F203,'feed pars'!B$6:B$43,0))</f>
-        <v>9.9416666666666664</v>
-      </c>
-    </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A204" t="s">
-        <v>24</v>
-      </c>
-      <c r="F204" t="s">
-        <v>17</v>
-      </c>
-      <c r="J204" t="s">
-        <v>18</v>
-      </c>
-      <c r="K204" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F204,'feed pars'!B$6:B$43,0))</f>
-        <v>14.1</v>
-      </c>
+      <c r="B204" s="7"/>
+      <c r="C204" s="6"/>
+      <c r="D204" s="6"/>
+      <c r="E204" s="6"/>
+      <c r="F204" s="6"/>
+      <c r="G204" s="6"/>
+      <c r="H204" s="6"/>
+      <c r="I204" s="6"/>
+      <c r="J204" s="6"/>
+      <c r="K204" s="6"/>
+      <c r="L204" s="6"/>
+      <c r="M204" s="6"/>
+      <c r="N204" s="6"/>
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>24</v>
       </c>
       <c r="F205" t="s">
-        <v>37</v>
+        <v>306</v>
       </c>
       <c r="J205" t="s">
         <v>18</v>
       </c>
       <c r="K205" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F205,'feed pars'!B$6:B$43,0))</f>
-        <v>13.2</v>
+        <v>11.3</v>
+      </c>
+      <c r="L205" t="s">
+        <v>19</v>
+      </c>
+      <c r="M205" s="26" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.25">
@@ -5915,44 +5978,46 @@
         <v>24</v>
       </c>
       <c r="F206" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
       <c r="J206" t="s">
         <v>18</v>
       </c>
       <c r="K206" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F206,'feed pars'!B$6:B$43,0))</f>
-        <v>11.7</v>
-      </c>
+        <v>10.1</v>
+      </c>
+      <c r="M206" s="3"/>
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>24</v>
       </c>
       <c r="F207" t="s">
-        <v>39</v>
+        <v>308</v>
       </c>
       <c r="J207" t="s">
         <v>18</v>
       </c>
       <c r="K207" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F207,'feed pars'!B$6:B$43,0))</f>
-        <v>14</v>
-      </c>
+        <v>9.25</v>
+      </c>
+      <c r="M207" s="3"/>
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>24</v>
       </c>
       <c r="F208" t="s">
-        <v>313</v>
+        <v>12</v>
       </c>
       <c r="J208" t="s">
         <v>18</v>
       </c>
       <c r="K208" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F208,'feed pars'!B$6:B$43,0))</f>
-        <v>13.9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.25">
@@ -5960,14 +6025,14 @@
         <v>24</v>
       </c>
       <c r="F209" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="J209" t="s">
         <v>18</v>
       </c>
       <c r="K209" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F209,'feed pars'!B$6:B$43,0))</f>
-        <v>12.8</v>
+        <v>9.9416666666666664</v>
       </c>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
@@ -5975,14 +6040,14 @@
         <v>24</v>
       </c>
       <c r="F210" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="J210" t="s">
         <v>18</v>
       </c>
       <c r="K210" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F210,'feed pars'!B$6:B$43,0))</f>
-        <v>13.8</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.25">
@@ -5990,14 +6055,14 @@
         <v>24</v>
       </c>
       <c r="F211" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="J211" t="s">
         <v>18</v>
       </c>
       <c r="K211" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F211,'feed pars'!B$6:B$43,0))</f>
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.25">
@@ -6005,14 +6070,14 @@
         <v>24</v>
       </c>
       <c r="F212" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J212" t="s">
         <v>18</v>
       </c>
       <c r="K212" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F212,'feed pars'!B$6:B$43,0))</f>
-        <v>22.1</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.25">
@@ -6020,14 +6085,14 @@
         <v>24</v>
       </c>
       <c r="F213" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J213" t="s">
         <v>18</v>
       </c>
       <c r="K213" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F213,'feed pars'!B$6:B$43,0))</f>
-        <v>20.100000000000001</v>
+        <v>14</v>
       </c>
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.25">
@@ -6035,14 +6100,14 @@
         <v>24</v>
       </c>
       <c r="F214" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="J214" t="s">
         <v>18</v>
       </c>
       <c r="K214" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F214,'feed pars'!B$6:B$43,0))</f>
-        <v>6.6</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.25">
@@ -6050,14 +6115,14 @@
         <v>24</v>
       </c>
       <c r="F215" t="s">
-        <v>310</v>
+        <v>40</v>
       </c>
       <c r="J215" t="s">
         <v>18</v>
       </c>
       <c r="K215" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F215,'feed pars'!B$6:B$43,0))</f>
-        <v>36.6</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.25">
@@ -6065,14 +6130,14 @@
         <v>24</v>
       </c>
       <c r="F216" t="s">
-        <v>314</v>
+        <v>41</v>
       </c>
       <c r="J216" t="s">
         <v>18</v>
       </c>
       <c r="K216" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F216,'feed pars'!B$6:B$43,0))</f>
-        <v>16.399999999999999</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.25">
@@ -6080,14 +6145,14 @@
         <v>24</v>
       </c>
       <c r="F217" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J217" t="s">
         <v>18</v>
       </c>
       <c r="K217" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F217,'feed pars'!B$6:B$43,0))</f>
-        <v>14.6</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.25">
@@ -6095,14 +6160,14 @@
         <v>24</v>
       </c>
       <c r="F218" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J218" t="s">
         <v>18</v>
       </c>
       <c r="K218" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F218,'feed pars'!B$6:B$43,0))</f>
-        <v>12.2</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.25">
@@ -6110,14 +6175,14 @@
         <v>24</v>
       </c>
       <c r="F219" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="J219" t="s">
         <v>18</v>
       </c>
       <c r="K219" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F219,'feed pars'!B$6:B$43,0))</f>
-        <v>11.4</v>
+        <v>20.100000000000001</v>
       </c>
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.25">
@@ -6125,14 +6190,14 @@
         <v>24</v>
       </c>
       <c r="F220" t="s">
-        <v>47</v>
+        <v>302</v>
       </c>
       <c r="J220" t="s">
         <v>18</v>
       </c>
       <c r="K220" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F220,'feed pars'!B$6:B$43,0))</f>
-        <v>13.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.25">
@@ -6140,14 +6205,14 @@
         <v>24</v>
       </c>
       <c r="F221" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="J221" t="s">
         <v>18</v>
       </c>
       <c r="K221" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F221,'feed pars'!B$6:B$43,0))</f>
-        <v>8.5</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.25">
@@ -6155,14 +6220,14 @@
         <v>24</v>
       </c>
       <c r="F222" t="s">
-        <v>48</v>
+        <v>314</v>
       </c>
       <c r="J222" t="s">
         <v>18</v>
       </c>
       <c r="K222" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F222,'feed pars'!B$6:B$43,0))</f>
-        <v>11</v>
+        <v>16.399999999999999</v>
       </c>
     </row>
     <row r="223" spans="1:11" x14ac:dyDescent="0.25">
@@ -6170,14 +6235,14 @@
         <v>24</v>
       </c>
       <c r="F223" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="J223" t="s">
         <v>18</v>
       </c>
       <c r="K223" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F223,'feed pars'!B$6:B$43,0))</f>
-        <v>13.3</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.25">
@@ -6185,14 +6250,14 @@
         <v>24</v>
       </c>
       <c r="F224" t="s">
-        <v>309</v>
+        <v>36</v>
       </c>
       <c r="J224" t="s">
         <v>18</v>
       </c>
       <c r="K224" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F224,'feed pars'!B$6:B$43,0))</f>
-        <v>11.6</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="225" spans="1:13" x14ac:dyDescent="0.25">
@@ -6200,14 +6265,14 @@
         <v>24</v>
       </c>
       <c r="F225" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="J225" t="s">
         <v>18</v>
       </c>
       <c r="K225" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F225,'feed pars'!B$6:B$43,0))</f>
-        <v>12.4</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="226" spans="1:13" x14ac:dyDescent="0.25">
@@ -6215,14 +6280,14 @@
         <v>24</v>
       </c>
       <c r="F226" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="J226" t="s">
         <v>18</v>
       </c>
       <c r="K226" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F226,'feed pars'!B$6:B$43,0))</f>
-        <v>12.3</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="227" spans="1:13" x14ac:dyDescent="0.25">
@@ -6230,14 +6295,14 @@
         <v>24</v>
       </c>
       <c r="F227" t="s">
-        <v>54</v>
+        <v>315</v>
       </c>
       <c r="J227" t="s">
         <v>18</v>
       </c>
       <c r="K227" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F227,'feed pars'!B$6:B$43,0))</f>
-        <v>13.6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="228" spans="1:13" x14ac:dyDescent="0.25">
@@ -6245,14 +6310,14 @@
         <v>24</v>
       </c>
       <c r="F228" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="J228" t="s">
         <v>18</v>
       </c>
       <c r="K228" s="25">
         <f>INDEX('feed pars'!I$6:I$43,MATCH(F228,'feed pars'!B$6:B$43,0))</f>
-        <v>15.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="229" spans="1:13" x14ac:dyDescent="0.25">
@@ -6260,13 +6325,14 @@
         <v>24</v>
       </c>
       <c r="F229" t="s">
-        <v>320</v>
+        <v>50</v>
       </c>
       <c r="J229" t="s">
         <v>18</v>
       </c>
-      <c r="K229" s="3">
-        <v>0</v>
+      <c r="K229" s="25">
+        <f>INDEX('feed pars'!I$6:I$43,MATCH(F229,'feed pars'!B$6:B$43,0))</f>
+        <v>13.3</v>
       </c>
     </row>
     <row r="230" spans="1:13" x14ac:dyDescent="0.25">
@@ -6274,20 +6340,14 @@
         <v>24</v>
       </c>
       <c r="F230" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="J230" t="s">
-        <v>500</v>
-      </c>
-      <c r="K230" s="82">
-        <f>INDEX('feed pars'!K$6:K$43,MATCH(F230,'feed pars'!B$6:B$43,0))</f>
-        <v>20</v>
-      </c>
-      <c r="L230" t="s">
-        <v>501</v>
-      </c>
-      <c r="M230" s="26" t="s">
-        <v>505</v>
+        <v>18</v>
+      </c>
+      <c r="K230" s="25">
+        <f>INDEX('feed pars'!I$6:I$43,MATCH(F230,'feed pars'!B$6:B$43,0))</f>
+        <v>11.6</v>
       </c>
     </row>
     <row r="231" spans="1:13" x14ac:dyDescent="0.25">
@@ -6295,46 +6355,44 @@
         <v>24</v>
       </c>
       <c r="F231" t="s">
-        <v>307</v>
+        <v>52</v>
       </c>
       <c r="J231" t="s">
-        <v>500</v>
-      </c>
-      <c r="K231" s="82">
-        <f>INDEX('feed pars'!K$6:K$43,MATCH(F231,'feed pars'!B$6:B$43,0))</f>
-        <v>20</v>
-      </c>
-      <c r="M231" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="K231" s="25">
+        <f>INDEX('feed pars'!I$6:I$43,MATCH(F231,'feed pars'!B$6:B$43,0))</f>
+        <v>12.4</v>
+      </c>
     </row>
     <row r="232" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>24</v>
       </c>
       <c r="F232" t="s">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="J232" t="s">
-        <v>500</v>
-      </c>
-      <c r="K232" s="82">
-        <f>INDEX('feed pars'!K$6:K$43,MATCH(F232,'feed pars'!B$6:B$43,0))</f>
-        <v>36</v>
-      </c>
-      <c r="M232" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="K232" s="25">
+        <f>INDEX('feed pars'!I$6:I$43,MATCH(F232,'feed pars'!B$6:B$43,0))</f>
+        <v>12.3</v>
+      </c>
     </row>
     <row r="233" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>24</v>
       </c>
       <c r="F233" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="J233" t="s">
-        <v>500</v>
-      </c>
-      <c r="K233" s="82">
-        <f>INDEX('feed pars'!K$6:K$43,MATCH(F233,'feed pars'!B$6:B$43,0))</f>
-        <v>30</v>
+        <v>18</v>
+      </c>
+      <c r="K233" s="25">
+        <f>INDEX('feed pars'!I$6:I$43,MATCH(F233,'feed pars'!B$6:B$43,0))</f>
+        <v>13.6</v>
       </c>
     </row>
     <row r="234" spans="1:13" x14ac:dyDescent="0.25">
@@ -6342,14 +6400,14 @@
         <v>24</v>
       </c>
       <c r="F234" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="J234" t="s">
-        <v>500</v>
-      </c>
-      <c r="K234" s="82">
-        <f>INDEX('feed pars'!K$6:K$43,MATCH(F234,'feed pars'!B$6:B$43,0))</f>
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="K234" s="25">
+        <f>INDEX('feed pars'!I$6:I$43,MATCH(F234,'feed pars'!B$6:B$43,0))</f>
+        <v>15.5</v>
       </c>
     </row>
     <row r="235" spans="1:13" x14ac:dyDescent="0.25">
@@ -6357,14 +6415,13 @@
         <v>24</v>
       </c>
       <c r="F235" t="s">
-        <v>17</v>
+        <v>320</v>
       </c>
       <c r="J235" t="s">
-        <v>500</v>
-      </c>
-      <c r="K235" s="82">
-        <f>INDEX('feed pars'!K$6:K$43,MATCH(F235,'feed pars'!B$6:B$43,0))</f>
-        <v>25</v>
+        <v>18</v>
+      </c>
+      <c r="K235" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="236" spans="1:13" x14ac:dyDescent="0.25">
@@ -6372,14 +6429,20 @@
         <v>24</v>
       </c>
       <c r="F236" t="s">
-        <v>37</v>
+        <v>306</v>
       </c>
       <c r="J236" t="s">
         <v>500</v>
       </c>
       <c r="K236" s="82">
         <f>INDEX('feed pars'!K$6:K$43,MATCH(F236,'feed pars'!B$6:B$43,0))</f>
-        <v>27</v>
+        <v>20</v>
+      </c>
+      <c r="L236" t="s">
+        <v>501</v>
+      </c>
+      <c r="M236" s="26" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="237" spans="1:13" x14ac:dyDescent="0.25">
@@ -6387,44 +6450,46 @@
         <v>24</v>
       </c>
       <c r="F237" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
       <c r="J237" t="s">
         <v>500</v>
       </c>
       <c r="K237" s="82">
         <f>INDEX('feed pars'!K$6:K$43,MATCH(F237,'feed pars'!B$6:B$43,0))</f>
-        <v>61</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="M237" s="3"/>
     </row>
     <row r="238" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>24</v>
       </c>
       <c r="F238" t="s">
-        <v>39</v>
+        <v>308</v>
       </c>
       <c r="J238" t="s">
         <v>500</v>
       </c>
       <c r="K238" s="82">
         <f>INDEX('feed pars'!K$6:K$43,MATCH(F238,'feed pars'!B$6:B$43,0))</f>
-        <v>26</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M238" s="3"/>
     </row>
     <row r="239" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>24</v>
       </c>
       <c r="F239" t="s">
-        <v>313</v>
+        <v>12</v>
       </c>
       <c r="J239" t="s">
         <v>500</v>
       </c>
       <c r="K239" s="82">
         <f>INDEX('feed pars'!K$6:K$43,MATCH(F239,'feed pars'!B$6:B$43,0))</f>
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="240" spans="1:13" x14ac:dyDescent="0.25">
@@ -6432,14 +6497,14 @@
         <v>24</v>
       </c>
       <c r="F240" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="J240" t="s">
         <v>500</v>
       </c>
       <c r="K240" s="82">
         <f>INDEX('feed pars'!K$6:K$43,MATCH(F240,'feed pars'!B$6:B$43,0))</f>
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="241" spans="1:11" x14ac:dyDescent="0.25">
@@ -6447,14 +6512,14 @@
         <v>24</v>
       </c>
       <c r="F241" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="J241" t="s">
         <v>500</v>
       </c>
       <c r="K241" s="82">
         <f>INDEX('feed pars'!K$6:K$43,MATCH(F241,'feed pars'!B$6:B$43,0))</f>
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.25">
@@ -6462,14 +6527,14 @@
         <v>24</v>
       </c>
       <c r="F242" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="J242" t="s">
         <v>500</v>
       </c>
       <c r="K242" s="82">
         <f>INDEX('feed pars'!K$6:K$43,MATCH(F242,'feed pars'!B$6:B$43,0))</f>
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.25">
@@ -6477,14 +6542,14 @@
         <v>24</v>
       </c>
       <c r="F243" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J243" t="s">
         <v>500</v>
       </c>
       <c r="K243" s="82">
         <f>INDEX('feed pars'!K$6:K$43,MATCH(F243,'feed pars'!B$6:B$43,0))</f>
-        <v>460</v>
+        <v>61</v>
       </c>
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.25">
@@ -6492,14 +6557,14 @@
         <v>24</v>
       </c>
       <c r="F244" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J244" t="s">
         <v>500</v>
       </c>
       <c r="K244" s="82">
         <f>INDEX('feed pars'!K$6:K$43,MATCH(F244,'feed pars'!B$6:B$43,0))</f>
-        <v>380</v>
+        <v>26</v>
       </c>
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.25">
@@ -6507,7 +6572,7 @@
         <v>24</v>
       </c>
       <c r="F245" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="J245" t="s">
         <v>500</v>
@@ -6522,14 +6587,14 @@
         <v>24</v>
       </c>
       <c r="F246" t="s">
-        <v>310</v>
+        <v>40</v>
       </c>
       <c r="J246" t="s">
         <v>500</v>
       </c>
       <c r="K246" s="82">
         <f>INDEX('feed pars'!K$6:K$43,MATCH(F246,'feed pars'!B$6:B$43,0))</f>
-        <v>1000</v>
+        <v>40</v>
       </c>
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.25">
@@ -6537,14 +6602,14 @@
         <v>24</v>
       </c>
       <c r="F247" t="s">
-        <v>314</v>
+        <v>41</v>
       </c>
       <c r="J247" t="s">
         <v>500</v>
       </c>
       <c r="K247" s="82">
         <f>INDEX('feed pars'!K$6:K$43,MATCH(F247,'feed pars'!B$6:B$43,0))</f>
-        <v>180</v>
+        <v>17</v>
       </c>
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.25">
@@ -6552,14 +6617,14 @@
         <v>24</v>
       </c>
       <c r="F248" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J248" t="s">
         <v>500</v>
       </c>
       <c r="K248" s="82">
         <f>INDEX('feed pars'!K$6:K$43,MATCH(F248,'feed pars'!B$6:B$43,0))</f>
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.25">
@@ -6567,14 +6632,14 @@
         <v>24</v>
       </c>
       <c r="F249" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J249" t="s">
         <v>500</v>
       </c>
       <c r="K249" s="82">
         <f>INDEX('feed pars'!K$6:K$43,MATCH(F249,'feed pars'!B$6:B$43,0))</f>
-        <v>46</v>
+        <v>460</v>
       </c>
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.25">
@@ -6582,14 +6647,14 @@
         <v>24</v>
       </c>
       <c r="F250" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="J250" t="s">
         <v>500</v>
       </c>
       <c r="K250" s="82">
         <f>INDEX('feed pars'!K$6:K$43,MATCH(F250,'feed pars'!B$6:B$43,0))</f>
-        <v>10</v>
+        <v>380</v>
       </c>
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.25">
@@ -6597,14 +6662,14 @@
         <v>24</v>
       </c>
       <c r="F251" t="s">
-        <v>47</v>
+        <v>302</v>
       </c>
       <c r="J251" t="s">
         <v>500</v>
       </c>
       <c r="K251" s="82">
         <f>INDEX('feed pars'!K$6:K$43,MATCH(F251,'feed pars'!B$6:B$43,0))</f>
-        <v>97</v>
+        <v>20</v>
       </c>
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.25">
@@ -6612,14 +6677,14 @@
         <v>24</v>
       </c>
       <c r="F252" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="J252" t="s">
         <v>500</v>
       </c>
       <c r="K252" s="82">
         <f>INDEX('feed pars'!K$6:K$43,MATCH(F252,'feed pars'!B$6:B$43,0))</f>
-        <v>27</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.25">
@@ -6627,14 +6692,14 @@
         <v>24</v>
       </c>
       <c r="F253" t="s">
-        <v>48</v>
+        <v>314</v>
       </c>
       <c r="J253" t="s">
         <v>500</v>
       </c>
       <c r="K253" s="82">
         <f>INDEX('feed pars'!K$6:K$43,MATCH(F253,'feed pars'!B$6:B$43,0))</f>
-        <v>45</v>
+        <v>180</v>
       </c>
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.25">
@@ -6642,14 +6707,14 @@
         <v>24</v>
       </c>
       <c r="F254" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="J254" t="s">
         <v>500</v>
       </c>
       <c r="K254" s="82">
         <f>INDEX('feed pars'!K$6:K$43,MATCH(F254,'feed pars'!B$6:B$43,0))</f>
-        <v>45</v>
+        <v>10</v>
       </c>
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.25">
@@ -6657,14 +6722,14 @@
         <v>24</v>
       </c>
       <c r="F255" t="s">
-        <v>309</v>
+        <v>36</v>
       </c>
       <c r="J255" t="s">
         <v>500</v>
       </c>
       <c r="K255" s="82">
         <f>INDEX('feed pars'!K$6:K$43,MATCH(F255,'feed pars'!B$6:B$43,0))</f>
-        <v>80</v>
+        <v>46</v>
       </c>
     </row>
     <row r="256" spans="1:11" x14ac:dyDescent="0.25">
@@ -6672,14 +6737,14 @@
         <v>24</v>
       </c>
       <c r="F256" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="J256" t="s">
         <v>500</v>
       </c>
       <c r="K256" s="82">
         <f>INDEX('feed pars'!K$6:K$43,MATCH(F256,'feed pars'!B$6:B$43,0))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="257" spans="1:14" x14ac:dyDescent="0.25">
@@ -6687,14 +6752,14 @@
         <v>24</v>
       </c>
       <c r="F257" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="J257" t="s">
         <v>500</v>
       </c>
       <c r="K257" s="82">
         <f>INDEX('feed pars'!K$6:K$43,MATCH(F257,'feed pars'!B$6:B$43,0))</f>
-        <v>32</v>
+        <v>97</v>
       </c>
     </row>
     <row r="258" spans="1:14" x14ac:dyDescent="0.25">
@@ -6702,14 +6767,14 @@
         <v>24</v>
       </c>
       <c r="F258" t="s">
-        <v>54</v>
+        <v>315</v>
       </c>
       <c r="J258" t="s">
         <v>500</v>
       </c>
       <c r="K258" s="82">
         <f>INDEX('feed pars'!K$6:K$43,MATCH(F258,'feed pars'!B$6:B$43,0))</f>
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="259" spans="1:14" x14ac:dyDescent="0.25">
@@ -6717,14 +6782,14 @@
         <v>24</v>
       </c>
       <c r="F259" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="J259" t="s">
         <v>500</v>
       </c>
       <c r="K259" s="82">
         <f>INDEX('feed pars'!K$6:K$43,MATCH(F259,'feed pars'!B$6:B$43,0))</f>
-        <v>33</v>
+        <v>45</v>
       </c>
     </row>
     <row r="260" spans="1:14" x14ac:dyDescent="0.25">
@@ -6732,130 +6797,142 @@
         <v>24</v>
       </c>
       <c r="F260" t="s">
-        <v>320</v>
+        <v>50</v>
       </c>
       <c r="J260" t="s">
         <v>500</v>
       </c>
-      <c r="K260" s="3">
-        <v>0</v>
+      <c r="K260" s="82">
+        <f>INDEX('feed pars'!K$6:K$43,MATCH(F260,'feed pars'!B$6:B$43,0))</f>
+        <v>45</v>
       </c>
     </row>
     <row r="261" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A261" s="7" t="s">
-        <v>405</v>
-      </c>
-      <c r="B261" s="7"/>
-      <c r="C261" s="6"/>
-      <c r="D261" s="6"/>
-      <c r="E261" s="6"/>
-      <c r="F261" s="6"/>
-      <c r="G261" s="6"/>
-      <c r="H261" s="6"/>
-      <c r="I261" s="6"/>
-      <c r="J261" s="6"/>
-      <c r="K261" s="6"/>
-      <c r="L261" s="6"/>
-      <c r="M261" s="6"/>
-      <c r="N261" s="6"/>
+      <c r="A261" t="s">
+        <v>24</v>
+      </c>
+      <c r="F261" t="s">
+        <v>309</v>
+      </c>
+      <c r="J261" t="s">
+        <v>500</v>
+      </c>
+      <c r="K261" s="82">
+        <f>INDEX('feed pars'!K$6:K$43,MATCH(F261,'feed pars'!B$6:B$43,0))</f>
+        <v>80</v>
+      </c>
     </row>
     <row r="262" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>391</v>
+        <v>24</v>
       </c>
       <c r="F262" t="s">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="J262" t="s">
-        <v>18</v>
-      </c>
-      <c r="K262" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F262,'feed pars'!B$6:B$43,0))</f>
-        <v>9.1</v>
-      </c>
-      <c r="L262" t="s">
-        <v>19</v>
-      </c>
-      <c r="M262" s="26" t="s">
-        <v>502</v>
+        <v>500</v>
+      </c>
+      <c r="K262" s="82">
+        <f>INDEX('feed pars'!K$6:K$43,MATCH(F262,'feed pars'!B$6:B$43,0))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="263" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>391</v>
+        <v>24</v>
       </c>
       <c r="F263" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="J263" t="s">
-        <v>18</v>
-      </c>
-      <c r="K263" s="31">
-        <f>K203</f>
-        <v>9.9416666666666664</v>
+        <v>500</v>
+      </c>
+      <c r="K263" s="82">
+        <f>INDEX('feed pars'!K$6:K$43,MATCH(F263,'feed pars'!B$6:B$43,0))</f>
+        <v>32</v>
       </c>
     </row>
     <row r="264" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K264" s="31"/>
+      <c r="A264" t="s">
+        <v>24</v>
+      </c>
+      <c r="F264" t="s">
+        <v>54</v>
+      </c>
+      <c r="J264" t="s">
+        <v>500</v>
+      </c>
+      <c r="K264" s="82">
+        <f>INDEX('feed pars'!K$6:K$43,MATCH(F264,'feed pars'!B$6:B$43,0))</f>
+        <v>10</v>
+      </c>
     </row>
     <row r="265" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>391</v>
+        <v>24</v>
       </c>
       <c r="F265" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="J265" t="s">
-        <v>18</v>
-      </c>
-      <c r="K265" s="31">
-        <f>K206</f>
-        <v>11.7</v>
+        <v>500</v>
+      </c>
+      <c r="K265" s="82">
+        <f>INDEX('feed pars'!K$6:K$43,MATCH(F265,'feed pars'!B$6:B$43,0))</f>
+        <v>33</v>
       </c>
     </row>
     <row r="266" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>391</v>
+        <v>24</v>
       </c>
       <c r="F266" t="s">
-        <v>37</v>
+        <v>320</v>
       </c>
       <c r="J266" t="s">
-        <v>18</v>
-      </c>
-      <c r="K266" s="31">
-        <f>K205</f>
-        <v>13.2</v>
+        <v>500</v>
+      </c>
+      <c r="K266" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="267" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A267" t="s">
-        <v>391</v>
-      </c>
-      <c r="F267" t="s">
-        <v>17</v>
-      </c>
-      <c r="J267" t="s">
-        <v>18</v>
-      </c>
-      <c r="K267" s="31">
-        <f>K204</f>
-        <v>14.1</v>
-      </c>
+      <c r="A267" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="B267" s="7"/>
+      <c r="C267" s="6"/>
+      <c r="D267" s="6"/>
+      <c r="E267" s="6"/>
+      <c r="F267" s="6"/>
+      <c r="G267" s="6"/>
+      <c r="H267" s="6"/>
+      <c r="I267" s="6"/>
+      <c r="J267" s="6"/>
+      <c r="K267" s="6"/>
+      <c r="L267" s="6"/>
+      <c r="M267" s="6"/>
+      <c r="N267" s="6"/>
     </row>
     <row r="268" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>391</v>
       </c>
       <c r="F268" t="s">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="J268" t="s">
         <v>18</v>
       </c>
-      <c r="K268" s="31">
-        <f t="shared" ref="K268:K274" si="14">K205</f>
-        <v>13.2</v>
+      <c r="K268" s="25">
+        <f>INDEX('feed pars'!I$6:I$43,MATCH(F268,'feed pars'!B$6:B$43,0))</f>
+        <v>9.1</v>
+      </c>
+      <c r="L268" t="s">
+        <v>19</v>
+      </c>
+      <c r="M268" s="26" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="269" spans="1:14" x14ac:dyDescent="0.25">
@@ -6863,44 +6940,32 @@
         <v>391</v>
       </c>
       <c r="F269" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="J269" t="s">
         <v>18</v>
       </c>
       <c r="K269" s="31">
-        <f t="shared" si="14"/>
-        <v>11.7</v>
+        <f>K209</f>
+        <v>9.9416666666666664</v>
       </c>
     </row>
     <row r="270" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A270" t="s">
-        <v>391</v>
-      </c>
-      <c r="F270" t="s">
-        <v>310</v>
-      </c>
-      <c r="J270" t="s">
-        <v>18</v>
-      </c>
-      <c r="K270" s="31">
-        <f t="shared" si="14"/>
-        <v>14</v>
-      </c>
+      <c r="K270" s="31"/>
     </row>
     <row r="271" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>391</v>
       </c>
       <c r="F271" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="J271" t="s">
         <v>18</v>
       </c>
       <c r="K271" s="31">
-        <f t="shared" si="14"/>
-        <v>13.9</v>
+        <f>K212</f>
+        <v>11.7</v>
       </c>
     </row>
     <row r="272" spans="1:14" x14ac:dyDescent="0.25">
@@ -6908,14 +6973,14 @@
         <v>391</v>
       </c>
       <c r="F272" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="J272" t="s">
         <v>18</v>
       </c>
       <c r="K272" s="31">
-        <f t="shared" si="14"/>
-        <v>12.8</v>
+        <f>K211</f>
+        <v>13.2</v>
       </c>
     </row>
     <row r="273" spans="1:14" x14ac:dyDescent="0.25">
@@ -6923,14 +6988,14 @@
         <v>391</v>
       </c>
       <c r="F273" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="J273" t="s">
         <v>18</v>
       </c>
       <c r="K273" s="31">
-        <f t="shared" si="14"/>
-        <v>13.8</v>
+        <f>K210</f>
+        <v>14.1</v>
       </c>
     </row>
     <row r="274" spans="1:14" x14ac:dyDescent="0.25">
@@ -6938,168 +7003,144 @@
         <v>391</v>
       </c>
       <c r="F274" t="s">
-        <v>315</v>
+        <v>49</v>
       </c>
       <c r="J274" t="s">
         <v>18</v>
       </c>
       <c r="K274" s="31">
+        <f t="shared" ref="K274:K280" si="14">K211</f>
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="275" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>391</v>
+      </c>
+      <c r="F275" t="s">
+        <v>48</v>
+      </c>
+      <c r="J275" t="s">
+        <v>18</v>
+      </c>
+      <c r="K275" s="31">
+        <f t="shared" si="14"/>
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="276" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>391</v>
+      </c>
+      <c r="F276" t="s">
+        <v>310</v>
+      </c>
+      <c r="J276" t="s">
+        <v>18</v>
+      </c>
+      <c r="K276" s="31">
+        <f t="shared" si="14"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="277" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>391</v>
+      </c>
+      <c r="F277" t="s">
+        <v>53</v>
+      </c>
+      <c r="J277" t="s">
+        <v>18</v>
+      </c>
+      <c r="K277" s="31">
+        <f t="shared" si="14"/>
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="278" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>391</v>
+      </c>
+      <c r="F278" t="s">
+        <v>52</v>
+      </c>
+      <c r="J278" t="s">
+        <v>18</v>
+      </c>
+      <c r="K278" s="31">
+        <f t="shared" si="14"/>
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="279" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>391</v>
+      </c>
+      <c r="F279" t="s">
+        <v>56</v>
+      </c>
+      <c r="J279" t="s">
+        <v>18</v>
+      </c>
+      <c r="K279" s="31">
+        <f t="shared" si="14"/>
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="280" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>391</v>
+      </c>
+      <c r="F280" t="s">
+        <v>315</v>
+      </c>
+      <c r="J280" t="s">
+        <v>18</v>
+      </c>
+      <c r="K280" s="31">
         <f t="shared" si="14"/>
         <v>13.3</v>
       </c>
     </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K275" s="3"/>
-    </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A276" s="8" t="s">
+    <row r="281" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K281" s="3"/>
+    </row>
+    <row r="282" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A282" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B276" s="8"/>
-      <c r="C276" s="9"/>
-      <c r="D276" s="9"/>
-      <c r="E276" s="9"/>
-      <c r="F276" s="9"/>
-      <c r="G276" s="9"/>
-      <c r="H276" s="9"/>
-      <c r="I276" s="9"/>
-      <c r="J276" s="9"/>
-      <c r="K276" s="9"/>
-      <c r="L276" s="9"/>
-      <c r="M276" s="9"/>
-      <c r="N276" s="9"/>
-    </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A277" s="27" t="s">
+      <c r="B282" s="8"/>
+      <c r="C282" s="9"/>
+      <c r="D282" s="9"/>
+      <c r="E282" s="9"/>
+      <c r="F282" s="9"/>
+      <c r="G282" s="9"/>
+      <c r="H282" s="9"/>
+      <c r="I282" s="9"/>
+      <c r="J282" s="9"/>
+      <c r="K282" s="9"/>
+      <c r="L282" s="9"/>
+      <c r="M282" s="9"/>
+      <c r="N282" s="9"/>
+    </row>
+    <row r="283" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A283" s="27" t="s">
         <v>387</v>
       </c>
-      <c r="B277" s="28"/>
-      <c r="C277" s="29"/>
-      <c r="D277" s="29"/>
-      <c r="E277" s="29"/>
-      <c r="F277" s="29"/>
-      <c r="G277" s="29"/>
-      <c r="H277" s="29"/>
-      <c r="I277" s="29"/>
-      <c r="J277" s="29"/>
-      <c r="K277" s="29"/>
-      <c r="L277" s="29"/>
-      <c r="M277" s="29"/>
-      <c r="N277" s="29"/>
-    </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A278" t="s">
-        <v>25</v>
-      </c>
-      <c r="E278" t="s">
-        <v>296</v>
-      </c>
-      <c r="F278" t="s">
-        <v>17</v>
-      </c>
-      <c r="J278" t="s">
-        <v>18</v>
-      </c>
-      <c r="K278" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F278,'feed pars'!B$6:B$43,0))</f>
-        <v>12.3</v>
-      </c>
-      <c r="L278" t="s">
-        <v>297</v>
-      </c>
-      <c r="M278" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A279" t="s">
-        <v>25</v>
-      </c>
-      <c r="E279" t="s">
-        <v>296</v>
-      </c>
-      <c r="F279" t="s">
-        <v>37</v>
-      </c>
-      <c r="J279" t="s">
-        <v>18</v>
-      </c>
-      <c r="K279" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F279,'feed pars'!B$6:B$43,0))</f>
-        <v>11.2</v>
-      </c>
-    </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A280" t="s">
-        <v>25</v>
-      </c>
-      <c r="E280" t="s">
-        <v>296</v>
-      </c>
-      <c r="F280" t="s">
-        <v>38</v>
-      </c>
-      <c r="J280" t="s">
-        <v>18</v>
-      </c>
-      <c r="K280" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F280,'feed pars'!B$6:B$43,0))</f>
-        <v>9.4</v>
-      </c>
-    </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A281" t="s">
-        <v>25</v>
-      </c>
-      <c r="E281" t="s">
-        <v>296</v>
-      </c>
-      <c r="F281" t="s">
-        <v>39</v>
-      </c>
-      <c r="J281" t="s">
-        <v>18</v>
-      </c>
-      <c r="K281" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F281,'feed pars'!B$6:B$43,0))</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A282" t="s">
-        <v>25</v>
-      </c>
-      <c r="E282" t="s">
-        <v>296</v>
-      </c>
-      <c r="F282" t="s">
-        <v>40</v>
-      </c>
-      <c r="J282" t="s">
-        <v>18</v>
-      </c>
-      <c r="K282" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F282,'feed pars'!B$6:B$43,0))</f>
-        <v>13.2</v>
-      </c>
-    </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A283" t="s">
-        <v>25</v>
-      </c>
-      <c r="E283" t="s">
-        <v>296</v>
-      </c>
-      <c r="F283" t="s">
-        <v>41</v>
-      </c>
-      <c r="J283" t="s">
-        <v>18</v>
-      </c>
-      <c r="K283" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F283,'feed pars'!B$6:B$43,0))</f>
-        <v>11.5</v>
-      </c>
+      <c r="B283" s="28"/>
+      <c r="C283" s="29"/>
+      <c r="D283" s="29"/>
+      <c r="E283" s="29"/>
+      <c r="F283" s="29"/>
+      <c r="G283" s="29"/>
+      <c r="H283" s="29"/>
+      <c r="I283" s="29"/>
+      <c r="J283" s="29"/>
+      <c r="K283" s="29"/>
+      <c r="L283" s="29"/>
+      <c r="M283" s="29"/>
+      <c r="N283" s="29"/>
     </row>
     <row r="284" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
@@ -7109,14 +7150,20 @@
         <v>296</v>
       </c>
       <c r="F284" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="J284" t="s">
         <v>18</v>
       </c>
       <c r="K284" s="25">
         <f>INDEX('feed pars'!U$6:U$43,MATCH(F284,'feed pars'!B$6:B$43,0))</f>
-        <v>10.9</v>
+        <v>12.3</v>
+      </c>
+      <c r="L284" t="s">
+        <v>297</v>
+      </c>
+      <c r="M284" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="285" spans="1:14" x14ac:dyDescent="0.25">
@@ -7127,14 +7174,14 @@
         <v>296</v>
       </c>
       <c r="F285" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J285" t="s">
         <v>18</v>
       </c>
       <c r="K285" s="25">
         <f>INDEX('feed pars'!U$6:U$43,MATCH(F285,'feed pars'!B$6:B$43,0))</f>
-        <v>18.5</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="286" spans="1:14" x14ac:dyDescent="0.25">
@@ -7145,14 +7192,14 @@
         <v>296</v>
       </c>
       <c r="F286" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="J286" t="s">
         <v>18</v>
       </c>
       <c r="K286" s="25">
         <f>INDEX('feed pars'!U$6:U$43,MATCH(F286,'feed pars'!B$6:B$43,0))</f>
-        <v>17.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="287" spans="1:14" x14ac:dyDescent="0.25">
@@ -7163,14 +7210,14 @@
         <v>296</v>
       </c>
       <c r="F287" t="s">
-        <v>310</v>
+        <v>39</v>
       </c>
       <c r="J287" t="s">
         <v>18</v>
       </c>
       <c r="K287" s="25">
         <f>INDEX('feed pars'!U$6:U$43,MATCH(F287,'feed pars'!B$6:B$43,0))</f>
-        <v>29.8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="288" spans="1:14" x14ac:dyDescent="0.25">
@@ -7181,17 +7228,17 @@
         <v>296</v>
       </c>
       <c r="F288" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J288" t="s">
         <v>18</v>
       </c>
       <c r="K288" s="25">
         <f>INDEX('feed pars'!U$6:U$43,MATCH(F288,'feed pars'!B$6:B$43,0))</f>
-        <v>9.9</v>
-      </c>
-    </row>
-    <row r="289" spans="1:14" x14ac:dyDescent="0.25">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="289" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>25</v>
       </c>
@@ -7199,17 +7246,17 @@
         <v>296</v>
       </c>
       <c r="F289" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="J289" t="s">
         <v>18</v>
       </c>
       <c r="K289" s="25">
         <f>INDEX('feed pars'!U$6:U$43,MATCH(F289,'feed pars'!B$6:B$43,0))</f>
-        <v>10.3</v>
-      </c>
-    </row>
-    <row r="290" spans="1:14" x14ac:dyDescent="0.25">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="290" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>25</v>
       </c>
@@ -7217,17 +7264,17 @@
         <v>296</v>
       </c>
       <c r="F290" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J290" t="s">
         <v>18</v>
       </c>
       <c r="K290" s="25">
         <f>INDEX('feed pars'!U$6:U$43,MATCH(F290,'feed pars'!B$6:B$43,0))</f>
-        <v>7.7</v>
-      </c>
-    </row>
-    <row r="291" spans="1:14" x14ac:dyDescent="0.25">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="291" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>25</v>
       </c>
@@ -7235,17 +7282,17 @@
         <v>296</v>
       </c>
       <c r="F291" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="J291" t="s">
         <v>18</v>
       </c>
       <c r="K291" s="25">
         <f>INDEX('feed pars'!U$6:U$43,MATCH(F291,'feed pars'!B$6:B$43,0))</f>
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="292" spans="1:14" x14ac:dyDescent="0.25">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="292" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>25</v>
       </c>
@@ -7253,17 +7300,17 @@
         <v>296</v>
       </c>
       <c r="F292" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="J292" t="s">
         <v>18</v>
       </c>
       <c r="K292" s="25">
         <f>INDEX('feed pars'!U$6:U$43,MATCH(F292,'feed pars'!B$6:B$43,0))</f>
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="293" spans="1:14" x14ac:dyDescent="0.25">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="293" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>25</v>
       </c>
@@ -7271,17 +7318,17 @@
         <v>296</v>
       </c>
       <c r="F293" t="s">
-        <v>48</v>
+        <v>310</v>
       </c>
       <c r="J293" t="s">
         <v>18</v>
       </c>
       <c r="K293" s="25">
         <f>INDEX('feed pars'!U$6:U$43,MATCH(F293,'feed pars'!B$6:B$43,0))</f>
-        <v>7.8</v>
-      </c>
-    </row>
-    <row r="294" spans="1:14" x14ac:dyDescent="0.25">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="294" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>25</v>
       </c>
@@ -7289,17 +7336,17 @@
         <v>296</v>
       </c>
       <c r="F294" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="J294" t="s">
         <v>18</v>
       </c>
       <c r="K294" s="25">
         <f>INDEX('feed pars'!U$6:U$43,MATCH(F294,'feed pars'!B$6:B$43,0))</f>
-        <v>9.1999999999999993</v>
-      </c>
-    </row>
-    <row r="295" spans="1:14" x14ac:dyDescent="0.25">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="295" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>25</v>
       </c>
@@ -7307,17 +7354,17 @@
         <v>296</v>
       </c>
       <c r="F295" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J295" t="s">
         <v>18</v>
       </c>
       <c r="K295" s="25">
         <f>INDEX('feed pars'!U$6:U$43,MATCH(F295,'feed pars'!B$6:B$43,0))</f>
-        <v>8.6999999999999993</v>
-      </c>
-    </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.25">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="296" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>25</v>
       </c>
@@ -7325,17 +7372,17 @@
         <v>296</v>
       </c>
       <c r="F296" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="J296" t="s">
         <v>18</v>
       </c>
       <c r="K296" s="25">
         <f>INDEX('feed pars'!U$6:U$43,MATCH(F296,'feed pars'!B$6:B$43,0))</f>
-        <v>8.9</v>
-      </c>
-    </row>
-    <row r="297" spans="1:14" x14ac:dyDescent="0.25">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="297" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>25</v>
       </c>
@@ -7343,17 +7390,17 @@
         <v>296</v>
       </c>
       <c r="F297" t="s">
-        <v>309</v>
+        <v>46</v>
       </c>
       <c r="J297" t="s">
         <v>18</v>
       </c>
       <c r="K297" s="25">
         <f>INDEX('feed pars'!U$6:U$43,MATCH(F297,'feed pars'!B$6:B$43,0))</f>
-        <v>7.0888888888888877</v>
-      </c>
-    </row>
-    <row r="298" spans="1:14" x14ac:dyDescent="0.25">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="298" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>25</v>
       </c>
@@ -7361,17 +7408,17 @@
         <v>296</v>
       </c>
       <c r="F298" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="J298" t="s">
         <v>18</v>
       </c>
       <c r="K298" s="25">
         <f>INDEX('feed pars'!U$6:U$43,MATCH(F298,'feed pars'!B$6:B$43,0))</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="299" spans="1:14" x14ac:dyDescent="0.25">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="299" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>25</v>
       </c>
@@ -7379,17 +7426,17 @@
         <v>296</v>
       </c>
       <c r="F299" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="J299" t="s">
         <v>18</v>
       </c>
       <c r="K299" s="25">
         <f>INDEX('feed pars'!U$6:U$43,MATCH(F299,'feed pars'!B$6:B$43,0))</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="300" spans="1:14" x14ac:dyDescent="0.25">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="300" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>25</v>
       </c>
@@ -7397,17 +7444,17 @@
         <v>296</v>
       </c>
       <c r="F300" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="J300" t="s">
         <v>18</v>
       </c>
       <c r="K300" s="25">
         <f>INDEX('feed pars'!U$6:U$43,MATCH(F300,'feed pars'!B$6:B$43,0))</f>
-        <v>12.2</v>
-      </c>
-    </row>
-    <row r="301" spans="1:14" x14ac:dyDescent="0.25">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="301" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>25</v>
       </c>
@@ -7415,17 +7462,17 @@
         <v>296</v>
       </c>
       <c r="F301" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="J301" t="s">
         <v>18</v>
       </c>
       <c r="K301" s="25">
         <f>INDEX('feed pars'!U$6:U$43,MATCH(F301,'feed pars'!B$6:B$43,0))</f>
-        <v>12.2</v>
-      </c>
-    </row>
-    <row r="302" spans="1:14" x14ac:dyDescent="0.25">
+        <v>8.6999999999999993</v>
+      </c>
+    </row>
+    <row r="302" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>25</v>
       </c>
@@ -7433,17 +7480,17 @@
         <v>296</v>
       </c>
       <c r="F302" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="J302" t="s">
         <v>18</v>
       </c>
       <c r="K302" s="25">
         <f>INDEX('feed pars'!U$6:U$43,MATCH(F302,'feed pars'!B$6:B$43,0))</f>
-        <v>11.3</v>
-      </c>
-    </row>
-    <row r="303" spans="1:14" x14ac:dyDescent="0.25">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="303" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>25</v>
       </c>
@@ -7451,278 +7498,296 @@
         <v>296</v>
       </c>
       <c r="F303" t="s">
-        <v>57</v>
+        <v>309</v>
       </c>
       <c r="J303" t="s">
         <v>18</v>
       </c>
       <c r="K303" s="25">
         <f>INDEX('feed pars'!U$6:U$43,MATCH(F303,'feed pars'!B$6:B$43,0))</f>
-        <v>10.8</v>
-      </c>
-    </row>
-    <row r="304" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A304" s="27" t="s">
-        <v>388</v>
-      </c>
-      <c r="B304" s="28"/>
-      <c r="C304" s="29"/>
-      <c r="D304" s="29"/>
-      <c r="E304" s="29"/>
-      <c r="F304" s="29"/>
-      <c r="G304" s="29"/>
-      <c r="H304" s="29"/>
-      <c r="I304" s="29"/>
-      <c r="J304" s="29"/>
-      <c r="K304" s="29"/>
-      <c r="L304" s="29"/>
-      <c r="M304" s="29"/>
-      <c r="N304" s="29"/>
-    </row>
-    <row r="305" spans="1:13" x14ac:dyDescent="0.25">
+        <v>7.0888888888888877</v>
+      </c>
+    </row>
+    <row r="304" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>25</v>
+      </c>
+      <c r="E304" t="s">
+        <v>296</v>
+      </c>
+      <c r="F304" t="s">
+        <v>52</v>
+      </c>
+      <c r="J304" t="s">
+        <v>18</v>
+      </c>
+      <c r="K304" s="25">
+        <f>INDEX('feed pars'!U$6:U$43,MATCH(F304,'feed pars'!B$6:B$43,0))</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="305" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>25</v>
       </c>
+      <c r="E305" t="s">
+        <v>296</v>
+      </c>
       <c r="F305" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="J305" t="s">
         <v>18</v>
       </c>
       <c r="K305" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F305,'feed pars'!B$6:B$43,0))</f>
-        <v>12.1</v>
-      </c>
-      <c r="L305" t="s">
-        <v>22</v>
-      </c>
-      <c r="M305" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="306" spans="1:13" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!U$6:U$43,MATCH(F305,'feed pars'!B$6:B$43,0))</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="306" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>25</v>
       </c>
+      <c r="E306" t="s">
+        <v>296</v>
+      </c>
       <c r="F306" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="J306" t="s">
         <v>18</v>
       </c>
       <c r="K306" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F306,'feed pars'!B$6:B$43,0))</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="307" spans="1:13" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!U$6:U$43,MATCH(F306,'feed pars'!B$6:B$43,0))</f>
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="307" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>25</v>
       </c>
+      <c r="E307" t="s">
+        <v>296</v>
+      </c>
       <c r="F307" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="J307" t="s">
         <v>18</v>
       </c>
       <c r="K307" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F307,'feed pars'!B$6:B$43,0))</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="308" spans="1:13" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!U$6:U$43,MATCH(F307,'feed pars'!B$6:B$43,0))</f>
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="308" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>25</v>
       </c>
+      <c r="E308" t="s">
+        <v>296</v>
+      </c>
       <c r="F308" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="J308" t="s">
         <v>18</v>
       </c>
       <c r="K308" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F308,'feed pars'!B$6:B$43,0))</f>
-        <v>11.9</v>
-      </c>
-    </row>
-    <row r="309" spans="1:13" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!U$6:U$43,MATCH(F308,'feed pars'!B$6:B$43,0))</f>
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="309" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>25</v>
       </c>
+      <c r="E309" t="s">
+        <v>296</v>
+      </c>
       <c r="F309" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="J309" t="s">
         <v>18</v>
       </c>
       <c r="K309" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F309,'feed pars'!B$6:B$43,0))</f>
-        <v>12.8</v>
-      </c>
-    </row>
-    <row r="310" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A310" t="s">
-        <v>25</v>
-      </c>
-      <c r="F310" t="s">
-        <v>41</v>
-      </c>
-      <c r="J310" t="s">
-        <v>18</v>
-      </c>
-      <c r="K310" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F310,'feed pars'!B$6:B$43,0))</f>
-        <v>11.2</v>
-      </c>
-    </row>
-    <row r="311" spans="1:13" x14ac:dyDescent="0.25">
+        <f>INDEX('feed pars'!U$6:U$43,MATCH(F309,'feed pars'!B$6:B$43,0))</f>
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="310" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A310" s="27" t="s">
+        <v>388</v>
+      </c>
+      <c r="B310" s="28"/>
+      <c r="C310" s="29"/>
+      <c r="D310" s="29"/>
+      <c r="E310" s="29"/>
+      <c r="F310" s="29"/>
+      <c r="G310" s="29"/>
+      <c r="H310" s="29"/>
+      <c r="I310" s="29"/>
+      <c r="J310" s="29"/>
+      <c r="K310" s="29"/>
+      <c r="L310" s="29"/>
+      <c r="M310" s="29"/>
+      <c r="N310" s="29"/>
+    </row>
+    <row r="311" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>25</v>
       </c>
       <c r="F311" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="J311" t="s">
         <v>18</v>
       </c>
       <c r="K311" s="25">
         <f>INDEX('feed pars'!T$6:T$43,MATCH(F311,'feed pars'!B$6:B$43,0))</f>
-        <v>10.7</v>
-      </c>
-    </row>
-    <row r="312" spans="1:13" x14ac:dyDescent="0.25">
+        <v>12.1</v>
+      </c>
+      <c r="L311" t="s">
+        <v>22</v>
+      </c>
+      <c r="M311" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="312" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>25</v>
       </c>
       <c r="F312" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J312" t="s">
         <v>18</v>
       </c>
       <c r="K312" s="25">
         <f>INDEX('feed pars'!T$6:T$43,MATCH(F312,'feed pars'!B$6:B$43,0))</f>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="313" spans="1:13" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="313" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>25</v>
       </c>
       <c r="F313" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="J313" t="s">
         <v>18</v>
       </c>
       <c r="K313" s="25">
         <f>INDEX('feed pars'!T$6:T$43,MATCH(F313,'feed pars'!B$6:B$43,0))</f>
-        <v>17.3</v>
-      </c>
-    </row>
-    <row r="314" spans="1:13" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="314" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>25</v>
       </c>
       <c r="F314" t="s">
-        <v>310</v>
+        <v>39</v>
       </c>
       <c r="J314" t="s">
         <v>18</v>
       </c>
       <c r="K314" s="25">
         <f>INDEX('feed pars'!T$6:T$43,MATCH(F314,'feed pars'!B$6:B$43,0))</f>
-        <v>29.8</v>
-      </c>
-    </row>
-    <row r="315" spans="1:13" x14ac:dyDescent="0.25">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="315" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>25</v>
       </c>
       <c r="F315" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J315" t="s">
         <v>18</v>
       </c>
       <c r="K315" s="25">
         <f>INDEX('feed pars'!T$6:T$43,MATCH(F315,'feed pars'!B$6:B$43,0))</f>
-        <v>9.3000000000000007</v>
-      </c>
-    </row>
-    <row r="316" spans="1:13" x14ac:dyDescent="0.25">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="316" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>25</v>
       </c>
       <c r="F316" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="J316" t="s">
         <v>18</v>
       </c>
       <c r="K316" s="25">
         <f>INDEX('feed pars'!T$6:T$43,MATCH(F316,'feed pars'!B$6:B$43,0))</f>
-        <v>9.6999999999999993</v>
-      </c>
-    </row>
-    <row r="317" spans="1:13" x14ac:dyDescent="0.25">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="317" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>25</v>
       </c>
       <c r="F317" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J317" t="s">
         <v>18</v>
       </c>
       <c r="K317" s="25">
         <f>INDEX('feed pars'!T$6:T$43,MATCH(F317,'feed pars'!B$6:B$43,0))</f>
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="318" spans="1:13" x14ac:dyDescent="0.25">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="318" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>25</v>
       </c>
       <c r="F318" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="J318" t="s">
         <v>18</v>
       </c>
       <c r="K318" s="25">
         <f>INDEX('feed pars'!T$6:T$43,MATCH(F318,'feed pars'!B$6:B$43,0))</f>
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="319" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="319" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>25</v>
       </c>
       <c r="F319" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="J319" t="s">
         <v>18</v>
       </c>
       <c r="K319" s="25">
         <f>INDEX('feed pars'!T$6:T$43,MATCH(F319,'feed pars'!B$6:B$43,0))</f>
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="320" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="320" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>25</v>
       </c>
       <c r="F320" t="s">
-        <v>48</v>
+        <v>310</v>
       </c>
       <c r="J320" t="s">
         <v>18</v>
       </c>
       <c r="K320" s="25">
         <f>INDEX('feed pars'!T$6:T$43,MATCH(F320,'feed pars'!B$6:B$43,0))</f>
-        <v>7.2</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="321" spans="1:11" x14ac:dyDescent="0.25">
@@ -7730,14 +7795,14 @@
         <v>25</v>
       </c>
       <c r="F321" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="J321" t="s">
         <v>18</v>
       </c>
       <c r="K321" s="25">
         <f>INDEX('feed pars'!T$6:T$43,MATCH(F321,'feed pars'!B$6:B$43,0))</f>
-        <v>8.6999999999999993</v>
+        <v>9.3000000000000007</v>
       </c>
     </row>
     <row r="322" spans="1:11" x14ac:dyDescent="0.25">
@@ -7745,14 +7810,14 @@
         <v>25</v>
       </c>
       <c r="F322" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J322" t="s">
         <v>18</v>
       </c>
       <c r="K322" s="25">
         <f>INDEX('feed pars'!T$6:T$43,MATCH(F322,'feed pars'!B$6:B$43,0))</f>
-        <v>8.1</v>
+        <v>9.6999999999999993</v>
       </c>
     </row>
     <row r="323" spans="1:11" x14ac:dyDescent="0.25">
@@ -7760,14 +7825,14 @@
         <v>25</v>
       </c>
       <c r="F323" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="J323" t="s">
         <v>18</v>
       </c>
       <c r="K323" s="25">
         <f>INDEX('feed pars'!T$6:T$43,MATCH(F323,'feed pars'!B$6:B$43,0))</f>
-        <v>8.1999999999999993</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="324" spans="1:11" x14ac:dyDescent="0.25">
@@ -7775,14 +7840,14 @@
         <v>25</v>
       </c>
       <c r="F324" t="s">
-        <v>309</v>
+        <v>46</v>
       </c>
       <c r="J324" t="s">
         <v>18</v>
       </c>
       <c r="K324" s="25">
         <f>INDEX('feed pars'!T$6:T$43,MATCH(F324,'feed pars'!B$6:B$43,0))</f>
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="325" spans="1:11" x14ac:dyDescent="0.25">
@@ -7790,14 +7855,14 @@
         <v>25</v>
       </c>
       <c r="F325" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="J325" t="s">
         <v>18</v>
       </c>
       <c r="K325" s="25">
         <f>INDEX('feed pars'!T$6:T$43,MATCH(F325,'feed pars'!B$6:B$43,0))</f>
-        <v>8.6999999999999993</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="326" spans="1:11" x14ac:dyDescent="0.25">
@@ -7805,14 +7870,14 @@
         <v>25</v>
       </c>
       <c r="F326" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="J326" t="s">
         <v>18</v>
       </c>
       <c r="K326" s="25">
         <f>INDEX('feed pars'!T$6:T$43,MATCH(F326,'feed pars'!B$6:B$43,0))</f>
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="327" spans="1:11" x14ac:dyDescent="0.25">
@@ -7820,14 +7885,14 @@
         <v>25</v>
       </c>
       <c r="F327" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="J327" t="s">
         <v>18</v>
       </c>
       <c r="K327" s="25">
         <f>INDEX('feed pars'!T$6:T$43,MATCH(F327,'feed pars'!B$6:B$43,0))</f>
-        <v>12.4</v>
+        <v>8.6999999999999993</v>
       </c>
     </row>
     <row r="328" spans="1:11" x14ac:dyDescent="0.25">
@@ -7835,14 +7900,14 @@
         <v>25</v>
       </c>
       <c r="F328" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="J328" t="s">
         <v>18</v>
       </c>
       <c r="K328" s="25">
         <f>INDEX('feed pars'!T$6:T$43,MATCH(F328,'feed pars'!B$6:B$43,0))</f>
-        <v>12.4</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="329" spans="1:11" x14ac:dyDescent="0.25">
@@ -7850,14 +7915,14 @@
         <v>25</v>
       </c>
       <c r="F329" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="J329" t="s">
         <v>18</v>
       </c>
       <c r="K329" s="25">
         <f>INDEX('feed pars'!T$6:T$43,MATCH(F329,'feed pars'!B$6:B$43,0))</f>
-        <v>11.1</v>
+        <v>8.1999999999999993</v>
       </c>
     </row>
     <row r="330" spans="1:11" x14ac:dyDescent="0.25">
@@ -7865,13 +7930,103 @@
         <v>25</v>
       </c>
       <c r="F330" t="s">
-        <v>57</v>
+        <v>309</v>
       </c>
       <c r="J330" t="s">
         <v>18</v>
       </c>
       <c r="K330" s="25">
         <f>INDEX('feed pars'!T$6:T$43,MATCH(F330,'feed pars'!B$6:B$43,0))</f>
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="331" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>25</v>
+      </c>
+      <c r="F331" t="s">
+        <v>52</v>
+      </c>
+      <c r="J331" t="s">
+        <v>18</v>
+      </c>
+      <c r="K331" s="25">
+        <f>INDEX('feed pars'!T$6:T$43,MATCH(F331,'feed pars'!B$6:B$43,0))</f>
+        <v>8.6999999999999993</v>
+      </c>
+    </row>
+    <row r="332" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>25</v>
+      </c>
+      <c r="F332" t="s">
+        <v>53</v>
+      </c>
+      <c r="J332" t="s">
+        <v>18</v>
+      </c>
+      <c r="K332" s="25">
+        <f>INDEX('feed pars'!T$6:T$43,MATCH(F332,'feed pars'!B$6:B$43,0))</f>
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="333" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>25</v>
+      </c>
+      <c r="F333" t="s">
+        <v>54</v>
+      </c>
+      <c r="J333" t="s">
+        <v>18</v>
+      </c>
+      <c r="K333" s="25">
+        <f>INDEX('feed pars'!T$6:T$43,MATCH(F333,'feed pars'!B$6:B$43,0))</f>
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="334" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>25</v>
+      </c>
+      <c r="F334" t="s">
+        <v>55</v>
+      </c>
+      <c r="J334" t="s">
+        <v>18</v>
+      </c>
+      <c r="K334" s="25">
+        <f>INDEX('feed pars'!T$6:T$43,MATCH(F334,'feed pars'!B$6:B$43,0))</f>
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="335" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>25</v>
+      </c>
+      <c r="F335" t="s">
+        <v>56</v>
+      </c>
+      <c r="J335" t="s">
+        <v>18</v>
+      </c>
+      <c r="K335" s="25">
+        <f>INDEX('feed pars'!T$6:T$43,MATCH(F335,'feed pars'!B$6:B$43,0))</f>
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="336" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>25</v>
+      </c>
+      <c r="F336" t="s">
+        <v>57</v>
+      </c>
+      <c r="J336" t="s">
+        <v>18</v>
+      </c>
+      <c r="K336" s="25">
+        <f>INDEX('feed pars'!T$6:T$43,MATCH(F336,'feed pars'!B$6:B$43,0))</f>
         <v>10.8</v>
       </c>
     </row>

--- a/data/prod_parameters/FeedMgmt.xlsx
+++ b/data/prod_parameters/FeedMgmt.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="5100"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="5100" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="default" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1523" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1534" uniqueCount="510">
   <si>
     <t>f_feed</t>
   </si>
@@ -1269,9 +1269,6 @@
     </r>
   </si>
   <si>
-    <t>https://glw-feeds.co.uk/index.php/wheat-feed-2/</t>
-  </si>
-  <si>
     <t>GE, MJ/kg DM</t>
   </si>
   <si>
@@ -1567,6 +1564,21 @@
   </si>
   <si>
     <t>Total fat</t>
+  </si>
+  <si>
+    <t>N, % of DM</t>
+  </si>
+  <si>
+    <t>P, % of DM</t>
+  </si>
+  <si>
+    <t>K, % of DM</t>
+  </si>
+  <si>
+    <t>CP --&gt; N</t>
+  </si>
+  <si>
+    <t>https://www.feedtables.com/content/wheat-feed-flour</t>
   </si>
 </sst>
 </file>
@@ -1905,7 +1917,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2015,10 +2027,23 @@
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2814,7 +2839,7 @@
       </c>
       <c r="K31" s="22">
         <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F31,'feed pars'!B$6:B$43,0))</f>
-        <v>1.1299435028248588</v>
+        <v>1.1389521640091116</v>
       </c>
     </row>
     <row r="32" spans="6:13" x14ac:dyDescent="0.25">
@@ -4767,7 +4792,7 @@
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A121" s="79" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B121" s="80"/>
       <c r="C121" s="80"/>
@@ -5135,7 +5160,7 @@
       </c>
       <c r="K148" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F148,'feed pars'!B$6:B$43,0))</f>
-        <v>88.5</v>
+        <v>87.8</v>
       </c>
       <c r="M148" s="3"/>
     </row>
@@ -5276,7 +5301,7 @@
       <c r="J159" t="s">
         <v>386</v>
       </c>
-      <c r="K159" s="86">
+      <c r="K159" s="85">
         <v>100</v>
       </c>
       <c r="M159" s="3"/>
@@ -5286,17 +5311,17 @@
         <v>306</v>
       </c>
       <c r="J160" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K160" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F160,'feed pars'!B$6:B$43,0))</f>
         <v>17.316948400000001</v>
       </c>
       <c r="L160" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="M160" s="26" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="161" spans="6:13" x14ac:dyDescent="0.25">
@@ -5304,7 +5329,7 @@
         <v>307</v>
       </c>
       <c r="J161" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K161" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F161,'feed pars'!B$6:B$43,0))</f>
@@ -5317,11 +5342,11 @@
         <v>308</v>
       </c>
       <c r="J162" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K162" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F162,'feed pars'!B$6:B$43,0))</f>
-        <v>16.819680000000002</v>
+        <v>16.789764399999999</v>
       </c>
       <c r="M162" s="3"/>
     </row>
@@ -5330,7 +5355,7 @@
         <v>2</v>
       </c>
       <c r="J163" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K163" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F163,'feed pars'!B$6:B$43,0))</f>
@@ -5343,7 +5368,7 @@
         <v>12</v>
       </c>
       <c r="J164" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K164" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F164,'feed pars'!B$6:B$43,0))</f>
@@ -5356,7 +5381,7 @@
         <v>33</v>
       </c>
       <c r="J165" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K165" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F165,'feed pars'!B$6:B$43,0))</f>
@@ -5369,7 +5394,7 @@
         <v>17</v>
       </c>
       <c r="J166" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K166" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F166,'feed pars'!B$6:B$43,0))</f>
@@ -5382,7 +5407,7 @@
         <v>37</v>
       </c>
       <c r="J167" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K167" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F167,'feed pars'!B$6:B$43,0))</f>
@@ -5395,7 +5420,7 @@
         <v>38</v>
       </c>
       <c r="J168" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K168" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F168,'feed pars'!B$6:B$43,0))</f>
@@ -5408,7 +5433,7 @@
         <v>39</v>
       </c>
       <c r="J169" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K169" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F169,'feed pars'!B$6:B$43,0))</f>
@@ -5421,7 +5446,7 @@
         <v>313</v>
       </c>
       <c r="J170" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K170" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F170,'feed pars'!B$6:B$43,0))</f>
@@ -5434,7 +5459,7 @@
         <v>40</v>
       </c>
       <c r="J171" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K171" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F171,'feed pars'!B$6:B$43,0))</f>
@@ -5447,7 +5472,7 @@
         <v>41</v>
       </c>
       <c r="J172" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K172" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F172,'feed pars'!B$6:B$43,0))</f>
@@ -5460,7 +5485,7 @@
         <v>42</v>
       </c>
       <c r="J173" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K173" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F173,'feed pars'!B$6:B$43,0))</f>
@@ -5473,7 +5498,7 @@
         <v>35</v>
       </c>
       <c r="J174" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K174" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F174,'feed pars'!B$6:B$43,0))</f>
@@ -5486,7 +5511,7 @@
         <v>43</v>
       </c>
       <c r="J175" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K175" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F175,'feed pars'!B$6:B$43,0))</f>
@@ -5499,7 +5524,7 @@
         <v>310</v>
       </c>
       <c r="J176" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K176" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F176,'feed pars'!B$6:B$43,0))</f>
@@ -5512,7 +5537,7 @@
         <v>302</v>
       </c>
       <c r="J177" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K177" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F177,'feed pars'!B$6:B$43,0))</f>
@@ -5525,7 +5550,7 @@
         <v>314</v>
       </c>
       <c r="J178" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K178" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F178,'feed pars'!B$6:B$43,0))</f>
@@ -5538,7 +5563,7 @@
         <v>44</v>
       </c>
       <c r="J179" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K179" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F179,'feed pars'!B$6:B$43,0))</f>
@@ -5551,7 +5576,7 @@
         <v>45</v>
       </c>
       <c r="J180" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K180" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F180,'feed pars'!B$6:B$43,0))</f>
@@ -5564,7 +5589,7 @@
         <v>36</v>
       </c>
       <c r="J181" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K181" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F181,'feed pars'!B$6:B$43,0))</f>
@@ -5577,7 +5602,7 @@
         <v>46</v>
       </c>
       <c r="J182" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K182" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F182,'feed pars'!B$6:B$43,0))</f>
@@ -5590,7 +5615,7 @@
         <v>47</v>
       </c>
       <c r="J183" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K183" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F183,'feed pars'!B$6:B$43,0))</f>
@@ -5603,7 +5628,7 @@
         <v>315</v>
       </c>
       <c r="J184" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K184" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F184,'feed pars'!B$6:B$43,0))</f>
@@ -5616,7 +5641,7 @@
         <v>48</v>
       </c>
       <c r="J185" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K185" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F185,'feed pars'!B$6:B$43,0))</f>
@@ -5629,11 +5654,11 @@
         <v>49</v>
       </c>
       <c r="J186" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K186" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F186,'feed pars'!B$6:B$43,0))</f>
-        <v>17.8828344</v>
+        <v>18.472360000000002</v>
       </c>
       <c r="M186" s="3"/>
     </row>
@@ -5642,7 +5667,7 @@
         <v>50</v>
       </c>
       <c r="J187" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K187" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F187,'feed pars'!B$6:B$43,0))</f>
@@ -5655,7 +5680,7 @@
         <v>51</v>
       </c>
       <c r="J188" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K188" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F188,'feed pars'!B$6:B$43,0))</f>
@@ -5668,7 +5693,7 @@
         <v>309</v>
       </c>
       <c r="J189" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K189" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F189,'feed pars'!B$6:B$43,0))</f>
@@ -5681,7 +5706,7 @@
         <v>384</v>
       </c>
       <c r="J190" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K190" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F190,'feed pars'!B$6:B$43,0))</f>
@@ -5694,7 +5719,7 @@
         <v>52</v>
       </c>
       <c r="J191" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K191" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F191,'feed pars'!B$6:B$43,0))</f>
@@ -5707,7 +5732,7 @@
         <v>53</v>
       </c>
       <c r="J192" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K192" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F192,'feed pars'!B$6:B$43,0))</f>
@@ -5720,7 +5745,7 @@
         <v>54</v>
       </c>
       <c r="J193" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K193" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F193,'feed pars'!B$6:B$43,0))</f>
@@ -5733,7 +5758,7 @@
         <v>55</v>
       </c>
       <c r="J194" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K194" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F194,'feed pars'!B$6:B$43,0))</f>
@@ -5746,7 +5771,7 @@
         <v>56</v>
       </c>
       <c r="J195" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K195" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F195,'feed pars'!B$6:B$43,0))</f>
@@ -5759,7 +5784,7 @@
         <v>57</v>
       </c>
       <c r="J196" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K196" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F196,'feed pars'!B$6:B$43,0))</f>
@@ -5772,9 +5797,9 @@
         <v>320</v>
       </c>
       <c r="J197" t="s">
-        <v>498</v>
-      </c>
-      <c r="K197" s="85">
+        <v>497</v>
+      </c>
+      <c r="K197" s="84">
         <v>0</v>
       </c>
       <c r="M197" s="3"/>
@@ -5808,14 +5833,14 @@
         <v>18</v>
       </c>
       <c r="K199" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F199,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F199,'feed pars'!B$6:B$43,0))</f>
         <v>11.3</v>
       </c>
       <c r="L199" t="s">
         <v>19</v>
       </c>
       <c r="M199" s="26" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.25">
@@ -5829,7 +5854,7 @@
         <v>18</v>
       </c>
       <c r="K200" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F200,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F200,'feed pars'!B$6:B$43,0))</f>
         <v>10.1</v>
       </c>
       <c r="M200" s="3"/>
@@ -5845,8 +5870,8 @@
         <v>18</v>
       </c>
       <c r="K201" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F201,'feed pars'!B$6:B$43,0))</f>
-        <v>9.25</v>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F201,'feed pars'!B$6:B$43,0))</f>
+        <v>8.5</v>
       </c>
       <c r="M201" s="3"/>
     </row>
@@ -5861,7 +5886,7 @@
         <v>18</v>
       </c>
       <c r="K202" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F202,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F202,'feed pars'!B$6:B$43,0))</f>
         <v>11</v>
       </c>
     </row>
@@ -5876,7 +5901,7 @@
         <v>18</v>
       </c>
       <c r="K203" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F203,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F203,'feed pars'!B$6:B$43,0))</f>
         <v>9.9416666666666664</v>
       </c>
     </row>
@@ -5891,7 +5916,7 @@
         <v>18</v>
       </c>
       <c r="K204" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F204,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F204,'feed pars'!B$6:B$43,0))</f>
         <v>14.1</v>
       </c>
     </row>
@@ -5906,7 +5931,7 @@
         <v>18</v>
       </c>
       <c r="K205" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F205,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F205,'feed pars'!B$6:B$43,0))</f>
         <v>13.2</v>
       </c>
     </row>
@@ -5921,7 +5946,7 @@
         <v>18</v>
       </c>
       <c r="K206" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F206,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F206,'feed pars'!B$6:B$43,0))</f>
         <v>11.7</v>
       </c>
     </row>
@@ -5936,7 +5961,7 @@
         <v>18</v>
       </c>
       <c r="K207" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F207,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F207,'feed pars'!B$6:B$43,0))</f>
         <v>14</v>
       </c>
     </row>
@@ -5951,7 +5976,7 @@
         <v>18</v>
       </c>
       <c r="K208" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F208,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F208,'feed pars'!B$6:B$43,0))</f>
         <v>13.9</v>
       </c>
     </row>
@@ -5966,7 +5991,7 @@
         <v>18</v>
       </c>
       <c r="K209" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F209,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F209,'feed pars'!B$6:B$43,0))</f>
         <v>12.8</v>
       </c>
     </row>
@@ -5981,7 +6006,7 @@
         <v>18</v>
       </c>
       <c r="K210" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F210,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F210,'feed pars'!B$6:B$43,0))</f>
         <v>13.8</v>
       </c>
     </row>
@@ -5996,7 +6021,7 @@
         <v>18</v>
       </c>
       <c r="K211" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F211,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F211,'feed pars'!B$6:B$43,0))</f>
         <v>13.3</v>
       </c>
     </row>
@@ -6011,7 +6036,7 @@
         <v>18</v>
       </c>
       <c r="K212" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F212,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F212,'feed pars'!B$6:B$43,0))</f>
         <v>22.1</v>
       </c>
     </row>
@@ -6026,7 +6051,7 @@
         <v>18</v>
       </c>
       <c r="K213" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F213,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F213,'feed pars'!B$6:B$43,0))</f>
         <v>20.100000000000001</v>
       </c>
     </row>
@@ -6041,7 +6066,7 @@
         <v>18</v>
       </c>
       <c r="K214" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F214,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F214,'feed pars'!B$6:B$43,0))</f>
         <v>6.6</v>
       </c>
     </row>
@@ -6056,7 +6081,7 @@
         <v>18</v>
       </c>
       <c r="K215" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F215,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F215,'feed pars'!B$6:B$43,0))</f>
         <v>36.6</v>
       </c>
     </row>
@@ -6071,7 +6096,7 @@
         <v>18</v>
       </c>
       <c r="K216" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F216,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F216,'feed pars'!B$6:B$43,0))</f>
         <v>16.399999999999999</v>
       </c>
     </row>
@@ -6086,7 +6111,7 @@
         <v>18</v>
       </c>
       <c r="K217" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F217,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F217,'feed pars'!B$6:B$43,0))</f>
         <v>14.6</v>
       </c>
     </row>
@@ -6101,7 +6126,7 @@
         <v>18</v>
       </c>
       <c r="K218" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F218,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F218,'feed pars'!B$6:B$43,0))</f>
         <v>12.2</v>
       </c>
     </row>
@@ -6116,7 +6141,7 @@
         <v>18</v>
       </c>
       <c r="K219" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F219,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F219,'feed pars'!B$6:B$43,0))</f>
         <v>11.4</v>
       </c>
     </row>
@@ -6131,7 +6156,7 @@
         <v>18</v>
       </c>
       <c r="K220" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F220,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F220,'feed pars'!B$6:B$43,0))</f>
         <v>13.4</v>
       </c>
     </row>
@@ -6146,7 +6171,7 @@
         <v>18</v>
       </c>
       <c r="K221" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F221,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F221,'feed pars'!B$6:B$43,0))</f>
         <v>8.5</v>
       </c>
     </row>
@@ -6161,7 +6186,7 @@
         <v>18</v>
       </c>
       <c r="K222" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F222,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F222,'feed pars'!B$6:B$43,0))</f>
         <v>11</v>
       </c>
     </row>
@@ -6176,7 +6201,7 @@
         <v>18</v>
       </c>
       <c r="K223" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F223,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F223,'feed pars'!B$6:B$43,0))</f>
         <v>13.3</v>
       </c>
     </row>
@@ -6191,7 +6216,7 @@
         <v>18</v>
       </c>
       <c r="K224" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F224,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F224,'feed pars'!B$6:B$43,0))</f>
         <v>11.6</v>
       </c>
     </row>
@@ -6206,7 +6231,7 @@
         <v>18</v>
       </c>
       <c r="K225" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F225,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F225,'feed pars'!B$6:B$43,0))</f>
         <v>12.4</v>
       </c>
     </row>
@@ -6221,7 +6246,7 @@
         <v>18</v>
       </c>
       <c r="K226" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F226,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F226,'feed pars'!B$6:B$43,0))</f>
         <v>12.3</v>
       </c>
     </row>
@@ -6236,7 +6261,7 @@
         <v>18</v>
       </c>
       <c r="K227" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F227,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F227,'feed pars'!B$6:B$43,0))</f>
         <v>13.6</v>
       </c>
     </row>
@@ -6251,7 +6276,7 @@
         <v>18</v>
       </c>
       <c r="K228" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F228,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F228,'feed pars'!B$6:B$43,0))</f>
         <v>15.5</v>
       </c>
     </row>
@@ -6277,17 +6302,17 @@
         <v>306</v>
       </c>
       <c r="J230" t="s">
+        <v>499</v>
+      </c>
+      <c r="K230" s="82">
+        <f>INDEX('feed pars'!N$6:N$43,MATCH(F230,'feed pars'!B$6:B$43,0))</f>
+        <v>20</v>
+      </c>
+      <c r="L230" t="s">
         <v>500</v>
       </c>
-      <c r="K230" s="82">
-        <f>INDEX('feed pars'!K$6:K$43,MATCH(F230,'feed pars'!B$6:B$43,0))</f>
-        <v>20</v>
-      </c>
-      <c r="L230" t="s">
-        <v>501</v>
-      </c>
       <c r="M230" s="26" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="231" spans="1:13" x14ac:dyDescent="0.25">
@@ -6298,10 +6323,10 @@
         <v>307</v>
       </c>
       <c r="J231" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K231" s="82">
-        <f>INDEX('feed pars'!K$6:K$43,MATCH(F231,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!N$6:N$43,MATCH(F231,'feed pars'!B$6:B$43,0))</f>
         <v>20</v>
       </c>
       <c r="M231" s="3"/>
@@ -6314,11 +6339,11 @@
         <v>308</v>
       </c>
       <c r="J232" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K232" s="82">
-        <f>INDEX('feed pars'!K$6:K$43,MATCH(F232,'feed pars'!B$6:B$43,0))</f>
-        <v>36</v>
+        <f>INDEX('feed pars'!N$6:N$43,MATCH(F232,'feed pars'!B$6:B$43,0))</f>
+        <v>22.5</v>
       </c>
       <c r="M232" s="3"/>
     </row>
@@ -6330,10 +6355,10 @@
         <v>12</v>
       </c>
       <c r="J233" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K233" s="82">
-        <f>INDEX('feed pars'!K$6:K$43,MATCH(F233,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!N$6:N$43,MATCH(F233,'feed pars'!B$6:B$43,0))</f>
         <v>30</v>
       </c>
     </row>
@@ -6345,10 +6370,10 @@
         <v>33</v>
       </c>
       <c r="J234" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K234" s="82">
-        <f>INDEX('feed pars'!K$6:K$43,MATCH(F234,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!N$6:N$43,MATCH(F234,'feed pars'!B$6:B$43,0))</f>
         <v>20</v>
       </c>
     </row>
@@ -6360,10 +6385,10 @@
         <v>17</v>
       </c>
       <c r="J235" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K235" s="82">
-        <f>INDEX('feed pars'!K$6:K$43,MATCH(F235,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!N$6:N$43,MATCH(F235,'feed pars'!B$6:B$43,0))</f>
         <v>25</v>
       </c>
     </row>
@@ -6375,10 +6400,10 @@
         <v>37</v>
       </c>
       <c r="J236" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K236" s="82">
-        <f>INDEX('feed pars'!K$6:K$43,MATCH(F236,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!N$6:N$43,MATCH(F236,'feed pars'!B$6:B$43,0))</f>
         <v>27</v>
       </c>
     </row>
@@ -6390,10 +6415,10 @@
         <v>38</v>
       </c>
       <c r="J237" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K237" s="82">
-        <f>INDEX('feed pars'!K$6:K$43,MATCH(F237,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!N$6:N$43,MATCH(F237,'feed pars'!B$6:B$43,0))</f>
         <v>61</v>
       </c>
     </row>
@@ -6405,10 +6430,10 @@
         <v>39</v>
       </c>
       <c r="J238" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K238" s="82">
-        <f>INDEX('feed pars'!K$6:K$43,MATCH(F238,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!N$6:N$43,MATCH(F238,'feed pars'!B$6:B$43,0))</f>
         <v>26</v>
       </c>
     </row>
@@ -6420,10 +6445,10 @@
         <v>313</v>
       </c>
       <c r="J239" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K239" s="82">
-        <f>INDEX('feed pars'!K$6:K$43,MATCH(F239,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!N$6:N$43,MATCH(F239,'feed pars'!B$6:B$43,0))</f>
         <v>20</v>
       </c>
     </row>
@@ -6435,10 +6460,10 @@
         <v>40</v>
       </c>
       <c r="J240" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K240" s="82">
-        <f>INDEX('feed pars'!K$6:K$43,MATCH(F240,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!N$6:N$43,MATCH(F240,'feed pars'!B$6:B$43,0))</f>
         <v>40</v>
       </c>
     </row>
@@ -6450,10 +6475,10 @@
         <v>41</v>
       </c>
       <c r="J241" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K241" s="82">
-        <f>INDEX('feed pars'!K$6:K$43,MATCH(F241,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!N$6:N$43,MATCH(F241,'feed pars'!B$6:B$43,0))</f>
         <v>17</v>
       </c>
     </row>
@@ -6465,10 +6490,10 @@
         <v>42</v>
       </c>
       <c r="J242" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K242" s="82">
-        <f>INDEX('feed pars'!K$6:K$43,MATCH(F242,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!N$6:N$43,MATCH(F242,'feed pars'!B$6:B$43,0))</f>
         <v>14</v>
       </c>
     </row>
@@ -6480,10 +6505,10 @@
         <v>35</v>
       </c>
       <c r="J243" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K243" s="82">
-        <f>INDEX('feed pars'!K$6:K$43,MATCH(F243,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!N$6:N$43,MATCH(F243,'feed pars'!B$6:B$43,0))</f>
         <v>460</v>
       </c>
     </row>
@@ -6495,10 +6520,10 @@
         <v>43</v>
       </c>
       <c r="J244" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K244" s="82">
-        <f>INDEX('feed pars'!K$6:K$43,MATCH(F244,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!N$6:N$43,MATCH(F244,'feed pars'!B$6:B$43,0))</f>
         <v>380</v>
       </c>
     </row>
@@ -6510,10 +6535,10 @@
         <v>302</v>
       </c>
       <c r="J245" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K245" s="82">
-        <f>INDEX('feed pars'!K$6:K$43,MATCH(F245,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!N$6:N$43,MATCH(F245,'feed pars'!B$6:B$43,0))</f>
         <v>20</v>
       </c>
     </row>
@@ -6525,10 +6550,10 @@
         <v>310</v>
       </c>
       <c r="J246" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K246" s="82">
-        <f>INDEX('feed pars'!K$6:K$43,MATCH(F246,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!N$6:N$43,MATCH(F246,'feed pars'!B$6:B$43,0))</f>
         <v>1000</v>
       </c>
     </row>
@@ -6540,10 +6565,10 @@
         <v>314</v>
       </c>
       <c r="J247" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K247" s="82">
-        <f>INDEX('feed pars'!K$6:K$43,MATCH(F247,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!N$6:N$43,MATCH(F247,'feed pars'!B$6:B$43,0))</f>
         <v>180</v>
       </c>
     </row>
@@ -6555,10 +6580,10 @@
         <v>44</v>
       </c>
       <c r="J248" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K248" s="82">
-        <f>INDEX('feed pars'!K$6:K$43,MATCH(F248,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!N$6:N$43,MATCH(F248,'feed pars'!B$6:B$43,0))</f>
         <v>10</v>
       </c>
     </row>
@@ -6570,10 +6595,10 @@
         <v>36</v>
       </c>
       <c r="J249" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K249" s="82">
-        <f>INDEX('feed pars'!K$6:K$43,MATCH(F249,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!N$6:N$43,MATCH(F249,'feed pars'!B$6:B$43,0))</f>
         <v>46</v>
       </c>
     </row>
@@ -6585,10 +6610,10 @@
         <v>46</v>
       </c>
       <c r="J250" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K250" s="82">
-        <f>INDEX('feed pars'!K$6:K$43,MATCH(F250,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!N$6:N$43,MATCH(F250,'feed pars'!B$6:B$43,0))</f>
         <v>10</v>
       </c>
     </row>
@@ -6600,10 +6625,10 @@
         <v>47</v>
       </c>
       <c r="J251" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K251" s="82">
-        <f>INDEX('feed pars'!K$6:K$43,MATCH(F251,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!N$6:N$43,MATCH(F251,'feed pars'!B$6:B$43,0))</f>
         <v>97</v>
       </c>
     </row>
@@ -6615,10 +6640,10 @@
         <v>315</v>
       </c>
       <c r="J252" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K252" s="82">
-        <f>INDEX('feed pars'!K$6:K$43,MATCH(F252,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!N$6:N$43,MATCH(F252,'feed pars'!B$6:B$43,0))</f>
         <v>27</v>
       </c>
     </row>
@@ -6630,10 +6655,10 @@
         <v>48</v>
       </c>
       <c r="J253" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K253" s="82">
-        <f>INDEX('feed pars'!K$6:K$43,MATCH(F253,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!N$6:N$43,MATCH(F253,'feed pars'!B$6:B$43,0))</f>
         <v>45</v>
       </c>
     </row>
@@ -6645,10 +6670,10 @@
         <v>50</v>
       </c>
       <c r="J254" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K254" s="82">
-        <f>INDEX('feed pars'!K$6:K$43,MATCH(F254,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!N$6:N$43,MATCH(F254,'feed pars'!B$6:B$43,0))</f>
         <v>45</v>
       </c>
     </row>
@@ -6660,10 +6685,10 @@
         <v>309</v>
       </c>
       <c r="J255" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K255" s="82">
-        <f>INDEX('feed pars'!K$6:K$43,MATCH(F255,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!N$6:N$43,MATCH(F255,'feed pars'!B$6:B$43,0))</f>
         <v>80</v>
       </c>
     </row>
@@ -6675,10 +6700,10 @@
         <v>52</v>
       </c>
       <c r="J256" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K256" s="82">
-        <f>INDEX('feed pars'!K$6:K$43,MATCH(F256,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!N$6:N$43,MATCH(F256,'feed pars'!B$6:B$43,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -6690,10 +6715,10 @@
         <v>53</v>
       </c>
       <c r="J257" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K257" s="82">
-        <f>INDEX('feed pars'!K$6:K$43,MATCH(F257,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!N$6:N$43,MATCH(F257,'feed pars'!B$6:B$43,0))</f>
         <v>32</v>
       </c>
     </row>
@@ -6705,10 +6730,10 @@
         <v>54</v>
       </c>
       <c r="J258" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K258" s="82">
-        <f>INDEX('feed pars'!K$6:K$43,MATCH(F258,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!N$6:N$43,MATCH(F258,'feed pars'!B$6:B$43,0))</f>
         <v>10</v>
       </c>
     </row>
@@ -6720,10 +6745,10 @@
         <v>56</v>
       </c>
       <c r="J259" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K259" s="82">
-        <f>INDEX('feed pars'!K$6:K$43,MATCH(F259,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!N$6:N$43,MATCH(F259,'feed pars'!B$6:B$43,0))</f>
         <v>33</v>
       </c>
     </row>
@@ -6735,7 +6760,7 @@
         <v>320</v>
       </c>
       <c r="J260" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K260" s="3">
         <v>0</v>
@@ -6770,14 +6795,14 @@
         <v>18</v>
       </c>
       <c r="K262" s="25">
-        <f>INDEX('feed pars'!I$6:I$43,MATCH(F262,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!L$6:L$43,MATCH(F262,'feed pars'!B$6:B$43,0))</f>
         <v>9.1</v>
       </c>
       <c r="L262" t="s">
         <v>19</v>
       </c>
       <c r="M262" s="26" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="263" spans="1:14" x14ac:dyDescent="0.25">
@@ -7001,14 +7026,14 @@
         <v>18</v>
       </c>
       <c r="K278" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F278,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F278,'feed pars'!B$6:B$43,0))</f>
         <v>12.3</v>
       </c>
       <c r="L278" t="s">
         <v>297</v>
       </c>
       <c r="M278" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="279" spans="1:14" x14ac:dyDescent="0.25">
@@ -7025,7 +7050,7 @@
         <v>18</v>
       </c>
       <c r="K279" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F279,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F279,'feed pars'!B$6:B$43,0))</f>
         <v>11.2</v>
       </c>
     </row>
@@ -7043,7 +7068,7 @@
         <v>18</v>
       </c>
       <c r="K280" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F280,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F280,'feed pars'!B$6:B$43,0))</f>
         <v>9.4</v>
       </c>
     </row>
@@ -7061,7 +7086,7 @@
         <v>18</v>
       </c>
       <c r="K281" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F281,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F281,'feed pars'!B$6:B$43,0))</f>
         <v>12</v>
       </c>
     </row>
@@ -7079,7 +7104,7 @@
         <v>18</v>
       </c>
       <c r="K282" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F282,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F282,'feed pars'!B$6:B$43,0))</f>
         <v>13.2</v>
       </c>
     </row>
@@ -7097,7 +7122,7 @@
         <v>18</v>
       </c>
       <c r="K283" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F283,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F283,'feed pars'!B$6:B$43,0))</f>
         <v>11.5</v>
       </c>
     </row>
@@ -7115,7 +7140,7 @@
         <v>18</v>
       </c>
       <c r="K284" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F284,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F284,'feed pars'!B$6:B$43,0))</f>
         <v>10.9</v>
       </c>
     </row>
@@ -7133,7 +7158,7 @@
         <v>18</v>
       </c>
       <c r="K285" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F285,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F285,'feed pars'!B$6:B$43,0))</f>
         <v>18.5</v>
       </c>
     </row>
@@ -7151,7 +7176,7 @@
         <v>18</v>
       </c>
       <c r="K286" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F286,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F286,'feed pars'!B$6:B$43,0))</f>
         <v>17.5</v>
       </c>
     </row>
@@ -7169,7 +7194,7 @@
         <v>18</v>
       </c>
       <c r="K287" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F287,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F287,'feed pars'!B$6:B$43,0))</f>
         <v>29.8</v>
       </c>
     </row>
@@ -7187,7 +7212,7 @@
         <v>18</v>
       </c>
       <c r="K288" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F288,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F288,'feed pars'!B$6:B$43,0))</f>
         <v>9.9</v>
       </c>
     </row>
@@ -7205,7 +7230,7 @@
         <v>18</v>
       </c>
       <c r="K289" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F289,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F289,'feed pars'!B$6:B$43,0))</f>
         <v>10.3</v>
       </c>
     </row>
@@ -7223,7 +7248,7 @@
         <v>18</v>
       </c>
       <c r="K290" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F290,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F290,'feed pars'!B$6:B$43,0))</f>
         <v>7.7</v>
       </c>
     </row>
@@ -7241,7 +7266,7 @@
         <v>18</v>
       </c>
       <c r="K291" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F291,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F291,'feed pars'!B$6:B$43,0))</f>
         <v>6.5</v>
       </c>
     </row>
@@ -7259,7 +7284,7 @@
         <v>18</v>
       </c>
       <c r="K292" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F292,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F292,'feed pars'!B$6:B$43,0))</f>
         <v>6.2</v>
       </c>
     </row>
@@ -7277,7 +7302,7 @@
         <v>18</v>
       </c>
       <c r="K293" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F293,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F293,'feed pars'!B$6:B$43,0))</f>
         <v>7.8</v>
       </c>
     </row>
@@ -7295,7 +7320,7 @@
         <v>18</v>
       </c>
       <c r="K294" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F294,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F294,'feed pars'!B$6:B$43,0))</f>
         <v>9.1999999999999993</v>
       </c>
     </row>
@@ -7313,7 +7338,7 @@
         <v>18</v>
       </c>
       <c r="K295" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F295,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F295,'feed pars'!B$6:B$43,0))</f>
         <v>8.6999999999999993</v>
       </c>
     </row>
@@ -7331,7 +7356,7 @@
         <v>18</v>
       </c>
       <c r="K296" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F296,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F296,'feed pars'!B$6:B$43,0))</f>
         <v>8.9</v>
       </c>
     </row>
@@ -7349,7 +7374,7 @@
         <v>18</v>
       </c>
       <c r="K297" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F297,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F297,'feed pars'!B$6:B$43,0))</f>
         <v>7.0888888888888877</v>
       </c>
     </row>
@@ -7367,7 +7392,7 @@
         <v>18</v>
       </c>
       <c r="K298" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F298,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F298,'feed pars'!B$6:B$43,0))</f>
         <v>9</v>
       </c>
     </row>
@@ -7385,7 +7410,7 @@
         <v>18</v>
       </c>
       <c r="K299" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F299,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F299,'feed pars'!B$6:B$43,0))</f>
         <v>8</v>
       </c>
     </row>
@@ -7403,7 +7428,7 @@
         <v>18</v>
       </c>
       <c r="K300" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F300,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F300,'feed pars'!B$6:B$43,0))</f>
         <v>12.2</v>
       </c>
     </row>
@@ -7421,7 +7446,7 @@
         <v>18</v>
       </c>
       <c r="K301" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F301,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F301,'feed pars'!B$6:B$43,0))</f>
         <v>12.2</v>
       </c>
     </row>
@@ -7439,7 +7464,7 @@
         <v>18</v>
       </c>
       <c r="K302" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F302,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F302,'feed pars'!B$6:B$43,0))</f>
         <v>11.3</v>
       </c>
     </row>
@@ -7457,7 +7482,7 @@
         <v>18</v>
       </c>
       <c r="K303" s="25">
-        <f>INDEX('feed pars'!U$6:U$43,MATCH(F303,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F303,'feed pars'!B$6:B$43,0))</f>
         <v>10.8</v>
       </c>
     </row>
@@ -7490,14 +7515,14 @@
         <v>18</v>
       </c>
       <c r="K305" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F305,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F305,'feed pars'!B$6:B$43,0))</f>
         <v>12.1</v>
       </c>
       <c r="L305" t="s">
         <v>22</v>
       </c>
       <c r="M305" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="306" spans="1:13" x14ac:dyDescent="0.25">
@@ -7511,7 +7536,7 @@
         <v>18</v>
       </c>
       <c r="K306" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F306,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F306,'feed pars'!B$6:B$43,0))</f>
         <v>11</v>
       </c>
     </row>
@@ -7526,7 +7551,7 @@
         <v>18</v>
       </c>
       <c r="K307" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F307,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F307,'feed pars'!B$6:B$43,0))</f>
         <v>9</v>
       </c>
     </row>
@@ -7541,7 +7566,7 @@
         <v>18</v>
       </c>
       <c r="K308" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F308,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F308,'feed pars'!B$6:B$43,0))</f>
         <v>11.9</v>
       </c>
     </row>
@@ -7556,7 +7581,7 @@
         <v>18</v>
       </c>
       <c r="K309" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F309,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F309,'feed pars'!B$6:B$43,0))</f>
         <v>12.8</v>
       </c>
     </row>
@@ -7571,7 +7596,7 @@
         <v>18</v>
       </c>
       <c r="K310" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F310,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F310,'feed pars'!B$6:B$43,0))</f>
         <v>11.2</v>
       </c>
     </row>
@@ -7586,7 +7611,7 @@
         <v>18</v>
       </c>
       <c r="K311" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F311,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F311,'feed pars'!B$6:B$43,0))</f>
         <v>10.7</v>
       </c>
     </row>
@@ -7601,7 +7626,7 @@
         <v>18</v>
       </c>
       <c r="K312" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F312,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F312,'feed pars'!B$6:B$43,0))</f>
         <v>18</v>
       </c>
     </row>
@@ -7616,7 +7641,7 @@
         <v>18</v>
       </c>
       <c r="K313" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F313,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F313,'feed pars'!B$6:B$43,0))</f>
         <v>17.3</v>
       </c>
     </row>
@@ -7631,7 +7656,7 @@
         <v>18</v>
       </c>
       <c r="K314" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F314,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F314,'feed pars'!B$6:B$43,0))</f>
         <v>29.8</v>
       </c>
     </row>
@@ -7646,7 +7671,7 @@
         <v>18</v>
       </c>
       <c r="K315" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F315,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F315,'feed pars'!B$6:B$43,0))</f>
         <v>9.3000000000000007</v>
       </c>
     </row>
@@ -7661,7 +7686,7 @@
         <v>18</v>
       </c>
       <c r="K316" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F316,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F316,'feed pars'!B$6:B$43,0))</f>
         <v>9.6999999999999993</v>
       </c>
     </row>
@@ -7676,7 +7701,7 @@
         <v>18</v>
       </c>
       <c r="K317" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F317,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F317,'feed pars'!B$6:B$43,0))</f>
         <v>7.1</v>
       </c>
     </row>
@@ -7691,7 +7716,7 @@
         <v>18</v>
       </c>
       <c r="K318" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F318,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F318,'feed pars'!B$6:B$43,0))</f>
         <v>5.9</v>
       </c>
     </row>
@@ -7706,7 +7731,7 @@
         <v>18</v>
       </c>
       <c r="K319" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F319,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F319,'feed pars'!B$6:B$43,0))</f>
         <v>5.4</v>
       </c>
     </row>
@@ -7721,7 +7746,7 @@
         <v>18</v>
       </c>
       <c r="K320" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F320,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F320,'feed pars'!B$6:B$43,0))</f>
         <v>7.2</v>
       </c>
     </row>
@@ -7736,7 +7761,7 @@
         <v>18</v>
       </c>
       <c r="K321" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F321,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F321,'feed pars'!B$6:B$43,0))</f>
         <v>8.6999999999999993</v>
       </c>
     </row>
@@ -7751,7 +7776,7 @@
         <v>18</v>
       </c>
       <c r="K322" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F322,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F322,'feed pars'!B$6:B$43,0))</f>
         <v>8.1</v>
       </c>
     </row>
@@ -7766,7 +7791,7 @@
         <v>18</v>
       </c>
       <c r="K323" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F323,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F323,'feed pars'!B$6:B$43,0))</f>
         <v>8.1999999999999993</v>
       </c>
     </row>
@@ -7781,7 +7806,7 @@
         <v>18</v>
       </c>
       <c r="K324" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F324,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F324,'feed pars'!B$6:B$43,0))</f>
         <v>6.6</v>
       </c>
     </row>
@@ -7796,7 +7821,7 @@
         <v>18</v>
       </c>
       <c r="K325" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F325,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F325,'feed pars'!B$6:B$43,0))</f>
         <v>8.6999999999999993</v>
       </c>
     </row>
@@ -7811,7 +7836,7 @@
         <v>18</v>
       </c>
       <c r="K326" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F326,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F326,'feed pars'!B$6:B$43,0))</f>
         <v>6.9</v>
       </c>
     </row>
@@ -7826,7 +7851,7 @@
         <v>18</v>
       </c>
       <c r="K327" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F327,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F327,'feed pars'!B$6:B$43,0))</f>
         <v>12.4</v>
       </c>
     </row>
@@ -7841,7 +7866,7 @@
         <v>18</v>
       </c>
       <c r="K328" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F328,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F328,'feed pars'!B$6:B$43,0))</f>
         <v>12.4</v>
       </c>
     </row>
@@ -7856,7 +7881,7 @@
         <v>18</v>
       </c>
       <c r="K329" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F329,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F329,'feed pars'!B$6:B$43,0))</f>
         <v>11.1</v>
       </c>
     </row>
@@ -7871,7 +7896,7 @@
         <v>18</v>
       </c>
       <c r="K330" s="25">
-        <f>INDEX('feed pars'!T$6:T$43,MATCH(F330,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F330,'feed pars'!B$6:B$43,0))</f>
         <v>10.8</v>
       </c>
     </row>
@@ -7883,120 +7908,159 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:AD46"/>
+  <dimension ref="B1:AM46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="7.5703125" customWidth="1"/>
-    <col min="17" max="17" width="7.5703125" customWidth="1"/>
+    <col min="3" max="8" width="7.5703125" customWidth="1"/>
+    <col min="23" max="23" width="7.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C1" s="11" t="s">
         <v>118</v>
       </c>
       <c r="D1" s="11"/>
       <c r="E1" s="11"/>
-      <c r="Q1" s="11"/>
-    </row>
-    <row r="3" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="W1" s="11"/>
+    </row>
+    <row r="3" spans="2:39" x14ac:dyDescent="0.25">
       <c r="C3" s="62" t="s">
         <v>303</v>
       </c>
       <c r="D3" s="63"/>
-      <c r="F3" s="62" t="s">
-        <v>489</v>
-      </c>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
       <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
+      <c r="I3" s="62" t="s">
+        <v>488</v>
+      </c>
       <c r="J3" s="63"/>
       <c r="K3" s="63"/>
       <c r="L3" s="63"/>
       <c r="M3" s="63"/>
       <c r="N3" s="63"/>
-      <c r="Q3" s="62" t="s">
-        <v>25</v>
-      </c>
-      <c r="R3" s="63"/>
+      <c r="O3" s="63"/>
+      <c r="P3" s="63"/>
+      <c r="Q3" s="89" t="s">
+        <v>508</v>
+      </c>
+      <c r="R3" s="63">
+        <f>1/6.25</f>
+        <v>0.16</v>
+      </c>
       <c r="S3" s="63"/>
       <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="63"/>
-      <c r="W3" s="63"/>
+      <c r="W3" s="62" t="s">
+        <v>25</v>
+      </c>
       <c r="X3" s="63"/>
       <c r="Y3" s="63"/>
-      <c r="AB3" s="62" t="s">
+      <c r="Z3" s="63"/>
+      <c r="AA3" s="63"/>
+      <c r="AB3" s="63"/>
+      <c r="AC3" s="63"/>
+      <c r="AD3" s="63"/>
+      <c r="AE3" s="89" t="s">
+        <v>508</v>
+      </c>
+      <c r="AF3" s="63">
+        <f>1/6.25</f>
+        <v>0.16</v>
+      </c>
+      <c r="AG3" s="63"/>
+      <c r="AH3" s="63"/>
+      <c r="AK3" s="62" t="s">
         <v>385</v>
       </c>
-      <c r="AC3" s="63"/>
-    </row>
-    <row r="4" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="AL3" s="63"/>
+    </row>
+    <row r="4" spans="2:39" x14ac:dyDescent="0.25">
       <c r="C4" s="61"/>
       <c r="D4" s="2"/>
-      <c r="F4" s="68" t="s">
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="I4" s="68" t="s">
         <v>294</v>
       </c>
-      <c r="G4" s="69">
+      <c r="J4" s="69">
         <v>1</v>
       </c>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69">
+      <c r="K4" s="69"/>
+      <c r="L4" s="69">
         <v>2</v>
       </c>
-      <c r="J4" s="69">
+      <c r="M4" s="69">
         <v>7</v>
       </c>
-      <c r="K4" s="69">
+      <c r="N4" s="69">
         <v>8</v>
       </c>
-      <c r="L4" s="69">
+      <c r="O4" s="69">
         <v>9</v>
       </c>
-      <c r="M4" s="69">
+      <c r="P4" s="69">
         <v>11</v>
       </c>
-      <c r="N4" s="69">
+      <c r="Q4" s="69">
         <v>10</v>
       </c>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="68" t="s">
+      <c r="R4" s="69"/>
+      <c r="S4" s="69">
+        <v>26</v>
+      </c>
+      <c r="T4" s="69">
+        <v>28</v>
+      </c>
+      <c r="U4" s="4"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="68" t="s">
         <v>294</v>
       </c>
-      <c r="R4" s="69">
+      <c r="X4" s="69">
         <v>1</v>
       </c>
-      <c r="S4" s="69"/>
-      <c r="T4" s="69">
+      <c r="Y4" s="69"/>
+      <c r="Z4" s="69">
         <v>2</v>
       </c>
-      <c r="U4" s="69">
+      <c r="AA4" s="69">
         <v>3</v>
       </c>
-      <c r="V4" s="69">
+      <c r="AB4" s="69">
         <v>5</v>
       </c>
-      <c r="W4" s="69">
+      <c r="AC4" s="69">
         <v>6</v>
       </c>
-      <c r="X4" s="69"/>
-      <c r="Y4" s="69">
+      <c r="AD4" s="69"/>
+      <c r="AE4" s="69">
         <v>12</v>
       </c>
-      <c r="Z4" s="4"/>
-      <c r="AA4" s="4"/>
-      <c r="AB4" s="68" t="s">
+      <c r="AF4" s="69"/>
+      <c r="AG4" s="69">
+        <v>29</v>
+      </c>
+      <c r="AH4" s="69">
+        <v>31</v>
+      </c>
+      <c r="AI4" s="4"/>
+      <c r="AJ4" s="4"/>
+      <c r="AK4" s="68" t="s">
         <v>294</v>
       </c>
-      <c r="AC4" s="69">
+      <c r="AL4" s="69">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>58</v>
       </c>
@@ -8004,132 +8068,186 @@
         <v>59</v>
       </c>
       <c r="D5" s="73" t="s">
-        <v>407</v>
-      </c>
-      <c r="F5" s="68" t="s">
+        <v>406</v>
+      </c>
+      <c r="E5" s="72" t="s">
+        <v>505</v>
+      </c>
+      <c r="F5" s="72" t="s">
+        <v>506</v>
+      </c>
+      <c r="G5" s="73" t="s">
+        <v>507</v>
+      </c>
+      <c r="I5" s="68" t="s">
         <v>295</v>
       </c>
-      <c r="G5" s="71" t="s">
+      <c r="J5" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="H5" s="72" t="s">
-        <v>495</v>
-      </c>
-      <c r="I5" s="72" t="s">
+      <c r="K5" s="72" t="s">
         <v>494</v>
       </c>
-      <c r="J5" s="72" t="s">
+      <c r="L5" s="72" t="s">
+        <v>493</v>
+      </c>
+      <c r="M5" s="71" t="s">
+        <v>409</v>
+      </c>
+      <c r="N5" s="72" t="s">
         <v>410</v>
       </c>
-      <c r="K5" s="72" t="s">
+      <c r="O5" s="72" t="s">
         <v>411</v>
       </c>
-      <c r="L5" s="72" t="s">
-        <v>412</v>
-      </c>
-      <c r="M5" s="72" t="s">
+      <c r="P5" s="72" t="s">
         <v>282</v>
       </c>
-      <c r="N5" s="73" t="s">
-        <v>487</v>
-      </c>
-      <c r="O5" s="75" t="s">
+      <c r="Q5" s="73" t="s">
+        <v>486</v>
+      </c>
+      <c r="R5" s="72" t="s">
+        <v>505</v>
+      </c>
+      <c r="S5" s="72" t="s">
+        <v>506</v>
+      </c>
+      <c r="T5" s="73" t="s">
+        <v>507</v>
+      </c>
+      <c r="U5" s="75" t="s">
+        <v>491</v>
+      </c>
+      <c r="W5" s="68" t="s">
+        <v>295</v>
+      </c>
+      <c r="X5" s="71" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y5" s="72" t="s">
+        <v>494</v>
+      </c>
+      <c r="Z5" s="72" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA5" s="72" t="s">
+        <v>120</v>
+      </c>
+      <c r="AB5" s="71" t="s">
+        <v>409</v>
+      </c>
+      <c r="AC5" s="72" t="s">
+        <v>410</v>
+      </c>
+      <c r="AD5" s="72" t="s">
         <v>492</v>
       </c>
-      <c r="Q5" s="68" t="s">
+      <c r="AE5" s="73" t="s">
+        <v>486</v>
+      </c>
+      <c r="AF5" s="72" t="s">
+        <v>505</v>
+      </c>
+      <c r="AG5" s="72" t="s">
+        <v>506</v>
+      </c>
+      <c r="AH5" s="73" t="s">
+        <v>507</v>
+      </c>
+      <c r="AI5" s="75" t="s">
+        <v>491</v>
+      </c>
+      <c r="AJ5" s="4"/>
+      <c r="AK5" s="68" t="s">
         <v>295</v>
       </c>
-      <c r="R5" s="71" t="s">
+      <c r="AL5" s="70" t="s">
         <v>59</v>
       </c>
-      <c r="S5" s="72" t="s">
-        <v>495</v>
-      </c>
-      <c r="T5" s="72" t="s">
-        <v>121</v>
-      </c>
-      <c r="U5" s="72" t="s">
-        <v>120</v>
-      </c>
-      <c r="V5" s="72" t="s">
-        <v>410</v>
-      </c>
-      <c r="W5" s="72" t="s">
-        <v>411</v>
-      </c>
-      <c r="X5" s="72" t="s">
-        <v>493</v>
-      </c>
-      <c r="Y5" s="73" t="s">
-        <v>487</v>
-      </c>
-      <c r="Z5" s="75" t="s">
-        <v>492</v>
-      </c>
-      <c r="AA5" s="4"/>
-      <c r="AB5" s="68" t="s">
-        <v>295</v>
-      </c>
-      <c r="AC5" s="70" t="s">
-        <v>59</v>
-      </c>
-      <c r="AD5" s="75" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="6" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="AM5" s="75" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="6" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>306</v>
       </c>
       <c r="C6" s="37">
-        <f t="shared" ref="C6:C11" si="0">AVERAGE(R6,G6)</f>
+        <f t="shared" ref="C6:C11" si="0">AVERAGE(X6,J6)</f>
         <v>100</v>
       </c>
       <c r="D6" s="64">
-        <f t="shared" ref="D6:D11" si="1">H6</f>
+        <f t="shared" ref="D6:D11" si="1">K6</f>
         <v>17.316948400000001</v>
       </c>
-      <c r="F6" s="68"/>
-      <c r="G6" s="37">
+      <c r="E6" s="38">
+        <f>AVERAGE(R6,AF6)</f>
+        <v>2.4239999999999999</v>
+      </c>
+      <c r="F6" s="91">
+        <f t="shared" ref="F6:G6" si="2">AVERAGE(S6,AG6)</f>
+        <v>0.27999999999999997</v>
+      </c>
+      <c r="G6" s="92">
+        <f t="shared" si="2"/>
+        <v>2.4250000000000003</v>
+      </c>
+      <c r="I6" s="68"/>
+      <c r="J6" s="37">
         <v>100</v>
       </c>
-      <c r="H6" s="77">
-        <f t="shared" ref="H6:H11" si="2">( 5.7*J6+9.4*K6+4.1*(L6+M6) ) * 0.004184</f>
+      <c r="K6" s="77">
+        <f t="shared" ref="K6:K11" si="3">( 5.7*M6+9.4*N6+4.1*(O6+P6) ) * 0.004184</f>
         <v>17.316948400000001</v>
       </c>
-      <c r="I6" s="38">
+      <c r="L6" s="38">
         <f>AVERAGE('ruminants, roughage'!D21:D22)</f>
         <v>11.3</v>
       </c>
-      <c r="J6" s="39">
+      <c r="M6" s="65">
         <f>AVERAGE('ruminants, roughage'!I21:I22)</f>
         <v>151.5</v>
       </c>
-      <c r="K6" s="44">
+      <c r="N6" s="44">
         <v>20</v>
       </c>
-      <c r="L6" s="39"/>
-      <c r="M6" s="41">
-        <f t="shared" ref="M6:M11" si="3">1000-SUM(J6:L6,N6)</f>
+      <c r="O6" s="39"/>
+      <c r="P6" s="41">
+        <f t="shared" ref="P6:P11" si="4">1000-SUM(M6:O6,Q6)</f>
         <v>753</v>
       </c>
-      <c r="N6" s="42">
+      <c r="Q6" s="42">
         <f>AVERAGE('ruminants, roughage'!K21:K22)</f>
         <v>75.5</v>
       </c>
-      <c r="Q6" s="68"/>
-      <c r="R6" s="37"/>
-      <c r="S6" s="54"/>
-      <c r="T6" s="54"/>
-      <c r="U6" s="54"/>
-      <c r="V6" s="54"/>
-      <c r="W6" s="54"/>
-      <c r="X6" s="54"/>
-      <c r="Y6" s="55"/>
-      <c r="AB6" s="68"/>
-      <c r="AC6" s="59"/>
-    </row>
-    <row r="7" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="R6" s="38">
+        <f>M6*R$3/1000*100</f>
+        <v>2.4239999999999999</v>
+      </c>
+      <c r="S6" s="91">
+        <f>AVERAGE('ruminants, roughage'!X21:X22)/1000*100</f>
+        <v>0.27999999999999997</v>
+      </c>
+      <c r="T6" s="92">
+        <f>AVERAGE('ruminants, roughage'!Z21:Z22)/1000*100</f>
+        <v>2.4250000000000003</v>
+      </c>
+      <c r="W6" s="68"/>
+      <c r="X6" s="37"/>
+      <c r="Y6" s="54"/>
+      <c r="Z6" s="54"/>
+      <c r="AA6" s="54"/>
+      <c r="AB6" s="37"/>
+      <c r="AC6" s="54"/>
+      <c r="AD6" s="54"/>
+      <c r="AE6" s="55"/>
+      <c r="AF6" s="39"/>
+      <c r="AG6" s="39"/>
+      <c r="AH6" s="42"/>
+      <c r="AK6" s="68"/>
+      <c r="AL6" s="59"/>
+    </row>
+    <row r="7" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>307</v>
       </c>
@@ -8141,47 +8259,74 @@
         <f t="shared" si="1"/>
         <v>17.150216</v>
       </c>
-      <c r="F7" s="68"/>
-      <c r="G7" s="37">
+      <c r="E7" s="38">
+        <f t="shared" ref="E7:E14" si="5">AVERAGE(R7,AF7)</f>
+        <v>2.1280000000000001</v>
+      </c>
+      <c r="F7" s="91">
+        <f t="shared" ref="F7:F14" si="6">AVERAGE(S7,AG7)</f>
+        <v>0.27</v>
+      </c>
+      <c r="G7" s="92">
+        <f t="shared" ref="G7:G14" si="7">AVERAGE(T7,AH7)</f>
+        <v>2.34</v>
+      </c>
+      <c r="I7" s="68"/>
+      <c r="J7" s="37">
         <v>100</v>
       </c>
-      <c r="H7" s="77">
-        <f t="shared" si="2"/>
+      <c r="K7" s="77">
+        <f t="shared" si="3"/>
         <v>17.150216</v>
       </c>
-      <c r="I7" s="38">
+      <c r="L7" s="38">
         <f>AVERAGE('ruminants, roughage'!D25:D25)</f>
         <v>10.1</v>
       </c>
-      <c r="J7" s="39">
+      <c r="M7" s="65">
         <f>AVERAGE('ruminants, roughage'!I25:I25)</f>
         <v>133</v>
       </c>
-      <c r="K7" s="44">
+      <c r="N7" s="44">
         <v>20</v>
       </c>
-      <c r="L7" s="39"/>
-      <c r="M7" s="41">
-        <f t="shared" si="3"/>
+      <c r="O7" s="39"/>
+      <c r="P7" s="41">
+        <f t="shared" si="4"/>
         <v>769</v>
       </c>
-      <c r="N7" s="42">
+      <c r="Q7" s="42">
         <f>AVERAGE('ruminants, roughage'!K25:K25)</f>
         <v>78</v>
       </c>
-      <c r="Q7" s="68"/>
-      <c r="R7" s="37"/>
-      <c r="S7" s="54"/>
-      <c r="T7" s="54"/>
-      <c r="U7" s="54"/>
-      <c r="V7" s="54"/>
-      <c r="W7" s="54"/>
-      <c r="X7" s="54"/>
-      <c r="Y7" s="55"/>
-      <c r="AB7" s="68"/>
-      <c r="AC7" s="59"/>
-    </row>
-    <row r="8" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="R7" s="38">
+        <f t="shared" ref="R7:R42" si="8">M7*R$3/1000*100</f>
+        <v>2.1280000000000001</v>
+      </c>
+      <c r="S7" s="91">
+        <f>AVERAGE('ruminants, roughage'!X25:X25)/1000*100</f>
+        <v>0.27</v>
+      </c>
+      <c r="T7" s="92">
+        <f>AVERAGE('ruminants, roughage'!Z25:Z25)/1000*100</f>
+        <v>2.34</v>
+      </c>
+      <c r="W7" s="68"/>
+      <c r="X7" s="37"/>
+      <c r="Y7" s="54"/>
+      <c r="Z7" s="54"/>
+      <c r="AA7" s="54"/>
+      <c r="AB7" s="37"/>
+      <c r="AC7" s="54"/>
+      <c r="AD7" s="54"/>
+      <c r="AE7" s="55"/>
+      <c r="AF7" s="39"/>
+      <c r="AG7" s="39"/>
+      <c r="AH7" s="42"/>
+      <c r="AK7" s="68"/>
+      <c r="AL7" s="59"/>
+    </row>
+    <row r="8" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>308</v>
       </c>
@@ -8191,56 +8336,83 @@
       </c>
       <c r="D8" s="64">
         <f t="shared" si="1"/>
-        <v>16.819680000000002</v>
-      </c>
-      <c r="F8" s="68"/>
-      <c r="G8" s="37">
+        <v>16.789764399999999</v>
+      </c>
+      <c r="E8" s="38">
+        <f t="shared" si="5"/>
+        <v>1.5439999999999998</v>
+      </c>
+      <c r="F8" s="91">
+        <f t="shared" si="6"/>
+        <v>0.21000000000000002</v>
+      </c>
+      <c r="G8" s="92">
+        <f t="shared" si="7"/>
+        <v>2.35</v>
+      </c>
+      <c r="I8" s="68"/>
+      <c r="J8" s="37">
         <v>100</v>
       </c>
-      <c r="H8" s="77">
-        <f t="shared" si="2"/>
-        <v>16.819680000000002</v>
-      </c>
-      <c r="I8" s="43">
-        <f>(9.3+9.2)/2</f>
-        <v>9.25</v>
-      </c>
-      <c r="J8" s="44">
-        <f>(105+110)/2</f>
-        <v>107.5</v>
-      </c>
-      <c r="K8" s="44">
-        <f>(34+38)/2</f>
-        <v>36</v>
-      </c>
-      <c r="L8" s="40"/>
-      <c r="M8" s="41">
+      <c r="K8" s="77">
         <f t="shared" si="3"/>
-        <v>748.5</v>
-      </c>
-      <c r="N8" s="45">
-        <f>(101+115)/2</f>
-        <v>108</v>
-      </c>
-      <c r="O8" t="s">
-        <v>488</v>
-      </c>
-      <c r="P8" t="s">
-        <v>490</v>
-      </c>
-      <c r="Q8" s="68"/>
-      <c r="R8" s="37"/>
-      <c r="S8" s="54"/>
-      <c r="T8" s="54"/>
-      <c r="U8" s="54"/>
-      <c r="V8" s="54"/>
-      <c r="W8" s="54"/>
-      <c r="X8" s="54"/>
-      <c r="Y8" s="55"/>
-      <c r="AB8" s="68"/>
-      <c r="AC8" s="59"/>
-    </row>
-    <row r="9" spans="2:30" x14ac:dyDescent="0.25">
+        <v>16.789764399999999</v>
+      </c>
+      <c r="L8" s="43">
+        <f>(8.3+8.7)/2</f>
+        <v>8.5</v>
+      </c>
+      <c r="M8" s="86">
+        <f>(91+102)/2</f>
+        <v>96.5</v>
+      </c>
+      <c r="N8" s="44">
+        <f>(22+23)/2</f>
+        <v>22.5</v>
+      </c>
+      <c r="O8" s="40"/>
+      <c r="P8" s="41">
+        <f t="shared" si="4"/>
+        <v>793</v>
+      </c>
+      <c r="Q8" s="45">
+        <f>(83+93)/2</f>
+        <v>88</v>
+      </c>
+      <c r="R8" s="38">
+        <f t="shared" si="8"/>
+        <v>1.5439999999999998</v>
+      </c>
+      <c r="S8" s="91">
+        <f>(2+2.2)/2/1000*100</f>
+        <v>0.21000000000000002</v>
+      </c>
+      <c r="T8" s="92">
+        <f>(20.3+26.7)/2/1000*100</f>
+        <v>2.35</v>
+      </c>
+      <c r="U8" t="s">
+        <v>487</v>
+      </c>
+      <c r="V8" t="s">
+        <v>489</v>
+      </c>
+      <c r="W8" s="68"/>
+      <c r="X8" s="37"/>
+      <c r="Y8" s="54"/>
+      <c r="Z8" s="54"/>
+      <c r="AA8" s="54"/>
+      <c r="AB8" s="37"/>
+      <c r="AC8" s="54"/>
+      <c r="AD8" s="54"/>
+      <c r="AE8" s="55"/>
+      <c r="AF8" s="40"/>
+      <c r="AG8" s="40"/>
+      <c r="AH8" s="45"/>
+      <c r="AK8" s="68"/>
+      <c r="AL8" s="59"/>
+    </row>
+    <row r="9" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>2</v>
       </c>
@@ -8252,47 +8424,74 @@
         <f t="shared" si="1"/>
         <v>17.160257599999998</v>
       </c>
-      <c r="F9" s="68"/>
-      <c r="G9" s="37">
+      <c r="E9" s="38">
+        <f t="shared" si="5"/>
+        <v>1.496</v>
+      </c>
+      <c r="F9" s="91">
+        <f t="shared" si="6"/>
+        <v>0.21000000000000002</v>
+      </c>
+      <c r="G9" s="92">
+        <f t="shared" si="7"/>
+        <v>1.81</v>
+      </c>
+      <c r="I9" s="68"/>
+      <c r="J9" s="37">
         <v>100</v>
       </c>
-      <c r="H9" s="77">
-        <f t="shared" si="2"/>
+      <c r="K9" s="77">
+        <f t="shared" si="3"/>
         <v>17.160257599999998</v>
       </c>
-      <c r="I9" s="38">
+      <c r="L9" s="38">
         <f>AVERAGE('ruminants, roughage'!D33:D33)</f>
         <v>9.1</v>
       </c>
-      <c r="J9" s="39">
+      <c r="M9" s="65">
         <f>AVERAGE('ruminants, roughage'!I33:I33)</f>
         <v>93.5</v>
       </c>
-      <c r="K9" s="44">
+      <c r="N9" s="44">
         <v>20</v>
       </c>
-      <c r="L9" s="39"/>
-      <c r="M9" s="41">
-        <f t="shared" si="3"/>
+      <c r="O9" s="39"/>
+      <c r="P9" s="41">
+        <f t="shared" si="4"/>
         <v>824.5</v>
       </c>
-      <c r="N9" s="42">
+      <c r="Q9" s="42">
         <f>AVERAGE('ruminants, roughage'!K33:K33)</f>
         <v>62</v>
       </c>
-      <c r="Q9" s="68"/>
-      <c r="R9" s="37"/>
-      <c r="S9" s="54"/>
-      <c r="T9" s="54"/>
-      <c r="U9" s="54"/>
-      <c r="V9" s="54"/>
-      <c r="W9" s="54"/>
-      <c r="X9" s="54"/>
-      <c r="Y9" s="55"/>
-      <c r="AB9" s="68"/>
-      <c r="AC9" s="59"/>
-    </row>
-    <row r="10" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="R9" s="38">
+        <f t="shared" si="8"/>
+        <v>1.496</v>
+      </c>
+      <c r="S9" s="91">
+        <f>AVERAGE('ruminants, roughage'!X33:X33)/1000*100</f>
+        <v>0.21000000000000002</v>
+      </c>
+      <c r="T9" s="92">
+        <f>AVERAGE('ruminants, roughage'!Z33:Z33)/1000*100</f>
+        <v>1.81</v>
+      </c>
+      <c r="W9" s="68"/>
+      <c r="X9" s="37"/>
+      <c r="Y9" s="54"/>
+      <c r="Z9" s="54"/>
+      <c r="AA9" s="54"/>
+      <c r="AB9" s="37"/>
+      <c r="AC9" s="54"/>
+      <c r="AD9" s="54"/>
+      <c r="AE9" s="55"/>
+      <c r="AF9" s="39"/>
+      <c r="AG9" s="39"/>
+      <c r="AH9" s="42"/>
+      <c r="AK9" s="68"/>
+      <c r="AL9" s="59"/>
+    </row>
+    <row r="10" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>12</v>
       </c>
@@ -8304,52 +8503,79 @@
         <f t="shared" si="1"/>
         <v>17.6573168</v>
       </c>
-      <c r="F10" s="68"/>
-      <c r="G10" s="37">
+      <c r="E10" s="38">
+        <f t="shared" si="5"/>
+        <v>1.0880000000000001</v>
+      </c>
+      <c r="F10" s="91">
+        <f t="shared" si="6"/>
+        <v>0.16999999999999998</v>
+      </c>
+      <c r="G10" s="92">
+        <f t="shared" si="7"/>
+        <v>1.03</v>
+      </c>
+      <c r="I10" s="68"/>
+      <c r="J10" s="37">
         <v>100</v>
       </c>
-      <c r="H10" s="77">
-        <f t="shared" si="2"/>
+      <c r="K10" s="77">
+        <f t="shared" si="3"/>
         <v>17.6573168</v>
       </c>
-      <c r="I10" s="38">
+      <c r="L10" s="38">
         <v>11</v>
       </c>
-      <c r="J10" s="39">
+      <c r="M10" s="65">
         <v>68</v>
       </c>
-      <c r="K10" s="39">
+      <c r="N10" s="39">
         <v>30</v>
       </c>
-      <c r="L10" s="39">
+      <c r="O10" s="39">
         <v>198</v>
       </c>
-      <c r="M10" s="41">
-        <f t="shared" si="3"/>
+      <c r="P10" s="41">
+        <f t="shared" si="4"/>
         <v>668</v>
       </c>
-      <c r="N10" s="42">
+      <c r="Q10" s="42">
         <v>36</v>
       </c>
-      <c r="O10" s="11" t="s">
-        <v>408</v>
-      </c>
-      <c r="P10" s="11" t="s">
-        <v>490</v>
-      </c>
-      <c r="Q10" s="68"/>
-      <c r="R10" s="37"/>
-      <c r="S10" s="54"/>
-      <c r="T10" s="54"/>
-      <c r="U10" s="54"/>
-      <c r="V10" s="54"/>
-      <c r="W10" s="54"/>
-      <c r="X10" s="54"/>
-      <c r="Y10" s="55"/>
-      <c r="AB10" s="68"/>
-      <c r="AC10" s="59"/>
-    </row>
-    <row r="11" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="R10" s="38">
+        <f t="shared" si="8"/>
+        <v>1.0880000000000001</v>
+      </c>
+      <c r="S10" s="91">
+        <f>1.7/1000*100</f>
+        <v>0.16999999999999998</v>
+      </c>
+      <c r="T10" s="92">
+        <f>10.3/1000*100</f>
+        <v>1.03</v>
+      </c>
+      <c r="U10" s="11" t="s">
+        <v>407</v>
+      </c>
+      <c r="V10" s="11" t="s">
+        <v>489</v>
+      </c>
+      <c r="W10" s="68"/>
+      <c r="X10" s="37"/>
+      <c r="Y10" s="54"/>
+      <c r="Z10" s="54"/>
+      <c r="AA10" s="54"/>
+      <c r="AB10" s="37"/>
+      <c r="AC10" s="54"/>
+      <c r="AD10" s="54"/>
+      <c r="AE10" s="55"/>
+      <c r="AF10" s="39"/>
+      <c r="AG10" s="39"/>
+      <c r="AH10" s="42"/>
+      <c r="AK10" s="68"/>
+      <c r="AL10" s="59"/>
+    </row>
+    <row r="11" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>33</v>
       </c>
@@ -8361,2647 +8587,3724 @@
         <f t="shared" si="1"/>
         <v>17.411437066666668</v>
       </c>
-      <c r="F11" s="68"/>
-      <c r="G11" s="37">
+      <c r="E11" s="38">
+        <f t="shared" si="5"/>
+        <v>2.2466666666666666</v>
+      </c>
+      <c r="F11" s="91">
+        <f t="shared" si="6"/>
+        <v>0.27</v>
+      </c>
+      <c r="G11" s="92">
+        <f t="shared" si="7"/>
+        <v>2.34</v>
+      </c>
+      <c r="I11" s="68"/>
+      <c r="J11" s="37">
         <v>100</v>
       </c>
-      <c r="H11" s="77">
-        <f t="shared" si="2"/>
+      <c r="K11" s="77">
+        <f t="shared" si="3"/>
         <v>17.411437066666668</v>
       </c>
-      <c r="I11" s="38">
+      <c r="L11" s="38">
         <f>AVERAGE('ruminants, roughage'!D3:D14)</f>
         <v>9.9416666666666664</v>
       </c>
-      <c r="J11" s="39">
+      <c r="M11" s="65">
         <f>AVERAGE('ruminants, roughage'!I3:I14)</f>
         <v>140.41666666666666</v>
       </c>
-      <c r="K11" s="44">
+      <c r="N11" s="44">
         <v>20</v>
       </c>
-      <c r="L11" s="39"/>
-      <c r="M11" s="41">
-        <f t="shared" si="3"/>
+      <c r="O11" s="39"/>
+      <c r="P11" s="41">
+        <f t="shared" si="4"/>
         <v>773.91666666666674</v>
       </c>
-      <c r="N11" s="42">
+      <c r="Q11" s="42">
         <f>AVERAGE('ruminants, roughage'!K3:K14)</f>
         <v>65.666666666666657</v>
       </c>
-      <c r="Q11" s="68"/>
-      <c r="R11" s="37"/>
-      <c r="S11" s="54"/>
-      <c r="T11" s="54"/>
-      <c r="U11" s="54"/>
-      <c r="V11" s="54"/>
-      <c r="W11" s="54"/>
-      <c r="X11" s="54"/>
-      <c r="Y11" s="55"/>
-      <c r="AB11" s="68"/>
-      <c r="AC11" s="59"/>
-    </row>
-    <row r="12" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="R11" s="38">
+        <f t="shared" si="8"/>
+        <v>2.2466666666666666</v>
+      </c>
+      <c r="S11" s="96">
+        <f>S7</f>
+        <v>0.27</v>
+      </c>
+      <c r="T11" s="97">
+        <f>T7</f>
+        <v>2.34</v>
+      </c>
+      <c r="W11" s="68"/>
+      <c r="X11" s="37"/>
+      <c r="Y11" s="54"/>
+      <c r="Z11" s="54"/>
+      <c r="AA11" s="54"/>
+      <c r="AB11" s="37"/>
+      <c r="AC11" s="54"/>
+      <c r="AD11" s="54"/>
+      <c r="AE11" s="55"/>
+      <c r="AF11" s="39"/>
+      <c r="AG11" s="39"/>
+      <c r="AH11" s="42"/>
+      <c r="AK11" s="68"/>
+      <c r="AL11" s="59"/>
+    </row>
+    <row r="12" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B12" s="4"/>
       <c r="C12" s="46"/>
       <c r="D12" s="55"/>
-      <c r="F12" s="68"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="56"/>
-      <c r="I12" s="47"/>
-      <c r="J12" s="48"/>
-      <c r="K12" s="48"/>
-      <c r="L12" s="48"/>
-      <c r="M12" s="48"/>
-      <c r="N12" s="49"/>
-      <c r="Q12" s="68"/>
-      <c r="R12" s="46"/>
-      <c r="S12" s="56"/>
-      <c r="T12" s="56"/>
-      <c r="U12" s="56"/>
-      <c r="V12" s="56"/>
-      <c r="W12" s="56"/>
-      <c r="X12" s="56"/>
-      <c r="Y12" s="57"/>
-      <c r="Z12" s="4"/>
-      <c r="AA12" s="4"/>
-      <c r="AB12" s="68"/>
-      <c r="AC12" s="59"/>
-    </row>
-    <row r="13" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="E12" s="48"/>
+      <c r="F12" s="48"/>
+      <c r="G12" s="49"/>
+      <c r="I12" s="68"/>
+      <c r="J12" s="46"/>
+      <c r="K12" s="56"/>
+      <c r="L12" s="47"/>
+      <c r="M12" s="87"/>
+      <c r="N12" s="48"/>
+      <c r="O12" s="48"/>
+      <c r="P12" s="48"/>
+      <c r="Q12" s="49"/>
+      <c r="R12" s="38"/>
+      <c r="S12" s="48"/>
+      <c r="T12" s="49"/>
+      <c r="W12" s="68"/>
+      <c r="X12" s="46"/>
+      <c r="Y12" s="56"/>
+      <c r="Z12" s="56"/>
+      <c r="AA12" s="56"/>
+      <c r="AB12" s="46"/>
+      <c r="AC12" s="56"/>
+      <c r="AD12" s="56"/>
+      <c r="AE12" s="57"/>
+      <c r="AF12" s="48"/>
+      <c r="AG12" s="48"/>
+      <c r="AH12" s="49"/>
+      <c r="AI12" s="4"/>
+      <c r="AJ12" s="4"/>
+      <c r="AK12" s="68"/>
+      <c r="AL12" s="59"/>
+    </row>
+    <row r="13" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>17</v>
       </c>
       <c r="C13" s="65">
-        <f t="shared" ref="C13:C36" si="4">AVERAGE(R13,G13)</f>
+        <f t="shared" ref="C13:C36" si="9">AVERAGE(X13,J13)</f>
         <v>87</v>
       </c>
       <c r="D13" s="64">
-        <f t="shared" ref="D13:D26" si="5">H13</f>
+        <f t="shared" ref="D13:D26" si="10">K13</f>
         <v>18.210023200000002</v>
       </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="68">
+      <c r="E13" s="38">
+        <f t="shared" si="5"/>
+        <v>1.9359999999999999</v>
+      </c>
+      <c r="F13" s="91">
+        <f t="shared" si="6"/>
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="G13" s="92">
+        <f t="shared" si="7"/>
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="H13" s="4"/>
+      <c r="I13" s="68">
         <f>MATCH($B13,ruminants!$A$3:$A$120,0)</f>
         <v>112</v>
       </c>
-      <c r="G13" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F13,G$4)</f>
+      <c r="J13" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I13,J$4)</f>
         <v>87</v>
       </c>
-      <c r="H13" s="77">
-        <f>( 5.7*J13+9.4*K13+4.1*(L13+M13) ) * 0.004184</f>
+      <c r="K13" s="77">
+        <f>( 5.7*M13+9.4*N13+4.1*(O13+P13) ) * 0.004184</f>
         <v>18.210023200000002</v>
       </c>
-      <c r="I13" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F13,I$4)</f>
+      <c r="L13" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I13,L$4)</f>
         <v>14.1</v>
       </c>
-      <c r="J13" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F13,J$4)</f>
+      <c r="M13" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I13,M$4)</f>
         <v>121</v>
       </c>
-      <c r="K13" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F13,K$4)</f>
+      <c r="N13" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I13,N$4)</f>
         <v>25</v>
       </c>
-      <c r="L13" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F13,L$4)</f>
+      <c r="O13" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I13,O$4)</f>
         <v>30</v>
       </c>
-      <c r="M13" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F13,M$4)</f>
+      <c r="P13" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I13,P$4)</f>
         <v>806</v>
       </c>
-      <c r="N13" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F13,N$4)</f>
+      <c r="Q13" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I13,Q$4)</f>
         <v>18</v>
       </c>
-      <c r="Q13" s="68">
+      <c r="R13" s="38">
+        <f t="shared" si="8"/>
+        <v>1.9359999999999999</v>
+      </c>
+      <c r="S13" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I13,S$4)/1000*100</f>
+        <v>0.37</v>
+      </c>
+      <c r="T13" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I13,T$4)/1000*100</f>
+        <v>0.47000000000000003</v>
+      </c>
+      <c r="W13" s="68">
         <f>MATCH($B13,pigs!$A$3:$A$60,0)</f>
         <v>53</v>
       </c>
-      <c r="R13" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q13,R$4)</f>
+      <c r="X13" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W13,X$4)</f>
         <v>87</v>
       </c>
-      <c r="S13" s="77">
-        <f>( 5.7*V13+9.4*W13+4.1*(X13) ) * 0.004184</f>
+      <c r="Y13" s="77">
+        <f>( 5.7*AB13+9.4*AC13+4.1*(AD13) ) * 0.004184</f>
         <v>18.032621599999999</v>
       </c>
-      <c r="T13" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q13,T$4)</f>
+      <c r="Z13" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W13,Z$4)</f>
         <v>12.1</v>
       </c>
-      <c r="U13" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q13,U$4)</f>
+      <c r="AA13" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W13,AA$4)</f>
         <v>12.3</v>
       </c>
-      <c r="V13" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q13,V$4)</f>
+      <c r="AB13" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W13,AB$4)</f>
         <v>121</v>
       </c>
-      <c r="W13" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q13,W$4)</f>
+      <c r="AC13" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W13,AC$4)</f>
         <v>17</v>
       </c>
-      <c r="X13" s="41">
-        <f>1000-SUM(V13:W13,Y13)</f>
+      <c r="AD13" s="41">
+        <f>1000-SUM(AB13:AC13,AE13)</f>
         <v>844</v>
       </c>
-      <c r="Y13" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q13,Y$4)</f>
+      <c r="AE13" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$W13,AE$4)</f>
         <v>18</v>
       </c>
-      <c r="AB13" s="68">
+      <c r="AF13" s="38">
+        <f>AB13*AF$3/1000*100</f>
+        <v>1.9359999999999999</v>
+      </c>
+      <c r="AG13" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$W13,AG$4)/1000*100</f>
+        <v>0.32</v>
+      </c>
+      <c r="AH13" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$W13,AH$4)/1000*100</f>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="AK13" s="68">
         <f>MATCH($B13,poultry!$A$3:$A$41,0)</f>
         <v>35</v>
       </c>
-      <c r="AC13" s="59">
-        <f>INDEX(poultry!$D$3:$U$41,$AB13,AC$4)</f>
+      <c r="AL13" s="59">
+        <f>INDEX(poultry!$D$3:$U$41,$AK13,AL$4)</f>
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>37</v>
       </c>
       <c r="C14" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>87</v>
       </c>
       <c r="D14" s="64">
+        <f t="shared" si="10"/>
+        <v>18.089524000000001</v>
+      </c>
+      <c r="E14" s="38">
         <f t="shared" si="5"/>
-        <v>18.089524000000001</v>
-      </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="68">
+        <v>1.9039999999999999</v>
+      </c>
+      <c r="F14" s="91">
+        <f t="shared" si="6"/>
+        <v>0.375</v>
+      </c>
+      <c r="G14" s="92">
+        <f t="shared" si="7"/>
+        <v>0.58000000000000007</v>
+      </c>
+      <c r="H14" s="4"/>
+      <c r="I14" s="68">
         <f>MATCH($B14,ruminants!$A$3:$A$120,0)</f>
         <v>42</v>
       </c>
-      <c r="G14" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F14,G$4)</f>
+      <c r="J14" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I14,J$4)</f>
         <v>87</v>
       </c>
-      <c r="H14" s="77">
-        <f t="shared" ref="H14:H42" si="6">( 5.7*J14+9.4*K14+4.1*(L14+M14) ) * 0.004184</f>
+      <c r="K14" s="77">
+        <f t="shared" ref="K14:K42" si="11">( 5.7*M14+9.4*N14+4.1*(O14+P14) ) * 0.004184</f>
         <v>18.089524000000001</v>
       </c>
-      <c r="I14" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F14,I$4)</f>
+      <c r="L14" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I14,L$4)</f>
         <v>13.2</v>
       </c>
-      <c r="J14" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F14,J$4)</f>
+      <c r="M14" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I14,M$4)</f>
         <v>122</v>
       </c>
-      <c r="K14" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F14,K$4)</f>
+      <c r="N14" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I14,N$4)</f>
         <v>27</v>
       </c>
-      <c r="L14" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F14,L$4)</f>
+      <c r="O14" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I14,O$4)</f>
         <v>62</v>
       </c>
-      <c r="M14" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F14,M$4)</f>
+      <c r="P14" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I14,P$4)</f>
         <v>761</v>
       </c>
-      <c r="N14" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F14,N$4)</f>
+      <c r="Q14" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I14,Q$4)</f>
         <v>28</v>
       </c>
-      <c r="Q14" s="68">
+      <c r="R14" s="38">
+        <f t="shared" si="8"/>
+        <v>1.952</v>
+      </c>
+      <c r="S14" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I14,S$4)/1000*100</f>
+        <v>0.4</v>
+      </c>
+      <c r="T14" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I14,T$4)/1000*100</f>
+        <v>0.59000000000000008</v>
+      </c>
+      <c r="W14" s="68">
         <f>MATCH($B14,pigs!$A$3:$A$60,0)</f>
         <v>13</v>
       </c>
-      <c r="R14" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q14,R$4)</f>
+      <c r="X14" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W14,X$4)</f>
         <v>87</v>
       </c>
-      <c r="S14" s="77">
-        <f t="shared" ref="S14:S16" si="7">( 5.7*V14+9.4*W14+4.1*(X14) ) * 0.004184</f>
+      <c r="Y14" s="77">
+        <f t="shared" ref="Y14:Y16" si="12">( 5.7*AB14+9.4*AC14+4.1*(AD14) ) * 0.004184</f>
         <v>17.950615200000001</v>
       </c>
-      <c r="T14" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q14,T$4)</f>
+      <c r="Z14" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W14,Z$4)</f>
         <v>11</v>
       </c>
-      <c r="U14" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q14,U$4)</f>
+      <c r="AA14" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W14,AA$4)</f>
         <v>11.2</v>
       </c>
-      <c r="V14" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q14,V$4)</f>
+      <c r="AB14" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W14,AB$4)</f>
         <v>116</v>
       </c>
-      <c r="W14" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q14,W$4)</f>
+      <c r="AC14" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W14,AC$4)</f>
         <v>21</v>
       </c>
-      <c r="X14" s="41">
-        <f t="shared" ref="X14:X16" si="8">1000-SUM(V14:W14,Y14)</f>
+      <c r="AD14" s="41">
+        <f t="shared" ref="AD14:AD16" si="13">1000-SUM(AB14:AC14,AE14)</f>
         <v>837</v>
       </c>
-      <c r="Y14" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q14,Y$4)</f>
+      <c r="AE14" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$W14,AE$4)</f>
         <v>26</v>
       </c>
-      <c r="AB14" s="68">
+      <c r="AF14" s="38">
+        <f t="shared" ref="AF14:AF43" si="14">AB14*AF$3/1000*100</f>
+        <v>1.8560000000000001</v>
+      </c>
+      <c r="AG14" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$W14,AG$4)/1000*100</f>
+        <v>0.35000000000000003</v>
+      </c>
+      <c r="AH14" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$W14,AH$4)/1000*100</f>
+        <v>0.57000000000000006</v>
+      </c>
+      <c r="AK14" s="68">
         <f>MATCH($B14,poultry!$A$3:$A$41,0)</f>
         <v>16</v>
       </c>
-      <c r="AC14" s="59">
-        <f>INDEX(poultry!$D$3:$U$41,$AB14,AC$4)</f>
+      <c r="AL14" s="59">
+        <f>INDEX(poultry!$D$3:$U$41,$AK14,AL$4)</f>
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>38</v>
       </c>
       <c r="C15" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>86</v>
       </c>
       <c r="D15" s="64">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>18.6602216</v>
       </c>
-      <c r="E15" s="4"/>
-      <c r="F15" s="68">
+      <c r="E15" s="38">
+        <f t="shared" ref="E15:E16" si="15">AVERAGE(R15,AF15)</f>
+        <v>1.7680000000000002</v>
+      </c>
+      <c r="F15" s="91">
+        <f t="shared" ref="F15:F16" si="16">AVERAGE(S15,AG15)</f>
+        <v>0.36499999999999999</v>
+      </c>
+      <c r="G15" s="92">
+        <f t="shared" ref="G15:G16" si="17">AVERAGE(T15,AH15)</f>
+        <v>0.54</v>
+      </c>
+      <c r="H15" s="4"/>
+      <c r="I15" s="68">
         <f>MATCH($B15,ruminants!$A$3:$A$120,0)</f>
         <v>28</v>
       </c>
-      <c r="G15" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F15,G$4)</f>
+      <c r="J15" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I15,J$4)</f>
         <v>85</v>
       </c>
-      <c r="H15" s="77">
-        <f t="shared" si="6"/>
+      <c r="K15" s="77">
+        <f t="shared" si="11"/>
         <v>18.6602216</v>
       </c>
-      <c r="I15" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F15,I$4)</f>
+      <c r="L15" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I15,L$4)</f>
         <v>11.7</v>
       </c>
-      <c r="J15" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F15,J$4)</f>
+      <c r="M15" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I15,M$4)</f>
         <v>110</v>
       </c>
-      <c r="K15" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F15,K$4)</f>
+      <c r="N15" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I15,N$4)</f>
         <v>61</v>
       </c>
-      <c r="L15" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F15,L$4)</f>
+      <c r="O15" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I15,O$4)</f>
         <v>141</v>
       </c>
-      <c r="M15" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F15,M$4)</f>
+      <c r="P15" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I15,P$4)</f>
         <v>654</v>
       </c>
-      <c r="N15" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F15,N$4)</f>
+      <c r="Q15" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I15,Q$4)</f>
         <v>34</v>
       </c>
-      <c r="Q15" s="68">
+      <c r="R15" s="38">
+        <f t="shared" si="8"/>
+        <v>1.76</v>
+      </c>
+      <c r="S15" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I15,S$4)/1000*100</f>
+        <v>0.37</v>
+      </c>
+      <c r="T15" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I15,T$4)/1000*100</f>
+        <v>0.53</v>
+      </c>
+      <c r="W15" s="68">
         <f>MATCH($B15,pigs!$A$3:$A$60,0)</f>
         <v>11</v>
       </c>
-      <c r="R15" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q15,R$4)</f>
+      <c r="X15" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W15,X$4)</f>
         <v>87</v>
       </c>
-      <c r="S15" s="77">
-        <f t="shared" si="7"/>
+      <c r="Y15" s="77">
+        <f t="shared" si="12"/>
         <v>18.580307199999996</v>
       </c>
-      <c r="T15" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q15,T$4)</f>
+      <c r="Z15" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W15,Z$4)</f>
         <v>9</v>
       </c>
-      <c r="U15" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q15,U$4)</f>
+      <c r="AA15" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W15,AA$4)</f>
         <v>9.4</v>
       </c>
-      <c r="V15" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q15,V$4)</f>
+      <c r="AB15" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W15,AB$4)</f>
         <v>111</v>
       </c>
-      <c r="W15" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q15,W$4)</f>
+      <c r="AC15" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W15,AC$4)</f>
         <v>54</v>
       </c>
-      <c r="X15" s="41">
-        <f t="shared" si="8"/>
+      <c r="AD15" s="41">
+        <f t="shared" si="13"/>
         <v>805</v>
       </c>
-      <c r="Y15" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q15,Y$4)</f>
+      <c r="AE15" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$W15,AE$4)</f>
         <v>30</v>
       </c>
-      <c r="AB15" s="68">
+      <c r="AF15" s="38">
+        <f t="shared" si="14"/>
+        <v>1.7760000000000002</v>
+      </c>
+      <c r="AG15" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$W15,AG$4)/1000*100</f>
+        <v>0.36</v>
+      </c>
+      <c r="AH15" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$W15,AH$4)/1000*100</f>
+        <v>0.54999999999999993</v>
+      </c>
+      <c r="AK15" s="68">
         <f>MATCH($B15,poultry!$A$3:$A$41,0)</f>
         <v>10</v>
       </c>
-      <c r="AC15" s="59">
-        <f>INDEX(poultry!$D$3:$U$41,$AB15,AC$4)</f>
+      <c r="AL15" s="59">
+        <f>INDEX(poultry!$D$3:$U$41,$AK15,AL$4)</f>
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>39</v>
       </c>
       <c r="C16" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>87</v>
       </c>
       <c r="D16" s="64">
-        <f t="shared" si="5"/>
+        <f>K16</f>
         <v>18.2284328</v>
       </c>
-      <c r="E16" s="4"/>
-      <c r="F16" s="68">
+      <c r="E16" s="38">
+        <f t="shared" si="15"/>
+        <v>1.8639999999999999</v>
+      </c>
+      <c r="F16" s="91">
+        <f t="shared" si="16"/>
+        <v>0.38</v>
+      </c>
+      <c r="G16" s="92">
+        <f t="shared" si="17"/>
+        <v>0.58000000000000007</v>
+      </c>
+      <c r="H16" s="4"/>
+      <c r="I16" s="68">
         <f>MATCH($B16,ruminants!$A$3:$A$120,0)</f>
         <v>78</v>
       </c>
-      <c r="G16" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F16,G$4)</f>
+      <c r="J16" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I16,J$4)</f>
         <v>87</v>
       </c>
-      <c r="H16" s="77">
-        <f t="shared" si="6"/>
+      <c r="K16" s="77">
+        <f t="shared" si="11"/>
         <v>18.2284328</v>
       </c>
-      <c r="I16" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F16,I$4)</f>
+      <c r="L16" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I16,L$4)</f>
         <v>14</v>
       </c>
-      <c r="J16" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F16,J$4)</f>
+      <c r="M16" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I16,M$4)</f>
         <v>123</v>
       </c>
-      <c r="K16" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F16,K$4)</f>
+      <c r="N16" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I16,N$4)</f>
         <v>26</v>
       </c>
-      <c r="L16" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F16,L$4)</f>
+      <c r="O16" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I16,O$4)</f>
         <v>33</v>
       </c>
-      <c r="M16" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F16,M$4)</f>
+      <c r="P16" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I16,P$4)</f>
         <v>799</v>
       </c>
-      <c r="N16" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F16,N$4)</f>
+      <c r="Q16" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I16,Q$4)</f>
         <v>19</v>
       </c>
-      <c r="Q16" s="68">
+      <c r="R16" s="38">
+        <f t="shared" si="8"/>
+        <v>1.968</v>
+      </c>
+      <c r="S16" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I16,S$4)/1000*100</f>
+        <v>0.4</v>
+      </c>
+      <c r="T16" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I16,T$4)/1000*100</f>
+        <v>0.54</v>
+      </c>
+      <c r="W16" s="68">
         <f>MATCH($B16,pigs!$A$3:$A$60,0)</f>
         <v>39</v>
       </c>
-      <c r="R16" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q16,R$4)</f>
+      <c r="X16" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W16,X$4)</f>
         <v>87</v>
       </c>
-      <c r="S16" s="77">
-        <f t="shared" si="7"/>
+      <c r="Y16" s="77">
+        <f t="shared" si="12"/>
         <v>17.846015199999997</v>
       </c>
-      <c r="T16" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q16,T$4)</f>
+      <c r="Z16" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W16,Z$4)</f>
         <v>11.9</v>
       </c>
-      <c r="U16" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q16,U$4)</f>
+      <c r="AA16" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W16,AA$4)</f>
         <v>12</v>
       </c>
-      <c r="V16" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q16,V$4)</f>
+      <c r="AB16" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W16,AB$4)</f>
         <v>110</v>
       </c>
-      <c r="W16" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q16,W$4)</f>
+      <c r="AC16" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W16,AC$4)</f>
         <v>15</v>
       </c>
-      <c r="X16" s="41">
-        <f t="shared" si="8"/>
+      <c r="AD16" s="41">
+        <f t="shared" si="13"/>
         <v>853</v>
       </c>
-      <c r="Y16" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q16,Y$4)</f>
+      <c r="AE16" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$W16,AE$4)</f>
         <v>22</v>
       </c>
-      <c r="AB16" s="68">
+      <c r="AF16" s="38">
+        <f t="shared" si="14"/>
+        <v>1.76</v>
+      </c>
+      <c r="AG16" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$W16,AG$4)/1000*100</f>
+        <v>0.36</v>
+      </c>
+      <c r="AH16" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$W16,AH$4)/1000*100</f>
+        <v>0.62</v>
+      </c>
+      <c r="AK16" s="68">
         <f>MATCH($B16,poultry!$A$3:$A$41,0)</f>
         <v>31</v>
       </c>
-      <c r="AC16" s="59">
-        <f>INDEX(poultry!$D$3:$U$41,$AB16,AC$4)</f>
+      <c r="AL16" s="59">
+        <f>INDEX(poultry!$D$3:$U$41,$AK16,AL$4)</f>
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>313</v>
       </c>
       <c r="C17" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>87</v>
       </c>
       <c r="D17" s="64">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>17.924256</v>
       </c>
-      <c r="E17" s="4"/>
-      <c r="F17" s="68">
+      <c r="E17" s="38">
+        <f t="shared" ref="E17:E43" si="18">AVERAGE(R17,AF17)</f>
+        <v>1.6</v>
+      </c>
+      <c r="F17" s="91">
+        <f t="shared" ref="F17:F43" si="19">AVERAGE(S17,AG17)</f>
+        <v>0.33999999999999997</v>
+      </c>
+      <c r="G17" s="92">
+        <f t="shared" ref="G17:G43" si="20">AVERAGE(T17,AH17)</f>
+        <v>0.54999999999999993</v>
+      </c>
+      <c r="H17" s="4"/>
+      <c r="I17" s="68">
         <f>MATCH($B17,ruminants!$A$3:$A$120,0)</f>
         <v>77</v>
       </c>
-      <c r="G17" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F17,G$4)</f>
+      <c r="J17" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I17,J$4)</f>
         <v>87</v>
       </c>
-      <c r="H17" s="77">
-        <f t="shared" si="6"/>
+      <c r="K17" s="77">
+        <f t="shared" si="11"/>
         <v>17.924256</v>
       </c>
-      <c r="I17" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F17,I$4)</f>
+      <c r="L17" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I17,L$4)</f>
         <v>13.9</v>
       </c>
-      <c r="J17" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F17,J$4)</f>
+      <c r="M17" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I17,M$4)</f>
         <v>100</v>
       </c>
-      <c r="K17" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F17,K$4)</f>
+      <c r="N17" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I17,N$4)</f>
         <v>20</v>
       </c>
-      <c r="L17" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F17,L$4)</f>
+      <c r="O17" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I17,O$4)</f>
         <v>25</v>
       </c>
-      <c r="M17" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F17,M$4)</f>
+      <c r="P17" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I17,P$4)</f>
         <v>835</v>
       </c>
-      <c r="N17" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F17,N$4)</f>
+      <c r="Q17" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I17,Q$4)</f>
         <v>20</v>
       </c>
-      <c r="Q17" s="68">
+      <c r="R17" s="38">
+        <f t="shared" si="8"/>
+        <v>1.6</v>
+      </c>
+      <c r="S17" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I17,S$4)/1000*100</f>
+        <v>0.33999999999999997</v>
+      </c>
+      <c r="T17" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I17,T$4)/1000*100</f>
+        <v>0.54999999999999993</v>
+      </c>
+      <c r="W17" s="68">
         <f>MATCH($B17,pigs!$A$3:$A$60,0)</f>
         <v>38</v>
       </c>
-      <c r="R17" s="37"/>
-      <c r="S17" s="54"/>
-      <c r="T17" s="54"/>
-      <c r="U17" s="54"/>
-      <c r="V17" s="54"/>
-      <c r="W17" s="54"/>
-      <c r="X17" s="54"/>
-      <c r="Y17" s="55"/>
-      <c r="AB17" s="68">
+      <c r="X17" s="37"/>
+      <c r="Y17" s="54"/>
+      <c r="Z17" s="54"/>
+      <c r="AA17" s="54"/>
+      <c r="AB17" s="37"/>
+      <c r="AC17" s="54"/>
+      <c r="AD17" s="54"/>
+      <c r="AE17" s="55"/>
+      <c r="AF17" s="38"/>
+      <c r="AG17" s="91"/>
+      <c r="AH17" s="92"/>
+      <c r="AK17" s="68">
         <f>MATCH($B17,poultry!$A$3:$A$41,0)</f>
         <v>30</v>
       </c>
-      <c r="AC17" s="59">
-        <f>INDEX(poultry!$D$3:$U$41,$AB17,AC$4)</f>
+      <c r="AL17" s="59">
+        <f>INDEX(poultry!$D$3:$U$41,$AK17,AL$4)</f>
         <v>87</v>
       </c>
     </row>
-    <row r="18" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>40</v>
       </c>
       <c r="C18" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>67.5</v>
       </c>
       <c r="D18" s="64">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>18.3899352</v>
       </c>
-      <c r="E18" s="4"/>
-      <c r="F18" s="68">
+      <c r="E18" s="38">
+        <f t="shared" si="18"/>
+        <v>1.6400000000000001</v>
+      </c>
+      <c r="F18" s="91">
+        <f t="shared" si="19"/>
+        <v>0.33999999999999997</v>
+      </c>
+      <c r="G18" s="92">
+        <f t="shared" si="20"/>
+        <v>0.46500000000000002</v>
+      </c>
+      <c r="H18" s="4"/>
+      <c r="I18" s="68">
         <f>MATCH($B18,ruminants!$A$3:$A$120,0)</f>
         <v>53</v>
       </c>
-      <c r="G18" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F18,G$4)</f>
+      <c r="J18" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I18,J$4)</f>
         <v>48</v>
       </c>
-      <c r="H18" s="77">
-        <f t="shared" si="6"/>
+      <c r="K18" s="77">
+        <f t="shared" si="11"/>
         <v>18.3899352</v>
       </c>
-      <c r="I18" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F18,I$4)</f>
+      <c r="L18" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I18,L$4)</f>
         <v>12.8</v>
       </c>
-      <c r="J18" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F18,J$4)</f>
+      <c r="M18" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I18,M$4)</f>
         <v>111</v>
       </c>
-      <c r="K18" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F18,K$4)</f>
+      <c r="N18" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I18,N$4)</f>
         <v>40</v>
       </c>
-      <c r="L18" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F18,L$4)</f>
+      <c r="O18" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I18,O$4)</f>
         <v>63</v>
       </c>
-      <c r="M18" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F18,M$4)</f>
+      <c r="P18" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I18,P$4)</f>
         <v>763</v>
       </c>
-      <c r="N18" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F18,N$4)</f>
+      <c r="Q18" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I18,Q$4)</f>
         <v>23</v>
       </c>
-      <c r="Q18" s="68">
+      <c r="R18" s="38">
+        <f t="shared" si="8"/>
+        <v>1.7760000000000002</v>
+      </c>
+      <c r="S18" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I18,S$4)/1000*100</f>
+        <v>0.36</v>
+      </c>
+      <c r="T18" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I18,T$4)/1000*100</f>
+        <v>0.53</v>
+      </c>
+      <c r="W18" s="68">
         <f>MATCH($B18,pigs!$A$3:$A$60,0)</f>
         <v>19</v>
       </c>
-      <c r="R18" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q18,R$4)</f>
+      <c r="X18" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W18,X$4)</f>
         <v>87</v>
       </c>
-      <c r="S18" s="77">
-        <f t="shared" ref="S18:S23" si="9">( 5.7*V18+9.4*W18+4.1*(X18) ) * 0.004184</f>
+      <c r="Y18" s="77">
+        <f t="shared" ref="Y18:Y23" si="21">( 5.7*AB18+9.4*AC18+4.1*(AD18) ) * 0.004184</f>
         <v>18.4970456</v>
       </c>
-      <c r="T18" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q18,T$4)</f>
+      <c r="Z18" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W18,Z$4)</f>
         <v>12.8</v>
       </c>
-      <c r="U18" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q18,U$4)</f>
+      <c r="AA18" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W18,AA$4)</f>
         <v>13.2</v>
       </c>
-      <c r="V18" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q18,V$4)</f>
+      <c r="AB18" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W18,AB$4)</f>
         <v>94</v>
       </c>
-      <c r="W18" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q18,W$4)</f>
+      <c r="AC18" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W18,AC$4)</f>
         <v>43</v>
       </c>
-      <c r="X18" s="41">
-        <f t="shared" ref="X18:X23" si="10">1000-SUM(V18:W18,Y18)</f>
+      <c r="AD18" s="41">
+        <f t="shared" ref="AD18:AD23" si="22">1000-SUM(AB18:AC18,AE18)</f>
         <v>849</v>
       </c>
-      <c r="Y18" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q18,Y$4)</f>
+      <c r="AE18" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$W18,AE$4)</f>
         <v>14</v>
       </c>
-      <c r="AB18" s="68">
+      <c r="AF18" s="38">
+        <f t="shared" si="14"/>
+        <v>1.5040000000000002</v>
+      </c>
+      <c r="AG18" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$W18,AG$4)/1000*100</f>
+        <v>0.32</v>
+      </c>
+      <c r="AH18" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$W18,AH$4)/1000*100</f>
+        <v>0.4</v>
+      </c>
+      <c r="AK18" s="68">
         <f>MATCH($B18,poultry!$A$3:$A$41,0)</f>
         <v>24</v>
       </c>
-      <c r="AC18" s="59">
-        <f>INDEX(poultry!$D$3:$U$41,$AB18,AC$4)</f>
+      <c r="AL18" s="59">
+        <f>INDEX(poultry!$D$3:$U$41,$AK18,AL$4)</f>
         <v>87</v>
       </c>
     </row>
-    <row r="19" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>41</v>
       </c>
       <c r="C19" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>87</v>
       </c>
       <c r="D19" s="64">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>18.478217600000001</v>
       </c>
-      <c r="E19" s="4"/>
-      <c r="F19" s="68">
+      <c r="E19" s="38">
+        <f t="shared" si="18"/>
+        <v>3.7200000000000006</v>
+      </c>
+      <c r="F19" s="91">
+        <f t="shared" si="19"/>
+        <v>0.44499999999999995</v>
+      </c>
+      <c r="G19" s="92">
+        <f t="shared" si="20"/>
+        <v>1.155</v>
+      </c>
+      <c r="H19" s="4"/>
+      <c r="I19" s="68">
         <f>MATCH($B19,ruminants!$A$3:$A$120,0)</f>
         <v>115</v>
       </c>
-      <c r="G19" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F19,G$4)</f>
+      <c r="J19" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I19,J$4)</f>
         <v>87</v>
       </c>
-      <c r="H19" s="77">
-        <f t="shared" si="6"/>
+      <c r="K19" s="77">
+        <f t="shared" si="11"/>
         <v>18.478217600000001</v>
       </c>
-      <c r="I19" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F19,I$4)</f>
+      <c r="L19" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I19,L$4)</f>
         <v>13.8</v>
       </c>
-      <c r="J19" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F19,J$4)</f>
+      <c r="M19" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I19,M$4)</f>
         <v>226</v>
       </c>
-      <c r="K19" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F19,K$4)</f>
+      <c r="N19" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I19,N$4)</f>
         <v>17</v>
       </c>
-      <c r="L19" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F19,L$4)</f>
+      <c r="O19" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I19,O$4)</f>
         <v>78</v>
       </c>
-      <c r="M19" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F19,M$4)</f>
+      <c r="P19" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I19,P$4)</f>
         <v>646</v>
       </c>
-      <c r="N19" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F19,N$4)</f>
+      <c r="Q19" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I19,Q$4)</f>
         <v>33</v>
       </c>
-      <c r="Q19" s="68">
+      <c r="R19" s="38">
+        <f t="shared" si="8"/>
+        <v>3.6160000000000005</v>
+      </c>
+      <c r="S19" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I19,S$4)/1000*100</f>
+        <v>0.43</v>
+      </c>
+      <c r="T19" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I19,T$4)/1000*100</f>
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="W19" s="68">
         <f>MATCH($B19,pigs!$A$3:$A$60,0)</f>
         <v>56</v>
       </c>
-      <c r="R19" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q19,R$4)</f>
+      <c r="X19" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W19,X$4)</f>
         <v>87</v>
       </c>
-      <c r="S19" s="77">
-        <f t="shared" si="9"/>
+      <c r="Y19" s="77">
+        <f t="shared" si="21"/>
         <v>18.420059999999999</v>
       </c>
-      <c r="T19" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q19,T$4)</f>
+      <c r="Z19" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W19,Z$4)</f>
         <v>11.2</v>
       </c>
-      <c r="U19" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q19,U$4)</f>
+      <c r="AA19" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W19,AA$4)</f>
         <v>11.5</v>
       </c>
-      <c r="V19" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q19,V$4)</f>
+      <c r="AB19" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W19,AB$4)</f>
         <v>239</v>
       </c>
-      <c r="W19" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q19,W$4)</f>
+      <c r="AC19" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W19,AC$4)</f>
         <v>12</v>
       </c>
-      <c r="X19" s="41">
-        <f t="shared" si="10"/>
+      <c r="AD19" s="41">
+        <f t="shared" si="22"/>
         <v>714</v>
       </c>
-      <c r="Y19" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q19,Y$4)</f>
+      <c r="AE19" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$W19,AE$4)</f>
         <v>35</v>
       </c>
-      <c r="AB19" s="68">
+      <c r="AF19" s="38">
+        <f t="shared" si="14"/>
+        <v>3.8240000000000003</v>
+      </c>
+      <c r="AG19" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$W19,AG$4)/1000*100</f>
+        <v>0.45999999999999996</v>
+      </c>
+      <c r="AH19" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$W19,AH$4)/1000*100</f>
+        <v>1.2</v>
+      </c>
+      <c r="AK19" s="68">
         <f>MATCH($B19,poultry!$A$3:$A$41,0)</f>
         <v>39</v>
       </c>
-      <c r="AC19" s="59">
-        <f>INDEX(poultry!$D$3:$U$41,$AB19,AC$4)</f>
+      <c r="AL19" s="59">
+        <f>INDEX(poultry!$D$3:$U$41,$AK19,AL$4)</f>
         <v>87</v>
       </c>
     </row>
-    <row r="20" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>42</v>
       </c>
       <c r="C20" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>86.8</v>
       </c>
       <c r="D20" s="64">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>18.737207199999997</v>
       </c>
-      <c r="E20" s="4"/>
-      <c r="F20" s="68"/>
-      <c r="G20" s="65">
+      <c r="E20" s="38">
+        <f t="shared" si="18"/>
+        <v>4.8079999999999998</v>
+      </c>
+      <c r="F20" s="91">
+        <f t="shared" si="19"/>
+        <v>0.61499999999999999</v>
+      </c>
+      <c r="G20" s="92">
+        <f t="shared" si="20"/>
+        <v>1.375</v>
+      </c>
+      <c r="H20" s="4"/>
+      <c r="I20" s="68"/>
+      <c r="J20" s="65">
         <v>86.6</v>
       </c>
-      <c r="H20" s="77">
-        <f t="shared" si="6"/>
+      <c r="K20" s="77">
+        <f t="shared" si="11"/>
         <v>18.737207199999997</v>
       </c>
-      <c r="I20" s="38">
+      <c r="L20" s="38">
         <v>13.3</v>
       </c>
-      <c r="J20" s="39">
+      <c r="M20" s="65">
         <v>290</v>
       </c>
-      <c r="K20" s="39">
+      <c r="N20" s="39">
         <v>14</v>
       </c>
-      <c r="L20" s="39">
+      <c r="O20" s="39">
         <v>91</v>
       </c>
-      <c r="M20" s="41">
-        <f>1000-SUM(J20:L20,N20)</f>
+      <c r="P20" s="41">
+        <f>1000-SUM(M20:O20,Q20)</f>
         <v>566</v>
       </c>
-      <c r="N20" s="42">
+      <c r="Q20" s="42">
         <v>39</v>
       </c>
-      <c r="O20" s="11" t="s">
+      <c r="R20" s="38">
+        <f t="shared" si="8"/>
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="S20" s="91">
+        <f>5.5/1000*100</f>
+        <v>0.54999999999999993</v>
+      </c>
+      <c r="T20" s="92">
+        <f>11.5/1000*100</f>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="U20" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="P20" s="11" t="s">
-        <v>490</v>
-      </c>
-      <c r="Q20" s="68">
+      <c r="V20" s="11" t="s">
+        <v>489</v>
+      </c>
+      <c r="W20" s="68">
         <f>MATCH($B20,pigs!$A$3:$A$60,0)</f>
         <v>57</v>
       </c>
-      <c r="R20" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q20,R$4)</f>
+      <c r="X20" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W20,X$4)</f>
         <v>87</v>
       </c>
-      <c r="S20" s="77">
-        <f t="shared" si="9"/>
+      <c r="Y20" s="77">
+        <f t="shared" si="21"/>
         <v>18.821305599999999</v>
       </c>
-      <c r="T20" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q20,T$4)</f>
+      <c r="Z20" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W20,Z$4)</f>
         <v>10.7</v>
       </c>
-      <c r="U20" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q20,U$4)</f>
+      <c r="AA20" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W20,AA$4)</f>
         <v>10.9</v>
       </c>
-      <c r="V20" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q20,V$4)</f>
+      <c r="AB20" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W20,AB$4)</f>
         <v>311</v>
       </c>
-      <c r="W20" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q20,W$4)</f>
+      <c r="AC20" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W20,AC$4)</f>
         <v>13</v>
       </c>
-      <c r="X20" s="41">
-        <f t="shared" si="10"/>
+      <c r="AD20" s="41">
+        <f t="shared" si="22"/>
         <v>635</v>
       </c>
-      <c r="Y20" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q20,Y$4)</f>
+      <c r="AE20" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$W20,AE$4)</f>
         <v>41</v>
       </c>
-      <c r="AB20" s="68"/>
-      <c r="AC20" s="59"/>
-    </row>
-    <row r="21" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AF20" s="38">
+        <f t="shared" si="14"/>
+        <v>4.976</v>
+      </c>
+      <c r="AG20" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$W20,AG$4)/1000*100</f>
+        <v>0.67999999999999994</v>
+      </c>
+      <c r="AH20" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$W20,AH$4)/1000*100</f>
+        <v>1.6</v>
+      </c>
+      <c r="AK20" s="68"/>
+      <c r="AL20" s="59"/>
+    </row>
+    <row r="21" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>35</v>
       </c>
       <c r="C21" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>92.5</v>
       </c>
       <c r="D21" s="64">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>27.903096000000001</v>
       </c>
-      <c r="E21" s="4"/>
-      <c r="F21" s="68">
+      <c r="E21" s="38">
+        <f t="shared" si="18"/>
+        <v>3.3360000000000003</v>
+      </c>
+      <c r="F21" s="91">
+        <f t="shared" si="19"/>
+        <v>0.81</v>
+      </c>
+      <c r="G21" s="92">
+        <f t="shared" si="20"/>
+        <v>0.90999999999999992</v>
+      </c>
+      <c r="H21" s="4"/>
+      <c r="I21" s="68">
         <f>MATCH($B21,ruminants!$A$3:$A$120,0)</f>
         <v>71</v>
       </c>
-      <c r="G21" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F21,G$4)</f>
+      <c r="J21" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I21,J$4)</f>
         <v>93</v>
       </c>
-      <c r="H21" s="77">
-        <f t="shared" si="6"/>
+      <c r="K21" s="77">
+        <f t="shared" si="11"/>
         <v>27.903096000000001</v>
       </c>
-      <c r="I21" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F21,I$4)</f>
+      <c r="L21" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I21,L$4)</f>
         <v>22.1</v>
       </c>
-      <c r="J21" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F21,J$4)</f>
+      <c r="M21" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I21,M$4)</f>
         <v>210</v>
       </c>
-      <c r="K21" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F21,K$4)</f>
+      <c r="N21" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I21,N$4)</f>
         <v>460</v>
       </c>
-      <c r="L21" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F21,L$4)</f>
+      <c r="O21" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I21,O$4)</f>
         <v>80</v>
       </c>
-      <c r="M21" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F21,M$4)</f>
+      <c r="P21" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I21,P$4)</f>
         <v>200</v>
       </c>
-      <c r="N21" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F21,N$4)</f>
+      <c r="Q21" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I21,Q$4)</f>
         <v>50</v>
       </c>
-      <c r="Q21" s="68">
+      <c r="R21" s="38">
+        <f t="shared" si="8"/>
+        <v>3.3600000000000003</v>
+      </c>
+      <c r="S21" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I21,S$4)/1000*100</f>
+        <v>0.86</v>
+      </c>
+      <c r="T21" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I21,T$4)/1000*100</f>
+        <v>0.81999999999999984</v>
+      </c>
+      <c r="W21" s="68">
         <f>MATCH($B21,pigs!$A$3:$A$60,0)</f>
         <v>33</v>
       </c>
-      <c r="R21" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q21,R$4)</f>
+      <c r="X21" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W21,X$4)</f>
         <v>92</v>
       </c>
-      <c r="S21" s="77">
-        <f t="shared" si="9"/>
+      <c r="Y21" s="77">
+        <f t="shared" si="21"/>
         <v>27.892217599999999</v>
       </c>
-      <c r="T21" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q21,T$4)</f>
+      <c r="Z21" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W21,Z$4)</f>
         <v>18</v>
       </c>
-      <c r="U21" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q21,U$4)</f>
+      <c r="AA21" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W21,AA$4)</f>
         <v>18.5</v>
       </c>
-      <c r="V21" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q21,V$4)</f>
+      <c r="AB21" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W21,AB$4)</f>
         <v>207</v>
       </c>
-      <c r="W21" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q21,W$4)</f>
+      <c r="AC21" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W21,AC$4)</f>
         <v>455</v>
       </c>
-      <c r="X21" s="41">
-        <f t="shared" si="10"/>
+      <c r="AD21" s="41">
+        <f t="shared" si="22"/>
         <v>295</v>
       </c>
-      <c r="Y21" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q21,Y$4)</f>
+      <c r="AE21" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$W21,AE$4)</f>
         <v>43</v>
       </c>
-      <c r="AB21" s="68"/>
-      <c r="AC21" s="59"/>
-    </row>
-    <row r="22" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AF21" s="38">
+        <f t="shared" si="14"/>
+        <v>3.3119999999999998</v>
+      </c>
+      <c r="AG21" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$W21,AG$4)/1000*100</f>
+        <v>0.76</v>
+      </c>
+      <c r="AH21" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$W21,AH$4)/1000*100</f>
+        <v>1</v>
+      </c>
+      <c r="AK21" s="68"/>
+      <c r="AL21" s="59"/>
+    </row>
+    <row r="22" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>43</v>
       </c>
       <c r="C22" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>92</v>
       </c>
       <c r="D22" s="64">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>26.501456000000001</v>
       </c>
-      <c r="E22" s="4"/>
-      <c r="F22" s="68">
+      <c r="E22" s="38">
+        <f t="shared" si="18"/>
+        <v>3.7359999999999998</v>
+      </c>
+      <c r="F22" s="91">
+        <f t="shared" si="19"/>
+        <v>0.57000000000000006</v>
+      </c>
+      <c r="G22" s="92">
+        <f t="shared" si="20"/>
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="H22" s="4"/>
+      <c r="I22" s="68">
         <f>MATCH($B22,ruminants!$A$3:$A$120,0)</f>
         <v>45</v>
       </c>
-      <c r="G22" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F22,G$4)</f>
+      <c r="J22" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I22,J$4)</f>
         <v>93</v>
       </c>
-      <c r="H22" s="77">
-        <f t="shared" si="6"/>
+      <c r="K22" s="77">
+        <f t="shared" si="11"/>
         <v>26.501456000000001</v>
       </c>
-      <c r="I22" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F22,I$4)</f>
+      <c r="L22" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I22,L$4)</f>
         <v>20.100000000000001</v>
       </c>
-      <c r="J22" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F22,J$4)</f>
+      <c r="M22" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I22,M$4)</f>
         <v>240</v>
       </c>
-      <c r="K22" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F22,K$4)</f>
+      <c r="N22" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I22,N$4)</f>
         <v>380</v>
       </c>
-      <c r="L22" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F22,L$4)</f>
+      <c r="O22" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I22,O$4)</f>
         <v>70</v>
       </c>
-      <c r="M22" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F22,M$4)</f>
+      <c r="P22" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I22,P$4)</f>
         <v>270</v>
       </c>
-      <c r="N22" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F22,N$4)</f>
+      <c r="Q22" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I22,Q$4)</f>
         <v>40</v>
       </c>
-      <c r="Q22" s="68">
+      <c r="R22" s="38">
+        <f t="shared" si="8"/>
+        <v>3.84</v>
+      </c>
+      <c r="S22" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I22,S$4)/1000*100</f>
+        <v>0.57000000000000006</v>
+      </c>
+      <c r="T22" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I22,T$4)/1000*100</f>
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="W22" s="68">
         <f>MATCH($B22,pigs!$A$3:$A$60,0)</f>
         <v>14</v>
       </c>
-      <c r="R22" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q22,R$4)</f>
+      <c r="X22" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W22,X$4)</f>
         <v>91</v>
       </c>
-      <c r="S22" s="77">
-        <f t="shared" si="9"/>
+      <c r="Y22" s="77">
+        <f t="shared" si="21"/>
         <v>27.712724000000005</v>
       </c>
-      <c r="T22" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q22,T$4)</f>
+      <c r="Z22" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W22,Z$4)</f>
         <v>17.3</v>
       </c>
-      <c r="U22" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q22,U$4)</f>
+      <c r="AA22" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W22,AA$4)</f>
         <v>17.5</v>
       </c>
-      <c r="V22" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q22,V$4)</f>
+      <c r="AB22" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W22,AB$4)</f>
         <v>227</v>
       </c>
-      <c r="W22" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q22,W$4)</f>
+      <c r="AC22" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W22,AC$4)</f>
         <v>437</v>
       </c>
-      <c r="X22" s="41">
-        <f t="shared" si="10"/>
+      <c r="AD22" s="41">
+        <f t="shared" si="22"/>
         <v>298</v>
       </c>
-      <c r="Y22" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q22,Y$4)</f>
+      <c r="AE22" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$W22,AE$4)</f>
         <v>38</v>
       </c>
-      <c r="AB22" s="68"/>
-      <c r="AC22" s="59"/>
-    </row>
-    <row r="23" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AF22" s="38">
+        <f t="shared" si="14"/>
+        <v>3.6319999999999997</v>
+      </c>
+      <c r="AG22" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$W22,AG$4)/1000*100</f>
+        <v>0.57000000000000006</v>
+      </c>
+      <c r="AH22" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$W22,AH$4)/1000*100</f>
+        <v>0.89</v>
+      </c>
+      <c r="AK22" s="68"/>
+      <c r="AL22" s="59"/>
+    </row>
+    <row r="23" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>310</v>
       </c>
       <c r="C23" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>100</v>
       </c>
       <c r="D23" s="64">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>39.329599999999999</v>
       </c>
-      <c r="E23" s="4"/>
-      <c r="F23" s="68"/>
-      <c r="G23" s="37">
+      <c r="E23" s="38">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="F23" s="91">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="G23" s="92">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="H23" s="4"/>
+      <c r="I23" s="68"/>
+      <c r="J23" s="37">
         <v>100</v>
       </c>
-      <c r="H23" s="77">
-        <f t="shared" si="6"/>
+      <c r="K23" s="77">
+        <f t="shared" si="11"/>
         <v>39.329599999999999</v>
       </c>
-      <c r="I23" s="38">
+      <c r="L23" s="38">
         <v>36.6</v>
       </c>
-      <c r="J23" s="39"/>
-      <c r="K23" s="39">
+      <c r="M23" s="65">
+        <v>0</v>
+      </c>
+      <c r="N23" s="39">
         <v>1000</v>
       </c>
-      <c r="L23" s="39"/>
-      <c r="M23" s="39"/>
-      <c r="N23" s="42"/>
-      <c r="O23" t="s">
+      <c r="O23" s="39">
+        <v>0</v>
+      </c>
+      <c r="P23" s="39">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="42">
+        <v>0</v>
+      </c>
+      <c r="R23" s="38">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="91">
+        <v>0</v>
+      </c>
+      <c r="T23" s="92">
+        <v>0</v>
+      </c>
+      <c r="U23" s="11" t="s">
         <v>319</v>
       </c>
-      <c r="P23" t="s">
-        <v>490</v>
-      </c>
-      <c r="Q23" s="68">
+      <c r="V23" t="s">
+        <v>489</v>
+      </c>
+      <c r="W23" s="68">
         <f>MATCH($B23,pigs!$A$3:$A$60,0)</f>
         <v>28</v>
       </c>
-      <c r="R23" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q23,R$4)</f>
+      <c r="X23" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W23,X$4)</f>
         <v>100</v>
       </c>
-      <c r="S23" s="77">
-        <f t="shared" si="9"/>
+      <c r="Y23" s="77">
+        <f t="shared" si="21"/>
         <v>39.329599999999999</v>
       </c>
-      <c r="T23" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q23,T$4)</f>
+      <c r="Z23" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W23,Z$4)</f>
         <v>29.8</v>
       </c>
-      <c r="U23" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q23,U$4)</f>
+      <c r="AA23" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W23,AA$4)</f>
         <v>29.8</v>
       </c>
-      <c r="V23" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q23,V$4)</f>
-        <v>0</v>
-      </c>
-      <c r="W23" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q23,W$4)</f>
+      <c r="AB23" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W23,AB$4)</f>
+        <v>0</v>
+      </c>
+      <c r="AC23" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W23,AC$4)</f>
         <v>1000</v>
       </c>
-      <c r="X23" s="41">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Y23" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q23,Y$4)</f>
-        <v>0</v>
-      </c>
-      <c r="AB23" s="68">
+      <c r="AD23" s="41">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AE23" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$W23,AE$4)</f>
+        <v>0</v>
+      </c>
+      <c r="AF23" s="38">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AG23" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$W23,AG$4)/1000*100</f>
+        <v>0</v>
+      </c>
+      <c r="AH23" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$W23,AH$4)/1000*100</f>
+        <v>0</v>
+      </c>
+      <c r="AK23" s="68">
         <f>MATCH($B23,poultry!$A$3:$A$41,0)</f>
         <v>1</v>
       </c>
-      <c r="AC23" s="59">
-        <f>INDEX(poultry!$D$3:$U$41,$AB23,AC$4)</f>
+      <c r="AL23" s="59">
+        <f>INDEX(poultry!$D$3:$U$41,$AK23,AL$4)</f>
         <v>99</v>
       </c>
     </row>
-    <row r="24" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>302</v>
       </c>
       <c r="C24" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>85</v>
       </c>
       <c r="D24" s="64">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>16.927627199999996</v>
       </c>
-      <c r="E24" s="4"/>
-      <c r="F24" s="68">
+      <c r="E24" s="38">
+        <f t="shared" si="18"/>
+        <v>1.1040000000000001</v>
+      </c>
+      <c r="F24" s="91">
+        <f t="shared" si="19"/>
+        <v>0.26</v>
+      </c>
+      <c r="G24" s="92">
+        <f t="shared" si="20"/>
+        <v>1.6800000000000002</v>
+      </c>
+      <c r="H24" s="4"/>
+      <c r="I24" s="68">
         <f>MATCH($B24,ruminants!$A$3:$A$120,0)</f>
         <v>22</v>
       </c>
-      <c r="G24" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F24,G$4)</f>
+      <c r="J24" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I24,J$4)</f>
         <v>85</v>
       </c>
-      <c r="H24" s="77">
-        <f t="shared" si="6"/>
+      <c r="K24" s="77">
+        <f t="shared" si="11"/>
         <v>16.927627199999996</v>
       </c>
-      <c r="I24" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F24,I$4)</f>
+      <c r="L24" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I24,L$4)</f>
         <v>6.6</v>
       </c>
-      <c r="J24" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F24,J$4)</f>
+      <c r="M24" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I24,M$4)</f>
         <v>69</v>
       </c>
-      <c r="K24" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F24,K$4)</f>
+      <c r="N24" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I24,N$4)</f>
         <v>20</v>
       </c>
-      <c r="L24" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F24,L$4)</f>
+      <c r="O24" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I24,O$4)</f>
         <v>436</v>
       </c>
-      <c r="M24" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F24,M$4)</f>
+      <c r="P24" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I24,P$4)</f>
         <v>409</v>
       </c>
-      <c r="N24" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F24,N$4)</f>
+      <c r="Q24" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I24,Q$4)</f>
         <v>66</v>
       </c>
-      <c r="Q24" s="68"/>
-      <c r="R24" s="37"/>
-      <c r="S24" s="54"/>
-      <c r="T24" s="54"/>
-      <c r="U24" s="54"/>
-      <c r="V24" s="54"/>
-      <c r="W24" s="54"/>
-      <c r="X24" s="54"/>
-      <c r="Y24" s="55"/>
-      <c r="AB24" s="68"/>
-      <c r="AC24" s="59"/>
-    </row>
-    <row r="25" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="R24" s="38">
+        <f t="shared" si="8"/>
+        <v>1.1040000000000001</v>
+      </c>
+      <c r="S24" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I24,S$4)/1000*100</f>
+        <v>0.26</v>
+      </c>
+      <c r="T24" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I24,T$4)/1000*100</f>
+        <v>1.6800000000000002</v>
+      </c>
+      <c r="W24" s="68"/>
+      <c r="X24" s="37"/>
+      <c r="Y24" s="54"/>
+      <c r="Z24" s="54"/>
+      <c r="AA24" s="54"/>
+      <c r="AB24" s="37"/>
+      <c r="AC24" s="54"/>
+      <c r="AD24" s="54"/>
+      <c r="AE24" s="55"/>
+      <c r="AF24" s="38"/>
+      <c r="AG24" s="91"/>
+      <c r="AH24" s="92"/>
+      <c r="AK24" s="68"/>
+      <c r="AL24" s="59"/>
+    </row>
+    <row r="25" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>314</v>
       </c>
       <c r="C25" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>87</v>
       </c>
       <c r="D25" s="64">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>22.965976000000001</v>
       </c>
-      <c r="E25" s="4"/>
-      <c r="F25" s="68">
+      <c r="E25" s="38">
+        <f t="shared" si="18"/>
+        <v>6.4</v>
+      </c>
+      <c r="F25" s="91">
+        <f t="shared" si="19"/>
+        <v>0.63</v>
+      </c>
+      <c r="G25" s="92">
+        <f t="shared" si="20"/>
+        <v>1.9</v>
+      </c>
+      <c r="H25" s="4"/>
+      <c r="I25" s="68">
         <f>MATCH($B25,ruminants!$A$3:$A$120,0)</f>
         <v>92</v>
       </c>
-      <c r="G25" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F25,G$4)</f>
+      <c r="J25" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I25,J$4)</f>
         <v>87</v>
       </c>
-      <c r="H25" s="77">
-        <f t="shared" si="6"/>
+      <c r="K25" s="77">
+        <f t="shared" si="11"/>
         <v>22.965976000000001</v>
       </c>
-      <c r="I25" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F25,I$4)</f>
+      <c r="L25" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I25,L$4)</f>
         <v>16.399999999999999</v>
       </c>
-      <c r="J25" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F25,J$4)</f>
+      <c r="M25" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I25,M$4)</f>
         <v>400</v>
       </c>
-      <c r="K25" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F25,K$4)</f>
+      <c r="N25" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I25,N$4)</f>
         <v>180</v>
       </c>
-      <c r="L25" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F25,L$4)</f>
+      <c r="O25" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I25,O$4)</f>
         <v>60</v>
       </c>
-      <c r="M25" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F25,M$4)</f>
+      <c r="P25" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I25,P$4)</f>
         <v>310</v>
       </c>
-      <c r="N25" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F25,N$4)</f>
+      <c r="Q25" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I25,Q$4)</f>
         <v>50</v>
       </c>
-      <c r="Q25" s="68"/>
-      <c r="R25" s="37"/>
-      <c r="S25" s="54"/>
-      <c r="T25" s="54"/>
-      <c r="U25" s="54"/>
-      <c r="V25" s="54"/>
-      <c r="W25" s="54"/>
-      <c r="X25" s="54"/>
-      <c r="Y25" s="55"/>
-      <c r="AB25" s="68"/>
-      <c r="AC25" s="59"/>
-    </row>
-    <row r="26" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="R25" s="38">
+        <f t="shared" si="8"/>
+        <v>6.4</v>
+      </c>
+      <c r="S25" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I25,S$4)/1000*100</f>
+        <v>0.63</v>
+      </c>
+      <c r="T25" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I25,T$4)/1000*100</f>
+        <v>1.9</v>
+      </c>
+      <c r="W25" s="68"/>
+      <c r="X25" s="37"/>
+      <c r="Y25" s="54"/>
+      <c r="Z25" s="54"/>
+      <c r="AA25" s="54"/>
+      <c r="AB25" s="37"/>
+      <c r="AC25" s="54"/>
+      <c r="AD25" s="54"/>
+      <c r="AE25" s="55"/>
+      <c r="AF25" s="38"/>
+      <c r="AG25" s="91"/>
+      <c r="AH25" s="92"/>
+      <c r="AK25" s="68"/>
+      <c r="AL25" s="59"/>
+    </row>
+    <row r="26" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>44</v>
       </c>
       <c r="C26" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>87.5</v>
       </c>
       <c r="D26" s="64">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>19.589487999999999</v>
       </c>
-      <c r="E26" s="4"/>
-      <c r="F26" s="68">
+      <c r="E26" s="38">
+        <f t="shared" si="18"/>
+        <v>8.2080000000000002</v>
+      </c>
+      <c r="F26" s="91">
+        <f t="shared" si="19"/>
+        <v>0.71499999999999997</v>
+      </c>
+      <c r="G26" s="92">
+        <f t="shared" si="20"/>
+        <v>2.3499999999999996</v>
+      </c>
+      <c r="H26" s="4"/>
+      <c r="I26" s="68">
         <f>MATCH($B26,ruminants!$A$3:$A$120,0)</f>
         <v>93</v>
       </c>
-      <c r="G26" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F26,G$4)</f>
+      <c r="J26" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I26,J$4)</f>
         <v>87</v>
       </c>
-      <c r="H26" s="77">
-        <f t="shared" si="6"/>
+      <c r="K26" s="77">
+        <f t="shared" si="11"/>
         <v>19.589487999999999</v>
       </c>
-      <c r="I26" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F26,I$4)</f>
+      <c r="L26" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I26,L$4)</f>
         <v>14.6</v>
       </c>
-      <c r="J26" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F26,J$4)</f>
+      <c r="M26" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I26,M$4)</f>
         <v>510</v>
       </c>
-      <c r="K26" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F26,K$4)</f>
+      <c r="N26" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I26,N$4)</f>
         <v>10</v>
       </c>
-      <c r="L26" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F26,L$4)</f>
+      <c r="O26" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I26,O$4)</f>
         <v>60</v>
       </c>
-      <c r="M26" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F26,M$4)</f>
+      <c r="P26" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I26,P$4)</f>
         <v>350</v>
       </c>
-      <c r="N26" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F26,N$4)</f>
+      <c r="Q26" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I26,Q$4)</f>
         <v>70</v>
       </c>
-      <c r="Q26" s="68">
+      <c r="R26" s="38">
+        <f t="shared" si="8"/>
+        <v>8.16</v>
+      </c>
+      <c r="S26" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I26,S$4)/1000*100</f>
+        <v>0.72</v>
+      </c>
+      <c r="T26" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I26,T$4)/1000*100</f>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="W26" s="68">
         <f>MATCH($B26,pigs!$A$3:$A$60,0)</f>
         <v>43</v>
       </c>
-      <c r="R26" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q26,R$4)</f>
+      <c r="X26" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W26,X$4)</f>
         <v>88</v>
       </c>
-      <c r="S26" s="77">
-        <f t="shared" ref="S26:S30" si="11">( 5.7*V26+9.4*W26+4.1*(X26) ) * 0.004184</f>
+      <c r="Y26" s="77">
+        <f t="shared" ref="Y26:Y30" si="23">( 5.7*AB26+9.4*AC26+4.1*(AD26) ) * 0.004184</f>
         <v>19.822118400000001</v>
       </c>
-      <c r="T26" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q26,T$4)</f>
+      <c r="Z26" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W26,Z$4)</f>
         <v>9.3000000000000007</v>
       </c>
-      <c r="U26" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q26,U$4)</f>
+      <c r="AA26" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W26,AA$4)</f>
         <v>9.9</v>
       </c>
-      <c r="V26" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q26,V$4)</f>
+      <c r="AB26" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W26,AB$4)</f>
         <v>516</v>
       </c>
-      <c r="W26" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q26,W$4)</f>
+      <c r="AC26" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W26,AC$4)</f>
         <v>21</v>
       </c>
-      <c r="X26" s="41">
-        <f t="shared" ref="X26:X30" si="12">1000-SUM(V26:W26,Y26)</f>
+      <c r="AD26" s="41">
+        <f t="shared" ref="AD26:AD30" si="24">1000-SUM(AB26:AC26,AE26)</f>
         <v>390</v>
       </c>
-      <c r="Y26" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q26,Y$4)</f>
+      <c r="AE26" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$W26,AE$4)</f>
         <v>73</v>
       </c>
-      <c r="AB26" s="68">
+      <c r="AF26" s="38">
+        <f t="shared" si="14"/>
+        <v>8.2560000000000002</v>
+      </c>
+      <c r="AG26" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$W26,AG$4)/1000*100</f>
+        <v>0.71</v>
+      </c>
+      <c r="AH26" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$W26,AH$4)/1000*100</f>
+        <v>2.4</v>
+      </c>
+      <c r="AK26" s="68">
         <f>MATCH($B26,poultry!$A$3:$A$41,0)</f>
         <v>33</v>
       </c>
-      <c r="AC26" s="59">
-        <f>INDEX(poultry!$D$3:$U$41,$AB26,AC$4)</f>
+      <c r="AL26" s="59">
+        <f>INDEX(poultry!$D$3:$U$41,$AK26,AL$4)</f>
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>45</v>
       </c>
       <c r="C27" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>87</v>
       </c>
       <c r="D27" s="64">
-        <f>S27</f>
+        <f>Y27</f>
         <v>20.560594400000003</v>
       </c>
-      <c r="E27" s="4"/>
-      <c r="F27" s="68"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="54"/>
-      <c r="I27" s="38"/>
-      <c r="J27" s="39"/>
-      <c r="K27" s="39"/>
-      <c r="L27" s="39"/>
-      <c r="M27" s="39"/>
-      <c r="N27" s="42"/>
-      <c r="Q27" s="68">
+      <c r="E27" s="38">
+        <f t="shared" si="18"/>
+        <v>9.7439999999999998</v>
+      </c>
+      <c r="F27" s="91">
+        <f t="shared" si="19"/>
+        <v>0.86999999999999988</v>
+      </c>
+      <c r="G27" s="92">
+        <f t="shared" si="20"/>
+        <v>2.5</v>
+      </c>
+      <c r="H27" s="4"/>
+      <c r="I27" s="68"/>
+      <c r="J27" s="37"/>
+      <c r="K27" s="54"/>
+      <c r="L27" s="38"/>
+      <c r="M27" s="65"/>
+      <c r="N27" s="39"/>
+      <c r="O27" s="39"/>
+      <c r="P27" s="39"/>
+      <c r="Q27" s="42"/>
+      <c r="R27" s="38"/>
+      <c r="S27" s="39"/>
+      <c r="T27" s="42"/>
+      <c r="W27" s="68">
         <f>MATCH($B27,pigs!$A$3:$A$60,0)</f>
         <v>45</v>
       </c>
-      <c r="R27" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q27,R$4)</f>
+      <c r="X27" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W27,X$4)</f>
         <v>87</v>
       </c>
-      <c r="S27" s="77">
-        <f t="shared" si="11"/>
+      <c r="Y27" s="77">
+        <f t="shared" si="23"/>
         <v>20.560594400000003</v>
       </c>
-      <c r="T27" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q27,T$4)</f>
+      <c r="Z27" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W27,Z$4)</f>
         <v>9.6999999999999993</v>
       </c>
-      <c r="U27" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q27,U$4)</f>
+      <c r="AA27" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W27,AA$4)</f>
         <v>10.3</v>
       </c>
-      <c r="V27" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q27,V$4)</f>
+      <c r="AB27" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W27,AB$4)</f>
         <v>609</v>
       </c>
-      <c r="W27" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q27,W$4)</f>
+      <c r="AC27" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W27,AC$4)</f>
         <v>27</v>
       </c>
-      <c r="X27" s="41">
-        <f t="shared" si="12"/>
+      <c r="AD27" s="41">
+        <f t="shared" si="24"/>
         <v>290</v>
       </c>
-      <c r="Y27" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q27,Y$4)</f>
+      <c r="AE27" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$W27,AE$4)</f>
         <v>74</v>
       </c>
-      <c r="AB27" s="68"/>
-      <c r="AC27" s="59"/>
-    </row>
-    <row r="28" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AF27" s="38">
+        <f t="shared" si="14"/>
+        <v>9.7439999999999998</v>
+      </c>
+      <c r="AG27" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$W27,AG$4)/1000*100</f>
+        <v>0.86999999999999988</v>
+      </c>
+      <c r="AH27" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$W27,AH$4)/1000*100</f>
+        <v>2.5</v>
+      </c>
+      <c r="AK27" s="68"/>
+      <c r="AL27" s="59"/>
+    </row>
+    <row r="28" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>36</v>
       </c>
       <c r="C28" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>89.5</v>
       </c>
       <c r="D28" s="64">
-        <f t="shared" ref="D28:D34" si="13">H28</f>
+        <f t="shared" ref="D28:D34" si="25">K28</f>
         <v>19.4920008</v>
       </c>
-      <c r="E28" s="4"/>
-      <c r="F28" s="68">
+      <c r="E28" s="38">
+        <f t="shared" si="18"/>
+        <v>6.152000000000001</v>
+      </c>
+      <c r="F28" s="91">
+        <f t="shared" si="19"/>
+        <v>1.2450000000000001</v>
+      </c>
+      <c r="G28" s="92">
+        <f t="shared" si="20"/>
+        <v>1.55</v>
+      </c>
+      <c r="H28" s="4"/>
+      <c r="I28" s="68">
         <f>MATCH($B28,ruminants!$A$3:$A$120,0)</f>
         <v>70</v>
       </c>
-      <c r="G28" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F28,G$4)</f>
+      <c r="J28" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I28,J$4)</f>
         <v>90</v>
       </c>
-      <c r="H28" s="77">
-        <f t="shared" si="6"/>
+      <c r="K28" s="77">
+        <f t="shared" si="11"/>
         <v>19.4920008</v>
       </c>
-      <c r="I28" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F28,I$4)</f>
+      <c r="L28" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I28,L$4)</f>
         <v>12.2</v>
       </c>
-      <c r="J28" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F28,J$4)</f>
+      <c r="M28" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I28,M$4)</f>
         <v>389</v>
       </c>
-      <c r="K28" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F28,K$4)</f>
+      <c r="N28" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I28,N$4)</f>
         <v>46</v>
       </c>
-      <c r="L28" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F28,L$4)</f>
+      <c r="O28" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I28,O$4)</f>
         <v>140</v>
       </c>
-      <c r="M28" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F28,M$4)</f>
+      <c r="P28" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I28,P$4)</f>
         <v>350</v>
       </c>
-      <c r="N28" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F28,N$4)</f>
+      <c r="Q28" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I28,Q$4)</f>
         <v>75</v>
       </c>
-      <c r="Q28" s="68">
+      <c r="R28" s="38">
+        <f t="shared" si="8"/>
+        <v>6.2240000000000002</v>
+      </c>
+      <c r="S28" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I28,S$4)/1000*100</f>
+        <v>1.2</v>
+      </c>
+      <c r="T28" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I28,T$4)/1000*100</f>
+        <v>1.6</v>
+      </c>
+      <c r="W28" s="68">
         <f>MATCH($B28,pigs!$A$3:$A$60,0)</f>
         <v>36</v>
       </c>
-      <c r="R28" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q28,R$4)</f>
+      <c r="X28" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W28,X$4)</f>
         <v>89</v>
       </c>
-      <c r="S28" s="77">
-        <f t="shared" si="11"/>
+      <c r="Y28" s="77">
+        <f t="shared" si="23"/>
         <v>18.9196296</v>
       </c>
-      <c r="T28" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q28,T$4)</f>
+      <c r="Z28" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W28,Z$4)</f>
         <v>7.1</v>
       </c>
-      <c r="U28" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q28,U$4)</f>
+      <c r="AA28" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W28,AA$4)</f>
         <v>7.7</v>
       </c>
-      <c r="V28" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q28,V$4)</f>
+      <c r="AB28" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W28,AB$4)</f>
         <v>380</v>
       </c>
-      <c r="W28" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q28,W$4)</f>
+      <c r="AC28" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W28,AC$4)</f>
         <v>26</v>
       </c>
-      <c r="X28" s="41">
-        <f t="shared" si="12"/>
+      <c r="AD28" s="41">
+        <f t="shared" si="24"/>
         <v>515</v>
       </c>
-      <c r="Y28" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q28,Y$4)</f>
+      <c r="AE28" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$W28,AE$4)</f>
         <v>79</v>
       </c>
-      <c r="AB28" s="68">
+      <c r="AF28" s="38">
+        <f t="shared" si="14"/>
+        <v>6.080000000000001</v>
+      </c>
+      <c r="AG28" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$W28,AG$4)/1000*100</f>
+        <v>1.29</v>
+      </c>
+      <c r="AH28" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$W28,AH$4)/1000*100</f>
+        <v>1.5</v>
+      </c>
+      <c r="AK28" s="68">
         <f>MATCH($B28,poultry!$A$3:$A$41,0)</f>
         <v>29</v>
       </c>
-      <c r="AC28" s="59">
-        <f>INDEX(poultry!$D$3:$U$41,$AB28,AC$4)</f>
+      <c r="AL28" s="59">
+        <f>INDEX(poultry!$D$3:$U$41,$AK28,AL$4)</f>
         <v>90</v>
       </c>
     </row>
-    <row r="29" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>46</v>
       </c>
       <c r="C29" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>91</v>
       </c>
       <c r="D29" s="64">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>19.083224000000001</v>
       </c>
-      <c r="E29" s="4"/>
-      <c r="F29" s="68">
+      <c r="E29" s="38">
+        <f t="shared" si="18"/>
+        <v>6.6640000000000006</v>
+      </c>
+      <c r="F29" s="91">
+        <f t="shared" si="19"/>
+        <v>1.3050000000000002</v>
+      </c>
+      <c r="G29" s="92">
+        <f t="shared" si="20"/>
+        <v>1.75</v>
+      </c>
+      <c r="H29" s="4"/>
+      <c r="I29" s="68">
         <f>MATCH($B29,ruminants!$A$3:$A$120,0)</f>
         <v>99</v>
       </c>
-      <c r="G29" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F29,G$4)</f>
+      <c r="J29" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I29,J$4)</f>
         <v>92</v>
       </c>
-      <c r="H29" s="77">
-        <f t="shared" si="6"/>
+      <c r="K29" s="77">
+        <f t="shared" si="11"/>
         <v>19.083224000000001</v>
       </c>
-      <c r="I29" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F29,I$4)</f>
+      <c r="L29" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I29,L$4)</f>
         <v>11.4</v>
       </c>
-      <c r="J29" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F29,J$4)</f>
+      <c r="M29" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I29,M$4)</f>
         <v>460</v>
       </c>
-      <c r="K29" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F29,K$4)</f>
+      <c r="N29" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I29,N$4)</f>
         <v>10</v>
       </c>
-      <c r="L29" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F29,L$4)</f>
+      <c r="O29" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I29,O$4)</f>
         <v>170</v>
       </c>
-      <c r="M29" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F29,M$4)</f>
+      <c r="P29" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I29,P$4)</f>
         <v>280</v>
       </c>
-      <c r="N29" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F29,N$4)</f>
+      <c r="Q29" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I29,Q$4)</f>
         <v>80</v>
       </c>
-      <c r="Q29" s="68">
+      <c r="R29" s="38">
+        <f t="shared" si="8"/>
+        <v>7.3600000000000012</v>
+      </c>
+      <c r="S29" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I29,S$4)/1000*100</f>
+        <v>1.35</v>
+      </c>
+      <c r="T29" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I29,T$4)/1000*100</f>
+        <v>1.7999999999999998</v>
+      </c>
+      <c r="W29" s="68">
         <f>MATCH($B29,pigs!$A$3:$A$60,0)</f>
         <v>46</v>
       </c>
-      <c r="R29" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q29,R$4)</f>
+      <c r="X29" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W29,X$4)</f>
         <v>90</v>
       </c>
-      <c r="S29" s="77">
-        <f t="shared" si="11"/>
+      <c r="Y29" s="77">
+        <f t="shared" si="23"/>
         <v>18.786160000000002</v>
       </c>
-      <c r="T29" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q29,T$4)</f>
+      <c r="Z29" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W29,Z$4)</f>
         <v>5.9</v>
       </c>
-      <c r="U29" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q29,U$4)</f>
+      <c r="AA29" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W29,AA$4)</f>
         <v>6.5</v>
       </c>
-      <c r="V29" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q29,V$4)</f>
+      <c r="AB29" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W29,AB$4)</f>
         <v>373</v>
       </c>
-      <c r="W29" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q29,W$4)</f>
+      <c r="AC29" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W29,AC$4)</f>
         <v>19</v>
       </c>
-      <c r="X29" s="41">
-        <f t="shared" si="12"/>
+      <c r="AD29" s="41">
+        <f t="shared" si="24"/>
         <v>533</v>
       </c>
-      <c r="Y29" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q29,Y$4)</f>
+      <c r="AE29" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$W29,AE$4)</f>
         <v>75</v>
       </c>
-      <c r="AB29" s="68"/>
-      <c r="AC29" s="59"/>
-    </row>
-    <row r="30" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AF29" s="38">
+        <f t="shared" si="14"/>
+        <v>5.968</v>
+      </c>
+      <c r="AG29" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$W29,AG$4)/1000*100</f>
+        <v>1.26</v>
+      </c>
+      <c r="AH29" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$W29,AH$4)/1000*100</f>
+        <v>1.7000000000000002</v>
+      </c>
+      <c r="AK29" s="68"/>
+      <c r="AL29" s="59"/>
+    </row>
+    <row r="30" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>47</v>
       </c>
       <c r="C30" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>91</v>
       </c>
       <c r="D30" s="64">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>19.581538399999999</v>
       </c>
-      <c r="E30" s="4"/>
-      <c r="F30" s="68">
+      <c r="E30" s="38">
+        <f t="shared" si="18"/>
+        <v>2.5360000000000005</v>
+      </c>
+      <c r="F30" s="91">
+        <f t="shared" si="19"/>
+        <v>0.64500000000000002</v>
+      </c>
+      <c r="G30" s="92">
+        <f t="shared" si="20"/>
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="H30" s="4"/>
+      <c r="I30" s="68">
         <f>MATCH($B30,ruminants!$A$3:$A$120,0)</f>
         <v>60</v>
       </c>
-      <c r="G30" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F30,G$4)</f>
+      <c r="J30" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I30,J$4)</f>
         <v>91</v>
       </c>
-      <c r="H30" s="77">
-        <f t="shared" si="6"/>
+      <c r="K30" s="77">
+        <f t="shared" si="11"/>
         <v>19.581538399999999</v>
       </c>
-      <c r="I30" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F30,I$4)</f>
+      <c r="L30" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I30,L$4)</f>
         <v>13.4</v>
       </c>
-      <c r="J30" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F30,J$4)</f>
+      <c r="M30" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I30,M$4)</f>
         <v>154</v>
       </c>
-      <c r="K30" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F30,K$4)</f>
+      <c r="N30" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I30,N$4)</f>
         <v>97</v>
       </c>
-      <c r="L30" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F30,L$4)</f>
+      <c r="O30" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I30,O$4)</f>
         <v>228</v>
       </c>
-      <c r="M30" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F30,M$4)</f>
+      <c r="P30" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I30,P$4)</f>
         <v>477</v>
       </c>
-      <c r="N30" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F30,N$4)</f>
+      <c r="Q30" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I30,Q$4)</f>
         <v>44</v>
       </c>
-      <c r="Q30" s="68">
+      <c r="R30" s="38">
+        <f t="shared" si="8"/>
+        <v>2.4640000000000004</v>
+      </c>
+      <c r="S30" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I30,S$4)/1000*100</f>
+        <v>0.65</v>
+      </c>
+      <c r="T30" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I30,T$4)/1000*100</f>
+        <v>0.8</v>
+      </c>
+      <c r="W30" s="68">
         <f>MATCH($B30,pigs!$A$3:$A$60,0)</f>
         <v>29</v>
       </c>
-      <c r="R30" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q30,R$4)</f>
+      <c r="X30" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W30,X$4)</f>
         <v>91</v>
       </c>
-      <c r="S30" s="77">
-        <f t="shared" si="11"/>
+      <c r="Y30" s="77">
+        <f t="shared" si="23"/>
         <v>19.540953599999998</v>
       </c>
-      <c r="T30" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q30,T$4)</f>
+      <c r="Z30" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W30,Z$4)</f>
         <v>5.4</v>
       </c>
-      <c r="U30" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q30,U$4)</f>
+      <c r="AA30" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W30,AA$4)</f>
         <v>6.2</v>
       </c>
-      <c r="V30" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q30,V$4)</f>
+      <c r="AB30" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W30,AB$4)</f>
         <v>163</v>
       </c>
-      <c r="W30" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q30,W$4)</f>
+      <c r="AC30" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W30,AC$4)</f>
         <v>94</v>
       </c>
-      <c r="X30" s="41">
-        <f t="shared" si="12"/>
+      <c r="AD30" s="41">
+        <f t="shared" si="24"/>
         <v>697</v>
       </c>
-      <c r="Y30" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q30,Y$4)</f>
+      <c r="AE30" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$W30,AE$4)</f>
         <v>46</v>
       </c>
-      <c r="AB30" s="68"/>
-      <c r="AC30" s="59"/>
-    </row>
-    <row r="31" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AF30" s="38">
+        <f t="shared" si="14"/>
+        <v>2.6080000000000001</v>
+      </c>
+      <c r="AG30" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$W30,AG$4)/1000*100</f>
+        <v>0.64</v>
+      </c>
+      <c r="AH30" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$W30,AH$4)/1000*100</f>
+        <v>0.75</v>
+      </c>
+      <c r="AK30" s="68"/>
+      <c r="AL30" s="59"/>
+    </row>
+    <row r="31" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>315</v>
       </c>
       <c r="C31" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>90</v>
       </c>
       <c r="D31" s="64">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>16.971140800000001</v>
       </c>
-      <c r="E31" s="4"/>
-      <c r="F31" s="68"/>
-      <c r="G31" s="37">
+      <c r="E31" s="38">
+        <f t="shared" si="18"/>
+        <v>2.9279999999999999</v>
+      </c>
+      <c r="F31" s="91">
+        <f t="shared" si="19"/>
+        <v>0.27</v>
+      </c>
+      <c r="G31" s="92">
+        <f t="shared" si="20"/>
+        <v>2.56</v>
+      </c>
+      <c r="H31" s="4"/>
+      <c r="I31" s="68"/>
+      <c r="J31" s="37">
         <v>90</v>
       </c>
-      <c r="H31" s="77">
-        <f t="shared" si="6"/>
+      <c r="K31" s="77">
+        <f t="shared" si="11"/>
         <v>16.971140800000001</v>
       </c>
-      <c r="I31" s="38">
+      <c r="L31" s="38">
         <v>8.5</v>
       </c>
-      <c r="J31" s="39">
+      <c r="M31" s="65">
         <v>183</v>
       </c>
-      <c r="K31" s="39">
+      <c r="N31" s="39">
         <v>27</v>
       </c>
-      <c r="L31" s="39">
+      <c r="O31" s="39">
         <v>286</v>
       </c>
-      <c r="M31" s="41">
-        <f>1000-SUM(J31:L31,N31)</f>
+      <c r="P31" s="41">
+        <f>1000-SUM(M31:O31,Q31)</f>
         <v>387</v>
       </c>
-      <c r="N31" s="42">
+      <c r="Q31" s="42">
         <v>117</v>
       </c>
-      <c r="O31" s="11" t="s">
+      <c r="R31" s="38">
+        <f t="shared" si="8"/>
+        <v>2.9279999999999999</v>
+      </c>
+      <c r="S31" s="91">
+        <f>2.7/1000*100</f>
+        <v>0.27</v>
+      </c>
+      <c r="T31" s="92">
+        <f>25.6/1000*100</f>
+        <v>2.56</v>
+      </c>
+      <c r="U31" s="11" t="s">
         <v>316</v>
       </c>
-      <c r="P31" s="11" t="s">
-        <v>490</v>
-      </c>
-      <c r="Q31" s="68"/>
-      <c r="R31" s="37"/>
-      <c r="S31" s="54"/>
-      <c r="T31" s="54"/>
-      <c r="U31" s="54"/>
-      <c r="V31" s="54"/>
-      <c r="W31" s="54"/>
-      <c r="X31" s="54"/>
-      <c r="Y31" s="55"/>
-      <c r="AB31" s="68"/>
-      <c r="AC31" s="59"/>
-    </row>
-    <row r="32" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="V31" s="11" t="s">
+        <v>489</v>
+      </c>
+      <c r="W31" s="68"/>
+      <c r="X31" s="37"/>
+      <c r="Y31" s="54"/>
+      <c r="Z31" s="54"/>
+      <c r="AA31" s="54"/>
+      <c r="AB31" s="37"/>
+      <c r="AC31" s="54"/>
+      <c r="AD31" s="54"/>
+      <c r="AE31" s="55"/>
+      <c r="AF31" s="38"/>
+      <c r="AG31" s="91"/>
+      <c r="AH31" s="92"/>
+      <c r="AK31" s="68"/>
+      <c r="AL31" s="59"/>
+    </row>
+    <row r="32" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>48</v>
       </c>
       <c r="C32" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>87</v>
       </c>
       <c r="D32" s="64">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>18.194124000000002</v>
       </c>
-      <c r="E32" s="4"/>
-      <c r="F32" s="68">
+      <c r="E32" s="38">
+        <f t="shared" si="18"/>
+        <v>2.6399999999999997</v>
+      </c>
+      <c r="F32" s="91">
+        <f t="shared" si="19"/>
+        <v>1.1950000000000001</v>
+      </c>
+      <c r="G32" s="92">
+        <f t="shared" si="20"/>
+        <v>1.35</v>
+      </c>
+      <c r="H32" s="4"/>
+      <c r="I32" s="68">
         <f>MATCH($B32,ruminants!$A$3:$A$120,0)</f>
         <v>111</v>
       </c>
-      <c r="G32" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F32,G$4)</f>
+      <c r="J32" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I32,J$4)</f>
         <v>87</v>
       </c>
-      <c r="H32" s="77">
-        <f t="shared" si="6"/>
+      <c r="K32" s="77">
+        <f t="shared" si="11"/>
         <v>18.194124000000002</v>
       </c>
-      <c r="I32" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F32,I$4)</f>
+      <c r="L32" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I32,L$4)</f>
         <v>11</v>
       </c>
-      <c r="J32" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F32,J$4)</f>
+      <c r="M32" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I32,M$4)</f>
         <v>160</v>
       </c>
-      <c r="K32" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F32,K$4)</f>
+      <c r="N32" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I32,N$4)</f>
         <v>45</v>
       </c>
-      <c r="L32" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F32,L$4)</f>
+      <c r="O32" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I32,O$4)</f>
         <v>115</v>
       </c>
-      <c r="M32" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F32,M$4)</f>
+      <c r="P32" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I32,P$4)</f>
         <v>620</v>
       </c>
-      <c r="N32" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F32,N$4)</f>
+      <c r="Q32" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I32,Q$4)</f>
         <v>60</v>
       </c>
-      <c r="Q32" s="68">
+      <c r="R32" s="38">
+        <f t="shared" si="8"/>
+        <v>2.56</v>
+      </c>
+      <c r="S32" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I32,S$4)/1000*100</f>
+        <v>1.2</v>
+      </c>
+      <c r="T32" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I32,T$4)/1000*100</f>
+        <v>1.2</v>
+      </c>
+      <c r="W32" s="68">
         <f>MATCH($B32,pigs!$A$3:$A$60,0)</f>
         <v>55</v>
       </c>
-      <c r="R32" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q32,R$4)</f>
+      <c r="X32" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W32,X$4)</f>
         <v>87</v>
       </c>
-      <c r="S32" s="77">
-        <f t="shared" ref="S32:S37" si="14">( 5.7*V32+9.4*W32+4.1*(X32) ) * 0.004184</f>
+      <c r="Y32" s="77">
+        <f t="shared" ref="Y32:Y37" si="26">( 5.7*AB32+9.4*AC32+4.1*(AD32) ) * 0.004184</f>
         <v>18.184500799999999</v>
       </c>
-      <c r="T32" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q32,T$4)</f>
+      <c r="Z32" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W32,Z$4)</f>
         <v>7.2</v>
       </c>
-      <c r="U32" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q32,U$4)</f>
+      <c r="AA32" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W32,AA$4)</f>
         <v>7.8</v>
       </c>
-      <c r="V32" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q32,V$4)</f>
+      <c r="AB32" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W32,AB$4)</f>
         <v>170</v>
       </c>
-      <c r="W32" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q32,W$4)</f>
+      <c r="AC32" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W32,AC$4)</f>
         <v>40</v>
       </c>
-      <c r="X32" s="41">
-        <f t="shared" ref="X32:X36" si="15">1000-SUM(V32:W32,Y32)</f>
+      <c r="AD32" s="41">
+        <f t="shared" ref="AD32:AD36" si="27">1000-SUM(AB32:AC32,AE32)</f>
         <v>732</v>
       </c>
-      <c r="Y32" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q32,Y$4)</f>
+      <c r="AE32" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$W32,AE$4)</f>
         <v>58</v>
       </c>
-      <c r="AB32" s="68">
+      <c r="AF32" s="38">
+        <f t="shared" si="14"/>
+        <v>2.7199999999999998</v>
+      </c>
+      <c r="AG32" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$W32,AG$4)/1000*100</f>
+        <v>1.1900000000000002</v>
+      </c>
+      <c r="AH32" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$W32,AH$4)/1000*100</f>
+        <v>1.5</v>
+      </c>
+      <c r="AK32" s="68">
         <f>MATCH($B32,poultry!$A$3:$A$41,0)</f>
         <v>38</v>
       </c>
-      <c r="AC32" s="59">
-        <f>INDEX(poultry!$D$3:$U$41,$AB32,AC$4)</f>
+      <c r="AL32" s="59">
+        <f>INDEX(poultry!$D$3:$U$41,$AK32,AL$4)</f>
         <v>87</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>49</v>
       </c>
       <c r="C33" s="65">
-        <f t="shared" si="4"/>
-        <v>88.5</v>
+        <f t="shared" si="9"/>
+        <v>87.8</v>
       </c>
       <c r="D33" s="64">
-        <f t="shared" si="13"/>
-        <v>17.8828344</v>
-      </c>
-      <c r="E33" s="4"/>
-      <c r="F33" s="68"/>
-      <c r="G33" s="37">
-        <v>89</v>
-      </c>
-      <c r="H33" s="77">
-        <f t="shared" si="6"/>
-        <v>17.8828344</v>
-      </c>
-      <c r="I33" s="38">
-        <v>11.5</v>
-      </c>
-      <c r="J33" s="39">
-        <v>140</v>
-      </c>
-      <c r="K33" s="39">
-        <v>37</v>
-      </c>
-      <c r="L33" s="39">
-        <v>85</v>
-      </c>
-      <c r="M33" s="41">
-        <f>1000-SUM(J33:L33,N33)</f>
-        <v>678</v>
-      </c>
-      <c r="N33" s="83">
-        <f>N32</f>
-        <v>60</v>
-      </c>
-      <c r="O33" s="11" t="s">
-        <v>406</v>
-      </c>
-      <c r="P33" s="11" t="s">
-        <v>490</v>
-      </c>
-      <c r="Q33" s="68">
+        <f t="shared" si="25"/>
+        <v>18.472360000000002</v>
+      </c>
+      <c r="E33" s="38">
+        <f t="shared" si="18"/>
+        <v>2.6160000000000001</v>
+      </c>
+      <c r="F33" s="91">
+        <f t="shared" si="19"/>
+        <v>0.81500000000000006</v>
+      </c>
+      <c r="G33" s="92">
+        <f t="shared" si="20"/>
+        <v>0.96</v>
+      </c>
+      <c r="H33" s="4"/>
+      <c r="I33" s="68"/>
+      <c r="J33" s="65">
+        <v>87.6</v>
+      </c>
+      <c r="K33" s="77">
+        <f t="shared" si="11"/>
+        <v>18.472360000000002</v>
+      </c>
+      <c r="L33" s="38">
+        <v>13.3</v>
+      </c>
+      <c r="M33" s="65">
+        <v>151</v>
+      </c>
+      <c r="N33" s="39">
+        <v>27</v>
+      </c>
+      <c r="O33" s="39">
+        <v>11</v>
+      </c>
+      <c r="P33" s="41">
+        <f>1000-SUM(M33:O33,Q33)</f>
+        <v>794</v>
+      </c>
+      <c r="Q33" s="45">
+        <v>17</v>
+      </c>
+      <c r="R33" s="38">
+        <f t="shared" si="8"/>
+        <v>2.4159999999999999</v>
+      </c>
+      <c r="S33" s="91">
+        <f>4.4/1000*100</f>
+        <v>0.44</v>
+      </c>
+      <c r="T33" s="92">
+        <f>6.2/1000*100</f>
+        <v>0.62</v>
+      </c>
+      <c r="U33" s="11" t="s">
+        <v>509</v>
+      </c>
+      <c r="V33" s="11" t="s">
+        <v>489</v>
+      </c>
+      <c r="W33" s="68">
         <f>MATCH($B33,pigs!$A$3:$A$60,0)</f>
         <v>54</v>
       </c>
-      <c r="R33" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q33,R$4)</f>
+      <c r="X33" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W33,X$4)</f>
         <v>88</v>
       </c>
-      <c r="S33" s="77">
+      <c r="Y33" s="77">
+        <f t="shared" si="26"/>
+        <v>18.379056800000001</v>
+      </c>
+      <c r="Z33" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W33,Z$4)</f>
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="AA33" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W33,AA$4)</f>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="AB33" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W33,AB$4)</f>
+        <v>176</v>
+      </c>
+      <c r="AC33" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W33,AC$4)</f>
+        <v>40</v>
+      </c>
+      <c r="AD33" s="41">
+        <f t="shared" si="27"/>
+        <v>735</v>
+      </c>
+      <c r="AE33" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$W33,AE$4)</f>
+        <v>49</v>
+      </c>
+      <c r="AF33" s="38">
         <f t="shared" si="14"/>
-        <v>18.379056800000001</v>
-      </c>
-      <c r="T33" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q33,T$4)</f>
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="U33" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q33,U$4)</f>
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="V33" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q33,V$4)</f>
-        <v>176</v>
-      </c>
-      <c r="W33" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q33,W$4)</f>
-        <v>40</v>
-      </c>
-      <c r="X33" s="41">
-        <f t="shared" si="15"/>
-        <v>735</v>
-      </c>
-      <c r="Y33" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q33,Y$4)</f>
-        <v>49</v>
-      </c>
-      <c r="AB33" s="68">
+        <v>2.8160000000000003</v>
+      </c>
+      <c r="AG33" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$W33,AG$4)/1000*100</f>
+        <v>1.1900000000000002</v>
+      </c>
+      <c r="AH33" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$W33,AH$4)/1000*100</f>
+        <v>1.3</v>
+      </c>
+      <c r="AK33" s="68">
         <f>MATCH($B33,poultry!$A$3:$A$41,0)</f>
         <v>36</v>
       </c>
-      <c r="AC33" s="59">
-        <f>INDEX(poultry!$D$3:$U$41,$AB33,AC$4)</f>
+      <c r="AL33" s="59">
+        <f>INDEX(poultry!$D$3:$U$41,$AK33,AL$4)</f>
         <v>87</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>50</v>
       </c>
       <c r="C34" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>90</v>
       </c>
       <c r="D34" s="64">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>19.659779199999999</v>
       </c>
-      <c r="E34" s="4"/>
-      <c r="F34" s="68">
+      <c r="E34" s="38">
+        <f t="shared" si="18"/>
+        <v>5.2799999999999994</v>
+      </c>
+      <c r="F34" s="91">
+        <f t="shared" si="19"/>
+        <v>0.88</v>
+      </c>
+      <c r="G34" s="92">
+        <f t="shared" si="20"/>
+        <v>1.165</v>
+      </c>
+      <c r="H34" s="4"/>
+      <c r="I34" s="68">
         <f>MATCH($B34,ruminants!$A$3:$A$120,0)</f>
         <v>109</v>
       </c>
-      <c r="G34" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F34,G$4)</f>
+      <c r="J34" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I34,J$4)</f>
         <v>90</v>
       </c>
-      <c r="H34" s="77">
-        <f t="shared" si="6"/>
+      <c r="K34" s="77">
+        <f t="shared" si="11"/>
         <v>19.659779199999999</v>
       </c>
-      <c r="I34" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F34,I$4)</f>
+      <c r="L34" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I34,L$4)</f>
         <v>13.3</v>
       </c>
-      <c r="J34" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F34,J$4)</f>
+      <c r="M34" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I34,M$4)</f>
         <v>320</v>
       </c>
-      <c r="K34" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F34,K$4)</f>
+      <c r="N34" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I34,N$4)</f>
         <v>45</v>
       </c>
-      <c r="L34" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F34,L$4)</f>
+      <c r="O34" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I34,O$4)</f>
         <v>106</v>
       </c>
-      <c r="M34" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F34,M$4)</f>
+      <c r="P34" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I34,P$4)</f>
         <v>492</v>
       </c>
-      <c r="N34" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F34,N$4)</f>
+      <c r="Q34" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I34,Q$4)</f>
         <v>37</v>
       </c>
-      <c r="Q34" s="68">
+      <c r="R34" s="38">
+        <f t="shared" si="8"/>
+        <v>5.12</v>
+      </c>
+      <c r="S34" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I34,S$4)/1000*100</f>
+        <v>1.03</v>
+      </c>
+      <c r="T34" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I34,T$4)/1000*100</f>
+        <v>1.3699999999999999</v>
+      </c>
+      <c r="W34" s="68">
         <f>MATCH($B34,pigs!$A$3:$A$60,0)</f>
         <v>3</v>
       </c>
-      <c r="R34" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q34,R$4)</f>
+      <c r="X34" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W34,X$4)</f>
         <v>90</v>
       </c>
-      <c r="S34" s="77">
+      <c r="Y34" s="77">
+        <f t="shared" si="26"/>
+        <v>20.139265599999998</v>
+      </c>
+      <c r="Z34" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W34,Z$4)</f>
+        <v>8.1</v>
+      </c>
+      <c r="AA34" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W34,AA$4)</f>
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="AB34" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W34,AB$4)</f>
+        <v>340</v>
+      </c>
+      <c r="AC34" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W34,AC$4)</f>
+        <v>66</v>
+      </c>
+      <c r="AD34" s="41">
+        <f t="shared" si="27"/>
+        <v>550</v>
+      </c>
+      <c r="AE34" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$W34,AE$4)</f>
+        <v>44</v>
+      </c>
+      <c r="AF34" s="38">
         <f t="shared" si="14"/>
-        <v>20.139265599999998</v>
-      </c>
-      <c r="T34" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q34,T$4)</f>
-        <v>8.1</v>
-      </c>
-      <c r="U34" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q34,U$4)</f>
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="V34" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q34,V$4)</f>
-        <v>340</v>
-      </c>
-      <c r="W34" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q34,W$4)</f>
-        <v>66</v>
-      </c>
-      <c r="X34" s="41">
-        <f t="shared" si="15"/>
-        <v>550</v>
-      </c>
-      <c r="Y34" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q34,Y$4)</f>
-        <v>44</v>
-      </c>
-      <c r="AB34" s="68"/>
-      <c r="AC34" s="59"/>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.25">
+        <v>5.4399999999999995</v>
+      </c>
+      <c r="AG34" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$W34,AG$4)/1000*100</f>
+        <v>0.73</v>
+      </c>
+      <c r="AH34" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$W34,AH$4)/1000*100</f>
+        <v>0.96</v>
+      </c>
+      <c r="AK34" s="68"/>
+      <c r="AL34" s="59"/>
+    </row>
+    <row r="35" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>51</v>
       </c>
       <c r="C35" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>11</v>
       </c>
       <c r="D35" s="64">
-        <f>S35</f>
+        <f>Y35</f>
         <v>18.8602168</v>
       </c>
-      <c r="E35" s="4"/>
-      <c r="F35" s="68"/>
-      <c r="G35" s="37"/>
-      <c r="H35" s="54"/>
-      <c r="I35" s="38"/>
-      <c r="J35" s="39"/>
-      <c r="K35" s="39"/>
-      <c r="L35" s="39"/>
-      <c r="M35" s="39"/>
-      <c r="N35" s="42"/>
-      <c r="Q35" s="68">
+      <c r="E35" s="38">
+        <f t="shared" si="18"/>
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="F35" s="91">
+        <f t="shared" si="19"/>
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="G35" s="92">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="H35" s="4"/>
+      <c r="I35" s="68"/>
+      <c r="J35" s="37"/>
+      <c r="K35" s="54"/>
+      <c r="L35" s="38"/>
+      <c r="M35" s="65"/>
+      <c r="N35" s="39"/>
+      <c r="O35" s="39"/>
+      <c r="P35" s="39"/>
+      <c r="Q35" s="42"/>
+      <c r="R35" s="38"/>
+      <c r="S35" s="39"/>
+      <c r="T35" s="42"/>
+      <c r="W35" s="68">
         <f>MATCH($B35,pigs!$A$3:$A$60,0)</f>
         <v>1</v>
       </c>
-      <c r="R35" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q35,R$4)</f>
+      <c r="X35" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W35,X$4)</f>
         <v>11</v>
       </c>
-      <c r="S35" s="77">
+      <c r="Y35" s="77">
+        <f t="shared" si="26"/>
+        <v>18.8602168</v>
+      </c>
+      <c r="Z35" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W35,Z$4)</f>
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="AA35" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W35,AA$4)</f>
+        <v>8.9</v>
+      </c>
+      <c r="AB35" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W35,AB$4)</f>
+        <v>280</v>
+      </c>
+      <c r="AC35" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W35,AC$4)</f>
+        <v>45</v>
+      </c>
+      <c r="AD35" s="41">
+        <f t="shared" si="27"/>
+        <v>607</v>
+      </c>
+      <c r="AE35" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$W35,AE$4)</f>
+        <v>68</v>
+      </c>
+      <c r="AF35" s="38">
         <f t="shared" si="14"/>
-        <v>18.8602168</v>
-      </c>
-      <c r="T35" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q35,T$4)</f>
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="U35" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q35,U$4)</f>
-        <v>8.9</v>
-      </c>
-      <c r="V35" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q35,V$4)</f>
-        <v>280</v>
-      </c>
-      <c r="W35" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q35,W$4)</f>
-        <v>45</v>
-      </c>
-      <c r="X35" s="41">
-        <f t="shared" si="15"/>
-        <v>607</v>
-      </c>
-      <c r="Y35" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q35,Y$4)</f>
-        <v>68</v>
-      </c>
-      <c r="AB35" s="68"/>
-      <c r="AC35" s="59"/>
-    </row>
-    <row r="36" spans="2:29" x14ac:dyDescent="0.25">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="AG35" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$W35,AG$4)/1000*100</f>
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="AH35" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$W35,AH$4)/1000*100</f>
+        <v>0</v>
+      </c>
+      <c r="AK35" s="68"/>
+      <c r="AL35" s="59"/>
+    </row>
+    <row r="36" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>309</v>
       </c>
       <c r="C36" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>90</v>
       </c>
       <c r="D36" s="64">
-        <f>H36</f>
+        <f>K36</f>
         <v>19.848896</v>
       </c>
-      <c r="E36" s="4"/>
-      <c r="F36" s="68">
+      <c r="E36" s="38">
+        <f t="shared" si="18"/>
+        <v>3.984</v>
+      </c>
+      <c r="F36" s="91">
+        <f t="shared" si="19"/>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="G36" s="92">
+        <f t="shared" si="20"/>
+        <v>0.19500000000000001</v>
+      </c>
+      <c r="H36" s="4"/>
+      <c r="I36" s="68">
         <f>MATCH($B36,ruminants!$A$3:$A$120,0)</f>
         <v>38</v>
       </c>
-      <c r="G36" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F36,G$4)</f>
+      <c r="J36" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I36,J$4)</f>
         <v>90</v>
       </c>
-      <c r="H36" s="77">
-        <f t="shared" si="6"/>
+      <c r="K36" s="77">
+        <f t="shared" si="11"/>
         <v>19.848896</v>
       </c>
-      <c r="I36" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F36,I$4)</f>
+      <c r="L36" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I36,L$4)</f>
         <v>11.6</v>
       </c>
-      <c r="J36" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F36,J$4)</f>
+      <c r="M36" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I36,M$4)</f>
         <v>240</v>
       </c>
-      <c r="K36" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F36,K$4)</f>
+      <c r="N36" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I36,N$4)</f>
         <v>80</v>
       </c>
-      <c r="L36" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F36,L$4)</f>
+      <c r="O36" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I36,O$4)</f>
         <v>170</v>
       </c>
-      <c r="M36" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F36,M$4)</f>
+      <c r="P36" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I36,P$4)</f>
         <v>470</v>
       </c>
-      <c r="N36" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F36,N$4)</f>
+      <c r="Q36" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I36,Q$4)</f>
         <v>40</v>
       </c>
-      <c r="Q36" s="68"/>
-      <c r="R36" s="37">
+      <c r="R36" s="38">
+        <f t="shared" si="8"/>
+        <v>3.84</v>
+      </c>
+      <c r="S36" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I36,S$4)/1000*100</f>
+        <v>0.54999999999999993</v>
+      </c>
+      <c r="T36" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I36,T$4)/1000*100</f>
+        <v>0.1</v>
+      </c>
+      <c r="W36" s="68"/>
+      <c r="X36" s="37">
         <v>90</v>
       </c>
-      <c r="S36" s="77">
+      <c r="Y36" s="77">
+        <f t="shared" si="26"/>
+        <v>19.578191199999999</v>
+      </c>
+      <c r="Z36" s="74">
+        <v>6.6</v>
+      </c>
+      <c r="AA36" s="83">
+        <f>AA34/Z34*Z36</f>
+        <v>7.0888888888888877</v>
+      </c>
+      <c r="AB36" s="88">
+        <v>258</v>
+      </c>
+      <c r="AC36" s="74">
+        <v>67</v>
+      </c>
+      <c r="AD36" s="41">
+        <f t="shared" si="27"/>
+        <v>629</v>
+      </c>
+      <c r="AE36" s="45">
+        <v>46</v>
+      </c>
+      <c r="AF36" s="38">
         <f t="shared" si="14"/>
-        <v>19.578191199999999</v>
-      </c>
-      <c r="T36" s="74">
-        <v>6.6</v>
-      </c>
-      <c r="U36" s="84">
-        <f>U34/T34*T36</f>
-        <v>7.0888888888888877</v>
-      </c>
-      <c r="V36" s="74">
-        <v>258</v>
-      </c>
-      <c r="W36" s="74">
-        <v>67</v>
-      </c>
-      <c r="X36" s="41">
-        <f t="shared" si="15"/>
-        <v>629</v>
-      </c>
-      <c r="Y36" s="45">
-        <v>46</v>
-      </c>
-      <c r="Z36" s="11" t="s">
+        <v>4.1280000000000001</v>
+      </c>
+      <c r="AG36" s="91">
+        <f>5.7/1000*100</f>
+        <v>0.57000000000000006</v>
+      </c>
+      <c r="AH36" s="92">
+        <f>2.9/1000*100</f>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AI36" s="11" t="s">
         <v>312</v>
       </c>
-      <c r="AA36" s="11" t="s">
-        <v>490</v>
-      </c>
-      <c r="AB36" s="68"/>
-      <c r="AC36" s="59"/>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AJ36" s="11" t="s">
+        <v>489</v>
+      </c>
+      <c r="AK36" s="68"/>
+      <c r="AL36" s="59"/>
+    </row>
+    <row r="37" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>384</v>
       </c>
       <c r="C37" s="65">
-        <f>AVERAGE(R37,G37,AC37)</f>
+        <f>AVERAGE(X37,J37,AL37)</f>
         <v>88.5</v>
       </c>
       <c r="D37" s="64">
-        <f>S37</f>
+        <f>Y37</f>
         <v>22.900705599999998</v>
       </c>
-      <c r="E37" s="4"/>
-      <c r="F37" s="68"/>
-      <c r="G37" s="37"/>
-      <c r="H37" s="54"/>
-      <c r="I37" s="38"/>
-      <c r="J37" s="39"/>
-      <c r="K37" s="39"/>
-      <c r="L37" s="39"/>
-      <c r="M37" s="39"/>
-      <c r="N37" s="42"/>
-      <c r="Q37" s="68">
+      <c r="E37" s="38">
+        <f t="shared" si="18"/>
+        <v>10.832000000000001</v>
+      </c>
+      <c r="F37" s="91">
+        <f t="shared" si="19"/>
+        <v>0.64</v>
+      </c>
+      <c r="G37" s="92">
+        <f t="shared" si="20"/>
+        <v>0.54999999999999993</v>
+      </c>
+      <c r="H37" s="4"/>
+      <c r="I37" s="68"/>
+      <c r="J37" s="37"/>
+      <c r="K37" s="54"/>
+      <c r="L37" s="38"/>
+      <c r="M37" s="65"/>
+      <c r="N37" s="39"/>
+      <c r="O37" s="39"/>
+      <c r="P37" s="39"/>
+      <c r="Q37" s="42"/>
+      <c r="R37" s="38"/>
+      <c r="S37" s="39"/>
+      <c r="T37" s="42"/>
+      <c r="W37" s="68">
         <f>MATCH($B37,pigs!$A$3:$A$60,0)</f>
         <v>22</v>
       </c>
-      <c r="R37" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q37,R$4)</f>
+      <c r="X37" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W37,X$4)</f>
         <v>90</v>
       </c>
-      <c r="S37" s="77">
+      <c r="Y37" s="77">
+        <f t="shared" si="26"/>
+        <v>22.900705599999998</v>
+      </c>
+      <c r="Z37" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W37,Z$4)</f>
+        <v>12.9</v>
+      </c>
+      <c r="AA37" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W37,AA$4)</f>
+        <v>13.3</v>
+      </c>
+      <c r="AB37" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W37,AB$4)</f>
+        <v>677</v>
+      </c>
+      <c r="AC37" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W37,AC$4)</f>
+        <v>71</v>
+      </c>
+      <c r="AD37" s="41">
+        <f t="shared" ref="AD37" si="28">1000-SUM(AB37:AC37,AE37)</f>
+        <v>231</v>
+      </c>
+      <c r="AE37" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$W37,AE$4)</f>
+        <v>21</v>
+      </c>
+      <c r="AF37" s="38">
         <f t="shared" si="14"/>
-        <v>22.900705599999998</v>
-      </c>
-      <c r="T37" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q37,T$4)</f>
-        <v>12.9</v>
-      </c>
-      <c r="U37" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q37,U$4)</f>
-        <v>13.3</v>
-      </c>
-      <c r="V37" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q37,V$4)</f>
-        <v>677</v>
-      </c>
-      <c r="W37" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q37,W$4)</f>
-        <v>71</v>
-      </c>
-      <c r="X37" s="41">
-        <f t="shared" ref="X37" si="16">1000-SUM(V37:W37,Y37)</f>
-        <v>231</v>
-      </c>
-      <c r="Y37" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q37,Y$4)</f>
-        <v>21</v>
-      </c>
-      <c r="Z37" s="11"/>
-      <c r="AA37" s="11"/>
-      <c r="AB37" s="68">
+        <v>10.832000000000001</v>
+      </c>
+      <c r="AG37" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$W37,AG$4)/1000*100</f>
+        <v>0.64</v>
+      </c>
+      <c r="AH37" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$W37,AH$4)/1000*100</f>
+        <v>0.54999999999999993</v>
+      </c>
+      <c r="AI37" s="11"/>
+      <c r="AJ37" s="11"/>
+      <c r="AK37" s="68">
         <f>MATCH($B37,poultry!$A$3:$A$41,0)</f>
         <v>25</v>
       </c>
-      <c r="AC37" s="59">
-        <f>INDEX(poultry!$D$3:$U$41,$AB37,AC$4)</f>
+      <c r="AL37" s="59">
+        <f>INDEX(poultry!$D$3:$U$41,$AK37,AL$4)</f>
         <v>87</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>52</v>
       </c>
       <c r="C38" s="65">
-        <f t="shared" ref="C38:C43" si="17">AVERAGE(R38,G38)</f>
+        <f t="shared" ref="C38:C43" si="29">AVERAGE(X38,J38)</f>
         <v>75.5</v>
       </c>
       <c r="D38" s="64">
-        <f>H38</f>
+        <f>K38</f>
         <v>16.1615368</v>
       </c>
-      <c r="E38" s="4"/>
-      <c r="F38" s="68">
+      <c r="E38" s="38">
+        <f t="shared" si="18"/>
+        <v>2.2080000000000002</v>
+      </c>
+      <c r="F38" s="91">
+        <f t="shared" si="19"/>
+        <v>0.03</v>
+      </c>
+      <c r="G38" s="92">
+        <f t="shared" si="20"/>
+        <v>3.6500000000000004</v>
+      </c>
+      <c r="H38" s="4"/>
+      <c r="I38" s="68">
         <f>MATCH($B38,ruminants!$A$3:$A$120,0)</f>
         <v>88</v>
       </c>
-      <c r="G38" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F38,G$4)</f>
+      <c r="J38" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I38,J$4)</f>
         <v>75</v>
       </c>
-      <c r="H38" s="77">
-        <f t="shared" si="6"/>
+      <c r="K38" s="77">
+        <f t="shared" si="11"/>
         <v>16.1615368</v>
       </c>
-      <c r="I38" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F38,I$4)</f>
+      <c r="L38" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I38,L$4)</f>
         <v>12.4</v>
       </c>
-      <c r="J38" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F38,J$4)</f>
+      <c r="M38" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I38,M$4)</f>
         <v>131</v>
       </c>
-      <c r="K38" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F38,K$4)</f>
-        <v>0</v>
-      </c>
-      <c r="L38" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F38,L$4)</f>
-        <v>0</v>
-      </c>
-      <c r="M38" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F38,M$4)</f>
+      <c r="N38" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I38,N$4)</f>
+        <v>0</v>
+      </c>
+      <c r="O38" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I38,O$4)</f>
+        <v>0</v>
+      </c>
+      <c r="P38" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I38,P$4)</f>
         <v>760</v>
       </c>
-      <c r="N38" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F38,N$4)</f>
+      <c r="Q38" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I38,Q$4)</f>
         <v>109</v>
       </c>
-      <c r="Q38" s="68">
+      <c r="R38" s="38">
+        <f t="shared" si="8"/>
+        <v>2.0960000000000001</v>
+      </c>
+      <c r="S38" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I38,S$4)/1000*100</f>
+        <v>0.02</v>
+      </c>
+      <c r="T38" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I38,T$4)/1000*100</f>
+        <v>4.5</v>
+      </c>
+      <c r="W38" s="68">
         <f>MATCH($B38,pigs!$A$3:$A$60,0)</f>
         <v>23</v>
       </c>
-      <c r="R38" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q38,R$4)</f>
+      <c r="X38" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W38,X$4)</f>
         <v>76</v>
       </c>
-      <c r="S38" s="77">
-        <f t="shared" ref="S38:S43" si="18">( 5.7*V38+9.4*W38+4.1*(X38) ) * 0.004184</f>
+      <c r="Y38" s="77">
+        <f t="shared" ref="Y38:Y43" si="30">( 5.7*AB38+9.4*AC38+4.1*(AD38) ) * 0.004184</f>
         <v>15.9565208</v>
       </c>
-      <c r="T38" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q38,T$4)</f>
+      <c r="Z38" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W38,Z$4)</f>
         <v>8.6999999999999993</v>
       </c>
-      <c r="U38" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q38,U$4)</f>
+      <c r="AA38" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W38,AA$4)</f>
         <v>9</v>
       </c>
-      <c r="V38" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q38,V$4)</f>
+      <c r="AB38" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W38,AB$4)</f>
         <v>145</v>
       </c>
-      <c r="W38" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q38,W$4)</f>
+      <c r="AC38" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W38,AC$4)</f>
         <v>2</v>
       </c>
-      <c r="X38" s="41">
-        <f t="shared" ref="X38:X43" si="19">1000-SUM(V38:W38,Y38)</f>
+      <c r="AD38" s="41">
+        <f t="shared" ref="AD38:AD43" si="31">1000-SUM(AB38:AC38,AE38)</f>
         <v>724</v>
       </c>
-      <c r="Y38" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q38,Y$4)</f>
+      <c r="AE38" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$W38,AE$4)</f>
         <v>129</v>
       </c>
-      <c r="AB38" s="68"/>
-      <c r="AC38" s="59"/>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AF38" s="38">
+        <f t="shared" si="14"/>
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="AG38" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$W38,AG$4)/1000*100</f>
+        <v>0.04</v>
+      </c>
+      <c r="AH38" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$W38,AH$4)/1000*100</f>
+        <v>2.8000000000000003</v>
+      </c>
+      <c r="AK38" s="68"/>
+      <c r="AL38" s="59"/>
+    </row>
+    <row r="39" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>53</v>
       </c>
       <c r="C39" s="65">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>89.5</v>
       </c>
       <c r="D39" s="64">
-        <f>H39</f>
+        <f>K39</f>
         <v>17.334312000000001</v>
       </c>
-      <c r="E39" s="4"/>
-      <c r="F39" s="68">
+      <c r="E39" s="38">
+        <f t="shared" si="18"/>
+        <v>1.448</v>
+      </c>
+      <c r="F39" s="91">
+        <f t="shared" si="19"/>
+        <v>0.1</v>
+      </c>
+      <c r="G39" s="92">
+        <f t="shared" si="20"/>
+        <v>0.48499999999999999</v>
+      </c>
+      <c r="H39" s="4"/>
+      <c r="I39" s="68">
         <f>MATCH($B39,ruminants!$A$3:$A$120,0)</f>
         <v>91</v>
       </c>
-      <c r="G39" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F39,G$4)</f>
+      <c r="J39" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I39,J$4)</f>
         <v>90</v>
       </c>
-      <c r="H39" s="77">
-        <f t="shared" si="6"/>
+      <c r="K39" s="77">
+        <f t="shared" si="11"/>
         <v>17.334312000000001</v>
       </c>
-      <c r="I39" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F39,I$4)</f>
+      <c r="L39" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I39,L$4)</f>
         <v>12.3</v>
       </c>
-      <c r="J39" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F39,J$4)</f>
+      <c r="M39" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I39,M$4)</f>
         <v>90</v>
       </c>
-      <c r="K39" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F39,K$4)</f>
+      <c r="N39" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I39,N$4)</f>
         <v>32</v>
       </c>
-      <c r="L39" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F39,L$4)</f>
+      <c r="O39" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I39,O$4)</f>
         <v>187</v>
       </c>
-      <c r="M39" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F39,M$4)</f>
+      <c r="P39" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I39,P$4)</f>
         <v>625</v>
       </c>
-      <c r="N39" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F39,N$4)</f>
+      <c r="Q39" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I39,Q$4)</f>
         <v>66</v>
       </c>
-      <c r="Q39" s="68">
+      <c r="R39" s="38">
+        <f t="shared" si="8"/>
+        <v>1.44</v>
+      </c>
+      <c r="S39" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I39,S$4)/1000*100</f>
+        <v>0.1</v>
+      </c>
+      <c r="T39" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I39,T$4)/1000*100</f>
+        <v>0.6</v>
+      </c>
+      <c r="W39" s="68">
         <f>MATCH($B39,pigs!$A$3:$A$60,0)</f>
         <v>4</v>
       </c>
-      <c r="R39" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q39,R$4)</f>
+      <c r="X39" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W39,X$4)</f>
         <v>89</v>
       </c>
-      <c r="S39" s="77">
-        <f t="shared" si="18"/>
+      <c r="Y39" s="77">
+        <f t="shared" si="30"/>
         <v>16.664453599999998</v>
       </c>
-      <c r="T39" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q39,T$4)</f>
+      <c r="Z39" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W39,Z$4)</f>
         <v>6.9</v>
       </c>
-      <c r="U39" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q39,U$4)</f>
+      <c r="AA39" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W39,AA$4)</f>
         <v>8</v>
       </c>
-      <c r="V39" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q39,V$4)</f>
+      <c r="AB39" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W39,AB$4)</f>
         <v>91</v>
       </c>
-      <c r="W39" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q39,W$4)</f>
+      <c r="AC39" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W39,AC$4)</f>
         <v>10</v>
       </c>
-      <c r="X39" s="41">
-        <f t="shared" si="19"/>
+      <c r="AD39" s="41">
+        <f t="shared" si="31"/>
         <v>822</v>
       </c>
-      <c r="Y39" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q39,Y$4)</f>
+      <c r="AE39" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$W39,AE$4)</f>
         <v>77</v>
       </c>
-      <c r="AB39" s="68"/>
-      <c r="AC39" s="59"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AF39" s="38">
+        <f t="shared" si="14"/>
+        <v>1.456</v>
+      </c>
+      <c r="AG39" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$W39,AG$4)/1000*100</f>
+        <v>0.1</v>
+      </c>
+      <c r="AH39" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$W39,AH$4)/1000*100</f>
+        <v>0.37</v>
+      </c>
+      <c r="AK39" s="68"/>
+      <c r="AL39" s="59"/>
+    </row>
+    <row r="40" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>54</v>
       </c>
       <c r="C40" s="65">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>6.25</v>
       </c>
       <c r="D40" s="64">
-        <f>H40</f>
+        <f>K40</f>
         <v>16.464040000000001</v>
       </c>
-      <c r="E40" s="4"/>
-      <c r="F40" s="68">
+      <c r="E40" s="38">
+        <f t="shared" si="18"/>
+        <v>1.8800000000000001</v>
+      </c>
+      <c r="F40" s="91">
+        <f t="shared" si="19"/>
+        <v>0.76</v>
+      </c>
+      <c r="G40" s="92">
+        <f t="shared" si="20"/>
+        <v>2.355</v>
+      </c>
+      <c r="H40" s="4"/>
+      <c r="I40" s="68">
         <f>MATCH($B40,ruminants!$A$3:$A$120,0)</f>
         <v>57</v>
       </c>
-      <c r="G40" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F40,G$4)</f>
+      <c r="J40" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I40,J$4)</f>
         <v>7</v>
       </c>
-      <c r="H40" s="77">
-        <f t="shared" si="6"/>
+      <c r="K40" s="77">
+        <f t="shared" si="11"/>
         <v>16.464040000000001</v>
       </c>
-      <c r="I40" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F40,I$4)</f>
+      <c r="L40" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I40,L$4)</f>
         <v>13.6</v>
       </c>
-      <c r="J40" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F40,J$4)</f>
+      <c r="M40" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I40,M$4)</f>
         <v>120</v>
       </c>
-      <c r="K40" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F40,K$4)</f>
+      <c r="N40" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I40,N$4)</f>
         <v>10</v>
       </c>
-      <c r="L40" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F40,L$4)</f>
-        <v>0</v>
-      </c>
-      <c r="M40" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F40,M$4)</f>
+      <c r="O40" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I40,O$4)</f>
+        <v>0</v>
+      </c>
+      <c r="P40" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I40,P$4)</f>
         <v>770</v>
       </c>
-      <c r="N40" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F40,N$4)</f>
+      <c r="Q40" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I40,Q$4)</f>
         <v>100</v>
       </c>
-      <c r="Q40" s="68">
+      <c r="R40" s="38">
+        <f t="shared" si="8"/>
+        <v>1.92</v>
+      </c>
+      <c r="S40" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I40,S$4)/1000*100</f>
+        <v>0.79</v>
+      </c>
+      <c r="T40" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I40,T$4)/1000*100</f>
+        <v>2.4</v>
+      </c>
+      <c r="W40" s="68">
         <f>MATCH($B40,pigs!$A$3:$A$60,0)</f>
         <v>50</v>
       </c>
-      <c r="R40" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q40,R$4)</f>
+      <c r="X40" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W40,X$4)</f>
         <v>5.5</v>
       </c>
-      <c r="S40" s="77">
-        <f t="shared" si="18"/>
+      <c r="Y40" s="77">
+        <f t="shared" si="30"/>
         <v>16.870306399999997</v>
       </c>
-      <c r="T40" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q40,T$4)</f>
+      <c r="Z40" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W40,Z$4)</f>
         <v>12.4</v>
       </c>
-      <c r="U40" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q40,U$4)</f>
+      <c r="AA40" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W40,AA$4)</f>
         <v>12.2</v>
       </c>
-      <c r="V40" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q40,V$4)</f>
+      <c r="AB40" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W40,AB$4)</f>
         <v>115</v>
       </c>
-      <c r="W40" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q40,W$4)</f>
+      <c r="AC40" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W40,AC$4)</f>
         <v>19</v>
       </c>
-      <c r="X40" s="41">
-        <f t="shared" si="19"/>
+      <c r="AD40" s="41">
+        <f t="shared" si="31"/>
         <v>780</v>
       </c>
-      <c r="Y40" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q40,Y$4)</f>
+      <c r="AE40" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$W40,AE$4)</f>
         <v>86</v>
       </c>
-      <c r="AB40" s="68"/>
-      <c r="AC40" s="59"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AF40" s="38">
+        <f t="shared" si="14"/>
+        <v>1.8400000000000003</v>
+      </c>
+      <c r="AG40" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$W40,AG$4)/1000*100</f>
+        <v>0.73</v>
+      </c>
+      <c r="AH40" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$W40,AH$4)/1000*100</f>
+        <v>2.31</v>
+      </c>
+      <c r="AK40" s="68"/>
+      <c r="AL40" s="59"/>
+    </row>
+    <row r="41" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>55</v>
       </c>
       <c r="C41" s="65">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>97</v>
       </c>
       <c r="D41" s="64">
-        <f>S41</f>
+        <f>Y41</f>
         <v>16.975324799999999</v>
       </c>
-      <c r="E41" s="4"/>
-      <c r="F41" s="68"/>
-      <c r="G41" s="37"/>
-      <c r="H41" s="54"/>
-      <c r="I41" s="38"/>
-      <c r="J41" s="39"/>
-      <c r="K41" s="39"/>
-      <c r="L41" s="39"/>
-      <c r="M41" s="39"/>
-      <c r="N41" s="42"/>
-      <c r="Q41" s="68">
+      <c r="E41" s="38">
+        <f t="shared" si="18"/>
+        <v>2.0960000000000001</v>
+      </c>
+      <c r="F41" s="91">
+        <f t="shared" si="19"/>
+        <v>0.72</v>
+      </c>
+      <c r="G41" s="92">
+        <f t="shared" si="20"/>
+        <v>2.1</v>
+      </c>
+      <c r="H41" s="4"/>
+      <c r="I41" s="68"/>
+      <c r="J41" s="37"/>
+      <c r="K41" s="54"/>
+      <c r="L41" s="38"/>
+      <c r="M41" s="65"/>
+      <c r="N41" s="39"/>
+      <c r="O41" s="39"/>
+      <c r="P41" s="39"/>
+      <c r="Q41" s="42"/>
+      <c r="R41" s="38"/>
+      <c r="S41" s="39"/>
+      <c r="T41" s="42"/>
+      <c r="W41" s="68">
         <f>MATCH($B41,pigs!$A$3:$A$60,0)</f>
         <v>52</v>
       </c>
-      <c r="R41" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q41,R$4)</f>
+      <c r="X41" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W41,X$4)</f>
         <v>97</v>
       </c>
-      <c r="S41" s="77">
-        <f t="shared" si="18"/>
+      <c r="Y41" s="77">
+        <f t="shared" si="30"/>
         <v>16.975324799999999</v>
       </c>
-      <c r="T41" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q41,T$4)</f>
+      <c r="Z41" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W41,Z$4)</f>
         <v>12.4</v>
       </c>
-      <c r="U41" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q41,U$4)</f>
+      <c r="AA41" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W41,AA$4)</f>
         <v>12.2</v>
       </c>
-      <c r="V41" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q41,V$4)</f>
+      <c r="AB41" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W41,AB$4)</f>
         <v>131</v>
       </c>
-      <c r="W41" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q41,W$4)</f>
+      <c r="AC41" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W41,AC$4)</f>
         <v>22</v>
       </c>
-      <c r="X41" s="41">
-        <f t="shared" si="19"/>
+      <c r="AD41" s="41">
+        <f t="shared" si="31"/>
         <v>757</v>
       </c>
-      <c r="Y41" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q41,Y$4)</f>
+      <c r="AE41" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$W41,AE$4)</f>
         <v>90</v>
       </c>
-      <c r="AB41" s="68"/>
-      <c r="AC41" s="59"/>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AF41" s="38">
+        <f t="shared" si="14"/>
+        <v>2.0960000000000001</v>
+      </c>
+      <c r="AG41" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$W41,AG$4)/1000*100</f>
+        <v>0.72</v>
+      </c>
+      <c r="AH41" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$W41,AH$4)/1000*100</f>
+        <v>2.1</v>
+      </c>
+      <c r="AK41" s="68"/>
+      <c r="AL41" s="59"/>
+    </row>
+    <row r="42" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>56</v>
       </c>
       <c r="C42" s="65">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>91</v>
       </c>
       <c r="D42" s="64">
-        <f>H42</f>
+        <f>K42</f>
         <v>23.055932000000002</v>
       </c>
-      <c r="E42" s="4"/>
-      <c r="F42" s="68">
+      <c r="E42" s="38">
+        <f t="shared" si="18"/>
+        <v>13.48</v>
+      </c>
+      <c r="F42" s="91">
+        <f t="shared" si="19"/>
+        <v>0.435</v>
+      </c>
+      <c r="G42" s="92">
+        <f t="shared" si="20"/>
+        <v>0.81499999999999995</v>
+      </c>
+      <c r="H42" s="4"/>
+      <c r="I42" s="68">
         <f>MATCH($B42,ruminants!$A$3:$A$120,0)</f>
         <v>65</v>
       </c>
-      <c r="G42" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F42,G$4)</f>
+      <c r="J42" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I42,J$4)</f>
         <v>90</v>
       </c>
-      <c r="H42" s="77">
-        <f t="shared" si="6"/>
+      <c r="K42" s="77">
+        <f t="shared" si="11"/>
         <v>23.055932000000002</v>
       </c>
-      <c r="I42" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F42,I$4)</f>
+      <c r="L42" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I42,L$4)</f>
         <v>15.5</v>
       </c>
-      <c r="J42" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F42,J$4)</f>
+      <c r="M42" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I42,M$4)</f>
         <v>844</v>
       </c>
-      <c r="K42" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F42,K$4)</f>
+      <c r="N42" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I42,N$4)</f>
         <v>33</v>
       </c>
-      <c r="L42" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F42,L$4)</f>
+      <c r="O42" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I42,O$4)</f>
         <v>4</v>
       </c>
-      <c r="M42" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F42,M$4)</f>
+      <c r="P42" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I42,P$4)</f>
         <v>91</v>
       </c>
-      <c r="N42" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$F42,N$4)</f>
+      <c r="Q42" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I42,Q$4)</f>
         <v>28</v>
       </c>
-      <c r="Q42" s="68">
+      <c r="R42" s="38">
+        <f t="shared" si="8"/>
+        <v>13.504</v>
+      </c>
+      <c r="S42" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I42,S$4)/1000*100</f>
+        <v>0.44</v>
+      </c>
+      <c r="T42" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$I42,T$4)/1000*100</f>
+        <v>0.89</v>
+      </c>
+      <c r="W42" s="68">
         <f>MATCH($B42,pigs!$A$3:$A$60,0)</f>
         <v>31</v>
       </c>
-      <c r="R42" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q42,R$4)</f>
+      <c r="X42" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W42,X$4)</f>
         <v>92</v>
       </c>
-      <c r="S42" s="77">
-        <f t="shared" si="18"/>
+      <c r="Y42" s="77">
+        <f t="shared" si="30"/>
         <v>22.525819200000001</v>
       </c>
-      <c r="T42" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q42,T$4)</f>
+      <c r="Z42" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W42,Z$4)</f>
         <v>11.1</v>
       </c>
-      <c r="U42" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q42,U$4)</f>
+      <c r="AA42" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W42,AA$4)</f>
         <v>11.3</v>
       </c>
-      <c r="V42" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q42,V$4)</f>
+      <c r="AB42" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$W42,AB$4)</f>
         <v>841</v>
       </c>
-      <c r="W42" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q42,W$4)</f>
+      <c r="AC42" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$W42,AC$4)</f>
         <v>10</v>
       </c>
-      <c r="X42" s="41">
-        <f t="shared" si="19"/>
+      <c r="AD42" s="41">
+        <f t="shared" si="31"/>
         <v>121</v>
       </c>
-      <c r="Y42" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q42,Y$4)</f>
+      <c r="AE42" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$W42,AE$4)</f>
         <v>28</v>
       </c>
-      <c r="AB42" s="68">
+      <c r="AF42" s="38">
+        <f t="shared" si="14"/>
+        <v>13.456000000000001</v>
+      </c>
+      <c r="AG42" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$W42,AG$4)/1000*100</f>
+        <v>0.43</v>
+      </c>
+      <c r="AH42" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$W42,AH$4)/1000*100</f>
+        <v>0.74</v>
+      </c>
+      <c r="AK42" s="68">
         <f>MATCH($B42,poultry!$A$3:$A$41,0)</f>
         <v>28</v>
       </c>
-      <c r="AC42" s="59">
-        <f>INDEX(poultry!$D$3:$U$41,$AB42,AC$4)</f>
+      <c r="AL42" s="59">
+        <f>INDEX(poultry!$D$3:$U$41,$AK42,AL$4)</f>
         <v>90</v>
       </c>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>57</v>
       </c>
       <c r="C43" s="66">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>92</v>
       </c>
       <c r="D43" s="67">
-        <f>S43</f>
+        <f>Y43</f>
         <v>22.254696000000003</v>
       </c>
-      <c r="E43" s="4"/>
-      <c r="F43" s="68"/>
-      <c r="G43" s="50"/>
-      <c r="H43" s="51"/>
-      <c r="I43" s="51"/>
-      <c r="J43" s="52"/>
-      <c r="K43" s="52"/>
-      <c r="L43" s="52"/>
-      <c r="M43" s="52"/>
-      <c r="N43" s="53"/>
-      <c r="Q43" s="68">
+      <c r="E43" s="95">
+        <f t="shared" si="18"/>
+        <v>12.160000000000002</v>
+      </c>
+      <c r="F43" s="93">
+        <f t="shared" si="19"/>
+        <v>2.4699999999999998</v>
+      </c>
+      <c r="G43" s="94">
+        <f t="shared" si="20"/>
+        <v>1.2</v>
+      </c>
+      <c r="H43" s="4"/>
+      <c r="I43" s="68"/>
+      <c r="J43" s="50"/>
+      <c r="K43" s="51"/>
+      <c r="L43" s="51"/>
+      <c r="M43" s="66"/>
+      <c r="N43" s="52"/>
+      <c r="O43" s="52"/>
+      <c r="P43" s="52"/>
+      <c r="Q43" s="53"/>
+      <c r="R43" s="52"/>
+      <c r="S43" s="52"/>
+      <c r="T43" s="53"/>
+      <c r="W43" s="68">
         <f>MATCH($B43,pigs!$A$3:$A$60,0)</f>
         <v>7</v>
       </c>
-      <c r="R43" s="50">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q43,R$4)</f>
+      <c r="X43" s="50">
+        <f>INDEX(pigs!$D$3:$AO$60,$W43,X$4)</f>
         <v>92</v>
       </c>
-      <c r="S43" s="78">
-        <f t="shared" si="18"/>
+      <c r="Y43" s="78">
+        <f t="shared" si="30"/>
         <v>22.254696000000003</v>
       </c>
-      <c r="T43" s="51">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q43,T$4)</f>
+      <c r="Z43" s="51">
+        <f>INDEX(pigs!$D$3:$AO$60,$W43,Z$4)</f>
         <v>10.8</v>
       </c>
-      <c r="U43" s="51">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q43,U$4)</f>
+      <c r="AA43" s="51">
+        <f>INDEX(pigs!$D$3:$AO$60,$W43,AA$4)</f>
         <v>10.8</v>
       </c>
-      <c r="V43" s="51">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q43,V$4)</f>
+      <c r="AB43" s="50">
+        <f>INDEX(pigs!$D$3:$AO$60,$W43,AB$4)</f>
         <v>760</v>
       </c>
-      <c r="W43" s="51">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q43,W$4)</f>
+      <c r="AC43" s="51">
+        <f>INDEX(pigs!$D$3:$AO$60,$W43,AC$4)</f>
         <v>105</v>
       </c>
-      <c r="X43" s="76">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="Y43" s="58">
-        <f>INDEX(pigs!$D$3:$AO$60,$Q43,Y$4)</f>
+      <c r="AD43" s="76">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AE43" s="58">
+        <f>INDEX(pigs!$D$3:$AO$60,$W43,AE$4)</f>
         <v>135</v>
       </c>
-      <c r="AB43" s="68">
+      <c r="AF43" s="90">
+        <f t="shared" si="14"/>
+        <v>12.160000000000002</v>
+      </c>
+      <c r="AG43" s="93">
+        <f>INDEX(pigs!$D$3:$AO$60,$W43,AG$4)/1000*100</f>
+        <v>2.4699999999999998</v>
+      </c>
+      <c r="AH43" s="94">
+        <f>INDEX(pigs!$D$3:$AO$60,$W43,AH$4)/1000*100</f>
+        <v>1.2</v>
+      </c>
+      <c r="AK43" s="68">
         <f>MATCH($B43,poultry!$A$3:$A$41,0)</f>
         <v>6</v>
       </c>
-      <c r="AC43" s="60">
-        <f>INDEX(poultry!$D$3:$U$41,$AB43,AC$4)</f>
+      <c r="AL43" s="60">
+        <f>INDEX(poultry!$D$3:$U$41,$AK43,AL$4)</f>
         <v>92</v>
       </c>
     </row>
-    <row r="46" spans="2:29" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B46" s="32" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C1" r:id="rId1"/>
-    <hyperlink ref="Z36" r:id="rId2"/>
-    <hyperlink ref="O31" r:id="rId3"/>
-    <hyperlink ref="O33" r:id="rId4"/>
-    <hyperlink ref="O10" r:id="rId5"/>
-    <hyperlink ref="O20" r:id="rId6"/>
+    <hyperlink ref="AI36" r:id="rId2"/>
+    <hyperlink ref="U31" r:id="rId3"/>
+    <hyperlink ref="U33" r:id="rId4"/>
+    <hyperlink ref="U10" r:id="rId5"/>
+    <hyperlink ref="U20" r:id="rId6"/>
+    <hyperlink ref="U23" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
 </worksheet>
 </file>
 
@@ -29141,52 +30444,52 @@
         <v>278</v>
       </c>
       <c r="G2" s="19" t="s">
+        <v>412</v>
+      </c>
+      <c r="H2" s="19" t="s">
         <v>413</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="I2" s="19" t="s">
         <v>414</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="J2" s="19" t="s">
         <v>415</v>
       </c>
-      <c r="J2" s="19" t="s">
+      <c r="K2" s="19" t="s">
         <v>416</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="L2" s="19" t="s">
         <v>417</v>
       </c>
-      <c r="L2" s="19" t="s">
+      <c r="M2" s="19" t="s">
         <v>418</v>
       </c>
-      <c r="M2" s="19" t="s">
+      <c r="N2" s="19" t="s">
         <v>419</v>
       </c>
-      <c r="N2" s="19" t="s">
+      <c r="O2" s="19" t="s">
         <v>420</v>
       </c>
-      <c r="O2" s="19" t="s">
+      <c r="P2" s="19" t="s">
         <v>421</v>
       </c>
-      <c r="P2" s="19" t="s">
+      <c r="Q2" s="19" t="s">
         <v>422</v>
       </c>
-      <c r="Q2" s="19" t="s">
+      <c r="R2" s="19" t="s">
         <v>423</v>
       </c>
-      <c r="R2" s="19" t="s">
+      <c r="S2" s="19" t="s">
         <v>424</v>
       </c>
-      <c r="S2" s="19" t="s">
+      <c r="T2" s="19" t="s">
         <v>425</v>
-      </c>
-      <c r="T2" s="19" t="s">
-        <v>426</v>
       </c>
       <c r="U2" s="19" t="s">
         <v>123</v>
       </c>
       <c r="V2" s="19" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="W2" s="19" t="s">
         <v>148</v>
@@ -29212,7 +30515,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D3" s="14">
         <v>9.4</v>
@@ -29281,7 +30584,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D4" s="17">
         <v>9.4</v>
@@ -29350,7 +30653,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D5" s="14">
         <v>6.1</v>
@@ -29419,7 +30722,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D6" s="17">
         <v>9.4</v>
@@ -29488,7 +30791,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D7" s="14">
         <v>10.5</v>
@@ -29557,7 +30860,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D8" s="17">
         <v>11.1</v>
@@ -29626,7 +30929,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D9" s="14">
         <v>11</v>
@@ -29700,7 +31003,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D10" s="17">
         <v>10.1</v>
@@ -29772,7 +31075,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D11" s="14">
         <v>9.5</v>
@@ -29840,7 +31143,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D12" s="17">
         <v>10.5</v>
@@ -29916,7 +31219,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D13" s="14">
         <v>10.8</v>
@@ -29990,7 +31293,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D14" s="17">
         <v>11.5</v>
@@ -30064,7 +31367,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D15" s="14">
         <v>9.8000000000000007</v>
@@ -30151,7 +31454,7 @@
         <v>14</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D16" s="17">
         <v>9.8000000000000007</v>
@@ -30238,7 +31541,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D17" s="14">
         <v>9.3000000000000007</v>
@@ -30323,7 +31626,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="34" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D18" s="17">
         <v>9.3000000000000007</v>
@@ -30408,7 +31711,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D19" s="14">
         <v>10.199999999999999</v>
@@ -30493,7 +31796,7 @@
         <v>18</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D20" s="17">
         <v>10.199999999999999</v>
@@ -30578,7 +31881,7 @@
         <v>19</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D21" s="14">
         <v>10.9</v>
@@ -30661,7 +31964,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="34" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D22" s="17">
         <v>11.7</v>
@@ -30742,7 +32045,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D23" s="14">
         <v>8</v>
@@ -30821,7 +32124,7 @@
         <v>22</v>
       </c>
       <c r="C24" s="34" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D24" s="17">
         <v>9.1999999999999993</v>
@@ -30904,7 +32207,7 @@
         <v>23</v>
       </c>
       <c r="C25" s="33" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D25" s="14">
         <v>10.1</v>
@@ -30987,7 +32290,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="34" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D26" s="17">
         <v>10.3</v>
@@ -31070,7 +32373,7 @@
         <v>25</v>
       </c>
       <c r="C27" s="33" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D27" s="14">
         <v>10.3</v>
@@ -31153,7 +32456,7 @@
         <v>26</v>
       </c>
       <c r="C28" s="34" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D28" s="17">
         <v>10.1</v>
@@ -31234,7 +32537,7 @@
         <v>27</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D29" s="14">
         <v>10.199999999999999</v>
@@ -31315,7 +32618,7 @@
         <v>28</v>
       </c>
       <c r="C30" s="34" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D30" s="17">
         <v>10.1</v>
@@ -31396,7 +32699,7 @@
         <v>29</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D31" s="14">
         <v>10.199999999999999</v>
@@ -31479,7 +32782,7 @@
         <v>30</v>
       </c>
       <c r="C32" s="34" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D32" s="17">
         <v>9.9</v>
@@ -31560,7 +32863,7 @@
         <v>31</v>
       </c>
       <c r="C33" s="33" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D33" s="14">
         <v>9.1</v>
@@ -31641,7 +32944,7 @@
         <v>32</v>
       </c>
       <c r="C34" s="34" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D34" s="17">
         <v>9.3000000000000007</v>
@@ -31722,7 +33025,7 @@
         <v>33</v>
       </c>
       <c r="C35" s="33" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D35" s="14">
         <v>9.1999999999999993</v>
@@ -31803,7 +33106,7 @@
         <v>34</v>
       </c>
       <c r="C36" s="34" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D36" s="17">
         <v>9.4</v>
@@ -31876,7 +33179,7 @@
         <v>35</v>
       </c>
       <c r="C37" s="33" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D37" s="14">
         <v>10.199999999999999</v>
@@ -31963,7 +33266,7 @@
         <v>36</v>
       </c>
       <c r="C38" s="34" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D38" s="17">
         <v>10.199999999999999</v>
@@ -32050,7 +33353,7 @@
         <v>37</v>
       </c>
       <c r="C39" s="33" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D39" s="14">
         <v>9.8000000000000007</v>
@@ -32135,7 +33438,7 @@
         <v>38</v>
       </c>
       <c r="C40" s="34" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D40" s="17">
         <v>9.8000000000000007</v>
@@ -32220,7 +33523,7 @@
         <v>39</v>
       </c>
       <c r="C41" s="33" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D41" s="14">
         <v>10.7</v>
@@ -32305,7 +33608,7 @@
         <v>40</v>
       </c>
       <c r="C42" s="34" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D42" s="17">
         <v>10.7</v>
@@ -32390,7 +33693,7 @@
         <v>41</v>
       </c>
       <c r="C43" s="33" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D43" s="14">
         <v>9.9</v>
@@ -32475,7 +33778,7 @@
         <v>42</v>
       </c>
       <c r="C44" s="34" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D44" s="17">
         <v>9.9</v>
@@ -32560,7 +33863,7 @@
         <v>43</v>
       </c>
       <c r="C45" s="33" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D45" s="14">
         <v>9.5</v>
@@ -32645,7 +33948,7 @@
         <v>44</v>
       </c>
       <c r="C46" s="34" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D46" s="17">
         <v>9.3000000000000007</v>
@@ -32730,7 +34033,7 @@
         <v>45</v>
       </c>
       <c r="C47" s="33" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D47" s="14">
         <v>10.4</v>
@@ -32815,7 +34118,7 @@
         <v>46</v>
       </c>
       <c r="C48" s="34" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D48" s="17">
         <v>10.4</v>
@@ -32900,7 +34203,7 @@
         <v>47</v>
       </c>
       <c r="C49" s="33" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D49" s="14">
         <v>10.199999999999999</v>
@@ -32987,7 +34290,7 @@
         <v>48</v>
       </c>
       <c r="C50" s="34" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D50" s="17">
         <v>10.199999999999999</v>
@@ -33074,7 +34377,7 @@
         <v>49</v>
       </c>
       <c r="C51" s="33" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D51" s="14">
         <v>9.5</v>
@@ -33159,7 +34462,7 @@
         <v>50</v>
       </c>
       <c r="C52" s="34" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D52" s="17">
         <v>9.5</v>
@@ -33244,7 +34547,7 @@
         <v>51</v>
       </c>
       <c r="C53" s="33" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D53" s="14">
         <v>11</v>
@@ -33329,7 +34632,7 @@
         <v>52</v>
       </c>
       <c r="C54" s="34" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D54" s="17">
         <v>11</v>
@@ -33414,7 +34717,7 @@
         <v>53</v>
       </c>
       <c r="C55" s="33" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D55" s="14">
         <v>10.6</v>
@@ -33499,7 +34802,7 @@
         <v>54</v>
       </c>
       <c r="C56" s="34" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D56" s="17">
         <v>10.6</v>
@@ -33584,7 +34887,7 @@
         <v>55</v>
       </c>
       <c r="C57" s="33" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D57" s="14">
         <v>10.199999999999999</v>
@@ -33669,7 +34972,7 @@
         <v>56</v>
       </c>
       <c r="C58" s="34" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D58" s="17">
         <v>10.199999999999999</v>
@@ -33754,7 +35057,7 @@
         <v>57</v>
       </c>
       <c r="C59" s="33" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D59" s="14">
         <v>11</v>
@@ -33839,7 +35142,7 @@
         <v>58</v>
       </c>
       <c r="C60" s="34" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D60" s="17">
         <v>11</v>
@@ -33924,7 +35227,7 @@
         <v>59</v>
       </c>
       <c r="C61" s="33" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D61" s="14">
         <v>10.5</v>

--- a/data/prod_parameters/FeedMgmt.xlsx
+++ b/data/prod_parameters/FeedMgmt.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1555" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="519">
   <si>
     <t>f_feed</t>
   </si>
@@ -1224,9 +1224,6 @@
   </si>
   <si>
     <t>Storage and feeding losses</t>
-  </si>
-  <si>
-    <t>100% - pasture utilisation</t>
   </si>
   <si>
     <t>sheep</t>
@@ -1613,6 +1610,15 @@
   <si>
     <t>NIR 2021</t>
   </si>
+  <si>
+    <t>%DM accrding to harvest stat</t>
+  </si>
+  <si>
+    <t>100% - 55% pasture utilisation</t>
+  </si>
+  <si>
+    <t>100% - 50% pasture utilisation</t>
+  </si>
 </sst>
 </file>
 
@@ -1621,7 +1627,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1739,6 +1745,13 @@
     <font>
       <sz val="11"/>
       <color theme="5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.34998626667073579"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1950,7 +1963,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2077,6 +2090,8 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2551,7 +2566,7 @@
       </c>
       <c r="K10" s="22">
         <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F10,'feed pars'!B$6:B$43,0))</f>
-        <v>1.1494252873563218</v>
+        <v>1.1627906976744187</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -2566,7 +2581,7 @@
       </c>
       <c r="K11" s="22">
         <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F11,'feed pars'!B$6:B$43,0))</f>
-        <v>1.1494252873563218</v>
+        <v>1.1627906976744187</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -2596,7 +2611,7 @@
       </c>
       <c r="K13" s="22">
         <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F13,'feed pars'!B$6:B$43,0))</f>
-        <v>1.1494252873563218</v>
+        <v>1.1627906976744187</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -2611,7 +2626,7 @@
       </c>
       <c r="K14" s="22">
         <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F14,'feed pars'!B$6:B$43,0))</f>
-        <v>1.1494252873563218</v>
+        <v>1.1627906976744187</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -2626,7 +2641,7 @@
       </c>
       <c r="K15" s="22">
         <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F15,'feed pars'!B$6:B$43,0))</f>
-        <v>1.4814814814814814</v>
+        <v>1.1627906976744187</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -2641,7 +2656,7 @@
       </c>
       <c r="K16" s="22">
         <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F16,'feed pars'!B$6:B$43,0))</f>
-        <v>1.1494252873563218</v>
+        <v>1.1764705882352942</v>
       </c>
     </row>
     <row r="17" spans="6:13" x14ac:dyDescent="0.25">
@@ -2656,7 +2671,7 @@
       </c>
       <c r="K17" s="22">
         <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F17,'feed pars'!B$6:B$43,0))</f>
-        <v>1.1520737327188941</v>
+        <v>1.1764705882352942</v>
       </c>
     </row>
     <row r="18" spans="6:13" x14ac:dyDescent="0.25">
@@ -2671,7 +2686,7 @@
       </c>
       <c r="K18" s="22">
         <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F18,'feed pars'!B$6:B$43,0))</f>
-        <v>1.0810810810810809</v>
+        <v>1.0989010989010988</v>
       </c>
     </row>
     <row r="19" spans="6:13" x14ac:dyDescent="0.25">
@@ -2686,7 +2701,7 @@
       </c>
       <c r="K19" s="22">
         <f>1/INDEX('feed pars'!C$6:C$43/100,MATCH(F19,'feed pars'!B$6:B$43,0))</f>
-        <v>1.0869565217391304</v>
+        <v>1.0989010989010988</v>
       </c>
     </row>
     <row r="20" spans="6:13" x14ac:dyDescent="0.25">
@@ -3735,7 +3750,7 @@
         <v>28</v>
       </c>
       <c r="M77" s="26" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="N77" t="s">
         <v>394</v>
@@ -3759,7 +3774,7 @@
         <v>28</v>
       </c>
       <c r="M78" s="26" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="N78" t="s">
         <v>394</v>
@@ -3767,7 +3782,7 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F79" t="s">
         <v>306</v>
@@ -3782,7 +3797,7 @@
         <v>28</v>
       </c>
       <c r="M79" s="26" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="N79" t="s">
         <v>394</v>
@@ -3805,7 +3820,7 @@
         <v>28</v>
       </c>
       <c r="M80" s="26" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="N80" t="s">
         <v>394</v>
@@ -3834,7 +3849,7 @@
         <v>28</v>
       </c>
       <c r="M81" s="26" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="N81" t="s">
         <v>394</v>
@@ -3860,7 +3875,7 @@
         <v>28</v>
       </c>
       <c r="M82" s="26" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="N82" t="s">
         <v>394</v>
@@ -3884,7 +3899,7 @@
         <v>28</v>
       </c>
       <c r="M83" s="26" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="N83" t="s">
         <v>394</v>
@@ -3892,7 +3907,7 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F84" t="s">
         <v>306</v>
@@ -4732,7 +4747,7 @@
         <v>28</v>
       </c>
       <c r="M113" s="26" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="N113" s="30"/>
     </row>
@@ -4754,7 +4769,7 @@
         <v>28</v>
       </c>
       <c r="M114" s="26" t="s">
-        <v>396</v>
+        <v>517</v>
       </c>
       <c r="N114" t="s">
         <v>394</v>
@@ -4778,7 +4793,7 @@
         <v>28</v>
       </c>
       <c r="M115" s="26" t="s">
-        <v>396</v>
+        <v>518</v>
       </c>
       <c r="N115" t="s">
         <v>394</v>
@@ -4790,7 +4805,7 @@
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K117" s="3"/>
       <c r="M117" s="26"/>
@@ -4801,7 +4816,7 @@
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -4821,32 +4836,32 @@
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F120" s="3"/>
       <c r="G120" s="3"/>
       <c r="H120" s="3"/>
       <c r="I120" s="3"/>
       <c r="J120" s="3" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="K120" s="3">
         <v>4.5</v>
       </c>
       <c r="L120" s="3" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="M120" s="3"/>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
@@ -4857,13 +4872,13 @@
       <c r="H121" s="3"/>
       <c r="I121" s="3"/>
       <c r="J121" s="3" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="K121" s="3">
         <v>6.5</v>
       </c>
       <c r="L121" s="3" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="M121" s="3"/>
     </row>
@@ -4872,17 +4887,17 @@
         <v>391</v>
       </c>
       <c r="J122" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="K122" s="26">
         <v>18</v>
       </c>
       <c r="L122" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M122" s="3"/>
       <c r="N122" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.25">
@@ -4890,17 +4905,17 @@
         <v>25</v>
       </c>
       <c r="J123" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="K123" s="26">
         <v>1.5</v>
       </c>
       <c r="L123" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M123" s="3"/>
       <c r="N123" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.25">
@@ -4908,17 +4923,17 @@
         <v>385</v>
       </c>
       <c r="J124" t="s">
+        <v>513</v>
+      </c>
+      <c r="K124" s="26">
+        <v>0</v>
+      </c>
+      <c r="L124" t="s">
         <v>514</v>
-      </c>
-      <c r="K124" s="26">
-        <v>0</v>
-      </c>
-      <c r="L124" t="s">
-        <v>515</v>
       </c>
       <c r="M124" s="3"/>
       <c r="N124" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.25">
@@ -4947,7 +4962,7 @@
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A127" s="79" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B127" s="80"/>
       <c r="C127" s="80"/>
@@ -5055,7 +5070,7 @@
       </c>
       <c r="K134" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F134,'feed pars'!B$6:B$43,0))</f>
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M134" s="3"/>
     </row>
@@ -5068,7 +5083,7 @@
       </c>
       <c r="K135" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F135,'feed pars'!B$6:B$43,0))</f>
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M135" s="3"/>
     </row>
@@ -5094,7 +5109,7 @@
       </c>
       <c r="K137" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F137,'feed pars'!B$6:B$43,0))</f>
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M137" s="3"/>
     </row>
@@ -5107,7 +5122,7 @@
       </c>
       <c r="K138" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F138,'feed pars'!B$6:B$43,0))</f>
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M138" s="3"/>
     </row>
@@ -5120,7 +5135,7 @@
       </c>
       <c r="K139" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F139,'feed pars'!B$6:B$43,0))</f>
-        <v>67.5</v>
+        <v>86</v>
       </c>
       <c r="M139" s="3"/>
     </row>
@@ -5133,7 +5148,7 @@
       </c>
       <c r="K140" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F140,'feed pars'!B$6:B$43,0))</f>
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="M140" s="3"/>
     </row>
@@ -5146,7 +5161,7 @@
       </c>
       <c r="K141" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F141,'feed pars'!B$6:B$43,0))</f>
-        <v>86.8</v>
+        <v>85</v>
       </c>
       <c r="M141" s="3"/>
     </row>
@@ -5159,7 +5174,7 @@
       </c>
       <c r="K142" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F142,'feed pars'!B$6:B$43,0))</f>
-        <v>92.5</v>
+        <v>91</v>
       </c>
       <c r="M142" s="3"/>
     </row>
@@ -5172,7 +5187,7 @@
       </c>
       <c r="K143" s="82">
         <f>INDEX('feed pars'!C$6:C$43,MATCH(F143,'feed pars'!B$6:B$43,0))</f>
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="M143" s="3"/>
     </row>
@@ -5466,17 +5481,17 @@
         <v>306</v>
       </c>
       <c r="J166" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K166" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F166,'feed pars'!B$6:B$43,0))</f>
         <v>17.316948400000001</v>
       </c>
       <c r="L166" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="M166" s="26" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="167" spans="6:13" x14ac:dyDescent="0.25">
@@ -5484,7 +5499,7 @@
         <v>307</v>
       </c>
       <c r="J167" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K167" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F167,'feed pars'!B$6:B$43,0))</f>
@@ -5497,7 +5512,7 @@
         <v>308</v>
       </c>
       <c r="J168" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K168" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F168,'feed pars'!B$6:B$43,0))</f>
@@ -5510,7 +5525,7 @@
         <v>2</v>
       </c>
       <c r="J169" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K169" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F169,'feed pars'!B$6:B$43,0))</f>
@@ -5523,7 +5538,7 @@
         <v>12</v>
       </c>
       <c r="J170" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K170" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F170,'feed pars'!B$6:B$43,0))</f>
@@ -5536,7 +5551,7 @@
         <v>33</v>
       </c>
       <c r="J171" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K171" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F171,'feed pars'!B$6:B$43,0))</f>
@@ -5549,7 +5564,7 @@
         <v>17</v>
       </c>
       <c r="J172" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K172" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F172,'feed pars'!B$6:B$43,0))</f>
@@ -5562,7 +5577,7 @@
         <v>37</v>
       </c>
       <c r="J173" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K173" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F173,'feed pars'!B$6:B$43,0))</f>
@@ -5575,7 +5590,7 @@
         <v>38</v>
       </c>
       <c r="J174" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K174" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F174,'feed pars'!B$6:B$43,0))</f>
@@ -5588,7 +5603,7 @@
         <v>39</v>
       </c>
       <c r="J175" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K175" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F175,'feed pars'!B$6:B$43,0))</f>
@@ -5601,7 +5616,7 @@
         <v>313</v>
       </c>
       <c r="J176" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K176" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F176,'feed pars'!B$6:B$43,0))</f>
@@ -5614,7 +5629,7 @@
         <v>40</v>
       </c>
       <c r="J177" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K177" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F177,'feed pars'!B$6:B$43,0))</f>
@@ -5627,7 +5642,7 @@
         <v>41</v>
       </c>
       <c r="J178" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K178" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F178,'feed pars'!B$6:B$43,0))</f>
@@ -5640,7 +5655,7 @@
         <v>42</v>
       </c>
       <c r="J179" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K179" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F179,'feed pars'!B$6:B$43,0))</f>
@@ -5653,7 +5668,7 @@
         <v>35</v>
       </c>
       <c r="J180" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K180" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F180,'feed pars'!B$6:B$43,0))</f>
@@ -5666,7 +5681,7 @@
         <v>43</v>
       </c>
       <c r="J181" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K181" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F181,'feed pars'!B$6:B$43,0))</f>
@@ -5679,7 +5694,7 @@
         <v>310</v>
       </c>
       <c r="J182" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K182" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F182,'feed pars'!B$6:B$43,0))</f>
@@ -5692,7 +5707,7 @@
         <v>302</v>
       </c>
       <c r="J183" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K183" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F183,'feed pars'!B$6:B$43,0))</f>
@@ -5705,7 +5720,7 @@
         <v>314</v>
       </c>
       <c r="J184" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K184" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F184,'feed pars'!B$6:B$43,0))</f>
@@ -5718,7 +5733,7 @@
         <v>44</v>
       </c>
       <c r="J185" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K185" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F185,'feed pars'!B$6:B$43,0))</f>
@@ -5731,7 +5746,7 @@
         <v>45</v>
       </c>
       <c r="J186" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K186" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F186,'feed pars'!B$6:B$43,0))</f>
@@ -5744,7 +5759,7 @@
         <v>36</v>
       </c>
       <c r="J187" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K187" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F187,'feed pars'!B$6:B$43,0))</f>
@@ -5757,7 +5772,7 @@
         <v>46</v>
       </c>
       <c r="J188" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K188" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F188,'feed pars'!B$6:B$43,0))</f>
@@ -5770,7 +5785,7 @@
         <v>47</v>
       </c>
       <c r="J189" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K189" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F189,'feed pars'!B$6:B$43,0))</f>
@@ -5783,7 +5798,7 @@
         <v>315</v>
       </c>
       <c r="J190" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K190" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F190,'feed pars'!B$6:B$43,0))</f>
@@ -5796,7 +5811,7 @@
         <v>48</v>
       </c>
       <c r="J191" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K191" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F191,'feed pars'!B$6:B$43,0))</f>
@@ -5809,7 +5824,7 @@
         <v>49</v>
       </c>
       <c r="J192" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K192" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F192,'feed pars'!B$6:B$43,0))</f>
@@ -5822,7 +5837,7 @@
         <v>50</v>
       </c>
       <c r="J193" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K193" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F193,'feed pars'!B$6:B$43,0))</f>
@@ -5835,7 +5850,7 @@
         <v>51</v>
       </c>
       <c r="J194" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K194" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F194,'feed pars'!B$6:B$43,0))</f>
@@ -5848,7 +5863,7 @@
         <v>309</v>
       </c>
       <c r="J195" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K195" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F195,'feed pars'!B$6:B$43,0))</f>
@@ -5861,7 +5876,7 @@
         <v>384</v>
       </c>
       <c r="J196" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K196" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F196,'feed pars'!B$6:B$43,0))</f>
@@ -5874,7 +5889,7 @@
         <v>52</v>
       </c>
       <c r="J197" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K197" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F197,'feed pars'!B$6:B$43,0))</f>
@@ -5887,7 +5902,7 @@
         <v>53</v>
       </c>
       <c r="J198" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K198" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F198,'feed pars'!B$6:B$43,0))</f>
@@ -5900,7 +5915,7 @@
         <v>54</v>
       </c>
       <c r="J199" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K199" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F199,'feed pars'!B$6:B$43,0))</f>
@@ -5913,7 +5928,7 @@
         <v>55</v>
       </c>
       <c r="J200" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K200" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F200,'feed pars'!B$6:B$43,0))</f>
@@ -5926,7 +5941,7 @@
         <v>56</v>
       </c>
       <c r="J201" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K201" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F201,'feed pars'!B$6:B$43,0))</f>
@@ -5939,7 +5954,7 @@
         <v>57</v>
       </c>
       <c r="J202" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K202" s="25">
         <f>INDEX('feed pars'!D$6:D$43,MATCH(F202,'feed pars'!B$6:B$43,0))</f>
@@ -5952,7 +5967,7 @@
         <v>320</v>
       </c>
       <c r="J203" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K203" s="84">
         <v>0</v>
@@ -5988,14 +6003,14 @@
         <v>18</v>
       </c>
       <c r="K205" s="25">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F205,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!M$6:M$43,MATCH(F205,'feed pars'!B$6:B$43,0))</f>
         <v>11.3</v>
       </c>
       <c r="L205" t="s">
         <v>19</v>
       </c>
       <c r="M205" s="26" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.25">
@@ -6009,7 +6024,7 @@
         <v>18</v>
       </c>
       <c r="K206" s="25">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F206,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!M$6:M$43,MATCH(F206,'feed pars'!B$6:B$43,0))</f>
         <v>10.1</v>
       </c>
       <c r="M206" s="3"/>
@@ -6025,7 +6040,7 @@
         <v>18</v>
       </c>
       <c r="K207" s="25">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F207,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!M$6:M$43,MATCH(F207,'feed pars'!B$6:B$43,0))</f>
         <v>8.5</v>
       </c>
       <c r="M207" s="3"/>
@@ -6041,7 +6056,7 @@
         <v>18</v>
       </c>
       <c r="K208" s="25">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F208,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!M$6:M$43,MATCH(F208,'feed pars'!B$6:B$43,0))</f>
         <v>11</v>
       </c>
     </row>
@@ -6056,7 +6071,7 @@
         <v>18</v>
       </c>
       <c r="K209" s="25">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F209,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!M$6:M$43,MATCH(F209,'feed pars'!B$6:B$43,0))</f>
         <v>9.9416666666666664</v>
       </c>
     </row>
@@ -6071,7 +6086,7 @@
         <v>18</v>
       </c>
       <c r="K210" s="25">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F210,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!M$6:M$43,MATCH(F210,'feed pars'!B$6:B$43,0))</f>
         <v>14.1</v>
       </c>
     </row>
@@ -6086,7 +6101,7 @@
         <v>18</v>
       </c>
       <c r="K211" s="25">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F211,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!M$6:M$43,MATCH(F211,'feed pars'!B$6:B$43,0))</f>
         <v>13.2</v>
       </c>
     </row>
@@ -6101,7 +6116,7 @@
         <v>18</v>
       </c>
       <c r="K212" s="25">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F212,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!M$6:M$43,MATCH(F212,'feed pars'!B$6:B$43,0))</f>
         <v>11.7</v>
       </c>
     </row>
@@ -6116,7 +6131,7 @@
         <v>18</v>
       </c>
       <c r="K213" s="25">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F213,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!M$6:M$43,MATCH(F213,'feed pars'!B$6:B$43,0))</f>
         <v>14</v>
       </c>
     </row>
@@ -6131,7 +6146,7 @@
         <v>18</v>
       </c>
       <c r="K214" s="25">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F214,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!M$6:M$43,MATCH(F214,'feed pars'!B$6:B$43,0))</f>
         <v>13.9</v>
       </c>
     </row>
@@ -6146,7 +6161,7 @@
         <v>18</v>
       </c>
       <c r="K215" s="25">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F215,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!M$6:M$43,MATCH(F215,'feed pars'!B$6:B$43,0))</f>
         <v>12.8</v>
       </c>
     </row>
@@ -6161,7 +6176,7 @@
         <v>18</v>
       </c>
       <c r="K216" s="25">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F216,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!M$6:M$43,MATCH(F216,'feed pars'!B$6:B$43,0))</f>
         <v>13.8</v>
       </c>
     </row>
@@ -6176,7 +6191,7 @@
         <v>18</v>
       </c>
       <c r="K217" s="25">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F217,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!M$6:M$43,MATCH(F217,'feed pars'!B$6:B$43,0))</f>
         <v>13.3</v>
       </c>
     </row>
@@ -6191,7 +6206,7 @@
         <v>18</v>
       </c>
       <c r="K218" s="25">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F218,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!M$6:M$43,MATCH(F218,'feed pars'!B$6:B$43,0))</f>
         <v>22.1</v>
       </c>
     </row>
@@ -6206,7 +6221,7 @@
         <v>18</v>
       </c>
       <c r="K219" s="25">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F219,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!M$6:M$43,MATCH(F219,'feed pars'!B$6:B$43,0))</f>
         <v>20.100000000000001</v>
       </c>
     </row>
@@ -6221,7 +6236,7 @@
         <v>18</v>
       </c>
       <c r="K220" s="25">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F220,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!M$6:M$43,MATCH(F220,'feed pars'!B$6:B$43,0))</f>
         <v>6.6</v>
       </c>
     </row>
@@ -6236,7 +6251,7 @@
         <v>18</v>
       </c>
       <c r="K221" s="25">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F221,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!M$6:M$43,MATCH(F221,'feed pars'!B$6:B$43,0))</f>
         <v>36.6</v>
       </c>
     </row>
@@ -6251,7 +6266,7 @@
         <v>18</v>
       </c>
       <c r="K222" s="25">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F222,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!M$6:M$43,MATCH(F222,'feed pars'!B$6:B$43,0))</f>
         <v>16.399999999999999</v>
       </c>
     </row>
@@ -6266,7 +6281,7 @@
         <v>18</v>
       </c>
       <c r="K223" s="25">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F223,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!M$6:M$43,MATCH(F223,'feed pars'!B$6:B$43,0))</f>
         <v>14.6</v>
       </c>
     </row>
@@ -6281,7 +6296,7 @@
         <v>18</v>
       </c>
       <c r="K224" s="25">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F224,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!M$6:M$43,MATCH(F224,'feed pars'!B$6:B$43,0))</f>
         <v>12.2</v>
       </c>
     </row>
@@ -6296,7 +6311,7 @@
         <v>18</v>
       </c>
       <c r="K225" s="25">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F225,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!M$6:M$43,MATCH(F225,'feed pars'!B$6:B$43,0))</f>
         <v>11.4</v>
       </c>
     </row>
@@ -6311,7 +6326,7 @@
         <v>18</v>
       </c>
       <c r="K226" s="25">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F226,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!M$6:M$43,MATCH(F226,'feed pars'!B$6:B$43,0))</f>
         <v>13.4</v>
       </c>
     </row>
@@ -6326,7 +6341,7 @@
         <v>18</v>
       </c>
       <c r="K227" s="25">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F227,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!M$6:M$43,MATCH(F227,'feed pars'!B$6:B$43,0))</f>
         <v>8.5</v>
       </c>
     </row>
@@ -6341,7 +6356,7 @@
         <v>18</v>
       </c>
       <c r="K228" s="25">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F228,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!M$6:M$43,MATCH(F228,'feed pars'!B$6:B$43,0))</f>
         <v>11</v>
       </c>
     </row>
@@ -6356,7 +6371,7 @@
         <v>18</v>
       </c>
       <c r="K229" s="25">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F229,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!M$6:M$43,MATCH(F229,'feed pars'!B$6:B$43,0))</f>
         <v>13.3</v>
       </c>
     </row>
@@ -6371,7 +6386,7 @@
         <v>18</v>
       </c>
       <c r="K230" s="25">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F230,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!M$6:M$43,MATCH(F230,'feed pars'!B$6:B$43,0))</f>
         <v>11.6</v>
       </c>
     </row>
@@ -6386,7 +6401,7 @@
         <v>18</v>
       </c>
       <c r="K231" s="25">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F231,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!M$6:M$43,MATCH(F231,'feed pars'!B$6:B$43,0))</f>
         <v>12.4</v>
       </c>
     </row>
@@ -6401,7 +6416,7 @@
         <v>18</v>
       </c>
       <c r="K232" s="25">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F232,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!M$6:M$43,MATCH(F232,'feed pars'!B$6:B$43,0))</f>
         <v>12.3</v>
       </c>
     </row>
@@ -6416,7 +6431,7 @@
         <v>18</v>
       </c>
       <c r="K233" s="25">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F233,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!M$6:M$43,MATCH(F233,'feed pars'!B$6:B$43,0))</f>
         <v>13.6</v>
       </c>
     </row>
@@ -6431,7 +6446,7 @@
         <v>18</v>
       </c>
       <c r="K234" s="25">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F234,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!M$6:M$43,MATCH(F234,'feed pars'!B$6:B$43,0))</f>
         <v>15.5</v>
       </c>
     </row>
@@ -6457,17 +6472,17 @@
         <v>306</v>
       </c>
       <c r="J236" t="s">
+        <v>498</v>
+      </c>
+      <c r="K236" s="82">
+        <f>INDEX('feed pars'!O$6:O$43,MATCH(F236,'feed pars'!B$6:B$43,0))</f>
+        <v>20</v>
+      </c>
+      <c r="L236" t="s">
         <v>499</v>
       </c>
-      <c r="K236" s="82">
-        <f>INDEX('feed pars'!N$6:N$43,MATCH(F236,'feed pars'!B$6:B$43,0))</f>
-        <v>20</v>
-      </c>
-      <c r="L236" t="s">
-        <v>500</v>
-      </c>
       <c r="M236" s="26" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="237" spans="1:13" x14ac:dyDescent="0.25">
@@ -6478,10 +6493,10 @@
         <v>307</v>
       </c>
       <c r="J237" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K237" s="82">
-        <f>INDEX('feed pars'!N$6:N$43,MATCH(F237,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!O$6:O$43,MATCH(F237,'feed pars'!B$6:B$43,0))</f>
         <v>20</v>
       </c>
       <c r="M237" s="3"/>
@@ -6494,10 +6509,10 @@
         <v>308</v>
       </c>
       <c r="J238" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K238" s="82">
-        <f>INDEX('feed pars'!N$6:N$43,MATCH(F238,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!O$6:O$43,MATCH(F238,'feed pars'!B$6:B$43,0))</f>
         <v>22.5</v>
       </c>
       <c r="M238" s="3"/>
@@ -6510,10 +6525,10 @@
         <v>12</v>
       </c>
       <c r="J239" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K239" s="82">
-        <f>INDEX('feed pars'!N$6:N$43,MATCH(F239,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!O$6:O$43,MATCH(F239,'feed pars'!B$6:B$43,0))</f>
         <v>30</v>
       </c>
     </row>
@@ -6525,10 +6540,10 @@
         <v>33</v>
       </c>
       <c r="J240" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K240" s="82">
-        <f>INDEX('feed pars'!N$6:N$43,MATCH(F240,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!O$6:O$43,MATCH(F240,'feed pars'!B$6:B$43,0))</f>
         <v>20</v>
       </c>
     </row>
@@ -6540,10 +6555,10 @@
         <v>17</v>
       </c>
       <c r="J241" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K241" s="82">
-        <f>INDEX('feed pars'!N$6:N$43,MATCH(F241,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!O$6:O$43,MATCH(F241,'feed pars'!B$6:B$43,0))</f>
         <v>25</v>
       </c>
     </row>
@@ -6555,10 +6570,10 @@
         <v>37</v>
       </c>
       <c r="J242" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K242" s="82">
-        <f>INDEX('feed pars'!N$6:N$43,MATCH(F242,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!O$6:O$43,MATCH(F242,'feed pars'!B$6:B$43,0))</f>
         <v>27</v>
       </c>
     </row>
@@ -6570,10 +6585,10 @@
         <v>38</v>
       </c>
       <c r="J243" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K243" s="82">
-        <f>INDEX('feed pars'!N$6:N$43,MATCH(F243,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!O$6:O$43,MATCH(F243,'feed pars'!B$6:B$43,0))</f>
         <v>61</v>
       </c>
     </row>
@@ -6585,10 +6600,10 @@
         <v>39</v>
       </c>
       <c r="J244" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K244" s="82">
-        <f>INDEX('feed pars'!N$6:N$43,MATCH(F244,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!O$6:O$43,MATCH(F244,'feed pars'!B$6:B$43,0))</f>
         <v>26</v>
       </c>
     </row>
@@ -6600,10 +6615,10 @@
         <v>313</v>
       </c>
       <c r="J245" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K245" s="82">
-        <f>INDEX('feed pars'!N$6:N$43,MATCH(F245,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!O$6:O$43,MATCH(F245,'feed pars'!B$6:B$43,0))</f>
         <v>20</v>
       </c>
     </row>
@@ -6615,10 +6630,10 @@
         <v>40</v>
       </c>
       <c r="J246" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K246" s="82">
-        <f>INDEX('feed pars'!N$6:N$43,MATCH(F246,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!O$6:O$43,MATCH(F246,'feed pars'!B$6:B$43,0))</f>
         <v>40</v>
       </c>
     </row>
@@ -6630,10 +6645,10 @@
         <v>41</v>
       </c>
       <c r="J247" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K247" s="82">
-        <f>INDEX('feed pars'!N$6:N$43,MATCH(F247,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!O$6:O$43,MATCH(F247,'feed pars'!B$6:B$43,0))</f>
         <v>17</v>
       </c>
     </row>
@@ -6645,10 +6660,10 @@
         <v>42</v>
       </c>
       <c r="J248" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K248" s="82">
-        <f>INDEX('feed pars'!N$6:N$43,MATCH(F248,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!O$6:O$43,MATCH(F248,'feed pars'!B$6:B$43,0))</f>
         <v>14</v>
       </c>
     </row>
@@ -6660,10 +6675,10 @@
         <v>35</v>
       </c>
       <c r="J249" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K249" s="82">
-        <f>INDEX('feed pars'!N$6:N$43,MATCH(F249,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!O$6:O$43,MATCH(F249,'feed pars'!B$6:B$43,0))</f>
         <v>460</v>
       </c>
     </row>
@@ -6675,10 +6690,10 @@
         <v>43</v>
       </c>
       <c r="J250" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K250" s="82">
-        <f>INDEX('feed pars'!N$6:N$43,MATCH(F250,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!O$6:O$43,MATCH(F250,'feed pars'!B$6:B$43,0))</f>
         <v>380</v>
       </c>
     </row>
@@ -6690,10 +6705,10 @@
         <v>302</v>
       </c>
       <c r="J251" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K251" s="82">
-        <f>INDEX('feed pars'!N$6:N$43,MATCH(F251,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!O$6:O$43,MATCH(F251,'feed pars'!B$6:B$43,0))</f>
         <v>20</v>
       </c>
     </row>
@@ -6705,10 +6720,10 @@
         <v>310</v>
       </c>
       <c r="J252" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K252" s="82">
-        <f>INDEX('feed pars'!N$6:N$43,MATCH(F252,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!O$6:O$43,MATCH(F252,'feed pars'!B$6:B$43,0))</f>
         <v>1000</v>
       </c>
     </row>
@@ -6720,10 +6735,10 @@
         <v>314</v>
       </c>
       <c r="J253" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K253" s="82">
-        <f>INDEX('feed pars'!N$6:N$43,MATCH(F253,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!O$6:O$43,MATCH(F253,'feed pars'!B$6:B$43,0))</f>
         <v>180</v>
       </c>
     </row>
@@ -6735,10 +6750,10 @@
         <v>44</v>
       </c>
       <c r="J254" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K254" s="82">
-        <f>INDEX('feed pars'!N$6:N$43,MATCH(F254,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!O$6:O$43,MATCH(F254,'feed pars'!B$6:B$43,0))</f>
         <v>10</v>
       </c>
     </row>
@@ -6750,10 +6765,10 @@
         <v>36</v>
       </c>
       <c r="J255" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K255" s="82">
-        <f>INDEX('feed pars'!N$6:N$43,MATCH(F255,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!O$6:O$43,MATCH(F255,'feed pars'!B$6:B$43,0))</f>
         <v>46</v>
       </c>
     </row>
@@ -6765,10 +6780,10 @@
         <v>46</v>
       </c>
       <c r="J256" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K256" s="82">
-        <f>INDEX('feed pars'!N$6:N$43,MATCH(F256,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!O$6:O$43,MATCH(F256,'feed pars'!B$6:B$43,0))</f>
         <v>10</v>
       </c>
     </row>
@@ -6780,10 +6795,10 @@
         <v>47</v>
       </c>
       <c r="J257" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K257" s="82">
-        <f>INDEX('feed pars'!N$6:N$43,MATCH(F257,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!O$6:O$43,MATCH(F257,'feed pars'!B$6:B$43,0))</f>
         <v>97</v>
       </c>
     </row>
@@ -6795,10 +6810,10 @@
         <v>315</v>
       </c>
       <c r="J258" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K258" s="82">
-        <f>INDEX('feed pars'!N$6:N$43,MATCH(F258,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!O$6:O$43,MATCH(F258,'feed pars'!B$6:B$43,0))</f>
         <v>27</v>
       </c>
     </row>
@@ -6810,10 +6825,10 @@
         <v>48</v>
       </c>
       <c r="J259" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K259" s="82">
-        <f>INDEX('feed pars'!N$6:N$43,MATCH(F259,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!O$6:O$43,MATCH(F259,'feed pars'!B$6:B$43,0))</f>
         <v>45</v>
       </c>
     </row>
@@ -6825,10 +6840,10 @@
         <v>50</v>
       </c>
       <c r="J260" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K260" s="82">
-        <f>INDEX('feed pars'!N$6:N$43,MATCH(F260,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!O$6:O$43,MATCH(F260,'feed pars'!B$6:B$43,0))</f>
         <v>45</v>
       </c>
     </row>
@@ -6840,10 +6855,10 @@
         <v>309</v>
       </c>
       <c r="J261" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K261" s="82">
-        <f>INDEX('feed pars'!N$6:N$43,MATCH(F261,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!O$6:O$43,MATCH(F261,'feed pars'!B$6:B$43,0))</f>
         <v>80</v>
       </c>
     </row>
@@ -6855,10 +6870,10 @@
         <v>52</v>
       </c>
       <c r="J262" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K262" s="82">
-        <f>INDEX('feed pars'!N$6:N$43,MATCH(F262,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!O$6:O$43,MATCH(F262,'feed pars'!B$6:B$43,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -6870,10 +6885,10 @@
         <v>53</v>
       </c>
       <c r="J263" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K263" s="82">
-        <f>INDEX('feed pars'!N$6:N$43,MATCH(F263,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!O$6:O$43,MATCH(F263,'feed pars'!B$6:B$43,0))</f>
         <v>32</v>
       </c>
     </row>
@@ -6885,10 +6900,10 @@
         <v>54</v>
       </c>
       <c r="J264" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K264" s="82">
-        <f>INDEX('feed pars'!N$6:N$43,MATCH(F264,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!O$6:O$43,MATCH(F264,'feed pars'!B$6:B$43,0))</f>
         <v>10</v>
       </c>
     </row>
@@ -6900,10 +6915,10 @@
         <v>56</v>
       </c>
       <c r="J265" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K265" s="82">
-        <f>INDEX('feed pars'!N$6:N$43,MATCH(F265,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!O$6:O$43,MATCH(F265,'feed pars'!B$6:B$43,0))</f>
         <v>33</v>
       </c>
     </row>
@@ -6915,7 +6930,7 @@
         <v>320</v>
       </c>
       <c r="J266" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K266" s="3">
         <v>0</v>
@@ -6923,7 +6938,7 @@
     </row>
     <row r="267" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A267" s="7" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B267" s="7"/>
       <c r="C267" s="6"/>
@@ -6950,14 +6965,14 @@
         <v>18</v>
       </c>
       <c r="K268" s="25">
-        <f>INDEX('feed pars'!L$6:L$43,MATCH(F268,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!M$6:M$43,MATCH(F268,'feed pars'!B$6:B$43,0))</f>
         <v>9.1</v>
       </c>
       <c r="L268" t="s">
         <v>19</v>
       </c>
       <c r="M268" s="26" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="269" spans="1:14" x14ac:dyDescent="0.25">
@@ -7181,14 +7196,14 @@
         <v>18</v>
       </c>
       <c r="K284" s="25">
-        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F284,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AB$6:AB$43,MATCH(F284,'feed pars'!B$6:B$43,0))</f>
         <v>12.3</v>
       </c>
       <c r="L284" t="s">
         <v>297</v>
       </c>
       <c r="M284" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="285" spans="1:14" x14ac:dyDescent="0.25">
@@ -7205,7 +7220,7 @@
         <v>18</v>
       </c>
       <c r="K285" s="25">
-        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F285,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AB$6:AB$43,MATCH(F285,'feed pars'!B$6:B$43,0))</f>
         <v>11.2</v>
       </c>
     </row>
@@ -7223,7 +7238,7 @@
         <v>18</v>
       </c>
       <c r="K286" s="25">
-        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F286,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AB$6:AB$43,MATCH(F286,'feed pars'!B$6:B$43,0))</f>
         <v>9.4</v>
       </c>
     </row>
@@ -7241,7 +7256,7 @@
         <v>18</v>
       </c>
       <c r="K287" s="25">
-        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F287,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AB$6:AB$43,MATCH(F287,'feed pars'!B$6:B$43,0))</f>
         <v>12</v>
       </c>
     </row>
@@ -7259,7 +7274,7 @@
         <v>18</v>
       </c>
       <c r="K288" s="25">
-        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F288,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AB$6:AB$43,MATCH(F288,'feed pars'!B$6:B$43,0))</f>
         <v>13.2</v>
       </c>
     </row>
@@ -7277,7 +7292,7 @@
         <v>18</v>
       </c>
       <c r="K289" s="25">
-        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F289,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AB$6:AB$43,MATCH(F289,'feed pars'!B$6:B$43,0))</f>
         <v>11.5</v>
       </c>
     </row>
@@ -7295,7 +7310,7 @@
         <v>18</v>
       </c>
       <c r="K290" s="25">
-        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F290,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AB$6:AB$43,MATCH(F290,'feed pars'!B$6:B$43,0))</f>
         <v>10.9</v>
       </c>
     </row>
@@ -7313,7 +7328,7 @@
         <v>18</v>
       </c>
       <c r="K291" s="25">
-        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F291,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AB$6:AB$43,MATCH(F291,'feed pars'!B$6:B$43,0))</f>
         <v>18.5</v>
       </c>
     </row>
@@ -7331,7 +7346,7 @@
         <v>18</v>
       </c>
       <c r="K292" s="25">
-        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F292,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AB$6:AB$43,MATCH(F292,'feed pars'!B$6:B$43,0))</f>
         <v>17.5</v>
       </c>
     </row>
@@ -7349,7 +7364,7 @@
         <v>18</v>
       </c>
       <c r="K293" s="25">
-        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F293,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AB$6:AB$43,MATCH(F293,'feed pars'!B$6:B$43,0))</f>
         <v>29.8</v>
       </c>
     </row>
@@ -7367,7 +7382,7 @@
         <v>18</v>
       </c>
       <c r="K294" s="25">
-        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F294,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AB$6:AB$43,MATCH(F294,'feed pars'!B$6:B$43,0))</f>
         <v>9.9</v>
       </c>
     </row>
@@ -7385,7 +7400,7 @@
         <v>18</v>
       </c>
       <c r="K295" s="25">
-        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F295,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AB$6:AB$43,MATCH(F295,'feed pars'!B$6:B$43,0))</f>
         <v>10.3</v>
       </c>
     </row>
@@ -7403,7 +7418,7 @@
         <v>18</v>
       </c>
       <c r="K296" s="25">
-        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F296,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AB$6:AB$43,MATCH(F296,'feed pars'!B$6:B$43,0))</f>
         <v>7.7</v>
       </c>
     </row>
@@ -7421,7 +7436,7 @@
         <v>18</v>
       </c>
       <c r="K297" s="25">
-        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F297,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AB$6:AB$43,MATCH(F297,'feed pars'!B$6:B$43,0))</f>
         <v>6.5</v>
       </c>
     </row>
@@ -7439,7 +7454,7 @@
         <v>18</v>
       </c>
       <c r="K298" s="25">
-        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F298,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AB$6:AB$43,MATCH(F298,'feed pars'!B$6:B$43,0))</f>
         <v>6.2</v>
       </c>
     </row>
@@ -7457,7 +7472,7 @@
         <v>18</v>
       </c>
       <c r="K299" s="25">
-        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F299,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AB$6:AB$43,MATCH(F299,'feed pars'!B$6:B$43,0))</f>
         <v>7.8</v>
       </c>
     </row>
@@ -7475,7 +7490,7 @@
         <v>18</v>
       </c>
       <c r="K300" s="25">
-        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F300,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AB$6:AB$43,MATCH(F300,'feed pars'!B$6:B$43,0))</f>
         <v>9.1999999999999993</v>
       </c>
     </row>
@@ -7493,7 +7508,7 @@
         <v>18</v>
       </c>
       <c r="K301" s="25">
-        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F301,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AB$6:AB$43,MATCH(F301,'feed pars'!B$6:B$43,0))</f>
         <v>8.6999999999999993</v>
       </c>
     </row>
@@ -7511,7 +7526,7 @@
         <v>18</v>
       </c>
       <c r="K302" s="25">
-        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F302,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AB$6:AB$43,MATCH(F302,'feed pars'!B$6:B$43,0))</f>
         <v>8.9</v>
       </c>
     </row>
@@ -7529,7 +7544,7 @@
         <v>18</v>
       </c>
       <c r="K303" s="25">
-        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F303,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AB$6:AB$43,MATCH(F303,'feed pars'!B$6:B$43,0))</f>
         <v>7.0888888888888877</v>
       </c>
     </row>
@@ -7547,7 +7562,7 @@
         <v>18</v>
       </c>
       <c r="K304" s="25">
-        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F304,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AB$6:AB$43,MATCH(F304,'feed pars'!B$6:B$43,0))</f>
         <v>9</v>
       </c>
     </row>
@@ -7565,7 +7580,7 @@
         <v>18</v>
       </c>
       <c r="K305" s="25">
-        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F305,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AB$6:AB$43,MATCH(F305,'feed pars'!B$6:B$43,0))</f>
         <v>8</v>
       </c>
     </row>
@@ -7583,7 +7598,7 @@
         <v>18</v>
       </c>
       <c r="K306" s="25">
-        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F306,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AB$6:AB$43,MATCH(F306,'feed pars'!B$6:B$43,0))</f>
         <v>12.2</v>
       </c>
     </row>
@@ -7601,7 +7616,7 @@
         <v>18</v>
       </c>
       <c r="K307" s="25">
-        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F307,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AB$6:AB$43,MATCH(F307,'feed pars'!B$6:B$43,0))</f>
         <v>12.2</v>
       </c>
     </row>
@@ -7619,7 +7634,7 @@
         <v>18</v>
       </c>
       <c r="K308" s="25">
-        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F308,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AB$6:AB$43,MATCH(F308,'feed pars'!B$6:B$43,0))</f>
         <v>11.3</v>
       </c>
     </row>
@@ -7637,7 +7652,7 @@
         <v>18</v>
       </c>
       <c r="K309" s="25">
-        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F309,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AB$6:AB$43,MATCH(F309,'feed pars'!B$6:B$43,0))</f>
         <v>10.8</v>
       </c>
     </row>
@@ -7670,14 +7685,14 @@
         <v>18</v>
       </c>
       <c r="K311" s="25">
-        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F311,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F311,'feed pars'!B$6:B$43,0))</f>
         <v>12.1</v>
       </c>
       <c r="L311" t="s">
         <v>22</v>
       </c>
       <c r="M311" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="312" spans="1:14" x14ac:dyDescent="0.25">
@@ -7691,7 +7706,7 @@
         <v>18</v>
       </c>
       <c r="K312" s="25">
-        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F312,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F312,'feed pars'!B$6:B$43,0))</f>
         <v>11</v>
       </c>
     </row>
@@ -7706,7 +7721,7 @@
         <v>18</v>
       </c>
       <c r="K313" s="25">
-        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F313,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F313,'feed pars'!B$6:B$43,0))</f>
         <v>9</v>
       </c>
     </row>
@@ -7721,7 +7736,7 @@
         <v>18</v>
       </c>
       <c r="K314" s="25">
-        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F314,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F314,'feed pars'!B$6:B$43,0))</f>
         <v>11.9</v>
       </c>
     </row>
@@ -7736,7 +7751,7 @@
         <v>18</v>
       </c>
       <c r="K315" s="25">
-        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F315,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F315,'feed pars'!B$6:B$43,0))</f>
         <v>12.8</v>
       </c>
     </row>
@@ -7751,7 +7766,7 @@
         <v>18</v>
       </c>
       <c r="K316" s="25">
-        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F316,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F316,'feed pars'!B$6:B$43,0))</f>
         <v>11.2</v>
       </c>
     </row>
@@ -7766,7 +7781,7 @@
         <v>18</v>
       </c>
       <c r="K317" s="25">
-        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F317,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F317,'feed pars'!B$6:B$43,0))</f>
         <v>10.7</v>
       </c>
     </row>
@@ -7781,7 +7796,7 @@
         <v>18</v>
       </c>
       <c r="K318" s="25">
-        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F318,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F318,'feed pars'!B$6:B$43,0))</f>
         <v>18</v>
       </c>
     </row>
@@ -7796,7 +7811,7 @@
         <v>18</v>
       </c>
       <c r="K319" s="25">
-        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F319,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F319,'feed pars'!B$6:B$43,0))</f>
         <v>17.3</v>
       </c>
     </row>
@@ -7811,7 +7826,7 @@
         <v>18</v>
       </c>
       <c r="K320" s="25">
-        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F320,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F320,'feed pars'!B$6:B$43,0))</f>
         <v>29.8</v>
       </c>
     </row>
@@ -7826,7 +7841,7 @@
         <v>18</v>
       </c>
       <c r="K321" s="25">
-        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F321,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F321,'feed pars'!B$6:B$43,0))</f>
         <v>9.3000000000000007</v>
       </c>
     </row>
@@ -7841,7 +7856,7 @@
         <v>18</v>
       </c>
       <c r="K322" s="25">
-        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F322,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F322,'feed pars'!B$6:B$43,0))</f>
         <v>9.6999999999999993</v>
       </c>
     </row>
@@ -7856,7 +7871,7 @@
         <v>18</v>
       </c>
       <c r="K323" s="25">
-        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F323,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F323,'feed pars'!B$6:B$43,0))</f>
         <v>7.1</v>
       </c>
     </row>
@@ -7871,7 +7886,7 @@
         <v>18</v>
       </c>
       <c r="K324" s="25">
-        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F324,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F324,'feed pars'!B$6:B$43,0))</f>
         <v>5.9</v>
       </c>
     </row>
@@ -7886,7 +7901,7 @@
         <v>18</v>
       </c>
       <c r="K325" s="25">
-        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F325,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F325,'feed pars'!B$6:B$43,0))</f>
         <v>5.4</v>
       </c>
     </row>
@@ -7901,7 +7916,7 @@
         <v>18</v>
       </c>
       <c r="K326" s="25">
-        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F326,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F326,'feed pars'!B$6:B$43,0))</f>
         <v>7.2</v>
       </c>
     </row>
@@ -7916,7 +7931,7 @@
         <v>18</v>
       </c>
       <c r="K327" s="25">
-        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F327,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F327,'feed pars'!B$6:B$43,0))</f>
         <v>8.6999999999999993</v>
       </c>
     </row>
@@ -7931,7 +7946,7 @@
         <v>18</v>
       </c>
       <c r="K328" s="25">
-        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F328,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F328,'feed pars'!B$6:B$43,0))</f>
         <v>8.1</v>
       </c>
     </row>
@@ -7946,7 +7961,7 @@
         <v>18</v>
       </c>
       <c r="K329" s="25">
-        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F329,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F329,'feed pars'!B$6:B$43,0))</f>
         <v>8.1999999999999993</v>
       </c>
     </row>
@@ -7961,7 +7976,7 @@
         <v>18</v>
       </c>
       <c r="K330" s="25">
-        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F330,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F330,'feed pars'!B$6:B$43,0))</f>
         <v>6.6</v>
       </c>
     </row>
@@ -7976,7 +7991,7 @@
         <v>18</v>
       </c>
       <c r="K331" s="25">
-        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F331,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F331,'feed pars'!B$6:B$43,0))</f>
         <v>8.6999999999999993</v>
       </c>
     </row>
@@ -7991,7 +8006,7 @@
         <v>18</v>
       </c>
       <c r="K332" s="25">
-        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F332,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F332,'feed pars'!B$6:B$43,0))</f>
         <v>6.9</v>
       </c>
     </row>
@@ -8006,7 +8021,7 @@
         <v>18</v>
       </c>
       <c r="K333" s="25">
-        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F333,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F333,'feed pars'!B$6:B$43,0))</f>
         <v>12.4</v>
       </c>
     </row>
@@ -8021,7 +8036,7 @@
         <v>18</v>
       </c>
       <c r="K334" s="25">
-        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F334,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F334,'feed pars'!B$6:B$43,0))</f>
         <v>12.4</v>
       </c>
     </row>
@@ -8036,7 +8051,7 @@
         <v>18</v>
       </c>
       <c r="K335" s="25">
-        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F335,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F335,'feed pars'!B$6:B$43,0))</f>
         <v>11.1</v>
       </c>
     </row>
@@ -8051,7 +8066,7 @@
         <v>18</v>
       </c>
       <c r="K336" s="25">
-        <f>INDEX('feed pars'!Z$6:Z$43,MATCH(F336,'feed pars'!B$6:B$43,0))</f>
+        <f>INDEX('feed pars'!AA$6:AA$43,MATCH(F336,'feed pars'!B$6:B$43,0))</f>
         <v>10.8</v>
       </c>
     </row>
@@ -8063,17 +8078,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:AM46"/>
+  <dimension ref="B1:AN46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="7.5703125" customWidth="1"/>
-    <col min="23" max="23" width="7.5703125" customWidth="1"/>
+    <col min="3" max="9" width="7.5703125" customWidth="1"/>
+    <col min="24" max="24" width="7.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C1" s="11" t="s">
         <v>118</v>
@@ -8083,9 +8098,10 @@
       <c r="F1" s="11"/>
       <c r="G1" s="11"/>
       <c r="H1" s="11"/>
-      <c r="W1" s="11"/>
-    </row>
-    <row r="3" spans="2:39" x14ac:dyDescent="0.25">
+      <c r="I1" s="11"/>
+      <c r="X1" s="11"/>
+    </row>
+    <row r="3" spans="2:40" x14ac:dyDescent="0.25">
       <c r="C3" s="62" t="s">
         <v>303</v>
       </c>
@@ -8093,129 +8109,129 @@
       <c r="E3" s="63"/>
       <c r="F3" s="63"/>
       <c r="G3" s="63"/>
-      <c r="I3" s="62" t="s">
-        <v>488</v>
-      </c>
-      <c r="J3" s="63"/>
+      <c r="J3" s="62" t="s">
+        <v>487</v>
+      </c>
       <c r="K3" s="63"/>
       <c r="L3" s="63"/>
       <c r="M3" s="63"/>
       <c r="N3" s="63"/>
       <c r="O3" s="63"/>
       <c r="P3" s="63"/>
-      <c r="Q3" s="89" t="s">
-        <v>508</v>
-      </c>
-      <c r="R3" s="63">
+      <c r="Q3" s="63"/>
+      <c r="R3" s="89" t="s">
+        <v>507</v>
+      </c>
+      <c r="S3" s="63">
         <f>1/6.25</f>
         <v>0.16</v>
       </c>
-      <c r="S3" s="63"/>
       <c r="T3" s="63"/>
-      <c r="W3" s="62" t="s">
+      <c r="U3" s="63"/>
+      <c r="X3" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="X3" s="63"/>
       <c r="Y3" s="63"/>
       <c r="Z3" s="63"/>
       <c r="AA3" s="63"/>
       <c r="AB3" s="63"/>
       <c r="AC3" s="63"/>
       <c r="AD3" s="63"/>
-      <c r="AE3" s="89" t="s">
-        <v>508</v>
-      </c>
-      <c r="AF3" s="63">
+      <c r="AE3" s="63"/>
+      <c r="AF3" s="89" t="s">
+        <v>507</v>
+      </c>
+      <c r="AG3" s="63">
         <f>1/6.25</f>
         <v>0.16</v>
       </c>
-      <c r="AG3" s="63"/>
       <c r="AH3" s="63"/>
-      <c r="AK3" s="62" t="s">
+      <c r="AI3" s="63"/>
+      <c r="AL3" s="62" t="s">
         <v>385</v>
       </c>
-      <c r="AL3" s="63"/>
-    </row>
-    <row r="4" spans="2:39" x14ac:dyDescent="0.25">
+      <c r="AM3" s="63"/>
+    </row>
+    <row r="4" spans="2:40" x14ac:dyDescent="0.25">
       <c r="C4" s="61"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
-      <c r="I4" s="68" t="s">
+      <c r="J4" s="68" t="s">
         <v>294</v>
       </c>
-      <c r="J4" s="69">
+      <c r="K4" s="69">
         <v>1</v>
       </c>
-      <c r="K4" s="69"/>
-      <c r="L4" s="69">
+      <c r="L4" s="69"/>
+      <c r="M4" s="69">
         <v>2</v>
       </c>
-      <c r="M4" s="69">
+      <c r="N4" s="69">
         <v>7</v>
       </c>
-      <c r="N4" s="69">
+      <c r="O4" s="69">
         <v>8</v>
       </c>
-      <c r="O4" s="69">
+      <c r="P4" s="69">
         <v>9</v>
       </c>
-      <c r="P4" s="69">
+      <c r="Q4" s="69">
         <v>11</v>
       </c>
-      <c r="Q4" s="69">
+      <c r="R4" s="69">
         <v>10</v>
       </c>
-      <c r="R4" s="69"/>
-      <c r="S4" s="69">
+      <c r="S4" s="69"/>
+      <c r="T4" s="69">
         <v>26</v>
       </c>
-      <c r="T4" s="69">
+      <c r="U4" s="69">
         <v>28</v>
       </c>
-      <c r="U4" s="4"/>
       <c r="V4" s="4"/>
-      <c r="W4" s="68" t="s">
+      <c r="W4" s="4"/>
+      <c r="X4" s="68" t="s">
         <v>294</v>
       </c>
-      <c r="X4" s="69">
+      <c r="Y4" s="69">
         <v>1</v>
       </c>
-      <c r="Y4" s="69"/>
-      <c r="Z4" s="69">
+      <c r="Z4" s="69"/>
+      <c r="AA4" s="69">
         <v>2</v>
       </c>
-      <c r="AA4" s="69">
+      <c r="AB4" s="69">
         <v>3</v>
       </c>
-      <c r="AB4" s="69">
+      <c r="AC4" s="69">
         <v>5</v>
       </c>
-      <c r="AC4" s="69">
+      <c r="AD4" s="69">
         <v>6</v>
       </c>
-      <c r="AD4" s="69"/>
-      <c r="AE4" s="69">
+      <c r="AE4" s="69"/>
+      <c r="AF4" s="69">
         <v>12</v>
       </c>
-      <c r="AF4" s="69"/>
-      <c r="AG4" s="69">
+      <c r="AG4" s="69"/>
+      <c r="AH4" s="69">
         <v>29</v>
       </c>
-      <c r="AH4" s="69">
+      <c r="AI4" s="69">
         <v>31</v>
       </c>
-      <c r="AI4" s="4"/>
       <c r="AJ4" s="4"/>
-      <c r="AK4" s="68" t="s">
+      <c r="AK4" s="4"/>
+      <c r="AL4" s="68" t="s">
         <v>294</v>
       </c>
-      <c r="AL4" s="69">
+      <c r="AM4" s="69">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>58</v>
       </c>
@@ -8223,186 +8239,189 @@
         <v>59</v>
       </c>
       <c r="D5" s="73" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E5" s="72" t="s">
+        <v>504</v>
+      </c>
+      <c r="F5" s="72" t="s">
         <v>505</v>
       </c>
-      <c r="F5" s="72" t="s">
+      <c r="G5" s="73" t="s">
         <v>506</v>
       </c>
-      <c r="G5" s="73" t="s">
-        <v>507</v>
-      </c>
-      <c r="I5" s="68" t="s">
+      <c r="H5" s="75" t="s">
+        <v>490</v>
+      </c>
+      <c r="J5" s="68" t="s">
         <v>295</v>
       </c>
-      <c r="J5" s="71" t="s">
+      <c r="K5" s="71" t="s">
         <v>59</v>
-      </c>
-      <c r="K5" s="72" t="s">
-        <v>494</v>
       </c>
       <c r="L5" s="72" t="s">
         <v>493</v>
       </c>
-      <c r="M5" s="71" t="s">
+      <c r="M5" s="72" t="s">
+        <v>492</v>
+      </c>
+      <c r="N5" s="71" t="s">
+        <v>408</v>
+      </c>
+      <c r="O5" s="72" t="s">
         <v>409</v>
       </c>
-      <c r="N5" s="72" t="s">
+      <c r="P5" s="72" t="s">
         <v>410</v>
       </c>
-      <c r="O5" s="72" t="s">
-        <v>411</v>
-      </c>
-      <c r="P5" s="72" t="s">
+      <c r="Q5" s="72" t="s">
         <v>282</v>
       </c>
-      <c r="Q5" s="73" t="s">
-        <v>486</v>
-      </c>
-      <c r="R5" s="72" t="s">
+      <c r="R5" s="73" t="s">
+        <v>485</v>
+      </c>
+      <c r="S5" s="72" t="s">
+        <v>504</v>
+      </c>
+      <c r="T5" s="72" t="s">
         <v>505</v>
       </c>
-      <c r="S5" s="72" t="s">
+      <c r="U5" s="73" t="s">
         <v>506</v>
       </c>
-      <c r="T5" s="73" t="s">
-        <v>507</v>
-      </c>
-      <c r="U5" s="75" t="s">
+      <c r="V5" s="75" t="s">
+        <v>490</v>
+      </c>
+      <c r="X5" s="68" t="s">
+        <v>295</v>
+      </c>
+      <c r="Y5" s="71" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z5" s="72" t="s">
+        <v>493</v>
+      </c>
+      <c r="AA5" s="72" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB5" s="72" t="s">
+        <v>120</v>
+      </c>
+      <c r="AC5" s="71" t="s">
+        <v>408</v>
+      </c>
+      <c r="AD5" s="72" t="s">
+        <v>409</v>
+      </c>
+      <c r="AE5" s="72" t="s">
         <v>491</v>
       </c>
-      <c r="W5" s="68" t="s">
+      <c r="AF5" s="73" t="s">
+        <v>485</v>
+      </c>
+      <c r="AG5" s="72" t="s">
+        <v>504</v>
+      </c>
+      <c r="AH5" s="72" t="s">
+        <v>505</v>
+      </c>
+      <c r="AI5" s="73" t="s">
+        <v>506</v>
+      </c>
+      <c r="AJ5" s="75" t="s">
+        <v>490</v>
+      </c>
+      <c r="AK5" s="4"/>
+      <c r="AL5" s="68" t="s">
         <v>295</v>
       </c>
-      <c r="X5" s="71" t="s">
+      <c r="AM5" s="70" t="s">
         <v>59</v>
       </c>
-      <c r="Y5" s="72" t="s">
-        <v>494</v>
-      </c>
-      <c r="Z5" s="72" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA5" s="72" t="s">
-        <v>120</v>
-      </c>
-      <c r="AB5" s="71" t="s">
-        <v>409</v>
-      </c>
-      <c r="AC5" s="72" t="s">
-        <v>410</v>
-      </c>
-      <c r="AD5" s="72" t="s">
-        <v>492</v>
-      </c>
-      <c r="AE5" s="73" t="s">
-        <v>486</v>
-      </c>
-      <c r="AF5" s="72" t="s">
-        <v>505</v>
-      </c>
-      <c r="AG5" s="72" t="s">
-        <v>506</v>
-      </c>
-      <c r="AH5" s="73" t="s">
-        <v>507</v>
-      </c>
-      <c r="AI5" s="75" t="s">
-        <v>491</v>
-      </c>
-      <c r="AJ5" s="4"/>
-      <c r="AK5" s="68" t="s">
-        <v>295</v>
-      </c>
-      <c r="AL5" s="70" t="s">
-        <v>59</v>
-      </c>
-      <c r="AM5" s="75" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="6" spans="2:39" x14ac:dyDescent="0.25">
+      <c r="AN5" s="75" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="6" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>306</v>
       </c>
       <c r="C6" s="37">
-        <f t="shared" ref="C6:C11" si="0">AVERAGE(X6,J6)</f>
+        <f t="shared" ref="C6:C11" si="0">AVERAGE(Y6,K6)</f>
         <v>100</v>
       </c>
       <c r="D6" s="64">
-        <f t="shared" ref="D6:D11" si="1">K6</f>
+        <f t="shared" ref="D6:D11" si="1">L6</f>
         <v>17.316948400000001</v>
       </c>
       <c r="E6" s="38">
-        <f>AVERAGE(R6,AF6)</f>
+        <f>AVERAGE(S6,AG6)</f>
         <v>2.4239999999999999</v>
       </c>
       <c r="F6" s="91">
-        <f t="shared" ref="F6:G6" si="2">AVERAGE(S6,AG6)</f>
+        <f t="shared" ref="F6:G6" si="2">AVERAGE(T6,AH6)</f>
         <v>0.27999999999999997</v>
       </c>
       <c r="G6" s="92">
         <f t="shared" si="2"/>
         <v>2.4250000000000003</v>
       </c>
-      <c r="I6" s="68"/>
-      <c r="J6" s="37">
+      <c r="J6" s="68"/>
+      <c r="K6" s="37">
         <v>100</v>
       </c>
-      <c r="K6" s="77">
-        <f t="shared" ref="K6:K11" si="3">( 5.7*M6+9.4*N6+4.1*(O6+P6) ) * 0.004184</f>
+      <c r="L6" s="77">
+        <f t="shared" ref="L6:L11" si="3">( 5.7*N6+9.4*O6+4.1*(P6+Q6) ) * 0.004184</f>
         <v>17.316948400000001</v>
       </c>
-      <c r="L6" s="38">
+      <c r="M6" s="38">
         <f>AVERAGE('ruminants, roughage'!D21:D22)</f>
         <v>11.3</v>
       </c>
-      <c r="M6" s="65">
+      <c r="N6" s="65">
         <f>AVERAGE('ruminants, roughage'!I21:I22)</f>
         <v>151.5</v>
       </c>
-      <c r="N6" s="44">
+      <c r="O6" s="44">
         <v>20</v>
       </c>
-      <c r="O6" s="39"/>
-      <c r="P6" s="41">
-        <f t="shared" ref="P6:P11" si="4">1000-SUM(M6:O6,Q6)</f>
+      <c r="P6" s="39"/>
+      <c r="Q6" s="41">
+        <f t="shared" ref="Q6:Q11" si="4">1000-SUM(N6:P6,R6)</f>
         <v>753</v>
       </c>
-      <c r="Q6" s="42">
+      <c r="R6" s="42">
         <f>AVERAGE('ruminants, roughage'!K21:K22)</f>
         <v>75.5</v>
       </c>
-      <c r="R6" s="38">
-        <f>M6*R$3/1000*100</f>
+      <c r="S6" s="38">
+        <f>N6*S$3/1000*100</f>
         <v>2.4239999999999999</v>
       </c>
-      <c r="S6" s="91">
+      <c r="T6" s="91">
         <f>AVERAGE('ruminants, roughage'!X21:X22)/1000*100</f>
         <v>0.27999999999999997</v>
       </c>
-      <c r="T6" s="92">
+      <c r="U6" s="92">
         <f>AVERAGE('ruminants, roughage'!Z21:Z22)/1000*100</f>
         <v>2.4250000000000003</v>
       </c>
-      <c r="W6" s="68"/>
-      <c r="X6" s="37"/>
-      <c r="Y6" s="54"/>
+      <c r="X6" s="68"/>
+      <c r="Y6" s="37"/>
       <c r="Z6" s="54"/>
       <c r="AA6" s="54"/>
-      <c r="AB6" s="37"/>
-      <c r="AC6" s="54"/>
+      <c r="AB6" s="54"/>
+      <c r="AC6" s="37"/>
       <c r="AD6" s="54"/>
-      <c r="AE6" s="55"/>
-      <c r="AF6" s="39"/>
+      <c r="AE6" s="54"/>
+      <c r="AF6" s="55"/>
       <c r="AG6" s="39"/>
-      <c r="AH6" s="42"/>
-      <c r="AK6" s="68"/>
-      <c r="AL6" s="59"/>
-    </row>
-    <row r="7" spans="2:39" x14ac:dyDescent="0.25">
+      <c r="AH6" s="39"/>
+      <c r="AI6" s="42"/>
+      <c r="AL6" s="68"/>
+      <c r="AM6" s="59"/>
+    </row>
+    <row r="7" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>307</v>
       </c>
@@ -8415,73 +8434,73 @@
         <v>17.150216</v>
       </c>
       <c r="E7" s="38">
-        <f t="shared" ref="E7:E14" si="5">AVERAGE(R7,AF7)</f>
+        <f t="shared" ref="E7:E14" si="5">AVERAGE(S7,AG7)</f>
         <v>2.1280000000000001</v>
       </c>
       <c r="F7" s="91">
-        <f t="shared" ref="F7:F14" si="6">AVERAGE(S7,AG7)</f>
+        <f t="shared" ref="F7:F14" si="6">AVERAGE(T7,AH7)</f>
         <v>0.27</v>
       </c>
       <c r="G7" s="92">
-        <f t="shared" ref="G7:G14" si="7">AVERAGE(T7,AH7)</f>
+        <f t="shared" ref="G7:G14" si="7">AVERAGE(U7,AI7)</f>
         <v>2.34</v>
       </c>
-      <c r="I7" s="68"/>
-      <c r="J7" s="37">
+      <c r="J7" s="68"/>
+      <c r="K7" s="37">
         <v>100</v>
       </c>
-      <c r="K7" s="77">
+      <c r="L7" s="77">
         <f t="shared" si="3"/>
         <v>17.150216</v>
       </c>
-      <c r="L7" s="38">
+      <c r="M7" s="38">
         <f>AVERAGE('ruminants, roughage'!D25:D25)</f>
         <v>10.1</v>
       </c>
-      <c r="M7" s="65">
+      <c r="N7" s="65">
         <f>AVERAGE('ruminants, roughage'!I25:I25)</f>
         <v>133</v>
       </c>
-      <c r="N7" s="44">
+      <c r="O7" s="44">
         <v>20</v>
       </c>
-      <c r="O7" s="39"/>
-      <c r="P7" s="41">
+      <c r="P7" s="39"/>
+      <c r="Q7" s="41">
         <f t="shared" si="4"/>
         <v>769</v>
       </c>
-      <c r="Q7" s="42">
+      <c r="R7" s="42">
         <f>AVERAGE('ruminants, roughage'!K25:K25)</f>
         <v>78</v>
       </c>
-      <c r="R7" s="38">
-        <f t="shared" ref="R7:R42" si="8">M7*R$3/1000*100</f>
+      <c r="S7" s="38">
+        <f t="shared" ref="S7:S42" si="8">N7*S$3/1000*100</f>
         <v>2.1280000000000001</v>
       </c>
-      <c r="S7" s="91">
+      <c r="T7" s="91">
         <f>AVERAGE('ruminants, roughage'!X25:X25)/1000*100</f>
         <v>0.27</v>
       </c>
-      <c r="T7" s="92">
+      <c r="U7" s="92">
         <f>AVERAGE('ruminants, roughage'!Z25:Z25)/1000*100</f>
         <v>2.34</v>
       </c>
-      <c r="W7" s="68"/>
-      <c r="X7" s="37"/>
-      <c r="Y7" s="54"/>
+      <c r="X7" s="68"/>
+      <c r="Y7" s="37"/>
       <c r="Z7" s="54"/>
       <c r="AA7" s="54"/>
-      <c r="AB7" s="37"/>
-      <c r="AC7" s="54"/>
+      <c r="AB7" s="54"/>
+      <c r="AC7" s="37"/>
       <c r="AD7" s="54"/>
-      <c r="AE7" s="55"/>
-      <c r="AF7" s="39"/>
+      <c r="AE7" s="54"/>
+      <c r="AF7" s="55"/>
       <c r="AG7" s="39"/>
-      <c r="AH7" s="42"/>
-      <c r="AK7" s="68"/>
-      <c r="AL7" s="59"/>
-    </row>
-    <row r="8" spans="2:39" x14ac:dyDescent="0.25">
+      <c r="AH7" s="39"/>
+      <c r="AI7" s="42"/>
+      <c r="AL7" s="68"/>
+      <c r="AM7" s="59"/>
+    </row>
+    <row r="8" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>308</v>
       </c>
@@ -8505,69 +8524,69 @@
         <f t="shared" si="7"/>
         <v>2.35</v>
       </c>
-      <c r="I8" s="68"/>
-      <c r="J8" s="37">
+      <c r="J8" s="68"/>
+      <c r="K8" s="37">
         <v>100</v>
       </c>
-      <c r="K8" s="77">
+      <c r="L8" s="77">
         <f t="shared" si="3"/>
         <v>16.789764399999999</v>
       </c>
-      <c r="L8" s="43">
+      <c r="M8" s="43">
         <f>(8.3+8.7)/2</f>
         <v>8.5</v>
       </c>
-      <c r="M8" s="86">
+      <c r="N8" s="86">
         <f>(91+102)/2</f>
         <v>96.5</v>
       </c>
-      <c r="N8" s="44">
+      <c r="O8" s="44">
         <f>(22+23)/2</f>
         <v>22.5</v>
       </c>
-      <c r="O8" s="40"/>
-      <c r="P8" s="41">
+      <c r="P8" s="40"/>
+      <c r="Q8" s="41">
         <f t="shared" si="4"/>
         <v>793</v>
       </c>
-      <c r="Q8" s="45">
+      <c r="R8" s="45">
         <f>(83+93)/2</f>
         <v>88</v>
       </c>
-      <c r="R8" s="38">
+      <c r="S8" s="38">
         <f t="shared" si="8"/>
         <v>1.5439999999999998</v>
       </c>
-      <c r="S8" s="91">
+      <c r="T8" s="91">
         <f>(2+2.2)/2/1000*100</f>
         <v>0.21000000000000002</v>
       </c>
-      <c r="T8" s="92">
+      <c r="U8" s="92">
         <f>(20.3+26.7)/2/1000*100</f>
         <v>2.35</v>
       </c>
-      <c r="U8" t="s">
-        <v>487</v>
-      </c>
       <c r="V8" t="s">
-        <v>489</v>
-      </c>
-      <c r="W8" s="68"/>
-      <c r="X8" s="37"/>
-      <c r="Y8" s="54"/>
+        <v>486</v>
+      </c>
+      <c r="W8" t="s">
+        <v>488</v>
+      </c>
+      <c r="X8" s="68"/>
+      <c r="Y8" s="37"/>
       <c r="Z8" s="54"/>
       <c r="AA8" s="54"/>
-      <c r="AB8" s="37"/>
-      <c r="AC8" s="54"/>
+      <c r="AB8" s="54"/>
+      <c r="AC8" s="37"/>
       <c r="AD8" s="54"/>
-      <c r="AE8" s="55"/>
-      <c r="AF8" s="40"/>
+      <c r="AE8" s="54"/>
+      <c r="AF8" s="55"/>
       <c r="AG8" s="40"/>
-      <c r="AH8" s="45"/>
-      <c r="AK8" s="68"/>
-      <c r="AL8" s="59"/>
-    </row>
-    <row r="9" spans="2:39" x14ac:dyDescent="0.25">
+      <c r="AH8" s="40"/>
+      <c r="AI8" s="45"/>
+      <c r="AL8" s="68"/>
+      <c r="AM8" s="59"/>
+    </row>
+    <row r="9" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>2</v>
       </c>
@@ -8591,62 +8610,62 @@
         <f t="shared" si="7"/>
         <v>1.81</v>
       </c>
-      <c r="I9" s="68"/>
-      <c r="J9" s="37">
+      <c r="J9" s="68"/>
+      <c r="K9" s="37">
         <v>100</v>
       </c>
-      <c r="K9" s="77">
+      <c r="L9" s="77">
         <f t="shared" si="3"/>
         <v>17.160257599999998</v>
       </c>
-      <c r="L9" s="38">
+      <c r="M9" s="38">
         <f>AVERAGE('ruminants, roughage'!D33:D33)</f>
         <v>9.1</v>
       </c>
-      <c r="M9" s="65">
+      <c r="N9" s="65">
         <f>AVERAGE('ruminants, roughage'!I33:I33)</f>
         <v>93.5</v>
       </c>
-      <c r="N9" s="44">
+      <c r="O9" s="44">
         <v>20</v>
       </c>
-      <c r="O9" s="39"/>
-      <c r="P9" s="41">
+      <c r="P9" s="39"/>
+      <c r="Q9" s="41">
         <f t="shared" si="4"/>
         <v>824.5</v>
       </c>
-      <c r="Q9" s="42">
+      <c r="R9" s="42">
         <f>AVERAGE('ruminants, roughage'!K33:K33)</f>
         <v>62</v>
       </c>
-      <c r="R9" s="38">
+      <c r="S9" s="38">
         <f t="shared" si="8"/>
         <v>1.496</v>
       </c>
-      <c r="S9" s="91">
+      <c r="T9" s="91">
         <f>AVERAGE('ruminants, roughage'!X33:X33)/1000*100</f>
         <v>0.21000000000000002</v>
       </c>
-      <c r="T9" s="92">
+      <c r="U9" s="92">
         <f>AVERAGE('ruminants, roughage'!Z33:Z33)/1000*100</f>
         <v>1.81</v>
       </c>
-      <c r="W9" s="68"/>
-      <c r="X9" s="37"/>
-      <c r="Y9" s="54"/>
+      <c r="X9" s="68"/>
+      <c r="Y9" s="37"/>
       <c r="Z9" s="54"/>
       <c r="AA9" s="54"/>
-      <c r="AB9" s="37"/>
-      <c r="AC9" s="54"/>
+      <c r="AB9" s="54"/>
+      <c r="AC9" s="37"/>
       <c r="AD9" s="54"/>
-      <c r="AE9" s="55"/>
-      <c r="AF9" s="39"/>
+      <c r="AE9" s="54"/>
+      <c r="AF9" s="55"/>
       <c r="AG9" s="39"/>
-      <c r="AH9" s="42"/>
-      <c r="AK9" s="68"/>
-      <c r="AL9" s="59"/>
-    </row>
-    <row r="10" spans="2:39" x14ac:dyDescent="0.25">
+      <c r="AH9" s="39"/>
+      <c r="AI9" s="42"/>
+      <c r="AL9" s="68"/>
+      <c r="AM9" s="59"/>
+    </row>
+    <row r="10" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>12</v>
       </c>
@@ -8670,67 +8689,67 @@
         <f t="shared" si="7"/>
         <v>1.03</v>
       </c>
-      <c r="I10" s="68"/>
-      <c r="J10" s="37">
+      <c r="J10" s="68"/>
+      <c r="K10" s="37">
         <v>100</v>
       </c>
-      <c r="K10" s="77">
+      <c r="L10" s="77">
         <f t="shared" si="3"/>
         <v>17.6573168</v>
       </c>
-      <c r="L10" s="38">
+      <c r="M10" s="38">
         <v>11</v>
       </c>
-      <c r="M10" s="65">
+      <c r="N10" s="65">
         <v>68</v>
       </c>
-      <c r="N10" s="39">
+      <c r="O10" s="39">
         <v>30</v>
       </c>
-      <c r="O10" s="39">
+      <c r="P10" s="39">
         <v>198</v>
       </c>
-      <c r="P10" s="41">
+      <c r="Q10" s="41">
         <f t="shared" si="4"/>
         <v>668</v>
       </c>
-      <c r="Q10" s="42">
+      <c r="R10" s="42">
         <v>36</v>
       </c>
-      <c r="R10" s="38">
+      <c r="S10" s="38">
         <f t="shared" si="8"/>
         <v>1.0880000000000001</v>
       </c>
-      <c r="S10" s="91">
+      <c r="T10" s="91">
         <f>1.7/1000*100</f>
         <v>0.16999999999999998</v>
       </c>
-      <c r="T10" s="92">
+      <c r="U10" s="92">
         <f>10.3/1000*100</f>
         <v>1.03</v>
       </c>
-      <c r="U10" s="11" t="s">
-        <v>407</v>
-      </c>
       <c r="V10" s="11" t="s">
-        <v>489</v>
-      </c>
-      <c r="W10" s="68"/>
-      <c r="X10" s="37"/>
-      <c r="Y10" s="54"/>
+        <v>406</v>
+      </c>
+      <c r="W10" s="11" t="s">
+        <v>488</v>
+      </c>
+      <c r="X10" s="68"/>
+      <c r="Y10" s="37"/>
       <c r="Z10" s="54"/>
       <c r="AA10" s="54"/>
-      <c r="AB10" s="37"/>
-      <c r="AC10" s="54"/>
+      <c r="AB10" s="54"/>
+      <c r="AC10" s="37"/>
       <c r="AD10" s="54"/>
-      <c r="AE10" s="55"/>
-      <c r="AF10" s="39"/>
+      <c r="AE10" s="54"/>
+      <c r="AF10" s="55"/>
       <c r="AG10" s="39"/>
-      <c r="AH10" s="42"/>
-      <c r="AK10" s="68"/>
-      <c r="AL10" s="59"/>
-    </row>
-    <row r="11" spans="2:39" x14ac:dyDescent="0.25">
+      <c r="AH10" s="39"/>
+      <c r="AI10" s="42"/>
+      <c r="AL10" s="68"/>
+      <c r="AM10" s="59"/>
+    </row>
+    <row r="11" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>33</v>
       </c>
@@ -8754,107 +8773,107 @@
         <f t="shared" si="7"/>
         <v>2.34</v>
       </c>
-      <c r="I11" s="68"/>
-      <c r="J11" s="37">
+      <c r="J11" s="68"/>
+      <c r="K11" s="37">
         <v>100</v>
       </c>
-      <c r="K11" s="77">
+      <c r="L11" s="77">
         <f t="shared" si="3"/>
         <v>17.411437066666668</v>
       </c>
-      <c r="L11" s="38">
+      <c r="M11" s="38">
         <f>AVERAGE('ruminants, roughage'!D3:D14)</f>
         <v>9.9416666666666664</v>
       </c>
-      <c r="M11" s="65">
+      <c r="N11" s="65">
         <f>AVERAGE('ruminants, roughage'!I3:I14)</f>
         <v>140.41666666666666</v>
       </c>
-      <c r="N11" s="44">
+      <c r="O11" s="44">
         <v>20</v>
       </c>
-      <c r="O11" s="39"/>
-      <c r="P11" s="41">
+      <c r="P11" s="39"/>
+      <c r="Q11" s="41">
         <f t="shared" si="4"/>
         <v>773.91666666666674</v>
       </c>
-      <c r="Q11" s="42">
+      <c r="R11" s="42">
         <f>AVERAGE('ruminants, roughage'!K3:K14)</f>
         <v>65.666666666666657</v>
       </c>
-      <c r="R11" s="38">
+      <c r="S11" s="38">
         <f t="shared" si="8"/>
         <v>2.2466666666666666</v>
       </c>
-      <c r="S11" s="96">
-        <f>S7</f>
+      <c r="T11" s="96">
+        <f>T7</f>
         <v>0.27</v>
       </c>
-      <c r="T11" s="97">
-        <f>T7</f>
+      <c r="U11" s="97">
+        <f>U7</f>
         <v>2.34</v>
       </c>
-      <c r="W11" s="68"/>
-      <c r="X11" s="37"/>
-      <c r="Y11" s="54"/>
+      <c r="X11" s="68"/>
+      <c r="Y11" s="37"/>
       <c r="Z11" s="54"/>
       <c r="AA11" s="54"/>
-      <c r="AB11" s="37"/>
-      <c r="AC11" s="54"/>
+      <c r="AB11" s="54"/>
+      <c r="AC11" s="37"/>
       <c r="AD11" s="54"/>
-      <c r="AE11" s="55"/>
-      <c r="AF11" s="39"/>
+      <c r="AE11" s="54"/>
+      <c r="AF11" s="55"/>
       <c r="AG11" s="39"/>
-      <c r="AH11" s="42"/>
-      <c r="AK11" s="68"/>
-      <c r="AL11" s="59"/>
-    </row>
-    <row r="12" spans="2:39" x14ac:dyDescent="0.25">
+      <c r="AH11" s="39"/>
+      <c r="AI11" s="42"/>
+      <c r="AL11" s="68"/>
+      <c r="AM11" s="59"/>
+    </row>
+    <row r="12" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B12" s="4"/>
       <c r="C12" s="46"/>
       <c r="D12" s="55"/>
       <c r="E12" s="48"/>
       <c r="F12" s="48"/>
       <c r="G12" s="49"/>
-      <c r="I12" s="68"/>
-      <c r="J12" s="46"/>
-      <c r="K12" s="56"/>
-      <c r="L12" s="47"/>
-      <c r="M12" s="87"/>
-      <c r="N12" s="48"/>
+      <c r="J12" s="68"/>
+      <c r="K12" s="46"/>
+      <c r="L12" s="56"/>
+      <c r="M12" s="47"/>
+      <c r="N12" s="87"/>
       <c r="O12" s="48"/>
       <c r="P12" s="48"/>
-      <c r="Q12" s="49"/>
-      <c r="R12" s="38"/>
-      <c r="S12" s="48"/>
-      <c r="T12" s="49"/>
-      <c r="W12" s="68"/>
-      <c r="X12" s="46"/>
-      <c r="Y12" s="56"/>
+      <c r="Q12" s="48"/>
+      <c r="R12" s="49"/>
+      <c r="S12" s="38"/>
+      <c r="T12" s="48"/>
+      <c r="U12" s="49"/>
+      <c r="X12" s="68"/>
+      <c r="Y12" s="46"/>
       <c r="Z12" s="56"/>
       <c r="AA12" s="56"/>
-      <c r="AB12" s="46"/>
-      <c r="AC12" s="56"/>
+      <c r="AB12" s="56"/>
+      <c r="AC12" s="46"/>
       <c r="AD12" s="56"/>
-      <c r="AE12" s="57"/>
-      <c r="AF12" s="48"/>
+      <c r="AE12" s="56"/>
+      <c r="AF12" s="57"/>
       <c r="AG12" s="48"/>
-      <c r="AH12" s="49"/>
-      <c r="AI12" s="4"/>
+      <c r="AH12" s="48"/>
+      <c r="AI12" s="49"/>
       <c r="AJ12" s="4"/>
-      <c r="AK12" s="68"/>
-      <c r="AL12" s="59"/>
-    </row>
-    <row r="13" spans="2:39" x14ac:dyDescent="0.25">
+      <c r="AK12" s="4"/>
+      <c r="AL12" s="68"/>
+      <c r="AM12" s="59"/>
+    </row>
+    <row r="13" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>17</v>
       </c>
       <c r="C13" s="65">
-        <f t="shared" ref="C13:C36" si="9">AVERAGE(X13,J13)</f>
-        <v>87</v>
+        <f>100-14</f>
+        <v>86</v>
       </c>
       <c r="D13" s="64">
-        <f t="shared" ref="D13:D26" si="10">K13</f>
+        <f t="shared" ref="D13:D26" si="9">L13</f>
         <v>18.210023200000002</v>
       </c>
       <c r="E13" s="38">
@@ -8869,122 +8888,125 @@
         <f t="shared" si="7"/>
         <v>0.52500000000000002</v>
       </c>
-      <c r="H13" s="4"/>
-      <c r="I13" s="68">
+      <c r="H13" s="99" t="s">
+        <v>516</v>
+      </c>
+      <c r="I13" s="98"/>
+      <c r="J13" s="68">
         <f>MATCH($B13,ruminants!$A$3:$A$120,0)</f>
         <v>112</v>
       </c>
-      <c r="J13" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I13,J$4)</f>
+      <c r="K13" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J13,K$4)</f>
         <v>87</v>
       </c>
-      <c r="K13" s="77">
-        <f>( 5.7*M13+9.4*N13+4.1*(O13+P13) ) * 0.004184</f>
+      <c r="L13" s="77">
+        <f>( 5.7*N13+9.4*O13+4.1*(P13+Q13) ) * 0.004184</f>
         <v>18.210023200000002</v>
       </c>
-      <c r="L13" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I13,L$4)</f>
+      <c r="M13" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J13,M$4)</f>
         <v>14.1</v>
       </c>
-      <c r="M13" s="65">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I13,M$4)</f>
+      <c r="N13" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J13,N$4)</f>
         <v>121</v>
       </c>
-      <c r="N13" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I13,N$4)</f>
+      <c r="O13" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J13,O$4)</f>
         <v>25</v>
       </c>
-      <c r="O13" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I13,O$4)</f>
+      <c r="P13" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J13,P$4)</f>
         <v>30</v>
       </c>
-      <c r="P13" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I13,P$4)</f>
+      <c r="Q13" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J13,Q$4)</f>
         <v>806</v>
       </c>
-      <c r="Q13" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I13,Q$4)</f>
+      <c r="R13" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J13,R$4)</f>
         <v>18</v>
       </c>
-      <c r="R13" s="38">
+      <c r="S13" s="38">
         <f t="shared" si="8"/>
         <v>1.9359999999999999</v>
       </c>
-      <c r="S13" s="91">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I13,S$4)/1000*100</f>
+      <c r="T13" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J13,T$4)/1000*100</f>
         <v>0.37</v>
       </c>
-      <c r="T13" s="92">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I13,T$4)/1000*100</f>
+      <c r="U13" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J13,U$4)/1000*100</f>
         <v>0.47000000000000003</v>
       </c>
-      <c r="W13" s="68">
+      <c r="X13" s="68">
         <f>MATCH($B13,pigs!$A$3:$A$60,0)</f>
         <v>53</v>
       </c>
-      <c r="X13" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W13,X$4)</f>
+      <c r="Y13" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X13,Y$4)</f>
         <v>87</v>
       </c>
-      <c r="Y13" s="77">
-        <f>( 5.7*AB13+9.4*AC13+4.1*(AD13) ) * 0.004184</f>
+      <c r="Z13" s="77">
+        <f>( 5.7*AC13+9.4*AD13+4.1*(AE13) ) * 0.004184</f>
         <v>18.032621599999999</v>
       </c>
-      <c r="Z13" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W13,Z$4)</f>
+      <c r="AA13" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X13,AA$4)</f>
         <v>12.1</v>
       </c>
-      <c r="AA13" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W13,AA$4)</f>
+      <c r="AB13" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X13,AB$4)</f>
         <v>12.3</v>
       </c>
-      <c r="AB13" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W13,AB$4)</f>
+      <c r="AC13" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X13,AC$4)</f>
         <v>121</v>
       </c>
-      <c r="AC13" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W13,AC$4)</f>
+      <c r="AD13" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X13,AD$4)</f>
         <v>17</v>
       </c>
-      <c r="AD13" s="41">
-        <f>1000-SUM(AB13:AC13,AE13)</f>
+      <c r="AE13" s="41">
+        <f>1000-SUM(AC13:AD13,AF13)</f>
         <v>844</v>
       </c>
-      <c r="AE13" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$W13,AE$4)</f>
+      <c r="AF13" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$X13,AF$4)</f>
         <v>18</v>
       </c>
-      <c r="AF13" s="38">
-        <f>AB13*AF$3/1000*100</f>
+      <c r="AG13" s="38">
+        <f>AC13*AG$3/1000*100</f>
         <v>1.9359999999999999</v>
       </c>
-      <c r="AG13" s="91">
-        <f>INDEX(pigs!$D$3:$AO$60,$W13,AG$4)/1000*100</f>
+      <c r="AH13" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$X13,AH$4)/1000*100</f>
         <v>0.32</v>
       </c>
-      <c r="AH13" s="92">
-        <f>INDEX(pigs!$D$3:$AO$60,$W13,AH$4)/1000*100</f>
+      <c r="AI13" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$X13,AI$4)/1000*100</f>
         <v>0.57999999999999996</v>
       </c>
-      <c r="AK13" s="68">
+      <c r="AL13" s="68">
         <f>MATCH($B13,poultry!$A$3:$A$41,0)</f>
         <v>35</v>
       </c>
-      <c r="AL13" s="59">
-        <f>INDEX(poultry!$D$3:$U$41,$AK13,AL$4)</f>
+      <c r="AM13" s="59">
+        <f>INDEX(poultry!$D$3:$U$41,$AL13,AM$4)</f>
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>37</v>
       </c>
       <c r="C14" s="65">
+        <f t="shared" ref="C14:C18" si="10">100-14</f>
+        <v>86</v>
+      </c>
+      <c r="D14" s="64">
         <f t="shared" si="9"/>
-        <v>87</v>
-      </c>
-      <c r="D14" s="64">
-        <f t="shared" si="10"/>
         <v>18.089524000000001</v>
       </c>
       <c r="E14" s="38">
@@ -8999,252 +9021,258 @@
         <f t="shared" si="7"/>
         <v>0.58000000000000007</v>
       </c>
-      <c r="H14" s="4"/>
-      <c r="I14" s="68">
+      <c r="H14" s="99" t="s">
+        <v>516</v>
+      </c>
+      <c r="I14" s="4"/>
+      <c r="J14" s="68">
         <f>MATCH($B14,ruminants!$A$3:$A$120,0)</f>
         <v>42</v>
       </c>
-      <c r="J14" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I14,J$4)</f>
+      <c r="K14" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J14,K$4)</f>
         <v>87</v>
       </c>
-      <c r="K14" s="77">
-        <f t="shared" ref="K14:K42" si="11">( 5.7*M14+9.4*N14+4.1*(O14+P14) ) * 0.004184</f>
+      <c r="L14" s="77">
+        <f t="shared" ref="L14:L42" si="11">( 5.7*N14+9.4*O14+4.1*(P14+Q14) ) * 0.004184</f>
         <v>18.089524000000001</v>
       </c>
-      <c r="L14" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I14,L$4)</f>
+      <c r="M14" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J14,M$4)</f>
         <v>13.2</v>
       </c>
-      <c r="M14" s="65">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I14,M$4)</f>
+      <c r="N14" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J14,N$4)</f>
         <v>122</v>
       </c>
-      <c r="N14" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I14,N$4)</f>
+      <c r="O14" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J14,O$4)</f>
         <v>27</v>
       </c>
-      <c r="O14" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I14,O$4)</f>
+      <c r="P14" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J14,P$4)</f>
         <v>62</v>
       </c>
-      <c r="P14" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I14,P$4)</f>
+      <c r="Q14" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J14,Q$4)</f>
         <v>761</v>
       </c>
-      <c r="Q14" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I14,Q$4)</f>
+      <c r="R14" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J14,R$4)</f>
         <v>28</v>
       </c>
-      <c r="R14" s="38">
+      <c r="S14" s="38">
         <f t="shared" si="8"/>
         <v>1.952</v>
       </c>
-      <c r="S14" s="91">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I14,S$4)/1000*100</f>
+      <c r="T14" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J14,T$4)/1000*100</f>
         <v>0.4</v>
       </c>
-      <c r="T14" s="92">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I14,T$4)/1000*100</f>
+      <c r="U14" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J14,U$4)/1000*100</f>
         <v>0.59000000000000008</v>
       </c>
-      <c r="W14" s="68">
+      <c r="X14" s="68">
         <f>MATCH($B14,pigs!$A$3:$A$60,0)</f>
         <v>13</v>
       </c>
-      <c r="X14" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W14,X$4)</f>
+      <c r="Y14" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X14,Y$4)</f>
         <v>87</v>
       </c>
-      <c r="Y14" s="77">
-        <f t="shared" ref="Y14:Y16" si="12">( 5.7*AB14+9.4*AC14+4.1*(AD14) ) * 0.004184</f>
+      <c r="Z14" s="77">
+        <f t="shared" ref="Z14:Z16" si="12">( 5.7*AC14+9.4*AD14+4.1*(AE14) ) * 0.004184</f>
         <v>17.950615200000001</v>
       </c>
-      <c r="Z14" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W14,Z$4)</f>
+      <c r="AA14" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X14,AA$4)</f>
         <v>11</v>
       </c>
-      <c r="AA14" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W14,AA$4)</f>
+      <c r="AB14" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X14,AB$4)</f>
         <v>11.2</v>
       </c>
-      <c r="AB14" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W14,AB$4)</f>
+      <c r="AC14" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X14,AC$4)</f>
         <v>116</v>
       </c>
-      <c r="AC14" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W14,AC$4)</f>
+      <c r="AD14" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X14,AD$4)</f>
         <v>21</v>
       </c>
-      <c r="AD14" s="41">
-        <f t="shared" ref="AD14:AD16" si="13">1000-SUM(AB14:AC14,AE14)</f>
+      <c r="AE14" s="41">
+        <f t="shared" ref="AE14:AE16" si="13">1000-SUM(AC14:AD14,AF14)</f>
         <v>837</v>
       </c>
-      <c r="AE14" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$W14,AE$4)</f>
+      <c r="AF14" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$X14,AF$4)</f>
         <v>26</v>
       </c>
-      <c r="AF14" s="38">
-        <f t="shared" ref="AF14:AF43" si="14">AB14*AF$3/1000*100</f>
+      <c r="AG14" s="38">
+        <f t="shared" ref="AG14:AG43" si="14">AC14*AG$3/1000*100</f>
         <v>1.8560000000000001</v>
       </c>
-      <c r="AG14" s="91">
-        <f>INDEX(pigs!$D$3:$AO$60,$W14,AG$4)/1000*100</f>
+      <c r="AH14" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$X14,AH$4)/1000*100</f>
         <v>0.35000000000000003</v>
       </c>
-      <c r="AH14" s="92">
-        <f>INDEX(pigs!$D$3:$AO$60,$W14,AH$4)/1000*100</f>
+      <c r="AI14" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$X14,AI$4)/1000*100</f>
         <v>0.57000000000000006</v>
       </c>
-      <c r="AK14" s="68">
+      <c r="AL14" s="68">
         <f>MATCH($B14,poultry!$A$3:$A$41,0)</f>
         <v>16</v>
       </c>
-      <c r="AL14" s="59">
-        <f>INDEX(poultry!$D$3:$U$41,$AK14,AL$4)</f>
+      <c r="AM14" s="59">
+        <f>INDEX(poultry!$D$3:$U$41,$AL14,AM$4)</f>
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>38</v>
       </c>
       <c r="C15" s="65">
+        <f t="shared" si="10"/>
+        <v>86</v>
+      </c>
+      <c r="D15" s="64">
         <f t="shared" si="9"/>
-        <v>86</v>
-      </c>
-      <c r="D15" s="64">
-        <f t="shared" si="10"/>
         <v>18.6602216</v>
       </c>
       <c r="E15" s="38">
-        <f t="shared" ref="E15:E16" si="15">AVERAGE(R15,AF15)</f>
+        <f t="shared" ref="E15:E16" si="15">AVERAGE(S15,AG15)</f>
         <v>1.7680000000000002</v>
       </c>
       <c r="F15" s="91">
-        <f t="shared" ref="F15:F16" si="16">AVERAGE(S15,AG15)</f>
+        <f t="shared" ref="F15:F16" si="16">AVERAGE(T15,AH15)</f>
         <v>0.36499999999999999</v>
       </c>
       <c r="G15" s="92">
-        <f t="shared" ref="G15:G16" si="17">AVERAGE(T15,AH15)</f>
+        <f t="shared" ref="G15:G16" si="17">AVERAGE(U15,AI15)</f>
         <v>0.54</v>
       </c>
-      <c r="H15" s="4"/>
-      <c r="I15" s="68">
+      <c r="H15" s="99" t="s">
+        <v>516</v>
+      </c>
+      <c r="I15" s="4"/>
+      <c r="J15" s="68">
         <f>MATCH($B15,ruminants!$A$3:$A$120,0)</f>
         <v>28</v>
       </c>
-      <c r="J15" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I15,J$4)</f>
+      <c r="K15" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J15,K$4)</f>
         <v>85</v>
       </c>
-      <c r="K15" s="77">
+      <c r="L15" s="77">
         <f t="shared" si="11"/>
         <v>18.6602216</v>
       </c>
-      <c r="L15" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I15,L$4)</f>
+      <c r="M15" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J15,M$4)</f>
         <v>11.7</v>
       </c>
-      <c r="M15" s="65">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I15,M$4)</f>
+      <c r="N15" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J15,N$4)</f>
         <v>110</v>
       </c>
-      <c r="N15" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I15,N$4)</f>
+      <c r="O15" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J15,O$4)</f>
         <v>61</v>
       </c>
-      <c r="O15" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I15,O$4)</f>
+      <c r="P15" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J15,P$4)</f>
         <v>141</v>
       </c>
-      <c r="P15" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I15,P$4)</f>
+      <c r="Q15" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J15,Q$4)</f>
         <v>654</v>
       </c>
-      <c r="Q15" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I15,Q$4)</f>
+      <c r="R15" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J15,R$4)</f>
         <v>34</v>
       </c>
-      <c r="R15" s="38">
+      <c r="S15" s="38">
         <f t="shared" si="8"/>
         <v>1.76</v>
       </c>
-      <c r="S15" s="91">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I15,S$4)/1000*100</f>
+      <c r="T15" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J15,T$4)/1000*100</f>
         <v>0.37</v>
       </c>
-      <c r="T15" s="92">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I15,T$4)/1000*100</f>
+      <c r="U15" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J15,U$4)/1000*100</f>
         <v>0.53</v>
       </c>
-      <c r="W15" s="68">
+      <c r="X15" s="68">
         <f>MATCH($B15,pigs!$A$3:$A$60,0)</f>
         <v>11</v>
       </c>
-      <c r="X15" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W15,X$4)</f>
+      <c r="Y15" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X15,Y$4)</f>
         <v>87</v>
       </c>
-      <c r="Y15" s="77">
+      <c r="Z15" s="77">
         <f t="shared" si="12"/>
         <v>18.580307199999996</v>
       </c>
-      <c r="Z15" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W15,Z$4)</f>
+      <c r="AA15" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X15,AA$4)</f>
         <v>9</v>
       </c>
-      <c r="AA15" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W15,AA$4)</f>
+      <c r="AB15" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X15,AB$4)</f>
         <v>9.4</v>
       </c>
-      <c r="AB15" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W15,AB$4)</f>
+      <c r="AC15" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X15,AC$4)</f>
         <v>111</v>
       </c>
-      <c r="AC15" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W15,AC$4)</f>
+      <c r="AD15" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X15,AD$4)</f>
         <v>54</v>
       </c>
-      <c r="AD15" s="41">
+      <c r="AE15" s="41">
         <f t="shared" si="13"/>
         <v>805</v>
       </c>
-      <c r="AE15" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$W15,AE$4)</f>
+      <c r="AF15" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$X15,AF$4)</f>
         <v>30</v>
       </c>
-      <c r="AF15" s="38">
+      <c r="AG15" s="38">
         <f t="shared" si="14"/>
         <v>1.7760000000000002</v>
       </c>
-      <c r="AG15" s="91">
-        <f>INDEX(pigs!$D$3:$AO$60,$W15,AG$4)/1000*100</f>
+      <c r="AH15" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$X15,AH$4)/1000*100</f>
         <v>0.36</v>
       </c>
-      <c r="AH15" s="92">
-        <f>INDEX(pigs!$D$3:$AO$60,$W15,AH$4)/1000*100</f>
+      <c r="AI15" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$X15,AI$4)/1000*100</f>
         <v>0.54999999999999993</v>
       </c>
-      <c r="AK15" s="68">
+      <c r="AL15" s="68">
         <f>MATCH($B15,poultry!$A$3:$A$41,0)</f>
         <v>10</v>
       </c>
-      <c r="AL15" s="59">
-        <f>INDEX(poultry!$D$3:$U$41,$AK15,AL$4)</f>
+      <c r="AM15" s="59">
+        <f>INDEX(poultry!$D$3:$U$41,$AL15,AM$4)</f>
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>39</v>
       </c>
       <c r="C16" s="65">
-        <f t="shared" si="9"/>
-        <v>87</v>
+        <f t="shared" si="10"/>
+        <v>86</v>
       </c>
       <c r="D16" s="64">
-        <f>K16</f>
+        <f>L16</f>
         <v>18.2284328</v>
       </c>
       <c r="E16" s="38">
@@ -9259,219 +9287,225 @@
         <f t="shared" si="17"/>
         <v>0.58000000000000007</v>
       </c>
-      <c r="H16" s="4"/>
-      <c r="I16" s="68">
+      <c r="H16" s="99" t="s">
+        <v>516</v>
+      </c>
+      <c r="I16" s="4"/>
+      <c r="J16" s="68">
         <f>MATCH($B16,ruminants!$A$3:$A$120,0)</f>
         <v>78</v>
       </c>
-      <c r="J16" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I16,J$4)</f>
+      <c r="K16" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J16,K$4)</f>
         <v>87</v>
       </c>
-      <c r="K16" s="77">
+      <c r="L16" s="77">
         <f t="shared" si="11"/>
         <v>18.2284328</v>
       </c>
-      <c r="L16" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I16,L$4)</f>
+      <c r="M16" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J16,M$4)</f>
         <v>14</v>
       </c>
-      <c r="M16" s="65">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I16,M$4)</f>
+      <c r="N16" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J16,N$4)</f>
         <v>123</v>
       </c>
-      <c r="N16" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I16,N$4)</f>
+      <c r="O16" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J16,O$4)</f>
         <v>26</v>
       </c>
-      <c r="O16" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I16,O$4)</f>
+      <c r="P16" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J16,P$4)</f>
         <v>33</v>
       </c>
-      <c r="P16" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I16,P$4)</f>
+      <c r="Q16" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J16,Q$4)</f>
         <v>799</v>
       </c>
-      <c r="Q16" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I16,Q$4)</f>
+      <c r="R16" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J16,R$4)</f>
         <v>19</v>
       </c>
-      <c r="R16" s="38">
+      <c r="S16" s="38">
         <f t="shared" si="8"/>
         <v>1.968</v>
       </c>
-      <c r="S16" s="91">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I16,S$4)/1000*100</f>
+      <c r="T16" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J16,T$4)/1000*100</f>
         <v>0.4</v>
       </c>
-      <c r="T16" s="92">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I16,T$4)/1000*100</f>
+      <c r="U16" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J16,U$4)/1000*100</f>
         <v>0.54</v>
       </c>
-      <c r="W16" s="68">
+      <c r="X16" s="68">
         <f>MATCH($B16,pigs!$A$3:$A$60,0)</f>
         <v>39</v>
       </c>
-      <c r="X16" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W16,X$4)</f>
+      <c r="Y16" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X16,Y$4)</f>
         <v>87</v>
       </c>
-      <c r="Y16" s="77">
+      <c r="Z16" s="77">
         <f t="shared" si="12"/>
         <v>17.846015199999997</v>
       </c>
-      <c r="Z16" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W16,Z$4)</f>
+      <c r="AA16" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X16,AA$4)</f>
         <v>11.9</v>
       </c>
-      <c r="AA16" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W16,AA$4)</f>
+      <c r="AB16" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X16,AB$4)</f>
         <v>12</v>
       </c>
-      <c r="AB16" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W16,AB$4)</f>
+      <c r="AC16" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X16,AC$4)</f>
         <v>110</v>
       </c>
-      <c r="AC16" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W16,AC$4)</f>
+      <c r="AD16" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X16,AD$4)</f>
         <v>15</v>
       </c>
-      <c r="AD16" s="41">
+      <c r="AE16" s="41">
         <f t="shared" si="13"/>
         <v>853</v>
       </c>
-      <c r="AE16" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$W16,AE$4)</f>
+      <c r="AF16" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$X16,AF$4)</f>
         <v>22</v>
       </c>
-      <c r="AF16" s="38">
+      <c r="AG16" s="38">
         <f t="shared" si="14"/>
         <v>1.76</v>
       </c>
-      <c r="AG16" s="91">
-        <f>INDEX(pigs!$D$3:$AO$60,$W16,AG$4)/1000*100</f>
+      <c r="AH16" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$X16,AH$4)/1000*100</f>
         <v>0.36</v>
       </c>
-      <c r="AH16" s="92">
-        <f>INDEX(pigs!$D$3:$AO$60,$W16,AH$4)/1000*100</f>
+      <c r="AI16" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$X16,AI$4)/1000*100</f>
         <v>0.62</v>
       </c>
-      <c r="AK16" s="68">
+      <c r="AL16" s="68">
         <f>MATCH($B16,poultry!$A$3:$A$41,0)</f>
         <v>31</v>
       </c>
-      <c r="AL16" s="59">
-        <f>INDEX(poultry!$D$3:$U$41,$AK16,AL$4)</f>
+      <c r="AM16" s="59">
+        <f>INDEX(poultry!$D$3:$U$41,$AL16,AM$4)</f>
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="2:38" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>313</v>
       </c>
       <c r="C17" s="65">
+        <f t="shared" si="10"/>
+        <v>86</v>
+      </c>
+      <c r="D17" s="64">
         <f t="shared" si="9"/>
-        <v>87</v>
-      </c>
-      <c r="D17" s="64">
-        <f t="shared" si="10"/>
         <v>17.924256</v>
       </c>
       <c r="E17" s="38">
-        <f t="shared" ref="E17:E43" si="18">AVERAGE(R17,AF17)</f>
+        <f t="shared" ref="E17:E43" si="18">AVERAGE(S17,AG17)</f>
         <v>1.6</v>
       </c>
       <c r="F17" s="91">
-        <f t="shared" ref="F17:F43" si="19">AVERAGE(S17,AG17)</f>
+        <f t="shared" ref="F17:F43" si="19">AVERAGE(T17,AH17)</f>
         <v>0.33999999999999997</v>
       </c>
       <c r="G17" s="92">
-        <f t="shared" ref="G17:G43" si="20">AVERAGE(T17,AH17)</f>
+        <f t="shared" ref="G17:G43" si="20">AVERAGE(U17,AI17)</f>
         <v>0.54999999999999993</v>
       </c>
-      <c r="H17" s="4"/>
-      <c r="I17" s="68">
+      <c r="H17" s="99" t="s">
+        <v>516</v>
+      </c>
+      <c r="I17" s="4"/>
+      <c r="J17" s="68">
         <f>MATCH($B17,ruminants!$A$3:$A$120,0)</f>
         <v>77</v>
       </c>
-      <c r="J17" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I17,J$4)</f>
+      <c r="K17" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J17,K$4)</f>
         <v>87</v>
       </c>
-      <c r="K17" s="77">
+      <c r="L17" s="77">
         <f t="shared" si="11"/>
         <v>17.924256</v>
       </c>
-      <c r="L17" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I17,L$4)</f>
+      <c r="M17" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J17,M$4)</f>
         <v>13.9</v>
       </c>
-      <c r="M17" s="65">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I17,M$4)</f>
+      <c r="N17" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J17,N$4)</f>
         <v>100</v>
       </c>
-      <c r="N17" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I17,N$4)</f>
+      <c r="O17" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J17,O$4)</f>
         <v>20</v>
       </c>
-      <c r="O17" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I17,O$4)</f>
+      <c r="P17" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J17,P$4)</f>
         <v>25</v>
       </c>
-      <c r="P17" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I17,P$4)</f>
+      <c r="Q17" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J17,Q$4)</f>
         <v>835</v>
       </c>
-      <c r="Q17" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I17,Q$4)</f>
+      <c r="R17" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J17,R$4)</f>
         <v>20</v>
       </c>
-      <c r="R17" s="38">
+      <c r="S17" s="38">
         <f t="shared" si="8"/>
         <v>1.6</v>
       </c>
-      <c r="S17" s="91">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I17,S$4)/1000*100</f>
+      <c r="T17" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J17,T$4)/1000*100</f>
         <v>0.33999999999999997</v>
       </c>
-      <c r="T17" s="92">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I17,T$4)/1000*100</f>
+      <c r="U17" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J17,U$4)/1000*100</f>
         <v>0.54999999999999993</v>
       </c>
-      <c r="W17" s="68">
+      <c r="X17" s="68">
         <f>MATCH($B17,pigs!$A$3:$A$60,0)</f>
         <v>38</v>
       </c>
-      <c r="X17" s="37"/>
-      <c r="Y17" s="54"/>
+      <c r="Y17" s="37"/>
       <c r="Z17" s="54"/>
       <c r="AA17" s="54"/>
-      <c r="AB17" s="37"/>
-      <c r="AC17" s="54"/>
+      <c r="AB17" s="54"/>
+      <c r="AC17" s="37"/>
       <c r="AD17" s="54"/>
-      <c r="AE17" s="55"/>
-      <c r="AF17" s="38"/>
-      <c r="AG17" s="91"/>
-      <c r="AH17" s="92"/>
-      <c r="AK17" s="68">
+      <c r="AE17" s="54"/>
+      <c r="AF17" s="55"/>
+      <c r="AG17" s="38"/>
+      <c r="AH17" s="91"/>
+      <c r="AI17" s="92"/>
+      <c r="AL17" s="68">
         <f>MATCH($B17,poultry!$A$3:$A$41,0)</f>
         <v>30</v>
       </c>
-      <c r="AL17" s="59">
-        <f>INDEX(poultry!$D$3:$U$41,$AK17,AL$4)</f>
+      <c r="AM17" s="59">
+        <f>INDEX(poultry!$D$3:$U$41,$AL17,AM$4)</f>
         <v>87</v>
       </c>
     </row>
-    <row r="18" spans="2:38" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>40</v>
       </c>
       <c r="C18" s="65">
+        <f t="shared" si="10"/>
+        <v>86</v>
+      </c>
+      <c r="D18" s="64">
         <f t="shared" si="9"/>
-        <v>67.5</v>
-      </c>
-      <c r="D18" s="64">
-        <f t="shared" si="10"/>
         <v>18.3899352</v>
       </c>
       <c r="E18" s="38">
@@ -9486,122 +9520,125 @@
         <f t="shared" si="20"/>
         <v>0.46500000000000002</v>
       </c>
-      <c r="H18" s="4"/>
-      <c r="I18" s="68">
+      <c r="H18" s="99" t="s">
+        <v>516</v>
+      </c>
+      <c r="I18" s="4"/>
+      <c r="J18" s="68">
         <f>MATCH($B18,ruminants!$A$3:$A$120,0)</f>
         <v>53</v>
       </c>
-      <c r="J18" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I18,J$4)</f>
+      <c r="K18" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J18,K$4)</f>
         <v>48</v>
       </c>
-      <c r="K18" s="77">
+      <c r="L18" s="77">
         <f t="shared" si="11"/>
         <v>18.3899352</v>
       </c>
-      <c r="L18" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I18,L$4)</f>
+      <c r="M18" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J18,M$4)</f>
         <v>12.8</v>
       </c>
-      <c r="M18" s="65">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I18,M$4)</f>
+      <c r="N18" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J18,N$4)</f>
         <v>111</v>
       </c>
-      <c r="N18" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I18,N$4)</f>
+      <c r="O18" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J18,O$4)</f>
         <v>40</v>
       </c>
-      <c r="O18" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I18,O$4)</f>
+      <c r="P18" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J18,P$4)</f>
         <v>63</v>
       </c>
-      <c r="P18" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I18,P$4)</f>
+      <c r="Q18" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J18,Q$4)</f>
         <v>763</v>
       </c>
-      <c r="Q18" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I18,Q$4)</f>
+      <c r="R18" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J18,R$4)</f>
         <v>23</v>
       </c>
-      <c r="R18" s="38">
+      <c r="S18" s="38">
         <f t="shared" si="8"/>
         <v>1.7760000000000002</v>
       </c>
-      <c r="S18" s="91">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I18,S$4)/1000*100</f>
+      <c r="T18" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J18,T$4)/1000*100</f>
         <v>0.36</v>
       </c>
-      <c r="T18" s="92">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I18,T$4)/1000*100</f>
+      <c r="U18" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J18,U$4)/1000*100</f>
         <v>0.53</v>
       </c>
-      <c r="W18" s="68">
+      <c r="X18" s="68">
         <f>MATCH($B18,pigs!$A$3:$A$60,0)</f>
         <v>19</v>
       </c>
-      <c r="X18" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W18,X$4)</f>
+      <c r="Y18" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X18,Y$4)</f>
         <v>87</v>
       </c>
-      <c r="Y18" s="77">
-        <f t="shared" ref="Y18:Y23" si="21">( 5.7*AB18+9.4*AC18+4.1*(AD18) ) * 0.004184</f>
+      <c r="Z18" s="77">
+        <f t="shared" ref="Z18:Z23" si="21">( 5.7*AC18+9.4*AD18+4.1*(AE18) ) * 0.004184</f>
         <v>18.4970456</v>
       </c>
-      <c r="Z18" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W18,Z$4)</f>
+      <c r="AA18" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X18,AA$4)</f>
         <v>12.8</v>
       </c>
-      <c r="AA18" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W18,AA$4)</f>
+      <c r="AB18" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X18,AB$4)</f>
         <v>13.2</v>
       </c>
-      <c r="AB18" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W18,AB$4)</f>
+      <c r="AC18" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X18,AC$4)</f>
         <v>94</v>
       </c>
-      <c r="AC18" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W18,AC$4)</f>
+      <c r="AD18" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X18,AD$4)</f>
         <v>43</v>
       </c>
-      <c r="AD18" s="41">
-        <f t="shared" ref="AD18:AD23" si="22">1000-SUM(AB18:AC18,AE18)</f>
+      <c r="AE18" s="41">
+        <f t="shared" ref="AE18:AE23" si="22">1000-SUM(AC18:AD18,AF18)</f>
         <v>849</v>
       </c>
-      <c r="AE18" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$W18,AE$4)</f>
+      <c r="AF18" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$X18,AF$4)</f>
         <v>14</v>
       </c>
-      <c r="AF18" s="38">
+      <c r="AG18" s="38">
         <f t="shared" si="14"/>
         <v>1.5040000000000002</v>
       </c>
-      <c r="AG18" s="91">
-        <f>INDEX(pigs!$D$3:$AO$60,$W18,AG$4)/1000*100</f>
+      <c r="AH18" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$X18,AH$4)/1000*100</f>
         <v>0.32</v>
       </c>
-      <c r="AH18" s="92">
-        <f>INDEX(pigs!$D$3:$AO$60,$W18,AH$4)/1000*100</f>
+      <c r="AI18" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$X18,AI$4)/1000*100</f>
         <v>0.4</v>
       </c>
-      <c r="AK18" s="68">
+      <c r="AL18" s="68">
         <f>MATCH($B18,poultry!$A$3:$A$41,0)</f>
         <v>24</v>
       </c>
-      <c r="AL18" s="59">
-        <f>INDEX(poultry!$D$3:$U$41,$AK18,AL$4)</f>
+      <c r="AM18" s="59">
+        <f>INDEX(poultry!$D$3:$U$41,$AL18,AM$4)</f>
         <v>87</v>
       </c>
     </row>
-    <row r="19" spans="2:38" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>41</v>
       </c>
       <c r="C19" s="65">
+        <f>100-15</f>
+        <v>85</v>
+      </c>
+      <c r="D19" s="64">
         <f t="shared" si="9"/>
-        <v>87</v>
-      </c>
-      <c r="D19" s="64">
-        <f t="shared" si="10"/>
         <v>18.478217600000001</v>
       </c>
       <c r="E19" s="38">
@@ -9616,122 +9653,125 @@
         <f t="shared" si="20"/>
         <v>1.155</v>
       </c>
-      <c r="H19" s="4"/>
-      <c r="I19" s="68">
+      <c r="H19" s="99" t="s">
+        <v>516</v>
+      </c>
+      <c r="I19" s="4"/>
+      <c r="J19" s="68">
         <f>MATCH($B19,ruminants!$A$3:$A$120,0)</f>
         <v>115</v>
       </c>
-      <c r="J19" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I19,J$4)</f>
+      <c r="K19" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J19,K$4)</f>
         <v>87</v>
       </c>
-      <c r="K19" s="77">
+      <c r="L19" s="77">
         <f t="shared" si="11"/>
         <v>18.478217600000001</v>
       </c>
-      <c r="L19" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I19,L$4)</f>
+      <c r="M19" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J19,M$4)</f>
         <v>13.8</v>
       </c>
-      <c r="M19" s="65">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I19,M$4)</f>
+      <c r="N19" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J19,N$4)</f>
         <v>226</v>
       </c>
-      <c r="N19" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I19,N$4)</f>
+      <c r="O19" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J19,O$4)</f>
         <v>17</v>
       </c>
-      <c r="O19" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I19,O$4)</f>
+      <c r="P19" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J19,P$4)</f>
         <v>78</v>
       </c>
-      <c r="P19" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I19,P$4)</f>
+      <c r="Q19" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J19,Q$4)</f>
         <v>646</v>
       </c>
-      <c r="Q19" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I19,Q$4)</f>
+      <c r="R19" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J19,R$4)</f>
         <v>33</v>
       </c>
-      <c r="R19" s="38">
+      <c r="S19" s="38">
         <f t="shared" si="8"/>
         <v>3.6160000000000005</v>
       </c>
-      <c r="S19" s="91">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I19,S$4)/1000*100</f>
+      <c r="T19" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J19,T$4)/1000*100</f>
         <v>0.43</v>
       </c>
-      <c r="T19" s="92">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I19,T$4)/1000*100</f>
+      <c r="U19" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J19,U$4)/1000*100</f>
         <v>1.1100000000000001</v>
       </c>
-      <c r="W19" s="68">
+      <c r="X19" s="68">
         <f>MATCH($B19,pigs!$A$3:$A$60,0)</f>
         <v>56</v>
       </c>
-      <c r="X19" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W19,X$4)</f>
+      <c r="Y19" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X19,Y$4)</f>
         <v>87</v>
       </c>
-      <c r="Y19" s="77">
+      <c r="Z19" s="77">
         <f t="shared" si="21"/>
         <v>18.420059999999999</v>
       </c>
-      <c r="Z19" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W19,Z$4)</f>
+      <c r="AA19" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X19,AA$4)</f>
         <v>11.2</v>
       </c>
-      <c r="AA19" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W19,AA$4)</f>
+      <c r="AB19" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X19,AB$4)</f>
         <v>11.5</v>
       </c>
-      <c r="AB19" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W19,AB$4)</f>
+      <c r="AC19" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X19,AC$4)</f>
         <v>239</v>
       </c>
-      <c r="AC19" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W19,AC$4)</f>
+      <c r="AD19" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X19,AD$4)</f>
         <v>12</v>
       </c>
-      <c r="AD19" s="41">
+      <c r="AE19" s="41">
         <f t="shared" si="22"/>
         <v>714</v>
       </c>
-      <c r="AE19" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$W19,AE$4)</f>
+      <c r="AF19" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$X19,AF$4)</f>
         <v>35</v>
       </c>
-      <c r="AF19" s="38">
+      <c r="AG19" s="38">
         <f t="shared" si="14"/>
         <v>3.8240000000000003</v>
       </c>
-      <c r="AG19" s="91">
-        <f>INDEX(pigs!$D$3:$AO$60,$W19,AG$4)/1000*100</f>
+      <c r="AH19" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$X19,AH$4)/1000*100</f>
         <v>0.45999999999999996</v>
       </c>
-      <c r="AH19" s="92">
-        <f>INDEX(pigs!$D$3:$AO$60,$W19,AH$4)/1000*100</f>
+      <c r="AI19" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$X19,AI$4)/1000*100</f>
         <v>1.2</v>
       </c>
-      <c r="AK19" s="68">
+      <c r="AL19" s="68">
         <f>MATCH($B19,poultry!$A$3:$A$41,0)</f>
         <v>39</v>
       </c>
-      <c r="AL19" s="59">
-        <f>INDEX(poultry!$D$3:$U$41,$AK19,AL$4)</f>
+      <c r="AM19" s="59">
+        <f>INDEX(poultry!$D$3:$U$41,$AL19,AM$4)</f>
         <v>87</v>
       </c>
     </row>
-    <row r="20" spans="2:38" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>42</v>
       </c>
       <c r="C20" s="65">
+        <f>100-15</f>
+        <v>85</v>
+      </c>
+      <c r="D20" s="64">
         <f t="shared" si="9"/>
-        <v>86.8</v>
-      </c>
-      <c r="D20" s="64">
-        <f t="shared" si="10"/>
         <v>18.737207199999997</v>
       </c>
       <c r="E20" s="38">
@@ -9746,113 +9786,116 @@
         <f t="shared" si="20"/>
         <v>1.375</v>
       </c>
-      <c r="H20" s="4"/>
-      <c r="I20" s="68"/>
-      <c r="J20" s="65">
+      <c r="H20" s="99" t="s">
+        <v>516</v>
+      </c>
+      <c r="I20" s="4"/>
+      <c r="J20" s="68"/>
+      <c r="K20" s="65">
         <v>86.6</v>
       </c>
-      <c r="K20" s="77">
+      <c r="L20" s="77">
         <f t="shared" si="11"/>
         <v>18.737207199999997</v>
       </c>
-      <c r="L20" s="38">
+      <c r="M20" s="38">
         <v>13.3</v>
       </c>
-      <c r="M20" s="65">
+      <c r="N20" s="65">
         <v>290</v>
       </c>
-      <c r="N20" s="39">
+      <c r="O20" s="39">
         <v>14</v>
       </c>
-      <c r="O20" s="39">
+      <c r="P20" s="39">
         <v>91</v>
       </c>
-      <c r="P20" s="41">
-        <f>1000-SUM(M20:O20,Q20)</f>
+      <c r="Q20" s="41">
+        <f>1000-SUM(N20:P20,R20)</f>
         <v>566</v>
       </c>
-      <c r="Q20" s="42">
+      <c r="R20" s="42">
         <v>39</v>
       </c>
-      <c r="R20" s="38">
+      <c r="S20" s="38">
         <f t="shared" si="8"/>
         <v>4.6399999999999997</v>
       </c>
-      <c r="S20" s="91">
+      <c r="T20" s="91">
         <f>5.5/1000*100</f>
         <v>0.54999999999999993</v>
       </c>
-      <c r="T20" s="92">
+      <c r="U20" s="92">
         <f>11.5/1000*100</f>
         <v>1.1499999999999999</v>
       </c>
-      <c r="U20" s="11" t="s">
+      <c r="V20" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="V20" s="11" t="s">
-        <v>489</v>
-      </c>
-      <c r="W20" s="68">
+      <c r="W20" s="11" t="s">
+        <v>488</v>
+      </c>
+      <c r="X20" s="68">
         <f>MATCH($B20,pigs!$A$3:$A$60,0)</f>
         <v>57</v>
       </c>
-      <c r="X20" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W20,X$4)</f>
+      <c r="Y20" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X20,Y$4)</f>
         <v>87</v>
       </c>
-      <c r="Y20" s="77">
+      <c r="Z20" s="77">
         <f t="shared" si="21"/>
         <v>18.821305599999999</v>
       </c>
-      <c r="Z20" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W20,Z$4)</f>
+      <c r="AA20" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X20,AA$4)</f>
         <v>10.7</v>
       </c>
-      <c r="AA20" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W20,AA$4)</f>
+      <c r="AB20" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X20,AB$4)</f>
         <v>10.9</v>
       </c>
-      <c r="AB20" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W20,AB$4)</f>
+      <c r="AC20" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X20,AC$4)</f>
         <v>311</v>
       </c>
-      <c r="AC20" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W20,AC$4)</f>
+      <c r="AD20" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X20,AD$4)</f>
         <v>13</v>
       </c>
-      <c r="AD20" s="41">
+      <c r="AE20" s="41">
         <f t="shared" si="22"/>
         <v>635</v>
       </c>
-      <c r="AE20" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$W20,AE$4)</f>
+      <c r="AF20" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$X20,AF$4)</f>
         <v>41</v>
       </c>
-      <c r="AF20" s="38">
+      <c r="AG20" s="38">
         <f t="shared" si="14"/>
         <v>4.976</v>
       </c>
-      <c r="AG20" s="91">
-        <f>INDEX(pigs!$D$3:$AO$60,$W20,AG$4)/1000*100</f>
+      <c r="AH20" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$X20,AH$4)/1000*100</f>
         <v>0.67999999999999994</v>
       </c>
-      <c r="AH20" s="92">
-        <f>INDEX(pigs!$D$3:$AO$60,$W20,AH$4)/1000*100</f>
+      <c r="AI20" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$X20,AI$4)/1000*100</f>
         <v>1.6</v>
       </c>
-      <c r="AK20" s="68"/>
-      <c r="AL20" s="59"/>
-    </row>
-    <row r="21" spans="2:38" x14ac:dyDescent="0.25">
+      <c r="AL20" s="68"/>
+      <c r="AM20" s="59"/>
+    </row>
+    <row r="21" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>35</v>
       </c>
       <c r="C21" s="65">
+        <f>100-9</f>
+        <v>91</v>
+      </c>
+      <c r="D21" s="64">
         <f t="shared" si="9"/>
-        <v>92.5</v>
-      </c>
-      <c r="D21" s="64">
-        <f t="shared" si="10"/>
         <v>27.903096000000001</v>
       </c>
       <c r="E21" s="38">
@@ -9867,116 +9910,119 @@
         <f t="shared" si="20"/>
         <v>0.90999999999999992</v>
       </c>
-      <c r="H21" s="4"/>
-      <c r="I21" s="68">
+      <c r="H21" s="99" t="s">
+        <v>516</v>
+      </c>
+      <c r="I21" s="4"/>
+      <c r="J21" s="68">
         <f>MATCH($B21,ruminants!$A$3:$A$120,0)</f>
         <v>71</v>
       </c>
-      <c r="J21" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I21,J$4)</f>
+      <c r="K21" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J21,K$4)</f>
         <v>93</v>
       </c>
-      <c r="K21" s="77">
+      <c r="L21" s="77">
         <f t="shared" si="11"/>
         <v>27.903096000000001</v>
       </c>
-      <c r="L21" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I21,L$4)</f>
+      <c r="M21" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J21,M$4)</f>
         <v>22.1</v>
       </c>
-      <c r="M21" s="65">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I21,M$4)</f>
+      <c r="N21" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J21,N$4)</f>
         <v>210</v>
       </c>
-      <c r="N21" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I21,N$4)</f>
+      <c r="O21" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J21,O$4)</f>
         <v>460</v>
       </c>
-      <c r="O21" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I21,O$4)</f>
+      <c r="P21" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J21,P$4)</f>
         <v>80</v>
       </c>
-      <c r="P21" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I21,P$4)</f>
+      <c r="Q21" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J21,Q$4)</f>
         <v>200</v>
       </c>
-      <c r="Q21" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I21,Q$4)</f>
+      <c r="R21" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J21,R$4)</f>
         <v>50</v>
       </c>
-      <c r="R21" s="38">
+      <c r="S21" s="38">
         <f t="shared" si="8"/>
         <v>3.3600000000000003</v>
       </c>
-      <c r="S21" s="91">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I21,S$4)/1000*100</f>
+      <c r="T21" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J21,T$4)/1000*100</f>
         <v>0.86</v>
       </c>
-      <c r="T21" s="92">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I21,T$4)/1000*100</f>
+      <c r="U21" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J21,U$4)/1000*100</f>
         <v>0.81999999999999984</v>
       </c>
-      <c r="W21" s="68">
+      <c r="X21" s="68">
         <f>MATCH($B21,pigs!$A$3:$A$60,0)</f>
         <v>33</v>
       </c>
-      <c r="X21" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W21,X$4)</f>
+      <c r="Y21" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X21,Y$4)</f>
         <v>92</v>
       </c>
-      <c r="Y21" s="77">
+      <c r="Z21" s="77">
         <f t="shared" si="21"/>
         <v>27.892217599999999</v>
       </c>
-      <c r="Z21" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W21,Z$4)</f>
+      <c r="AA21" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X21,AA$4)</f>
         <v>18</v>
       </c>
-      <c r="AA21" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W21,AA$4)</f>
+      <c r="AB21" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X21,AB$4)</f>
         <v>18.5</v>
       </c>
-      <c r="AB21" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W21,AB$4)</f>
+      <c r="AC21" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X21,AC$4)</f>
         <v>207</v>
       </c>
-      <c r="AC21" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W21,AC$4)</f>
+      <c r="AD21" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X21,AD$4)</f>
         <v>455</v>
       </c>
-      <c r="AD21" s="41">
+      <c r="AE21" s="41">
         <f t="shared" si="22"/>
         <v>295</v>
       </c>
-      <c r="AE21" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$W21,AE$4)</f>
+      <c r="AF21" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$X21,AF$4)</f>
         <v>43</v>
       </c>
-      <c r="AF21" s="38">
+      <c r="AG21" s="38">
         <f t="shared" si="14"/>
         <v>3.3119999999999998</v>
       </c>
-      <c r="AG21" s="91">
-        <f>INDEX(pigs!$D$3:$AO$60,$W21,AG$4)/1000*100</f>
+      <c r="AH21" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$X21,AH$4)/1000*100</f>
         <v>0.76</v>
       </c>
-      <c r="AH21" s="92">
-        <f>INDEX(pigs!$D$3:$AO$60,$W21,AH$4)/1000*100</f>
+      <c r="AI21" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$X21,AI$4)/1000*100</f>
         <v>1</v>
       </c>
-      <c r="AK21" s="68"/>
-      <c r="AL21" s="59"/>
-    </row>
-    <row r="22" spans="2:38" x14ac:dyDescent="0.25">
+      <c r="AL21" s="68"/>
+      <c r="AM21" s="59"/>
+    </row>
+    <row r="22" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>43</v>
       </c>
       <c r="C22" s="65">
+        <f>100-9</f>
+        <v>91</v>
+      </c>
+      <c r="D22" s="64">
         <f t="shared" si="9"/>
-        <v>92</v>
-      </c>
-      <c r="D22" s="64">
-        <f t="shared" si="10"/>
         <v>26.501456000000001</v>
       </c>
       <c r="E22" s="38">
@@ -9991,116 +10037,119 @@
         <f t="shared" si="20"/>
         <v>0.89500000000000002</v>
       </c>
-      <c r="H22" s="4"/>
-      <c r="I22" s="68">
+      <c r="H22" s="99" t="s">
+        <v>516</v>
+      </c>
+      <c r="I22" s="4"/>
+      <c r="J22" s="68">
         <f>MATCH($B22,ruminants!$A$3:$A$120,0)</f>
         <v>45</v>
       </c>
-      <c r="J22" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I22,J$4)</f>
+      <c r="K22" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J22,K$4)</f>
         <v>93</v>
       </c>
-      <c r="K22" s="77">
+      <c r="L22" s="77">
         <f t="shared" si="11"/>
         <v>26.501456000000001</v>
       </c>
-      <c r="L22" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I22,L$4)</f>
+      <c r="M22" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J22,M$4)</f>
         <v>20.100000000000001</v>
       </c>
-      <c r="M22" s="65">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I22,M$4)</f>
+      <c r="N22" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J22,N$4)</f>
         <v>240</v>
       </c>
-      <c r="N22" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I22,N$4)</f>
+      <c r="O22" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J22,O$4)</f>
         <v>380</v>
       </c>
-      <c r="O22" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I22,O$4)</f>
+      <c r="P22" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J22,P$4)</f>
         <v>70</v>
       </c>
-      <c r="P22" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I22,P$4)</f>
+      <c r="Q22" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J22,Q$4)</f>
         <v>270</v>
       </c>
-      <c r="Q22" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I22,Q$4)</f>
+      <c r="R22" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J22,R$4)</f>
         <v>40</v>
       </c>
-      <c r="R22" s="38">
+      <c r="S22" s="38">
         <f t="shared" si="8"/>
         <v>3.84</v>
       </c>
-      <c r="S22" s="91">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I22,S$4)/1000*100</f>
+      <c r="T22" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J22,T$4)/1000*100</f>
         <v>0.57000000000000006</v>
       </c>
-      <c r="T22" s="92">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I22,T$4)/1000*100</f>
+      <c r="U22" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J22,U$4)/1000*100</f>
         <v>0.89999999999999991</v>
       </c>
-      <c r="W22" s="68">
+      <c r="X22" s="68">
         <f>MATCH($B22,pigs!$A$3:$A$60,0)</f>
         <v>14</v>
       </c>
-      <c r="X22" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W22,X$4)</f>
+      <c r="Y22" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X22,Y$4)</f>
         <v>91</v>
       </c>
-      <c r="Y22" s="77">
+      <c r="Z22" s="77">
         <f t="shared" si="21"/>
         <v>27.712724000000005</v>
       </c>
-      <c r="Z22" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W22,Z$4)</f>
+      <c r="AA22" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X22,AA$4)</f>
         <v>17.3</v>
       </c>
-      <c r="AA22" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W22,AA$4)</f>
+      <c r="AB22" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X22,AB$4)</f>
         <v>17.5</v>
       </c>
-      <c r="AB22" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W22,AB$4)</f>
+      <c r="AC22" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X22,AC$4)</f>
         <v>227</v>
       </c>
-      <c r="AC22" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W22,AC$4)</f>
+      <c r="AD22" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X22,AD$4)</f>
         <v>437</v>
       </c>
-      <c r="AD22" s="41">
+      <c r="AE22" s="41">
         <f t="shared" si="22"/>
         <v>298</v>
       </c>
-      <c r="AE22" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$W22,AE$4)</f>
+      <c r="AF22" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$X22,AF$4)</f>
         <v>38</v>
       </c>
-      <c r="AF22" s="38">
+      <c r="AG22" s="38">
         <f t="shared" si="14"/>
         <v>3.6319999999999997</v>
       </c>
-      <c r="AG22" s="91">
-        <f>INDEX(pigs!$D$3:$AO$60,$W22,AG$4)/1000*100</f>
+      <c r="AH22" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$X22,AH$4)/1000*100</f>
         <v>0.57000000000000006</v>
       </c>
-      <c r="AH22" s="92">
-        <f>INDEX(pigs!$D$3:$AO$60,$W22,AH$4)/1000*100</f>
+      <c r="AI22" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$X22,AI$4)/1000*100</f>
         <v>0.89</v>
       </c>
-      <c r="AK22" s="68"/>
-      <c r="AL22" s="59"/>
-    </row>
-    <row r="23" spans="2:38" x14ac:dyDescent="0.25">
+      <c r="AL22" s="68"/>
+      <c r="AM22" s="59"/>
+    </row>
+    <row r="23" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>310</v>
       </c>
       <c r="C23" s="65">
+        <f>AVERAGE(Y23,K23)</f>
+        <v>100</v>
+      </c>
+      <c r="D23" s="64">
         <f t="shared" si="9"/>
-        <v>100</v>
-      </c>
-      <c r="D23" s="64">
-        <f t="shared" si="10"/>
         <v>39.329599999999999</v>
       </c>
       <c r="E23" s="38">
@@ -10116,115 +10165,116 @@
         <v>0</v>
       </c>
       <c r="H23" s="4"/>
-      <c r="I23" s="68"/>
-      <c r="J23" s="37">
+      <c r="I23" s="4"/>
+      <c r="J23" s="68"/>
+      <c r="K23" s="37">
         <v>100</v>
       </c>
-      <c r="K23" s="77">
+      <c r="L23" s="77">
         <f t="shared" si="11"/>
         <v>39.329599999999999</v>
       </c>
-      <c r="L23" s="38">
+      <c r="M23" s="38">
         <v>36.6</v>
       </c>
-      <c r="M23" s="65">
-        <v>0</v>
-      </c>
-      <c r="N23" s="39">
+      <c r="N23" s="65">
+        <v>0</v>
+      </c>
+      <c r="O23" s="39">
         <v>1000</v>
       </c>
-      <c r="O23" s="39">
-        <v>0</v>
-      </c>
       <c r="P23" s="39">
         <v>0</v>
       </c>
-      <c r="Q23" s="42">
-        <v>0</v>
-      </c>
-      <c r="R23" s="38">
+      <c r="Q23" s="39">
+        <v>0</v>
+      </c>
+      <c r="R23" s="42">
+        <v>0</v>
+      </c>
+      <c r="S23" s="38">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S23" s="91">
-        <v>0</v>
-      </c>
-      <c r="T23" s="92">
-        <v>0</v>
-      </c>
-      <c r="U23" s="11" t="s">
+      <c r="T23" s="91">
+        <v>0</v>
+      </c>
+      <c r="U23" s="92">
+        <v>0</v>
+      </c>
+      <c r="V23" s="11" t="s">
         <v>319</v>
       </c>
-      <c r="V23" t="s">
-        <v>489</v>
-      </c>
-      <c r="W23" s="68">
+      <c r="W23" t="s">
+        <v>488</v>
+      </c>
+      <c r="X23" s="68">
         <f>MATCH($B23,pigs!$A$3:$A$60,0)</f>
         <v>28</v>
       </c>
-      <c r="X23" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W23,X$4)</f>
+      <c r="Y23" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X23,Y$4)</f>
         <v>100</v>
       </c>
-      <c r="Y23" s="77">
+      <c r="Z23" s="77">
         <f t="shared" si="21"/>
         <v>39.329599999999999</v>
       </c>
-      <c r="Z23" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W23,Z$4)</f>
+      <c r="AA23" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X23,AA$4)</f>
         <v>29.8</v>
       </c>
-      <c r="AA23" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W23,AA$4)</f>
+      <c r="AB23" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X23,AB$4)</f>
         <v>29.8</v>
       </c>
-      <c r="AB23" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W23,AB$4)</f>
-        <v>0</v>
-      </c>
-      <c r="AC23" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W23,AC$4)</f>
+      <c r="AC23" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X23,AC$4)</f>
+        <v>0</v>
+      </c>
+      <c r="AD23" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X23,AD$4)</f>
         <v>1000</v>
       </c>
-      <c r="AD23" s="41">
+      <c r="AE23" s="41">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AE23" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$W23,AE$4)</f>
-        <v>0</v>
-      </c>
-      <c r="AF23" s="38">
+      <c r="AF23" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$X23,AF$4)</f>
+        <v>0</v>
+      </c>
+      <c r="AG23" s="38">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AG23" s="91">
-        <f>INDEX(pigs!$D$3:$AO$60,$W23,AG$4)/1000*100</f>
-        <v>0</v>
-      </c>
-      <c r="AH23" s="92">
-        <f>INDEX(pigs!$D$3:$AO$60,$W23,AH$4)/1000*100</f>
-        <v>0</v>
-      </c>
-      <c r="AK23" s="68">
+      <c r="AH23" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$X23,AH$4)/1000*100</f>
+        <v>0</v>
+      </c>
+      <c r="AI23" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$X23,AI$4)/1000*100</f>
+        <v>0</v>
+      </c>
+      <c r="AL23" s="68">
         <f>MATCH($B23,poultry!$A$3:$A$41,0)</f>
         <v>1</v>
       </c>
-      <c r="AL23" s="59">
-        <f>INDEX(poultry!$D$3:$U$41,$AK23,AL$4)</f>
+      <c r="AM23" s="59">
+        <f>INDEX(poultry!$D$3:$U$41,$AL23,AM$4)</f>
         <v>99</v>
       </c>
     </row>
-    <row r="24" spans="2:38" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>302</v>
       </c>
       <c r="C24" s="65">
+        <f>AVERAGE(Y24,K24)</f>
+        <v>85</v>
+      </c>
+      <c r="D24" s="64">
         <f t="shared" si="9"/>
-        <v>85</v>
-      </c>
-      <c r="D24" s="64">
-        <f t="shared" si="10"/>
         <v>16.927627199999996</v>
       </c>
       <c r="E24" s="38">
@@ -10240,79 +10290,80 @@
         <v>1.6800000000000002</v>
       </c>
       <c r="H24" s="4"/>
-      <c r="I24" s="68">
+      <c r="I24" s="4"/>
+      <c r="J24" s="68">
         <f>MATCH($B24,ruminants!$A$3:$A$120,0)</f>
         <v>22</v>
       </c>
-      <c r="J24" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I24,J$4)</f>
+      <c r="K24" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J24,K$4)</f>
         <v>85</v>
       </c>
-      <c r="K24" s="77">
+      <c r="L24" s="77">
         <f t="shared" si="11"/>
         <v>16.927627199999996</v>
       </c>
-      <c r="L24" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I24,L$4)</f>
+      <c r="M24" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J24,M$4)</f>
         <v>6.6</v>
       </c>
-      <c r="M24" s="65">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I24,M$4)</f>
+      <c r="N24" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J24,N$4)</f>
         <v>69</v>
       </c>
-      <c r="N24" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I24,N$4)</f>
+      <c r="O24" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J24,O$4)</f>
         <v>20</v>
       </c>
-      <c r="O24" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I24,O$4)</f>
+      <c r="P24" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J24,P$4)</f>
         <v>436</v>
       </c>
-      <c r="P24" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I24,P$4)</f>
+      <c r="Q24" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J24,Q$4)</f>
         <v>409</v>
       </c>
-      <c r="Q24" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I24,Q$4)</f>
+      <c r="R24" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J24,R$4)</f>
         <v>66</v>
       </c>
-      <c r="R24" s="38">
+      <c r="S24" s="38">
         <f t="shared" si="8"/>
         <v>1.1040000000000001</v>
       </c>
-      <c r="S24" s="91">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I24,S$4)/1000*100</f>
+      <c r="T24" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J24,T$4)/1000*100</f>
         <v>0.26</v>
       </c>
-      <c r="T24" s="92">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I24,T$4)/1000*100</f>
+      <c r="U24" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J24,U$4)/1000*100</f>
         <v>1.6800000000000002</v>
       </c>
-      <c r="W24" s="68"/>
-      <c r="X24" s="37"/>
-      <c r="Y24" s="54"/>
+      <c r="X24" s="68"/>
+      <c r="Y24" s="37"/>
       <c r="Z24" s="54"/>
       <c r="AA24" s="54"/>
-      <c r="AB24" s="37"/>
-      <c r="AC24" s="54"/>
+      <c r="AB24" s="54"/>
+      <c r="AC24" s="37"/>
       <c r="AD24" s="54"/>
-      <c r="AE24" s="55"/>
-      <c r="AF24" s="38"/>
-      <c r="AG24" s="91"/>
-      <c r="AH24" s="92"/>
-      <c r="AK24" s="68"/>
-      <c r="AL24" s="59"/>
-    </row>
-    <row r="25" spans="2:38" x14ac:dyDescent="0.25">
+      <c r="AE24" s="54"/>
+      <c r="AF24" s="55"/>
+      <c r="AG24" s="38"/>
+      <c r="AH24" s="91"/>
+      <c r="AI24" s="92"/>
+      <c r="AL24" s="68"/>
+      <c r="AM24" s="59"/>
+    </row>
+    <row r="25" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>314</v>
       </c>
       <c r="C25" s="65">
+        <f>AVERAGE(Y25,K25)</f>
+        <v>87</v>
+      </c>
+      <c r="D25" s="64">
         <f t="shared" si="9"/>
-        <v>87</v>
-      </c>
-      <c r="D25" s="64">
-        <f t="shared" si="10"/>
         <v>22.965976000000001</v>
       </c>
       <c r="E25" s="38">
@@ -10328,79 +10379,80 @@
         <v>1.9</v>
       </c>
       <c r="H25" s="4"/>
-      <c r="I25" s="68">
+      <c r="I25" s="4"/>
+      <c r="J25" s="68">
         <f>MATCH($B25,ruminants!$A$3:$A$120,0)</f>
         <v>92</v>
       </c>
-      <c r="J25" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I25,J$4)</f>
+      <c r="K25" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J25,K$4)</f>
         <v>87</v>
       </c>
-      <c r="K25" s="77">
+      <c r="L25" s="77">
         <f t="shared" si="11"/>
         <v>22.965976000000001</v>
       </c>
-      <c r="L25" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I25,L$4)</f>
+      <c r="M25" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J25,M$4)</f>
         <v>16.399999999999999</v>
       </c>
-      <c r="M25" s="65">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I25,M$4)</f>
+      <c r="N25" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J25,N$4)</f>
         <v>400</v>
       </c>
-      <c r="N25" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I25,N$4)</f>
+      <c r="O25" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J25,O$4)</f>
         <v>180</v>
       </c>
-      <c r="O25" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I25,O$4)</f>
+      <c r="P25" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J25,P$4)</f>
         <v>60</v>
       </c>
-      <c r="P25" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I25,P$4)</f>
+      <c r="Q25" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J25,Q$4)</f>
         <v>310</v>
       </c>
-      <c r="Q25" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I25,Q$4)</f>
+      <c r="R25" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J25,R$4)</f>
         <v>50</v>
       </c>
-      <c r="R25" s="38">
+      <c r="S25" s="38">
         <f t="shared" si="8"/>
         <v>6.4</v>
       </c>
-      <c r="S25" s="91">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I25,S$4)/1000*100</f>
+      <c r="T25" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J25,T$4)/1000*100</f>
         <v>0.63</v>
       </c>
-      <c r="T25" s="92">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I25,T$4)/1000*100</f>
+      <c r="U25" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J25,U$4)/1000*100</f>
         <v>1.9</v>
       </c>
-      <c r="W25" s="68"/>
-      <c r="X25" s="37"/>
-      <c r="Y25" s="54"/>
+      <c r="X25" s="68"/>
+      <c r="Y25" s="37"/>
       <c r="Z25" s="54"/>
       <c r="AA25" s="54"/>
-      <c r="AB25" s="37"/>
-      <c r="AC25" s="54"/>
+      <c r="AB25" s="54"/>
+      <c r="AC25" s="37"/>
       <c r="AD25" s="54"/>
-      <c r="AE25" s="55"/>
-      <c r="AF25" s="38"/>
-      <c r="AG25" s="91"/>
-      <c r="AH25" s="92"/>
-      <c r="AK25" s="68"/>
-      <c r="AL25" s="59"/>
-    </row>
-    <row r="26" spans="2:38" x14ac:dyDescent="0.25">
+      <c r="AE25" s="54"/>
+      <c r="AF25" s="55"/>
+      <c r="AG25" s="38"/>
+      <c r="AH25" s="91"/>
+      <c r="AI25" s="92"/>
+      <c r="AL25" s="68"/>
+      <c r="AM25" s="59"/>
+    </row>
+    <row r="26" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>44</v>
       </c>
       <c r="C26" s="65">
+        <f>AVERAGE(Y26,K26)</f>
+        <v>87.5</v>
+      </c>
+      <c r="D26" s="64">
         <f t="shared" si="9"/>
-        <v>87.5</v>
-      </c>
-      <c r="D26" s="64">
-        <f t="shared" si="10"/>
         <v>19.589487999999999</v>
       </c>
       <c r="E26" s="38">
@@ -10416,121 +10468,122 @@
         <v>2.3499999999999996</v>
       </c>
       <c r="H26" s="4"/>
-      <c r="I26" s="68">
+      <c r="I26" s="4"/>
+      <c r="J26" s="68">
         <f>MATCH($B26,ruminants!$A$3:$A$120,0)</f>
         <v>93</v>
       </c>
-      <c r="J26" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I26,J$4)</f>
+      <c r="K26" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J26,K$4)</f>
         <v>87</v>
       </c>
-      <c r="K26" s="77">
+      <c r="L26" s="77">
         <f t="shared" si="11"/>
         <v>19.589487999999999</v>
       </c>
-      <c r="L26" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I26,L$4)</f>
+      <c r="M26" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J26,M$4)</f>
         <v>14.6</v>
       </c>
-      <c r="M26" s="65">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I26,M$4)</f>
+      <c r="N26" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J26,N$4)</f>
         <v>510</v>
       </c>
-      <c r="N26" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I26,N$4)</f>
+      <c r="O26" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J26,O$4)</f>
         <v>10</v>
       </c>
-      <c r="O26" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I26,O$4)</f>
+      <c r="P26" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J26,P$4)</f>
         <v>60</v>
       </c>
-      <c r="P26" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I26,P$4)</f>
+      <c r="Q26" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J26,Q$4)</f>
         <v>350</v>
       </c>
-      <c r="Q26" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I26,Q$4)</f>
+      <c r="R26" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J26,R$4)</f>
         <v>70</v>
       </c>
-      <c r="R26" s="38">
+      <c r="S26" s="38">
         <f t="shared" si="8"/>
         <v>8.16</v>
       </c>
-      <c r="S26" s="91">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I26,S$4)/1000*100</f>
+      <c r="T26" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J26,T$4)/1000*100</f>
         <v>0.72</v>
       </c>
-      <c r="T26" s="92">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I26,T$4)/1000*100</f>
+      <c r="U26" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J26,U$4)/1000*100</f>
         <v>2.2999999999999998</v>
       </c>
-      <c r="W26" s="68">
+      <c r="X26" s="68">
         <f>MATCH($B26,pigs!$A$3:$A$60,0)</f>
         <v>43</v>
       </c>
-      <c r="X26" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W26,X$4)</f>
+      <c r="Y26" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X26,Y$4)</f>
         <v>88</v>
       </c>
-      <c r="Y26" s="77">
-        <f t="shared" ref="Y26:Y30" si="23">( 5.7*AB26+9.4*AC26+4.1*(AD26) ) * 0.004184</f>
+      <c r="Z26" s="77">
+        <f t="shared" ref="Z26:Z30" si="23">( 5.7*AC26+9.4*AD26+4.1*(AE26) ) * 0.004184</f>
         <v>19.822118400000001</v>
       </c>
-      <c r="Z26" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W26,Z$4)</f>
+      <c r="AA26" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X26,AA$4)</f>
         <v>9.3000000000000007</v>
       </c>
-      <c r="AA26" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W26,AA$4)</f>
+      <c r="AB26" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X26,AB$4)</f>
         <v>9.9</v>
       </c>
-      <c r="AB26" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W26,AB$4)</f>
+      <c r="AC26" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X26,AC$4)</f>
         <v>516</v>
       </c>
-      <c r="AC26" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W26,AC$4)</f>
+      <c r="AD26" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X26,AD$4)</f>
         <v>21</v>
       </c>
-      <c r="AD26" s="41">
-        <f t="shared" ref="AD26:AD30" si="24">1000-SUM(AB26:AC26,AE26)</f>
+      <c r="AE26" s="41">
+        <f t="shared" ref="AE26:AE30" si="24">1000-SUM(AC26:AD26,AF26)</f>
         <v>390</v>
       </c>
-      <c r="AE26" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$W26,AE$4)</f>
+      <c r="AF26" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$X26,AF$4)</f>
         <v>73</v>
       </c>
-      <c r="AF26" s="38">
+      <c r="AG26" s="38">
         <f t="shared" si="14"/>
         <v>8.2560000000000002</v>
       </c>
-      <c r="AG26" s="91">
-        <f>INDEX(pigs!$D$3:$AO$60,$W26,AG$4)/1000*100</f>
+      <c r="AH26" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$X26,AH$4)/1000*100</f>
         <v>0.71</v>
       </c>
-      <c r="AH26" s="92">
-        <f>INDEX(pigs!$D$3:$AO$60,$W26,AH$4)/1000*100</f>
+      <c r="AI26" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$X26,AI$4)/1000*100</f>
         <v>2.4</v>
       </c>
-      <c r="AK26" s="68">
+      <c r="AL26" s="68">
         <f>MATCH($B26,poultry!$A$3:$A$41,0)</f>
         <v>33</v>
       </c>
-      <c r="AL26" s="59">
-        <f>INDEX(poultry!$D$3:$U$41,$AK26,AL$4)</f>
+      <c r="AM26" s="59">
+        <f>INDEX(poultry!$D$3:$U$41,$AL26,AM$4)</f>
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="2:38" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>45</v>
       </c>
       <c r="C27" s="65">
-        <f t="shared" si="9"/>
+        <f>AVERAGE(Y27,K27)</f>
         <v>87</v>
       </c>
       <c r="D27" s="64">
-        <f>Y27</f>
+        <f>Z27</f>
         <v>20.560594400000003</v>
       </c>
       <c r="E27" s="38">
@@ -10546,79 +10599,80 @@
         <v>2.5</v>
       </c>
       <c r="H27" s="4"/>
-      <c r="I27" s="68"/>
-      <c r="J27" s="37"/>
-      <c r="K27" s="54"/>
-      <c r="L27" s="38"/>
-      <c r="M27" s="65"/>
-      <c r="N27" s="39"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="68"/>
+      <c r="K27" s="37"/>
+      <c r="L27" s="54"/>
+      <c r="M27" s="38"/>
+      <c r="N27" s="65"/>
       <c r="O27" s="39"/>
       <c r="P27" s="39"/>
-      <c r="Q27" s="42"/>
-      <c r="R27" s="38"/>
-      <c r="S27" s="39"/>
-      <c r="T27" s="42"/>
-      <c r="W27" s="68">
+      <c r="Q27" s="39"/>
+      <c r="R27" s="42"/>
+      <c r="S27" s="38"/>
+      <c r="T27" s="39"/>
+      <c r="U27" s="42"/>
+      <c r="X27" s="68">
         <f>MATCH($B27,pigs!$A$3:$A$60,0)</f>
         <v>45</v>
       </c>
-      <c r="X27" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W27,X$4)</f>
+      <c r="Y27" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X27,Y$4)</f>
         <v>87</v>
       </c>
-      <c r="Y27" s="77">
+      <c r="Z27" s="77">
         <f t="shared" si="23"/>
         <v>20.560594400000003</v>
       </c>
-      <c r="Z27" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W27,Z$4)</f>
+      <c r="AA27" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X27,AA$4)</f>
         <v>9.6999999999999993</v>
       </c>
-      <c r="AA27" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W27,AA$4)</f>
+      <c r="AB27" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X27,AB$4)</f>
         <v>10.3</v>
       </c>
-      <c r="AB27" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W27,AB$4)</f>
+      <c r="AC27" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X27,AC$4)</f>
         <v>609</v>
       </c>
-      <c r="AC27" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W27,AC$4)</f>
+      <c r="AD27" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X27,AD$4)</f>
         <v>27</v>
       </c>
-      <c r="AD27" s="41">
+      <c r="AE27" s="41">
         <f t="shared" si="24"/>
         <v>290</v>
       </c>
-      <c r="AE27" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$W27,AE$4)</f>
+      <c r="AF27" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$X27,AF$4)</f>
         <v>74</v>
       </c>
-      <c r="AF27" s="38">
+      <c r="AG27" s="38">
         <f t="shared" si="14"/>
         <v>9.7439999999999998</v>
       </c>
-      <c r="AG27" s="91">
-        <f>INDEX(pigs!$D$3:$AO$60,$W27,AG$4)/1000*100</f>
+      <c r="AH27" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$X27,AH$4)/1000*100</f>
         <v>0.86999999999999988</v>
       </c>
-      <c r="AH27" s="92">
-        <f>INDEX(pigs!$D$3:$AO$60,$W27,AH$4)/1000*100</f>
+      <c r="AI27" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$X27,AI$4)/1000*100</f>
         <v>2.5</v>
       </c>
-      <c r="AK27" s="68"/>
-      <c r="AL27" s="59"/>
-    </row>
-    <row r="28" spans="2:38" x14ac:dyDescent="0.25">
+      <c r="AL27" s="68"/>
+      <c r="AM27" s="59"/>
+    </row>
+    <row r="28" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>36</v>
       </c>
       <c r="C28" s="65">
-        <f t="shared" si="9"/>
+        <f>AVERAGE(Y28,K28)</f>
         <v>89.5</v>
       </c>
       <c r="D28" s="64">
-        <f t="shared" ref="D28:D34" si="25">K28</f>
+        <f t="shared" ref="D28:D34" si="25">L28</f>
         <v>19.4920008</v>
       </c>
       <c r="E28" s="38">
@@ -10634,117 +10688,118 @@
         <v>1.55</v>
       </c>
       <c r="H28" s="4"/>
-      <c r="I28" s="68">
+      <c r="I28" s="4"/>
+      <c r="J28" s="68">
         <f>MATCH($B28,ruminants!$A$3:$A$120,0)</f>
         <v>70</v>
       </c>
-      <c r="J28" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I28,J$4)</f>
+      <c r="K28" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J28,K$4)</f>
         <v>90</v>
       </c>
-      <c r="K28" s="77">
+      <c r="L28" s="77">
         <f t="shared" si="11"/>
         <v>19.4920008</v>
       </c>
-      <c r="L28" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I28,L$4)</f>
+      <c r="M28" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J28,M$4)</f>
         <v>12.2</v>
       </c>
-      <c r="M28" s="65">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I28,M$4)</f>
+      <c r="N28" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J28,N$4)</f>
         <v>389</v>
       </c>
-      <c r="N28" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I28,N$4)</f>
+      <c r="O28" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J28,O$4)</f>
         <v>46</v>
       </c>
-      <c r="O28" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I28,O$4)</f>
+      <c r="P28" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J28,P$4)</f>
         <v>140</v>
       </c>
-      <c r="P28" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I28,P$4)</f>
+      <c r="Q28" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J28,Q$4)</f>
         <v>350</v>
       </c>
-      <c r="Q28" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I28,Q$4)</f>
+      <c r="R28" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J28,R$4)</f>
         <v>75</v>
       </c>
-      <c r="R28" s="38">
+      <c r="S28" s="38">
         <f t="shared" si="8"/>
         <v>6.2240000000000002</v>
       </c>
-      <c r="S28" s="91">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I28,S$4)/1000*100</f>
+      <c r="T28" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J28,T$4)/1000*100</f>
         <v>1.2</v>
       </c>
-      <c r="T28" s="92">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I28,T$4)/1000*100</f>
+      <c r="U28" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J28,U$4)/1000*100</f>
         <v>1.6</v>
       </c>
-      <c r="W28" s="68">
+      <c r="X28" s="68">
         <f>MATCH($B28,pigs!$A$3:$A$60,0)</f>
         <v>36</v>
       </c>
-      <c r="X28" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W28,X$4)</f>
+      <c r="Y28" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X28,Y$4)</f>
         <v>89</v>
       </c>
-      <c r="Y28" s="77">
+      <c r="Z28" s="77">
         <f t="shared" si="23"/>
         <v>18.9196296</v>
       </c>
-      <c r="Z28" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W28,Z$4)</f>
+      <c r="AA28" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X28,AA$4)</f>
         <v>7.1</v>
       </c>
-      <c r="AA28" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W28,AA$4)</f>
+      <c r="AB28" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X28,AB$4)</f>
         <v>7.7</v>
       </c>
-      <c r="AB28" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W28,AB$4)</f>
+      <c r="AC28" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X28,AC$4)</f>
         <v>380</v>
       </c>
-      <c r="AC28" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W28,AC$4)</f>
+      <c r="AD28" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X28,AD$4)</f>
         <v>26</v>
       </c>
-      <c r="AD28" s="41">
+      <c r="AE28" s="41">
         <f t="shared" si="24"/>
         <v>515</v>
       </c>
-      <c r="AE28" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$W28,AE$4)</f>
+      <c r="AF28" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$X28,AF$4)</f>
         <v>79</v>
       </c>
-      <c r="AF28" s="38">
+      <c r="AG28" s="38">
         <f t="shared" si="14"/>
         <v>6.080000000000001</v>
       </c>
-      <c r="AG28" s="91">
-        <f>INDEX(pigs!$D$3:$AO$60,$W28,AG$4)/1000*100</f>
+      <c r="AH28" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$X28,AH$4)/1000*100</f>
         <v>1.29</v>
       </c>
-      <c r="AH28" s="92">
-        <f>INDEX(pigs!$D$3:$AO$60,$W28,AH$4)/1000*100</f>
+      <c r="AI28" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$X28,AI$4)/1000*100</f>
         <v>1.5</v>
       </c>
-      <c r="AK28" s="68">
+      <c r="AL28" s="68">
         <f>MATCH($B28,poultry!$A$3:$A$41,0)</f>
         <v>29</v>
       </c>
-      <c r="AL28" s="59">
-        <f>INDEX(poultry!$D$3:$U$41,$AK28,AL$4)</f>
+      <c r="AM28" s="59">
+        <f>INDEX(poultry!$D$3:$U$41,$AL28,AM$4)</f>
         <v>90</v>
       </c>
     </row>
-    <row r="29" spans="2:38" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>46</v>
       </c>
       <c r="C29" s="65">
-        <f t="shared" si="9"/>
+        <f>AVERAGE(Y29,K29)</f>
         <v>91</v>
       </c>
       <c r="D29" s="64">
@@ -10764,111 +10819,112 @@
         <v>1.75</v>
       </c>
       <c r="H29" s="4"/>
-      <c r="I29" s="68">
+      <c r="I29" s="4"/>
+      <c r="J29" s="68">
         <f>MATCH($B29,ruminants!$A$3:$A$120,0)</f>
         <v>99</v>
       </c>
-      <c r="J29" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I29,J$4)</f>
+      <c r="K29" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J29,K$4)</f>
         <v>92</v>
       </c>
-      <c r="K29" s="77">
+      <c r="L29" s="77">
         <f t="shared" si="11"/>
         <v>19.083224000000001</v>
       </c>
-      <c r="L29" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I29,L$4)</f>
+      <c r="M29" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J29,M$4)</f>
         <v>11.4</v>
       </c>
-      <c r="M29" s="65">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I29,M$4)</f>
+      <c r="N29" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J29,N$4)</f>
         <v>460</v>
       </c>
-      <c r="N29" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I29,N$4)</f>
+      <c r="O29" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J29,O$4)</f>
         <v>10</v>
       </c>
-      <c r="O29" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I29,O$4)</f>
+      <c r="P29" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J29,P$4)</f>
         <v>170</v>
       </c>
-      <c r="P29" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I29,P$4)</f>
+      <c r="Q29" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J29,Q$4)</f>
         <v>280</v>
       </c>
-      <c r="Q29" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I29,Q$4)</f>
+      <c r="R29" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J29,R$4)</f>
         <v>80</v>
       </c>
-      <c r="R29" s="38">
+      <c r="S29" s="38">
         <f t="shared" si="8"/>
         <v>7.3600000000000012</v>
       </c>
-      <c r="S29" s="91">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I29,S$4)/1000*100</f>
+      <c r="T29" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J29,T$4)/1000*100</f>
         <v>1.35</v>
       </c>
-      <c r="T29" s="92">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I29,T$4)/1000*100</f>
+      <c r="U29" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J29,U$4)/1000*100</f>
         <v>1.7999999999999998</v>
       </c>
-      <c r="W29" s="68">
+      <c r="X29" s="68">
         <f>MATCH($B29,pigs!$A$3:$A$60,0)</f>
         <v>46</v>
       </c>
-      <c r="X29" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W29,X$4)</f>
+      <c r="Y29" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X29,Y$4)</f>
         <v>90</v>
       </c>
-      <c r="Y29" s="77">
+      <c r="Z29" s="77">
         <f t="shared" si="23"/>
         <v>18.786160000000002</v>
       </c>
-      <c r="Z29" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W29,Z$4)</f>
+      <c r="AA29" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X29,AA$4)</f>
         <v>5.9</v>
       </c>
-      <c r="AA29" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W29,AA$4)</f>
+      <c r="AB29" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X29,AB$4)</f>
         <v>6.5</v>
       </c>
-      <c r="AB29" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W29,AB$4)</f>
+      <c r="AC29" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X29,AC$4)</f>
         <v>373</v>
       </c>
-      <c r="AC29" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W29,AC$4)</f>
+      <c r="AD29" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X29,AD$4)</f>
         <v>19</v>
       </c>
-      <c r="AD29" s="41">
+      <c r="AE29" s="41">
         <f t="shared" si="24"/>
         <v>533</v>
       </c>
-      <c r="AE29" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$W29,AE$4)</f>
+      <c r="AF29" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$X29,AF$4)</f>
         <v>75</v>
       </c>
-      <c r="AF29" s="38">
+      <c r="AG29" s="38">
         <f t="shared" si="14"/>
         <v>5.968</v>
       </c>
-      <c r="AG29" s="91">
-        <f>INDEX(pigs!$D$3:$AO$60,$W29,AG$4)/1000*100</f>
+      <c r="AH29" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$X29,AH$4)/1000*100</f>
         <v>1.26</v>
       </c>
-      <c r="AH29" s="92">
-        <f>INDEX(pigs!$D$3:$AO$60,$W29,AH$4)/1000*100</f>
+      <c r="AI29" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$X29,AI$4)/1000*100</f>
         <v>1.7000000000000002</v>
       </c>
-      <c r="AK29" s="68"/>
-      <c r="AL29" s="59"/>
-    </row>
-    <row r="30" spans="2:38" x14ac:dyDescent="0.25">
+      <c r="AL29" s="68"/>
+      <c r="AM29" s="59"/>
+    </row>
+    <row r="30" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>47</v>
       </c>
       <c r="C30" s="65">
-        <f t="shared" si="9"/>
+        <f>AVERAGE(Y30,K30)</f>
         <v>91</v>
       </c>
       <c r="D30" s="64">
@@ -10888,111 +10944,112 @@
         <v>0.77500000000000002</v>
       </c>
       <c r="H30" s="4"/>
-      <c r="I30" s="68">
+      <c r="I30" s="4"/>
+      <c r="J30" s="68">
         <f>MATCH($B30,ruminants!$A$3:$A$120,0)</f>
         <v>60</v>
       </c>
-      <c r="J30" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I30,J$4)</f>
+      <c r="K30" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J30,K$4)</f>
         <v>91</v>
       </c>
-      <c r="K30" s="77">
+      <c r="L30" s="77">
         <f t="shared" si="11"/>
         <v>19.581538399999999</v>
       </c>
-      <c r="L30" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I30,L$4)</f>
+      <c r="M30" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J30,M$4)</f>
         <v>13.4</v>
       </c>
-      <c r="M30" s="65">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I30,M$4)</f>
+      <c r="N30" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J30,N$4)</f>
         <v>154</v>
       </c>
-      <c r="N30" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I30,N$4)</f>
+      <c r="O30" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J30,O$4)</f>
         <v>97</v>
       </c>
-      <c r="O30" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I30,O$4)</f>
+      <c r="P30" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J30,P$4)</f>
         <v>228</v>
       </c>
-      <c r="P30" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I30,P$4)</f>
+      <c r="Q30" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J30,Q$4)</f>
         <v>477</v>
       </c>
-      <c r="Q30" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I30,Q$4)</f>
+      <c r="R30" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J30,R$4)</f>
         <v>44</v>
       </c>
-      <c r="R30" s="38">
+      <c r="S30" s="38">
         <f t="shared" si="8"/>
         <v>2.4640000000000004</v>
       </c>
-      <c r="S30" s="91">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I30,S$4)/1000*100</f>
+      <c r="T30" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J30,T$4)/1000*100</f>
         <v>0.65</v>
       </c>
-      <c r="T30" s="92">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I30,T$4)/1000*100</f>
+      <c r="U30" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J30,U$4)/1000*100</f>
         <v>0.8</v>
       </c>
-      <c r="W30" s="68">
+      <c r="X30" s="68">
         <f>MATCH($B30,pigs!$A$3:$A$60,0)</f>
         <v>29</v>
       </c>
-      <c r="X30" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W30,X$4)</f>
+      <c r="Y30" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X30,Y$4)</f>
         <v>91</v>
       </c>
-      <c r="Y30" s="77">
+      <c r="Z30" s="77">
         <f t="shared" si="23"/>
         <v>19.540953599999998</v>
       </c>
-      <c r="Z30" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W30,Z$4)</f>
+      <c r="AA30" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X30,AA$4)</f>
         <v>5.4</v>
       </c>
-      <c r="AA30" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W30,AA$4)</f>
+      <c r="AB30" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X30,AB$4)</f>
         <v>6.2</v>
       </c>
-      <c r="AB30" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W30,AB$4)</f>
+      <c r="AC30" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X30,AC$4)</f>
         <v>163</v>
       </c>
-      <c r="AC30" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W30,AC$4)</f>
+      <c r="AD30" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X30,AD$4)</f>
         <v>94</v>
       </c>
-      <c r="AD30" s="41">
+      <c r="AE30" s="41">
         <f t="shared" si="24"/>
         <v>697</v>
       </c>
-      <c r="AE30" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$W30,AE$4)</f>
+      <c r="AF30" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$X30,AF$4)</f>
         <v>46</v>
       </c>
-      <c r="AF30" s="38">
+      <c r="AG30" s="38">
         <f t="shared" si="14"/>
         <v>2.6080000000000001</v>
       </c>
-      <c r="AG30" s="91">
-        <f>INDEX(pigs!$D$3:$AO$60,$W30,AG$4)/1000*100</f>
+      <c r="AH30" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$X30,AH$4)/1000*100</f>
         <v>0.64</v>
       </c>
-      <c r="AH30" s="92">
-        <f>INDEX(pigs!$D$3:$AO$60,$W30,AH$4)/1000*100</f>
+      <c r="AI30" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$X30,AI$4)/1000*100</f>
         <v>0.75</v>
       </c>
-      <c r="AK30" s="68"/>
-      <c r="AL30" s="59"/>
-    </row>
-    <row r="31" spans="2:38" x14ac:dyDescent="0.25">
+      <c r="AL30" s="68"/>
+      <c r="AM30" s="59"/>
+    </row>
+    <row r="31" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>315</v>
       </c>
       <c r="C31" s="65">
-        <f t="shared" si="9"/>
+        <f>AVERAGE(Y31,K31)</f>
         <v>90</v>
       </c>
       <c r="D31" s="64">
@@ -11012,72 +11069,73 @@
         <v>2.56</v>
       </c>
       <c r="H31" s="4"/>
-      <c r="I31" s="68"/>
-      <c r="J31" s="37">
+      <c r="I31" s="4"/>
+      <c r="J31" s="68"/>
+      <c r="K31" s="37">
         <v>90</v>
       </c>
-      <c r="K31" s="77">
+      <c r="L31" s="77">
         <f t="shared" si="11"/>
         <v>16.971140800000001</v>
       </c>
-      <c r="L31" s="38">
+      <c r="M31" s="38">
         <v>8.5</v>
       </c>
-      <c r="M31" s="65">
+      <c r="N31" s="65">
         <v>183</v>
       </c>
-      <c r="N31" s="39">
+      <c r="O31" s="39">
         <v>27</v>
       </c>
-      <c r="O31" s="39">
+      <c r="P31" s="39">
         <v>286</v>
       </c>
-      <c r="P31" s="41">
-        <f>1000-SUM(M31:O31,Q31)</f>
+      <c r="Q31" s="41">
+        <f>1000-SUM(N31:P31,R31)</f>
         <v>387</v>
       </c>
-      <c r="Q31" s="42">
+      <c r="R31" s="42">
         <v>117</v>
       </c>
-      <c r="R31" s="38">
+      <c r="S31" s="38">
         <f t="shared" si="8"/>
         <v>2.9279999999999999</v>
       </c>
-      <c r="S31" s="91">
+      <c r="T31" s="91">
         <f>2.7/1000*100</f>
         <v>0.27</v>
       </c>
-      <c r="T31" s="92">
+      <c r="U31" s="92">
         <f>25.6/1000*100</f>
         <v>2.56</v>
       </c>
-      <c r="U31" s="11" t="s">
+      <c r="V31" s="11" t="s">
         <v>316</v>
       </c>
-      <c r="V31" s="11" t="s">
-        <v>489</v>
-      </c>
-      <c r="W31" s="68"/>
-      <c r="X31" s="37"/>
-      <c r="Y31" s="54"/>
+      <c r="W31" s="11" t="s">
+        <v>488</v>
+      </c>
+      <c r="X31" s="68"/>
+      <c r="Y31" s="37"/>
       <c r="Z31" s="54"/>
       <c r="AA31" s="54"/>
-      <c r="AB31" s="37"/>
-      <c r="AC31" s="54"/>
+      <c r="AB31" s="54"/>
+      <c r="AC31" s="37"/>
       <c r="AD31" s="54"/>
-      <c r="AE31" s="55"/>
-      <c r="AF31" s="38"/>
-      <c r="AG31" s="91"/>
-      <c r="AH31" s="92"/>
-      <c r="AK31" s="68"/>
-      <c r="AL31" s="59"/>
-    </row>
-    <row r="32" spans="2:38" x14ac:dyDescent="0.25">
+      <c r="AE31" s="54"/>
+      <c r="AF31" s="55"/>
+      <c r="AG31" s="38"/>
+      <c r="AH31" s="91"/>
+      <c r="AI31" s="92"/>
+      <c r="AL31" s="68"/>
+      <c r="AM31" s="59"/>
+    </row>
+    <row r="32" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>48</v>
       </c>
       <c r="C32" s="65">
-        <f t="shared" si="9"/>
+        <f>AVERAGE(Y32,K32)</f>
         <v>87</v>
       </c>
       <c r="D32" s="64">
@@ -11097,117 +11155,118 @@
         <v>1.35</v>
       </c>
       <c r="H32" s="4"/>
-      <c r="I32" s="68">
+      <c r="I32" s="4"/>
+      <c r="J32" s="68">
         <f>MATCH($B32,ruminants!$A$3:$A$120,0)</f>
         <v>111</v>
       </c>
-      <c r="J32" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I32,J$4)</f>
+      <c r="K32" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J32,K$4)</f>
         <v>87</v>
       </c>
-      <c r="K32" s="77">
+      <c r="L32" s="77">
         <f t="shared" si="11"/>
         <v>18.194124000000002</v>
       </c>
-      <c r="L32" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I32,L$4)</f>
+      <c r="M32" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J32,M$4)</f>
         <v>11</v>
       </c>
-      <c r="M32" s="65">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I32,M$4)</f>
+      <c r="N32" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J32,N$4)</f>
         <v>160</v>
       </c>
-      <c r="N32" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I32,N$4)</f>
+      <c r="O32" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J32,O$4)</f>
         <v>45</v>
       </c>
-      <c r="O32" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I32,O$4)</f>
+      <c r="P32" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J32,P$4)</f>
         <v>115</v>
       </c>
-      <c r="P32" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I32,P$4)</f>
+      <c r="Q32" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J32,Q$4)</f>
         <v>620</v>
       </c>
-      <c r="Q32" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I32,Q$4)</f>
+      <c r="R32" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J32,R$4)</f>
         <v>60</v>
       </c>
-      <c r="R32" s="38">
+      <c r="S32" s="38">
         <f t="shared" si="8"/>
         <v>2.56</v>
       </c>
-      <c r="S32" s="91">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I32,S$4)/1000*100</f>
+      <c r="T32" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J32,T$4)/1000*100</f>
         <v>1.2</v>
       </c>
-      <c r="T32" s="92">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I32,T$4)/1000*100</f>
+      <c r="U32" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J32,U$4)/1000*100</f>
         <v>1.2</v>
       </c>
-      <c r="W32" s="68">
+      <c r="X32" s="68">
         <f>MATCH($B32,pigs!$A$3:$A$60,0)</f>
         <v>55</v>
       </c>
-      <c r="X32" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W32,X$4)</f>
+      <c r="Y32" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X32,Y$4)</f>
         <v>87</v>
       </c>
-      <c r="Y32" s="77">
-        <f t="shared" ref="Y32:Y37" si="26">( 5.7*AB32+9.4*AC32+4.1*(AD32) ) * 0.004184</f>
+      <c r="Z32" s="77">
+        <f t="shared" ref="Z32:Z37" si="26">( 5.7*AC32+9.4*AD32+4.1*(AE32) ) * 0.004184</f>
         <v>18.184500799999999</v>
       </c>
-      <c r="Z32" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W32,Z$4)</f>
+      <c r="AA32" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X32,AA$4)</f>
         <v>7.2</v>
       </c>
-      <c r="AA32" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W32,AA$4)</f>
+      <c r="AB32" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X32,AB$4)</f>
         <v>7.8</v>
       </c>
-      <c r="AB32" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W32,AB$4)</f>
+      <c r="AC32" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X32,AC$4)</f>
         <v>170</v>
       </c>
-      <c r="AC32" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W32,AC$4)</f>
+      <c r="AD32" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X32,AD$4)</f>
         <v>40</v>
       </c>
-      <c r="AD32" s="41">
-        <f t="shared" ref="AD32:AD36" si="27">1000-SUM(AB32:AC32,AE32)</f>
+      <c r="AE32" s="41">
+        <f t="shared" ref="AE32:AE36" si="27">1000-SUM(AC32:AD32,AF32)</f>
         <v>732</v>
       </c>
-      <c r="AE32" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$W32,AE$4)</f>
+      <c r="AF32" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$X32,AF$4)</f>
         <v>58</v>
       </c>
-      <c r="AF32" s="38">
+      <c r="AG32" s="38">
         <f t="shared" si="14"/>
         <v>2.7199999999999998</v>
       </c>
-      <c r="AG32" s="91">
-        <f>INDEX(pigs!$D$3:$AO$60,$W32,AG$4)/1000*100</f>
+      <c r="AH32" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$X32,AH$4)/1000*100</f>
         <v>1.1900000000000002</v>
       </c>
-      <c r="AH32" s="92">
-        <f>INDEX(pigs!$D$3:$AO$60,$W32,AH$4)/1000*100</f>
+      <c r="AI32" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$X32,AI$4)/1000*100</f>
         <v>1.5</v>
       </c>
-      <c r="AK32" s="68">
+      <c r="AL32" s="68">
         <f>MATCH($B32,poultry!$A$3:$A$41,0)</f>
         <v>38</v>
       </c>
-      <c r="AL32" s="59">
-        <f>INDEX(poultry!$D$3:$U$41,$AK32,AL$4)</f>
+      <c r="AM32" s="59">
+        <f>INDEX(poultry!$D$3:$U$41,$AL32,AM$4)</f>
         <v>87</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>49</v>
       </c>
       <c r="C33" s="65">
-        <f t="shared" si="9"/>
+        <f>AVERAGE(Y33,K33)</f>
         <v>87.8</v>
       </c>
       <c r="D33" s="64">
@@ -11227,114 +11286,115 @@
         <v>0.96</v>
       </c>
       <c r="H33" s="4"/>
-      <c r="I33" s="68"/>
-      <c r="J33" s="65">
+      <c r="I33" s="4"/>
+      <c r="J33" s="68"/>
+      <c r="K33" s="65">
         <v>87.6</v>
       </c>
-      <c r="K33" s="77">
+      <c r="L33" s="77">
         <f t="shared" si="11"/>
         <v>18.472360000000002</v>
       </c>
-      <c r="L33" s="38">
+      <c r="M33" s="38">
         <v>13.3</v>
       </c>
-      <c r="M33" s="65">
+      <c r="N33" s="65">
         <v>151</v>
       </c>
-      <c r="N33" s="39">
+      <c r="O33" s="39">
         <v>27</v>
       </c>
-      <c r="O33" s="39">
+      <c r="P33" s="39">
         <v>11</v>
       </c>
-      <c r="P33" s="41">
-        <f>1000-SUM(M33:O33,Q33)</f>
+      <c r="Q33" s="41">
+        <f>1000-SUM(N33:P33,R33)</f>
         <v>794</v>
       </c>
-      <c r="Q33" s="45">
+      <c r="R33" s="45">
         <v>17</v>
       </c>
-      <c r="R33" s="38">
+      <c r="S33" s="38">
         <f t="shared" si="8"/>
         <v>2.4159999999999999</v>
       </c>
-      <c r="S33" s="91">
+      <c r="T33" s="91">
         <f>4.4/1000*100</f>
         <v>0.44</v>
       </c>
-      <c r="T33" s="92">
+      <c r="U33" s="92">
         <f>6.2/1000*100</f>
         <v>0.62</v>
       </c>
-      <c r="U33" s="11" t="s">
-        <v>509</v>
-      </c>
       <c r="V33" s="11" t="s">
-        <v>489</v>
-      </c>
-      <c r="W33" s="68">
+        <v>508</v>
+      </c>
+      <c r="W33" s="11" t="s">
+        <v>488</v>
+      </c>
+      <c r="X33" s="68">
         <f>MATCH($B33,pigs!$A$3:$A$60,0)</f>
         <v>54</v>
       </c>
-      <c r="X33" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W33,X$4)</f>
+      <c r="Y33" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X33,Y$4)</f>
         <v>88</v>
       </c>
-      <c r="Y33" s="77">
+      <c r="Z33" s="77">
         <f t="shared" si="26"/>
         <v>18.379056800000001</v>
       </c>
-      <c r="Z33" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W33,Z$4)</f>
+      <c r="AA33" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X33,AA$4)</f>
         <v>8.6999999999999993</v>
       </c>
-      <c r="AA33" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W33,AA$4)</f>
+      <c r="AB33" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X33,AB$4)</f>
         <v>9.1999999999999993</v>
       </c>
-      <c r="AB33" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W33,AB$4)</f>
+      <c r="AC33" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X33,AC$4)</f>
         <v>176</v>
       </c>
-      <c r="AC33" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W33,AC$4)</f>
+      <c r="AD33" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X33,AD$4)</f>
         <v>40</v>
       </c>
-      <c r="AD33" s="41">
+      <c r="AE33" s="41">
         <f t="shared" si="27"/>
         <v>735</v>
       </c>
-      <c r="AE33" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$W33,AE$4)</f>
+      <c r="AF33" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$X33,AF$4)</f>
         <v>49</v>
       </c>
-      <c r="AF33" s="38">
+      <c r="AG33" s="38">
         <f t="shared" si="14"/>
         <v>2.8160000000000003</v>
       </c>
-      <c r="AG33" s="91">
-        <f>INDEX(pigs!$D$3:$AO$60,$W33,AG$4)/1000*100</f>
+      <c r="AH33" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$X33,AH$4)/1000*100</f>
         <v>1.1900000000000002</v>
       </c>
-      <c r="AH33" s="92">
-        <f>INDEX(pigs!$D$3:$AO$60,$W33,AH$4)/1000*100</f>
+      <c r="AI33" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$X33,AI$4)/1000*100</f>
         <v>1.3</v>
       </c>
-      <c r="AK33" s="68">
+      <c r="AL33" s="68">
         <f>MATCH($B33,poultry!$A$3:$A$41,0)</f>
         <v>36</v>
       </c>
-      <c r="AL33" s="59">
-        <f>INDEX(poultry!$D$3:$U$41,$AK33,AL$4)</f>
+      <c r="AM33" s="59">
+        <f>INDEX(poultry!$D$3:$U$41,$AL33,AM$4)</f>
         <v>87</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>50</v>
       </c>
       <c r="C34" s="65">
-        <f t="shared" si="9"/>
+        <f>AVERAGE(Y34,K34)</f>
         <v>90</v>
       </c>
       <c r="D34" s="64">
@@ -11354,115 +11414,116 @@
         <v>1.165</v>
       </c>
       <c r="H34" s="4"/>
-      <c r="I34" s="68">
+      <c r="I34" s="4"/>
+      <c r="J34" s="68">
         <f>MATCH($B34,ruminants!$A$3:$A$120,0)</f>
         <v>109</v>
       </c>
-      <c r="J34" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I34,J$4)</f>
+      <c r="K34" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J34,K$4)</f>
         <v>90</v>
       </c>
-      <c r="K34" s="77">
+      <c r="L34" s="77">
         <f t="shared" si="11"/>
         <v>19.659779199999999</v>
       </c>
-      <c r="L34" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I34,L$4)</f>
+      <c r="M34" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J34,M$4)</f>
         <v>13.3</v>
       </c>
-      <c r="M34" s="65">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I34,M$4)</f>
+      <c r="N34" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J34,N$4)</f>
         <v>320</v>
       </c>
-      <c r="N34" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I34,N$4)</f>
+      <c r="O34" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J34,O$4)</f>
         <v>45</v>
       </c>
-      <c r="O34" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I34,O$4)</f>
+      <c r="P34" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J34,P$4)</f>
         <v>106</v>
       </c>
-      <c r="P34" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I34,P$4)</f>
+      <c r="Q34" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J34,Q$4)</f>
         <v>492</v>
       </c>
-      <c r="Q34" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I34,Q$4)</f>
+      <c r="R34" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J34,R$4)</f>
         <v>37</v>
       </c>
-      <c r="R34" s="38">
+      <c r="S34" s="38">
         <f t="shared" si="8"/>
         <v>5.12</v>
       </c>
-      <c r="S34" s="91">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I34,S$4)/1000*100</f>
+      <c r="T34" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J34,T$4)/1000*100</f>
         <v>1.03</v>
       </c>
-      <c r="T34" s="92">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I34,T$4)/1000*100</f>
+      <c r="U34" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J34,U$4)/1000*100</f>
         <v>1.3699999999999999</v>
       </c>
-      <c r="W34" s="68">
+      <c r="X34" s="68">
         <f>MATCH($B34,pigs!$A$3:$A$60,0)</f>
         <v>3</v>
       </c>
-      <c r="X34" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W34,X$4)</f>
+      <c r="Y34" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X34,Y$4)</f>
         <v>90</v>
       </c>
-      <c r="Y34" s="77">
+      <c r="Z34" s="77">
         <f t="shared" si="26"/>
         <v>20.139265599999998</v>
       </c>
-      <c r="Z34" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W34,Z$4)</f>
+      <c r="AA34" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X34,AA$4)</f>
         <v>8.1</v>
       </c>
-      <c r="AA34" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W34,AA$4)</f>
+      <c r="AB34" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X34,AB$4)</f>
         <v>8.6999999999999993</v>
       </c>
-      <c r="AB34" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W34,AB$4)</f>
+      <c r="AC34" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X34,AC$4)</f>
         <v>340</v>
       </c>
-      <c r="AC34" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W34,AC$4)</f>
+      <c r="AD34" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X34,AD$4)</f>
         <v>66</v>
       </c>
-      <c r="AD34" s="41">
+      <c r="AE34" s="41">
         <f t="shared" si="27"/>
         <v>550</v>
       </c>
-      <c r="AE34" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$W34,AE$4)</f>
+      <c r="AF34" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$X34,AF$4)</f>
         <v>44</v>
       </c>
-      <c r="AF34" s="38">
+      <c r="AG34" s="38">
         <f t="shared" si="14"/>
         <v>5.4399999999999995</v>
       </c>
-      <c r="AG34" s="91">
-        <f>INDEX(pigs!$D$3:$AO$60,$W34,AG$4)/1000*100</f>
+      <c r="AH34" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$X34,AH$4)/1000*100</f>
         <v>0.73</v>
       </c>
-      <c r="AH34" s="92">
-        <f>INDEX(pigs!$D$3:$AO$60,$W34,AH$4)/1000*100</f>
+      <c r="AI34" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$X34,AI$4)/1000*100</f>
         <v>0.96</v>
       </c>
-      <c r="AK34" s="68"/>
-      <c r="AL34" s="59"/>
-    </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.25">
+      <c r="AL34" s="68"/>
+      <c r="AM34" s="59"/>
+    </row>
+    <row r="35" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>51</v>
       </c>
       <c r="C35" s="65">
-        <f t="shared" si="9"/>
+        <f>AVERAGE(Y35,K35)</f>
         <v>11</v>
       </c>
       <c r="D35" s="64">
-        <f>Y35</f>
+        <f>Z35</f>
         <v>18.8602168</v>
       </c>
       <c r="E35" s="38">
@@ -11478,79 +11539,80 @@
         <v>0</v>
       </c>
       <c r="H35" s="4"/>
-      <c r="I35" s="68"/>
-      <c r="J35" s="37"/>
-      <c r="K35" s="54"/>
-      <c r="L35" s="38"/>
-      <c r="M35" s="65"/>
-      <c r="N35" s="39"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="68"/>
+      <c r="K35" s="37"/>
+      <c r="L35" s="54"/>
+      <c r="M35" s="38"/>
+      <c r="N35" s="65"/>
       <c r="O35" s="39"/>
       <c r="P35" s="39"/>
-      <c r="Q35" s="42"/>
-      <c r="R35" s="38"/>
-      <c r="S35" s="39"/>
-      <c r="T35" s="42"/>
-      <c r="W35" s="68">
+      <c r="Q35" s="39"/>
+      <c r="R35" s="42"/>
+      <c r="S35" s="38"/>
+      <c r="T35" s="39"/>
+      <c r="U35" s="42"/>
+      <c r="X35" s="68">
         <f>MATCH($B35,pigs!$A$3:$A$60,0)</f>
         <v>1</v>
       </c>
-      <c r="X35" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W35,X$4)</f>
+      <c r="Y35" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X35,Y$4)</f>
         <v>11</v>
       </c>
-      <c r="Y35" s="77">
+      <c r="Z35" s="77">
         <f t="shared" si="26"/>
         <v>18.8602168</v>
       </c>
-      <c r="Z35" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W35,Z$4)</f>
+      <c r="AA35" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X35,AA$4)</f>
         <v>8.1999999999999993</v>
       </c>
-      <c r="AA35" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W35,AA$4)</f>
+      <c r="AB35" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X35,AB$4)</f>
         <v>8.9</v>
       </c>
-      <c r="AB35" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W35,AB$4)</f>
+      <c r="AC35" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X35,AC$4)</f>
         <v>280</v>
       </c>
-      <c r="AC35" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W35,AC$4)</f>
+      <c r="AD35" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X35,AD$4)</f>
         <v>45</v>
       </c>
-      <c r="AD35" s="41">
+      <c r="AE35" s="41">
         <f t="shared" si="27"/>
         <v>607</v>
       </c>
-      <c r="AE35" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$W35,AE$4)</f>
+      <c r="AF35" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$X35,AF$4)</f>
         <v>68</v>
       </c>
-      <c r="AF35" s="38">
+      <c r="AG35" s="38">
         <f t="shared" si="14"/>
         <v>4.4800000000000004</v>
       </c>
-      <c r="AG35" s="91">
-        <f>INDEX(pigs!$D$3:$AO$60,$W35,AG$4)/1000*100</f>
+      <c r="AH35" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$X35,AH$4)/1000*100</f>
         <v>1.0900000000000001</v>
       </c>
-      <c r="AH35" s="92">
-        <f>INDEX(pigs!$D$3:$AO$60,$W35,AH$4)/1000*100</f>
-        <v>0</v>
-      </c>
-      <c r="AK35" s="68"/>
-      <c r="AL35" s="59"/>
-    </row>
-    <row r="36" spans="2:38" x14ac:dyDescent="0.25">
+      <c r="AI35" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$X35,AI$4)/1000*100</f>
+        <v>0</v>
+      </c>
+      <c r="AL35" s="68"/>
+      <c r="AM35" s="59"/>
+    </row>
+    <row r="36" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>309</v>
       </c>
       <c r="C36" s="65">
-        <f t="shared" si="9"/>
+        <f>AVERAGE(Y36,K36)</f>
         <v>90</v>
       </c>
       <c r="D36" s="64">
-        <f>K36</f>
+        <f>L36</f>
         <v>19.848896</v>
       </c>
       <c r="E36" s="38">
@@ -11566,113 +11628,114 @@
         <v>0.19500000000000001</v>
       </c>
       <c r="H36" s="4"/>
-      <c r="I36" s="68">
+      <c r="I36" s="4"/>
+      <c r="J36" s="68">
         <f>MATCH($B36,ruminants!$A$3:$A$120,0)</f>
         <v>38</v>
       </c>
-      <c r="J36" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I36,J$4)</f>
+      <c r="K36" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J36,K$4)</f>
         <v>90</v>
       </c>
-      <c r="K36" s="77">
+      <c r="L36" s="77">
         <f t="shared" si="11"/>
         <v>19.848896</v>
       </c>
-      <c r="L36" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I36,L$4)</f>
+      <c r="M36" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J36,M$4)</f>
         <v>11.6</v>
       </c>
-      <c r="M36" s="65">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I36,M$4)</f>
+      <c r="N36" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J36,N$4)</f>
         <v>240</v>
       </c>
-      <c r="N36" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I36,N$4)</f>
+      <c r="O36" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J36,O$4)</f>
         <v>80</v>
       </c>
-      <c r="O36" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I36,O$4)</f>
+      <c r="P36" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J36,P$4)</f>
         <v>170</v>
       </c>
-      <c r="P36" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I36,P$4)</f>
+      <c r="Q36" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J36,Q$4)</f>
         <v>470</v>
       </c>
-      <c r="Q36" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I36,Q$4)</f>
+      <c r="R36" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J36,R$4)</f>
         <v>40</v>
       </c>
-      <c r="R36" s="38">
+      <c r="S36" s="38">
         <f t="shared" si="8"/>
         <v>3.84</v>
       </c>
-      <c r="S36" s="91">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I36,S$4)/1000*100</f>
+      <c r="T36" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J36,T$4)/1000*100</f>
         <v>0.54999999999999993</v>
       </c>
-      <c r="T36" s="92">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I36,T$4)/1000*100</f>
+      <c r="U36" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J36,U$4)/1000*100</f>
         <v>0.1</v>
       </c>
-      <c r="W36" s="68"/>
-      <c r="X36" s="37">
+      <c r="X36" s="68"/>
+      <c r="Y36" s="37">
         <v>90</v>
       </c>
-      <c r="Y36" s="77">
+      <c r="Z36" s="77">
         <f t="shared" si="26"/>
         <v>19.578191199999999</v>
       </c>
-      <c r="Z36" s="74">
+      <c r="AA36" s="74">
         <v>6.6</v>
       </c>
-      <c r="AA36" s="83">
-        <f>AA34/Z34*Z36</f>
+      <c r="AB36" s="83">
+        <f>AB34/AA34*AA36</f>
         <v>7.0888888888888877</v>
       </c>
-      <c r="AB36" s="88">
+      <c r="AC36" s="88">
         <v>258</v>
       </c>
-      <c r="AC36" s="74">
+      <c r="AD36" s="74">
         <v>67</v>
       </c>
-      <c r="AD36" s="41">
+      <c r="AE36" s="41">
         <f t="shared" si="27"/>
         <v>629</v>
       </c>
-      <c r="AE36" s="45">
+      <c r="AF36" s="45">
         <v>46</v>
       </c>
-      <c r="AF36" s="38">
+      <c r="AG36" s="38">
         <f t="shared" si="14"/>
         <v>4.1280000000000001</v>
       </c>
-      <c r="AG36" s="91">
+      <c r="AH36" s="91">
         <f>5.7/1000*100</f>
         <v>0.57000000000000006</v>
       </c>
-      <c r="AH36" s="92">
+      <c r="AI36" s="92">
         <f>2.9/1000*100</f>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AI36" s="11" t="s">
+      <c r="AJ36" s="11" t="s">
         <v>312</v>
       </c>
-      <c r="AJ36" s="11" t="s">
-        <v>489</v>
-      </c>
-      <c r="AK36" s="68"/>
-      <c r="AL36" s="59"/>
-    </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.25">
+      <c r="AK36" s="11" t="s">
+        <v>488</v>
+      </c>
+      <c r="AL36" s="68"/>
+      <c r="AM36" s="59"/>
+    </row>
+    <row r="37" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>384</v>
       </c>
       <c r="C37" s="65">
-        <f>AVERAGE(X37,J37,AL37)</f>
+        <f>AVERAGE(Y37,K37,AM37)</f>
         <v>88.5</v>
       </c>
       <c r="D37" s="64">
-        <f>Y37</f>
+        <f>Z37</f>
         <v>22.900705599999998</v>
       </c>
       <c r="E37" s="38">
@@ -11688,87 +11751,88 @@
         <v>0.54999999999999993</v>
       </c>
       <c r="H37" s="4"/>
-      <c r="I37" s="68"/>
-      <c r="J37" s="37"/>
-      <c r="K37" s="54"/>
-      <c r="L37" s="38"/>
-      <c r="M37" s="65"/>
-      <c r="N37" s="39"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="68"/>
+      <c r="K37" s="37"/>
+      <c r="L37" s="54"/>
+      <c r="M37" s="38"/>
+      <c r="N37" s="65"/>
       <c r="O37" s="39"/>
       <c r="P37" s="39"/>
-      <c r="Q37" s="42"/>
-      <c r="R37" s="38"/>
-      <c r="S37" s="39"/>
-      <c r="T37" s="42"/>
-      <c r="W37" s="68">
+      <c r="Q37" s="39"/>
+      <c r="R37" s="42"/>
+      <c r="S37" s="38"/>
+      <c r="T37" s="39"/>
+      <c r="U37" s="42"/>
+      <c r="X37" s="68">
         <f>MATCH($B37,pigs!$A$3:$A$60,0)</f>
         <v>22</v>
       </c>
-      <c r="X37" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W37,X$4)</f>
+      <c r="Y37" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X37,Y$4)</f>
         <v>90</v>
       </c>
-      <c r="Y37" s="77">
+      <c r="Z37" s="77">
         <f t="shared" si="26"/>
         <v>22.900705599999998</v>
       </c>
-      <c r="Z37" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W37,Z$4)</f>
+      <c r="AA37" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X37,AA$4)</f>
         <v>12.9</v>
       </c>
-      <c r="AA37" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W37,AA$4)</f>
+      <c r="AB37" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X37,AB$4)</f>
         <v>13.3</v>
       </c>
-      <c r="AB37" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W37,AB$4)</f>
+      <c r="AC37" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X37,AC$4)</f>
         <v>677</v>
       </c>
-      <c r="AC37" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W37,AC$4)</f>
+      <c r="AD37" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X37,AD$4)</f>
         <v>71</v>
       </c>
-      <c r="AD37" s="41">
-        <f t="shared" ref="AD37" si="28">1000-SUM(AB37:AC37,AE37)</f>
+      <c r="AE37" s="41">
+        <f t="shared" ref="AE37" si="28">1000-SUM(AC37:AD37,AF37)</f>
         <v>231</v>
       </c>
-      <c r="AE37" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$W37,AE$4)</f>
+      <c r="AF37" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$X37,AF$4)</f>
         <v>21</v>
       </c>
-      <c r="AF37" s="38">
+      <c r="AG37" s="38">
         <f t="shared" si="14"/>
         <v>10.832000000000001</v>
       </c>
-      <c r="AG37" s="91">
-        <f>INDEX(pigs!$D$3:$AO$60,$W37,AG$4)/1000*100</f>
+      <c r="AH37" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$X37,AH$4)/1000*100</f>
         <v>0.64</v>
       </c>
-      <c r="AH37" s="92">
-        <f>INDEX(pigs!$D$3:$AO$60,$W37,AH$4)/1000*100</f>
+      <c r="AI37" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$X37,AI$4)/1000*100</f>
         <v>0.54999999999999993</v>
       </c>
-      <c r="AI37" s="11"/>
       <c r="AJ37" s="11"/>
-      <c r="AK37" s="68">
+      <c r="AK37" s="11"/>
+      <c r="AL37" s="68">
         <f>MATCH($B37,poultry!$A$3:$A$41,0)</f>
         <v>25</v>
       </c>
-      <c r="AL37" s="59">
-        <f>INDEX(poultry!$D$3:$U$41,$AK37,AL$4)</f>
+      <c r="AM37" s="59">
+        <f>INDEX(poultry!$D$3:$U$41,$AL37,AM$4)</f>
         <v>87</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>52</v>
       </c>
       <c r="C38" s="65">
-        <f t="shared" ref="C38:C43" si="29">AVERAGE(X38,J38)</f>
+        <f t="shared" ref="C38:C43" si="29">AVERAGE(Y38,K38)</f>
         <v>75.5</v>
       </c>
       <c r="D38" s="64">
-        <f>K38</f>
+        <f>L38</f>
         <v>16.1615368</v>
       </c>
       <c r="E38" s="38">
@@ -11784,106 +11848,107 @@
         <v>3.6500000000000004</v>
       </c>
       <c r="H38" s="4"/>
-      <c r="I38" s="68">
+      <c r="I38" s="4"/>
+      <c r="J38" s="68">
         <f>MATCH($B38,ruminants!$A$3:$A$120,0)</f>
         <v>88</v>
       </c>
-      <c r="J38" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I38,J$4)</f>
+      <c r="K38" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J38,K$4)</f>
         <v>75</v>
       </c>
-      <c r="K38" s="77">
+      <c r="L38" s="77">
         <f t="shared" si="11"/>
         <v>16.1615368</v>
       </c>
-      <c r="L38" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I38,L$4)</f>
+      <c r="M38" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J38,M$4)</f>
         <v>12.4</v>
       </c>
-      <c r="M38" s="65">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I38,M$4)</f>
+      <c r="N38" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J38,N$4)</f>
         <v>131</v>
       </c>
-      <c r="N38" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I38,N$4)</f>
-        <v>0</v>
-      </c>
       <c r="O38" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I38,O$4)</f>
+        <f>INDEX(ruminants!$D$3:$AH$120,$J38,O$4)</f>
         <v>0</v>
       </c>
       <c r="P38" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I38,P$4)</f>
+        <f>INDEX(ruminants!$D$3:$AH$120,$J38,P$4)</f>
+        <v>0</v>
+      </c>
+      <c r="Q38" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J38,Q$4)</f>
         <v>760</v>
       </c>
-      <c r="Q38" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I38,Q$4)</f>
+      <c r="R38" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J38,R$4)</f>
         <v>109</v>
       </c>
-      <c r="R38" s="38">
+      <c r="S38" s="38">
         <f t="shared" si="8"/>
         <v>2.0960000000000001</v>
       </c>
-      <c r="S38" s="91">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I38,S$4)/1000*100</f>
+      <c r="T38" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J38,T$4)/1000*100</f>
         <v>0.02</v>
       </c>
-      <c r="T38" s="92">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I38,T$4)/1000*100</f>
+      <c r="U38" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J38,U$4)/1000*100</f>
         <v>4.5</v>
       </c>
-      <c r="W38" s="68">
+      <c r="X38" s="68">
         <f>MATCH($B38,pigs!$A$3:$A$60,0)</f>
         <v>23</v>
       </c>
-      <c r="X38" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W38,X$4)</f>
+      <c r="Y38" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X38,Y$4)</f>
         <v>76</v>
       </c>
-      <c r="Y38" s="77">
-        <f t="shared" ref="Y38:Y43" si="30">( 5.7*AB38+9.4*AC38+4.1*(AD38) ) * 0.004184</f>
+      <c r="Z38" s="77">
+        <f t="shared" ref="Z38:Z43" si="30">( 5.7*AC38+9.4*AD38+4.1*(AE38) ) * 0.004184</f>
         <v>15.9565208</v>
       </c>
-      <c r="Z38" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W38,Z$4)</f>
+      <c r="AA38" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X38,AA$4)</f>
         <v>8.6999999999999993</v>
       </c>
-      <c r="AA38" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W38,AA$4)</f>
+      <c r="AB38" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X38,AB$4)</f>
         <v>9</v>
       </c>
-      <c r="AB38" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W38,AB$4)</f>
+      <c r="AC38" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X38,AC$4)</f>
         <v>145</v>
       </c>
-      <c r="AC38" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W38,AC$4)</f>
+      <c r="AD38" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X38,AD$4)</f>
         <v>2</v>
       </c>
-      <c r="AD38" s="41">
-        <f t="shared" ref="AD38:AD43" si="31">1000-SUM(AB38:AC38,AE38)</f>
+      <c r="AE38" s="41">
+        <f t="shared" ref="AE38:AE43" si="31">1000-SUM(AC38:AD38,AF38)</f>
         <v>724</v>
       </c>
-      <c r="AE38" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$W38,AE$4)</f>
+      <c r="AF38" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$X38,AF$4)</f>
         <v>129</v>
       </c>
-      <c r="AF38" s="38">
+      <c r="AG38" s="38">
         <f t="shared" si="14"/>
         <v>2.3199999999999998</v>
       </c>
-      <c r="AG38" s="91">
-        <f>INDEX(pigs!$D$3:$AO$60,$W38,AG$4)/1000*100</f>
+      <c r="AH38" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$X38,AH$4)/1000*100</f>
         <v>0.04</v>
       </c>
-      <c r="AH38" s="92">
-        <f>INDEX(pigs!$D$3:$AO$60,$W38,AH$4)/1000*100</f>
+      <c r="AI38" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$X38,AI$4)/1000*100</f>
         <v>2.8000000000000003</v>
       </c>
-      <c r="AK38" s="68"/>
-      <c r="AL38" s="59"/>
-    </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.25">
+      <c r="AL38" s="68"/>
+      <c r="AM38" s="59"/>
+    </row>
+    <row r="39" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>53</v>
       </c>
@@ -11892,7 +11957,7 @@
         <v>89.5</v>
       </c>
       <c r="D39" s="64">
-        <f>K39</f>
+        <f>L39</f>
         <v>17.334312000000001</v>
       </c>
       <c r="E39" s="38">
@@ -11908,106 +11973,107 @@
         <v>0.48499999999999999</v>
       </c>
       <c r="H39" s="4"/>
-      <c r="I39" s="68">
+      <c r="I39" s="4"/>
+      <c r="J39" s="68">
         <f>MATCH($B39,ruminants!$A$3:$A$120,0)</f>
         <v>91</v>
       </c>
-      <c r="J39" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I39,J$4)</f>
+      <c r="K39" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J39,K$4)</f>
         <v>90</v>
       </c>
-      <c r="K39" s="77">
+      <c r="L39" s="77">
         <f t="shared" si="11"/>
         <v>17.334312000000001</v>
       </c>
-      <c r="L39" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I39,L$4)</f>
+      <c r="M39" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J39,M$4)</f>
         <v>12.3</v>
       </c>
-      <c r="M39" s="65">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I39,M$4)</f>
+      <c r="N39" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J39,N$4)</f>
         <v>90</v>
       </c>
-      <c r="N39" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I39,N$4)</f>
+      <c r="O39" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J39,O$4)</f>
         <v>32</v>
       </c>
-      <c r="O39" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I39,O$4)</f>
+      <c r="P39" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J39,P$4)</f>
         <v>187</v>
       </c>
-      <c r="P39" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I39,P$4)</f>
+      <c r="Q39" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J39,Q$4)</f>
         <v>625</v>
       </c>
-      <c r="Q39" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I39,Q$4)</f>
+      <c r="R39" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J39,R$4)</f>
         <v>66</v>
       </c>
-      <c r="R39" s="38">
+      <c r="S39" s="38">
         <f t="shared" si="8"/>
         <v>1.44</v>
       </c>
-      <c r="S39" s="91">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I39,S$4)/1000*100</f>
+      <c r="T39" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J39,T$4)/1000*100</f>
         <v>0.1</v>
       </c>
-      <c r="T39" s="92">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I39,T$4)/1000*100</f>
+      <c r="U39" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J39,U$4)/1000*100</f>
         <v>0.6</v>
       </c>
-      <c r="W39" s="68">
+      <c r="X39" s="68">
         <f>MATCH($B39,pigs!$A$3:$A$60,0)</f>
         <v>4</v>
       </c>
-      <c r="X39" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W39,X$4)</f>
+      <c r="Y39" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X39,Y$4)</f>
         <v>89</v>
       </c>
-      <c r="Y39" s="77">
+      <c r="Z39" s="77">
         <f t="shared" si="30"/>
         <v>16.664453599999998</v>
       </c>
-      <c r="Z39" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W39,Z$4)</f>
+      <c r="AA39" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X39,AA$4)</f>
         <v>6.9</v>
       </c>
-      <c r="AA39" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W39,AA$4)</f>
+      <c r="AB39" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X39,AB$4)</f>
         <v>8</v>
       </c>
-      <c r="AB39" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W39,AB$4)</f>
+      <c r="AC39" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X39,AC$4)</f>
         <v>91</v>
       </c>
-      <c r="AC39" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W39,AC$4)</f>
+      <c r="AD39" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X39,AD$4)</f>
         <v>10</v>
       </c>
-      <c r="AD39" s="41">
+      <c r="AE39" s="41">
         <f t="shared" si="31"/>
         <v>822</v>
       </c>
-      <c r="AE39" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$W39,AE$4)</f>
+      <c r="AF39" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$X39,AF$4)</f>
         <v>77</v>
       </c>
-      <c r="AF39" s="38">
+      <c r="AG39" s="38">
         <f t="shared" si="14"/>
         <v>1.456</v>
       </c>
-      <c r="AG39" s="91">
-        <f>INDEX(pigs!$D$3:$AO$60,$W39,AG$4)/1000*100</f>
+      <c r="AH39" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$X39,AH$4)/1000*100</f>
         <v>0.1</v>
       </c>
-      <c r="AH39" s="92">
-        <f>INDEX(pigs!$D$3:$AO$60,$W39,AH$4)/1000*100</f>
+      <c r="AI39" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$X39,AI$4)/1000*100</f>
         <v>0.37</v>
       </c>
-      <c r="AK39" s="68"/>
-      <c r="AL39" s="59"/>
-    </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.25">
+      <c r="AL39" s="68"/>
+      <c r="AM39" s="59"/>
+    </row>
+    <row r="40" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>54</v>
       </c>
@@ -12016,7 +12082,7 @@
         <v>6.25</v>
       </c>
       <c r="D40" s="64">
-        <f>K40</f>
+        <f>L40</f>
         <v>16.464040000000001</v>
       </c>
       <c r="E40" s="38">
@@ -12032,106 +12098,107 @@
         <v>2.355</v>
       </c>
       <c r="H40" s="4"/>
-      <c r="I40" s="68">
+      <c r="I40" s="4"/>
+      <c r="J40" s="68">
         <f>MATCH($B40,ruminants!$A$3:$A$120,0)</f>
         <v>57</v>
       </c>
-      <c r="J40" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I40,J$4)</f>
+      <c r="K40" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J40,K$4)</f>
         <v>7</v>
       </c>
-      <c r="K40" s="77">
+      <c r="L40" s="77">
         <f t="shared" si="11"/>
         <v>16.464040000000001</v>
       </c>
-      <c r="L40" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I40,L$4)</f>
+      <c r="M40" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J40,M$4)</f>
         <v>13.6</v>
       </c>
-      <c r="M40" s="65">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I40,M$4)</f>
+      <c r="N40" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J40,N$4)</f>
         <v>120</v>
       </c>
-      <c r="N40" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I40,N$4)</f>
+      <c r="O40" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J40,O$4)</f>
         <v>10</v>
       </c>
-      <c r="O40" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I40,O$4)</f>
-        <v>0</v>
-      </c>
       <c r="P40" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I40,P$4)</f>
+        <f>INDEX(ruminants!$D$3:$AH$120,$J40,P$4)</f>
+        <v>0</v>
+      </c>
+      <c r="Q40" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J40,Q$4)</f>
         <v>770</v>
       </c>
-      <c r="Q40" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I40,Q$4)</f>
+      <c r="R40" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J40,R$4)</f>
         <v>100</v>
       </c>
-      <c r="R40" s="38">
+      <c r="S40" s="38">
         <f t="shared" si="8"/>
         <v>1.92</v>
       </c>
-      <c r="S40" s="91">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I40,S$4)/1000*100</f>
+      <c r="T40" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J40,T$4)/1000*100</f>
         <v>0.79</v>
       </c>
-      <c r="T40" s="92">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I40,T$4)/1000*100</f>
+      <c r="U40" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J40,U$4)/1000*100</f>
         <v>2.4</v>
       </c>
-      <c r="W40" s="68">
+      <c r="X40" s="68">
         <f>MATCH($B40,pigs!$A$3:$A$60,0)</f>
         <v>50</v>
       </c>
-      <c r="X40" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W40,X$4)</f>
+      <c r="Y40" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X40,Y$4)</f>
         <v>5.5</v>
       </c>
-      <c r="Y40" s="77">
+      <c r="Z40" s="77">
         <f t="shared" si="30"/>
         <v>16.870306399999997</v>
       </c>
-      <c r="Z40" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W40,Z$4)</f>
+      <c r="AA40" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X40,AA$4)</f>
         <v>12.4</v>
       </c>
-      <c r="AA40" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W40,AA$4)</f>
+      <c r="AB40" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X40,AB$4)</f>
         <v>12.2</v>
       </c>
-      <c r="AB40" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W40,AB$4)</f>
+      <c r="AC40" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X40,AC$4)</f>
         <v>115</v>
       </c>
-      <c r="AC40" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W40,AC$4)</f>
+      <c r="AD40" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X40,AD$4)</f>
         <v>19</v>
       </c>
-      <c r="AD40" s="41">
+      <c r="AE40" s="41">
         <f t="shared" si="31"/>
         <v>780</v>
       </c>
-      <c r="AE40" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$W40,AE$4)</f>
+      <c r="AF40" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$X40,AF$4)</f>
         <v>86</v>
       </c>
-      <c r="AF40" s="38">
+      <c r="AG40" s="38">
         <f t="shared" si="14"/>
         <v>1.8400000000000003</v>
       </c>
-      <c r="AG40" s="91">
-        <f>INDEX(pigs!$D$3:$AO$60,$W40,AG$4)/1000*100</f>
+      <c r="AH40" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$X40,AH$4)/1000*100</f>
         <v>0.73</v>
       </c>
-      <c r="AH40" s="92">
-        <f>INDEX(pigs!$D$3:$AO$60,$W40,AH$4)/1000*100</f>
+      <c r="AI40" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$X40,AI$4)/1000*100</f>
         <v>2.31</v>
       </c>
-      <c r="AK40" s="68"/>
-      <c r="AL40" s="59"/>
-    </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.25">
+      <c r="AL40" s="68"/>
+      <c r="AM40" s="59"/>
+    </row>
+    <row r="41" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>55</v>
       </c>
@@ -12140,7 +12207,7 @@
         <v>97</v>
       </c>
       <c r="D41" s="64">
-        <f>Y41</f>
+        <f>Z41</f>
         <v>16.975324799999999</v>
       </c>
       <c r="E41" s="38">
@@ -12156,70 +12223,71 @@
         <v>2.1</v>
       </c>
       <c r="H41" s="4"/>
-      <c r="I41" s="68"/>
-      <c r="J41" s="37"/>
-      <c r="K41" s="54"/>
-      <c r="L41" s="38"/>
-      <c r="M41" s="65"/>
-      <c r="N41" s="39"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="68"/>
+      <c r="K41" s="37"/>
+      <c r="L41" s="54"/>
+      <c r="M41" s="38"/>
+      <c r="N41" s="65"/>
       <c r="O41" s="39"/>
       <c r="P41" s="39"/>
-      <c r="Q41" s="42"/>
-      <c r="R41" s="38"/>
-      <c r="S41" s="39"/>
-      <c r="T41" s="42"/>
-      <c r="W41" s="68">
+      <c r="Q41" s="39"/>
+      <c r="R41" s="42"/>
+      <c r="S41" s="38"/>
+      <c r="T41" s="39"/>
+      <c r="U41" s="42"/>
+      <c r="X41" s="68">
         <f>MATCH($B41,pigs!$A$3:$A$60,0)</f>
         <v>52</v>
       </c>
-      <c r="X41" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W41,X$4)</f>
+      <c r="Y41" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X41,Y$4)</f>
         <v>97</v>
       </c>
-      <c r="Y41" s="77">
+      <c r="Z41" s="77">
         <f t="shared" si="30"/>
         <v>16.975324799999999</v>
       </c>
-      <c r="Z41" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W41,Z$4)</f>
+      <c r="AA41" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X41,AA$4)</f>
         <v>12.4</v>
       </c>
-      <c r="AA41" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W41,AA$4)</f>
+      <c r="AB41" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X41,AB$4)</f>
         <v>12.2</v>
       </c>
-      <c r="AB41" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W41,AB$4)</f>
+      <c r="AC41" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X41,AC$4)</f>
         <v>131</v>
       </c>
-      <c r="AC41" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W41,AC$4)</f>
+      <c r="AD41" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X41,AD$4)</f>
         <v>22</v>
       </c>
-      <c r="AD41" s="41">
+      <c r="AE41" s="41">
         <f t="shared" si="31"/>
         <v>757</v>
       </c>
-      <c r="AE41" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$W41,AE$4)</f>
+      <c r="AF41" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$X41,AF$4)</f>
         <v>90</v>
       </c>
-      <c r="AF41" s="38">
+      <c r="AG41" s="38">
         <f t="shared" si="14"/>
         <v>2.0960000000000001</v>
       </c>
-      <c r="AG41" s="91">
-        <f>INDEX(pigs!$D$3:$AO$60,$W41,AG$4)/1000*100</f>
+      <c r="AH41" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$X41,AH$4)/1000*100</f>
         <v>0.72</v>
       </c>
-      <c r="AH41" s="92">
-        <f>INDEX(pigs!$D$3:$AO$60,$W41,AH$4)/1000*100</f>
+      <c r="AI41" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$X41,AI$4)/1000*100</f>
         <v>2.1</v>
       </c>
-      <c r="AK41" s="68"/>
-      <c r="AL41" s="59"/>
-    </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.25">
+      <c r="AL41" s="68"/>
+      <c r="AM41" s="59"/>
+    </row>
+    <row r="42" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>56</v>
       </c>
@@ -12228,7 +12296,7 @@
         <v>91</v>
       </c>
       <c r="D42" s="64">
-        <f>K42</f>
+        <f>L42</f>
         <v>23.055932000000002</v>
       </c>
       <c r="E42" s="38">
@@ -12244,112 +12312,113 @@
         <v>0.81499999999999995</v>
       </c>
       <c r="H42" s="4"/>
-      <c r="I42" s="68">
+      <c r="I42" s="4"/>
+      <c r="J42" s="68">
         <f>MATCH($B42,ruminants!$A$3:$A$120,0)</f>
         <v>65</v>
       </c>
-      <c r="J42" s="37">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I42,J$4)</f>
+      <c r="K42" s="37">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J42,K$4)</f>
         <v>90</v>
       </c>
-      <c r="K42" s="77">
+      <c r="L42" s="77">
         <f t="shared" si="11"/>
         <v>23.055932000000002</v>
       </c>
-      <c r="L42" s="38">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I42,L$4)</f>
+      <c r="M42" s="38">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J42,M$4)</f>
         <v>15.5</v>
       </c>
-      <c r="M42" s="65">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I42,M$4)</f>
+      <c r="N42" s="65">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J42,N$4)</f>
         <v>844</v>
       </c>
-      <c r="N42" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I42,N$4)</f>
+      <c r="O42" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J42,O$4)</f>
         <v>33</v>
       </c>
-      <c r="O42" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I42,O$4)</f>
+      <c r="P42" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J42,P$4)</f>
         <v>4</v>
       </c>
-      <c r="P42" s="39">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I42,P$4)</f>
+      <c r="Q42" s="39">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J42,Q$4)</f>
         <v>91</v>
       </c>
-      <c r="Q42" s="42">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I42,Q$4)</f>
+      <c r="R42" s="42">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J42,R$4)</f>
         <v>28</v>
       </c>
-      <c r="R42" s="38">
+      <c r="S42" s="38">
         <f t="shared" si="8"/>
         <v>13.504</v>
       </c>
-      <c r="S42" s="91">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I42,S$4)/1000*100</f>
+      <c r="T42" s="91">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J42,T$4)/1000*100</f>
         <v>0.44</v>
       </c>
-      <c r="T42" s="92">
-        <f>INDEX(ruminants!$D$3:$AH$120,$I42,T$4)/1000*100</f>
+      <c r="U42" s="92">
+        <f>INDEX(ruminants!$D$3:$AH$120,$J42,U$4)/1000*100</f>
         <v>0.89</v>
       </c>
-      <c r="W42" s="68">
+      <c r="X42" s="68">
         <f>MATCH($B42,pigs!$A$3:$A$60,0)</f>
         <v>31</v>
       </c>
-      <c r="X42" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W42,X$4)</f>
+      <c r="Y42" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X42,Y$4)</f>
         <v>92</v>
       </c>
-      <c r="Y42" s="77">
+      <c r="Z42" s="77">
         <f t="shared" si="30"/>
         <v>22.525819200000001</v>
       </c>
-      <c r="Z42" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W42,Z$4)</f>
+      <c r="AA42" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X42,AA$4)</f>
         <v>11.1</v>
       </c>
-      <c r="AA42" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W42,AA$4)</f>
+      <c r="AB42" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X42,AB$4)</f>
         <v>11.3</v>
       </c>
-      <c r="AB42" s="37">
-        <f>INDEX(pigs!$D$3:$AO$60,$W42,AB$4)</f>
+      <c r="AC42" s="37">
+        <f>INDEX(pigs!$D$3:$AO$60,$X42,AC$4)</f>
         <v>841</v>
       </c>
-      <c r="AC42" s="54">
-        <f>INDEX(pigs!$D$3:$AO$60,$W42,AC$4)</f>
+      <c r="AD42" s="54">
+        <f>INDEX(pigs!$D$3:$AO$60,$X42,AD$4)</f>
         <v>10</v>
       </c>
-      <c r="AD42" s="41">
+      <c r="AE42" s="41">
         <f t="shared" si="31"/>
         <v>121</v>
       </c>
-      <c r="AE42" s="55">
-        <f>INDEX(pigs!$D$3:$AO$60,$W42,AE$4)</f>
+      <c r="AF42" s="55">
+        <f>INDEX(pigs!$D$3:$AO$60,$X42,AF$4)</f>
         <v>28</v>
       </c>
-      <c r="AF42" s="38">
+      <c r="AG42" s="38">
         <f t="shared" si="14"/>
         <v>13.456000000000001</v>
       </c>
-      <c r="AG42" s="91">
-        <f>INDEX(pigs!$D$3:$AO$60,$W42,AG$4)/1000*100</f>
+      <c r="AH42" s="91">
+        <f>INDEX(pigs!$D$3:$AO$60,$X42,AH$4)/1000*100</f>
         <v>0.43</v>
       </c>
-      <c r="AH42" s="92">
-        <f>INDEX(pigs!$D$3:$AO$60,$W42,AH$4)/1000*100</f>
+      <c r="AI42" s="92">
+        <f>INDEX(pigs!$D$3:$AO$60,$X42,AI$4)/1000*100</f>
         <v>0.74</v>
       </c>
-      <c r="AK42" s="68">
+      <c r="AL42" s="68">
         <f>MATCH($B42,poultry!$A$3:$A$41,0)</f>
         <v>28</v>
       </c>
-      <c r="AL42" s="59">
-        <f>INDEX(poultry!$D$3:$U$41,$AK42,AL$4)</f>
+      <c r="AM42" s="59">
+        <f>INDEX(poultry!$D$3:$U$41,$AL42,AM$4)</f>
         <v>90</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>57</v>
       </c>
@@ -12358,7 +12427,7 @@
         <v>92</v>
       </c>
       <c r="D43" s="67">
-        <f>Y43</f>
+        <f>Z43</f>
         <v>22.254696000000003</v>
       </c>
       <c r="E43" s="95">
@@ -12374,89 +12443,90 @@
         <v>1.2</v>
       </c>
       <c r="H43" s="4"/>
-      <c r="I43" s="68"/>
-      <c r="J43" s="50"/>
-      <c r="K43" s="51"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="68"/>
+      <c r="K43" s="50"/>
       <c r="L43" s="51"/>
-      <c r="M43" s="66"/>
-      <c r="N43" s="52"/>
+      <c r="M43" s="51"/>
+      <c r="N43" s="66"/>
       <c r="O43" s="52"/>
       <c r="P43" s="52"/>
-      <c r="Q43" s="53"/>
-      <c r="R43" s="52"/>
+      <c r="Q43" s="52"/>
+      <c r="R43" s="53"/>
       <c r="S43" s="52"/>
-      <c r="T43" s="53"/>
-      <c r="W43" s="68">
+      <c r="T43" s="52"/>
+      <c r="U43" s="53"/>
+      <c r="X43" s="68">
         <f>MATCH($B43,pigs!$A$3:$A$60,0)</f>
         <v>7</v>
       </c>
-      <c r="X43" s="50">
-        <f>INDEX(pigs!$D$3:$AO$60,$W43,X$4)</f>
+      <c r="Y43" s="50">
+        <f>INDEX(pigs!$D$3:$AO$60,$X43,Y$4)</f>
         <v>92</v>
       </c>
-      <c r="Y43" s="78">
+      <c r="Z43" s="78">
         <f t="shared" si="30"/>
         <v>22.254696000000003</v>
       </c>
-      <c r="Z43" s="51">
-        <f>INDEX(pigs!$D$3:$AO$60,$W43,Z$4)</f>
+      <c r="AA43" s="51">
+        <f>INDEX(pigs!$D$3:$AO$60,$X43,AA$4)</f>
         <v>10.8</v>
       </c>
-      <c r="AA43" s="51">
-        <f>INDEX(pigs!$D$3:$AO$60,$W43,AA$4)</f>
+      <c r="AB43" s="51">
+        <f>INDEX(pigs!$D$3:$AO$60,$X43,AB$4)</f>
         <v>10.8</v>
       </c>
-      <c r="AB43" s="50">
-        <f>INDEX(pigs!$D$3:$AO$60,$W43,AB$4)</f>
+      <c r="AC43" s="50">
+        <f>INDEX(pigs!$D$3:$AO$60,$X43,AC$4)</f>
         <v>760</v>
       </c>
-      <c r="AC43" s="51">
-        <f>INDEX(pigs!$D$3:$AO$60,$W43,AC$4)</f>
+      <c r="AD43" s="51">
+        <f>INDEX(pigs!$D$3:$AO$60,$X43,AD$4)</f>
         <v>105</v>
       </c>
-      <c r="AD43" s="76">
+      <c r="AE43" s="76">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="AE43" s="58">
-        <f>INDEX(pigs!$D$3:$AO$60,$W43,AE$4)</f>
+      <c r="AF43" s="58">
+        <f>INDEX(pigs!$D$3:$AO$60,$X43,AF$4)</f>
         <v>135</v>
       </c>
-      <c r="AF43" s="90">
+      <c r="AG43" s="90">
         <f t="shared" si="14"/>
         <v>12.160000000000002</v>
       </c>
-      <c r="AG43" s="93">
-        <f>INDEX(pigs!$D$3:$AO$60,$W43,AG$4)/1000*100</f>
+      <c r="AH43" s="93">
+        <f>INDEX(pigs!$D$3:$AO$60,$X43,AH$4)/1000*100</f>
         <v>2.4699999999999998</v>
       </c>
-      <c r="AH43" s="94">
-        <f>INDEX(pigs!$D$3:$AO$60,$W43,AH$4)/1000*100</f>
+      <c r="AI43" s="94">
+        <f>INDEX(pigs!$D$3:$AO$60,$X43,AI$4)/1000*100</f>
         <v>1.2</v>
       </c>
-      <c r="AK43" s="68">
+      <c r="AL43" s="68">
         <f>MATCH($B43,poultry!$A$3:$A$41,0)</f>
         <v>6</v>
       </c>
-      <c r="AL43" s="60">
-        <f>INDEX(poultry!$D$3:$U$41,$AK43,AL$4)</f>
+      <c r="AM43" s="60">
+        <f>INDEX(poultry!$D$3:$U$41,$AL43,AM$4)</f>
         <v>92</v>
       </c>
     </row>
-    <row r="46" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:39" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B46" s="32" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C1" r:id="rId1"/>
-    <hyperlink ref="AI36" r:id="rId2"/>
-    <hyperlink ref="U31" r:id="rId3"/>
-    <hyperlink ref="U33" r:id="rId4"/>
-    <hyperlink ref="U10" r:id="rId5"/>
-    <hyperlink ref="U20" r:id="rId6"/>
-    <hyperlink ref="U23" r:id="rId7"/>
+    <hyperlink ref="AJ36" r:id="rId2"/>
+    <hyperlink ref="V31" r:id="rId3"/>
+    <hyperlink ref="V33" r:id="rId4"/>
+    <hyperlink ref="V10" r:id="rId5"/>
+    <hyperlink ref="V20" r:id="rId6"/>
+    <hyperlink ref="V23" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
@@ -30599,52 +30669,52 @@
         <v>278</v>
       </c>
       <c r="G2" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="H2" s="19" t="s">
         <v>412</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="I2" s="19" t="s">
         <v>413</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="J2" s="19" t="s">
         <v>414</v>
       </c>
-      <c r="J2" s="19" t="s">
+      <c r="K2" s="19" t="s">
         <v>415</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="L2" s="19" t="s">
         <v>416</v>
       </c>
-      <c r="L2" s="19" t="s">
+      <c r="M2" s="19" t="s">
         <v>417</v>
       </c>
-      <c r="M2" s="19" t="s">
+      <c r="N2" s="19" t="s">
         <v>418</v>
       </c>
-      <c r="N2" s="19" t="s">
+      <c r="O2" s="19" t="s">
         <v>419</v>
       </c>
-      <c r="O2" s="19" t="s">
+      <c r="P2" s="19" t="s">
         <v>420</v>
       </c>
-      <c r="P2" s="19" t="s">
+      <c r="Q2" s="19" t="s">
         <v>421</v>
       </c>
-      <c r="Q2" s="19" t="s">
+      <c r="R2" s="19" t="s">
         <v>422</v>
       </c>
-      <c r="R2" s="19" t="s">
+      <c r="S2" s="19" t="s">
         <v>423</v>
       </c>
-      <c r="S2" s="19" t="s">
+      <c r="T2" s="19" t="s">
         <v>424</v>
-      </c>
-      <c r="T2" s="19" t="s">
-        <v>425</v>
       </c>
       <c r="U2" s="19" t="s">
         <v>123</v>
       </c>
       <c r="V2" s="19" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="W2" s="19" t="s">
         <v>148</v>
@@ -30670,7 +30740,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D3" s="14">
         <v>9.4</v>
@@ -30739,7 +30809,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D4" s="17">
         <v>9.4</v>
@@ -30808,7 +30878,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D5" s="14">
         <v>6.1</v>
@@ -30877,7 +30947,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D6" s="17">
         <v>9.4</v>
@@ -30946,7 +31016,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D7" s="14">
         <v>10.5</v>
@@ -31015,7 +31085,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D8" s="17">
         <v>11.1</v>
@@ -31084,7 +31154,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D9" s="14">
         <v>11</v>
@@ -31158,7 +31228,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D10" s="17">
         <v>10.1</v>
@@ -31230,7 +31300,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D11" s="14">
         <v>9.5</v>
@@ -31298,7 +31368,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D12" s="17">
         <v>10.5</v>
@@ -31374,7 +31444,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D13" s="14">
         <v>10.8</v>
@@ -31448,7 +31518,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D14" s="17">
         <v>11.5</v>
@@ -31522,7 +31592,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D15" s="14">
         <v>9.8000000000000007</v>
@@ -31609,7 +31679,7 @@
         <v>14</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D16" s="17">
         <v>9.8000000000000007</v>
@@ -31696,7 +31766,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D17" s="14">
         <v>9.3000000000000007</v>
@@ -31781,7 +31851,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="34" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D18" s="17">
         <v>9.3000000000000007</v>
@@ -31866,7 +31936,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D19" s="14">
         <v>10.199999999999999</v>
@@ -31951,7 +32021,7 @@
         <v>18</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D20" s="17">
         <v>10.199999999999999</v>
@@ -32036,7 +32106,7 @@
         <v>19</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D21" s="14">
         <v>10.9</v>
@@ -32119,7 +32189,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="34" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D22" s="17">
         <v>11.7</v>
@@ -32200,7 +32270,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D23" s="14">
         <v>8</v>
@@ -32279,7 +32349,7 @@
         <v>22</v>
       </c>
       <c r="C24" s="34" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D24" s="17">
         <v>9.1999999999999993</v>
@@ -32362,7 +32432,7 @@
         <v>23</v>
       </c>
       <c r="C25" s="33" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D25" s="14">
         <v>10.1</v>
@@ -32445,7 +32515,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="34" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D26" s="17">
         <v>10.3</v>
@@ -32528,7 +32598,7 @@
         <v>25</v>
       </c>
       <c r="C27" s="33" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D27" s="14">
         <v>10.3</v>
@@ -32611,7 +32681,7 @@
         <v>26</v>
       </c>
       <c r="C28" s="34" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D28" s="17">
         <v>10.1</v>
@@ -32692,7 +32762,7 @@
         <v>27</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D29" s="14">
         <v>10.199999999999999</v>
@@ -32773,7 +32843,7 @@
         <v>28</v>
       </c>
       <c r="C30" s="34" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D30" s="17">
         <v>10.1</v>
@@ -32854,7 +32924,7 @@
         <v>29</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D31" s="14">
         <v>10.199999999999999</v>
@@ -32937,7 +33007,7 @@
         <v>30</v>
       </c>
       <c r="C32" s="34" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D32" s="17">
         <v>9.9</v>
@@ -33018,7 +33088,7 @@
         <v>31</v>
       </c>
       <c r="C33" s="33" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D33" s="14">
         <v>9.1</v>
@@ -33099,7 +33169,7 @@
         <v>32</v>
       </c>
       <c r="C34" s="34" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D34" s="17">
         <v>9.3000000000000007</v>
@@ -33180,7 +33250,7 @@
         <v>33</v>
       </c>
       <c r="C35" s="33" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D35" s="14">
         <v>9.1999999999999993</v>
@@ -33261,7 +33331,7 @@
         <v>34</v>
       </c>
       <c r="C36" s="34" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D36" s="17">
         <v>9.4</v>
@@ -33334,7 +33404,7 @@
         <v>35</v>
       </c>
       <c r="C37" s="33" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D37" s="14">
         <v>10.199999999999999</v>
@@ -33421,7 +33491,7 @@
         <v>36</v>
       </c>
       <c r="C38" s="34" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D38" s="17">
         <v>10.199999999999999</v>
@@ -33508,7 +33578,7 @@
         <v>37</v>
       </c>
       <c r="C39" s="33" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D39" s="14">
         <v>9.8000000000000007</v>
@@ -33593,7 +33663,7 @@
         <v>38</v>
       </c>
       <c r="C40" s="34" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D40" s="17">
         <v>9.8000000000000007</v>
@@ -33678,7 +33748,7 @@
         <v>39</v>
       </c>
       <c r="C41" s="33" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D41" s="14">
         <v>10.7</v>
@@ -33763,7 +33833,7 @@
         <v>40</v>
       </c>
       <c r="C42" s="34" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D42" s="17">
         <v>10.7</v>
@@ -33848,7 +33918,7 @@
         <v>41</v>
       </c>
       <c r="C43" s="33" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D43" s="14">
         <v>9.9</v>
@@ -33933,7 +34003,7 @@
         <v>42</v>
       </c>
       <c r="C44" s="34" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D44" s="17">
         <v>9.9</v>
@@ -34018,7 +34088,7 @@
         <v>43</v>
       </c>
       <c r="C45" s="33" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D45" s="14">
         <v>9.5</v>
@@ -34103,7 +34173,7 @@
         <v>44</v>
       </c>
       <c r="C46" s="34" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D46" s="17">
         <v>9.3000000000000007</v>
@@ -34188,7 +34258,7 @@
         <v>45</v>
       </c>
       <c r="C47" s="33" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D47" s="14">
         <v>10.4</v>
@@ -34273,7 +34343,7 @@
         <v>46</v>
       </c>
       <c r="C48" s="34" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D48" s="17">
         <v>10.4</v>
@@ -34358,7 +34428,7 @@
         <v>47</v>
       </c>
       <c r="C49" s="33" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D49" s="14">
         <v>10.199999999999999</v>
@@ -34445,7 +34515,7 @@
         <v>48</v>
       </c>
       <c r="C50" s="34" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D50" s="17">
         <v>10.199999999999999</v>
@@ -34532,7 +34602,7 @@
         <v>49</v>
       </c>
       <c r="C51" s="33" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D51" s="14">
         <v>9.5</v>
@@ -34617,7 +34687,7 @@
         <v>50</v>
       </c>
       <c r="C52" s="34" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D52" s="17">
         <v>9.5</v>
@@ -34702,7 +34772,7 @@
         <v>51</v>
       </c>
       <c r="C53" s="33" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D53" s="14">
         <v>11</v>
@@ -34787,7 +34857,7 @@
         <v>52</v>
       </c>
       <c r="C54" s="34" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D54" s="17">
         <v>11</v>
@@ -34872,7 +34942,7 @@
         <v>53</v>
       </c>
       <c r="C55" s="33" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D55" s="14">
         <v>10.6</v>
@@ -34957,7 +35027,7 @@
         <v>54</v>
       </c>
       <c r="C56" s="34" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D56" s="17">
         <v>10.6</v>
@@ -35042,7 +35112,7 @@
         <v>55</v>
       </c>
       <c r="C57" s="33" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D57" s="14">
         <v>10.199999999999999</v>
@@ -35127,7 +35197,7 @@
         <v>56</v>
       </c>
       <c r="C58" s="34" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D58" s="17">
         <v>10.199999999999999</v>
@@ -35212,7 +35282,7 @@
         <v>57</v>
       </c>
       <c r="C59" s="33" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D59" s="14">
         <v>11</v>
@@ -35297,7 +35367,7 @@
         <v>58</v>
       </c>
       <c r="C60" s="34" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D60" s="17">
         <v>11</v>
@@ -35382,7 +35452,7 @@
         <v>59</v>
       </c>
       <c r="C61" s="33" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D61" s="14">
         <v>10.5</v>

--- a/data/prod_parameters/FeedMgmt.xlsx
+++ b/data/prod_parameters/FeedMgmt.xlsx
@@ -10145,7 +10145,7 @@
         <v>310</v>
       </c>
       <c r="C23" s="65">
-        <f>AVERAGE(Y23,K23)</f>
+        <f t="shared" ref="C23:C36" si="23">AVERAGE(Y23,K23)</f>
         <v>100</v>
       </c>
       <c r="D23" s="64">
@@ -10270,7 +10270,7 @@
         <v>302</v>
       </c>
       <c r="C24" s="65">
-        <f>AVERAGE(Y24,K24)</f>
+        <f t="shared" si="23"/>
         <v>85</v>
       </c>
       <c r="D24" s="64">
@@ -10359,7 +10359,7 @@
         <v>314</v>
       </c>
       <c r="C25" s="65">
-        <f>AVERAGE(Y25,K25)</f>
+        <f t="shared" si="23"/>
         <v>87</v>
       </c>
       <c r="D25" s="64">
@@ -10448,7 +10448,7 @@
         <v>44</v>
       </c>
       <c r="C26" s="65">
-        <f>AVERAGE(Y26,K26)</f>
+        <f t="shared" si="23"/>
         <v>87.5</v>
       </c>
       <c r="D26" s="64">
@@ -10526,7 +10526,7 @@
         <v>88</v>
       </c>
       <c r="Z26" s="77">
-        <f t="shared" ref="Z26:Z30" si="23">( 5.7*AC26+9.4*AD26+4.1*(AE26) ) * 0.004184</f>
+        <f t="shared" ref="Z26:Z30" si="24">( 5.7*AC26+9.4*AD26+4.1*(AE26) ) * 0.004184</f>
         <v>19.822118400000001</v>
       </c>
       <c r="AA26" s="54">
@@ -10546,7 +10546,7 @@
         <v>21</v>
       </c>
       <c r="AE26" s="41">
-        <f t="shared" ref="AE26:AE30" si="24">1000-SUM(AC26:AD26,AF26)</f>
+        <f t="shared" ref="AE26:AE30" si="25">1000-SUM(AC26:AD26,AF26)</f>
         <v>390</v>
       </c>
       <c r="AF26" s="55">
@@ -10579,7 +10579,7 @@
         <v>45</v>
       </c>
       <c r="C27" s="65">
-        <f>AVERAGE(Y27,K27)</f>
+        <f t="shared" si="23"/>
         <v>87</v>
       </c>
       <c r="D27" s="64">
@@ -10621,7 +10621,7 @@
         <v>87</v>
       </c>
       <c r="Z27" s="77">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>20.560594400000003</v>
       </c>
       <c r="AA27" s="54">
@@ -10641,7 +10641,7 @@
         <v>27</v>
       </c>
       <c r="AE27" s="41">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>290</v>
       </c>
       <c r="AF27" s="55">
@@ -10668,11 +10668,11 @@
         <v>36</v>
       </c>
       <c r="C28" s="65">
-        <f>AVERAGE(Y28,K28)</f>
+        <f t="shared" si="23"/>
         <v>89.5</v>
       </c>
       <c r="D28" s="64">
-        <f t="shared" ref="D28:D34" si="25">L28</f>
+        <f t="shared" ref="D28:D34" si="26">L28</f>
         <v>19.4920008</v>
       </c>
       <c r="E28" s="38">
@@ -10746,7 +10746,7 @@
         <v>89</v>
       </c>
       <c r="Z28" s="77">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>18.9196296</v>
       </c>
       <c r="AA28" s="54">
@@ -10766,7 +10766,7 @@
         <v>26</v>
       </c>
       <c r="AE28" s="41">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>515</v>
       </c>
       <c r="AF28" s="55">
@@ -10799,11 +10799,11 @@
         <v>46</v>
       </c>
       <c r="C29" s="65">
-        <f>AVERAGE(Y29,K29)</f>
+        <f t="shared" si="23"/>
         <v>91</v>
       </c>
       <c r="D29" s="64">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>19.083224000000001</v>
       </c>
       <c r="E29" s="38">
@@ -10877,7 +10877,7 @@
         <v>90</v>
       </c>
       <c r="Z29" s="77">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>18.786160000000002</v>
       </c>
       <c r="AA29" s="54">
@@ -10897,7 +10897,7 @@
         <v>19</v>
       </c>
       <c r="AE29" s="41">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>533</v>
       </c>
       <c r="AF29" s="55">
@@ -10924,11 +10924,11 @@
         <v>47</v>
       </c>
       <c r="C30" s="65">
-        <f>AVERAGE(Y30,K30)</f>
+        <f t="shared" si="23"/>
         <v>91</v>
       </c>
       <c r="D30" s="64">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>19.581538399999999</v>
       </c>
       <c r="E30" s="38">
@@ -11002,7 +11002,7 @@
         <v>91</v>
       </c>
       <c r="Z30" s="77">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>19.540953599999998</v>
       </c>
       <c r="AA30" s="54">
@@ -11022,7 +11022,7 @@
         <v>94</v>
       </c>
       <c r="AE30" s="41">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>697</v>
       </c>
       <c r="AF30" s="55">
@@ -11049,11 +11049,11 @@
         <v>315</v>
       </c>
       <c r="C31" s="65">
-        <f>AVERAGE(Y31,K31)</f>
+        <f t="shared" si="23"/>
         <v>90</v>
       </c>
       <c r="D31" s="64">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>16.971140800000001</v>
       </c>
       <c r="E31" s="38">
@@ -11135,11 +11135,11 @@
         <v>48</v>
       </c>
       <c r="C32" s="65">
-        <f>AVERAGE(Y32,K32)</f>
+        <f t="shared" si="23"/>
         <v>87</v>
       </c>
       <c r="D32" s="64">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>18.194124000000002</v>
       </c>
       <c r="E32" s="38">
@@ -11213,7 +11213,7 @@
         <v>87</v>
       </c>
       <c r="Z32" s="77">
-        <f t="shared" ref="Z32:Z37" si="26">( 5.7*AC32+9.4*AD32+4.1*(AE32) ) * 0.004184</f>
+        <f t="shared" ref="Z32:Z37" si="27">( 5.7*AC32+9.4*AD32+4.1*(AE32) ) * 0.004184</f>
         <v>18.184500799999999</v>
       </c>
       <c r="AA32" s="54">
@@ -11233,7 +11233,7 @@
         <v>40</v>
       </c>
       <c r="AE32" s="41">
-        <f t="shared" ref="AE32:AE36" si="27">1000-SUM(AC32:AD32,AF32)</f>
+        <f t="shared" ref="AE32:AE36" si="28">1000-SUM(AC32:AD32,AF32)</f>
         <v>732</v>
       </c>
       <c r="AF32" s="55">
@@ -11266,11 +11266,11 @@
         <v>49</v>
       </c>
       <c r="C33" s="65">
-        <f>AVERAGE(Y33,K33)</f>
+        <f t="shared" si="23"/>
         <v>87.8</v>
       </c>
       <c r="D33" s="64">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>18.472360000000002</v>
       </c>
       <c r="E33" s="38">
@@ -11341,7 +11341,7 @@
         <v>88</v>
       </c>
       <c r="Z33" s="77">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>18.379056800000001</v>
       </c>
       <c r="AA33" s="54">
@@ -11361,7 +11361,7 @@
         <v>40</v>
       </c>
       <c r="AE33" s="41">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>735</v>
       </c>
       <c r="AF33" s="55">
@@ -11394,11 +11394,11 @@
         <v>50</v>
       </c>
       <c r="C34" s="65">
-        <f>AVERAGE(Y34,K34)</f>
+        <f t="shared" si="23"/>
         <v>90</v>
       </c>
       <c r="D34" s="64">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>19.659779199999999</v>
       </c>
       <c r="E34" s="38">
@@ -11472,7 +11472,7 @@
         <v>90</v>
       </c>
       <c r="Z34" s="77">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>20.139265599999998</v>
       </c>
       <c r="AA34" s="54">
@@ -11492,7 +11492,7 @@
         <v>66</v>
       </c>
       <c r="AE34" s="41">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>550</v>
       </c>
       <c r="AF34" s="55">
@@ -11519,7 +11519,7 @@
         <v>51</v>
       </c>
       <c r="C35" s="65">
-        <f>AVERAGE(Y35,K35)</f>
+        <f t="shared" si="23"/>
         <v>11</v>
       </c>
       <c r="D35" s="64">
@@ -11561,7 +11561,7 @@
         <v>11</v>
       </c>
       <c r="Z35" s="77">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>18.8602168</v>
       </c>
       <c r="AA35" s="54">
@@ -11581,7 +11581,7 @@
         <v>45</v>
       </c>
       <c r="AE35" s="41">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>607</v>
       </c>
       <c r="AF35" s="55">
@@ -11608,7 +11608,7 @@
         <v>309</v>
       </c>
       <c r="C36" s="65">
-        <f>AVERAGE(Y36,K36)</f>
+        <f t="shared" si="23"/>
         <v>90</v>
       </c>
       <c r="D36" s="64">
@@ -11682,7 +11682,7 @@
         <v>90</v>
       </c>
       <c r="Z36" s="77">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>19.578191199999999</v>
       </c>
       <c r="AA36" s="74">
@@ -11699,7 +11699,7 @@
         <v>67</v>
       </c>
       <c r="AE36" s="41">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>629</v>
       </c>
       <c r="AF36" s="45">
@@ -11773,7 +11773,7 @@
         <v>90</v>
       </c>
       <c r="Z37" s="77">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>22.900705599999998</v>
       </c>
       <c r="AA37" s="54">
@@ -11793,7 +11793,7 @@
         <v>71</v>
       </c>
       <c r="AE37" s="41">
-        <f t="shared" ref="AE37" si="28">1000-SUM(AC37:AD37,AF37)</f>
+        <f t="shared" ref="AE37" si="29">1000-SUM(AC37:AD37,AF37)</f>
         <v>231</v>
       </c>
       <c r="AF37" s="55">
@@ -11828,7 +11828,7 @@
         <v>52</v>
       </c>
       <c r="C38" s="65">
-        <f t="shared" ref="C38:C43" si="29">AVERAGE(Y38,K38)</f>
+        <f t="shared" ref="C38:C43" si="30">AVERAGE(Y38,K38)</f>
         <v>75.5</v>
       </c>
       <c r="D38" s="64">
@@ -11906,7 +11906,7 @@
         <v>76</v>
       </c>
       <c r="Z38" s="77">
-        <f t="shared" ref="Z38:Z43" si="30">( 5.7*AC38+9.4*AD38+4.1*(AE38) ) * 0.004184</f>
+        <f t="shared" ref="Z38:Z43" si="31">( 5.7*AC38+9.4*AD38+4.1*(AE38) ) * 0.004184</f>
         <v>15.9565208</v>
       </c>
       <c r="AA38" s="54">
@@ -11926,7 +11926,7 @@
         <v>2</v>
       </c>
       <c r="AE38" s="41">
-        <f t="shared" ref="AE38:AE43" si="31">1000-SUM(AC38:AD38,AF38)</f>
+        <f t="shared" ref="AE38:AE43" si="32">1000-SUM(AC38:AD38,AF38)</f>
         <v>724</v>
       </c>
       <c r="AF38" s="55">
@@ -11953,7 +11953,7 @@
         <v>53</v>
       </c>
       <c r="C39" s="65">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>89.5</v>
       </c>
       <c r="D39" s="64">
@@ -12031,7 +12031,7 @@
         <v>89</v>
       </c>
       <c r="Z39" s="77">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>16.664453599999998</v>
       </c>
       <c r="AA39" s="54">
@@ -12051,7 +12051,7 @@
         <v>10</v>
       </c>
       <c r="AE39" s="41">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>822</v>
       </c>
       <c r="AF39" s="55">
@@ -12078,7 +12078,7 @@
         <v>54</v>
       </c>
       <c r="C40" s="65">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>6.25</v>
       </c>
       <c r="D40" s="64">
@@ -12156,7 +12156,7 @@
         <v>5.5</v>
       </c>
       <c r="Z40" s="77">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>16.870306399999997</v>
       </c>
       <c r="AA40" s="54">
@@ -12176,7 +12176,7 @@
         <v>19</v>
       </c>
       <c r="AE40" s="41">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>780</v>
       </c>
       <c r="AF40" s="55">
@@ -12203,7 +12203,7 @@
         <v>55</v>
       </c>
       <c r="C41" s="65">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>97</v>
       </c>
       <c r="D41" s="64">
@@ -12245,7 +12245,7 @@
         <v>97</v>
       </c>
       <c r="Z41" s="77">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>16.975324799999999</v>
       </c>
       <c r="AA41" s="54">
@@ -12265,7 +12265,7 @@
         <v>22</v>
       </c>
       <c r="AE41" s="41">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>757</v>
       </c>
       <c r="AF41" s="55">
@@ -12292,7 +12292,7 @@
         <v>56</v>
       </c>
       <c r="C42" s="65">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>91</v>
       </c>
       <c r="D42" s="64">
@@ -12370,7 +12370,7 @@
         <v>92</v>
       </c>
       <c r="Z42" s="77">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>22.525819200000001</v>
       </c>
       <c r="AA42" s="54">
@@ -12390,7 +12390,7 @@
         <v>10</v>
       </c>
       <c r="AE42" s="41">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>121</v>
       </c>
       <c r="AF42" s="55">
@@ -12423,7 +12423,7 @@
         <v>57</v>
       </c>
       <c r="C43" s="66">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>92</v>
       </c>
       <c r="D43" s="67">
@@ -12465,7 +12465,7 @@
         <v>92</v>
       </c>
       <c r="Z43" s="78">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>22.254696000000003</v>
       </c>
       <c r="AA43" s="51">
@@ -12485,7 +12485,7 @@
         <v>105</v>
       </c>
       <c r="AE43" s="76">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AF43" s="58">

--- a/data/prod_parameters/FeedMgmt.xlsx
+++ b/data/prod_parameters/FeedMgmt.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="5100" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="5100" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="default" sheetId="1" r:id="rId1"/>
@@ -9775,7 +9775,7 @@
         <v>87.6</v>
       </c>
       <c r="D33" s="101">
-        <f t="shared" ref="D33:D34" si="32">M33</f>
+        <f t="shared" ref="D33" si="32">M33</f>
         <v>16.941015999999998</v>
       </c>
       <c r="E33" s="43">
@@ -9783,7 +9783,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="28">
-        <f t="shared" ref="F33:F34" si="33">AVERAGE(U33,AJ33)</f>
+        <f t="shared" ref="F33" si="33">AVERAGE(U33,AJ33)</f>
         <v>0.48</v>
       </c>
       <c r="G33" s="58">

--- a/data/prod_parameters/FeedMgmt.xlsx
+++ b/data/prod_parameters/FeedMgmt.xlsx
@@ -4,17 +4,18 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="5100" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="5100"/>
   </bookViews>
   <sheets>
     <sheet name="default" sheetId="1" r:id="rId1"/>
-    <sheet name="feed pars" sheetId="2" r:id="rId2"/>
-    <sheet name="feed pars csv" sheetId="8" r:id="rId3"/>
-    <sheet name="pigs" sheetId="3" r:id="rId4"/>
-    <sheet name="ruminants" sheetId="4" r:id="rId5"/>
-    <sheet name="ruminants, roughage" sheetId="6" r:id="rId6"/>
-    <sheet name="horses" sheetId="7" r:id="rId7"/>
-    <sheet name="poultry" sheetId="5" r:id="rId8"/>
+    <sheet name="references" sheetId="9" r:id="rId2"/>
+    <sheet name="feed pars" sheetId="2" r:id="rId3"/>
+    <sheet name="feed pars csv" sheetId="8" r:id="rId4"/>
+    <sheet name="pigs" sheetId="3" r:id="rId5"/>
+    <sheet name="ruminants" sheetId="4" r:id="rId6"/>
+    <sheet name="ruminants, roughage" sheetId="6" r:id="rId7"/>
+    <sheet name="horses" sheetId="7" r:id="rId8"/>
+    <sheet name="poultry" sheetId="5" r:id="rId9"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1580" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1564" uniqueCount="643">
   <si>
     <t>f_feed</t>
   </si>
@@ -1183,9 +1184,6 @@
     <t>feeding_losses</t>
   </si>
   <si>
-    <t>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</t>
-  </si>
-  <si>
     <t>Storage and feeding losses</t>
   </si>
   <si>
@@ -1207,12 +1205,6 @@
     <t>10% feeding on pasture</t>
   </si>
   <si>
-    <t>Need to add losses for grains and concentrates</t>
-  </si>
-  <si>
-    <t>No storage</t>
-  </si>
-  <si>
     <t>GE, MJ/kg DM</t>
   </si>
   <si>
@@ -1528,12 +1520,6 @@
     <t>%DM accrding to harvest stat</t>
   </si>
   <si>
-    <t>100% - 55% pasture utilisation</t>
-  </si>
-  <si>
-    <t>100% - 50% pasture utilisation</t>
-  </si>
-  <si>
     <t>DE, MJ</t>
   </si>
   <si>
@@ -1949,6 +1935,39 @@
   </si>
   <si>
     <t>rye bran</t>
+  </si>
+  <si>
+    <t>f_feed_group:feed</t>
+  </si>
+  <si>
+    <t>ley silage</t>
+  </si>
+  <si>
+    <t>hay and straw</t>
+  </si>
+  <si>
+    <t>dry concentrates</t>
+  </si>
+  <si>
+    <t>wet concentrates</t>
+  </si>
+  <si>
+    <t>??</t>
+  </si>
+  <si>
+    <t>Statistics Netherlands (2012) Standardised calculation methods for animal manure and nutrients. Standard data 1990–2008</t>
+  </si>
+  <si>
+    <t>Statistics Netherlands (2012)</t>
+  </si>
+  <si>
+    <t>Cederberg &amp; Henriksson (2020)</t>
+  </si>
+  <si>
+    <t>for cattle</t>
+  </si>
+  <si>
+    <t>Cederberg, C. &amp; Henriksson, M. (2020). Gräsmarkernas användning i jordbruket</t>
   </si>
 </sst>
 </file>
@@ -2742,22 +2761,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P164"/>
+  <dimension ref="A1:Q149"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="20.28515625" customWidth="1"/>
-    <col min="7" max="7" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" customWidth="1"/>
-    <col min="10" max="10" width="9.7109375" customWidth="1"/>
-    <col min="11" max="11" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="38.140625" customWidth="1"/>
-    <col min="15" max="15" width="58" customWidth="1"/>
+    <col min="6" max="7" width="20.28515625" customWidth="1"/>
+    <col min="8" max="8" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.140625" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" customWidth="1"/>
+    <col min="12" max="12" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="38.140625" customWidth="1"/>
+    <col min="16" max="16" width="58" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>19</v>
       </c>
@@ -2777,34 +2796,37 @@
         <v>0</v>
       </c>
       <c r="G1" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="4" t="s">
-        <v>589</v>
-      </c>
       <c r="K1" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="L1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -2817,670 +2839,676 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="2"/>
+      <c r="K2" s="1"/>
       <c r="L2" s="2"/>
-      <c r="M2" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="N2" s="20" t="s">
+      <c r="M2" s="2"/>
+      <c r="N2" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="O2" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="O2" s="2"/>
-      <c r="P2" s="5"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="K3" s="6" t="s">
+      <c r="P2" s="2"/>
+      <c r="Q2" s="5"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="L3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="17">
-        <v>0</v>
-      </c>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6" t="s">
+      <c r="M3" s="17">
+        <v>0</v>
+      </c>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F4" t="s">
         <v>300</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>10</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>28</v>
       </c>
-      <c r="L4" s="18">
+      <c r="M4" s="18">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F4,'feed pars'!B$6:B$46,0))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F5" t="s">
         <v>301</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>10</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>28</v>
       </c>
-      <c r="L5" s="18">
+      <c r="M5" s="18">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F5,'feed pars'!B$6:B$46,0))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F6" t="s">
         <v>302</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>10</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
         <v>28</v>
       </c>
-      <c r="L6" s="18">
+      <c r="M6" s="18">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F6,'feed pars'!B$6:B$46,0))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F7" t="s">
         <v>2</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>10</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
         <v>28</v>
       </c>
-      <c r="L7" s="18">
+      <c r="M7" s="18">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F7,'feed pars'!B$6:B$46,0))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F8" t="s">
         <v>12</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>11</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
         <v>28</v>
       </c>
-      <c r="L8" s="18">
+      <c r="M8" s="18">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F8,'feed pars'!B$6:B$46,0))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F9" t="s">
         <v>29</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>29</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>28</v>
       </c>
-      <c r="L9" s="18">
+      <c r="M9" s="18">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F9,'feed pars'!B$6:B$46,0))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F10" t="s">
         <v>17</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>17</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
         <v>28</v>
       </c>
-      <c r="L10" s="18">
+      <c r="M10" s="18">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F10,'feed pars'!B$6:B$46,0))</f>
         <v>1.1627906976744187</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F11" t="s">
         <v>33</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>33</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" t="s">
         <v>28</v>
       </c>
-      <c r="L11" s="18">
+      <c r="M11" s="18">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F11,'feed pars'!B$6:B$46,0))</f>
         <v>1.1627906976744187</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F12" t="s">
         <v>34</v>
       </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
         <v>34</v>
       </c>
-      <c r="K12" t="s">
+      <c r="L12" t="s">
         <v>28</v>
       </c>
-      <c r="L12" s="18">
+      <c r="M12" s="18">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F12,'feed pars'!B$6:B$46,0))</f>
         <v>1.1627906976744187</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F13" t="s">
         <v>35</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>35</v>
       </c>
-      <c r="K13" t="s">
+      <c r="L13" t="s">
         <v>28</v>
       </c>
-      <c r="L13" s="18">
+      <c r="M13" s="18">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F13,'feed pars'!B$6:B$46,0))</f>
         <v>1.1627906976744187</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F14" t="s">
         <v>306</v>
       </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>306</v>
       </c>
-      <c r="K14" t="s">
+      <c r="L14" t="s">
         <v>28</v>
       </c>
-      <c r="L14" s="18">
+      <c r="M14" s="18">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F14,'feed pars'!B$6:B$46,0))</f>
         <v>1.1627906976744187</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F15" t="s">
         <v>36</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>36</v>
       </c>
-      <c r="K15" t="s">
+      <c r="L15" t="s">
         <v>28</v>
       </c>
-      <c r="L15" s="18">
+      <c r="M15" s="18">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F15,'feed pars'!B$6:B$46,0))</f>
         <v>1.1627906976744187</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F16" t="s">
         <v>37</v>
       </c>
-      <c r="H16" t="s">
+      <c r="I16" t="s">
         <v>37</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" t="s">
         <v>28</v>
       </c>
-      <c r="L16" s="18">
+      <c r="M16" s="18">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F16,'feed pars'!B$6:B$46,0))</f>
         <v>1.1764705882352942</v>
       </c>
     </row>
-    <row r="17" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F17" t="s">
         <v>38</v>
       </c>
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>38</v>
       </c>
-      <c r="K17" t="s">
+      <c r="L17" t="s">
         <v>28</v>
       </c>
-      <c r="L17" s="18">
+      <c r="M17" s="18">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F17,'feed pars'!B$6:B$46,0))</f>
         <v>1.1764705882352942</v>
       </c>
     </row>
-    <row r="18" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F18" t="s">
         <v>31</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>31</v>
       </c>
-      <c r="K18" t="s">
+      <c r="L18" t="s">
         <v>28</v>
       </c>
-      <c r="L18" s="18">
+      <c r="M18" s="18">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F18,'feed pars'!B$6:B$46,0))</f>
         <v>1.0989010989010988</v>
       </c>
     </row>
-    <row r="19" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F19" t="s">
         <v>39</v>
       </c>
-      <c r="H19" t="s">
+      <c r="I19" t="s">
         <v>39</v>
       </c>
-      <c r="K19" t="s">
+      <c r="L19" t="s">
         <v>28</v>
       </c>
-      <c r="L19" s="18">
+      <c r="M19" s="18">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F19,'feed pars'!B$6:B$46,0))</f>
         <v>1.0989010989010988</v>
       </c>
     </row>
-    <row r="20" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F20" s="3" t="s">
         <v>304</v>
       </c>
       <c r="G20" s="3"/>
-      <c r="H20" s="3" t="s">
+      <c r="H20" s="3"/>
+      <c r="I20" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="I20" s="3"/>
       <c r="J20" s="3"/>
-      <c r="K20" s="3" t="s">
+      <c r="K20" s="3"/>
+      <c r="L20" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="L20" s="16">
+      <c r="M20" s="16">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F20,'feed pars'!B$6:B$46,0))*1/0.38</f>
         <v>2.6315789473684212</v>
       </c>
     </row>
-    <row r="21" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F21" s="3" t="s">
         <v>304</v>
       </c>
       <c r="G21" s="3"/>
-      <c r="H21" s="3" t="s">
+      <c r="H21" s="3"/>
+      <c r="I21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3" t="s">
+      <c r="K21" s="3"/>
+      <c r="L21" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="L21" s="18"/>
-      <c r="N21" s="3" t="s">
+      <c r="M21" s="18"/>
+      <c r="O21" s="3" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="22" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F22" t="s">
         <v>296</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>296</v>
       </c>
-      <c r="K22" t="s">
+      <c r="L22" t="s">
         <v>28</v>
       </c>
-      <c r="L22" s="18">
+      <c r="M22" s="18">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F22,'feed pars'!B$6:B$46,0))</f>
         <v>1.1764705882352942</v>
       </c>
     </row>
-    <row r="23" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F23" s="21" t="s">
         <v>307</v>
       </c>
       <c r="G23" s="21"/>
-      <c r="H23" s="21" t="s">
+      <c r="H23" s="21"/>
+      <c r="I23" s="21" t="s">
         <v>307</v>
       </c>
-      <c r="I23" s="21"/>
       <c r="J23" s="21"/>
-      <c r="K23" s="21" t="s">
+      <c r="K23" s="21"/>
+      <c r="L23" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="L23" s="18">
+      <c r="M23" s="18">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F23,'feed pars'!B$6:B$46,0))</f>
         <v>1.1494252873563218</v>
       </c>
-      <c r="M23" s="21"/>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="6:14" x14ac:dyDescent="0.25">
+      <c r="N23" s="21"/>
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F24" t="s">
         <v>40</v>
       </c>
-      <c r="I24" t="s">
+      <c r="J24" t="s">
         <v>40</v>
       </c>
-      <c r="K24" t="s">
+      <c r="L24" t="s">
         <v>28</v>
       </c>
-      <c r="L24" s="18">
+      <c r="M24" s="18">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F24,'feed pars'!B$6:B$46,0))</f>
         <v>1.1428571428571428</v>
       </c>
     </row>
-    <row r="25" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F25" s="3" t="s">
         <v>41</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
-      <c r="I25" s="3" t="s">
+      <c r="I25" s="3"/>
+      <c r="J25" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3" t="s">
+      <c r="K25" s="3"/>
+      <c r="L25" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="L25" s="16">
+      <c r="M25" s="16">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F25,'feed pars'!B$6:B$46,0))</f>
         <v>1.1428571428571428</v>
       </c>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="26" spans="6:14" x14ac:dyDescent="0.25">
+      <c r="N25" s="3"/>
+      <c r="O25" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="26" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F26" t="s">
         <v>32</v>
       </c>
-      <c r="I26" t="s">
+      <c r="J26" t="s">
         <v>32</v>
       </c>
-      <c r="K26" t="s">
+      <c r="L26" t="s">
         <v>28</v>
       </c>
-      <c r="L26" s="18">
+      <c r="M26" s="18">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F26,'feed pars'!B$6:B$46,0))</f>
         <v>1.1173184357541899</v>
       </c>
     </row>
-    <row r="27" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F27" t="s">
         <v>42</v>
       </c>
-      <c r="I27" t="s">
+      <c r="J27" t="s">
         <v>42</v>
       </c>
-      <c r="K27" t="s">
+      <c r="L27" t="s">
         <v>28</v>
       </c>
-      <c r="L27" s="18">
+      <c r="M27" s="18">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F27,'feed pars'!B$6:B$46,0))</f>
         <v>1.0989010989010988</v>
       </c>
     </row>
-    <row r="28" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F28" t="s">
         <v>43</v>
       </c>
-      <c r="I28" t="s">
+      <c r="J28" t="s">
         <v>43</v>
       </c>
-      <c r="K28" t="s">
+      <c r="L28" t="s">
         <v>28</v>
       </c>
-      <c r="L28" s="18">
+      <c r="M28" s="18">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F28,'feed pars'!B$6:B$46,0))</f>
         <v>1.0989010989010988</v>
       </c>
     </row>
-    <row r="29" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F29" s="3" t="s">
         <v>308</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
-      <c r="I29" s="3" t="s">
+      <c r="I29" s="3"/>
+      <c r="J29" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3" t="s">
+      <c r="K29" s="3"/>
+      <c r="L29" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="L29" s="16">
+      <c r="M29" s="16">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F29,'feed pars'!B$6:B$46,0))</f>
         <v>1.1111111111111112</v>
       </c>
-      <c r="M29" s="3"/>
       <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="6:14" x14ac:dyDescent="0.25">
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F30" t="s">
         <v>44</v>
       </c>
-      <c r="I30" t="s">
+      <c r="J30" t="s">
         <v>44</v>
       </c>
-      <c r="K30" t="s">
+      <c r="L30" t="s">
         <v>28</v>
       </c>
-      <c r="L30" s="18">
+      <c r="M30" s="18">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F30,'feed pars'!B$6:B$46,0))</f>
         <v>1.1494252873563218</v>
       </c>
     </row>
-    <row r="31" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F31" t="s">
         <v>45</v>
       </c>
-      <c r="I31" t="s">
+      <c r="J31" t="s">
         <v>44</v>
       </c>
-      <c r="K31" t="s">
+      <c r="L31" t="s">
         <v>28</v>
       </c>
-      <c r="L31" s="18">
+      <c r="M31" s="18">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F31,'feed pars'!B$6:B$46,0))</f>
         <v>1.1389521640091116</v>
       </c>
     </row>
-    <row r="32" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F32" t="s">
-        <v>592</v>
-      </c>
-      <c r="I32" t="s">
-        <v>592</v>
-      </c>
-      <c r="K32" t="s">
+        <v>587</v>
+      </c>
+      <c r="J32" t="s">
+        <v>587</v>
+      </c>
+      <c r="L32" t="s">
         <v>28</v>
       </c>
-      <c r="L32" s="18">
+      <c r="M32" s="18">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F32,'feed pars'!B$6:B$46,0))</f>
         <v>1.1415525114155252</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="F33" t="s">
-        <v>593</v>
-      </c>
-      <c r="I33" t="s">
-        <v>593</v>
-      </c>
-      <c r="K33" t="s">
+        <v>588</v>
+      </c>
+      <c r="J33" t="s">
+        <v>588</v>
+      </c>
+      <c r="L33" t="s">
         <v>28</v>
       </c>
-      <c r="L33" s="18">
+      <c r="M33" s="18">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F33,'feed pars'!B$6:B$46,0))</f>
         <v>1.1415525114155252</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="F34" t="s">
-        <v>636</v>
-      </c>
-      <c r="I34" t="s">
-        <v>636</v>
-      </c>
-      <c r="K34" t="s">
+        <v>631</v>
+      </c>
+      <c r="J34" t="s">
+        <v>631</v>
+      </c>
+      <c r="L34" t="s">
         <v>28</v>
       </c>
-      <c r="L34" s="18">
+      <c r="M34" s="18">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F34,'feed pars'!B$6:B$46,0))</f>
         <v>1.1415525114155252</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="F35" t="s">
         <v>46</v>
       </c>
-      <c r="I35" t="s">
+      <c r="J35" t="s">
         <v>293</v>
       </c>
-      <c r="K35" t="s">
+      <c r="L35" t="s">
         <v>28</v>
       </c>
-      <c r="L35" s="18">
+      <c r="M35" s="18">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F35,'feed pars'!B$6:B$46,0))</f>
         <v>1.1111111111111112</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="F36" t="s">
         <v>47</v>
       </c>
-      <c r="I36" t="s">
+      <c r="J36" t="s">
         <v>293</v>
       </c>
-      <c r="K36" t="s">
+      <c r="L36" t="s">
         <v>28</v>
       </c>
-      <c r="L36" s="18">
-        <f>L35</f>
+      <c r="M36" s="18">
+        <f>M35</f>
         <v>1.1111111111111112</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="F37" t="s">
         <v>303</v>
       </c>
-      <c r="I37" t="s">
+      <c r="J37" t="s">
         <v>303</v>
       </c>
-      <c r="K37" t="s">
+      <c r="L37" t="s">
         <v>28</v>
       </c>
-      <c r="L37" s="16">
+      <c r="M37" s="16">
         <f>1/0.25</f>
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="F38" t="s">
         <v>48</v>
       </c>
-      <c r="I38" t="s">
+      <c r="J38" t="s">
         <v>48</v>
       </c>
-      <c r="K38" t="s">
+      <c r="L38" t="s">
         <v>28</v>
       </c>
-      <c r="L38" s="18">
+      <c r="M38" s="18">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F38,'feed pars'!B$6:B$46,0))</f>
         <v>1.3245033112582782</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="F39" t="s">
         <v>49</v>
       </c>
-      <c r="I39" t="s">
+      <c r="J39" t="s">
         <v>49</v>
       </c>
-      <c r="K39" t="s">
+      <c r="L39" t="s">
         <v>28</v>
       </c>
-      <c r="L39" s="18">
+      <c r="M39" s="18">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F39,'feed pars'!B$6:B$46,0))</f>
         <v>1.1173184357541899</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="F40" t="s">
         <v>50</v>
       </c>
-      <c r="I40" t="s">
+      <c r="J40" t="s">
         <v>50</v>
       </c>
-      <c r="K40" t="s">
+      <c r="L40" t="s">
         <v>28</v>
       </c>
-      <c r="L40" s="18">
+      <c r="M40" s="18">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F40,'feed pars'!B$6:B$46,0))</f>
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="F41" t="s">
         <v>51</v>
       </c>
-      <c r="I41" t="s">
+      <c r="J41" t="s">
         <v>50</v>
       </c>
-      <c r="K41" t="s">
+      <c r="L41" t="s">
         <v>28</v>
       </c>
-      <c r="L41" s="16">
-        <f>L40</f>
+      <c r="M41" s="16">
+        <f>M40</f>
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="F42" t="s">
         <v>52</v>
       </c>
-      <c r="I42" t="s">
+      <c r="J42" t="s">
         <v>52</v>
       </c>
-      <c r="K42" t="s">
+      <c r="L42" t="s">
         <v>28</v>
       </c>
-      <c r="L42" s="18">
+      <c r="M42" s="18">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F42,'feed pars'!B$6:B$46,0))</f>
         <v>1.0989010989010988</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="F43" t="s">
-        <v>605</v>
-      </c>
-      <c r="I43" t="s">
-        <v>605</v>
-      </c>
-      <c r="K43" t="s">
+        <v>600</v>
+      </c>
+      <c r="J43" t="s">
+        <v>600</v>
+      </c>
+      <c r="L43" t="s">
         <v>28</v>
       </c>
-      <c r="L43" s="18">
+      <c r="M43" s="18">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F43,'feed pars'!B$6:B$46,0))</f>
         <v>4.3478260869565215</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="F44" t="s">
         <v>53</v>
       </c>
-      <c r="I44" t="s">
+      <c r="J44" t="s">
         <v>53</v>
       </c>
-      <c r="K44" t="s">
+      <c r="L44" t="s">
         <v>28</v>
       </c>
-      <c r="L44" s="18">
+      <c r="M44" s="18">
         <f>1/INDEX('feed pars'!C$6:C$46/100,MATCH(F44,'feed pars'!B$6:B$46,0))</f>
         <v>1.0863661053775122</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>25</v>
       </c>
@@ -3498,170 +3526,171 @@
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="K46" s="6" t="s">
+      <c r="P45" s="2"/>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L46" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="L46" s="6">
-        <v>0</v>
-      </c>
-      <c r="M46" s="6"/>
-      <c r="N46" s="6" t="s">
+      <c r="M46" s="6">
+        <v>0</v>
+      </c>
+      <c r="N46" s="6"/>
+      <c r="O46" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="H47" t="s">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I47" t="s">
         <v>10</v>
       </c>
-      <c r="K47" t="s">
+      <c r="L47" t="s">
         <v>23</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>95</v>
       </c>
-      <c r="M47" t="s">
+      <c r="N47" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="H48" t="s">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I48" t="s">
         <v>11</v>
       </c>
-      <c r="K48" t="s">
+      <c r="L48" t="s">
         <v>23</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>95</v>
       </c>
-      <c r="M48" t="s">
+      <c r="N48" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="H49" t="s">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I49" t="s">
         <v>29</v>
       </c>
-      <c r="K49" t="s">
+      <c r="L49" t="s">
         <v>23</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>95</v>
       </c>
-      <c r="M49" t="s">
+      <c r="N49" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>21</v>
       </c>
-      <c r="H50" t="s">
+      <c r="I50" t="s">
         <v>33</v>
       </c>
-      <c r="K50" t="s">
+      <c r="L50" t="s">
         <v>23</v>
       </c>
-      <c r="L50" s="3">
+      <c r="M50" s="3">
         <v>50</v>
       </c>
-      <c r="M50" t="s">
+      <c r="N50" t="s">
         <v>24</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>375</v>
       </c>
-      <c r="H51" t="s">
+      <c r="I51" t="s">
         <v>33</v>
       </c>
-      <c r="K51" t="s">
+      <c r="L51" t="s">
         <v>23</v>
       </c>
-      <c r="L51" s="3">
+      <c r="M51" s="3">
         <v>50</v>
       </c>
-      <c r="M51" t="s">
+      <c r="N51" t="s">
         <v>24</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>21</v>
       </c>
-      <c r="H52" t="s">
+      <c r="I52" t="s">
         <v>17</v>
       </c>
-      <c r="K52" t="s">
+      <c r="L52" t="s">
         <v>23</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>50</v>
       </c>
-      <c r="M52" t="s">
+      <c r="N52" t="s">
         <v>24</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>375</v>
       </c>
-      <c r="H53" t="s">
+      <c r="I53" t="s">
         <v>17</v>
       </c>
-      <c r="K53" t="s">
+      <c r="L53" t="s">
         <v>23</v>
       </c>
-      <c r="L53" s="3">
+      <c r="M53" s="3">
         <v>50</v>
       </c>
-      <c r="M53" t="s">
+      <c r="N53" t="s">
         <v>24</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>21</v>
       </c>
-      <c r="H54" t="s">
+      <c r="I54" t="s">
         <v>34</v>
       </c>
-      <c r="K54" t="s">
+      <c r="L54" t="s">
         <v>23</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>50</v>
       </c>
-      <c r="M54" t="s">
+      <c r="N54" t="s">
         <v>24</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>375</v>
       </c>
-      <c r="H55" t="s">
+      <c r="I55" t="s">
         <v>34</v>
       </c>
-      <c r="K55" t="s">
+      <c r="L55" t="s">
         <v>23</v>
       </c>
-      <c r="L55" s="3">
+      <c r="M55" s="3">
         <v>50</v>
       </c>
-      <c r="M55" t="s">
+      <c r="N55" t="s">
         <v>24</v>
       </c>
-      <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>26</v>
       </c>
@@ -3679,98 +3708,99 @@
       <c r="M56" s="2"/>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="K57" s="6" t="s">
+      <c r="P56" s="2"/>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L57" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="L57" s="6">
-        <v>0</v>
-      </c>
-      <c r="M57" s="6"/>
-      <c r="N57" s="6" t="s">
+      <c r="M57" s="6">
+        <v>0</v>
+      </c>
+      <c r="N57" s="6"/>
+      <c r="O57" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="H58" t="s">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I58" t="s">
         <v>307</v>
       </c>
-      <c r="K58" t="s">
+      <c r="L58" t="s">
         <v>27</v>
       </c>
-      <c r="L58" s="21">
+      <c r="M58" s="21">
         <v>100</v>
       </c>
-      <c r="M58" s="21" t="s">
+      <c r="N58" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="N58" s="6"/>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="I59" t="s">
+      <c r="O58" s="6"/>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J59" t="s">
         <v>40</v>
       </c>
-      <c r="K59" t="s">
+      <c r="L59" t="s">
         <v>27</v>
       </c>
-      <c r="L59" s="21">
+      <c r="M59" s="21">
         <v>100</v>
       </c>
-      <c r="M59" s="21" t="s">
+      <c r="N59" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="N59" s="6"/>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="I60" t="s">
+      <c r="O59" s="6"/>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J60" t="s">
         <v>32</v>
       </c>
-      <c r="K60" t="s">
+      <c r="L60" t="s">
         <v>27</v>
       </c>
-      <c r="L60" s="21">
+      <c r="M60" s="21">
         <v>61</v>
       </c>
-      <c r="M60" t="s">
+      <c r="N60" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="H61" t="s">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I61" t="s">
         <v>39</v>
       </c>
-      <c r="K61" t="s">
+      <c r="L61" t="s">
         <v>27</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>100</v>
       </c>
-      <c r="M61" t="s">
+      <c r="N61" t="s">
         <v>24</v>
       </c>
-      <c r="N61" s="3" t="s">
+      <c r="O61" s="3" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="H62" t="s">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I62" t="s">
         <v>36</v>
       </c>
-      <c r="K62" t="s">
+      <c r="L62" t="s">
         <v>27</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>50</v>
       </c>
-      <c r="M62" t="s">
+      <c r="N62" t="s">
         <v>24</v>
       </c>
-      <c r="N62" s="3" t="s">
+      <c r="O62" s="3" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>322</v>
       </c>
@@ -3788,29 +3818,30 @@
       <c r="M63" s="2"/>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P63" s="2"/>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>20</v>
       </c>
-      <c r="G64" t="s">
+      <c r="H64" t="s">
         <v>320</v>
       </c>
-      <c r="H64" t="s">
+      <c r="I64" t="s">
         <v>29</v>
       </c>
-      <c r="K64" t="s">
+      <c r="L64" t="s">
         <v>321</v>
       </c>
-      <c r="L64" s="3">
+      <c r="M64" s="3">
         <v>90</v>
       </c>
-      <c r="M64" t="s">
+      <c r="N64" t="s">
         <v>24</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>20</v>
       </c>
@@ -3820,24 +3851,24 @@
       <c r="E65" t="s">
         <v>316</v>
       </c>
-      <c r="G65" t="s">
+      <c r="H65" t="s">
         <v>320</v>
       </c>
-      <c r="H65" t="s">
+      <c r="I65" t="s">
         <v>29</v>
       </c>
-      <c r="K65" t="s">
+      <c r="L65" t="s">
         <v>321</v>
       </c>
-      <c r="L65" s="3">
+      <c r="M65" s="3">
         <v>5</v>
       </c>
-      <c r="M65" t="s">
+      <c r="N65" t="s">
         <v>24</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>20</v>
       </c>
@@ -3847,48 +3878,48 @@
       <c r="E66" t="s">
         <v>317</v>
       </c>
-      <c r="G66" t="s">
+      <c r="H66" t="s">
         <v>320</v>
       </c>
-      <c r="H66" t="s">
+      <c r="I66" t="s">
         <v>29</v>
       </c>
-      <c r="K66" t="s">
+      <c r="L66" t="s">
         <v>321</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5</v>
       </c>
-      <c r="M66" t="s">
+      <c r="N66" t="s">
         <v>24</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>20</v>
       </c>
       <c r="E67" t="s">
         <v>318</v>
       </c>
-      <c r="G67" t="s">
+      <c r="H67" t="s">
         <v>320</v>
       </c>
-      <c r="H67" t="s">
+      <c r="I67" t="s">
         <v>29</v>
       </c>
-      <c r="K67" t="s">
+      <c r="L67" t="s">
         <v>321</v>
       </c>
-      <c r="L67" s="3">
-        <v>0</v>
-      </c>
-      <c r="M67" t="s">
+      <c r="M67" s="3">
+        <v>0</v>
+      </c>
+      <c r="N67" t="s">
         <v>24</v>
       </c>
-      <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>20</v>
       </c>
@@ -3898,52 +3929,52 @@
       <c r="E68" t="s">
         <v>319</v>
       </c>
-      <c r="G68" t="s">
+      <c r="H68" t="s">
         <v>320</v>
       </c>
-      <c r="H68" t="s">
+      <c r="I68" t="s">
         <v>29</v>
       </c>
-      <c r="K68" t="s">
+      <c r="L68" t="s">
         <v>321</v>
       </c>
-      <c r="L68" s="3">
-        <v>0</v>
-      </c>
-      <c r="M68" t="s">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" t="s">
         <v>24</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="L69" s="3"/>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M69" s="3"/>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>20</v>
       </c>
-      <c r="G70" t="s">
+      <c r="H70" t="s">
         <v>320</v>
       </c>
-      <c r="H70" t="s">
+      <c r="I70" t="s">
         <v>29</v>
       </c>
-      <c r="J70">
+      <c r="K70">
         <v>811</v>
       </c>
-      <c r="K70" t="s">
+      <c r="L70" t="s">
         <v>321</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>100</v>
       </c>
-      <c r="M70" t="s">
+      <c r="N70" t="s">
         <v>24</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>20</v>
       </c>
@@ -3953,27 +3984,27 @@
       <c r="E71" t="s">
         <v>316</v>
       </c>
-      <c r="G71" t="s">
+      <c r="H71" t="s">
         <v>320</v>
       </c>
-      <c r="H71" t="s">
+      <c r="I71" t="s">
         <v>29</v>
       </c>
-      <c r="J71">
+      <c r="K71">
         <v>811</v>
       </c>
-      <c r="K71" t="s">
+      <c r="L71" t="s">
         <v>321</v>
       </c>
-      <c r="L71" s="3">
+      <c r="M71" s="3">
         <v>50</v>
       </c>
-      <c r="M71" t="s">
+      <c r="N71" t="s">
         <v>24</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>20</v>
       </c>
@@ -3983,54 +4014,54 @@
       <c r="E72" t="s">
         <v>317</v>
       </c>
-      <c r="G72" t="s">
+      <c r="H72" t="s">
         <v>320</v>
       </c>
-      <c r="H72" t="s">
+      <c r="I72" t="s">
         <v>29</v>
       </c>
-      <c r="J72">
+      <c r="K72">
         <v>811</v>
       </c>
-      <c r="K72" t="s">
+      <c r="L72" t="s">
         <v>321</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>50</v>
       </c>
-      <c r="M72" t="s">
+      <c r="N72" t="s">
         <v>24</v>
       </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>20</v>
       </c>
       <c r="E73" t="s">
         <v>318</v>
       </c>
-      <c r="G73" t="s">
+      <c r="H73" t="s">
         <v>320</v>
       </c>
-      <c r="H73" t="s">
+      <c r="I73" t="s">
         <v>29</v>
       </c>
-      <c r="J73">
+      <c r="K73">
         <v>811</v>
       </c>
-      <c r="K73" t="s">
+      <c r="L73" t="s">
         <v>321</v>
       </c>
-      <c r="L73" s="3">
-        <v>0</v>
-      </c>
-      <c r="M73" t="s">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" t="s">
         <v>24</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>20</v>
       </c>
@@ -4040,51 +4071,51 @@
       <c r="E74" t="s">
         <v>319</v>
       </c>
-      <c r="G74" t="s">
+      <c r="H74" t="s">
         <v>320</v>
       </c>
-      <c r="H74" t="s">
+      <c r="I74" t="s">
         <v>29</v>
       </c>
-      <c r="J74">
+      <c r="K74">
         <v>811</v>
       </c>
-      <c r="K74" t="s">
+      <c r="L74" t="s">
         <v>321</v>
       </c>
-      <c r="L74" s="3">
-        <v>0</v>
-      </c>
-      <c r="M74" t="s">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" t="s">
         <v>24</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>20</v>
       </c>
-      <c r="G75" t="s">
+      <c r="H75" t="s">
         <v>320</v>
       </c>
-      <c r="H75" t="s">
+      <c r="I75" t="s">
         <v>29</v>
       </c>
-      <c r="J75">
+      <c r="K75">
         <v>812</v>
       </c>
-      <c r="K75" t="s">
+      <c r="L75" t="s">
         <v>321</v>
       </c>
-      <c r="L75" s="3">
+      <c r="M75" s="3">
         <v>100</v>
       </c>
-      <c r="M75" t="s">
+      <c r="N75" t="s">
         <v>24</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>20</v>
       </c>
@@ -4094,27 +4125,27 @@
       <c r="E76" t="s">
         <v>316</v>
       </c>
-      <c r="G76" t="s">
+      <c r="H76" t="s">
         <v>320</v>
       </c>
-      <c r="H76" t="s">
+      <c r="I76" t="s">
         <v>29</v>
       </c>
-      <c r="J76">
+      <c r="K76">
         <v>812</v>
       </c>
-      <c r="K76" t="s">
+      <c r="L76" t="s">
         <v>321</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>50</v>
       </c>
-      <c r="M76" t="s">
+      <c r="N76" t="s">
         <v>24</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>20</v>
       </c>
@@ -4124,54 +4155,54 @@
       <c r="E77" t="s">
         <v>317</v>
       </c>
-      <c r="G77" t="s">
+      <c r="H77" t="s">
         <v>320</v>
       </c>
-      <c r="H77" t="s">
+      <c r="I77" t="s">
         <v>29</v>
       </c>
-      <c r="J77">
+      <c r="K77">
         <v>812</v>
       </c>
-      <c r="K77" t="s">
+      <c r="L77" t="s">
         <v>321</v>
       </c>
-      <c r="L77" s="3">
+      <c r="M77" s="3">
         <v>50</v>
       </c>
-      <c r="M77" t="s">
+      <c r="N77" t="s">
         <v>24</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O77" s="3"/>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>20</v>
       </c>
       <c r="E78" t="s">
         <v>318</v>
       </c>
-      <c r="G78" t="s">
+      <c r="H78" t="s">
         <v>320</v>
       </c>
-      <c r="H78" t="s">
+      <c r="I78" t="s">
         <v>29</v>
       </c>
-      <c r="J78">
+      <c r="K78">
         <v>812</v>
       </c>
-      <c r="K78" t="s">
+      <c r="L78" t="s">
         <v>321</v>
       </c>
-      <c r="L78" s="3">
-        <v>0</v>
-      </c>
-      <c r="M78" t="s">
+      <c r="M78" s="3">
+        <v>0</v>
+      </c>
+      <c r="N78" t="s">
         <v>24</v>
       </c>
-      <c r="N78" s="3"/>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O78" s="3"/>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>20</v>
       </c>
@@ -4181,58 +4212,58 @@
       <c r="E79" t="s">
         <v>319</v>
       </c>
-      <c r="G79" t="s">
+      <c r="H79" t="s">
         <v>320</v>
       </c>
-      <c r="H79" t="s">
+      <c r="I79" t="s">
         <v>29</v>
       </c>
-      <c r="J79">
+      <c r="K79">
         <v>812</v>
       </c>
-      <c r="K79" t="s">
+      <c r="L79" t="s">
         <v>321</v>
       </c>
-      <c r="L79" s="3">
-        <v>0</v>
-      </c>
-      <c r="M79" t="s">
+      <c r="M79" s="3">
+        <v>0</v>
+      </c>
+      <c r="N79" t="s">
         <v>24</v>
       </c>
-      <c r="N79" s="3"/>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="L80" s="3"/>
-      <c r="N80" s="3"/>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O79" s="3"/>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M80" s="3"/>
+      <c r="O80" s="3"/>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>378</v>
       </c>
-      <c r="G81" t="s">
+      <c r="H81" t="s">
         <v>320</v>
       </c>
-      <c r="H81" t="s">
+      <c r="I81" t="s">
         <v>29</v>
       </c>
-      <c r="K81" t="s">
+      <c r="L81" t="s">
         <v>321</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>10</v>
       </c>
-      <c r="M81" t="s">
+      <c r="N81" t="s">
         <v>24</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="L82" s="3"/>
-      <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M82" s="3"/>
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -4248,36 +4279,37 @@
       <c r="M83" s="2"/>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="K84" s="6" t="s">
+      <c r="P83" s="2"/>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L84" s="6" t="s">
         <v>379</v>
       </c>
-      <c r="L84" s="6">
-        <v>0</v>
-      </c>
-      <c r="M84" s="6" t="s">
+      <c r="M84" s="6">
+        <v>0</v>
+      </c>
+      <c r="N84" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="N84" s="6" t="s">
+      <c r="O84" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="K85" s="6" t="s">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L85" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="L85" s="6">
-        <v>0</v>
-      </c>
-      <c r="M85" s="6" t="s">
+      <c r="M85" s="6">
+        <v>0</v>
+      </c>
+      <c r="N85" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="N85" s="6" t="s">
+      <c r="O85" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>20</v>
       </c>
@@ -4287,97 +4319,97 @@
       <c r="E86" t="s">
         <v>316</v>
       </c>
-      <c r="F86" t="s">
-        <v>300</v>
-      </c>
-      <c r="K86" s="21" t="s">
+      <c r="G86" t="s">
+        <v>633</v>
+      </c>
+      <c r="L86" s="21" t="s">
         <v>379</v>
       </c>
-      <c r="L86" s="21">
+      <c r="M86" s="21">
         <f>(0.8*20+0.2*2)</f>
         <v>16.399999999999999</v>
       </c>
-      <c r="M86" s="21" t="s">
+      <c r="N86" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="N86" s="21" t="s">
-        <v>384</v>
-      </c>
-      <c r="O86" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O86" s="21" t="s">
+        <v>383</v>
+      </c>
+      <c r="P86" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>20</v>
       </c>
-      <c r="F87" t="s">
-        <v>300</v>
-      </c>
-      <c r="K87" s="21" t="s">
+      <c r="G87" t="s">
+        <v>633</v>
+      </c>
+      <c r="L87" s="21" t="s">
         <v>379</v>
       </c>
-      <c r="L87" s="21">
+      <c r="M87" s="21">
         <f>(0.6*20+0.4*2)</f>
         <v>12.8</v>
       </c>
-      <c r="M87" s="21" t="s">
+      <c r="N87" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="N87" s="21" t="s">
+      <c r="O87" s="21" t="s">
+        <v>384</v>
+      </c>
+      <c r="P87" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>382</v>
+      </c>
+      <c r="G88" t="s">
+        <v>633</v>
+      </c>
+      <c r="L88" s="21" t="s">
+        <v>379</v>
+      </c>
+      <c r="M88" s="21">
+        <v>2</v>
+      </c>
+      <c r="N88" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="O88" s="21" t="s">
         <v>385</v>
       </c>
-      <c r="O87" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>383</v>
-      </c>
-      <c r="F88" t="s">
-        <v>300</v>
-      </c>
-      <c r="K88" s="21" t="s">
-        <v>379</v>
-      </c>
-      <c r="L88" s="21">
-        <v>2</v>
-      </c>
-      <c r="M88" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="N88" s="21" t="s">
-        <v>386</v>
-      </c>
-      <c r="O88" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P88" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>378</v>
       </c>
-      <c r="F89" t="s">
-        <v>300</v>
-      </c>
-      <c r="K89" s="21" t="s">
+      <c r="G89" t="s">
+        <v>633</v>
+      </c>
+      <c r="L89" s="21" t="s">
         <v>379</v>
       </c>
-      <c r="L89" s="21">
+      <c r="M89" s="21">
         <v>2</v>
       </c>
-      <c r="M89" s="21" t="s">
+      <c r="N89" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="N89" s="21" t="s">
-        <v>386</v>
-      </c>
-      <c r="O89" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O89" s="21" t="s">
+        <v>385</v>
+      </c>
+      <c r="P89" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>20</v>
       </c>
@@ -4387,1458 +4419,1012 @@
       <c r="E90" t="s">
         <v>316</v>
       </c>
-      <c r="F90" t="s">
-        <v>300</v>
-      </c>
-      <c r="K90" s="21" t="s">
+      <c r="G90" t="s">
+        <v>633</v>
+      </c>
+      <c r="L90" s="21" t="s">
         <v>380</v>
       </c>
-      <c r="L90" s="21">
+      <c r="M90" s="21">
         <v>5</v>
       </c>
-      <c r="M90" s="21" t="s">
+      <c r="N90" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="N90" s="21" t="s">
-        <v>387</v>
-      </c>
-      <c r="O90" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O90" s="21" t="s">
+        <v>386</v>
+      </c>
+      <c r="P90" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>20</v>
       </c>
       <c r="E91" t="s">
         <v>318</v>
       </c>
-      <c r="F91" t="s">
-        <v>300</v>
-      </c>
-      <c r="K91" s="21" t="s">
+      <c r="G91" t="s">
+        <v>633</v>
+      </c>
+      <c r="L91" s="21" t="s">
         <v>380</v>
       </c>
-      <c r="L91" s="21">
+      <c r="M91" s="21">
         <v>5</v>
       </c>
-      <c r="M91" s="21" t="s">
+      <c r="N91" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="N91" s="21" t="s">
-        <v>387</v>
-      </c>
-      <c r="O91" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O91" s="21" t="s">
+        <v>386</v>
+      </c>
+      <c r="P91" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>20</v>
       </c>
-      <c r="F92" t="s">
-        <v>300</v>
-      </c>
-      <c r="K92" s="21" t="s">
+      <c r="G92" t="s">
+        <v>633</v>
+      </c>
+      <c r="L92" s="21" t="s">
         <v>380</v>
       </c>
-      <c r="L92" s="21">
+      <c r="M92" s="21">
         <f>0.9*5+0.1*15</f>
         <v>6</v>
       </c>
-      <c r="M92" s="21" t="s">
+      <c r="N92" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="N92" s="21" t="s">
-        <v>388</v>
-      </c>
-      <c r="O92" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O92" s="21" t="s">
+        <v>387</v>
+      </c>
+      <c r="P92" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>383</v>
-      </c>
-      <c r="F93" t="s">
-        <v>300</v>
-      </c>
-      <c r="K93" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="G93" t="s">
+        <v>633</v>
+      </c>
+      <c r="L93" s="21" t="s">
         <v>380</v>
       </c>
-      <c r="L93" s="21">
+      <c r="M93" s="21">
         <v>15</v>
       </c>
-      <c r="M93" s="21" t="s">
+      <c r="N93" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="N93" s="21"/>
-      <c r="O93" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O93" s="21"/>
+      <c r="P93" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>378</v>
       </c>
-      <c r="F94" t="s">
-        <v>300</v>
-      </c>
-      <c r="K94" s="21" t="s">
+      <c r="G94" t="s">
+        <v>633</v>
+      </c>
+      <c r="L94" s="21" t="s">
         <v>380</v>
       </c>
-      <c r="L94" s="21">
+      <c r="M94" s="21">
         <v>15</v>
       </c>
-      <c r="M94" s="21" t="s">
+      <c r="N94" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="N94" s="21"/>
-      <c r="O94" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A95" s="22" t="str">
-        <f>A86</f>
+      <c r="O94" s="21"/>
+      <c r="P94" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A95" s="22"/>
+      <c r="B95" s="22"/>
+      <c r="E95" s="22"/>
+      <c r="G95" t="s">
+        <v>302</v>
+      </c>
+      <c r="L95" s="21" t="s">
+        <v>379</v>
+      </c>
+      <c r="M95" s="21">
+        <v>5</v>
+      </c>
+      <c r="N95" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="O95" s="21"/>
+      <c r="P95" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A96" s="22" t="str">
+        <f>A90</f>
         <v>cattle</v>
       </c>
-      <c r="B95" s="22" t="str">
-        <f>B86</f>
+      <c r="B96" s="22" t="str">
+        <f>B90</f>
         <v>dairy</v>
       </c>
-      <c r="E95" s="22" t="str">
-        <f>E86</f>
+      <c r="E96" s="22" t="str">
+        <f t="shared" ref="E96:E97" si="0">E90</f>
         <v>cows</v>
       </c>
-      <c r="F95" t="s">
-        <v>301</v>
-      </c>
-      <c r="K95" s="22" t="str">
-        <f>K86</f>
-        <v>storage_losses</v>
-      </c>
-      <c r="L95" s="22">
-        <f>L86</f>
-        <v>16.399999999999999</v>
-      </c>
-      <c r="M95" s="22" t="str">
-        <f>M86</f>
-        <v>%</v>
-      </c>
-      <c r="N95" s="22" t="str">
-        <f>N86</f>
-        <v>80% in silo</v>
-      </c>
-      <c r="O95" s="22" t="str">
-        <f>O86</f>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A96" s="22" t="str">
-        <f t="shared" ref="A96:A103" si="0">A87</f>
-        <v>cattle</v>
-      </c>
-      <c r="F96" t="s">
-        <v>301</v>
-      </c>
-      <c r="K96" s="22" t="str">
-        <f t="shared" ref="K96:O103" si="1">K87</f>
-        <v>storage_losses</v>
-      </c>
-      <c r="L96" s="22">
+      <c r="G96" t="s">
+        <v>302</v>
+      </c>
+      <c r="L96" s="22" t="str">
+        <f t="shared" ref="L96:P100" si="1">L90</f>
+        <v>feeding_losses</v>
+      </c>
+      <c r="M96" s="22">
         <f t="shared" si="1"/>
-        <v>12.8</v>
-      </c>
-      <c r="M96" s="22" t="str">
+        <v>5</v>
+      </c>
+      <c r="N96" s="22" t="str">
         <f t="shared" si="1"/>
         <v>%</v>
       </c>
-      <c r="N96" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>60% in silo</v>
-      </c>
       <c r="O96" s="22" t="str">
         <f t="shared" si="1"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+        <v>No feeding on pasture</v>
+      </c>
+      <c r="P96" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>Cederberg &amp; Henriksson (2020)</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97" s="22" t="str">
+        <f t="shared" ref="A97:A100" si="2">A91</f>
+        <v>cattle</v>
+      </c>
+      <c r="E97" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>sheep</v>
-      </c>
-      <c r="F97" t="s">
-        <v>301</v>
-      </c>
-      <c r="K97" s="22" t="str">
+        <v>bulls</v>
+      </c>
+      <c r="G97" t="s">
+        <v>302</v>
+      </c>
+      <c r="L97" s="22" t="str">
         <f t="shared" si="1"/>
-        <v>storage_losses</v>
-      </c>
-      <c r="L97" s="22">
+        <v>feeding_losses</v>
+      </c>
+      <c r="M97" s="22">
         <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="M97" s="22" t="str">
+        <v>5</v>
+      </c>
+      <c r="N97" s="22" t="str">
         <f t="shared" si="1"/>
         <v>%</v>
       </c>
-      <c r="N97" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>0% in silo</v>
-      </c>
       <c r="O97" s="22" t="str">
         <f t="shared" si="1"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+        <v>No feeding on pasture</v>
+      </c>
+      <c r="P97" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>Cederberg &amp; Henriksson (2020)</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v>horses</v>
-      </c>
-      <c r="F98" t="s">
-        <v>301</v>
-      </c>
-      <c r="K98" s="22" t="str">
+        <f t="shared" si="2"/>
+        <v>cattle</v>
+      </c>
+      <c r="G98" t="s">
+        <v>302</v>
+      </c>
+      <c r="L98" s="22" t="str">
         <f t="shared" si="1"/>
-        <v>storage_losses</v>
-      </c>
-      <c r="L98" s="22">
+        <v>feeding_losses</v>
+      </c>
+      <c r="M98" s="22">
         <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="M98" s="22" t="str">
+        <v>6</v>
+      </c>
+      <c r="N98" s="22" t="str">
         <f t="shared" si="1"/>
         <v>%</v>
       </c>
-      <c r="N98" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>0% in silo</v>
-      </c>
       <c r="O98" s="22" t="str">
         <f t="shared" si="1"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+        <v>10% feeding on pasture</v>
+      </c>
+      <c r="P98" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>Cederberg &amp; Henriksson (2020)</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A99" s="22" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
+        <v>sheep</v>
+      </c>
+      <c r="G99" t="s">
+        <v>302</v>
+      </c>
+      <c r="L99" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="M99" s="22">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="N99" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>%</v>
+      </c>
+      <c r="O99" s="22"/>
+      <c r="P99" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>Cederberg &amp; Henriksson (2020)</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A100" s="22" t="str">
+        <f t="shared" si="2"/>
+        <v>horses</v>
+      </c>
+      <c r="G100" t="s">
+        <v>302</v>
+      </c>
+      <c r="L100" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="M100" s="22">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="N100" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>%</v>
+      </c>
+      <c r="O100" s="22"/>
+      <c r="P100" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>Cederberg &amp; Henriksson (2020)</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G101" t="s">
+        <v>634</v>
+      </c>
+      <c r="L101" s="21" t="s">
+        <v>379</v>
+      </c>
+      <c r="M101" s="21">
+        <v>5</v>
+      </c>
+      <c r="N101" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="O101" s="21"/>
+      <c r="P101" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A102" s="22" t="str">
+        <f>A90</f>
         <v>cattle</v>
       </c>
-      <c r="B99" s="22" t="str">
+      <c r="B102" s="22" t="str">
         <f>B90</f>
         <v>dairy</v>
       </c>
-      <c r="E99" s="22" t="str">
-        <f>E90</f>
+      <c r="E102" s="22" t="str">
+        <f t="shared" ref="E102:E103" si="3">E90</f>
         <v>cows</v>
       </c>
-      <c r="F99" t="s">
-        <v>301</v>
-      </c>
-      <c r="K99" s="22" t="str">
-        <f t="shared" si="1"/>
+      <c r="G102" t="s">
+        <v>634</v>
+      </c>
+      <c r="L102" s="22" t="str">
+        <f t="shared" ref="L102:P106" si="4">L90</f>
         <v>feeding_losses</v>
       </c>
-      <c r="L99" s="22">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="M99" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>%</v>
-      </c>
-      <c r="N99" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>No feeding on pasture</v>
-      </c>
-      <c r="O99" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A100" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v>cattle</v>
-      </c>
-      <c r="E100" s="22" t="str">
-        <f>E91</f>
-        <v>bulls</v>
-      </c>
-      <c r="F100" t="s">
-        <v>301</v>
-      </c>
-      <c r="K100" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="L100" s="22">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="M100" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>%</v>
-      </c>
-      <c r="N100" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>No feeding on pasture</v>
-      </c>
-      <c r="O100" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A101" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v>cattle</v>
-      </c>
-      <c r="F101" t="s">
-        <v>301</v>
-      </c>
-      <c r="K101" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="L101" s="22">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="M101" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>%</v>
-      </c>
-      <c r="N101" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>10% feeding on pasture</v>
-      </c>
-      <c r="O101" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A102" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v>sheep</v>
-      </c>
-      <c r="F102" t="s">
-        <v>301</v>
-      </c>
-      <c r="K102" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="L102" s="22">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="M102" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>%</v>
-      </c>
-      <c r="N102" s="22"/>
-      <c r="O102" s="22" t="str">
-        <f t="shared" ref="O102:O103" si="2">O93</f>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A103" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v>horses</v>
-      </c>
-      <c r="F103" t="s">
-        <v>301</v>
-      </c>
-      <c r="K103" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="L103" s="22">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="M103" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>%</v>
-      </c>
-      <c r="N103" s="22"/>
-      <c r="O103" s="22" t="str">
-        <f t="shared" si="2"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A104" s="22"/>
-      <c r="B104" s="22"/>
-      <c r="E104" s="22"/>
-      <c r="F104" t="s">
-        <v>302</v>
-      </c>
-      <c r="K104" s="21" t="s">
-        <v>379</v>
-      </c>
-      <c r="L104" s="21">
-        <v>5</v>
-      </c>
-      <c r="M104" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="N104" s="21"/>
-      <c r="O104" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A105" s="22" t="str">
-        <f>A90</f>
-        <v>cattle</v>
-      </c>
-      <c r="B105" s="22" t="str">
-        <f>B90</f>
-        <v>dairy</v>
-      </c>
-      <c r="E105" s="22" t="str">
-        <f t="shared" ref="E105:E106" si="3">E90</f>
-        <v>cows</v>
-      </c>
-      <c r="F105" t="s">
-        <v>302</v>
-      </c>
-      <c r="K105" s="22" t="str">
-        <f t="shared" ref="K105:O109" si="4">K90</f>
-        <v>feeding_losses</v>
-      </c>
-      <c r="L105" s="22">
+      <c r="M102" s="22">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="M105" s="22" t="str">
+      <c r="N102" s="22" t="str">
         <f t="shared" si="4"/>
         <v>%</v>
       </c>
+      <c r="O102" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>No feeding on pasture</v>
+      </c>
+      <c r="P102" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>Cederberg &amp; Henriksson (2020)</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A103" s="22" t="str">
+        <f t="shared" ref="A103:A106" si="5">A91</f>
+        <v>cattle</v>
+      </c>
+      <c r="E103" s="22" t="str">
+        <f t="shared" si="3"/>
+        <v>bulls</v>
+      </c>
+      <c r="G103" t="s">
+        <v>634</v>
+      </c>
+      <c r="L103" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="M103" s="22">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="N103" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>%</v>
+      </c>
+      <c r="O103" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>No feeding on pasture</v>
+      </c>
+      <c r="P103" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>Cederberg &amp; Henriksson (2020)</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A104" s="22" t="str">
+        <f t="shared" si="5"/>
+        <v>cattle</v>
+      </c>
+      <c r="G104" t="s">
+        <v>634</v>
+      </c>
+      <c r="L104" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="M104" s="22">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="N104" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>%</v>
+      </c>
+      <c r="O104" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>10% feeding on pasture</v>
+      </c>
+      <c r="P104" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>Cederberg &amp; Henriksson (2020)</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A105" s="22" t="str">
+        <f t="shared" si="5"/>
+        <v>sheep</v>
+      </c>
+      <c r="G105" t="s">
+        <v>634</v>
+      </c>
+      <c r="L105" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>feeding_losses</v>
+      </c>
+      <c r="M105" s="22">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
       <c r="N105" s="22" t="str">
         <f t="shared" si="4"/>
-        <v>No feeding on pasture</v>
-      </c>
-      <c r="O105" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+        <v>%</v>
+      </c>
+      <c r="O105" s="21"/>
+      <c r="P105" s="22" t="str">
+        <f t="shared" ref="P105:P106" si="6">P93</f>
+        <v>Cederberg &amp; Henriksson (2020)</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A106" s="22" t="str">
-        <f t="shared" ref="A106:A109" si="5">A91</f>
-        <v>cattle</v>
-      </c>
-      <c r="E106" s="22" t="str">
-        <f t="shared" si="3"/>
-        <v>bulls</v>
-      </c>
-      <c r="F106" t="s">
-        <v>302</v>
-      </c>
-      <c r="K106" s="22" t="str">
+        <f t="shared" si="5"/>
+        <v>horses</v>
+      </c>
+      <c r="G106" t="s">
+        <v>634</v>
+      </c>
+      <c r="L106" s="22" t="str">
         <f t="shared" si="4"/>
         <v>feeding_losses</v>
       </c>
-      <c r="L106" s="22">
+      <c r="M106" s="22">
         <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="M106" s="22" t="str">
+        <v>15</v>
+      </c>
+      <c r="N106" s="22" t="str">
         <f t="shared" si="4"/>
         <v>%</v>
       </c>
-      <c r="N106" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>No feeding on pasture</v>
-      </c>
-      <c r="O106" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A107" s="22" t="str">
-        <f t="shared" si="5"/>
-        <v>cattle</v>
-      </c>
-      <c r="F107" t="s">
-        <v>302</v>
-      </c>
-      <c r="K107" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="L107" s="22">
-        <f t="shared" si="4"/>
-        <v>6</v>
-      </c>
-      <c r="M107" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>%</v>
-      </c>
-      <c r="N107" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>10% feeding on pasture</v>
-      </c>
-      <c r="O107" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A108" s="22" t="str">
-        <f t="shared" si="5"/>
-        <v>sheep</v>
-      </c>
-      <c r="F108" t="s">
-        <v>302</v>
-      </c>
-      <c r="K108" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="L108" s="22">
-        <f t="shared" si="4"/>
-        <v>15</v>
-      </c>
-      <c r="M108" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>%</v>
-      </c>
-      <c r="N108" s="22"/>
-      <c r="O108" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A109" s="22" t="str">
-        <f t="shared" si="5"/>
-        <v>horses</v>
-      </c>
-      <c r="F109" t="s">
-        <v>302</v>
-      </c>
-      <c r="K109" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="L109" s="22">
-        <f t="shared" si="4"/>
-        <v>15</v>
-      </c>
-      <c r="M109" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>%</v>
-      </c>
-      <c r="N109" s="22"/>
-      <c r="O109" s="22" t="str">
-        <f t="shared" si="4"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F110" t="s">
+      <c r="O106" s="21"/>
+      <c r="P106" s="22" t="str">
+        <f t="shared" si="6"/>
+        <v>Cederberg &amp; Henriksson (2020)</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M107" s="3"/>
+      <c r="O107" s="21"/>
+    </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A108" s="3"/>
+      <c r="G108" t="s">
+        <v>635</v>
+      </c>
+      <c r="L108" s="21" t="s">
+        <v>379</v>
+      </c>
+      <c r="M108" s="21"/>
+      <c r="O108" s="3" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A109" s="3"/>
+      <c r="G109" t="s">
+        <v>635</v>
+      </c>
+      <c r="L109" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="M109" s="21">
         <v>2</v>
       </c>
-      <c r="K110" s="21" t="s">
+      <c r="N109" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="O109" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="P109" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A110" s="3"/>
+      <c r="G110" t="s">
+        <v>636</v>
+      </c>
+      <c r="L110" s="21" t="s">
         <v>379</v>
       </c>
-      <c r="L110" s="21">
-        <v>5</v>
-      </c>
-      <c r="M110" s="21" t="s">
+      <c r="M110" s="21"/>
+      <c r="O110" s="3" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A111" s="3"/>
+      <c r="G111" t="s">
+        <v>636</v>
+      </c>
+      <c r="L111" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="M111" s="21">
+        <v>3</v>
+      </c>
+      <c r="N111" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="N110" s="21"/>
-      <c r="O110" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A111" s="22" t="str">
-        <f>A90</f>
-        <v>cattle</v>
-      </c>
-      <c r="B111" s="22" t="str">
-        <f>B90</f>
-        <v>dairy</v>
-      </c>
-      <c r="E111" s="22" t="str">
-        <f t="shared" ref="E111:E112" si="6">E90</f>
-        <v>cows</v>
-      </c>
-      <c r="F111" t="s">
-        <v>2</v>
-      </c>
-      <c r="K111" s="22" t="str">
-        <f t="shared" ref="K111:O115" si="7">K90</f>
-        <v>feeding_losses</v>
-      </c>
-      <c r="L111" s="22">
-        <f t="shared" si="7"/>
-        <v>5</v>
-      </c>
-      <c r="M111" s="22" t="str">
-        <f t="shared" si="7"/>
-        <v>%</v>
-      </c>
-      <c r="N111" s="22" t="str">
-        <f t="shared" si="7"/>
-        <v>No feeding on pasture</v>
-      </c>
-      <c r="O111" s="22" t="str">
-        <f t="shared" si="7"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A112" s="22" t="str">
-        <f t="shared" ref="A112:A115" si="8">A91</f>
-        <v>cattle</v>
-      </c>
-      <c r="E112" s="22" t="str">
-        <f t="shared" si="6"/>
-        <v>bulls</v>
-      </c>
-      <c r="F112" t="s">
-        <v>2</v>
-      </c>
-      <c r="K112" s="22" t="str">
-        <f t="shared" si="7"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="L112" s="22">
-        <f t="shared" si="7"/>
-        <v>5</v>
-      </c>
-      <c r="M112" s="22" t="str">
-        <f t="shared" si="7"/>
-        <v>%</v>
-      </c>
-      <c r="N112" s="22" t="str">
-        <f t="shared" si="7"/>
-        <v>No feeding on pasture</v>
-      </c>
-      <c r="O112" s="22" t="str">
-        <f t="shared" si="7"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A113" s="22" t="str">
-        <f t="shared" si="8"/>
-        <v>cattle</v>
-      </c>
-      <c r="F113" t="s">
-        <v>2</v>
-      </c>
-      <c r="K113" s="22" t="str">
-        <f t="shared" si="7"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="L113" s="22">
-        <f t="shared" si="7"/>
-        <v>6</v>
-      </c>
-      <c r="M113" s="22" t="str">
-        <f t="shared" si="7"/>
-        <v>%</v>
-      </c>
-      <c r="N113" s="22" t="str">
-        <f t="shared" si="7"/>
-        <v>10% feeding on pasture</v>
-      </c>
-      <c r="O113" s="22" t="str">
-        <f t="shared" si="7"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A114" s="22" t="str">
-        <f t="shared" si="8"/>
-        <v>sheep</v>
-      </c>
-      <c r="F114" t="s">
-        <v>2</v>
-      </c>
-      <c r="K114" s="22" t="str">
-        <f t="shared" si="7"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="L114" s="22">
-        <f t="shared" si="7"/>
-        <v>15</v>
-      </c>
-      <c r="M114" s="22" t="str">
-        <f t="shared" si="7"/>
-        <v>%</v>
-      </c>
-      <c r="N114" s="21"/>
-      <c r="O114" s="22" t="str">
-        <f t="shared" ref="O114:O115" si="9">O93</f>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A115" s="22" t="str">
-        <f t="shared" si="8"/>
-        <v>horses</v>
-      </c>
-      <c r="F115" t="s">
-        <v>2</v>
-      </c>
-      <c r="K115" s="22" t="str">
-        <f t="shared" si="7"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="L115" s="22">
-        <f t="shared" si="7"/>
-        <v>15</v>
-      </c>
-      <c r="M115" s="22" t="str">
-        <f t="shared" si="7"/>
-        <v>%</v>
-      </c>
-      <c r="N115" s="21"/>
-      <c r="O115" s="22" t="str">
-        <f t="shared" si="9"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F116" t="s">
-        <v>12</v>
-      </c>
-      <c r="K116" s="21" t="s">
-        <v>379</v>
-      </c>
-      <c r="L116" s="21">
-        <v>5</v>
-      </c>
-      <c r="M116" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="N116" s="21"/>
-      <c r="O116" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A117" s="22" t="str">
-        <f>A90</f>
-        <v>cattle</v>
-      </c>
-      <c r="B117" s="22" t="str">
-        <f>B90</f>
-        <v>dairy</v>
-      </c>
-      <c r="E117" s="22" t="str">
-        <f t="shared" ref="E117:E118" si="10">E90</f>
-        <v>cows</v>
-      </c>
-      <c r="F117" t="s">
-        <v>12</v>
-      </c>
-      <c r="K117" s="22" t="str">
-        <f t="shared" ref="K117:O121" si="11">K90</f>
-        <v>feeding_losses</v>
-      </c>
-      <c r="L117" s="22">
-        <f t="shared" si="11"/>
-        <v>5</v>
-      </c>
-      <c r="M117" s="22" t="str">
-        <f t="shared" si="11"/>
-        <v>%</v>
-      </c>
-      <c r="N117" s="22" t="str">
-        <f t="shared" si="11"/>
-        <v>No feeding on pasture</v>
-      </c>
-      <c r="O117" s="22" t="str">
-        <f t="shared" si="11"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A118" s="22" t="str">
-        <f t="shared" ref="A118:A121" si="12">A91</f>
-        <v>cattle</v>
-      </c>
-      <c r="E118" s="22" t="str">
-        <f t="shared" si="10"/>
-        <v>bulls</v>
-      </c>
-      <c r="F118" t="s">
-        <v>12</v>
-      </c>
-      <c r="K118" s="22" t="str">
-        <f t="shared" si="11"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="L118" s="22">
-        <f t="shared" si="11"/>
-        <v>5</v>
-      </c>
-      <c r="M118" s="22" t="str">
-        <f t="shared" si="11"/>
-        <v>%</v>
-      </c>
-      <c r="N118" s="22" t="str">
-        <f t="shared" si="11"/>
-        <v>No feeding on pasture</v>
-      </c>
-      <c r="O118" s="22" t="str">
-        <f t="shared" si="11"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A119" s="22" t="str">
-        <f t="shared" si="12"/>
-        <v>cattle</v>
-      </c>
-      <c r="F119" t="s">
-        <v>12</v>
-      </c>
-      <c r="K119" s="22" t="str">
-        <f t="shared" si="11"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="L119" s="22">
-        <f t="shared" si="11"/>
-        <v>6</v>
-      </c>
-      <c r="M119" s="22" t="str">
-        <f t="shared" si="11"/>
-        <v>%</v>
-      </c>
-      <c r="N119" s="22" t="str">
-        <f t="shared" si="11"/>
-        <v>10% feeding on pasture</v>
-      </c>
-      <c r="O119" s="22" t="str">
-        <f t="shared" si="11"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A120" s="22" t="str">
-        <f t="shared" si="12"/>
-        <v>sheep</v>
-      </c>
-      <c r="F120" t="s">
-        <v>12</v>
-      </c>
-      <c r="K120" s="22" t="str">
-        <f t="shared" si="11"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="L120" s="22">
-        <f t="shared" si="11"/>
-        <v>15</v>
-      </c>
-      <c r="M120" s="22" t="str">
-        <f t="shared" si="11"/>
-        <v>%</v>
-      </c>
-      <c r="N120" s="21"/>
-      <c r="O120" s="22" t="str">
-        <f t="shared" ref="O120:O121" si="13">O93</f>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A121" s="22" t="str">
-        <f t="shared" si="12"/>
-        <v>horses</v>
-      </c>
-      <c r="F121" t="s">
-        <v>12</v>
-      </c>
-      <c r="K121" s="22" t="str">
-        <f t="shared" si="11"/>
-        <v>feeding_losses</v>
-      </c>
-      <c r="L121" s="22">
-        <f t="shared" si="11"/>
-        <v>15</v>
-      </c>
-      <c r="M121" s="22" t="str">
-        <f t="shared" si="11"/>
-        <v>%</v>
-      </c>
-      <c r="N121" s="21"/>
-      <c r="O121" s="22" t="str">
-        <f t="shared" si="13"/>
-        <v>Cederberg &amp; Henriksson. 2020. Gräsmarkernas användning i jordbruket</v>
-      </c>
-    </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A122" s="22"/>
-      <c r="F122" t="s">
-        <v>29</v>
-      </c>
-      <c r="K122" s="21" t="s">
-        <v>379</v>
-      </c>
-      <c r="L122" s="21">
-        <v>0</v>
-      </c>
-      <c r="M122" t="s">
-        <v>24</v>
+      <c r="O111" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="P111" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M112" s="3"/>
+      <c r="O112" s="21"/>
+    </row>
+    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B113" s="1"/>
+      <c r="C113" s="1"/>
+      <c r="D113" s="1"/>
+      <c r="E113" s="2"/>
+      <c r="F113" s="2"/>
+      <c r="G113" s="2"/>
+      <c r="H113" s="2"/>
+      <c r="I113" s="2"/>
+      <c r="J113" s="2"/>
+      <c r="K113" s="2"/>
+      <c r="L113" s="2"/>
+      <c r="M113" s="2"/>
+      <c r="N113" s="2"/>
+      <c r="O113" s="2"/>
+      <c r="P113" s="2"/>
+    </row>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>20</v>
+      </c>
+      <c r="M114" s="21"/>
+      <c r="O114" s="21" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A115" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="B115" s="3"/>
+      <c r="C115" s="3"/>
+      <c r="D115" s="3"/>
+      <c r="E115" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="F115" s="3"/>
+      <c r="G115" s="3"/>
+      <c r="H115" s="3"/>
+      <c r="I115" s="3"/>
+      <c r="J115" s="3"/>
+      <c r="K115" s="3"/>
+      <c r="L115" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="M115" s="3">
+        <v>4.5</v>
+      </c>
+      <c r="N115" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="O115" s="3"/>
+    </row>
+    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A116" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="B116" s="3"/>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3"/>
+      <c r="E116" s="3"/>
+      <c r="F116" s="3"/>
+      <c r="G116" s="3"/>
+      <c r="H116" s="3"/>
+      <c r="I116" s="3"/>
+      <c r="J116" s="3"/>
+      <c r="K116" s="3"/>
+      <c r="L116" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="M116" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="N116" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="O116" s="3"/>
+    </row>
+    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>378</v>
+      </c>
+      <c r="L117" t="s">
+        <v>489</v>
+      </c>
+      <c r="M117" s="21">
+        <v>18</v>
+      </c>
+      <c r="N117" t="s">
+        <v>490</v>
+      </c>
+      <c r="O117" s="3"/>
+      <c r="P117" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>21</v>
+      </c>
+      <c r="L118" t="s">
+        <v>489</v>
+      </c>
+      <c r="M118" s="21">
+        <v>1.5</v>
+      </c>
+      <c r="N118" t="s">
+        <v>490</v>
+      </c>
+      <c r="O118" s="3"/>
+      <c r="P118" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>375</v>
+      </c>
+      <c r="L119" t="s">
+        <v>489</v>
+      </c>
+      <c r="M119" s="21">
+        <v>0</v>
+      </c>
+      <c r="N119" t="s">
+        <v>490</v>
+      </c>
+      <c r="O119" s="3"/>
+      <c r="P119" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M120" s="21"/>
+      <c r="O120" s="3"/>
+    </row>
+    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L121" t="s">
+        <v>603</v>
+      </c>
+      <c r="M121" s="21">
+        <v>1</v>
+      </c>
+      <c r="N121" s="21" t="s">
+        <v>604</v>
+      </c>
+      <c r="O121" s="21" t="s">
+        <v>605</v>
+      </c>
+      <c r="P121" s="21"/>
+    </row>
+    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>20</v>
+      </c>
+      <c r="L122" t="s">
+        <v>603</v>
+      </c>
+      <c r="M122" s="21">
+        <v>1</v>
       </c>
       <c r="N122" s="21" t="s">
-        <v>390</v>
-      </c>
-      <c r="O122" s="22"/>
-    </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+        <v>604</v>
+      </c>
+      <c r="O122" s="21"/>
+      <c r="P122" s="21"/>
+    </row>
+    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>20</v>
       </c>
-      <c r="F123" t="s">
-        <v>29</v>
-      </c>
-      <c r="K123" t="s">
-        <v>380</v>
-      </c>
-      <c r="L123" s="21">
-        <f>100-55</f>
-        <v>45</v>
-      </c>
-      <c r="M123" t="s">
-        <v>24</v>
+      <c r="B123" t="s">
+        <v>315</v>
+      </c>
+      <c r="E123" t="s">
+        <v>316</v>
+      </c>
+      <c r="L123" t="s">
+        <v>603</v>
+      </c>
+      <c r="M123" s="21">
+        <v>1</v>
       </c>
       <c r="N123" s="21" t="s">
-        <v>496</v>
-      </c>
-      <c r="O123" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+        <v>604</v>
+      </c>
+      <c r="O123" s="21"/>
+      <c r="P123" s="21"/>
+    </row>
+    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>378</v>
-      </c>
-      <c r="F124" t="s">
-        <v>29</v>
-      </c>
-      <c r="K124" t="s">
-        <v>380</v>
-      </c>
-      <c r="L124" s="21">
-        <f>100-50</f>
-        <v>50</v>
-      </c>
-      <c r="M124" t="s">
-        <v>24</v>
+        <v>20</v>
+      </c>
+      <c r="B124" t="s">
+        <v>315</v>
+      </c>
+      <c r="E124" t="s">
+        <v>318</v>
+      </c>
+      <c r="L124" t="s">
+        <v>603</v>
+      </c>
+      <c r="M124" s="21">
+        <v>1</v>
       </c>
       <c r="N124" s="21" t="s">
-        <v>497</v>
-      </c>
-      <c r="O124" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="L125" s="3"/>
-      <c r="N125" s="21"/>
-    </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A126" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="L126" s="3"/>
-      <c r="N126" s="21"/>
-    </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="L127" s="3"/>
-      <c r="N127" s="21"/>
-    </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A128" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="O124" s="21"/>
+      <c r="P124" s="21"/>
+    </row>
+    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>20</v>
+      </c>
+      <c r="B125" t="s">
         <v>606</v>
       </c>
-      <c r="B128" s="1"/>
-      <c r="C128" s="1"/>
-      <c r="D128" s="1"/>
-      <c r="E128" s="2"/>
-      <c r="F128" s="2"/>
-      <c r="G128" s="2"/>
-      <c r="H128" s="2"/>
-      <c r="I128" s="2"/>
-      <c r="J128" s="2"/>
-      <c r="K128" s="2"/>
-      <c r="L128" s="2"/>
-      <c r="M128" s="2"/>
-      <c r="N128" s="2"/>
-      <c r="O128" s="2"/>
-    </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>20</v>
-      </c>
-      <c r="L129" s="21"/>
-      <c r="N129" s="21" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A130" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="B130" s="3"/>
-      <c r="C130" s="3"/>
-      <c r="D130" s="3"/>
-      <c r="E130" s="3" t="s">
-        <v>489</v>
-      </c>
-      <c r="F130" s="3"/>
-      <c r="G130" s="3"/>
-      <c r="H130" s="3"/>
-      <c r="I130" s="3"/>
-      <c r="J130" s="3"/>
-      <c r="K130" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="L130" s="3">
-        <v>4.5</v>
-      </c>
-      <c r="M130" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="N130" s="3"/>
-    </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A131" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="B131" s="3"/>
-      <c r="C131" s="3"/>
-      <c r="D131" s="3"/>
-      <c r="E131" s="3"/>
-      <c r="F131" s="3"/>
-      <c r="G131" s="3"/>
-      <c r="H131" s="3"/>
-      <c r="I131" s="3"/>
-      <c r="J131" s="3"/>
-      <c r="K131" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="L131" s="3">
-        <v>6.5</v>
-      </c>
-      <c r="M131" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="N131" s="3"/>
-    </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>378</v>
-      </c>
-      <c r="K132" t="s">
-        <v>492</v>
-      </c>
-      <c r="L132" s="21">
+      <c r="E125" t="s">
+        <v>318</v>
+      </c>
+      <c r="L125" t="s">
+        <v>603</v>
+      </c>
+      <c r="M125" s="21">
+        <v>1</v>
+      </c>
+      <c r="N125" s="21" t="s">
+        <v>604</v>
+      </c>
+      <c r="O125" s="21"/>
+      <c r="P125" s="21"/>
+    </row>
+    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M126" s="3"/>
+      <c r="O126" s="3"/>
+    </row>
+    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B127" s="1"/>
+      <c r="C127" s="1"/>
+      <c r="D127" s="1"/>
+      <c r="E127" s="2"/>
+      <c r="F127" s="2"/>
+      <c r="G127" s="2"/>
+      <c r="H127" s="2"/>
+      <c r="I127" s="2"/>
+      <c r="J127" s="2"/>
+      <c r="K127" s="2"/>
+      <c r="L127" s="2"/>
+      <c r="M127" s="2"/>
+      <c r="N127" s="2"/>
+      <c r="O127" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="P127" s="2"/>
+    </row>
+    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K128" s="103" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="129" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="L129" t="s">
+        <v>376</v>
+      </c>
+      <c r="M129" s="21" t="s">
+        <v>615</v>
+      </c>
+      <c r="N129" t="s">
+        <v>599</v>
+      </c>
+      <c r="O129" s="3"/>
+    </row>
+    <row r="130" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="L130" t="s">
+        <v>477</v>
+      </c>
+      <c r="M130" s="21" t="s">
+        <v>615</v>
+      </c>
+      <c r="N130" t="s">
+        <v>598</v>
+      </c>
+      <c r="O130" s="3"/>
+    </row>
+    <row r="131" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="L131" s="37" t="s">
+        <v>609</v>
+      </c>
+      <c r="M131" s="21" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="132" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="L132" s="37" t="s">
+        <v>610</v>
+      </c>
+      <c r="M132" s="21" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="133" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="L133" s="37" t="s">
+        <v>611</v>
+      </c>
+      <c r="M133" s="21" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="134" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="L134" s="37" t="s">
+        <v>612</v>
+      </c>
+      <c r="M134" s="21" t="s">
+        <v>615</v>
+      </c>
+      <c r="O134" s="3"/>
+    </row>
+    <row r="135" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="K135" s="103" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="136" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="L136" t="s">
         <v>18</v>
       </c>
-      <c r="M132" t="s">
-        <v>493</v>
-      </c>
-      <c r="N132" s="3"/>
-      <c r="O132" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>21</v>
-      </c>
-      <c r="K133" t="s">
-        <v>492</v>
-      </c>
-      <c r="L133" s="21">
-        <v>1.5</v>
-      </c>
-      <c r="M133" t="s">
-        <v>493</v>
-      </c>
-      <c r="N133" s="3"/>
-      <c r="O133" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>375</v>
-      </c>
-      <c r="K134" t="s">
-        <v>492</v>
-      </c>
-      <c r="L134" s="21">
-        <v>0</v>
-      </c>
-      <c r="M134" t="s">
-        <v>493</v>
-      </c>
-      <c r="N134" s="3"/>
-      <c r="O134" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="L135" s="21"/>
-      <c r="N135" s="3"/>
-    </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="K136" t="s">
-        <v>608</v>
-      </c>
-      <c r="L136" s="21">
-        <v>1</v>
-      </c>
       <c r="M136" s="21" t="s">
-        <v>609</v>
-      </c>
-      <c r="N136" s="21" t="s">
-        <v>610</v>
-      </c>
-      <c r="O136" s="21"/>
-    </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>20</v>
-      </c>
-      <c r="K137" t="s">
-        <v>608</v>
-      </c>
-      <c r="L137" s="21">
-        <v>1</v>
+        <v>616</v>
+      </c>
+      <c r="N136" t="s">
+        <v>623</v>
+      </c>
+      <c r="O136" s="21" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="137" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="L137" t="s">
+        <v>589</v>
       </c>
       <c r="M137" s="21" t="s">
-        <v>609</v>
-      </c>
-      <c r="N137" s="21"/>
-      <c r="O137" s="21"/>
-    </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>20</v>
-      </c>
-      <c r="B138" t="s">
-        <v>315</v>
-      </c>
-      <c r="E138" t="s">
-        <v>316</v>
-      </c>
-      <c r="K138" t="s">
-        <v>608</v>
-      </c>
-      <c r="L138" s="21">
-        <v>1</v>
+        <v>616</v>
+      </c>
+      <c r="N137" t="s">
+        <v>597</v>
+      </c>
+      <c r="O137" s="3"/>
+    </row>
+    <row r="138" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="L138" t="s">
+        <v>478</v>
       </c>
       <c r="M138" s="21" t="s">
-        <v>609</v>
-      </c>
-      <c r="N138" s="21"/>
-      <c r="O138" s="21"/>
-    </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>20</v>
-      </c>
-      <c r="B139" t="s">
-        <v>315</v>
-      </c>
-      <c r="E139" t="s">
-        <v>318</v>
-      </c>
-      <c r="K139" t="s">
-        <v>608</v>
-      </c>
-      <c r="L139" s="21">
-        <v>1</v>
-      </c>
-      <c r="M139" s="21" t="s">
-        <v>609</v>
-      </c>
-      <c r="N139" s="21"/>
-      <c r="O139" s="21"/>
-    </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>20</v>
-      </c>
-      <c r="B140" t="s">
-        <v>611</v>
-      </c>
-      <c r="E140" t="s">
-        <v>318</v>
-      </c>
-      <c r="K140" t="s">
-        <v>608</v>
-      </c>
-      <c r="L140" s="21">
-        <v>1</v>
+        <v>616</v>
+      </c>
+      <c r="N138" t="s">
+        <v>479</v>
+      </c>
+      <c r="O138" s="21" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="139" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="K139" s="103" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="140" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="L140" t="s">
+        <v>18</v>
       </c>
       <c r="M140" s="21" t="s">
-        <v>609</v>
-      </c>
-      <c r="N140" s="21"/>
-      <c r="O140" s="21"/>
-    </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="L141" s="3"/>
-      <c r="N141" s="3"/>
-    </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A142" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B142" s="1"/>
-      <c r="C142" s="1"/>
-      <c r="D142" s="1"/>
-      <c r="E142" s="2"/>
-      <c r="F142" s="2"/>
-      <c r="G142" s="2"/>
-      <c r="H142" s="2"/>
-      <c r="I142" s="2"/>
-      <c r="J142" s="2"/>
-      <c r="K142" s="2"/>
-      <c r="L142" s="2"/>
-      <c r="M142" s="2"/>
-      <c r="N142" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="O142" s="2"/>
-    </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="J143" s="103" t="s">
+        <v>626</v>
+      </c>
+      <c r="N140" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="K144" t="s">
-        <v>376</v>
-      </c>
-      <c r="L144" s="21" t="s">
+      <c r="O140" s="21" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="141" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="L141" t="s">
+        <v>589</v>
+      </c>
+      <c r="M141" s="21" t="s">
+        <v>626</v>
+      </c>
+      <c r="N141" t="s">
+        <v>597</v>
+      </c>
+      <c r="O141" s="3"/>
+    </row>
+    <row r="142" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="K142" s="103" t="s">
         <v>620</v>
       </c>
-      <c r="M144" t="s">
-        <v>604</v>
-      </c>
-      <c r="N144" s="3"/>
-    </row>
-    <row r="145" spans="10:14" x14ac:dyDescent="0.25">
-      <c r="K145" t="s">
-        <v>480</v>
-      </c>
-      <c r="L145" s="21" t="s">
-        <v>620</v>
-      </c>
-      <c r="M145" t="s">
-        <v>603</v>
-      </c>
-      <c r="N145" s="3"/>
-    </row>
-    <row r="146" spans="10:14" x14ac:dyDescent="0.25">
-      <c r="K146" s="37" t="s">
+    </row>
+    <row r="143" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="L143" t="s">
+        <v>18</v>
+      </c>
+      <c r="M143" s="21" t="s">
+        <v>627</v>
+      </c>
+      <c r="N143" t="s">
+        <v>623</v>
+      </c>
+      <c r="O143" s="21" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="144" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="L144" t="s">
+        <v>589</v>
+      </c>
+      <c r="M144" s="21" t="s">
+        <v>627</v>
+      </c>
+      <c r="N144" t="s">
+        <v>597</v>
+      </c>
+      <c r="O144" s="3"/>
+    </row>
+    <row r="145" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="K145" s="103" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="146" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="L146" t="s">
+        <v>18</v>
+      </c>
+      <c r="M146" s="21" t="s">
+        <v>628</v>
+      </c>
+      <c r="N146" t="s">
+        <v>624</v>
+      </c>
+      <c r="O146" s="21" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="147" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="L147" t="s">
+        <v>589</v>
+      </c>
+      <c r="M147" s="21" t="s">
+        <v>628</v>
+      </c>
+      <c r="N147" t="s">
+        <v>597</v>
+      </c>
+      <c r="O147" s="3"/>
+    </row>
+    <row r="148" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="K148" s="103" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="149" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="L149" t="s">
         <v>614</v>
       </c>
-      <c r="L146" s="21" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="147" spans="10:14" x14ac:dyDescent="0.25">
-      <c r="K147" s="37" t="s">
-        <v>615</v>
-      </c>
-      <c r="L147" s="21" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="148" spans="10:14" x14ac:dyDescent="0.25">
-      <c r="K148" s="37" t="s">
-        <v>616</v>
-      </c>
-      <c r="L148" s="21" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="149" spans="10:14" x14ac:dyDescent="0.25">
-      <c r="K149" s="37" t="s">
-        <v>617</v>
-      </c>
-      <c r="L149" s="21" t="s">
-        <v>620</v>
-      </c>
-      <c r="N149" s="3"/>
-    </row>
-    <row r="150" spans="10:14" x14ac:dyDescent="0.25">
-      <c r="J150" s="103" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="151" spans="10:14" x14ac:dyDescent="0.25">
-      <c r="K151" t="s">
-        <v>18</v>
-      </c>
-      <c r="L151" s="21" t="s">
-        <v>621</v>
-      </c>
-      <c r="M151" t="s">
-        <v>628</v>
-      </c>
-      <c r="N151" s="21" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="152" spans="10:14" x14ac:dyDescent="0.25">
-      <c r="K152" t="s">
-        <v>594</v>
-      </c>
-      <c r="L152" s="21" t="s">
-        <v>621</v>
-      </c>
-      <c r="M152" t="s">
-        <v>602</v>
-      </c>
-      <c r="N152" s="3"/>
-    </row>
-    <row r="153" spans="10:14" x14ac:dyDescent="0.25">
-      <c r="K153" t="s">
-        <v>481</v>
-      </c>
-      <c r="L153" s="21" t="s">
-        <v>621</v>
-      </c>
-      <c r="M153" t="s">
-        <v>482</v>
-      </c>
-      <c r="N153" s="21" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="154" spans="10:14" x14ac:dyDescent="0.25">
-      <c r="J154" s="103" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="155" spans="10:14" x14ac:dyDescent="0.25">
-      <c r="K155" t="s">
-        <v>18</v>
-      </c>
-      <c r="L155" s="21" t="s">
-        <v>631</v>
-      </c>
-      <c r="M155" t="s">
-        <v>628</v>
-      </c>
-      <c r="N155" s="21" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="156" spans="10:14" x14ac:dyDescent="0.25">
-      <c r="K156" t="s">
-        <v>594</v>
-      </c>
-      <c r="L156" s="21" t="s">
-        <v>631</v>
-      </c>
-      <c r="M156" t="s">
-        <v>602</v>
-      </c>
-      <c r="N156" s="3"/>
-    </row>
-    <row r="157" spans="10:14" x14ac:dyDescent="0.25">
-      <c r="J157" s="103" t="s">
+      <c r="M149" s="21" t="s">
+        <v>629</v>
+      </c>
+      <c r="N149" t="s">
         <v>625</v>
       </c>
-    </row>
-    <row r="158" spans="10:14" x14ac:dyDescent="0.25">
-      <c r="K158" t="s">
-        <v>18</v>
-      </c>
-      <c r="L158" s="21" t="s">
-        <v>632</v>
-      </c>
-      <c r="M158" t="s">
-        <v>628</v>
-      </c>
-      <c r="N158" s="21" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="159" spans="10:14" x14ac:dyDescent="0.25">
-      <c r="K159" t="s">
-        <v>594</v>
-      </c>
-      <c r="L159" s="21" t="s">
-        <v>632</v>
-      </c>
-      <c r="M159" t="s">
-        <v>602</v>
-      </c>
-      <c r="N159" s="3"/>
-    </row>
-    <row r="160" spans="10:14" x14ac:dyDescent="0.25">
-      <c r="J160" s="103" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="161" spans="10:14" x14ac:dyDescent="0.25">
-      <c r="K161" t="s">
-        <v>18</v>
-      </c>
-      <c r="L161" s="21" t="s">
-        <v>633</v>
-      </c>
-      <c r="M161" t="s">
-        <v>629</v>
-      </c>
-      <c r="N161" s="21" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="162" spans="10:14" x14ac:dyDescent="0.25">
-      <c r="K162" t="s">
-        <v>594</v>
-      </c>
-      <c r="L162" s="21" t="s">
-        <v>633</v>
-      </c>
-      <c r="M162" t="s">
-        <v>602</v>
-      </c>
-      <c r="N162" s="3"/>
-    </row>
-    <row r="163" spans="10:14" x14ac:dyDescent="0.25">
-      <c r="J163" s="103" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="164" spans="10:14" x14ac:dyDescent="0.25">
-      <c r="K164" t="s">
-        <v>619</v>
-      </c>
-      <c r="L164" s="21" t="s">
-        <v>634</v>
-      </c>
-      <c r="M164" t="s">
-        <v>630</v>
-      </c>
-      <c r="N164" s="21"/>
+      <c r="O149" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5847,6 +5433,26 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>642</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:AS52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5859,7 +5465,7 @@
   <sheetData>
     <row r="1" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>114</v>
@@ -5883,7 +5489,7 @@
       <c r="G3" s="42"/>
       <c r="H3" s="42"/>
       <c r="K3" s="41" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="L3" s="42"/>
       <c r="M3" s="42"/>
@@ -5894,7 +5500,7 @@
       <c r="R3" s="42"/>
       <c r="S3" s="42"/>
       <c r="T3" s="56" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="U3" s="42">
         <f>1/6.25</f>
@@ -5914,7 +5520,7 @@
       <c r="AG3" s="42"/>
       <c r="AH3" s="42"/>
       <c r="AI3" s="56" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="AJ3" s="42">
         <f>1/6.25</f>
@@ -5942,7 +5548,7 @@
         <v>1</v>
       </c>
       <c r="M4" s="46" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="N4" s="46">
         <v>2</v>
@@ -5981,10 +5587,10 @@
         <v>1</v>
       </c>
       <c r="AB4" s="46" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="AC4" s="46" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="AD4" s="46">
         <v>2</v>
@@ -6030,22 +5636,22 @@
         <v>55</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E5" s="48" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="F5" s="48" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="G5" s="48" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="H5" s="49" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="I5" s="51" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="K5" s="45" t="s">
         <v>291</v>
@@ -6054,40 +5660,40 @@
         <v>55</v>
       </c>
       <c r="M5" s="48" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="N5" s="48" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="O5" s="48" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="P5" s="47" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="Q5" s="48" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="R5" s="48" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="S5" s="48" t="s">
         <v>278</v>
       </c>
       <c r="T5" s="49" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="U5" s="48" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="V5" s="48" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="W5" s="49" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="X5" s="77" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="Z5" s="45" t="s">
         <v>291</v>
@@ -6096,10 +5702,10 @@
         <v>55</v>
       </c>
       <c r="AB5" s="48" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="AC5" s="71" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="AD5" s="48" t="s">
         <v>117</v>
@@ -6108,31 +5714,31 @@
         <v>116</v>
       </c>
       <c r="AF5" s="47" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="AG5" s="48" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AH5" s="48" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="AI5" s="49" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="AJ5" s="48" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="AK5" s="48" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AL5" s="49" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="AM5" s="77" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="AN5" s="70" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="AO5" s="4"/>
       <c r="AP5" s="45" t="s">
@@ -6142,10 +5748,10 @@
         <v>55</v>
       </c>
       <c r="AR5" s="94" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="AS5" s="51" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="6" spans="2:45" x14ac:dyDescent="0.25">
@@ -6236,7 +5842,7 @@
       <c r="AL6" s="32"/>
       <c r="AM6" s="78"/>
       <c r="AO6" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP6" s="45"/>
       <c r="AQ6" s="96"/>
@@ -6330,7 +5936,7 @@
       <c r="AL7" s="32"/>
       <c r="AM7" s="78"/>
       <c r="AO7" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP7" s="45"/>
       <c r="AQ7" s="27"/>
@@ -6410,10 +6016,10 @@
         <v>2.35</v>
       </c>
       <c r="X8" s="79" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="Y8" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="Z8" s="45"/>
       <c r="AA8" s="27"/>
@@ -6430,7 +6036,7 @@
       <c r="AL8" s="35"/>
       <c r="AM8" s="78"/>
       <c r="AO8" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP8" s="45"/>
       <c r="AQ8" s="27"/>
@@ -6524,7 +6130,7 @@
       <c r="AL9" s="32"/>
       <c r="AM9" s="78"/>
       <c r="AO9" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP9" s="45"/>
       <c r="AQ9" s="27"/>
@@ -6602,10 +6208,10 @@
         <v>1.03</v>
       </c>
       <c r="X10" s="79" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="Y10" s="7" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="Z10" s="45"/>
       <c r="AA10" s="27"/>
@@ -6622,7 +6228,7 @@
       <c r="AL10" s="32"/>
       <c r="AM10" s="78"/>
       <c r="AO10" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP10" s="45"/>
       <c r="AQ10" s="27"/>
@@ -6716,7 +6322,7 @@
       <c r="AL11" s="32"/>
       <c r="AM11" s="78"/>
       <c r="AO11" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP11" s="45"/>
       <c r="AQ11" s="27"/>
@@ -6751,7 +6357,7 @@
         <v>0.52500000000000002</v>
       </c>
       <c r="I12" s="63" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="J12" s="62"/>
       <c r="K12" s="45">
@@ -6861,10 +6467,10 @@
       </c>
       <c r="AM12" s="78"/>
       <c r="AN12" s="75" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="AO12" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP12" s="45">
         <f>MATCH($B12,poultry!$A$3:$A$41,0)</f>
@@ -6908,7 +6514,7 @@
         <v>0.58000000000000007</v>
       </c>
       <c r="I13" s="63" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="J13" s="4"/>
       <c r="K13" s="45">
@@ -7018,10 +6624,10 @@
       </c>
       <c r="AM13" s="78"/>
       <c r="AN13" s="75" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="AO13" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP13" s="45">
         <f>MATCH($B13,poultry!$A$3:$A$41,0)</f>
@@ -7065,7 +6671,7 @@
         <v>0.54</v>
       </c>
       <c r="I14" s="63" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="J14" s="4"/>
       <c r="K14" s="45">
@@ -7175,10 +6781,10 @@
       </c>
       <c r="AM14" s="78"/>
       <c r="AN14" s="75" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="AO14" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP14" s="45">
         <f>MATCH($B14,poultry!$A$3:$A$41,0)</f>
@@ -7222,7 +6828,7 @@
         <v>0.58000000000000007</v>
       </c>
       <c r="I15" s="63" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="J15" s="4"/>
       <c r="K15" s="45">
@@ -7332,10 +6938,10 @@
       </c>
       <c r="AM15" s="78"/>
       <c r="AN15" s="75" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="AO15" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP15" s="45">
         <f>MATCH($B15,poultry!$A$3:$A$41,0)</f>
@@ -7379,7 +6985,7 @@
         <v>0.55499999999999994</v>
       </c>
       <c r="I16" s="63" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="J16" s="4"/>
       <c r="K16" s="45">
@@ -7488,7 +7094,7 @@
       <c r="AM16" s="78"/>
       <c r="AN16" s="74"/>
       <c r="AO16" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP16" s="45">
         <f>MATCH($B16,poultry!$A$3:$A$41,0)</f>
@@ -7532,7 +7138,7 @@
         <v>0.46500000000000002</v>
       </c>
       <c r="I17" s="63" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="J17" s="4"/>
       <c r="K17" s="45">
@@ -7642,10 +7248,10 @@
       </c>
       <c r="AM17" s="78"/>
       <c r="AN17" s="75" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="AO17" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP17" s="45">
         <f>MATCH($B17,poultry!$A$3:$A$41,0)</f>
@@ -7689,7 +7295,7 @@
         <v>1.155</v>
       </c>
       <c r="I18" s="63" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="J18" s="4"/>
       <c r="K18" s="45">
@@ -7798,10 +7404,10 @@
       </c>
       <c r="AM18" s="78"/>
       <c r="AN18" s="75" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="AO18" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP18" s="45">
         <f>MATCH($B18,poultry!$A$3:$A$41,0)</f>
@@ -7845,7 +7451,7 @@
         <v>1.375</v>
       </c>
       <c r="I19" s="63" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="J19" s="4"/>
       <c r="K19" s="45"/>
@@ -7895,7 +7501,7 @@
         <v>311</v>
       </c>
       <c r="Y19" s="7" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="Z19" s="45">
         <f>MATCH($B19,pigs!$A$3:$A$60,0)</f>
@@ -7953,7 +7559,7 @@
         <v>311</v>
       </c>
       <c r="AO19" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP19" s="45"/>
       <c r="AQ19" s="27"/>
@@ -7988,7 +7594,7 @@
         <v>0.90999999999999992</v>
       </c>
       <c r="I20" s="63" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="J20" s="4"/>
       <c r="K20" s="45">
@@ -8097,10 +7703,10 @@
       </c>
       <c r="AM20" s="78"/>
       <c r="AN20" s="75" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="AO20" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP20" s="45"/>
       <c r="AQ20" s="27"/>
@@ -8108,7 +7714,7 @@
         <v>16.8</v>
       </c>
       <c r="AS20" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
     </row>
     <row r="21" spans="2:45" x14ac:dyDescent="0.25">
@@ -8140,7 +7746,7 @@
         <v>0.89500000000000002</v>
       </c>
       <c r="I21" s="63" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="J21" s="4"/>
       <c r="K21" s="45">
@@ -8249,10 +7855,10 @@
       </c>
       <c r="AM21" s="78"/>
       <c r="AN21" s="75" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="AO21" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP21" s="45"/>
       <c r="AQ21" s="27"/>
@@ -8332,7 +7938,7 @@
         <v>312</v>
       </c>
       <c r="Y22" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="Z22" s="45">
         <f>MATCH($B22,pigs!$A$3:$A$60,0)</f>
@@ -8390,7 +7996,7 @@
         <v>312</v>
       </c>
       <c r="AO22" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP22" s="45">
         <f>MATCH($B22,poultry!$A$3:$A$41,0)</f>
@@ -8504,7 +8110,7 @@
       <c r="AM23" s="78"/>
       <c r="AN23" s="75"/>
       <c r="AO23" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP23" s="45"/>
       <c r="AQ23" s="27"/>
@@ -8609,7 +8215,7 @@
       <c r="AM24" s="78"/>
       <c r="AN24" s="75"/>
       <c r="AO24" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP24" s="45"/>
       <c r="AQ24" s="27"/>
@@ -8617,7 +8223,7 @@
         <v>16</v>
       </c>
       <c r="AS24" s="7" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
     </row>
     <row r="25" spans="2:45" x14ac:dyDescent="0.25">
@@ -8756,10 +8362,10 @@
       </c>
       <c r="AM25" s="78"/>
       <c r="AN25" s="75" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="AO25" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP25" s="45">
         <f>MATCH($B25,poultry!$A$3:$A$41,0)</f>
@@ -8848,10 +8454,10 @@
         <v>2.4300000000000002</v>
       </c>
       <c r="X26" s="79" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="Y26" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="Z26" s="45">
         <f>MATCH($B26,pigs!$A$3:$A$60,0)</f>
@@ -8906,10 +8512,10 @@
       </c>
       <c r="AM26" s="78"/>
       <c r="AN26" s="75" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="AO26" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP26" s="45"/>
       <c r="AQ26" s="27"/>
@@ -9051,10 +8657,10 @@
       </c>
       <c r="AM27" s="78"/>
       <c r="AN27" s="75" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="AO27" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP27" s="45">
         <f>MATCH($B27,poultry!$A$3:$A$41,0)</f>
@@ -9205,10 +8811,10 @@
       </c>
       <c r="AM28" s="78"/>
       <c r="AN28" s="75" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="AO28" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP28" s="45"/>
       <c r="AQ28" s="27"/>
@@ -9216,7 +8822,7 @@
         <v>8.6</v>
       </c>
       <c r="AS28" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
     </row>
     <row r="29" spans="2:45" x14ac:dyDescent="0.25">
@@ -9356,7 +8962,7 @@
       <c r="AM29" s="78"/>
       <c r="AN29" s="75"/>
       <c r="AO29" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP29" s="45"/>
       <c r="AQ29" s="27"/>
@@ -9438,7 +9044,7 @@
         <v>309</v>
       </c>
       <c r="Y30" s="7" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="Z30" s="45"/>
       <c r="AA30" s="27"/>
@@ -9456,7 +9062,7 @@
       <c r="AM30" s="78"/>
       <c r="AN30" s="75"/>
       <c r="AO30" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP30" s="45"/>
       <c r="AQ30" s="27"/>
@@ -9598,10 +9204,10 @@
       </c>
       <c r="AM31" s="78"/>
       <c r="AN31" s="75" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="AO31" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP31" s="45">
         <f>MATCH($B31,poultry!$A$3:$A$41,0)</f>
@@ -9690,10 +9296,10 @@
         <v>0.62</v>
       </c>
       <c r="X32" s="79" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="Y32" s="7" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="Z32" s="45">
         <f>MATCH($B32,pigs!$A$3:$A$60,0)</f>
@@ -9748,10 +9354,10 @@
       </c>
       <c r="AM32" s="78"/>
       <c r="AN32" s="75" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="AO32" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP32" s="45">
         <f>MATCH($B32,poultry!$A$3:$A$41,0)</f>
@@ -9768,7 +9374,7 @@
     </row>
     <row r="33" spans="2:44" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="C33" s="44">
         <f t="shared" ref="C33:C35" si="31">AVERAGE(AA33,L33)</f>
@@ -9870,7 +9476,7 @@
     </row>
     <row r="34" spans="2:44" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="C34" s="44">
         <f>AVERAGE(AA34,L34)</f>
@@ -9972,7 +9578,7 @@
     </row>
     <row r="35" spans="2:44" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="C35" s="44">
         <f t="shared" si="31"/>
@@ -10208,10 +9814,10 @@
       </c>
       <c r="AM36" s="78"/>
       <c r="AN36" s="75" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="AO36" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP36" s="45"/>
       <c r="AQ36" s="27"/>
@@ -10316,7 +9922,7 @@
       <c r="AM37" s="78"/>
       <c r="AN37" s="75"/>
       <c r="AO37" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP37" s="45"/>
       <c r="AQ37" s="27"/>
@@ -10449,13 +10055,13 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="AM38" s="79" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="AN38" s="75" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="AO38" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP38" s="45"/>
       <c r="AQ38" s="27"/>
@@ -10597,10 +10203,10 @@
       </c>
       <c r="AM39" s="79"/>
       <c r="AN39" s="75" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="AO39" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP39" s="45">
         <f>MATCH($B39,poultry!$A$3:$A$41,0)</f>
@@ -10751,10 +10357,10 @@
       </c>
       <c r="AM40" s="78"/>
       <c r="AN40" s="75" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="AO40" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP40" s="45"/>
       <c r="AQ40" s="27"/>
@@ -10896,10 +10502,10 @@
       </c>
       <c r="AM41" s="78"/>
       <c r="AN41" s="75" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="AO41" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP41" s="45"/>
       <c r="AQ41" s="27"/>
@@ -11043,7 +10649,7 @@
       <c r="AM42" s="78"/>
       <c r="AN42" s="75"/>
       <c r="AO42" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP42" s="45"/>
       <c r="AQ42" s="27"/>
@@ -11123,10 +10729,10 @@
         <v>2.1</v>
       </c>
       <c r="X43" s="79" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="Y43" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="Z43" s="45">
         <f>MATCH($B43,pigs!$A$3:$A$60,0)</f>
@@ -11181,10 +10787,10 @@
       </c>
       <c r="AM43" s="78"/>
       <c r="AN43" s="75" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="AO43" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP43" s="45"/>
       <c r="AQ43" s="27"/>
@@ -11326,10 +10932,10 @@
       </c>
       <c r="AM44" s="78"/>
       <c r="AN44" s="75" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="AO44" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP44" s="45">
         <f>MATCH($B44,poultry!$A$3:$A$41,0)</f>
@@ -11346,7 +10952,7 @@
     </row>
     <row r="45" spans="2:44" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="C45" s="44">
         <f t="shared" ref="C45" si="44">AVERAGE(AA45,L45)</f>
@@ -11519,10 +11125,10 @@
         <v>1.1900000000000002</v>
       </c>
       <c r="X46" s="79" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="Y46" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="Z46" s="45">
         <f>MATCH($B46,pigs!$A$3:$A$60,0)</f>
@@ -11578,10 +11184,10 @@
       </c>
       <c r="AM46" s="78"/>
       <c r="AN46" s="75" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="AO46" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AP46" s="45">
         <f>MATCH($B46,poultry!$A$3:$A$41,0)</f>
@@ -11680,7 +11286,7 @@
     </row>
     <row r="49" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D49" s="64" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E49" s="98"/>
       <c r="F49" s="65"/>
@@ -11692,7 +11298,7 @@
     </row>
     <row r="50" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D50" s="27" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="E50" s="37"/>
       <c r="F50" s="37"/>
@@ -11704,7 +11310,7 @@
     </row>
     <row r="51" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D51" s="67" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="E51" s="99"/>
       <c r="F51" s="37"/>
@@ -11716,7 +11322,7 @@
     </row>
     <row r="52" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D52" s="68" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="E52" s="100"/>
       <c r="F52" s="36"/>
@@ -11769,7 +11375,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AS43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11783,25 +11389,25 @@
   <sheetData>
     <row r="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="AD1" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="AJ1" s="4" t="s">
         <v>595</v>
       </c>
-      <c r="I1" s="4" t="s">
-        <v>596</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>598</v>
-      </c>
-      <c r="W1" s="4" t="s">
-        <v>597</v>
-      </c>
-      <c r="AD1" s="4" t="s">
-        <v>599</v>
-      </c>
-      <c r="AJ1" s="4" t="s">
-        <v>600</v>
-      </c>
       <c r="AP1" s="4" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
     </row>
     <row r="2" spans="1:45" x14ac:dyDescent="0.25">
@@ -11812,19 +11418,19 @@
         <v>376</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="D2" s="36" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="E2" s="36" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="F2" s="36" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="G2" s="36" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="H2" s="37"/>
       <c r="I2" s="36" t="s">
@@ -11837,13 +11443,13 @@
         <v>16</v>
       </c>
       <c r="L2" s="36" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="M2" s="36" t="s">
         <v>18</v>
       </c>
       <c r="N2" s="36" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="P2" s="36" t="s">
         <v>0</v>
@@ -11855,13 +11461,13 @@
         <v>16</v>
       </c>
       <c r="S2" s="36" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="T2" s="36" t="s">
         <v>18</v>
       </c>
       <c r="U2" s="36" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="W2" s="36" t="s">
         <v>0</v>
@@ -11873,13 +11479,13 @@
         <v>16</v>
       </c>
       <c r="Z2" s="36" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="AA2" s="36" t="s">
         <v>18</v>
       </c>
       <c r="AB2" s="36" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="AD2" s="36" t="s">
         <v>0</v>
@@ -11891,7 +11497,7 @@
         <v>16</v>
       </c>
       <c r="AG2" s="36" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="AH2" s="36" t="s">
         <v>18</v>
@@ -11906,7 +11512,7 @@
         <v>16</v>
       </c>
       <c r="AM2" s="36" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="AN2" s="36" t="s">
         <v>18</v>
@@ -11921,7 +11527,7 @@
         <v>16</v>
       </c>
       <c r="AS2" s="102" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
     </row>
     <row r="3" spans="1:45" x14ac:dyDescent="0.25">
@@ -11978,7 +11584,7 @@
         <v>ley silage, 1st cut</v>
       </c>
       <c r="Q3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S3" s="65">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A3,'feed pars'!$B$6:$B$47,0))</f>
@@ -12094,7 +11700,7 @@
         <v>ley silage, regrowth</v>
       </c>
       <c r="Q4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S4" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A4,'feed pars'!$B$6:$B$47,0))</f>
@@ -12210,7 +11816,7 @@
         <v>other silage</v>
       </c>
       <c r="Q5" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S5" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A5,'feed pars'!$B$6:$B$47,0))</f>
@@ -12326,7 +11932,7 @@
         <v>hay</v>
       </c>
       <c r="Q6" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S6" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A6,'feed pars'!$B$6:$B$47,0))</f>
@@ -12442,7 +12048,7 @@
         <v>maize silage</v>
       </c>
       <c r="Q7" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S7" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A7,'feed pars'!$B$6:$B$47,0))</f>
@@ -12558,7 +12164,7 @@
         <v>grazing</v>
       </c>
       <c r="Q8" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S8" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A8,'feed pars'!$B$6:$B$47,0))</f>
@@ -12674,7 +12280,7 @@
         <v>wheat</v>
       </c>
       <c r="Q9" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S9" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A9,'feed pars'!$B$6:$B$47,0))</f>
@@ -12804,7 +12410,7 @@
         <v>barley</v>
       </c>
       <c r="Q10" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S10" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A10,'feed pars'!$B$6:$B$47,0))</f>
@@ -12934,7 +12540,7 @@
         <v>oats</v>
       </c>
       <c r="Q11" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S11" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A11,'feed pars'!$B$6:$B$47,0))</f>
@@ -13064,7 +12670,7 @@
         <v>triticale</v>
       </c>
       <c r="Q12" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S12" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A12,'feed pars'!$B$6:$B$47,0))</f>
@@ -13194,7 +12800,7 @@
         <v>rye</v>
       </c>
       <c r="Q13" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S13" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A13,'feed pars'!$B$6:$B$47,0))</f>
@@ -13324,7 +12930,7 @@
         <v>maize</v>
       </c>
       <c r="Q14" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S14" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A14,'feed pars'!$B$6:$B$47,0))</f>
@@ -13454,7 +13060,7 @@
         <v>peas</v>
       </c>
       <c r="Q15" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S15" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A15,'feed pars'!$B$6:$B$47,0))</f>
@@ -13584,7 +13190,7 @@
         <v>broad beans</v>
       </c>
       <c r="Q16" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S16" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A16,'feed pars'!$B$6:$B$47,0))</f>
@@ -13711,7 +13317,7 @@
         <v>rapeseed</v>
       </c>
       <c r="Q17" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S17" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A17,'feed pars'!$B$6:$B$47,0))</f>
@@ -13841,7 +13447,7 @@
         <v>linseed</v>
       </c>
       <c r="Q18" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S18" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A18,'feed pars'!$B$6:$B$47,0))</f>
@@ -13968,7 +13574,7 @@
         <v>vegetable oils</v>
       </c>
       <c r="Q19" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S19" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A19,'feed pars'!$B$6:$B$47,0))</f>
@@ -14098,7 +13704,7 @@
         <v>straw</v>
       </c>
       <c r="Q20" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S20" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A20,'feed pars'!$B$6:$B$47,0))</f>
@@ -14216,7 +13822,7 @@
         <v>soybeans</v>
       </c>
       <c r="Q21" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S21" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A21,'feed pars'!$B$6:$B$47,0))</f>
@@ -14337,7 +13943,7 @@
         <v>soybean meal</v>
       </c>
       <c r="Q22" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S22" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A22,'feed pars'!$B$6:$B$47,0))</f>
@@ -14467,7 +14073,7 @@
         <v>soybean protein concentrate</v>
       </c>
       <c r="Q23" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S23" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A23,'feed pars'!$B$6:$B$47,0))</f>
@@ -14585,7 +14191,7 @@
         <v>rapeseed meal</v>
       </c>
       <c r="Q24" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S24" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A24,'feed pars'!$B$6:$B$47,0))</f>
@@ -14715,7 +14321,7 @@
         <v>sunflower seed meal</v>
       </c>
       <c r="Q25" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S25" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A25,'feed pars'!$B$6:$B$47,0))</f>
@@ -14845,7 +14451,7 @@
         <v>palm kernel expeller</v>
       </c>
       <c r="Q26" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S26" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A26,'feed pars'!$B$6:$B$47,0))</f>
@@ -14972,7 +14578,7 @@
         <v>luzern meal</v>
       </c>
       <c r="Q27" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S27" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A27,'feed pars'!$B$6:$B$47,0))</f>
@@ -15090,7 +14696,7 @@
         <v>wheat bran</v>
       </c>
       <c r="Q28" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S28" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A28,'feed pars'!$B$6:$B$47,0))</f>
@@ -15220,7 +14826,7 @@
         <v>wheat bran, fine</v>
       </c>
       <c r="Q29" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S29" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A29,'feed pars'!$B$6:$B$47,0))</f>
@@ -15350,7 +14956,7 @@
         <v>oat hulls</v>
       </c>
       <c r="Q30" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S30" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A30,'feed pars'!$B$6:$B$47,0))</f>
@@ -15468,7 +15074,7 @@
         <v>oat bran</v>
       </c>
       <c r="Q31" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S31" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A31,'feed pars'!$B$6:$B$47,0))</f>
@@ -15585,7 +15191,7 @@
         <v>rye bran</v>
       </c>
       <c r="Q32" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S32" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A32,'feed pars'!$B$6:$B$47,0))</f>
@@ -15673,7 +15279,7 @@
         <v>wheat distillers grain, dry</v>
       </c>
       <c r="Q33" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S33" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A33,'feed pars'!$B$6:$B$47,0))</f>
@@ -15791,7 +15397,7 @@
         <v>wheat distillers grain, wet</v>
       </c>
       <c r="Q34" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S34" s="37"/>
       <c r="T34" s="37"/>
@@ -15900,7 +15506,7 @@
         <v>barley brewers grain</v>
       </c>
       <c r="Q35" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S35" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A35,'feed pars'!$B$6:$B$47,0))</f>
@@ -16027,7 +15633,7 @@
         <v>maize gluten meal</v>
       </c>
       <c r="Q36" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S36" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A36,'feed pars'!$B$6:$B$47,0))</f>
@@ -16157,7 +15763,7 @@
         <v>sugar beet molasses</v>
       </c>
       <c r="Q37" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S37" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A37,'feed pars'!$B$6:$B$47,0))</f>
@@ -16284,7 +15890,7 @@
         <v>sugar beet pulp</v>
       </c>
       <c r="Q38" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S38" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A38,'feed pars'!$B$6:$B$47,0))</f>
@@ -16411,7 +16017,7 @@
         <v>whey</v>
       </c>
       <c r="Q39" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S39" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A39,'feed pars'!$B$6:$B$47,0))</f>
@@ -16538,7 +16144,7 @@
         <v>whey powder</v>
       </c>
       <c r="Q40" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S40" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A40,'feed pars'!$B$6:$B$47,0))</f>
@@ -16656,7 +16262,7 @@
         <v>potatoe protein</v>
       </c>
       <c r="Q41" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="S41" s="37">
         <f>INDEX('feed pars'!$O$6:$O$47,MATCH($A41,'feed pars'!$B$6:$B$47,0))</f>
@@ -16788,7 +16394,7 @@
         <v>fish meal</v>
       </c>
       <c r="Q42" s="37" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="R42" s="37"/>
       <c r="S42" s="37">
@@ -16916,7 +16522,7 @@
         <v>minerals</v>
       </c>
       <c r="Q43" s="36" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="R43" s="36"/>
       <c r="S43" s="36">
@@ -17001,7 +16607,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AO60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -24335,7 +23941,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AH120"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -26768,7 +26374,7 @@
     </row>
     <row r="29" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="B29" s="8">
         <v>27</v>
@@ -26954,7 +26560,7 @@
     </row>
     <row r="31" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B31" s="8">
         <v>29</v>
@@ -30115,7 +29721,7 @@
     </row>
     <row r="65" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="B65" s="8">
         <v>63</v>
@@ -31337,7 +30943,7 @@
     </row>
     <row r="78" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="B78" s="11">
         <v>76</v>
@@ -35125,7 +34731,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:AE61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -35152,52 +34758,52 @@
         <v>274</v>
       </c>
       <c r="G2" s="15" t="s">
+        <v>394</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>395</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>396</v>
+      </c>
+      <c r="J2" s="15" t="s">
         <v>397</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="K2" s="15" t="s">
         <v>398</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="L2" s="15" t="s">
         <v>399</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="M2" s="15" t="s">
         <v>400</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="N2" s="15" t="s">
         <v>401</v>
       </c>
-      <c r="L2" s="15" t="s">
+      <c r="O2" s="15" t="s">
         <v>402</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="P2" s="15" t="s">
         <v>403</v>
       </c>
-      <c r="N2" s="15" t="s">
+      <c r="Q2" s="15" t="s">
         <v>404</v>
       </c>
-      <c r="O2" s="15" t="s">
+      <c r="R2" s="15" t="s">
         <v>405</v>
       </c>
-      <c r="P2" s="15" t="s">
+      <c r="S2" s="15" t="s">
         <v>406</v>
       </c>
-      <c r="Q2" s="15" t="s">
+      <c r="T2" s="15" t="s">
         <v>407</v>
-      </c>
-      <c r="R2" s="15" t="s">
-        <v>408</v>
-      </c>
-      <c r="S2" s="15" t="s">
-        <v>409</v>
-      </c>
-      <c r="T2" s="15" t="s">
-        <v>410</v>
       </c>
       <c r="U2" s="15" t="s">
         <v>119</v>
       </c>
       <c r="V2" s="15" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="W2" s="15" t="s">
         <v>144</v>
@@ -35223,7 +34829,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="D3" s="10">
         <v>9.4</v>
@@ -35292,7 +34898,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D4" s="13">
         <v>9.4</v>
@@ -35361,7 +34967,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D5" s="10">
         <v>6.1</v>
@@ -35430,7 +35036,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D6" s="13">
         <v>9.4</v>
@@ -35499,7 +35105,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="D7" s="10">
         <v>10.5</v>
@@ -35568,7 +35174,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="D8" s="13">
         <v>11.1</v>
@@ -35637,7 +35243,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="D9" s="10">
         <v>11</v>
@@ -35711,7 +35317,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D10" s="13">
         <v>10.1</v>
@@ -35783,7 +35389,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D11" s="10">
         <v>9.5</v>
@@ -35851,7 +35457,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="D12" s="13">
         <v>10.5</v>
@@ -35927,7 +35533,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="D13" s="10">
         <v>10.8</v>
@@ -36001,7 +35607,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D14" s="13">
         <v>11.5</v>
@@ -36075,7 +35681,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="D15" s="10">
         <v>9.8000000000000007</v>
@@ -36162,7 +35768,7 @@
         <v>14</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D16" s="13">
         <v>9.8000000000000007</v>
@@ -36249,7 +35855,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="D17" s="10">
         <v>9.3000000000000007</v>
@@ -36334,7 +35940,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="D18" s="13">
         <v>9.3000000000000007</v>
@@ -36419,7 +36025,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D19" s="10">
         <v>10.199999999999999</v>
@@ -36504,7 +36110,7 @@
         <v>18</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="D20" s="13">
         <v>10.199999999999999</v>
@@ -36589,7 +36195,7 @@
         <v>19</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D21" s="10">
         <v>10.9</v>
@@ -36672,7 +36278,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D22" s="13">
         <v>11.7</v>
@@ -36753,7 +36359,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="D23" s="10">
         <v>8</v>
@@ -36832,7 +36438,7 @@
         <v>22</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="D24" s="13">
         <v>9.1999999999999993</v>
@@ -36915,7 +36521,7 @@
         <v>23</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D25" s="10">
         <v>10.1</v>
@@ -36998,7 +36604,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="D26" s="13">
         <v>10.3</v>
@@ -37081,7 +36687,7 @@
         <v>25</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D27" s="10">
         <v>10.3</v>
@@ -37164,7 +36770,7 @@
         <v>26</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D28" s="13">
         <v>10.1</v>
@@ -37245,7 +36851,7 @@
         <v>27</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D29" s="10">
         <v>10.199999999999999</v>
@@ -37326,7 +36932,7 @@
         <v>28</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="D30" s="13">
         <v>10.1</v>
@@ -37407,7 +37013,7 @@
         <v>29</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D31" s="10">
         <v>10.199999999999999</v>
@@ -37490,7 +37096,7 @@
         <v>30</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D32" s="13">
         <v>9.9</v>
@@ -37571,7 +37177,7 @@
         <v>31</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="D33" s="10">
         <v>9.1</v>
@@ -37652,7 +37258,7 @@
         <v>32</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D34" s="13">
         <v>9.3000000000000007</v>
@@ -37733,7 +37339,7 @@
         <v>33</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="D35" s="10">
         <v>9.1999999999999993</v>
@@ -37814,7 +37420,7 @@
         <v>34</v>
       </c>
       <c r="C36" s="24" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="D36" s="13">
         <v>9.4</v>
@@ -37887,7 +37493,7 @@
         <v>35</v>
       </c>
       <c r="C37" s="23" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D37" s="10">
         <v>10.199999999999999</v>
@@ -37974,7 +37580,7 @@
         <v>36</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="D38" s="13">
         <v>10.199999999999999</v>
@@ -38061,7 +37667,7 @@
         <v>37</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D39" s="10">
         <v>9.8000000000000007</v>
@@ -38146,7 +37752,7 @@
         <v>38</v>
       </c>
       <c r="C40" s="24" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D40" s="13">
         <v>9.8000000000000007</v>
@@ -38231,7 +37837,7 @@
         <v>39</v>
       </c>
       <c r="C41" s="23" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="D41" s="10">
         <v>10.7</v>
@@ -38316,7 +37922,7 @@
         <v>40</v>
       </c>
       <c r="C42" s="24" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="D42" s="13">
         <v>10.7</v>
@@ -38401,7 +38007,7 @@
         <v>41</v>
       </c>
       <c r="C43" s="23" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="D43" s="10">
         <v>9.9</v>
@@ -38486,7 +38092,7 @@
         <v>42</v>
       </c>
       <c r="C44" s="24" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="D44" s="13">
         <v>9.9</v>
@@ -38571,7 +38177,7 @@
         <v>43</v>
       </c>
       <c r="C45" s="23" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="D45" s="10">
         <v>9.5</v>
@@ -38656,7 +38262,7 @@
         <v>44</v>
       </c>
       <c r="C46" s="24" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D46" s="13">
         <v>9.3000000000000007</v>
@@ -38741,7 +38347,7 @@
         <v>45</v>
       </c>
       <c r="C47" s="23" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="D47" s="10">
         <v>10.4</v>
@@ -38826,7 +38432,7 @@
         <v>46</v>
       </c>
       <c r="C48" s="24" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D48" s="13">
         <v>10.4</v>
@@ -38911,7 +38517,7 @@
         <v>47</v>
       </c>
       <c r="C49" s="23" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="D49" s="10">
         <v>10.199999999999999</v>
@@ -38998,7 +38604,7 @@
         <v>48</v>
       </c>
       <c r="C50" s="24" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="D50" s="13">
         <v>10.199999999999999</v>
@@ -39085,7 +38691,7 @@
         <v>49</v>
       </c>
       <c r="C51" s="23" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="D51" s="10">
         <v>9.5</v>
@@ -39170,7 +38776,7 @@
         <v>50</v>
       </c>
       <c r="C52" s="24" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D52" s="13">
         <v>9.5</v>
@@ -39255,7 +38861,7 @@
         <v>51</v>
       </c>
       <c r="C53" s="23" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="D53" s="10">
         <v>11</v>
@@ -39340,7 +38946,7 @@
         <v>52</v>
       </c>
       <c r="C54" s="24" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="D54" s="13">
         <v>11</v>
@@ -39425,7 +39031,7 @@
         <v>53</v>
       </c>
       <c r="C55" s="23" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D55" s="10">
         <v>10.6</v>
@@ -39510,7 +39116,7 @@
         <v>54</v>
       </c>
       <c r="C56" s="24" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="D56" s="13">
         <v>10.6</v>
@@ -39595,7 +39201,7 @@
         <v>55</v>
       </c>
       <c r="C57" s="23" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="D57" s="10">
         <v>10.199999999999999</v>
@@ -39680,7 +39286,7 @@
         <v>56</v>
       </c>
       <c r="C58" s="24" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D58" s="13">
         <v>10.199999999999999</v>
@@ -39765,7 +39371,7 @@
         <v>57</v>
       </c>
       <c r="C59" s="23" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="D59" s="10">
         <v>11</v>
@@ -39850,7 +39456,7 @@
         <v>58</v>
       </c>
       <c r="C60" s="24" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D60" s="13">
         <v>11</v>
@@ -39935,7 +39541,7 @@
         <v>59</v>
       </c>
       <c r="C61" s="23" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="D61" s="10">
         <v>10.5</v>
@@ -40018,7 +39624,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:N56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -40034,40 +39640,40 @@
         <v>118</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="D2" s="15" t="s">
         <v>323</v>
       </c>
       <c r="E2" s="15" t="s">
+        <v>497</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>500</v>
+      </c>
+      <c r="I2" s="15" t